--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="875">
   <si>
     <t>ID</t>
   </si>
@@ -2321,79 +2321,106 @@
     <t>4000000000</t>
   </si>
   <si>
+    <t>10116</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>地狱狼</t>
+  </si>
+  <si>
+    <t>100000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>4100000000</t>
+  </si>
+  <si>
+    <t>10117</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>地狱沙虫</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>2000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>4200000000</t>
+  </si>
+  <si>
+    <t>10118</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>地狱小鹰</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>40000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>4300000000</t>
+  </si>
+  <si>
+    <t>10119</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>地狱多角虫</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>800000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>4400000000</t>
+  </si>
+  <si>
+    <t>10120</t>
+  </si>
+  <si>
+    <t>1119</t>
+  </si>
+  <si>
+    <t>地狱蜈蚣</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>16000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>4500000000</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
-    <t>10116</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>地狱狼</t>
+    <t>10121</t>
+  </si>
+  <si>
+    <t>1120</t>
+  </si>
+  <si>
+    <t>地狱钳虫</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>4100000000</t>
-  </si>
-  <si>
-    <t>10117</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>地狱沙虫</t>
-  </si>
-  <si>
-    <t>4200000000</t>
-  </si>
-  <si>
-    <t>10118</t>
-  </si>
-  <si>
-    <t>1117</t>
-  </si>
-  <si>
-    <t>地狱小鹰</t>
-  </si>
-  <si>
-    <t>4300000000</t>
-  </si>
-  <si>
-    <t>10119</t>
-  </si>
-  <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>地狱多角虫</t>
-  </si>
-  <si>
-    <t>4400000000</t>
-  </si>
-  <si>
-    <t>10120</t>
-  </si>
-  <si>
-    <t>1119</t>
-  </si>
-  <si>
-    <t>地狱蜈蚣</t>
-  </si>
-  <si>
-    <t>4500000000</t>
-  </si>
-  <si>
-    <t>10121</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>地狱钳虫</t>
   </si>
   <si>
     <t>4600000000</t>
@@ -9828,23 +9855,23 @@
         <v>714</v>
       </c>
       <c r="J112" s="1">
-        <f t="shared" ref="J112:J145" si="26">J111+100</f>
+        <f>J111+100</f>
         <v>1500</v>
       </c>
       <c r="K112" s="1">
-        <f t="shared" ref="K112:K145" si="27">K111+100</f>
+        <f>K111+100</f>
         <v>1200</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" ref="L112:L145" si="28">L111+50</f>
+        <f t="shared" ref="L112:L145" si="26">L111+50</f>
         <v>950</v>
       </c>
       <c r="M112" s="1">
-        <f t="shared" ref="M112:M145" si="29">M111+50</f>
+        <f t="shared" ref="M112:M145" si="27">M111+50</f>
         <v>950</v>
       </c>
       <c r="N112" s="2">
-        <f t="shared" ref="N112:N145" si="30">N111+1</f>
+        <f t="shared" ref="N112:N145" si="28">N111+1</f>
         <v>31</v>
       </c>
       <c r="O112" s="4">
@@ -9888,23 +9915,23 @@
         <v>720</v>
       </c>
       <c r="J113" s="1">
+        <f>J112+100</f>
+        <v>1600</v>
+      </c>
+      <c r="K113" s="1">
+        <f>K112+100</f>
+        <v>1300</v>
+      </c>
+      <c r="L113" s="1">
         <f t="shared" si="26"/>
-        <v>1600</v>
-      </c>
-      <c r="K113" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M113" s="1">
         <f t="shared" si="27"/>
-        <v>1300</v>
-      </c>
-      <c r="L113" s="1">
+        <v>1000</v>
+      </c>
+      <c r="N113" s="2">
         <f t="shared" si="28"/>
-        <v>1000</v>
-      </c>
-      <c r="M113" s="1">
-        <f t="shared" si="29"/>
-        <v>1000</v>
-      </c>
-      <c r="N113" s="2">
-        <f t="shared" si="30"/>
         <v>32</v>
       </c>
       <c r="O113" s="4">
@@ -9948,23 +9975,23 @@
         <v>726</v>
       </c>
       <c r="J114" s="1">
+        <f>J113+100</f>
+        <v>1700</v>
+      </c>
+      <c r="K114" s="1">
+        <f>K113+100</f>
+        <v>1400</v>
+      </c>
+      <c r="L114" s="1">
         <f t="shared" si="26"/>
-        <v>1700</v>
-      </c>
-      <c r="K114" s="1">
+        <v>1050</v>
+      </c>
+      <c r="M114" s="1">
         <f t="shared" si="27"/>
-        <v>1400</v>
-      </c>
-      <c r="L114" s="1">
+        <v>1050</v>
+      </c>
+      <c r="N114" s="2">
         <f t="shared" si="28"/>
-        <v>1050</v>
-      </c>
-      <c r="M114" s="1">
-        <f t="shared" si="29"/>
-        <v>1050</v>
-      </c>
-      <c r="N114" s="2">
-        <f t="shared" si="30"/>
         <v>33</v>
       </c>
       <c r="O114" s="4">
@@ -10008,23 +10035,23 @@
         <v>732</v>
       </c>
       <c r="J115" s="1">
+        <f>J114+100</f>
+        <v>1800</v>
+      </c>
+      <c r="K115" s="1">
+        <f>K114+100</f>
+        <v>1500</v>
+      </c>
+      <c r="L115" s="1">
         <f t="shared" si="26"/>
-        <v>1800</v>
-      </c>
-      <c r="K115" s="1">
+        <v>1100</v>
+      </c>
+      <c r="M115" s="1">
         <f t="shared" si="27"/>
-        <v>1500</v>
-      </c>
-      <c r="L115" s="1">
+        <v>1100</v>
+      </c>
+      <c r="N115" s="2">
         <f t="shared" si="28"/>
-        <v>1100</v>
-      </c>
-      <c r="M115" s="1">
-        <f t="shared" si="29"/>
-        <v>1100</v>
-      </c>
-      <c r="N115" s="2">
-        <f t="shared" si="30"/>
         <v>34</v>
       </c>
       <c r="O115" s="4">
@@ -10068,23 +10095,23 @@
         <v>738</v>
       </c>
       <c r="J116" s="1">
+        <f t="shared" ref="J116:J145" si="29">J115+200</f>
+        <v>2000</v>
+      </c>
+      <c r="K116" s="1">
+        <f t="shared" ref="K116:K145" si="30">K115+300</f>
+        <v>1800</v>
+      </c>
+      <c r="L116" s="1">
         <f t="shared" si="26"/>
-        <v>1900</v>
-      </c>
-      <c r="K116" s="1">
+        <v>1150</v>
+      </c>
+      <c r="M116" s="1">
         <f t="shared" si="27"/>
-        <v>1600</v>
-      </c>
-      <c r="L116" s="1">
+        <v>1150</v>
+      </c>
+      <c r="N116" s="2">
         <f t="shared" si="28"/>
-        <v>1150</v>
-      </c>
-      <c r="M116" s="1">
-        <f t="shared" si="29"/>
-        <v>1150</v>
-      </c>
-      <c r="N116" s="2">
-        <f t="shared" si="30"/>
         <v>35</v>
       </c>
       <c r="O116" s="4">
@@ -10130,23 +10157,23 @@
         <v>744</v>
       </c>
       <c r="J117" s="1">
+        <f t="shared" si="29"/>
+        <v>2200</v>
+      </c>
+      <c r="K117" s="1">
+        <f t="shared" si="30"/>
+        <v>2100</v>
+      </c>
+      <c r="L117" s="1">
         <f t="shared" si="26"/>
-        <v>2000</v>
-      </c>
-      <c r="K117" s="1">
+        <v>1200</v>
+      </c>
+      <c r="M117" s="1">
         <f t="shared" si="27"/>
-        <v>1700</v>
-      </c>
-      <c r="L117" s="1">
+        <v>1200</v>
+      </c>
+      <c r="N117" s="2">
         <f t="shared" si="28"/>
-        <v>1200</v>
-      </c>
-      <c r="M117" s="1">
-        <f t="shared" si="29"/>
-        <v>1200</v>
-      </c>
-      <c r="N117" s="2">
-        <f t="shared" si="30"/>
         <v>36</v>
       </c>
       <c r="O117" s="4">
@@ -10192,23 +10219,23 @@
         <v>750</v>
       </c>
       <c r="J118" s="1">
+        <f t="shared" si="29"/>
+        <v>2400</v>
+      </c>
+      <c r="K118" s="1">
+        <f t="shared" si="30"/>
+        <v>2400</v>
+      </c>
+      <c r="L118" s="1">
         <f t="shared" si="26"/>
-        <v>2100</v>
-      </c>
-      <c r="K118" s="1">
+        <v>1250</v>
+      </c>
+      <c r="M118" s="1">
         <f t="shared" si="27"/>
-        <v>1800</v>
-      </c>
-      <c r="L118" s="1">
+        <v>1250</v>
+      </c>
+      <c r="N118" s="2">
         <f t="shared" si="28"/>
-        <v>1250</v>
-      </c>
-      <c r="M118" s="1">
-        <f t="shared" si="29"/>
-        <v>1250</v>
-      </c>
-      <c r="N118" s="2">
-        <f t="shared" si="30"/>
         <v>37</v>
       </c>
       <c r="O118" s="4">
@@ -10254,23 +10281,23 @@
         <v>756</v>
       </c>
       <c r="J119" s="1">
+        <f t="shared" si="29"/>
+        <v>2600</v>
+      </c>
+      <c r="K119" s="1">
+        <f t="shared" si="30"/>
+        <v>2700</v>
+      </c>
+      <c r="L119" s="1">
         <f t="shared" si="26"/>
-        <v>2200</v>
-      </c>
-      <c r="K119" s="1">
+        <v>1300</v>
+      </c>
+      <c r="M119" s="1">
         <f t="shared" si="27"/>
-        <v>1900</v>
-      </c>
-      <c r="L119" s="1">
+        <v>1300</v>
+      </c>
+      <c r="N119" s="2">
         <f t="shared" si="28"/>
-        <v>1300</v>
-      </c>
-      <c r="M119" s="1">
-        <f t="shared" si="29"/>
-        <v>1300</v>
-      </c>
-      <c r="N119" s="2">
-        <f t="shared" si="30"/>
         <v>38</v>
       </c>
       <c r="O119" s="4">
@@ -10316,23 +10343,23 @@
         <v>762</v>
       </c>
       <c r="J120" s="1">
+        <f t="shared" si="29"/>
+        <v>2800</v>
+      </c>
+      <c r="K120" s="1">
+        <f t="shared" si="30"/>
+        <v>3000</v>
+      </c>
+      <c r="L120" s="1">
         <f t="shared" si="26"/>
-        <v>2300</v>
-      </c>
-      <c r="K120" s="1">
+        <v>1350</v>
+      </c>
+      <c r="M120" s="1">
         <f t="shared" si="27"/>
-        <v>2000</v>
-      </c>
-      <c r="L120" s="1">
+        <v>1350</v>
+      </c>
+      <c r="N120" s="2">
         <f t="shared" si="28"/>
-        <v>1350</v>
-      </c>
-      <c r="M120" s="1">
-        <f t="shared" si="29"/>
-        <v>1350</v>
-      </c>
-      <c r="N120" s="2">
-        <f t="shared" si="30"/>
         <v>39</v>
       </c>
       <c r="O120" s="4">
@@ -10354,51 +10381,47 @@
       <c r="W120" s="2"/>
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>765</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>766</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="G121" s="14" t="s">
+        <v>708</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>708</v>
+      </c>
+      <c r="I121" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="G121" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="H121" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="I121" s="14" t="s">
-        <v>768</v>
-      </c>
       <c r="J121" s="1">
+        <f t="shared" si="29"/>
+        <v>3000</v>
+      </c>
+      <c r="K121" s="1">
+        <f t="shared" si="30"/>
+        <v>3300</v>
+      </c>
+      <c r="L121" s="1">
         <f t="shared" si="26"/>
-        <v>2400</v>
-      </c>
-      <c r="K121" s="1">
+        <v>1400</v>
+      </c>
+      <c r="M121" s="1">
         <f t="shared" si="27"/>
-        <v>2100</v>
-      </c>
-      <c r="L121" s="1">
+        <v>1400</v>
+      </c>
+      <c r="N121" s="2">
         <f t="shared" si="28"/>
-        <v>1400</v>
-      </c>
-      <c r="M121" s="1">
-        <f t="shared" si="29"/>
-        <v>1400</v>
-      </c>
-      <c r="N121" s="2">
-        <f t="shared" si="30"/>
         <v>40</v>
       </c>
       <c r="O121" s="4">
@@ -10408,10 +10431,10 @@
         <v>90</v>
       </c>
       <c r="Q121" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="R121" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="S121" s="2"/>
       <c r="T121" s="2"/>
@@ -10420,51 +10443,47 @@
       <c r="W121" s="2"/>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A122" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>764</v>
-      </c>
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
       <c r="C122" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>770</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>771</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G122" s="14" t="s">
         <v>772</v>
       </c>
-      <c r="G122" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="H122" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="I122" s="14" t="s">
-        <v>768</v>
+      <c r="H122" s="10" t="s">
+        <v>772</v>
+      </c>
+      <c r="I122" s="15" t="s">
+        <v>773</v>
       </c>
       <c r="J122" s="1">
+        <f t="shared" si="29"/>
+        <v>3200</v>
+      </c>
+      <c r="K122" s="1">
+        <f t="shared" si="30"/>
+        <v>3600</v>
+      </c>
+      <c r="L122" s="1">
         <f t="shared" si="26"/>
-        <v>2500</v>
-      </c>
-      <c r="K122" s="1">
+        <v>1450</v>
+      </c>
+      <c r="M122" s="1">
         <f t="shared" si="27"/>
-        <v>2200</v>
-      </c>
-      <c r="L122" s="1">
+        <v>1450</v>
+      </c>
+      <c r="N122" s="2">
         <f t="shared" si="28"/>
-        <v>1450</v>
-      </c>
-      <c r="M122" s="1">
-        <f t="shared" si="29"/>
-        <v>1450</v>
-      </c>
-      <c r="N122" s="2">
-        <f t="shared" si="30"/>
         <v>41</v>
       </c>
       <c r="O122" s="4">
@@ -10474,10 +10493,10 @@
         <v>90</v>
       </c>
       <c r="Q122" s="10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="R122" s="10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="S122" s="2"/>
       <c r="T122" s="2"/>
@@ -10486,51 +10505,47 @@
       <c r="W122" s="2"/>
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A123" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>764</v>
-      </c>
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
       <c r="C123" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="G123" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="H123" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="I123" s="14" t="s">
-        <v>768</v>
+        <v>778</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="I123" s="15" t="s">
+        <v>779</v>
       </c>
       <c r="J123" s="1">
+        <f t="shared" si="29"/>
+        <v>3400</v>
+      </c>
+      <c r="K123" s="1">
+        <f t="shared" si="30"/>
+        <v>3900</v>
+      </c>
+      <c r="L123" s="1">
         <f t="shared" si="26"/>
-        <v>2600</v>
-      </c>
-      <c r="K123" s="1">
+        <v>1500</v>
+      </c>
+      <c r="M123" s="1">
         <f t="shared" si="27"/>
-        <v>2300</v>
-      </c>
-      <c r="L123" s="1">
+        <v>1500</v>
+      </c>
+      <c r="N123" s="2">
         <f t="shared" si="28"/>
-        <v>1500</v>
-      </c>
-      <c r="M123" s="1">
-        <f t="shared" si="29"/>
-        <v>1500</v>
-      </c>
-      <c r="N123" s="2">
-        <f t="shared" si="30"/>
         <v>42</v>
       </c>
       <c r="O123" s="4">
@@ -10540,10 +10555,10 @@
         <v>90</v>
       </c>
       <c r="Q123" s="10" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="R123" s="10" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="S123" s="2"/>
       <c r="T123" s="2"/>
@@ -10552,51 +10567,47 @@
       <c r="W123" s="2"/>
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A124" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>764</v>
-      </c>
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
       <c r="C124" s="1" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="G124" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="H124" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="I124" s="14" t="s">
-        <v>768</v>
+        <v>784</v>
+      </c>
+      <c r="H124" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="I124" s="15" t="s">
+        <v>785</v>
       </c>
       <c r="J124" s="1">
+        <f t="shared" si="29"/>
+        <v>3600</v>
+      </c>
+      <c r="K124" s="1">
+        <f t="shared" si="30"/>
+        <v>4200</v>
+      </c>
+      <c r="L124" s="1">
         <f t="shared" si="26"/>
-        <v>2700</v>
-      </c>
-      <c r="K124" s="1">
+        <v>1550</v>
+      </c>
+      <c r="M124" s="1">
         <f t="shared" si="27"/>
-        <v>2400</v>
-      </c>
-      <c r="L124" s="1">
+        <v>1550</v>
+      </c>
+      <c r="N124" s="2">
         <f t="shared" si="28"/>
-        <v>1550</v>
-      </c>
-      <c r="M124" s="1">
-        <f t="shared" si="29"/>
-        <v>1550</v>
-      </c>
-      <c r="N124" s="2">
-        <f t="shared" si="30"/>
         <v>43</v>
       </c>
       <c r="O124" s="4">
@@ -10606,10 +10617,10 @@
         <v>90</v>
       </c>
       <c r="Q124" s="10" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="R124" s="10" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="S124" s="2"/>
       <c r="T124" s="2"/>
@@ -10618,51 +10629,47 @@
       <c r="W124" s="2"/>
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A125" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>764</v>
-      </c>
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
       <c r="C125" s="1" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="G125" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="H125" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="I125" s="14" t="s">
-        <v>768</v>
+        <v>790</v>
+      </c>
+      <c r="H125" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="I125" s="15" t="s">
+        <v>791</v>
       </c>
       <c r="J125" s="1">
+        <f t="shared" si="29"/>
+        <v>3800</v>
+      </c>
+      <c r="K125" s="1">
+        <f t="shared" si="30"/>
+        <v>4500</v>
+      </c>
+      <c r="L125" s="1">
         <f t="shared" si="26"/>
-        <v>2800</v>
-      </c>
-      <c r="K125" s="1">
+        <v>1600</v>
+      </c>
+      <c r="M125" s="1">
         <f t="shared" si="27"/>
-        <v>2500</v>
-      </c>
-      <c r="L125" s="1">
+        <v>1600</v>
+      </c>
+      <c r="N125" s="2">
         <f t="shared" si="28"/>
-        <v>1600</v>
-      </c>
-      <c r="M125" s="1">
-        <f t="shared" si="29"/>
-        <v>1600</v>
-      </c>
-      <c r="N125" s="2">
-        <f t="shared" si="30"/>
         <v>44</v>
       </c>
       <c r="O125" s="4">
@@ -10672,10 +10679,10 @@
         <v>90</v>
       </c>
       <c r="Q125" s="10" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="R125" s="10" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="S125" s="2"/>
       <c r="T125" s="2"/>
@@ -10685,50 +10692,50 @@
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A126" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="G126" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H126" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I126" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J126" s="1">
+        <f t="shared" si="29"/>
+        <v>4000</v>
+      </c>
+      <c r="K126" s="1">
+        <f t="shared" si="30"/>
+        <v>4800</v>
+      </c>
+      <c r="L126" s="1">
         <f t="shared" si="26"/>
-        <v>2900</v>
-      </c>
-      <c r="K126" s="1">
+        <v>1650</v>
+      </c>
+      <c r="M126" s="1">
         <f t="shared" si="27"/>
-        <v>2600</v>
-      </c>
-      <c r="L126" s="1">
+        <v>1650</v>
+      </c>
+      <c r="N126" s="2">
         <f t="shared" si="28"/>
-        <v>1650</v>
-      </c>
-      <c r="M126" s="1">
-        <f t="shared" si="29"/>
-        <v>1650</v>
-      </c>
-      <c r="N126" s="2">
-        <f t="shared" si="30"/>
         <v>45</v>
       </c>
       <c r="O126" s="4">
@@ -10738,10 +10745,10 @@
         <v>90</v>
       </c>
       <c r="Q126" s="10" t="s">
-        <v>789</v>
+        <v>798</v>
       </c>
       <c r="R126" s="10" t="s">
-        <v>789</v>
+        <v>798</v>
       </c>
       <c r="S126" s="2"/>
       <c r="T126" s="2"/>
@@ -10751,50 +10758,50 @@
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A127" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>791</v>
+        <v>800</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>792</v>
+        <v>801</v>
       </c>
       <c r="G127" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H127" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I127" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J127" s="1">
+        <f t="shared" si="29"/>
+        <v>4200</v>
+      </c>
+      <c r="K127" s="1">
+        <f t="shared" si="30"/>
+        <v>5100</v>
+      </c>
+      <c r="L127" s="1">
         <f t="shared" si="26"/>
-        <v>3000</v>
-      </c>
-      <c r="K127" s="1">
+        <v>1700</v>
+      </c>
+      <c r="M127" s="1">
         <f t="shared" si="27"/>
-        <v>2700</v>
-      </c>
-      <c r="L127" s="1">
+        <v>1700</v>
+      </c>
+      <c r="N127" s="2">
         <f t="shared" si="28"/>
-        <v>1700</v>
-      </c>
-      <c r="M127" s="1">
-        <f t="shared" si="29"/>
-        <v>1700</v>
-      </c>
-      <c r="N127" s="2">
-        <f t="shared" si="30"/>
         <v>46</v>
       </c>
       <c r="O127" s="4">
@@ -10804,10 +10811,10 @@
         <v>90</v>
       </c>
       <c r="Q127" s="10" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="R127" s="10" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="S127" s="2"/>
       <c r="T127" s="2"/>
@@ -10817,50 +10824,50 @@
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A128" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>796</v>
+        <v>805</v>
       </c>
       <c r="G128" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H128" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I128" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J128" s="1">
+        <f t="shared" si="29"/>
+        <v>4400</v>
+      </c>
+      <c r="K128" s="1">
+        <f t="shared" si="30"/>
+        <v>5400</v>
+      </c>
+      <c r="L128" s="1">
         <f t="shared" si="26"/>
-        <v>3100</v>
-      </c>
-      <c r="K128" s="1">
+        <v>1750</v>
+      </c>
+      <c r="M128" s="1">
         <f t="shared" si="27"/>
-        <v>2800</v>
-      </c>
-      <c r="L128" s="1">
+        <v>1750</v>
+      </c>
+      <c r="N128" s="2">
         <f t="shared" si="28"/>
-        <v>1750</v>
-      </c>
-      <c r="M128" s="1">
-        <f t="shared" si="29"/>
-        <v>1750</v>
-      </c>
-      <c r="N128" s="2">
-        <f t="shared" si="30"/>
         <v>47</v>
       </c>
       <c r="O128" s="4">
@@ -10870,10 +10877,10 @@
         <v>90</v>
       </c>
       <c r="Q128" s="10" t="s">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="R128" s="10" t="s">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="S128" s="2"/>
       <c r="T128" s="2"/>
@@ -10883,50 +10890,50 @@
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A129" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>798</v>
+        <v>807</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>799</v>
+        <v>808</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="G129" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H129" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I129" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J129" s="1">
+        <f t="shared" si="29"/>
+        <v>4600</v>
+      </c>
+      <c r="K129" s="1">
+        <f t="shared" si="30"/>
+        <v>5700</v>
+      </c>
+      <c r="L129" s="1">
         <f t="shared" si="26"/>
-        <v>3200</v>
-      </c>
-      <c r="K129" s="1">
+        <v>1800</v>
+      </c>
+      <c r="M129" s="1">
         <f t="shared" si="27"/>
-        <v>2900</v>
-      </c>
-      <c r="L129" s="1">
+        <v>1800</v>
+      </c>
+      <c r="N129" s="2">
         <f t="shared" si="28"/>
-        <v>1800</v>
-      </c>
-      <c r="M129" s="1">
-        <f t="shared" si="29"/>
-        <v>1800</v>
-      </c>
-      <c r="N129" s="2">
-        <f t="shared" si="30"/>
         <v>48</v>
       </c>
       <c r="O129" s="4">
@@ -10936,10 +10943,10 @@
         <v>90</v>
       </c>
       <c r="Q129" s="10" t="s">
-        <v>801</v>
+        <v>810</v>
       </c>
       <c r="R129" s="10" t="s">
-        <v>801</v>
+        <v>810</v>
       </c>
       <c r="S129" s="2"/>
       <c r="T129" s="2"/>
@@ -10949,50 +10956,50 @@
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A130" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>803</v>
+        <v>812</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="G130" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H130" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I130" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J130" s="1">
+        <f t="shared" si="29"/>
+        <v>4800</v>
+      </c>
+      <c r="K130" s="1">
+        <f t="shared" si="30"/>
+        <v>6000</v>
+      </c>
+      <c r="L130" s="1">
         <f t="shared" si="26"/>
-        <v>3300</v>
-      </c>
-      <c r="K130" s="1">
+        <v>1850</v>
+      </c>
+      <c r="M130" s="1">
         <f t="shared" si="27"/>
-        <v>3000</v>
-      </c>
-      <c r="L130" s="1">
+        <v>1850</v>
+      </c>
+      <c r="N130" s="2">
         <f t="shared" si="28"/>
-        <v>1850</v>
-      </c>
-      <c r="M130" s="1">
-        <f t="shared" si="29"/>
-        <v>1850</v>
-      </c>
-      <c r="N130" s="2">
-        <f t="shared" si="30"/>
         <v>49</v>
       </c>
       <c r="O130" s="4">
@@ -11002,10 +11009,10 @@
         <v>90</v>
       </c>
       <c r="Q130" s="10" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="R130" s="10" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="S130" s="2"/>
       <c r="T130" s="2"/>
@@ -11015,50 +11022,50 @@
     </row>
     <row r="131" customHeight="1" spans="1:18">
       <c r="A131" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>806</v>
+        <v>815</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>807</v>
+        <v>816</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="G131" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H131" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I131" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J131" s="1">
+        <f t="shared" si="29"/>
+        <v>5000</v>
+      </c>
+      <c r="K131" s="1">
+        <f t="shared" si="30"/>
+        <v>6300</v>
+      </c>
+      <c r="L131" s="1">
         <f t="shared" si="26"/>
-        <v>3400</v>
-      </c>
-      <c r="K131" s="1">
+        <v>1900</v>
+      </c>
+      <c r="M131" s="1">
         <f t="shared" si="27"/>
-        <v>3100</v>
-      </c>
-      <c r="L131" s="1">
+        <v>1900</v>
+      </c>
+      <c r="N131" s="2">
         <f t="shared" si="28"/>
-        <v>1900</v>
-      </c>
-      <c r="M131" s="1">
-        <f t="shared" si="29"/>
-        <v>1900</v>
-      </c>
-      <c r="N131" s="2">
-        <f t="shared" si="30"/>
         <v>50</v>
       </c>
       <c r="O131" s="4">
@@ -11068,58 +11075,58 @@
         <v>90</v>
       </c>
       <c r="Q131" s="10" t="s">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="R131" s="10" t="s">
-        <v>809</v>
+        <v>818</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="1:18">
       <c r="A132" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>812</v>
+        <v>821</v>
       </c>
       <c r="G132" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H132" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I132" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J132" s="1">
+        <f t="shared" si="29"/>
+        <v>5200</v>
+      </c>
+      <c r="K132" s="1">
+        <f t="shared" si="30"/>
+        <v>6600</v>
+      </c>
+      <c r="L132" s="1">
         <f t="shared" si="26"/>
-        <v>3500</v>
-      </c>
-      <c r="K132" s="1">
+        <v>1950</v>
+      </c>
+      <c r="M132" s="1">
         <f t="shared" si="27"/>
-        <v>3200</v>
-      </c>
-      <c r="L132" s="1">
+        <v>1950</v>
+      </c>
+      <c r="N132" s="2">
         <f t="shared" si="28"/>
-        <v>1950</v>
-      </c>
-      <c r="M132" s="1">
-        <f t="shared" si="29"/>
-        <v>1950</v>
-      </c>
-      <c r="N132" s="2">
-        <f t="shared" si="30"/>
         <v>51</v>
       </c>
       <c r="O132" s="4">
@@ -11129,58 +11136,58 @@
         <v>90</v>
       </c>
       <c r="Q132" s="10" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="R132" s="10" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:18">
       <c r="A133" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="G133" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H133" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I133" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J133" s="1">
+        <f t="shared" si="29"/>
+        <v>5400</v>
+      </c>
+      <c r="K133" s="1">
+        <f t="shared" si="30"/>
+        <v>6900</v>
+      </c>
+      <c r="L133" s="1">
         <f t="shared" si="26"/>
-        <v>3600</v>
-      </c>
-      <c r="K133" s="1">
+        <v>2000</v>
+      </c>
+      <c r="M133" s="1">
         <f t="shared" si="27"/>
-        <v>3300</v>
-      </c>
-      <c r="L133" s="1">
+        <v>2000</v>
+      </c>
+      <c r="N133" s="2">
         <f t="shared" si="28"/>
-        <v>2000</v>
-      </c>
-      <c r="M133" s="1">
-        <f t="shared" si="29"/>
-        <v>2000</v>
-      </c>
-      <c r="N133" s="2">
-        <f t="shared" si="30"/>
         <v>52</v>
       </c>
       <c r="O133" s="4">
@@ -11190,58 +11197,58 @@
         <v>90</v>
       </c>
       <c r="Q133" s="10" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="R133" s="10" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:18">
       <c r="A134" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>820</v>
+        <v>829</v>
       </c>
       <c r="G134" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H134" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I134" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J134" s="1">
+        <f t="shared" si="29"/>
+        <v>5600</v>
+      </c>
+      <c r="K134" s="1">
+        <f t="shared" si="30"/>
+        <v>7200</v>
+      </c>
+      <c r="L134" s="1">
         <f t="shared" si="26"/>
-        <v>3700</v>
-      </c>
-      <c r="K134" s="1">
+        <v>2050</v>
+      </c>
+      <c r="M134" s="1">
         <f t="shared" si="27"/>
-        <v>3400</v>
-      </c>
-      <c r="L134" s="1">
+        <v>2050</v>
+      </c>
+      <c r="N134" s="2">
         <f t="shared" si="28"/>
-        <v>2050</v>
-      </c>
-      <c r="M134" s="1">
-        <f t="shared" si="29"/>
-        <v>2050</v>
-      </c>
-      <c r="N134" s="2">
-        <f t="shared" si="30"/>
         <v>53</v>
       </c>
       <c r="O134" s="4">
@@ -11251,58 +11258,58 @@
         <v>90</v>
       </c>
       <c r="Q134" s="10" t="s">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="R134" s="10" t="s">
-        <v>821</v>
+        <v>830</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:18">
       <c r="A135" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>823</v>
+        <v>832</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="G135" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H135" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I135" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J135" s="1">
+        <f t="shared" si="29"/>
+        <v>5800</v>
+      </c>
+      <c r="K135" s="1">
+        <f t="shared" si="30"/>
+        <v>7500</v>
+      </c>
+      <c r="L135" s="1">
         <f t="shared" si="26"/>
-        <v>3800</v>
-      </c>
-      <c r="K135" s="1">
+        <v>2100</v>
+      </c>
+      <c r="M135" s="1">
         <f t="shared" si="27"/>
-        <v>3500</v>
-      </c>
-      <c r="L135" s="1">
+        <v>2100</v>
+      </c>
+      <c r="N135" s="2">
         <f t="shared" si="28"/>
-        <v>2100</v>
-      </c>
-      <c r="M135" s="1">
-        <f t="shared" si="29"/>
-        <v>2100</v>
-      </c>
-      <c r="N135" s="2">
-        <f t="shared" si="30"/>
         <v>54</v>
       </c>
       <c r="O135" s="4">
@@ -11312,58 +11319,58 @@
         <v>90</v>
       </c>
       <c r="Q135" s="10" t="s">
-        <v>825</v>
+        <v>834</v>
       </c>
       <c r="R135" s="10" t="s">
-        <v>825</v>
+        <v>834</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:18">
       <c r="A136" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>826</v>
+        <v>835</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>827</v>
+        <v>836</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>828</v>
+        <v>837</v>
       </c>
       <c r="G136" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H136" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I136" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J136" s="1">
+        <f t="shared" si="29"/>
+        <v>6000</v>
+      </c>
+      <c r="K136" s="1">
+        <f t="shared" si="30"/>
+        <v>7800</v>
+      </c>
+      <c r="L136" s="1">
         <f t="shared" si="26"/>
-        <v>3900</v>
-      </c>
-      <c r="K136" s="1">
+        <v>2150</v>
+      </c>
+      <c r="M136" s="1">
         <f t="shared" si="27"/>
-        <v>3600</v>
-      </c>
-      <c r="L136" s="1">
+        <v>2150</v>
+      </c>
+      <c r="N136" s="2">
         <f t="shared" si="28"/>
-        <v>2150</v>
-      </c>
-      <c r="M136" s="1">
-        <f t="shared" si="29"/>
-        <v>2150</v>
-      </c>
-      <c r="N136" s="2">
-        <f t="shared" si="30"/>
         <v>55</v>
       </c>
       <c r="O136" s="4">
@@ -11373,58 +11380,58 @@
         <v>90</v>
       </c>
       <c r="Q136" s="10" t="s">
-        <v>829</v>
+        <v>838</v>
       </c>
       <c r="R136" s="10" t="s">
-        <v>829</v>
+        <v>838</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="1:18">
       <c r="A137" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>830</v>
+        <v>839</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="G137" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H137" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I137" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J137" s="1">
+        <f t="shared" si="29"/>
+        <v>6200</v>
+      </c>
+      <c r="K137" s="1">
+        <f t="shared" si="30"/>
+        <v>8100</v>
+      </c>
+      <c r="L137" s="1">
         <f t="shared" si="26"/>
-        <v>4000</v>
-      </c>
-      <c r="K137" s="1">
+        <v>2200</v>
+      </c>
+      <c r="M137" s="1">
         <f t="shared" si="27"/>
-        <v>3700</v>
-      </c>
-      <c r="L137" s="1">
+        <v>2200</v>
+      </c>
+      <c r="N137" s="2">
         <f t="shared" si="28"/>
-        <v>2200</v>
-      </c>
-      <c r="M137" s="1">
-        <f t="shared" si="29"/>
-        <v>2200</v>
-      </c>
-      <c r="N137" s="2">
-        <f t="shared" si="30"/>
         <v>56</v>
       </c>
       <c r="O137" s="4">
@@ -11434,58 +11441,58 @@
         <v>90</v>
       </c>
       <c r="Q137" s="10" t="s">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="R137" s="10" t="s">
-        <v>833</v>
+        <v>842</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:18">
       <c r="A138" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>835</v>
+        <v>844</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H138" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I138" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J138" s="1">
+        <f t="shared" si="29"/>
+        <v>6400</v>
+      </c>
+      <c r="K138" s="1">
+        <f t="shared" si="30"/>
+        <v>8400</v>
+      </c>
+      <c r="L138" s="1">
         <f t="shared" si="26"/>
-        <v>4100</v>
-      </c>
-      <c r="K138" s="1">
+        <v>2250</v>
+      </c>
+      <c r="M138" s="1">
         <f t="shared" si="27"/>
-        <v>3800</v>
-      </c>
-      <c r="L138" s="1">
+        <v>2250</v>
+      </c>
+      <c r="N138" s="2">
         <f t="shared" si="28"/>
-        <v>2250</v>
-      </c>
-      <c r="M138" s="1">
-        <f t="shared" si="29"/>
-        <v>2250</v>
-      </c>
-      <c r="N138" s="2">
-        <f t="shared" si="30"/>
         <v>57</v>
       </c>
       <c r="O138" s="4">
@@ -11495,58 +11502,58 @@
         <v>90</v>
       </c>
       <c r="Q138" s="10" t="s">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="R138" s="10" t="s">
-        <v>837</v>
+        <v>846</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:18">
       <c r="A139" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>840</v>
+        <v>849</v>
       </c>
       <c r="G139" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H139" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I139" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J139" s="1">
+        <f t="shared" si="29"/>
+        <v>6600</v>
+      </c>
+      <c r="K139" s="1">
+        <f t="shared" si="30"/>
+        <v>8700</v>
+      </c>
+      <c r="L139" s="1">
         <f t="shared" si="26"/>
-        <v>4200</v>
-      </c>
-      <c r="K139" s="1">
+        <v>2300</v>
+      </c>
+      <c r="M139" s="1">
         <f t="shared" si="27"/>
-        <v>3900</v>
-      </c>
-      <c r="L139" s="1">
+        <v>2300</v>
+      </c>
+      <c r="N139" s="2">
         <f t="shared" si="28"/>
-        <v>2300</v>
-      </c>
-      <c r="M139" s="1">
-        <f t="shared" si="29"/>
-        <v>2300</v>
-      </c>
-      <c r="N139" s="2">
-        <f t="shared" si="30"/>
         <v>58</v>
       </c>
       <c r="O139" s="4">
@@ -11556,58 +11563,58 @@
         <v>90</v>
       </c>
       <c r="Q139" s="10" t="s">
-        <v>841</v>
+        <v>850</v>
       </c>
       <c r="R139" s="10" t="s">
-        <v>841</v>
+        <v>850</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:18">
       <c r="A140" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="G140" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H140" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I140" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J140" s="1">
+        <f t="shared" si="29"/>
+        <v>6800</v>
+      </c>
+      <c r="K140" s="1">
+        <f t="shared" si="30"/>
+        <v>9000</v>
+      </c>
+      <c r="L140" s="1">
         <f t="shared" si="26"/>
-        <v>4300</v>
-      </c>
-      <c r="K140" s="1">
+        <v>2350</v>
+      </c>
+      <c r="M140" s="1">
         <f t="shared" si="27"/>
-        <v>4000</v>
-      </c>
-      <c r="L140" s="1">
+        <v>2350</v>
+      </c>
+      <c r="N140" s="2">
         <f t="shared" si="28"/>
-        <v>2350</v>
-      </c>
-      <c r="M140" s="1">
-        <f t="shared" si="29"/>
-        <v>2350</v>
-      </c>
-      <c r="N140" s="2">
-        <f t="shared" si="30"/>
         <v>59</v>
       </c>
       <c r="O140" s="4">
@@ -11617,58 +11624,58 @@
         <v>90</v>
       </c>
       <c r="Q140" s="10" t="s">
-        <v>845</v>
+        <v>854</v>
       </c>
       <c r="R140" s="10" t="s">
-        <v>845</v>
+        <v>854</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A141" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>848</v>
+        <v>857</v>
       </c>
       <c r="G141" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H141" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I141" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J141" s="1">
+        <f t="shared" si="29"/>
+        <v>7000</v>
+      </c>
+      <c r="K141" s="1">
+        <f t="shared" si="30"/>
+        <v>9300</v>
+      </c>
+      <c r="L141" s="1">
         <f t="shared" si="26"/>
-        <v>4400</v>
-      </c>
-      <c r="K141" s="1">
+        <v>2400</v>
+      </c>
+      <c r="M141" s="1">
         <f t="shared" si="27"/>
-        <v>4100</v>
-      </c>
-      <c r="L141" s="1">
+        <v>2400</v>
+      </c>
+      <c r="N141" s="2">
         <f t="shared" si="28"/>
-        <v>2400</v>
-      </c>
-      <c r="M141" s="1">
-        <f t="shared" si="29"/>
-        <v>2400</v>
-      </c>
-      <c r="N141" s="2">
-        <f t="shared" si="30"/>
         <v>60</v>
       </c>
       <c r="O141" s="4">
@@ -11678,10 +11685,10 @@
         <v>90</v>
       </c>
       <c r="Q141" s="10" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="R141" s="10" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="S141" s="2"/>
       <c r="T141" s="2"/>
@@ -11691,50 +11698,50 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A142" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="G142" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H142" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I142" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J142" s="1">
+        <f t="shared" si="29"/>
+        <v>7200</v>
+      </c>
+      <c r="K142" s="1">
+        <f t="shared" si="30"/>
+        <v>9600</v>
+      </c>
+      <c r="L142" s="1">
         <f t="shared" si="26"/>
-        <v>4500</v>
-      </c>
-      <c r="K142" s="1">
+        <v>2450</v>
+      </c>
+      <c r="M142" s="1">
         <f t="shared" si="27"/>
-        <v>4200</v>
-      </c>
-      <c r="L142" s="1">
+        <v>2450</v>
+      </c>
+      <c r="N142" s="2">
         <f t="shared" si="28"/>
-        <v>2450</v>
-      </c>
-      <c r="M142" s="1">
-        <f t="shared" si="29"/>
-        <v>2450</v>
-      </c>
-      <c r="N142" s="2">
-        <f t="shared" si="30"/>
         <v>61</v>
       </c>
       <c r="O142" s="4">
@@ -11744,10 +11751,10 @@
         <v>90</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="R142" s="10" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="S142" s="2"/>
       <c r="T142" s="2"/>
@@ -11757,50 +11764,50 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A143" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>855</v>
+        <v>864</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="G143" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H143" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I143" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J143" s="1">
+        <f t="shared" si="29"/>
+        <v>7400</v>
+      </c>
+      <c r="K143" s="1">
+        <f t="shared" si="30"/>
+        <v>9900</v>
+      </c>
+      <c r="L143" s="1">
         <f t="shared" si="26"/>
-        <v>4600</v>
-      </c>
-      <c r="K143" s="1">
+        <v>2500</v>
+      </c>
+      <c r="M143" s="1">
         <f t="shared" si="27"/>
-        <v>4300</v>
-      </c>
-      <c r="L143" s="1">
+        <v>2500</v>
+      </c>
+      <c r="N143" s="2">
         <f t="shared" si="28"/>
-        <v>2500</v>
-      </c>
-      <c r="M143" s="1">
-        <f t="shared" si="29"/>
-        <v>2500</v>
-      </c>
-      <c r="N143" s="2">
-        <f t="shared" si="30"/>
         <v>62</v>
       </c>
       <c r="O143" s="4">
@@ -11810,10 +11817,10 @@
         <v>90</v>
       </c>
       <c r="Q143" s="10" t="s">
-        <v>857</v>
+        <v>866</v>
       </c>
       <c r="R143" s="10" t="s">
-        <v>857</v>
+        <v>866</v>
       </c>
       <c r="S143" s="2"/>
       <c r="T143" s="2"/>
@@ -11823,50 +11830,50 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A144" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>858</v>
+        <v>867</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="G144" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H144" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I144" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J144" s="1">
+        <f t="shared" si="29"/>
+        <v>7600</v>
+      </c>
+      <c r="K144" s="1">
+        <f t="shared" si="30"/>
+        <v>10200</v>
+      </c>
+      <c r="L144" s="1">
         <f t="shared" si="26"/>
-        <v>4700</v>
-      </c>
-      <c r="K144" s="1">
+        <v>2550</v>
+      </c>
+      <c r="M144" s="1">
         <f t="shared" si="27"/>
-        <v>4400</v>
-      </c>
-      <c r="L144" s="1">
+        <v>2550</v>
+      </c>
+      <c r="N144" s="2">
         <f t="shared" si="28"/>
-        <v>2550</v>
-      </c>
-      <c r="M144" s="1">
-        <f t="shared" si="29"/>
-        <v>2550</v>
-      </c>
-      <c r="N144" s="2">
-        <f t="shared" si="30"/>
         <v>63</v>
       </c>
       <c r="O144" s="4">
@@ -11876,10 +11883,10 @@
         <v>90</v>
       </c>
       <c r="Q144" s="10" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
       <c r="R144" s="10" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
       <c r="S144" s="2"/>
       <c r="T144" s="2"/>
@@ -11889,50 +11896,50 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A145" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>864</v>
+        <v>873</v>
       </c>
       <c r="G145" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="H145" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="I145" s="14" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="J145" s="1">
+        <f t="shared" si="29"/>
+        <v>7800</v>
+      </c>
+      <c r="K145" s="1">
+        <f t="shared" si="30"/>
+        <v>10500</v>
+      </c>
+      <c r="L145" s="1">
         <f t="shared" si="26"/>
-        <v>4800</v>
-      </c>
-      <c r="K145" s="1">
+        <v>2600</v>
+      </c>
+      <c r="M145" s="1">
         <f t="shared" si="27"/>
-        <v>4500</v>
-      </c>
-      <c r="L145" s="1">
+        <v>2600</v>
+      </c>
+      <c r="N145" s="2">
         <f t="shared" si="28"/>
-        <v>2600</v>
-      </c>
-      <c r="M145" s="1">
-        <f t="shared" si="29"/>
-        <v>2600</v>
-      </c>
-      <c r="N145" s="2">
-        <f t="shared" si="30"/>
         <v>64</v>
       </c>
       <c r="O145" s="4">
@@ -11942,10 +11949,10 @@
         <v>90</v>
       </c>
       <c r="Q145" s="10" t="s">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="R145" s="10" t="s">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="S145" s="2"/>
       <c r="T145" s="2"/>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="871">
   <si>
     <t>ID</t>
   </si>
@@ -2333,7 +2333,7 @@
     <t>100000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>4100000000</t>
+    <t>4400000000</t>
   </si>
   <si>
     <t>10117</t>
@@ -2351,7 +2351,7 @@
     <t>2000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>4200000000</t>
+    <t>4800000000</t>
   </si>
   <si>
     <t>10118</t>
@@ -2369,7 +2369,7 @@
     <t>40000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>4300000000</t>
+    <t>5200000000</t>
   </si>
   <si>
     <t>10119</t>
@@ -2387,7 +2387,7 @@
     <t>800000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>4400000000</t>
+    <t>5600000000</t>
   </si>
   <si>
     <t>10120</t>
@@ -2405,7 +2405,7 @@
     <t>16000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>4500000000</t>
+    <t>6000000000</t>
   </si>
   <si>
     <t>#</t>
@@ -2447,9 +2447,6 @@
     <t>地狱黑猪</t>
   </si>
   <si>
-    <t>4800000000</t>
-  </si>
-  <si>
     <t>10124</t>
   </si>
   <si>
@@ -2495,9 +2492,6 @@
     <t>地狱勇士</t>
   </si>
   <si>
-    <t>5200000000</t>
-  </si>
-  <si>
     <t>10128</t>
   </si>
   <si>
@@ -2543,9 +2537,6 @@
     <t>地狱树妖</t>
   </si>
   <si>
-    <t>5600000000</t>
-  </si>
-  <si>
     <t>10132</t>
   </si>
   <si>
@@ -2589,9 +2580,6 @@
   </si>
   <si>
     <t>地狱将军</t>
-  </si>
-  <si>
-    <t>6000000000</t>
   </si>
   <si>
     <t>10136</t>
@@ -3632,8 +3620,8 @@
     <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="36.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="40.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="38" style="2" customWidth="1"/>
+    <col min="8" max="8" width="38.375" style="2" customWidth="1"/>
     <col min="9" max="9" width="52.625" style="2" customWidth="1"/>
     <col min="10" max="10" width="12.75" style="2" customWidth="1"/>
     <col min="11" max="11" width="9.375" style="2" customWidth="1"/>
@@ -10425,7 +10413,7 @@
         <v>40</v>
       </c>
       <c r="O121" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P121" s="2">
         <v>90</v>
@@ -10486,8 +10474,9 @@
         <f t="shared" si="28"/>
         <v>41</v>
       </c>
-      <c r="O122" s="4">
-        <v>0</v>
+      <c r="O122" s="2">
+        <f t="shared" ref="O122:O125" si="31">O121+3</f>
+        <v>6</v>
       </c>
       <c r="P122" s="2">
         <v>90</v>
@@ -10548,8 +10537,9 @@
         <f t="shared" si="28"/>
         <v>42</v>
       </c>
-      <c r="O123" s="4">
-        <v>0</v>
+      <c r="O123" s="2">
+        <f t="shared" si="31"/>
+        <v>9</v>
       </c>
       <c r="P123" s="2">
         <v>90</v>
@@ -10610,8 +10600,9 @@
         <f t="shared" si="28"/>
         <v>43</v>
       </c>
-      <c r="O124" s="4">
-        <v>0</v>
+      <c r="O124" s="2">
+        <f t="shared" si="31"/>
+        <v>12</v>
       </c>
       <c r="P124" s="2">
         <v>90</v>
@@ -10672,8 +10663,9 @@
         <f t="shared" si="28"/>
         <v>44</v>
       </c>
-      <c r="O125" s="4">
-        <v>0</v>
+      <c r="O125" s="2">
+        <f t="shared" si="31"/>
+        <v>15</v>
       </c>
       <c r="P125" s="2">
         <v>90</v>
@@ -10877,10 +10869,10 @@
         <v>90</v>
       </c>
       <c r="Q128" s="10" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
       <c r="R128" s="10" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
       <c r="S128" s="2"/>
       <c r="T128" s="2"/>
@@ -10896,16 +10888,16 @@
         <v>793</v>
       </c>
       <c r="C129" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>807</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>808</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G129" s="14" t="s">
         <v>797</v>
@@ -10943,10 +10935,10 @@
         <v>90</v>
       </c>
       <c r="Q129" s="10" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="R129" s="10" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="S129" s="2"/>
       <c r="T129" s="2"/>
@@ -10962,16 +10954,16 @@
         <v>793</v>
       </c>
       <c r="C130" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>811</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>812</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G130" s="14" t="s">
         <v>797</v>
@@ -11009,10 +11001,10 @@
         <v>90</v>
       </c>
       <c r="Q130" s="10" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="R130" s="10" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="S130" s="2"/>
       <c r="T130" s="2"/>
@@ -11028,16 +11020,16 @@
         <v>793</v>
       </c>
       <c r="C131" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>815</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>816</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G131" s="14" t="s">
         <v>797</v>
@@ -11075,10 +11067,10 @@
         <v>90</v>
       </c>
       <c r="Q131" s="10" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R131" s="10" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="1:18">
@@ -11089,16 +11081,16 @@
         <v>793</v>
       </c>
       <c r="C132" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>819</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>820</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G132" s="14" t="s">
         <v>797</v>
@@ -11136,10 +11128,10 @@
         <v>90</v>
       </c>
       <c r="Q132" s="10" t="s">
-        <v>822</v>
+        <v>780</v>
       </c>
       <c r="R132" s="10" t="s">
-        <v>822</v>
+        <v>780</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:18">
@@ -11150,16 +11142,16 @@
         <v>793</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G133" s="14" t="s">
         <v>797</v>
@@ -11197,10 +11189,10 @@
         <v>90</v>
       </c>
       <c r="Q133" s="10" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="R133" s="10" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:18">
@@ -11211,16 +11203,16 @@
         <v>793</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G134" s="14" t="s">
         <v>797</v>
@@ -11258,10 +11250,10 @@
         <v>90</v>
       </c>
       <c r="Q134" s="10" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="R134" s="10" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:18">
@@ -11272,16 +11264,16 @@
         <v>793</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G135" s="14" t="s">
         <v>797</v>
@@ -11319,10 +11311,10 @@
         <v>90</v>
       </c>
       <c r="Q135" s="10" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="R135" s="10" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:18">
@@ -11333,16 +11325,16 @@
         <v>793</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G136" s="14" t="s">
         <v>797</v>
@@ -11380,10 +11372,10 @@
         <v>90</v>
       </c>
       <c r="Q136" s="10" t="s">
-        <v>838</v>
+        <v>786</v>
       </c>
       <c r="R136" s="10" t="s">
-        <v>838</v>
+        <v>786</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="1:18">
@@ -11394,16 +11386,16 @@
         <v>793</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="G137" s="14" t="s">
         <v>797</v>
@@ -11441,10 +11433,10 @@
         <v>90</v>
       </c>
       <c r="Q137" s="10" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="R137" s="10" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:18">
@@ -11455,16 +11447,16 @@
         <v>793</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G138" s="14" t="s">
         <v>797</v>
@@ -11502,10 +11494,10 @@
         <v>90</v>
       </c>
       <c r="Q138" s="10" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="R138" s="10" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:18">
@@ -11516,16 +11508,16 @@
         <v>793</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="G139" s="14" t="s">
         <v>797</v>
@@ -11563,10 +11555,10 @@
         <v>90</v>
       </c>
       <c r="Q139" s="10" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="R139" s="10" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:18">
@@ -11577,16 +11569,16 @@
         <v>793</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="G140" s="14" t="s">
         <v>797</v>
@@ -11624,10 +11616,10 @@
         <v>90</v>
       </c>
       <c r="Q140" s="10" t="s">
-        <v>854</v>
+        <v>792</v>
       </c>
       <c r="R140" s="10" t="s">
-        <v>854</v>
+        <v>792</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
@@ -11638,16 +11630,16 @@
         <v>793</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="G141" s="14" t="s">
         <v>797</v>
@@ -11685,10 +11677,10 @@
         <v>90</v>
       </c>
       <c r="Q141" s="10" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="R141" s="10" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="S141" s="2"/>
       <c r="T141" s="2"/>
@@ -11704,16 +11696,16 @@
         <v>793</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="G142" s="14" t="s">
         <v>797</v>
@@ -11751,10 +11743,10 @@
         <v>90</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="R142" s="10" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="S142" s="2"/>
       <c r="T142" s="2"/>
@@ -11770,16 +11762,16 @@
         <v>793</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="G143" s="14" t="s">
         <v>797</v>
@@ -11817,10 +11809,10 @@
         <v>90</v>
       </c>
       <c r="Q143" s="10" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="R143" s="10" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="S143" s="2"/>
       <c r="T143" s="2"/>
@@ -11836,16 +11828,16 @@
         <v>793</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="G144" s="14" t="s">
         <v>797</v>
@@ -11883,10 +11875,10 @@
         <v>90</v>
       </c>
       <c r="Q144" s="10" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="R144" s="10" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="S144" s="2"/>
       <c r="T144" s="2"/>
@@ -11902,16 +11894,16 @@
         <v>793</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="G145" s="14" t="s">
         <v>797</v>
@@ -11949,10 +11941,10 @@
         <v>90</v>
       </c>
       <c r="Q145" s="10" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="R145" s="10" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="S145" s="2"/>
       <c r="T145" s="2"/>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -143,7 +143,7 @@
     <t>1002</t>
   </si>
   <si>
-    <t>稻草人</t>
+    <t>草人</t>
   </si>
   <si>
     <t>2000</t>
@@ -161,7 +161,7 @@
     <t>1003</t>
   </si>
   <si>
-    <t>钉耙猫</t>
+    <t>野猫</t>
   </si>
   <si>
     <t>50000</t>
@@ -209,7 +209,7 @@
     <t>1006</t>
   </si>
   <si>
-    <t>山洞蝙蝠</t>
+    <t>蝙蝠</t>
   </si>
   <si>
     <t>19783</t>
@@ -269,7 +269,7 @@
     <t>1009</t>
   </si>
   <si>
-    <t>虎蛇</t>
+    <t>毒蛇</t>
   </si>
   <si>
     <t>55048</t>
@@ -290,7 +290,7 @@
     <t>1010</t>
   </si>
   <si>
-    <t>狼</t>
+    <t>野狼</t>
   </si>
   <si>
     <t>77426</t>
@@ -332,7 +332,7 @@
     <t>1012</t>
   </si>
   <si>
-    <t>鹰</t>
+    <t>小鹰</t>
   </si>
   <si>
     <t>153174</t>
@@ -353,7 +353,7 @@
     <t>1013</t>
   </si>
   <si>
-    <t>多角虫</t>
+    <t>角虫</t>
   </si>
   <si>
     <t>215443</t>
@@ -458,7 +458,7 @@
     <t>1018</t>
   </si>
   <si>
-    <t>野猪</t>
+    <t>白野猪</t>
   </si>
   <si>
     <t>1185971</t>
@@ -500,7 +500,7 @@
     <t>1020</t>
   </si>
   <si>
-    <t>火焰沃玛</t>
+    <t>火焰恶魔</t>
   </si>
   <si>
     <t>2346229</t>
@@ -521,7 +521,7 @@
     <t>1021</t>
   </si>
   <si>
-    <t>沃玛勇士</t>
+    <t>恶魔勇士</t>
   </si>
   <si>
     <t>3300035</t>
@@ -542,7 +542,7 @@
     <t>1022</t>
   </si>
   <si>
-    <t>祖玛雕像</t>
+    <t>邪魔雕像</t>
   </si>
   <si>
     <t>4641589</t>
@@ -563,7 +563,7 @@
     <t>1023</t>
   </si>
   <si>
-    <t>祖玛卫士</t>
+    <t>邪魔卫士</t>
   </si>
   <si>
     <t>6528521</t>
@@ -626,7 +626,7 @@
     <t>1026</t>
   </si>
   <si>
-    <t>虹魔侍卫</t>
+    <t>邪魔侍卫</t>
   </si>
   <si>
     <t>18165998</t>
@@ -710,7 +710,7 @@
     <t>1030</t>
   </si>
   <si>
-    <t>钢牙蜘蛛</t>
+    <t>水龙</t>
   </si>
   <si>
     <t>71097094</t>
@@ -731,7 +731,7 @@
     <t>1031</t>
   </si>
   <si>
-    <t>天狼蜘蛛</t>
+    <t>土龙</t>
   </si>
   <si>
     <t>100000000</t>
@@ -752,7 +752,7 @@
     <t>1032</t>
   </si>
   <si>
-    <t>血巨人</t>
+    <t>毒龙</t>
   </si>
   <si>
     <t>140652724</t>
@@ -773,7 +773,7 @@
     <t>1033</t>
   </si>
   <si>
-    <t>魔龙力士</t>
+    <t>火龙</t>
   </si>
   <si>
     <t>197831888</t>
@@ -794,7 +794,7 @@
     <t>1034</t>
   </si>
   <si>
-    <t>火龙守护兽</t>
+    <t>冰龙</t>
   </si>
   <si>
     <t>278255940</t>
@@ -1004,7 +1004,7 @@
     <t>1044</t>
   </si>
   <si>
-    <t>幻影虎蛇</t>
+    <t>幻影毒蛇</t>
   </si>
   <si>
     <t>8431900000</t>
@@ -1025,7 +1025,7 @@
     <t>1045</t>
   </si>
   <si>
-    <t>幻影狼</t>
+    <t>幻影野狼</t>
   </si>
   <si>
     <t>11859710000</t>
@@ -1088,7 +1088,7 @@
     <t>1048</t>
   </si>
   <si>
-    <t>幻影多角虫</t>
+    <t>幻影角虫</t>
   </si>
   <si>
     <t>33000340000</t>
@@ -1235,7 +1235,7 @@
     <t>1055</t>
   </si>
   <si>
-    <t>幻影火焰</t>
+    <t>幻影恶魔</t>
   </si>
   <si>
     <t>359381360000</t>
@@ -1424,7 +1424,7 @@
     <t>1064</t>
   </si>
   <si>
-    <t>幻影将军</t>
+    <t>幻影魔牛</t>
   </si>
   <si>
     <t>8000000000000</t>
@@ -1445,7 +1445,7 @@
     <t>1065</t>
   </si>
   <si>
-    <t>幻影钢牙</t>
+    <t>幻影水龙</t>
   </si>
   <si>
     <t>16000000000000</t>
@@ -1466,7 +1466,7 @@
     <t>1066</t>
   </si>
   <si>
-    <t>幻影天狼</t>
+    <t>幻影土龙</t>
   </si>
   <si>
     <t>32000000000000</t>
@@ -1487,7 +1487,7 @@
     <t>1067</t>
   </si>
   <si>
-    <t>幻影血巨人</t>
+    <t>幻影毒龙</t>
   </si>
   <si>
     <t>64000000000000</t>
@@ -1508,7 +1508,7 @@
     <t>1068</t>
   </si>
   <si>
-    <t>幻影魔龙兵</t>
+    <t>幻影火龙</t>
   </si>
   <si>
     <t>128000000000000</t>
@@ -1529,7 +1529,7 @@
     <t>1069</t>
   </si>
   <si>
-    <t>幻影火龙兽</t>
+    <t>幻影冰龙</t>
   </si>
   <si>
     <t>200000000000000</t>
@@ -1712,7 +1712,7 @@
     <t>1079</t>
   </si>
   <si>
-    <t>噩梦虎蛇</t>
+    <t>噩梦毒蛇</t>
   </si>
   <si>
     <t>32000000000000000</t>
@@ -1730,7 +1730,7 @@
     <t>1080</t>
   </si>
   <si>
-    <t>噩梦狼</t>
+    <t>噩梦野狼</t>
   </si>
   <si>
     <t>60000000000000000</t>
@@ -1775,7 +1775,7 @@
     <t>1083</t>
   </si>
   <si>
-    <t>噩梦多角虫</t>
+    <t>噩梦角虫</t>
   </si>
   <si>
     <t>30000000000000000</t>
@@ -1889,7 +1889,7 @@
     <t>1090</t>
   </si>
   <si>
-    <t>噩梦火焰</t>
+    <t>噩梦恶魔</t>
   </si>
   <si>
     <t>100000000000000000000</t>
@@ -2042,7 +2042,7 @@
     <t>1099</t>
   </si>
   <si>
-    <t>噩梦将军</t>
+    <t>噩梦魔牛</t>
   </si>
   <si>
     <t>9000000000000000000000000</t>
@@ -2057,7 +2057,7 @@
     <t>1100</t>
   </si>
   <si>
-    <t>噩梦钢牙</t>
+    <t>噩梦水龙</t>
   </si>
   <si>
     <t>27000000000000000000000000</t>
@@ -2075,7 +2075,7 @@
     <t>1101</t>
   </si>
   <si>
-    <t>噩梦天狼</t>
+    <t>噩梦土龙</t>
   </si>
   <si>
     <t>81000000000000000000000000</t>
@@ -2093,7 +2093,7 @@
     <t>1102</t>
   </si>
   <si>
-    <t>噩梦血巨人</t>
+    <t>噩梦毒龙</t>
   </si>
   <si>
     <t>240000000000000000000000000</t>
@@ -2111,7 +2111,7 @@
     <t>1103</t>
   </si>
   <si>
-    <t>噩梦魔龙兵</t>
+    <t>噩梦火龙</t>
   </si>
   <si>
     <t>720000000000000000000000000</t>
@@ -2129,7 +2129,7 @@
     <t>1104</t>
   </si>
   <si>
-    <t>噩梦火龙兽</t>
+    <t>噩梦冰龙</t>
   </si>
   <si>
     <t>2100000000000000000000000000</t>
@@ -2309,7 +2309,7 @@
     <t>1114</t>
   </si>
   <si>
-    <t>地狱虎蛇</t>
+    <t>地狱毒蛇</t>
   </si>
   <si>
     <t>900000000000000000000000000000000000000000000</t>
@@ -2327,7 +2327,7 @@
     <t>1115</t>
   </si>
   <si>
-    <t>地狱狼</t>
+    <t>地狱野狼</t>
   </si>
   <si>
     <t>100000000000000000000000000000000000000000000000000000000000</t>
@@ -2378,7 +2378,7 @@
     <t>1118</t>
   </si>
   <si>
-    <t>地狱多角虫</t>
+    <t>地狱角虫</t>
   </si>
   <si>
     <t>9000000000000000000000000000000000000000000000000</t>
@@ -2477,7 +2477,7 @@
     <t>1125</t>
   </si>
   <si>
-    <t>地狱火焰</t>
+    <t>地狱恶魔</t>
   </si>
   <si>
     <t>5100000000</t>
@@ -2579,7 +2579,7 @@
     <t>1134</t>
   </si>
   <si>
-    <t>地狱将军</t>
+    <t>地狱魔牛</t>
   </si>
   <si>
     <t>10136</t>
@@ -2588,7 +2588,7 @@
     <t>1135</t>
   </si>
   <si>
-    <t>地狱钢牙</t>
+    <t>地狱水龙</t>
   </si>
   <si>
     <t>6100000000</t>
@@ -2600,7 +2600,7 @@
     <t>1136</t>
   </si>
   <si>
-    <t>地狱天狼</t>
+    <t>地狱土龙</t>
   </si>
   <si>
     <t>6200000000</t>
@@ -2612,7 +2612,7 @@
     <t>1137</t>
   </si>
   <si>
-    <t>地狱血巨人</t>
+    <t>地狱毒龙</t>
   </si>
   <si>
     <t>6300000000</t>
@@ -2624,7 +2624,7 @@
     <t>1138</t>
   </si>
   <si>
-    <t>地狱魔龙兵</t>
+    <t>地狱火龙</t>
   </si>
   <si>
     <t>6400000000</t>
@@ -2636,7 +2636,7 @@
     <t>1139</t>
   </si>
   <si>
-    <t>地狱火龙兽</t>
+    <t>地狱冰龙</t>
   </si>
   <si>
     <t>6500000000</t>
@@ -5615,7 +5615,7 @@
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
+      <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
         <v>260</v>
       </c>
@@ -5671,7 +5671,7 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
+      <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
         <v>267</v>
       </c>
@@ -5727,7 +5727,7 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
+      <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
         <v>274</v>
       </c>
@@ -5783,7 +5783,7 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
+      <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
         <v>281</v>
       </c>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
+      <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
         <v>288</v>
       </c>
@@ -5895,7 +5895,7 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
+      <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
         <v>295</v>
       </c>
@@ -5953,7 +5953,7 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
+      <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
         <v>302</v>
       </c>
@@ -6011,7 +6011,7 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
+      <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
         <v>309</v>
       </c>
@@ -6069,7 +6069,7 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
+      <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
         <v>316</v>
       </c>
@@ -6127,7 +6127,7 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
+      <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
         <v>323</v>
       </c>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
+      <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
         <v>330</v>
       </c>
@@ -6246,7 +6246,7 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
+      <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
         <v>337</v>
       </c>
@@ -6307,7 +6307,7 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
+      <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
         <v>344</v>
       </c>
@@ -6368,7 +6368,7 @@
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
+      <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
         <v>351</v>
       </c>
@@ -6429,7 +6429,7 @@
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
+      <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
         <v>358</v>
       </c>
@@ -6490,7 +6490,7 @@
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
+      <c r="B56" s="1"/>
       <c r="C56" s="1" t="s">
         <v>365</v>
       </c>
@@ -6551,7 +6551,7 @@
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
+      <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
         <v>372</v>
       </c>
@@ -6612,7 +6612,7 @@
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
+      <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
         <v>379</v>
       </c>
@@ -6673,7 +6673,7 @@
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
+      <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
         <v>386</v>
       </c>
@@ -6734,7 +6734,7 @@
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
+      <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
         <v>393</v>
       </c>
@@ -6795,7 +6795,7 @@
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
+      <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
         <v>400</v>
       </c>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
+      <c r="B62" s="1"/>
       <c r="C62" s="1" t="s">
         <v>407</v>
       </c>
@@ -6917,7 +6917,7 @@
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
+      <c r="B63" s="1"/>
       <c r="C63" s="1" t="s">
         <v>414</v>
       </c>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
+      <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
         <v>421</v>
       </c>
@@ -7039,7 +7039,7 @@
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
+      <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
         <v>428</v>
       </c>
@@ -7100,7 +7100,7 @@
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
+      <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
         <v>435</v>
       </c>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
+      <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
         <v>442</v>
       </c>
@@ -7222,7 +7222,7 @@
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
+      <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
         <v>449</v>
       </c>
@@ -7283,7 +7283,7 @@
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
+      <c r="B69" s="1"/>
       <c r="C69" s="1" t="s">
         <v>456</v>
       </c>
@@ -7344,7 +7344,7 @@
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
+      <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
         <v>463</v>
       </c>
@@ -7405,7 +7405,7 @@
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
+      <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
         <v>470</v>
       </c>
@@ -7466,7 +7466,7 @@
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
+      <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
         <v>477</v>
       </c>
@@ -7527,7 +7527,7 @@
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
+      <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
         <v>484</v>
       </c>
@@ -7588,7 +7588,7 @@
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
+      <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
         <v>491</v>
       </c>
@@ -7649,7 +7649,7 @@
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
+      <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
         <v>498</v>
       </c>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="881">
   <si>
     <t>ID</t>
   </si>
@@ -2408,78 +2408,111 @@
     <t>6000000000</t>
   </si>
   <si>
+    <t>10121</t>
+  </si>
+  <si>
+    <t>1120</t>
+  </si>
+  <si>
+    <t>地狱钳虫</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>320000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>6400000000</t>
+  </si>
+  <si>
+    <t>10122</t>
+  </si>
+  <si>
+    <t>1121</t>
+  </si>
+  <si>
+    <t>地狱蠕虫</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>6400000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>6800000000</t>
+  </si>
+  <si>
+    <t>10123</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>地狱黑猪</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>128000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>7200000000</t>
+  </si>
+  <si>
+    <t>10124</t>
+  </si>
+  <si>
+    <t>1123</t>
+  </si>
+  <si>
+    <t>地狱红猪</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>2560000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>7600000000</t>
+  </si>
+  <si>
+    <t>10125</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>地狱蝎蛇</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>51200000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>8000000000</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
-    <t>10121</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>地狱钳虫</t>
+    <t>10126</t>
+  </si>
+  <si>
+    <t>1125</t>
+  </si>
+  <si>
+    <t>地狱恶魔</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>4600000000</t>
-  </si>
-  <si>
-    <t>10122</t>
-  </si>
-  <si>
-    <t>1121</t>
-  </si>
-  <si>
-    <t>地狱蠕虫</t>
-  </si>
-  <si>
-    <t>4700000000</t>
-  </si>
-  <si>
-    <t>10123</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>地狱黑猪</t>
-  </si>
-  <si>
-    <t>10124</t>
-  </si>
-  <si>
-    <t>1123</t>
-  </si>
-  <si>
-    <t>地狱红猪</t>
-  </si>
-  <si>
-    <t>4900000000</t>
-  </si>
-  <si>
-    <t>10125</t>
-  </si>
-  <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>地狱蝎蛇</t>
-  </si>
-  <si>
-    <t>5000000000</t>
-  </si>
-  <si>
-    <t>10126</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>地狱恶魔</t>
-  </si>
-  <si>
     <t>5100000000</t>
   </si>
   <si>
@@ -2625,9 +2658,6 @@
   </si>
   <si>
     <t>地狱火龙</t>
-  </si>
-  <si>
-    <t>6400000000</t>
   </si>
   <si>
     <t>10140</t>
@@ -3620,9 +3650,9 @@
     <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="38" style="2" customWidth="1"/>
-    <col min="8" max="8" width="38.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="52.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="41.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="41.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="56.5" style="2" customWidth="1"/>
     <col min="10" max="10" width="12.75" style="2" customWidth="1"/>
     <col min="11" max="11" width="9.375" style="2" customWidth="1"/>
     <col min="12" max="12" width="9.125" style="2" customWidth="1"/>
@@ -10683,31 +10713,27 @@
       <c r="W125" s="2"/>
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="C126" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>794</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>795</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="G126" s="14" t="s">
         <v>796</v>
       </c>
-      <c r="G126" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="H126" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="I126" s="14" t="s">
+      <c r="H126" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="I126" s="15" t="s">
         <v>797</v>
       </c>
       <c r="J126" s="1">
@@ -10749,12 +10775,8 @@
       <c r="W126" s="2"/>
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A127" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>793</v>
-      </c>
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
       <c r="C127" s="1" t="s">
         <v>799</v>
       </c>
@@ -10768,13 +10790,13 @@
         <v>801</v>
       </c>
       <c r="G127" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="H127" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="I127" s="14" t="s">
-        <v>797</v>
+        <v>802</v>
+      </c>
+      <c r="H127" s="10" t="s">
+        <v>802</v>
+      </c>
+      <c r="I127" s="15" t="s">
+        <v>803</v>
       </c>
       <c r="J127" s="1">
         <f t="shared" si="29"/>
@@ -10803,10 +10825,10 @@
         <v>90</v>
       </c>
       <c r="Q127" s="10" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="R127" s="10" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="S127" s="2"/>
       <c r="T127" s="2"/>
@@ -10815,32 +10837,28 @@
       <c r="W127" s="2"/>
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A128" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>793</v>
-      </c>
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
       <c r="C128" s="1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="G128" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="H128" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="I128" s="14" t="s">
-        <v>797</v>
+        <v>808</v>
+      </c>
+      <c r="H128" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="I128" s="15" t="s">
+        <v>809</v>
       </c>
       <c r="J128" s="1">
         <f t="shared" si="29"/>
@@ -10869,10 +10887,10 @@
         <v>90</v>
       </c>
       <c r="Q128" s="10" t="s">
-        <v>774</v>
+        <v>810</v>
       </c>
       <c r="R128" s="10" t="s">
-        <v>774</v>
+        <v>810</v>
       </c>
       <c r="S128" s="2"/>
       <c r="T128" s="2"/>
@@ -10881,32 +10899,28 @@
       <c r="W128" s="2"/>
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A129" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>793</v>
-      </c>
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
       <c r="C129" s="1" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="G129" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="H129" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="I129" s="14" t="s">
-        <v>797</v>
+        <v>814</v>
+      </c>
+      <c r="H129" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="I129" s="15" t="s">
+        <v>815</v>
       </c>
       <c r="J129" s="1">
         <f t="shared" si="29"/>
@@ -10935,10 +10949,10 @@
         <v>90</v>
       </c>
       <c r="Q129" s="10" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="R129" s="10" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="S129" s="2"/>
       <c r="T129" s="2"/>
@@ -10947,32 +10961,28 @@
       <c r="W129" s="2"/>
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A130" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>793</v>
-      </c>
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
       <c r="C130" s="1" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="G130" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="H130" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="I130" s="14" t="s">
-        <v>797</v>
+        <v>820</v>
+      </c>
+      <c r="H130" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="I130" s="15" t="s">
+        <v>821</v>
       </c>
       <c r="J130" s="1">
         <f t="shared" si="29"/>
@@ -11001,10 +11011,10 @@
         <v>90</v>
       </c>
       <c r="Q130" s="10" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="R130" s="10" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="S130" s="2"/>
       <c r="T130" s="2"/>
@@ -11014,31 +11024,31 @@
     </row>
     <row r="131" customHeight="1" spans="1:18">
       <c r="A131" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>814</v>
+        <v>824</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>815</v>
+        <v>825</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="G131" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H131" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I131" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J131" s="1">
         <f t="shared" si="29"/>
@@ -11067,39 +11077,39 @@
         <v>90</v>
       </c>
       <c r="Q131" s="10" t="s">
-        <v>817</v>
+        <v>828</v>
       </c>
       <c r="R131" s="10" t="s">
-        <v>817</v>
+        <v>828</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="1:18">
       <c r="A132" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>818</v>
+        <v>829</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>819</v>
+        <v>830</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>820</v>
+        <v>831</v>
       </c>
       <c r="G132" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H132" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I132" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J132" s="1">
         <f t="shared" si="29"/>
@@ -11136,31 +11146,31 @@
     </row>
     <row r="133" customHeight="1" spans="1:18">
       <c r="A133" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>821</v>
+        <v>832</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>822</v>
+        <v>833</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>823</v>
+        <v>834</v>
       </c>
       <c r="G133" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H133" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I133" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J133" s="1">
         <f t="shared" si="29"/>
@@ -11189,39 +11199,39 @@
         <v>90</v>
       </c>
       <c r="Q133" s="10" t="s">
-        <v>824</v>
+        <v>835</v>
       </c>
       <c r="R133" s="10" t="s">
-        <v>824</v>
+        <v>835</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:18">
       <c r="A134" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>825</v>
+        <v>836</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>826</v>
+        <v>837</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="G134" s="14" t="s">
         <v>827</v>
       </c>
-      <c r="G134" s="14" t="s">
-        <v>797</v>
-      </c>
       <c r="H134" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I134" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J134" s="1">
         <f t="shared" si="29"/>
@@ -11250,39 +11260,39 @@
         <v>90</v>
       </c>
       <c r="Q134" s="10" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="R134" s="10" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:18">
       <c r="A135" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>829</v>
+        <v>840</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>830</v>
+        <v>841</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>831</v>
+        <v>842</v>
       </c>
       <c r="G135" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H135" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I135" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J135" s="1">
         <f t="shared" si="29"/>
@@ -11311,39 +11321,39 @@
         <v>90</v>
       </c>
       <c r="Q135" s="10" t="s">
-        <v>832</v>
+        <v>843</v>
       </c>
       <c r="R135" s="10" t="s">
-        <v>832</v>
+        <v>843</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:18">
       <c r="A136" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>833</v>
+        <v>844</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>834</v>
+        <v>845</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>835</v>
+        <v>846</v>
       </c>
       <c r="G136" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H136" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I136" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J136" s="1">
         <f t="shared" si="29"/>
@@ -11380,31 +11390,31 @@
     </row>
     <row r="137" customHeight="1" spans="1:18">
       <c r="A137" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>836</v>
+        <v>847</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>837</v>
+        <v>848</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>838</v>
+        <v>849</v>
       </c>
       <c r="G137" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H137" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I137" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J137" s="1">
         <f t="shared" si="29"/>
@@ -11433,39 +11443,39 @@
         <v>90</v>
       </c>
       <c r="Q137" s="10" t="s">
-        <v>839</v>
+        <v>850</v>
       </c>
       <c r="R137" s="10" t="s">
-        <v>839</v>
+        <v>850</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:18">
       <c r="A138" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>840</v>
+        <v>851</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>841</v>
+        <v>852</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H138" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I138" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J138" s="1">
         <f t="shared" si="29"/>
@@ -11494,39 +11504,39 @@
         <v>90</v>
       </c>
       <c r="Q138" s="10" t="s">
-        <v>843</v>
+        <v>854</v>
       </c>
       <c r="R138" s="10" t="s">
-        <v>843</v>
+        <v>854</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:18">
       <c r="A139" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="G139" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H139" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I139" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J139" s="1">
         <f t="shared" si="29"/>
@@ -11555,39 +11565,39 @@
         <v>90</v>
       </c>
       <c r="Q139" s="10" t="s">
-        <v>847</v>
+        <v>858</v>
       </c>
       <c r="R139" s="10" t="s">
-        <v>847</v>
+        <v>858</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:18">
       <c r="A140" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>849</v>
+        <v>860</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>850</v>
+        <v>861</v>
       </c>
       <c r="G140" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H140" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I140" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J140" s="1">
         <f t="shared" si="29"/>
@@ -11624,31 +11634,31 @@
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A141" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>853</v>
+        <v>864</v>
       </c>
       <c r="G141" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H141" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I141" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J141" s="1">
         <f t="shared" si="29"/>
@@ -11677,10 +11687,10 @@
         <v>90</v>
       </c>
       <c r="Q141" s="10" t="s">
-        <v>854</v>
+        <v>865</v>
       </c>
       <c r="R141" s="10" t="s">
-        <v>854</v>
+        <v>865</v>
       </c>
       <c r="S141" s="2"/>
       <c r="T141" s="2"/>
@@ -11690,31 +11700,31 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A142" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>855</v>
+        <v>866</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>856</v>
+        <v>867</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>857</v>
+        <v>868</v>
       </c>
       <c r="G142" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H142" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I142" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J142" s="1">
         <f t="shared" si="29"/>
@@ -11743,10 +11753,10 @@
         <v>90</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>858</v>
+        <v>869</v>
       </c>
       <c r="R142" s="10" t="s">
-        <v>858</v>
+        <v>869</v>
       </c>
       <c r="S142" s="2"/>
       <c r="T142" s="2"/>
@@ -11756,31 +11766,31 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A143" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>859</v>
+        <v>870</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>860</v>
+        <v>871</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>861</v>
+        <v>872</v>
       </c>
       <c r="G143" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H143" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I143" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J143" s="1">
         <f t="shared" si="29"/>
@@ -11809,10 +11819,10 @@
         <v>90</v>
       </c>
       <c r="Q143" s="10" t="s">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="R143" s="10" t="s">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="S143" s="2"/>
       <c r="T143" s="2"/>
@@ -11822,31 +11832,31 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A144" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="G144" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H144" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I144" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J144" s="1">
         <f t="shared" si="29"/>
@@ -11875,10 +11885,10 @@
         <v>90</v>
       </c>
       <c r="Q144" s="10" t="s">
-        <v>866</v>
+        <v>798</v>
       </c>
       <c r="R144" s="10" t="s">
-        <v>866</v>
+        <v>798</v>
       </c>
       <c r="S144" s="2"/>
       <c r="T144" s="2"/>
@@ -11888,31 +11898,31 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A145" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="G145" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="H145" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="I145" s="14" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J145" s="1">
         <f t="shared" si="29"/>
@@ -11941,10 +11951,10 @@
         <v>90</v>
       </c>
       <c r="Q145" s="10" t="s">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="R145" s="10" t="s">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="S145" s="2"/>
       <c r="T145" s="2"/>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="883">
   <si>
     <t>ID</t>
   </si>
@@ -119,6 +119,15 @@
     <t>鸡</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
@@ -129,9 +138,6 @@
   </si>
   <si>
     <t>鹿</t>
-  </si>
-  <si>
-    <t>500</t>
   </si>
   <si>
     <t>5000</t>
@@ -3873,7 +3879,7 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" ht="14.25" spans="3:18">
+    <row r="6" spans="3:18">
       <c r="C6" s="1" t="s">
         <v>27</v>
       </c>
@@ -3886,14 +3892,14 @@
       <c r="F6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="1">
-        <v>5</v>
-      </c>
-      <c r="H6" s="1">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1000</v>
+      <c r="G6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -3917,33 +3923,33 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:18">
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -3967,83 +3973,83 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:18">
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="R8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:18">
       <c r="C9" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -4067,33 +4073,33 @@
         <v>0</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:18">
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
@@ -4117,33 +4123,33 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:18">
       <c r="C11" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J11" s="1">
         <v>0</v>
@@ -4167,33 +4173,33 @@
         <v>0</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:18">
       <c r="C12" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -4217,33 +4223,33 @@
         <v>0</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:18">
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J13" s="1">
         <v>0</v>
@@ -4267,33 +4273,33 @@
         <v>0</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:18">
       <c r="C14" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J14" s="1">
         <v>0</v>
@@ -4317,33 +4323,33 @@
         <v>0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:18">
       <c r="C15" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
@@ -4367,33 +4373,33 @@
         <v>0</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:18">
       <c r="C16" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J16" s="1">
         <v>0</v>
@@ -4417,33 +4423,33 @@
         <v>0</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:18">
       <c r="C17" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
@@ -4467,33 +4473,33 @@
         <v>0</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:18">
       <c r="C18" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
@@ -4517,33 +4523,33 @@
         <v>0</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:18">
       <c r="C19" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J19" s="1">
         <v>0</v>
@@ -4567,33 +4573,33 @@
         <v>0</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:18">
       <c r="C20" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J20" s="1">
         <v>0</v>
@@ -4617,33 +4623,33 @@
         <v>0</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:18">
       <c r="C21" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J21" s="1">
         <f t="shared" ref="J21:J66" si="0">(D21-1014)*3</f>
@@ -4668,33 +4674,33 @@
         <v>0</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:18">
       <c r="C22" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J22" s="1">
         <f t="shared" si="0"/>
@@ -4719,33 +4725,33 @@
         <v>0</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:18">
       <c r="C23" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" si="0"/>
@@ -4770,33 +4776,33 @@
         <v>0</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:18">
       <c r="C24" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" si="0"/>
@@ -4821,33 +4827,33 @@
         <v>0</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:18">
       <c r="C25" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J25" s="1">
         <f t="shared" si="0"/>
@@ -4872,33 +4878,33 @@
         <v>0</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:18">
       <c r="C26" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J26" s="1">
         <f t="shared" si="0"/>
@@ -4923,33 +4929,33 @@
         <v>0</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:18">
       <c r="C27" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" si="0"/>
@@ -4974,33 +4980,33 @@
         <v>0</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:18">
       <c r="C28" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J28" s="1">
         <f t="shared" si="0"/>
@@ -5025,33 +5031,33 @@
         <v>0</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:18">
       <c r="C29" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J29" s="1">
         <f t="shared" si="0"/>
@@ -5076,33 +5082,33 @@
         <v>0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:18">
       <c r="C30" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J30" s="1">
         <f t="shared" si="0"/>
@@ -5127,33 +5133,33 @@
         <v>0</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:18">
       <c r="C31" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J31" s="1">
         <f t="shared" si="0"/>
@@ -5178,33 +5184,33 @@
         <v>0</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:18">
       <c r="C32" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J32" s="1">
         <f t="shared" si="0"/>
@@ -5229,33 +5235,33 @@
         <v>0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:18">
       <c r="C33" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J33" s="1">
         <f t="shared" si="0"/>
@@ -5280,33 +5286,33 @@
         <v>0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:18">
       <c r="C34" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J34" s="1">
         <f t="shared" si="0"/>
@@ -5331,33 +5337,33 @@
         <v>0</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:18">
       <c r="C35" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J35" s="1">
         <f t="shared" si="0"/>
@@ -5382,33 +5388,33 @@
         <v>0</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:18">
       <c r="C36" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" si="0"/>
@@ -5433,33 +5439,33 @@
         <v>0</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:18">
       <c r="C37" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" si="0"/>
@@ -5484,33 +5490,33 @@
         <v>0</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:18">
       <c r="C38" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J38" s="1">
         <f t="shared" si="0"/>
@@ -5535,33 +5541,33 @@
         <v>0</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:18">
       <c r="C39" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J39" s="1">
         <f t="shared" si="0"/>
@@ -5586,33 +5592,33 @@
         <v>0</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:18">
       <c r="C40" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J40" s="1">
         <f t="shared" si="0"/>
@@ -5637,35 +5643,34 @@
         <v>0</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A41" s="2"/>
-      <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J41" s="1">
         <f t="shared" si="0"/>
@@ -5690,10 +5695,10 @@
         <v>0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
@@ -5701,27 +5706,26 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A42" s="2"/>
-      <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J42" s="1">
         <f t="shared" si="0"/>
@@ -5746,10 +5750,10 @@
         <v>0</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
@@ -5757,27 +5761,26 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A43" s="2"/>
-      <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J43" s="1">
         <f t="shared" si="0"/>
@@ -5802,10 +5805,10 @@
         <v>0</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
@@ -5813,27 +5816,26 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A44" s="2"/>
-      <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J44" s="1">
         <f t="shared" si="0"/>
@@ -5858,10 +5860,10 @@
         <v>0</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
@@ -5869,27 +5871,26 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A45" s="2"/>
-      <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J45" s="1">
         <f t="shared" si="0"/>
@@ -5914,10 +5915,10 @@
         <v>0</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
@@ -5925,27 +5926,26 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A46" s="2"/>
-      <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J46" s="1">
         <f t="shared" si="0"/>
@@ -5970,10 +5970,10 @@
         <v>0</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
@@ -5983,27 +5983,26 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A47" s="2"/>
-      <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J47" s="1">
         <f t="shared" si="0"/>
@@ -6028,10 +6027,10 @@
         <v>0</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="S47" s="2"/>
       <c r="T47" s="2"/>
@@ -6041,27 +6040,26 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A48" s="2"/>
-      <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J48" s="1">
         <f t="shared" si="0"/>
@@ -6086,10 +6084,10 @@
         <v>0</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="S48" s="2"/>
       <c r="T48" s="2"/>
@@ -6099,27 +6097,26 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A49" s="2"/>
-      <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J49" s="1">
         <f t="shared" si="0"/>
@@ -6144,10 +6141,10 @@
         <v>0</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="S49" s="2"/>
       <c r="T49" s="2"/>
@@ -6157,27 +6154,26 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A50" s="2"/>
-      <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J50" s="1">
         <f t="shared" si="0"/>
@@ -6202,10 +6198,10 @@
         <v>0</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="S50" s="2"/>
       <c r="T50" s="2"/>
@@ -6215,27 +6211,26 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A51" s="2"/>
-      <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J51" s="1">
         <f t="shared" si="0"/>
@@ -6263,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="S51" s="2"/>
       <c r="T51" s="2"/>
@@ -6276,27 +6271,26 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A52" s="2"/>
-      <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J52" s="1">
         <f t="shared" si="0"/>
@@ -6324,10 +6318,10 @@
         <v>0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="S52" s="2"/>
       <c r="T52" s="2"/>
@@ -6337,27 +6331,26 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A53" s="2"/>
-      <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J53" s="1">
         <f t="shared" si="0"/>
@@ -6385,10 +6378,10 @@
         <v>0</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="S53" s="2"/>
       <c r="T53" s="2"/>
@@ -6398,27 +6391,26 @@
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A54" s="2"/>
-      <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J54" s="1">
         <f t="shared" si="0"/>
@@ -6446,10 +6438,10 @@
         <v>0</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="S54" s="2"/>
       <c r="T54" s="2"/>
@@ -6459,27 +6451,26 @@
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A55" s="2"/>
-      <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J55" s="1">
         <f t="shared" si="0"/>
@@ -6507,10 +6498,10 @@
         <v>0</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
@@ -6520,27 +6511,26 @@
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A56" s="2"/>
-      <c r="B56" s="1"/>
       <c r="C56" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J56" s="1">
         <f t="shared" si="0"/>
@@ -6568,10 +6558,10 @@
         <v>0</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="S56" s="2"/>
       <c r="T56" s="2"/>
@@ -6581,27 +6571,26 @@
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A57" s="2"/>
-      <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J57" s="1">
         <f t="shared" si="0"/>
@@ -6629,10 +6618,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="S57" s="2"/>
       <c r="T57" s="2"/>
@@ -6642,27 +6631,26 @@
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A58" s="2"/>
-      <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J58" s="1">
         <f t="shared" si="0"/>
@@ -6690,10 +6678,10 @@
         <v>0</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="S58" s="2"/>
       <c r="T58" s="2"/>
@@ -6703,27 +6691,26 @@
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A59" s="2"/>
-      <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J59" s="1">
         <f t="shared" si="0"/>
@@ -6751,10 +6738,10 @@
         <v>0</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="S59" s="2"/>
       <c r="T59" s="2"/>
@@ -6764,27 +6751,26 @@
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A60" s="2"/>
-      <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J60" s="1">
         <f t="shared" si="0"/>
@@ -6812,10 +6798,10 @@
         <v>0</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="S60" s="2"/>
       <c r="T60" s="2"/>
@@ -6825,27 +6811,26 @@
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A61" s="2"/>
-      <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J61" s="1">
         <f t="shared" si="0"/>
@@ -6873,10 +6858,10 @@
         <v>0</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="S61" s="2"/>
       <c r="T61" s="2"/>
@@ -6886,27 +6871,26 @@
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A62" s="2"/>
-      <c r="B62" s="1"/>
       <c r="C62" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J62" s="1">
         <f t="shared" si="0"/>
@@ -6934,10 +6918,10 @@
         <v>0</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="S62" s="2"/>
       <c r="T62" s="2"/>
@@ -6947,27 +6931,26 @@
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A63" s="2"/>
-      <c r="B63" s="1"/>
       <c r="C63" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J63" s="1">
         <f t="shared" si="0"/>
@@ -6995,10 +6978,10 @@
         <v>0</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="S63" s="2"/>
       <c r="T63" s="2"/>
@@ -7008,27 +6991,26 @@
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A64" s="2"/>
-      <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J64" s="1">
         <f t="shared" si="0"/>
@@ -7056,10 +7038,10 @@
         <v>0</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="S64" s="2"/>
       <c r="T64" s="2"/>
@@ -7069,27 +7051,26 @@
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A65" s="2"/>
-      <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J65" s="1">
         <f t="shared" si="0"/>
@@ -7117,10 +7098,10 @@
         <v>0</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="S65" s="2"/>
       <c r="T65" s="2"/>
@@ -7130,27 +7111,26 @@
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A66" s="2"/>
-      <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J66" s="1">
         <f t="shared" ref="J66:M66" si="4">J65+5</f>
@@ -7178,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="S66" s="2"/>
       <c r="T66" s="2"/>
@@ -7191,27 +7171,26 @@
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A67" s="2"/>
-      <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J67" s="1">
         <f t="shared" ref="J66:J71" si="6">J66+5</f>
@@ -7239,10 +7218,10 @@
         <v>0</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="S67" s="2"/>
       <c r="T67" s="2"/>
@@ -7252,27 +7231,26 @@
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A68" s="2"/>
-      <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J68" s="1">
         <f t="shared" si="6"/>
@@ -7300,10 +7278,10 @@
         <v>0</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="S68" s="2"/>
       <c r="T68" s="2"/>
@@ -7313,27 +7291,26 @@
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A69" s="2"/>
-      <c r="B69" s="1"/>
       <c r="C69" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J69" s="1">
         <f t="shared" si="6"/>
@@ -7361,10 +7338,10 @@
         <v>0</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="S69" s="2"/>
       <c r="T69" s="2"/>
@@ -7374,27 +7351,26 @@
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A70" s="2"/>
-      <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J70" s="1">
         <f t="shared" si="6"/>
@@ -7422,10 +7398,10 @@
         <v>0</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="S70" s="2"/>
       <c r="T70" s="2"/>
@@ -7435,27 +7411,26 @@
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A71" s="2"/>
-      <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J71" s="1">
         <f>J70+15</f>
@@ -7483,10 +7458,10 @@
         <v>0</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="S71" s="2"/>
       <c r="T71" s="2"/>
@@ -7496,27 +7471,26 @@
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A72" s="2"/>
-      <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J72" s="1">
         <f t="shared" ref="J71:J81" si="10">J71+15</f>
@@ -7544,10 +7518,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="S72" s="2"/>
       <c r="T72" s="2"/>
@@ -7557,27 +7531,26 @@
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A73" s="2"/>
-      <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J73" s="1">
         <f t="shared" si="10"/>
@@ -7605,10 +7578,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="S73" s="2"/>
       <c r="T73" s="2"/>
@@ -7618,27 +7591,26 @@
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A74" s="2"/>
-      <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J74" s="1">
         <f t="shared" si="10"/>
@@ -7666,10 +7638,10 @@
         <v>0</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="S74" s="2"/>
       <c r="T74" s="2"/>
@@ -7679,27 +7651,26 @@
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A75" s="2"/>
-      <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="J75" s="1">
         <f t="shared" si="10"/>
@@ -7727,10 +7698,10 @@
         <v>0</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="R75" s="10" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="S75" s="2"/>
       <c r="T75" s="2"/>
@@ -7742,25 +7713,25 @@
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E76" s="1">
         <v>3</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="J76" s="1">
         <f t="shared" si="10"/>
@@ -7801,25 +7772,25 @@
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E77" s="1">
         <v>3</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J77" s="1">
         <f t="shared" si="10"/>
@@ -7860,25 +7831,25 @@
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E78" s="1">
         <v>3</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J78" s="1">
         <f t="shared" si="10"/>
@@ -7919,25 +7890,25 @@
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E79" s="1">
         <v>3</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J79" s="1">
         <f t="shared" si="10"/>
@@ -7978,25 +7949,25 @@
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E80" s="1">
         <v>3</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J80" s="1">
         <f t="shared" si="10"/>
@@ -8037,25 +8008,25 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E81" s="1">
         <v>3</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J81" s="1">
         <f t="shared" ref="J81:J91" si="13">J80+25</f>
@@ -8098,25 +8069,25 @@
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E82" s="1">
         <v>3</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J82" s="1">
         <f t="shared" si="13"/>
@@ -8159,25 +8130,25 @@
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E83" s="1">
         <v>3</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J83" s="1">
         <f t="shared" si="13"/>
@@ -8220,25 +8191,25 @@
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E84" s="1">
         <v>3</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="J84" s="1">
         <f t="shared" si="13"/>
@@ -8281,25 +8252,25 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E85" s="1">
         <v>3</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J85" s="1">
         <f t="shared" si="13"/>
@@ -8342,25 +8313,25 @@
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E86" s="1">
         <v>3</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J86" s="1">
         <f t="shared" si="13"/>
@@ -8403,25 +8374,25 @@
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E87" s="1">
         <v>3</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="J87" s="1">
         <f t="shared" si="13"/>
@@ -8464,25 +8435,25 @@
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E88" s="1">
         <v>3</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="J88" s="1">
         <f t="shared" si="13"/>
@@ -8525,25 +8496,25 @@
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E89" s="1">
         <v>3</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J89" s="1">
         <f t="shared" si="13"/>
@@ -8586,25 +8557,25 @@
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E90" s="1">
         <v>3</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="J90" s="1">
         <f t="shared" si="13"/>
@@ -8647,25 +8618,25 @@
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E91" s="1">
         <v>3</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="J91" s="1">
         <f t="shared" ref="J91:J100" si="15">J90+30</f>
@@ -8708,25 +8679,25 @@
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E92" s="1">
         <v>3</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="J92" s="1">
         <f t="shared" si="15"/>
@@ -8769,25 +8740,25 @@
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E93" s="1">
         <v>3</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="J93" s="1">
         <f t="shared" si="15"/>
@@ -8830,25 +8801,25 @@
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E94" s="1">
         <v>3</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="J94" s="1">
         <f t="shared" si="15"/>
@@ -8891,25 +8862,25 @@
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E95" s="1">
         <v>3</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="J95" s="1">
         <f t="shared" si="15"/>
@@ -8950,25 +8921,25 @@
     </row>
     <row r="96" customHeight="1" spans="3:18">
       <c r="C96" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E96" s="1">
         <v>3</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="J96" s="1">
         <f t="shared" ref="J96:J105" si="19">J95+40</f>
@@ -9004,25 +8975,25 @@
     </row>
     <row r="97" customHeight="1" spans="3:18">
       <c r="C97" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E97" s="1">
         <v>3</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="J97" s="1">
         <f t="shared" si="19"/>
@@ -9058,25 +9029,25 @@
     </row>
     <row r="98" customHeight="1" spans="3:18">
       <c r="C98" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E98" s="1">
         <v>3</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="J98" s="1">
         <f t="shared" si="19"/>
@@ -9112,25 +9083,25 @@
     </row>
     <row r="99" customHeight="1" spans="3:18">
       <c r="C99" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E99" s="1">
         <v>3</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="J99" s="1">
         <f t="shared" si="19"/>
@@ -9166,25 +9137,25 @@
     </row>
     <row r="100" customHeight="1" spans="3:18">
       <c r="C100" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E100" s="1">
         <v>3</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="J100" s="1">
         <f t="shared" si="19"/>
@@ -9220,25 +9191,25 @@
     </row>
     <row r="101" customHeight="1" spans="3:18">
       <c r="C101" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E101" s="1">
         <v>3</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="J101" s="1">
         <f t="shared" si="19"/>
@@ -9274,25 +9245,25 @@
     </row>
     <row r="102" customHeight="1" spans="3:18">
       <c r="C102" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E102" s="1">
         <v>3</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="J102" s="1">
         <f t="shared" si="19"/>
@@ -9328,25 +9299,25 @@
     </row>
     <row r="103" customHeight="1" spans="3:18">
       <c r="C103" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E103" s="1">
         <v>3</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="J103" s="1">
         <f t="shared" si="19"/>
@@ -9382,25 +9353,25 @@
     </row>
     <row r="104" customHeight="1" spans="3:18">
       <c r="C104" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E104" s="1">
         <v>3</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="J104" s="1">
         <f t="shared" si="19"/>
@@ -9436,25 +9407,25 @@
     </row>
     <row r="105" customHeight="1" spans="3:18">
       <c r="C105" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E105" s="1">
         <v>3</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="J105" s="1">
         <f t="shared" si="19"/>
@@ -9492,25 +9463,25 @@
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E106" s="1">
         <v>3</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="J106" s="1">
         <f t="shared" ref="J106:M106" si="23">J105+15</f>
@@ -9553,25 +9524,25 @@
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E107" s="1">
         <v>3</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="J107" s="1">
         <f t="shared" ref="J107:M107" si="24">J106+15</f>
@@ -9614,25 +9585,25 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E108" s="1">
         <v>3</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="J108" s="1">
         <f>J107+15</f>
@@ -9675,25 +9646,25 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E109" s="1">
         <v>3</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="J109" s="1">
         <f>J108+15</f>
@@ -9736,25 +9707,25 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E110" s="1">
         <v>3</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="J110" s="1">
         <f>J109+15</f>
@@ -9797,25 +9768,25 @@
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E111" s="1">
         <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="J111" s="1">
         <v>1400</v>
@@ -9839,10 +9810,10 @@
         <v>90</v>
       </c>
       <c r="Q111" s="10" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="R111" s="10" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="U111" s="2"/>
       <c r="V111" s="2"/>
@@ -9852,25 +9823,25 @@
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E112" s="1">
         <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G112" s="14" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="H112" s="10" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="I112" s="15" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="J112" s="1">
         <f>J111+100</f>
@@ -9899,10 +9870,10 @@
         <v>90</v>
       </c>
       <c r="Q112" s="10" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="R112" s="10" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="U112" s="2"/>
       <c r="V112" s="2"/>
@@ -9912,25 +9883,25 @@
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E113" s="1">
         <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="G113" s="14" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="I113" s="15" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="J113" s="1">
         <f>J112+100</f>
@@ -9959,10 +9930,10 @@
         <v>90</v>
       </c>
       <c r="Q113" s="10" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="R113" s="10" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="U113" s="2"/>
       <c r="V113" s="2"/>
@@ -9972,25 +9943,25 @@
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E114" s="1">
         <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="G114" s="14" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="H114" s="10" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="I114" s="15" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="J114" s="1">
         <f>J113+100</f>
@@ -10019,10 +9990,10 @@
         <v>90</v>
       </c>
       <c r="Q114" s="10" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="R114" s="10" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="U114" s="2"/>
       <c r="V114" s="2"/>
@@ -10032,25 +10003,25 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E115" s="1">
         <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="G115" s="14" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="I115" s="15" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="J115" s="1">
         <f>J114+100</f>
@@ -10079,10 +10050,10 @@
         <v>90</v>
       </c>
       <c r="Q115" s="10" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="R115" s="10" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="U115" s="2"/>
       <c r="V115" s="2"/>
@@ -10092,25 +10063,25 @@
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E116" s="1">
         <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="G116" s="14" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="H116" s="10" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="I116" s="15" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="J116" s="1">
         <f t="shared" ref="J116:J145" si="29">J115+200</f>
@@ -10139,10 +10110,10 @@
         <v>90</v>
       </c>
       <c r="Q116" s="10" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="R116" s="10" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="S116" s="2"/>
       <c r="T116" s="2"/>
@@ -10154,25 +10125,25 @@
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E117" s="1">
         <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G117" s="14" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="I117" s="15" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="J117" s="1">
         <f t="shared" si="29"/>
@@ -10201,10 +10172,10 @@
         <v>90</v>
       </c>
       <c r="Q117" s="10" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="R117" s="10" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="S117" s="2"/>
       <c r="T117" s="2"/>
@@ -10216,25 +10187,25 @@
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E118" s="1">
         <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="G118" s="14" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="I118" s="15" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="J118" s="1">
         <f t="shared" si="29"/>
@@ -10263,10 +10234,10 @@
         <v>90</v>
       </c>
       <c r="Q118" s="10" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="R118" s="10" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="S118" s="2"/>
       <c r="T118" s="2"/>
@@ -10278,25 +10249,25 @@
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E119" s="1">
         <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="G119" s="14" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="I119" s="15" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="J119" s="1">
         <f t="shared" si="29"/>
@@ -10325,10 +10296,10 @@
         <v>90</v>
       </c>
       <c r="Q119" s="10" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="R119" s="10" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="S119" s="2"/>
       <c r="T119" s="2"/>
@@ -10340,25 +10311,25 @@
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="1" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E120" s="1">
         <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="G120" s="14" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="I120" s="15" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="J120" s="1">
         <f t="shared" si="29"/>
@@ -10387,10 +10358,10 @@
         <v>90</v>
       </c>
       <c r="Q120" s="10" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="R120" s="10" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="S120" s="2"/>
       <c r="T120" s="2"/>
@@ -10402,25 +10373,25 @@
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G121" s="14" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="I121" s="15" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="J121" s="1">
         <f t="shared" si="29"/>
@@ -10449,10 +10420,10 @@
         <v>90</v>
       </c>
       <c r="Q121" s="10" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="R121" s="10" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="S121" s="2"/>
       <c r="T121" s="2"/>
@@ -10464,25 +10435,25 @@
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G122" s="14" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="I122" s="15" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="J122" s="1">
         <f t="shared" si="29"/>
@@ -10512,10 +10483,10 @@
         <v>90</v>
       </c>
       <c r="Q122" s="10" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="R122" s="10" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="S122" s="2"/>
       <c r="T122" s="2"/>
@@ -10527,25 +10498,25 @@
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="G123" s="14" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="I123" s="15" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="J123" s="1">
         <f t="shared" si="29"/>
@@ -10575,10 +10546,10 @@
         <v>90</v>
       </c>
       <c r="Q123" s="10" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="R123" s="10" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="S123" s="2"/>
       <c r="T123" s="2"/>
@@ -10590,25 +10561,25 @@
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="1" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="G124" s="14" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="I124" s="15" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="J124" s="1">
         <f t="shared" si="29"/>
@@ -10638,10 +10609,10 @@
         <v>90</v>
       </c>
       <c r="Q124" s="10" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="R124" s="10" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="S124" s="2"/>
       <c r="T124" s="2"/>
@@ -10653,25 +10624,25 @@
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="1" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="G125" s="14" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="I125" s="15" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="J125" s="1">
         <f t="shared" si="29"/>
@@ -10701,10 +10672,10 @@
         <v>90</v>
       </c>
       <c r="Q125" s="10" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="R125" s="10" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="S125" s="2"/>
       <c r="T125" s="2"/>
@@ -10716,25 +10687,25 @@
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="G126" s="14" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="I126" s="15" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="J126" s="1">
         <f t="shared" si="29"/>
@@ -10763,10 +10734,10 @@
         <v>90</v>
       </c>
       <c r="Q126" s="10" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="R126" s="10" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="S126" s="2"/>
       <c r="T126" s="2"/>
@@ -10778,25 +10749,25 @@
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="G127" s="14" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="I127" s="15" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="J127" s="1">
         <f t="shared" si="29"/>
@@ -10825,10 +10796,10 @@
         <v>90</v>
       </c>
       <c r="Q127" s="10" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="R127" s="10" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="S127" s="2"/>
       <c r="T127" s="2"/>
@@ -10840,25 +10811,25 @@
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="1" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G128" s="14" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="I128" s="15" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="J128" s="1">
         <f t="shared" si="29"/>
@@ -10887,10 +10858,10 @@
         <v>90</v>
       </c>
       <c r="Q128" s="10" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="R128" s="10" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="S128" s="2"/>
       <c r="T128" s="2"/>
@@ -10902,25 +10873,25 @@
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="1" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="G129" s="14" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="I129" s="15" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="J129" s="1">
         <f t="shared" si="29"/>
@@ -10949,10 +10920,10 @@
         <v>90</v>
       </c>
       <c r="Q129" s="10" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="R129" s="10" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="S129" s="2"/>
       <c r="T129" s="2"/>
@@ -10964,25 +10935,25 @@
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="G130" s="14" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="I130" s="15" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="J130" s="1">
         <f t="shared" si="29"/>
@@ -11011,10 +10982,10 @@
         <v>90</v>
       </c>
       <c r="Q130" s="10" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="R130" s="10" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="S130" s="2"/>
       <c r="T130" s="2"/>
@@ -11024,31 +10995,31 @@
     </row>
     <row r="131" customHeight="1" spans="1:18">
       <c r="A131" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="G131" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H131" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I131" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J131" s="1">
         <f t="shared" si="29"/>
@@ -11077,39 +11048,39 @@
         <v>90</v>
       </c>
       <c r="Q131" s="10" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="R131" s="10" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="1:18">
       <c r="A132" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="G132" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H132" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I132" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J132" s="1">
         <f t="shared" si="29"/>
@@ -11138,39 +11109,39 @@
         <v>90</v>
       </c>
       <c r="Q132" s="10" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="R132" s="10" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:18">
       <c r="A133" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="G133" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H133" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I133" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J133" s="1">
         <f t="shared" si="29"/>
@@ -11199,39 +11170,39 @@
         <v>90</v>
       </c>
       <c r="Q133" s="10" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="R133" s="10" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:18">
       <c r="A134" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="G134" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H134" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I134" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J134" s="1">
         <f t="shared" si="29"/>
@@ -11260,39 +11231,39 @@
         <v>90</v>
       </c>
       <c r="Q134" s="10" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="R134" s="10" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:18">
       <c r="A135" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="G135" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H135" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I135" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J135" s="1">
         <f t="shared" si="29"/>
@@ -11321,39 +11292,39 @@
         <v>90</v>
       </c>
       <c r="Q135" s="10" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="R135" s="10" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:18">
       <c r="A136" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="G136" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H136" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I136" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J136" s="1">
         <f t="shared" si="29"/>
@@ -11382,39 +11353,39 @@
         <v>90</v>
       </c>
       <c r="Q136" s="10" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="R136" s="10" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="1:18">
       <c r="A137" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="G137" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H137" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I137" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J137" s="1">
         <f t="shared" si="29"/>
@@ -11443,39 +11414,39 @@
         <v>90</v>
       </c>
       <c r="Q137" s="10" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="R137" s="10" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:18">
       <c r="A138" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H138" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I138" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J138" s="1">
         <f t="shared" si="29"/>
@@ -11504,39 +11475,39 @@
         <v>90</v>
       </c>
       <c r="Q138" s="10" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="R138" s="10" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:18">
       <c r="A139" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="G139" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H139" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I139" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J139" s="1">
         <f t="shared" si="29"/>
@@ -11565,39 +11536,39 @@
         <v>90</v>
       </c>
       <c r="Q139" s="10" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="R139" s="10" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:18">
       <c r="A140" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="G140" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H140" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I140" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J140" s="1">
         <f t="shared" si="29"/>
@@ -11626,39 +11597,39 @@
         <v>90</v>
       </c>
       <c r="Q140" s="10" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="R140" s="10" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A141" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="G141" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H141" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I141" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J141" s="1">
         <f t="shared" si="29"/>
@@ -11687,10 +11658,10 @@
         <v>90</v>
       </c>
       <c r="Q141" s="10" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="R141" s="10" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="S141" s="2"/>
       <c r="T141" s="2"/>
@@ -11700,31 +11671,31 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A142" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="G142" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H142" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I142" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J142" s="1">
         <f t="shared" si="29"/>
@@ -11753,10 +11724,10 @@
         <v>90</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="R142" s="10" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="S142" s="2"/>
       <c r="T142" s="2"/>
@@ -11766,31 +11737,31 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A143" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="G143" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H143" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I143" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J143" s="1">
         <f t="shared" si="29"/>
@@ -11819,10 +11790,10 @@
         <v>90</v>
       </c>
       <c r="Q143" s="10" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="R143" s="10" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="S143" s="2"/>
       <c r="T143" s="2"/>
@@ -11832,31 +11803,31 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A144" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="G144" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H144" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I144" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J144" s="1">
         <f t="shared" si="29"/>
@@ -11885,10 +11856,10 @@
         <v>90</v>
       </c>
       <c r="Q144" s="10" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="R144" s="10" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="S144" s="2"/>
       <c r="T144" s="2"/>
@@ -11898,31 +11869,31 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A145" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="G145" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H145" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I145" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J145" s="1">
         <f t="shared" si="29"/>
@@ -11951,10 +11922,10 @@
         <v>90</v>
       </c>
       <c r="Q145" s="10" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="R145" s="10" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="S145" s="2"/>
       <c r="T145" s="2"/>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="895">
   <si>
     <t>ID</t>
   </si>
@@ -107,6 +107,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
@@ -2504,76 +2507,109 @@
     <t>8000000000</t>
   </si>
   <si>
+    <t>10126</t>
+  </si>
+  <si>
+    <t>1125</t>
+  </si>
+  <si>
+    <t>地狱恶魔</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>8400000000</t>
+  </si>
+  <si>
+    <t>10127</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>地狱勇士</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>20000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>8800000000</t>
+  </si>
+  <si>
+    <t>10128</t>
+  </si>
+  <si>
+    <t>1127</t>
+  </si>
+  <si>
+    <t>地狱雕像</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>400000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>9200000000</t>
+  </si>
+  <si>
+    <t>10129</t>
+  </si>
+  <si>
+    <t>1128</t>
+  </si>
+  <si>
+    <t>地狱卫士</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>8000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>9600000000</t>
+  </si>
+  <si>
+    <t>10130</t>
+  </si>
+  <si>
+    <t>1129</t>
+  </si>
+  <si>
+    <t>地狱魔猪</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>160000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>10000000000</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
-    <t>10126</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>地狱恶魔</t>
+    <t>10131</t>
+  </si>
+  <si>
+    <t>1130</t>
+  </si>
+  <si>
+    <t>地狱树妖</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>5100000000</t>
-  </si>
-  <si>
-    <t>10127</t>
-  </si>
-  <si>
-    <t>1126</t>
-  </si>
-  <si>
-    <t>地狱勇士</t>
-  </si>
-  <si>
-    <t>10128</t>
-  </si>
-  <si>
-    <t>1127</t>
-  </si>
-  <si>
-    <t>地狱雕像</t>
-  </si>
-  <si>
-    <t>5300000000</t>
-  </si>
-  <si>
-    <t>10129</t>
-  </si>
-  <si>
-    <t>1128</t>
-  </si>
-  <si>
-    <t>地狱卫士</t>
-  </si>
-  <si>
-    <t>5400000000</t>
-  </si>
-  <si>
-    <t>10130</t>
-  </si>
-  <si>
-    <t>1129</t>
-  </si>
-  <si>
-    <t>地狱魔猪</t>
-  </si>
-  <si>
-    <t>5500000000</t>
-  </si>
-  <si>
-    <t>10131</t>
-  </si>
-  <si>
-    <t>1130</t>
-  </si>
-  <si>
-    <t>地狱树妖</t>
   </si>
   <si>
     <t>10132</t>
@@ -3656,9 +3692,9 @@
     <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="41.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="41.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="56.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="47.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="47.4166666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="59.5" style="2" customWidth="1"/>
     <col min="10" max="10" width="12.75" style="2" customWidth="1"/>
     <col min="11" max="11" width="9.375" style="2" customWidth="1"/>
     <col min="12" max="12" width="9.125" style="2" customWidth="1"/>
@@ -3867,39 +3903,39 @@
         <v>24</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" spans="3:18">
+    <row r="6" ht="14" spans="3:18">
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -3923,133 +3959,133 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:18">
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="R7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:18">
       <c r="C8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="R8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:18">
       <c r="C9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -4073,83 +4109,83 @@
         <v>0</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:18">
       <c r="C10" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="R10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:18">
       <c r="C11" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J11" s="1">
         <v>0</v>
@@ -4173,33 +4209,33 @@
         <v>0</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:18">
       <c r="C12" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -4223,33 +4259,33 @@
         <v>0</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:18">
       <c r="C13" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J13" s="1">
         <v>0</v>
@@ -4273,33 +4309,33 @@
         <v>0</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:18">
       <c r="C14" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J14" s="1">
         <v>0</v>
@@ -4323,33 +4359,33 @@
         <v>0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:18">
       <c r="C15" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
@@ -4373,33 +4409,33 @@
         <v>0</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:18">
       <c r="C16" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J16" s="1">
         <v>0</v>
@@ -4423,33 +4459,33 @@
         <v>0</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:18">
       <c r="C17" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
@@ -4473,33 +4509,33 @@
         <v>0</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:18">
       <c r="C18" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
@@ -4523,33 +4559,33 @@
         <v>0</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:18">
       <c r="C19" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J19" s="1">
         <v>0</v>
@@ -4573,33 +4609,33 @@
         <v>0</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:18">
       <c r="C20" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J20" s="1">
         <v>0</v>
@@ -4623,33 +4659,33 @@
         <v>0</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:18">
       <c r="C21" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J21" s="1">
         <f t="shared" ref="J21:J66" si="0">(D21-1014)*3</f>
@@ -4674,33 +4710,33 @@
         <v>0</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:18">
       <c r="C22" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J22" s="1">
         <f t="shared" si="0"/>
@@ -4725,33 +4761,33 @@
         <v>0</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:18">
       <c r="C23" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" si="0"/>
@@ -4776,33 +4812,33 @@
         <v>0</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:18">
       <c r="C24" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" si="0"/>
@@ -4827,33 +4863,33 @@
         <v>0</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:18">
       <c r="C25" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J25" s="1">
         <f t="shared" si="0"/>
@@ -4878,33 +4914,33 @@
         <v>0</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:18">
       <c r="C26" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J26" s="1">
         <f t="shared" si="0"/>
@@ -4929,33 +4965,33 @@
         <v>0</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:18">
       <c r="C27" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" si="0"/>
@@ -4980,33 +5016,33 @@
         <v>0</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:18">
       <c r="C28" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J28" s="1">
         <f t="shared" si="0"/>
@@ -5031,33 +5067,33 @@
         <v>0</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:18">
       <c r="C29" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J29" s="1">
         <f t="shared" si="0"/>
@@ -5082,33 +5118,33 @@
         <v>0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:18">
       <c r="C30" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J30" s="1">
         <f t="shared" si="0"/>
@@ -5133,33 +5169,33 @@
         <v>0</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:18">
       <c r="C31" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J31" s="1">
         <f t="shared" si="0"/>
@@ -5184,33 +5220,33 @@
         <v>0</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:18">
       <c r="C32" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J32" s="1">
         <f t="shared" si="0"/>
@@ -5235,33 +5271,33 @@
         <v>0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:18">
       <c r="C33" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J33" s="1">
         <f t="shared" si="0"/>
@@ -5286,33 +5322,33 @@
         <v>0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:18">
       <c r="C34" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J34" s="1">
         <f t="shared" si="0"/>
@@ -5337,33 +5373,33 @@
         <v>0</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:18">
       <c r="C35" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J35" s="1">
         <f t="shared" si="0"/>
@@ -5388,33 +5424,33 @@
         <v>0</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:18">
       <c r="C36" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" si="0"/>
@@ -5439,33 +5475,33 @@
         <v>0</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:18">
       <c r="C37" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" si="0"/>
@@ -5490,33 +5526,33 @@
         <v>0</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:18">
       <c r="C38" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J38" s="1">
         <f t="shared" si="0"/>
@@ -5541,33 +5577,33 @@
         <v>0</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:18">
       <c r="C39" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J39" s="1">
         <f t="shared" si="0"/>
@@ -5592,33 +5628,33 @@
         <v>0</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:18">
       <c r="C40" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J40" s="1">
         <f t="shared" si="0"/>
@@ -5643,34 +5679,34 @@
         <v>0</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A41" s="2"/>
       <c r="C41" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J41" s="1">
         <f t="shared" si="0"/>
@@ -5695,10 +5731,10 @@
         <v>0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
@@ -5707,25 +5743,25 @@
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A42" s="2"/>
       <c r="C42" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J42" s="1">
         <f t="shared" si="0"/>
@@ -5750,10 +5786,10 @@
         <v>0</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
@@ -5762,25 +5798,25 @@
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A43" s="2"/>
       <c r="C43" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J43" s="1">
         <f t="shared" si="0"/>
@@ -5805,10 +5841,10 @@
         <v>0</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
@@ -5817,25 +5853,25 @@
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A44" s="2"/>
       <c r="C44" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J44" s="1">
         <f t="shared" si="0"/>
@@ -5860,10 +5896,10 @@
         <v>0</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
@@ -5872,25 +5908,25 @@
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A45" s="2"/>
       <c r="C45" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J45" s="1">
         <f t="shared" si="0"/>
@@ -5915,10 +5951,10 @@
         <v>0</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
@@ -5927,25 +5963,25 @@
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A46" s="2"/>
       <c r="C46" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J46" s="1">
         <f t="shared" si="0"/>
@@ -5970,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
@@ -5984,25 +6020,25 @@
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A47" s="2"/>
       <c r="C47" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J47" s="1">
         <f t="shared" si="0"/>
@@ -6027,10 +6063,10 @@
         <v>0</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S47" s="2"/>
       <c r="T47" s="2"/>
@@ -6041,25 +6077,25 @@
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A48" s="2"/>
       <c r="C48" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J48" s="1">
         <f t="shared" si="0"/>
@@ -6084,10 +6120,10 @@
         <v>0</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="S48" s="2"/>
       <c r="T48" s="2"/>
@@ -6098,25 +6134,25 @@
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A49" s="2"/>
       <c r="C49" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J49" s="1">
         <f t="shared" si="0"/>
@@ -6141,10 +6177,10 @@
         <v>0</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="S49" s="2"/>
       <c r="T49" s="2"/>
@@ -6155,25 +6191,25 @@
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A50" s="2"/>
       <c r="C50" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J50" s="1">
         <f t="shared" si="0"/>
@@ -6198,10 +6234,10 @@
         <v>0</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="S50" s="2"/>
       <c r="T50" s="2"/>
@@ -6212,25 +6248,25 @@
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A51" s="2"/>
       <c r="C51" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J51" s="1">
         <f t="shared" si="0"/>
@@ -6258,10 +6294,10 @@
         <v>0</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S51" s="2"/>
       <c r="T51" s="2"/>
@@ -6272,25 +6308,25 @@
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A52" s="2"/>
       <c r="C52" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J52" s="1">
         <f t="shared" si="0"/>
@@ -6318,10 +6354,10 @@
         <v>0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="S52" s="2"/>
       <c r="T52" s="2"/>
@@ -6332,25 +6368,25 @@
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A53" s="2"/>
       <c r="C53" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J53" s="1">
         <f t="shared" si="0"/>
@@ -6378,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="S53" s="2"/>
       <c r="T53" s="2"/>
@@ -6392,25 +6428,25 @@
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A54" s="2"/>
       <c r="C54" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J54" s="1">
         <f t="shared" si="0"/>
@@ -6438,10 +6474,10 @@
         <v>0</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S54" s="2"/>
       <c r="T54" s="2"/>
@@ -6452,25 +6488,25 @@
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A55" s="2"/>
       <c r="C55" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J55" s="1">
         <f t="shared" si="0"/>
@@ -6498,10 +6534,10 @@
         <v>0</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
@@ -6512,25 +6548,25 @@
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A56" s="2"/>
       <c r="C56" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J56" s="1">
         <f t="shared" si="0"/>
@@ -6558,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="S56" s="2"/>
       <c r="T56" s="2"/>
@@ -6572,25 +6608,25 @@
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A57" s="2"/>
       <c r="C57" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J57" s="1">
         <f t="shared" si="0"/>
@@ -6618,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="S57" s="2"/>
       <c r="T57" s="2"/>
@@ -6632,25 +6668,25 @@
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A58" s="2"/>
       <c r="C58" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J58" s="1">
         <f t="shared" si="0"/>
@@ -6678,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="S58" s="2"/>
       <c r="T58" s="2"/>
@@ -6692,25 +6728,25 @@
     <row r="59" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A59" s="2"/>
       <c r="C59" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J59" s="1">
         <f t="shared" si="0"/>
@@ -6738,10 +6774,10 @@
         <v>0</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="S59" s="2"/>
       <c r="T59" s="2"/>
@@ -6752,25 +6788,25 @@
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A60" s="2"/>
       <c r="C60" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J60" s="1">
         <f t="shared" si="0"/>
@@ -6798,10 +6834,10 @@
         <v>0</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="S60" s="2"/>
       <c r="T60" s="2"/>
@@ -6812,25 +6848,25 @@
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A61" s="2"/>
       <c r="C61" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J61" s="1">
         <f t="shared" si="0"/>
@@ -6858,10 +6894,10 @@
         <v>0</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="S61" s="2"/>
       <c r="T61" s="2"/>
@@ -6872,25 +6908,25 @@
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A62" s="2"/>
       <c r="C62" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J62" s="1">
         <f t="shared" si="0"/>
@@ -6918,10 +6954,10 @@
         <v>0</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="S62" s="2"/>
       <c r="T62" s="2"/>
@@ -6932,25 +6968,25 @@
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A63" s="2"/>
       <c r="C63" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J63" s="1">
         <f t="shared" si="0"/>
@@ -6978,10 +7014,10 @@
         <v>0</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="S63" s="2"/>
       <c r="T63" s="2"/>
@@ -6992,25 +7028,25 @@
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A64" s="2"/>
       <c r="C64" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J64" s="1">
         <f t="shared" si="0"/>
@@ -7038,10 +7074,10 @@
         <v>0</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="S64" s="2"/>
       <c r="T64" s="2"/>
@@ -7052,25 +7088,25 @@
     <row r="65" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A65" s="2"/>
       <c r="C65" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J65" s="1">
         <f t="shared" si="0"/>
@@ -7098,10 +7134,10 @@
         <v>0</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="S65" s="2"/>
       <c r="T65" s="2"/>
@@ -7112,25 +7148,25 @@
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A66" s="2"/>
       <c r="C66" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J66" s="1">
         <f t="shared" ref="J66:M66" si="4">J65+5</f>
@@ -7158,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="S66" s="2"/>
       <c r="T66" s="2"/>
@@ -7172,25 +7208,25 @@
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A67" s="2"/>
       <c r="C67" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J67" s="1">
         <f t="shared" ref="J66:J71" si="6">J66+5</f>
@@ -7218,10 +7254,10 @@
         <v>0</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="S67" s="2"/>
       <c r="T67" s="2"/>
@@ -7232,25 +7268,25 @@
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A68" s="2"/>
       <c r="C68" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J68" s="1">
         <f t="shared" si="6"/>
@@ -7278,10 +7314,10 @@
         <v>0</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="S68" s="2"/>
       <c r="T68" s="2"/>
@@ -7292,25 +7328,25 @@
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A69" s="2"/>
       <c r="C69" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J69" s="1">
         <f t="shared" si="6"/>
@@ -7338,10 +7374,10 @@
         <v>0</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="S69" s="2"/>
       <c r="T69" s="2"/>
@@ -7352,25 +7388,25 @@
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A70" s="2"/>
       <c r="C70" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J70" s="1">
         <f t="shared" si="6"/>
@@ -7398,10 +7434,10 @@
         <v>0</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="S70" s="2"/>
       <c r="T70" s="2"/>
@@ -7412,25 +7448,25 @@
     <row r="71" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A71" s="2"/>
       <c r="C71" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J71" s="1">
         <f>J70+15</f>
@@ -7458,10 +7494,10 @@
         <v>0</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="S71" s="2"/>
       <c r="T71" s="2"/>
@@ -7472,25 +7508,25 @@
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A72" s="2"/>
       <c r="C72" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J72" s="1">
         <f t="shared" ref="J71:J81" si="10">J71+15</f>
@@ -7518,10 +7554,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="S72" s="2"/>
       <c r="T72" s="2"/>
@@ -7532,25 +7568,25 @@
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A73" s="2"/>
       <c r="C73" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J73" s="1">
         <f t="shared" si="10"/>
@@ -7578,10 +7614,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="S73" s="2"/>
       <c r="T73" s="2"/>
@@ -7592,25 +7628,25 @@
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A74" s="2"/>
       <c r="C74" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J74" s="1">
         <f t="shared" si="10"/>
@@ -7638,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="S74" s="2"/>
       <c r="T74" s="2"/>
@@ -7652,25 +7688,25 @@
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A75" s="2"/>
       <c r="C75" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J75" s="1">
         <f t="shared" si="10"/>
@@ -7698,10 +7734,10 @@
         <v>0</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="R75" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="S75" s="2"/>
       <c r="T75" s="2"/>
@@ -7713,25 +7749,25 @@
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E76" s="1">
         <v>3</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J76" s="1">
         <f t="shared" si="10"/>
@@ -7772,25 +7808,25 @@
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E77" s="1">
         <v>3</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J77" s="1">
         <f t="shared" si="10"/>
@@ -7831,25 +7867,25 @@
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E78" s="1">
         <v>3</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J78" s="1">
         <f t="shared" si="10"/>
@@ -7890,25 +7926,25 @@
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E79" s="1">
         <v>3</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J79" s="1">
         <f t="shared" si="10"/>
@@ -7949,25 +7985,25 @@
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E80" s="1">
         <v>3</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J80" s="1">
         <f t="shared" si="10"/>
@@ -8008,25 +8044,25 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E81" s="1">
         <v>3</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J81" s="1">
         <f t="shared" ref="J81:J91" si="13">J80+25</f>
@@ -8069,25 +8105,25 @@
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E82" s="1">
         <v>3</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J82" s="1">
         <f t="shared" si="13"/>
@@ -8130,25 +8166,25 @@
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E83" s="1">
         <v>3</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J83" s="1">
         <f t="shared" si="13"/>
@@ -8191,25 +8227,25 @@
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E84" s="1">
         <v>3</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J84" s="1">
         <f t="shared" si="13"/>
@@ -8252,25 +8288,25 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E85" s="1">
         <v>3</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J85" s="1">
         <f t="shared" si="13"/>
@@ -8313,25 +8349,25 @@
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E86" s="1">
         <v>3</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="J86" s="1">
         <f t="shared" si="13"/>
@@ -8374,25 +8410,25 @@
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E87" s="1">
         <v>3</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="J87" s="1">
         <f t="shared" si="13"/>
@@ -8435,25 +8471,25 @@
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E88" s="1">
         <v>3</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J88" s="1">
         <f t="shared" si="13"/>
@@ -8496,25 +8532,25 @@
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E89" s="1">
         <v>3</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="J89" s="1">
         <f t="shared" si="13"/>
@@ -8557,25 +8593,25 @@
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E90" s="1">
         <v>3</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J90" s="1">
         <f t="shared" si="13"/>
@@ -8618,25 +8654,25 @@
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E91" s="1">
         <v>3</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="J91" s="1">
         <f t="shared" ref="J91:J100" si="15">J90+30</f>
@@ -8679,25 +8715,25 @@
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E92" s="1">
         <v>3</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J92" s="1">
         <f t="shared" si="15"/>
@@ -8740,25 +8776,25 @@
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E93" s="1">
         <v>3</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J93" s="1">
         <f t="shared" si="15"/>
@@ -8801,25 +8837,25 @@
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E94" s="1">
         <v>3</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J94" s="1">
         <f t="shared" si="15"/>
@@ -8862,25 +8898,25 @@
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E95" s="1">
         <v>3</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J95" s="1">
         <f t="shared" si="15"/>
@@ -8921,25 +8957,25 @@
     </row>
     <row r="96" customHeight="1" spans="3:18">
       <c r="C96" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E96" s="1">
         <v>3</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J96" s="1">
         <f t="shared" ref="J96:J105" si="19">J95+40</f>
@@ -8975,25 +9011,25 @@
     </row>
     <row r="97" customHeight="1" spans="3:18">
       <c r="C97" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E97" s="1">
         <v>3</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J97" s="1">
         <f t="shared" si="19"/>
@@ -9029,25 +9065,25 @@
     </row>
     <row r="98" customHeight="1" spans="3:18">
       <c r="C98" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E98" s="1">
         <v>3</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="J98" s="1">
         <f t="shared" si="19"/>
@@ -9083,25 +9119,25 @@
     </row>
     <row r="99" customHeight="1" spans="3:18">
       <c r="C99" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E99" s="1">
         <v>3</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="J99" s="1">
         <f t="shared" si="19"/>
@@ -9137,25 +9173,25 @@
     </row>
     <row r="100" customHeight="1" spans="3:18">
       <c r="C100" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E100" s="1">
         <v>3</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="J100" s="1">
         <f t="shared" si="19"/>
@@ -9191,25 +9227,25 @@
     </row>
     <row r="101" customHeight="1" spans="3:18">
       <c r="C101" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E101" s="1">
         <v>3</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J101" s="1">
         <f t="shared" si="19"/>
@@ -9245,25 +9281,25 @@
     </row>
     <row r="102" customHeight="1" spans="3:18">
       <c r="C102" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E102" s="1">
         <v>3</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J102" s="1">
         <f t="shared" si="19"/>
@@ -9299,25 +9335,25 @@
     </row>
     <row r="103" customHeight="1" spans="3:18">
       <c r="C103" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E103" s="1">
         <v>3</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J103" s="1">
         <f t="shared" si="19"/>
@@ -9353,25 +9389,25 @@
     </row>
     <row r="104" customHeight="1" spans="3:18">
       <c r="C104" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E104" s="1">
         <v>3</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="J104" s="1">
         <f t="shared" si="19"/>
@@ -9407,25 +9443,25 @@
     </row>
     <row r="105" customHeight="1" spans="3:18">
       <c r="C105" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E105" s="1">
         <v>3</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="J105" s="1">
         <f t="shared" si="19"/>
@@ -9463,25 +9499,25 @@
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E106" s="1">
         <v>3</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="J106" s="1">
         <f t="shared" ref="J106:M106" si="23">J105+15</f>
@@ -9524,25 +9560,25 @@
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E107" s="1">
         <v>3</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J107" s="1">
         <f t="shared" ref="J107:M107" si="24">J106+15</f>
@@ -9585,25 +9621,25 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E108" s="1">
         <v>3</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J108" s="1">
         <f>J107+15</f>
@@ -9646,25 +9682,25 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E109" s="1">
         <v>3</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="J109" s="1">
         <f>J108+15</f>
@@ -9707,25 +9743,25 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E110" s="1">
         <v>3</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="J110" s="1">
         <f>J109+15</f>
@@ -9768,25 +9804,25 @@
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E111" s="1">
         <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="J111" s="1">
         <v>1400</v>
@@ -9810,10 +9846,10 @@
         <v>90</v>
       </c>
       <c r="Q111" s="10" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="R111" s="10" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="U111" s="2"/>
       <c r="V111" s="2"/>
@@ -9823,25 +9859,25 @@
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E112" s="1">
         <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G112" s="14" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H112" s="10" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I112" s="15" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="J112" s="1">
         <f>J111+100</f>
@@ -9870,10 +9906,10 @@
         <v>90</v>
       </c>
       <c r="Q112" s="10" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="R112" s="10" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="U112" s="2"/>
       <c r="V112" s="2"/>
@@ -9883,25 +9919,25 @@
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E113" s="1">
         <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G113" s="14" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I113" s="15" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J113" s="1">
         <f>J112+100</f>
@@ -9930,10 +9966,10 @@
         <v>90</v>
       </c>
       <c r="Q113" s="10" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="R113" s="10" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="U113" s="2"/>
       <c r="V113" s="2"/>
@@ -9943,25 +9979,25 @@
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E114" s="1">
         <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G114" s="14" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H114" s="10" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="I114" s="15" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="J114" s="1">
         <f>J113+100</f>
@@ -9990,10 +10026,10 @@
         <v>90</v>
       </c>
       <c r="Q114" s="10" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="R114" s="10" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="U114" s="2"/>
       <c r="V114" s="2"/>
@@ -10003,25 +10039,25 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E115" s="1">
         <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G115" s="14" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I115" s="15" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="J115" s="1">
         <f>J114+100</f>
@@ -10050,10 +10086,10 @@
         <v>90</v>
       </c>
       <c r="Q115" s="10" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="R115" s="10" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="U115" s="2"/>
       <c r="V115" s="2"/>
@@ -10063,25 +10099,25 @@
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E116" s="1">
         <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="G116" s="14" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H116" s="10" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I116" s="15" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J116" s="1">
         <f t="shared" ref="J116:J145" si="29">J115+200</f>
@@ -10110,10 +10146,10 @@
         <v>90</v>
       </c>
       <c r="Q116" s="10" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="R116" s="10" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="S116" s="2"/>
       <c r="T116" s="2"/>
@@ -10125,25 +10161,25 @@
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E117" s="1">
         <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="G117" s="14" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I117" s="15" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="J117" s="1">
         <f t="shared" si="29"/>
@@ -10172,10 +10208,10 @@
         <v>90</v>
       </c>
       <c r="Q117" s="10" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="R117" s="10" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="S117" s="2"/>
       <c r="T117" s="2"/>
@@ -10187,25 +10223,25 @@
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E118" s="1">
         <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G118" s="14" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="I118" s="15" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J118" s="1">
         <f t="shared" si="29"/>
@@ -10234,10 +10270,10 @@
         <v>90</v>
       </c>
       <c r="Q118" s="10" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="R118" s="10" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="S118" s="2"/>
       <c r="T118" s="2"/>
@@ -10249,25 +10285,25 @@
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E119" s="1">
         <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="G119" s="14" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="I119" s="15" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="J119" s="1">
         <f t="shared" si="29"/>
@@ -10296,10 +10332,10 @@
         <v>90</v>
       </c>
       <c r="Q119" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="R119" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="S119" s="2"/>
       <c r="T119" s="2"/>
@@ -10311,25 +10347,25 @@
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E120" s="1">
         <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="G120" s="14" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="I120" s="15" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J120" s="1">
         <f t="shared" si="29"/>
@@ -10358,10 +10394,10 @@
         <v>90</v>
       </c>
       <c r="Q120" s="10" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="R120" s="10" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="S120" s="2"/>
       <c r="T120" s="2"/>
@@ -10373,25 +10409,25 @@
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="G121" s="14" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I121" s="15" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J121" s="1">
         <f t="shared" si="29"/>
@@ -10420,10 +10456,10 @@
         <v>90</v>
       </c>
       <c r="Q121" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="R121" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="S121" s="2"/>
       <c r="T121" s="2"/>
@@ -10435,25 +10471,25 @@
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G122" s="14" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="I122" s="15" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="J122" s="1">
         <f t="shared" si="29"/>
@@ -10476,17 +10512,17 @@
         <v>41</v>
       </c>
       <c r="O122" s="2">
-        <f t="shared" ref="O122:O125" si="31">O121+3</f>
+        <f>O121+3</f>
         <v>6</v>
       </c>
       <c r="P122" s="2">
         <v>90</v>
       </c>
       <c r="Q122" s="10" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="R122" s="10" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="S122" s="2"/>
       <c r="T122" s="2"/>
@@ -10498,25 +10534,25 @@
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G123" s="14" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="I123" s="15" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="J123" s="1">
         <f t="shared" si="29"/>
@@ -10539,17 +10575,17 @@
         <v>42</v>
       </c>
       <c r="O123" s="2">
-        <f t="shared" si="31"/>
+        <f>O122+3</f>
         <v>9</v>
       </c>
       <c r="P123" s="2">
         <v>90</v>
       </c>
       <c r="Q123" s="10" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="R123" s="10" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="S123" s="2"/>
       <c r="T123" s="2"/>
@@ -10561,25 +10597,25 @@
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G124" s="14" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="I124" s="15" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="J124" s="1">
         <f t="shared" si="29"/>
@@ -10602,17 +10638,17 @@
         <v>43</v>
       </c>
       <c r="O124" s="2">
-        <f t="shared" si="31"/>
+        <f>O123+3</f>
         <v>12</v>
       </c>
       <c r="P124" s="2">
         <v>90</v>
       </c>
       <c r="Q124" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="R124" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="S124" s="2"/>
       <c r="T124" s="2"/>
@@ -10624,25 +10660,25 @@
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G125" s="14" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="I125" s="15" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="J125" s="1">
         <f t="shared" si="29"/>
@@ -10665,17 +10701,17 @@
         <v>44</v>
       </c>
       <c r="O125" s="2">
-        <f t="shared" si="31"/>
+        <f>O124+3</f>
         <v>15</v>
       </c>
       <c r="P125" s="2">
         <v>90</v>
       </c>
       <c r="Q125" s="10" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="R125" s="10" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="S125" s="2"/>
       <c r="T125" s="2"/>
@@ -10687,25 +10723,25 @@
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G126" s="14" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="I126" s="15" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J126" s="1">
         <f t="shared" si="29"/>
@@ -10727,17 +10763,18 @@
         <f t="shared" si="28"/>
         <v>45</v>
       </c>
-      <c r="O126" s="4">
-        <v>0</v>
+      <c r="O126" s="2">
+        <f>O125+3</f>
+        <v>18</v>
       </c>
       <c r="P126" s="2">
         <v>90</v>
       </c>
       <c r="Q126" s="10" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="R126" s="10" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="S126" s="2"/>
       <c r="T126" s="2"/>
@@ -10749,25 +10786,25 @@
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G127" s="14" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="I127" s="15" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="J127" s="1">
         <f t="shared" si="29"/>
@@ -10789,17 +10826,18 @@
         <f t="shared" si="28"/>
         <v>46</v>
       </c>
-      <c r="O127" s="4">
-        <v>0</v>
+      <c r="O127" s="2">
+        <f>O126+3</f>
+        <v>21</v>
       </c>
       <c r="P127" s="2">
         <v>90</v>
       </c>
       <c r="Q127" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="R127" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="S127" s="2"/>
       <c r="T127" s="2"/>
@@ -10811,25 +10849,25 @@
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G128" s="14" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I128" s="15" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="J128" s="1">
         <f t="shared" si="29"/>
@@ -10851,17 +10889,18 @@
         <f t="shared" si="28"/>
         <v>47</v>
       </c>
-      <c r="O128" s="4">
-        <v>0</v>
+      <c r="O128" s="2">
+        <f>O127+3</f>
+        <v>24</v>
       </c>
       <c r="P128" s="2">
         <v>90</v>
       </c>
       <c r="Q128" s="10" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="R128" s="10" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="S128" s="2"/>
       <c r="T128" s="2"/>
@@ -10873,25 +10912,25 @@
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G129" s="14" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="I129" s="15" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="J129" s="1">
         <f t="shared" si="29"/>
@@ -10913,17 +10952,18 @@
         <f t="shared" si="28"/>
         <v>48</v>
       </c>
-      <c r="O129" s="4">
-        <v>0</v>
+      <c r="O129" s="2">
+        <f>O128+3</f>
+        <v>27</v>
       </c>
       <c r="P129" s="2">
         <v>90</v>
       </c>
       <c r="Q129" s="10" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="R129" s="10" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="S129" s="2"/>
       <c r="T129" s="2"/>
@@ -10935,25 +10975,25 @@
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="G130" s="14" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I130" s="15" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="J130" s="1">
         <f t="shared" si="29"/>
@@ -10975,17 +11015,18 @@
         <f t="shared" si="28"/>
         <v>49</v>
       </c>
-      <c r="O130" s="4">
-        <v>0</v>
+      <c r="O130" s="2">
+        <f>O129+3</f>
+        <v>30</v>
       </c>
       <c r="P130" s="2">
         <v>90</v>
       </c>
       <c r="Q130" s="10" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="R130" s="10" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="S130" s="2"/>
       <c r="T130" s="2"/>
@@ -10993,13 +11034,7 @@
       <c r="V130" s="2"/>
       <c r="W130" s="2"/>
     </row>
-    <row r="131" customHeight="1" spans="1:18">
-      <c r="A131" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>825</v>
-      </c>
+    <row r="131" customHeight="1" spans="3:18">
       <c r="C131" s="1" t="s">
         <v>826</v>
       </c>
@@ -11015,653 +11050,640 @@
       <c r="G131" s="14" t="s">
         <v>829</v>
       </c>
-      <c r="H131" s="14" t="s">
+      <c r="H131" s="10" t="s">
         <v>829</v>
       </c>
-      <c r="I131" s="14" t="s">
-        <v>829</v>
+      <c r="I131" s="15" t="s">
+        <v>830</v>
       </c>
       <c r="J131" s="1">
-        <f t="shared" si="29"/>
-        <v>5000</v>
+        <f t="shared" ref="J131:J136" si="31">J130+300</f>
+        <v>5100</v>
       </c>
       <c r="K131" s="1">
-        <f t="shared" si="30"/>
-        <v>6300</v>
+        <f t="shared" ref="K131:K140" si="32">K130+400</f>
+        <v>6400</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" si="26"/>
-        <v>1900</v>
+        <f t="shared" ref="L131:L135" si="33">L130+100</f>
+        <v>1950</v>
       </c>
       <c r="M131" s="1">
-        <f t="shared" si="27"/>
-        <v>1900</v>
+        <f t="shared" ref="M131:M135" si="34">M130+100</f>
+        <v>1950</v>
       </c>
       <c r="N131" s="2">
-        <f t="shared" si="28"/>
-        <v>50</v>
-      </c>
-      <c r="O131" s="4">
-        <v>0</v>
+        <f t="shared" ref="N131:N145" si="35">N130+2</f>
+        <v>51</v>
+      </c>
+      <c r="O131" s="2">
+        <f t="shared" ref="O131:O145" si="36">O130+4</f>
+        <v>34</v>
       </c>
       <c r="P131" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q131" s="10" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="R131" s="10" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="132" customHeight="1" spans="1:18">
-      <c r="A132" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>825</v>
-      </c>
+        <v>831</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:18">
       <c r="C132" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="G132" s="14" t="s">
-        <v>829</v>
-      </c>
-      <c r="H132" s="14" t="s">
-        <v>829</v>
-      </c>
-      <c r="I132" s="14" t="s">
-        <v>829</v>
+        <v>835</v>
+      </c>
+      <c r="H132" s="10" t="s">
+        <v>835</v>
+      </c>
+      <c r="I132" s="15" t="s">
+        <v>836</v>
       </c>
       <c r="J132" s="1">
-        <f t="shared" si="29"/>
-        <v>5200</v>
+        <f t="shared" si="31"/>
+        <v>5400</v>
       </c>
       <c r="K132" s="1">
-        <f t="shared" si="30"/>
-        <v>6600</v>
+        <f t="shared" si="32"/>
+        <v>6800</v>
       </c>
       <c r="L132" s="1">
-        <f t="shared" si="26"/>
-        <v>1950</v>
+        <f t="shared" si="33"/>
+        <v>2050</v>
       </c>
       <c r="M132" s="1">
-        <f t="shared" si="27"/>
-        <v>1950</v>
+        <f t="shared" si="34"/>
+        <v>2050</v>
       </c>
       <c r="N132" s="2">
-        <f t="shared" si="28"/>
-        <v>51</v>
-      </c>
-      <c r="O132" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>53</v>
+      </c>
+      <c r="O132" s="2">
+        <f t="shared" si="36"/>
+        <v>38</v>
       </c>
       <c r="P132" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="Q132" s="10" t="s">
-        <v>782</v>
+        <v>837</v>
       </c>
       <c r="R132" s="10" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="133" customHeight="1" spans="1:18">
-      <c r="A133" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>825</v>
-      </c>
+        <v>837</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:18">
       <c r="C133" s="1" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="G133" s="14" t="s">
-        <v>829</v>
-      </c>
-      <c r="H133" s="14" t="s">
-        <v>829</v>
-      </c>
-      <c r="I133" s="14" t="s">
-        <v>829</v>
+        <v>841</v>
+      </c>
+      <c r="H133" s="10" t="s">
+        <v>841</v>
+      </c>
+      <c r="I133" s="15" t="s">
+        <v>842</v>
       </c>
       <c r="J133" s="1">
-        <f t="shared" si="29"/>
-        <v>5400</v>
+        <f t="shared" si="31"/>
+        <v>5700</v>
       </c>
       <c r="K133" s="1">
-        <f t="shared" si="30"/>
-        <v>6900</v>
+        <f t="shared" si="32"/>
+        <v>7200</v>
       </c>
       <c r="L133" s="1">
-        <f t="shared" si="26"/>
-        <v>2000</v>
+        <f t="shared" si="33"/>
+        <v>2150</v>
       </c>
       <c r="M133" s="1">
-        <f t="shared" si="27"/>
-        <v>2000</v>
+        <f t="shared" si="34"/>
+        <v>2150</v>
       </c>
       <c r="N133" s="2">
-        <f t="shared" si="28"/>
-        <v>52</v>
-      </c>
-      <c r="O133" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>55</v>
+      </c>
+      <c r="O133" s="2">
+        <f t="shared" si="36"/>
+        <v>42</v>
       </c>
       <c r="P133" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="Q133" s="10" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="R133" s="10" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="134" customHeight="1" spans="1:18">
-      <c r="A134" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>825</v>
-      </c>
+        <v>843</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:18">
       <c r="C134" s="1" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="G134" s="14" t="s">
-        <v>829</v>
-      </c>
-      <c r="H134" s="14" t="s">
-        <v>829</v>
-      </c>
-      <c r="I134" s="14" t="s">
-        <v>829</v>
+        <v>847</v>
+      </c>
+      <c r="H134" s="10" t="s">
+        <v>847</v>
+      </c>
+      <c r="I134" s="15" t="s">
+        <v>848</v>
       </c>
       <c r="J134" s="1">
-        <f t="shared" si="29"/>
-        <v>5600</v>
+        <f t="shared" si="31"/>
+        <v>6000</v>
       </c>
       <c r="K134" s="1">
-        <f t="shared" si="30"/>
-        <v>7200</v>
+        <f t="shared" si="32"/>
+        <v>7600</v>
       </c>
       <c r="L134" s="1">
-        <f t="shared" si="26"/>
-        <v>2050</v>
+        <f t="shared" si="33"/>
+        <v>2250</v>
       </c>
       <c r="M134" s="1">
-        <f t="shared" si="27"/>
-        <v>2050</v>
+        <f t="shared" si="34"/>
+        <v>2250</v>
       </c>
       <c r="N134" s="2">
-        <f t="shared" si="28"/>
-        <v>53</v>
-      </c>
-      <c r="O134" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>57</v>
+      </c>
+      <c r="O134" s="2">
+        <f t="shared" si="36"/>
+        <v>46</v>
       </c>
       <c r="P134" s="2">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="Q134" s="10" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="R134" s="10" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="135" customHeight="1" spans="1:18">
-      <c r="A135" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>825</v>
-      </c>
+        <v>849</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:18">
       <c r="C135" s="1" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="G135" s="14" t="s">
-        <v>829</v>
-      </c>
-      <c r="H135" s="14" t="s">
-        <v>829</v>
-      </c>
-      <c r="I135" s="14" t="s">
-        <v>829</v>
+        <v>853</v>
+      </c>
+      <c r="H135" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="I135" s="15" t="s">
+        <v>854</v>
       </c>
       <c r="J135" s="1">
-        <f t="shared" si="29"/>
-        <v>5800</v>
+        <f t="shared" si="31"/>
+        <v>6300</v>
       </c>
       <c r="K135" s="1">
-        <f t="shared" si="30"/>
-        <v>7500</v>
+        <f t="shared" si="32"/>
+        <v>8000</v>
       </c>
       <c r="L135" s="1">
-        <f t="shared" si="26"/>
-        <v>2100</v>
+        <f t="shared" si="33"/>
+        <v>2350</v>
       </c>
       <c r="M135" s="1">
-        <f t="shared" si="27"/>
-        <v>2100</v>
+        <f t="shared" si="34"/>
+        <v>2350</v>
       </c>
       <c r="N135" s="2">
-        <f t="shared" si="28"/>
-        <v>54</v>
-      </c>
-      <c r="O135" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>59</v>
+      </c>
+      <c r="O135" s="2">
+        <f t="shared" si="36"/>
+        <v>50</v>
       </c>
       <c r="P135" s="2">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="Q135" s="10" t="s">
-        <v>845</v>
+        <v>855</v>
       </c>
       <c r="R135" s="10" t="s">
-        <v>845</v>
+        <v>855</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:18">
       <c r="A136" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>847</v>
+        <v>858</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="G136" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="H136" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="I136" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="J136" s="1">
-        <f t="shared" si="29"/>
-        <v>6000</v>
+        <f t="shared" ref="J136:J140" si="37">J135+400</f>
+        <v>6700</v>
       </c>
       <c r="K136" s="1">
-        <f t="shared" si="30"/>
-        <v>7800</v>
+        <f t="shared" si="32"/>
+        <v>8400</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" si="26"/>
-        <v>2150</v>
+        <f t="shared" ref="L136:L140" si="38">L135+150</f>
+        <v>2500</v>
       </c>
       <c r="M136" s="1">
-        <f t="shared" si="27"/>
-        <v>2150</v>
+        <f t="shared" ref="M136:M140" si="39">M135+150</f>
+        <v>2500</v>
       </c>
       <c r="N136" s="2">
-        <f t="shared" si="28"/>
-        <v>55</v>
-      </c>
-      <c r="O136" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>61</v>
+      </c>
+      <c r="O136" s="2">
+        <f t="shared" si="36"/>
+        <v>54</v>
       </c>
       <c r="P136" s="2">
-        <v>90</v>
+        <v>99.2</v>
       </c>
       <c r="Q136" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="R136" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="1:18">
       <c r="A137" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="G137" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="H137" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="I137" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="J137" s="1">
-        <f t="shared" si="29"/>
-        <v>6200</v>
+        <f t="shared" si="37"/>
+        <v>7100</v>
       </c>
       <c r="K137" s="1">
-        <f t="shared" si="30"/>
-        <v>8100</v>
+        <f t="shared" si="32"/>
+        <v>8800</v>
       </c>
       <c r="L137" s="1">
-        <f t="shared" si="26"/>
-        <v>2200</v>
+        <f t="shared" si="38"/>
+        <v>2650</v>
       </c>
       <c r="M137" s="1">
-        <f t="shared" si="27"/>
-        <v>2200</v>
+        <f t="shared" si="39"/>
+        <v>2650</v>
       </c>
       <c r="N137" s="2">
-        <f t="shared" si="28"/>
-        <v>56</v>
-      </c>
-      <c r="O137" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>63</v>
+      </c>
+      <c r="O137" s="2">
+        <f t="shared" si="36"/>
+        <v>58</v>
       </c>
       <c r="P137" s="2">
-        <v>90</v>
+        <v>99.4</v>
       </c>
       <c r="Q137" s="10" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="R137" s="10" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:18">
       <c r="A138" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="H138" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="I138" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="J138" s="1">
-        <f t="shared" si="29"/>
-        <v>6400</v>
+        <f t="shared" si="37"/>
+        <v>7500</v>
       </c>
       <c r="K138" s="1">
-        <f t="shared" si="30"/>
-        <v>8400</v>
+        <f t="shared" si="32"/>
+        <v>9200</v>
       </c>
       <c r="L138" s="1">
-        <f t="shared" si="26"/>
-        <v>2250</v>
+        <f t="shared" si="38"/>
+        <v>2800</v>
       </c>
       <c r="M138" s="1">
-        <f t="shared" si="27"/>
-        <v>2250</v>
+        <f t="shared" si="39"/>
+        <v>2800</v>
       </c>
       <c r="N138" s="2">
-        <f t="shared" si="28"/>
-        <v>57</v>
-      </c>
-      <c r="O138" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>65</v>
+      </c>
+      <c r="O138" s="2">
+        <f t="shared" si="36"/>
+        <v>62</v>
       </c>
       <c r="P138" s="2">
-        <v>90</v>
+        <v>99.6</v>
       </c>
       <c r="Q138" s="10" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="R138" s="10" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:18">
       <c r="A139" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="G139" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="H139" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="I139" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="J139" s="1">
-        <f t="shared" si="29"/>
-        <v>6600</v>
+        <f t="shared" si="37"/>
+        <v>7900</v>
       </c>
       <c r="K139" s="1">
-        <f t="shared" si="30"/>
-        <v>8700</v>
+        <f t="shared" si="32"/>
+        <v>9600</v>
       </c>
       <c r="L139" s="1">
-        <f t="shared" si="26"/>
-        <v>2300</v>
+        <f t="shared" si="38"/>
+        <v>2950</v>
       </c>
       <c r="M139" s="1">
-        <f t="shared" si="27"/>
-        <v>2300</v>
+        <f t="shared" si="39"/>
+        <v>2950</v>
       </c>
       <c r="N139" s="2">
-        <f t="shared" si="28"/>
-        <v>58</v>
-      </c>
-      <c r="O139" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>67</v>
+      </c>
+      <c r="O139" s="2">
+        <f t="shared" si="36"/>
+        <v>66</v>
       </c>
       <c r="P139" s="2">
-        <v>90</v>
+        <v>99.8</v>
       </c>
       <c r="Q139" s="10" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="R139" s="10" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:18">
       <c r="A140" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="G140" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="H140" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="I140" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="J140" s="1">
-        <f t="shared" si="29"/>
-        <v>6800</v>
+        <f t="shared" si="37"/>
+        <v>8300</v>
       </c>
       <c r="K140" s="1">
-        <f t="shared" si="30"/>
-        <v>9000</v>
+        <f t="shared" si="32"/>
+        <v>10000</v>
       </c>
       <c r="L140" s="1">
-        <f t="shared" si="26"/>
-        <v>2350</v>
+        <f t="shared" si="38"/>
+        <v>3100</v>
       </c>
       <c r="M140" s="1">
-        <f t="shared" si="27"/>
-        <v>2350</v>
+        <f t="shared" si="39"/>
+        <v>3100</v>
       </c>
       <c r="N140" s="2">
-        <f t="shared" si="28"/>
-        <v>59</v>
-      </c>
-      <c r="O140" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>69</v>
+      </c>
+      <c r="O140" s="2">
+        <f t="shared" si="36"/>
+        <v>70</v>
       </c>
       <c r="P140" s="2">
-        <v>90</v>
+        <v>99.9</v>
       </c>
       <c r="Q140" s="10" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="R140" s="10" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A141" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="G141" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="H141" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="I141" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="J141" s="1">
-        <f t="shared" si="29"/>
-        <v>7000</v>
+        <f t="shared" ref="J141:J145" si="40">J140+500</f>
+        <v>8800</v>
       </c>
       <c r="K141" s="1">
-        <f t="shared" si="30"/>
-        <v>9300</v>
+        <f t="shared" ref="K141:K145" si="41">K140+500</f>
+        <v>10500</v>
       </c>
       <c r="L141" s="1">
-        <f t="shared" si="26"/>
-        <v>2400</v>
+        <f t="shared" ref="L141:L145" si="42">L140+200</f>
+        <v>3300</v>
       </c>
       <c r="M141" s="1">
-        <f t="shared" si="27"/>
-        <v>2400</v>
+        <f t="shared" ref="M141:M145" si="43">M140+200</f>
+        <v>3300</v>
       </c>
       <c r="N141" s="2">
-        <f t="shared" si="28"/>
-        <v>60</v>
-      </c>
-      <c r="O141" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>71</v>
+      </c>
+      <c r="O141" s="2">
+        <f t="shared" si="36"/>
+        <v>74</v>
       </c>
       <c r="P141" s="2">
-        <v>90</v>
+        <v>99.92</v>
       </c>
       <c r="Q141" s="10" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="R141" s="10" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="S141" s="2"/>
       <c r="T141" s="2"/>
@@ -11671,63 +11693,64 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A142" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="G142" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="H142" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="I142" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="J142" s="1">
-        <f t="shared" si="29"/>
-        <v>7200</v>
+        <f t="shared" si="40"/>
+        <v>9300</v>
       </c>
       <c r="K142" s="1">
-        <f t="shared" si="30"/>
-        <v>9600</v>
+        <f t="shared" si="41"/>
+        <v>11000</v>
       </c>
       <c r="L142" s="1">
-        <f t="shared" si="26"/>
-        <v>2450</v>
+        <f t="shared" si="42"/>
+        <v>3500</v>
       </c>
       <c r="M142" s="1">
-        <f t="shared" si="27"/>
-        <v>2450</v>
+        <f t="shared" si="43"/>
+        <v>3500</v>
       </c>
       <c r="N142" s="2">
-        <f t="shared" si="28"/>
-        <v>61</v>
-      </c>
-      <c r="O142" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>73</v>
+      </c>
+      <c r="O142" s="2">
+        <f t="shared" si="36"/>
+        <v>78</v>
       </c>
       <c r="P142" s="2">
-        <v>90</v>
+        <v>99.94</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="R142" s="10" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="S142" s="2"/>
       <c r="T142" s="2"/>
@@ -11737,63 +11760,64 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A143" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="G143" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="H143" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="I143" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="J143" s="1">
-        <f t="shared" si="29"/>
-        <v>7400</v>
+        <f t="shared" si="40"/>
+        <v>9800</v>
       </c>
       <c r="K143" s="1">
-        <f t="shared" si="30"/>
-        <v>9900</v>
+        <f t="shared" si="41"/>
+        <v>11500</v>
       </c>
       <c r="L143" s="1">
-        <f t="shared" si="26"/>
-        <v>2500</v>
+        <f t="shared" si="42"/>
+        <v>3700</v>
       </c>
       <c r="M143" s="1">
-        <f t="shared" si="27"/>
-        <v>2500</v>
+        <f t="shared" si="43"/>
+        <v>3700</v>
       </c>
       <c r="N143" s="2">
-        <f t="shared" si="28"/>
-        <v>62</v>
-      </c>
-      <c r="O143" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>75</v>
+      </c>
+      <c r="O143" s="2">
+        <f t="shared" si="36"/>
+        <v>82</v>
       </c>
       <c r="P143" s="2">
-        <v>90</v>
+        <v>99.96</v>
       </c>
       <c r="Q143" s="10" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
       <c r="R143" s="10" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
       <c r="S143" s="2"/>
       <c r="T143" s="2"/>
@@ -11803,63 +11827,64 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A144" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="G144" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="H144" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="I144" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="J144" s="1">
-        <f t="shared" si="29"/>
-        <v>7600</v>
+        <f t="shared" si="40"/>
+        <v>10300</v>
       </c>
       <c r="K144" s="1">
-        <f t="shared" si="30"/>
-        <v>10200</v>
+        <f t="shared" si="41"/>
+        <v>12000</v>
       </c>
       <c r="L144" s="1">
-        <f t="shared" si="26"/>
-        <v>2550</v>
+        <f t="shared" si="42"/>
+        <v>3900</v>
       </c>
       <c r="M144" s="1">
-        <f t="shared" si="27"/>
-        <v>2550</v>
+        <f t="shared" si="43"/>
+        <v>3900</v>
       </c>
       <c r="N144" s="2">
-        <f t="shared" si="28"/>
-        <v>63</v>
-      </c>
-      <c r="O144" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>77</v>
+      </c>
+      <c r="O144" s="2">
+        <f t="shared" si="36"/>
+        <v>86</v>
       </c>
       <c r="P144" s="2">
-        <v>90</v>
+        <v>99.98</v>
       </c>
       <c r="Q144" s="10" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="R144" s="10" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="S144" s="2"/>
       <c r="T144" s="2"/>
@@ -11869,63 +11894,64 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A145" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="G145" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="H145" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="I145" s="14" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="J145" s="1">
-        <f t="shared" si="29"/>
-        <v>7800</v>
+        <f t="shared" si="40"/>
+        <v>10800</v>
       </c>
       <c r="K145" s="1">
-        <f t="shared" si="30"/>
-        <v>10500</v>
+        <f t="shared" si="41"/>
+        <v>12500</v>
       </c>
       <c r="L145" s="1">
-        <f t="shared" si="26"/>
-        <v>2600</v>
+        <f t="shared" si="42"/>
+        <v>4100</v>
       </c>
       <c r="M145" s="1">
-        <f t="shared" si="27"/>
-        <v>2600</v>
+        <f t="shared" si="43"/>
+        <v>4100</v>
       </c>
       <c r="N145" s="2">
-        <f t="shared" si="28"/>
-        <v>64</v>
-      </c>
-      <c r="O145" s="4">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>79</v>
+      </c>
+      <c r="O145" s="2">
+        <f t="shared" si="36"/>
+        <v>90</v>
       </c>
       <c r="P145" s="2">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="Q145" s="10" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="R145" s="10" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="S145" s="2"/>
       <c r="T145" s="2"/>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="907">
   <si>
     <t>ID</t>
   </si>
@@ -2597,73 +2597,109 @@
     <t>10000000000</t>
   </si>
   <si>
+    <t>10131</t>
+  </si>
+  <si>
+    <t>1130</t>
+  </si>
+  <si>
+    <t>地狱树妖</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>3200000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>11000000000</t>
+  </si>
+  <si>
+    <t>10132</t>
+  </si>
+  <si>
+    <t>1131</t>
+  </si>
+  <si>
+    <t>地狱侍卫</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>64000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>12000000000</t>
+  </si>
+  <si>
+    <t>10133</t>
+  </si>
+  <si>
+    <t>1132</t>
+  </si>
+  <si>
+    <t>地狱剧毒</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1280000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>13000000000</t>
+  </si>
+  <si>
+    <t>10134</t>
+  </si>
+  <si>
+    <t>1133</t>
+  </si>
+  <si>
+    <t>地狱锤兵</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>25600000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>14000000000</t>
+  </si>
+  <si>
+    <t>10135</t>
+  </si>
+  <si>
+    <t>1134</t>
+  </si>
+  <si>
+    <t>地狱魔牛</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>512000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>15000000000</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
-    <t>10131</t>
-  </si>
-  <si>
-    <t>1130</t>
-  </si>
-  <si>
-    <t>地狱树妖</t>
+    <t>10136</t>
+  </si>
+  <si>
+    <t>1135</t>
+  </si>
+  <si>
+    <t>地狱水龙</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>10132</t>
-  </si>
-  <si>
-    <t>1131</t>
-  </si>
-  <si>
-    <t>地狱侍卫</t>
-  </si>
-  <si>
-    <t>5700000000</t>
-  </si>
-  <si>
-    <t>10133</t>
-  </si>
-  <si>
-    <t>1132</t>
-  </si>
-  <si>
-    <t>地狱剧毒</t>
-  </si>
-  <si>
-    <t>5800000000</t>
-  </si>
-  <si>
-    <t>10134</t>
-  </si>
-  <si>
-    <t>1133</t>
-  </si>
-  <si>
-    <t>地狱锤兵</t>
-  </si>
-  <si>
-    <t>5900000000</t>
-  </si>
-  <si>
-    <t>10135</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>地狱魔牛</t>
-  </si>
-  <si>
-    <t>10136</t>
-  </si>
-  <si>
-    <t>1135</t>
-  </si>
-  <si>
-    <t>地狱水龙</t>
   </si>
   <si>
     <t>6100000000</t>
@@ -3692,9 +3728,9 @@
     <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="47.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="50" style="2" customWidth="1"/>
     <col min="8" max="8" width="47.4166666666667" style="2" customWidth="1"/>
-    <col min="9" max="9" width="59.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="63.625" style="2" customWidth="1"/>
     <col min="10" max="10" width="12.75" style="2" customWidth="1"/>
     <col min="11" max="11" width="9.375" style="2" customWidth="1"/>
     <col min="12" max="12" width="9.125" style="2" customWidth="1"/>
@@ -3915,7 +3951,7 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" ht="14" spans="3:18">
+    <row r="6" ht="14.25" spans="3:18">
       <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
@@ -10512,7 +10548,7 @@
         <v>41</v>
       </c>
       <c r="O122" s="2">
-        <f>O121+3</f>
+        <f t="shared" ref="O122:O130" si="31">O121+3</f>
         <v>6</v>
       </c>
       <c r="P122" s="2">
@@ -10575,7 +10611,7 @@
         <v>42</v>
       </c>
       <c r="O123" s="2">
-        <f>O122+3</f>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="P123" s="2">
@@ -10638,7 +10674,7 @@
         <v>43</v>
       </c>
       <c r="O124" s="2">
-        <f>O123+3</f>
+        <f t="shared" si="31"/>
         <v>12</v>
       </c>
       <c r="P124" s="2">
@@ -10701,7 +10737,7 @@
         <v>44</v>
       </c>
       <c r="O125" s="2">
-        <f>O124+3</f>
+        <f t="shared" si="31"/>
         <v>15</v>
       </c>
       <c r="P125" s="2">
@@ -10764,7 +10800,7 @@
         <v>45</v>
       </c>
       <c r="O126" s="2">
-        <f>O125+3</f>
+        <f t="shared" si="31"/>
         <v>18</v>
       </c>
       <c r="P126" s="2">
@@ -10827,7 +10863,7 @@
         <v>46</v>
       </c>
       <c r="O127" s="2">
-        <f>O126+3</f>
+        <f t="shared" si="31"/>
         <v>21</v>
       </c>
       <c r="P127" s="2">
@@ -10890,7 +10926,7 @@
         <v>47</v>
       </c>
       <c r="O128" s="2">
-        <f>O127+3</f>
+        <f t="shared" si="31"/>
         <v>24</v>
       </c>
       <c r="P128" s="2">
@@ -10953,7 +10989,7 @@
         <v>48</v>
       </c>
       <c r="O129" s="2">
-        <f>O128+3</f>
+        <f t="shared" si="31"/>
         <v>27</v>
       </c>
       <c r="P129" s="2">
@@ -11016,7 +11052,7 @@
         <v>49</v>
       </c>
       <c r="O130" s="2">
-        <f>O129+3</f>
+        <f t="shared" si="31"/>
         <v>30</v>
       </c>
       <c r="P130" s="2">
@@ -11057,27 +11093,27 @@
         <v>830</v>
       </c>
       <c r="J131" s="1">
-        <f t="shared" ref="J131:J136" si="31">J130+300</f>
+        <f t="shared" ref="J131:J136" si="32">J130+300</f>
         <v>5100</v>
       </c>
       <c r="K131" s="1">
-        <f t="shared" ref="K131:K140" si="32">K130+400</f>
+        <f t="shared" ref="K131:K140" si="33">K130+400</f>
         <v>6400</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" ref="L131:L135" si="33">L130+100</f>
+        <f t="shared" ref="L131:L135" si="34">L130+100</f>
         <v>1950</v>
       </c>
       <c r="M131" s="1">
-        <f t="shared" ref="M131:M135" si="34">M130+100</f>
+        <f t="shared" ref="M131:M135" si="35">M130+100</f>
         <v>1950</v>
       </c>
       <c r="N131" s="2">
-        <f t="shared" ref="N131:N145" si="35">N130+2</f>
+        <f t="shared" ref="N131:N145" si="36">N130+2</f>
         <v>51</v>
       </c>
       <c r="O131" s="2">
-        <f t="shared" ref="O131:O145" si="36">O130+4</f>
+        <f t="shared" ref="O131:O145" si="37">O130+4</f>
         <v>34</v>
       </c>
       <c r="P131" s="2">
@@ -11113,27 +11149,27 @@
         <v>836</v>
       </c>
       <c r="J132" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>5400</v>
       </c>
       <c r="K132" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>6800</v>
       </c>
       <c r="L132" s="1">
-        <f t="shared" si="33"/>
-        <v>2050</v>
-      </c>
-      <c r="M132" s="1">
         <f t="shared" si="34"/>
         <v>2050</v>
       </c>
+      <c r="M132" s="1">
+        <f t="shared" si="35"/>
+        <v>2050</v>
+      </c>
       <c r="N132" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>53</v>
       </c>
       <c r="O132" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>38</v>
       </c>
       <c r="P132" s="2">
@@ -11169,27 +11205,27 @@
         <v>842</v>
       </c>
       <c r="J133" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>5700</v>
       </c>
       <c r="K133" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7200</v>
       </c>
       <c r="L133" s="1">
-        <f t="shared" si="33"/>
-        <v>2150</v>
-      </c>
-      <c r="M133" s="1">
         <f t="shared" si="34"/>
         <v>2150</v>
       </c>
+      <c r="M133" s="1">
+        <f t="shared" si="35"/>
+        <v>2150</v>
+      </c>
       <c r="N133" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>55</v>
       </c>
       <c r="O133" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>42</v>
       </c>
       <c r="P133" s="2">
@@ -11225,27 +11261,27 @@
         <v>848</v>
       </c>
       <c r="J134" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>6000</v>
       </c>
       <c r="K134" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7600</v>
       </c>
       <c r="L134" s="1">
-        <f t="shared" si="33"/>
-        <v>2250</v>
-      </c>
-      <c r="M134" s="1">
         <f t="shared" si="34"/>
         <v>2250</v>
       </c>
+      <c r="M134" s="1">
+        <f t="shared" si="35"/>
+        <v>2250</v>
+      </c>
       <c r="N134" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>57</v>
       </c>
       <c r="O134" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>46</v>
       </c>
       <c r="P134" s="2">
@@ -11281,27 +11317,27 @@
         <v>854</v>
       </c>
       <c r="J135" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>6300</v>
       </c>
       <c r="K135" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8000</v>
       </c>
       <c r="L135" s="1">
-        <f t="shared" si="33"/>
-        <v>2350</v>
-      </c>
-      <c r="M135" s="1">
         <f t="shared" si="34"/>
         <v>2350</v>
       </c>
+      <c r="M135" s="1">
+        <f t="shared" si="35"/>
+        <v>2350</v>
+      </c>
       <c r="N135" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>59</v>
       </c>
       <c r="O135" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>50</v>
       </c>
       <c r="P135" s="2">
@@ -11314,376 +11350,346 @@
         <v>855</v>
       </c>
     </row>
-    <row r="136" customHeight="1" spans="1:18">
-      <c r="A136" s="2" t="s">
+    <row r="136" customHeight="1" spans="3:18">
+      <c r="C136" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>857</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>858</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="G136" s="14" t="s">
         <v>859</v>
       </c>
-      <c r="G136" s="14" t="s">
+      <c r="H136" s="10" t="s">
+        <v>859</v>
+      </c>
+      <c r="I136" s="15" t="s">
         <v>860</v>
       </c>
-      <c r="H136" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="I136" s="14" t="s">
-        <v>860</v>
-      </c>
       <c r="J136" s="1">
-        <f t="shared" ref="J136:J140" si="37">J135+400</f>
-        <v>6700</v>
+        <f t="shared" ref="J136:J145" si="38">J135+500</f>
+        <v>6800</v>
       </c>
       <c r="K136" s="1">
-        <f t="shared" si="32"/>
-        <v>8400</v>
+        <f t="shared" ref="K136:K145" si="39">K135+500</f>
+        <v>8500</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" ref="L136:L140" si="38">L135+150</f>
-        <v>2500</v>
+        <f t="shared" ref="L136:L145" si="40">L135+200</f>
+        <v>2550</v>
       </c>
       <c r="M136" s="1">
-        <f t="shared" ref="M136:M140" si="39">M135+150</f>
-        <v>2500</v>
+        <f t="shared" ref="M136:M145" si="41">M135+200</f>
+        <v>2550</v>
       </c>
       <c r="N136" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>61</v>
       </c>
       <c r="O136" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>54</v>
       </c>
       <c r="P136" s="2">
         <v>99.2</v>
       </c>
       <c r="Q136" s="10" t="s">
-        <v>789</v>
+        <v>861</v>
       </c>
       <c r="R136" s="10" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="137" customHeight="1" spans="1:18">
-      <c r="A137" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>856</v>
-      </c>
+        <v>861</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="3:18">
       <c r="C137" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G137" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="H137" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="I137" s="14" t="s">
-        <v>860</v>
+        <v>865</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>865</v>
+      </c>
+      <c r="I137" s="15" t="s">
+        <v>866</v>
       </c>
       <c r="J137" s="1">
+        <f t="shared" si="38"/>
+        <v>7300</v>
+      </c>
+      <c r="K137" s="1">
+        <f t="shared" si="39"/>
+        <v>9000</v>
+      </c>
+      <c r="L137" s="1">
+        <f t="shared" si="40"/>
+        <v>2750</v>
+      </c>
+      <c r="M137" s="1">
+        <f t="shared" si="41"/>
+        <v>2750</v>
+      </c>
+      <c r="N137" s="2">
+        <f t="shared" si="36"/>
+        <v>63</v>
+      </c>
+      <c r="O137" s="2">
         <f t="shared" si="37"/>
-        <v>7100</v>
-      </c>
-      <c r="K137" s="1">
-        <f t="shared" si="32"/>
-        <v>8800</v>
-      </c>
-      <c r="L137" s="1">
-        <f t="shared" si="38"/>
-        <v>2650</v>
-      </c>
-      <c r="M137" s="1">
-        <f t="shared" si="39"/>
-        <v>2650</v>
-      </c>
-      <c r="N137" s="2">
-        <f t="shared" si="35"/>
-        <v>63</v>
-      </c>
-      <c r="O137" s="2">
-        <f t="shared" si="36"/>
         <v>58</v>
       </c>
       <c r="P137" s="2">
         <v>99.4</v>
       </c>
       <c r="Q137" s="10" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="R137" s="10" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="138" customHeight="1" spans="1:18">
-      <c r="A138" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>856</v>
-      </c>
+        <v>867</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="3:18">
       <c r="C138" s="1" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="H138" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="I138" s="14" t="s">
-        <v>860</v>
+        <v>871</v>
+      </c>
+      <c r="H138" s="10" t="s">
+        <v>871</v>
+      </c>
+      <c r="I138" s="15" t="s">
+        <v>872</v>
       </c>
       <c r="J138" s="1">
+        <f t="shared" si="38"/>
+        <v>7800</v>
+      </c>
+      <c r="K138" s="1">
+        <f t="shared" si="39"/>
+        <v>9500</v>
+      </c>
+      <c r="L138" s="1">
+        <f t="shared" si="40"/>
+        <v>2950</v>
+      </c>
+      <c r="M138" s="1">
+        <f t="shared" si="41"/>
+        <v>2950</v>
+      </c>
+      <c r="N138" s="2">
+        <f t="shared" si="36"/>
+        <v>65</v>
+      </c>
+      <c r="O138" s="2">
         <f t="shared" si="37"/>
-        <v>7500</v>
-      </c>
-      <c r="K138" s="1">
-        <f t="shared" si="32"/>
-        <v>9200</v>
-      </c>
-      <c r="L138" s="1">
-        <f t="shared" si="38"/>
-        <v>2800</v>
-      </c>
-      <c r="M138" s="1">
-        <f t="shared" si="39"/>
-        <v>2800</v>
-      </c>
-      <c r="N138" s="2">
-        <f t="shared" si="35"/>
-        <v>65</v>
-      </c>
-      <c r="O138" s="2">
-        <f t="shared" si="36"/>
         <v>62</v>
       </c>
       <c r="P138" s="2">
         <v>99.6</v>
       </c>
       <c r="Q138" s="10" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="R138" s="10" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="139" customHeight="1" spans="1:18">
-      <c r="A139" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>856</v>
-      </c>
+        <v>873</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="3:18">
       <c r="C139" s="1" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="G139" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="H139" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="I139" s="14" t="s">
-        <v>860</v>
+        <v>877</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>877</v>
+      </c>
+      <c r="I139" s="15" t="s">
+        <v>878</v>
       </c>
       <c r="J139" s="1">
+        <f t="shared" si="38"/>
+        <v>8300</v>
+      </c>
+      <c r="K139" s="1">
+        <f t="shared" si="39"/>
+        <v>10000</v>
+      </c>
+      <c r="L139" s="1">
+        <f t="shared" si="40"/>
+        <v>3150</v>
+      </c>
+      <c r="M139" s="1">
+        <f t="shared" si="41"/>
+        <v>3150</v>
+      </c>
+      <c r="N139" s="2">
+        <f t="shared" si="36"/>
+        <v>67</v>
+      </c>
+      <c r="O139" s="2">
         <f t="shared" si="37"/>
-        <v>7900</v>
-      </c>
-      <c r="K139" s="1">
-        <f t="shared" si="32"/>
-        <v>9600</v>
-      </c>
-      <c r="L139" s="1">
-        <f t="shared" si="38"/>
-        <v>2950</v>
-      </c>
-      <c r="M139" s="1">
-        <f t="shared" si="39"/>
-        <v>2950</v>
-      </c>
-      <c r="N139" s="2">
-        <f t="shared" si="35"/>
-        <v>67</v>
-      </c>
-      <c r="O139" s="2">
-        <f t="shared" si="36"/>
         <v>66</v>
       </c>
       <c r="P139" s="2">
         <v>99.8</v>
       </c>
       <c r="Q139" s="10" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="R139" s="10" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="140" customHeight="1" spans="1:18">
-      <c r="A140" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>856</v>
-      </c>
+        <v>879</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="3:18">
       <c r="C140" s="1" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="G140" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="H140" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="I140" s="14" t="s">
-        <v>860</v>
+        <v>883</v>
+      </c>
+      <c r="H140" s="10" t="s">
+        <v>883</v>
+      </c>
+      <c r="I140" s="15" t="s">
+        <v>884</v>
       </c>
       <c r="J140" s="1">
+        <f t="shared" si="38"/>
+        <v>8800</v>
+      </c>
+      <c r="K140" s="1">
+        <f t="shared" si="39"/>
+        <v>10500</v>
+      </c>
+      <c r="L140" s="1">
+        <f t="shared" si="40"/>
+        <v>3350</v>
+      </c>
+      <c r="M140" s="1">
+        <f t="shared" si="41"/>
+        <v>3350</v>
+      </c>
+      <c r="N140" s="2">
+        <f t="shared" si="36"/>
+        <v>69</v>
+      </c>
+      <c r="O140" s="2">
         <f t="shared" si="37"/>
-        <v>8300</v>
-      </c>
-      <c r="K140" s="1">
-        <f t="shared" si="32"/>
-        <v>10000</v>
-      </c>
-      <c r="L140" s="1">
-        <f t="shared" si="38"/>
-        <v>3100</v>
-      </c>
-      <c r="M140" s="1">
-        <f t="shared" si="39"/>
-        <v>3100</v>
-      </c>
-      <c r="N140" s="2">
-        <f t="shared" si="35"/>
-        <v>69</v>
-      </c>
-      <c r="O140" s="2">
-        <f t="shared" si="36"/>
         <v>70</v>
       </c>
       <c r="P140" s="2">
         <v>99.9</v>
       </c>
       <c r="Q140" s="10" t="s">
-        <v>795</v>
+        <v>885</v>
       </c>
       <c r="R140" s="10" t="s">
-        <v>795</v>
+        <v>885</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A141" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="G141" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="H141" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="I141" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="J141" s="1">
-        <f t="shared" ref="J141:J145" si="40">J140+500</f>
-        <v>8800</v>
+        <f t="shared" ref="J141:J145" si="42">J140+600</f>
+        <v>9400</v>
       </c>
       <c r="K141" s="1">
-        <f t="shared" ref="K141:K145" si="41">K140+500</f>
-        <v>10500</v>
+        <f t="shared" ref="K141:K145" si="43">K140+600</f>
+        <v>11100</v>
       </c>
       <c r="L141" s="1">
-        <f t="shared" ref="L141:L145" si="42">L140+200</f>
-        <v>3300</v>
+        <f t="shared" ref="L141:L145" si="44">L140+250</f>
+        <v>3600</v>
       </c>
       <c r="M141" s="1">
-        <f t="shared" ref="M141:M145" si="43">M140+200</f>
-        <v>3300</v>
+        <f t="shared" ref="M141:M145" si="45">M140+250</f>
+        <v>3600</v>
       </c>
       <c r="N141" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>71</v>
       </c>
       <c r="O141" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>74</v>
       </c>
       <c r="P141" s="2">
         <v>99.92</v>
       </c>
       <c r="Q141" s="10" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="R141" s="10" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="S141" s="2"/>
       <c r="T141" s="2"/>
@@ -11693,64 +11699,64 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A142" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="G142" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="H142" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="I142" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="J142" s="1">
-        <f t="shared" si="40"/>
-        <v>9300</v>
+        <f t="shared" si="42"/>
+        <v>10000</v>
       </c>
       <c r="K142" s="1">
-        <f t="shared" si="41"/>
-        <v>11000</v>
+        <f t="shared" si="43"/>
+        <v>11700</v>
       </c>
       <c r="L142" s="1">
-        <f t="shared" si="42"/>
-        <v>3500</v>
+        <f t="shared" si="44"/>
+        <v>3850</v>
       </c>
       <c r="M142" s="1">
-        <f t="shared" si="43"/>
-        <v>3500</v>
+        <f t="shared" si="45"/>
+        <v>3850</v>
       </c>
       <c r="N142" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>73</v>
       </c>
       <c r="O142" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>78</v>
       </c>
       <c r="P142" s="2">
         <v>99.94</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="R142" s="10" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="S142" s="2"/>
       <c r="T142" s="2"/>
@@ -11760,64 +11766,64 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A143" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="G143" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="H143" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="I143" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="J143" s="1">
-        <f t="shared" si="40"/>
-        <v>9800</v>
+        <f t="shared" si="42"/>
+        <v>10600</v>
       </c>
       <c r="K143" s="1">
-        <f t="shared" si="41"/>
-        <v>11500</v>
+        <f t="shared" si="43"/>
+        <v>12300</v>
       </c>
       <c r="L143" s="1">
-        <f t="shared" si="42"/>
-        <v>3700</v>
+        <f t="shared" si="44"/>
+        <v>4100</v>
       </c>
       <c r="M143" s="1">
-        <f t="shared" si="43"/>
-        <v>3700</v>
+        <f t="shared" si="45"/>
+        <v>4100</v>
       </c>
       <c r="N143" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>75</v>
       </c>
       <c r="O143" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>82</v>
       </c>
       <c r="P143" s="2">
         <v>99.96</v>
       </c>
       <c r="Q143" s="10" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="R143" s="10" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="S143" s="2"/>
       <c r="T143" s="2"/>
@@ -11827,54 +11833,54 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A144" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="G144" s="14" t="s">
         <v>890</v>
       </c>
-      <c r="G144" s="14" t="s">
-        <v>860</v>
-      </c>
       <c r="H144" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="I144" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="J144" s="1">
-        <f t="shared" si="40"/>
-        <v>10300</v>
+        <f t="shared" si="42"/>
+        <v>11200</v>
       </c>
       <c r="K144" s="1">
-        <f t="shared" si="41"/>
-        <v>12000</v>
+        <f t="shared" si="43"/>
+        <v>12900</v>
       </c>
       <c r="L144" s="1">
-        <f t="shared" si="42"/>
-        <v>3900</v>
+        <f t="shared" si="44"/>
+        <v>4350</v>
       </c>
       <c r="M144" s="1">
-        <f t="shared" si="43"/>
-        <v>3900</v>
+        <f t="shared" si="45"/>
+        <v>4350</v>
       </c>
       <c r="N144" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>77</v>
       </c>
       <c r="O144" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>86</v>
       </c>
       <c r="P144" s="2">
@@ -11894,64 +11900,64 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A145" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="G145" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="H145" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="I145" s="14" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="J145" s="1">
-        <f t="shared" si="40"/>
-        <v>10800</v>
+        <f t="shared" si="42"/>
+        <v>11800</v>
       </c>
       <c r="K145" s="1">
-        <f t="shared" si="41"/>
-        <v>12500</v>
+        <f t="shared" si="43"/>
+        <v>13500</v>
       </c>
       <c r="L145" s="1">
-        <f t="shared" si="42"/>
-        <v>4100</v>
+        <f t="shared" si="44"/>
+        <v>4600</v>
       </c>
       <c r="M145" s="1">
-        <f t="shared" si="43"/>
-        <v>4100</v>
+        <f t="shared" si="45"/>
+        <v>4600</v>
       </c>
       <c r="N145" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>79</v>
       </c>
       <c r="O145" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>90</v>
       </c>
       <c r="P145" s="2">
         <v>99.99</v>
       </c>
       <c r="Q145" s="10" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="R145" s="10" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="S145" s="2"/>
       <c r="T145" s="2"/>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="916">
   <si>
     <t>ID</t>
   </si>
@@ -2687,9 +2687,6 @@
     <t>15000000000</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>10136</t>
   </si>
   <si>
@@ -2699,10 +2696,13 @@
     <t>地狱水龙</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>6100000000</t>
+    <t>900000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>10000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>18000000000</t>
   </si>
   <si>
     <t>10137</t>
@@ -2714,7 +2714,13 @@
     <t>地狱土龙</t>
   </si>
   <si>
-    <t>6200000000</t>
+    <t>9000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>200000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>21000000000</t>
   </si>
   <si>
     <t>10138</t>
@@ -2726,7 +2732,13 @@
     <t>地狱毒龙</t>
   </si>
   <si>
-    <t>6300000000</t>
+    <t>90000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>4000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>24000000000</t>
   </si>
   <si>
     <t>10139</t>
@@ -2738,6 +2750,15 @@
     <t>地狱火龙</t>
   </si>
   <si>
+    <t>900000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>80000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>27000000000</t>
+  </si>
+  <si>
     <t>10140</t>
   </si>
   <si>
@@ -2747,7 +2768,13 @@
     <t>地狱冰龙</t>
   </si>
   <si>
-    <t>6500000000</t>
+    <t>9000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1600000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>30000000000</t>
   </si>
 </sst>
 </file>
@@ -3728,9 +3755,9 @@
     <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="50" style="2" customWidth="1"/>
-    <col min="8" max="8" width="47.4166666666667" style="2" customWidth="1"/>
-    <col min="9" max="9" width="63.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="57.1666666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="60.5833333333333" style="2" customWidth="1"/>
+    <col min="9" max="9" width="69.1666666666667" style="2" customWidth="1"/>
     <col min="10" max="10" width="12.75" style="2" customWidth="1"/>
     <col min="11" max="11" width="9.375" style="2" customWidth="1"/>
     <col min="12" max="12" width="9.125" style="2" customWidth="1"/>
@@ -3951,7 +3978,7 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" ht="14.25" spans="3:18">
+    <row r="6" ht="14" spans="3:18">
       <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
@@ -11631,31 +11658,27 @@
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A141" s="2" t="s">
+      <c r="A141" s="2"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="C141" s="1" t="s">
+      <c r="D141" s="1" t="s">
         <v>887</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>888</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="G141" s="14" t="s">
         <v>889</v>
       </c>
-      <c r="G141" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="H141" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="I141" s="14" t="s">
+      <c r="H141" s="10" t="s">
+        <v>889</v>
+      </c>
+      <c r="I141" s="15" t="s">
         <v>890</v>
       </c>
       <c r="J141" s="1">
@@ -11698,12 +11721,8 @@
       <c r="W141" s="2"/>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A142" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>886</v>
-      </c>
+      <c r="A142" s="2"/>
+      <c r="B142" s="2"/>
       <c r="C142" s="1" t="s">
         <v>892</v>
       </c>
@@ -11717,13 +11736,13 @@
         <v>894</v>
       </c>
       <c r="G142" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="H142" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="I142" s="14" t="s">
-        <v>890</v>
+        <v>895</v>
+      </c>
+      <c r="H142" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="I142" s="15" t="s">
+        <v>896</v>
       </c>
       <c r="J142" s="1">
         <f t="shared" si="42"/>
@@ -11753,10 +11772,10 @@
         <v>99.94</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="R142" s="10" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="S142" s="2"/>
       <c r="T142" s="2"/>
@@ -11765,32 +11784,28 @@
       <c r="W142" s="2"/>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A143" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>886</v>
-      </c>
+      <c r="A143" s="2"/>
+      <c r="B143" s="2"/>
       <c r="C143" s="1" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="G143" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="H143" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="I143" s="14" t="s">
-        <v>890</v>
+        <v>901</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="I143" s="15" t="s">
+        <v>902</v>
       </c>
       <c r="J143" s="1">
         <f t="shared" si="42"/>
@@ -11820,10 +11835,10 @@
         <v>99.96</v>
       </c>
       <c r="Q143" s="10" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="R143" s="10" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="S143" s="2"/>
       <c r="T143" s="2"/>
@@ -11832,32 +11847,28 @@
       <c r="W143" s="2"/>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A144" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>886</v>
-      </c>
+      <c r="A144" s="2"/>
+      <c r="B144" s="2"/>
       <c r="C144" s="1" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="G144" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="H144" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="I144" s="14" t="s">
-        <v>890</v>
+        <v>907</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>907</v>
+      </c>
+      <c r="I144" s="15" t="s">
+        <v>908</v>
       </c>
       <c r="J144" s="1">
         <f t="shared" si="42"/>
@@ -11887,10 +11898,10 @@
         <v>99.98</v>
       </c>
       <c r="Q144" s="10" t="s">
-        <v>801</v>
+        <v>909</v>
       </c>
       <c r="R144" s="10" t="s">
-        <v>801</v>
+        <v>909</v>
       </c>
       <c r="S144" s="2"/>
       <c r="T144" s="2"/>
@@ -11899,32 +11910,28 @@
       <c r="W144" s="2"/>
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A145" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>886</v>
-      </c>
+      <c r="A145" s="2"/>
+      <c r="B145" s="2"/>
       <c r="C145" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="G145" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="H145" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="I145" s="14" t="s">
-        <v>890</v>
+        <v>913</v>
+      </c>
+      <c r="H145" s="10" t="s">
+        <v>913</v>
+      </c>
+      <c r="I145" s="15" t="s">
+        <v>914</v>
       </c>
       <c r="J145" s="1">
         <f t="shared" si="42"/>
@@ -11954,10 +11961,10 @@
         <v>99.99</v>
       </c>
       <c r="Q145" s="10" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="R145" s="10" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="S145" s="2"/>
       <c r="T145" s="2"/>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="1102">
   <si>
     <t>ID</t>
   </si>
@@ -2792,7 +2792,7 @@
     <t>900僧</t>
   </si>
   <si>
-    <t>1600不</t>
+    <t>3200不</t>
   </si>
   <si>
     <t>33000000000</t>
@@ -2807,6 +2807,12 @@
     <t>深渊鹿</t>
   </si>
   <si>
+    <t>9000僧</t>
+  </si>
+  <si>
+    <t>64000不</t>
+  </si>
+  <si>
     <t>36000000000</t>
   </si>
   <si>
@@ -2819,6 +2825,12 @@
     <t>深渊草人</t>
   </si>
   <si>
+    <t>9祇</t>
+  </si>
+  <si>
+    <t>128可</t>
+  </si>
+  <si>
     <t>39000000000</t>
   </si>
   <si>
@@ -2831,6 +2843,12 @@
     <t>深渊猫</t>
   </si>
   <si>
+    <t>90祇</t>
+  </si>
+  <si>
+    <t>2560可</t>
+  </si>
+  <si>
     <t>42000000000</t>
   </si>
   <si>
@@ -2843,6 +2861,12 @@
     <t>深渊花</t>
   </si>
   <si>
+    <t>900祇</t>
+  </si>
+  <si>
+    <t>5思</t>
+  </si>
+  <si>
     <t>45000000000</t>
   </si>
   <si>
@@ -2855,6 +2879,12 @@
     <t>深渊雪人</t>
   </si>
   <si>
+    <t>9000祇</t>
+  </si>
+  <si>
+    <t>100思</t>
+  </si>
+  <si>
     <t>48000000000</t>
   </si>
   <si>
@@ -2867,6 +2897,12 @@
     <t>深渊蝙蝠</t>
   </si>
   <si>
+    <t>9那</t>
+  </si>
+  <si>
+    <t>2000思</t>
+  </si>
+  <si>
     <t>51000000000</t>
   </si>
   <si>
@@ -2879,6 +2915,12 @@
     <t>深渊骷髅</t>
   </si>
   <si>
+    <t>90那</t>
+  </si>
+  <si>
+    <t>4议</t>
+  </si>
+  <si>
     <t>54000000000</t>
   </si>
   <si>
@@ -2891,6 +2933,12 @@
     <t>深渊僵尸</t>
   </si>
   <si>
+    <t>900那</t>
+  </si>
+  <si>
+    <t>80议</t>
+  </si>
+  <si>
     <t>57000000000</t>
   </si>
   <si>
@@ -2903,6 +2951,12 @@
     <t>深渊毒蛇</t>
   </si>
   <si>
+    <t>9000那</t>
+  </si>
+  <si>
+    <t>1600议</t>
+  </si>
+  <si>
     <t>60000000000</t>
   </si>
   <si>
@@ -2915,6 +2969,9 @@
     <t>深渊野狼</t>
   </si>
   <si>
+    <t>9由</t>
+  </si>
+  <si>
     <t>1亿</t>
   </si>
   <si>
@@ -2927,6 +2984,9 @@
     <t>深渊沙虫</t>
   </si>
   <si>
+    <t>90由</t>
+  </si>
+  <si>
     <t>5亿</t>
   </si>
   <si>
@@ -2939,6 +2999,9 @@
     <t>深渊小鹰</t>
   </si>
   <si>
+    <t>900由</t>
+  </si>
+  <si>
     <t>20亿</t>
   </si>
   <si>
@@ -2951,6 +3014,9 @@
     <t>深渊角虫</t>
   </si>
   <si>
+    <t>9000由</t>
+  </si>
+  <si>
     <t>100亿</t>
   </si>
   <si>
@@ -2963,6 +3029,9 @@
     <t>深渊蜈蚣</t>
   </si>
   <si>
+    <t>9他</t>
+  </si>
+  <si>
     <t>500亿</t>
   </si>
   <si>
@@ -2975,6 +3044,9 @@
     <t>深渊钳虫</t>
   </si>
   <si>
+    <t>90他</t>
+  </si>
+  <si>
     <t>2500亿</t>
   </si>
   <si>
@@ -2987,6 +3059,9 @@
     <t>深渊蠕虫</t>
   </si>
   <si>
+    <t>900他</t>
+  </si>
+  <si>
     <t>12500亿</t>
   </si>
   <si>
@@ -2999,6 +3074,9 @@
     <t>深渊黑猪</t>
   </si>
   <si>
+    <t>9000他</t>
+  </si>
+  <si>
     <t>62500亿</t>
   </si>
   <si>
@@ -3011,6 +3089,9 @@
     <t>深渊红猪</t>
   </si>
   <si>
+    <t>9不</t>
+  </si>
+  <si>
     <t>32兆</t>
   </si>
   <si>
@@ -3023,6 +3104,9 @@
     <t>深渊蝎蛇</t>
   </si>
   <si>
+    <t>90不</t>
+  </si>
+  <si>
     <t>160兆</t>
   </si>
   <si>
@@ -3035,6 +3119,9 @@
     <t>深渊恶魔</t>
   </si>
   <si>
+    <t>900不</t>
+  </si>
+  <si>
     <t>800兆</t>
   </si>
   <si>
@@ -3047,6 +3134,9 @@
     <t>深渊勇士</t>
   </si>
   <si>
+    <t>9000不</t>
+  </si>
+  <si>
     <t>4000兆</t>
   </si>
   <si>
@@ -3059,6 +3149,9 @@
     <t>深渊雕像</t>
   </si>
   <si>
+    <t>9可</t>
+  </si>
+  <si>
     <t>2京</t>
   </si>
   <si>
@@ -3071,6 +3164,9 @@
     <t>深渊卫士</t>
   </si>
   <si>
+    <t>90可</t>
+  </si>
+  <si>
     <t>10京</t>
   </si>
   <si>
@@ -3083,6 +3179,9 @@
     <t>深渊魔猪</t>
   </si>
   <si>
+    <t>900可</t>
+  </si>
+  <si>
     <t>50京</t>
   </si>
   <si>
@@ -3095,6 +3194,9 @@
     <t>深渊树妖</t>
   </si>
   <si>
+    <t>9000可</t>
+  </si>
+  <si>
     <t>250京</t>
   </si>
   <si>
@@ -3107,6 +3209,9 @@
     <t>深渊侍卫</t>
   </si>
   <si>
+    <t>9思</t>
+  </si>
+  <si>
     <t>1250京</t>
   </si>
   <si>
@@ -3119,6 +3224,9 @@
     <t>深渊剧毒</t>
   </si>
   <si>
+    <t>90思</t>
+  </si>
+  <si>
     <t>6250京</t>
   </si>
   <si>
@@ -3131,6 +3239,9 @@
     <t>深渊锤兵</t>
   </si>
   <si>
+    <t>900思</t>
+  </si>
+  <si>
     <t>3垓</t>
   </si>
   <si>
@@ -3143,6 +3254,9 @@
     <t>深渊魔牛</t>
   </si>
   <si>
+    <t>9000思</t>
+  </si>
+  <si>
     <t>15垓</t>
   </si>
   <si>
@@ -3155,6 +3269,9 @@
     <t>深渊水龙</t>
   </si>
   <si>
+    <t>9议</t>
+  </si>
+  <si>
     <t>75垓</t>
   </si>
   <si>
@@ -3167,6 +3284,9 @@
     <t>深渊土龙</t>
   </si>
   <si>
+    <t>90议</t>
+  </si>
+  <si>
     <t>375垓</t>
   </si>
   <si>
@@ -3179,6 +3299,9 @@
     <t>深渊毒龙</t>
   </si>
   <si>
+    <t>900议</t>
+  </si>
+  <si>
     <t>2000垓</t>
   </si>
   <si>
@@ -3191,6 +3314,9 @@
     <t>深渊火龙</t>
   </si>
   <si>
+    <t>9000议</t>
+  </si>
+  <si>
     <t>1秭</t>
   </si>
   <si>
@@ -3201,6 +3327,9 @@
   </si>
   <si>
     <t>深渊冰龙</t>
+  </si>
+  <si>
+    <t>9无</t>
   </si>
   <si>
     <t>5秭</t>
@@ -4184,10 +4313,10 @@
     <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="57.1666666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="54.5833333333333" style="2" customWidth="1"/>
     <col min="8" max="8" width="60.5833333333333" style="2" customWidth="1"/>
     <col min="9" max="9" width="69.1666666666667" style="2" customWidth="1"/>
-    <col min="10" max="10" width="26.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.75" style="2" customWidth="1"/>
     <col min="11" max="11" width="12.75" style="2" customWidth="1"/>
     <col min="12" max="12" width="9.375" style="2" customWidth="1"/>
     <col min="13" max="13" width="9.125" style="2" customWidth="1"/>
@@ -4419,7 +4548,7 @@
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
     </row>
-    <row r="6" ht="14.25" spans="3:19">
+    <row r="6" ht="14" spans="3:19">
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
@@ -12912,17 +13041,17 @@
       <c r="F147" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="G147" s="14" t="s">
-        <v>717</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>717</v>
-      </c>
-      <c r="I147" s="15" t="s">
-        <v>718</v>
+      <c r="G147" s="7" t="s">
+        <v>926</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>926</v>
+      </c>
+      <c r="I147" s="9" t="s">
+        <v>927</v>
       </c>
       <c r="J147" s="1">
-        <f>J146*5</f>
+        <f t="shared" ref="J147:J155" si="46">J146*5</f>
         <v>50</v>
       </c>
       <c r="K147" s="1">
@@ -12953,10 +13082,10 @@
         <v>99.99</v>
       </c>
       <c r="R147" s="10" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="S147" s="10" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="V147" s="2"/>
       <c r="W147" s="2"/>
@@ -12966,28 +13095,28 @@
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="1" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="E148" s="1">
         <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>929</v>
-      </c>
-      <c r="G148" s="14" t="s">
-        <v>723</v>
-      </c>
-      <c r="H148" s="10" t="s">
-        <v>723</v>
-      </c>
-      <c r="I148" s="15" t="s">
-        <v>724</v>
+        <v>931</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>932</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>932</v>
+      </c>
+      <c r="I148" s="9" t="s">
+        <v>933</v>
       </c>
       <c r="J148" s="1">
-        <f>J147*5</f>
+        <f t="shared" si="46"/>
         <v>250</v>
       </c>
       <c r="K148" s="1">
@@ -13018,10 +13147,10 @@
         <v>99.99</v>
       </c>
       <c r="R148" s="10" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="S148" s="10" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="V148" s="2"/>
       <c r="W148" s="2"/>
@@ -13031,28 +13160,28 @@
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="1" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="E149" s="1">
         <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>933</v>
-      </c>
-      <c r="G149" s="14" t="s">
-        <v>729</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>729</v>
-      </c>
-      <c r="I149" s="15" t="s">
-        <v>730</v>
+        <v>937</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>938</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>938</v>
+      </c>
+      <c r="I149" s="9" t="s">
+        <v>939</v>
       </c>
       <c r="J149" s="1">
-        <f>J148*5</f>
+        <f t="shared" si="46"/>
         <v>1250</v>
       </c>
       <c r="K149" s="1">
@@ -13083,10 +13212,10 @@
         <v>99.99</v>
       </c>
       <c r="R149" s="10" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="S149" s="10" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="V149" s="2"/>
       <c r="W149" s="2"/>
@@ -13096,28 +13225,28 @@
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="1" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="E150" s="1">
         <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>937</v>
-      </c>
-      <c r="G150" s="14" t="s">
-        <v>735</v>
-      </c>
-      <c r="H150" s="10" t="s">
-        <v>735</v>
-      </c>
-      <c r="I150" s="15" t="s">
-        <v>736</v>
+        <v>943</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="I150" s="9" t="s">
+        <v>945</v>
       </c>
       <c r="J150" s="1">
-        <f>J149*5</f>
+        <f t="shared" si="46"/>
         <v>6250</v>
       </c>
       <c r="K150" s="1">
@@ -13148,10 +13277,10 @@
         <v>99.99</v>
       </c>
       <c r="R150" s="10" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="S150" s="10" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="V150" s="2"/>
       <c r="W150" s="2"/>
@@ -13161,28 +13290,28 @@
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="1" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E151" s="1">
         <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="G151" s="14" t="s">
-        <v>741</v>
-      </c>
-      <c r="H151" s="10" t="s">
-        <v>741</v>
-      </c>
-      <c r="I151" s="15" t="s">
-        <v>742</v>
+        <v>949</v>
+      </c>
+      <c r="G151" s="7" t="s">
+        <v>950</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>950</v>
+      </c>
+      <c r="I151" s="9" t="s">
+        <v>951</v>
       </c>
       <c r="J151" s="1">
-        <f>J150*5</f>
+        <f t="shared" si="46"/>
         <v>31250</v>
       </c>
       <c r="K151" s="1">
@@ -13213,10 +13342,10 @@
         <v>99.99</v>
       </c>
       <c r="R151" s="10" t="s">
-        <v>942</v>
+        <v>952</v>
       </c>
       <c r="S151" s="10" t="s">
-        <v>942</v>
+        <v>952</v>
       </c>
       <c r="T151" s="2"/>
       <c r="U151" s="2"/>
@@ -13228,28 +13357,28 @@
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="1" t="s">
-        <v>943</v>
+        <v>953</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="E152" s="1">
         <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="G152" s="14" t="s">
-        <v>747</v>
-      </c>
-      <c r="H152" s="10" t="s">
-        <v>747</v>
-      </c>
-      <c r="I152" s="15" t="s">
-        <v>748</v>
+        <v>955</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>956</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>956</v>
+      </c>
+      <c r="I152" s="9" t="s">
+        <v>957</v>
       </c>
       <c r="J152" s="1">
-        <f>J151*5</f>
+        <f t="shared" si="46"/>
         <v>156250</v>
       </c>
       <c r="K152" s="1">
@@ -13280,10 +13409,10 @@
         <v>99.99</v>
       </c>
       <c r="R152" s="10" t="s">
-        <v>946</v>
+        <v>958</v>
       </c>
       <c r="S152" s="10" t="s">
-        <v>946</v>
+        <v>958</v>
       </c>
       <c r="T152" s="2"/>
       <c r="U152" s="2"/>
@@ -13295,28 +13424,28 @@
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="1" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>948</v>
+        <v>960</v>
       </c>
       <c r="E153" s="1">
         <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>949</v>
-      </c>
-      <c r="G153" s="14" t="s">
-        <v>753</v>
-      </c>
-      <c r="H153" s="10" t="s">
-        <v>753</v>
-      </c>
-      <c r="I153" s="15" t="s">
-        <v>754</v>
+        <v>961</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>962</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>962</v>
+      </c>
+      <c r="I153" s="9" t="s">
+        <v>963</v>
       </c>
       <c r="J153" s="1">
-        <f>J152*5</f>
+        <f t="shared" si="46"/>
         <v>781250</v>
       </c>
       <c r="K153" s="1">
@@ -13347,10 +13476,10 @@
         <v>99.99</v>
       </c>
       <c r="R153" s="10" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="S153" s="10" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="T153" s="2"/>
       <c r="U153" s="2"/>
@@ -13362,28 +13491,28 @@
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="1" t="s">
-        <v>951</v>
+        <v>965</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>952</v>
+        <v>966</v>
       </c>
       <c r="E154" s="1">
         <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>953</v>
-      </c>
-      <c r="G154" s="14" t="s">
-        <v>759</v>
-      </c>
-      <c r="H154" s="10" t="s">
-        <v>759</v>
-      </c>
-      <c r="I154" s="15" t="s">
-        <v>760</v>
+        <v>967</v>
+      </c>
+      <c r="G154" s="7" t="s">
+        <v>968</v>
+      </c>
+      <c r="H154" s="7" t="s">
+        <v>968</v>
+      </c>
+      <c r="I154" s="9" t="s">
+        <v>969</v>
       </c>
       <c r="J154" s="1">
-        <f>J153*5</f>
+        <f t="shared" si="46"/>
         <v>3906250</v>
       </c>
       <c r="K154" s="1">
@@ -13414,10 +13543,10 @@
         <v>99.99</v>
       </c>
       <c r="R154" s="10" t="s">
-        <v>954</v>
+        <v>970</v>
       </c>
       <c r="S154" s="10" t="s">
-        <v>954</v>
+        <v>970</v>
       </c>
       <c r="T154" s="2"/>
       <c r="U154" s="2"/>
@@ -13429,28 +13558,28 @@
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="1" t="s">
-        <v>955</v>
+        <v>971</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>956</v>
+        <v>972</v>
       </c>
       <c r="E155" s="1">
         <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>957</v>
-      </c>
-      <c r="G155" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="H155" s="10" t="s">
-        <v>765</v>
-      </c>
-      <c r="I155" s="15" t="s">
-        <v>766</v>
+        <v>973</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>974</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>974</v>
+      </c>
+      <c r="I155" s="9" t="s">
+        <v>975</v>
       </c>
       <c r="J155" s="1">
-        <f>J154*5</f>
+        <f t="shared" si="46"/>
         <v>19531250</v>
       </c>
       <c r="K155" s="1">
@@ -13481,10 +13610,10 @@
         <v>99.99</v>
       </c>
       <c r="R155" s="10" t="s">
-        <v>958</v>
+        <v>976</v>
       </c>
       <c r="S155" s="10" t="s">
-        <v>958</v>
+        <v>976</v>
       </c>
       <c r="T155" s="2"/>
       <c r="U155" s="2"/>
@@ -13496,28 +13625,28 @@
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="1" t="s">
-        <v>959</v>
+        <v>977</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>960</v>
+        <v>978</v>
       </c>
       <c r="E156" s="1">
         <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="G156" s="14" t="s">
-        <v>712</v>
-      </c>
-      <c r="H156" s="10" t="s">
-        <v>712</v>
+        <v>979</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>980</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>980</v>
       </c>
       <c r="I156" s="15" t="s">
         <v>771</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>962</v>
+        <v>981</v>
       </c>
       <c r="K156" s="1">
         <f t="shared" si="42"/>
@@ -13562,28 +13691,28 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="1" t="s">
-        <v>963</v>
+        <v>982</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>964</v>
+        <v>983</v>
       </c>
       <c r="E157" s="1">
         <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>965</v>
-      </c>
-      <c r="G157" s="14" t="s">
-        <v>776</v>
-      </c>
-      <c r="H157" s="10" t="s">
-        <v>776</v>
+        <v>984</v>
+      </c>
+      <c r="G157" s="7" t="s">
+        <v>985</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>985</v>
       </c>
       <c r="I157" s="15" t="s">
         <v>777</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>966</v>
+        <v>986</v>
       </c>
       <c r="K157" s="1">
         <f t="shared" si="42"/>
@@ -13628,28 +13757,28 @@
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="1" t="s">
-        <v>967</v>
+        <v>987</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>968</v>
+        <v>988</v>
       </c>
       <c r="E158" s="1">
         <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>969</v>
-      </c>
-      <c r="G158" s="14" t="s">
-        <v>782</v>
-      </c>
-      <c r="H158" s="10" t="s">
-        <v>782</v>
+        <v>989</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>990</v>
+      </c>
+      <c r="H158" s="7" t="s">
+        <v>990</v>
       </c>
       <c r="I158" s="15" t="s">
         <v>783</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>970</v>
+        <v>991</v>
       </c>
       <c r="K158" s="1">
         <f t="shared" si="42"/>
@@ -13694,28 +13823,28 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="1" t="s">
-        <v>971</v>
+        <v>992</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="E159" s="1">
         <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>973</v>
-      </c>
-      <c r="G159" s="14" t="s">
-        <v>788</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>788</v>
+        <v>994</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>995</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>995</v>
       </c>
       <c r="I159" s="15" t="s">
         <v>789</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>974</v>
+        <v>996</v>
       </c>
       <c r="K159" s="1">
         <f t="shared" si="42"/>
@@ -13760,28 +13889,28 @@
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="1" t="s">
-        <v>975</v>
+        <v>997</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>976</v>
+        <v>998</v>
       </c>
       <c r="E160" s="1">
         <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="G160" s="14" t="s">
-        <v>794</v>
-      </c>
-      <c r="H160" s="10" t="s">
-        <v>794</v>
+        <v>999</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H160" s="7" t="s">
+        <v>1000</v>
       </c>
       <c r="I160" s="15" t="s">
         <v>795</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>978</v>
+        <v>1001</v>
       </c>
       <c r="K160" s="1">
         <f t="shared" si="42"/>
@@ -13826,28 +13955,28 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="1" t="s">
-        <v>979</v>
+        <v>1002</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>980</v>
+        <v>1003</v>
       </c>
       <c r="E161" s="1">
         <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>981</v>
-      </c>
-      <c r="G161" s="14" t="s">
-        <v>800</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>800</v>
+        <v>1004</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>1005</v>
       </c>
       <c r="I161" s="15" t="s">
         <v>801</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>982</v>
+        <v>1006</v>
       </c>
       <c r="K161" s="1">
         <f t="shared" si="42"/>
@@ -13892,28 +14021,28 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="1" t="s">
-        <v>983</v>
+        <v>1007</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>984</v>
+        <v>1008</v>
       </c>
       <c r="E162" s="1">
         <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="G162" s="14" t="s">
-        <v>806</v>
-      </c>
-      <c r="H162" s="10" t="s">
-        <v>806</v>
+        <v>1009</v>
+      </c>
+      <c r="G162" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>1010</v>
       </c>
       <c r="I162" s="15" t="s">
         <v>807</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>986</v>
+        <v>1011</v>
       </c>
       <c r="K162" s="1">
         <f t="shared" si="42"/>
@@ -13958,28 +14087,28 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="1" t="s">
-        <v>987</v>
+        <v>1012</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>988</v>
+        <v>1013</v>
       </c>
       <c r="E163" s="1">
         <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="G163" s="14" t="s">
-        <v>812</v>
-      </c>
-      <c r="H163" s="10" t="s">
-        <v>812</v>
+        <v>1014</v>
+      </c>
+      <c r="G163" s="7" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H163" s="7" t="s">
+        <v>1015</v>
       </c>
       <c r="I163" s="15" t="s">
         <v>813</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>990</v>
+        <v>1016</v>
       </c>
       <c r="K163" s="1">
         <f t="shared" si="42"/>
@@ -14024,28 +14153,28 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="1" t="s">
-        <v>991</v>
+        <v>1017</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>992</v>
+        <v>1018</v>
       </c>
       <c r="E164" s="1">
         <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>993</v>
-      </c>
-      <c r="G164" s="14" t="s">
-        <v>818</v>
-      </c>
-      <c r="H164" s="10" t="s">
-        <v>818</v>
+        <v>1019</v>
+      </c>
+      <c r="G164" s="7" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>1020</v>
       </c>
       <c r="I164" s="15" t="s">
         <v>819</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>994</v>
+        <v>1021</v>
       </c>
       <c r="K164" s="1">
         <f t="shared" si="42"/>
@@ -14090,28 +14219,28 @@
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="1" t="s">
-        <v>995</v>
+        <v>1022</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>996</v>
+        <v>1023</v>
       </c>
       <c r="E165" s="1">
         <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="G165" s="14" t="s">
-        <v>824</v>
-      </c>
-      <c r="H165" s="10" t="s">
-        <v>824</v>
+        <v>1024</v>
+      </c>
+      <c r="G165" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H165" s="7" t="s">
+        <v>1025</v>
       </c>
       <c r="I165" s="15" t="s">
         <v>825</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>998</v>
+        <v>1026</v>
       </c>
       <c r="K165" s="1">
         <f t="shared" si="42"/>
@@ -14154,28 +14283,28 @@
     </row>
     <row r="166" customHeight="1" spans="3:19">
       <c r="C166" s="1" t="s">
-        <v>999</v>
+        <v>1027</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>1000</v>
+        <v>1028</v>
       </c>
       <c r="E166" s="1">
         <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G166" s="14" t="s">
-        <v>830</v>
-      </c>
-      <c r="H166" s="10" t="s">
-        <v>830</v>
+        <v>1029</v>
+      </c>
+      <c r="G166" s="7" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H166" s="7" t="s">
+        <v>1030</v>
       </c>
       <c r="I166" s="15" t="s">
         <v>831</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>1002</v>
+        <v>1031</v>
       </c>
       <c r="K166" s="1">
         <f t="shared" si="42"/>
@@ -14213,28 +14342,28 @@
     </row>
     <row r="167" customHeight="1" spans="3:19">
       <c r="C167" s="1" t="s">
-        <v>1003</v>
+        <v>1032</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>1004</v>
+        <v>1033</v>
       </c>
       <c r="E167" s="1">
         <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G167" s="14" t="s">
-        <v>836</v>
-      </c>
-      <c r="H167" s="10" t="s">
-        <v>836</v>
+        <v>1034</v>
+      </c>
+      <c r="G167" s="7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H167" s="7" t="s">
+        <v>1035</v>
       </c>
       <c r="I167" s="15" t="s">
         <v>837</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>1006</v>
+        <v>1036</v>
       </c>
       <c r="K167" s="1">
         <f t="shared" si="42"/>
@@ -14272,28 +14401,28 @@
     </row>
     <row r="168" customHeight="1" spans="3:19">
       <c r="C168" s="1" t="s">
-        <v>1007</v>
+        <v>1037</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>1008</v>
+        <v>1038</v>
       </c>
       <c r="E168" s="1">
         <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G168" s="14" t="s">
-        <v>842</v>
-      </c>
-      <c r="H168" s="10" t="s">
-        <v>842</v>
+        <v>1039</v>
+      </c>
+      <c r="G168" s="7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H168" s="7" t="s">
+        <v>1040</v>
       </c>
       <c r="I168" s="15" t="s">
         <v>843</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>1010</v>
+        <v>1041</v>
       </c>
       <c r="K168" s="1">
         <f t="shared" si="42"/>
@@ -14331,28 +14460,28 @@
     </row>
     <row r="169" customHeight="1" spans="3:19">
       <c r="C169" s="1" t="s">
-        <v>1011</v>
+        <v>1042</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>1012</v>
+        <v>1043</v>
       </c>
       <c r="E169" s="1">
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G169" s="14" t="s">
-        <v>848</v>
-      </c>
-      <c r="H169" s="10" t="s">
-        <v>848</v>
+        <v>1044</v>
+      </c>
+      <c r="G169" s="7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H169" s="7" t="s">
+        <v>1045</v>
       </c>
       <c r="I169" s="15" t="s">
         <v>849</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>1014</v>
+        <v>1046</v>
       </c>
       <c r="K169" s="1">
         <f t="shared" si="42"/>
@@ -14390,28 +14519,28 @@
     </row>
     <row r="170" customHeight="1" spans="3:19">
       <c r="C170" s="1" t="s">
-        <v>1015</v>
+        <v>1047</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>1016</v>
+        <v>1048</v>
       </c>
       <c r="E170" s="1">
         <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G170" s="14" t="s">
-        <v>854</v>
-      </c>
-      <c r="H170" s="10" t="s">
-        <v>854</v>
+        <v>1049</v>
+      </c>
+      <c r="G170" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H170" s="7" t="s">
+        <v>1050</v>
       </c>
       <c r="I170" s="15" t="s">
         <v>855</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>1018</v>
+        <v>1051</v>
       </c>
       <c r="K170" s="1">
         <f t="shared" si="42"/>
@@ -14449,28 +14578,28 @@
     </row>
     <row r="171" customHeight="1" spans="3:19">
       <c r="C171" s="1" t="s">
-        <v>1019</v>
+        <v>1052</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>1020</v>
+        <v>1053</v>
       </c>
       <c r="E171" s="1">
         <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1021</v>
-      </c>
-      <c r="G171" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="H171" s="10" t="s">
-        <v>860</v>
+        <v>1054</v>
+      </c>
+      <c r="G171" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H171" s="7" t="s">
+        <v>1055</v>
       </c>
       <c r="I171" s="15" t="s">
         <v>861</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>1022</v>
+        <v>1056</v>
       </c>
       <c r="K171" s="1">
         <f t="shared" si="42"/>
@@ -14508,28 +14637,28 @@
     </row>
     <row r="172" customHeight="1" spans="3:19">
       <c r="C172" s="1" t="s">
-        <v>1023</v>
+        <v>1057</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>1024</v>
+        <v>1058</v>
       </c>
       <c r="E172" s="1">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G172" s="14" t="s">
-        <v>866</v>
-      </c>
-      <c r="H172" s="10" t="s">
-        <v>866</v>
+        <v>1059</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H172" s="7" t="s">
+        <v>1060</v>
       </c>
       <c r="I172" s="15" t="s">
         <v>867</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>1026</v>
+        <v>1061</v>
       </c>
       <c r="K172" s="1">
         <f t="shared" si="42"/>
@@ -14567,28 +14696,28 @@
     </row>
     <row r="173" customHeight="1" spans="3:19">
       <c r="C173" s="1" t="s">
-        <v>1027</v>
+        <v>1062</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>1028</v>
+        <v>1063</v>
       </c>
       <c r="E173" s="1">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G173" s="14" t="s">
-        <v>872</v>
-      </c>
-      <c r="H173" s="10" t="s">
-        <v>872</v>
+        <v>1064</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H173" s="7" t="s">
+        <v>1065</v>
       </c>
       <c r="I173" s="15" t="s">
         <v>873</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>1030</v>
+        <v>1066</v>
       </c>
       <c r="K173" s="1">
         <f t="shared" si="42"/>
@@ -14626,28 +14755,28 @@
     </row>
     <row r="174" customHeight="1" spans="3:19">
       <c r="C174" s="1" t="s">
-        <v>1031</v>
+        <v>1067</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>1032</v>
+        <v>1068</v>
       </c>
       <c r="E174" s="1">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G174" s="14" t="s">
-        <v>878</v>
-      </c>
-      <c r="H174" s="10" t="s">
-        <v>878</v>
+        <v>1069</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H174" s="7" t="s">
+        <v>1070</v>
       </c>
       <c r="I174" s="15" t="s">
         <v>879</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>1034</v>
+        <v>1071</v>
       </c>
       <c r="K174" s="1">
         <f t="shared" si="42"/>
@@ -14685,28 +14814,28 @@
     </row>
     <row r="175" customHeight="1" spans="3:19">
       <c r="C175" s="1" t="s">
-        <v>1035</v>
+        <v>1072</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>1036</v>
+        <v>1073</v>
       </c>
       <c r="E175" s="1">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1037</v>
-      </c>
-      <c r="G175" s="14" t="s">
-        <v>884</v>
-      </c>
-      <c r="H175" s="10" t="s">
-        <v>884</v>
+        <v>1074</v>
+      </c>
+      <c r="G175" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H175" s="7" t="s">
+        <v>1075</v>
       </c>
       <c r="I175" s="15" t="s">
         <v>885</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1038</v>
+        <v>1076</v>
       </c>
       <c r="K175" s="1">
         <f t="shared" si="42"/>
@@ -14746,28 +14875,28 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="1" t="s">
-        <v>1039</v>
+        <v>1077</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>1040</v>
+        <v>1078</v>
       </c>
       <c r="E176" s="1">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1041</v>
-      </c>
-      <c r="G176" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="H176" s="10" t="s">
-        <v>890</v>
+        <v>1079</v>
+      </c>
+      <c r="G176" s="7" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H176" s="7" t="s">
+        <v>1080</v>
       </c>
       <c r="I176" s="15" t="s">
         <v>891</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>1042</v>
+        <v>1081</v>
       </c>
       <c r="K176" s="1">
         <f t="shared" si="42"/>
@@ -14812,28 +14941,28 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="1" t="s">
-        <v>1043</v>
+        <v>1082</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>1044</v>
+        <v>1083</v>
       </c>
       <c r="E177" s="1">
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G177" s="14" t="s">
-        <v>896</v>
-      </c>
-      <c r="H177" s="10" t="s">
-        <v>896</v>
+        <v>1084</v>
+      </c>
+      <c r="G177" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H177" s="7" t="s">
+        <v>1085</v>
       </c>
       <c r="I177" s="15" t="s">
         <v>897</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1046</v>
+        <v>1086</v>
       </c>
       <c r="K177" s="1">
         <f t="shared" si="42"/>
@@ -14878,28 +15007,28 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="1" t="s">
-        <v>1047</v>
+        <v>1087</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1048</v>
+        <v>1088</v>
       </c>
       <c r="E178" s="1">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1049</v>
-      </c>
-      <c r="G178" s="14" t="s">
-        <v>902</v>
-      </c>
-      <c r="H178" s="10" t="s">
-        <v>902</v>
+        <v>1089</v>
+      </c>
+      <c r="G178" s="7" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H178" s="7" t="s">
+        <v>1090</v>
       </c>
       <c r="I178" s="15" t="s">
         <v>903</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>1050</v>
+        <v>1091</v>
       </c>
       <c r="K178" s="1">
         <f t="shared" si="42"/>
@@ -14944,28 +15073,28 @@
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="1" t="s">
-        <v>1051</v>
+        <v>1092</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1052</v>
+        <v>1093</v>
       </c>
       <c r="E179" s="1">
         <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1053</v>
-      </c>
-      <c r="G179" s="14" t="s">
-        <v>908</v>
-      </c>
-      <c r="H179" s="10" t="s">
-        <v>908</v>
+        <v>1094</v>
+      </c>
+      <c r="G179" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H179" s="7" t="s">
+        <v>1095</v>
       </c>
       <c r="I179" s="15" t="s">
         <v>909</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1054</v>
+        <v>1096</v>
       </c>
       <c r="K179" s="1">
         <f t="shared" si="42"/>
@@ -15010,28 +15139,28 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="1" t="s">
-        <v>1055</v>
+        <v>1097</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1056</v>
+        <v>1098</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="G180" s="14" t="s">
-        <v>914</v>
-      </c>
-      <c r="H180" s="10" t="s">
-        <v>914</v>
+        <v>1099</v>
+      </c>
+      <c r="G180" s="7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H180" s="7" t="s">
+        <v>1100</v>
       </c>
       <c r="I180" s="15" t="s">
         <v>915</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>1058</v>
+        <v>1101</v>
       </c>
       <c r="K180" s="1">
         <f t="shared" si="42"/>
@@ -15074,7 +15203,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3 J4 J5 C3:I5 K3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="1102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="1116">
   <si>
     <t>ID</t>
   </si>
@@ -2972,6 +2972,9 @@
     <t>9由</t>
   </si>
   <si>
+    <t>32000无</t>
+  </si>
+  <si>
     <t>1亿</t>
   </si>
   <si>
@@ -2987,6 +2990,9 @@
     <t>90由</t>
   </si>
   <si>
+    <t>64无</t>
+  </si>
+  <si>
     <t>5亿</t>
   </si>
   <si>
@@ -3002,6 +3008,9 @@
     <t>900由</t>
   </si>
   <si>
+    <t>1280无</t>
+  </si>
+  <si>
     <t>20亿</t>
   </si>
   <si>
@@ -3017,6 +3026,9 @@
     <t>9000由</t>
   </si>
   <si>
+    <t>51200无</t>
+  </si>
+  <si>
     <t>100亿</t>
   </si>
   <si>
@@ -3032,6 +3044,9 @@
     <t>9他</t>
   </si>
   <si>
+    <t>10量</t>
+  </si>
+  <si>
     <t>500亿</t>
   </si>
   <si>
@@ -3047,6 +3062,9 @@
     <t>90他</t>
   </si>
   <si>
+    <t>200量</t>
+  </si>
+  <si>
     <t>2500亿</t>
   </si>
   <si>
@@ -3062,6 +3080,9 @@
     <t>900他</t>
   </si>
   <si>
+    <t>4000量</t>
+  </si>
+  <si>
     <t>12500亿</t>
   </si>
   <si>
@@ -3077,6 +3098,9 @@
     <t>9000他</t>
   </si>
   <si>
+    <t>8大</t>
+  </si>
+  <si>
     <t>62500亿</t>
   </si>
   <si>
@@ -3092,6 +3116,9 @@
     <t>9不</t>
   </si>
   <si>
+    <t>160大</t>
+  </si>
+  <si>
     <t>32兆</t>
   </si>
   <si>
@@ -3107,6 +3134,9 @@
     <t>90不</t>
   </si>
   <si>
+    <t>3200大</t>
+  </si>
+  <si>
     <t>160兆</t>
   </si>
   <si>
@@ -3122,6 +3152,9 @@
     <t>900不</t>
   </si>
   <si>
+    <t>64000大</t>
+  </si>
+  <si>
     <t>800兆</t>
   </si>
   <si>
@@ -3137,6 +3170,9 @@
     <t>9000不</t>
   </si>
   <si>
+    <t>128数</t>
+  </si>
+  <si>
     <t>4000兆</t>
   </si>
   <si>
@@ -3152,6 +3188,9 @@
     <t>9可</t>
   </si>
   <si>
+    <t>2560数</t>
+  </si>
+  <si>
     <t>2京</t>
   </si>
   <si>
@@ -3165,6 +3204,9 @@
   </si>
   <si>
     <t>90可</t>
+  </si>
+  <si>
+    <t>5120数</t>
   </si>
   <si>
     <t>10京</t>
@@ -12084,11 +12126,11 @@
         <v>1950</v>
       </c>
       <c r="O131" s="2">
-        <f t="shared" ref="O131:O180" si="36">O130+2</f>
+        <f>O130+2</f>
         <v>51</v>
       </c>
       <c r="P131" s="2">
-        <f t="shared" ref="P131:P180" si="37">P130+4</f>
+        <f t="shared" ref="P131:P180" si="36">P130+4</f>
         <v>34</v>
       </c>
       <c r="Q131" s="2">
@@ -12143,11 +12185,11 @@
         <v>2050</v>
       </c>
       <c r="O132" s="2">
+        <f>O131+2</f>
+        <v>53</v>
+      </c>
+      <c r="P132" s="2">
         <f t="shared" si="36"/>
-        <v>53</v>
-      </c>
-      <c r="P132" s="2">
-        <f t="shared" si="37"/>
         <v>38</v>
       </c>
       <c r="Q132" s="2">
@@ -12202,11 +12244,11 @@
         <v>2150</v>
       </c>
       <c r="O133" s="2">
+        <f>O132+2</f>
+        <v>55</v>
+      </c>
+      <c r="P133" s="2">
         <f t="shared" si="36"/>
-        <v>55</v>
-      </c>
-      <c r="P133" s="2">
-        <f t="shared" si="37"/>
         <v>42</v>
       </c>
       <c r="Q133" s="2">
@@ -12261,11 +12303,11 @@
         <v>2250</v>
       </c>
       <c r="O134" s="2">
+        <f>O133+2</f>
+        <v>57</v>
+      </c>
+      <c r="P134" s="2">
         <f t="shared" si="36"/>
-        <v>57</v>
-      </c>
-      <c r="P134" s="2">
-        <f t="shared" si="37"/>
         <v>46</v>
       </c>
       <c r="Q134" s="2">
@@ -12320,11 +12362,11 @@
         <v>2350</v>
       </c>
       <c r="O135" s="2">
+        <f>O134+2</f>
+        <v>59</v>
+      </c>
+      <c r="P135" s="2">
         <f t="shared" si="36"/>
-        <v>59</v>
-      </c>
-      <c r="P135" s="2">
-        <f t="shared" si="37"/>
         <v>50</v>
       </c>
       <c r="Q135" s="2">
@@ -12363,27 +12405,27 @@
         <v>0</v>
       </c>
       <c r="K136" s="1">
-        <f t="shared" ref="K136:K145" si="38">K135+500</f>
+        <f t="shared" ref="K136:K145" si="37">K135+500</f>
         <v>6800</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" ref="L136:L145" si="39">L135+500</f>
+        <f t="shared" ref="L136:L145" si="38">L135+500</f>
         <v>8500</v>
       </c>
       <c r="M136" s="1">
-        <f t="shared" ref="M136:M145" si="40">M135+200</f>
+        <f t="shared" ref="M136:M145" si="39">M135+200</f>
         <v>2550</v>
       </c>
       <c r="N136" s="1">
-        <f t="shared" ref="N136:N145" si="41">N135+200</f>
+        <f t="shared" ref="N136:N145" si="40">N135+200</f>
         <v>2550</v>
       </c>
       <c r="O136" s="2">
+        <f>O135+2</f>
+        <v>61</v>
+      </c>
+      <c r="P136" s="2">
         <f t="shared" si="36"/>
-        <v>61</v>
-      </c>
-      <c r="P136" s="2">
-        <f t="shared" si="37"/>
         <v>54</v>
       </c>
       <c r="Q136" s="2">
@@ -12422,27 +12464,27 @@
         <v>0</v>
       </c>
       <c r="K137" s="1">
+        <f t="shared" si="37"/>
+        <v>7300</v>
+      </c>
+      <c r="L137" s="1">
         <f t="shared" si="38"/>
-        <v>7300</v>
-      </c>
-      <c r="L137" s="1">
+        <v>9000</v>
+      </c>
+      <c r="M137" s="1">
         <f t="shared" si="39"/>
-        <v>9000</v>
-      </c>
-      <c r="M137" s="1">
+        <v>2750</v>
+      </c>
+      <c r="N137" s="1">
         <f t="shared" si="40"/>
         <v>2750</v>
       </c>
-      <c r="N137" s="1">
-        <f t="shared" si="41"/>
-        <v>2750</v>
-      </c>
       <c r="O137" s="2">
+        <f>O136+2</f>
+        <v>63</v>
+      </c>
+      <c r="P137" s="2">
         <f t="shared" si="36"/>
-        <v>63</v>
-      </c>
-      <c r="P137" s="2">
-        <f t="shared" si="37"/>
         <v>58</v>
       </c>
       <c r="Q137" s="2">
@@ -12481,27 +12523,27 @@
         <v>0</v>
       </c>
       <c r="K138" s="1">
+        <f t="shared" si="37"/>
+        <v>7800</v>
+      </c>
+      <c r="L138" s="1">
         <f t="shared" si="38"/>
-        <v>7800</v>
-      </c>
-      <c r="L138" s="1">
+        <v>9500</v>
+      </c>
+      <c r="M138" s="1">
         <f t="shared" si="39"/>
-        <v>9500</v>
-      </c>
-      <c r="M138" s="1">
+        <v>2950</v>
+      </c>
+      <c r="N138" s="1">
         <f t="shared" si="40"/>
         <v>2950</v>
       </c>
-      <c r="N138" s="1">
-        <f t="shared" si="41"/>
-        <v>2950</v>
-      </c>
       <c r="O138" s="2">
+        <f>O137+2</f>
+        <v>65</v>
+      </c>
+      <c r="P138" s="2">
         <f t="shared" si="36"/>
-        <v>65</v>
-      </c>
-      <c r="P138" s="2">
-        <f t="shared" si="37"/>
         <v>62</v>
       </c>
       <c r="Q138" s="2">
@@ -12540,27 +12582,27 @@
         <v>0</v>
       </c>
       <c r="K139" s="1">
+        <f t="shared" si="37"/>
+        <v>8300</v>
+      </c>
+      <c r="L139" s="1">
         <f t="shared" si="38"/>
-        <v>8300</v>
-      </c>
-      <c r="L139" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M139" s="1">
         <f t="shared" si="39"/>
-        <v>10000</v>
-      </c>
-      <c r="M139" s="1">
+        <v>3150</v>
+      </c>
+      <c r="N139" s="1">
         <f t="shared" si="40"/>
         <v>3150</v>
       </c>
-      <c r="N139" s="1">
-        <f t="shared" si="41"/>
-        <v>3150</v>
-      </c>
       <c r="O139" s="2">
+        <f>O138+2</f>
+        <v>67</v>
+      </c>
+      <c r="P139" s="2">
         <f t="shared" si="36"/>
-        <v>67</v>
-      </c>
-      <c r="P139" s="2">
-        <f t="shared" si="37"/>
         <v>66</v>
       </c>
       <c r="Q139" s="2">
@@ -12599,27 +12641,27 @@
         <v>0</v>
       </c>
       <c r="K140" s="1">
+        <f t="shared" si="37"/>
+        <v>8800</v>
+      </c>
+      <c r="L140" s="1">
         <f t="shared" si="38"/>
-        <v>8800</v>
-      </c>
-      <c r="L140" s="1">
+        <v>10500</v>
+      </c>
+      <c r="M140" s="1">
         <f t="shared" si="39"/>
-        <v>10500</v>
-      </c>
-      <c r="M140" s="1">
+        <v>3350</v>
+      </c>
+      <c r="N140" s="1">
         <f t="shared" si="40"/>
         <v>3350</v>
       </c>
-      <c r="N140" s="1">
-        <f t="shared" si="41"/>
-        <v>3350</v>
-      </c>
       <c r="O140" s="2">
+        <f>O139+2</f>
+        <v>69</v>
+      </c>
+      <c r="P140" s="2">
         <f t="shared" si="36"/>
-        <v>69</v>
-      </c>
-      <c r="P140" s="2">
-        <f t="shared" si="37"/>
         <v>70</v>
       </c>
       <c r="Q140" s="2">
@@ -12660,27 +12702,27 @@
         <v>0</v>
       </c>
       <c r="K141" s="1">
-        <f t="shared" ref="K141:K180" si="42">K140+600</f>
+        <f t="shared" ref="K141:K180" si="41">K140+600</f>
         <v>9400</v>
       </c>
       <c r="L141" s="1">
-        <f t="shared" ref="L141:L180" si="43">L140+600</f>
+        <f t="shared" ref="L141:L180" si="42">L140+600</f>
         <v>11100</v>
       </c>
       <c r="M141" s="1">
-        <f t="shared" ref="M141:M180" si="44">M140+250</f>
+        <f t="shared" ref="M141:M180" si="43">M140+250</f>
         <v>3600</v>
       </c>
       <c r="N141" s="1">
-        <f t="shared" ref="N141:N180" si="45">N140+250</f>
+        <f t="shared" ref="N141:N180" si="44">N140+250</f>
         <v>3600</v>
       </c>
       <c r="O141" s="2">
+        <f>O140+2</f>
+        <v>71</v>
+      </c>
+      <c r="P141" s="2">
         <f t="shared" si="36"/>
-        <v>71</v>
-      </c>
-      <c r="P141" s="2">
-        <f t="shared" si="37"/>
         <v>74</v>
       </c>
       <c r="Q141" s="2">
@@ -12726,27 +12768,27 @@
         <v>0</v>
       </c>
       <c r="K142" s="1">
+        <f t="shared" si="41"/>
+        <v>10000</v>
+      </c>
+      <c r="L142" s="1">
         <f t="shared" si="42"/>
-        <v>10000</v>
-      </c>
-      <c r="L142" s="1">
+        <v>11700</v>
+      </c>
+      <c r="M142" s="1">
         <f t="shared" si="43"/>
-        <v>11700</v>
-      </c>
-      <c r="M142" s="1">
+        <v>3850</v>
+      </c>
+      <c r="N142" s="1">
         <f t="shared" si="44"/>
         <v>3850</v>
       </c>
-      <c r="N142" s="1">
-        <f t="shared" si="45"/>
-        <v>3850</v>
-      </c>
       <c r="O142" s="2">
+        <f>O141+2</f>
+        <v>73</v>
+      </c>
+      <c r="P142" s="2">
         <f t="shared" si="36"/>
-        <v>73</v>
-      </c>
-      <c r="P142" s="2">
-        <f t="shared" si="37"/>
         <v>78</v>
       </c>
       <c r="Q142" s="2">
@@ -12792,27 +12834,27 @@
         <v>0</v>
       </c>
       <c r="K143" s="1">
+        <f t="shared" si="41"/>
+        <v>10600</v>
+      </c>
+      <c r="L143" s="1">
         <f t="shared" si="42"/>
-        <v>10600</v>
-      </c>
-      <c r="L143" s="1">
+        <v>12300</v>
+      </c>
+      <c r="M143" s="1">
         <f t="shared" si="43"/>
-        <v>12300</v>
-      </c>
-      <c r="M143" s="1">
+        <v>4100</v>
+      </c>
+      <c r="N143" s="1">
         <f t="shared" si="44"/>
         <v>4100</v>
       </c>
-      <c r="N143" s="1">
-        <f t="shared" si="45"/>
-        <v>4100</v>
-      </c>
       <c r="O143" s="2">
+        <f>O142+2</f>
+        <v>75</v>
+      </c>
+      <c r="P143" s="2">
         <f t="shared" si="36"/>
-        <v>75</v>
-      </c>
-      <c r="P143" s="2">
-        <f t="shared" si="37"/>
         <v>82</v>
       </c>
       <c r="Q143" s="2">
@@ -12858,27 +12900,27 @@
         <v>0</v>
       </c>
       <c r="K144" s="1">
+        <f t="shared" si="41"/>
+        <v>11200</v>
+      </c>
+      <c r="L144" s="1">
         <f t="shared" si="42"/>
-        <v>11200</v>
-      </c>
-      <c r="L144" s="1">
+        <v>12900</v>
+      </c>
+      <c r="M144" s="1">
         <f t="shared" si="43"/>
-        <v>12900</v>
-      </c>
-      <c r="M144" s="1">
+        <v>4350</v>
+      </c>
+      <c r="N144" s="1">
         <f t="shared" si="44"/>
         <v>4350</v>
       </c>
-      <c r="N144" s="1">
-        <f t="shared" si="45"/>
-        <v>4350</v>
-      </c>
       <c r="O144" s="2">
+        <f>O143+2</f>
+        <v>77</v>
+      </c>
+      <c r="P144" s="2">
         <f t="shared" si="36"/>
-        <v>77</v>
-      </c>
-      <c r="P144" s="2">
-        <f t="shared" si="37"/>
         <v>86</v>
       </c>
       <c r="Q144" s="2">
@@ -12924,27 +12966,27 @@
         <v>0</v>
       </c>
       <c r="K145" s="1">
+        <f t="shared" si="41"/>
+        <v>11800</v>
+      </c>
+      <c r="L145" s="1">
         <f t="shared" si="42"/>
-        <v>11800</v>
-      </c>
-      <c r="L145" s="1">
+        <v>13500</v>
+      </c>
+      <c r="M145" s="1">
         <f t="shared" si="43"/>
-        <v>13500</v>
-      </c>
-      <c r="M145" s="1">
+        <v>4600</v>
+      </c>
+      <c r="N145" s="1">
         <f t="shared" si="44"/>
         <v>4600</v>
       </c>
-      <c r="N145" s="1">
-        <f t="shared" si="45"/>
-        <v>4600</v>
-      </c>
       <c r="O145" s="2">
+        <f>O144+2</f>
+        <v>79</v>
+      </c>
+      <c r="P145" s="2">
         <f t="shared" si="36"/>
-        <v>79</v>
-      </c>
-      <c r="P145" s="2">
-        <f t="shared" si="37"/>
         <v>90</v>
       </c>
       <c r="Q145" s="2">
@@ -12990,27 +13032,27 @@
         <v>10</v>
       </c>
       <c r="K146" s="1">
+        <f t="shared" si="41"/>
+        <v>12400</v>
+      </c>
+      <c r="L146" s="1">
         <f t="shared" si="42"/>
-        <v>12400</v>
-      </c>
-      <c r="L146" s="1">
+        <v>14100</v>
+      </c>
+      <c r="M146" s="1">
         <f t="shared" si="43"/>
-        <v>14100</v>
-      </c>
-      <c r="M146" s="1">
+        <v>4850</v>
+      </c>
+      <c r="N146" s="1">
         <f t="shared" si="44"/>
         <v>4850</v>
       </c>
-      <c r="N146" s="1">
-        <f t="shared" si="45"/>
-        <v>4850</v>
-      </c>
       <c r="O146" s="2">
+        <f t="shared" ref="O146:O180" si="45">O145+3</f>
+        <v>82</v>
+      </c>
+      <c r="P146" s="2">
         <f t="shared" si="36"/>
-        <v>81</v>
-      </c>
-      <c r="P146" s="2">
-        <f t="shared" si="37"/>
         <v>94</v>
       </c>
       <c r="Q146" s="2">
@@ -13055,27 +13097,27 @@
         <v>50</v>
       </c>
       <c r="K147" s="1">
+        <f t="shared" si="41"/>
+        <v>13000</v>
+      </c>
+      <c r="L147" s="1">
         <f t="shared" si="42"/>
-        <v>13000</v>
-      </c>
-      <c r="L147" s="1">
+        <v>14700</v>
+      </c>
+      <c r="M147" s="1">
         <f t="shared" si="43"/>
-        <v>14700</v>
-      </c>
-      <c r="M147" s="1">
+        <v>5100</v>
+      </c>
+      <c r="N147" s="1">
         <f t="shared" si="44"/>
         <v>5100</v>
       </c>
-      <c r="N147" s="1">
+      <c r="O147" s="2">
         <f t="shared" si="45"/>
-        <v>5100</v>
-      </c>
-      <c r="O147" s="2">
+        <v>85</v>
+      </c>
+      <c r="P147" s="2">
         <f t="shared" si="36"/>
-        <v>83</v>
-      </c>
-      <c r="P147" s="2">
-        <f t="shared" si="37"/>
         <v>98</v>
       </c>
       <c r="Q147" s="2">
@@ -13120,27 +13162,27 @@
         <v>250</v>
       </c>
       <c r="K148" s="1">
+        <f t="shared" si="41"/>
+        <v>13600</v>
+      </c>
+      <c r="L148" s="1">
         <f t="shared" si="42"/>
-        <v>13600</v>
-      </c>
-      <c r="L148" s="1">
+        <v>15300</v>
+      </c>
+      <c r="M148" s="1">
         <f t="shared" si="43"/>
-        <v>15300</v>
-      </c>
-      <c r="M148" s="1">
+        <v>5350</v>
+      </c>
+      <c r="N148" s="1">
         <f t="shared" si="44"/>
         <v>5350</v>
       </c>
-      <c r="N148" s="1">
+      <c r="O148" s="2">
         <f t="shared" si="45"/>
-        <v>5350</v>
-      </c>
-      <c r="O148" s="2">
+        <v>88</v>
+      </c>
+      <c r="P148" s="2">
         <f t="shared" si="36"/>
-        <v>85</v>
-      </c>
-      <c r="P148" s="2">
-        <f t="shared" si="37"/>
         <v>102</v>
       </c>
       <c r="Q148" s="2">
@@ -13185,27 +13227,27 @@
         <v>1250</v>
       </c>
       <c r="K149" s="1">
+        <f t="shared" si="41"/>
+        <v>14200</v>
+      </c>
+      <c r="L149" s="1">
         <f t="shared" si="42"/>
-        <v>14200</v>
-      </c>
-      <c r="L149" s="1">
+        <v>15900</v>
+      </c>
+      <c r="M149" s="1">
         <f t="shared" si="43"/>
-        <v>15900</v>
-      </c>
-      <c r="M149" s="1">
+        <v>5600</v>
+      </c>
+      <c r="N149" s="1">
         <f t="shared" si="44"/>
         <v>5600</v>
       </c>
-      <c r="N149" s="1">
+      <c r="O149" s="2">
         <f t="shared" si="45"/>
-        <v>5600</v>
-      </c>
-      <c r="O149" s="2">
+        <v>91</v>
+      </c>
+      <c r="P149" s="2">
         <f t="shared" si="36"/>
-        <v>87</v>
-      </c>
-      <c r="P149" s="2">
-        <f t="shared" si="37"/>
         <v>106</v>
       </c>
       <c r="Q149" s="2">
@@ -13250,27 +13292,27 @@
         <v>6250</v>
       </c>
       <c r="K150" s="1">
+        <f t="shared" si="41"/>
+        <v>14800</v>
+      </c>
+      <c r="L150" s="1">
         <f t="shared" si="42"/>
-        <v>14800</v>
-      </c>
-      <c r="L150" s="1">
+        <v>16500</v>
+      </c>
+      <c r="M150" s="1">
         <f t="shared" si="43"/>
-        <v>16500</v>
-      </c>
-      <c r="M150" s="1">
+        <v>5850</v>
+      </c>
+      <c r="N150" s="1">
         <f t="shared" si="44"/>
         <v>5850</v>
       </c>
-      <c r="N150" s="1">
+      <c r="O150" s="2">
         <f t="shared" si="45"/>
-        <v>5850</v>
-      </c>
-      <c r="O150" s="2">
+        <v>94</v>
+      </c>
+      <c r="P150" s="2">
         <f t="shared" si="36"/>
-        <v>89</v>
-      </c>
-      <c r="P150" s="2">
-        <f t="shared" si="37"/>
         <v>110</v>
       </c>
       <c r="Q150" s="2">
@@ -13315,27 +13357,27 @@
         <v>31250</v>
       </c>
       <c r="K151" s="1">
+        <f t="shared" si="41"/>
+        <v>15400</v>
+      </c>
+      <c r="L151" s="1">
         <f t="shared" si="42"/>
-        <v>15400</v>
-      </c>
-      <c r="L151" s="1">
+        <v>17100</v>
+      </c>
+      <c r="M151" s="1">
         <f t="shared" si="43"/>
-        <v>17100</v>
-      </c>
-      <c r="M151" s="1">
+        <v>6100</v>
+      </c>
+      <c r="N151" s="1">
         <f t="shared" si="44"/>
         <v>6100</v>
       </c>
-      <c r="N151" s="1">
+      <c r="O151" s="2">
         <f t="shared" si="45"/>
-        <v>6100</v>
-      </c>
-      <c r="O151" s="2">
+        <v>97</v>
+      </c>
+      <c r="P151" s="2">
         <f t="shared" si="36"/>
-        <v>91</v>
-      </c>
-      <c r="P151" s="2">
-        <f t="shared" si="37"/>
         <v>114</v>
       </c>
       <c r="Q151" s="2">
@@ -13382,27 +13424,27 @@
         <v>156250</v>
       </c>
       <c r="K152" s="1">
+        <f t="shared" si="41"/>
+        <v>16000</v>
+      </c>
+      <c r="L152" s="1">
         <f t="shared" si="42"/>
-        <v>16000</v>
-      </c>
-      <c r="L152" s="1">
+        <v>17700</v>
+      </c>
+      <c r="M152" s="1">
         <f t="shared" si="43"/>
-        <v>17700</v>
-      </c>
-      <c r="M152" s="1">
+        <v>6350</v>
+      </c>
+      <c r="N152" s="1">
         <f t="shared" si="44"/>
         <v>6350</v>
       </c>
-      <c r="N152" s="1">
+      <c r="O152" s="2">
         <f t="shared" si="45"/>
-        <v>6350</v>
-      </c>
-      <c r="O152" s="2">
+        <v>100</v>
+      </c>
+      <c r="P152" s="2">
         <f t="shared" si="36"/>
-        <v>93</v>
-      </c>
-      <c r="P152" s="2">
-        <f t="shared" si="37"/>
         <v>118</v>
       </c>
       <c r="Q152" s="2">
@@ -13449,27 +13491,27 @@
         <v>781250</v>
       </c>
       <c r="K153" s="1">
+        <f t="shared" si="41"/>
+        <v>16600</v>
+      </c>
+      <c r="L153" s="1">
         <f t="shared" si="42"/>
-        <v>16600</v>
-      </c>
-      <c r="L153" s="1">
+        <v>18300</v>
+      </c>
+      <c r="M153" s="1">
         <f t="shared" si="43"/>
-        <v>18300</v>
-      </c>
-      <c r="M153" s="1">
+        <v>6600</v>
+      </c>
+      <c r="N153" s="1">
         <f t="shared" si="44"/>
         <v>6600</v>
       </c>
-      <c r="N153" s="1">
+      <c r="O153" s="2">
         <f t="shared" si="45"/>
-        <v>6600</v>
-      </c>
-      <c r="O153" s="2">
+        <v>103</v>
+      </c>
+      <c r="P153" s="2">
         <f t="shared" si="36"/>
-        <v>95</v>
-      </c>
-      <c r="P153" s="2">
-        <f t="shared" si="37"/>
         <v>122</v>
       </c>
       <c r="Q153" s="2">
@@ -13516,27 +13558,27 @@
         <v>3906250</v>
       </c>
       <c r="K154" s="1">
+        <f t="shared" si="41"/>
+        <v>17200</v>
+      </c>
+      <c r="L154" s="1">
         <f t="shared" si="42"/>
-        <v>17200</v>
-      </c>
-      <c r="L154" s="1">
+        <v>18900</v>
+      </c>
+      <c r="M154" s="1">
         <f t="shared" si="43"/>
-        <v>18900</v>
-      </c>
-      <c r="M154" s="1">
+        <v>6850</v>
+      </c>
+      <c r="N154" s="1">
         <f t="shared" si="44"/>
         <v>6850</v>
       </c>
-      <c r="N154" s="1">
+      <c r="O154" s="2">
         <f t="shared" si="45"/>
-        <v>6850</v>
-      </c>
-      <c r="O154" s="2">
+        <v>106</v>
+      </c>
+      <c r="P154" s="2">
         <f t="shared" si="36"/>
-        <v>97</v>
-      </c>
-      <c r="P154" s="2">
-        <f t="shared" si="37"/>
         <v>126</v>
       </c>
       <c r="Q154" s="2">
@@ -13583,27 +13625,27 @@
         <v>19531250</v>
       </c>
       <c r="K155" s="1">
+        <f t="shared" si="41"/>
+        <v>17800</v>
+      </c>
+      <c r="L155" s="1">
         <f t="shared" si="42"/>
-        <v>17800</v>
-      </c>
-      <c r="L155" s="1">
+        <v>19500</v>
+      </c>
+      <c r="M155" s="1">
         <f t="shared" si="43"/>
-        <v>19500</v>
-      </c>
-      <c r="M155" s="1">
+        <v>7100</v>
+      </c>
+      <c r="N155" s="1">
         <f t="shared" si="44"/>
         <v>7100</v>
       </c>
-      <c r="N155" s="1">
+      <c r="O155" s="2">
         <f t="shared" si="45"/>
-        <v>7100</v>
-      </c>
-      <c r="O155" s="2">
+        <v>109</v>
+      </c>
+      <c r="P155" s="2">
         <f t="shared" si="36"/>
-        <v>99</v>
-      </c>
-      <c r="P155" s="2">
-        <f t="shared" si="37"/>
         <v>130</v>
       </c>
       <c r="Q155" s="2">
@@ -13642,34 +13684,34 @@
       <c r="H156" s="7" t="s">
         <v>980</v>
       </c>
-      <c r="I156" s="15" t="s">
-        <v>771</v>
+      <c r="I156" s="9" t="s">
+        <v>981</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="K156" s="1">
+        <f t="shared" si="41"/>
+        <v>18400</v>
+      </c>
+      <c r="L156" s="1">
         <f t="shared" si="42"/>
-        <v>18400</v>
-      </c>
-      <c r="L156" s="1">
+        <v>20100</v>
+      </c>
+      <c r="M156" s="1">
         <f t="shared" si="43"/>
-        <v>20100</v>
-      </c>
-      <c r="M156" s="1">
+        <v>7350</v>
+      </c>
+      <c r="N156" s="1">
         <f t="shared" si="44"/>
         <v>7350</v>
       </c>
-      <c r="N156" s="1">
+      <c r="O156" s="2">
         <f t="shared" si="45"/>
-        <v>7350</v>
-      </c>
-      <c r="O156" s="2">
+        <v>112</v>
+      </c>
+      <c r="P156" s="2">
         <f t="shared" si="36"/>
-        <v>101</v>
-      </c>
-      <c r="P156" s="2">
-        <f t="shared" si="37"/>
         <v>134</v>
       </c>
       <c r="Q156" s="2">
@@ -13691,51 +13733,51 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E157" s="1">
         <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H157" s="7" t="s">
-        <v>985</v>
-      </c>
-      <c r="I157" s="15" t="s">
-        <v>777</v>
+        <v>986</v>
+      </c>
+      <c r="I157" s="9" t="s">
+        <v>987</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="K157" s="1">
+        <f t="shared" si="41"/>
+        <v>19000</v>
+      </c>
+      <c r="L157" s="1">
         <f t="shared" si="42"/>
-        <v>19000</v>
-      </c>
-      <c r="L157" s="1">
+        <v>20700</v>
+      </c>
+      <c r="M157" s="1">
         <f t="shared" si="43"/>
-        <v>20700</v>
-      </c>
-      <c r="M157" s="1">
+        <v>7600</v>
+      </c>
+      <c r="N157" s="1">
         <f t="shared" si="44"/>
         <v>7600</v>
       </c>
-      <c r="N157" s="1">
+      <c r="O157" s="2">
         <f t="shared" si="45"/>
-        <v>7600</v>
-      </c>
-      <c r="O157" s="2">
+        <v>115</v>
+      </c>
+      <c r="P157" s="2">
         <f t="shared" si="36"/>
-        <v>103</v>
-      </c>
-      <c r="P157" s="2">
-        <f t="shared" si="37"/>
         <v>138</v>
       </c>
       <c r="Q157" s="2">
@@ -13757,51 +13799,51 @@
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="1" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="E158" s="1">
         <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="G158" s="7" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H158" s="7" t="s">
-        <v>990</v>
-      </c>
-      <c r="I158" s="15" t="s">
-        <v>783</v>
+        <v>992</v>
+      </c>
+      <c r="I158" s="9" t="s">
+        <v>993</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="K158" s="1">
+        <f t="shared" si="41"/>
+        <v>19600</v>
+      </c>
+      <c r="L158" s="1">
         <f t="shared" si="42"/>
-        <v>19600</v>
-      </c>
-      <c r="L158" s="1">
+        <v>21300</v>
+      </c>
+      <c r="M158" s="1">
         <f t="shared" si="43"/>
-        <v>21300</v>
-      </c>
-      <c r="M158" s="1">
+        <v>7850</v>
+      </c>
+      <c r="N158" s="1">
         <f t="shared" si="44"/>
         <v>7850</v>
       </c>
-      <c r="N158" s="1">
+      <c r="O158" s="2">
         <f t="shared" si="45"/>
-        <v>7850</v>
-      </c>
-      <c r="O158" s="2">
+        <v>118</v>
+      </c>
+      <c r="P158" s="2">
         <f t="shared" si="36"/>
-        <v>105</v>
-      </c>
-      <c r="P158" s="2">
-        <f t="shared" si="37"/>
         <v>142</v>
       </c>
       <c r="Q158" s="2">
@@ -13823,51 +13865,51 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="E159" s="1">
         <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="H159" s="7" t="s">
-        <v>995</v>
-      </c>
-      <c r="I159" s="15" t="s">
-        <v>789</v>
+        <v>998</v>
+      </c>
+      <c r="I159" s="9" t="s">
+        <v>999</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="K159" s="1">
+        <f t="shared" si="41"/>
+        <v>20200</v>
+      </c>
+      <c r="L159" s="1">
         <f t="shared" si="42"/>
-        <v>20200</v>
-      </c>
-      <c r="L159" s="1">
+        <v>21900</v>
+      </c>
+      <c r="M159" s="1">
         <f t="shared" si="43"/>
-        <v>21900</v>
-      </c>
-      <c r="M159" s="1">
+        <v>8100</v>
+      </c>
+      <c r="N159" s="1">
         <f t="shared" si="44"/>
         <v>8100</v>
       </c>
-      <c r="N159" s="1">
+      <c r="O159" s="2">
         <f t="shared" si="45"/>
-        <v>8100</v>
-      </c>
-      <c r="O159" s="2">
+        <v>121</v>
+      </c>
+      <c r="P159" s="2">
         <f t="shared" si="36"/>
-        <v>107</v>
-      </c>
-      <c r="P159" s="2">
-        <f t="shared" si="37"/>
         <v>146</v>
       </c>
       <c r="Q159" s="2">
@@ -13889,51 +13931,51 @@
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="1" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="E160" s="1">
         <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="H160" s="7" t="s">
-        <v>1000</v>
-      </c>
-      <c r="I160" s="15" t="s">
-        <v>795</v>
+        <v>1004</v>
+      </c>
+      <c r="I160" s="9" t="s">
+        <v>1005</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="K160" s="1">
+        <f t="shared" si="41"/>
+        <v>20800</v>
+      </c>
+      <c r="L160" s="1">
         <f t="shared" si="42"/>
-        <v>20800</v>
-      </c>
-      <c r="L160" s="1">
+        <v>22500</v>
+      </c>
+      <c r="M160" s="1">
         <f t="shared" si="43"/>
-        <v>22500</v>
-      </c>
-      <c r="M160" s="1">
+        <v>8350</v>
+      </c>
+      <c r="N160" s="1">
         <f t="shared" si="44"/>
         <v>8350</v>
       </c>
-      <c r="N160" s="1">
+      <c r="O160" s="2">
         <f t="shared" si="45"/>
-        <v>8350</v>
-      </c>
-      <c r="O160" s="2">
+        <v>124</v>
+      </c>
+      <c r="P160" s="2">
         <f t="shared" si="36"/>
-        <v>109</v>
-      </c>
-      <c r="P160" s="2">
-        <f t="shared" si="37"/>
         <v>150</v>
       </c>
       <c r="Q160" s="2">
@@ -13955,51 +13997,51 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="E161" s="1">
         <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="H161" s="7" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I161" s="15" t="s">
-        <v>801</v>
+        <v>1010</v>
+      </c>
+      <c r="I161" s="9" t="s">
+        <v>1011</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="K161" s="1">
+        <f t="shared" si="41"/>
+        <v>21400</v>
+      </c>
+      <c r="L161" s="1">
         <f t="shared" si="42"/>
-        <v>21400</v>
-      </c>
-      <c r="L161" s="1">
+        <v>23100</v>
+      </c>
+      <c r="M161" s="1">
         <f t="shared" si="43"/>
-        <v>23100</v>
-      </c>
-      <c r="M161" s="1">
+        <v>8600</v>
+      </c>
+      <c r="N161" s="1">
         <f t="shared" si="44"/>
         <v>8600</v>
       </c>
-      <c r="N161" s="1">
+      <c r="O161" s="2">
         <f t="shared" si="45"/>
-        <v>8600</v>
-      </c>
-      <c r="O161" s="2">
+        <v>127</v>
+      </c>
+      <c r="P161" s="2">
         <f t="shared" si="36"/>
-        <v>111</v>
-      </c>
-      <c r="P161" s="2">
-        <f t="shared" si="37"/>
         <v>154</v>
       </c>
       <c r="Q161" s="2">
@@ -14021,51 +14063,51 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="1" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="E162" s="1">
         <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="G162" s="7" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="H162" s="7" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I162" s="15" t="s">
-        <v>807</v>
+        <v>1016</v>
+      </c>
+      <c r="I162" s="9" t="s">
+        <v>1017</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="K162" s="1">
+        <f t="shared" si="41"/>
+        <v>22000</v>
+      </c>
+      <c r="L162" s="1">
         <f t="shared" si="42"/>
-        <v>22000</v>
-      </c>
-      <c r="L162" s="1">
+        <v>23700</v>
+      </c>
+      <c r="M162" s="1">
         <f t="shared" si="43"/>
-        <v>23700</v>
-      </c>
-      <c r="M162" s="1">
+        <v>8850</v>
+      </c>
+      <c r="N162" s="1">
         <f t="shared" si="44"/>
         <v>8850</v>
       </c>
-      <c r="N162" s="1">
+      <c r="O162" s="2">
         <f t="shared" si="45"/>
-        <v>8850</v>
-      </c>
-      <c r="O162" s="2">
+        <v>130</v>
+      </c>
+      <c r="P162" s="2">
         <f t="shared" si="36"/>
-        <v>113</v>
-      </c>
-      <c r="P162" s="2">
-        <f t="shared" si="37"/>
         <v>158</v>
       </c>
       <c r="Q162" s="2">
@@ -14087,51 +14129,51 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="1" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="E163" s="1">
         <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="H163" s="7" t="s">
-        <v>1015</v>
-      </c>
-      <c r="I163" s="15" t="s">
-        <v>813</v>
+        <v>1022</v>
+      </c>
+      <c r="I163" s="9" t="s">
+        <v>1023</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="K163" s="1">
+        <f t="shared" si="41"/>
+        <v>22600</v>
+      </c>
+      <c r="L163" s="1">
         <f t="shared" si="42"/>
-        <v>22600</v>
-      </c>
-      <c r="L163" s="1">
+        <v>24300</v>
+      </c>
+      <c r="M163" s="1">
         <f t="shared" si="43"/>
-        <v>24300</v>
-      </c>
-      <c r="M163" s="1">
+        <v>9100</v>
+      </c>
+      <c r="N163" s="1">
         <f t="shared" si="44"/>
         <v>9100</v>
       </c>
-      <c r="N163" s="1">
+      <c r="O163" s="2">
         <f t="shared" si="45"/>
-        <v>9100</v>
-      </c>
-      <c r="O163" s="2">
+        <v>133</v>
+      </c>
+      <c r="P163" s="2">
         <f t="shared" si="36"/>
-        <v>115</v>
-      </c>
-      <c r="P163" s="2">
-        <f t="shared" si="37"/>
         <v>162</v>
       </c>
       <c r="Q163" s="2">
@@ -14153,51 +14195,51 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="1" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="E164" s="1">
         <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="G164" s="7" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="H164" s="7" t="s">
-        <v>1020</v>
-      </c>
-      <c r="I164" s="15" t="s">
-        <v>819</v>
+        <v>1028</v>
+      </c>
+      <c r="I164" s="9" t="s">
+        <v>1029</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>1021</v>
+        <v>1030</v>
       </c>
       <c r="K164" s="1">
+        <f t="shared" si="41"/>
+        <v>23200</v>
+      </c>
+      <c r="L164" s="1">
         <f t="shared" si="42"/>
-        <v>23200</v>
-      </c>
-      <c r="L164" s="1">
+        <v>24900</v>
+      </c>
+      <c r="M164" s="1">
         <f t="shared" si="43"/>
-        <v>24900</v>
-      </c>
-      <c r="M164" s="1">
+        <v>9350</v>
+      </c>
+      <c r="N164" s="1">
         <f t="shared" si="44"/>
         <v>9350</v>
       </c>
-      <c r="N164" s="1">
+      <c r="O164" s="2">
         <f t="shared" si="45"/>
-        <v>9350</v>
-      </c>
-      <c r="O164" s="2">
+        <v>136</v>
+      </c>
+      <c r="P164" s="2">
         <f t="shared" si="36"/>
-        <v>117</v>
-      </c>
-      <c r="P164" s="2">
-        <f t="shared" si="37"/>
         <v>166</v>
       </c>
       <c r="Q164" s="2">
@@ -14219,51 +14261,51 @@
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="1" t="s">
-        <v>1022</v>
+        <v>1031</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>1023</v>
+        <v>1032</v>
       </c>
       <c r="E165" s="1">
         <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1024</v>
+        <v>1033</v>
       </c>
       <c r="G165" s="7" t="s">
-        <v>1025</v>
+        <v>1034</v>
       </c>
       <c r="H165" s="7" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I165" s="15" t="s">
-        <v>825</v>
+        <v>1034</v>
+      </c>
+      <c r="I165" s="9" t="s">
+        <v>1035</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
       <c r="K165" s="1">
+        <f t="shared" si="41"/>
+        <v>23800</v>
+      </c>
+      <c r="L165" s="1">
         <f t="shared" si="42"/>
-        <v>23800</v>
-      </c>
-      <c r="L165" s="1">
+        <v>25500</v>
+      </c>
+      <c r="M165" s="1">
         <f t="shared" si="43"/>
-        <v>25500</v>
-      </c>
-      <c r="M165" s="1">
+        <v>9600</v>
+      </c>
+      <c r="N165" s="1">
         <f t="shared" si="44"/>
         <v>9600</v>
       </c>
-      <c r="N165" s="1">
+      <c r="O165" s="2">
         <f t="shared" si="45"/>
-        <v>9600</v>
-      </c>
-      <c r="O165" s="2">
+        <v>139</v>
+      </c>
+      <c r="P165" s="2">
         <f t="shared" si="36"/>
-        <v>119</v>
-      </c>
-      <c r="P165" s="2">
-        <f t="shared" si="37"/>
         <v>170</v>
       </c>
       <c r="Q165" s="2">
@@ -14283,51 +14325,51 @@
     </row>
     <row r="166" customHeight="1" spans="3:19">
       <c r="C166" s="1" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>1028</v>
+        <v>1038</v>
       </c>
       <c r="E166" s="1">
         <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1029</v>
+        <v>1039</v>
       </c>
       <c r="G166" s="7" t="s">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="H166" s="7" t="s">
-        <v>1030</v>
-      </c>
-      <c r="I166" s="15" t="s">
-        <v>831</v>
+        <v>1040</v>
+      </c>
+      <c r="I166" s="9" t="s">
+        <v>1041</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
       <c r="K166" s="1">
+        <f t="shared" si="41"/>
+        <v>24400</v>
+      </c>
+      <c r="L166" s="1">
         <f t="shared" si="42"/>
-        <v>24400</v>
-      </c>
-      <c r="L166" s="1">
+        <v>26100</v>
+      </c>
+      <c r="M166" s="1">
         <f t="shared" si="43"/>
-        <v>26100</v>
-      </c>
-      <c r="M166" s="1">
+        <v>9850</v>
+      </c>
+      <c r="N166" s="1">
         <f t="shared" si="44"/>
         <v>9850</v>
       </c>
-      <c r="N166" s="1">
+      <c r="O166" s="2">
         <f t="shared" si="45"/>
-        <v>9850</v>
-      </c>
-      <c r="O166" s="2">
+        <v>142</v>
+      </c>
+      <c r="P166" s="2">
         <f t="shared" si="36"/>
-        <v>121</v>
-      </c>
-      <c r="P166" s="2">
-        <f t="shared" si="37"/>
         <v>174</v>
       </c>
       <c r="Q166" s="2">
@@ -14342,51 +14384,51 @@
     </row>
     <row r="167" customHeight="1" spans="3:19">
       <c r="C167" s="1" t="s">
-        <v>1032</v>
+        <v>1043</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>1033</v>
+        <v>1044</v>
       </c>
       <c r="E167" s="1">
         <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1034</v>
+        <v>1045</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>1035</v>
+        <v>1046</v>
       </c>
       <c r="H167" s="7" t="s">
-        <v>1035</v>
-      </c>
-      <c r="I167" s="15" t="s">
-        <v>837</v>
+        <v>1046</v>
+      </c>
+      <c r="I167" s="9" t="s">
+        <v>1047</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>1036</v>
+        <v>1048</v>
       </c>
       <c r="K167" s="1">
+        <f t="shared" si="41"/>
+        <v>25000</v>
+      </c>
+      <c r="L167" s="1">
         <f t="shared" si="42"/>
-        <v>25000</v>
-      </c>
-      <c r="L167" s="1">
+        <v>26700</v>
+      </c>
+      <c r="M167" s="1">
         <f t="shared" si="43"/>
-        <v>26700</v>
-      </c>
-      <c r="M167" s="1">
+        <v>10100</v>
+      </c>
+      <c r="N167" s="1">
         <f t="shared" si="44"/>
         <v>10100</v>
       </c>
-      <c r="N167" s="1">
+      <c r="O167" s="2">
         <f t="shared" si="45"/>
-        <v>10100</v>
-      </c>
-      <c r="O167" s="2">
+        <v>145</v>
+      </c>
+      <c r="P167" s="2">
         <f t="shared" si="36"/>
-        <v>123</v>
-      </c>
-      <c r="P167" s="2">
-        <f t="shared" si="37"/>
         <v>178</v>
       </c>
       <c r="Q167" s="2">
@@ -14401,51 +14443,51 @@
     </row>
     <row r="168" customHeight="1" spans="3:19">
       <c r="C168" s="1" t="s">
-        <v>1037</v>
+        <v>1049</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
       <c r="E168" s="1">
         <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
       <c r="G168" s="7" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="H168" s="7" t="s">
-        <v>1040</v>
-      </c>
-      <c r="I168" s="15" t="s">
-        <v>843</v>
+        <v>1052</v>
+      </c>
+      <c r="I168" s="9" t="s">
+        <v>1053</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="K168" s="1">
+        <f t="shared" si="41"/>
+        <v>25600</v>
+      </c>
+      <c r="L168" s="1">
         <f t="shared" si="42"/>
-        <v>25600</v>
-      </c>
-      <c r="L168" s="1">
+        <v>27300</v>
+      </c>
+      <c r="M168" s="1">
         <f t="shared" si="43"/>
-        <v>27300</v>
-      </c>
-      <c r="M168" s="1">
+        <v>10350</v>
+      </c>
+      <c r="N168" s="1">
         <f t="shared" si="44"/>
         <v>10350</v>
       </c>
-      <c r="N168" s="1">
+      <c r="O168" s="2">
         <f t="shared" si="45"/>
-        <v>10350</v>
-      </c>
-      <c r="O168" s="2">
+        <v>148</v>
+      </c>
+      <c r="P168" s="2">
         <f t="shared" si="36"/>
-        <v>125</v>
-      </c>
-      <c r="P168" s="2">
-        <f t="shared" si="37"/>
         <v>182</v>
       </c>
       <c r="Q168" s="2">
@@ -14460,51 +14502,51 @@
     </row>
     <row r="169" customHeight="1" spans="3:19">
       <c r="C169" s="1" t="s">
-        <v>1042</v>
+        <v>1055</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>1043</v>
+        <v>1056</v>
       </c>
       <c r="E169" s="1">
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1044</v>
+        <v>1057</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="H169" s="7" t="s">
-        <v>1045</v>
-      </c>
-      <c r="I169" s="15" t="s">
-        <v>849</v>
+        <v>1058</v>
+      </c>
+      <c r="I169" s="9" t="s">
+        <v>1059</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>1046</v>
+        <v>1060</v>
       </c>
       <c r="K169" s="1">
+        <f t="shared" si="41"/>
+        <v>26200</v>
+      </c>
+      <c r="L169" s="1">
         <f t="shared" si="42"/>
-        <v>26200</v>
-      </c>
-      <c r="L169" s="1">
+        <v>27900</v>
+      </c>
+      <c r="M169" s="1">
         <f t="shared" si="43"/>
-        <v>27900</v>
-      </c>
-      <c r="M169" s="1">
+        <v>10600</v>
+      </c>
+      <c r="N169" s="1">
         <f t="shared" si="44"/>
         <v>10600</v>
       </c>
-      <c r="N169" s="1">
+      <c r="O169" s="2">
         <f t="shared" si="45"/>
-        <v>10600</v>
-      </c>
-      <c r="O169" s="2">
+        <v>151</v>
+      </c>
+      <c r="P169" s="2">
         <f t="shared" si="36"/>
-        <v>127</v>
-      </c>
-      <c r="P169" s="2">
-        <f t="shared" si="37"/>
         <v>186</v>
       </c>
       <c r="Q169" s="2">
@@ -14519,51 +14561,51 @@
     </row>
     <row r="170" customHeight="1" spans="3:19">
       <c r="C170" s="1" t="s">
-        <v>1047</v>
+        <v>1061</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>1048</v>
+        <v>1062</v>
       </c>
       <c r="E170" s="1">
         <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1049</v>
+        <v>1063</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>1050</v>
+        <v>1064</v>
       </c>
       <c r="H170" s="7" t="s">
-        <v>1050</v>
-      </c>
-      <c r="I170" s="15" t="s">
-        <v>855</v>
+        <v>1064</v>
+      </c>
+      <c r="I170" s="9" t="s">
+        <v>1059</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>1051</v>
+        <v>1065</v>
       </c>
       <c r="K170" s="1">
+        <f t="shared" si="41"/>
+        <v>26800</v>
+      </c>
+      <c r="L170" s="1">
         <f t="shared" si="42"/>
-        <v>26800</v>
-      </c>
-      <c r="L170" s="1">
+        <v>28500</v>
+      </c>
+      <c r="M170" s="1">
         <f t="shared" si="43"/>
-        <v>28500</v>
-      </c>
-      <c r="M170" s="1">
+        <v>10850</v>
+      </c>
+      <c r="N170" s="1">
         <f t="shared" si="44"/>
         <v>10850</v>
       </c>
-      <c r="N170" s="1">
+      <c r="O170" s="2">
         <f t="shared" si="45"/>
-        <v>10850</v>
-      </c>
-      <c r="O170" s="2">
+        <v>154</v>
+      </c>
+      <c r="P170" s="2">
         <f t="shared" si="36"/>
-        <v>129</v>
-      </c>
-      <c r="P170" s="2">
-        <f t="shared" si="37"/>
         <v>190</v>
       </c>
       <c r="Q170" s="2">
@@ -14578,51 +14620,51 @@
     </row>
     <row r="171" customHeight="1" spans="3:19">
       <c r="C171" s="1" t="s">
-        <v>1052</v>
+        <v>1066</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>1053</v>
+        <v>1067</v>
       </c>
       <c r="E171" s="1">
         <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1054</v>
+        <v>1068</v>
       </c>
       <c r="G171" s="7" t="s">
-        <v>1055</v>
+        <v>1069</v>
       </c>
       <c r="H171" s="7" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I171" s="15" t="s">
-        <v>861</v>
+        <v>1069</v>
+      </c>
+      <c r="I171" s="9" t="s">
+        <v>1059</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>1056</v>
+        <v>1070</v>
       </c>
       <c r="K171" s="1">
+        <f t="shared" si="41"/>
+        <v>27400</v>
+      </c>
+      <c r="L171" s="1">
         <f t="shared" si="42"/>
-        <v>27400</v>
-      </c>
-      <c r="L171" s="1">
+        <v>29100</v>
+      </c>
+      <c r="M171" s="1">
         <f t="shared" si="43"/>
-        <v>29100</v>
-      </c>
-      <c r="M171" s="1">
+        <v>11100</v>
+      </c>
+      <c r="N171" s="1">
         <f t="shared" si="44"/>
         <v>11100</v>
       </c>
-      <c r="N171" s="1">
+      <c r="O171" s="2">
         <f t="shared" si="45"/>
-        <v>11100</v>
-      </c>
-      <c r="O171" s="2">
+        <v>157</v>
+      </c>
+      <c r="P171" s="2">
         <f t="shared" si="36"/>
-        <v>131</v>
-      </c>
-      <c r="P171" s="2">
-        <f t="shared" si="37"/>
         <v>194</v>
       </c>
       <c r="Q171" s="2">
@@ -14637,51 +14679,51 @@
     </row>
     <row r="172" customHeight="1" spans="3:19">
       <c r="C172" s="1" t="s">
-        <v>1057</v>
+        <v>1071</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>1058</v>
+        <v>1072</v>
       </c>
       <c r="E172" s="1">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H172" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="I172" s="9" t="s">
         <v>1059</v>
       </c>
-      <c r="G172" s="7" t="s">
-        <v>1060</v>
-      </c>
-      <c r="H172" s="7" t="s">
-        <v>1060</v>
-      </c>
-      <c r="I172" s="15" t="s">
-        <v>867</v>
-      </c>
       <c r="J172" s="1" t="s">
-        <v>1061</v>
+        <v>1075</v>
       </c>
       <c r="K172" s="1">
+        <f t="shared" si="41"/>
+        <v>28000</v>
+      </c>
+      <c r="L172" s="1">
         <f t="shared" si="42"/>
-        <v>28000</v>
-      </c>
-      <c r="L172" s="1">
+        <v>29700</v>
+      </c>
+      <c r="M172" s="1">
         <f t="shared" si="43"/>
-        <v>29700</v>
-      </c>
-      <c r="M172" s="1">
+        <v>11350</v>
+      </c>
+      <c r="N172" s="1">
         <f t="shared" si="44"/>
         <v>11350</v>
       </c>
-      <c r="N172" s="1">
+      <c r="O172" s="2">
         <f t="shared" si="45"/>
-        <v>11350</v>
-      </c>
-      <c r="O172" s="2">
+        <v>160</v>
+      </c>
+      <c r="P172" s="2">
         <f t="shared" si="36"/>
-        <v>133</v>
-      </c>
-      <c r="P172" s="2">
-        <f t="shared" si="37"/>
         <v>198</v>
       </c>
       <c r="Q172" s="2">
@@ -14696,51 +14738,51 @@
     </row>
     <row r="173" customHeight="1" spans="3:19">
       <c r="C173" s="1" t="s">
-        <v>1062</v>
+        <v>1076</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>1063</v>
+        <v>1077</v>
       </c>
       <c r="E173" s="1">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1064</v>
+        <v>1078</v>
       </c>
       <c r="G173" s="7" t="s">
-        <v>1065</v>
+        <v>1079</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>1065</v>
-      </c>
-      <c r="I173" s="15" t="s">
-        <v>873</v>
+        <v>1079</v>
+      </c>
+      <c r="I173" s="9" t="s">
+        <v>1059</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>1066</v>
+        <v>1080</v>
       </c>
       <c r="K173" s="1">
+        <f t="shared" si="41"/>
+        <v>28600</v>
+      </c>
+      <c r="L173" s="1">
         <f t="shared" si="42"/>
-        <v>28600</v>
-      </c>
-      <c r="L173" s="1">
+        <v>30300</v>
+      </c>
+      <c r="M173" s="1">
         <f t="shared" si="43"/>
-        <v>30300</v>
-      </c>
-      <c r="M173" s="1">
+        <v>11600</v>
+      </c>
+      <c r="N173" s="1">
         <f t="shared" si="44"/>
         <v>11600</v>
       </c>
-      <c r="N173" s="1">
+      <c r="O173" s="2">
         <f t="shared" si="45"/>
-        <v>11600</v>
-      </c>
-      <c r="O173" s="2">
+        <v>163</v>
+      </c>
+      <c r="P173" s="2">
         <f t="shared" si="36"/>
-        <v>135</v>
-      </c>
-      <c r="P173" s="2">
-        <f t="shared" si="37"/>
         <v>202</v>
       </c>
       <c r="Q173" s="2">
@@ -14755,51 +14797,51 @@
     </row>
     <row r="174" customHeight="1" spans="3:19">
       <c r="C174" s="1" t="s">
-        <v>1067</v>
+        <v>1081</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>1068</v>
+        <v>1082</v>
       </c>
       <c r="E174" s="1">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1069</v>
+        <v>1083</v>
       </c>
       <c r="G174" s="7" t="s">
-        <v>1070</v>
+        <v>1084</v>
       </c>
       <c r="H174" s="7" t="s">
-        <v>1070</v>
-      </c>
-      <c r="I174" s="15" t="s">
-        <v>879</v>
+        <v>1084</v>
+      </c>
+      <c r="I174" s="9" t="s">
+        <v>1059</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>1071</v>
+        <v>1085</v>
       </c>
       <c r="K174" s="1">
+        <f t="shared" si="41"/>
+        <v>29200</v>
+      </c>
+      <c r="L174" s="1">
         <f t="shared" si="42"/>
-        <v>29200</v>
-      </c>
-      <c r="L174" s="1">
+        <v>30900</v>
+      </c>
+      <c r="M174" s="1">
         <f t="shared" si="43"/>
-        <v>30900</v>
-      </c>
-      <c r="M174" s="1">
+        <v>11850</v>
+      </c>
+      <c r="N174" s="1">
         <f t="shared" si="44"/>
         <v>11850</v>
       </c>
-      <c r="N174" s="1">
+      <c r="O174" s="2">
         <f t="shared" si="45"/>
-        <v>11850</v>
-      </c>
-      <c r="O174" s="2">
+        <v>166</v>
+      </c>
+      <c r="P174" s="2">
         <f t="shared" si="36"/>
-        <v>137</v>
-      </c>
-      <c r="P174" s="2">
-        <f t="shared" si="37"/>
         <v>206</v>
       </c>
       <c r="Q174" s="2">
@@ -14814,51 +14856,51 @@
     </row>
     <row r="175" customHeight="1" spans="3:19">
       <c r="C175" s="1" t="s">
-        <v>1072</v>
+        <v>1086</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>1073</v>
+        <v>1087</v>
       </c>
       <c r="E175" s="1">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1074</v>
+        <v>1088</v>
       </c>
       <c r="G175" s="7" t="s">
-        <v>1075</v>
+        <v>1089</v>
       </c>
       <c r="H175" s="7" t="s">
-        <v>1075</v>
-      </c>
-      <c r="I175" s="15" t="s">
-        <v>885</v>
+        <v>1089</v>
+      </c>
+      <c r="I175" s="9" t="s">
+        <v>1059</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1076</v>
+        <v>1090</v>
       </c>
       <c r="K175" s="1">
+        <f t="shared" si="41"/>
+        <v>29800</v>
+      </c>
+      <c r="L175" s="1">
         <f t="shared" si="42"/>
-        <v>29800</v>
-      </c>
-      <c r="L175" s="1">
+        <v>31500</v>
+      </c>
+      <c r="M175" s="1">
         <f t="shared" si="43"/>
-        <v>31500</v>
-      </c>
-      <c r="M175" s="1">
+        <v>12100</v>
+      </c>
+      <c r="N175" s="1">
         <f t="shared" si="44"/>
         <v>12100</v>
       </c>
-      <c r="N175" s="1">
+      <c r="O175" s="2">
         <f t="shared" si="45"/>
-        <v>12100</v>
-      </c>
-      <c r="O175" s="2">
+        <v>169</v>
+      </c>
+      <c r="P175" s="2">
         <f t="shared" si="36"/>
-        <v>139</v>
-      </c>
-      <c r="P175" s="2">
-        <f t="shared" si="37"/>
         <v>210</v>
       </c>
       <c r="Q175" s="2">
@@ -14875,51 +14917,51 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="1" t="s">
-        <v>1077</v>
+        <v>1091</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>1078</v>
+        <v>1092</v>
       </c>
       <c r="E176" s="1">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1079</v>
+        <v>1093</v>
       </c>
       <c r="G176" s="7" t="s">
-        <v>1080</v>
+        <v>1094</v>
       </c>
       <c r="H176" s="7" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I176" s="15" t="s">
-        <v>891</v>
+        <v>1094</v>
+      </c>
+      <c r="I176" s="9" t="s">
+        <v>1059</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>1081</v>
+        <v>1095</v>
       </c>
       <c r="K176" s="1">
+        <f t="shared" si="41"/>
+        <v>30400</v>
+      </c>
+      <c r="L176" s="1">
         <f t="shared" si="42"/>
-        <v>30400</v>
-      </c>
-      <c r="L176" s="1">
+        <v>32100</v>
+      </c>
+      <c r="M176" s="1">
         <f t="shared" si="43"/>
-        <v>32100</v>
-      </c>
-      <c r="M176" s="1">
+        <v>12350</v>
+      </c>
+      <c r="N176" s="1">
         <f t="shared" si="44"/>
         <v>12350</v>
       </c>
-      <c r="N176" s="1">
+      <c r="O176" s="2">
         <f t="shared" si="45"/>
-        <v>12350</v>
-      </c>
-      <c r="O176" s="2">
+        <v>172</v>
+      </c>
+      <c r="P176" s="2">
         <f t="shared" si="36"/>
-        <v>141</v>
-      </c>
-      <c r="P176" s="2">
-        <f t="shared" si="37"/>
         <v>214</v>
       </c>
       <c r="Q176" s="2">
@@ -14941,51 +14983,51 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="1" t="s">
-        <v>1082</v>
+        <v>1096</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>1083</v>
+        <v>1097</v>
       </c>
       <c r="E177" s="1">
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1084</v>
+        <v>1098</v>
       </c>
       <c r="G177" s="7" t="s">
-        <v>1085</v>
+        <v>1099</v>
       </c>
       <c r="H177" s="7" t="s">
-        <v>1085</v>
-      </c>
-      <c r="I177" s="15" t="s">
-        <v>897</v>
+        <v>1099</v>
+      </c>
+      <c r="I177" s="9" t="s">
+        <v>1059</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1086</v>
+        <v>1100</v>
       </c>
       <c r="K177" s="1">
+        <f t="shared" si="41"/>
+        <v>31000</v>
+      </c>
+      <c r="L177" s="1">
         <f t="shared" si="42"/>
-        <v>31000</v>
-      </c>
-      <c r="L177" s="1">
+        <v>32700</v>
+      </c>
+      <c r="M177" s="1">
         <f t="shared" si="43"/>
-        <v>32700</v>
-      </c>
-      <c r="M177" s="1">
+        <v>12600</v>
+      </c>
+      <c r="N177" s="1">
         <f t="shared" si="44"/>
         <v>12600</v>
       </c>
-      <c r="N177" s="1">
+      <c r="O177" s="2">
         <f t="shared" si="45"/>
-        <v>12600</v>
-      </c>
-      <c r="O177" s="2">
+        <v>175</v>
+      </c>
+      <c r="P177" s="2">
         <f t="shared" si="36"/>
-        <v>143</v>
-      </c>
-      <c r="P177" s="2">
-        <f t="shared" si="37"/>
         <v>218</v>
       </c>
       <c r="Q177" s="2">
@@ -15007,51 +15049,51 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="1" t="s">
-        <v>1087</v>
+        <v>1101</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1088</v>
+        <v>1102</v>
       </c>
       <c r="E178" s="1">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1089</v>
+        <v>1103</v>
       </c>
       <c r="G178" s="7" t="s">
-        <v>1090</v>
+        <v>1104</v>
       </c>
       <c r="H178" s="7" t="s">
-        <v>1090</v>
-      </c>
-      <c r="I178" s="15" t="s">
-        <v>903</v>
+        <v>1104</v>
+      </c>
+      <c r="I178" s="9" t="s">
+        <v>1059</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>1091</v>
+        <v>1105</v>
       </c>
       <c r="K178" s="1">
+        <f t="shared" si="41"/>
+        <v>31600</v>
+      </c>
+      <c r="L178" s="1">
         <f t="shared" si="42"/>
-        <v>31600</v>
-      </c>
-      <c r="L178" s="1">
+        <v>33300</v>
+      </c>
+      <c r="M178" s="1">
         <f t="shared" si="43"/>
-        <v>33300</v>
-      </c>
-      <c r="M178" s="1">
+        <v>12850</v>
+      </c>
+      <c r="N178" s="1">
         <f t="shared" si="44"/>
         <v>12850</v>
       </c>
-      <c r="N178" s="1">
+      <c r="O178" s="2">
         <f t="shared" si="45"/>
-        <v>12850</v>
-      </c>
-      <c r="O178" s="2">
+        <v>178</v>
+      </c>
+      <c r="P178" s="2">
         <f t="shared" si="36"/>
-        <v>145</v>
-      </c>
-      <c r="P178" s="2">
-        <f t="shared" si="37"/>
         <v>222</v>
       </c>
       <c r="Q178" s="2">
@@ -15073,51 +15115,51 @@
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="1" t="s">
-        <v>1092</v>
+        <v>1106</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1093</v>
+        <v>1107</v>
       </c>
       <c r="E179" s="1">
         <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1094</v>
+        <v>1108</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>1095</v>
+        <v>1109</v>
       </c>
       <c r="H179" s="7" t="s">
-        <v>1095</v>
-      </c>
-      <c r="I179" s="15" t="s">
-        <v>909</v>
+        <v>1109</v>
+      </c>
+      <c r="I179" s="9" t="s">
+        <v>1059</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1096</v>
+        <v>1110</v>
       </c>
       <c r="K179" s="1">
+        <f t="shared" si="41"/>
+        <v>32200</v>
+      </c>
+      <c r="L179" s="1">
         <f t="shared" si="42"/>
-        <v>32200</v>
-      </c>
-      <c r="L179" s="1">
+        <v>33900</v>
+      </c>
+      <c r="M179" s="1">
         <f t="shared" si="43"/>
-        <v>33900</v>
-      </c>
-      <c r="M179" s="1">
+        <v>13100</v>
+      </c>
+      <c r="N179" s="1">
         <f t="shared" si="44"/>
         <v>13100</v>
       </c>
-      <c r="N179" s="1">
+      <c r="O179" s="2">
         <f t="shared" si="45"/>
-        <v>13100</v>
-      </c>
-      <c r="O179" s="2">
+        <v>181</v>
+      </c>
+      <c r="P179" s="2">
         <f t="shared" si="36"/>
-        <v>147</v>
-      </c>
-      <c r="P179" s="2">
-        <f t="shared" si="37"/>
         <v>226</v>
       </c>
       <c r="Q179" s="2">
@@ -15139,51 +15181,51 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="1" t="s">
-        <v>1097</v>
+        <v>1111</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1098</v>
+        <v>1112</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1099</v>
+        <v>1113</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>1100</v>
+        <v>1114</v>
       </c>
       <c r="H180" s="7" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I180" s="15" t="s">
-        <v>915</v>
+        <v>1114</v>
+      </c>
+      <c r="I180" s="9" t="s">
+        <v>1059</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>1101</v>
+        <v>1115</v>
       </c>
       <c r="K180" s="1">
+        <f t="shared" si="41"/>
+        <v>32800</v>
+      </c>
+      <c r="L180" s="1">
         <f t="shared" si="42"/>
-        <v>32800</v>
-      </c>
-      <c r="L180" s="1">
+        <v>34500</v>
+      </c>
+      <c r="M180" s="1">
         <f t="shared" si="43"/>
-        <v>34500</v>
-      </c>
-      <c r="M180" s="1">
+        <v>13350</v>
+      </c>
+      <c r="N180" s="1">
         <f t="shared" si="44"/>
         <v>13350</v>
       </c>
-      <c r="N180" s="1">
+      <c r="O180" s="2">
         <f t="shared" si="45"/>
-        <v>13350</v>
-      </c>
-      <c r="O180" s="2">
+        <v>184</v>
+      </c>
+      <c r="P180" s="2">
         <f t="shared" si="36"/>
-        <v>149</v>
-      </c>
-      <c r="P180" s="2">
-        <f t="shared" si="37"/>
         <v>230</v>
       </c>
       <c r="Q180" s="2">

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -4557,7 +4557,7 @@
         <v>26</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>25</v>
@@ -4590,7 +4590,7 @@
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
     </row>
-    <row r="6" ht="14" spans="3:19">
+    <row r="6" ht="14.25" spans="3:19">
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
@@ -12126,11 +12126,11 @@
         <v>1950</v>
       </c>
       <c r="O131" s="2">
-        <f>O130+2</f>
+        <f t="shared" ref="O131:O145" si="36">O130+2</f>
         <v>51</v>
       </c>
       <c r="P131" s="2">
-        <f t="shared" ref="P131:P180" si="36">P130+4</f>
+        <f t="shared" ref="P131:P180" si="37">P130+4</f>
         <v>34</v>
       </c>
       <c r="Q131" s="2">
@@ -12185,11 +12185,11 @@
         <v>2050</v>
       </c>
       <c r="O132" s="2">
-        <f>O131+2</f>
+        <f t="shared" si="36"/>
         <v>53</v>
       </c>
       <c r="P132" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>38</v>
       </c>
       <c r="Q132" s="2">
@@ -12244,11 +12244,11 @@
         <v>2150</v>
       </c>
       <c r="O133" s="2">
-        <f>O132+2</f>
+        <f t="shared" si="36"/>
         <v>55</v>
       </c>
       <c r="P133" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>42</v>
       </c>
       <c r="Q133" s="2">
@@ -12303,11 +12303,11 @@
         <v>2250</v>
       </c>
       <c r="O134" s="2">
-        <f>O133+2</f>
+        <f t="shared" si="36"/>
         <v>57</v>
       </c>
       <c r="P134" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>46</v>
       </c>
       <c r="Q134" s="2">
@@ -12362,11 +12362,11 @@
         <v>2350</v>
       </c>
       <c r="O135" s="2">
-        <f>O134+2</f>
+        <f t="shared" si="36"/>
         <v>59</v>
       </c>
       <c r="P135" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>50</v>
       </c>
       <c r="Q135" s="2">
@@ -12405,27 +12405,27 @@
         <v>0</v>
       </c>
       <c r="K136" s="1">
-        <f t="shared" ref="K136:K145" si="37">K135+500</f>
+        <f t="shared" ref="K136:K145" si="38">K135+500</f>
         <v>6800</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" ref="L136:L145" si="38">L135+500</f>
+        <f t="shared" ref="L136:L145" si="39">L135+500</f>
         <v>8500</v>
       </c>
       <c r="M136" s="1">
-        <f t="shared" ref="M136:M145" si="39">M135+200</f>
+        <f t="shared" ref="M136:M145" si="40">M135+200</f>
         <v>2550</v>
       </c>
       <c r="N136" s="1">
-        <f t="shared" ref="N136:N145" si="40">N135+200</f>
+        <f t="shared" ref="N136:N145" si="41">N135+200</f>
         <v>2550</v>
       </c>
       <c r="O136" s="2">
-        <f>O135+2</f>
+        <f t="shared" si="36"/>
         <v>61</v>
       </c>
       <c r="P136" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>54</v>
       </c>
       <c r="Q136" s="2">
@@ -12464,27 +12464,27 @@
         <v>0</v>
       </c>
       <c r="K137" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>7300</v>
       </c>
       <c r="L137" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>9000</v>
       </c>
       <c r="M137" s="1">
-        <f t="shared" si="39"/>
-        <v>2750</v>
-      </c>
-      <c r="N137" s="1">
         <f t="shared" si="40"/>
         <v>2750</v>
       </c>
+      <c r="N137" s="1">
+        <f t="shared" si="41"/>
+        <v>2750</v>
+      </c>
       <c r="O137" s="2">
-        <f>O136+2</f>
+        <f t="shared" si="36"/>
         <v>63</v>
       </c>
       <c r="P137" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>58</v>
       </c>
       <c r="Q137" s="2">
@@ -12523,27 +12523,27 @@
         <v>0</v>
       </c>
       <c r="K138" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>7800</v>
       </c>
       <c r="L138" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>9500</v>
       </c>
       <c r="M138" s="1">
-        <f t="shared" si="39"/>
-        <v>2950</v>
-      </c>
-      <c r="N138" s="1">
         <f t="shared" si="40"/>
         <v>2950</v>
       </c>
+      <c r="N138" s="1">
+        <f t="shared" si="41"/>
+        <v>2950</v>
+      </c>
       <c r="O138" s="2">
-        <f>O137+2</f>
+        <f t="shared" si="36"/>
         <v>65</v>
       </c>
       <c r="P138" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>62</v>
       </c>
       <c r="Q138" s="2">
@@ -12582,27 +12582,27 @@
         <v>0</v>
       </c>
       <c r="K139" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>8300</v>
       </c>
       <c r="L139" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>10000</v>
       </c>
       <c r="M139" s="1">
-        <f t="shared" si="39"/>
-        <v>3150</v>
-      </c>
-      <c r="N139" s="1">
         <f t="shared" si="40"/>
         <v>3150</v>
       </c>
+      <c r="N139" s="1">
+        <f t="shared" si="41"/>
+        <v>3150</v>
+      </c>
       <c r="O139" s="2">
-        <f>O138+2</f>
+        <f t="shared" si="36"/>
         <v>67</v>
       </c>
       <c r="P139" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>66</v>
       </c>
       <c r="Q139" s="2">
@@ -12641,27 +12641,27 @@
         <v>0</v>
       </c>
       <c r="K140" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>8800</v>
       </c>
       <c r="L140" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>10500</v>
       </c>
       <c r="M140" s="1">
-        <f t="shared" si="39"/>
-        <v>3350</v>
-      </c>
-      <c r="N140" s="1">
         <f t="shared" si="40"/>
         <v>3350</v>
       </c>
+      <c r="N140" s="1">
+        <f t="shared" si="41"/>
+        <v>3350</v>
+      </c>
       <c r="O140" s="2">
-        <f>O139+2</f>
+        <f t="shared" si="36"/>
         <v>69</v>
       </c>
       <c r="P140" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>70</v>
       </c>
       <c r="Q140" s="2">
@@ -12702,27 +12702,27 @@
         <v>0</v>
       </c>
       <c r="K141" s="1">
-        <f t="shared" ref="K141:K180" si="41">K140+600</f>
+        <f t="shared" ref="K141:K180" si="42">K140+600</f>
         <v>9400</v>
       </c>
       <c r="L141" s="1">
-        <f t="shared" ref="L141:L180" si="42">L140+600</f>
+        <f t="shared" ref="L141:L180" si="43">L140+600</f>
         <v>11100</v>
       </c>
       <c r="M141" s="1">
-        <f t="shared" ref="M141:M180" si="43">M140+250</f>
+        <f t="shared" ref="M141:M180" si="44">M140+250</f>
         <v>3600</v>
       </c>
       <c r="N141" s="1">
-        <f t="shared" ref="N141:N180" si="44">N140+250</f>
+        <f t="shared" ref="N141:N180" si="45">N140+250</f>
         <v>3600</v>
       </c>
       <c r="O141" s="2">
-        <f>O140+2</f>
+        <f t="shared" si="36"/>
         <v>71</v>
       </c>
       <c r="P141" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>74</v>
       </c>
       <c r="Q141" s="2">
@@ -12768,27 +12768,27 @@
         <v>0</v>
       </c>
       <c r="K142" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>10000</v>
       </c>
       <c r="L142" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>11700</v>
       </c>
       <c r="M142" s="1">
-        <f t="shared" si="43"/>
-        <v>3850</v>
-      </c>
-      <c r="N142" s="1">
         <f t="shared" si="44"/>
         <v>3850</v>
       </c>
+      <c r="N142" s="1">
+        <f t="shared" si="45"/>
+        <v>3850</v>
+      </c>
       <c r="O142" s="2">
-        <f>O141+2</f>
+        <f t="shared" si="36"/>
         <v>73</v>
       </c>
       <c r="P142" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>78</v>
       </c>
       <c r="Q142" s="2">
@@ -12834,27 +12834,27 @@
         <v>0</v>
       </c>
       <c r="K143" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>10600</v>
       </c>
       <c r="L143" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>12300</v>
       </c>
       <c r="M143" s="1">
-        <f t="shared" si="43"/>
-        <v>4100</v>
-      </c>
-      <c r="N143" s="1">
         <f t="shared" si="44"/>
         <v>4100</v>
       </c>
+      <c r="N143" s="1">
+        <f t="shared" si="45"/>
+        <v>4100</v>
+      </c>
       <c r="O143" s="2">
-        <f>O142+2</f>
+        <f t="shared" si="36"/>
         <v>75</v>
       </c>
       <c r="P143" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>82</v>
       </c>
       <c r="Q143" s="2">
@@ -12900,27 +12900,27 @@
         <v>0</v>
       </c>
       <c r="K144" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>11200</v>
       </c>
       <c r="L144" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>12900</v>
       </c>
       <c r="M144" s="1">
-        <f t="shared" si="43"/>
-        <v>4350</v>
-      </c>
-      <c r="N144" s="1">
         <f t="shared" si="44"/>
         <v>4350</v>
       </c>
+      <c r="N144" s="1">
+        <f t="shared" si="45"/>
+        <v>4350</v>
+      </c>
       <c r="O144" s="2">
-        <f>O143+2</f>
+        <f t="shared" si="36"/>
         <v>77</v>
       </c>
       <c r="P144" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>86</v>
       </c>
       <c r="Q144" s="2">
@@ -12966,27 +12966,27 @@
         <v>0</v>
       </c>
       <c r="K145" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>11800</v>
       </c>
       <c r="L145" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>13500</v>
       </c>
       <c r="M145" s="1">
-        <f t="shared" si="43"/>
-        <v>4600</v>
-      </c>
-      <c r="N145" s="1">
         <f t="shared" si="44"/>
         <v>4600</v>
       </c>
+      <c r="N145" s="1">
+        <f t="shared" si="45"/>
+        <v>4600</v>
+      </c>
       <c r="O145" s="2">
-        <f>O144+2</f>
+        <f t="shared" si="36"/>
         <v>79</v>
       </c>
       <c r="P145" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>90</v>
       </c>
       <c r="Q145" s="2">
@@ -13032,27 +13032,27 @@
         <v>10</v>
       </c>
       <c r="K146" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>12400</v>
       </c>
       <c r="L146" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>14100</v>
       </c>
       <c r="M146" s="1">
-        <f t="shared" si="43"/>
-        <v>4850</v>
-      </c>
-      <c r="N146" s="1">
         <f t="shared" si="44"/>
         <v>4850</v>
       </c>
+      <c r="N146" s="1">
+        <f t="shared" si="45"/>
+        <v>4850</v>
+      </c>
       <c r="O146" s="2">
-        <f t="shared" ref="O146:O180" si="45">O145+3</f>
+        <f t="shared" ref="O146:O180" si="46">O145+3</f>
         <v>82</v>
       </c>
       <c r="P146" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>94</v>
       </c>
       <c r="Q146" s="2">
@@ -13093,31 +13093,31 @@
         <v>927</v>
       </c>
       <c r="J147" s="1">
-        <f t="shared" ref="J147:J155" si="46">J146*5</f>
+        <f t="shared" ref="J147:J155" si="47">J146*5</f>
         <v>50</v>
       </c>
       <c r="K147" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>13000</v>
       </c>
       <c r="L147" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>14700</v>
       </c>
       <c r="M147" s="1">
-        <f t="shared" si="43"/>
-        <v>5100</v>
-      </c>
-      <c r="N147" s="1">
         <f t="shared" si="44"/>
         <v>5100</v>
       </c>
+      <c r="N147" s="1">
+        <f t="shared" si="45"/>
+        <v>5100</v>
+      </c>
       <c r="O147" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>85</v>
       </c>
       <c r="P147" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>98</v>
       </c>
       <c r="Q147" s="2">
@@ -13158,31 +13158,31 @@
         <v>933</v>
       </c>
       <c r="J148" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>250</v>
       </c>
       <c r="K148" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>13600</v>
       </c>
       <c r="L148" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>15300</v>
       </c>
       <c r="M148" s="1">
-        <f t="shared" si="43"/>
-        <v>5350</v>
-      </c>
-      <c r="N148" s="1">
         <f t="shared" si="44"/>
         <v>5350</v>
       </c>
+      <c r="N148" s="1">
+        <f t="shared" si="45"/>
+        <v>5350</v>
+      </c>
       <c r="O148" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>88</v>
       </c>
       <c r="P148" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>102</v>
       </c>
       <c r="Q148" s="2">
@@ -13223,31 +13223,31 @@
         <v>939</v>
       </c>
       <c r="J149" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>1250</v>
       </c>
       <c r="K149" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>14200</v>
       </c>
       <c r="L149" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>15900</v>
       </c>
       <c r="M149" s="1">
-        <f t="shared" si="43"/>
-        <v>5600</v>
-      </c>
-      <c r="N149" s="1">
         <f t="shared" si="44"/>
         <v>5600</v>
       </c>
+      <c r="N149" s="1">
+        <f t="shared" si="45"/>
+        <v>5600</v>
+      </c>
       <c r="O149" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>91</v>
       </c>
       <c r="P149" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>106</v>
       </c>
       <c r="Q149" s="2">
@@ -13288,31 +13288,31 @@
         <v>945</v>
       </c>
       <c r="J150" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>6250</v>
       </c>
       <c r="K150" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>14800</v>
       </c>
       <c r="L150" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>16500</v>
       </c>
       <c r="M150" s="1">
-        <f t="shared" si="43"/>
-        <v>5850</v>
-      </c>
-      <c r="N150" s="1">
         <f t="shared" si="44"/>
         <v>5850</v>
       </c>
+      <c r="N150" s="1">
+        <f t="shared" si="45"/>
+        <v>5850</v>
+      </c>
       <c r="O150" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>94</v>
       </c>
       <c r="P150" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>110</v>
       </c>
       <c r="Q150" s="2">
@@ -13353,31 +13353,31 @@
         <v>951</v>
       </c>
       <c r="J151" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>31250</v>
       </c>
       <c r="K151" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>15400</v>
       </c>
       <c r="L151" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>17100</v>
       </c>
       <c r="M151" s="1">
-        <f t="shared" si="43"/>
-        <v>6100</v>
-      </c>
-      <c r="N151" s="1">
         <f t="shared" si="44"/>
         <v>6100</v>
       </c>
+      <c r="N151" s="1">
+        <f t="shared" si="45"/>
+        <v>6100</v>
+      </c>
       <c r="O151" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>97</v>
       </c>
       <c r="P151" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>114</v>
       </c>
       <c r="Q151" s="2">
@@ -13420,31 +13420,31 @@
         <v>957</v>
       </c>
       <c r="J152" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>156250</v>
       </c>
       <c r="K152" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>16000</v>
       </c>
       <c r="L152" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>17700</v>
       </c>
       <c r="M152" s="1">
-        <f t="shared" si="43"/>
-        <v>6350</v>
-      </c>
-      <c r="N152" s="1">
         <f t="shared" si="44"/>
         <v>6350</v>
       </c>
+      <c r="N152" s="1">
+        <f t="shared" si="45"/>
+        <v>6350</v>
+      </c>
       <c r="O152" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>100</v>
       </c>
       <c r="P152" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>118</v>
       </c>
       <c r="Q152" s="2">
@@ -13487,31 +13487,31 @@
         <v>963</v>
       </c>
       <c r="J153" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>781250</v>
       </c>
       <c r="K153" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>16600</v>
       </c>
       <c r="L153" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>18300</v>
       </c>
       <c r="M153" s="1">
-        <f t="shared" si="43"/>
-        <v>6600</v>
-      </c>
-      <c r="N153" s="1">
         <f t="shared" si="44"/>
         <v>6600</v>
       </c>
+      <c r="N153" s="1">
+        <f t="shared" si="45"/>
+        <v>6600</v>
+      </c>
       <c r="O153" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>103</v>
       </c>
       <c r="P153" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>122</v>
       </c>
       <c r="Q153" s="2">
@@ -13554,31 +13554,31 @@
         <v>969</v>
       </c>
       <c r="J154" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>3906250</v>
       </c>
       <c r="K154" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>17200</v>
       </c>
       <c r="L154" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>18900</v>
       </c>
       <c r="M154" s="1">
-        <f t="shared" si="43"/>
-        <v>6850</v>
-      </c>
-      <c r="N154" s="1">
         <f t="shared" si="44"/>
         <v>6850</v>
       </c>
+      <c r="N154" s="1">
+        <f t="shared" si="45"/>
+        <v>6850</v>
+      </c>
       <c r="O154" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>106</v>
       </c>
       <c r="P154" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>126</v>
       </c>
       <c r="Q154" s="2">
@@ -13621,31 +13621,31 @@
         <v>975</v>
       </c>
       <c r="J155" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>19531250</v>
       </c>
       <c r="K155" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>17800</v>
       </c>
       <c r="L155" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>19500</v>
       </c>
       <c r="M155" s="1">
-        <f t="shared" si="43"/>
-        <v>7100</v>
-      </c>
-      <c r="N155" s="1">
         <f t="shared" si="44"/>
         <v>7100</v>
       </c>
+      <c r="N155" s="1">
+        <f t="shared" si="45"/>
+        <v>7100</v>
+      </c>
       <c r="O155" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>109</v>
       </c>
       <c r="P155" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>130</v>
       </c>
       <c r="Q155" s="2">
@@ -13691,27 +13691,27 @@
         <v>982</v>
       </c>
       <c r="K156" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>18400</v>
       </c>
       <c r="L156" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>20100</v>
       </c>
       <c r="M156" s="1">
-        <f t="shared" si="43"/>
-        <v>7350</v>
-      </c>
-      <c r="N156" s="1">
         <f t="shared" si="44"/>
         <v>7350</v>
       </c>
+      <c r="N156" s="1">
+        <f t="shared" si="45"/>
+        <v>7350</v>
+      </c>
       <c r="O156" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>112</v>
       </c>
       <c r="P156" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>134</v>
       </c>
       <c r="Q156" s="2">
@@ -13757,27 +13757,27 @@
         <v>988</v>
       </c>
       <c r="K157" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>19000</v>
       </c>
       <c r="L157" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>20700</v>
       </c>
       <c r="M157" s="1">
-        <f t="shared" si="43"/>
-        <v>7600</v>
-      </c>
-      <c r="N157" s="1">
         <f t="shared" si="44"/>
         <v>7600</v>
       </c>
+      <c r="N157" s="1">
+        <f t="shared" si="45"/>
+        <v>7600</v>
+      </c>
       <c r="O157" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>115</v>
       </c>
       <c r="P157" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>138</v>
       </c>
       <c r="Q157" s="2">
@@ -13823,27 +13823,27 @@
         <v>994</v>
       </c>
       <c r="K158" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>19600</v>
       </c>
       <c r="L158" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>21300</v>
       </c>
       <c r="M158" s="1">
-        <f t="shared" si="43"/>
-        <v>7850</v>
-      </c>
-      <c r="N158" s="1">
         <f t="shared" si="44"/>
         <v>7850</v>
       </c>
+      <c r="N158" s="1">
+        <f t="shared" si="45"/>
+        <v>7850</v>
+      </c>
       <c r="O158" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>118</v>
       </c>
       <c r="P158" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>142</v>
       </c>
       <c r="Q158" s="2">
@@ -13889,27 +13889,27 @@
         <v>1000</v>
       </c>
       <c r="K159" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>20200</v>
       </c>
       <c r="L159" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>21900</v>
       </c>
       <c r="M159" s="1">
-        <f t="shared" si="43"/>
-        <v>8100</v>
-      </c>
-      <c r="N159" s="1">
         <f t="shared" si="44"/>
         <v>8100</v>
       </c>
+      <c r="N159" s="1">
+        <f t="shared" si="45"/>
+        <v>8100</v>
+      </c>
       <c r="O159" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>121</v>
       </c>
       <c r="P159" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>146</v>
       </c>
       <c r="Q159" s="2">
@@ -13955,27 +13955,27 @@
         <v>1006</v>
       </c>
       <c r="K160" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>20800</v>
       </c>
       <c r="L160" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>22500</v>
       </c>
       <c r="M160" s="1">
-        <f t="shared" si="43"/>
-        <v>8350</v>
-      </c>
-      <c r="N160" s="1">
         <f t="shared" si="44"/>
         <v>8350</v>
       </c>
+      <c r="N160" s="1">
+        <f t="shared" si="45"/>
+        <v>8350</v>
+      </c>
       <c r="O160" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>124</v>
       </c>
       <c r="P160" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>150</v>
       </c>
       <c r="Q160" s="2">
@@ -14021,27 +14021,27 @@
         <v>1012</v>
       </c>
       <c r="K161" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>21400</v>
       </c>
       <c r="L161" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>23100</v>
       </c>
       <c r="M161" s="1">
-        <f t="shared" si="43"/>
-        <v>8600</v>
-      </c>
-      <c r="N161" s="1">
         <f t="shared" si="44"/>
         <v>8600</v>
       </c>
+      <c r="N161" s="1">
+        <f t="shared" si="45"/>
+        <v>8600</v>
+      </c>
       <c r="O161" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>127</v>
       </c>
       <c r="P161" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>154</v>
       </c>
       <c r="Q161" s="2">
@@ -14087,27 +14087,27 @@
         <v>1018</v>
       </c>
       <c r="K162" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>22000</v>
       </c>
       <c r="L162" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>23700</v>
       </c>
       <c r="M162" s="1">
-        <f t="shared" si="43"/>
-        <v>8850</v>
-      </c>
-      <c r="N162" s="1">
         <f t="shared" si="44"/>
         <v>8850</v>
       </c>
+      <c r="N162" s="1">
+        <f t="shared" si="45"/>
+        <v>8850</v>
+      </c>
       <c r="O162" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>130</v>
       </c>
       <c r="P162" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>158</v>
       </c>
       <c r="Q162" s="2">
@@ -14153,27 +14153,27 @@
         <v>1024</v>
       </c>
       <c r="K163" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>22600</v>
       </c>
       <c r="L163" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>24300</v>
       </c>
       <c r="M163" s="1">
-        <f t="shared" si="43"/>
-        <v>9100</v>
-      </c>
-      <c r="N163" s="1">
         <f t="shared" si="44"/>
         <v>9100</v>
       </c>
+      <c r="N163" s="1">
+        <f t="shared" si="45"/>
+        <v>9100</v>
+      </c>
       <c r="O163" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>133</v>
       </c>
       <c r="P163" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>162</v>
       </c>
       <c r="Q163" s="2">
@@ -14219,27 +14219,27 @@
         <v>1030</v>
       </c>
       <c r="K164" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>23200</v>
       </c>
       <c r="L164" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>24900</v>
       </c>
       <c r="M164" s="1">
-        <f t="shared" si="43"/>
-        <v>9350</v>
-      </c>
-      <c r="N164" s="1">
         <f t="shared" si="44"/>
         <v>9350</v>
       </c>
+      <c r="N164" s="1">
+        <f t="shared" si="45"/>
+        <v>9350</v>
+      </c>
       <c r="O164" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>136</v>
       </c>
       <c r="P164" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>166</v>
       </c>
       <c r="Q164" s="2">
@@ -14285,27 +14285,27 @@
         <v>1036</v>
       </c>
       <c r="K165" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>23800</v>
       </c>
       <c r="L165" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>25500</v>
       </c>
       <c r="M165" s="1">
-        <f t="shared" si="43"/>
-        <v>9600</v>
-      </c>
-      <c r="N165" s="1">
         <f t="shared" si="44"/>
         <v>9600</v>
       </c>
+      <c r="N165" s="1">
+        <f t="shared" si="45"/>
+        <v>9600</v>
+      </c>
       <c r="O165" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>139</v>
       </c>
       <c r="P165" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>170</v>
       </c>
       <c r="Q165" s="2">
@@ -14349,27 +14349,27 @@
         <v>1042</v>
       </c>
       <c r="K166" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>24400</v>
       </c>
       <c r="L166" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>26100</v>
       </c>
       <c r="M166" s="1">
-        <f t="shared" si="43"/>
-        <v>9850</v>
-      </c>
-      <c r="N166" s="1">
         <f t="shared" si="44"/>
         <v>9850</v>
       </c>
+      <c r="N166" s="1">
+        <f t="shared" si="45"/>
+        <v>9850</v>
+      </c>
       <c r="O166" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>142</v>
       </c>
       <c r="P166" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>174</v>
       </c>
       <c r="Q166" s="2">
@@ -14408,27 +14408,27 @@
         <v>1048</v>
       </c>
       <c r="K167" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>25000</v>
       </c>
       <c r="L167" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>26700</v>
       </c>
       <c r="M167" s="1">
-        <f t="shared" si="43"/>
-        <v>10100</v>
-      </c>
-      <c r="N167" s="1">
         <f t="shared" si="44"/>
         <v>10100</v>
       </c>
+      <c r="N167" s="1">
+        <f t="shared" si="45"/>
+        <v>10100</v>
+      </c>
       <c r="O167" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>145</v>
       </c>
       <c r="P167" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>178</v>
       </c>
       <c r="Q167" s="2">
@@ -14467,27 +14467,27 @@
         <v>1054</v>
       </c>
       <c r="K168" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>25600</v>
       </c>
       <c r="L168" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>27300</v>
       </c>
       <c r="M168" s="1">
-        <f t="shared" si="43"/>
-        <v>10350</v>
-      </c>
-      <c r="N168" s="1">
         <f t="shared" si="44"/>
         <v>10350</v>
       </c>
+      <c r="N168" s="1">
+        <f t="shared" si="45"/>
+        <v>10350</v>
+      </c>
       <c r="O168" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>148</v>
       </c>
       <c r="P168" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>182</v>
       </c>
       <c r="Q168" s="2">
@@ -14526,27 +14526,27 @@
         <v>1060</v>
       </c>
       <c r="K169" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>26200</v>
       </c>
       <c r="L169" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>27900</v>
       </c>
       <c r="M169" s="1">
-        <f t="shared" si="43"/>
-        <v>10600</v>
-      </c>
-      <c r="N169" s="1">
         <f t="shared" si="44"/>
         <v>10600</v>
       </c>
+      <c r="N169" s="1">
+        <f t="shared" si="45"/>
+        <v>10600</v>
+      </c>
       <c r="O169" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>151</v>
       </c>
       <c r="P169" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>186</v>
       </c>
       <c r="Q169" s="2">
@@ -14585,27 +14585,27 @@
         <v>1065</v>
       </c>
       <c r="K170" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>26800</v>
       </c>
       <c r="L170" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>28500</v>
       </c>
       <c r="M170" s="1">
-        <f t="shared" si="43"/>
-        <v>10850</v>
-      </c>
-      <c r="N170" s="1">
         <f t="shared" si="44"/>
         <v>10850</v>
       </c>
+      <c r="N170" s="1">
+        <f t="shared" si="45"/>
+        <v>10850</v>
+      </c>
       <c r="O170" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>154</v>
       </c>
       <c r="P170" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>190</v>
       </c>
       <c r="Q170" s="2">
@@ -14644,27 +14644,27 @@
         <v>1070</v>
       </c>
       <c r="K171" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>27400</v>
       </c>
       <c r="L171" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>29100</v>
       </c>
       <c r="M171" s="1">
-        <f t="shared" si="43"/>
-        <v>11100</v>
-      </c>
-      <c r="N171" s="1">
         <f t="shared" si="44"/>
         <v>11100</v>
       </c>
+      <c r="N171" s="1">
+        <f t="shared" si="45"/>
+        <v>11100</v>
+      </c>
       <c r="O171" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>157</v>
       </c>
       <c r="P171" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>194</v>
       </c>
       <c r="Q171" s="2">
@@ -14703,27 +14703,27 @@
         <v>1075</v>
       </c>
       <c r="K172" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>28000</v>
       </c>
       <c r="L172" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>29700</v>
       </c>
       <c r="M172" s="1">
-        <f t="shared" si="43"/>
-        <v>11350</v>
-      </c>
-      <c r="N172" s="1">
         <f t="shared" si="44"/>
         <v>11350</v>
       </c>
+      <c r="N172" s="1">
+        <f t="shared" si="45"/>
+        <v>11350</v>
+      </c>
       <c r="O172" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>160</v>
       </c>
       <c r="P172" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>198</v>
       </c>
       <c r="Q172" s="2">
@@ -14762,27 +14762,27 @@
         <v>1080</v>
       </c>
       <c r="K173" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>28600</v>
       </c>
       <c r="L173" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>30300</v>
       </c>
       <c r="M173" s="1">
-        <f t="shared" si="43"/>
-        <v>11600</v>
-      </c>
-      <c r="N173" s="1">
         <f t="shared" si="44"/>
         <v>11600</v>
       </c>
+      <c r="N173" s="1">
+        <f t="shared" si="45"/>
+        <v>11600</v>
+      </c>
       <c r="O173" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>163</v>
       </c>
       <c r="P173" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>202</v>
       </c>
       <c r="Q173" s="2">
@@ -14821,27 +14821,27 @@
         <v>1085</v>
       </c>
       <c r="K174" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>29200</v>
       </c>
       <c r="L174" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>30900</v>
       </c>
       <c r="M174" s="1">
-        <f t="shared" si="43"/>
-        <v>11850</v>
-      </c>
-      <c r="N174" s="1">
         <f t="shared" si="44"/>
         <v>11850</v>
       </c>
+      <c r="N174" s="1">
+        <f t="shared" si="45"/>
+        <v>11850</v>
+      </c>
       <c r="O174" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>166</v>
       </c>
       <c r="P174" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>206</v>
       </c>
       <c r="Q174" s="2">
@@ -14880,27 +14880,27 @@
         <v>1090</v>
       </c>
       <c r="K175" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>29800</v>
       </c>
       <c r="L175" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>31500</v>
       </c>
       <c r="M175" s="1">
-        <f t="shared" si="43"/>
-        <v>12100</v>
-      </c>
-      <c r="N175" s="1">
         <f t="shared" si="44"/>
         <v>12100</v>
       </c>
+      <c r="N175" s="1">
+        <f t="shared" si="45"/>
+        <v>12100</v>
+      </c>
       <c r="O175" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>169</v>
       </c>
       <c r="P175" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>210</v>
       </c>
       <c r="Q175" s="2">
@@ -14941,27 +14941,27 @@
         <v>1095</v>
       </c>
       <c r="K176" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>30400</v>
       </c>
       <c r="L176" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>32100</v>
       </c>
       <c r="M176" s="1">
-        <f t="shared" si="43"/>
-        <v>12350</v>
-      </c>
-      <c r="N176" s="1">
         <f t="shared" si="44"/>
         <v>12350</v>
       </c>
+      <c r="N176" s="1">
+        <f t="shared" si="45"/>
+        <v>12350</v>
+      </c>
       <c r="O176" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>172</v>
       </c>
       <c r="P176" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>214</v>
       </c>
       <c r="Q176" s="2">
@@ -15007,27 +15007,27 @@
         <v>1100</v>
       </c>
       <c r="K177" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>31000</v>
       </c>
       <c r="L177" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>32700</v>
       </c>
       <c r="M177" s="1">
-        <f t="shared" si="43"/>
-        <v>12600</v>
-      </c>
-      <c r="N177" s="1">
         <f t="shared" si="44"/>
         <v>12600</v>
       </c>
+      <c r="N177" s="1">
+        <f t="shared" si="45"/>
+        <v>12600</v>
+      </c>
       <c r="O177" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>175</v>
       </c>
       <c r="P177" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>218</v>
       </c>
       <c r="Q177" s="2">
@@ -15073,27 +15073,27 @@
         <v>1105</v>
       </c>
       <c r="K178" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>31600</v>
       </c>
       <c r="L178" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>33300</v>
       </c>
       <c r="M178" s="1">
-        <f t="shared" si="43"/>
-        <v>12850</v>
-      </c>
-      <c r="N178" s="1">
         <f t="shared" si="44"/>
         <v>12850</v>
       </c>
+      <c r="N178" s="1">
+        <f t="shared" si="45"/>
+        <v>12850</v>
+      </c>
       <c r="O178" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>178</v>
       </c>
       <c r="P178" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>222</v>
       </c>
       <c r="Q178" s="2">
@@ -15139,27 +15139,27 @@
         <v>1110</v>
       </c>
       <c r="K179" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>32200</v>
       </c>
       <c r="L179" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>33900</v>
       </c>
       <c r="M179" s="1">
-        <f t="shared" si="43"/>
-        <v>13100</v>
-      </c>
-      <c r="N179" s="1">
         <f t="shared" si="44"/>
         <v>13100</v>
       </c>
+      <c r="N179" s="1">
+        <f t="shared" si="45"/>
+        <v>13100</v>
+      </c>
       <c r="O179" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>181</v>
       </c>
       <c r="P179" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>226</v>
       </c>
       <c r="Q179" s="2">
@@ -15205,27 +15205,27 @@
         <v>1115</v>
       </c>
       <c r="K180" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>32800</v>
       </c>
       <c r="L180" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>34500</v>
       </c>
       <c r="M180" s="1">
-        <f t="shared" si="43"/>
-        <v>13350</v>
-      </c>
-      <c r="N180" s="1">
         <f t="shared" si="44"/>
         <v>13350</v>
       </c>
+      <c r="N180" s="1">
+        <f t="shared" si="45"/>
+        <v>13350</v>
+      </c>
       <c r="O180" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>184</v>
       </c>
       <c r="P180" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>230</v>
       </c>
       <c r="Q180" s="2">
@@ -15245,7 +15245,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:I5 J5 K5:Q5 C3:Q4" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="1129">
   <si>
     <t>ID</t>
   </si>
@@ -2792,12 +2792,18 @@
     <t>深渊鸡</t>
   </si>
   <si>
+    <t>1000恒</t>
+  </si>
+  <si>
     <t>900僧</t>
   </si>
   <si>
     <t>3200不</t>
   </si>
   <si>
+    <t>1垓</t>
+  </si>
+  <si>
     <t>33000000000</t>
   </si>
   <si>
@@ -2810,12 +2816,18 @@
     <t>深渊鹿</t>
   </si>
   <si>
+    <t>4000恒</t>
+  </si>
+  <si>
     <t>9000僧</t>
   </si>
   <si>
     <t>64000不</t>
   </si>
   <si>
+    <t>5垓</t>
+  </si>
+  <si>
     <t>36000000000</t>
   </si>
   <si>
@@ -2828,12 +2840,18 @@
     <t>深渊草人</t>
   </si>
   <si>
+    <t>16000恒</t>
+  </si>
+  <si>
     <t>9祇</t>
   </si>
   <si>
     <t>128可</t>
   </si>
   <si>
+    <t>25垓</t>
+  </si>
+  <si>
     <t>39000000000</t>
   </si>
   <si>
@@ -2846,12 +2864,18 @@
     <t>深渊猫</t>
   </si>
   <si>
+    <t>64000恒</t>
+  </si>
+  <si>
     <t>90祇</t>
   </si>
   <si>
     <t>2560可</t>
   </si>
   <si>
+    <t>125垓</t>
+  </si>
+  <si>
     <t>42000000000</t>
   </si>
   <si>
@@ -2864,12 +2888,18 @@
     <t>深渊花</t>
   </si>
   <si>
+    <t>24河</t>
+  </si>
+  <si>
     <t>900祇</t>
   </si>
   <si>
     <t>5思</t>
   </si>
   <si>
+    <t>625垓</t>
+  </si>
+  <si>
     <t>45000000000</t>
   </si>
   <si>
@@ -2882,10 +2912,16 @@
     <t>深渊雪人</t>
   </si>
   <si>
+    <t>96河</t>
+  </si>
+  <si>
     <t>9000祇</t>
   </si>
   <si>
     <t>100思</t>
+  </si>
+  <si>
+    <t>2500垓</t>
   </si>
   <si>
     <t>48000000000</t>
@@ -4358,8 +4394,8 @@
     <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21" style="2" customWidth="1"/>
+    <col min="7" max="7" width="32.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="24.6666666666667" style="2" customWidth="1"/>
     <col min="9" max="9" width="21.75" style="2" customWidth="1"/>
     <col min="10" max="11" width="11.75" style="2" customWidth="1"/>
     <col min="12" max="12" width="12.75" style="2" customWidth="1"/>
@@ -4604,7 +4640,7 @@
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
     </row>
-    <row r="6" ht="14.25" spans="3:20">
+    <row r="6" ht="14" spans="3:20">
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
@@ -13457,16 +13493,16 @@
         <v>921</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I146" s="8" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="J146" s="1">
         <v>10</v>
       </c>
-      <c r="K146" s="1">
-        <v>0</v>
+      <c r="K146" s="1" t="s">
+        <v>924</v>
       </c>
       <c r="L146" s="1">
         <f t="shared" si="42"/>
@@ -13485,21 +13521,20 @@
         <v>4850</v>
       </c>
       <c r="P146" s="2">
-        <f t="shared" ref="P146:P180" si="46">P145+3</f>
+        <f>P145+3</f>
         <v>82</v>
       </c>
       <c r="Q146" s="2">
-        <f t="shared" si="37"/>
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="R146" s="2">
         <v>99.99</v>
       </c>
       <c r="S146" s="10" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="T146" s="10" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="W146" s="2"/>
       <c r="X146" s="2"/>
@@ -13509,32 +13544,32 @@
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="1" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="E147" s="1">
         <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="I147" s="9" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="J147" s="1">
-        <f t="shared" ref="J147:J155" si="47">J146*5</f>
+        <f t="shared" ref="J147:J155" si="46">J146*5</f>
         <v>50</v>
       </c>
-      <c r="K147" s="1">
-        <v>0</v>
+      <c r="K147" s="1" t="s">
+        <v>932</v>
       </c>
       <c r="L147" s="1">
         <f t="shared" si="42"/>
@@ -13553,21 +13588,21 @@
         <v>5100</v>
       </c>
       <c r="P147" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="P146:P180" si="47">P146+3</f>
         <v>85</v>
       </c>
       <c r="Q147" s="2">
         <f t="shared" si="37"/>
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="R147" s="2">
         <v>99.99</v>
       </c>
       <c r="S147" s="10" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="T147" s="10" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="W147" s="2"/>
       <c r="X147" s="2"/>
@@ -13577,32 +13612,32 @@
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="1" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="E148" s="1">
         <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="I148" s="9" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="J148" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>250</v>
       </c>
-      <c r="K148" s="1">
-        <v>0</v>
+      <c r="K148" s="1" t="s">
+        <v>940</v>
       </c>
       <c r="L148" s="1">
         <f t="shared" si="42"/>
@@ -13621,21 +13656,21 @@
         <v>5350</v>
       </c>
       <c r="P148" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>88</v>
       </c>
       <c r="Q148" s="2">
         <f t="shared" si="37"/>
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="R148" s="2">
         <v>99.99</v>
       </c>
       <c r="S148" s="10" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="T148" s="10" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="W148" s="2"/>
       <c r="X148" s="2"/>
@@ -13645,32 +13680,32 @@
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="1" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="E149" s="1">
         <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="I149" s="9" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="J149" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1250</v>
       </c>
-      <c r="K149" s="1">
-        <v>0</v>
+      <c r="K149" s="1" t="s">
+        <v>948</v>
       </c>
       <c r="L149" s="1">
         <f t="shared" si="42"/>
@@ -13689,21 +13724,21 @@
         <v>5600</v>
       </c>
       <c r="P149" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>91</v>
       </c>
       <c r="Q149" s="2">
         <f t="shared" si="37"/>
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="R149" s="2">
         <v>99.99</v>
       </c>
       <c r="S149" s="10" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="T149" s="10" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="W149" s="2"/>
       <c r="X149" s="2"/>
@@ -13713,32 +13748,32 @@
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="1" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="E150" s="1">
         <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="G150" s="7" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="H150" s="7" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="I150" s="9" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
       <c r="J150" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>6250</v>
       </c>
-      <c r="K150" s="1">
-        <v>0</v>
+      <c r="K150" s="1" t="s">
+        <v>956</v>
       </c>
       <c r="L150" s="1">
         <f t="shared" si="42"/>
@@ -13757,21 +13792,21 @@
         <v>5850</v>
       </c>
       <c r="P150" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>94</v>
       </c>
       <c r="Q150" s="2">
         <f t="shared" si="37"/>
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="R150" s="2">
         <v>99.99</v>
       </c>
       <c r="S150" s="10" t="s">
-        <v>947</v>
+        <v>957</v>
       </c>
       <c r="T150" s="10" t="s">
-        <v>947</v>
+        <v>957</v>
       </c>
       <c r="W150" s="2"/>
       <c r="X150" s="2"/>
@@ -13781,32 +13816,32 @@
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="1" t="s">
-        <v>948</v>
+        <v>958</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>949</v>
+        <v>959</v>
       </c>
       <c r="E151" s="1">
         <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="I151" s="9" t="s">
-        <v>952</v>
+        <v>963</v>
       </c>
       <c r="J151" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>31250</v>
       </c>
-      <c r="K151" s="1">
-        <v>0</v>
+      <c r="K151" s="1" t="s">
+        <v>964</v>
       </c>
       <c r="L151" s="1">
         <f t="shared" si="42"/>
@@ -13825,21 +13860,21 @@
         <v>6100</v>
       </c>
       <c r="P151" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>97</v>
       </c>
       <c r="Q151" s="2">
         <f t="shared" si="37"/>
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="R151" s="2">
         <v>99.99</v>
       </c>
       <c r="S151" s="10" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="T151" s="10" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="U151" s="2"/>
       <c r="V151" s="2"/>
@@ -13851,28 +13886,28 @@
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="1" t="s">
-        <v>954</v>
+        <v>966</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>955</v>
+        <v>967</v>
       </c>
       <c r="E152" s="1">
         <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>957</v>
+        <v>969</v>
       </c>
       <c r="H152" s="7" t="s">
-        <v>957</v>
+        <v>969</v>
       </c>
       <c r="I152" s="9" t="s">
-        <v>958</v>
+        <v>970</v>
       </c>
       <c r="J152" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>156250</v>
       </c>
       <c r="K152" s="1">
@@ -13895,21 +13930,21 @@
         <v>6350</v>
       </c>
       <c r="P152" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>100</v>
       </c>
       <c r="Q152" s="2">
         <f t="shared" si="37"/>
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="R152" s="2">
         <v>99.99</v>
       </c>
       <c r="S152" s="10" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="T152" s="10" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="U152" s="2"/>
       <c r="V152" s="2"/>
@@ -13921,28 +13956,28 @@
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="1" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
       <c r="E153" s="1">
         <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="H153" s="7" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="I153" s="9" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="J153" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>781250</v>
       </c>
       <c r="K153" s="1">
@@ -13965,21 +14000,21 @@
         <v>6600</v>
       </c>
       <c r="P153" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>103</v>
       </c>
       <c r="Q153" s="2">
         <f t="shared" si="37"/>
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="R153" s="2">
         <v>99.99</v>
       </c>
       <c r="S153" s="10" t="s">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="T153" s="10" t="s">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="U153" s="2"/>
       <c r="V153" s="2"/>
@@ -13991,28 +14026,28 @@
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="1" t="s">
-        <v>966</v>
+        <v>978</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
       <c r="E154" s="1">
         <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>968</v>
+        <v>980</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>969</v>
+        <v>981</v>
       </c>
       <c r="H154" s="7" t="s">
-        <v>969</v>
+        <v>981</v>
       </c>
       <c r="I154" s="9" t="s">
-        <v>970</v>
+        <v>982</v>
       </c>
       <c r="J154" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>3906250</v>
       </c>
       <c r="K154" s="1">
@@ -14035,21 +14070,21 @@
         <v>6850</v>
       </c>
       <c r="P154" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>106</v>
       </c>
       <c r="Q154" s="2">
         <f t="shared" si="37"/>
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="R154" s="2">
         <v>99.99</v>
       </c>
       <c r="S154" s="10" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="T154" s="10" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="U154" s="2"/>
       <c r="V154" s="2"/>
@@ -14061,28 +14096,28 @@
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="1" t="s">
-        <v>972</v>
+        <v>984</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>973</v>
+        <v>985</v>
       </c>
       <c r="E155" s="1">
         <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>974</v>
+        <v>986</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="H155" s="7" t="s">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="I155" s="9" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="J155" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>19531250</v>
       </c>
       <c r="K155" s="1">
@@ -14105,21 +14140,21 @@
         <v>7100</v>
       </c>
       <c r="P155" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>109</v>
       </c>
       <c r="Q155" s="2">
         <f t="shared" si="37"/>
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="R155" s="2">
         <v>99.99</v>
       </c>
       <c r="S155" s="10" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
       <c r="T155" s="10" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
       <c r="U155" s="2"/>
       <c r="V155" s="2"/>
@@ -14131,28 +14166,28 @@
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="1" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="E156" s="1">
         <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="H156" s="7" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="I156" s="9" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="K156" s="1">
         <v>0</v>
@@ -14174,12 +14209,12 @@
         <v>7350</v>
       </c>
       <c r="P156" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>112</v>
       </c>
       <c r="Q156" s="2">
         <f t="shared" si="37"/>
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="R156" s="2">
         <v>99.99</v>
@@ -14200,28 +14235,28 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="1" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
       <c r="E157" s="1">
         <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="H157" s="7" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="I157" s="9" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="K157" s="1">
         <v>0</v>
@@ -14243,12 +14278,12 @@
         <v>7600</v>
       </c>
       <c r="P157" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>115</v>
       </c>
       <c r="Q157" s="2">
         <f t="shared" si="37"/>
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="R157" s="2">
         <v>99.99</v>
@@ -14269,28 +14304,28 @@
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="1" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="E158" s="1">
         <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
       <c r="G158" s="7" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="H158" s="7" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="I158" s="9" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
       <c r="K158" s="1">
         <v>0</v>
@@ -14312,12 +14347,12 @@
         <v>7850</v>
       </c>
       <c r="P158" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>118</v>
       </c>
       <c r="Q158" s="2">
         <f t="shared" si="37"/>
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="R158" s="2">
         <v>99.99</v>
@@ -14338,28 +14373,28 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="1" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="E159" s="1">
         <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="H159" s="7" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="I159" s="9" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1001</v>
+        <v>1013</v>
       </c>
       <c r="K159" s="1">
         <v>0</v>
@@ -14381,12 +14416,12 @@
         <v>8100</v>
       </c>
       <c r="P159" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>121</v>
       </c>
       <c r="Q159" s="2">
         <f t="shared" si="37"/>
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="R159" s="2">
         <v>99.99</v>
@@ -14407,28 +14442,28 @@
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="1" t="s">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
       <c r="E160" s="1">
         <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="H160" s="7" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="I160" s="9" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="K160" s="1">
         <v>0</v>
@@ -14450,12 +14485,12 @@
         <v>8350</v>
       </c>
       <c r="P160" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>124</v>
       </c>
       <c r="Q160" s="2">
         <f t="shared" si="37"/>
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="R160" s="2">
         <v>99.99</v>
@@ -14476,28 +14511,28 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="1" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="E161" s="1">
         <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>1011</v>
+        <v>1023</v>
       </c>
       <c r="H161" s="7" t="s">
-        <v>1011</v>
+        <v>1023</v>
       </c>
       <c r="I161" s="9" t="s">
-        <v>1012</v>
+        <v>1024</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
       <c r="K161" s="1">
         <v>0</v>
@@ -14519,12 +14554,12 @@
         <v>8600</v>
       </c>
       <c r="P161" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>127</v>
       </c>
       <c r="Q161" s="2">
         <f t="shared" si="37"/>
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="R161" s="2">
         <v>99.99</v>
@@ -14545,28 +14580,28 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="1" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="E162" s="1">
         <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="G162" s="7" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
       <c r="H162" s="7" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
       <c r="I162" s="9" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="K162" s="1">
         <v>0</v>
@@ -14588,12 +14623,12 @@
         <v>8850</v>
       </c>
       <c r="P162" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>130</v>
       </c>
       <c r="Q162" s="2">
         <f t="shared" si="37"/>
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="R162" s="2">
         <v>99.99</v>
@@ -14614,28 +14649,28 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="1" t="s">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="E163" s="1">
         <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1022</v>
+        <v>1034</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>1023</v>
+        <v>1035</v>
       </c>
       <c r="H163" s="7" t="s">
-        <v>1023</v>
+        <v>1035</v>
       </c>
       <c r="I163" s="9" t="s">
-        <v>1024</v>
+        <v>1036</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
       <c r="K163" s="1">
         <v>0</v>
@@ -14657,12 +14692,12 @@
         <v>9100</v>
       </c>
       <c r="P163" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>133</v>
       </c>
       <c r="Q163" s="2">
         <f t="shared" si="37"/>
-        <v>162</v>
+        <v>218</v>
       </c>
       <c r="R163" s="2">
         <v>99.99</v>
@@ -14683,28 +14718,28 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="1" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>1027</v>
+        <v>1039</v>
       </c>
       <c r="E164" s="1">
         <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="G164" s="7" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="H164" s="7" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="I164" s="9" t="s">
-        <v>1030</v>
+        <v>1042</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>1031</v>
+        <v>1043</v>
       </c>
       <c r="K164" s="1">
         <v>0</v>
@@ -14726,12 +14761,12 @@
         <v>9350</v>
       </c>
       <c r="P164" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>136</v>
       </c>
       <c r="Q164" s="2">
         <f t="shared" si="37"/>
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="R164" s="2">
         <v>99.99</v>
@@ -14752,28 +14787,28 @@
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="1" t="s">
-        <v>1032</v>
+        <v>1044</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>1033</v>
+        <v>1045</v>
       </c>
       <c r="E165" s="1">
         <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1034</v>
+        <v>1046</v>
       </c>
       <c r="G165" s="7" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="H165" s="7" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="I165" s="9" t="s">
-        <v>1036</v>
+        <v>1048</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>1037</v>
+        <v>1049</v>
       </c>
       <c r="K165" s="1">
         <v>0</v>
@@ -14795,12 +14830,12 @@
         <v>9600</v>
       </c>
       <c r="P165" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>139</v>
       </c>
       <c r="Q165" s="2">
         <f t="shared" si="37"/>
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="R165" s="2">
         <v>99.99</v>
@@ -14819,28 +14854,28 @@
     </row>
     <row r="166" customHeight="1" spans="3:20">
       <c r="C166" s="1" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
       <c r="E166" s="1">
         <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="G166" s="7" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
       <c r="H166" s="7" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
       <c r="I166" s="9" t="s">
-        <v>1042</v>
+        <v>1054</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>1043</v>
+        <v>1055</v>
       </c>
       <c r="K166" s="1">
         <v>0</v>
@@ -14862,12 +14897,12 @@
         <v>9850</v>
       </c>
       <c r="P166" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>142</v>
       </c>
       <c r="Q166" s="2">
         <f t="shared" si="37"/>
-        <v>174</v>
+        <v>230</v>
       </c>
       <c r="R166" s="2">
         <v>99.99</v>
@@ -14881,28 +14916,28 @@
     </row>
     <row r="167" customHeight="1" spans="3:20">
       <c r="C167" s="1" t="s">
-        <v>1044</v>
+        <v>1056</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>1045</v>
+        <v>1057</v>
       </c>
       <c r="E167" s="1">
         <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1046</v>
+        <v>1058</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>1047</v>
+        <v>1059</v>
       </c>
       <c r="H167" s="7" t="s">
-        <v>1047</v>
+        <v>1059</v>
       </c>
       <c r="I167" s="9" t="s">
-        <v>1048</v>
+        <v>1060</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="K167" s="1">
         <v>0</v>
@@ -14924,12 +14959,12 @@
         <v>10100</v>
       </c>
       <c r="P167" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>145</v>
       </c>
       <c r="Q167" s="2">
         <f t="shared" si="37"/>
-        <v>178</v>
+        <v>234</v>
       </c>
       <c r="R167" s="2">
         <v>99.99</v>
@@ -14943,28 +14978,28 @@
     </row>
     <row r="168" customHeight="1" spans="3:20">
       <c r="C168" s="1" t="s">
-        <v>1050</v>
+        <v>1062</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>1051</v>
+        <v>1063</v>
       </c>
       <c r="E168" s="1">
         <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="G168" s="7" t="s">
-        <v>1053</v>
+        <v>1065</v>
       </c>
       <c r="H168" s="7" t="s">
-        <v>1053</v>
+        <v>1065</v>
       </c>
       <c r="I168" s="9" t="s">
-        <v>1054</v>
+        <v>1066</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>1055</v>
+        <v>1067</v>
       </c>
       <c r="K168" s="1">
         <v>0</v>
@@ -14986,12 +15021,12 @@
         <v>10350</v>
       </c>
       <c r="P168" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>148</v>
       </c>
       <c r="Q168" s="2">
         <f t="shared" si="37"/>
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="R168" s="2">
         <v>99.99</v>
@@ -15005,28 +15040,28 @@
     </row>
     <row r="169" customHeight="1" spans="3:20">
       <c r="C169" s="1" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="E169" s="1">
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="H169" s="7" t="s">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="I169" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
       <c r="K169" s="1">
         <v>0</v>
@@ -15048,12 +15083,12 @@
         <v>10600</v>
       </c>
       <c r="P169" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>151</v>
       </c>
       <c r="Q169" s="2">
         <f t="shared" si="37"/>
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="R169" s="2">
         <v>99.99</v>
@@ -15067,28 +15102,28 @@
     </row>
     <row r="170" customHeight="1" spans="3:20">
       <c r="C170" s="1" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="E170" s="1">
         <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1064</v>
+        <v>1076</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
       <c r="H170" s="7" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
       <c r="I170" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="K170" s="1">
         <v>0</v>
@@ -15110,12 +15145,12 @@
         <v>10850</v>
       </c>
       <c r="P170" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>154</v>
       </c>
       <c r="Q170" s="2">
         <f t="shared" si="37"/>
-        <v>190</v>
+        <v>246</v>
       </c>
       <c r="R170" s="2">
         <v>99.99</v>
@@ -15129,28 +15164,28 @@
     </row>
     <row r="171" customHeight="1" spans="3:20">
       <c r="C171" s="1" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
       <c r="E171" s="1">
         <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1069</v>
+        <v>1081</v>
       </c>
       <c r="G171" s="7" t="s">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="H171" s="7" t="s">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="I171" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>1071</v>
+        <v>1083</v>
       </c>
       <c r="K171" s="1">
         <v>0</v>
@@ -15172,12 +15207,12 @@
         <v>11100</v>
       </c>
       <c r="P171" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>157</v>
       </c>
       <c r="Q171" s="2">
         <f t="shared" si="37"/>
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="R171" s="2">
         <v>99.99</v>
@@ -15191,28 +15226,28 @@
     </row>
     <row r="172" customHeight="1" spans="3:20">
       <c r="C172" s="1" t="s">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>1073</v>
+        <v>1085</v>
       </c>
       <c r="E172" s="1">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1074</v>
+        <v>1086</v>
       </c>
       <c r="G172" s="7" t="s">
-        <v>1075</v>
+        <v>1087</v>
       </c>
       <c r="H172" s="7" t="s">
-        <v>1075</v>
+        <v>1087</v>
       </c>
       <c r="I172" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>1076</v>
+        <v>1088</v>
       </c>
       <c r="K172" s="1">
         <v>0</v>
@@ -15234,12 +15269,12 @@
         <v>11350</v>
       </c>
       <c r="P172" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>160</v>
       </c>
       <c r="Q172" s="2">
         <f t="shared" si="37"/>
-        <v>198</v>
+        <v>254</v>
       </c>
       <c r="R172" s="2">
         <v>99.99</v>
@@ -15253,28 +15288,28 @@
     </row>
     <row r="173" customHeight="1" spans="3:20">
       <c r="C173" s="1" t="s">
-        <v>1077</v>
+        <v>1089</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>1078</v>
+        <v>1090</v>
       </c>
       <c r="E173" s="1">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1079</v>
+        <v>1091</v>
       </c>
       <c r="G173" s="7" t="s">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="I173" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>1081</v>
+        <v>1093</v>
       </c>
       <c r="K173" s="1">
         <v>0</v>
@@ -15296,12 +15331,12 @@
         <v>11600</v>
       </c>
       <c r="P173" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>163</v>
       </c>
       <c r="Q173" s="2">
         <f t="shared" si="37"/>
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="R173" s="2">
         <v>99.99</v>
@@ -15315,28 +15350,28 @@
     </row>
     <row r="174" customHeight="1" spans="3:20">
       <c r="C174" s="1" t="s">
-        <v>1082</v>
+        <v>1094</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>1083</v>
+        <v>1095</v>
       </c>
       <c r="E174" s="1">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1084</v>
+        <v>1096</v>
       </c>
       <c r="G174" s="7" t="s">
-        <v>1085</v>
+        <v>1097</v>
       </c>
       <c r="H174" s="7" t="s">
-        <v>1085</v>
+        <v>1097</v>
       </c>
       <c r="I174" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>1086</v>
+        <v>1098</v>
       </c>
       <c r="K174" s="1">
         <v>0</v>
@@ -15358,12 +15393,12 @@
         <v>11850</v>
       </c>
       <c r="P174" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>166</v>
       </c>
       <c r="Q174" s="2">
         <f t="shared" si="37"/>
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="R174" s="2">
         <v>99.99</v>
@@ -15377,28 +15412,28 @@
     </row>
     <row r="175" customHeight="1" spans="3:20">
       <c r="C175" s="1" t="s">
-        <v>1087</v>
+        <v>1099</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>1088</v>
+        <v>1100</v>
       </c>
       <c r="E175" s="1">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1089</v>
+        <v>1101</v>
       </c>
       <c r="G175" s="7" t="s">
-        <v>1090</v>
+        <v>1102</v>
       </c>
       <c r="H175" s="7" t="s">
-        <v>1090</v>
+        <v>1102</v>
       </c>
       <c r="I175" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1091</v>
+        <v>1103</v>
       </c>
       <c r="K175" s="1">
         <v>0</v>
@@ -15420,12 +15455,12 @@
         <v>12100</v>
       </c>
       <c r="P175" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>169</v>
       </c>
       <c r="Q175" s="2">
         <f t="shared" si="37"/>
-        <v>210</v>
+        <v>266</v>
       </c>
       <c r="R175" s="2">
         <v>99.99</v>
@@ -15441,28 +15476,28 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="1" t="s">
-        <v>1092</v>
+        <v>1104</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
       <c r="E176" s="1">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1094</v>
+        <v>1106</v>
       </c>
       <c r="G176" s="7" t="s">
-        <v>1095</v>
+        <v>1107</v>
       </c>
       <c r="H176" s="7" t="s">
-        <v>1095</v>
+        <v>1107</v>
       </c>
       <c r="I176" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>1096</v>
+        <v>1108</v>
       </c>
       <c r="K176" s="1">
         <v>0</v>
@@ -15484,12 +15519,12 @@
         <v>12350</v>
       </c>
       <c r="P176" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>172</v>
       </c>
       <c r="Q176" s="2">
         <f t="shared" si="37"/>
-        <v>214</v>
+        <v>270</v>
       </c>
       <c r="R176" s="2">
         <v>99.99</v>
@@ -15510,28 +15545,28 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="1" t="s">
-        <v>1097</v>
+        <v>1109</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>1098</v>
+        <v>1110</v>
       </c>
       <c r="E177" s="1">
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1099</v>
+        <v>1111</v>
       </c>
       <c r="G177" s="7" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
       <c r="H177" s="7" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
       <c r="I177" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="K177" s="1">
         <v>0</v>
@@ -15553,12 +15588,12 @@
         <v>12600</v>
       </c>
       <c r="P177" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>175</v>
       </c>
       <c r="Q177" s="2">
         <f t="shared" si="37"/>
-        <v>218</v>
+        <v>274</v>
       </c>
       <c r="R177" s="2">
         <v>99.99</v>
@@ -15579,28 +15614,28 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="1" t="s">
-        <v>1102</v>
+        <v>1114</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="E178" s="1">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1104</v>
+        <v>1116</v>
       </c>
       <c r="G178" s="7" t="s">
-        <v>1105</v>
+        <v>1117</v>
       </c>
       <c r="H178" s="7" t="s">
-        <v>1105</v>
+        <v>1117</v>
       </c>
       <c r="I178" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>1106</v>
+        <v>1118</v>
       </c>
       <c r="K178" s="1">
         <v>0</v>
@@ -15622,12 +15657,12 @@
         <v>12850</v>
       </c>
       <c r="P178" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>178</v>
       </c>
       <c r="Q178" s="2">
         <f t="shared" si="37"/>
-        <v>222</v>
+        <v>278</v>
       </c>
       <c r="R178" s="2">
         <v>99.99</v>
@@ -15648,28 +15683,28 @@
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="1" t="s">
-        <v>1107</v>
+        <v>1119</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1108</v>
+        <v>1120</v>
       </c>
       <c r="E179" s="1">
         <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>1110</v>
+        <v>1122</v>
       </c>
       <c r="H179" s="7" t="s">
-        <v>1110</v>
+        <v>1122</v>
       </c>
       <c r="I179" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1111</v>
+        <v>1123</v>
       </c>
       <c r="K179" s="1">
         <v>0</v>
@@ -15691,12 +15726,12 @@
         <v>13100</v>
       </c>
       <c r="P179" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>181</v>
       </c>
       <c r="Q179" s="2">
         <f t="shared" si="37"/>
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="R179" s="2">
         <v>99.99</v>
@@ -15717,28 +15752,28 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="1" t="s">
-        <v>1112</v>
+        <v>1124</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1113</v>
+        <v>1125</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="H180" s="7" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="I180" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>1116</v>
+        <v>1128</v>
       </c>
       <c r="K180" s="1">
         <v>0</v>
@@ -15760,12 +15795,12 @@
         <v>13350</v>
       </c>
       <c r="P180" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>184</v>
       </c>
       <c r="Q180" s="2">
         <f t="shared" si="37"/>
-        <v>230</v>
+        <v>286</v>
       </c>
       <c r="R180" s="2">
         <v>99.99</v>
@@ -15784,7 +15819,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3 K4 K5 C3:J5 L3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:R5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -13898,7 +13898,7 @@
         <v>968</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="H152" s="7" t="s">
         <v>969</v>
@@ -13968,7 +13968,7 @@
         <v>974</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>975</v>
+        <v>961</v>
       </c>
       <c r="H153" s="7" t="s">
         <v>975</v>
@@ -14038,7 +14038,7 @@
         <v>980</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>981</v>
+        <v>961</v>
       </c>
       <c r="H154" s="7" t="s">
         <v>981</v>
@@ -14108,7 +14108,7 @@
         <v>986</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>987</v>
+        <v>961</v>
       </c>
       <c r="H155" s="7" t="s">
         <v>987</v>
@@ -14178,7 +14178,7 @@
         <v>992</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>993</v>
+        <v>961</v>
       </c>
       <c r="H156" s="7" t="s">
         <v>993</v>
@@ -14247,7 +14247,7 @@
         <v>998</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>999</v>
+        <v>961</v>
       </c>
       <c r="H157" s="7" t="s">
         <v>999</v>
@@ -14316,7 +14316,7 @@
         <v>1004</v>
       </c>
       <c r="G158" s="7" t="s">
-        <v>1005</v>
+        <v>961</v>
       </c>
       <c r="H158" s="7" t="s">
         <v>1005</v>
@@ -14385,7 +14385,7 @@
         <v>1010</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>1011</v>
+        <v>961</v>
       </c>
       <c r="H159" s="7" t="s">
         <v>1011</v>
@@ -14454,7 +14454,7 @@
         <v>1016</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>1017</v>
+        <v>961</v>
       </c>
       <c r="H160" s="7" t="s">
         <v>1017</v>
@@ -14523,7 +14523,7 @@
         <v>1022</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>1023</v>
+        <v>961</v>
       </c>
       <c r="H161" s="7" t="s">
         <v>1023</v>
@@ -14592,7 +14592,7 @@
         <v>1028</v>
       </c>
       <c r="G162" s="7" t="s">
-        <v>1029</v>
+        <v>961</v>
       </c>
       <c r="H162" s="7" t="s">
         <v>1029</v>
@@ -14661,7 +14661,7 @@
         <v>1034</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>1035</v>
+        <v>961</v>
       </c>
       <c r="H163" s="7" t="s">
         <v>1035</v>
@@ -14730,7 +14730,7 @@
         <v>1040</v>
       </c>
       <c r="G164" s="7" t="s">
-        <v>1041</v>
+        <v>961</v>
       </c>
       <c r="H164" s="7" t="s">
         <v>1041</v>
@@ -14799,7 +14799,7 @@
         <v>1046</v>
       </c>
       <c r="G165" s="7" t="s">
-        <v>1047</v>
+        <v>961</v>
       </c>
       <c r="H165" s="7" t="s">
         <v>1047</v>
@@ -14866,7 +14866,7 @@
         <v>1052</v>
       </c>
       <c r="G166" s="7" t="s">
-        <v>1053</v>
+        <v>961</v>
       </c>
       <c r="H166" s="7" t="s">
         <v>1053</v>
@@ -14928,7 +14928,7 @@
         <v>1058</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>1059</v>
+        <v>961</v>
       </c>
       <c r="H167" s="7" t="s">
         <v>1059</v>
@@ -14990,7 +14990,7 @@
         <v>1064</v>
       </c>
       <c r="G168" s="7" t="s">
-        <v>1065</v>
+        <v>961</v>
       </c>
       <c r="H168" s="7" t="s">
         <v>1065</v>
@@ -15052,7 +15052,7 @@
         <v>1070</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>1071</v>
+        <v>961</v>
       </c>
       <c r="H169" s="7" t="s">
         <v>1071</v>
@@ -15114,7 +15114,7 @@
         <v>1076</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>1077</v>
+        <v>961</v>
       </c>
       <c r="H170" s="7" t="s">
         <v>1077</v>
@@ -15176,7 +15176,7 @@
         <v>1081</v>
       </c>
       <c r="G171" s="7" t="s">
-        <v>1082</v>
+        <v>961</v>
       </c>
       <c r="H171" s="7" t="s">
         <v>1082</v>
@@ -15238,7 +15238,7 @@
         <v>1086</v>
       </c>
       <c r="G172" s="7" t="s">
-        <v>1087</v>
+        <v>961</v>
       </c>
       <c r="H172" s="7" t="s">
         <v>1087</v>
@@ -15300,7 +15300,7 @@
         <v>1091</v>
       </c>
       <c r="G173" s="7" t="s">
-        <v>1092</v>
+        <v>961</v>
       </c>
       <c r="H173" s="7" t="s">
         <v>1092</v>
@@ -15362,7 +15362,7 @@
         <v>1096</v>
       </c>
       <c r="G174" s="7" t="s">
-        <v>1097</v>
+        <v>961</v>
       </c>
       <c r="H174" s="7" t="s">
         <v>1097</v>
@@ -15424,7 +15424,7 @@
         <v>1101</v>
       </c>
       <c r="G175" s="7" t="s">
-        <v>1102</v>
+        <v>961</v>
       </c>
       <c r="H175" s="7" t="s">
         <v>1102</v>
@@ -15488,7 +15488,7 @@
         <v>1106</v>
       </c>
       <c r="G176" s="7" t="s">
-        <v>1107</v>
+        <v>961</v>
       </c>
       <c r="H176" s="7" t="s">
         <v>1107</v>
@@ -15557,7 +15557,7 @@
         <v>1111</v>
       </c>
       <c r="G177" s="7" t="s">
-        <v>1112</v>
+        <v>961</v>
       </c>
       <c r="H177" s="7" t="s">
         <v>1112</v>
@@ -15626,7 +15626,7 @@
         <v>1116</v>
       </c>
       <c r="G178" s="7" t="s">
-        <v>1117</v>
+        <v>961</v>
       </c>
       <c r="H178" s="7" t="s">
         <v>1117</v>
@@ -15695,7 +15695,7 @@
         <v>1121</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>1122</v>
+        <v>961</v>
       </c>
       <c r="H179" s="7" t="s">
         <v>1122</v>
@@ -15764,7 +15764,7 @@
         <v>1126</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>1127</v>
+        <v>961</v>
       </c>
       <c r="H180" s="7" t="s">
         <v>1127</v>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="1128">
   <si>
     <t>ID</t>
   </si>
@@ -2774,10 +2774,10 @@
     <t>地狱冰龙</t>
   </si>
   <si>
-    <t>9000000000000000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>1600000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+    <t>90僧</t>
+  </si>
+  <si>
+    <t>160不</t>
   </si>
   <si>
     <t>30000000000</t>
@@ -2792,7 +2792,7 @@
     <t>深渊鸡</t>
   </si>
   <si>
-    <t>1000恒</t>
+    <t>1000极</t>
   </si>
   <si>
     <t>900僧</t>
@@ -2801,7 +2801,7 @@
     <t>3200不</t>
   </si>
   <si>
-    <t>1垓</t>
+    <t>1秭</t>
   </si>
   <si>
     <t>33000000000</t>
@@ -2816,7 +2816,7 @@
     <t>深渊鹿</t>
   </si>
   <si>
-    <t>4000恒</t>
+    <t>4000极</t>
   </si>
   <si>
     <t>9000僧</t>
@@ -2825,7 +2825,7 @@
     <t>64000不</t>
   </si>
   <si>
-    <t>5垓</t>
+    <t>10秭</t>
   </si>
   <si>
     <t>36000000000</t>
@@ -2840,7 +2840,7 @@
     <t>深渊草人</t>
   </si>
   <si>
-    <t>16000恒</t>
+    <t>16000极</t>
   </si>
   <si>
     <t>9祇</t>
@@ -2849,7 +2849,7 @@
     <t>128可</t>
   </si>
   <si>
-    <t>25垓</t>
+    <t>100秭</t>
   </si>
   <si>
     <t>39000000000</t>
@@ -2864,7 +2864,7 @@
     <t>深渊猫</t>
   </si>
   <si>
-    <t>64000恒</t>
+    <t>64000极</t>
   </si>
   <si>
     <t>90祇</t>
@@ -2873,7 +2873,7 @@
     <t>2560可</t>
   </si>
   <si>
-    <t>125垓</t>
+    <t>1000秭</t>
   </si>
   <si>
     <t>42000000000</t>
@@ -2897,7 +2897,7 @@
     <t>5思</t>
   </si>
   <si>
-    <t>625垓</t>
+    <t>1穰</t>
   </si>
   <si>
     <t>45000000000</t>
@@ -2921,7 +2921,7 @@
     <t>100思</t>
   </si>
   <si>
-    <t>2500垓</t>
+    <t>10穰</t>
   </si>
   <si>
     <t>48000000000</t>
@@ -3396,9 +3396,6 @@
   </si>
   <si>
     <t>9000议</t>
-  </si>
-  <si>
-    <t>1秭</t>
   </si>
   <si>
     <t>10175</t>
@@ -4640,7 +4637,7 @@
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
     </row>
-    <row r="6" ht="14" spans="3:20">
+    <row r="6" ht="14.25" spans="3:20">
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
@@ -13420,13 +13417,13 @@
       <c r="F145" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="G145" s="14" t="s">
+      <c r="G145" s="7" t="s">
         <v>915</v>
       </c>
-      <c r="H145" s="10" t="s">
+      <c r="H145" s="7" t="s">
         <v>915</v>
       </c>
-      <c r="I145" s="15" t="s">
+      <c r="I145" s="9" t="s">
         <v>916</v>
       </c>
       <c r="J145" s="1">
@@ -15704,7 +15701,7 @@
         <v>1072</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1123</v>
+        <v>924</v>
       </c>
       <c r="K179" s="1">
         <v>0</v>
@@ -15752,28 +15749,28 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>1124</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>1125</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G180" s="7" t="s">
         <v>961</v>
       </c>
       <c r="H180" s="7" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="I180" s="9" t="s">
         <v>1072</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="K180" s="1">
         <v>0</v>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -2822,7 +2822,7 @@
     <t>9000僧</t>
   </si>
   <si>
-    <t>64不</t>
+    <t>64可</t>
   </si>
   <si>
     <t>100秭</t>
@@ -4417,7 +4417,7 @@
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
     </row>
-    <row r="6" ht="14" spans="3:20">
+    <row r="6" ht="14.25" spans="3:20">
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="1053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="1078">
   <si>
     <t>ID</t>
   </si>
@@ -2912,6 +2912,21 @@
     <t>深渊雪人</t>
   </si>
   <si>
+    <t>96恒</t>
+  </si>
+  <si>
+    <t>9000祇</t>
+  </si>
+  <si>
+    <t>1000思</t>
+  </si>
+  <si>
+    <t>3万</t>
+  </si>
+  <si>
+    <t>100穰</t>
+  </si>
+  <si>
     <t>48000000000</t>
   </si>
   <si>
@@ -2924,6 +2939,21 @@
     <t>深渊蝙蝠</t>
   </si>
   <si>
+    <t>400恒</t>
+  </si>
+  <si>
+    <t>9那</t>
+  </si>
+  <si>
+    <t>2议</t>
+  </si>
+  <si>
+    <t>15万</t>
+  </si>
+  <si>
+    <t>1000穰</t>
+  </si>
+  <si>
     <t>51000000000</t>
   </si>
   <si>
@@ -2936,6 +2966,21 @@
     <t>深渊骷髅</t>
   </si>
   <si>
+    <t>1600恒</t>
+  </si>
+  <si>
+    <t>90那</t>
+  </si>
+  <si>
+    <t>40议</t>
+  </si>
+  <si>
+    <t>75万</t>
+  </si>
+  <si>
+    <t>10000穰</t>
+  </si>
+  <si>
     <t>54000000000</t>
   </si>
   <si>
@@ -2948,6 +2993,21 @@
     <t>深渊僵尸</t>
   </si>
   <si>
+    <t>6400恒</t>
+  </si>
+  <si>
+    <t>900那</t>
+  </si>
+  <si>
+    <t>800议</t>
+  </si>
+  <si>
+    <t>375万</t>
+  </si>
+  <si>
+    <t>10沟</t>
+  </si>
+  <si>
     <t>57000000000</t>
   </si>
   <si>
@@ -2958,6 +3018,21 @@
   </si>
   <si>
     <t>深渊毒蛇</t>
+  </si>
+  <si>
+    <t>3河</t>
+  </si>
+  <si>
+    <t>9000那</t>
+  </si>
+  <si>
+    <t>16000议</t>
+  </si>
+  <si>
+    <t>2000万</t>
+  </si>
+  <si>
+    <t>100沟</t>
   </si>
   <si>
     <t>60000000000</t>
@@ -13604,20 +13679,20 @@
       <c r="F151" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="G151" s="1">
-        <v>0</v>
-      </c>
-      <c r="H151" s="1">
-        <v>0</v>
-      </c>
-      <c r="I151" s="1">
-        <v>0</v>
-      </c>
-      <c r="J151" s="1">
-        <v>0</v>
-      </c>
-      <c r="K151" s="1">
-        <v>0</v>
+      <c r="G151" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="H151" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>965</v>
       </c>
       <c r="L151" s="1">
         <f t="shared" si="42"/>
@@ -13647,10 +13722,10 @@
         <v>99.99</v>
       </c>
       <c r="S151" s="14" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="T151" s="14" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="U151" s="3"/>
       <c r="V151" s="3"/>
@@ -13662,31 +13737,31 @@
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="1" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="E152" s="1">
         <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="G152" s="1">
-        <v>0</v>
-      </c>
-      <c r="H152" s="1">
-        <v>0</v>
-      </c>
-      <c r="I152" s="1">
-        <v>0</v>
-      </c>
-      <c r="J152" s="1">
-        <v>0</v>
-      </c>
-      <c r="K152" s="1">
-        <v>0</v>
+        <v>969</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="H152" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>974</v>
       </c>
       <c r="L152" s="1">
         <f t="shared" si="42"/>
@@ -13716,10 +13791,10 @@
         <v>99.99</v>
       </c>
       <c r="S152" s="14" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="T152" s="14" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="U152" s="3"/>
       <c r="V152" s="3"/>
@@ -13731,31 +13806,31 @@
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="1" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="E153" s="1">
         <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>968</v>
-      </c>
-      <c r="G153" s="1">
-        <v>0</v>
-      </c>
-      <c r="H153" s="1">
-        <v>0</v>
-      </c>
-      <c r="I153" s="1">
-        <v>0</v>
-      </c>
-      <c r="J153" s="1">
-        <v>0</v>
-      </c>
-      <c r="K153" s="1">
-        <v>0</v>
+        <v>978</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="H153" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>983</v>
       </c>
       <c r="L153" s="1">
         <f t="shared" si="42"/>
@@ -13785,10 +13860,10 @@
         <v>99.99</v>
       </c>
       <c r="S153" s="14" t="s">
-        <v>969</v>
+        <v>984</v>
       </c>
       <c r="T153" s="14" t="s">
-        <v>969</v>
+        <v>984</v>
       </c>
       <c r="U153" s="3"/>
       <c r="V153" s="3"/>
@@ -13800,31 +13875,31 @@
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="1" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="E154" s="1">
         <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>972</v>
-      </c>
-      <c r="G154" s="1">
-        <v>0</v>
-      </c>
-      <c r="H154" s="1">
-        <v>0</v>
-      </c>
-      <c r="I154" s="1">
-        <v>0</v>
-      </c>
-      <c r="J154" s="1">
-        <v>0</v>
-      </c>
-      <c r="K154" s="1">
-        <v>0</v>
+        <v>987</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="H154" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>992</v>
       </c>
       <c r="L154" s="1">
         <f t="shared" si="42"/>
@@ -13854,10 +13929,10 @@
         <v>99.99</v>
       </c>
       <c r="S154" s="14" t="s">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="T154" s="14" t="s">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="U154" s="3"/>
       <c r="V154" s="3"/>
@@ -13869,31 +13944,31 @@
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="1" t="s">
-        <v>974</v>
+        <v>994</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>975</v>
+        <v>995</v>
       </c>
       <c r="E155" s="1">
         <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>976</v>
-      </c>
-      <c r="G155" s="1">
-        <v>0</v>
-      </c>
-      <c r="H155" s="1">
-        <v>0</v>
-      </c>
-      <c r="I155" s="1">
-        <v>0</v>
-      </c>
-      <c r="J155" s="1">
-        <v>0</v>
-      </c>
-      <c r="K155" s="1">
-        <v>0</v>
+        <v>996</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="H155" s="8" t="s">
+        <v>998</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>1001</v>
       </c>
       <c r="L155" s="1">
         <f t="shared" si="42"/>
@@ -13923,10 +13998,10 @@
         <v>99.99</v>
       </c>
       <c r="S155" s="14" t="s">
-        <v>977</v>
+        <v>1002</v>
       </c>
       <c r="T155" s="14" t="s">
-        <v>977</v>
+        <v>1002</v>
       </c>
       <c r="U155" s="3"/>
       <c r="V155" s="3"/>
@@ -13938,16 +14013,16 @@
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="1" t="s">
-        <v>978</v>
+        <v>1003</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>979</v>
+        <v>1004</v>
       </c>
       <c r="E156" s="1">
         <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>980</v>
+        <v>1005</v>
       </c>
       <c r="G156" s="1">
         <v>0</v>
@@ -14007,16 +14082,16 @@
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="1" t="s">
-        <v>981</v>
+        <v>1006</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>982</v>
+        <v>1007</v>
       </c>
       <c r="E157" s="1">
         <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>983</v>
+        <v>1008</v>
       </c>
       <c r="G157" s="1">
         <v>0</v>
@@ -14076,16 +14151,16 @@
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="1" t="s">
-        <v>984</v>
+        <v>1009</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>985</v>
+        <v>1010</v>
       </c>
       <c r="E158" s="1">
         <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>986</v>
+        <v>1011</v>
       </c>
       <c r="G158" s="1">
         <v>0</v>
@@ -14145,16 +14220,16 @@
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="1" t="s">
-        <v>987</v>
+        <v>1012</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>988</v>
+        <v>1013</v>
       </c>
       <c r="E159" s="1">
         <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>989</v>
+        <v>1014</v>
       </c>
       <c r="G159" s="1">
         <v>0</v>
@@ -14214,16 +14289,16 @@
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="1" t="s">
-        <v>990</v>
+        <v>1015</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>991</v>
+        <v>1016</v>
       </c>
       <c r="E160" s="1">
         <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>992</v>
+        <v>1017</v>
       </c>
       <c r="G160" s="1">
         <v>0</v>
@@ -14283,16 +14358,16 @@
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="1" t="s">
-        <v>993</v>
+        <v>1018</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>994</v>
+        <v>1019</v>
       </c>
       <c r="E161" s="1">
         <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>995</v>
+        <v>1020</v>
       </c>
       <c r="G161" s="1">
         <v>0</v>
@@ -14352,16 +14427,16 @@
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="1" t="s">
-        <v>996</v>
+        <v>1021</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>997</v>
+        <v>1022</v>
       </c>
       <c r="E162" s="1">
         <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>998</v>
+        <v>1023</v>
       </c>
       <c r="G162" s="1">
         <v>0</v>
@@ -14421,16 +14496,16 @@
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="1" t="s">
-        <v>999</v>
+        <v>1024</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="E163" s="1">
         <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="G163" s="1">
         <v>0</v>
@@ -14490,16 +14565,16 @@
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="1" t="s">
-        <v>1002</v>
+        <v>1027</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>1003</v>
+        <v>1028</v>
       </c>
       <c r="E164" s="1">
         <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1004</v>
+        <v>1029</v>
       </c>
       <c r="G164" s="1">
         <v>0</v>
@@ -14559,16 +14634,16 @@
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="1" t="s">
-        <v>1005</v>
+        <v>1030</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>1006</v>
+        <v>1031</v>
       </c>
       <c r="E165" s="1">
         <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1007</v>
+        <v>1032</v>
       </c>
       <c r="G165" s="1">
         <v>0</v>
@@ -14626,16 +14701,16 @@
     </row>
     <row r="166" customHeight="1" spans="3:20">
       <c r="C166" s="1" t="s">
-        <v>1008</v>
+        <v>1033</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>1009</v>
+        <v>1034</v>
       </c>
       <c r="E166" s="1">
         <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1010</v>
+        <v>1035</v>
       </c>
       <c r="G166" s="1">
         <v>0</v>
@@ -14688,16 +14763,16 @@
     </row>
     <row r="167" customHeight="1" spans="3:20">
       <c r="C167" s="1" t="s">
-        <v>1011</v>
+        <v>1036</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>1012</v>
+        <v>1037</v>
       </c>
       <c r="E167" s="1">
         <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1013</v>
+        <v>1038</v>
       </c>
       <c r="G167" s="1">
         <v>0</v>
@@ -14750,16 +14825,16 @@
     </row>
     <row r="168" customHeight="1" spans="3:20">
       <c r="C168" s="1" t="s">
-        <v>1014</v>
+        <v>1039</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>1015</v>
+        <v>1040</v>
       </c>
       <c r="E168" s="1">
         <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1016</v>
+        <v>1041</v>
       </c>
       <c r="G168" s="1">
         <v>0</v>
@@ -14812,16 +14887,16 @@
     </row>
     <row r="169" customHeight="1" spans="3:20">
       <c r="C169" s="1" t="s">
-        <v>1017</v>
+        <v>1042</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>1018</v>
+        <v>1043</v>
       </c>
       <c r="E169" s="1">
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1019</v>
+        <v>1044</v>
       </c>
       <c r="G169" s="1">
         <v>0</v>
@@ -14874,16 +14949,16 @@
     </row>
     <row r="170" customHeight="1" spans="3:20">
       <c r="C170" s="1" t="s">
-        <v>1020</v>
+        <v>1045</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>1021</v>
+        <v>1046</v>
       </c>
       <c r="E170" s="1">
         <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1022</v>
+        <v>1047</v>
       </c>
       <c r="G170" s="1">
         <v>0</v>
@@ -14936,16 +15011,16 @@
     </row>
     <row r="171" customHeight="1" spans="3:20">
       <c r="C171" s="1" t="s">
-        <v>1023</v>
+        <v>1048</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>1024</v>
+        <v>1049</v>
       </c>
       <c r="E171" s="1">
         <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G171" s="1">
         <v>0</v>
@@ -14998,16 +15073,16 @@
     </row>
     <row r="172" customHeight="1" spans="3:20">
       <c r="C172" s="1" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>1027</v>
+        <v>1052</v>
       </c>
       <c r="E172" s="1">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1028</v>
+        <v>1053</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
@@ -15060,16 +15135,16 @@
     </row>
     <row r="173" customHeight="1" spans="3:20">
       <c r="C173" s="1" t="s">
-        <v>1029</v>
+        <v>1054</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="E173" s="1">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -15122,16 +15197,16 @@
     </row>
     <row r="174" customHeight="1" spans="3:20">
       <c r="C174" s="1" t="s">
-        <v>1032</v>
+        <v>1057</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>1033</v>
+        <v>1058</v>
       </c>
       <c r="E174" s="1">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
@@ -15184,16 +15259,16 @@
     </row>
     <row r="175" customHeight="1" spans="3:20">
       <c r="C175" s="1" t="s">
-        <v>1035</v>
+        <v>1060</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>1036</v>
+        <v>1061</v>
       </c>
       <c r="E175" s="1">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1037</v>
+        <v>1062</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
@@ -15248,16 +15323,16 @@
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="1" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>1039</v>
+        <v>1064</v>
       </c>
       <c r="E176" s="1">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1040</v>
+        <v>1065</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -15317,16 +15392,16 @@
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="1" t="s">
-        <v>1041</v>
+        <v>1066</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>1042</v>
+        <v>1067</v>
       </c>
       <c r="E177" s="1">
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1043</v>
+        <v>1068</v>
       </c>
       <c r="G177" s="1">
         <v>0</v>
@@ -15386,16 +15461,16 @@
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="1" t="s">
-        <v>1044</v>
+        <v>1069</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1045</v>
+        <v>1070</v>
       </c>
       <c r="E178" s="1">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1046</v>
+        <v>1071</v>
       </c>
       <c r="G178" s="1">
         <v>0</v>
@@ -15455,16 +15530,16 @@
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="1" t="s">
-        <v>1047</v>
+        <v>1072</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1048</v>
+        <v>1073</v>
       </c>
       <c r="E179" s="1">
         <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1049</v>
+        <v>1074</v>
       </c>
       <c r="G179" s="1">
         <v>0</v>
@@ -15524,16 +15599,16 @@
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="1" t="s">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1052</v>
+        <v>1077</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="1078">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="1108">
   <si>
     <t>ID</t>
   </si>
@@ -3047,6 +3047,24 @@
     <t>深渊野狼</t>
   </si>
   <si>
+    <t>15河</t>
+  </si>
+  <si>
+    <t>9由</t>
+  </si>
+  <si>
+    <t>32无</t>
+  </si>
+  <si>
+    <t>2亿</t>
+  </si>
+  <si>
+    <t>1000沟</t>
+  </si>
+  <si>
+    <t>63000000000</t>
+  </si>
+  <si>
     <t>10152</t>
   </si>
   <si>
@@ -3056,6 +3074,24 @@
     <t>深渊沙虫</t>
   </si>
   <si>
+    <t>75河</t>
+  </si>
+  <si>
+    <t>90由</t>
+  </si>
+  <si>
+    <t>640无</t>
+  </si>
+  <si>
+    <t>20亿</t>
+  </si>
+  <si>
+    <t>1涧</t>
+  </si>
+  <si>
+    <t>66000000000</t>
+  </si>
+  <si>
     <t>10153</t>
   </si>
   <si>
@@ -3065,6 +3101,24 @@
     <t>深渊小鹰</t>
   </si>
   <si>
+    <t>375河</t>
+  </si>
+  <si>
+    <t>900由</t>
+  </si>
+  <si>
+    <t>12800无</t>
+  </si>
+  <si>
+    <t>200亿</t>
+  </si>
+  <si>
+    <t>10涧</t>
+  </si>
+  <si>
+    <t>69000000000</t>
+  </si>
+  <si>
     <t>10154</t>
   </si>
   <si>
@@ -3074,6 +3128,24 @@
     <t>深渊角虫</t>
   </si>
   <si>
+    <t>2000河</t>
+  </si>
+  <si>
+    <t>9000由</t>
+  </si>
+  <si>
+    <t>25量</t>
+  </si>
+  <si>
+    <t>2000亿</t>
+  </si>
+  <si>
+    <t>100涧</t>
+  </si>
+  <si>
+    <t>72000000000</t>
+  </si>
+  <si>
     <t>10155</t>
   </si>
   <si>
@@ -3081,6 +3153,24 @@
   </si>
   <si>
     <t>深渊蜈蚣</t>
+  </si>
+  <si>
+    <t>1沙</t>
+  </si>
+  <si>
+    <t>9他</t>
+  </si>
+  <si>
+    <t>125量</t>
+  </si>
+  <si>
+    <t>2兆</t>
+  </si>
+  <si>
+    <t>1000涧</t>
+  </si>
+  <si>
+    <t>75000000000</t>
   </si>
   <si>
     <t>10156</t>
@@ -14024,20 +14114,20 @@
       <c r="F156" s="1" t="s">
         <v>1005</v>
       </c>
-      <c r="G156" s="1">
-        <v>0</v>
-      </c>
-      <c r="H156" s="1">
-        <v>0</v>
-      </c>
-      <c r="I156" s="1">
-        <v>0</v>
-      </c>
-      <c r="J156" s="1">
-        <v>0</v>
-      </c>
-      <c r="K156" s="1">
-        <v>0</v>
+      <c r="G156" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H156" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K156" s="1" t="s">
+        <v>1010</v>
       </c>
       <c r="L156" s="1">
         <f t="shared" si="42"/>
@@ -14067,10 +14157,10 @@
         <v>99.99</v>
       </c>
       <c r="S156" s="14" t="s">
-        <v>773</v>
+        <v>1011</v>
       </c>
       <c r="T156" s="14" t="s">
-        <v>773</v>
+        <v>1011</v>
       </c>
       <c r="U156" s="3"/>
       <c r="V156" s="3"/>
@@ -14082,31 +14172,31 @@
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="1" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="E157" s="1">
         <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G157" s="1">
-        <v>0</v>
-      </c>
-      <c r="H157" s="1">
-        <v>0</v>
-      </c>
-      <c r="I157" s="1">
-        <v>0</v>
-      </c>
-      <c r="J157" s="1">
-        <v>0</v>
-      </c>
-      <c r="K157" s="1">
-        <v>0</v>
+        <v>1014</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H157" s="8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="K157" s="1" t="s">
+        <v>1019</v>
       </c>
       <c r="L157" s="1">
         <f t="shared" si="42"/>
@@ -14136,10 +14226,10 @@
         <v>99.99</v>
       </c>
       <c r="S157" s="14" t="s">
-        <v>779</v>
+        <v>1020</v>
       </c>
       <c r="T157" s="14" t="s">
-        <v>779</v>
+        <v>1020</v>
       </c>
       <c r="U157" s="3"/>
       <c r="V157" s="3"/>
@@ -14151,31 +14241,31 @@
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="1" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="E158" s="1">
         <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G158" s="1">
-        <v>0</v>
-      </c>
-      <c r="H158" s="1">
-        <v>0</v>
-      </c>
-      <c r="I158" s="1">
-        <v>0</v>
-      </c>
-      <c r="J158" s="1">
-        <v>0</v>
-      </c>
-      <c r="K158" s="1">
-        <v>0</v>
+        <v>1023</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H158" s="8" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>1028</v>
       </c>
       <c r="L158" s="1">
         <f t="shared" si="42"/>
@@ -14205,10 +14295,10 @@
         <v>99.99</v>
       </c>
       <c r="S158" s="14" t="s">
-        <v>785</v>
+        <v>1029</v>
       </c>
       <c r="T158" s="14" t="s">
-        <v>785</v>
+        <v>1029</v>
       </c>
       <c r="U158" s="3"/>
       <c r="V158" s="3"/>
@@ -14220,31 +14310,31 @@
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="1" t="s">
-        <v>1012</v>
+        <v>1030</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>1013</v>
+        <v>1031</v>
       </c>
       <c r="E159" s="1">
         <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="G159" s="1">
-        <v>0</v>
-      </c>
-      <c r="H159" s="1">
-        <v>0</v>
-      </c>
-      <c r="I159" s="1">
-        <v>0</v>
-      </c>
-      <c r="J159" s="1">
-        <v>0</v>
-      </c>
-      <c r="K159" s="1">
-        <v>0</v>
+        <v>1032</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H159" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>1037</v>
       </c>
       <c r="L159" s="1">
         <f t="shared" si="42"/>
@@ -14274,10 +14364,10 @@
         <v>99.99</v>
       </c>
       <c r="S159" s="14" t="s">
-        <v>791</v>
+        <v>1038</v>
       </c>
       <c r="T159" s="14" t="s">
-        <v>791</v>
+        <v>1038</v>
       </c>
       <c r="U159" s="3"/>
       <c r="V159" s="3"/>
@@ -14289,31 +14379,31 @@
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="1" t="s">
-        <v>1015</v>
+        <v>1039</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>1016</v>
+        <v>1040</v>
       </c>
       <c r="E160" s="1">
         <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G160" s="1">
-        <v>0</v>
-      </c>
-      <c r="H160" s="1">
-        <v>0</v>
-      </c>
-      <c r="I160" s="1">
-        <v>0</v>
-      </c>
-      <c r="J160" s="1">
-        <v>0</v>
-      </c>
-      <c r="K160" s="1">
-        <v>0</v>
+        <v>1041</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H160" s="8" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>1046</v>
       </c>
       <c r="L160" s="1">
         <f t="shared" si="42"/>
@@ -14343,10 +14433,10 @@
         <v>99.99</v>
       </c>
       <c r="S160" s="14" t="s">
-        <v>797</v>
+        <v>1047</v>
       </c>
       <c r="T160" s="14" t="s">
-        <v>797</v>
+        <v>1047</v>
       </c>
       <c r="U160" s="3"/>
       <c r="V160" s="3"/>
@@ -14358,16 +14448,16 @@
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="1" t="s">
-        <v>1018</v>
+        <v>1048</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>1019</v>
+        <v>1049</v>
       </c>
       <c r="E161" s="1">
         <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1020</v>
+        <v>1050</v>
       </c>
       <c r="G161" s="1">
         <v>0</v>
@@ -14427,16 +14517,16 @@
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="1" t="s">
-        <v>1021</v>
+        <v>1051</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>1022</v>
+        <v>1052</v>
       </c>
       <c r="E162" s="1">
         <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1023</v>
+        <v>1053</v>
       </c>
       <c r="G162" s="1">
         <v>0</v>
@@ -14496,16 +14586,16 @@
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="1" t="s">
-        <v>1024</v>
+        <v>1054</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>1025</v>
+        <v>1055</v>
       </c>
       <c r="E163" s="1">
         <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1026</v>
+        <v>1056</v>
       </c>
       <c r="G163" s="1">
         <v>0</v>
@@ -14565,16 +14655,16 @@
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="1" t="s">
-        <v>1027</v>
+        <v>1057</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>1028</v>
+        <v>1058</v>
       </c>
       <c r="E164" s="1">
         <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1029</v>
+        <v>1059</v>
       </c>
       <c r="G164" s="1">
         <v>0</v>
@@ -14634,16 +14724,16 @@
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="1" t="s">
-        <v>1030</v>
+        <v>1060</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>1031</v>
+        <v>1061</v>
       </c>
       <c r="E165" s="1">
         <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1032</v>
+        <v>1062</v>
       </c>
       <c r="G165" s="1">
         <v>0</v>
@@ -14701,16 +14791,16 @@
     </row>
     <row r="166" customHeight="1" spans="3:20">
       <c r="C166" s="1" t="s">
-        <v>1033</v>
+        <v>1063</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>1034</v>
+        <v>1064</v>
       </c>
       <c r="E166" s="1">
         <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1035</v>
+        <v>1065</v>
       </c>
       <c r="G166" s="1">
         <v>0</v>
@@ -14763,16 +14853,16 @@
     </row>
     <row r="167" customHeight="1" spans="3:20">
       <c r="C167" s="1" t="s">
-        <v>1036</v>
+        <v>1066</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>1037</v>
+        <v>1067</v>
       </c>
       <c r="E167" s="1">
         <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1038</v>
+        <v>1068</v>
       </c>
       <c r="G167" s="1">
         <v>0</v>
@@ -14825,16 +14915,16 @@
     </row>
     <row r="168" customHeight="1" spans="3:20">
       <c r="C168" s="1" t="s">
-        <v>1039</v>
+        <v>1069</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>1040</v>
+        <v>1070</v>
       </c>
       <c r="E168" s="1">
         <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1041</v>
+        <v>1071</v>
       </c>
       <c r="G168" s="1">
         <v>0</v>
@@ -14887,16 +14977,16 @@
     </row>
     <row r="169" customHeight="1" spans="3:20">
       <c r="C169" s="1" t="s">
-        <v>1042</v>
+        <v>1072</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>1043</v>
+        <v>1073</v>
       </c>
       <c r="E169" s="1">
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1044</v>
+        <v>1074</v>
       </c>
       <c r="G169" s="1">
         <v>0</v>
@@ -14949,16 +15039,16 @@
     </row>
     <row r="170" customHeight="1" spans="3:20">
       <c r="C170" s="1" t="s">
-        <v>1045</v>
+        <v>1075</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>1046</v>
+        <v>1076</v>
       </c>
       <c r="E170" s="1">
         <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1047</v>
+        <v>1077</v>
       </c>
       <c r="G170" s="1">
         <v>0</v>
@@ -15011,16 +15101,16 @@
     </row>
     <row r="171" customHeight="1" spans="3:20">
       <c r="C171" s="1" t="s">
-        <v>1048</v>
+        <v>1078</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>1049</v>
+        <v>1079</v>
       </c>
       <c r="E171" s="1">
         <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1050</v>
+        <v>1080</v>
       </c>
       <c r="G171" s="1">
         <v>0</v>
@@ -15073,16 +15163,16 @@
     </row>
     <row r="172" customHeight="1" spans="3:20">
       <c r="C172" s="1" t="s">
-        <v>1051</v>
+        <v>1081</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>1052</v>
+        <v>1082</v>
       </c>
       <c r="E172" s="1">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1053</v>
+        <v>1083</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
@@ -15135,16 +15225,16 @@
     </row>
     <row r="173" customHeight="1" spans="3:20">
       <c r="C173" s="1" t="s">
-        <v>1054</v>
+        <v>1084</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>1055</v>
+        <v>1085</v>
       </c>
       <c r="E173" s="1">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1056</v>
+        <v>1086</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -15197,16 +15287,16 @@
     </row>
     <row r="174" customHeight="1" spans="3:20">
       <c r="C174" s="1" t="s">
-        <v>1057</v>
+        <v>1087</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>1058</v>
+        <v>1088</v>
       </c>
       <c r="E174" s="1">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1059</v>
+        <v>1089</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
@@ -15259,16 +15349,16 @@
     </row>
     <row r="175" customHeight="1" spans="3:20">
       <c r="C175" s="1" t="s">
-        <v>1060</v>
+        <v>1090</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>1061</v>
+        <v>1091</v>
       </c>
       <c r="E175" s="1">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1062</v>
+        <v>1092</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
@@ -15323,16 +15413,16 @@
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="1" t="s">
-        <v>1063</v>
+        <v>1093</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>1064</v>
+        <v>1094</v>
       </c>
       <c r="E176" s="1">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1065</v>
+        <v>1095</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -15392,16 +15482,16 @@
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="1" t="s">
-        <v>1066</v>
+        <v>1096</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>1067</v>
+        <v>1097</v>
       </c>
       <c r="E177" s="1">
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1068</v>
+        <v>1098</v>
       </c>
       <c r="G177" s="1">
         <v>0</v>
@@ -15461,16 +15551,16 @@
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="1" t="s">
-        <v>1069</v>
+        <v>1099</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1070</v>
+        <v>1100</v>
       </c>
       <c r="E178" s="1">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1071</v>
+        <v>1101</v>
       </c>
       <c r="G178" s="1">
         <v>0</v>
@@ -15530,16 +15620,16 @@
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="1" t="s">
-        <v>1072</v>
+        <v>1102</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1073</v>
+        <v>1103</v>
       </c>
       <c r="E179" s="1">
         <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1074</v>
+        <v>1104</v>
       </c>
       <c r="G179" s="1">
         <v>0</v>
@@ -15599,16 +15689,16 @@
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="1" t="s">
-        <v>1075</v>
+        <v>1105</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1076</v>
+        <v>1106</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1077</v>
+        <v>1107</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="1123">
   <si>
     <t>ID</t>
   </si>
@@ -3047,7 +3047,7 @@
     <t>深渊野狼</t>
   </si>
   <si>
-    <t>15河</t>
+    <t>90河</t>
   </si>
   <si>
     <t>9由</t>
@@ -3056,10 +3056,10 @@
     <t>32无</t>
   </si>
   <si>
-    <t>2亿</t>
-  </si>
-  <si>
-    <t>1000沟</t>
+    <t>4亿</t>
+  </si>
+  <si>
+    <t>2000沟</t>
   </si>
   <si>
     <t>63000000000</t>
@@ -3074,7 +3074,7 @@
     <t>深渊沙虫</t>
   </si>
   <si>
-    <t>75河</t>
+    <t>900河</t>
   </si>
   <si>
     <t>90由</t>
@@ -3083,10 +3083,10 @@
     <t>640无</t>
   </si>
   <si>
-    <t>20亿</t>
-  </si>
-  <si>
-    <t>1涧</t>
+    <t>80亿</t>
+  </si>
+  <si>
+    <t>4涧</t>
   </si>
   <si>
     <t>66000000000</t>
@@ -3101,7 +3101,7 @@
     <t>深渊小鹰</t>
   </si>
   <si>
-    <t>375河</t>
+    <t>9000河</t>
   </si>
   <si>
     <t>900由</t>
@@ -3110,10 +3110,10 @@
     <t>12800无</t>
   </si>
   <si>
-    <t>200亿</t>
-  </si>
-  <si>
-    <t>10涧</t>
+    <t>1600亿</t>
+  </si>
+  <si>
+    <t>80涧</t>
   </si>
   <si>
     <t>69000000000</t>
@@ -3128,7 +3128,7 @@
     <t>深渊角虫</t>
   </si>
   <si>
-    <t>2000河</t>
+    <t>9沙</t>
   </si>
   <si>
     <t>9000由</t>
@@ -3137,10 +3137,10 @@
     <t>25量</t>
   </si>
   <si>
-    <t>2000亿</t>
-  </si>
-  <si>
-    <t>100涧</t>
+    <t>32兆</t>
+  </si>
+  <si>
+    <t>1600涧</t>
   </si>
   <si>
     <t>72000000000</t>
@@ -3155,7 +3155,7 @@
     <t>深渊蜈蚣</t>
   </si>
   <si>
-    <t>1沙</t>
+    <t>90沙</t>
   </si>
   <si>
     <t>9他</t>
@@ -3164,10 +3164,10 @@
     <t>125量</t>
   </si>
   <si>
-    <t>2兆</t>
-  </si>
-  <si>
-    <t>1000涧</t>
+    <t>640兆</t>
+  </si>
+  <si>
+    <t>32正</t>
   </si>
   <si>
     <t>75000000000</t>
@@ -3182,6 +3182,15 @@
     <t>深渊钳虫</t>
   </si>
   <si>
+    <t>900沙</t>
+  </si>
+  <si>
+    <t>90他</t>
+  </si>
+  <si>
+    <t>5000量</t>
+  </si>
+  <si>
     <t>10157</t>
   </si>
   <si>
@@ -3191,6 +3200,15 @@
     <t>深渊蠕虫</t>
   </si>
   <si>
+    <t>9000沙</t>
+  </si>
+  <si>
+    <t>900他</t>
+  </si>
+  <si>
+    <t>10大</t>
+  </si>
+  <si>
     <t>10158</t>
   </si>
   <si>
@@ -3200,6 +3218,15 @@
     <t>深渊黑猪</t>
   </si>
   <si>
+    <t>9阿</t>
+  </si>
+  <si>
+    <t>9000他</t>
+  </si>
+  <si>
+    <t>200大</t>
+  </si>
+  <si>
     <t>10159</t>
   </si>
   <si>
@@ -3209,6 +3236,15 @@
     <t>深渊红猪</t>
   </si>
   <si>
+    <t>90阿</t>
+  </si>
+  <si>
+    <t>9不</t>
+  </si>
+  <si>
+    <t>4000大</t>
+  </si>
+  <si>
     <t>10160</t>
   </si>
   <si>
@@ -3216,6 +3252,32 @@
   </si>
   <si>
     <t>深渊蝎蛇</t>
+  </si>
+  <si>
+    <t>900阿</t>
+  </si>
+  <si>
+    <t>90不</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
   </si>
   <si>
     <t>10161</t>
@@ -3364,7 +3426,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3528,6 +3590,12 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -14459,21 +14527,17 @@
       <c r="F161" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="G161" s="1">
-        <v>0</v>
-      </c>
-      <c r="H161" s="1">
-        <v>0</v>
-      </c>
-      <c r="I161" s="1">
-        <v>0</v>
-      </c>
-      <c r="J161" s="1">
-        <v>0</v>
-      </c>
-      <c r="K161" s="1">
-        <v>0</v>
-      </c>
+      <c r="G161" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H161" s="8" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
       <c r="L161" s="1">
         <f t="shared" si="42"/>
         <v>21400</v>
@@ -14517,32 +14581,28 @@
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="1" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="E162" s="1">
         <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1053</v>
-      </c>
-      <c r="G162" s="1">
-        <v>0</v>
-      </c>
-      <c r="H162" s="1">
-        <v>0</v>
-      </c>
-      <c r="I162" s="1">
-        <v>0</v>
-      </c>
-      <c r="J162" s="1">
-        <v>0</v>
-      </c>
-      <c r="K162" s="1">
-        <v>0</v>
-      </c>
+        <v>1056</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H162" s="8" t="s">
+        <v>1058</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="J162" s="1"/>
+      <c r="K162" s="1"/>
       <c r="L162" s="1">
         <f t="shared" si="42"/>
         <v>22000</v>
@@ -14586,32 +14646,28 @@
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="1" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="E163" s="1">
         <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1056</v>
-      </c>
-      <c r="G163" s="1">
-        <v>0</v>
-      </c>
-      <c r="H163" s="1">
-        <v>0</v>
-      </c>
-      <c r="I163" s="1">
-        <v>0</v>
-      </c>
-      <c r="J163" s="1">
-        <v>0</v>
-      </c>
-      <c r="K163" s="1">
-        <v>0</v>
-      </c>
+        <v>1062</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H163" s="8" t="s">
+        <v>1064</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="J163" s="1"/>
+      <c r="K163" s="1"/>
       <c r="L163" s="1">
         <f t="shared" si="42"/>
         <v>22600</v>
@@ -14655,32 +14711,28 @@
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="1" t="s">
-        <v>1057</v>
+        <v>1066</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>1058</v>
+        <v>1067</v>
       </c>
       <c r="E164" s="1">
         <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="G164" s="1">
-        <v>0</v>
-      </c>
-      <c r="H164" s="1">
-        <v>0</v>
-      </c>
-      <c r="I164" s="1">
-        <v>0</v>
-      </c>
-      <c r="J164" s="1">
-        <v>0</v>
-      </c>
-      <c r="K164" s="1">
-        <v>0</v>
-      </c>
+        <v>1068</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J164" s="1"/>
+      <c r="K164" s="1"/>
       <c r="L164" s="1">
         <f t="shared" si="42"/>
         <v>23200</v>
@@ -14724,31 +14776,25 @@
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="1" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
       <c r="E165" s="1">
         <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="G165" s="1">
-        <v>0</v>
-      </c>
-      <c r="H165" s="1">
-        <v>0</v>
-      </c>
-      <c r="I165" s="1">
-        <v>0</v>
-      </c>
-      <c r="J165" s="1">
-        <v>0</v>
-      </c>
-      <c r="K165" s="1">
-        <v>0</v>
+        <v>1074</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>1077</v>
       </c>
       <c r="L165" s="1">
         <f t="shared" si="42"/>
@@ -14791,16 +14837,16 @@
     </row>
     <row r="166" customHeight="1" spans="3:20">
       <c r="C166" s="1" t="s">
-        <v>1063</v>
+        <v>1078</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>1064</v>
+        <v>1079</v>
       </c>
       <c r="E166" s="1">
         <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1065</v>
+        <v>1080</v>
       </c>
       <c r="G166" s="1">
         <v>0</v>
@@ -14853,16 +14899,16 @@
     </row>
     <row r="167" customHeight="1" spans="3:20">
       <c r="C167" s="1" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>1067</v>
+        <v>1082</v>
       </c>
       <c r="E167" s="1">
         <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1068</v>
+        <v>1083</v>
       </c>
       <c r="G167" s="1">
         <v>0</v>
@@ -14915,16 +14961,16 @@
     </row>
     <row r="168" customHeight="1" spans="3:20">
       <c r="C168" s="1" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>1070</v>
+        <v>1085</v>
       </c>
       <c r="E168" s="1">
         <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1071</v>
+        <v>1086</v>
       </c>
       <c r="G168" s="1">
         <v>0</v>
@@ -14977,16 +15023,16 @@
     </row>
     <row r="169" customHeight="1" spans="3:20">
       <c r="C169" s="1" t="s">
-        <v>1072</v>
+        <v>1087</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>1073</v>
+        <v>1088</v>
       </c>
       <c r="E169" s="1">
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1074</v>
+        <v>1089</v>
       </c>
       <c r="G169" s="1">
         <v>0</v>
@@ -15039,16 +15085,16 @@
     </row>
     <row r="170" customHeight="1" spans="3:20">
       <c r="C170" s="1" t="s">
-        <v>1075</v>
+        <v>1090</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>1076</v>
+        <v>1091</v>
       </c>
       <c r="E170" s="1">
         <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1077</v>
+        <v>1092</v>
       </c>
       <c r="G170" s="1">
         <v>0</v>
@@ -15101,16 +15147,16 @@
     </row>
     <row r="171" customHeight="1" spans="3:20">
       <c r="C171" s="1" t="s">
-        <v>1078</v>
+        <v>1093</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>1079</v>
+        <v>1094</v>
       </c>
       <c r="E171" s="1">
         <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="G171" s="1">
         <v>0</v>
@@ -15163,16 +15209,16 @@
     </row>
     <row r="172" customHeight="1" spans="3:20">
       <c r="C172" s="1" t="s">
-        <v>1081</v>
+        <v>1096</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>1082</v>
+        <v>1097</v>
       </c>
       <c r="E172" s="1">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1083</v>
+        <v>1098</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
@@ -15225,16 +15271,16 @@
     </row>
     <row r="173" customHeight="1" spans="3:20">
       <c r="C173" s="1" t="s">
-        <v>1084</v>
+        <v>1099</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>1085</v>
+        <v>1100</v>
       </c>
       <c r="E173" s="1">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1086</v>
+        <v>1101</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -15287,16 +15333,16 @@
     </row>
     <row r="174" customHeight="1" spans="3:20">
       <c r="C174" s="1" t="s">
-        <v>1087</v>
+        <v>1102</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>1088</v>
+        <v>1103</v>
       </c>
       <c r="E174" s="1">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1089</v>
+        <v>1104</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
@@ -15349,16 +15395,16 @@
     </row>
     <row r="175" customHeight="1" spans="3:20">
       <c r="C175" s="1" t="s">
-        <v>1090</v>
+        <v>1105</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="E175" s="1">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1092</v>
+        <v>1107</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
@@ -15413,16 +15459,16 @@
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="1" t="s">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>1094</v>
+        <v>1109</v>
       </c>
       <c r="E176" s="1">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1095</v>
+        <v>1110</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -15482,16 +15528,16 @@
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="1" t="s">
-        <v>1096</v>
+        <v>1111</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>1097</v>
+        <v>1112</v>
       </c>
       <c r="E177" s="1">
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1098</v>
+        <v>1113</v>
       </c>
       <c r="G177" s="1">
         <v>0</v>
@@ -15551,16 +15597,16 @@
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="1" t="s">
-        <v>1099</v>
+        <v>1114</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1100</v>
+        <v>1115</v>
       </c>
       <c r="E178" s="1">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1101</v>
+        <v>1116</v>
       </c>
       <c r="G178" s="1">
         <v>0</v>
@@ -15620,16 +15666,16 @@
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="1" t="s">
-        <v>1102</v>
+        <v>1117</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1103</v>
+        <v>1118</v>
       </c>
       <c r="E179" s="1">
         <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1104</v>
+        <v>1119</v>
       </c>
       <c r="G179" s="1">
         <v>0</v>
@@ -15689,16 +15735,16 @@
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="1" t="s">
-        <v>1105</v>
+        <v>1120</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1106</v>
+        <v>1121</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1107</v>
+        <v>1122</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="1138">
   <si>
     <t>ID</t>
   </si>
@@ -3191,6 +3191,15 @@
     <t>5000量</t>
   </si>
   <si>
+    <t>12800兆</t>
+  </si>
+  <si>
+    <t>640正</t>
+  </si>
+  <si>
+    <t>78000000000</t>
+  </si>
+  <si>
     <t>10157</t>
   </si>
   <si>
@@ -3209,6 +3218,15 @@
     <t>10大</t>
   </si>
   <si>
+    <t>25京</t>
+  </si>
+  <si>
+    <t>12800正</t>
+  </si>
+  <si>
+    <t>81000000000</t>
+  </si>
+  <si>
     <t>10158</t>
   </si>
   <si>
@@ -3227,6 +3245,15 @@
     <t>200大</t>
   </si>
   <si>
+    <t>500京</t>
+  </si>
+  <si>
+    <t>25载</t>
+  </si>
+  <si>
+    <t>84000000000</t>
+  </si>
+  <si>
     <t>10159</t>
   </si>
   <si>
@@ -3243,6 +3270,15 @@
   </si>
   <si>
     <t>4000大</t>
+  </si>
+  <si>
+    <t>1垓</t>
+  </si>
+  <si>
+    <t>500载</t>
+  </si>
+  <si>
+    <t>87000000000</t>
   </si>
   <si>
     <t>10160</t>
@@ -3278,6 +3314,15 @@
       </rPr>
       <t>‌</t>
     </r>
+  </si>
+  <si>
+    <t>20垓</t>
+  </si>
+  <si>
+    <t>1极</t>
+  </si>
+  <si>
+    <t>90000000000</t>
   </si>
   <si>
     <t>10161</t>
@@ -4398,30 +4443,30 @@
   <dimension ref="A1:Y180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="6.87610619469027" style="3" customWidth="1"/>
     <col min="2" max="2" width="9" style="3"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="32.5" style="3" customWidth="1"/>
-    <col min="8" max="8" width="24.6666666666667" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.75" style="3" customWidth="1"/>
-    <col min="10" max="11" width="11.75" style="3" customWidth="1"/>
-    <col min="12" max="12" width="12.75" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="9.125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="8.75" style="3" customWidth="1"/>
-    <col min="16" max="16" width="9.875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="7.5" style="3" customWidth="1"/>
-    <col min="18" max="18" width="7.125" style="3" customWidth="1"/>
-    <col min="19" max="19" width="16.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1238938053097" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.87610619469027" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1238938053097" style="1" customWidth="1"/>
+    <col min="7" max="7" width="32.5044247787611" style="3" customWidth="1"/>
+    <col min="8" max="8" width="24.6637168141593" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.7522123893805" style="3" customWidth="1"/>
+    <col min="10" max="11" width="11.7522123893805" style="3" customWidth="1"/>
+    <col min="12" max="12" width="12.7522123893805" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.3716814159292" style="3" customWidth="1"/>
+    <col min="14" max="14" width="9.12389380530973" style="3" customWidth="1"/>
+    <col min="15" max="15" width="8.75221238938053" style="3" customWidth="1"/>
+    <col min="16" max="16" width="9.87610619469027" style="3" customWidth="1"/>
+    <col min="17" max="17" width="7.50442477876106" style="3" customWidth="1"/>
+    <col min="18" max="18" width="7.12389380530973" style="3" customWidth="1"/>
+    <col min="19" max="19" width="16.3716814159292" style="3" customWidth="1"/>
     <col min="20" max="20" width="13" style="3" customWidth="1"/>
-    <col min="21" max="21" width="11.125" style="1"/>
+    <col min="21" max="21" width="11.1238938053097" style="1"/>
     <col min="22" max="22" width="9" style="1"/>
-    <col min="23" max="23" width="13.625" style="3" customWidth="1"/>
-    <col min="24" max="24" width="8.125" style="3" customWidth="1"/>
-    <col min="25" max="25" width="9.625" style="3" customWidth="1"/>
+    <col min="23" max="23" width="13.6283185840708" style="3" customWidth="1"/>
+    <col min="24" max="24" width="8.12389380530973" style="3" customWidth="1"/>
+    <col min="25" max="25" width="9.6283185840708" style="3" customWidth="1"/>
     <col min="26" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -4650,7 +4695,7 @@
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
     </row>
-    <row r="6" ht="14.25" spans="3:20">
+    <row r="6" ht="13.85" spans="3:20">
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
@@ -13598,7 +13643,7 @@
         <v>5100</v>
       </c>
       <c r="P147" s="3">
-        <f t="shared" ref="P146:P180" si="47">P146+3</f>
+        <f>P146+3</f>
         <v>85</v>
       </c>
       <c r="Q147" s="3">
@@ -13666,7 +13711,7 @@
         <v>5350</v>
       </c>
       <c r="P148" s="3">
-        <f t="shared" si="47"/>
+        <f>P147+3</f>
         <v>88</v>
       </c>
       <c r="Q148" s="3">
@@ -13734,7 +13779,7 @@
         <v>5600</v>
       </c>
       <c r="P149" s="3">
-        <f t="shared" si="47"/>
+        <f>P148+3</f>
         <v>91</v>
       </c>
       <c r="Q149" s="3">
@@ -13802,7 +13847,7 @@
         <v>5850</v>
       </c>
       <c r="P150" s="3">
-        <f t="shared" si="47"/>
+        <f>P149+3</f>
         <v>94</v>
       </c>
       <c r="Q150" s="3">
@@ -13869,7 +13914,7 @@
         <v>6100</v>
       </c>
       <c r="P151" s="3">
-        <f t="shared" si="47"/>
+        <f>P150+3</f>
         <v>97</v>
       </c>
       <c r="Q151" s="3">
@@ -13938,7 +13983,7 @@
         <v>6350</v>
       </c>
       <c r="P152" s="3">
-        <f t="shared" si="47"/>
+        <f>P151+3</f>
         <v>100</v>
       </c>
       <c r="Q152" s="3">
@@ -14007,7 +14052,7 @@
         <v>6600</v>
       </c>
       <c r="P153" s="3">
-        <f t="shared" si="47"/>
+        <f>P152+3</f>
         <v>103</v>
       </c>
       <c r="Q153" s="3">
@@ -14076,7 +14121,7 @@
         <v>6850</v>
       </c>
       <c r="P154" s="3">
-        <f t="shared" si="47"/>
+        <f>P153+3</f>
         <v>106</v>
       </c>
       <c r="Q154" s="3">
@@ -14145,7 +14190,7 @@
         <v>7100</v>
       </c>
       <c r="P155" s="3">
-        <f t="shared" si="47"/>
+        <f>P154+3</f>
         <v>109</v>
       </c>
       <c r="Q155" s="3">
@@ -14214,7 +14259,7 @@
         <v>7350</v>
       </c>
       <c r="P156" s="3">
-        <f t="shared" si="47"/>
+        <f>P155+3</f>
         <v>112</v>
       </c>
       <c r="Q156" s="3">
@@ -14283,7 +14328,7 @@
         <v>7600</v>
       </c>
       <c r="P157" s="3">
-        <f t="shared" si="47"/>
+        <f>P156+3</f>
         <v>115</v>
       </c>
       <c r="Q157" s="3">
@@ -14352,7 +14397,7 @@
         <v>7850</v>
       </c>
       <c r="P158" s="3">
-        <f t="shared" si="47"/>
+        <f>P157+3</f>
         <v>118</v>
       </c>
       <c r="Q158" s="3">
@@ -14421,7 +14466,7 @@
         <v>8100</v>
       </c>
       <c r="P159" s="3">
-        <f t="shared" si="47"/>
+        <f>P158+3</f>
         <v>121</v>
       </c>
       <c r="Q159" s="3">
@@ -14490,7 +14535,7 @@
         <v>8350</v>
       </c>
       <c r="P160" s="3">
-        <f t="shared" si="47"/>
+        <f>P159+3</f>
         <v>124</v>
       </c>
       <c r="Q160" s="3">
@@ -14536,8 +14581,12 @@
       <c r="I161" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="J161" s="1"/>
-      <c r="K161" s="1"/>
+      <c r="J161" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>1055</v>
+      </c>
       <c r="L161" s="1">
         <f t="shared" si="42"/>
         <v>21400</v>
@@ -14555,21 +14604,21 @@
         <v>8600</v>
       </c>
       <c r="P161" s="3">
-        <f t="shared" si="47"/>
-        <v>127</v>
+        <f>P160+4</f>
+        <v>128</v>
       </c>
       <c r="Q161" s="3">
-        <f t="shared" si="37"/>
-        <v>210</v>
+        <f>Q160+5</f>
+        <v>211</v>
       </c>
       <c r="R161" s="3">
         <v>99.99</v>
       </c>
       <c r="S161" s="14" t="s">
-        <v>803</v>
+        <v>1056</v>
       </c>
       <c r="T161" s="14" t="s">
-        <v>803</v>
+        <v>1056</v>
       </c>
       <c r="U161" s="3"/>
       <c r="V161" s="3"/>
@@ -14581,28 +14630,32 @@
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="1" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="E162" s="1">
         <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="J162" s="1"/>
-      <c r="K162" s="1"/>
+        <v>1062</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>1064</v>
+      </c>
       <c r="L162" s="1">
         <f t="shared" si="42"/>
         <v>22000</v>
@@ -14620,21 +14673,21 @@
         <v>8850</v>
       </c>
       <c r="P162" s="3">
-        <f t="shared" si="47"/>
-        <v>130</v>
+        <f>P161+4</f>
+        <v>132</v>
       </c>
       <c r="Q162" s="3">
-        <f t="shared" si="37"/>
-        <v>214</v>
+        <f>Q161+5</f>
+        <v>216</v>
       </c>
       <c r="R162" s="3">
         <v>99.99</v>
       </c>
       <c r="S162" s="14" t="s">
-        <v>809</v>
+        <v>1065</v>
       </c>
       <c r="T162" s="14" t="s">
-        <v>809</v>
+        <v>1065</v>
       </c>
       <c r="U162" s="3"/>
       <c r="V162" s="3"/>
@@ -14646,28 +14699,32 @@
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="1" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="E163" s="1">
         <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="J163" s="1"/>
-      <c r="K163" s="1"/>
+        <v>1071</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="K163" s="1" t="s">
+        <v>1073</v>
+      </c>
       <c r="L163" s="1">
         <f t="shared" si="42"/>
         <v>22600</v>
@@ -14685,21 +14742,21 @@
         <v>9100</v>
       </c>
       <c r="P163" s="3">
-        <f t="shared" si="47"/>
-        <v>133</v>
+        <f>P162+4</f>
+        <v>136</v>
       </c>
       <c r="Q163" s="3">
-        <f t="shared" si="37"/>
-        <v>218</v>
+        <f>Q162+5</f>
+        <v>221</v>
       </c>
       <c r="R163" s="3">
         <v>99.99</v>
       </c>
       <c r="S163" s="14" t="s">
-        <v>815</v>
+        <v>1074</v>
       </c>
       <c r="T163" s="14" t="s">
-        <v>815</v>
+        <v>1074</v>
       </c>
       <c r="U163" s="3"/>
       <c r="V163" s="3"/>
@@ -14711,28 +14768,32 @@
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="1" t="s">
-        <v>1066</v>
+        <v>1075</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>1067</v>
+        <v>1076</v>
       </c>
       <c r="E164" s="1">
         <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1068</v>
+        <v>1077</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>1069</v>
+        <v>1078</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>1070</v>
+        <v>1079</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="J164" s="1"/>
-      <c r="K164" s="1"/>
+        <v>1080</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>1082</v>
+      </c>
       <c r="L164" s="1">
         <f t="shared" si="42"/>
         <v>23200</v>
@@ -14750,21 +14811,21 @@
         <v>9350</v>
       </c>
       <c r="P164" s="3">
-        <f t="shared" si="47"/>
-        <v>136</v>
+        <f>P163+4</f>
+        <v>140</v>
       </c>
       <c r="Q164" s="3">
-        <f t="shared" si="37"/>
-        <v>222</v>
+        <f>Q163+5</f>
+        <v>226</v>
       </c>
       <c r="R164" s="3">
         <v>99.99</v>
       </c>
       <c r="S164" s="14" t="s">
-        <v>821</v>
+        <v>1083</v>
       </c>
       <c r="T164" s="14" t="s">
-        <v>821</v>
+        <v>1083</v>
       </c>
       <c r="U164" s="3"/>
       <c r="V164" s="3"/>
@@ -14776,25 +14837,31 @@
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="1" t="s">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>1073</v>
+        <v>1085</v>
       </c>
       <c r="E165" s="1">
         <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1074</v>
+        <v>1086</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>1075</v>
+        <v>1087</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>1076</v>
+        <v>1088</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>1077</v>
+        <v>1089</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="K165" s="1" t="s">
+        <v>1091</v>
       </c>
       <c r="L165" s="1">
         <f t="shared" si="42"/>
@@ -14813,21 +14880,21 @@
         <v>9600</v>
       </c>
       <c r="P165" s="3">
-        <f t="shared" si="47"/>
-        <v>139</v>
+        <f>P164+4</f>
+        <v>144</v>
       </c>
       <c r="Q165" s="3">
-        <f t="shared" si="37"/>
-        <v>226</v>
+        <f>Q164+5</f>
+        <v>231</v>
       </c>
       <c r="R165" s="3">
         <v>99.99</v>
       </c>
       <c r="S165" s="14" t="s">
-        <v>827</v>
+        <v>1092</v>
       </c>
       <c r="T165" s="14" t="s">
-        <v>827</v>
+        <v>1092</v>
       </c>
       <c r="U165" s="3"/>
       <c r="V165" s="3"/>
@@ -14837,16 +14904,16 @@
     </row>
     <row r="166" customHeight="1" spans="3:20">
       <c r="C166" s="1" t="s">
-        <v>1078</v>
+        <v>1093</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>1079</v>
+        <v>1094</v>
       </c>
       <c r="E166" s="1">
         <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="G166" s="1">
         <v>0</v>
@@ -14880,12 +14947,12 @@
         <v>9850</v>
       </c>
       <c r="P166" s="3">
-        <f t="shared" si="47"/>
-        <v>142</v>
+        <f t="shared" ref="P166:P180" si="47">P165+5</f>
+        <v>149</v>
       </c>
       <c r="Q166" s="3">
-        <f t="shared" si="37"/>
-        <v>230</v>
+        <f t="shared" ref="Q166:Q180" si="48">Q165+6</f>
+        <v>237</v>
       </c>
       <c r="R166" s="3">
         <v>99.99</v>
@@ -14899,16 +14966,16 @@
     </row>
     <row r="167" customHeight="1" spans="3:20">
       <c r="C167" s="1" t="s">
-        <v>1081</v>
+        <v>1096</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>1082</v>
+        <v>1097</v>
       </c>
       <c r="E167" s="1">
         <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1083</v>
+        <v>1098</v>
       </c>
       <c r="G167" s="1">
         <v>0</v>
@@ -14943,11 +15010,11 @@
       </c>
       <c r="P167" s="3">
         <f t="shared" si="47"/>
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q167" s="3">
-        <f t="shared" si="37"/>
-        <v>234</v>
+        <f t="shared" si="48"/>
+        <v>243</v>
       </c>
       <c r="R167" s="3">
         <v>99.99</v>
@@ -14961,16 +15028,16 @@
     </row>
     <row r="168" customHeight="1" spans="3:20">
       <c r="C168" s="1" t="s">
-        <v>1084</v>
+        <v>1099</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>1085</v>
+        <v>1100</v>
       </c>
       <c r="E168" s="1">
         <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1086</v>
+        <v>1101</v>
       </c>
       <c r="G168" s="1">
         <v>0</v>
@@ -15005,11 +15072,11 @@
       </c>
       <c r="P168" s="3">
         <f t="shared" si="47"/>
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="Q168" s="3">
-        <f t="shared" si="37"/>
-        <v>238</v>
+        <f t="shared" si="48"/>
+        <v>249</v>
       </c>
       <c r="R168" s="3">
         <v>99.99</v>
@@ -15023,16 +15090,16 @@
     </row>
     <row r="169" customHeight="1" spans="3:20">
       <c r="C169" s="1" t="s">
-        <v>1087</v>
+        <v>1102</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>1088</v>
+        <v>1103</v>
       </c>
       <c r="E169" s="1">
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1089</v>
+        <v>1104</v>
       </c>
       <c r="G169" s="1">
         <v>0</v>
@@ -15067,11 +15134,11 @@
       </c>
       <c r="P169" s="3">
         <f t="shared" si="47"/>
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="Q169" s="3">
-        <f t="shared" si="37"/>
-        <v>242</v>
+        <f t="shared" si="48"/>
+        <v>255</v>
       </c>
       <c r="R169" s="3">
         <v>99.99</v>
@@ -15085,16 +15152,16 @@
     </row>
     <row r="170" customHeight="1" spans="3:20">
       <c r="C170" s="1" t="s">
-        <v>1090</v>
+        <v>1105</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="E170" s="1">
         <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1092</v>
+        <v>1107</v>
       </c>
       <c r="G170" s="1">
         <v>0</v>
@@ -15129,11 +15196,11 @@
       </c>
       <c r="P170" s="3">
         <f t="shared" si="47"/>
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="Q170" s="3">
-        <f t="shared" si="37"/>
-        <v>246</v>
+        <f t="shared" si="48"/>
+        <v>261</v>
       </c>
       <c r="R170" s="3">
         <v>99.99</v>
@@ -15147,16 +15214,16 @@
     </row>
     <row r="171" customHeight="1" spans="3:20">
       <c r="C171" s="1" t="s">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>1094</v>
+        <v>1109</v>
       </c>
       <c r="E171" s="1">
         <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1095</v>
+        <v>1110</v>
       </c>
       <c r="G171" s="1">
         <v>0</v>
@@ -15191,11 +15258,11 @@
       </c>
       <c r="P171" s="3">
         <f t="shared" si="47"/>
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="Q171" s="3">
-        <f t="shared" si="37"/>
-        <v>250</v>
+        <f t="shared" si="48"/>
+        <v>267</v>
       </c>
       <c r="R171" s="3">
         <v>99.99</v>
@@ -15209,16 +15276,16 @@
     </row>
     <row r="172" customHeight="1" spans="3:20">
       <c r="C172" s="1" t="s">
-        <v>1096</v>
+        <v>1111</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>1097</v>
+        <v>1112</v>
       </c>
       <c r="E172" s="1">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1098</v>
+        <v>1113</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
@@ -15253,11 +15320,11 @@
       </c>
       <c r="P172" s="3">
         <f t="shared" si="47"/>
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="Q172" s="3">
-        <f t="shared" si="37"/>
-        <v>254</v>
+        <f t="shared" si="48"/>
+        <v>273</v>
       </c>
       <c r="R172" s="3">
         <v>99.99</v>
@@ -15271,16 +15338,16 @@
     </row>
     <row r="173" customHeight="1" spans="3:20">
       <c r="C173" s="1" t="s">
-        <v>1099</v>
+        <v>1114</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>1100</v>
+        <v>1115</v>
       </c>
       <c r="E173" s="1">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1101</v>
+        <v>1116</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -15315,11 +15382,11 @@
       </c>
       <c r="P173" s="3">
         <f t="shared" si="47"/>
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="Q173" s="3">
-        <f t="shared" si="37"/>
-        <v>258</v>
+        <f t="shared" si="48"/>
+        <v>279</v>
       </c>
       <c r="R173" s="3">
         <v>99.99</v>
@@ -15333,16 +15400,16 @@
     </row>
     <row r="174" customHeight="1" spans="3:20">
       <c r="C174" s="1" t="s">
-        <v>1102</v>
+        <v>1117</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>1103</v>
+        <v>1118</v>
       </c>
       <c r="E174" s="1">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1104</v>
+        <v>1119</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
@@ -15377,11 +15444,11 @@
       </c>
       <c r="P174" s="3">
         <f t="shared" si="47"/>
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="Q174" s="3">
-        <f t="shared" si="37"/>
-        <v>262</v>
+        <f t="shared" si="48"/>
+        <v>285</v>
       </c>
       <c r="R174" s="3">
         <v>99.99</v>
@@ -15395,16 +15462,16 @@
     </row>
     <row r="175" customHeight="1" spans="3:20">
       <c r="C175" s="1" t="s">
-        <v>1105</v>
+        <v>1120</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>1106</v>
+        <v>1121</v>
       </c>
       <c r="E175" s="1">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1107</v>
+        <v>1122</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
@@ -15439,11 +15506,11 @@
       </c>
       <c r="P175" s="3">
         <f t="shared" si="47"/>
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="Q175" s="3">
-        <f t="shared" si="37"/>
-        <v>266</v>
+        <f t="shared" si="48"/>
+        <v>291</v>
       </c>
       <c r="R175" s="3">
         <v>99.99</v>
@@ -15459,16 +15526,16 @@
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="1" t="s">
-        <v>1108</v>
+        <v>1123</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>1109</v>
+        <v>1124</v>
       </c>
       <c r="E176" s="1">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -15503,11 +15570,11 @@
       </c>
       <c r="P176" s="3">
         <f t="shared" si="47"/>
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="Q176" s="3">
-        <f t="shared" si="37"/>
-        <v>270</v>
+        <f t="shared" si="48"/>
+        <v>297</v>
       </c>
       <c r="R176" s="3">
         <v>99.99</v>
@@ -15528,16 +15595,16 @@
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="1" t="s">
-        <v>1111</v>
+        <v>1126</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>1112</v>
+        <v>1127</v>
       </c>
       <c r="E177" s="1">
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1113</v>
+        <v>1128</v>
       </c>
       <c r="G177" s="1">
         <v>0</v>
@@ -15572,11 +15639,11 @@
       </c>
       <c r="P177" s="3">
         <f t="shared" si="47"/>
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="Q177" s="3">
-        <f t="shared" si="37"/>
-        <v>274</v>
+        <f t="shared" si="48"/>
+        <v>303</v>
       </c>
       <c r="R177" s="3">
         <v>99.99</v>
@@ -15597,16 +15664,16 @@
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="1" t="s">
-        <v>1114</v>
+        <v>1129</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1115</v>
+        <v>1130</v>
       </c>
       <c r="E178" s="1">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1116</v>
+        <v>1131</v>
       </c>
       <c r="G178" s="1">
         <v>0</v>
@@ -15641,11 +15708,11 @@
       </c>
       <c r="P178" s="3">
         <f t="shared" si="47"/>
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="Q178" s="3">
-        <f t="shared" si="37"/>
-        <v>278</v>
+        <f t="shared" si="48"/>
+        <v>309</v>
       </c>
       <c r="R178" s="3">
         <v>99.99</v>
@@ -15666,16 +15733,16 @@
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="1" t="s">
-        <v>1117</v>
+        <v>1132</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1118</v>
+        <v>1133</v>
       </c>
       <c r="E179" s="1">
         <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1119</v>
+        <v>1134</v>
       </c>
       <c r="G179" s="1">
         <v>0</v>
@@ -15710,11 +15777,11 @@
       </c>
       <c r="P179" s="3">
         <f t="shared" si="47"/>
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="Q179" s="3">
-        <f t="shared" si="37"/>
-        <v>282</v>
+        <f t="shared" si="48"/>
+        <v>315</v>
       </c>
       <c r="R179" s="3">
         <v>99.99</v>
@@ -15735,16 +15802,16 @@
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>
@@ -15779,11 +15846,11 @@
       </c>
       <c r="P180" s="3">
         <f t="shared" si="47"/>
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="Q180" s="3">
-        <f t="shared" si="37"/>
-        <v>286</v>
+        <f t="shared" si="48"/>
+        <v>321</v>
       </c>
       <c r="R180" s="3">
         <v>99.99</v>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -3296,24 +3296,7 @@
     <t>90不</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
+    <t>8数</t>
   </si>
   <si>
     <t>20垓</t>
@@ -3471,7 +3454,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3635,12 +3618,6 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -13576,7 +13553,7 @@
         <v>4850</v>
       </c>
       <c r="P146" s="11">
-        <f>P145+3</f>
+        <f t="shared" ref="P146:P160" si="46">P145+3</f>
         <v>82</v>
       </c>
       <c r="Q146" s="11">
@@ -13620,7 +13597,7 @@
         <v>931</v>
       </c>
       <c r="J147" s="1">
-        <f t="shared" ref="J147:J155" si="46">J146*5</f>
+        <f t="shared" ref="J147:J155" si="47">J146*5</f>
         <v>50</v>
       </c>
       <c r="K147" s="1" t="s">
@@ -13643,7 +13620,7 @@
         <v>5100</v>
       </c>
       <c r="P147" s="3">
-        <f>P146+3</f>
+        <f t="shared" si="46"/>
         <v>85</v>
       </c>
       <c r="Q147" s="3">
@@ -13688,7 +13665,7 @@
         <v>939</v>
       </c>
       <c r="J148" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>250</v>
       </c>
       <c r="K148" s="1" t="s">
@@ -13711,7 +13688,7 @@
         <v>5350</v>
       </c>
       <c r="P148" s="3">
-        <f>P147+3</f>
+        <f t="shared" si="46"/>
         <v>88</v>
       </c>
       <c r="Q148" s="3">
@@ -13756,7 +13733,7 @@
         <v>947</v>
       </c>
       <c r="J149" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>1250</v>
       </c>
       <c r="K149" s="1" t="s">
@@ -13779,7 +13756,7 @@
         <v>5600</v>
       </c>
       <c r="P149" s="3">
-        <f>P148+3</f>
+        <f t="shared" si="46"/>
         <v>91</v>
       </c>
       <c r="Q149" s="3">
@@ -13824,7 +13801,7 @@
         <v>955</v>
       </c>
       <c r="J150" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>6250</v>
       </c>
       <c r="K150" s="1" t="s">
@@ -13847,7 +13824,7 @@
         <v>5850</v>
       </c>
       <c r="P150" s="3">
-        <f>P149+3</f>
+        <f t="shared" si="46"/>
         <v>94</v>
       </c>
       <c r="Q150" s="3">
@@ -13914,7 +13891,7 @@
         <v>6100</v>
       </c>
       <c r="P151" s="3">
-        <f>P150+3</f>
+        <f t="shared" si="46"/>
         <v>97</v>
       </c>
       <c r="Q151" s="3">
@@ -13983,7 +13960,7 @@
         <v>6350</v>
       </c>
       <c r="P152" s="3">
-        <f>P151+3</f>
+        <f t="shared" si="46"/>
         <v>100</v>
       </c>
       <c r="Q152" s="3">
@@ -14052,7 +14029,7 @@
         <v>6600</v>
       </c>
       <c r="P153" s="3">
-        <f>P152+3</f>
+        <f t="shared" si="46"/>
         <v>103</v>
       </c>
       <c r="Q153" s="3">
@@ -14121,7 +14098,7 @@
         <v>6850</v>
       </c>
       <c r="P154" s="3">
-        <f>P153+3</f>
+        <f t="shared" si="46"/>
         <v>106</v>
       </c>
       <c r="Q154" s="3">
@@ -14190,7 +14167,7 @@
         <v>7100</v>
       </c>
       <c r="P155" s="3">
-        <f>P154+3</f>
+        <f t="shared" si="46"/>
         <v>109</v>
       </c>
       <c r="Q155" s="3">
@@ -14259,7 +14236,7 @@
         <v>7350</v>
       </c>
       <c r="P156" s="3">
-        <f>P155+3</f>
+        <f t="shared" si="46"/>
         <v>112</v>
       </c>
       <c r="Q156" s="3">
@@ -14328,7 +14305,7 @@
         <v>7600</v>
       </c>
       <c r="P157" s="3">
-        <f>P156+3</f>
+        <f t="shared" si="46"/>
         <v>115</v>
       </c>
       <c r="Q157" s="3">
@@ -14397,7 +14374,7 @@
         <v>7850</v>
       </c>
       <c r="P158" s="3">
-        <f>P157+3</f>
+        <f t="shared" si="46"/>
         <v>118</v>
       </c>
       <c r="Q158" s="3">
@@ -14466,7 +14443,7 @@
         <v>8100</v>
       </c>
       <c r="P159" s="3">
-        <f>P158+3</f>
+        <f t="shared" si="46"/>
         <v>121</v>
       </c>
       <c r="Q159" s="3">
@@ -14535,7 +14512,7 @@
         <v>8350</v>
       </c>
       <c r="P160" s="3">
-        <f>P159+3</f>
+        <f t="shared" si="46"/>
         <v>124</v>
       </c>
       <c r="Q160" s="3">
@@ -14947,11 +14924,11 @@
         <v>9850</v>
       </c>
       <c r="P166" s="3">
-        <f t="shared" ref="P166:P180" si="47">P165+5</f>
+        <f t="shared" ref="P166:P180" si="48">P165+5</f>
         <v>149</v>
       </c>
       <c r="Q166" s="3">
-        <f t="shared" ref="Q166:Q180" si="48">Q165+6</f>
+        <f t="shared" ref="Q166:Q180" si="49">Q165+6</f>
         <v>237</v>
       </c>
       <c r="R166" s="3">
@@ -15009,11 +14986,11 @@
         <v>10100</v>
       </c>
       <c r="P167" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>154</v>
       </c>
       <c r="Q167" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>243</v>
       </c>
       <c r="R167" s="3">
@@ -15071,11 +15048,11 @@
         <v>10350</v>
       </c>
       <c r="P168" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>159</v>
       </c>
       <c r="Q168" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>249</v>
       </c>
       <c r="R168" s="3">
@@ -15133,11 +15110,11 @@
         <v>10600</v>
       </c>
       <c r="P169" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>164</v>
       </c>
       <c r="Q169" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>255</v>
       </c>
       <c r="R169" s="3">
@@ -15195,11 +15172,11 @@
         <v>10850</v>
       </c>
       <c r="P170" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>169</v>
       </c>
       <c r="Q170" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>261</v>
       </c>
       <c r="R170" s="3">
@@ -15257,11 +15234,11 @@
         <v>11100</v>
       </c>
       <c r="P171" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>174</v>
       </c>
       <c r="Q171" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>267</v>
       </c>
       <c r="R171" s="3">
@@ -15319,11 +15296,11 @@
         <v>11350</v>
       </c>
       <c r="P172" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>179</v>
       </c>
       <c r="Q172" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>273</v>
       </c>
       <c r="R172" s="3">
@@ -15381,11 +15358,11 @@
         <v>11600</v>
       </c>
       <c r="P173" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>184</v>
       </c>
       <c r="Q173" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>279</v>
       </c>
       <c r="R173" s="3">
@@ -15443,11 +15420,11 @@
         <v>11850</v>
       </c>
       <c r="P174" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>189</v>
       </c>
       <c r="Q174" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>285</v>
       </c>
       <c r="R174" s="3">
@@ -15505,11 +15482,11 @@
         <v>12100</v>
       </c>
       <c r="P175" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>194</v>
       </c>
       <c r="Q175" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>291</v>
       </c>
       <c r="R175" s="3">
@@ -15569,11 +15546,11 @@
         <v>12350</v>
       </c>
       <c r="P176" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>199</v>
       </c>
       <c r="Q176" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>297</v>
       </c>
       <c r="R176" s="3">
@@ -15638,11 +15615,11 @@
         <v>12600</v>
       </c>
       <c r="P177" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>204</v>
       </c>
       <c r="Q177" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>303</v>
       </c>
       <c r="R177" s="3">
@@ -15707,11 +15684,11 @@
         <v>12850</v>
       </c>
       <c r="P178" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>209</v>
       </c>
       <c r="Q178" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>309</v>
       </c>
       <c r="R178" s="3">
@@ -15776,11 +15753,11 @@
         <v>13100</v>
       </c>
       <c r="P179" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>214</v>
       </c>
       <c r="Q179" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>315</v>
       </c>
       <c r="R179" s="3">
@@ -15845,11 +15822,11 @@
         <v>13350</v>
       </c>
       <c r="P180" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>219</v>
       </c>
       <c r="Q180" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>321</v>
       </c>
       <c r="R180" s="3">

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="1138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="1178">
   <si>
     <t>ID</t>
   </si>
@@ -3290,7 +3290,7 @@
     <t>深渊蝎蛇</t>
   </si>
   <si>
-    <t>900阿</t>
+    <t>9E+66</t>
   </si>
   <si>
     <t>90不</t>
@@ -3317,6 +3317,24 @@
     <t>深渊恶魔</t>
   </si>
   <si>
+    <t>9E+67</t>
+  </si>
+  <si>
+    <t>9E+90</t>
+  </si>
+  <si>
+    <t>16E+117</t>
+  </si>
+  <si>
+    <t>2E+21</t>
+  </si>
+  <si>
+    <t>2E+49</t>
+  </si>
+  <si>
+    <t>93000000000</t>
+  </si>
+  <si>
     <t>10162</t>
   </si>
   <si>
@@ -3326,6 +3344,24 @@
     <t>深渊勇士</t>
   </si>
   <si>
+    <t>9E+68</t>
+  </si>
+  <si>
+    <t>9E+91</t>
+  </si>
+  <si>
+    <t>32E+118</t>
+  </si>
+  <si>
+    <t>4E+22</t>
+  </si>
+  <si>
+    <t>4E+50</t>
+  </si>
+  <si>
+    <t>96000000000</t>
+  </si>
+  <si>
     <t>10163</t>
   </si>
   <si>
@@ -3335,6 +3371,24 @@
     <t>深渊雕像</t>
   </si>
   <si>
+    <t>9E+69</t>
+  </si>
+  <si>
+    <t>9E+92</t>
+  </si>
+  <si>
+    <t>64E+119</t>
+  </si>
+  <si>
+    <t>8E+23</t>
+  </si>
+  <si>
+    <t>8E+51</t>
+  </si>
+  <si>
+    <t>99000000000</t>
+  </si>
+  <si>
     <t>10164</t>
   </si>
   <si>
@@ -3344,6 +3398,24 @@
     <t>深渊卫士</t>
   </si>
   <si>
+    <t>9E+70</t>
+  </si>
+  <si>
+    <t>9E+93</t>
+  </si>
+  <si>
+    <t>128E+120</t>
+  </si>
+  <si>
+    <t>16E+24</t>
+  </si>
+  <si>
+    <t>16E+52</t>
+  </si>
+  <si>
+    <t>102000000000</t>
+  </si>
+  <si>
     <t>10165</t>
   </si>
   <si>
@@ -3353,6 +3425,24 @@
     <t>深渊魔猪</t>
   </si>
   <si>
+    <t>9E+71</t>
+  </si>
+  <si>
+    <t>9E+94</t>
+  </si>
+  <si>
+    <t>256E+121</t>
+  </si>
+  <si>
+    <t>32E+25</t>
+  </si>
+  <si>
+    <t>32E+53</t>
+  </si>
+  <si>
+    <t>105000000000</t>
+  </si>
+  <si>
     <t>10166</t>
   </si>
   <si>
@@ -3362,6 +3452,9 @@
     <t>深渊树妖</t>
   </si>
   <si>
+    <t>108000000000</t>
+  </si>
+  <si>
     <t>10167</t>
   </si>
   <si>
@@ -3371,6 +3464,9 @@
     <t>深渊侍卫</t>
   </si>
   <si>
+    <t>111000000000</t>
+  </si>
+  <si>
     <t>10168</t>
   </si>
   <si>
@@ -3380,6 +3476,9 @@
     <t>深渊剧毒</t>
   </si>
   <si>
+    <t>114000000000</t>
+  </si>
+  <si>
     <t>10169</t>
   </si>
   <si>
@@ -3389,6 +3488,9 @@
     <t>深渊锤兵</t>
   </si>
   <si>
+    <t>117000000000</t>
+  </si>
+  <si>
     <t>10170</t>
   </si>
   <si>
@@ -3398,6 +3500,9 @@
     <t>深渊魔牛</t>
   </si>
   <si>
+    <t>120000000000</t>
+  </si>
+  <si>
     <t>10171</t>
   </si>
   <si>
@@ -3407,6 +3512,9 @@
     <t>深渊水龙</t>
   </si>
   <si>
+    <t>123000000000</t>
+  </si>
+  <si>
     <t>10172</t>
   </si>
   <si>
@@ -3416,6 +3524,9 @@
     <t>深渊土龙</t>
   </si>
   <si>
+    <t>126000000000</t>
+  </si>
+  <si>
     <t>10173</t>
   </si>
   <si>
@@ -3425,6 +3536,9 @@
     <t>深渊毒龙</t>
   </si>
   <si>
+    <t>129000000000</t>
+  </si>
+  <si>
     <t>10174</t>
   </si>
   <si>
@@ -3434,6 +3548,9 @@
     <t>深渊火龙</t>
   </si>
   <si>
+    <t>132000000000</t>
+  </si>
+  <si>
     <t>10175</t>
   </si>
   <si>
@@ -3441,6 +3558,9 @@
   </si>
   <si>
     <t>深渊冰龙</t>
+  </si>
+  <si>
+    <t>135000000000</t>
   </si>
 </sst>
 </file>
@@ -3454,7 +3574,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3465,6 +3585,17 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -3944,142 +4075,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -4090,6 +4223,14 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -4098,6 +4239,14 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4420,257 +4569,257 @@
   <dimension ref="A1:Y180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3"/>
+    <col min="1" max="1" width="6.87610619469027" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9" style="5"/>
     <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.1238938053097" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.87610619469027" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.1238938053097" style="1" customWidth="1"/>
-    <col min="7" max="7" width="32.5044247787611" style="3" customWidth="1"/>
-    <col min="8" max="8" width="24.6637168141593" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.7522123893805" style="3" customWidth="1"/>
-    <col min="10" max="11" width="11.7522123893805" style="3" customWidth="1"/>
-    <col min="12" max="12" width="12.7522123893805" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.3716814159292" style="3" customWidth="1"/>
-    <col min="14" max="14" width="9.12389380530973" style="3" customWidth="1"/>
-    <col min="15" max="15" width="8.75221238938053" style="3" customWidth="1"/>
-    <col min="16" max="16" width="9.87610619469027" style="3" customWidth="1"/>
-    <col min="17" max="17" width="7.50442477876106" style="3" customWidth="1"/>
-    <col min="18" max="18" width="7.12389380530973" style="3" customWidth="1"/>
-    <col min="19" max="19" width="16.3716814159292" style="3" customWidth="1"/>
-    <col min="20" max="20" width="13" style="3" customWidth="1"/>
+    <col min="7" max="7" width="32.5044247787611" style="5" customWidth="1"/>
+    <col min="8" max="8" width="24.6637168141593" style="5" customWidth="1"/>
+    <col min="9" max="9" width="21.7522123893805" style="5" customWidth="1"/>
+    <col min="10" max="11" width="11.7522123893805" style="5" customWidth="1"/>
+    <col min="12" max="12" width="12.7522123893805" style="5" customWidth="1"/>
+    <col min="13" max="13" width="9.3716814159292" style="5" customWidth="1"/>
+    <col min="14" max="14" width="9.12389380530973" style="5" customWidth="1"/>
+    <col min="15" max="15" width="8.75221238938053" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9.87610619469027" style="5" customWidth="1"/>
+    <col min="17" max="17" width="7.50442477876106" style="5" customWidth="1"/>
+    <col min="18" max="18" width="7.12389380530973" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.3716814159292" style="5" customWidth="1"/>
+    <col min="20" max="20" width="13" style="5" customWidth="1"/>
     <col min="21" max="21" width="11.1238938053097" style="1"/>
     <col min="22" max="22" width="9" style="1"/>
-    <col min="23" max="23" width="13.6283185840708" style="3" customWidth="1"/>
-    <col min="24" max="24" width="8.12389380530973" style="3" customWidth="1"/>
-    <col min="25" max="25" width="9.6283185840708" style="3" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="3"/>
+    <col min="23" max="23" width="13.6283185840708" style="5" customWidth="1"/>
+    <col min="24" max="24" width="8.12389380530973" style="5" customWidth="1"/>
+    <col min="25" max="25" width="9.6283185840708" style="5" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="T3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="T4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="T5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
     </row>
     <row r="6" ht="13.85" spans="3:20">
       <c r="C6" s="1" t="s">
@@ -4685,13 +4834,13 @@
       <c r="F6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="20" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="1">
@@ -4712,13 +4861,13 @@
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5">
-        <v>0</v>
-      </c>
-      <c r="R6" s="5">
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
         <v>0</v>
       </c>
       <c r="S6" s="1" t="s">
@@ -4768,13 +4917,13 @@
       <c r="O7" s="1">
         <v>0</v>
       </c>
-      <c r="P7" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>0</v>
-      </c>
-      <c r="R7" s="5">
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
         <v>0</v>
       </c>
       <c r="S7" s="1" t="s">
@@ -4824,13 +4973,13 @@
       <c r="O8" s="1">
         <v>0</v>
       </c>
-      <c r="P8" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5">
-        <v>0</v>
-      </c>
-      <c r="R8" s="5">
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
         <v>0</v>
       </c>
       <c r="S8" s="1" t="s">
@@ -4880,13 +5029,13 @@
       <c r="O9" s="1">
         <v>0</v>
       </c>
-      <c r="P9" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>0</v>
-      </c>
-      <c r="R9" s="5">
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
       <c r="S9" s="1" t="s">
@@ -4936,13 +5085,13 @@
       <c r="O10" s="1">
         <v>0</v>
       </c>
-      <c r="P10" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>0</v>
-      </c>
-      <c r="R10" s="5">
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
         <v>0</v>
       </c>
       <c r="S10" s="1" t="s">
@@ -4992,13 +5141,13 @@
       <c r="O11" s="1">
         <v>0</v>
       </c>
-      <c r="P11" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5">
-        <v>0</v>
-      </c>
-      <c r="R11" s="5">
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
         <v>0</v>
       </c>
       <c r="S11" s="1" t="s">
@@ -5048,13 +5197,13 @@
       <c r="O12" s="1">
         <v>0</v>
       </c>
-      <c r="P12" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5">
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
         <v>0</v>
       </c>
       <c r="S12" s="1" t="s">
@@ -5104,13 +5253,13 @@
       <c r="O13" s="1">
         <v>0</v>
       </c>
-      <c r="P13" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="5">
-        <v>0</v>
-      </c>
-      <c r="R13" s="5">
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0</v>
+      </c>
+      <c r="R13" s="7">
         <v>0</v>
       </c>
       <c r="S13" s="1" t="s">
@@ -5160,13 +5309,13 @@
       <c r="O14" s="1">
         <v>0</v>
       </c>
-      <c r="P14" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5">
-        <v>0</v>
-      </c>
-      <c r="R14" s="5">
+      <c r="P14" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7">
         <v>0</v>
       </c>
       <c r="S14" s="1" t="s">
@@ -5216,13 +5365,13 @@
       <c r="O15" s="1">
         <v>0</v>
       </c>
-      <c r="P15" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5">
-        <v>0</v>
-      </c>
-      <c r="R15" s="5">
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7">
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
@@ -5272,13 +5421,13 @@
       <c r="O16" s="1">
         <v>0</v>
       </c>
-      <c r="P16" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="5">
-        <v>0</v>
-      </c>
-      <c r="R16" s="5">
+      <c r="P16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7">
         <v>0</v>
       </c>
       <c r="S16" s="1" t="s">
@@ -5328,13 +5477,13 @@
       <c r="O17" s="1">
         <v>0</v>
       </c>
-      <c r="P17" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5">
-        <v>0</v>
-      </c>
-      <c r="R17" s="5">
+      <c r="P17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>0</v>
+      </c>
+      <c r="R17" s="7">
         <v>0</v>
       </c>
       <c r="S17" s="1" t="s">
@@ -5384,13 +5533,13 @@
       <c r="O18" s="1">
         <v>0</v>
       </c>
-      <c r="P18" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5">
-        <v>0</v>
-      </c>
-      <c r="R18" s="5">
+      <c r="P18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0</v>
+      </c>
+      <c r="R18" s="7">
         <v>0</v>
       </c>
       <c r="S18" s="1" t="s">
@@ -5440,13 +5589,13 @@
       <c r="O19" s="1">
         <v>0</v>
       </c>
-      <c r="P19" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5">
-        <v>0</v>
-      </c>
-      <c r="R19" s="5">
+      <c r="P19" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>0</v>
+      </c>
+      <c r="R19" s="7">
         <v>0</v>
       </c>
       <c r="S19" s="1" t="s">
@@ -5496,13 +5645,13 @@
       <c r="O20" s="1">
         <v>0</v>
       </c>
-      <c r="P20" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5">
-        <v>0</v>
-      </c>
-      <c r="R20" s="5">
+      <c r="P20" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>0</v>
+      </c>
+      <c r="R20" s="7">
         <v>0</v>
       </c>
       <c r="S20" s="1" t="s">
@@ -5553,13 +5702,13 @@
       <c r="O21" s="1">
         <v>0</v>
       </c>
-      <c r="P21" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5">
-        <v>0</v>
-      </c>
-      <c r="R21" s="5">
+      <c r="P21" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>0</v>
+      </c>
+      <c r="R21" s="7">
         <v>0</v>
       </c>
       <c r="S21" s="1" t="s">
@@ -5610,13 +5759,13 @@
       <c r="O22" s="1">
         <v>0</v>
       </c>
-      <c r="P22" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>0</v>
-      </c>
-      <c r="R22" s="5">
+      <c r="P22" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>0</v>
+      </c>
+      <c r="R22" s="7">
         <v>0</v>
       </c>
       <c r="S22" s="1" t="s">
@@ -5667,13 +5816,13 @@
       <c r="O23" s="1">
         <v>0</v>
       </c>
-      <c r="P23" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="5">
-        <v>0</v>
-      </c>
-      <c r="R23" s="5">
+      <c r="P23" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>0</v>
+      </c>
+      <c r="R23" s="7">
         <v>0</v>
       </c>
       <c r="S23" s="1" t="s">
@@ -5724,13 +5873,13 @@
       <c r="O24" s="1">
         <v>0</v>
       </c>
-      <c r="P24" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5">
-        <v>0</v>
-      </c>
-      <c r="R24" s="5">
+      <c r="P24" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="7">
+        <v>0</v>
+      </c>
+      <c r="R24" s="7">
         <v>0</v>
       </c>
       <c r="S24" s="1" t="s">
@@ -5781,13 +5930,13 @@
       <c r="O25" s="1">
         <v>0</v>
       </c>
-      <c r="P25" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="5">
-        <v>0</v>
-      </c>
-      <c r="R25" s="5">
+      <c r="P25" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>0</v>
+      </c>
+      <c r="R25" s="7">
         <v>0</v>
       </c>
       <c r="S25" s="1" t="s">
@@ -5838,13 +5987,13 @@
       <c r="O26" s="1">
         <v>0</v>
       </c>
-      <c r="P26" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="5">
-        <v>0</v>
-      </c>
-      <c r="R26" s="5">
+      <c r="P26" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7">
         <v>0</v>
       </c>
       <c r="S26" s="1" t="s">
@@ -5895,13 +6044,13 @@
       <c r="O27" s="1">
         <v>0</v>
       </c>
-      <c r="P27" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="5">
-        <v>0</v>
-      </c>
-      <c r="R27" s="5">
+      <c r="P27" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>0</v>
+      </c>
+      <c r="R27" s="7">
         <v>0</v>
       </c>
       <c r="S27" s="1" t="s">
@@ -5952,13 +6101,13 @@
       <c r="O28" s="1">
         <v>0</v>
       </c>
-      <c r="P28" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="5">
-        <v>0</v>
-      </c>
-      <c r="R28" s="5">
+      <c r="P28" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="7">
+        <v>0</v>
+      </c>
+      <c r="R28" s="7">
         <v>0</v>
       </c>
       <c r="S28" s="1" t="s">
@@ -6009,13 +6158,13 @@
       <c r="O29" s="1">
         <v>0</v>
       </c>
-      <c r="P29" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="5">
-        <v>0</v>
-      </c>
-      <c r="R29" s="5">
+      <c r="P29" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="7">
+        <v>0</v>
+      </c>
+      <c r="R29" s="7">
         <v>0</v>
       </c>
       <c r="S29" s="1" t="s">
@@ -6066,13 +6215,13 @@
       <c r="O30" s="1">
         <v>0</v>
       </c>
-      <c r="P30" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5">
+      <c r="P30" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="7">
+        <v>0</v>
+      </c>
+      <c r="R30" s="7">
         <v>0</v>
       </c>
       <c r="S30" s="1" t="s">
@@ -6123,13 +6272,13 @@
       <c r="O31" s="1">
         <v>0</v>
       </c>
-      <c r="P31" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="5">
-        <v>0</v>
-      </c>
-      <c r="R31" s="5">
+      <c r="P31" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="7">
+        <v>0</v>
+      </c>
+      <c r="R31" s="7">
         <v>0</v>
       </c>
       <c r="S31" s="1" t="s">
@@ -6180,13 +6329,13 @@
       <c r="O32" s="1">
         <v>0</v>
       </c>
-      <c r="P32" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5">
-        <v>0</v>
-      </c>
-      <c r="R32" s="5">
+      <c r="P32" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="7">
+        <v>0</v>
+      </c>
+      <c r="R32" s="7">
         <v>0</v>
       </c>
       <c r="S32" s="1" t="s">
@@ -6237,13 +6386,13 @@
       <c r="O33" s="1">
         <v>0</v>
       </c>
-      <c r="P33" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="5">
-        <v>0</v>
-      </c>
-      <c r="R33" s="5">
+      <c r="P33" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="7">
+        <v>0</v>
+      </c>
+      <c r="R33" s="7">
         <v>0</v>
       </c>
       <c r="S33" s="1" t="s">
@@ -6294,13 +6443,13 @@
       <c r="O34" s="1">
         <v>0</v>
       </c>
-      <c r="P34" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="5">
-        <v>0</v>
-      </c>
-      <c r="R34" s="5">
+      <c r="P34" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="7">
+        <v>0</v>
+      </c>
+      <c r="R34" s="7">
         <v>0</v>
       </c>
       <c r="S34" s="1" t="s">
@@ -6351,13 +6500,13 @@
       <c r="O35" s="1">
         <v>0</v>
       </c>
-      <c r="P35" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="5">
-        <v>0</v>
-      </c>
-      <c r="R35" s="5">
+      <c r="P35" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="7">
+        <v>0</v>
+      </c>
+      <c r="R35" s="7">
         <v>0</v>
       </c>
       <c r="S35" s="1" t="s">
@@ -6408,13 +6557,13 @@
       <c r="O36" s="1">
         <v>0</v>
       </c>
-      <c r="P36" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="5">
-        <v>0</v>
-      </c>
-      <c r="R36" s="5">
+      <c r="P36" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="7">
+        <v>0</v>
+      </c>
+      <c r="R36" s="7">
         <v>0</v>
       </c>
       <c r="S36" s="1" t="s">
@@ -6465,13 +6614,13 @@
       <c r="O37" s="1">
         <v>0</v>
       </c>
-      <c r="P37" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="5">
-        <v>0</v>
-      </c>
-      <c r="R37" s="5">
+      <c r="P37" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="7">
+        <v>0</v>
+      </c>
+      <c r="R37" s="7">
         <v>0</v>
       </c>
       <c r="S37" s="1" t="s">
@@ -6522,13 +6671,13 @@
       <c r="O38" s="1">
         <v>0</v>
       </c>
-      <c r="P38" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="5">
-        <v>0</v>
-      </c>
-      <c r="R38" s="5">
+      <c r="P38" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="7">
+        <v>0</v>
+      </c>
+      <c r="R38" s="7">
         <v>0</v>
       </c>
       <c r="S38" s="1" t="s">
@@ -6579,13 +6728,13 @@
       <c r="O39" s="1">
         <v>0</v>
       </c>
-      <c r="P39" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="5">
-        <v>0</v>
-      </c>
-      <c r="R39" s="5">
+      <c r="P39" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="7">
+        <v>0</v>
+      </c>
+      <c r="R39" s="7">
         <v>0</v>
       </c>
       <c r="S39" s="1" t="s">
@@ -6636,13 +6785,13 @@
       <c r="O40" s="1">
         <v>0</v>
       </c>
-      <c r="P40" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>0</v>
-      </c>
-      <c r="R40" s="5">
+      <c r="P40" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="7">
+        <v>0</v>
+      </c>
+      <c r="R40" s="7">
         <v>0</v>
       </c>
       <c r="S40" s="1" t="s">
@@ -6653,7 +6802,7 @@
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A41" s="3"/>
+      <c r="A41" s="5"/>
       <c r="C41" s="1" t="s">
         <v>265</v>
       </c>
@@ -6694,13 +6843,13 @@
       <c r="O41" s="1">
         <v>0</v>
       </c>
-      <c r="P41" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="5">
-        <v>0</v>
-      </c>
-      <c r="R41" s="5">
+      <c r="P41" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="7">
+        <v>0</v>
+      </c>
+      <c r="R41" s="7">
         <v>0</v>
       </c>
       <c r="S41" s="1" t="s">
@@ -6709,12 +6858,12 @@
       <c r="T41" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
+      <c r="W41" s="5"/>
+      <c r="X41" s="5"/>
+      <c r="Y41" s="5"/>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A42" s="3"/>
+      <c r="A42" s="5"/>
       <c r="C42" s="1" t="s">
         <v>272</v>
       </c>
@@ -6755,13 +6904,13 @@
       <c r="O42" s="1">
         <v>0</v>
       </c>
-      <c r="P42" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="5">
-        <v>0</v>
-      </c>
-      <c r="R42" s="5">
+      <c r="P42" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="7">
+        <v>0</v>
+      </c>
+      <c r="R42" s="7">
         <v>0</v>
       </c>
       <c r="S42" s="1" t="s">
@@ -6770,12 +6919,12 @@
       <c r="T42" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
+      <c r="W42" s="5"/>
+      <c r="X42" s="5"/>
+      <c r="Y42" s="5"/>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A43" s="3"/>
+      <c r="A43" s="5"/>
       <c r="C43" s="1" t="s">
         <v>279</v>
       </c>
@@ -6816,13 +6965,13 @@
       <c r="O43" s="1">
         <v>0</v>
       </c>
-      <c r="P43" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="5">
-        <v>0</v>
-      </c>
-      <c r="R43" s="5">
+      <c r="P43" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>0</v>
+      </c>
+      <c r="R43" s="7">
         <v>0</v>
       </c>
       <c r="S43" s="1" t="s">
@@ -6831,12 +6980,12 @@
       <c r="T43" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
+      <c r="W43" s="5"/>
+      <c r="X43" s="5"/>
+      <c r="Y43" s="5"/>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A44" s="3"/>
+      <c r="A44" s="5"/>
       <c r="C44" s="1" t="s">
         <v>286</v>
       </c>
@@ -6877,13 +7026,13 @@
       <c r="O44" s="1">
         <v>0</v>
       </c>
-      <c r="P44" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>0</v>
-      </c>
-      <c r="R44" s="5">
+      <c r="P44" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="7">
+        <v>0</v>
+      </c>
+      <c r="R44" s="7">
         <v>0</v>
       </c>
       <c r="S44" s="1" t="s">
@@ -6892,12 +7041,12 @@
       <c r="T44" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
+      <c r="W44" s="5"/>
+      <c r="X44" s="5"/>
+      <c r="Y44" s="5"/>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A45" s="3"/>
+      <c r="A45" s="5"/>
       <c r="C45" s="1" t="s">
         <v>293</v>
       </c>
@@ -6938,13 +7087,13 @@
       <c r="O45" s="1">
         <v>0</v>
       </c>
-      <c r="P45" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="5">
-        <v>0</v>
-      </c>
-      <c r="R45" s="5">
+      <c r="P45" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="7">
+        <v>0</v>
+      </c>
+      <c r="R45" s="7">
         <v>0</v>
       </c>
       <c r="S45" s="1" t="s">
@@ -6953,12 +7102,12 @@
       <c r="T45" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
+      <c r="W45" s="5"/>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="5"/>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A46" s="3"/>
+      <c r="A46" s="5"/>
       <c r="C46" s="1" t="s">
         <v>300</v>
       </c>
@@ -6999,13 +7148,13 @@
       <c r="O46" s="1">
         <v>0</v>
       </c>
-      <c r="P46" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="5">
-        <v>0</v>
-      </c>
-      <c r="R46" s="5">
+      <c r="P46" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="7">
+        <v>0</v>
+      </c>
+      <c r="R46" s="7">
         <v>0</v>
       </c>
       <c r="S46" s="1" t="s">
@@ -7014,14 +7163,14 @@
       <c r="T46" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="U46" s="3"/>
-      <c r="V46" s="3"/>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="W46" s="5"/>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="5"/>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A47" s="3"/>
+      <c r="A47" s="5"/>
       <c r="C47" s="1" t="s">
         <v>307</v>
       </c>
@@ -7062,13 +7211,13 @@
       <c r="O47" s="1">
         <v>0</v>
       </c>
-      <c r="P47" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="5">
-        <v>0</v>
-      </c>
-      <c r="R47" s="5">
+      <c r="P47" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="7">
+        <v>0</v>
+      </c>
+      <c r="R47" s="7">
         <v>0</v>
       </c>
       <c r="S47" s="1" t="s">
@@ -7077,14 +7226,14 @@
       <c r="T47" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="5"/>
+      <c r="W47" s="5"/>
+      <c r="X47" s="5"/>
+      <c r="Y47" s="5"/>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A48" s="3"/>
+      <c r="A48" s="5"/>
       <c r="C48" s="1" t="s">
         <v>314</v>
       </c>
@@ -7125,13 +7274,13 @@
       <c r="O48" s="1">
         <v>0</v>
       </c>
-      <c r="P48" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="5">
-        <v>0</v>
-      </c>
-      <c r="R48" s="5">
+      <c r="P48" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="7">
+        <v>0</v>
+      </c>
+      <c r="R48" s="7">
         <v>0</v>
       </c>
       <c r="S48" s="1" t="s">
@@ -7140,14 +7289,14 @@
       <c r="T48" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
-      <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
+      <c r="U48" s="5"/>
+      <c r="V48" s="5"/>
+      <c r="W48" s="5"/>
+      <c r="X48" s="5"/>
+      <c r="Y48" s="5"/>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A49" s="3"/>
+      <c r="A49" s="5"/>
       <c r="C49" s="1" t="s">
         <v>321</v>
       </c>
@@ -7188,13 +7337,13 @@
       <c r="O49" s="1">
         <v>0</v>
       </c>
-      <c r="P49" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="5">
-        <v>0</v>
-      </c>
-      <c r="R49" s="5">
+      <c r="P49" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="7">
+        <v>0</v>
+      </c>
+      <c r="R49" s="7">
         <v>0</v>
       </c>
       <c r="S49" s="1" t="s">
@@ -7203,14 +7352,14 @@
       <c r="T49" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5"/>
+      <c r="W49" s="5"/>
+      <c r="X49" s="5"/>
+      <c r="Y49" s="5"/>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A50" s="3"/>
+      <c r="A50" s="5"/>
       <c r="C50" s="1" t="s">
         <v>328</v>
       </c>
@@ -7251,13 +7400,13 @@
       <c r="O50" s="1">
         <v>0</v>
       </c>
-      <c r="P50" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="5">
-        <v>0</v>
-      </c>
-      <c r="R50" s="5">
+      <c r="P50" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="7">
+        <v>0</v>
+      </c>
+      <c r="R50" s="7">
         <v>0</v>
       </c>
       <c r="S50" s="1" t="s">
@@ -7266,14 +7415,14 @@
       <c r="T50" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
+      <c r="U50" s="5"/>
+      <c r="V50" s="5"/>
+      <c r="W50" s="5"/>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5"/>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A51" s="3"/>
+      <c r="A51" s="5"/>
       <c r="C51" s="1" t="s">
         <v>335</v>
       </c>
@@ -7317,13 +7466,13 @@
         <f t="shared" ref="O51:O65" si="3">(D51-1044)*5</f>
         <v>5</v>
       </c>
-      <c r="P51" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="5">
-        <v>0</v>
-      </c>
-      <c r="R51" s="5">
+      <c r="P51" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="7">
+        <v>0</v>
+      </c>
+      <c r="R51" s="7">
         <v>0</v>
       </c>
       <c r="S51" s="1" t="s">
@@ -7332,14 +7481,14 @@
       <c r="T51" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5"/>
+      <c r="W51" s="5"/>
+      <c r="X51" s="5"/>
+      <c r="Y51" s="5"/>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A52" s="3"/>
+      <c r="A52" s="5"/>
       <c r="C52" s="1" t="s">
         <v>342</v>
       </c>
@@ -7383,13 +7532,13 @@
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="P52" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="5">
-        <v>0</v>
-      </c>
-      <c r="R52" s="5">
+      <c r="P52" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="7">
+        <v>0</v>
+      </c>
+      <c r="R52" s="7">
         <v>0</v>
       </c>
       <c r="S52" s="1" t="s">
@@ -7398,14 +7547,14 @@
       <c r="T52" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="U52" s="3"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
+      <c r="U52" s="5"/>
+      <c r="V52" s="5"/>
+      <c r="W52" s="5"/>
+      <c r="X52" s="5"/>
+      <c r="Y52" s="5"/>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A53" s="3"/>
+      <c r="A53" s="5"/>
       <c r="C53" s="1" t="s">
         <v>349</v>
       </c>
@@ -7449,13 +7598,13 @@
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="P53" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="5">
-        <v>0</v>
-      </c>
-      <c r="R53" s="5">
+      <c r="P53" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="7">
+        <v>0</v>
+      </c>
+      <c r="R53" s="7">
         <v>0</v>
       </c>
       <c r="S53" s="1" t="s">
@@ -7464,14 +7613,14 @@
       <c r="T53" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3"/>
-      <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
+      <c r="U53" s="5"/>
+      <c r="V53" s="5"/>
+      <c r="W53" s="5"/>
+      <c r="X53" s="5"/>
+      <c r="Y53" s="5"/>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A54" s="3"/>
+      <c r="A54" s="5"/>
       <c r="C54" s="1" t="s">
         <v>356</v>
       </c>
@@ -7515,13 +7664,13 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="P54" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="5">
-        <v>0</v>
-      </c>
-      <c r="R54" s="5">
+      <c r="P54" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="7">
+        <v>0</v>
+      </c>
+      <c r="R54" s="7">
         <v>0</v>
       </c>
       <c r="S54" s="1" t="s">
@@ -7530,14 +7679,14 @@
       <c r="T54" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="U54" s="3"/>
-      <c r="V54" s="3"/>
-      <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
+      <c r="U54" s="5"/>
+      <c r="V54" s="5"/>
+      <c r="W54" s="5"/>
+      <c r="X54" s="5"/>
+      <c r="Y54" s="5"/>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A55" s="3"/>
+      <c r="A55" s="5"/>
       <c r="C55" s="1" t="s">
         <v>363</v>
       </c>
@@ -7581,13 +7730,13 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="P55" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="5">
-        <v>0</v>
-      </c>
-      <c r="R55" s="5">
+      <c r="P55" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="7">
+        <v>0</v>
+      </c>
+      <c r="R55" s="7">
         <v>0</v>
       </c>
       <c r="S55" s="1" t="s">
@@ -7596,14 +7745,14 @@
       <c r="T55" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
+      <c r="U55" s="5"/>
+      <c r="V55" s="5"/>
+      <c r="W55" s="5"/>
+      <c r="X55" s="5"/>
+      <c r="Y55" s="5"/>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A56" s="3"/>
+      <c r="A56" s="5"/>
       <c r="C56" s="1" t="s">
         <v>370</v>
       </c>
@@ -7647,13 +7796,13 @@
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="P56" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="5">
-        <v>0</v>
-      </c>
-      <c r="R56" s="5">
+      <c r="P56" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="7">
+        <v>0</v>
+      </c>
+      <c r="R56" s="7">
         <v>0</v>
       </c>
       <c r="S56" s="1" t="s">
@@ -7662,14 +7811,14 @@
       <c r="T56" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
-      <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
+      <c r="U56" s="5"/>
+      <c r="V56" s="5"/>
+      <c r="W56" s="5"/>
+      <c r="X56" s="5"/>
+      <c r="Y56" s="5"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A57" s="3"/>
+      <c r="A57" s="5"/>
       <c r="C57" s="1" t="s">
         <v>377</v>
       </c>
@@ -7713,13 +7862,13 @@
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="P57" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="5">
-        <v>0</v>
-      </c>
-      <c r="R57" s="5">
+      <c r="P57" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="7">
+        <v>0</v>
+      </c>
+      <c r="R57" s="7">
         <v>0</v>
       </c>
       <c r="S57" s="1" t="s">
@@ -7728,14 +7877,14 @@
       <c r="T57" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="U57" s="3"/>
-      <c r="V57" s="3"/>
-      <c r="W57" s="3"/>
-      <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
+      <c r="U57" s="5"/>
+      <c r="V57" s="5"/>
+      <c r="W57" s="5"/>
+      <c r="X57" s="5"/>
+      <c r="Y57" s="5"/>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A58" s="3"/>
+      <c r="A58" s="5"/>
       <c r="C58" s="1" t="s">
         <v>384</v>
       </c>
@@ -7779,13 +7928,13 @@
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="P58" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="5">
-        <v>0</v>
-      </c>
-      <c r="R58" s="5">
+      <c r="P58" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="7">
+        <v>0</v>
+      </c>
+      <c r="R58" s="7">
         <v>0</v>
       </c>
       <c r="S58" s="1" t="s">
@@ -7794,14 +7943,14 @@
       <c r="T58" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="U58" s="3"/>
-      <c r="V58" s="3"/>
-      <c r="W58" s="3"/>
-      <c r="X58" s="3"/>
-      <c r="Y58" s="3"/>
+      <c r="U58" s="5"/>
+      <c r="V58" s="5"/>
+      <c r="W58" s="5"/>
+      <c r="X58" s="5"/>
+      <c r="Y58" s="5"/>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A59" s="3"/>
+      <c r="A59" s="5"/>
       <c r="C59" s="1" t="s">
         <v>391</v>
       </c>
@@ -7845,13 +7994,13 @@
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="P59" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="5">
-        <v>0</v>
-      </c>
-      <c r="R59" s="5">
+      <c r="P59" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="7">
+        <v>0</v>
+      </c>
+      <c r="R59" s="7">
         <v>0</v>
       </c>
       <c r="S59" s="1" t="s">
@@ -7860,14 +8009,14 @@
       <c r="T59" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
-      <c r="W59" s="3"/>
-      <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
+      <c r="U59" s="5"/>
+      <c r="V59" s="5"/>
+      <c r="W59" s="5"/>
+      <c r="X59" s="5"/>
+      <c r="Y59" s="5"/>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A60" s="3"/>
+      <c r="A60" s="5"/>
       <c r="C60" s="1" t="s">
         <v>398</v>
       </c>
@@ -7911,13 +8060,13 @@
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="P60" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="5">
-        <v>0</v>
-      </c>
-      <c r="R60" s="5">
+      <c r="P60" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="7">
+        <v>0</v>
+      </c>
+      <c r="R60" s="7">
         <v>0</v>
       </c>
       <c r="S60" s="1" t="s">
@@ -7926,14 +8075,14 @@
       <c r="T60" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="U60" s="3"/>
-      <c r="V60" s="3"/>
-      <c r="W60" s="3"/>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
+      <c r="U60" s="5"/>
+      <c r="V60" s="5"/>
+      <c r="W60" s="5"/>
+      <c r="X60" s="5"/>
+      <c r="Y60" s="5"/>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A61" s="3"/>
+      <c r="A61" s="5"/>
       <c r="C61" s="1" t="s">
         <v>405</v>
       </c>
@@ -7977,13 +8126,13 @@
         <f t="shared" si="3"/>
         <v>55</v>
       </c>
-      <c r="P61" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="5">
-        <v>0</v>
-      </c>
-      <c r="R61" s="5">
+      <c r="P61" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="7">
+        <v>0</v>
+      </c>
+      <c r="R61" s="7">
         <v>0</v>
       </c>
       <c r="S61" s="1" t="s">
@@ -7992,14 +8141,14 @@
       <c r="T61" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="U61" s="3"/>
-      <c r="V61" s="3"/>
-      <c r="W61" s="3"/>
-      <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
+      <c r="U61" s="5"/>
+      <c r="V61" s="5"/>
+      <c r="W61" s="5"/>
+      <c r="X61" s="5"/>
+      <c r="Y61" s="5"/>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A62" s="3"/>
+      <c r="A62" s="5"/>
       <c r="C62" s="1" t="s">
         <v>412</v>
       </c>
@@ -8043,13 +8192,13 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="P62" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="5">
-        <v>0</v>
-      </c>
-      <c r="R62" s="5">
+      <c r="P62" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="7">
+        <v>0</v>
+      </c>
+      <c r="R62" s="7">
         <v>0</v>
       </c>
       <c r="S62" s="1" t="s">
@@ -8058,14 +8207,14 @@
       <c r="T62" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="U62" s="3"/>
-      <c r="V62" s="3"/>
-      <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
+      <c r="U62" s="5"/>
+      <c r="V62" s="5"/>
+      <c r="W62" s="5"/>
+      <c r="X62" s="5"/>
+      <c r="Y62" s="5"/>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A63" s="3"/>
+      <c r="A63" s="5"/>
       <c r="C63" s="1" t="s">
         <v>419</v>
       </c>
@@ -8109,13 +8258,13 @@
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
-      <c r="P63" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="5">
-        <v>0</v>
-      </c>
-      <c r="R63" s="5">
+      <c r="P63" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="7">
+        <v>0</v>
+      </c>
+      <c r="R63" s="7">
         <v>0</v>
       </c>
       <c r="S63" s="1" t="s">
@@ -8124,14 +8273,14 @@
       <c r="T63" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="U63" s="3"/>
-      <c r="V63" s="3"/>
-      <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
+      <c r="U63" s="5"/>
+      <c r="V63" s="5"/>
+      <c r="W63" s="5"/>
+      <c r="X63" s="5"/>
+      <c r="Y63" s="5"/>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A64" s="3"/>
+      <c r="A64" s="5"/>
       <c r="C64" s="1" t="s">
         <v>426</v>
       </c>
@@ -8175,13 +8324,13 @@
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-      <c r="P64" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>0</v>
-      </c>
-      <c r="R64" s="5">
+      <c r="P64" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="7">
+        <v>0</v>
+      </c>
+      <c r="R64" s="7">
         <v>0</v>
       </c>
       <c r="S64" s="1" t="s">
@@ -8190,14 +8339,14 @@
       <c r="T64" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="U64" s="3"/>
-      <c r="V64" s="3"/>
-      <c r="W64" s="3"/>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
+      <c r="U64" s="5"/>
+      <c r="V64" s="5"/>
+      <c r="W64" s="5"/>
+      <c r="X64" s="5"/>
+      <c r="Y64" s="5"/>
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A65" s="3"/>
+      <c r="A65" s="5"/>
       <c r="C65" s="1" t="s">
         <v>433</v>
       </c>
@@ -8216,7 +8365,7 @@
       <c r="H65" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="I65" s="14" t="s">
+      <c r="I65" s="20" t="s">
         <v>438</v>
       </c>
       <c r="J65" s="1">
@@ -8241,13 +8390,13 @@
         <f t="shared" si="3"/>
         <v>75</v>
       </c>
-      <c r="P65" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="5">
-        <v>0</v>
-      </c>
-      <c r="R65" s="5">
+      <c r="P65" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="7">
+        <v>0</v>
+      </c>
+      <c r="R65" s="7">
         <v>0</v>
       </c>
       <c r="S65" s="1" t="s">
@@ -8256,14 +8405,14 @@
       <c r="T65" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="U65" s="3"/>
-      <c r="V65" s="3"/>
-      <c r="W65" s="3"/>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
+      <c r="U65" s="5"/>
+      <c r="V65" s="5"/>
+      <c r="W65" s="5"/>
+      <c r="X65" s="5"/>
+      <c r="Y65" s="5"/>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A66" s="3"/>
+      <c r="A66" s="5"/>
       <c r="C66" s="1" t="s">
         <v>440</v>
       </c>
@@ -8282,7 +8431,7 @@
       <c r="H66" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="I66" s="14" t="s">
+      <c r="I66" s="20" t="s">
         <v>445</v>
       </c>
       <c r="J66" s="1">
@@ -8307,13 +8456,13 @@
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="P66" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="5">
-        <v>0</v>
-      </c>
-      <c r="R66" s="5">
+      <c r="P66" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="7">
+        <v>0</v>
+      </c>
+      <c r="R66" s="7">
         <v>0</v>
       </c>
       <c r="S66" s="1" t="s">
@@ -8322,14 +8471,14 @@
       <c r="T66" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="U66" s="3"/>
-      <c r="V66" s="3"/>
-      <c r="W66" s="3"/>
-      <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
+      <c r="U66" s="5"/>
+      <c r="V66" s="5"/>
+      <c r="W66" s="5"/>
+      <c r="X66" s="5"/>
+      <c r="Y66" s="5"/>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A67" s="3"/>
+      <c r="A67" s="5"/>
       <c r="C67" s="1" t="s">
         <v>447</v>
       </c>
@@ -8348,7 +8497,7 @@
       <c r="H67" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="I67" s="14" t="s">
+      <c r="I67" s="20" t="s">
         <v>452</v>
       </c>
       <c r="J67" s="1">
@@ -8373,13 +8522,13 @@
         <f t="shared" ref="O67:O70" si="8">O66+5</f>
         <v>85</v>
       </c>
-      <c r="P67" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="5">
-        <v>0</v>
-      </c>
-      <c r="R67" s="5">
+      <c r="P67" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="7">
+        <v>0</v>
+      </c>
+      <c r="R67" s="7">
         <v>0</v>
       </c>
       <c r="S67" s="1" t="s">
@@ -8388,14 +8537,14 @@
       <c r="T67" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-      <c r="W67" s="3"/>
-      <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
+      <c r="U67" s="5"/>
+      <c r="V67" s="5"/>
+      <c r="W67" s="5"/>
+      <c r="X67" s="5"/>
+      <c r="Y67" s="5"/>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A68" s="3"/>
+      <c r="A68" s="5"/>
       <c r="C68" s="1" t="s">
         <v>454</v>
       </c>
@@ -8414,7 +8563,7 @@
       <c r="H68" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="I68" s="14" t="s">
+      <c r="I68" s="20" t="s">
         <v>459</v>
       </c>
       <c r="J68" s="1">
@@ -8439,13 +8588,13 @@
         <f t="shared" si="8"/>
         <v>90</v>
       </c>
-      <c r="P68" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="5">
-        <v>0</v>
-      </c>
-      <c r="R68" s="5">
+      <c r="P68" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="7">
+        <v>0</v>
+      </c>
+      <c r="R68" s="7">
         <v>0</v>
       </c>
       <c r="S68" s="1" t="s">
@@ -8454,14 +8603,14 @@
       <c r="T68" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="U68" s="3"/>
-      <c r="V68" s="3"/>
-      <c r="W68" s="3"/>
-      <c r="X68" s="3"/>
-      <c r="Y68" s="3"/>
+      <c r="U68" s="5"/>
+      <c r="V68" s="5"/>
+      <c r="W68" s="5"/>
+      <c r="X68" s="5"/>
+      <c r="Y68" s="5"/>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A69" s="3"/>
+      <c r="A69" s="5"/>
       <c r="C69" s="1" t="s">
         <v>461</v>
       </c>
@@ -8477,10 +8626,10 @@
       <c r="G69" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="H69" s="14" t="s">
+      <c r="H69" s="20" t="s">
         <v>465</v>
       </c>
-      <c r="I69" s="14" t="s">
+      <c r="I69" s="20" t="s">
         <v>466</v>
       </c>
       <c r="J69" s="1">
@@ -8505,13 +8654,13 @@
         <f t="shared" si="8"/>
         <v>95</v>
       </c>
-      <c r="P69" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="5">
-        <v>0</v>
-      </c>
-      <c r="R69" s="5">
+      <c r="P69" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="7">
+        <v>0</v>
+      </c>
+      <c r="R69" s="7">
         <v>0</v>
       </c>
       <c r="S69" s="1" t="s">
@@ -8520,14 +8669,14 @@
       <c r="T69" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="U69" s="3"/>
-      <c r="V69" s="3"/>
-      <c r="W69" s="3"/>
-      <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
+      <c r="U69" s="5"/>
+      <c r="V69" s="5"/>
+      <c r="W69" s="5"/>
+      <c r="X69" s="5"/>
+      <c r="Y69" s="5"/>
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A70" s="3"/>
+      <c r="A70" s="5"/>
       <c r="C70" s="1" t="s">
         <v>468</v>
       </c>
@@ -8540,13 +8689,13 @@
       <c r="F70" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="G70" s="14" t="s">
+      <c r="G70" s="20" t="s">
         <v>471</v>
       </c>
-      <c r="H70" s="14" t="s">
+      <c r="H70" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="I70" s="14" t="s">
+      <c r="I70" s="20" t="s">
         <v>473</v>
       </c>
       <c r="J70" s="1">
@@ -8571,13 +8720,13 @@
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="P70" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="5">
-        <v>0</v>
-      </c>
-      <c r="R70" s="5">
+      <c r="P70" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="7">
+        <v>0</v>
+      </c>
+      <c r="R70" s="7">
         <v>0</v>
       </c>
       <c r="S70" s="1" t="s">
@@ -8586,14 +8735,14 @@
       <c r="T70" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="U70" s="3"/>
-      <c r="V70" s="3"/>
-      <c r="W70" s="3"/>
-      <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
+      <c r="U70" s="5"/>
+      <c r="V70" s="5"/>
+      <c r="W70" s="5"/>
+      <c r="X70" s="5"/>
+      <c r="Y70" s="5"/>
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A71" s="3"/>
+      <c r="A71" s="5"/>
       <c r="C71" s="1" t="s">
         <v>475</v>
       </c>
@@ -8606,13 +8755,13 @@
       <c r="F71" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="G71" s="14" t="s">
+      <c r="G71" s="20" t="s">
         <v>478</v>
       </c>
-      <c r="H71" s="14" t="s">
+      <c r="H71" s="20" t="s">
         <v>479</v>
       </c>
-      <c r="I71" s="14" t="s">
+      <c r="I71" s="20" t="s">
         <v>480</v>
       </c>
       <c r="J71" s="1">
@@ -8637,13 +8786,13 @@
         <f t="shared" si="9"/>
         <v>115</v>
       </c>
-      <c r="P71" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="5">
-        <v>0</v>
-      </c>
-      <c r="R71" s="5">
+      <c r="P71" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="7">
+        <v>0</v>
+      </c>
+      <c r="R71" s="7">
         <v>0</v>
       </c>
       <c r="S71" s="1" t="s">
@@ -8652,14 +8801,14 @@
       <c r="T71" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="U71" s="3"/>
-      <c r="V71" s="3"/>
-      <c r="W71" s="3"/>
-      <c r="X71" s="3"/>
-      <c r="Y71" s="3"/>
+      <c r="U71" s="5"/>
+      <c r="V71" s="5"/>
+      <c r="W71" s="5"/>
+      <c r="X71" s="5"/>
+      <c r="Y71" s="5"/>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A72" s="3"/>
+      <c r="A72" s="5"/>
       <c r="C72" s="1" t="s">
         <v>482</v>
       </c>
@@ -8672,13 +8821,13 @@
       <c r="F72" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="G72" s="14" t="s">
+      <c r="G72" s="20" t="s">
         <v>485</v>
       </c>
-      <c r="H72" s="14" t="s">
+      <c r="H72" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="I72" s="14" t="s">
+      <c r="I72" s="20" t="s">
         <v>487</v>
       </c>
       <c r="J72" s="1">
@@ -8703,13 +8852,13 @@
         <f t="shared" ref="O72:O95" si="11">O71+15</f>
         <v>130</v>
       </c>
-      <c r="P72" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>0</v>
-      </c>
-      <c r="R72" s="5">
+      <c r="P72" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="7">
+        <v>0</v>
+      </c>
+      <c r="R72" s="7">
         <v>0</v>
       </c>
       <c r="S72" s="1" t="s">
@@ -8718,14 +8867,14 @@
       <c r="T72" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="U72" s="3"/>
-      <c r="V72" s="3"/>
-      <c r="W72" s="3"/>
-      <c r="X72" s="3"/>
-      <c r="Y72" s="3"/>
+      <c r="U72" s="5"/>
+      <c r="V72" s="5"/>
+      <c r="W72" s="5"/>
+      <c r="X72" s="5"/>
+      <c r="Y72" s="5"/>
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A73" s="3"/>
+      <c r="A73" s="5"/>
       <c r="C73" s="1" t="s">
         <v>489</v>
       </c>
@@ -8738,13 +8887,13 @@
       <c r="F73" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="G73" s="14" t="s">
+      <c r="G73" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="H73" s="14" t="s">
+      <c r="H73" s="20" t="s">
         <v>493</v>
       </c>
-      <c r="I73" s="14" t="s">
+      <c r="I73" s="20" t="s">
         <v>494</v>
       </c>
       <c r="J73" s="1">
@@ -8769,13 +8918,13 @@
         <f t="shared" si="11"/>
         <v>145</v>
       </c>
-      <c r="P73" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="5">
-        <v>0</v>
-      </c>
-      <c r="R73" s="5">
+      <c r="P73" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="7">
+        <v>0</v>
+      </c>
+      <c r="R73" s="7">
         <v>0</v>
       </c>
       <c r="S73" s="1" t="s">
@@ -8784,14 +8933,14 @@
       <c r="T73" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="U73" s="3"/>
-      <c r="V73" s="3"/>
-      <c r="W73" s="3"/>
-      <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
+      <c r="U73" s="5"/>
+      <c r="V73" s="5"/>
+      <c r="W73" s="5"/>
+      <c r="X73" s="5"/>
+      <c r="Y73" s="5"/>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A74" s="3"/>
+      <c r="A74" s="5"/>
       <c r="C74" s="1" t="s">
         <v>496</v>
       </c>
@@ -8804,13 +8953,13 @@
       <c r="F74" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="G74" s="14" t="s">
+      <c r="G74" s="20" t="s">
         <v>499</v>
       </c>
-      <c r="H74" s="14" t="s">
+      <c r="H74" s="20" t="s">
         <v>500</v>
       </c>
-      <c r="I74" s="14" t="s">
+      <c r="I74" s="20" t="s">
         <v>501</v>
       </c>
       <c r="J74" s="1">
@@ -8835,13 +8984,13 @@
         <f t="shared" si="11"/>
         <v>160</v>
       </c>
-      <c r="P74" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>0</v>
-      </c>
-      <c r="R74" s="5">
+      <c r="P74" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="7">
+        <v>0</v>
+      </c>
+      <c r="R74" s="7">
         <v>0</v>
       </c>
       <c r="S74" s="1" t="s">
@@ -8850,14 +8999,14 @@
       <c r="T74" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="U74" s="3"/>
-      <c r="V74" s="3"/>
-      <c r="W74" s="3"/>
-      <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
+      <c r="U74" s="5"/>
+      <c r="V74" s="5"/>
+      <c r="W74" s="5"/>
+      <c r="X74" s="5"/>
+      <c r="Y74" s="5"/>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A75" s="3"/>
+      <c r="A75" s="5"/>
       <c r="C75" s="1" t="s">
         <v>503</v>
       </c>
@@ -8870,13 +9019,13 @@
       <c r="F75" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="G75" s="14" t="s">
+      <c r="G75" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="H75" s="14" t="s">
+      <c r="H75" s="20" t="s">
         <v>507</v>
       </c>
-      <c r="I75" s="14" t="s">
+      <c r="I75" s="20" t="s">
         <v>508</v>
       </c>
       <c r="J75" s="1">
@@ -8901,30 +9050,30 @@
         <f t="shared" si="11"/>
         <v>175</v>
       </c>
-      <c r="P75" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="5">
-        <v>0</v>
-      </c>
-      <c r="R75" s="5">
+      <c r="P75" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="7">
+        <v>0</v>
+      </c>
+      <c r="R75" s="7">
         <v>0</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="T75" s="14" t="s">
+      <c r="T75" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="U75" s="3"/>
-      <c r="V75" s="3"/>
-      <c r="W75" s="3"/>
-      <c r="X75" s="3"/>
-      <c r="Y75" s="3"/>
+      <c r="U75" s="5"/>
+      <c r="V75" s="5"/>
+      <c r="W75" s="5"/>
+      <c r="X75" s="5"/>
+      <c r="Y75" s="5"/>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
       <c r="C76" s="1" t="s">
         <v>510</v>
       </c>
@@ -8937,13 +9086,13 @@
       <c r="F76" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="G76" s="14" t="s">
+      <c r="G76" s="20" t="s">
         <v>513</v>
       </c>
-      <c r="H76" s="14" t="s">
+      <c r="H76" s="20" t="s">
         <v>514</v>
       </c>
-      <c r="I76" s="14" t="s">
+      <c r="I76" s="20" t="s">
         <v>515</v>
       </c>
       <c r="J76" s="1">
@@ -8968,13 +9117,13 @@
         <f t="shared" si="11"/>
         <v>190</v>
       </c>
-      <c r="P76" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="5">
-        <v>0</v>
-      </c>
-      <c r="R76" s="5">
+      <c r="P76" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="7">
+        <v>0</v>
+      </c>
+      <c r="R76" s="7">
         <v>0</v>
       </c>
       <c r="S76" s="1">
@@ -8983,13 +9132,13 @@
       <c r="T76" s="1">
         <v>229385000</v>
       </c>
-      <c r="W76" s="3"/>
-      <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
+      <c r="W76" s="5"/>
+      <c r="X76" s="5"/>
+      <c r="Y76" s="5"/>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
       <c r="C77" s="1" t="s">
         <v>516</v>
       </c>
@@ -9002,13 +9151,13 @@
       <c r="F77" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="G77" s="14" t="s">
+      <c r="G77" s="20" t="s">
         <v>519</v>
       </c>
-      <c r="H77" s="14" t="s">
+      <c r="H77" s="20" t="s">
         <v>520</v>
       </c>
-      <c r="I77" s="14" t="s">
+      <c r="I77" s="20" t="s">
         <v>521</v>
       </c>
       <c r="J77" s="1">
@@ -9033,13 +9182,13 @@
         <f t="shared" si="11"/>
         <v>205</v>
       </c>
-      <c r="P77" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="5">
-        <v>0</v>
-      </c>
-      <c r="R77" s="5">
+      <c r="P77" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="7">
+        <v>0</v>
+      </c>
+      <c r="R77" s="7">
         <v>0</v>
       </c>
       <c r="S77" s="1">
@@ -9048,13 +9197,13 @@
       <c r="T77" s="1">
         <v>239385000</v>
       </c>
-      <c r="W77" s="3"/>
-      <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
+      <c r="W77" s="5"/>
+      <c r="X77" s="5"/>
+      <c r="Y77" s="5"/>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
       <c r="C78" s="1" t="s">
         <v>522</v>
       </c>
@@ -9067,13 +9216,13 @@
       <c r="F78" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G78" s="14" t="s">
+      <c r="G78" s="20" t="s">
         <v>525</v>
       </c>
-      <c r="H78" s="14" t="s">
+      <c r="H78" s="20" t="s">
         <v>526</v>
       </c>
-      <c r="I78" s="14" t="s">
+      <c r="I78" s="20" t="s">
         <v>527</v>
       </c>
       <c r="J78" s="1">
@@ -9098,13 +9247,13 @@
         <f t="shared" si="11"/>
         <v>220</v>
       </c>
-      <c r="P78" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="5">
-        <v>0</v>
-      </c>
-      <c r="R78" s="5">
+      <c r="P78" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="7">
+        <v>0</v>
+      </c>
+      <c r="R78" s="7">
         <v>0</v>
       </c>
       <c r="S78" s="1">
@@ -9113,13 +9262,13 @@
       <c r="T78" s="1">
         <v>249385000</v>
       </c>
-      <c r="W78" s="3"/>
-      <c r="X78" s="3"/>
-      <c r="Y78" s="3"/>
+      <c r="W78" s="5"/>
+      <c r="X78" s="5"/>
+      <c r="Y78" s="5"/>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
       <c r="C79" s="1" t="s">
         <v>528</v>
       </c>
@@ -9132,13 +9281,13 @@
       <c r="F79" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="G79" s="14" t="s">
+      <c r="G79" s="20" t="s">
         <v>531</v>
       </c>
-      <c r="H79" s="14" t="s">
+      <c r="H79" s="20" t="s">
         <v>532</v>
       </c>
-      <c r="I79" s="14" t="s">
+      <c r="I79" s="20" t="s">
         <v>533</v>
       </c>
       <c r="J79" s="1">
@@ -9163,13 +9312,13 @@
         <f t="shared" si="11"/>
         <v>235</v>
       </c>
-      <c r="P79" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="5">
-        <v>0</v>
-      </c>
-      <c r="R79" s="5">
+      <c r="P79" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="7">
+        <v>0</v>
+      </c>
+      <c r="R79" s="7">
         <v>0</v>
       </c>
       <c r="S79" s="1">
@@ -9178,13 +9327,13 @@
       <c r="T79" s="1">
         <v>259385000</v>
       </c>
-      <c r="W79" s="3"/>
-      <c r="X79" s="3"/>
-      <c r="Y79" s="3"/>
+      <c r="W79" s="5"/>
+      <c r="X79" s="5"/>
+      <c r="Y79" s="5"/>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
       <c r="C80" s="1" t="s">
         <v>534</v>
       </c>
@@ -9197,13 +9346,13 @@
       <c r="F80" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="G80" s="14" t="s">
+      <c r="G80" s="20" t="s">
         <v>537</v>
       </c>
-      <c r="H80" s="14" t="s">
+      <c r="H80" s="20" t="s">
         <v>538</v>
       </c>
-      <c r="I80" s="14" t="s">
+      <c r="I80" s="20" t="s">
         <v>539</v>
       </c>
       <c r="J80" s="1">
@@ -9228,13 +9377,13 @@
         <f t="shared" si="11"/>
         <v>250</v>
       </c>
-      <c r="P80" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>0</v>
-      </c>
-      <c r="R80" s="5">
+      <c r="P80" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="7">
+        <v>0</v>
+      </c>
+      <c r="R80" s="7">
         <v>0</v>
       </c>
       <c r="S80" s="1">
@@ -9243,13 +9392,13 @@
       <c r="T80" s="1">
         <v>269385000</v>
       </c>
-      <c r="W80" s="3"/>
-      <c r="X80" s="3"/>
-      <c r="Y80" s="3"/>
+      <c r="W80" s="5"/>
+      <c r="X80" s="5"/>
+      <c r="Y80" s="5"/>
     </row>
     <row r="81" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
+      <c r="A81" s="5"/>
+      <c r="B81" s="5"/>
       <c r="C81" s="1" t="s">
         <v>540</v>
       </c>
@@ -9262,13 +9411,13 @@
       <c r="F81" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="G81" s="14" t="s">
+      <c r="G81" s="20" t="s">
         <v>543</v>
       </c>
-      <c r="H81" s="14" t="s">
+      <c r="H81" s="20" t="s">
         <v>544</v>
       </c>
-      <c r="I81" s="14" t="s">
+      <c r="I81" s="20" t="s">
         <v>545</v>
       </c>
       <c r="J81" s="1">
@@ -9293,13 +9442,13 @@
         <f t="shared" si="11"/>
         <v>265</v>
       </c>
-      <c r="P81" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="5">
-        <v>0</v>
-      </c>
-      <c r="R81" s="5">
+      <c r="P81" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="7">
+        <v>0</v>
+      </c>
+      <c r="R81" s="7">
         <v>0</v>
       </c>
       <c r="S81" s="1">
@@ -9308,15 +9457,15 @@
       <c r="T81" s="1">
         <v>300000000</v>
       </c>
-      <c r="U81" s="3"/>
-      <c r="V81" s="3"/>
-      <c r="W81" s="3"/>
-      <c r="X81" s="3"/>
-      <c r="Y81" s="3"/>
+      <c r="U81" s="5"/>
+      <c r="V81" s="5"/>
+      <c r="W81" s="5"/>
+      <c r="X81" s="5"/>
+      <c r="Y81" s="5"/>
     </row>
     <row r="82" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
+      <c r="A82" s="5"/>
+      <c r="B82" s="5"/>
       <c r="C82" s="1" t="s">
         <v>546</v>
       </c>
@@ -9329,13 +9478,13 @@
       <c r="F82" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="G82" s="14" t="s">
+      <c r="G82" s="20" t="s">
         <v>549</v>
       </c>
-      <c r="H82" s="14" t="s">
+      <c r="H82" s="20" t="s">
         <v>550</v>
       </c>
-      <c r="I82" s="14" t="s">
+      <c r="I82" s="20" t="s">
         <v>551</v>
       </c>
       <c r="J82" s="1">
@@ -9360,13 +9509,13 @@
         <f t="shared" si="11"/>
         <v>280</v>
       </c>
-      <c r="P82" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="5">
-        <v>0</v>
-      </c>
-      <c r="R82" s="5">
+      <c r="P82" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="7">
+        <v>0</v>
+      </c>
+      <c r="R82" s="7">
         <v>0</v>
       </c>
       <c r="S82" s="1">
@@ -9375,15 +9524,15 @@
       <c r="T82" s="1">
         <v>320000000</v>
       </c>
-      <c r="U82" s="3"/>
-      <c r="V82" s="3"/>
-      <c r="W82" s="3"/>
-      <c r="X82" s="3"/>
-      <c r="Y82" s="3"/>
+      <c r="U82" s="5"/>
+      <c r="V82" s="5"/>
+      <c r="W82" s="5"/>
+      <c r="X82" s="5"/>
+      <c r="Y82" s="5"/>
     </row>
     <row r="83" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
+      <c r="A83" s="5"/>
+      <c r="B83" s="5"/>
       <c r="C83" s="1" t="s">
         <v>552</v>
       </c>
@@ -9396,13 +9545,13 @@
       <c r="F83" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="G83" s="14" t="s">
+      <c r="G83" s="20" t="s">
         <v>555</v>
       </c>
-      <c r="H83" s="14" t="s">
+      <c r="H83" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="I83" s="14" t="s">
+      <c r="I83" s="20" t="s">
         <v>557</v>
       </c>
       <c r="J83" s="1">
@@ -9427,13 +9576,13 @@
         <f t="shared" si="11"/>
         <v>295</v>
       </c>
-      <c r="P83" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="5">
-        <v>0</v>
-      </c>
-      <c r="R83" s="5">
+      <c r="P83" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="7">
+        <v>0</v>
+      </c>
+      <c r="R83" s="7">
         <v>0</v>
       </c>
       <c r="S83" s="1">
@@ -9442,15 +9591,15 @@
       <c r="T83" s="1">
         <v>340000000</v>
       </c>
-      <c r="U83" s="3"/>
-      <c r="V83" s="3"/>
-      <c r="W83" s="3"/>
-      <c r="X83" s="3"/>
-      <c r="Y83" s="3"/>
+      <c r="U83" s="5"/>
+      <c r="V83" s="5"/>
+      <c r="W83" s="5"/>
+      <c r="X83" s="5"/>
+      <c r="Y83" s="5"/>
     </row>
     <row r="84" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
+      <c r="A84" s="5"/>
+      <c r="B84" s="5"/>
       <c r="C84" s="1" t="s">
         <v>558</v>
       </c>
@@ -9463,13 +9612,13 @@
       <c r="F84" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="G84" s="14" t="s">
+      <c r="G84" s="20" t="s">
         <v>561</v>
       </c>
-      <c r="H84" s="14" t="s">
+      <c r="H84" s="20" t="s">
         <v>562</v>
       </c>
-      <c r="I84" s="14" t="s">
+      <c r="I84" s="20" t="s">
         <v>563</v>
       </c>
       <c r="J84" s="1">
@@ -9494,13 +9643,13 @@
         <f t="shared" si="11"/>
         <v>310</v>
       </c>
-      <c r="P84" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="5">
-        <v>0</v>
-      </c>
-      <c r="R84" s="5">
+      <c r="P84" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="7">
+        <v>0</v>
+      </c>
+      <c r="R84" s="7">
         <v>0</v>
       </c>
       <c r="S84" s="1">
@@ -9509,15 +9658,15 @@
       <c r="T84" s="1">
         <v>370000000</v>
       </c>
-      <c r="U84" s="3"/>
-      <c r="V84" s="3"/>
-      <c r="W84" s="3"/>
-      <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
+      <c r="U84" s="5"/>
+      <c r="V84" s="5"/>
+      <c r="W84" s="5"/>
+      <c r="X84" s="5"/>
+      <c r="Y84" s="5"/>
     </row>
     <row r="85" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
+      <c r="A85" s="5"/>
+      <c r="B85" s="5"/>
       <c r="C85" s="1" t="s">
         <v>564</v>
       </c>
@@ -9530,13 +9679,13 @@
       <c r="F85" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="G85" s="14" t="s">
+      <c r="G85" s="20" t="s">
         <v>567</v>
       </c>
-      <c r="H85" s="14" t="s">
+      <c r="H85" s="20" t="s">
         <v>568</v>
       </c>
-      <c r="I85" s="14" t="s">
+      <c r="I85" s="20" t="s">
         <v>569</v>
       </c>
       <c r="J85" s="1">
@@ -9561,13 +9710,13 @@
         <f t="shared" si="11"/>
         <v>325</v>
       </c>
-      <c r="P85" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="5">
-        <v>0</v>
-      </c>
-      <c r="R85" s="5">
+      <c r="P85" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="7">
+        <v>0</v>
+      </c>
+      <c r="R85" s="7">
         <v>0</v>
       </c>
       <c r="S85" s="1">
@@ -9576,15 +9725,15 @@
       <c r="T85" s="1">
         <v>400000000</v>
       </c>
-      <c r="U85" s="3"/>
-      <c r="V85" s="3"/>
-      <c r="W85" s="3"/>
-      <c r="X85" s="3"/>
-      <c r="Y85" s="3"/>
+      <c r="U85" s="5"/>
+      <c r="V85" s="5"/>
+      <c r="W85" s="5"/>
+      <c r="X85" s="5"/>
+      <c r="Y85" s="5"/>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
+      <c r="A86" s="5"/>
+      <c r="B86" s="5"/>
       <c r="C86" s="1" t="s">
         <v>570</v>
       </c>
@@ -9597,13 +9746,13 @@
       <c r="F86" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="G86" s="14" t="s">
+      <c r="G86" s="20" t="s">
         <v>573</v>
       </c>
-      <c r="H86" s="14" t="s">
+      <c r="H86" s="20" t="s">
         <v>537</v>
       </c>
-      <c r="I86" s="14" t="s">
+      <c r="I86" s="20" t="s">
         <v>574</v>
       </c>
       <c r="J86" s="1">
@@ -9628,13 +9777,13 @@
         <f t="shared" si="11"/>
         <v>340</v>
       </c>
-      <c r="P86" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="5">
-        <v>0</v>
-      </c>
-      <c r="R86" s="5">
+      <c r="P86" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="7">
+        <v>0</v>
+      </c>
+      <c r="R86" s="7">
         <v>0</v>
       </c>
       <c r="S86" s="1">
@@ -9643,15 +9792,15 @@
       <c r="T86" s="1">
         <v>500000000</v>
       </c>
-      <c r="U86" s="3"/>
-      <c r="V86" s="3"/>
-      <c r="W86" s="3"/>
-      <c r="X86" s="3"/>
-      <c r="Y86" s="3"/>
+      <c r="U86" s="5"/>
+      <c r="V86" s="5"/>
+      <c r="W86" s="5"/>
+      <c r="X86" s="5"/>
+      <c r="Y86" s="5"/>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
+      <c r="A87" s="5"/>
+      <c r="B87" s="5"/>
       <c r="C87" s="1" t="s">
         <v>575</v>
       </c>
@@ -9664,13 +9813,13 @@
       <c r="F87" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="G87" s="14" t="s">
+      <c r="G87" s="20" t="s">
         <v>578</v>
       </c>
-      <c r="H87" s="14" t="s">
+      <c r="H87" s="20" t="s">
         <v>579</v>
       </c>
-      <c r="I87" s="14" t="s">
+      <c r="I87" s="20" t="s">
         <v>580</v>
       </c>
       <c r="J87" s="1">
@@ -9695,13 +9844,13 @@
         <f t="shared" si="11"/>
         <v>355</v>
       </c>
-      <c r="P87" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="5">
-        <v>0</v>
-      </c>
-      <c r="R87" s="5">
+      <c r="P87" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="7">
+        <v>0</v>
+      </c>
+      <c r="R87" s="7">
         <v>0</v>
       </c>
       <c r="S87" s="1">
@@ -9710,15 +9859,15 @@
       <c r="T87" s="1">
         <v>600000000</v>
       </c>
-      <c r="U87" s="3"/>
-      <c r="V87" s="3"/>
-      <c r="W87" s="3"/>
-      <c r="X87" s="3"/>
-      <c r="Y87" s="3"/>
+      <c r="U87" s="5"/>
+      <c r="V87" s="5"/>
+      <c r="W87" s="5"/>
+      <c r="X87" s="5"/>
+      <c r="Y87" s="5"/>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
+      <c r="A88" s="5"/>
+      <c r="B88" s="5"/>
       <c r="C88" s="1" t="s">
         <v>581</v>
       </c>
@@ -9731,13 +9880,13 @@
       <c r="F88" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="G88" s="14" t="s">
+      <c r="G88" s="20" t="s">
         <v>487</v>
       </c>
-      <c r="H88" s="14" t="s">
+      <c r="H88" s="20" t="s">
         <v>452</v>
       </c>
-      <c r="I88" s="14" t="s">
+      <c r="I88" s="20" t="s">
         <v>584</v>
       </c>
       <c r="J88" s="1">
@@ -9762,13 +9911,13 @@
         <f t="shared" si="11"/>
         <v>370</v>
       </c>
-      <c r="P88" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="5">
-        <v>0</v>
-      </c>
-      <c r="R88" s="5">
+      <c r="P88" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="7">
+        <v>0</v>
+      </c>
+      <c r="R88" s="7">
         <v>0</v>
       </c>
       <c r="S88" s="1">
@@ -9777,15 +9926,15 @@
       <c r="T88" s="1">
         <v>700000000</v>
       </c>
-      <c r="U88" s="3"/>
-      <c r="V88" s="3"/>
-      <c r="W88" s="3"/>
-      <c r="X88" s="3"/>
-      <c r="Y88" s="3"/>
+      <c r="U88" s="5"/>
+      <c r="V88" s="5"/>
+      <c r="W88" s="5"/>
+      <c r="X88" s="5"/>
+      <c r="Y88" s="5"/>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
+      <c r="A89" s="5"/>
+      <c r="B89" s="5"/>
       <c r="C89" s="1" t="s">
         <v>585</v>
       </c>
@@ -9798,13 +9947,13 @@
       <c r="F89" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="G89" s="14" t="s">
+      <c r="G89" s="20" t="s">
         <v>501</v>
       </c>
-      <c r="H89" s="14" t="s">
+      <c r="H89" s="20" t="s">
         <v>588</v>
       </c>
-      <c r="I89" s="14" t="s">
+      <c r="I89" s="20" t="s">
         <v>589</v>
       </c>
       <c r="J89" s="1">
@@ -9829,13 +9978,13 @@
         <f t="shared" si="11"/>
         <v>385</v>
       </c>
-      <c r="P89" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="5">
-        <v>0</v>
-      </c>
-      <c r="R89" s="5">
+      <c r="P89" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="7">
+        <v>0</v>
+      </c>
+      <c r="R89" s="7">
         <v>0</v>
       </c>
       <c r="S89" s="1">
@@ -9844,15 +9993,15 @@
       <c r="T89" s="1">
         <v>800000000</v>
       </c>
-      <c r="U89" s="3"/>
-      <c r="V89" s="3"/>
-      <c r="W89" s="3"/>
-      <c r="X89" s="3"/>
-      <c r="Y89" s="3"/>
+      <c r="U89" s="5"/>
+      <c r="V89" s="5"/>
+      <c r="W89" s="5"/>
+      <c r="X89" s="5"/>
+      <c r="Y89" s="5"/>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
+      <c r="A90" s="5"/>
+      <c r="B90" s="5"/>
       <c r="C90" s="1" t="s">
         <v>590</v>
       </c>
@@ -9865,13 +10014,13 @@
       <c r="F90" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="G90" s="14" t="s">
+      <c r="G90" s="20" t="s">
         <v>593</v>
       </c>
-      <c r="H90" s="14" t="s">
+      <c r="H90" s="20" t="s">
         <v>578</v>
       </c>
-      <c r="I90" s="14" t="s">
+      <c r="I90" s="20" t="s">
         <v>594</v>
       </c>
       <c r="J90" s="1">
@@ -9896,13 +10045,13 @@
         <f t="shared" si="11"/>
         <v>400</v>
       </c>
-      <c r="P90" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="5">
-        <v>0</v>
-      </c>
-      <c r="R90" s="5">
+      <c r="P90" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="7">
+        <v>0</v>
+      </c>
+      <c r="R90" s="7">
         <v>0</v>
       </c>
       <c r="S90" s="1">
@@ -9911,15 +10060,15 @@
       <c r="T90" s="1">
         <v>1000000000</v>
       </c>
-      <c r="U90" s="3"/>
-      <c r="V90" s="3"/>
-      <c r="W90" s="3"/>
-      <c r="X90" s="3"/>
-      <c r="Y90" s="3"/>
+      <c r="U90" s="5"/>
+      <c r="V90" s="5"/>
+      <c r="W90" s="5"/>
+      <c r="X90" s="5"/>
+      <c r="Y90" s="5"/>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
+      <c r="A91" s="5"/>
+      <c r="B91" s="5"/>
       <c r="C91" s="1" t="s">
         <v>595</v>
       </c>
@@ -9932,13 +10081,13 @@
       <c r="F91" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="G91" s="14" t="s">
+      <c r="G91" s="20" t="s">
         <v>598</v>
       </c>
-      <c r="H91" s="14" t="s">
+      <c r="H91" s="20" t="s">
         <v>599</v>
       </c>
-      <c r="I91" s="14" t="s">
+      <c r="I91" s="20" t="s">
         <v>600</v>
       </c>
       <c r="J91" s="1">
@@ -9963,13 +10112,13 @@
         <f t="shared" ref="O91:O96" si="18">O90+20</f>
         <v>420</v>
       </c>
-      <c r="P91" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="5">
-        <v>0</v>
-      </c>
-      <c r="R91" s="5">
+      <c r="P91" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="7">
+        <v>0</v>
+      </c>
+      <c r="R91" s="7">
         <v>0</v>
       </c>
       <c r="S91" s="1">
@@ -9978,15 +10127,15 @@
       <c r="T91" s="1">
         <v>1100000000</v>
       </c>
-      <c r="U91" s="3"/>
-      <c r="V91" s="3"/>
-      <c r="W91" s="3"/>
-      <c r="X91" s="3"/>
-      <c r="Y91" s="3"/>
+      <c r="U91" s="5"/>
+      <c r="V91" s="5"/>
+      <c r="W91" s="5"/>
+      <c r="X91" s="5"/>
+      <c r="Y91" s="5"/>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
+      <c r="A92" s="5"/>
+      <c r="B92" s="5"/>
       <c r="C92" s="1" t="s">
         <v>601</v>
       </c>
@@ -9999,13 +10148,13 @@
       <c r="F92" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="G92" s="14" t="s">
+      <c r="G92" s="20" t="s">
         <v>604</v>
       </c>
-      <c r="H92" s="14" t="s">
+      <c r="H92" s="20" t="s">
         <v>605</v>
       </c>
-      <c r="I92" s="14" t="s">
+      <c r="I92" s="20" t="s">
         <v>606</v>
       </c>
       <c r="J92" s="1">
@@ -10030,13 +10179,13 @@
         <f t="shared" si="18"/>
         <v>440</v>
       </c>
-      <c r="P92" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="5">
-        <v>0</v>
-      </c>
-      <c r="R92" s="5">
+      <c r="P92" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="7">
+        <v>0</v>
+      </c>
+      <c r="R92" s="7">
         <v>0</v>
       </c>
       <c r="S92" s="1">
@@ -10045,15 +10194,15 @@
       <c r="T92" s="1">
         <v>1200000000</v>
       </c>
-      <c r="U92" s="3"/>
-      <c r="V92" s="3"/>
-      <c r="W92" s="3"/>
-      <c r="X92" s="3"/>
-      <c r="Y92" s="3"/>
+      <c r="U92" s="5"/>
+      <c r="V92" s="5"/>
+      <c r="W92" s="5"/>
+      <c r="X92" s="5"/>
+      <c r="Y92" s="5"/>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
+      <c r="A93" s="5"/>
+      <c r="B93" s="5"/>
       <c r="C93" s="1" t="s">
         <v>607</v>
       </c>
@@ -10066,13 +10215,13 @@
       <c r="F93" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="G93" s="14" t="s">
+      <c r="G93" s="20" t="s">
         <v>610</v>
       </c>
-      <c r="H93" s="14" t="s">
+      <c r="H93" s="20" t="s">
         <v>611</v>
       </c>
-      <c r="I93" s="14" t="s">
+      <c r="I93" s="20" t="s">
         <v>612</v>
       </c>
       <c r="J93" s="1">
@@ -10097,13 +10246,13 @@
         <f t="shared" si="18"/>
         <v>460</v>
       </c>
-      <c r="P93" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q93" s="5">
-        <v>0</v>
-      </c>
-      <c r="R93" s="5">
+      <c r="P93" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="7">
+        <v>0</v>
+      </c>
+      <c r="R93" s="7">
         <v>0</v>
       </c>
       <c r="S93" s="1">
@@ -10112,15 +10261,15 @@
       <c r="T93" s="1">
         <v>1300000000</v>
       </c>
-      <c r="U93" s="3"/>
-      <c r="V93" s="3"/>
-      <c r="W93" s="3"/>
-      <c r="X93" s="3"/>
-      <c r="Y93" s="3"/>
+      <c r="U93" s="5"/>
+      <c r="V93" s="5"/>
+      <c r="W93" s="5"/>
+      <c r="X93" s="5"/>
+      <c r="Y93" s="5"/>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
+      <c r="A94" s="5"/>
+      <c r="B94" s="5"/>
       <c r="C94" s="1" t="s">
         <v>613</v>
       </c>
@@ -10133,13 +10282,13 @@
       <c r="F94" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="G94" s="14" t="s">
+      <c r="G94" s="20" t="s">
         <v>569</v>
       </c>
-      <c r="H94" s="14" t="s">
+      <c r="H94" s="20" t="s">
         <v>616</v>
       </c>
-      <c r="I94" s="14" t="s">
+      <c r="I94" s="20" t="s">
         <v>617</v>
       </c>
       <c r="J94" s="1">
@@ -10164,13 +10313,13 @@
         <f t="shared" si="18"/>
         <v>480</v>
       </c>
-      <c r="P94" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="5">
-        <v>0</v>
-      </c>
-      <c r="R94" s="5">
+      <c r="P94" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="7">
+        <v>0</v>
+      </c>
+      <c r="R94" s="7">
         <v>0</v>
       </c>
       <c r="S94" s="1">
@@ -10179,15 +10328,15 @@
       <c r="T94" s="1">
         <v>1400000000</v>
       </c>
-      <c r="U94" s="3"/>
-      <c r="V94" s="3"/>
-      <c r="W94" s="3"/>
-      <c r="X94" s="3"/>
-      <c r="Y94" s="3"/>
+      <c r="U94" s="5"/>
+      <c r="V94" s="5"/>
+      <c r="W94" s="5"/>
+      <c r="X94" s="5"/>
+      <c r="Y94" s="5"/>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
       <c r="C95" s="1" t="s">
         <v>618</v>
       </c>
@@ -10200,13 +10349,13 @@
       <c r="F95" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="G95" s="14" t="s">
+      <c r="G95" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="H95" s="14" t="s">
+      <c r="H95" s="20" t="s">
         <v>621</v>
       </c>
-      <c r="I95" s="14" t="s">
+      <c r="I95" s="20" t="s">
         <v>622</v>
       </c>
       <c r="J95" s="1">
@@ -10231,13 +10380,13 @@
         <f t="shared" si="18"/>
         <v>500</v>
       </c>
-      <c r="P95" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="5">
-        <v>0</v>
-      </c>
-      <c r="R95" s="5">
+      <c r="P95" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="7">
+        <v>0</v>
+      </c>
+      <c r="R95" s="7">
         <v>0</v>
       </c>
       <c r="S95" s="1">
@@ -10246,11 +10395,11 @@
       <c r="T95" s="1">
         <v>1500000000</v>
       </c>
-      <c r="U95" s="3"/>
-      <c r="V95" s="3"/>
-      <c r="W95" s="3"/>
-      <c r="X95" s="3"/>
-      <c r="Y95" s="3"/>
+      <c r="U95" s="5"/>
+      <c r="V95" s="5"/>
+      <c r="W95" s="5"/>
+      <c r="X95" s="5"/>
+      <c r="Y95" s="5"/>
     </row>
     <row r="96" customHeight="1" spans="3:20">
       <c r="C96" s="1" t="s">
@@ -10265,13 +10414,13 @@
       <c r="F96" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G96" s="14" t="s">
+      <c r="G96" s="20" t="s">
         <v>580</v>
       </c>
-      <c r="H96" s="14" t="s">
+      <c r="H96" s="20" t="s">
         <v>626</v>
       </c>
-      <c r="I96" s="14" t="s">
+      <c r="I96" s="20" t="s">
         <v>627</v>
       </c>
       <c r="J96" s="1">
@@ -10296,13 +10445,13 @@
         <f t="shared" ref="O96:O105" si="22">O95+30</f>
         <v>530</v>
       </c>
-      <c r="P96" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="5">
-        <v>0</v>
-      </c>
-      <c r="R96" s="5">
+      <c r="P96" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="7">
+        <v>0</v>
+      </c>
+      <c r="R96" s="7">
         <v>0</v>
       </c>
       <c r="S96" s="1">
@@ -10325,13 +10474,13 @@
       <c r="F97" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="G97" s="14" t="s">
+      <c r="G97" s="20" t="s">
         <v>584</v>
       </c>
-      <c r="H97" s="14" t="s">
+      <c r="H97" s="20" t="s">
         <v>631</v>
       </c>
-      <c r="I97" s="14" t="s">
+      <c r="I97" s="20" t="s">
         <v>632</v>
       </c>
       <c r="J97" s="1">
@@ -10356,13 +10505,13 @@
         <f t="shared" si="22"/>
         <v>560</v>
       </c>
-      <c r="P97" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="5">
-        <v>0</v>
-      </c>
-      <c r="R97" s="5">
+      <c r="P97" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="7">
+        <v>0</v>
+      </c>
+      <c r="R97" s="7">
         <v>0</v>
       </c>
       <c r="S97" s="1">
@@ -10385,13 +10534,13 @@
       <c r="F98" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="G98" s="14" t="s">
+      <c r="G98" s="20" t="s">
         <v>636</v>
       </c>
-      <c r="H98" s="14" t="s">
+      <c r="H98" s="20" t="s">
         <v>637</v>
       </c>
-      <c r="I98" s="14" t="s">
+      <c r="I98" s="20" t="s">
         <v>638</v>
       </c>
       <c r="J98" s="1">
@@ -10416,13 +10565,13 @@
         <f t="shared" si="22"/>
         <v>590</v>
       </c>
-      <c r="P98" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="5">
-        <v>0</v>
-      </c>
-      <c r="R98" s="5">
+      <c r="P98" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="7">
+        <v>0</v>
+      </c>
+      <c r="R98" s="7">
         <v>0</v>
       </c>
       <c r="S98" s="1">
@@ -10445,13 +10594,13 @@
       <c r="F99" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="G99" s="14" t="s">
+      <c r="G99" s="20" t="s">
         <v>642</v>
       </c>
-      <c r="H99" s="14" t="s">
+      <c r="H99" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="I99" s="14" t="s">
+      <c r="I99" s="20" t="s">
         <v>644</v>
       </c>
       <c r="J99" s="1">
@@ -10476,13 +10625,13 @@
         <f t="shared" si="22"/>
         <v>620</v>
       </c>
-      <c r="P99" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="5">
-        <v>0</v>
-      </c>
-      <c r="R99" s="5">
+      <c r="P99" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="7">
+        <v>0</v>
+      </c>
+      <c r="R99" s="7">
         <v>0</v>
       </c>
       <c r="S99" s="1">
@@ -10505,13 +10654,13 @@
       <c r="F100" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="G100" s="14" t="s">
+      <c r="G100" s="20" t="s">
         <v>648</v>
       </c>
-      <c r="H100" s="14" t="s">
+      <c r="H100" s="20" t="s">
         <v>649</v>
       </c>
-      <c r="I100" s="14" t="s">
+      <c r="I100" s="20" t="s">
         <v>650</v>
       </c>
       <c r="J100" s="1">
@@ -10536,13 +10685,13 @@
         <f t="shared" si="22"/>
         <v>650</v>
       </c>
-      <c r="P100" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="5">
-        <v>0</v>
-      </c>
-      <c r="R100" s="5">
+      <c r="P100" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="7">
+        <v>0</v>
+      </c>
+      <c r="R100" s="7">
         <v>0</v>
       </c>
       <c r="S100" s="1">
@@ -10565,13 +10714,13 @@
       <c r="F101" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="G101" s="14" t="s">
+      <c r="G101" s="20" t="s">
         <v>654</v>
       </c>
-      <c r="H101" s="14" t="s">
+      <c r="H101" s="20" t="s">
         <v>655</v>
       </c>
-      <c r="I101" s="14" t="s">
+      <c r="I101" s="20" t="s">
         <v>656</v>
       </c>
       <c r="J101" s="1">
@@ -10596,13 +10745,13 @@
         <f t="shared" si="22"/>
         <v>680</v>
       </c>
-      <c r="P101" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="5">
-        <v>0</v>
-      </c>
-      <c r="R101" s="5">
+      <c r="P101" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="7">
+        <v>0</v>
+      </c>
+      <c r="R101" s="7">
         <v>0</v>
       </c>
       <c r="S101" s="1">
@@ -10625,13 +10774,13 @@
       <c r="F102" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="G102" s="14" t="s">
+      <c r="G102" s="20" t="s">
         <v>660</v>
       </c>
-      <c r="H102" s="14" t="s">
+      <c r="H102" s="20" t="s">
         <v>661</v>
       </c>
-      <c r="I102" s="14" t="s">
+      <c r="I102" s="20" t="s">
         <v>662</v>
       </c>
       <c r="J102" s="1">
@@ -10656,13 +10805,13 @@
         <f t="shared" si="22"/>
         <v>710</v>
       </c>
-      <c r="P102" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="5">
-        <v>0</v>
-      </c>
-      <c r="R102" s="5">
+      <c r="P102" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="7">
+        <v>0</v>
+      </c>
+      <c r="R102" s="7">
         <v>0</v>
       </c>
       <c r="S102" s="1">
@@ -10685,13 +10834,13 @@
       <c r="F103" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="G103" s="14" t="s">
+      <c r="G103" s="20" t="s">
         <v>666</v>
       </c>
-      <c r="H103" s="14" t="s">
+      <c r="H103" s="20" t="s">
         <v>667</v>
       </c>
-      <c r="I103" s="14" t="s">
+      <c r="I103" s="20" t="s">
         <v>668</v>
       </c>
       <c r="J103" s="1">
@@ -10716,13 +10865,13 @@
         <f t="shared" si="22"/>
         <v>740</v>
       </c>
-      <c r="P103" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="5">
-        <v>0</v>
-      </c>
-      <c r="R103" s="5">
+      <c r="P103" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="7">
+        <v>0</v>
+      </c>
+      <c r="R103" s="7">
         <v>0</v>
       </c>
       <c r="S103" s="1">
@@ -10745,13 +10894,13 @@
       <c r="F104" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="G104" s="14" t="s">
+      <c r="G104" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="H104" s="14" t="s">
+      <c r="H104" s="20" t="s">
         <v>666</v>
       </c>
-      <c r="I104" s="14" t="s">
+      <c r="I104" s="20" t="s">
         <v>673</v>
       </c>
       <c r="J104" s="1">
@@ -10776,13 +10925,13 @@
         <f t="shared" si="22"/>
         <v>770</v>
       </c>
-      <c r="P104" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="5">
-        <v>0</v>
-      </c>
-      <c r="R104" s="5">
+      <c r="P104" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="7">
+        <v>0</v>
+      </c>
+      <c r="R104" s="7">
         <v>0</v>
       </c>
       <c r="S104" s="1">
@@ -10805,13 +10954,13 @@
       <c r="F105" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="G105" s="14" t="s">
+      <c r="G105" s="20" t="s">
         <v>677</v>
       </c>
-      <c r="H105" s="14" t="s">
+      <c r="H105" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="I105" s="14" t="s">
+      <c r="I105" s="20" t="s">
         <v>678</v>
       </c>
       <c r="J105" s="1">
@@ -10836,13 +10985,13 @@
         <f t="shared" si="22"/>
         <v>800</v>
       </c>
-      <c r="P105" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="5">
-        <v>0</v>
-      </c>
-      <c r="R105" s="5">
+      <c r="P105" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="7">
+        <v>0</v>
+      </c>
+      <c r="R105" s="7">
         <v>0</v>
       </c>
       <c r="S105" s="1">
@@ -10853,8 +11002,8 @@
       </c>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
+      <c r="A106" s="5"/>
+      <c r="B106" s="5"/>
       <c r="C106" s="1" t="s">
         <v>679</v>
       </c>
@@ -10867,13 +11016,13 @@
       <c r="F106" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="G106" s="14" t="s">
+      <c r="G106" s="20" t="s">
         <v>682</v>
       </c>
-      <c r="H106" s="14" t="s">
+      <c r="H106" s="20" t="s">
         <v>683</v>
       </c>
-      <c r="I106" s="14" t="s">
+      <c r="I106" s="20" t="s">
         <v>684</v>
       </c>
       <c r="J106" s="1">
@@ -10898,13 +11047,13 @@
         <f t="shared" si="23"/>
         <v>815</v>
       </c>
-      <c r="P106" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="5">
-        <v>0</v>
-      </c>
-      <c r="R106" s="5">
+      <c r="P106" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="7">
+        <v>0</v>
+      </c>
+      <c r="R106" s="7">
         <v>0</v>
       </c>
       <c r="S106" s="1">
@@ -10913,15 +11062,15 @@
       <c r="T106" s="1">
         <v>2600000000</v>
       </c>
-      <c r="U106" s="3"/>
-      <c r="V106" s="3"/>
-      <c r="W106" s="3"/>
-      <c r="X106" s="3"/>
-      <c r="Y106" s="3"/>
+      <c r="U106" s="5"/>
+      <c r="V106" s="5"/>
+      <c r="W106" s="5"/>
+      <c r="X106" s="5"/>
+      <c r="Y106" s="5"/>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A107" s="3"/>
-      <c r="B107" s="3"/>
+      <c r="A107" s="5"/>
+      <c r="B107" s="5"/>
       <c r="C107" s="1" t="s">
         <v>685</v>
       </c>
@@ -10934,13 +11083,13 @@
       <c r="F107" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="G107" s="14" t="s">
+      <c r="G107" s="20" t="s">
         <v>688</v>
       </c>
-      <c r="H107" s="14" t="s">
+      <c r="H107" s="20" t="s">
         <v>689</v>
       </c>
-      <c r="I107" s="14" t="s">
+      <c r="I107" s="20" t="s">
         <v>690</v>
       </c>
       <c r="J107" s="1">
@@ -10965,13 +11114,13 @@
         <f t="shared" si="24"/>
         <v>830</v>
       </c>
-      <c r="P107" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q107" s="5">
-        <v>0</v>
-      </c>
-      <c r="R107" s="5">
+      <c r="P107" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="7">
+        <v>0</v>
+      </c>
+      <c r="R107" s="7">
         <v>0</v>
       </c>
       <c r="S107" s="1">
@@ -10980,15 +11129,15 @@
       <c r="T107" s="1">
         <v>2700000000</v>
       </c>
-      <c r="U107" s="3"/>
-      <c r="V107" s="3"/>
-      <c r="W107" s="3"/>
-      <c r="X107" s="3"/>
-      <c r="Y107" s="3"/>
+      <c r="U107" s="5"/>
+      <c r="V107" s="5"/>
+      <c r="W107" s="5"/>
+      <c r="X107" s="5"/>
+      <c r="Y107" s="5"/>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
+      <c r="A108" s="5"/>
+      <c r="B108" s="5"/>
       <c r="C108" s="1" t="s">
         <v>691</v>
       </c>
@@ -11001,13 +11150,13 @@
       <c r="F108" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="G108" s="14" t="s">
+      <c r="G108" s="20" t="s">
         <v>694</v>
       </c>
-      <c r="H108" s="14" t="s">
+      <c r="H108" s="20" t="s">
         <v>695</v>
       </c>
-      <c r="I108" s="14" t="s">
+      <c r="I108" s="20" t="s">
         <v>696</v>
       </c>
       <c r="J108" s="1">
@@ -11032,13 +11181,13 @@
         <f>O107+15</f>
         <v>845</v>
       </c>
-      <c r="P108" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="5">
-        <v>0</v>
-      </c>
-      <c r="R108" s="5">
+      <c r="P108" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="7">
+        <v>0</v>
+      </c>
+      <c r="R108" s="7">
         <v>0</v>
       </c>
       <c r="S108" s="1">
@@ -11047,15 +11196,15 @@
       <c r="T108" s="1">
         <v>2800000000</v>
       </c>
-      <c r="U108" s="3"/>
-      <c r="V108" s="3"/>
-      <c r="W108" s="3"/>
-      <c r="X108" s="3"/>
-      <c r="Y108" s="3"/>
+      <c r="U108" s="5"/>
+      <c r="V108" s="5"/>
+      <c r="W108" s="5"/>
+      <c r="X108" s="5"/>
+      <c r="Y108" s="5"/>
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A109" s="3"/>
-      <c r="B109" s="3"/>
+      <c r="A109" s="5"/>
+      <c r="B109" s="5"/>
       <c r="C109" s="1" t="s">
         <v>697</v>
       </c>
@@ -11068,13 +11217,13 @@
       <c r="F109" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="G109" s="14" t="s">
+      <c r="G109" s="20" t="s">
         <v>700</v>
       </c>
-      <c r="H109" s="14" t="s">
+      <c r="H109" s="20" t="s">
         <v>701</v>
       </c>
-      <c r="I109" s="14" t="s">
+      <c r="I109" s="20" t="s">
         <v>702</v>
       </c>
       <c r="J109" s="1">
@@ -11099,13 +11248,13 @@
         <f>O108+15</f>
         <v>860</v>
       </c>
-      <c r="P109" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="5">
-        <v>0</v>
-      </c>
-      <c r="R109" s="5">
+      <c r="P109" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="7">
+        <v>0</v>
+      </c>
+      <c r="R109" s="7">
         <v>0</v>
       </c>
       <c r="S109" s="1">
@@ -11114,15 +11263,15 @@
       <c r="T109" s="1">
         <v>2900000000</v>
       </c>
-      <c r="U109" s="3"/>
-      <c r="V109" s="3"/>
-      <c r="W109" s="3"/>
-      <c r="X109" s="3"/>
-      <c r="Y109" s="3"/>
+      <c r="U109" s="5"/>
+      <c r="V109" s="5"/>
+      <c r="W109" s="5"/>
+      <c r="X109" s="5"/>
+      <c r="Y109" s="5"/>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
+      <c r="A110" s="5"/>
+      <c r="B110" s="5"/>
       <c r="C110" s="1" t="s">
         <v>703</v>
       </c>
@@ -11135,13 +11284,13 @@
       <c r="F110" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="G110" s="14" t="s">
+      <c r="G110" s="20" t="s">
         <v>706</v>
       </c>
-      <c r="H110" s="14" t="s">
+      <c r="H110" s="20" t="s">
         <v>707</v>
       </c>
-      <c r="I110" s="14" t="s">
+      <c r="I110" s="20" t="s">
         <v>708</v>
       </c>
       <c r="J110" s="1">
@@ -11166,13 +11315,13 @@
         <f>O109+15</f>
         <v>875</v>
       </c>
-      <c r="P110" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="5">
-        <v>0</v>
-      </c>
-      <c r="R110" s="5">
+      <c r="P110" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="7">
+        <v>0</v>
+      </c>
+      <c r="R110" s="7">
         <v>0</v>
       </c>
       <c r="S110" s="1">
@@ -11181,15 +11330,15 @@
       <c r="T110" s="1">
         <v>3000000000</v>
       </c>
-      <c r="U110" s="3"/>
-      <c r="V110" s="3"/>
-      <c r="W110" s="3"/>
-      <c r="X110" s="3"/>
-      <c r="Y110" s="3"/>
+      <c r="U110" s="5"/>
+      <c r="V110" s="5"/>
+      <c r="W110" s="5"/>
+      <c r="X110" s="5"/>
+      <c r="Y110" s="5"/>
     </row>
     <row r="111" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
+      <c r="A111" s="5"/>
+      <c r="B111" s="5"/>
       <c r="C111" s="1" t="s">
         <v>709</v>
       </c>
@@ -11202,13 +11351,13 @@
       <c r="F111" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="G111" s="15" t="s">
+      <c r="G111" s="21" t="s">
         <v>712</v>
       </c>
-      <c r="H111" s="16" t="s">
+      <c r="H111" s="22" t="s">
         <v>712</v>
       </c>
-      <c r="I111" s="17" t="s">
+      <c r="I111" s="23" t="s">
         <v>713</v>
       </c>
       <c r="J111" s="1">
@@ -11229,28 +11378,28 @@
       <c r="O111" s="1">
         <v>900</v>
       </c>
-      <c r="P111" s="3">
+      <c r="P111" s="5">
         <v>30</v>
       </c>
-      <c r="Q111" s="5">
-        <v>0</v>
-      </c>
-      <c r="R111" s="3">
+      <c r="Q111" s="7">
+        <v>0</v>
+      </c>
+      <c r="R111" s="5">
         <v>90</v>
       </c>
-      <c r="S111" s="14" t="s">
+      <c r="S111" s="20" t="s">
         <v>714</v>
       </c>
-      <c r="T111" s="14" t="s">
+      <c r="T111" s="20" t="s">
         <v>714</v>
       </c>
-      <c r="W111" s="3"/>
-      <c r="X111" s="3"/>
-      <c r="Y111" s="3"/>
+      <c r="W111" s="5"/>
+      <c r="X111" s="5"/>
+      <c r="Y111" s="5"/>
     </row>
     <row r="112" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A112" s="3"/>
-      <c r="B112" s="3"/>
+      <c r="A112" s="5"/>
+      <c r="B112" s="5"/>
       <c r="C112" s="1" t="s">
         <v>715</v>
       </c>
@@ -11263,13 +11412,13 @@
       <c r="F112" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="G112" s="18" t="s">
+      <c r="G112" s="24" t="s">
         <v>718</v>
       </c>
-      <c r="H112" s="14" t="s">
+      <c r="H112" s="20" t="s">
         <v>718</v>
       </c>
-      <c r="I112" s="19" t="s">
+      <c r="I112" s="25" t="s">
         <v>719</v>
       </c>
       <c r="J112" s="1">
@@ -11294,29 +11443,29 @@
         <f t="shared" ref="O112:O145" si="27">O111+50</f>
         <v>950</v>
       </c>
-      <c r="P112" s="3">
+      <c r="P112" s="5">
         <f t="shared" ref="P112:P145" si="28">P111+1</f>
         <v>31</v>
       </c>
-      <c r="Q112" s="5">
-        <v>0</v>
-      </c>
-      <c r="R112" s="3">
+      <c r="Q112" s="7">
+        <v>0</v>
+      </c>
+      <c r="R112" s="5">
         <v>90</v>
       </c>
-      <c r="S112" s="14" t="s">
+      <c r="S112" s="20" t="s">
         <v>720</v>
       </c>
-      <c r="T112" s="14" t="s">
+      <c r="T112" s="20" t="s">
         <v>720</v>
       </c>
-      <c r="W112" s="3"/>
-      <c r="X112" s="3"/>
-      <c r="Y112" s="3"/>
+      <c r="W112" s="5"/>
+      <c r="X112" s="5"/>
+      <c r="Y112" s="5"/>
     </row>
     <row r="113" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
+      <c r="A113" s="5"/>
+      <c r="B113" s="5"/>
       <c r="C113" s="1" t="s">
         <v>721</v>
       </c>
@@ -11329,13 +11478,13 @@
       <c r="F113" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="G113" s="18" t="s">
+      <c r="G113" s="24" t="s">
         <v>724</v>
       </c>
-      <c r="H113" s="14" t="s">
+      <c r="H113" s="20" t="s">
         <v>724</v>
       </c>
-      <c r="I113" s="19" t="s">
+      <c r="I113" s="25" t="s">
         <v>725</v>
       </c>
       <c r="J113" s="1">
@@ -11360,29 +11509,29 @@
         <f t="shared" si="27"/>
         <v>1000</v>
       </c>
-      <c r="P113" s="3">
+      <c r="P113" s="5">
         <f t="shared" si="28"/>
         <v>32</v>
       </c>
-      <c r="Q113" s="5">
-        <v>0</v>
-      </c>
-      <c r="R113" s="3">
+      <c r="Q113" s="7">
+        <v>0</v>
+      </c>
+      <c r="R113" s="5">
         <v>90</v>
       </c>
-      <c r="S113" s="14" t="s">
+      <c r="S113" s="20" t="s">
         <v>726</v>
       </c>
-      <c r="T113" s="14" t="s">
+      <c r="T113" s="20" t="s">
         <v>726</v>
       </c>
-      <c r="W113" s="3"/>
-      <c r="X113" s="3"/>
-      <c r="Y113" s="3"/>
+      <c r="W113" s="5"/>
+      <c r="X113" s="5"/>
+      <c r="Y113" s="5"/>
     </row>
     <row r="114" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A114" s="3"/>
-      <c r="B114" s="3"/>
+      <c r="A114" s="5"/>
+      <c r="B114" s="5"/>
       <c r="C114" s="1" t="s">
         <v>727</v>
       </c>
@@ -11395,13 +11544,13 @@
       <c r="F114" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="G114" s="18" t="s">
+      <c r="G114" s="24" t="s">
         <v>730</v>
       </c>
-      <c r="H114" s="14" t="s">
+      <c r="H114" s="20" t="s">
         <v>730</v>
       </c>
-      <c r="I114" s="19" t="s">
+      <c r="I114" s="25" t="s">
         <v>731</v>
       </c>
       <c r="J114" s="1">
@@ -11426,29 +11575,29 @@
         <f t="shared" si="27"/>
         <v>1050</v>
       </c>
-      <c r="P114" s="3">
+      <c r="P114" s="5">
         <f t="shared" si="28"/>
         <v>33</v>
       </c>
-      <c r="Q114" s="5">
-        <v>0</v>
-      </c>
-      <c r="R114" s="3">
+      <c r="Q114" s="7">
+        <v>0</v>
+      </c>
+      <c r="R114" s="5">
         <v>90</v>
       </c>
-      <c r="S114" s="14" t="s">
+      <c r="S114" s="20" t="s">
         <v>732</v>
       </c>
-      <c r="T114" s="14" t="s">
+      <c r="T114" s="20" t="s">
         <v>732</v>
       </c>
-      <c r="W114" s="3"/>
-      <c r="X114" s="3"/>
-      <c r="Y114" s="3"/>
+      <c r="W114" s="5"/>
+      <c r="X114" s="5"/>
+      <c r="Y114" s="5"/>
     </row>
     <row r="115" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
+      <c r="A115" s="5"/>
+      <c r="B115" s="5"/>
       <c r="C115" s="1" t="s">
         <v>733</v>
       </c>
@@ -11461,13 +11610,13 @@
       <c r="F115" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="G115" s="18" t="s">
+      <c r="G115" s="24" t="s">
         <v>736</v>
       </c>
-      <c r="H115" s="14" t="s">
+      <c r="H115" s="20" t="s">
         <v>736</v>
       </c>
-      <c r="I115" s="19" t="s">
+      <c r="I115" s="25" t="s">
         <v>737</v>
       </c>
       <c r="J115" s="1">
@@ -11492,29 +11641,29 @@
         <f t="shared" si="27"/>
         <v>1100</v>
       </c>
-      <c r="P115" s="3">
+      <c r="P115" s="5">
         <f t="shared" si="28"/>
         <v>34</v>
       </c>
-      <c r="Q115" s="5">
-        <v>0</v>
-      </c>
-      <c r="R115" s="3">
+      <c r="Q115" s="7">
+        <v>0</v>
+      </c>
+      <c r="R115" s="5">
         <v>90</v>
       </c>
-      <c r="S115" s="14" t="s">
+      <c r="S115" s="20" t="s">
         <v>738</v>
       </c>
-      <c r="T115" s="14" t="s">
+      <c r="T115" s="20" t="s">
         <v>738</v>
       </c>
-      <c r="W115" s="3"/>
-      <c r="X115" s="3"/>
-      <c r="Y115" s="3"/>
+      <c r="W115" s="5"/>
+      <c r="X115" s="5"/>
+      <c r="Y115" s="5"/>
     </row>
     <row r="116" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
+      <c r="A116" s="5"/>
+      <c r="B116" s="5"/>
       <c r="C116" s="1" t="s">
         <v>739</v>
       </c>
@@ -11527,13 +11676,13 @@
       <c r="F116" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="G116" s="18" t="s">
+      <c r="G116" s="24" t="s">
         <v>742</v>
       </c>
-      <c r="H116" s="14" t="s">
+      <c r="H116" s="20" t="s">
         <v>742</v>
       </c>
-      <c r="I116" s="19" t="s">
+      <c r="I116" s="25" t="s">
         <v>743</v>
       </c>
       <c r="J116" s="1">
@@ -11558,31 +11707,31 @@
         <f t="shared" si="27"/>
         <v>1150</v>
       </c>
-      <c r="P116" s="3">
+      <c r="P116" s="5">
         <f t="shared" si="28"/>
         <v>35</v>
       </c>
-      <c r="Q116" s="5">
-        <v>0</v>
-      </c>
-      <c r="R116" s="3">
+      <c r="Q116" s="7">
+        <v>0</v>
+      </c>
+      <c r="R116" s="5">
         <v>90</v>
       </c>
-      <c r="S116" s="14" t="s">
+      <c r="S116" s="20" t="s">
         <v>744</v>
       </c>
-      <c r="T116" s="14" t="s">
+      <c r="T116" s="20" t="s">
         <v>744</v>
       </c>
-      <c r="U116" s="3"/>
-      <c r="V116" s="3"/>
-      <c r="W116" s="3"/>
-      <c r="X116" s="3"/>
-      <c r="Y116" s="3"/>
+      <c r="U116" s="5"/>
+      <c r="V116" s="5"/>
+      <c r="W116" s="5"/>
+      <c r="X116" s="5"/>
+      <c r="Y116" s="5"/>
     </row>
     <row r="117" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A117" s="3"/>
-      <c r="B117" s="3"/>
+      <c r="A117" s="5"/>
+      <c r="B117" s="5"/>
       <c r="C117" s="1" t="s">
         <v>745</v>
       </c>
@@ -11595,13 +11744,13 @@
       <c r="F117" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="G117" s="18" t="s">
+      <c r="G117" s="24" t="s">
         <v>748</v>
       </c>
-      <c r="H117" s="14" t="s">
+      <c r="H117" s="20" t="s">
         <v>748</v>
       </c>
-      <c r="I117" s="19" t="s">
+      <c r="I117" s="25" t="s">
         <v>749</v>
       </c>
       <c r="J117" s="1">
@@ -11626,31 +11775,31 @@
         <f t="shared" si="27"/>
         <v>1200</v>
       </c>
-      <c r="P117" s="3">
+      <c r="P117" s="5">
         <f t="shared" si="28"/>
         <v>36</v>
       </c>
-      <c r="Q117" s="5">
-        <v>0</v>
-      </c>
-      <c r="R117" s="3">
+      <c r="Q117" s="7">
+        <v>0</v>
+      </c>
+      <c r="R117" s="5">
         <v>90</v>
       </c>
-      <c r="S117" s="14" t="s">
+      <c r="S117" s="20" t="s">
         <v>750</v>
       </c>
-      <c r="T117" s="14" t="s">
+      <c r="T117" s="20" t="s">
         <v>750</v>
       </c>
-      <c r="U117" s="3"/>
-      <c r="V117" s="3"/>
-      <c r="W117" s="3"/>
-      <c r="X117" s="3"/>
-      <c r="Y117" s="3"/>
+      <c r="U117" s="5"/>
+      <c r="V117" s="5"/>
+      <c r="W117" s="5"/>
+      <c r="X117" s="5"/>
+      <c r="Y117" s="5"/>
     </row>
     <row r="118" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A118" s="3"/>
-      <c r="B118" s="3"/>
+      <c r="A118" s="5"/>
+      <c r="B118" s="5"/>
       <c r="C118" s="1" t="s">
         <v>751</v>
       </c>
@@ -11663,13 +11812,13 @@
       <c r="F118" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="G118" s="18" t="s">
+      <c r="G118" s="24" t="s">
         <v>754</v>
       </c>
-      <c r="H118" s="14" t="s">
+      <c r="H118" s="20" t="s">
         <v>754</v>
       </c>
-      <c r="I118" s="19" t="s">
+      <c r="I118" s="25" t="s">
         <v>755</v>
       </c>
       <c r="J118" s="1">
@@ -11694,31 +11843,31 @@
         <f t="shared" si="27"/>
         <v>1250</v>
       </c>
-      <c r="P118" s="3">
+      <c r="P118" s="5">
         <f t="shared" si="28"/>
         <v>37</v>
       </c>
-      <c r="Q118" s="5">
-        <v>0</v>
-      </c>
-      <c r="R118" s="3">
+      <c r="Q118" s="7">
+        <v>0</v>
+      </c>
+      <c r="R118" s="5">
         <v>90</v>
       </c>
-      <c r="S118" s="14" t="s">
+      <c r="S118" s="20" t="s">
         <v>756</v>
       </c>
-      <c r="T118" s="14" t="s">
+      <c r="T118" s="20" t="s">
         <v>756</v>
       </c>
-      <c r="U118" s="3"/>
-      <c r="V118" s="3"/>
-      <c r="W118" s="3"/>
-      <c r="X118" s="3"/>
-      <c r="Y118" s="3"/>
+      <c r="U118" s="5"/>
+      <c r="V118" s="5"/>
+      <c r="W118" s="5"/>
+      <c r="X118" s="5"/>
+      <c r="Y118" s="5"/>
     </row>
     <row r="119" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A119" s="3"/>
-      <c r="B119" s="3"/>
+      <c r="A119" s="5"/>
+      <c r="B119" s="5"/>
       <c r="C119" s="1" t="s">
         <v>757</v>
       </c>
@@ -11731,13 +11880,13 @@
       <c r="F119" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="G119" s="18" t="s">
+      <c r="G119" s="24" t="s">
         <v>760</v>
       </c>
-      <c r="H119" s="14" t="s">
+      <c r="H119" s="20" t="s">
         <v>760</v>
       </c>
-      <c r="I119" s="19" t="s">
+      <c r="I119" s="25" t="s">
         <v>761</v>
       </c>
       <c r="J119" s="1">
@@ -11762,31 +11911,31 @@
         <f t="shared" si="27"/>
         <v>1300</v>
       </c>
-      <c r="P119" s="3">
+      <c r="P119" s="5">
         <f t="shared" si="28"/>
         <v>38</v>
       </c>
-      <c r="Q119" s="5">
-        <v>0</v>
-      </c>
-      <c r="R119" s="3">
+      <c r="Q119" s="7">
+        <v>0</v>
+      </c>
+      <c r="R119" s="5">
         <v>90</v>
       </c>
-      <c r="S119" s="14" t="s">
+      <c r="S119" s="20" t="s">
         <v>762</v>
       </c>
-      <c r="T119" s="14" t="s">
+      <c r="T119" s="20" t="s">
         <v>762</v>
       </c>
-      <c r="U119" s="3"/>
-      <c r="V119" s="3"/>
-      <c r="W119" s="3"/>
-      <c r="X119" s="3"/>
-      <c r="Y119" s="3"/>
+      <c r="U119" s="5"/>
+      <c r="V119" s="5"/>
+      <c r="W119" s="5"/>
+      <c r="X119" s="5"/>
+      <c r="Y119" s="5"/>
     </row>
     <row r="120" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A120" s="3"/>
-      <c r="B120" s="3"/>
+      <c r="A120" s="5"/>
+      <c r="B120" s="5"/>
       <c r="C120" s="1" t="s">
         <v>763</v>
       </c>
@@ -11799,13 +11948,13 @@
       <c r="F120" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="G120" s="18" t="s">
+      <c r="G120" s="24" t="s">
         <v>766</v>
       </c>
-      <c r="H120" s="14" t="s">
+      <c r="H120" s="20" t="s">
         <v>766</v>
       </c>
-      <c r="I120" s="19" t="s">
+      <c r="I120" s="25" t="s">
         <v>767</v>
       </c>
       <c r="J120" s="1">
@@ -11830,31 +11979,31 @@
         <f t="shared" si="27"/>
         <v>1350</v>
       </c>
-      <c r="P120" s="3">
+      <c r="P120" s="5">
         <f t="shared" si="28"/>
         <v>39</v>
       </c>
-      <c r="Q120" s="5">
-        <v>0</v>
-      </c>
-      <c r="R120" s="3">
+      <c r="Q120" s="7">
+        <v>0</v>
+      </c>
+      <c r="R120" s="5">
         <v>90</v>
       </c>
-      <c r="S120" s="14" t="s">
+      <c r="S120" s="20" t="s">
         <v>768</v>
       </c>
-      <c r="T120" s="14" t="s">
+      <c r="T120" s="20" t="s">
         <v>768</v>
       </c>
-      <c r="U120" s="3"/>
-      <c r="V120" s="3"/>
-      <c r="W120" s="3"/>
-      <c r="X120" s="3"/>
-      <c r="Y120" s="3"/>
+      <c r="U120" s="5"/>
+      <c r="V120" s="5"/>
+      <c r="W120" s="5"/>
+      <c r="X120" s="5"/>
+      <c r="Y120" s="5"/>
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A121" s="3"/>
-      <c r="B121" s="3"/>
+      <c r="A121" s="5"/>
+      <c r="B121" s="5"/>
       <c r="C121" s="1" t="s">
         <v>769</v>
       </c>
@@ -11867,13 +12016,13 @@
       <c r="F121" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G121" s="18" t="s">
+      <c r="G121" s="24" t="s">
         <v>713</v>
       </c>
-      <c r="H121" s="14" t="s">
+      <c r="H121" s="20" t="s">
         <v>713</v>
       </c>
-      <c r="I121" s="19" t="s">
+      <c r="I121" s="25" t="s">
         <v>772</v>
       </c>
       <c r="J121" s="1">
@@ -11898,31 +12047,31 @@
         <f t="shared" si="27"/>
         <v>1400</v>
       </c>
-      <c r="P121" s="3">
+      <c r="P121" s="5">
         <f t="shared" si="28"/>
         <v>40</v>
       </c>
-      <c r="Q121" s="5">
+      <c r="Q121" s="7">
         <v>3</v>
       </c>
-      <c r="R121" s="3">
+      <c r="R121" s="5">
         <v>90</v>
       </c>
-      <c r="S121" s="14" t="s">
+      <c r="S121" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="T121" s="14" t="s">
+      <c r="T121" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="U121" s="3"/>
-      <c r="V121" s="3"/>
-      <c r="W121" s="3"/>
-      <c r="X121" s="3"/>
-      <c r="Y121" s="3"/>
+      <c r="U121" s="5"/>
+      <c r="V121" s="5"/>
+      <c r="W121" s="5"/>
+      <c r="X121" s="5"/>
+      <c r="Y121" s="5"/>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A122" s="3"/>
-      <c r="B122" s="3"/>
+      <c r="A122" s="5"/>
+      <c r="B122" s="5"/>
       <c r="C122" s="1" t="s">
         <v>774</v>
       </c>
@@ -11935,13 +12084,13 @@
       <c r="F122" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="G122" s="18" t="s">
+      <c r="G122" s="24" t="s">
         <v>777</v>
       </c>
-      <c r="H122" s="14" t="s">
+      <c r="H122" s="20" t="s">
         <v>777</v>
       </c>
-      <c r="I122" s="19" t="s">
+      <c r="I122" s="25" t="s">
         <v>778</v>
       </c>
       <c r="J122" s="1">
@@ -11966,32 +12115,32 @@
         <f t="shared" si="27"/>
         <v>1450</v>
       </c>
-      <c r="P122" s="3">
+      <c r="P122" s="5">
         <f t="shared" si="28"/>
         <v>41</v>
       </c>
-      <c r="Q122" s="3">
+      <c r="Q122" s="5">
         <f t="shared" ref="Q122:Q130" si="31">Q121+3</f>
         <v>6</v>
       </c>
-      <c r="R122" s="3">
+      <c r="R122" s="5">
         <v>90</v>
       </c>
-      <c r="S122" s="14" t="s">
+      <c r="S122" s="20" t="s">
         <v>779</v>
       </c>
-      <c r="T122" s="14" t="s">
+      <c r="T122" s="20" t="s">
         <v>779</v>
       </c>
-      <c r="U122" s="3"/>
-      <c r="V122" s="3"/>
-      <c r="W122" s="3"/>
-      <c r="X122" s="3"/>
-      <c r="Y122" s="3"/>
+      <c r="U122" s="5"/>
+      <c r="V122" s="5"/>
+      <c r="W122" s="5"/>
+      <c r="X122" s="5"/>
+      <c r="Y122" s="5"/>
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A123" s="3"/>
-      <c r="B123" s="3"/>
+      <c r="A123" s="5"/>
+      <c r="B123" s="5"/>
       <c r="C123" s="1" t="s">
         <v>780</v>
       </c>
@@ -12004,13 +12153,13 @@
       <c r="F123" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="G123" s="18" t="s">
+      <c r="G123" s="24" t="s">
         <v>783</v>
       </c>
-      <c r="H123" s="14" t="s">
+      <c r="H123" s="20" t="s">
         <v>783</v>
       </c>
-      <c r="I123" s="19" t="s">
+      <c r="I123" s="25" t="s">
         <v>784</v>
       </c>
       <c r="J123" s="1">
@@ -12035,32 +12184,32 @@
         <f t="shared" si="27"/>
         <v>1500</v>
       </c>
-      <c r="P123" s="3">
+      <c r="P123" s="5">
         <f t="shared" si="28"/>
         <v>42</v>
       </c>
-      <c r="Q123" s="3">
+      <c r="Q123" s="5">
         <f t="shared" si="31"/>
         <v>9</v>
       </c>
-      <c r="R123" s="3">
+      <c r="R123" s="5">
         <v>90</v>
       </c>
-      <c r="S123" s="14" t="s">
+      <c r="S123" s="20" t="s">
         <v>785</v>
       </c>
-      <c r="T123" s="14" t="s">
+      <c r="T123" s="20" t="s">
         <v>785</v>
       </c>
-      <c r="U123" s="3"/>
-      <c r="V123" s="3"/>
-      <c r="W123" s="3"/>
-      <c r="X123" s="3"/>
-      <c r="Y123" s="3"/>
+      <c r="U123" s="5"/>
+      <c r="V123" s="5"/>
+      <c r="W123" s="5"/>
+      <c r="X123" s="5"/>
+      <c r="Y123" s="5"/>
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A124" s="3"/>
-      <c r="B124" s="3"/>
+      <c r="A124" s="5"/>
+      <c r="B124" s="5"/>
       <c r="C124" s="1" t="s">
         <v>786</v>
       </c>
@@ -12073,13 +12222,13 @@
       <c r="F124" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="G124" s="18" t="s">
+      <c r="G124" s="24" t="s">
         <v>789</v>
       </c>
-      <c r="H124" s="14" t="s">
+      <c r="H124" s="20" t="s">
         <v>789</v>
       </c>
-      <c r="I124" s="19" t="s">
+      <c r="I124" s="25" t="s">
         <v>790</v>
       </c>
       <c r="J124" s="1">
@@ -12104,32 +12253,32 @@
         <f t="shared" si="27"/>
         <v>1550</v>
       </c>
-      <c r="P124" s="3">
+      <c r="P124" s="5">
         <f t="shared" si="28"/>
         <v>43</v>
       </c>
-      <c r="Q124" s="3">
+      <c r="Q124" s="5">
         <f t="shared" si="31"/>
         <v>12</v>
       </c>
-      <c r="R124" s="3">
+      <c r="R124" s="5">
         <v>90</v>
       </c>
-      <c r="S124" s="14" t="s">
+      <c r="S124" s="20" t="s">
         <v>791</v>
       </c>
-      <c r="T124" s="14" t="s">
+      <c r="T124" s="20" t="s">
         <v>791</v>
       </c>
-      <c r="U124" s="3"/>
-      <c r="V124" s="3"/>
-      <c r="W124" s="3"/>
-      <c r="X124" s="3"/>
-      <c r="Y124" s="3"/>
+      <c r="U124" s="5"/>
+      <c r="V124" s="5"/>
+      <c r="W124" s="5"/>
+      <c r="X124" s="5"/>
+      <c r="Y124" s="5"/>
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A125" s="3"/>
-      <c r="B125" s="3"/>
+      <c r="A125" s="5"/>
+      <c r="B125" s="5"/>
       <c r="C125" s="1" t="s">
         <v>792</v>
       </c>
@@ -12142,13 +12291,13 @@
       <c r="F125" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="G125" s="18" t="s">
+      <c r="G125" s="24" t="s">
         <v>795</v>
       </c>
-      <c r="H125" s="14" t="s">
+      <c r="H125" s="20" t="s">
         <v>795</v>
       </c>
-      <c r="I125" s="19" t="s">
+      <c r="I125" s="25" t="s">
         <v>796</v>
       </c>
       <c r="J125" s="1">
@@ -12173,32 +12322,32 @@
         <f t="shared" si="27"/>
         <v>1600</v>
       </c>
-      <c r="P125" s="3">
+      <c r="P125" s="5">
         <f t="shared" si="28"/>
         <v>44</v>
       </c>
-      <c r="Q125" s="3">
+      <c r="Q125" s="5">
         <f t="shared" si="31"/>
         <v>15</v>
       </c>
-      <c r="R125" s="3">
+      <c r="R125" s="5">
         <v>90</v>
       </c>
-      <c r="S125" s="14" t="s">
+      <c r="S125" s="20" t="s">
         <v>797</v>
       </c>
-      <c r="T125" s="14" t="s">
+      <c r="T125" s="20" t="s">
         <v>797</v>
       </c>
-      <c r="U125" s="3"/>
-      <c r="V125" s="3"/>
-      <c r="W125" s="3"/>
-      <c r="X125" s="3"/>
-      <c r="Y125" s="3"/>
+      <c r="U125" s="5"/>
+      <c r="V125" s="5"/>
+      <c r="W125" s="5"/>
+      <c r="X125" s="5"/>
+      <c r="Y125" s="5"/>
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A126" s="3"/>
-      <c r="B126" s="3"/>
+      <c r="A126" s="5"/>
+      <c r="B126" s="5"/>
       <c r="C126" s="1" t="s">
         <v>798</v>
       </c>
@@ -12211,13 +12360,13 @@
       <c r="F126" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="G126" s="18" t="s">
+      <c r="G126" s="24" t="s">
         <v>801</v>
       </c>
-      <c r="H126" s="14" t="s">
+      <c r="H126" s="20" t="s">
         <v>801</v>
       </c>
-      <c r="I126" s="19" t="s">
+      <c r="I126" s="25" t="s">
         <v>802</v>
       </c>
       <c r="J126" s="1">
@@ -12242,32 +12391,32 @@
         <f t="shared" si="27"/>
         <v>1650</v>
       </c>
-      <c r="P126" s="3">
+      <c r="P126" s="5">
         <f t="shared" si="28"/>
         <v>45</v>
       </c>
-      <c r="Q126" s="3">
+      <c r="Q126" s="5">
         <f t="shared" si="31"/>
         <v>18</v>
       </c>
-      <c r="R126" s="3">
+      <c r="R126" s="5">
         <v>90</v>
       </c>
-      <c r="S126" s="14" t="s">
+      <c r="S126" s="20" t="s">
         <v>803</v>
       </c>
-      <c r="T126" s="14" t="s">
+      <c r="T126" s="20" t="s">
         <v>803</v>
       </c>
-      <c r="U126" s="3"/>
-      <c r="V126" s="3"/>
-      <c r="W126" s="3"/>
-      <c r="X126" s="3"/>
-      <c r="Y126" s="3"/>
+      <c r="U126" s="5"/>
+      <c r="V126" s="5"/>
+      <c r="W126" s="5"/>
+      <c r="X126" s="5"/>
+      <c r="Y126" s="5"/>
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A127" s="3"/>
-      <c r="B127" s="3"/>
+      <c r="A127" s="5"/>
+      <c r="B127" s="5"/>
       <c r="C127" s="1" t="s">
         <v>804</v>
       </c>
@@ -12280,13 +12429,13 @@
       <c r="F127" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="G127" s="18" t="s">
+      <c r="G127" s="24" t="s">
         <v>807</v>
       </c>
-      <c r="H127" s="14" t="s">
+      <c r="H127" s="20" t="s">
         <v>807</v>
       </c>
-      <c r="I127" s="19" t="s">
+      <c r="I127" s="25" t="s">
         <v>808</v>
       </c>
       <c r="J127" s="1">
@@ -12311,32 +12460,32 @@
         <f t="shared" si="27"/>
         <v>1700</v>
       </c>
-      <c r="P127" s="3">
+      <c r="P127" s="5">
         <f t="shared" si="28"/>
         <v>46</v>
       </c>
-      <c r="Q127" s="3">
+      <c r="Q127" s="5">
         <f t="shared" si="31"/>
         <v>21</v>
       </c>
-      <c r="R127" s="3">
+      <c r="R127" s="5">
         <v>90</v>
       </c>
-      <c r="S127" s="14" t="s">
+      <c r="S127" s="20" t="s">
         <v>809</v>
       </c>
-      <c r="T127" s="14" t="s">
+      <c r="T127" s="20" t="s">
         <v>809</v>
       </c>
-      <c r="U127" s="3"/>
-      <c r="V127" s="3"/>
-      <c r="W127" s="3"/>
-      <c r="X127" s="3"/>
-      <c r="Y127" s="3"/>
+      <c r="U127" s="5"/>
+      <c r="V127" s="5"/>
+      <c r="W127" s="5"/>
+      <c r="X127" s="5"/>
+      <c r="Y127" s="5"/>
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A128" s="3"/>
-      <c r="B128" s="3"/>
+      <c r="A128" s="5"/>
+      <c r="B128" s="5"/>
       <c r="C128" s="1" t="s">
         <v>810</v>
       </c>
@@ -12349,13 +12498,13 @@
       <c r="F128" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="G128" s="18" t="s">
+      <c r="G128" s="24" t="s">
         <v>813</v>
       </c>
-      <c r="H128" s="14" t="s">
+      <c r="H128" s="20" t="s">
         <v>813</v>
       </c>
-      <c r="I128" s="19" t="s">
+      <c r="I128" s="25" t="s">
         <v>814</v>
       </c>
       <c r="J128" s="1">
@@ -12380,32 +12529,32 @@
         <f t="shared" si="27"/>
         <v>1750</v>
       </c>
-      <c r="P128" s="3">
+      <c r="P128" s="5">
         <f t="shared" si="28"/>
         <v>47</v>
       </c>
-      <c r="Q128" s="3">
+      <c r="Q128" s="5">
         <f t="shared" si="31"/>
         <v>24</v>
       </c>
-      <c r="R128" s="3">
+      <c r="R128" s="5">
         <v>90</v>
       </c>
-      <c r="S128" s="14" t="s">
+      <c r="S128" s="20" t="s">
         <v>815</v>
       </c>
-      <c r="T128" s="14" t="s">
+      <c r="T128" s="20" t="s">
         <v>815</v>
       </c>
-      <c r="U128" s="3"/>
-      <c r="V128" s="3"/>
-      <c r="W128" s="3"/>
-      <c r="X128" s="3"/>
-      <c r="Y128" s="3"/>
+      <c r="U128" s="5"/>
+      <c r="V128" s="5"/>
+      <c r="W128" s="5"/>
+      <c r="X128" s="5"/>
+      <c r="Y128" s="5"/>
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
+      <c r="A129" s="5"/>
+      <c r="B129" s="5"/>
       <c r="C129" s="1" t="s">
         <v>816</v>
       </c>
@@ -12418,13 +12567,13 @@
       <c r="F129" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="G129" s="18" t="s">
+      <c r="G129" s="24" t="s">
         <v>819</v>
       </c>
-      <c r="H129" s="14" t="s">
+      <c r="H129" s="20" t="s">
         <v>819</v>
       </c>
-      <c r="I129" s="19" t="s">
+      <c r="I129" s="25" t="s">
         <v>820</v>
       </c>
       <c r="J129" s="1">
@@ -12449,32 +12598,32 @@
         <f t="shared" si="27"/>
         <v>1800</v>
       </c>
-      <c r="P129" s="3">
+      <c r="P129" s="5">
         <f t="shared" si="28"/>
         <v>48</v>
       </c>
-      <c r="Q129" s="3">
+      <c r="Q129" s="5">
         <f t="shared" si="31"/>
         <v>27</v>
       </c>
-      <c r="R129" s="3">
+      <c r="R129" s="5">
         <v>90</v>
       </c>
-      <c r="S129" s="14" t="s">
+      <c r="S129" s="20" t="s">
         <v>821</v>
       </c>
-      <c r="T129" s="14" t="s">
+      <c r="T129" s="20" t="s">
         <v>821</v>
       </c>
-      <c r="U129" s="3"/>
-      <c r="V129" s="3"/>
-      <c r="W129" s="3"/>
-      <c r="X129" s="3"/>
-      <c r="Y129" s="3"/>
+      <c r="U129" s="5"/>
+      <c r="V129" s="5"/>
+      <c r="W129" s="5"/>
+      <c r="X129" s="5"/>
+      <c r="Y129" s="5"/>
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A130" s="3"/>
-      <c r="B130" s="3"/>
+      <c r="A130" s="5"/>
+      <c r="B130" s="5"/>
       <c r="C130" s="1" t="s">
         <v>822</v>
       </c>
@@ -12487,13 +12636,13 @@
       <c r="F130" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="G130" s="18" t="s">
+      <c r="G130" s="24" t="s">
         <v>825</v>
       </c>
-      <c r="H130" s="14" t="s">
+      <c r="H130" s="20" t="s">
         <v>825</v>
       </c>
-      <c r="I130" s="19" t="s">
+      <c r="I130" s="25" t="s">
         <v>826</v>
       </c>
       <c r="J130" s="1">
@@ -12518,28 +12667,28 @@
         <f t="shared" si="27"/>
         <v>1850</v>
       </c>
-      <c r="P130" s="3">
+      <c r="P130" s="5">
         <f t="shared" si="28"/>
         <v>49</v>
       </c>
-      <c r="Q130" s="3">
+      <c r="Q130" s="5">
         <f t="shared" si="31"/>
         <v>30</v>
       </c>
-      <c r="R130" s="3">
+      <c r="R130" s="5">
         <v>90</v>
       </c>
-      <c r="S130" s="14" t="s">
+      <c r="S130" s="20" t="s">
         <v>827</v>
       </c>
-      <c r="T130" s="14" t="s">
+      <c r="T130" s="20" t="s">
         <v>827</v>
       </c>
-      <c r="U130" s="3"/>
-      <c r="V130" s="3"/>
-      <c r="W130" s="3"/>
-      <c r="X130" s="3"/>
-      <c r="Y130" s="3"/>
+      <c r="U130" s="5"/>
+      <c r="V130" s="5"/>
+      <c r="W130" s="5"/>
+      <c r="X130" s="5"/>
+      <c r="Y130" s="5"/>
     </row>
     <row r="131" customHeight="1" spans="3:20">
       <c r="C131" s="1" t="s">
@@ -12554,13 +12703,13 @@
       <c r="F131" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="G131" s="18" t="s">
+      <c r="G131" s="24" t="s">
         <v>831</v>
       </c>
-      <c r="H131" s="14" t="s">
+      <c r="H131" s="20" t="s">
         <v>831</v>
       </c>
-      <c r="I131" s="19" t="s">
+      <c r="I131" s="25" t="s">
         <v>832</v>
       </c>
       <c r="J131" s="1">
@@ -12585,21 +12734,21 @@
         <f t="shared" ref="O131:O135" si="35">O130+100</f>
         <v>1950</v>
       </c>
-      <c r="P131" s="3">
+      <c r="P131" s="5">
         <f t="shared" ref="P131:P145" si="36">P130+2</f>
         <v>51</v>
       </c>
-      <c r="Q131" s="3">
+      <c r="Q131" s="5">
         <f t="shared" ref="Q131:Q180" si="37">Q130+4</f>
         <v>34</v>
       </c>
-      <c r="R131" s="3">
+      <c r="R131" s="5">
         <v>92</v>
       </c>
-      <c r="S131" s="14" t="s">
+      <c r="S131" s="20" t="s">
         <v>833</v>
       </c>
-      <c r="T131" s="14" t="s">
+      <c r="T131" s="20" t="s">
         <v>833</v>
       </c>
     </row>
@@ -12616,13 +12765,13 @@
       <c r="F132" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="G132" s="18" t="s">
+      <c r="G132" s="24" t="s">
         <v>837</v>
       </c>
-      <c r="H132" s="14" t="s">
+      <c r="H132" s="20" t="s">
         <v>837</v>
       </c>
-      <c r="I132" s="19" t="s">
+      <c r="I132" s="25" t="s">
         <v>838</v>
       </c>
       <c r="J132" s="1">
@@ -12647,21 +12796,21 @@
         <f t="shared" si="35"/>
         <v>2050</v>
       </c>
-      <c r="P132" s="3">
+      <c r="P132" s="5">
         <f t="shared" si="36"/>
         <v>53</v>
       </c>
-      <c r="Q132" s="3">
+      <c r="Q132" s="5">
         <f t="shared" si="37"/>
         <v>38</v>
       </c>
-      <c r="R132" s="3">
+      <c r="R132" s="5">
         <v>94</v>
       </c>
-      <c r="S132" s="14" t="s">
+      <c r="S132" s="20" t="s">
         <v>839</v>
       </c>
-      <c r="T132" s="14" t="s">
+      <c r="T132" s="20" t="s">
         <v>839</v>
       </c>
     </row>
@@ -12678,13 +12827,13 @@
       <c r="F133" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="G133" s="18" t="s">
+      <c r="G133" s="24" t="s">
         <v>843</v>
       </c>
-      <c r="H133" s="14" t="s">
+      <c r="H133" s="20" t="s">
         <v>843</v>
       </c>
-      <c r="I133" s="19" t="s">
+      <c r="I133" s="25" t="s">
         <v>844</v>
       </c>
       <c r="J133" s="1">
@@ -12709,21 +12858,21 @@
         <f t="shared" si="35"/>
         <v>2150</v>
       </c>
-      <c r="P133" s="3">
+      <c r="P133" s="5">
         <f t="shared" si="36"/>
         <v>55</v>
       </c>
-      <c r="Q133" s="3">
+      <c r="Q133" s="5">
         <f t="shared" si="37"/>
         <v>42</v>
       </c>
-      <c r="R133" s="3">
+      <c r="R133" s="5">
         <v>96</v>
       </c>
-      <c r="S133" s="14" t="s">
+      <c r="S133" s="20" t="s">
         <v>845</v>
       </c>
-      <c r="T133" s="14" t="s">
+      <c r="T133" s="20" t="s">
         <v>845</v>
       </c>
     </row>
@@ -12740,13 +12889,13 @@
       <c r="F134" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="G134" s="18" t="s">
+      <c r="G134" s="24" t="s">
         <v>849</v>
       </c>
-      <c r="H134" s="14" t="s">
+      <c r="H134" s="20" t="s">
         <v>849</v>
       </c>
-      <c r="I134" s="19" t="s">
+      <c r="I134" s="25" t="s">
         <v>850</v>
       </c>
       <c r="J134" s="1">
@@ -12771,21 +12920,21 @@
         <f t="shared" si="35"/>
         <v>2250</v>
       </c>
-      <c r="P134" s="3">
+      <c r="P134" s="5">
         <f t="shared" si="36"/>
         <v>57</v>
       </c>
-      <c r="Q134" s="3">
+      <c r="Q134" s="5">
         <f t="shared" si="37"/>
         <v>46</v>
       </c>
-      <c r="R134" s="3">
+      <c r="R134" s="5">
         <v>98</v>
       </c>
-      <c r="S134" s="14" t="s">
+      <c r="S134" s="20" t="s">
         <v>851</v>
       </c>
-      <c r="T134" s="14" t="s">
+      <c r="T134" s="20" t="s">
         <v>851</v>
       </c>
     </row>
@@ -12802,13 +12951,13 @@
       <c r="F135" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="G135" s="18" t="s">
+      <c r="G135" s="24" t="s">
         <v>855</v>
       </c>
-      <c r="H135" s="14" t="s">
+      <c r="H135" s="20" t="s">
         <v>855</v>
       </c>
-      <c r="I135" s="19" t="s">
+      <c r="I135" s="25" t="s">
         <v>856</v>
       </c>
       <c r="J135" s="1">
@@ -12833,21 +12982,21 @@
         <f t="shared" si="35"/>
         <v>2350</v>
       </c>
-      <c r="P135" s="3">
+      <c r="P135" s="5">
         <f t="shared" si="36"/>
         <v>59</v>
       </c>
-      <c r="Q135" s="3">
+      <c r="Q135" s="5">
         <f t="shared" si="37"/>
         <v>50</v>
       </c>
-      <c r="R135" s="3">
+      <c r="R135" s="5">
         <v>99</v>
       </c>
-      <c r="S135" s="14" t="s">
+      <c r="S135" s="20" t="s">
         <v>857</v>
       </c>
-      <c r="T135" s="14" t="s">
+      <c r="T135" s="20" t="s">
         <v>857</v>
       </c>
     </row>
@@ -12864,13 +13013,13 @@
       <c r="F136" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="G136" s="18" t="s">
+      <c r="G136" s="24" t="s">
         <v>861</v>
       </c>
-      <c r="H136" s="14" t="s">
+      <c r="H136" s="20" t="s">
         <v>861</v>
       </c>
-      <c r="I136" s="19" t="s">
+      <c r="I136" s="25" t="s">
         <v>862</v>
       </c>
       <c r="J136" s="1">
@@ -12895,21 +13044,21 @@
         <f t="shared" ref="O136:O145" si="41">O135+200</f>
         <v>2550</v>
       </c>
-      <c r="P136" s="3">
+      <c r="P136" s="5">
         <f t="shared" si="36"/>
         <v>61</v>
       </c>
-      <c r="Q136" s="3">
+      <c r="Q136" s="5">
         <f t="shared" si="37"/>
         <v>54</v>
       </c>
-      <c r="R136" s="3">
+      <c r="R136" s="5">
         <v>99.2</v>
       </c>
-      <c r="S136" s="14" t="s">
+      <c r="S136" s="20" t="s">
         <v>863</v>
       </c>
-      <c r="T136" s="14" t="s">
+      <c r="T136" s="20" t="s">
         <v>863</v>
       </c>
     </row>
@@ -12926,13 +13075,13 @@
       <c r="F137" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="G137" s="18" t="s">
+      <c r="G137" s="24" t="s">
         <v>867</v>
       </c>
-      <c r="H137" s="14" t="s">
+      <c r="H137" s="20" t="s">
         <v>867</v>
       </c>
-      <c r="I137" s="19" t="s">
+      <c r="I137" s="25" t="s">
         <v>868</v>
       </c>
       <c r="J137" s="1">
@@ -12957,21 +13106,21 @@
         <f t="shared" si="41"/>
         <v>2750</v>
       </c>
-      <c r="P137" s="3">
+      <c r="P137" s="5">
         <f t="shared" si="36"/>
         <v>63</v>
       </c>
-      <c r="Q137" s="3">
+      <c r="Q137" s="5">
         <f t="shared" si="37"/>
         <v>58</v>
       </c>
-      <c r="R137" s="3">
+      <c r="R137" s="5">
         <v>99.4</v>
       </c>
-      <c r="S137" s="14" t="s">
+      <c r="S137" s="20" t="s">
         <v>869</v>
       </c>
-      <c r="T137" s="14" t="s">
+      <c r="T137" s="20" t="s">
         <v>869</v>
       </c>
     </row>
@@ -12988,13 +13137,13 @@
       <c r="F138" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="G138" s="18" t="s">
+      <c r="G138" s="24" t="s">
         <v>873</v>
       </c>
-      <c r="H138" s="14" t="s">
+      <c r="H138" s="20" t="s">
         <v>873</v>
       </c>
-      <c r="I138" s="19" t="s">
+      <c r="I138" s="25" t="s">
         <v>874</v>
       </c>
       <c r="J138" s="1">
@@ -13019,21 +13168,21 @@
         <f t="shared" si="41"/>
         <v>2950</v>
       </c>
-      <c r="P138" s="3">
+      <c r="P138" s="5">
         <f t="shared" si="36"/>
         <v>65</v>
       </c>
-      <c r="Q138" s="3">
+      <c r="Q138" s="5">
         <f t="shared" si="37"/>
         <v>62</v>
       </c>
-      <c r="R138" s="3">
+      <c r="R138" s="5">
         <v>99.6</v>
       </c>
-      <c r="S138" s="14" t="s">
+      <c r="S138" s="20" t="s">
         <v>875</v>
       </c>
-      <c r="T138" s="14" t="s">
+      <c r="T138" s="20" t="s">
         <v>875</v>
       </c>
     </row>
@@ -13050,13 +13199,13 @@
       <c r="F139" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="G139" s="18" t="s">
+      <c r="G139" s="24" t="s">
         <v>879</v>
       </c>
-      <c r="H139" s="14" t="s">
+      <c r="H139" s="20" t="s">
         <v>879</v>
       </c>
-      <c r="I139" s="19" t="s">
+      <c r="I139" s="25" t="s">
         <v>880</v>
       </c>
       <c r="J139" s="1">
@@ -13081,21 +13230,21 @@
         <f t="shared" si="41"/>
         <v>3150</v>
       </c>
-      <c r="P139" s="3">
+      <c r="P139" s="5">
         <f t="shared" si="36"/>
         <v>67</v>
       </c>
-      <c r="Q139" s="3">
+      <c r="Q139" s="5">
         <f t="shared" si="37"/>
         <v>66</v>
       </c>
-      <c r="R139" s="3">
+      <c r="R139" s="5">
         <v>99.8</v>
       </c>
-      <c r="S139" s="14" t="s">
+      <c r="S139" s="20" t="s">
         <v>881</v>
       </c>
-      <c r="T139" s="14" t="s">
+      <c r="T139" s="20" t="s">
         <v>881</v>
       </c>
     </row>
@@ -13112,13 +13261,13 @@
       <c r="F140" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="G140" s="18" t="s">
+      <c r="G140" s="24" t="s">
         <v>885</v>
       </c>
-      <c r="H140" s="14" t="s">
+      <c r="H140" s="20" t="s">
         <v>885</v>
       </c>
-      <c r="I140" s="19" t="s">
+      <c r="I140" s="25" t="s">
         <v>886</v>
       </c>
       <c r="J140" s="1">
@@ -13143,27 +13292,27 @@
         <f t="shared" si="41"/>
         <v>3350</v>
       </c>
-      <c r="P140" s="3">
+      <c r="P140" s="5">
         <f t="shared" si="36"/>
         <v>69</v>
       </c>
-      <c r="Q140" s="3">
+      <c r="Q140" s="5">
         <f t="shared" si="37"/>
         <v>70</v>
       </c>
-      <c r="R140" s="3">
+      <c r="R140" s="5">
         <v>99.9</v>
       </c>
-      <c r="S140" s="14" t="s">
+      <c r="S140" s="20" t="s">
         <v>887</v>
       </c>
-      <c r="T140" s="14" t="s">
+      <c r="T140" s="20" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A141" s="3"/>
-      <c r="B141" s="3"/>
+      <c r="A141" s="5"/>
+      <c r="B141" s="5"/>
       <c r="C141" s="1" t="s">
         <v>888</v>
       </c>
@@ -13176,13 +13325,13 @@
       <c r="F141" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="G141" s="18" t="s">
+      <c r="G141" s="24" t="s">
         <v>891</v>
       </c>
-      <c r="H141" s="14" t="s">
+      <c r="H141" s="20" t="s">
         <v>891</v>
       </c>
-      <c r="I141" s="19" t="s">
+      <c r="I141" s="25" t="s">
         <v>892</v>
       </c>
       <c r="J141" s="1">
@@ -13207,32 +13356,32 @@
         <f t="shared" ref="O141:O180" si="45">O140+250</f>
         <v>3600</v>
       </c>
-      <c r="P141" s="3">
+      <c r="P141" s="5">
         <f t="shared" si="36"/>
         <v>71</v>
       </c>
-      <c r="Q141" s="3">
+      <c r="Q141" s="5">
         <f t="shared" si="37"/>
         <v>74</v>
       </c>
-      <c r="R141" s="3">
+      <c r="R141" s="5">
         <v>99.92</v>
       </c>
-      <c r="S141" s="14" t="s">
+      <c r="S141" s="20" t="s">
         <v>893</v>
       </c>
-      <c r="T141" s="14" t="s">
+      <c r="T141" s="20" t="s">
         <v>893</v>
       </c>
-      <c r="U141" s="3"/>
-      <c r="V141" s="3"/>
-      <c r="W141" s="3"/>
-      <c r="X141" s="3"/>
-      <c r="Y141" s="3"/>
+      <c r="U141" s="5"/>
+      <c r="V141" s="5"/>
+      <c r="W141" s="5"/>
+      <c r="X141" s="5"/>
+      <c r="Y141" s="5"/>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A142" s="3"/>
-      <c r="B142" s="3"/>
+      <c r="A142" s="5"/>
+      <c r="B142" s="5"/>
       <c r="C142" s="1" t="s">
         <v>894</v>
       </c>
@@ -13245,13 +13394,13 @@
       <c r="F142" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="G142" s="18" t="s">
+      <c r="G142" s="24" t="s">
         <v>897</v>
       </c>
-      <c r="H142" s="14" t="s">
+      <c r="H142" s="20" t="s">
         <v>897</v>
       </c>
-      <c r="I142" s="19" t="s">
+      <c r="I142" s="25" t="s">
         <v>898</v>
       </c>
       <c r="J142" s="1">
@@ -13276,32 +13425,32 @@
         <f t="shared" si="45"/>
         <v>3850</v>
       </c>
-      <c r="P142" s="3">
+      <c r="P142" s="5">
         <f t="shared" si="36"/>
         <v>73</v>
       </c>
-      <c r="Q142" s="3">
+      <c r="Q142" s="5">
         <f t="shared" si="37"/>
         <v>78</v>
       </c>
-      <c r="R142" s="3">
+      <c r="R142" s="5">
         <v>99.94</v>
       </c>
-      <c r="S142" s="14" t="s">
+      <c r="S142" s="20" t="s">
         <v>899</v>
       </c>
-      <c r="T142" s="14" t="s">
+      <c r="T142" s="20" t="s">
         <v>899</v>
       </c>
-      <c r="U142" s="3"/>
-      <c r="V142" s="3"/>
-      <c r="W142" s="3"/>
-      <c r="X142" s="3"/>
-      <c r="Y142" s="3"/>
+      <c r="U142" s="5"/>
+      <c r="V142" s="5"/>
+      <c r="W142" s="5"/>
+      <c r="X142" s="5"/>
+      <c r="Y142" s="5"/>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A143" s="3"/>
-      <c r="B143" s="3"/>
+      <c r="A143" s="5"/>
+      <c r="B143" s="5"/>
       <c r="C143" s="1" t="s">
         <v>900</v>
       </c>
@@ -13314,13 +13463,13 @@
       <c r="F143" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="G143" s="18" t="s">
+      <c r="G143" s="24" t="s">
         <v>903</v>
       </c>
-      <c r="H143" s="14" t="s">
+      <c r="H143" s="20" t="s">
         <v>903</v>
       </c>
-      <c r="I143" s="19" t="s">
+      <c r="I143" s="25" t="s">
         <v>904</v>
       </c>
       <c r="J143" s="1">
@@ -13345,32 +13494,32 @@
         <f t="shared" si="45"/>
         <v>4100</v>
       </c>
-      <c r="P143" s="3">
+      <c r="P143" s="5">
         <f t="shared" si="36"/>
         <v>75</v>
       </c>
-      <c r="Q143" s="3">
+      <c r="Q143" s="5">
         <f t="shared" si="37"/>
         <v>82</v>
       </c>
-      <c r="R143" s="3">
+      <c r="R143" s="5">
         <v>99.96</v>
       </c>
-      <c r="S143" s="14" t="s">
+      <c r="S143" s="20" t="s">
         <v>905</v>
       </c>
-      <c r="T143" s="14" t="s">
+      <c r="T143" s="20" t="s">
         <v>905</v>
       </c>
-      <c r="U143" s="3"/>
-      <c r="V143" s="3"/>
-      <c r="W143" s="3"/>
-      <c r="X143" s="3"/>
-      <c r="Y143" s="3"/>
+      <c r="U143" s="5"/>
+      <c r="V143" s="5"/>
+      <c r="W143" s="5"/>
+      <c r="X143" s="5"/>
+      <c r="Y143" s="5"/>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A144" s="3"/>
-      <c r="B144" s="3"/>
+      <c r="A144" s="5"/>
+      <c r="B144" s="5"/>
       <c r="C144" s="1" t="s">
         <v>906</v>
       </c>
@@ -13383,13 +13532,13 @@
       <c r="F144" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="G144" s="18" t="s">
+      <c r="G144" s="24" t="s">
         <v>909</v>
       </c>
-      <c r="H144" s="14" t="s">
+      <c r="H144" s="20" t="s">
         <v>909</v>
       </c>
-      <c r="I144" s="19" t="s">
+      <c r="I144" s="25" t="s">
         <v>910</v>
       </c>
       <c r="J144" s="1">
@@ -13414,32 +13563,32 @@
         <f t="shared" si="45"/>
         <v>4350</v>
       </c>
-      <c r="P144" s="3">
+      <c r="P144" s="5">
         <f t="shared" si="36"/>
         <v>77</v>
       </c>
-      <c r="Q144" s="3">
+      <c r="Q144" s="5">
         <f t="shared" si="37"/>
         <v>86</v>
       </c>
-      <c r="R144" s="3">
+      <c r="R144" s="5">
         <v>99.98</v>
       </c>
-      <c r="S144" s="14" t="s">
+      <c r="S144" s="20" t="s">
         <v>911</v>
       </c>
-      <c r="T144" s="14" t="s">
+      <c r="T144" s="20" t="s">
         <v>911</v>
       </c>
-      <c r="U144" s="3"/>
-      <c r="V144" s="3"/>
-      <c r="W144" s="3"/>
-      <c r="X144" s="3"/>
-      <c r="Y144" s="3"/>
+      <c r="U144" s="5"/>
+      <c r="V144" s="5"/>
+      <c r="W144" s="5"/>
+      <c r="X144" s="5"/>
+      <c r="Y144" s="5"/>
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A145" s="3"/>
-      <c r="B145" s="3"/>
+      <c r="A145" s="5"/>
+      <c r="B145" s="5"/>
       <c r="C145" s="1" t="s">
         <v>912</v>
       </c>
@@ -13452,13 +13601,13 @@
       <c r="F145" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="G145" s="8" t="s">
+      <c r="G145" s="10" t="s">
         <v>915</v>
       </c>
-      <c r="H145" s="8" t="s">
+      <c r="H145" s="10" t="s">
         <v>915</v>
       </c>
-      <c r="I145" s="10" t="s">
+      <c r="I145" s="12" t="s">
         <v>916</v>
       </c>
       <c r="J145" s="1">
@@ -13483,32 +13632,32 @@
         <f t="shared" si="45"/>
         <v>4600</v>
       </c>
-      <c r="P145" s="3">
+      <c r="P145" s="5">
         <f t="shared" si="36"/>
         <v>79</v>
       </c>
-      <c r="Q145" s="3">
+      <c r="Q145" s="5">
         <f t="shared" si="37"/>
         <v>90</v>
       </c>
-      <c r="R145" s="3">
+      <c r="R145" s="5">
         <v>99.99</v>
       </c>
-      <c r="S145" s="14" t="s">
+      <c r="S145" s="20" t="s">
         <v>917</v>
       </c>
-      <c r="T145" s="14" t="s">
+      <c r="T145" s="20" t="s">
         <v>917</v>
       </c>
-      <c r="U145" s="3"/>
-      <c r="V145" s="3"/>
-      <c r="W145" s="3"/>
-      <c r="X145" s="3"/>
-      <c r="Y145" s="3"/>
+      <c r="U145" s="5"/>
+      <c r="V145" s="5"/>
+      <c r="W145" s="5"/>
+      <c r="X145" s="5"/>
+      <c r="Y145" s="5"/>
     </row>
     <row r="146" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A146" s="11"/>
-      <c r="B146" s="11"/>
+      <c r="A146" s="13"/>
+      <c r="B146" s="13"/>
       <c r="C146" s="2" t="s">
         <v>918</v>
       </c>
@@ -13521,13 +13670,13 @@
       <c r="F146" s="2" t="s">
         <v>920</v>
       </c>
-      <c r="G146" s="12" t="s">
+      <c r="G146" s="14" t="s">
         <v>921</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="I146" s="13" t="s">
+      <c r="I146" s="19" t="s">
         <v>923</v>
       </c>
       <c r="J146" s="2">
@@ -13552,29 +13701,29 @@
         <f t="shared" si="45"/>
         <v>4850</v>
       </c>
-      <c r="P146" s="11">
+      <c r="P146" s="13">
         <f t="shared" ref="P146:P160" si="46">P145+3</f>
         <v>82</v>
       </c>
-      <c r="Q146" s="11">
+      <c r="Q146" s="13">
         <v>150</v>
       </c>
-      <c r="R146" s="11">
+      <c r="R146" s="13">
         <v>99.99</v>
       </c>
-      <c r="S146" s="20" t="s">
+      <c r="S146" s="26" t="s">
         <v>925</v>
       </c>
-      <c r="T146" s="20" t="s">
+      <c r="T146" s="26" t="s">
         <v>925</v>
       </c>
-      <c r="W146" s="11"/>
-      <c r="X146" s="11"/>
-      <c r="Y146" s="11"/>
+      <c r="W146" s="13"/>
+      <c r="X146" s="13"/>
+      <c r="Y146" s="13"/>
     </row>
     <row r="147" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A147" s="3"/>
-      <c r="B147" s="3"/>
+      <c r="A147" s="5"/>
+      <c r="B147" s="5"/>
       <c r="C147" s="1" t="s">
         <v>926</v>
       </c>
@@ -13587,13 +13736,13 @@
       <c r="F147" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="G147" s="8" t="s">
+      <c r="G147" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="H147" s="8" t="s">
+      <c r="H147" s="10" t="s">
         <v>930</v>
       </c>
-      <c r="I147" s="10" t="s">
+      <c r="I147" s="12" t="s">
         <v>931</v>
       </c>
       <c r="J147" s="1">
@@ -13619,30 +13768,30 @@
         <f t="shared" si="45"/>
         <v>5100</v>
       </c>
-      <c r="P147" s="3">
+      <c r="P147" s="5">
         <f t="shared" si="46"/>
         <v>85</v>
       </c>
-      <c r="Q147" s="3">
+      <c r="Q147" s="5">
         <f t="shared" si="37"/>
         <v>154</v>
       </c>
-      <c r="R147" s="3">
+      <c r="R147" s="5">
         <v>99.99</v>
       </c>
-      <c r="S147" s="14" t="s">
+      <c r="S147" s="20" t="s">
         <v>933</v>
       </c>
-      <c r="T147" s="14" t="s">
+      <c r="T147" s="20" t="s">
         <v>933</v>
       </c>
-      <c r="W147" s="3"/>
-      <c r="X147" s="3"/>
-      <c r="Y147" s="3"/>
+      <c r="W147" s="5"/>
+      <c r="X147" s="5"/>
+      <c r="Y147" s="5"/>
     </row>
     <row r="148" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A148" s="3"/>
-      <c r="B148" s="3"/>
+      <c r="A148" s="5"/>
+      <c r="B148" s="5"/>
       <c r="C148" s="1" t="s">
         <v>934</v>
       </c>
@@ -13655,13 +13804,13 @@
       <c r="F148" s="1" t="s">
         <v>936</v>
       </c>
-      <c r="G148" s="8" t="s">
+      <c r="G148" s="10" t="s">
         <v>937</v>
       </c>
-      <c r="H148" s="8" t="s">
+      <c r="H148" s="10" t="s">
         <v>938</v>
       </c>
-      <c r="I148" s="10" t="s">
+      <c r="I148" s="12" t="s">
         <v>939</v>
       </c>
       <c r="J148" s="1">
@@ -13687,30 +13836,30 @@
         <f t="shared" si="45"/>
         <v>5350</v>
       </c>
-      <c r="P148" s="3">
+      <c r="P148" s="5">
         <f t="shared" si="46"/>
         <v>88</v>
       </c>
-      <c r="Q148" s="3">
+      <c r="Q148" s="5">
         <f t="shared" si="37"/>
         <v>158</v>
       </c>
-      <c r="R148" s="3">
+      <c r="R148" s="5">
         <v>99.99</v>
       </c>
-      <c r="S148" s="14" t="s">
+      <c r="S148" s="20" t="s">
         <v>941</v>
       </c>
-      <c r="T148" s="14" t="s">
+      <c r="T148" s="20" t="s">
         <v>941</v>
       </c>
-      <c r="W148" s="3"/>
-      <c r="X148" s="3"/>
-      <c r="Y148" s="3"/>
+      <c r="W148" s="5"/>
+      <c r="X148" s="5"/>
+      <c r="Y148" s="5"/>
     </row>
     <row r="149" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A149" s="3"/>
-      <c r="B149" s="3"/>
+      <c r="A149" s="5"/>
+      <c r="B149" s="5"/>
       <c r="C149" s="1" t="s">
         <v>942</v>
       </c>
@@ -13723,13 +13872,13 @@
       <c r="F149" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="G149" s="8" t="s">
+      <c r="G149" s="10" t="s">
         <v>945</v>
       </c>
-      <c r="H149" s="8" t="s">
+      <c r="H149" s="10" t="s">
         <v>946</v>
       </c>
-      <c r="I149" s="10" t="s">
+      <c r="I149" s="12" t="s">
         <v>947</v>
       </c>
       <c r="J149" s="1">
@@ -13755,30 +13904,30 @@
         <f t="shared" si="45"/>
         <v>5600</v>
       </c>
-      <c r="P149" s="3">
+      <c r="P149" s="5">
         <f t="shared" si="46"/>
         <v>91</v>
       </c>
-      <c r="Q149" s="3">
+      <c r="Q149" s="5">
         <f t="shared" si="37"/>
         <v>162</v>
       </c>
-      <c r="R149" s="3">
+      <c r="R149" s="5">
         <v>99.99</v>
       </c>
-      <c r="S149" s="14" t="s">
+      <c r="S149" s="20" t="s">
         <v>949</v>
       </c>
-      <c r="T149" s="14" t="s">
+      <c r="T149" s="20" t="s">
         <v>949</v>
       </c>
-      <c r="W149" s="3"/>
-      <c r="X149" s="3"/>
-      <c r="Y149" s="3"/>
+      <c r="W149" s="5"/>
+      <c r="X149" s="5"/>
+      <c r="Y149" s="5"/>
     </row>
     <row r="150" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A150" s="3"/>
-      <c r="B150" s="3"/>
+      <c r="A150" s="5"/>
+      <c r="B150" s="5"/>
       <c r="C150" s="1" t="s">
         <v>950</v>
       </c>
@@ -13791,13 +13940,13 @@
       <c r="F150" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="G150" s="8" t="s">
+      <c r="G150" s="10" t="s">
         <v>953</v>
       </c>
-      <c r="H150" s="8" t="s">
+      <c r="H150" s="10" t="s">
         <v>954</v>
       </c>
-      <c r="I150" s="10" t="s">
+      <c r="I150" s="12" t="s">
         <v>955</v>
       </c>
       <c r="J150" s="1">
@@ -13823,30 +13972,30 @@
         <f t="shared" si="45"/>
         <v>5850</v>
       </c>
-      <c r="P150" s="3">
+      <c r="P150" s="5">
         <f t="shared" si="46"/>
         <v>94</v>
       </c>
-      <c r="Q150" s="3">
+      <c r="Q150" s="5">
         <f t="shared" si="37"/>
         <v>166</v>
       </c>
-      <c r="R150" s="3">
+      <c r="R150" s="5">
         <v>99.99</v>
       </c>
-      <c r="S150" s="14" t="s">
+      <c r="S150" s="20" t="s">
         <v>957</v>
       </c>
-      <c r="T150" s="14" t="s">
+      <c r="T150" s="20" t="s">
         <v>957</v>
       </c>
-      <c r="W150" s="3"/>
-      <c r="X150" s="3"/>
-      <c r="Y150" s="3"/>
+      <c r="W150" s="5"/>
+      <c r="X150" s="5"/>
+      <c r="Y150" s="5"/>
     </row>
     <row r="151" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A151" s="3"/>
-      <c r="B151" s="3"/>
+      <c r="A151" s="5"/>
+      <c r="B151" s="5"/>
       <c r="C151" s="1" t="s">
         <v>958</v>
       </c>
@@ -13862,7 +14011,7 @@
       <c r="G151" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="H151" s="8" t="s">
+      <c r="H151" s="10" t="s">
         <v>962</v>
       </c>
       <c r="I151" s="1" t="s">
@@ -13890,32 +14039,32 @@
         <f t="shared" si="45"/>
         <v>6100</v>
       </c>
-      <c r="P151" s="3">
+      <c r="P151" s="5">
         <f t="shared" si="46"/>
         <v>97</v>
       </c>
-      <c r="Q151" s="3">
+      <c r="Q151" s="5">
         <f t="shared" si="37"/>
         <v>170</v>
       </c>
-      <c r="R151" s="3">
+      <c r="R151" s="5">
         <v>99.99</v>
       </c>
-      <c r="S151" s="14" t="s">
+      <c r="S151" s="20" t="s">
         <v>966</v>
       </c>
-      <c r="T151" s="14" t="s">
+      <c r="T151" s="20" t="s">
         <v>966</v>
       </c>
-      <c r="U151" s="3"/>
-      <c r="V151" s="3"/>
-      <c r="W151" s="3"/>
-      <c r="X151" s="3"/>
-      <c r="Y151" s="3"/>
+      <c r="U151" s="5"/>
+      <c r="V151" s="5"/>
+      <c r="W151" s="5"/>
+      <c r="X151" s="5"/>
+      <c r="Y151" s="5"/>
     </row>
     <row r="152" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A152" s="3"/>
-      <c r="B152" s="3"/>
+      <c r="A152" s="5"/>
+      <c r="B152" s="5"/>
       <c r="C152" s="1" t="s">
         <v>967</v>
       </c>
@@ -13931,7 +14080,7 @@
       <c r="G152" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="H152" s="8" t="s">
+      <c r="H152" s="10" t="s">
         <v>971</v>
       </c>
       <c r="I152" s="1" t="s">
@@ -13959,32 +14108,32 @@
         <f t="shared" si="45"/>
         <v>6350</v>
       </c>
-      <c r="P152" s="3">
+      <c r="P152" s="5">
         <f t="shared" si="46"/>
         <v>100</v>
       </c>
-      <c r="Q152" s="3">
+      <c r="Q152" s="5">
         <f t="shared" si="37"/>
         <v>174</v>
       </c>
-      <c r="R152" s="3">
+      <c r="R152" s="5">
         <v>99.99</v>
       </c>
-      <c r="S152" s="14" t="s">
+      <c r="S152" s="20" t="s">
         <v>975</v>
       </c>
-      <c r="T152" s="14" t="s">
+      <c r="T152" s="20" t="s">
         <v>975</v>
       </c>
-      <c r="U152" s="3"/>
-      <c r="V152" s="3"/>
-      <c r="W152" s="3"/>
-      <c r="X152" s="3"/>
-      <c r="Y152" s="3"/>
+      <c r="U152" s="5"/>
+      <c r="V152" s="5"/>
+      <c r="W152" s="5"/>
+      <c r="X152" s="5"/>
+      <c r="Y152" s="5"/>
     </row>
     <row r="153" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A153" s="3"/>
-      <c r="B153" s="3"/>
+      <c r="A153" s="5"/>
+      <c r="B153" s="5"/>
       <c r="C153" s="1" t="s">
         <v>976</v>
       </c>
@@ -14000,7 +14149,7 @@
       <c r="G153" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="H153" s="8" t="s">
+      <c r="H153" s="10" t="s">
         <v>980</v>
       </c>
       <c r="I153" s="1" t="s">
@@ -14028,32 +14177,32 @@
         <f t="shared" si="45"/>
         <v>6600</v>
       </c>
-      <c r="P153" s="3">
+      <c r="P153" s="5">
         <f t="shared" si="46"/>
         <v>103</v>
       </c>
-      <c r="Q153" s="3">
+      <c r="Q153" s="5">
         <f t="shared" si="37"/>
         <v>178</v>
       </c>
-      <c r="R153" s="3">
+      <c r="R153" s="5">
         <v>99.99</v>
       </c>
-      <c r="S153" s="14" t="s">
+      <c r="S153" s="20" t="s">
         <v>984</v>
       </c>
-      <c r="T153" s="14" t="s">
+      <c r="T153" s="20" t="s">
         <v>984</v>
       </c>
-      <c r="U153" s="3"/>
-      <c r="V153" s="3"/>
-      <c r="W153" s="3"/>
-      <c r="X153" s="3"/>
-      <c r="Y153" s="3"/>
+      <c r="U153" s="5"/>
+      <c r="V153" s="5"/>
+      <c r="W153" s="5"/>
+      <c r="X153" s="5"/>
+      <c r="Y153" s="5"/>
     </row>
     <row r="154" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A154" s="3"/>
-      <c r="B154" s="3"/>
+      <c r="A154" s="5"/>
+      <c r="B154" s="5"/>
       <c r="C154" s="1" t="s">
         <v>985</v>
       </c>
@@ -14069,7 +14218,7 @@
       <c r="G154" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="H154" s="8" t="s">
+      <c r="H154" s="10" t="s">
         <v>989</v>
       </c>
       <c r="I154" s="1" t="s">
@@ -14097,32 +14246,32 @@
         <f t="shared" si="45"/>
         <v>6850</v>
       </c>
-      <c r="P154" s="3">
+      <c r="P154" s="5">
         <f t="shared" si="46"/>
         <v>106</v>
       </c>
-      <c r="Q154" s="3">
+      <c r="Q154" s="5">
         <f t="shared" si="37"/>
         <v>182</v>
       </c>
-      <c r="R154" s="3">
+      <c r="R154" s="5">
         <v>99.99</v>
       </c>
-      <c r="S154" s="14" t="s">
+      <c r="S154" s="20" t="s">
         <v>993</v>
       </c>
-      <c r="T154" s="14" t="s">
+      <c r="T154" s="20" t="s">
         <v>993</v>
       </c>
-      <c r="U154" s="3"/>
-      <c r="V154" s="3"/>
-      <c r="W154" s="3"/>
-      <c r="X154" s="3"/>
-      <c r="Y154" s="3"/>
+      <c r="U154" s="5"/>
+      <c r="V154" s="5"/>
+      <c r="W154" s="5"/>
+      <c r="X154" s="5"/>
+      <c r="Y154" s="5"/>
     </row>
     <row r="155" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A155" s="3"/>
-      <c r="B155" s="3"/>
+      <c r="A155" s="5"/>
+      <c r="B155" s="5"/>
       <c r="C155" s="1" t="s">
         <v>994</v>
       </c>
@@ -14138,7 +14287,7 @@
       <c r="G155" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="H155" s="8" t="s">
+      <c r="H155" s="10" t="s">
         <v>998</v>
       </c>
       <c r="I155" s="1" t="s">
@@ -14166,32 +14315,32 @@
         <f t="shared" si="45"/>
         <v>7100</v>
       </c>
-      <c r="P155" s="3">
+      <c r="P155" s="5">
         <f t="shared" si="46"/>
         <v>109</v>
       </c>
-      <c r="Q155" s="3">
+      <c r="Q155" s="5">
         <f t="shared" si="37"/>
         <v>186</v>
       </c>
-      <c r="R155" s="3">
+      <c r="R155" s="5">
         <v>99.99</v>
       </c>
-      <c r="S155" s="14" t="s">
+      <c r="S155" s="20" t="s">
         <v>1002</v>
       </c>
-      <c r="T155" s="14" t="s">
+      <c r="T155" s="20" t="s">
         <v>1002</v>
       </c>
-      <c r="U155" s="3"/>
-      <c r="V155" s="3"/>
-      <c r="W155" s="3"/>
-      <c r="X155" s="3"/>
-      <c r="Y155" s="3"/>
+      <c r="U155" s="5"/>
+      <c r="V155" s="5"/>
+      <c r="W155" s="5"/>
+      <c r="X155" s="5"/>
+      <c r="Y155" s="5"/>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A156" s="3"/>
-      <c r="B156" s="3"/>
+      <c r="A156" s="5"/>
+      <c r="B156" s="5"/>
       <c r="C156" s="1" t="s">
         <v>1003</v>
       </c>
@@ -14207,7 +14356,7 @@
       <c r="G156" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H156" s="8" t="s">
+      <c r="H156" s="10" t="s">
         <v>1007</v>
       </c>
       <c r="I156" s="1" t="s">
@@ -14235,32 +14384,32 @@
         <f t="shared" si="45"/>
         <v>7350</v>
       </c>
-      <c r="P156" s="3">
+      <c r="P156" s="5">
         <f t="shared" si="46"/>
         <v>112</v>
       </c>
-      <c r="Q156" s="3">
+      <c r="Q156" s="5">
         <f t="shared" si="37"/>
         <v>190</v>
       </c>
-      <c r="R156" s="3">
+      <c r="R156" s="5">
         <v>99.99</v>
       </c>
-      <c r="S156" s="14" t="s">
+      <c r="S156" s="20" t="s">
         <v>1011</v>
       </c>
-      <c r="T156" s="14" t="s">
+      <c r="T156" s="20" t="s">
         <v>1011</v>
       </c>
-      <c r="U156" s="3"/>
-      <c r="V156" s="3"/>
-      <c r="W156" s="3"/>
-      <c r="X156" s="3"/>
-      <c r="Y156" s="3"/>
+      <c r="U156" s="5"/>
+      <c r="V156" s="5"/>
+      <c r="W156" s="5"/>
+      <c r="X156" s="5"/>
+      <c r="Y156" s="5"/>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A157" s="3"/>
-      <c r="B157" s="3"/>
+      <c r="A157" s="5"/>
+      <c r="B157" s="5"/>
       <c r="C157" s="1" t="s">
         <v>1012</v>
       </c>
@@ -14276,7 +14425,7 @@
       <c r="G157" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="H157" s="8" t="s">
+      <c r="H157" s="10" t="s">
         <v>1016</v>
       </c>
       <c r="I157" s="1" t="s">
@@ -14304,32 +14453,32 @@
         <f t="shared" si="45"/>
         <v>7600</v>
       </c>
-      <c r="P157" s="3">
+      <c r="P157" s="5">
         <f t="shared" si="46"/>
         <v>115</v>
       </c>
-      <c r="Q157" s="3">
+      <c r="Q157" s="5">
         <f t="shared" si="37"/>
         <v>194</v>
       </c>
-      <c r="R157" s="3">
+      <c r="R157" s="5">
         <v>99.99</v>
       </c>
-      <c r="S157" s="14" t="s">
+      <c r="S157" s="20" t="s">
         <v>1020</v>
       </c>
-      <c r="T157" s="14" t="s">
+      <c r="T157" s="20" t="s">
         <v>1020</v>
       </c>
-      <c r="U157" s="3"/>
-      <c r="V157" s="3"/>
-      <c r="W157" s="3"/>
-      <c r="X157" s="3"/>
-      <c r="Y157" s="3"/>
+      <c r="U157" s="5"/>
+      <c r="V157" s="5"/>
+      <c r="W157" s="5"/>
+      <c r="X157" s="5"/>
+      <c r="Y157" s="5"/>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A158" s="3"/>
-      <c r="B158" s="3"/>
+      <c r="A158" s="5"/>
+      <c r="B158" s="5"/>
       <c r="C158" s="1" t="s">
         <v>1021</v>
       </c>
@@ -14345,7 +14494,7 @@
       <c r="G158" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="H158" s="8" t="s">
+      <c r="H158" s="10" t="s">
         <v>1025</v>
       </c>
       <c r="I158" s="1" t="s">
@@ -14373,32 +14522,32 @@
         <f t="shared" si="45"/>
         <v>7850</v>
       </c>
-      <c r="P158" s="3">
+      <c r="P158" s="5">
         <f t="shared" si="46"/>
         <v>118</v>
       </c>
-      <c r="Q158" s="3">
+      <c r="Q158" s="5">
         <f t="shared" si="37"/>
         <v>198</v>
       </c>
-      <c r="R158" s="3">
+      <c r="R158" s="5">
         <v>99.99</v>
       </c>
-      <c r="S158" s="14" t="s">
+      <c r="S158" s="20" t="s">
         <v>1029</v>
       </c>
-      <c r="T158" s="14" t="s">
+      <c r="T158" s="20" t="s">
         <v>1029</v>
       </c>
-      <c r="U158" s="3"/>
-      <c r="V158" s="3"/>
-      <c r="W158" s="3"/>
-      <c r="X158" s="3"/>
-      <c r="Y158" s="3"/>
+      <c r="U158" s="5"/>
+      <c r="V158" s="5"/>
+      <c r="W158" s="5"/>
+      <c r="X158" s="5"/>
+      <c r="Y158" s="5"/>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A159" s="3"/>
-      <c r="B159" s="3"/>
+      <c r="A159" s="5"/>
+      <c r="B159" s="5"/>
       <c r="C159" s="1" t="s">
         <v>1030</v>
       </c>
@@ -14414,7 +14563,7 @@
       <c r="G159" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="H159" s="8" t="s">
+      <c r="H159" s="10" t="s">
         <v>1034</v>
       </c>
       <c r="I159" s="1" t="s">
@@ -14442,32 +14591,32 @@
         <f t="shared" si="45"/>
         <v>8100</v>
       </c>
-      <c r="P159" s="3">
+      <c r="P159" s="5">
         <f t="shared" si="46"/>
         <v>121</v>
       </c>
-      <c r="Q159" s="3">
+      <c r="Q159" s="5">
         <f t="shared" si="37"/>
         <v>202</v>
       </c>
-      <c r="R159" s="3">
+      <c r="R159" s="5">
         <v>99.99</v>
       </c>
-      <c r="S159" s="14" t="s">
+      <c r="S159" s="20" t="s">
         <v>1038</v>
       </c>
-      <c r="T159" s="14" t="s">
+      <c r="T159" s="20" t="s">
         <v>1038</v>
       </c>
-      <c r="U159" s="3"/>
-      <c r="V159" s="3"/>
-      <c r="W159" s="3"/>
-      <c r="X159" s="3"/>
-      <c r="Y159" s="3"/>
+      <c r="U159" s="5"/>
+      <c r="V159" s="5"/>
+      <c r="W159" s="5"/>
+      <c r="X159" s="5"/>
+      <c r="Y159" s="5"/>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A160" s="3"/>
-      <c r="B160" s="3"/>
+      <c r="A160" s="5"/>
+      <c r="B160" s="5"/>
       <c r="C160" s="1" t="s">
         <v>1039</v>
       </c>
@@ -14483,7 +14632,7 @@
       <c r="G160" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="H160" s="8" t="s">
+      <c r="H160" s="10" t="s">
         <v>1043</v>
       </c>
       <c r="I160" s="1" t="s">
@@ -14511,32 +14660,32 @@
         <f t="shared" si="45"/>
         <v>8350</v>
       </c>
-      <c r="P160" s="3">
+      <c r="P160" s="5">
         <f t="shared" si="46"/>
         <v>124</v>
       </c>
-      <c r="Q160" s="3">
+      <c r="Q160" s="5">
         <f t="shared" si="37"/>
         <v>206</v>
       </c>
-      <c r="R160" s="3">
+      <c r="R160" s="5">
         <v>99.99</v>
       </c>
-      <c r="S160" s="14" t="s">
+      <c r="S160" s="20" t="s">
         <v>1047</v>
       </c>
-      <c r="T160" s="14" t="s">
+      <c r="T160" s="20" t="s">
         <v>1047</v>
       </c>
-      <c r="U160" s="3"/>
-      <c r="V160" s="3"/>
-      <c r="W160" s="3"/>
-      <c r="X160" s="3"/>
-      <c r="Y160" s="3"/>
+      <c r="U160" s="5"/>
+      <c r="V160" s="5"/>
+      <c r="W160" s="5"/>
+      <c r="X160" s="5"/>
+      <c r="Y160" s="5"/>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A161" s="3"/>
-      <c r="B161" s="3"/>
+      <c r="A161" s="5"/>
+      <c r="B161" s="5"/>
       <c r="C161" s="1" t="s">
         <v>1048</v>
       </c>
@@ -14552,7 +14701,7 @@
       <c r="G161" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="H161" s="8" t="s">
+      <c r="H161" s="10" t="s">
         <v>1052</v>
       </c>
       <c r="I161" s="1" t="s">
@@ -14580,32 +14729,32 @@
         <f t="shared" si="45"/>
         <v>8600</v>
       </c>
-      <c r="P161" s="3">
+      <c r="P161" s="5">
         <f>P160+4</f>
         <v>128</v>
       </c>
-      <c r="Q161" s="3">
+      <c r="Q161" s="5">
         <f>Q160+5</f>
         <v>211</v>
       </c>
-      <c r="R161" s="3">
+      <c r="R161" s="5">
         <v>99.99</v>
       </c>
-      <c r="S161" s="14" t="s">
+      <c r="S161" s="20" t="s">
         <v>1056</v>
       </c>
-      <c r="T161" s="14" t="s">
+      <c r="T161" s="20" t="s">
         <v>1056</v>
       </c>
-      <c r="U161" s="3"/>
-      <c r="V161" s="3"/>
-      <c r="W161" s="3"/>
-      <c r="X161" s="3"/>
-      <c r="Y161" s="3"/>
+      <c r="U161" s="5"/>
+      <c r="V161" s="5"/>
+      <c r="W161" s="5"/>
+      <c r="X161" s="5"/>
+      <c r="Y161" s="5"/>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A162" s="3"/>
-      <c r="B162" s="3"/>
+      <c r="A162" s="5"/>
+      <c r="B162" s="5"/>
       <c r="C162" s="1" t="s">
         <v>1057</v>
       </c>
@@ -14621,7 +14770,7 @@
       <c r="G162" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="H162" s="8" t="s">
+      <c r="H162" s="10" t="s">
         <v>1061</v>
       </c>
       <c r="I162" s="1" t="s">
@@ -14649,32 +14798,32 @@
         <f t="shared" si="45"/>
         <v>8850</v>
       </c>
-      <c r="P162" s="3">
+      <c r="P162" s="5">
         <f>P161+4</f>
         <v>132</v>
       </c>
-      <c r="Q162" s="3">
+      <c r="Q162" s="5">
         <f>Q161+5</f>
         <v>216</v>
       </c>
-      <c r="R162" s="3">
+      <c r="R162" s="5">
         <v>99.99</v>
       </c>
-      <c r="S162" s="14" t="s">
+      <c r="S162" s="20" t="s">
         <v>1065</v>
       </c>
-      <c r="T162" s="14" t="s">
+      <c r="T162" s="20" t="s">
         <v>1065</v>
       </c>
-      <c r="U162" s="3"/>
-      <c r="V162" s="3"/>
-      <c r="W162" s="3"/>
-      <c r="X162" s="3"/>
-      <c r="Y162" s="3"/>
+      <c r="U162" s="5"/>
+      <c r="V162" s="5"/>
+      <c r="W162" s="5"/>
+      <c r="X162" s="5"/>
+      <c r="Y162" s="5"/>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A163" s="3"/>
-      <c r="B163" s="3"/>
+      <c r="A163" s="5"/>
+      <c r="B163" s="5"/>
       <c r="C163" s="1" t="s">
         <v>1066</v>
       </c>
@@ -14690,7 +14839,7 @@
       <c r="G163" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="H163" s="8" t="s">
+      <c r="H163" s="10" t="s">
         <v>1070</v>
       </c>
       <c r="I163" s="1" t="s">
@@ -14718,166 +14867,166 @@
         <f t="shared" si="45"/>
         <v>9100</v>
       </c>
-      <c r="P163" s="3">
+      <c r="P163" s="5">
         <f>P162+4</f>
         <v>136</v>
       </c>
-      <c r="Q163" s="3">
+      <c r="Q163" s="5">
         <f>Q162+5</f>
         <v>221</v>
       </c>
-      <c r="R163" s="3">
+      <c r="R163" s="5">
         <v>99.99</v>
       </c>
-      <c r="S163" s="14" t="s">
+      <c r="S163" s="20" t="s">
         <v>1074</v>
       </c>
-      <c r="T163" s="14" t="s">
+      <c r="T163" s="20" t="s">
         <v>1074</v>
       </c>
-      <c r="U163" s="3"/>
-      <c r="V163" s="3"/>
-      <c r="W163" s="3"/>
-      <c r="X163" s="3"/>
-      <c r="Y163" s="3"/>
-    </row>
-    <row r="164" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A164" s="3"/>
-      <c r="B164" s="3"/>
-      <c r="C164" s="1" t="s">
+      <c r="U163" s="5"/>
+      <c r="V163" s="5"/>
+      <c r="W163" s="5"/>
+      <c r="X163" s="5"/>
+      <c r="Y163" s="5"/>
+    </row>
+    <row r="164" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A164" s="15"/>
+      <c r="B164" s="15"/>
+      <c r="C164" s="3" t="s">
         <v>1075</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="D164" s="3" t="s">
         <v>1076</v>
       </c>
-      <c r="E164" s="1">
+      <c r="E164" s="3">
         <v>4</v>
       </c>
-      <c r="F164" s="1" t="s">
+      <c r="F164" s="3" t="s">
         <v>1077</v>
       </c>
-      <c r="G164" s="1" t="s">
+      <c r="G164" s="3" t="s">
         <v>1078</v>
       </c>
-      <c r="H164" s="1" t="s">
+      <c r="H164" s="3" t="s">
         <v>1079</v>
       </c>
-      <c r="I164" s="1" t="s">
+      <c r="I164" s="3" t="s">
         <v>1080</v>
       </c>
-      <c r="J164" s="1" t="s">
+      <c r="J164" s="3" t="s">
         <v>1081</v>
       </c>
-      <c r="K164" s="1" t="s">
+      <c r="K164" s="3" t="s">
         <v>1082</v>
       </c>
-      <c r="L164" s="1">
+      <c r="L164" s="3">
         <f t="shared" si="42"/>
         <v>23200</v>
       </c>
-      <c r="M164" s="1">
+      <c r="M164" s="3">
         <f t="shared" si="43"/>
         <v>24900</v>
       </c>
-      <c r="N164" s="1">
+      <c r="N164" s="3">
         <f t="shared" si="44"/>
         <v>9350</v>
       </c>
-      <c r="O164" s="1">
+      <c r="O164" s="3">
         <f t="shared" si="45"/>
         <v>9350</v>
       </c>
-      <c r="P164" s="3">
+      <c r="P164" s="15">
         <f>P163+4</f>
         <v>140</v>
       </c>
-      <c r="Q164" s="3">
+      <c r="Q164" s="15">
         <f>Q163+5</f>
         <v>226</v>
       </c>
-      <c r="R164" s="3">
+      <c r="R164" s="15">
         <v>99.99</v>
       </c>
-      <c r="S164" s="14" t="s">
+      <c r="S164" s="27" t="s">
         <v>1083</v>
       </c>
-      <c r="T164" s="14" t="s">
+      <c r="T164" s="27" t="s">
         <v>1083</v>
       </c>
-      <c r="U164" s="3"/>
-      <c r="V164" s="3"/>
-      <c r="W164" s="3"/>
-      <c r="X164" s="3"/>
-      <c r="Y164" s="3"/>
-    </row>
-    <row r="165" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A165" s="3"/>
-      <c r="B165" s="3"/>
-      <c r="C165" s="1" t="s">
+      <c r="U164" s="15"/>
+      <c r="V164" s="15"/>
+      <c r="W164" s="15"/>
+      <c r="X164" s="15"/>
+      <c r="Y164" s="15"/>
+    </row>
+    <row r="165" s="4" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A165" s="16"/>
+      <c r="B165" s="16"/>
+      <c r="C165" s="4" t="s">
         <v>1084</v>
       </c>
-      <c r="D165" s="1" t="s">
+      <c r="D165" s="4" t="s">
         <v>1085</v>
       </c>
-      <c r="E165" s="1">
+      <c r="E165" s="4">
         <v>4</v>
       </c>
-      <c r="F165" s="1" t="s">
+      <c r="F165" s="4" t="s">
         <v>1086</v>
       </c>
-      <c r="G165" s="1" t="s">
+      <c r="G165" s="28" t="s">
         <v>1087</v>
       </c>
-      <c r="H165" s="1" t="s">
+      <c r="H165" s="4" t="s">
         <v>1088</v>
       </c>
-      <c r="I165" s="1" t="s">
+      <c r="I165" s="4" t="s">
         <v>1089</v>
       </c>
-      <c r="J165" s="1" t="s">
+      <c r="J165" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="K165" s="1" t="s">
+      <c r="K165" s="4" t="s">
         <v>1091</v>
       </c>
-      <c r="L165" s="1">
+      <c r="L165" s="4">
         <f t="shared" si="42"/>
         <v>23800</v>
       </c>
-      <c r="M165" s="1">
+      <c r="M165" s="4">
         <f t="shared" si="43"/>
         <v>25500</v>
       </c>
-      <c r="N165" s="1">
+      <c r="N165" s="4">
         <f t="shared" si="44"/>
         <v>9600</v>
       </c>
-      <c r="O165" s="1">
+      <c r="O165" s="4">
         <f t="shared" si="45"/>
         <v>9600</v>
       </c>
-      <c r="P165" s="3">
+      <c r="P165" s="16">
         <f>P164+4</f>
         <v>144</v>
       </c>
-      <c r="Q165" s="3">
+      <c r="Q165" s="16">
         <f>Q164+5</f>
         <v>231</v>
       </c>
-      <c r="R165" s="3">
+      <c r="R165" s="16">
         <v>99.99</v>
       </c>
-      <c r="S165" s="14" t="s">
+      <c r="S165" s="29" t="s">
         <v>1092</v>
       </c>
-      <c r="T165" s="14" t="s">
+      <c r="T165" s="29" t="s">
         <v>1092</v>
       </c>
-      <c r="U165" s="3"/>
-      <c r="V165" s="3"/>
-      <c r="W165" s="3"/>
-      <c r="X165" s="3"/>
-      <c r="Y165" s="3"/>
+      <c r="U165" s="16"/>
+      <c r="V165" s="16"/>
+      <c r="W165" s="16"/>
+      <c r="X165" s="16"/>
+      <c r="Y165" s="16"/>
     </row>
     <row r="166" customHeight="1" spans="3:20">
       <c r="C166" s="1" t="s">
@@ -14892,20 +15041,20 @@
       <c r="F166" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="G166" s="1">
-        <v>0</v>
-      </c>
-      <c r="H166" s="1">
-        <v>0</v>
-      </c>
-      <c r="I166" s="1">
-        <v>0</v>
-      </c>
-      <c r="J166" s="1">
-        <v>0</v>
-      </c>
-      <c r="K166" s="1">
-        <v>0</v>
+      <c r="G166" s="30" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H166" s="30" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I166" s="30" t="s">
+        <v>1098</v>
+      </c>
+      <c r="J166" s="30" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K166" s="30" t="s">
+        <v>1100</v>
       </c>
       <c r="L166" s="1">
         <f t="shared" si="42"/>
@@ -14916,58 +15065,58 @@
         <v>26100</v>
       </c>
       <c r="N166" s="1">
-        <f t="shared" si="44"/>
-        <v>9850</v>
+        <f t="shared" ref="N166:N170" si="48">N165+300</f>
+        <v>9900</v>
       </c>
       <c r="O166" s="1">
-        <f t="shared" si="45"/>
-        <v>9850</v>
-      </c>
-      <c r="P166" s="3">
-        <f t="shared" ref="P166:P180" si="48">P165+5</f>
+        <f t="shared" ref="O166:O170" si="49">O165+300</f>
+        <v>9900</v>
+      </c>
+      <c r="P166" s="5">
+        <f t="shared" ref="P166:P180" si="50">P165+5</f>
         <v>149</v>
       </c>
-      <c r="Q166" s="3">
-        <f t="shared" ref="Q166:Q180" si="49">Q165+6</f>
+      <c r="Q166" s="5">
+        <f t="shared" ref="Q166:Q180" si="51">Q165+6</f>
         <v>237</v>
       </c>
-      <c r="R166" s="3">
+      <c r="R166" s="5">
         <v>99.99</v>
       </c>
-      <c r="S166" s="14" t="s">
-        <v>833</v>
-      </c>
-      <c r="T166" s="14" t="s">
-        <v>833</v>
+      <c r="S166" s="20" t="s">
+        <v>1101</v>
+      </c>
+      <c r="T166" s="20" t="s">
+        <v>1101</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="3:20">
       <c r="C167" s="1" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="E167" s="1">
         <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="G167" s="1">
-        <v>0</v>
-      </c>
-      <c r="H167" s="1">
-        <v>0</v>
-      </c>
-      <c r="I167" s="1">
-        <v>0</v>
-      </c>
-      <c r="J167" s="1">
-        <v>0</v>
-      </c>
-      <c r="K167" s="1">
-        <v>0</v>
+        <v>1104</v>
+      </c>
+      <c r="G167" s="30" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H167" s="30" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I167" s="30" t="s">
+        <v>1107</v>
+      </c>
+      <c r="J167" s="30" t="s">
+        <v>1108</v>
+      </c>
+      <c r="K167" s="30" t="s">
+        <v>1109</v>
       </c>
       <c r="L167" s="1">
         <f t="shared" si="42"/>
@@ -14978,58 +15127,58 @@
         <v>26700</v>
       </c>
       <c r="N167" s="1">
-        <f t="shared" si="44"/>
-        <v>10100</v>
+        <f t="shared" si="48"/>
+        <v>10200</v>
       </c>
       <c r="O167" s="1">
-        <f t="shared" si="45"/>
-        <v>10100</v>
-      </c>
-      <c r="P167" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
+        <v>10200</v>
+      </c>
+      <c r="P167" s="5">
+        <f t="shared" si="50"/>
         <v>154</v>
       </c>
-      <c r="Q167" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q167" s="5">
+        <f t="shared" si="51"/>
         <v>243</v>
       </c>
-      <c r="R167" s="3">
+      <c r="R167" s="5">
         <v>99.99</v>
       </c>
-      <c r="S167" s="14" t="s">
-        <v>839</v>
-      </c>
-      <c r="T167" s="14" t="s">
-        <v>839</v>
+      <c r="S167" s="20" t="s">
+        <v>1110</v>
+      </c>
+      <c r="T167" s="20" t="s">
+        <v>1110</v>
       </c>
     </row>
     <row r="168" customHeight="1" spans="3:20">
       <c r="C168" s="1" t="s">
-        <v>1099</v>
+        <v>1111</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
       <c r="E168" s="1">
         <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G168" s="1">
-        <v>0</v>
-      </c>
-      <c r="H168" s="1">
-        <v>0</v>
-      </c>
-      <c r="I168" s="1">
-        <v>0</v>
-      </c>
-      <c r="J168" s="1">
-        <v>0</v>
-      </c>
-      <c r="K168" s="1">
-        <v>0</v>
+        <v>1113</v>
+      </c>
+      <c r="G168" s="30" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H168" s="30" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I168" s="30" t="s">
+        <v>1116</v>
+      </c>
+      <c r="J168" s="30" t="s">
+        <v>1117</v>
+      </c>
+      <c r="K168" s="30" t="s">
+        <v>1118</v>
       </c>
       <c r="L168" s="1">
         <f t="shared" si="42"/>
@@ -15040,58 +15189,58 @@
         <v>27300</v>
       </c>
       <c r="N168" s="1">
-        <f t="shared" si="44"/>
-        <v>10350</v>
+        <f t="shared" si="48"/>
+        <v>10500</v>
       </c>
       <c r="O168" s="1">
-        <f t="shared" si="45"/>
-        <v>10350</v>
-      </c>
-      <c r="P168" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
+        <v>10500</v>
+      </c>
+      <c r="P168" s="5">
+        <f t="shared" si="50"/>
         <v>159</v>
       </c>
-      <c r="Q168" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q168" s="5">
+        <f t="shared" si="51"/>
         <v>249</v>
       </c>
-      <c r="R168" s="3">
+      <c r="R168" s="5">
         <v>99.99</v>
       </c>
-      <c r="S168" s="14" t="s">
-        <v>845</v>
-      </c>
-      <c r="T168" s="14" t="s">
-        <v>845</v>
+      <c r="S168" s="20" t="s">
+        <v>1119</v>
+      </c>
+      <c r="T168" s="20" t="s">
+        <v>1119</v>
       </c>
     </row>
     <row r="169" customHeight="1" spans="3:20">
       <c r="C169" s="1" t="s">
-        <v>1102</v>
+        <v>1120</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>1103</v>
+        <v>1121</v>
       </c>
       <c r="E169" s="1">
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G169" s="1">
-        <v>0</v>
-      </c>
-      <c r="H169" s="1">
-        <v>0</v>
-      </c>
-      <c r="I169" s="1">
-        <v>0</v>
-      </c>
-      <c r="J169" s="1">
-        <v>0</v>
-      </c>
-      <c r="K169" s="1">
-        <v>0</v>
+        <v>1122</v>
+      </c>
+      <c r="G169" s="30" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H169" s="30" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I169" s="30" t="s">
+        <v>1125</v>
+      </c>
+      <c r="J169" s="30" t="s">
+        <v>1126</v>
+      </c>
+      <c r="K169" s="30" t="s">
+        <v>1127</v>
       </c>
       <c r="L169" s="1">
         <f t="shared" si="42"/>
@@ -15102,58 +15251,58 @@
         <v>27900</v>
       </c>
       <c r="N169" s="1">
-        <f t="shared" si="44"/>
-        <v>10600</v>
+        <f t="shared" si="48"/>
+        <v>10800</v>
       </c>
       <c r="O169" s="1">
-        <f t="shared" si="45"/>
-        <v>10600</v>
-      </c>
-      <c r="P169" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
+        <v>10800</v>
+      </c>
+      <c r="P169" s="5">
+        <f t="shared" si="50"/>
         <v>164</v>
       </c>
-      <c r="Q169" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q169" s="5">
+        <f t="shared" si="51"/>
         <v>255</v>
       </c>
-      <c r="R169" s="3">
+      <c r="R169" s="5">
         <v>99.99</v>
       </c>
-      <c r="S169" s="14" t="s">
-        <v>851</v>
-      </c>
-      <c r="T169" s="14" t="s">
-        <v>851</v>
+      <c r="S169" s="20" t="s">
+        <v>1128</v>
+      </c>
+      <c r="T169" s="20" t="s">
+        <v>1128</v>
       </c>
     </row>
     <row r="170" customHeight="1" spans="3:20">
       <c r="C170" s="1" t="s">
-        <v>1105</v>
+        <v>1129</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>1106</v>
+        <v>1130</v>
       </c>
       <c r="E170" s="1">
         <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G170" s="1">
-        <v>0</v>
-      </c>
-      <c r="H170" s="1">
-        <v>0</v>
-      </c>
-      <c r="I170" s="1">
-        <v>0</v>
-      </c>
-      <c r="J170" s="1">
-        <v>0</v>
-      </c>
-      <c r="K170" s="1">
-        <v>0</v>
+        <v>1131</v>
+      </c>
+      <c r="G170" s="30" t="s">
+        <v>1132</v>
+      </c>
+      <c r="H170" s="30" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I170" s="30" t="s">
+        <v>1134</v>
+      </c>
+      <c r="J170" s="30" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K170" s="30" t="s">
+        <v>1136</v>
       </c>
       <c r="L170" s="1">
         <f t="shared" si="42"/>
@@ -15164,43 +15313,43 @@
         <v>28500</v>
       </c>
       <c r="N170" s="1">
-        <f t="shared" si="44"/>
-        <v>10850</v>
+        <f t="shared" si="48"/>
+        <v>11100</v>
       </c>
       <c r="O170" s="1">
-        <f t="shared" si="45"/>
-        <v>10850</v>
-      </c>
-      <c r="P170" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
+        <v>11100</v>
+      </c>
+      <c r="P170" s="5">
+        <f t="shared" si="50"/>
         <v>169</v>
       </c>
-      <c r="Q170" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q170" s="5">
+        <f t="shared" si="51"/>
         <v>261</v>
       </c>
-      <c r="R170" s="3">
+      <c r="R170" s="5">
         <v>99.99</v>
       </c>
-      <c r="S170" s="14" t="s">
-        <v>857</v>
-      </c>
-      <c r="T170" s="14" t="s">
-        <v>857</v>
+      <c r="S170" s="20" t="s">
+        <v>1137</v>
+      </c>
+      <c r="T170" s="20" t="s">
+        <v>1137</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="3:20">
       <c r="C171" s="1" t="s">
-        <v>1108</v>
+        <v>1138</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>1109</v>
+        <v>1139</v>
       </c>
       <c r="E171" s="1">
         <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1110</v>
+        <v>1140</v>
       </c>
       <c r="G171" s="1">
         <v>0</v>
@@ -15226,43 +15375,43 @@
         <v>29100</v>
       </c>
       <c r="N171" s="1">
-        <f t="shared" si="44"/>
-        <v>11100</v>
+        <f t="shared" ref="N171:N175" si="52">N170+400</f>
+        <v>11500</v>
       </c>
       <c r="O171" s="1">
-        <f t="shared" si="45"/>
-        <v>11100</v>
-      </c>
-      <c r="P171" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" ref="O171:O175" si="53">O170+400</f>
+        <v>11500</v>
+      </c>
+      <c r="P171" s="5">
+        <f t="shared" si="50"/>
         <v>174</v>
       </c>
-      <c r="Q171" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q171" s="5">
+        <f t="shared" si="51"/>
         <v>267</v>
       </c>
-      <c r="R171" s="3">
+      <c r="R171" s="5">
         <v>99.99</v>
       </c>
-      <c r="S171" s="14" t="s">
-        <v>863</v>
-      </c>
-      <c r="T171" s="14" t="s">
-        <v>863</v>
+      <c r="S171" s="20" t="s">
+        <v>1141</v>
+      </c>
+      <c r="T171" s="20" t="s">
+        <v>1141</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="3:20">
       <c r="C172" s="1" t="s">
-        <v>1111</v>
+        <v>1142</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>1112</v>
+        <v>1143</v>
       </c>
       <c r="E172" s="1">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1113</v>
+        <v>1144</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
@@ -15288,43 +15437,43 @@
         <v>29700</v>
       </c>
       <c r="N172" s="1">
-        <f t="shared" si="44"/>
-        <v>11350</v>
+        <f t="shared" si="52"/>
+        <v>11900</v>
       </c>
       <c r="O172" s="1">
-        <f t="shared" si="45"/>
-        <v>11350</v>
-      </c>
-      <c r="P172" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
+        <v>11900</v>
+      </c>
+      <c r="P172" s="5">
+        <f t="shared" si="50"/>
         <v>179</v>
       </c>
-      <c r="Q172" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q172" s="5">
+        <f t="shared" si="51"/>
         <v>273</v>
       </c>
-      <c r="R172" s="3">
+      <c r="R172" s="5">
         <v>99.99</v>
       </c>
-      <c r="S172" s="14" t="s">
-        <v>869</v>
-      </c>
-      <c r="T172" s="14" t="s">
-        <v>869</v>
+      <c r="S172" s="20" t="s">
+        <v>1145</v>
+      </c>
+      <c r="T172" s="20" t="s">
+        <v>1145</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="3:20">
       <c r="C173" s="1" t="s">
-        <v>1114</v>
+        <v>1146</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>1115</v>
+        <v>1147</v>
       </c>
       <c r="E173" s="1">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1116</v>
+        <v>1148</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -15350,43 +15499,43 @@
         <v>30300</v>
       </c>
       <c r="N173" s="1">
-        <f t="shared" si="44"/>
-        <v>11600</v>
+        <f t="shared" si="52"/>
+        <v>12300</v>
       </c>
       <c r="O173" s="1">
-        <f t="shared" si="45"/>
-        <v>11600</v>
-      </c>
-      <c r="P173" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
+        <v>12300</v>
+      </c>
+      <c r="P173" s="5">
+        <f t="shared" si="50"/>
         <v>184</v>
       </c>
-      <c r="Q173" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q173" s="5">
+        <f t="shared" si="51"/>
         <v>279</v>
       </c>
-      <c r="R173" s="3">
+      <c r="R173" s="5">
         <v>99.99</v>
       </c>
-      <c r="S173" s="14" t="s">
-        <v>875</v>
-      </c>
-      <c r="T173" s="14" t="s">
-        <v>875</v>
+      <c r="S173" s="20" t="s">
+        <v>1149</v>
+      </c>
+      <c r="T173" s="20" t="s">
+        <v>1149</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="3:20">
       <c r="C174" s="1" t="s">
-        <v>1117</v>
+        <v>1150</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>1118</v>
+        <v>1151</v>
       </c>
       <c r="E174" s="1">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1119</v>
+        <v>1152</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
@@ -15412,43 +15561,43 @@
         <v>30900</v>
       </c>
       <c r="N174" s="1">
-        <f t="shared" si="44"/>
-        <v>11850</v>
+        <f t="shared" si="52"/>
+        <v>12700</v>
       </c>
       <c r="O174" s="1">
-        <f t="shared" si="45"/>
-        <v>11850</v>
-      </c>
-      <c r="P174" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
+        <v>12700</v>
+      </c>
+      <c r="P174" s="5">
+        <f t="shared" si="50"/>
         <v>189</v>
       </c>
-      <c r="Q174" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q174" s="5">
+        <f t="shared" si="51"/>
         <v>285</v>
       </c>
-      <c r="R174" s="3">
+      <c r="R174" s="5">
         <v>99.99</v>
       </c>
-      <c r="S174" s="14" t="s">
-        <v>881</v>
-      </c>
-      <c r="T174" s="14" t="s">
-        <v>881</v>
+      <c r="S174" s="20" t="s">
+        <v>1153</v>
+      </c>
+      <c r="T174" s="20" t="s">
+        <v>1153</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="3:20">
       <c r="C175" s="1" t="s">
-        <v>1120</v>
+        <v>1154</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>1121</v>
+        <v>1155</v>
       </c>
       <c r="E175" s="1">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1122</v>
+        <v>1156</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
@@ -15474,45 +15623,45 @@
         <v>31500</v>
       </c>
       <c r="N175" s="1">
-        <f t="shared" si="44"/>
-        <v>12100</v>
+        <f t="shared" si="52"/>
+        <v>13100</v>
       </c>
       <c r="O175" s="1">
-        <f t="shared" si="45"/>
-        <v>12100</v>
-      </c>
-      <c r="P175" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
+        <v>13100</v>
+      </c>
+      <c r="P175" s="5">
+        <f t="shared" si="50"/>
         <v>194</v>
       </c>
-      <c r="Q175" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q175" s="5">
+        <f t="shared" si="51"/>
         <v>291</v>
       </c>
-      <c r="R175" s="3">
+      <c r="R175" s="5">
         <v>99.99</v>
       </c>
-      <c r="S175" s="14" t="s">
-        <v>887</v>
-      </c>
-      <c r="T175" s="14" t="s">
-        <v>887</v>
+      <c r="S175" s="20" t="s">
+        <v>1157</v>
+      </c>
+      <c r="T175" s="20" t="s">
+        <v>1157</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A176" s="3"/>
-      <c r="B176" s="3"/>
+      <c r="A176" s="5"/>
+      <c r="B176" s="5"/>
       <c r="C176" s="1" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>1124</v>
+        <v>1159</v>
       </c>
       <c r="E176" s="1">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1125</v>
+        <v>1160</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -15538,50 +15687,50 @@
         <v>32100</v>
       </c>
       <c r="N176" s="1">
-        <f t="shared" si="44"/>
-        <v>12350</v>
+        <f t="shared" ref="N176:N180" si="54">N175+500</f>
+        <v>13600</v>
       </c>
       <c r="O176" s="1">
-        <f t="shared" si="45"/>
-        <v>12350</v>
-      </c>
-      <c r="P176" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" ref="O176:O180" si="55">O175+500</f>
+        <v>13600</v>
+      </c>
+      <c r="P176" s="5">
+        <f t="shared" si="50"/>
         <v>199</v>
       </c>
-      <c r="Q176" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q176" s="5">
+        <f t="shared" si="51"/>
         <v>297</v>
       </c>
-      <c r="R176" s="3">
+      <c r="R176" s="5">
         <v>99.99</v>
       </c>
-      <c r="S176" s="14" t="s">
-        <v>893</v>
-      </c>
-      <c r="T176" s="14" t="s">
-        <v>893</v>
-      </c>
-      <c r="U176" s="3"/>
-      <c r="V176" s="3"/>
-      <c r="W176" s="3"/>
-      <c r="X176" s="3"/>
-      <c r="Y176" s="3"/>
+      <c r="S176" s="20" t="s">
+        <v>1161</v>
+      </c>
+      <c r="T176" s="20" t="s">
+        <v>1161</v>
+      </c>
+      <c r="U176" s="5"/>
+      <c r="V176" s="5"/>
+      <c r="W176" s="5"/>
+      <c r="X176" s="5"/>
+      <c r="Y176" s="5"/>
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A177" s="3"/>
-      <c r="B177" s="3"/>
+      <c r="A177" s="5"/>
+      <c r="B177" s="5"/>
       <c r="C177" s="1" t="s">
-        <v>1126</v>
+        <v>1162</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>1127</v>
+        <v>1163</v>
       </c>
       <c r="E177" s="1">
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1128</v>
+        <v>1164</v>
       </c>
       <c r="G177" s="1">
         <v>0</v>
@@ -15607,50 +15756,50 @@
         <v>32700</v>
       </c>
       <c r="N177" s="1">
-        <f t="shared" si="44"/>
-        <v>12600</v>
+        <f t="shared" si="54"/>
+        <v>14100</v>
       </c>
       <c r="O177" s="1">
-        <f t="shared" si="45"/>
-        <v>12600</v>
-      </c>
-      <c r="P177" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="55"/>
+        <v>14100</v>
+      </c>
+      <c r="P177" s="5">
+        <f t="shared" si="50"/>
         <v>204</v>
       </c>
-      <c r="Q177" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q177" s="5">
+        <f t="shared" si="51"/>
         <v>303</v>
       </c>
-      <c r="R177" s="3">
+      <c r="R177" s="5">
         <v>99.99</v>
       </c>
-      <c r="S177" s="14" t="s">
-        <v>899</v>
-      </c>
-      <c r="T177" s="14" t="s">
-        <v>899</v>
-      </c>
-      <c r="U177" s="3"/>
-      <c r="V177" s="3"/>
-      <c r="W177" s="3"/>
-      <c r="X177" s="3"/>
-      <c r="Y177" s="3"/>
+      <c r="S177" s="20" t="s">
+        <v>1165</v>
+      </c>
+      <c r="T177" s="20" t="s">
+        <v>1165</v>
+      </c>
+      <c r="U177" s="5"/>
+      <c r="V177" s="5"/>
+      <c r="W177" s="5"/>
+      <c r="X177" s="5"/>
+      <c r="Y177" s="5"/>
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A178" s="3"/>
-      <c r="B178" s="3"/>
+      <c r="A178" s="5"/>
+      <c r="B178" s="5"/>
       <c r="C178" s="1" t="s">
-        <v>1129</v>
+        <v>1166</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1130</v>
+        <v>1167</v>
       </c>
       <c r="E178" s="1">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1131</v>
+        <v>1168</v>
       </c>
       <c r="G178" s="1">
         <v>0</v>
@@ -15676,50 +15825,50 @@
         <v>33300</v>
       </c>
       <c r="N178" s="1">
-        <f t="shared" si="44"/>
-        <v>12850</v>
+        <f t="shared" si="54"/>
+        <v>14600</v>
       </c>
       <c r="O178" s="1">
-        <f t="shared" si="45"/>
-        <v>12850</v>
-      </c>
-      <c r="P178" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="55"/>
+        <v>14600</v>
+      </c>
+      <c r="P178" s="5">
+        <f t="shared" si="50"/>
         <v>209</v>
       </c>
-      <c r="Q178" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q178" s="5">
+        <f t="shared" si="51"/>
         <v>309</v>
       </c>
-      <c r="R178" s="3">
+      <c r="R178" s="5">
         <v>99.99</v>
       </c>
-      <c r="S178" s="14" t="s">
-        <v>905</v>
-      </c>
-      <c r="T178" s="14" t="s">
-        <v>905</v>
-      </c>
-      <c r="U178" s="3"/>
-      <c r="V178" s="3"/>
-      <c r="W178" s="3"/>
-      <c r="X178" s="3"/>
-      <c r="Y178" s="3"/>
+      <c r="S178" s="20" t="s">
+        <v>1169</v>
+      </c>
+      <c r="T178" s="20" t="s">
+        <v>1169</v>
+      </c>
+      <c r="U178" s="5"/>
+      <c r="V178" s="5"/>
+      <c r="W178" s="5"/>
+      <c r="X178" s="5"/>
+      <c r="Y178" s="5"/>
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A179" s="3"/>
-      <c r="B179" s="3"/>
+      <c r="A179" s="5"/>
+      <c r="B179" s="5"/>
       <c r="C179" s="1" t="s">
-        <v>1132</v>
+        <v>1170</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1133</v>
+        <v>1171</v>
       </c>
       <c r="E179" s="1">
         <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1134</v>
+        <v>1172</v>
       </c>
       <c r="G179" s="1">
         <v>0</v>
@@ -15745,50 +15894,50 @@
         <v>33900</v>
       </c>
       <c r="N179" s="1">
-        <f t="shared" si="44"/>
-        <v>13100</v>
+        <f t="shared" si="54"/>
+        <v>15100</v>
       </c>
       <c r="O179" s="1">
-        <f t="shared" si="45"/>
-        <v>13100</v>
-      </c>
-      <c r="P179" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="55"/>
+        <v>15100</v>
+      </c>
+      <c r="P179" s="5">
+        <f t="shared" si="50"/>
         <v>214</v>
       </c>
-      <c r="Q179" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q179" s="5">
+        <f t="shared" si="51"/>
         <v>315</v>
       </c>
-      <c r="R179" s="3">
+      <c r="R179" s="5">
         <v>99.99</v>
       </c>
-      <c r="S179" s="14" t="s">
-        <v>911</v>
-      </c>
-      <c r="T179" s="14" t="s">
-        <v>911</v>
-      </c>
-      <c r="U179" s="3"/>
-      <c r="V179" s="3"/>
-      <c r="W179" s="3"/>
-      <c r="X179" s="3"/>
-      <c r="Y179" s="3"/>
+      <c r="S179" s="20" t="s">
+        <v>1173</v>
+      </c>
+      <c r="T179" s="20" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U179" s="5"/>
+      <c r="V179" s="5"/>
+      <c r="W179" s="5"/>
+      <c r="X179" s="5"/>
+      <c r="Y179" s="5"/>
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A180" s="3"/>
-      <c r="B180" s="3"/>
+      <c r="A180" s="5"/>
+      <c r="B180" s="5"/>
       <c r="C180" s="1" t="s">
-        <v>1135</v>
+        <v>1174</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1136</v>
+        <v>1175</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1137</v>
+        <v>1176</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>
@@ -15814,35 +15963,35 @@
         <v>34500</v>
       </c>
       <c r="N180" s="1">
-        <f t="shared" si="44"/>
-        <v>13350</v>
+        <f t="shared" si="54"/>
+        <v>15600</v>
       </c>
       <c r="O180" s="1">
-        <f t="shared" si="45"/>
-        <v>13350</v>
-      </c>
-      <c r="P180" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="55"/>
+        <v>15600</v>
+      </c>
+      <c r="P180" s="5">
+        <f t="shared" si="50"/>
         <v>219</v>
       </c>
-      <c r="Q180" s="3">
-        <f t="shared" si="49"/>
+      <c r="Q180" s="5">
+        <f t="shared" si="51"/>
         <v>321</v>
       </c>
-      <c r="R180" s="3">
+      <c r="R180" s="5">
         <v>99.99</v>
       </c>
-      <c r="S180" s="14" t="s">
-        <v>917</v>
-      </c>
-      <c r="T180" s="14" t="s">
-        <v>917</v>
-      </c>
-      <c r="U180" s="3"/>
-      <c r="V180" s="3"/>
-      <c r="W180" s="3"/>
-      <c r="X180" s="3"/>
-      <c r="Y180" s="3"/>
+      <c r="S180" s="20" t="s">
+        <v>1177</v>
+      </c>
+      <c r="T180" s="20" t="s">
+        <v>1177</v>
+      </c>
+      <c r="U180" s="5"/>
+      <c r="V180" s="5"/>
+      <c r="W180" s="5"/>
+      <c r="X180" s="5"/>
+      <c r="Y180" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="1228">
   <si>
     <t>ID</t>
   </si>
@@ -3452,6 +3452,21 @@
     <t>深渊树妖</t>
   </si>
   <si>
+    <t>9E+72</t>
+  </si>
+  <si>
+    <t>9E+95</t>
+  </si>
+  <si>
+    <t>512E+122</t>
+  </si>
+  <si>
+    <t>64E+26</t>
+  </si>
+  <si>
+    <t>64E+54</t>
+  </si>
+  <si>
     <t>108000000000</t>
   </si>
   <si>
@@ -3464,6 +3479,21 @@
     <t>深渊侍卫</t>
   </si>
   <si>
+    <t>9E+73</t>
+  </si>
+  <si>
+    <t>9E+96</t>
+  </si>
+  <si>
+    <t>1E+126</t>
+  </si>
+  <si>
+    <t>128E+27</t>
+  </si>
+  <si>
+    <t>128E+55</t>
+  </si>
+  <si>
     <t>111000000000</t>
   </si>
   <si>
@@ -3476,6 +3506,21 @@
     <t>深渊剧毒</t>
   </si>
   <si>
+    <t>9E+74</t>
+  </si>
+  <si>
+    <t>9E+97</t>
+  </si>
+  <si>
+    <t>2E+127</t>
+  </si>
+  <si>
+    <t>256E+28</t>
+  </si>
+  <si>
+    <t>256E+56</t>
+  </si>
+  <si>
     <t>114000000000</t>
   </si>
   <si>
@@ -3488,6 +3533,21 @@
     <t>深渊锤兵</t>
   </si>
   <si>
+    <t>9E+75</t>
+  </si>
+  <si>
+    <t>9E+98</t>
+  </si>
+  <si>
+    <t>4E+128</t>
+  </si>
+  <si>
+    <t>512E+29</t>
+  </si>
+  <si>
+    <t>512E+57</t>
+  </si>
+  <si>
     <t>117000000000</t>
   </si>
   <si>
@@ -3500,6 +3560,21 @@
     <t>深渊魔牛</t>
   </si>
   <si>
+    <t>9E+76</t>
+  </si>
+  <si>
+    <t>9E+99</t>
+  </si>
+  <si>
+    <t>8E+129</t>
+  </si>
+  <si>
+    <t>1E+33</t>
+  </si>
+  <si>
+    <t>1E+61</t>
+  </si>
+  <si>
     <t>120000000000</t>
   </si>
   <si>
@@ -3512,6 +3587,21 @@
     <t>深渊水龙</t>
   </si>
   <si>
+    <t>9E+77</t>
+  </si>
+  <si>
+    <t>9E+100</t>
+  </si>
+  <si>
+    <t>16E+130</t>
+  </si>
+  <si>
+    <t>2E+34</t>
+  </si>
+  <si>
+    <t>2E+62</t>
+  </si>
+  <si>
     <t>123000000000</t>
   </si>
   <si>
@@ -3524,6 +3614,21 @@
     <t>深渊土龙</t>
   </si>
   <si>
+    <t>9E+78</t>
+  </si>
+  <si>
+    <t>9E+101</t>
+  </si>
+  <si>
+    <t>32E+131</t>
+  </si>
+  <si>
+    <t>4E+35</t>
+  </si>
+  <si>
+    <t>4E+63</t>
+  </si>
+  <si>
     <t>126000000000</t>
   </si>
   <si>
@@ -3536,6 +3641,21 @@
     <t>深渊毒龙</t>
   </si>
   <si>
+    <t>9E+79</t>
+  </si>
+  <si>
+    <t>9E+102</t>
+  </si>
+  <si>
+    <t>64E+132</t>
+  </si>
+  <si>
+    <t>8E+36</t>
+  </si>
+  <si>
+    <t>8E+64</t>
+  </si>
+  <si>
     <t>129000000000</t>
   </si>
   <si>
@@ -3548,6 +3668,21 @@
     <t>深渊火龙</t>
   </si>
   <si>
+    <t>9E+80</t>
+  </si>
+  <si>
+    <t>9E+103</t>
+  </si>
+  <si>
+    <t>128E+133</t>
+  </si>
+  <si>
+    <t>16E+37</t>
+  </si>
+  <si>
+    <t>16E+65</t>
+  </si>
+  <si>
     <t>132000000000</t>
   </si>
   <si>
@@ -3558,6 +3693,21 @@
   </si>
   <si>
     <t>深渊冰龙</t>
+  </si>
+  <si>
+    <t>9E+81</t>
+  </si>
+  <si>
+    <t>9E+104</t>
+  </si>
+  <si>
+    <t>256E+134</t>
+  </si>
+  <si>
+    <t>32E+38</t>
+  </si>
+  <si>
+    <t>32E+66</t>
   </si>
   <si>
     <t>135000000000</t>
@@ -15073,11 +15223,11 @@
         <v>9900</v>
       </c>
       <c r="P166" s="5">
-        <f t="shared" ref="P166:P180" si="50">P165+5</f>
+        <f>P165+5</f>
         <v>149</v>
       </c>
       <c r="Q166" s="5">
-        <f t="shared" ref="Q166:Q180" si="51">Q165+6</f>
+        <f>Q165+6</f>
         <v>237</v>
       </c>
       <c r="R166" s="5">
@@ -15135,11 +15285,11 @@
         <v>10200</v>
       </c>
       <c r="P167" s="5">
-        <f t="shared" si="50"/>
+        <f>P166+5</f>
         <v>154</v>
       </c>
       <c r="Q167" s="5">
-        <f t="shared" si="51"/>
+        <f>Q166+6</f>
         <v>243</v>
       </c>
       <c r="R167" s="5">
@@ -15197,11 +15347,11 @@
         <v>10500</v>
       </c>
       <c r="P168" s="5">
-        <f t="shared" si="50"/>
+        <f>P167+5</f>
         <v>159</v>
       </c>
       <c r="Q168" s="5">
-        <f t="shared" si="51"/>
+        <f>Q167+6</f>
         <v>249</v>
       </c>
       <c r="R168" s="5">
@@ -15259,11 +15409,11 @@
         <v>10800</v>
       </c>
       <c r="P169" s="5">
-        <f t="shared" si="50"/>
+        <f>P168+5</f>
         <v>164</v>
       </c>
       <c r="Q169" s="5">
-        <f t="shared" si="51"/>
+        <f>Q168+6</f>
         <v>255</v>
       </c>
       <c r="R169" s="5">
@@ -15321,11 +15471,11 @@
         <v>11100</v>
       </c>
       <c r="P170" s="5">
-        <f t="shared" si="50"/>
+        <f>P169+5</f>
         <v>169</v>
       </c>
       <c r="Q170" s="5">
-        <f t="shared" si="51"/>
+        <f>Q169+6</f>
         <v>261</v>
       </c>
       <c r="R170" s="5">
@@ -15351,20 +15501,20 @@
       <c r="F171" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="G171" s="1">
-        <v>0</v>
-      </c>
-      <c r="H171" s="1">
-        <v>0</v>
-      </c>
-      <c r="I171" s="1">
-        <v>0</v>
-      </c>
-      <c r="J171" s="1">
-        <v>0</v>
-      </c>
-      <c r="K171" s="1">
-        <v>0</v>
+      <c r="G171" s="30" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H171" s="30" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I171" s="30" t="s">
+        <v>1143</v>
+      </c>
+      <c r="J171" s="30" t="s">
+        <v>1144</v>
+      </c>
+      <c r="K171" s="30" t="s">
+        <v>1145</v>
       </c>
       <c r="L171" s="1">
         <f t="shared" si="42"/>
@@ -15375,58 +15525,58 @@
         <v>29100</v>
       </c>
       <c r="N171" s="1">
-        <f t="shared" ref="N171:N175" si="52">N170+400</f>
+        <f t="shared" ref="N171:N175" si="50">N170+400</f>
         <v>11500</v>
       </c>
       <c r="O171" s="1">
-        <f t="shared" ref="O171:O175" si="53">O170+400</f>
+        <f t="shared" ref="O171:O175" si="51">O170+400</f>
         <v>11500</v>
       </c>
       <c r="P171" s="5">
-        <f t="shared" si="50"/>
-        <v>174</v>
+        <f t="shared" ref="P171:P175" si="52">P170+6</f>
+        <v>175</v>
       </c>
       <c r="Q171" s="5">
-        <f t="shared" si="51"/>
-        <v>267</v>
+        <f t="shared" ref="Q171:Q175" si="53">Q170+7</f>
+        <v>268</v>
       </c>
       <c r="R171" s="5">
         <v>99.99</v>
       </c>
       <c r="S171" s="20" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="T171" s="20" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="3:20">
       <c r="C172" s="1" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="E172" s="1">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1144</v>
-      </c>
-      <c r="G172" s="1">
-        <v>0</v>
-      </c>
-      <c r="H172" s="1">
-        <v>0</v>
-      </c>
-      <c r="I172" s="1">
-        <v>0</v>
-      </c>
-      <c r="J172" s="1">
-        <v>0</v>
-      </c>
-      <c r="K172" s="1">
-        <v>0</v>
+        <v>1149</v>
+      </c>
+      <c r="G172" s="30" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H172" s="30" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I172" s="30" t="s">
+        <v>1152</v>
+      </c>
+      <c r="J172" s="30" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K172" s="30" t="s">
+        <v>1154</v>
       </c>
       <c r="L172" s="1">
         <f t="shared" si="42"/>
@@ -15437,58 +15587,58 @@
         <v>29700</v>
       </c>
       <c r="N172" s="1">
+        <f t="shared" si="50"/>
+        <v>11900</v>
+      </c>
+      <c r="O172" s="1">
+        <f t="shared" si="51"/>
+        <v>11900</v>
+      </c>
+      <c r="P172" s="5">
         <f t="shared" si="52"/>
-        <v>11900</v>
-      </c>
-      <c r="O172" s="1">
+        <v>181</v>
+      </c>
+      <c r="Q172" s="5">
         <f t="shared" si="53"/>
-        <v>11900</v>
-      </c>
-      <c r="P172" s="5">
-        <f t="shared" si="50"/>
-        <v>179</v>
-      </c>
-      <c r="Q172" s="5">
-        <f t="shared" si="51"/>
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R172" s="5">
         <v>99.99</v>
       </c>
       <c r="S172" s="20" t="s">
-        <v>1145</v>
+        <v>1155</v>
       </c>
       <c r="T172" s="20" t="s">
-        <v>1145</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="3:20">
       <c r="C173" s="1" t="s">
-        <v>1146</v>
+        <v>1156</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>1147</v>
+        <v>1157</v>
       </c>
       <c r="E173" s="1">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="G173" s="1">
-        <v>0</v>
-      </c>
-      <c r="H173" s="1">
-        <v>0</v>
-      </c>
-      <c r="I173" s="1">
-        <v>0</v>
-      </c>
-      <c r="J173" s="1">
-        <v>0</v>
-      </c>
-      <c r="K173" s="1">
-        <v>0</v>
+        <v>1158</v>
+      </c>
+      <c r="G173" s="30" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H173" s="30" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I173" s="30" t="s">
+        <v>1161</v>
+      </c>
+      <c r="J173" s="30" t="s">
+        <v>1162</v>
+      </c>
+      <c r="K173" s="30" t="s">
+        <v>1163</v>
       </c>
       <c r="L173" s="1">
         <f t="shared" si="42"/>
@@ -15499,58 +15649,58 @@
         <v>30300</v>
       </c>
       <c r="N173" s="1">
+        <f t="shared" si="50"/>
+        <v>12300</v>
+      </c>
+      <c r="O173" s="1">
+        <f t="shared" si="51"/>
+        <v>12300</v>
+      </c>
+      <c r="P173" s="5">
         <f t="shared" si="52"/>
-        <v>12300</v>
-      </c>
-      <c r="O173" s="1">
+        <v>187</v>
+      </c>
+      <c r="Q173" s="5">
         <f t="shared" si="53"/>
-        <v>12300</v>
-      </c>
-      <c r="P173" s="5">
-        <f t="shared" si="50"/>
-        <v>184</v>
-      </c>
-      <c r="Q173" s="5">
-        <f t="shared" si="51"/>
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="R173" s="5">
         <v>99.99</v>
       </c>
       <c r="S173" s="20" t="s">
-        <v>1149</v>
+        <v>1164</v>
       </c>
       <c r="T173" s="20" t="s">
-        <v>1149</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="3:20">
       <c r="C174" s="1" t="s">
-        <v>1150</v>
+        <v>1165</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>1151</v>
+        <v>1166</v>
       </c>
       <c r="E174" s="1">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="G174" s="1">
-        <v>0</v>
-      </c>
-      <c r="H174" s="1">
-        <v>0</v>
-      </c>
-      <c r="I174" s="1">
-        <v>0</v>
-      </c>
-      <c r="J174" s="1">
-        <v>0</v>
-      </c>
-      <c r="K174" s="1">
-        <v>0</v>
+        <v>1167</v>
+      </c>
+      <c r="G174" s="30" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H174" s="30" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I174" s="30" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J174" s="30" t="s">
+        <v>1171</v>
+      </c>
+      <c r="K174" s="30" t="s">
+        <v>1172</v>
       </c>
       <c r="L174" s="1">
         <f t="shared" si="42"/>
@@ -15561,58 +15711,58 @@
         <v>30900</v>
       </c>
       <c r="N174" s="1">
+        <f t="shared" si="50"/>
+        <v>12700</v>
+      </c>
+      <c r="O174" s="1">
+        <f t="shared" si="51"/>
+        <v>12700</v>
+      </c>
+      <c r="P174" s="5">
         <f t="shared" si="52"/>
-        <v>12700</v>
-      </c>
-      <c r="O174" s="1">
+        <v>193</v>
+      </c>
+      <c r="Q174" s="5">
         <f t="shared" si="53"/>
-        <v>12700</v>
-      </c>
-      <c r="P174" s="5">
-        <f t="shared" si="50"/>
-        <v>189</v>
-      </c>
-      <c r="Q174" s="5">
-        <f t="shared" si="51"/>
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="R174" s="5">
         <v>99.99</v>
       </c>
       <c r="S174" s="20" t="s">
-        <v>1153</v>
+        <v>1173</v>
       </c>
       <c r="T174" s="20" t="s">
-        <v>1153</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="3:20">
       <c r="C175" s="1" t="s">
-        <v>1154</v>
+        <v>1174</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>1155</v>
+        <v>1175</v>
       </c>
       <c r="E175" s="1">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="G175" s="1">
-        <v>0</v>
-      </c>
-      <c r="H175" s="1">
-        <v>0</v>
-      </c>
-      <c r="I175" s="1">
-        <v>0</v>
-      </c>
-      <c r="J175" s="1">
-        <v>0</v>
-      </c>
-      <c r="K175" s="1">
-        <v>0</v>
+        <v>1176</v>
+      </c>
+      <c r="G175" s="30" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H175" s="30" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I175" s="30" t="s">
+        <v>1179</v>
+      </c>
+      <c r="J175" s="30" t="s">
+        <v>1180</v>
+      </c>
+      <c r="K175" s="30" t="s">
+        <v>1181</v>
       </c>
       <c r="L175" s="1">
         <f t="shared" si="42"/>
@@ -15623,60 +15773,60 @@
         <v>31500</v>
       </c>
       <c r="N175" s="1">
+        <f t="shared" si="50"/>
+        <v>13100</v>
+      </c>
+      <c r="O175" s="1">
+        <f t="shared" si="51"/>
+        <v>13100</v>
+      </c>
+      <c r="P175" s="5">
         <f t="shared" si="52"/>
-        <v>13100</v>
-      </c>
-      <c r="O175" s="1">
+        <v>199</v>
+      </c>
+      <c r="Q175" s="5">
         <f t="shared" si="53"/>
-        <v>13100</v>
-      </c>
-      <c r="P175" s="5">
-        <f t="shared" si="50"/>
-        <v>194</v>
-      </c>
-      <c r="Q175" s="5">
-        <f t="shared" si="51"/>
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="R175" s="5">
         <v>99.99</v>
       </c>
       <c r="S175" s="20" t="s">
-        <v>1157</v>
+        <v>1182</v>
       </c>
       <c r="T175" s="20" t="s">
-        <v>1157</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="1" t="s">
-        <v>1158</v>
+        <v>1183</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>1159</v>
+        <v>1184</v>
       </c>
       <c r="E176" s="1">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="G176" s="1">
-        <v>0</v>
-      </c>
-      <c r="H176" s="1">
-        <v>0</v>
-      </c>
-      <c r="I176" s="1">
-        <v>0</v>
-      </c>
-      <c r="J176" s="1">
-        <v>0</v>
-      </c>
-      <c r="K176" s="1">
-        <v>0</v>
+        <v>1185</v>
+      </c>
+      <c r="G176" s="30" t="s">
+        <v>1186</v>
+      </c>
+      <c r="H176" s="30" t="s">
+        <v>1187</v>
+      </c>
+      <c r="I176" s="30" t="s">
+        <v>1188</v>
+      </c>
+      <c r="J176" s="30" t="s">
+        <v>1189</v>
+      </c>
+      <c r="K176" s="30" t="s">
+        <v>1190</v>
       </c>
       <c r="L176" s="1">
         <f t="shared" si="42"/>
@@ -15695,21 +15845,21 @@
         <v>13600</v>
       </c>
       <c r="P176" s="5">
-        <f t="shared" si="50"/>
-        <v>199</v>
+        <f t="shared" ref="P176:P180" si="56">P175+7</f>
+        <v>206</v>
       </c>
       <c r="Q176" s="5">
-        <f t="shared" si="51"/>
-        <v>297</v>
+        <f t="shared" ref="Q176:Q180" si="57">Q175+8</f>
+        <v>304</v>
       </c>
       <c r="R176" s="5">
         <v>99.99</v>
       </c>
       <c r="S176" s="20" t="s">
-        <v>1161</v>
+        <v>1191</v>
       </c>
       <c r="T176" s="20" t="s">
-        <v>1161</v>
+        <v>1191</v>
       </c>
       <c r="U176" s="5"/>
       <c r="V176" s="5"/>
@@ -15721,31 +15871,31 @@
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="1" t="s">
-        <v>1162</v>
+        <v>1192</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="E177" s="1">
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1164</v>
-      </c>
-      <c r="G177" s="1">
-        <v>0</v>
-      </c>
-      <c r="H177" s="1">
-        <v>0</v>
-      </c>
-      <c r="I177" s="1">
-        <v>0</v>
-      </c>
-      <c r="J177" s="1">
-        <v>0</v>
-      </c>
-      <c r="K177" s="1">
-        <v>0</v>
+        <v>1194</v>
+      </c>
+      <c r="G177" s="30" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H177" s="30" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I177" s="30" t="s">
+        <v>1197</v>
+      </c>
+      <c r="J177" s="30" t="s">
+        <v>1198</v>
+      </c>
+      <c r="K177" s="30" t="s">
+        <v>1199</v>
       </c>
       <c r="L177" s="1">
         <f t="shared" si="42"/>
@@ -15764,21 +15914,21 @@
         <v>14100</v>
       </c>
       <c r="P177" s="5">
-        <f t="shared" si="50"/>
-        <v>204</v>
+        <f t="shared" si="56"/>
+        <v>213</v>
       </c>
       <c r="Q177" s="5">
-        <f t="shared" si="51"/>
-        <v>303</v>
+        <f t="shared" si="57"/>
+        <v>312</v>
       </c>
       <c r="R177" s="5">
         <v>99.99</v>
       </c>
       <c r="S177" s="20" t="s">
-        <v>1165</v>
+        <v>1200</v>
       </c>
       <c r="T177" s="20" t="s">
-        <v>1165</v>
+        <v>1200</v>
       </c>
       <c r="U177" s="5"/>
       <c r="V177" s="5"/>
@@ -15790,31 +15940,31 @@
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="1" t="s">
-        <v>1166</v>
+        <v>1201</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1167</v>
+        <v>1202</v>
       </c>
       <c r="E178" s="1">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1168</v>
-      </c>
-      <c r="G178" s="1">
-        <v>0</v>
-      </c>
-      <c r="H178" s="1">
-        <v>0</v>
-      </c>
-      <c r="I178" s="1">
-        <v>0</v>
-      </c>
-      <c r="J178" s="1">
-        <v>0</v>
-      </c>
-      <c r="K178" s="1">
-        <v>0</v>
+        <v>1203</v>
+      </c>
+      <c r="G178" s="30" t="s">
+        <v>1204</v>
+      </c>
+      <c r="H178" s="30" t="s">
+        <v>1205</v>
+      </c>
+      <c r="I178" s="30" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J178" s="30" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K178" s="30" t="s">
+        <v>1208</v>
       </c>
       <c r="L178" s="1">
         <f t="shared" si="42"/>
@@ -15833,21 +15983,21 @@
         <v>14600</v>
       </c>
       <c r="P178" s="5">
-        <f t="shared" si="50"/>
-        <v>209</v>
+        <f t="shared" si="56"/>
+        <v>220</v>
       </c>
       <c r="Q178" s="5">
-        <f t="shared" si="51"/>
-        <v>309</v>
+        <f t="shared" si="57"/>
+        <v>320</v>
       </c>
       <c r="R178" s="5">
         <v>99.99</v>
       </c>
       <c r="S178" s="20" t="s">
-        <v>1169</v>
+        <v>1209</v>
       </c>
       <c r="T178" s="20" t="s">
-        <v>1169</v>
+        <v>1209</v>
       </c>
       <c r="U178" s="5"/>
       <c r="V178" s="5"/>
@@ -15859,31 +16009,31 @@
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="1" t="s">
-        <v>1170</v>
+        <v>1210</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1171</v>
+        <v>1211</v>
       </c>
       <c r="E179" s="1">
         <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1172</v>
-      </c>
-      <c r="G179" s="1">
-        <v>0</v>
-      </c>
-      <c r="H179" s="1">
-        <v>0</v>
-      </c>
-      <c r="I179" s="1">
-        <v>0</v>
-      </c>
-      <c r="J179" s="1">
-        <v>0</v>
-      </c>
-      <c r="K179" s="1">
-        <v>0</v>
+        <v>1212</v>
+      </c>
+      <c r="G179" s="30" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H179" s="30" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I179" s="30" t="s">
+        <v>1215</v>
+      </c>
+      <c r="J179" s="30" t="s">
+        <v>1216</v>
+      </c>
+      <c r="K179" s="30" t="s">
+        <v>1217</v>
       </c>
       <c r="L179" s="1">
         <f t="shared" si="42"/>
@@ -15902,21 +16052,21 @@
         <v>15100</v>
       </c>
       <c r="P179" s="5">
-        <f t="shared" si="50"/>
-        <v>214</v>
+        <f t="shared" si="56"/>
+        <v>227</v>
       </c>
       <c r="Q179" s="5">
-        <f t="shared" si="51"/>
-        <v>315</v>
+        <f t="shared" si="57"/>
+        <v>328</v>
       </c>
       <c r="R179" s="5">
         <v>99.99</v>
       </c>
       <c r="S179" s="20" t="s">
-        <v>1173</v>
+        <v>1218</v>
       </c>
       <c r="T179" s="20" t="s">
-        <v>1173</v>
+        <v>1218</v>
       </c>
       <c r="U179" s="5"/>
       <c r="V179" s="5"/>
@@ -15928,31 +16078,31 @@
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="1" t="s">
-        <v>1174</v>
+        <v>1219</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1175</v>
+        <v>1220</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="G180" s="1">
-        <v>0</v>
-      </c>
-      <c r="H180" s="1">
-        <v>0</v>
-      </c>
-      <c r="I180" s="1">
-        <v>0</v>
-      </c>
-      <c r="J180" s="1">
-        <v>0</v>
-      </c>
-      <c r="K180" s="1">
-        <v>0</v>
+        <v>1221</v>
+      </c>
+      <c r="G180" s="30" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H180" s="30" t="s">
+        <v>1223</v>
+      </c>
+      <c r="I180" s="30" t="s">
+        <v>1224</v>
+      </c>
+      <c r="J180" s="30" t="s">
+        <v>1225</v>
+      </c>
+      <c r="K180" s="30" t="s">
+        <v>1226</v>
       </c>
       <c r="L180" s="1">
         <f t="shared" si="42"/>
@@ -15971,21 +16121,21 @@
         <v>15600</v>
       </c>
       <c r="P180" s="5">
-        <f t="shared" si="50"/>
-        <v>219</v>
+        <f t="shared" si="56"/>
+        <v>234</v>
       </c>
       <c r="Q180" s="5">
-        <f t="shared" si="51"/>
-        <v>321</v>
+        <f t="shared" si="57"/>
+        <v>336</v>
       </c>
       <c r="R180" s="5">
         <v>99.99</v>
       </c>
       <c r="S180" s="20" t="s">
-        <v>1177</v>
+        <v>1227</v>
       </c>
       <c r="T180" s="20" t="s">
-        <v>1177</v>
+        <v>1227</v>
       </c>
       <c r="U180" s="5"/>
       <c r="V180" s="5"/>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -4423,7 +4423,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4445,12 +4445,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4765,7 +4759,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4789,16 +4783,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -4807,89 +4801,89 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4917,11 +4911,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -4937,10 +4930,10 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5528,13 +5521,13 @@
       <c r="F6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="23" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="1">
@@ -9059,7 +9052,7 @@
       <c r="H65" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="I65" s="24" t="s">
+      <c r="I65" s="23" t="s">
         <v>438</v>
       </c>
       <c r="J65" s="1">
@@ -9125,7 +9118,7 @@
       <c r="H66" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="I66" s="24" t="s">
+      <c r="I66" s="23" t="s">
         <v>445</v>
       </c>
       <c r="J66" s="1">
@@ -9191,7 +9184,7 @@
       <c r="H67" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="I67" s="24" t="s">
+      <c r="I67" s="23" t="s">
         <v>452</v>
       </c>
       <c r="J67" s="1">
@@ -9257,7 +9250,7 @@
       <c r="H68" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="I68" s="24" t="s">
+      <c r="I68" s="23" t="s">
         <v>459</v>
       </c>
       <c r="J68" s="1">
@@ -9320,10 +9313,10 @@
       <c r="G69" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="H69" s="24" t="s">
+      <c r="H69" s="23" t="s">
         <v>465</v>
       </c>
-      <c r="I69" s="24" t="s">
+      <c r="I69" s="23" t="s">
         <v>466</v>
       </c>
       <c r="J69" s="1">
@@ -9383,13 +9376,13 @@
       <c r="F70" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="G70" s="24" t="s">
+      <c r="G70" s="23" t="s">
         <v>471</v>
       </c>
-      <c r="H70" s="24" t="s">
+      <c r="H70" s="23" t="s">
         <v>472</v>
       </c>
-      <c r="I70" s="24" t="s">
+      <c r="I70" s="23" t="s">
         <v>473</v>
       </c>
       <c r="J70" s="1">
@@ -9449,13 +9442,13 @@
       <c r="F71" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="G71" s="24" t="s">
+      <c r="G71" s="23" t="s">
         <v>478</v>
       </c>
-      <c r="H71" s="24" t="s">
+      <c r="H71" s="23" t="s">
         <v>479</v>
       </c>
-      <c r="I71" s="24" t="s">
+      <c r="I71" s="23" t="s">
         <v>480</v>
       </c>
       <c r="J71" s="1">
@@ -9515,13 +9508,13 @@
       <c r="F72" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="G72" s="24" t="s">
+      <c r="G72" s="23" t="s">
         <v>485</v>
       </c>
-      <c r="H72" s="24" t="s">
+      <c r="H72" s="23" t="s">
         <v>486</v>
       </c>
-      <c r="I72" s="24" t="s">
+      <c r="I72" s="23" t="s">
         <v>487</v>
       </c>
       <c r="J72" s="1">
@@ -9581,13 +9574,13 @@
       <c r="F73" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="G73" s="24" t="s">
+      <c r="G73" s="23" t="s">
         <v>492</v>
       </c>
-      <c r="H73" s="24" t="s">
+      <c r="H73" s="23" t="s">
         <v>493</v>
       </c>
-      <c r="I73" s="24" t="s">
+      <c r="I73" s="23" t="s">
         <v>494</v>
       </c>
       <c r="J73" s="1">
@@ -9647,13 +9640,13 @@
       <c r="F74" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="G74" s="24" t="s">
+      <c r="G74" s="23" t="s">
         <v>499</v>
       </c>
-      <c r="H74" s="24" t="s">
+      <c r="H74" s="23" t="s">
         <v>500</v>
       </c>
-      <c r="I74" s="24" t="s">
+      <c r="I74" s="23" t="s">
         <v>501</v>
       </c>
       <c r="J74" s="1">
@@ -9713,13 +9706,13 @@
       <c r="F75" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="G75" s="24" t="s">
+      <c r="G75" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="H75" s="24" t="s">
+      <c r="H75" s="23" t="s">
         <v>507</v>
       </c>
-      <c r="I75" s="24" t="s">
+      <c r="I75" s="23" t="s">
         <v>508</v>
       </c>
       <c r="J75" s="1">
@@ -9756,7 +9749,7 @@
       <c r="S75" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="T75" s="24" t="s">
+      <c r="T75" s="23" t="s">
         <v>509</v>
       </c>
       <c r="U75" s="6"/>
@@ -9780,13 +9773,13 @@
       <c r="F76" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="G76" s="24" t="s">
+      <c r="G76" s="23" t="s">
         <v>513</v>
       </c>
-      <c r="H76" s="24" t="s">
+      <c r="H76" s="23" t="s">
         <v>514</v>
       </c>
-      <c r="I76" s="24" t="s">
+      <c r="I76" s="23" t="s">
         <v>515</v>
       </c>
       <c r="J76" s="1">
@@ -9845,13 +9838,13 @@
       <c r="F77" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="G77" s="24" t="s">
+      <c r="G77" s="23" t="s">
         <v>519</v>
       </c>
-      <c r="H77" s="24" t="s">
+      <c r="H77" s="23" t="s">
         <v>520</v>
       </c>
-      <c r="I77" s="24" t="s">
+      <c r="I77" s="23" t="s">
         <v>521</v>
       </c>
       <c r="J77" s="1">
@@ -9910,13 +9903,13 @@
       <c r="F78" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G78" s="24" t="s">
+      <c r="G78" s="23" t="s">
         <v>525</v>
       </c>
-      <c r="H78" s="24" t="s">
+      <c r="H78" s="23" t="s">
         <v>526</v>
       </c>
-      <c r="I78" s="24" t="s">
+      <c r="I78" s="23" t="s">
         <v>527</v>
       </c>
       <c r="J78" s="1">
@@ -9975,13 +9968,13 @@
       <c r="F79" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="G79" s="24" t="s">
+      <c r="G79" s="23" t="s">
         <v>531</v>
       </c>
-      <c r="H79" s="24" t="s">
+      <c r="H79" s="23" t="s">
         <v>532</v>
       </c>
-      <c r="I79" s="24" t="s">
+      <c r="I79" s="23" t="s">
         <v>533</v>
       </c>
       <c r="J79" s="1">
@@ -10040,13 +10033,13 @@
       <c r="F80" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="G80" s="24" t="s">
+      <c r="G80" s="23" t="s">
         <v>537</v>
       </c>
-      <c r="H80" s="24" t="s">
+      <c r="H80" s="23" t="s">
         <v>538</v>
       </c>
-      <c r="I80" s="24" t="s">
+      <c r="I80" s="23" t="s">
         <v>539</v>
       </c>
       <c r="J80" s="1">
@@ -10105,13 +10098,13 @@
       <c r="F81" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="G81" s="24" t="s">
+      <c r="G81" s="23" t="s">
         <v>543</v>
       </c>
-      <c r="H81" s="24" t="s">
+      <c r="H81" s="23" t="s">
         <v>544</v>
       </c>
-      <c r="I81" s="24" t="s">
+      <c r="I81" s="23" t="s">
         <v>545</v>
       </c>
       <c r="J81" s="1">
@@ -10172,13 +10165,13 @@
       <c r="F82" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="G82" s="24" t="s">
+      <c r="G82" s="23" t="s">
         <v>549</v>
       </c>
-      <c r="H82" s="24" t="s">
+      <c r="H82" s="23" t="s">
         <v>550</v>
       </c>
-      <c r="I82" s="24" t="s">
+      <c r="I82" s="23" t="s">
         <v>551</v>
       </c>
       <c r="J82" s="1">
@@ -10239,13 +10232,13 @@
       <c r="F83" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="G83" s="24" t="s">
+      <c r="G83" s="23" t="s">
         <v>555</v>
       </c>
-      <c r="H83" s="24" t="s">
+      <c r="H83" s="23" t="s">
         <v>556</v>
       </c>
-      <c r="I83" s="24" t="s">
+      <c r="I83" s="23" t="s">
         <v>557</v>
       </c>
       <c r="J83" s="1">
@@ -10306,13 +10299,13 @@
       <c r="F84" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="G84" s="24" t="s">
+      <c r="G84" s="23" t="s">
         <v>561</v>
       </c>
-      <c r="H84" s="24" t="s">
+      <c r="H84" s="23" t="s">
         <v>562</v>
       </c>
-      <c r="I84" s="24" t="s">
+      <c r="I84" s="23" t="s">
         <v>563</v>
       </c>
       <c r="J84" s="1">
@@ -10373,13 +10366,13 @@
       <c r="F85" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="G85" s="24" t="s">
+      <c r="G85" s="23" t="s">
         <v>567</v>
       </c>
-      <c r="H85" s="24" t="s">
+      <c r="H85" s="23" t="s">
         <v>568</v>
       </c>
-      <c r="I85" s="24" t="s">
+      <c r="I85" s="23" t="s">
         <v>569</v>
       </c>
       <c r="J85" s="1">
@@ -10440,13 +10433,13 @@
       <c r="F86" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="G86" s="24" t="s">
+      <c r="G86" s="23" t="s">
         <v>573</v>
       </c>
-      <c r="H86" s="24" t="s">
+      <c r="H86" s="23" t="s">
         <v>537</v>
       </c>
-      <c r="I86" s="24" t="s">
+      <c r="I86" s="23" t="s">
         <v>574</v>
       </c>
       <c r="J86" s="1">
@@ -10507,13 +10500,13 @@
       <c r="F87" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="G87" s="24" t="s">
+      <c r="G87" s="23" t="s">
         <v>578</v>
       </c>
-      <c r="H87" s="24" t="s">
+      <c r="H87" s="23" t="s">
         <v>579</v>
       </c>
-      <c r="I87" s="24" t="s">
+      <c r="I87" s="23" t="s">
         <v>580</v>
       </c>
       <c r="J87" s="1">
@@ -10574,13 +10567,13 @@
       <c r="F88" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="G88" s="24" t="s">
+      <c r="G88" s="23" t="s">
         <v>487</v>
       </c>
-      <c r="H88" s="24" t="s">
+      <c r="H88" s="23" t="s">
         <v>452</v>
       </c>
-      <c r="I88" s="24" t="s">
+      <c r="I88" s="23" t="s">
         <v>584</v>
       </c>
       <c r="J88" s="1">
@@ -10641,13 +10634,13 @@
       <c r="F89" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="G89" s="24" t="s">
+      <c r="G89" s="23" t="s">
         <v>501</v>
       </c>
-      <c r="H89" s="24" t="s">
+      <c r="H89" s="23" t="s">
         <v>588</v>
       </c>
-      <c r="I89" s="24" t="s">
+      <c r="I89" s="23" t="s">
         <v>589</v>
       </c>
       <c r="J89" s="1">
@@ -10708,13 +10701,13 @@
       <c r="F90" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="G90" s="24" t="s">
+      <c r="G90" s="23" t="s">
         <v>593</v>
       </c>
-      <c r="H90" s="24" t="s">
+      <c r="H90" s="23" t="s">
         <v>578</v>
       </c>
-      <c r="I90" s="24" t="s">
+      <c r="I90" s="23" t="s">
         <v>594</v>
       </c>
       <c r="J90" s="1">
@@ -10775,13 +10768,13 @@
       <c r="F91" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="G91" s="24" t="s">
+      <c r="G91" s="23" t="s">
         <v>598</v>
       </c>
-      <c r="H91" s="24" t="s">
+      <c r="H91" s="23" t="s">
         <v>599</v>
       </c>
-      <c r="I91" s="24" t="s">
+      <c r="I91" s="23" t="s">
         <v>600</v>
       </c>
       <c r="J91" s="1">
@@ -10842,13 +10835,13 @@
       <c r="F92" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="G92" s="24" t="s">
+      <c r="G92" s="23" t="s">
         <v>604</v>
       </c>
-      <c r="H92" s="24" t="s">
+      <c r="H92" s="23" t="s">
         <v>605</v>
       </c>
-      <c r="I92" s="24" t="s">
+      <c r="I92" s="23" t="s">
         <v>606</v>
       </c>
       <c r="J92" s="1">
@@ -10909,13 +10902,13 @@
       <c r="F93" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="G93" s="24" t="s">
+      <c r="G93" s="23" t="s">
         <v>610</v>
       </c>
-      <c r="H93" s="24" t="s">
+      <c r="H93" s="23" t="s">
         <v>611</v>
       </c>
-      <c r="I93" s="24" t="s">
+      <c r="I93" s="23" t="s">
         <v>612</v>
       </c>
       <c r="J93" s="1">
@@ -10976,13 +10969,13 @@
       <c r="F94" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="G94" s="24" t="s">
+      <c r="G94" s="23" t="s">
         <v>569</v>
       </c>
-      <c r="H94" s="24" t="s">
+      <c r="H94" s="23" t="s">
         <v>616</v>
       </c>
-      <c r="I94" s="24" t="s">
+      <c r="I94" s="23" t="s">
         <v>617</v>
       </c>
       <c r="J94" s="1">
@@ -11043,13 +11036,13 @@
       <c r="F95" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="G95" s="24" t="s">
+      <c r="G95" s="23" t="s">
         <v>574</v>
       </c>
-      <c r="H95" s="24" t="s">
+      <c r="H95" s="23" t="s">
         <v>621</v>
       </c>
-      <c r="I95" s="24" t="s">
+      <c r="I95" s="23" t="s">
         <v>622</v>
       </c>
       <c r="J95" s="1">
@@ -11108,13 +11101,13 @@
       <c r="F96" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G96" s="24" t="s">
+      <c r="G96" s="23" t="s">
         <v>580</v>
       </c>
-      <c r="H96" s="24" t="s">
+      <c r="H96" s="23" t="s">
         <v>626</v>
       </c>
-      <c r="I96" s="24" t="s">
+      <c r="I96" s="23" t="s">
         <v>627</v>
       </c>
       <c r="J96" s="1">
@@ -11168,13 +11161,13 @@
       <c r="F97" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="G97" s="24" t="s">
+      <c r="G97" s="23" t="s">
         <v>584</v>
       </c>
-      <c r="H97" s="24" t="s">
+      <c r="H97" s="23" t="s">
         <v>631</v>
       </c>
-      <c r="I97" s="24" t="s">
+      <c r="I97" s="23" t="s">
         <v>632</v>
       </c>
       <c r="J97" s="1">
@@ -11228,13 +11221,13 @@
       <c r="F98" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="G98" s="24" t="s">
+      <c r="G98" s="23" t="s">
         <v>636</v>
       </c>
-      <c r="H98" s="24" t="s">
+      <c r="H98" s="23" t="s">
         <v>637</v>
       </c>
-      <c r="I98" s="24" t="s">
+      <c r="I98" s="23" t="s">
         <v>638</v>
       </c>
       <c r="J98" s="1">
@@ -11288,13 +11281,13 @@
       <c r="F99" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="G99" s="24" t="s">
+      <c r="G99" s="23" t="s">
         <v>642</v>
       </c>
-      <c r="H99" s="24" t="s">
+      <c r="H99" s="23" t="s">
         <v>643</v>
       </c>
-      <c r="I99" s="24" t="s">
+      <c r="I99" s="23" t="s">
         <v>644</v>
       </c>
       <c r="J99" s="1">
@@ -11348,13 +11341,13 @@
       <c r="F100" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="G100" s="24" t="s">
+      <c r="G100" s="23" t="s">
         <v>648</v>
       </c>
-      <c r="H100" s="24" t="s">
+      <c r="H100" s="23" t="s">
         <v>649</v>
       </c>
-      <c r="I100" s="24" t="s">
+      <c r="I100" s="23" t="s">
         <v>650</v>
       </c>
       <c r="J100" s="1">
@@ -11408,13 +11401,13 @@
       <c r="F101" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="G101" s="24" t="s">
+      <c r="G101" s="23" t="s">
         <v>654</v>
       </c>
-      <c r="H101" s="24" t="s">
+      <c r="H101" s="23" t="s">
         <v>655</v>
       </c>
-      <c r="I101" s="24" t="s">
+      <c r="I101" s="23" t="s">
         <v>656</v>
       </c>
       <c r="J101" s="1">
@@ -11468,13 +11461,13 @@
       <c r="F102" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="G102" s="24" t="s">
+      <c r="G102" s="23" t="s">
         <v>660</v>
       </c>
-      <c r="H102" s="24" t="s">
+      <c r="H102" s="23" t="s">
         <v>661</v>
       </c>
-      <c r="I102" s="24" t="s">
+      <c r="I102" s="23" t="s">
         <v>662</v>
       </c>
       <c r="J102" s="1">
@@ -11528,13 +11521,13 @@
       <c r="F103" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="G103" s="24" t="s">
+      <c r="G103" s="23" t="s">
         <v>666</v>
       </c>
-      <c r="H103" s="24" t="s">
+      <c r="H103" s="23" t="s">
         <v>667</v>
       </c>
-      <c r="I103" s="24" t="s">
+      <c r="I103" s="23" t="s">
         <v>668</v>
       </c>
       <c r="J103" s="1">
@@ -11588,13 +11581,13 @@
       <c r="F104" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="G104" s="24" t="s">
+      <c r="G104" s="23" t="s">
         <v>672</v>
       </c>
-      <c r="H104" s="24" t="s">
+      <c r="H104" s="23" t="s">
         <v>666</v>
       </c>
-      <c r="I104" s="24" t="s">
+      <c r="I104" s="23" t="s">
         <v>673</v>
       </c>
       <c r="J104" s="1">
@@ -11648,13 +11641,13 @@
       <c r="F105" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="G105" s="24" t="s">
+      <c r="G105" s="23" t="s">
         <v>677</v>
       </c>
-      <c r="H105" s="24" t="s">
+      <c r="H105" s="23" t="s">
         <v>672</v>
       </c>
-      <c r="I105" s="24" t="s">
+      <c r="I105" s="23" t="s">
         <v>678</v>
       </c>
       <c r="J105" s="1">
@@ -11710,13 +11703,13 @@
       <c r="F106" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="G106" s="24" t="s">
+      <c r="G106" s="23" t="s">
         <v>682</v>
       </c>
-      <c r="H106" s="24" t="s">
+      <c r="H106" s="23" t="s">
         <v>683</v>
       </c>
-      <c r="I106" s="24" t="s">
+      <c r="I106" s="23" t="s">
         <v>684</v>
       </c>
       <c r="J106" s="1">
@@ -11777,13 +11770,13 @@
       <c r="F107" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="G107" s="24" t="s">
+      <c r="G107" s="23" t="s">
         <v>688</v>
       </c>
-      <c r="H107" s="24" t="s">
+      <c r="H107" s="23" t="s">
         <v>689</v>
       </c>
-      <c r="I107" s="24" t="s">
+      <c r="I107" s="23" t="s">
         <v>690</v>
       </c>
       <c r="J107" s="1">
@@ -11844,13 +11837,13 @@
       <c r="F108" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="G108" s="24" t="s">
+      <c r="G108" s="23" t="s">
         <v>694</v>
       </c>
-      <c r="H108" s="24" t="s">
+      <c r="H108" s="23" t="s">
         <v>695</v>
       </c>
-      <c r="I108" s="24" t="s">
+      <c r="I108" s="23" t="s">
         <v>696</v>
       </c>
       <c r="J108" s="1">
@@ -11911,13 +11904,13 @@
       <c r="F109" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="G109" s="24" t="s">
+      <c r="G109" s="23" t="s">
         <v>700</v>
       </c>
-      <c r="H109" s="24" t="s">
+      <c r="H109" s="23" t="s">
         <v>701</v>
       </c>
-      <c r="I109" s="24" t="s">
+      <c r="I109" s="23" t="s">
         <v>702</v>
       </c>
       <c r="J109" s="1">
@@ -11978,13 +11971,13 @@
       <c r="F110" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="G110" s="24" t="s">
+      <c r="G110" s="23" t="s">
         <v>706</v>
       </c>
-      <c r="H110" s="24" t="s">
+      <c r="H110" s="23" t="s">
         <v>707</v>
       </c>
-      <c r="I110" s="24" t="s">
+      <c r="I110" s="23" t="s">
         <v>708</v>
       </c>
       <c r="J110" s="1">
@@ -12045,13 +12038,13 @@
       <c r="F111" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="G111" s="25" t="s">
+      <c r="G111" s="24" t="s">
         <v>712</v>
       </c>
-      <c r="H111" s="26" t="s">
+      <c r="H111" s="25" t="s">
         <v>712</v>
       </c>
-      <c r="I111" s="27" t="s">
+      <c r="I111" s="26" t="s">
         <v>713</v>
       </c>
       <c r="J111" s="1">
@@ -12081,10 +12074,10 @@
       <c r="R111" s="6">
         <v>90</v>
       </c>
-      <c r="S111" s="24" t="s">
+      <c r="S111" s="23" t="s">
         <v>714</v>
       </c>
-      <c r="T111" s="24" t="s">
+      <c r="T111" s="23" t="s">
         <v>714</v>
       </c>
       <c r="W111" s="6"/>
@@ -12106,13 +12099,13 @@
       <c r="F112" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="G112" s="28" t="s">
+      <c r="G112" s="27" t="s">
         <v>718</v>
       </c>
-      <c r="H112" s="24" t="s">
+      <c r="H112" s="23" t="s">
         <v>718</v>
       </c>
-      <c r="I112" s="29" t="s">
+      <c r="I112" s="28" t="s">
         <v>719</v>
       </c>
       <c r="J112" s="1">
@@ -12147,10 +12140,10 @@
       <c r="R112" s="6">
         <v>90</v>
       </c>
-      <c r="S112" s="24" t="s">
+      <c r="S112" s="23" t="s">
         <v>720</v>
       </c>
-      <c r="T112" s="24" t="s">
+      <c r="T112" s="23" t="s">
         <v>720</v>
       </c>
       <c r="W112" s="6"/>
@@ -12172,13 +12165,13 @@
       <c r="F113" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="G113" s="28" t="s">
+      <c r="G113" s="27" t="s">
         <v>724</v>
       </c>
-      <c r="H113" s="24" t="s">
+      <c r="H113" s="23" t="s">
         <v>724</v>
       </c>
-      <c r="I113" s="29" t="s">
+      <c r="I113" s="28" t="s">
         <v>725</v>
       </c>
       <c r="J113" s="1">
@@ -12213,10 +12206,10 @@
       <c r="R113" s="6">
         <v>90</v>
       </c>
-      <c r="S113" s="24" t="s">
+      <c r="S113" s="23" t="s">
         <v>726</v>
       </c>
-      <c r="T113" s="24" t="s">
+      <c r="T113" s="23" t="s">
         <v>726</v>
       </c>
       <c r="W113" s="6"/>
@@ -12238,13 +12231,13 @@
       <c r="F114" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="G114" s="28" t="s">
+      <c r="G114" s="27" t="s">
         <v>730</v>
       </c>
-      <c r="H114" s="24" t="s">
+      <c r="H114" s="23" t="s">
         <v>730</v>
       </c>
-      <c r="I114" s="29" t="s">
+      <c r="I114" s="28" t="s">
         <v>731</v>
       </c>
       <c r="J114" s="1">
@@ -12279,10 +12272,10 @@
       <c r="R114" s="6">
         <v>90</v>
       </c>
-      <c r="S114" s="24" t="s">
+      <c r="S114" s="23" t="s">
         <v>732</v>
       </c>
-      <c r="T114" s="24" t="s">
+      <c r="T114" s="23" t="s">
         <v>732</v>
       </c>
       <c r="W114" s="6"/>
@@ -12304,13 +12297,13 @@
       <c r="F115" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="G115" s="28" t="s">
+      <c r="G115" s="27" t="s">
         <v>736</v>
       </c>
-      <c r="H115" s="24" t="s">
+      <c r="H115" s="23" t="s">
         <v>736</v>
       </c>
-      <c r="I115" s="29" t="s">
+      <c r="I115" s="28" t="s">
         <v>737</v>
       </c>
       <c r="J115" s="1">
@@ -12345,10 +12338,10 @@
       <c r="R115" s="6">
         <v>90</v>
       </c>
-      <c r="S115" s="24" t="s">
+      <c r="S115" s="23" t="s">
         <v>738</v>
       </c>
-      <c r="T115" s="24" t="s">
+      <c r="T115" s="23" t="s">
         <v>738</v>
       </c>
       <c r="W115" s="6"/>
@@ -12370,13 +12363,13 @@
       <c r="F116" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="G116" s="28" t="s">
+      <c r="G116" s="27" t="s">
         <v>742</v>
       </c>
-      <c r="H116" s="24" t="s">
+      <c r="H116" s="23" t="s">
         <v>742</v>
       </c>
-      <c r="I116" s="29" t="s">
+      <c r="I116" s="28" t="s">
         <v>743</v>
       </c>
       <c r="J116" s="1">
@@ -12411,10 +12404,10 @@
       <c r="R116" s="6">
         <v>90</v>
       </c>
-      <c r="S116" s="24" t="s">
+      <c r="S116" s="23" t="s">
         <v>744</v>
       </c>
-      <c r="T116" s="24" t="s">
+      <c r="T116" s="23" t="s">
         <v>744</v>
       </c>
       <c r="U116" s="6"/>
@@ -12438,13 +12431,13 @@
       <c r="F117" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="G117" s="28" t="s">
+      <c r="G117" s="27" t="s">
         <v>748</v>
       </c>
-      <c r="H117" s="24" t="s">
+      <c r="H117" s="23" t="s">
         <v>748</v>
       </c>
-      <c r="I117" s="29" t="s">
+      <c r="I117" s="28" t="s">
         <v>749</v>
       </c>
       <c r="J117" s="1">
@@ -12479,10 +12472,10 @@
       <c r="R117" s="6">
         <v>90</v>
       </c>
-      <c r="S117" s="24" t="s">
+      <c r="S117" s="23" t="s">
         <v>750</v>
       </c>
-      <c r="T117" s="24" t="s">
+      <c r="T117" s="23" t="s">
         <v>750</v>
       </c>
       <c r="U117" s="6"/>
@@ -12506,13 +12499,13 @@
       <c r="F118" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="G118" s="28" t="s">
+      <c r="G118" s="27" t="s">
         <v>754</v>
       </c>
-      <c r="H118" s="24" t="s">
+      <c r="H118" s="23" t="s">
         <v>754</v>
       </c>
-      <c r="I118" s="29" t="s">
+      <c r="I118" s="28" t="s">
         <v>755</v>
       </c>
       <c r="J118" s="1">
@@ -12547,10 +12540,10 @@
       <c r="R118" s="6">
         <v>90</v>
       </c>
-      <c r="S118" s="24" t="s">
+      <c r="S118" s="23" t="s">
         <v>756</v>
       </c>
-      <c r="T118" s="24" t="s">
+      <c r="T118" s="23" t="s">
         <v>756</v>
       </c>
       <c r="U118" s="6"/>
@@ -12574,13 +12567,13 @@
       <c r="F119" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="G119" s="28" t="s">
+      <c r="G119" s="27" t="s">
         <v>760</v>
       </c>
-      <c r="H119" s="24" t="s">
+      <c r="H119" s="23" t="s">
         <v>760</v>
       </c>
-      <c r="I119" s="29" t="s">
+      <c r="I119" s="28" t="s">
         <v>761</v>
       </c>
       <c r="J119" s="1">
@@ -12615,10 +12608,10 @@
       <c r="R119" s="6">
         <v>90</v>
       </c>
-      <c r="S119" s="24" t="s">
+      <c r="S119" s="23" t="s">
         <v>762</v>
       </c>
-      <c r="T119" s="24" t="s">
+      <c r="T119" s="23" t="s">
         <v>762</v>
       </c>
       <c r="U119" s="6"/>
@@ -12642,13 +12635,13 @@
       <c r="F120" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="G120" s="28" t="s">
+      <c r="G120" s="27" t="s">
         <v>766</v>
       </c>
-      <c r="H120" s="24" t="s">
+      <c r="H120" s="23" t="s">
         <v>766</v>
       </c>
-      <c r="I120" s="29" t="s">
+      <c r="I120" s="28" t="s">
         <v>767</v>
       </c>
       <c r="J120" s="1">
@@ -12683,10 +12676,10 @@
       <c r="R120" s="6">
         <v>90</v>
       </c>
-      <c r="S120" s="24" t="s">
+      <c r="S120" s="23" t="s">
         <v>768</v>
       </c>
-      <c r="T120" s="24" t="s">
+      <c r="T120" s="23" t="s">
         <v>768</v>
       </c>
       <c r="U120" s="6"/>
@@ -12710,13 +12703,13 @@
       <c r="F121" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G121" s="28" t="s">
+      <c r="G121" s="27" t="s">
         <v>713</v>
       </c>
-      <c r="H121" s="24" t="s">
+      <c r="H121" s="23" t="s">
         <v>713</v>
       </c>
-      <c r="I121" s="29" t="s">
+      <c r="I121" s="28" t="s">
         <v>772</v>
       </c>
       <c r="J121" s="1">
@@ -12751,10 +12744,10 @@
       <c r="R121" s="6">
         <v>90</v>
       </c>
-      <c r="S121" s="24" t="s">
+      <c r="S121" s="23" t="s">
         <v>773</v>
       </c>
-      <c r="T121" s="24" t="s">
+      <c r="T121" s="23" t="s">
         <v>773</v>
       </c>
       <c r="U121" s="6"/>
@@ -12778,13 +12771,13 @@
       <c r="F122" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="G122" s="28" t="s">
+      <c r="G122" s="27" t="s">
         <v>777</v>
       </c>
-      <c r="H122" s="24" t="s">
+      <c r="H122" s="23" t="s">
         <v>777</v>
       </c>
-      <c r="I122" s="29" t="s">
+      <c r="I122" s="28" t="s">
         <v>778</v>
       </c>
       <c r="J122" s="1">
@@ -12820,10 +12813,10 @@
       <c r="R122" s="6">
         <v>90</v>
       </c>
-      <c r="S122" s="24" t="s">
+      <c r="S122" s="23" t="s">
         <v>779</v>
       </c>
-      <c r="T122" s="24" t="s">
+      <c r="T122" s="23" t="s">
         <v>779</v>
       </c>
       <c r="U122" s="6"/>
@@ -12847,13 +12840,13 @@
       <c r="F123" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="G123" s="28" t="s">
+      <c r="G123" s="27" t="s">
         <v>783</v>
       </c>
-      <c r="H123" s="24" t="s">
+      <c r="H123" s="23" t="s">
         <v>783</v>
       </c>
-      <c r="I123" s="29" t="s">
+      <c r="I123" s="28" t="s">
         <v>784</v>
       </c>
       <c r="J123" s="1">
@@ -12889,10 +12882,10 @@
       <c r="R123" s="6">
         <v>90</v>
       </c>
-      <c r="S123" s="24" t="s">
+      <c r="S123" s="23" t="s">
         <v>785</v>
       </c>
-      <c r="T123" s="24" t="s">
+      <c r="T123" s="23" t="s">
         <v>785</v>
       </c>
       <c r="U123" s="6"/>
@@ -12916,13 +12909,13 @@
       <c r="F124" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="G124" s="28" t="s">
+      <c r="G124" s="27" t="s">
         <v>789</v>
       </c>
-      <c r="H124" s="24" t="s">
+      <c r="H124" s="23" t="s">
         <v>789</v>
       </c>
-      <c r="I124" s="29" t="s">
+      <c r="I124" s="28" t="s">
         <v>790</v>
       </c>
       <c r="J124" s="1">
@@ -12958,10 +12951,10 @@
       <c r="R124" s="6">
         <v>90</v>
       </c>
-      <c r="S124" s="24" t="s">
+      <c r="S124" s="23" t="s">
         <v>791</v>
       </c>
-      <c r="T124" s="24" t="s">
+      <c r="T124" s="23" t="s">
         <v>791</v>
       </c>
       <c r="U124" s="6"/>
@@ -12985,13 +12978,13 @@
       <c r="F125" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="G125" s="28" t="s">
+      <c r="G125" s="27" t="s">
         <v>795</v>
       </c>
-      <c r="H125" s="24" t="s">
+      <c r="H125" s="23" t="s">
         <v>795</v>
       </c>
-      <c r="I125" s="29" t="s">
+      <c r="I125" s="28" t="s">
         <v>796</v>
       </c>
       <c r="J125" s="1">
@@ -13027,10 +13020,10 @@
       <c r="R125" s="6">
         <v>90</v>
       </c>
-      <c r="S125" s="24" t="s">
+      <c r="S125" s="23" t="s">
         <v>797</v>
       </c>
-      <c r="T125" s="24" t="s">
+      <c r="T125" s="23" t="s">
         <v>797</v>
       </c>
       <c r="U125" s="6"/>
@@ -13054,13 +13047,13 @@
       <c r="F126" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="G126" s="28" t="s">
+      <c r="G126" s="27" t="s">
         <v>801</v>
       </c>
-      <c r="H126" s="24" t="s">
+      <c r="H126" s="23" t="s">
         <v>801</v>
       </c>
-      <c r="I126" s="29" t="s">
+      <c r="I126" s="28" t="s">
         <v>802</v>
       </c>
       <c r="J126" s="1">
@@ -13096,10 +13089,10 @@
       <c r="R126" s="6">
         <v>90</v>
       </c>
-      <c r="S126" s="24" t="s">
+      <c r="S126" s="23" t="s">
         <v>803</v>
       </c>
-      <c r="T126" s="24" t="s">
+      <c r="T126" s="23" t="s">
         <v>803</v>
       </c>
       <c r="U126" s="6"/>
@@ -13123,13 +13116,13 @@
       <c r="F127" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="G127" s="28" t="s">
+      <c r="G127" s="27" t="s">
         <v>807</v>
       </c>
-      <c r="H127" s="24" t="s">
+      <c r="H127" s="23" t="s">
         <v>807</v>
       </c>
-      <c r="I127" s="29" t="s">
+      <c r="I127" s="28" t="s">
         <v>808</v>
       </c>
       <c r="J127" s="1">
@@ -13165,10 +13158,10 @@
       <c r="R127" s="6">
         <v>90</v>
       </c>
-      <c r="S127" s="24" t="s">
+      <c r="S127" s="23" t="s">
         <v>809</v>
       </c>
-      <c r="T127" s="24" t="s">
+      <c r="T127" s="23" t="s">
         <v>809</v>
       </c>
       <c r="U127" s="6"/>
@@ -13192,13 +13185,13 @@
       <c r="F128" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="G128" s="28" t="s">
+      <c r="G128" s="27" t="s">
         <v>813</v>
       </c>
-      <c r="H128" s="24" t="s">
+      <c r="H128" s="23" t="s">
         <v>813</v>
       </c>
-      <c r="I128" s="29" t="s">
+      <c r="I128" s="28" t="s">
         <v>814</v>
       </c>
       <c r="J128" s="1">
@@ -13234,10 +13227,10 @@
       <c r="R128" s="6">
         <v>90</v>
       </c>
-      <c r="S128" s="24" t="s">
+      <c r="S128" s="23" t="s">
         <v>815</v>
       </c>
-      <c r="T128" s="24" t="s">
+      <c r="T128" s="23" t="s">
         <v>815</v>
       </c>
       <c r="U128" s="6"/>
@@ -13261,13 +13254,13 @@
       <c r="F129" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="G129" s="28" t="s">
+      <c r="G129" s="27" t="s">
         <v>819</v>
       </c>
-      <c r="H129" s="24" t="s">
+      <c r="H129" s="23" t="s">
         <v>819</v>
       </c>
-      <c r="I129" s="29" t="s">
+      <c r="I129" s="28" t="s">
         <v>820</v>
       </c>
       <c r="J129" s="1">
@@ -13303,10 +13296,10 @@
       <c r="R129" s="6">
         <v>90</v>
       </c>
-      <c r="S129" s="24" t="s">
+      <c r="S129" s="23" t="s">
         <v>821</v>
       </c>
-      <c r="T129" s="24" t="s">
+      <c r="T129" s="23" t="s">
         <v>821</v>
       </c>
       <c r="U129" s="6"/>
@@ -13330,13 +13323,13 @@
       <c r="F130" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="G130" s="28" t="s">
+      <c r="G130" s="27" t="s">
         <v>825</v>
       </c>
-      <c r="H130" s="24" t="s">
+      <c r="H130" s="23" t="s">
         <v>825</v>
       </c>
-      <c r="I130" s="29" t="s">
+      <c r="I130" s="28" t="s">
         <v>826</v>
       </c>
       <c r="J130" s="1">
@@ -13372,10 +13365,10 @@
       <c r="R130" s="6">
         <v>90</v>
       </c>
-      <c r="S130" s="24" t="s">
+      <c r="S130" s="23" t="s">
         <v>827</v>
       </c>
-      <c r="T130" s="24" t="s">
+      <c r="T130" s="23" t="s">
         <v>827</v>
       </c>
       <c r="U130" s="6"/>
@@ -13397,13 +13390,13 @@
       <c r="F131" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="G131" s="28" t="s">
+      <c r="G131" s="27" t="s">
         <v>831</v>
       </c>
-      <c r="H131" s="24" t="s">
+      <c r="H131" s="23" t="s">
         <v>831</v>
       </c>
-      <c r="I131" s="29" t="s">
+      <c r="I131" s="28" t="s">
         <v>832</v>
       </c>
       <c r="J131" s="1">
@@ -13439,10 +13432,10 @@
       <c r="R131" s="6">
         <v>92</v>
       </c>
-      <c r="S131" s="24" t="s">
+      <c r="S131" s="23" t="s">
         <v>833</v>
       </c>
-      <c r="T131" s="24" t="s">
+      <c r="T131" s="23" t="s">
         <v>833</v>
       </c>
     </row>
@@ -13459,13 +13452,13 @@
       <c r="F132" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="G132" s="28" t="s">
+      <c r="G132" s="27" t="s">
         <v>837</v>
       </c>
-      <c r="H132" s="24" t="s">
+      <c r="H132" s="23" t="s">
         <v>837</v>
       </c>
-      <c r="I132" s="29" t="s">
+      <c r="I132" s="28" t="s">
         <v>838</v>
       </c>
       <c r="J132" s="1">
@@ -13501,10 +13494,10 @@
       <c r="R132" s="6">
         <v>94</v>
       </c>
-      <c r="S132" s="24" t="s">
+      <c r="S132" s="23" t="s">
         <v>839</v>
       </c>
-      <c r="T132" s="24" t="s">
+      <c r="T132" s="23" t="s">
         <v>839</v>
       </c>
     </row>
@@ -13521,13 +13514,13 @@
       <c r="F133" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="G133" s="28" t="s">
+      <c r="G133" s="27" t="s">
         <v>843</v>
       </c>
-      <c r="H133" s="24" t="s">
+      <c r="H133" s="23" t="s">
         <v>843</v>
       </c>
-      <c r="I133" s="29" t="s">
+      <c r="I133" s="28" t="s">
         <v>844</v>
       </c>
       <c r="J133" s="1">
@@ -13563,10 +13556,10 @@
       <c r="R133" s="6">
         <v>96</v>
       </c>
-      <c r="S133" s="24" t="s">
+      <c r="S133" s="23" t="s">
         <v>845</v>
       </c>
-      <c r="T133" s="24" t="s">
+      <c r="T133" s="23" t="s">
         <v>845</v>
       </c>
     </row>
@@ -13583,13 +13576,13 @@
       <c r="F134" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="G134" s="28" t="s">
+      <c r="G134" s="27" t="s">
         <v>849</v>
       </c>
-      <c r="H134" s="24" t="s">
+      <c r="H134" s="23" t="s">
         <v>849</v>
       </c>
-      <c r="I134" s="29" t="s">
+      <c r="I134" s="28" t="s">
         <v>850</v>
       </c>
       <c r="J134" s="1">
@@ -13625,10 +13618,10 @@
       <c r="R134" s="6">
         <v>98</v>
       </c>
-      <c r="S134" s="24" t="s">
+      <c r="S134" s="23" t="s">
         <v>851</v>
       </c>
-      <c r="T134" s="24" t="s">
+      <c r="T134" s="23" t="s">
         <v>851</v>
       </c>
     </row>
@@ -13645,13 +13638,13 @@
       <c r="F135" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="G135" s="28" t="s">
+      <c r="G135" s="27" t="s">
         <v>855</v>
       </c>
-      <c r="H135" s="24" t="s">
+      <c r="H135" s="23" t="s">
         <v>855</v>
       </c>
-      <c r="I135" s="29" t="s">
+      <c r="I135" s="28" t="s">
         <v>856</v>
       </c>
       <c r="J135" s="1">
@@ -13687,10 +13680,10 @@
       <c r="R135" s="6">
         <v>99</v>
       </c>
-      <c r="S135" s="24" t="s">
+      <c r="S135" s="23" t="s">
         <v>857</v>
       </c>
-      <c r="T135" s="24" t="s">
+      <c r="T135" s="23" t="s">
         <v>857</v>
       </c>
     </row>
@@ -13707,13 +13700,13 @@
       <c r="F136" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="G136" s="28" t="s">
+      <c r="G136" s="27" t="s">
         <v>861</v>
       </c>
-      <c r="H136" s="24" t="s">
+      <c r="H136" s="23" t="s">
         <v>861</v>
       </c>
-      <c r="I136" s="29" t="s">
+      <c r="I136" s="28" t="s">
         <v>862</v>
       </c>
       <c r="J136" s="1">
@@ -13749,10 +13742,10 @@
       <c r="R136" s="6">
         <v>99.2</v>
       </c>
-      <c r="S136" s="24" t="s">
+      <c r="S136" s="23" t="s">
         <v>863</v>
       </c>
-      <c r="T136" s="24" t="s">
+      <c r="T136" s="23" t="s">
         <v>863</v>
       </c>
     </row>
@@ -13769,13 +13762,13 @@
       <c r="F137" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="G137" s="28" t="s">
+      <c r="G137" s="27" t="s">
         <v>867</v>
       </c>
-      <c r="H137" s="24" t="s">
+      <c r="H137" s="23" t="s">
         <v>867</v>
       </c>
-      <c r="I137" s="29" t="s">
+      <c r="I137" s="28" t="s">
         <v>868</v>
       </c>
       <c r="J137" s="1">
@@ -13811,10 +13804,10 @@
       <c r="R137" s="6">
         <v>99.4</v>
       </c>
-      <c r="S137" s="24" t="s">
+      <c r="S137" s="23" t="s">
         <v>869</v>
       </c>
-      <c r="T137" s="24" t="s">
+      <c r="T137" s="23" t="s">
         <v>869</v>
       </c>
     </row>
@@ -13831,13 +13824,13 @@
       <c r="F138" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="G138" s="28" t="s">
+      <c r="G138" s="27" t="s">
         <v>873</v>
       </c>
-      <c r="H138" s="24" t="s">
+      <c r="H138" s="23" t="s">
         <v>873</v>
       </c>
-      <c r="I138" s="29" t="s">
+      <c r="I138" s="28" t="s">
         <v>874</v>
       </c>
       <c r="J138" s="1">
@@ -13873,10 +13866,10 @@
       <c r="R138" s="6">
         <v>99.6</v>
       </c>
-      <c r="S138" s="24" t="s">
+      <c r="S138" s="23" t="s">
         <v>875</v>
       </c>
-      <c r="T138" s="24" t="s">
+      <c r="T138" s="23" t="s">
         <v>875</v>
       </c>
     </row>
@@ -13893,13 +13886,13 @@
       <c r="F139" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="G139" s="28" t="s">
+      <c r="G139" s="27" t="s">
         <v>879</v>
       </c>
-      <c r="H139" s="24" t="s">
+      <c r="H139" s="23" t="s">
         <v>879</v>
       </c>
-      <c r="I139" s="29" t="s">
+      <c r="I139" s="28" t="s">
         <v>880</v>
       </c>
       <c r="J139" s="1">
@@ -13935,10 +13928,10 @@
       <c r="R139" s="6">
         <v>99.8</v>
       </c>
-      <c r="S139" s="24" t="s">
+      <c r="S139" s="23" t="s">
         <v>881</v>
       </c>
-      <c r="T139" s="24" t="s">
+      <c r="T139" s="23" t="s">
         <v>881</v>
       </c>
     </row>
@@ -13955,13 +13948,13 @@
       <c r="F140" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="G140" s="28" t="s">
+      <c r="G140" s="27" t="s">
         <v>885</v>
       </c>
-      <c r="H140" s="24" t="s">
+      <c r="H140" s="23" t="s">
         <v>885</v>
       </c>
-      <c r="I140" s="29" t="s">
+      <c r="I140" s="28" t="s">
         <v>886</v>
       </c>
       <c r="J140" s="1">
@@ -13997,10 +13990,10 @@
       <c r="R140" s="6">
         <v>99.9</v>
       </c>
-      <c r="S140" s="24" t="s">
+      <c r="S140" s="23" t="s">
         <v>887</v>
       </c>
-      <c r="T140" s="24" t="s">
+      <c r="T140" s="23" t="s">
         <v>887</v>
       </c>
     </row>
@@ -14019,13 +14012,13 @@
       <c r="F141" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="G141" s="28" t="s">
+      <c r="G141" s="27" t="s">
         <v>891</v>
       </c>
-      <c r="H141" s="24" t="s">
+      <c r="H141" s="23" t="s">
         <v>891</v>
       </c>
-      <c r="I141" s="29" t="s">
+      <c r="I141" s="28" t="s">
         <v>892</v>
       </c>
       <c r="J141" s="1">
@@ -14061,10 +14054,10 @@
       <c r="R141" s="6">
         <v>99.92</v>
       </c>
-      <c r="S141" s="24" t="s">
+      <c r="S141" s="23" t="s">
         <v>893</v>
       </c>
-      <c r="T141" s="24" t="s">
+      <c r="T141" s="23" t="s">
         <v>893</v>
       </c>
       <c r="U141" s="6"/>
@@ -14088,13 +14081,13 @@
       <c r="F142" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="G142" s="28" t="s">
+      <c r="G142" s="27" t="s">
         <v>897</v>
       </c>
-      <c r="H142" s="24" t="s">
+      <c r="H142" s="23" t="s">
         <v>897</v>
       </c>
-      <c r="I142" s="29" t="s">
+      <c r="I142" s="28" t="s">
         <v>898</v>
       </c>
       <c r="J142" s="1">
@@ -14130,10 +14123,10 @@
       <c r="R142" s="6">
         <v>99.94</v>
       </c>
-      <c r="S142" s="24" t="s">
+      <c r="S142" s="23" t="s">
         <v>899</v>
       </c>
-      <c r="T142" s="24" t="s">
+      <c r="T142" s="23" t="s">
         <v>899</v>
       </c>
       <c r="U142" s="6"/>
@@ -14157,13 +14150,13 @@
       <c r="F143" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="G143" s="28" t="s">
+      <c r="G143" s="27" t="s">
         <v>903</v>
       </c>
-      <c r="H143" s="24" t="s">
+      <c r="H143" s="23" t="s">
         <v>903</v>
       </c>
-      <c r="I143" s="29" t="s">
+      <c r="I143" s="28" t="s">
         <v>904</v>
       </c>
       <c r="J143" s="1">
@@ -14199,10 +14192,10 @@
       <c r="R143" s="6">
         <v>99.96</v>
       </c>
-      <c r="S143" s="24" t="s">
+      <c r="S143" s="23" t="s">
         <v>905</v>
       </c>
-      <c r="T143" s="24" t="s">
+      <c r="T143" s="23" t="s">
         <v>905</v>
       </c>
       <c r="U143" s="6"/>
@@ -14226,13 +14219,13 @@
       <c r="F144" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="G144" s="28" t="s">
+      <c r="G144" s="27" t="s">
         <v>909</v>
       </c>
-      <c r="H144" s="24" t="s">
+      <c r="H144" s="23" t="s">
         <v>909</v>
       </c>
-      <c r="I144" s="29" t="s">
+      <c r="I144" s="28" t="s">
         <v>910</v>
       </c>
       <c r="J144" s="1">
@@ -14268,10 +14261,10 @@
       <c r="R144" s="6">
         <v>99.98</v>
       </c>
-      <c r="S144" s="24" t="s">
+      <c r="S144" s="23" t="s">
         <v>911</v>
       </c>
-      <c r="T144" s="24" t="s">
+      <c r="T144" s="23" t="s">
         <v>911</v>
       </c>
       <c r="U144" s="6"/>
@@ -14337,10 +14330,10 @@
       <c r="R145" s="6">
         <v>99.99</v>
       </c>
-      <c r="S145" s="24" t="s">
+      <c r="S145" s="23" t="s">
         <v>917</v>
       </c>
-      <c r="T145" s="24" t="s">
+      <c r="T145" s="23" t="s">
         <v>917</v>
       </c>
       <c r="U145" s="6"/>
@@ -14405,10 +14398,10 @@
       <c r="R146" s="14">
         <v>99.99</v>
       </c>
-      <c r="S146" s="30" t="s">
+      <c r="S146" s="29" t="s">
         <v>925</v>
       </c>
-      <c r="T146" s="30" t="s">
+      <c r="T146" s="29" t="s">
         <v>925</v>
       </c>
       <c r="W146" s="14"/>
@@ -14473,10 +14466,10 @@
       <c r="R147" s="6">
         <v>99.99</v>
       </c>
-      <c r="S147" s="24" t="s">
+      <c r="S147" s="23" t="s">
         <v>933</v>
       </c>
-      <c r="T147" s="24" t="s">
+      <c r="T147" s="23" t="s">
         <v>933</v>
       </c>
       <c r="W147" s="6"/>
@@ -14541,10 +14534,10 @@
       <c r="R148" s="6">
         <v>99.99</v>
       </c>
-      <c r="S148" s="24" t="s">
+      <c r="S148" s="23" t="s">
         <v>941</v>
       </c>
-      <c r="T148" s="24" t="s">
+      <c r="T148" s="23" t="s">
         <v>941</v>
       </c>
       <c r="W148" s="6"/>
@@ -14609,10 +14602,10 @@
       <c r="R149" s="6">
         <v>99.99</v>
       </c>
-      <c r="S149" s="24" t="s">
+      <c r="S149" s="23" t="s">
         <v>949</v>
       </c>
-      <c r="T149" s="24" t="s">
+      <c r="T149" s="23" t="s">
         <v>949</v>
       </c>
       <c r="W149" s="6"/>
@@ -14677,10 +14670,10 @@
       <c r="R150" s="6">
         <v>99.99</v>
       </c>
-      <c r="S150" s="24" t="s">
+      <c r="S150" s="23" t="s">
         <v>957</v>
       </c>
-      <c r="T150" s="24" t="s">
+      <c r="T150" s="23" t="s">
         <v>957</v>
       </c>
       <c r="W150" s="6"/>
@@ -14744,10 +14737,10 @@
       <c r="R151" s="6">
         <v>99.99</v>
       </c>
-      <c r="S151" s="24" t="s">
+      <c r="S151" s="23" t="s">
         <v>966</v>
       </c>
-      <c r="T151" s="24" t="s">
+      <c r="T151" s="23" t="s">
         <v>966</v>
       </c>
       <c r="U151" s="6"/>
@@ -14813,10 +14806,10 @@
       <c r="R152" s="6">
         <v>99.99</v>
       </c>
-      <c r="S152" s="24" t="s">
+      <c r="S152" s="23" t="s">
         <v>975</v>
       </c>
-      <c r="T152" s="24" t="s">
+      <c r="T152" s="23" t="s">
         <v>975</v>
       </c>
       <c r="U152" s="6"/>
@@ -14882,10 +14875,10 @@
       <c r="R153" s="6">
         <v>99.99</v>
       </c>
-      <c r="S153" s="24" t="s">
+      <c r="S153" s="23" t="s">
         <v>984</v>
       </c>
-      <c r="T153" s="24" t="s">
+      <c r="T153" s="23" t="s">
         <v>984</v>
       </c>
       <c r="U153" s="6"/>
@@ -14951,10 +14944,10 @@
       <c r="R154" s="6">
         <v>99.99</v>
       </c>
-      <c r="S154" s="24" t="s">
+      <c r="S154" s="23" t="s">
         <v>993</v>
       </c>
-      <c r="T154" s="24" t="s">
+      <c r="T154" s="23" t="s">
         <v>993</v>
       </c>
       <c r="U154" s="6"/>
@@ -15020,10 +15013,10 @@
       <c r="R155" s="6">
         <v>99.99</v>
       </c>
-      <c r="S155" s="24" t="s">
+      <c r="S155" s="23" t="s">
         <v>1002</v>
       </c>
-      <c r="T155" s="24" t="s">
+      <c r="T155" s="23" t="s">
         <v>1002</v>
       </c>
       <c r="U155" s="6"/>
@@ -15089,10 +15082,10 @@
       <c r="R156" s="6">
         <v>99.99</v>
       </c>
-      <c r="S156" s="24" t="s">
+      <c r="S156" s="23" t="s">
         <v>1011</v>
       </c>
-      <c r="T156" s="24" t="s">
+      <c r="T156" s="23" t="s">
         <v>1011</v>
       </c>
       <c r="U156" s="6"/>
@@ -15158,10 +15151,10 @@
       <c r="R157" s="6">
         <v>99.99</v>
       </c>
-      <c r="S157" s="24" t="s">
+      <c r="S157" s="23" t="s">
         <v>1020</v>
       </c>
-      <c r="T157" s="24" t="s">
+      <c r="T157" s="23" t="s">
         <v>1020</v>
       </c>
       <c r="U157" s="6"/>
@@ -15227,10 +15220,10 @@
       <c r="R158" s="6">
         <v>99.99</v>
       </c>
-      <c r="S158" s="24" t="s">
+      <c r="S158" s="23" t="s">
         <v>1029</v>
       </c>
-      <c r="T158" s="24" t="s">
+      <c r="T158" s="23" t="s">
         <v>1029</v>
       </c>
       <c r="U158" s="6"/>
@@ -15296,10 +15289,10 @@
       <c r="R159" s="6">
         <v>99.99</v>
       </c>
-      <c r="S159" s="24" t="s">
+      <c r="S159" s="23" t="s">
         <v>1038</v>
       </c>
-      <c r="T159" s="24" t="s">
+      <c r="T159" s="23" t="s">
         <v>1038</v>
       </c>
       <c r="U159" s="6"/>
@@ -15365,10 +15358,10 @@
       <c r="R160" s="6">
         <v>99.99</v>
       </c>
-      <c r="S160" s="24" t="s">
+      <c r="S160" s="23" t="s">
         <v>1047</v>
       </c>
-      <c r="T160" s="24" t="s">
+      <c r="T160" s="23" t="s">
         <v>1047</v>
       </c>
       <c r="U160" s="6"/>
@@ -15434,10 +15427,10 @@
       <c r="R161" s="6">
         <v>99.99</v>
       </c>
-      <c r="S161" s="24" t="s">
+      <c r="S161" s="23" t="s">
         <v>1056</v>
       </c>
-      <c r="T161" s="24" t="s">
+      <c r="T161" s="23" t="s">
         <v>1056</v>
       </c>
       <c r="U161" s="6"/>
@@ -15503,10 +15496,10 @@
       <c r="R162" s="6">
         <v>99.99</v>
       </c>
-      <c r="S162" s="24" t="s">
+      <c r="S162" s="23" t="s">
         <v>1065</v>
       </c>
-      <c r="T162" s="24" t="s">
+      <c r="T162" s="23" t="s">
         <v>1065</v>
       </c>
       <c r="U162" s="6"/>
@@ -15572,10 +15565,10 @@
       <c r="R163" s="6">
         <v>99.99</v>
       </c>
-      <c r="S163" s="24" t="s">
+      <c r="S163" s="23" t="s">
         <v>1074</v>
       </c>
-      <c r="T163" s="24" t="s">
+      <c r="T163" s="23" t="s">
         <v>1074</v>
       </c>
       <c r="U163" s="6"/>
@@ -15641,10 +15634,10 @@
       <c r="R164" s="16">
         <v>99.99</v>
       </c>
-      <c r="S164" s="31" t="s">
+      <c r="S164" s="30" t="s">
         <v>1083</v>
       </c>
-      <c r="T164" s="31" t="s">
+      <c r="T164" s="30" t="s">
         <v>1083</v>
       </c>
       <c r="U164" s="16"/>
@@ -15668,7 +15661,7 @@
       <c r="F165" s="4" t="s">
         <v>1086</v>
       </c>
-      <c r="G165" s="32" t="s">
+      <c r="G165" s="31" t="s">
         <v>1087</v>
       </c>
       <c r="H165" s="4" t="s">
@@ -15710,10 +15703,10 @@
       <c r="R165" s="17">
         <v>99.99</v>
       </c>
-      <c r="S165" s="33" t="s">
+      <c r="S165" s="32" t="s">
         <v>1092</v>
       </c>
-      <c r="T165" s="33" t="s">
+      <c r="T165" s="32" t="s">
         <v>1092</v>
       </c>
       <c r="U165" s="17"/>
@@ -15735,19 +15728,19 @@
       <c r="F166" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="G166" s="34" t="s">
+      <c r="G166" s="33" t="s">
         <v>1096</v>
       </c>
-      <c r="H166" s="34" t="s">
+      <c r="H166" s="33" t="s">
         <v>1097</v>
       </c>
-      <c r="I166" s="34" t="s">
+      <c r="I166" s="33" t="s">
         <v>1098</v>
       </c>
-      <c r="J166" s="34" t="s">
+      <c r="J166" s="33" t="s">
         <v>1099</v>
       </c>
-      <c r="K166" s="34" t="s">
+      <c r="K166" s="33" t="s">
         <v>1100</v>
       </c>
       <c r="L166" s="1">
@@ -15777,10 +15770,10 @@
       <c r="R166" s="6">
         <v>99.99</v>
       </c>
-      <c r="S166" s="24" t="s">
+      <c r="S166" s="23" t="s">
         <v>1101</v>
       </c>
-      <c r="T166" s="24" t="s">
+      <c r="T166" s="23" t="s">
         <v>1101</v>
       </c>
     </row>
@@ -15797,19 +15790,19 @@
       <c r="F167" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="G167" s="34" t="s">
+      <c r="G167" s="33" t="s">
         <v>1105</v>
       </c>
-      <c r="H167" s="34" t="s">
+      <c r="H167" s="33" t="s">
         <v>1106</v>
       </c>
-      <c r="I167" s="34" t="s">
+      <c r="I167" s="33" t="s">
         <v>1107</v>
       </c>
-      <c r="J167" s="34" t="s">
+      <c r="J167" s="33" t="s">
         <v>1108</v>
       </c>
-      <c r="K167" s="34" t="s">
+      <c r="K167" s="33" t="s">
         <v>1109</v>
       </c>
       <c r="L167" s="1">
@@ -15839,10 +15832,10 @@
       <c r="R167" s="6">
         <v>99.99</v>
       </c>
-      <c r="S167" s="24" t="s">
+      <c r="S167" s="23" t="s">
         <v>1110</v>
       </c>
-      <c r="T167" s="24" t="s">
+      <c r="T167" s="23" t="s">
         <v>1110</v>
       </c>
     </row>
@@ -15859,19 +15852,19 @@
       <c r="F168" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="G168" s="34" t="s">
+      <c r="G168" s="33" t="s">
         <v>1114</v>
       </c>
-      <c r="H168" s="34" t="s">
+      <c r="H168" s="33" t="s">
         <v>1115</v>
       </c>
-      <c r="I168" s="34" t="s">
+      <c r="I168" s="33" t="s">
         <v>1116</v>
       </c>
-      <c r="J168" s="34" t="s">
+      <c r="J168" s="33" t="s">
         <v>1117</v>
       </c>
-      <c r="K168" s="34" t="s">
+      <c r="K168" s="33" t="s">
         <v>1118</v>
       </c>
       <c r="L168" s="1">
@@ -15901,10 +15894,10 @@
       <c r="R168" s="6">
         <v>99.99</v>
       </c>
-      <c r="S168" s="24" t="s">
+      <c r="S168" s="23" t="s">
         <v>1119</v>
       </c>
-      <c r="T168" s="24" t="s">
+      <c r="T168" s="23" t="s">
         <v>1119</v>
       </c>
     </row>
@@ -15921,19 +15914,19 @@
       <c r="F169" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="G169" s="34" t="s">
+      <c r="G169" s="33" t="s">
         <v>1123</v>
       </c>
-      <c r="H169" s="34" t="s">
+      <c r="H169" s="33" t="s">
         <v>1124</v>
       </c>
-      <c r="I169" s="34" t="s">
+      <c r="I169" s="33" t="s">
         <v>1125</v>
       </c>
-      <c r="J169" s="34" t="s">
+      <c r="J169" s="33" t="s">
         <v>1126</v>
       </c>
-      <c r="K169" s="34" t="s">
+      <c r="K169" s="33" t="s">
         <v>1127</v>
       </c>
       <c r="L169" s="1">
@@ -15963,10 +15956,10 @@
       <c r="R169" s="6">
         <v>99.99</v>
       </c>
-      <c r="S169" s="24" t="s">
+      <c r="S169" s="23" t="s">
         <v>1128</v>
       </c>
-      <c r="T169" s="24" t="s">
+      <c r="T169" s="23" t="s">
         <v>1128</v>
       </c>
     </row>
@@ -15983,19 +15976,19 @@
       <c r="F170" s="1" t="s">
         <v>1131</v>
       </c>
-      <c r="G170" s="34" t="s">
+      <c r="G170" s="33" t="s">
         <v>1132</v>
       </c>
-      <c r="H170" s="34" t="s">
+      <c r="H170" s="33" t="s">
         <v>1133</v>
       </c>
-      <c r="I170" s="34" t="s">
+      <c r="I170" s="33" t="s">
         <v>1134</v>
       </c>
-      <c r="J170" s="34" t="s">
+      <c r="J170" s="33" t="s">
         <v>1135</v>
       </c>
-      <c r="K170" s="34" t="s">
+      <c r="K170" s="33" t="s">
         <v>1136</v>
       </c>
       <c r="L170" s="1">
@@ -16025,10 +16018,10 @@
       <c r="R170" s="6">
         <v>99.99</v>
       </c>
-      <c r="S170" s="24" t="s">
+      <c r="S170" s="23" t="s">
         <v>1137</v>
       </c>
-      <c r="T170" s="24" t="s">
+      <c r="T170" s="23" t="s">
         <v>1137</v>
       </c>
     </row>
@@ -16045,19 +16038,19 @@
       <c r="F171" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="G171" s="34" t="s">
+      <c r="G171" s="33" t="s">
         <v>1141</v>
       </c>
-      <c r="H171" s="34" t="s">
+      <c r="H171" s="33" t="s">
         <v>1142</v>
       </c>
-      <c r="I171" s="34" t="s">
+      <c r="I171" s="33" t="s">
         <v>1143</v>
       </c>
-      <c r="J171" s="34" t="s">
+      <c r="J171" s="33" t="s">
         <v>1144</v>
       </c>
-      <c r="K171" s="34" t="s">
+      <c r="K171" s="33" t="s">
         <v>1145</v>
       </c>
       <c r="L171" s="1">
@@ -16087,10 +16080,10 @@
       <c r="R171" s="6">
         <v>99.99</v>
       </c>
-      <c r="S171" s="24" t="s">
+      <c r="S171" s="23" t="s">
         <v>1146</v>
       </c>
-      <c r="T171" s="24" t="s">
+      <c r="T171" s="23" t="s">
         <v>1146</v>
       </c>
     </row>
@@ -16107,19 +16100,19 @@
       <c r="F172" s="1" t="s">
         <v>1149</v>
       </c>
-      <c r="G172" s="34" t="s">
+      <c r="G172" s="33" t="s">
         <v>1150</v>
       </c>
-      <c r="H172" s="34" t="s">
+      <c r="H172" s="33" t="s">
         <v>1151</v>
       </c>
-      <c r="I172" s="34" t="s">
+      <c r="I172" s="33" t="s">
         <v>1152</v>
       </c>
-      <c r="J172" s="34" t="s">
+      <c r="J172" s="33" t="s">
         <v>1153</v>
       </c>
-      <c r="K172" s="34" t="s">
+      <c r="K172" s="33" t="s">
         <v>1154</v>
       </c>
       <c r="L172" s="1">
@@ -16149,10 +16142,10 @@
       <c r="R172" s="6">
         <v>99.99</v>
       </c>
-      <c r="S172" s="24" t="s">
+      <c r="S172" s="23" t="s">
         <v>1155</v>
       </c>
-      <c r="T172" s="24" t="s">
+      <c r="T172" s="23" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -16169,19 +16162,19 @@
       <c r="F173" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="G173" s="34" t="s">
+      <c r="G173" s="33" t="s">
         <v>1159</v>
       </c>
-      <c r="H173" s="34" t="s">
+      <c r="H173" s="33" t="s">
         <v>1160</v>
       </c>
-      <c r="I173" s="34" t="s">
+      <c r="I173" s="33" t="s">
         <v>1161</v>
       </c>
-      <c r="J173" s="34" t="s">
+      <c r="J173" s="33" t="s">
         <v>1162</v>
       </c>
-      <c r="K173" s="34" t="s">
+      <c r="K173" s="33" t="s">
         <v>1163</v>
       </c>
       <c r="L173" s="1">
@@ -16211,10 +16204,10 @@
       <c r="R173" s="6">
         <v>99.99</v>
       </c>
-      <c r="S173" s="24" t="s">
+      <c r="S173" s="23" t="s">
         <v>1164</v>
       </c>
-      <c r="T173" s="24" t="s">
+      <c r="T173" s="23" t="s">
         <v>1164</v>
       </c>
     </row>
@@ -16231,19 +16224,19 @@
       <c r="F174" s="1" t="s">
         <v>1167</v>
       </c>
-      <c r="G174" s="34" t="s">
+      <c r="G174" s="33" t="s">
         <v>1168</v>
       </c>
-      <c r="H174" s="34" t="s">
+      <c r="H174" s="33" t="s">
         <v>1169</v>
       </c>
-      <c r="I174" s="34" t="s">
+      <c r="I174" s="33" t="s">
         <v>1170</v>
       </c>
-      <c r="J174" s="34" t="s">
+      <c r="J174" s="33" t="s">
         <v>1171</v>
       </c>
-      <c r="K174" s="34" t="s">
+      <c r="K174" s="33" t="s">
         <v>1172</v>
       </c>
       <c r="L174" s="1">
@@ -16273,10 +16266,10 @@
       <c r="R174" s="6">
         <v>99.99</v>
       </c>
-      <c r="S174" s="24" t="s">
+      <c r="S174" s="23" t="s">
         <v>1173</v>
       </c>
-      <c r="T174" s="24" t="s">
+      <c r="T174" s="23" t="s">
         <v>1173</v>
       </c>
     </row>
@@ -16293,19 +16286,19 @@
       <c r="F175" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="G175" s="34" t="s">
+      <c r="G175" s="33" t="s">
         <v>1177</v>
       </c>
-      <c r="H175" s="34" t="s">
+      <c r="H175" s="33" t="s">
         <v>1178</v>
       </c>
-      <c r="I175" s="34" t="s">
+      <c r="I175" s="33" t="s">
         <v>1179</v>
       </c>
-      <c r="J175" s="34" t="s">
+      <c r="J175" s="33" t="s">
         <v>1180</v>
       </c>
-      <c r="K175" s="34" t="s">
+      <c r="K175" s="33" t="s">
         <v>1181</v>
       </c>
       <c r="L175" s="1">
@@ -16335,10 +16328,10 @@
       <c r="R175" s="6">
         <v>99.99</v>
       </c>
-      <c r="S175" s="24" t="s">
+      <c r="S175" s="23" t="s">
         <v>1182</v>
       </c>
-      <c r="T175" s="24" t="s">
+      <c r="T175" s="23" t="s">
         <v>1182</v>
       </c>
     </row>
@@ -16357,19 +16350,19 @@
       <c r="F176" s="1" t="s">
         <v>1185</v>
       </c>
-      <c r="G176" s="34" t="s">
+      <c r="G176" s="33" t="s">
         <v>1186</v>
       </c>
-      <c r="H176" s="34" t="s">
+      <c r="H176" s="33" t="s">
         <v>1187</v>
       </c>
-      <c r="I176" s="34" t="s">
+      <c r="I176" s="33" t="s">
         <v>1188</v>
       </c>
-      <c r="J176" s="34" t="s">
+      <c r="J176" s="33" t="s">
         <v>1189</v>
       </c>
-      <c r="K176" s="34" t="s">
+      <c r="K176" s="33" t="s">
         <v>1190</v>
       </c>
       <c r="L176" s="1">
@@ -16399,10 +16392,10 @@
       <c r="R176" s="6">
         <v>99.99</v>
       </c>
-      <c r="S176" s="24" t="s">
+      <c r="S176" s="23" t="s">
         <v>1191</v>
       </c>
-      <c r="T176" s="24" t="s">
+      <c r="T176" s="23" t="s">
         <v>1191</v>
       </c>
       <c r="U176" s="6"/>
@@ -16426,19 +16419,19 @@
       <c r="F177" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="G177" s="34" t="s">
+      <c r="G177" s="33" t="s">
         <v>1195</v>
       </c>
-      <c r="H177" s="34" t="s">
+      <c r="H177" s="33" t="s">
         <v>1196</v>
       </c>
-      <c r="I177" s="34" t="s">
+      <c r="I177" s="33" t="s">
         <v>1197</v>
       </c>
-      <c r="J177" s="34" t="s">
+      <c r="J177" s="33" t="s">
         <v>1198</v>
       </c>
-      <c r="K177" s="34" t="s">
+      <c r="K177" s="33" t="s">
         <v>1199</v>
       </c>
       <c r="L177" s="1">
@@ -16468,10 +16461,10 @@
       <c r="R177" s="6">
         <v>99.99</v>
       </c>
-      <c r="S177" s="24" t="s">
+      <c r="S177" s="23" t="s">
         <v>1200</v>
       </c>
-      <c r="T177" s="24" t="s">
+      <c r="T177" s="23" t="s">
         <v>1200</v>
       </c>
       <c r="U177" s="6"/>
@@ -16495,19 +16488,19 @@
       <c r="F178" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="G178" s="34" t="s">
+      <c r="G178" s="33" t="s">
         <v>1204</v>
       </c>
-      <c r="H178" s="34" t="s">
+      <c r="H178" s="33" t="s">
         <v>1205</v>
       </c>
-      <c r="I178" s="34" t="s">
+      <c r="I178" s="33" t="s">
         <v>1206</v>
       </c>
-      <c r="J178" s="34" t="s">
+      <c r="J178" s="33" t="s">
         <v>1207</v>
       </c>
-      <c r="K178" s="34" t="s">
+      <c r="K178" s="33" t="s">
         <v>1208</v>
       </c>
       <c r="L178" s="1">
@@ -16537,10 +16530,10 @@
       <c r="R178" s="6">
         <v>99.99</v>
       </c>
-      <c r="S178" s="24" t="s">
+      <c r="S178" s="23" t="s">
         <v>1209</v>
       </c>
-      <c r="T178" s="24" t="s">
+      <c r="T178" s="23" t="s">
         <v>1209</v>
       </c>
       <c r="U178" s="6"/>
@@ -16564,19 +16557,19 @@
       <c r="F179" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="G179" s="34" t="s">
+      <c r="G179" s="33" t="s">
         <v>1213</v>
       </c>
-      <c r="H179" s="34" t="s">
+      <c r="H179" s="33" t="s">
         <v>1214</v>
       </c>
-      <c r="I179" s="34" t="s">
+      <c r="I179" s="33" t="s">
         <v>1215</v>
       </c>
-      <c r="J179" s="34" t="s">
+      <c r="J179" s="33" t="s">
         <v>1216</v>
       </c>
-      <c r="K179" s="34" t="s">
+      <c r="K179" s="33" t="s">
         <v>1217</v>
       </c>
       <c r="L179" s="1">
@@ -16606,10 +16599,10 @@
       <c r="R179" s="6">
         <v>99.99</v>
       </c>
-      <c r="S179" s="24" t="s">
+      <c r="S179" s="23" t="s">
         <v>1218</v>
       </c>
-      <c r="T179" s="24" t="s">
+      <c r="T179" s="23" t="s">
         <v>1218</v>
       </c>
       <c r="U179" s="6"/>
@@ -16633,19 +16626,19 @@
       <c r="F180" s="1" t="s">
         <v>1221</v>
       </c>
-      <c r="G180" s="34" t="s">
+      <c r="G180" s="33" t="s">
         <v>1222</v>
       </c>
-      <c r="H180" s="34" t="s">
+      <c r="H180" s="33" t="s">
         <v>1223</v>
       </c>
-      <c r="I180" s="34" t="s">
+      <c r="I180" s="33" t="s">
         <v>1224</v>
       </c>
-      <c r="J180" s="34" t="s">
+      <c r="J180" s="33" t="s">
         <v>1225</v>
       </c>
-      <c r="K180" s="34" t="s">
+      <c r="K180" s="33" t="s">
         <v>1226</v>
       </c>
       <c r="L180" s="1">
@@ -16675,10 +16668,10 @@
       <c r="R180" s="6">
         <v>99.99</v>
       </c>
-      <c r="S180" s="24" t="s">
+      <c r="S180" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T180" s="24" t="s">
+      <c r="T180" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U180" s="6"/>
@@ -16702,19 +16695,19 @@
       <c r="F181" s="5" t="s">
         <v>1228</v>
       </c>
-      <c r="G181" s="35" t="s">
+      <c r="G181" s="34" t="s">
         <v>1229</v>
       </c>
-      <c r="H181" s="35" t="s">
+      <c r="H181" s="34" t="s">
         <v>1230</v>
       </c>
-      <c r="I181" s="35" t="s">
+      <c r="I181" s="34" t="s">
         <v>1231</v>
       </c>
-      <c r="J181" s="35" t="s">
+      <c r="J181" s="34" t="s">
         <v>1232</v>
       </c>
-      <c r="K181" s="35" t="s">
+      <c r="K181" s="34" t="s">
         <v>1233</v>
       </c>
       <c r="L181" s="5">
@@ -16743,10 +16736,10 @@
       <c r="R181" s="20">
         <v>99.99</v>
       </c>
-      <c r="S181" s="36" t="s">
+      <c r="S181" s="35" t="s">
         <v>1227</v>
       </c>
-      <c r="T181" s="36" t="s">
+      <c r="T181" s="35" t="s">
         <v>1227</v>
       </c>
       <c r="W181" s="20"/>
@@ -16768,19 +16761,19 @@
       <c r="F182" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="G182" s="34" t="s">
+      <c r="G182" s="33" t="s">
         <v>1235</v>
       </c>
-      <c r="H182" s="34" t="s">
+      <c r="H182" s="33" t="s">
         <v>1236</v>
       </c>
-      <c r="I182" s="34" t="s">
+      <c r="I182" s="33" t="s">
         <v>1237</v>
       </c>
-      <c r="J182" s="34" t="s">
+      <c r="J182" s="33" t="s">
         <v>1238</v>
       </c>
-      <c r="K182" s="34" t="s">
+      <c r="K182" s="33" t="s">
         <v>1239</v>
       </c>
       <c r="L182" s="1">
@@ -16810,10 +16803,10 @@
       <c r="R182" s="6">
         <v>99.99</v>
       </c>
-      <c r="S182" s="24" t="s">
+      <c r="S182" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T182" s="24" t="s">
+      <c r="T182" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="W182" s="6"/>
@@ -16835,19 +16828,19 @@
       <c r="F183" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="G183" s="34" t="s">
+      <c r="G183" s="33" t="s">
         <v>1241</v>
       </c>
-      <c r="H183" s="34" t="s">
+      <c r="H183" s="33" t="s">
         <v>1242</v>
       </c>
-      <c r="I183" s="34" t="s">
+      <c r="I183" s="33" t="s">
         <v>1243</v>
       </c>
-      <c r="J183" s="34" t="s">
+      <c r="J183" s="33" t="s">
         <v>1244</v>
       </c>
-      <c r="K183" s="34" t="s">
+      <c r="K183" s="33" t="s">
         <v>1245</v>
       </c>
       <c r="L183" s="1">
@@ -16877,10 +16870,10 @@
       <c r="R183" s="6">
         <v>99.99</v>
       </c>
-      <c r="S183" s="24" t="s">
+      <c r="S183" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T183" s="24" t="s">
+      <c r="T183" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="W183" s="6"/>
@@ -16902,19 +16895,19 @@
       <c r="F184" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="G184" s="34" t="s">
+      <c r="G184" s="33" t="s">
         <v>1247</v>
       </c>
-      <c r="H184" s="34" t="s">
+      <c r="H184" s="33" t="s">
         <v>1248</v>
       </c>
-      <c r="I184" s="34" t="s">
+      <c r="I184" s="33" t="s">
         <v>1249</v>
       </c>
-      <c r="J184" s="34" t="s">
+      <c r="J184" s="33" t="s">
         <v>1250</v>
       </c>
-      <c r="K184" s="34" t="s">
+      <c r="K184" s="33" t="s">
         <v>1251</v>
       </c>
       <c r="L184" s="1">
@@ -16944,10 +16937,10 @@
       <c r="R184" s="6">
         <v>99.99</v>
       </c>
-      <c r="S184" s="24" t="s">
+      <c r="S184" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T184" s="24" t="s">
+      <c r="T184" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="W184" s="6"/>
@@ -16969,19 +16962,19 @@
       <c r="F185" s="1" t="s">
         <v>1252</v>
       </c>
-      <c r="G185" s="34" t="s">
+      <c r="G185" s="33" t="s">
         <v>1253</v>
       </c>
-      <c r="H185" s="34" t="s">
+      <c r="H185" s="33" t="s">
         <v>1254</v>
       </c>
-      <c r="I185" s="34" t="s">
+      <c r="I185" s="33" t="s">
         <v>1255</v>
       </c>
-      <c r="J185" s="34" t="s">
+      <c r="J185" s="33" t="s">
         <v>1256</v>
       </c>
-      <c r="K185" s="34" t="s">
+      <c r="K185" s="33" t="s">
         <v>1257</v>
       </c>
       <c r="L185" s="1">
@@ -17011,10 +17004,10 @@
       <c r="R185" s="6">
         <v>99.99</v>
       </c>
-      <c r="S185" s="24" t="s">
+      <c r="S185" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T185" s="24" t="s">
+      <c r="T185" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="W185" s="6"/>
@@ -17036,19 +17029,19 @@
       <c r="F186" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="G186" s="34" t="s">
+      <c r="G186" s="33" t="s">
         <v>1259</v>
       </c>
-      <c r="H186" s="34" t="s">
+      <c r="H186" s="33" t="s">
         <v>1260</v>
       </c>
-      <c r="I186" s="34" t="s">
+      <c r="I186" s="33" t="s">
         <v>1261</v>
       </c>
-      <c r="J186" s="34" t="s">
+      <c r="J186" s="33" t="s">
         <v>1262</v>
       </c>
-      <c r="K186" s="34" t="s">
+      <c r="K186" s="33" t="s">
         <v>1263</v>
       </c>
       <c r="L186" s="1">
@@ -17078,10 +17071,10 @@
       <c r="R186" s="6">
         <v>99.99</v>
       </c>
-      <c r="S186" s="24" t="s">
+      <c r="S186" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T186" s="24" t="s">
+      <c r="T186" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U186" s="6"/>
@@ -17105,19 +17098,19 @@
       <c r="F187" s="1" t="s">
         <v>1264</v>
       </c>
-      <c r="G187" s="34" t="s">
+      <c r="G187" s="33" t="s">
         <v>1265</v>
       </c>
-      <c r="H187" s="34" t="s">
+      <c r="H187" s="33" t="s">
         <v>1266</v>
       </c>
-      <c r="I187" s="34" t="s">
+      <c r="I187" s="33" t="s">
         <v>1267</v>
       </c>
-      <c r="J187" s="34" t="s">
+      <c r="J187" s="33" t="s">
         <v>1268</v>
       </c>
-      <c r="K187" s="34" t="s">
+      <c r="K187" s="33" t="s">
         <v>1269</v>
       </c>
       <c r="L187" s="1">
@@ -17147,10 +17140,10 @@
       <c r="R187" s="6">
         <v>99.99</v>
       </c>
-      <c r="S187" s="24" t="s">
+      <c r="S187" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T187" s="24" t="s">
+      <c r="T187" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U187" s="6"/>
@@ -17174,19 +17167,19 @@
       <c r="F188" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="G188" s="34" t="s">
+      <c r="G188" s="33" t="s">
         <v>1271</v>
       </c>
-      <c r="H188" s="34" t="s">
+      <c r="H188" s="33" t="s">
         <v>1272</v>
       </c>
-      <c r="I188" s="34" t="s">
+      <c r="I188" s="33" t="s">
         <v>1273</v>
       </c>
-      <c r="J188" s="34" t="s">
+      <c r="J188" s="33" t="s">
         <v>1274</v>
       </c>
-      <c r="K188" s="34" t="s">
+      <c r="K188" s="33" t="s">
         <v>1275</v>
       </c>
       <c r="L188" s="1">
@@ -17216,10 +17209,10 @@
       <c r="R188" s="6">
         <v>99.99</v>
       </c>
-      <c r="S188" s="24" t="s">
+      <c r="S188" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T188" s="24" t="s">
+      <c r="T188" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U188" s="6"/>
@@ -17243,19 +17236,19 @@
       <c r="F189" s="1" t="s">
         <v>1276</v>
       </c>
-      <c r="G189" s="34" t="s">
+      <c r="G189" s="33" t="s">
         <v>1097</v>
       </c>
-      <c r="H189" s="34" t="s">
+      <c r="H189" s="33" t="s">
         <v>1277</v>
       </c>
-      <c r="I189" s="34" t="s">
+      <c r="I189" s="33" t="s">
         <v>1278</v>
       </c>
-      <c r="J189" s="34" t="s">
+      <c r="J189" s="33" t="s">
         <v>1279</v>
       </c>
-      <c r="K189" s="34" t="s">
+      <c r="K189" s="33" t="s">
         <v>1280</v>
       </c>
       <c r="L189" s="1">
@@ -17285,10 +17278,10 @@
       <c r="R189" s="6">
         <v>99.99</v>
       </c>
-      <c r="S189" s="24" t="s">
+      <c r="S189" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T189" s="24" t="s">
+      <c r="T189" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U189" s="6"/>
@@ -17312,19 +17305,19 @@
       <c r="F190" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="G190" s="34" t="s">
+      <c r="G190" s="33" t="s">
         <v>1106</v>
       </c>
-      <c r="H190" s="34" t="s">
+      <c r="H190" s="33" t="s">
         <v>1282</v>
       </c>
-      <c r="I190" s="34" t="s">
+      <c r="I190" s="33" t="s">
         <v>1283</v>
       </c>
-      <c r="J190" s="34" t="s">
+      <c r="J190" s="33" t="s">
         <v>1284</v>
       </c>
-      <c r="K190" s="34" t="s">
+      <c r="K190" s="33" t="s">
         <v>1285</v>
       </c>
       <c r="L190" s="1">
@@ -17354,10 +17347,10 @@
       <c r="R190" s="6">
         <v>99.99</v>
       </c>
-      <c r="S190" s="24" t="s">
+      <c r="S190" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T190" s="24" t="s">
+      <c r="T190" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U190" s="6"/>
@@ -17381,19 +17374,19 @@
       <c r="F191" s="1" t="s">
         <v>1286</v>
       </c>
-      <c r="G191" s="34" t="s">
+      <c r="G191" s="33" t="s">
         <v>1115</v>
       </c>
-      <c r="H191" s="34" t="s">
+      <c r="H191" s="33" t="s">
         <v>1287</v>
       </c>
-      <c r="I191" s="34" t="s">
+      <c r="I191" s="33" t="s">
         <v>1288</v>
       </c>
-      <c r="J191" s="34" t="s">
+      <c r="J191" s="33" t="s">
         <v>1289</v>
       </c>
-      <c r="K191" s="34" t="s">
+      <c r="K191" s="33" t="s">
         <v>1290</v>
       </c>
       <c r="L191" s="1">
@@ -17423,10 +17416,10 @@
       <c r="R191" s="6">
         <v>99.99</v>
       </c>
-      <c r="S191" s="24" t="s">
+      <c r="S191" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T191" s="24" t="s">
+      <c r="T191" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U191" s="6"/>
@@ -17450,19 +17443,19 @@
       <c r="F192" s="1" t="s">
         <v>1291</v>
       </c>
-      <c r="G192" s="34" t="s">
+      <c r="G192" s="33" t="s">
         <v>1124</v>
       </c>
-      <c r="H192" s="34" t="s">
+      <c r="H192" s="33" t="s">
         <v>1292</v>
       </c>
-      <c r="I192" s="34" t="s">
+      <c r="I192" s="33" t="s">
         <v>1293</v>
       </c>
-      <c r="J192" s="34" t="s">
+      <c r="J192" s="33" t="s">
         <v>1294</v>
       </c>
-      <c r="K192" s="34" t="s">
+      <c r="K192" s="33" t="s">
         <v>1295</v>
       </c>
       <c r="L192" s="1">
@@ -17492,10 +17485,10 @@
       <c r="R192" s="6">
         <v>99.99</v>
       </c>
-      <c r="S192" s="24" t="s">
+      <c r="S192" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T192" s="24" t="s">
+      <c r="T192" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U192" s="6"/>
@@ -17519,19 +17512,19 @@
       <c r="F193" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="G193" s="34" t="s">
+      <c r="G193" s="33" t="s">
         <v>1133</v>
       </c>
-      <c r="H193" s="34" t="s">
+      <c r="H193" s="33" t="s">
         <v>1297</v>
       </c>
-      <c r="I193" s="34" t="s">
+      <c r="I193" s="33" t="s">
         <v>1298</v>
       </c>
-      <c r="J193" s="34" t="s">
+      <c r="J193" s="33" t="s">
         <v>1299</v>
       </c>
-      <c r="K193" s="34" t="s">
+      <c r="K193" s="33" t="s">
         <v>1300</v>
       </c>
       <c r="L193" s="1">
@@ -17561,10 +17554,10 @@
       <c r="R193" s="6">
         <v>99.99</v>
       </c>
-      <c r="S193" s="24" t="s">
+      <c r="S193" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T193" s="24" t="s">
+      <c r="T193" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U193" s="6"/>
@@ -17588,19 +17581,19 @@
       <c r="F194" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="G194" s="34" t="s">
+      <c r="G194" s="33" t="s">
         <v>1142</v>
       </c>
-      <c r="H194" s="34" t="s">
+      <c r="H194" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I194" s="34" t="s">
+      <c r="I194" s="33" t="s">
         <v>1303</v>
       </c>
-      <c r="J194" s="34" t="s">
+      <c r="J194" s="33" t="s">
         <v>1304</v>
       </c>
-      <c r="K194" s="34" t="s">
+      <c r="K194" s="33" t="s">
         <v>1305</v>
       </c>
       <c r="L194" s="1">
@@ -17630,10 +17623,10 @@
       <c r="R194" s="6">
         <v>99.99</v>
       </c>
-      <c r="S194" s="24" t="s">
+      <c r="S194" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T194" s="24" t="s">
+      <c r="T194" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U194" s="6"/>
@@ -17657,19 +17650,19 @@
       <c r="F195" s="1" t="s">
         <v>1306</v>
       </c>
-      <c r="G195" s="34" t="s">
+      <c r="G195" s="33" t="s">
         <v>1151</v>
       </c>
-      <c r="H195" s="34" t="s">
+      <c r="H195" s="33" t="s">
         <v>1307</v>
       </c>
-      <c r="I195" s="34" t="s">
+      <c r="I195" s="33" t="s">
         <v>1308</v>
       </c>
-      <c r="J195" s="34" t="s">
+      <c r="J195" s="33" t="s">
         <v>1136</v>
       </c>
-      <c r="K195" s="34" t="s">
+      <c r="K195" s="33" t="s">
         <v>1309</v>
       </c>
       <c r="L195" s="1">
@@ -17699,10 +17692,10 @@
       <c r="R195" s="6">
         <v>99.99</v>
       </c>
-      <c r="S195" s="24" t="s">
+      <c r="S195" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T195" s="24" t="s">
+      <c r="T195" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U195" s="6"/>
@@ -17726,19 +17719,19 @@
       <c r="F196" s="1" t="s">
         <v>1310</v>
       </c>
-      <c r="G196" s="34" t="s">
+      <c r="G196" s="33" t="s">
         <v>1160</v>
       </c>
-      <c r="H196" s="34" t="s">
+      <c r="H196" s="33" t="s">
         <v>1311</v>
       </c>
-      <c r="I196" s="34" t="s">
+      <c r="I196" s="33" t="s">
         <v>1312</v>
       </c>
-      <c r="J196" s="34" t="s">
+      <c r="J196" s="33" t="s">
         <v>1313</v>
       </c>
-      <c r="K196" s="34" t="s">
+      <c r="K196" s="33" t="s">
         <v>1314</v>
       </c>
       <c r="L196" s="1">
@@ -17768,10 +17761,10 @@
       <c r="R196" s="6">
         <v>99.99</v>
       </c>
-      <c r="S196" s="24" t="s">
+      <c r="S196" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T196" s="24" t="s">
+      <c r="T196" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U196" s="6"/>
@@ -17795,19 +17788,19 @@
       <c r="F197" s="1" t="s">
         <v>1315</v>
       </c>
-      <c r="G197" s="34" t="s">
+      <c r="G197" s="33" t="s">
         <v>1169</v>
       </c>
-      <c r="H197" s="34" t="s">
+      <c r="H197" s="33" t="s">
         <v>1316</v>
       </c>
-      <c r="I197" s="34" t="s">
+      <c r="I197" s="33" t="s">
         <v>1317</v>
       </c>
-      <c r="J197" s="34" t="s">
+      <c r="J197" s="33" t="s">
         <v>1318</v>
       </c>
-      <c r="K197" s="34" t="s">
+      <c r="K197" s="33" t="s">
         <v>1319</v>
       </c>
       <c r="L197" s="1">
@@ -17837,10 +17830,10 @@
       <c r="R197" s="6">
         <v>99.99</v>
       </c>
-      <c r="S197" s="24" t="s">
+      <c r="S197" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T197" s="24" t="s">
+      <c r="T197" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U197" s="6"/>
@@ -17864,19 +17857,19 @@
       <c r="F198" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="G198" s="34" t="s">
+      <c r="G198" s="33" t="s">
         <v>1178</v>
       </c>
-      <c r="H198" s="34" t="s">
+      <c r="H198" s="33" t="s">
         <v>1321</v>
       </c>
-      <c r="I198" s="34" t="s">
+      <c r="I198" s="33" t="s">
         <v>1322</v>
       </c>
-      <c r="J198" s="34" t="s">
+      <c r="J198" s="33" t="s">
         <v>1323</v>
       </c>
-      <c r="K198" s="34" t="s">
+      <c r="K198" s="33" t="s">
         <v>1324</v>
       </c>
       <c r="L198" s="1">
@@ -17906,10 +17899,10 @@
       <c r="R198" s="6">
         <v>99.99</v>
       </c>
-      <c r="S198" s="24" t="s">
+      <c r="S198" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T198" s="24" t="s">
+      <c r="T198" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U198" s="6"/>
@@ -17933,19 +17926,19 @@
       <c r="F199" s="3" t="s">
         <v>1325</v>
       </c>
-      <c r="G199" s="34" t="s">
+      <c r="G199" s="33" t="s">
         <v>1187</v>
       </c>
-      <c r="H199" s="34" t="s">
+      <c r="H199" s="33" t="s">
         <v>1326</v>
       </c>
-      <c r="I199" s="34" t="s">
+      <c r="I199" s="33" t="s">
         <v>1327</v>
       </c>
-      <c r="J199" s="34" t="s">
+      <c r="J199" s="33" t="s">
         <v>1328</v>
       </c>
-      <c r="K199" s="34" t="s">
+      <c r="K199" s="33" t="s">
         <v>1329</v>
       </c>
       <c r="L199" s="3">
@@ -17975,10 +17968,10 @@
       <c r="R199" s="16">
         <v>99.99</v>
       </c>
-      <c r="S199" s="24" t="s">
+      <c r="S199" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T199" s="24" t="s">
+      <c r="T199" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U199" s="16"/>
@@ -18002,19 +17995,19 @@
       <c r="F200" s="4" t="s">
         <v>1330</v>
       </c>
-      <c r="G200" s="34" t="s">
+      <c r="G200" s="33" t="s">
         <v>1196</v>
       </c>
-      <c r="H200" s="34" t="s">
+      <c r="H200" s="33" t="s">
         <v>1331</v>
       </c>
-      <c r="I200" s="34" t="s">
+      <c r="I200" s="33" t="s">
         <v>1332</v>
       </c>
-      <c r="J200" s="34" t="s">
+      <c r="J200" s="33" t="s">
         <v>1333</v>
       </c>
-      <c r="K200" s="34" t="s">
+      <c r="K200" s="33" t="s">
         <v>1334</v>
       </c>
       <c r="L200" s="4">
@@ -18044,10 +18037,10 @@
       <c r="R200" s="17">
         <v>99.99</v>
       </c>
-      <c r="S200" s="24" t="s">
+      <c r="S200" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T200" s="24" t="s">
+      <c r="T200" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U200" s="17"/>
@@ -18069,19 +18062,19 @@
       <c r="F201" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="G201" s="34" t="s">
+      <c r="G201" s="33" t="s">
         <v>1205</v>
       </c>
-      <c r="H201" s="34" t="s">
+      <c r="H201" s="33" t="s">
         <v>1336</v>
       </c>
-      <c r="I201" s="34" t="s">
+      <c r="I201" s="33" t="s">
         <v>1337</v>
       </c>
-      <c r="J201" s="34" t="s">
+      <c r="J201" s="33" t="s">
         <v>1338</v>
       </c>
-      <c r="K201" s="34" t="s">
+      <c r="K201" s="33" t="s">
         <v>1339</v>
       </c>
       <c r="L201" s="1">
@@ -18111,10 +18104,10 @@
       <c r="R201" s="6">
         <v>99.99</v>
       </c>
-      <c r="S201" s="24" t="s">
+      <c r="S201" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T201" s="24" t="s">
+      <c r="T201" s="23" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -18131,19 +18124,19 @@
       <c r="F202" s="1" t="s">
         <v>1340</v>
       </c>
-      <c r="G202" s="34" t="s">
+      <c r="G202" s="33" t="s">
         <v>1214</v>
       </c>
-      <c r="H202" s="34" t="s">
+      <c r="H202" s="33" t="s">
         <v>1341</v>
       </c>
-      <c r="I202" s="34" t="s">
+      <c r="I202" s="33" t="s">
         <v>1342</v>
       </c>
-      <c r="J202" s="34" t="s">
+      <c r="J202" s="33" t="s">
         <v>1343</v>
       </c>
-      <c r="K202" s="34" t="s">
+      <c r="K202" s="33" t="s">
         <v>1344</v>
       </c>
       <c r="L202" s="1">
@@ -18173,10 +18166,10 @@
       <c r="R202" s="6">
         <v>99.99</v>
       </c>
-      <c r="S202" s="24" t="s">
+      <c r="S202" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T202" s="24" t="s">
+      <c r="T202" s="23" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -18193,19 +18186,19 @@
       <c r="F203" s="1" t="s">
         <v>1345</v>
       </c>
-      <c r="G203" s="34" t="s">
+      <c r="G203" s="33" t="s">
         <v>1223</v>
       </c>
-      <c r="H203" s="34" t="s">
+      <c r="H203" s="33" t="s">
         <v>1346</v>
       </c>
-      <c r="I203" s="34" t="s">
+      <c r="I203" s="33" t="s">
         <v>1347</v>
       </c>
-      <c r="J203" s="34" t="s">
+      <c r="J203" s="33" t="s">
         <v>1348</v>
       </c>
-      <c r="K203" s="34" t="s">
+      <c r="K203" s="33" t="s">
         <v>1349</v>
       </c>
       <c r="L203" s="1">
@@ -18235,10 +18228,10 @@
       <c r="R203" s="6">
         <v>99.99</v>
       </c>
-      <c r="S203" s="24" t="s">
+      <c r="S203" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T203" s="24" t="s">
+      <c r="T203" s="23" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -18255,19 +18248,19 @@
       <c r="F204" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="G204" s="34" t="s">
+      <c r="G204" s="33" t="s">
         <v>1230</v>
       </c>
-      <c r="H204" s="34" t="s">
+      <c r="H204" s="33" t="s">
         <v>1351</v>
       </c>
-      <c r="I204" s="34" t="s">
+      <c r="I204" s="33" t="s">
         <v>1352</v>
       </c>
-      <c r="J204" s="34" t="s">
+      <c r="J204" s="33" t="s">
         <v>1353</v>
       </c>
-      <c r="K204" s="34" t="s">
+      <c r="K204" s="33" t="s">
         <v>1354</v>
       </c>
       <c r="L204" s="1">
@@ -18297,10 +18290,10 @@
       <c r="R204" s="6">
         <v>99.99</v>
       </c>
-      <c r="S204" s="24" t="s">
+      <c r="S204" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T204" s="24" t="s">
+      <c r="T204" s="23" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -18317,19 +18310,19 @@
       <c r="F205" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="G205" s="34" t="s">
+      <c r="G205" s="33" t="s">
         <v>1236</v>
       </c>
-      <c r="H205" s="34" t="s">
+      <c r="H205" s="33" t="s">
         <v>1356</v>
       </c>
-      <c r="I205" s="34" t="s">
+      <c r="I205" s="33" t="s">
         <v>1357</v>
       </c>
-      <c r="J205" s="34" t="s">
+      <c r="J205" s="33" t="s">
         <v>1358</v>
       </c>
-      <c r="K205" s="34" t="s">
+      <c r="K205" s="33" t="s">
         <v>1359</v>
       </c>
       <c r="L205" s="1">
@@ -18359,10 +18352,10 @@
       <c r="R205" s="6">
         <v>99.99</v>
       </c>
-      <c r="S205" s="24" t="s">
+      <c r="S205" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T205" s="24" t="s">
+      <c r="T205" s="23" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -18379,19 +18372,19 @@
       <c r="F206" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="G206" s="34" t="s">
+      <c r="G206" s="33" t="s">
         <v>1242</v>
       </c>
-      <c r="H206" s="34" t="s">
+      <c r="H206" s="33" t="s">
         <v>1361</v>
       </c>
-      <c r="I206" s="34" t="s">
+      <c r="I206" s="33" t="s">
         <v>1362</v>
       </c>
-      <c r="J206" s="34" t="s">
+      <c r="J206" s="33" t="s">
         <v>1363</v>
       </c>
-      <c r="K206" s="34" t="s">
+      <c r="K206" s="33" t="s">
         <v>1364</v>
       </c>
       <c r="L206" s="1">
@@ -18421,10 +18414,10 @@
       <c r="R206" s="6">
         <v>99.99</v>
       </c>
-      <c r="S206" s="24" t="s">
+      <c r="S206" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T206" s="24" t="s">
+      <c r="T206" s="23" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -18441,19 +18434,19 @@
       <c r="F207" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="G207" s="34" t="s">
+      <c r="G207" s="33" t="s">
         <v>1248</v>
       </c>
-      <c r="H207" s="34" t="s">
+      <c r="H207" s="33" t="s">
         <v>1366</v>
       </c>
-      <c r="I207" s="34" t="s">
+      <c r="I207" s="33" t="s">
         <v>1367</v>
       </c>
-      <c r="J207" s="34" t="s">
+      <c r="J207" s="33" t="s">
         <v>1368</v>
       </c>
-      <c r="K207" s="34" t="s">
+      <c r="K207" s="33" t="s">
         <v>1369</v>
       </c>
       <c r="L207" s="1">
@@ -18483,10 +18476,10 @@
       <c r="R207" s="6">
         <v>99.99</v>
       </c>
-      <c r="S207" s="24" t="s">
+      <c r="S207" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T207" s="24" t="s">
+      <c r="T207" s="23" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -18503,19 +18496,19 @@
       <c r="F208" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="G208" s="34" t="s">
+      <c r="G208" s="33" t="s">
         <v>1254</v>
       </c>
-      <c r="H208" s="34" t="s">
+      <c r="H208" s="33" t="s">
         <v>1371</v>
       </c>
-      <c r="I208" s="34" t="s">
+      <c r="I208" s="33" t="s">
         <v>1372</v>
       </c>
-      <c r="J208" s="34" t="s">
+      <c r="J208" s="33" t="s">
         <v>1226</v>
       </c>
-      <c r="K208" s="34" t="s">
+      <c r="K208" s="33" t="s">
         <v>1373</v>
       </c>
       <c r="L208" s="1">
@@ -18545,10 +18538,10 @@
       <c r="R208" s="6">
         <v>99.99</v>
       </c>
-      <c r="S208" s="24" t="s">
+      <c r="S208" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T208" s="24" t="s">
+      <c r="T208" s="23" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -18565,19 +18558,19 @@
       <c r="F209" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="G209" s="34" t="s">
+      <c r="G209" s="33" t="s">
         <v>1260</v>
       </c>
-      <c r="H209" s="34" t="s">
+      <c r="H209" s="33" t="s">
         <v>1375</v>
       </c>
-      <c r="I209" s="34" t="s">
+      <c r="I209" s="33" t="s">
         <v>1376</v>
       </c>
-      <c r="J209" s="34" t="s">
+      <c r="J209" s="33" t="s">
         <v>1233</v>
       </c>
-      <c r="K209" s="34" t="s">
+      <c r="K209" s="33" t="s">
         <v>1377</v>
       </c>
       <c r="L209" s="1">
@@ -18607,10 +18600,10 @@
       <c r="R209" s="6">
         <v>99.99</v>
       </c>
-      <c r="S209" s="24" t="s">
+      <c r="S209" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T209" s="24" t="s">
+      <c r="T209" s="23" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -18627,19 +18620,19 @@
       <c r="F210" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="G210" s="34" t="s">
+      <c r="G210" s="33" t="s">
         <v>1266</v>
       </c>
-      <c r="H210" s="34" t="s">
+      <c r="H210" s="33" t="s">
         <v>1379</v>
       </c>
-      <c r="I210" s="34" t="s">
+      <c r="I210" s="33" t="s">
         <v>1380</v>
       </c>
-      <c r="J210" s="34" t="s">
+      <c r="J210" s="33" t="s">
         <v>1239</v>
       </c>
-      <c r="K210" s="34" t="s">
+      <c r="K210" s="33" t="s">
         <v>1381</v>
       </c>
       <c r="L210" s="1">
@@ -18669,10 +18662,10 @@
       <c r="R210" s="6">
         <v>99.99</v>
       </c>
-      <c r="S210" s="24" t="s">
+      <c r="S210" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T210" s="24" t="s">
+      <c r="T210" s="23" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -18691,19 +18684,19 @@
       <c r="F211" s="1" t="s">
         <v>1382</v>
       </c>
-      <c r="G211" s="34" t="s">
+      <c r="G211" s="33" t="s">
         <v>1272</v>
       </c>
-      <c r="H211" s="34" t="s">
+      <c r="H211" s="33" t="s">
         <v>1383</v>
       </c>
-      <c r="I211" s="34" t="s">
+      <c r="I211" s="33" t="s">
         <v>1384</v>
       </c>
-      <c r="J211" s="34" t="s">
+      <c r="J211" s="33" t="s">
         <v>1245</v>
       </c>
-      <c r="K211" s="34" t="s">
+      <c r="K211" s="33" t="s">
         <v>1385</v>
       </c>
       <c r="L211" s="1">
@@ -18733,10 +18726,10 @@
       <c r="R211" s="6">
         <v>99.99</v>
       </c>
-      <c r="S211" s="24" t="s">
+      <c r="S211" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T211" s="24" t="s">
+      <c r="T211" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U211" s="6"/>
@@ -18760,19 +18753,19 @@
       <c r="F212" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="G212" s="34" t="s">
+      <c r="G212" s="33" t="s">
         <v>1277</v>
       </c>
-      <c r="H212" s="34" t="s">
+      <c r="H212" s="33" t="s">
         <v>1387</v>
       </c>
-      <c r="I212" s="34" t="s">
+      <c r="I212" s="33" t="s">
         <v>1388</v>
       </c>
-      <c r="J212" s="34" t="s">
+      <c r="J212" s="33" t="s">
         <v>1251</v>
       </c>
-      <c r="K212" s="34" t="s">
+      <c r="K212" s="33" t="s">
         <v>1389</v>
       </c>
       <c r="L212" s="1">
@@ -18802,10 +18795,10 @@
       <c r="R212" s="6">
         <v>99.99</v>
       </c>
-      <c r="S212" s="24" t="s">
+      <c r="S212" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T212" s="24" t="s">
+      <c r="T212" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U212" s="6"/>
@@ -18829,19 +18822,19 @@
       <c r="F213" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="G213" s="34" t="s">
+      <c r="G213" s="33" t="s">
         <v>1282</v>
       </c>
-      <c r="H213" s="34" t="s">
+      <c r="H213" s="33" t="s">
         <v>1391</v>
       </c>
-      <c r="I213" s="34" t="s">
+      <c r="I213" s="33" t="s">
         <v>1392</v>
       </c>
-      <c r="J213" s="34" t="s">
+      <c r="J213" s="33" t="s">
         <v>1257</v>
       </c>
-      <c r="K213" s="34" t="s">
+      <c r="K213" s="33" t="s">
         <v>1393</v>
       </c>
       <c r="L213" s="1">
@@ -18871,10 +18864,10 @@
       <c r="R213" s="6">
         <v>99.99</v>
       </c>
-      <c r="S213" s="24" t="s">
+      <c r="S213" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T213" s="24" t="s">
+      <c r="T213" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U213" s="6"/>
@@ -18898,19 +18891,19 @@
       <c r="F214" s="1" t="s">
         <v>1394</v>
       </c>
-      <c r="G214" s="34" t="s">
+      <c r="G214" s="33" t="s">
         <v>1287</v>
       </c>
-      <c r="H214" s="34" t="s">
+      <c r="H214" s="33" t="s">
         <v>1395</v>
       </c>
-      <c r="I214" s="34" t="s">
+      <c r="I214" s="33" t="s">
         <v>1396</v>
       </c>
-      <c r="J214" s="34" t="s">
+      <c r="J214" s="33" t="s">
         <v>1263</v>
       </c>
-      <c r="K214" s="34" t="s">
+      <c r="K214" s="33" t="s">
         <v>1397</v>
       </c>
       <c r="L214" s="1">
@@ -18940,10 +18933,10 @@
       <c r="R214" s="6">
         <v>99.99</v>
       </c>
-      <c r="S214" s="24" t="s">
+      <c r="S214" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T214" s="24" t="s">
+      <c r="T214" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U214" s="6"/>
@@ -18967,19 +18960,19 @@
       <c r="F215" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="G215" s="34" t="s">
+      <c r="G215" s="33" t="s">
         <v>1292</v>
       </c>
-      <c r="H215" s="34" t="s">
+      <c r="H215" s="33" t="s">
         <v>1399</v>
       </c>
-      <c r="I215" s="34" t="s">
+      <c r="I215" s="33" t="s">
         <v>1400</v>
       </c>
-      <c r="J215" s="34" t="s">
+      <c r="J215" s="33" t="s">
         <v>1269</v>
       </c>
-      <c r="K215" s="34" t="s">
+      <c r="K215" s="33" t="s">
         <v>1401</v>
       </c>
       <c r="L215" s="1">
@@ -19009,10 +19002,10 @@
       <c r="R215" s="6">
         <v>99.99</v>
       </c>
-      <c r="S215" s="24" t="s">
+      <c r="S215" s="23" t="s">
         <v>1227</v>
       </c>
-      <c r="T215" s="24" t="s">
+      <c r="T215" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="U215" s="6"/>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="1417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="1418">
   <si>
     <t>ID</t>
   </si>
@@ -3719,100 +3719,103 @@
     <t>混沌鸡</t>
   </si>
   <si>
+    <t>1E+87</t>
+  </si>
+  <si>
+    <t>1E+112</t>
+  </si>
+  <si>
+    <t>1E+142</t>
+  </si>
+  <si>
+    <t>1E+46</t>
+  </si>
+  <si>
+    <t>1E+74</t>
+  </si>
+  <si>
+    <t>140000000000</t>
+  </si>
+  <si>
+    <t>混沌鹿</t>
+  </si>
+  <si>
+    <t>1E+91</t>
+  </si>
+  <si>
+    <t>1E+116</t>
+  </si>
+  <si>
+    <t>1E+146</t>
+  </si>
+  <si>
+    <t>1E+50</t>
+  </si>
+  <si>
+    <t>1E+78</t>
+  </si>
+  <si>
+    <t>145000000000</t>
+  </si>
+  <si>
+    <t>混沌草人</t>
+  </si>
+  <si>
+    <t>1E+95</t>
+  </si>
+  <si>
+    <t>1E+120</t>
+  </si>
+  <si>
+    <t>1E+150</t>
+  </si>
+  <si>
+    <t>1E+54</t>
+  </si>
+  <si>
+    <t>1E+82</t>
+  </si>
+  <si>
+    <t>150000000000</t>
+  </si>
+  <si>
+    <t>混沌猫</t>
+  </si>
+  <si>
+    <t>1E+99</t>
+  </si>
+  <si>
+    <t>1E+124</t>
+  </si>
+  <si>
+    <t>1E+154</t>
+  </si>
+  <si>
+    <t>1E+58</t>
+  </si>
+  <si>
     <t>1E+86</t>
   </si>
   <si>
-    <t>1E+109</t>
-  </si>
-  <si>
-    <t>1E+141</t>
-  </si>
-  <si>
-    <t>1E+45</t>
-  </si>
-  <si>
-    <t>1E+74</t>
-  </si>
-  <si>
-    <t>140000000000</t>
-  </si>
-  <si>
-    <t>混沌鹿</t>
-  </si>
-  <si>
-    <t>1E+89</t>
-  </si>
-  <si>
-    <t>1E+112</t>
-  </si>
-  <si>
-    <t>1E+144</t>
-  </si>
-  <si>
-    <t>1E+48</t>
-  </si>
-  <si>
-    <t>1E+77</t>
-  </si>
-  <si>
-    <t>145000000000</t>
-  </si>
-  <si>
-    <t>混沌草人</t>
-  </si>
-  <si>
-    <t>1E+92</t>
-  </si>
-  <si>
-    <t>1E+115</t>
-  </si>
-  <si>
-    <t>1E+147</t>
-  </si>
-  <si>
-    <t>1E+51</t>
-  </si>
-  <si>
-    <t>1E+80</t>
-  </si>
-  <si>
-    <t>150000000000</t>
-  </si>
-  <si>
-    <t>混沌猫</t>
-  </si>
-  <si>
-    <t>1E+95</t>
-  </si>
-  <si>
-    <t>1E+118</t>
-  </si>
-  <si>
-    <t>1E+150</t>
-  </si>
-  <si>
-    <t>1E+54</t>
-  </si>
-  <si>
-    <t>1E+83</t>
-  </si>
-  <si>
     <t>155000000000</t>
   </si>
   <si>
     <t>混沌花</t>
   </si>
   <si>
-    <t>1E+98</t>
-  </si>
-  <si>
-    <t>1E+121</t>
-  </si>
-  <si>
-    <t>1E+153</t>
-  </si>
-  <si>
-    <t>1E+57</t>
+    <t>1E+103</t>
+  </si>
+  <si>
+    <t>1E+128</t>
+  </si>
+  <si>
+    <t>1E+157</t>
+  </si>
+  <si>
+    <t>1E+62</t>
+  </si>
+  <si>
+    <t>1E+90</t>
   </si>
   <si>
     <t>160000000000</t>
@@ -4928,7 +4931,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4960,14 +4963,11 @@
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -4984,9 +4984,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -5592,13 +5589,13 @@
       <c r="F6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="27" t="s">
+      <c r="I6" s="26" t="s">
         <v>36</v>
       </c>
       <c r="J6" s="1">
@@ -9300,7 +9297,7 @@
       <c r="H65" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="I65" s="27" t="s">
+      <c r="I65" s="26" t="s">
         <v>439</v>
       </c>
       <c r="J65" s="1">
@@ -9369,7 +9366,7 @@
       <c r="H66" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="I66" s="27" t="s">
+      <c r="I66" s="26" t="s">
         <v>446</v>
       </c>
       <c r="J66" s="1">
@@ -9438,7 +9435,7 @@
       <c r="H67" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="I67" s="27" t="s">
+      <c r="I67" s="26" t="s">
         <v>453</v>
       </c>
       <c r="J67" s="1">
@@ -9507,7 +9504,7 @@
       <c r="H68" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="I68" s="27" t="s">
+      <c r="I68" s="26" t="s">
         <v>460</v>
       </c>
       <c r="J68" s="1">
@@ -9573,10 +9570,10 @@
       <c r="G69" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="H69" s="27" t="s">
+      <c r="H69" s="26" t="s">
         <v>466</v>
       </c>
-      <c r="I69" s="27" t="s">
+      <c r="I69" s="26" t="s">
         <v>467</v>
       </c>
       <c r="J69" s="1">
@@ -9639,13 +9636,13 @@
       <c r="F70" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="G70" s="27" t="s">
+      <c r="G70" s="26" t="s">
         <v>472</v>
       </c>
-      <c r="H70" s="27" t="s">
+      <c r="H70" s="26" t="s">
         <v>473</v>
       </c>
-      <c r="I70" s="27" t="s">
+      <c r="I70" s="26" t="s">
         <v>474</v>
       </c>
       <c r="J70" s="1">
@@ -9708,13 +9705,13 @@
       <c r="F71" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="G71" s="27" t="s">
+      <c r="G71" s="26" t="s">
         <v>479</v>
       </c>
-      <c r="H71" s="27" t="s">
+      <c r="H71" s="26" t="s">
         <v>480</v>
       </c>
-      <c r="I71" s="27" t="s">
+      <c r="I71" s="26" t="s">
         <v>481</v>
       </c>
       <c r="J71" s="1">
@@ -9777,13 +9774,13 @@
       <c r="F72" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="G72" s="27" t="s">
+      <c r="G72" s="26" t="s">
         <v>486</v>
       </c>
-      <c r="H72" s="27" t="s">
+      <c r="H72" s="26" t="s">
         <v>487</v>
       </c>
-      <c r="I72" s="27" t="s">
+      <c r="I72" s="26" t="s">
         <v>488</v>
       </c>
       <c r="J72" s="1">
@@ -9846,13 +9843,13 @@
       <c r="F73" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="G73" s="27" t="s">
+      <c r="G73" s="26" t="s">
         <v>493</v>
       </c>
-      <c r="H73" s="27" t="s">
+      <c r="H73" s="26" t="s">
         <v>494</v>
       </c>
-      <c r="I73" s="27" t="s">
+      <c r="I73" s="26" t="s">
         <v>495</v>
       </c>
       <c r="J73" s="1">
@@ -9915,13 +9912,13 @@
       <c r="F74" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="G74" s="27" t="s">
+      <c r="G74" s="26" t="s">
         <v>500</v>
       </c>
-      <c r="H74" s="27" t="s">
+      <c r="H74" s="26" t="s">
         <v>501</v>
       </c>
-      <c r="I74" s="27" t="s">
+      <c r="I74" s="26" t="s">
         <v>502</v>
       </c>
       <c r="J74" s="1">
@@ -9984,13 +9981,13 @@
       <c r="F75" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="G75" s="27" t="s">
+      <c r="G75" s="26" t="s">
         <v>507</v>
       </c>
-      <c r="H75" s="27" t="s">
+      <c r="H75" s="26" t="s">
         <v>508</v>
       </c>
-      <c r="I75" s="27" t="s">
+      <c r="I75" s="26" t="s">
         <v>509</v>
       </c>
       <c r="J75" s="1">
@@ -10030,7 +10027,7 @@
       <c r="T75" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="U75" s="27" t="s">
+      <c r="U75" s="26" t="s">
         <v>510</v>
       </c>
       <c r="V75" s="8"/>
@@ -10054,13 +10051,13 @@
       <c r="F76" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="G76" s="27" t="s">
+      <c r="G76" s="26" t="s">
         <v>514</v>
       </c>
-      <c r="H76" s="27" t="s">
+      <c r="H76" s="26" t="s">
         <v>515</v>
       </c>
-      <c r="I76" s="27" t="s">
+      <c r="I76" s="26" t="s">
         <v>516</v>
       </c>
       <c r="J76" s="1">
@@ -10122,13 +10119,13 @@
       <c r="F77" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="G77" s="27" t="s">
+      <c r="G77" s="26" t="s">
         <v>520</v>
       </c>
-      <c r="H77" s="27" t="s">
+      <c r="H77" s="26" t="s">
         <v>521</v>
       </c>
-      <c r="I77" s="27" t="s">
+      <c r="I77" s="26" t="s">
         <v>522</v>
       </c>
       <c r="J77" s="1">
@@ -10190,13 +10187,13 @@
       <c r="F78" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="G78" s="27" t="s">
+      <c r="G78" s="26" t="s">
         <v>526</v>
       </c>
-      <c r="H78" s="27" t="s">
+      <c r="H78" s="26" t="s">
         <v>527</v>
       </c>
-      <c r="I78" s="27" t="s">
+      <c r="I78" s="26" t="s">
         <v>528</v>
       </c>
       <c r="J78" s="1">
@@ -10258,13 +10255,13 @@
       <c r="F79" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="G79" s="27" t="s">
+      <c r="G79" s="26" t="s">
         <v>532</v>
       </c>
-      <c r="H79" s="27" t="s">
+      <c r="H79" s="26" t="s">
         <v>533</v>
       </c>
-      <c r="I79" s="27" t="s">
+      <c r="I79" s="26" t="s">
         <v>534</v>
       </c>
       <c r="J79" s="1">
@@ -10326,13 +10323,13 @@
       <c r="F80" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="G80" s="27" t="s">
+      <c r="G80" s="26" t="s">
         <v>538</v>
       </c>
-      <c r="H80" s="27" t="s">
+      <c r="H80" s="26" t="s">
         <v>539</v>
       </c>
-      <c r="I80" s="27" t="s">
+      <c r="I80" s="26" t="s">
         <v>540</v>
       </c>
       <c r="J80" s="1">
@@ -10394,13 +10391,13 @@
       <c r="F81" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="G81" s="27" t="s">
+      <c r="G81" s="26" t="s">
         <v>544</v>
       </c>
-      <c r="H81" s="27" t="s">
+      <c r="H81" s="26" t="s">
         <v>545</v>
       </c>
-      <c r="I81" s="27" t="s">
+      <c r="I81" s="26" t="s">
         <v>546</v>
       </c>
       <c r="J81" s="1">
@@ -10464,13 +10461,13 @@
       <c r="F82" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="G82" s="27" t="s">
+      <c r="G82" s="26" t="s">
         <v>550</v>
       </c>
-      <c r="H82" s="27" t="s">
+      <c r="H82" s="26" t="s">
         <v>551</v>
       </c>
-      <c r="I82" s="27" t="s">
+      <c r="I82" s="26" t="s">
         <v>552</v>
       </c>
       <c r="J82" s="1">
@@ -10534,13 +10531,13 @@
       <c r="F83" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="G83" s="27" t="s">
+      <c r="G83" s="26" t="s">
         <v>556</v>
       </c>
-      <c r="H83" s="27" t="s">
+      <c r="H83" s="26" t="s">
         <v>557</v>
       </c>
-      <c r="I83" s="27" t="s">
+      <c r="I83" s="26" t="s">
         <v>558</v>
       </c>
       <c r="J83" s="1">
@@ -10604,13 +10601,13 @@
       <c r="F84" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="G84" s="27" t="s">
+      <c r="G84" s="26" t="s">
         <v>562</v>
       </c>
-      <c r="H84" s="27" t="s">
+      <c r="H84" s="26" t="s">
         <v>563</v>
       </c>
-      <c r="I84" s="27" t="s">
+      <c r="I84" s="26" t="s">
         <v>564</v>
       </c>
       <c r="J84" s="1">
@@ -10674,13 +10671,13 @@
       <c r="F85" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="G85" s="27" t="s">
+      <c r="G85" s="26" t="s">
         <v>568</v>
       </c>
-      <c r="H85" s="27" t="s">
+      <c r="H85" s="26" t="s">
         <v>569</v>
       </c>
-      <c r="I85" s="27" t="s">
+      <c r="I85" s="26" t="s">
         <v>570</v>
       </c>
       <c r="J85" s="1">
@@ -10744,13 +10741,13 @@
       <c r="F86" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="G86" s="27" t="s">
+      <c r="G86" s="26" t="s">
         <v>574</v>
       </c>
-      <c r="H86" s="27" t="s">
+      <c r="H86" s="26" t="s">
         <v>538</v>
       </c>
-      <c r="I86" s="27" t="s">
+      <c r="I86" s="26" t="s">
         <v>575</v>
       </c>
       <c r="J86" s="1">
@@ -10814,13 +10811,13 @@
       <c r="F87" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="G87" s="27" t="s">
+      <c r="G87" s="26" t="s">
         <v>579</v>
       </c>
-      <c r="H87" s="27" t="s">
+      <c r="H87" s="26" t="s">
         <v>580</v>
       </c>
-      <c r="I87" s="27" t="s">
+      <c r="I87" s="26" t="s">
         <v>581</v>
       </c>
       <c r="J87" s="1">
@@ -10884,13 +10881,13 @@
       <c r="F88" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="G88" s="27" t="s">
+      <c r="G88" s="26" t="s">
         <v>488</v>
       </c>
-      <c r="H88" s="27" t="s">
+      <c r="H88" s="26" t="s">
         <v>453</v>
       </c>
-      <c r="I88" s="27" t="s">
+      <c r="I88" s="26" t="s">
         <v>585</v>
       </c>
       <c r="J88" s="1">
@@ -10954,13 +10951,13 @@
       <c r="F89" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="G89" s="27" t="s">
+      <c r="G89" s="26" t="s">
         <v>502</v>
       </c>
-      <c r="H89" s="27" t="s">
+      <c r="H89" s="26" t="s">
         <v>589</v>
       </c>
-      <c r="I89" s="27" t="s">
+      <c r="I89" s="26" t="s">
         <v>590</v>
       </c>
       <c r="J89" s="1">
@@ -11024,13 +11021,13 @@
       <c r="F90" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="G90" s="27" t="s">
+      <c r="G90" s="26" t="s">
         <v>594</v>
       </c>
-      <c r="H90" s="27" t="s">
+      <c r="H90" s="26" t="s">
         <v>579</v>
       </c>
-      <c r="I90" s="27" t="s">
+      <c r="I90" s="26" t="s">
         <v>595</v>
       </c>
       <c r="J90" s="1">
@@ -11094,13 +11091,13 @@
       <c r="F91" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="G91" s="27" t="s">
+      <c r="G91" s="26" t="s">
         <v>599</v>
       </c>
-      <c r="H91" s="27" t="s">
+      <c r="H91" s="26" t="s">
         <v>600</v>
       </c>
-      <c r="I91" s="27" t="s">
+      <c r="I91" s="26" t="s">
         <v>601</v>
       </c>
       <c r="J91" s="1">
@@ -11164,13 +11161,13 @@
       <c r="F92" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="G92" s="27" t="s">
+      <c r="G92" s="26" t="s">
         <v>605</v>
       </c>
-      <c r="H92" s="27" t="s">
+      <c r="H92" s="26" t="s">
         <v>606</v>
       </c>
-      <c r="I92" s="27" t="s">
+      <c r="I92" s="26" t="s">
         <v>607</v>
       </c>
       <c r="J92" s="1">
@@ -11234,13 +11231,13 @@
       <c r="F93" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="G93" s="27" t="s">
+      <c r="G93" s="26" t="s">
         <v>611</v>
       </c>
-      <c r="H93" s="27" t="s">
+      <c r="H93" s="26" t="s">
         <v>612</v>
       </c>
-      <c r="I93" s="27" t="s">
+      <c r="I93" s="26" t="s">
         <v>613</v>
       </c>
       <c r="J93" s="1">
@@ -11304,13 +11301,13 @@
       <c r="F94" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="G94" s="27" t="s">
+      <c r="G94" s="26" t="s">
         <v>570</v>
       </c>
-      <c r="H94" s="27" t="s">
+      <c r="H94" s="26" t="s">
         <v>617</v>
       </c>
-      <c r="I94" s="27" t="s">
+      <c r="I94" s="26" t="s">
         <v>618</v>
       </c>
       <c r="J94" s="1">
@@ -11374,13 +11371,13 @@
       <c r="F95" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="G95" s="27" t="s">
+      <c r="G95" s="26" t="s">
         <v>575</v>
       </c>
-      <c r="H95" s="27" t="s">
+      <c r="H95" s="26" t="s">
         <v>622</v>
       </c>
-      <c r="I95" s="27" t="s">
+      <c r="I95" s="26" t="s">
         <v>623</v>
       </c>
       <c r="J95" s="1">
@@ -11442,13 +11439,13 @@
       <c r="F96" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="G96" s="27" t="s">
+      <c r="G96" s="26" t="s">
         <v>581</v>
       </c>
-      <c r="H96" s="27" t="s">
+      <c r="H96" s="26" t="s">
         <v>627</v>
       </c>
-      <c r="I96" s="27" t="s">
+      <c r="I96" s="26" t="s">
         <v>628</v>
       </c>
       <c r="J96" s="1">
@@ -11505,13 +11502,13 @@
       <c r="F97" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="G97" s="27" t="s">
+      <c r="G97" s="26" t="s">
         <v>585</v>
       </c>
-      <c r="H97" s="27" t="s">
+      <c r="H97" s="26" t="s">
         <v>632</v>
       </c>
-      <c r="I97" s="27" t="s">
+      <c r="I97" s="26" t="s">
         <v>633</v>
       </c>
       <c r="J97" s="1">
@@ -11568,13 +11565,13 @@
       <c r="F98" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="G98" s="27" t="s">
+      <c r="G98" s="26" t="s">
         <v>637</v>
       </c>
-      <c r="H98" s="27" t="s">
+      <c r="H98" s="26" t="s">
         <v>638</v>
       </c>
-      <c r="I98" s="27" t="s">
+      <c r="I98" s="26" t="s">
         <v>639</v>
       </c>
       <c r="J98" s="1">
@@ -11631,13 +11628,13 @@
       <c r="F99" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="G99" s="27" t="s">
+      <c r="G99" s="26" t="s">
         <v>643</v>
       </c>
-      <c r="H99" s="27" t="s">
+      <c r="H99" s="26" t="s">
         <v>644</v>
       </c>
-      <c r="I99" s="27" t="s">
+      <c r="I99" s="26" t="s">
         <v>645</v>
       </c>
       <c r="J99" s="1">
@@ -11694,13 +11691,13 @@
       <c r="F100" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="G100" s="27" t="s">
+      <c r="G100" s="26" t="s">
         <v>649</v>
       </c>
-      <c r="H100" s="27" t="s">
+      <c r="H100" s="26" t="s">
         <v>650</v>
       </c>
-      <c r="I100" s="27" t="s">
+      <c r="I100" s="26" t="s">
         <v>651</v>
       </c>
       <c r="J100" s="1">
@@ -11757,13 +11754,13 @@
       <c r="F101" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="G101" s="27" t="s">
+      <c r="G101" s="26" t="s">
         <v>655</v>
       </c>
-      <c r="H101" s="27" t="s">
+      <c r="H101" s="26" t="s">
         <v>656</v>
       </c>
-      <c r="I101" s="27" t="s">
+      <c r="I101" s="26" t="s">
         <v>657</v>
       </c>
       <c r="J101" s="1">
@@ -11820,13 +11817,13 @@
       <c r="F102" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="G102" s="27" t="s">
+      <c r="G102" s="26" t="s">
         <v>661</v>
       </c>
-      <c r="H102" s="27" t="s">
+      <c r="H102" s="26" t="s">
         <v>662</v>
       </c>
-      <c r="I102" s="27" t="s">
+      <c r="I102" s="26" t="s">
         <v>663</v>
       </c>
       <c r="J102" s="1">
@@ -11883,13 +11880,13 @@
       <c r="F103" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="G103" s="27" t="s">
+      <c r="G103" s="26" t="s">
         <v>667</v>
       </c>
-      <c r="H103" s="27" t="s">
+      <c r="H103" s="26" t="s">
         <v>668</v>
       </c>
-      <c r="I103" s="27" t="s">
+      <c r="I103" s="26" t="s">
         <v>669</v>
       </c>
       <c r="J103" s="1">
@@ -11946,13 +11943,13 @@
       <c r="F104" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="G104" s="27" t="s">
+      <c r="G104" s="26" t="s">
         <v>673</v>
       </c>
-      <c r="H104" s="27" t="s">
+      <c r="H104" s="26" t="s">
         <v>667</v>
       </c>
-      <c r="I104" s="27" t="s">
+      <c r="I104" s="26" t="s">
         <v>674</v>
       </c>
       <c r="J104" s="1">
@@ -12009,13 +12006,13 @@
       <c r="F105" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="G105" s="27" t="s">
+      <c r="G105" s="26" t="s">
         <v>678</v>
       </c>
-      <c r="H105" s="27" t="s">
+      <c r="H105" s="26" t="s">
         <v>673</v>
       </c>
-      <c r="I105" s="27" t="s">
+      <c r="I105" s="26" t="s">
         <v>679</v>
       </c>
       <c r="J105" s="1">
@@ -12074,13 +12071,13 @@
       <c r="F106" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="G106" s="27" t="s">
+      <c r="G106" s="26" t="s">
         <v>683</v>
       </c>
-      <c r="H106" s="27" t="s">
+      <c r="H106" s="26" t="s">
         <v>684</v>
       </c>
-      <c r="I106" s="27" t="s">
+      <c r="I106" s="26" t="s">
         <v>685</v>
       </c>
       <c r="J106" s="1">
@@ -12144,13 +12141,13 @@
       <c r="F107" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="G107" s="27" t="s">
+      <c r="G107" s="26" t="s">
         <v>689</v>
       </c>
-      <c r="H107" s="27" t="s">
+      <c r="H107" s="26" t="s">
         <v>690</v>
       </c>
-      <c r="I107" s="27" t="s">
+      <c r="I107" s="26" t="s">
         <v>691</v>
       </c>
       <c r="J107" s="1">
@@ -12214,13 +12211,13 @@
       <c r="F108" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="G108" s="27" t="s">
+      <c r="G108" s="26" t="s">
         <v>695</v>
       </c>
-      <c r="H108" s="27" t="s">
+      <c r="H108" s="26" t="s">
         <v>696</v>
       </c>
-      <c r="I108" s="27" t="s">
+      <c r="I108" s="26" t="s">
         <v>697</v>
       </c>
       <c r="J108" s="1">
@@ -12284,13 +12281,13 @@
       <c r="F109" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="G109" s="27" t="s">
+      <c r="G109" s="26" t="s">
         <v>701</v>
       </c>
-      <c r="H109" s="27" t="s">
+      <c r="H109" s="26" t="s">
         <v>702</v>
       </c>
-      <c r="I109" s="27" t="s">
+      <c r="I109" s="26" t="s">
         <v>703</v>
       </c>
       <c r="J109" s="1">
@@ -12354,13 +12351,13 @@
       <c r="F110" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="G110" s="27" t="s">
+      <c r="G110" s="26" t="s">
         <v>707</v>
       </c>
-      <c r="H110" s="27" t="s">
+      <c r="H110" s="26" t="s">
         <v>708</v>
       </c>
-      <c r="I110" s="27" t="s">
+      <c r="I110" s="26" t="s">
         <v>709</v>
       </c>
       <c r="J110" s="1">
@@ -12424,13 +12421,13 @@
       <c r="F111" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="G111" s="28" t="s">
+      <c r="G111" s="27" t="s">
         <v>713</v>
       </c>
-      <c r="H111" s="29" t="s">
+      <c r="H111" s="28" t="s">
         <v>713</v>
       </c>
-      <c r="I111" s="30" t="s">
+      <c r="I111" s="29" t="s">
         <v>714</v>
       </c>
       <c r="J111" s="1">
@@ -12463,10 +12460,10 @@
       <c r="S111" s="8">
         <v>90</v>
       </c>
-      <c r="T111" s="27" t="s">
+      <c r="T111" s="26" t="s">
         <v>715</v>
       </c>
-      <c r="U111" s="27" t="s">
+      <c r="U111" s="26" t="s">
         <v>715</v>
       </c>
       <c r="X111" s="8"/>
@@ -12488,13 +12485,13 @@
       <c r="F112" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="G112" s="31" t="s">
+      <c r="G112" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="H112" s="27" t="s">
+      <c r="H112" s="26" t="s">
         <v>719</v>
       </c>
-      <c r="I112" s="32" t="s">
+      <c r="I112" s="31" t="s">
         <v>720</v>
       </c>
       <c r="J112" s="1">
@@ -12532,10 +12529,10 @@
       <c r="S112" s="8">
         <v>90</v>
       </c>
-      <c r="T112" s="27" t="s">
+      <c r="T112" s="26" t="s">
         <v>721</v>
       </c>
-      <c r="U112" s="27" t="s">
+      <c r="U112" s="26" t="s">
         <v>721</v>
       </c>
       <c r="X112" s="8"/>
@@ -12557,13 +12554,13 @@
       <c r="F113" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="G113" s="31" t="s">
+      <c r="G113" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="H113" s="27" t="s">
+      <c r="H113" s="26" t="s">
         <v>725</v>
       </c>
-      <c r="I113" s="32" t="s">
+      <c r="I113" s="31" t="s">
         <v>726</v>
       </c>
       <c r="J113" s="1">
@@ -12601,10 +12598,10 @@
       <c r="S113" s="8">
         <v>90</v>
       </c>
-      <c r="T113" s="27" t="s">
+      <c r="T113" s="26" t="s">
         <v>727</v>
       </c>
-      <c r="U113" s="27" t="s">
+      <c r="U113" s="26" t="s">
         <v>727</v>
       </c>
       <c r="X113" s="8"/>
@@ -12626,13 +12623,13 @@
       <c r="F114" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="G114" s="31" t="s">
+      <c r="G114" s="30" t="s">
         <v>731</v>
       </c>
-      <c r="H114" s="27" t="s">
+      <c r="H114" s="26" t="s">
         <v>731</v>
       </c>
-      <c r="I114" s="32" t="s">
+      <c r="I114" s="31" t="s">
         <v>732</v>
       </c>
       <c r="J114" s="1">
@@ -12670,10 +12667,10 @@
       <c r="S114" s="8">
         <v>90</v>
       </c>
-      <c r="T114" s="27" t="s">
+      <c r="T114" s="26" t="s">
         <v>733</v>
       </c>
-      <c r="U114" s="27" t="s">
+      <c r="U114" s="26" t="s">
         <v>733</v>
       </c>
       <c r="X114" s="8"/>
@@ -12695,13 +12692,13 @@
       <c r="F115" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="G115" s="31" t="s">
+      <c r="G115" s="30" t="s">
         <v>737</v>
       </c>
-      <c r="H115" s="27" t="s">
+      <c r="H115" s="26" t="s">
         <v>737</v>
       </c>
-      <c r="I115" s="32" t="s">
+      <c r="I115" s="31" t="s">
         <v>738</v>
       </c>
       <c r="J115" s="1">
@@ -12739,10 +12736,10 @@
       <c r="S115" s="8">
         <v>90</v>
       </c>
-      <c r="T115" s="27" t="s">
+      <c r="T115" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="U115" s="27" t="s">
+      <c r="U115" s="26" t="s">
         <v>739</v>
       </c>
       <c r="X115" s="8"/>
@@ -12764,13 +12761,13 @@
       <c r="F116" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="G116" s="31" t="s">
+      <c r="G116" s="30" t="s">
         <v>743</v>
       </c>
-      <c r="H116" s="27" t="s">
+      <c r="H116" s="26" t="s">
         <v>743</v>
       </c>
-      <c r="I116" s="32" t="s">
+      <c r="I116" s="31" t="s">
         <v>744</v>
       </c>
       <c r="J116" s="1">
@@ -12808,10 +12805,10 @@
       <c r="S116" s="8">
         <v>90</v>
       </c>
-      <c r="T116" s="27" t="s">
+      <c r="T116" s="26" t="s">
         <v>745</v>
       </c>
-      <c r="U116" s="27" t="s">
+      <c r="U116" s="26" t="s">
         <v>745</v>
       </c>
       <c r="V116" s="8"/>
@@ -12835,13 +12832,13 @@
       <c r="F117" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="G117" s="31" t="s">
+      <c r="G117" s="30" t="s">
         <v>749</v>
       </c>
-      <c r="H117" s="27" t="s">
+      <c r="H117" s="26" t="s">
         <v>749</v>
       </c>
-      <c r="I117" s="32" t="s">
+      <c r="I117" s="31" t="s">
         <v>750</v>
       </c>
       <c r="J117" s="1">
@@ -12879,10 +12876,10 @@
       <c r="S117" s="8">
         <v>90</v>
       </c>
-      <c r="T117" s="27" t="s">
+      <c r="T117" s="26" t="s">
         <v>751</v>
       </c>
-      <c r="U117" s="27" t="s">
+      <c r="U117" s="26" t="s">
         <v>751</v>
       </c>
       <c r="V117" s="8"/>
@@ -12906,13 +12903,13 @@
       <c r="F118" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="G118" s="31" t="s">
+      <c r="G118" s="30" t="s">
         <v>755</v>
       </c>
-      <c r="H118" s="27" t="s">
+      <c r="H118" s="26" t="s">
         <v>755</v>
       </c>
-      <c r="I118" s="32" t="s">
+      <c r="I118" s="31" t="s">
         <v>756</v>
       </c>
       <c r="J118" s="1">
@@ -12950,10 +12947,10 @@
       <c r="S118" s="8">
         <v>90</v>
       </c>
-      <c r="T118" s="27" t="s">
+      <c r="T118" s="26" t="s">
         <v>757</v>
       </c>
-      <c r="U118" s="27" t="s">
+      <c r="U118" s="26" t="s">
         <v>757</v>
       </c>
       <c r="V118" s="8"/>
@@ -12977,13 +12974,13 @@
       <c r="F119" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="G119" s="31" t="s">
+      <c r="G119" s="30" t="s">
         <v>761</v>
       </c>
-      <c r="H119" s="27" t="s">
+      <c r="H119" s="26" t="s">
         <v>761</v>
       </c>
-      <c r="I119" s="32" t="s">
+      <c r="I119" s="31" t="s">
         <v>762</v>
       </c>
       <c r="J119" s="1">
@@ -13021,10 +13018,10 @@
       <c r="S119" s="8">
         <v>90</v>
       </c>
-      <c r="T119" s="27" t="s">
+      <c r="T119" s="26" t="s">
         <v>763</v>
       </c>
-      <c r="U119" s="27" t="s">
+      <c r="U119" s="26" t="s">
         <v>763</v>
       </c>
       <c r="V119" s="8"/>
@@ -13048,13 +13045,13 @@
       <c r="F120" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="G120" s="31" t="s">
+      <c r="G120" s="30" t="s">
         <v>767</v>
       </c>
-      <c r="H120" s="27" t="s">
+      <c r="H120" s="26" t="s">
         <v>767</v>
       </c>
-      <c r="I120" s="32" t="s">
+      <c r="I120" s="31" t="s">
         <v>768</v>
       </c>
       <c r="J120" s="1">
@@ -13092,10 +13089,10 @@
       <c r="S120" s="8">
         <v>90</v>
       </c>
-      <c r="T120" s="27" t="s">
+      <c r="T120" s="26" t="s">
         <v>769</v>
       </c>
-      <c r="U120" s="27" t="s">
+      <c r="U120" s="26" t="s">
         <v>769</v>
       </c>
       <c r="V120" s="8"/>
@@ -13119,13 +13116,13 @@
       <c r="F121" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="G121" s="31" t="s">
+      <c r="G121" s="30" t="s">
         <v>714</v>
       </c>
-      <c r="H121" s="27" t="s">
+      <c r="H121" s="26" t="s">
         <v>714</v>
       </c>
-      <c r="I121" s="32" t="s">
+      <c r="I121" s="31" t="s">
         <v>773</v>
       </c>
       <c r="J121" s="1">
@@ -13163,10 +13160,10 @@
       <c r="S121" s="8">
         <v>90</v>
       </c>
-      <c r="T121" s="27" t="s">
+      <c r="T121" s="26" t="s">
         <v>774</v>
       </c>
-      <c r="U121" s="27" t="s">
+      <c r="U121" s="26" t="s">
         <v>774</v>
       </c>
       <c r="V121" s="8"/>
@@ -13190,13 +13187,13 @@
       <c r="F122" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="G122" s="31" t="s">
+      <c r="G122" s="30" t="s">
         <v>778</v>
       </c>
-      <c r="H122" s="27" t="s">
+      <c r="H122" s="26" t="s">
         <v>778</v>
       </c>
-      <c r="I122" s="32" t="s">
+      <c r="I122" s="31" t="s">
         <v>779</v>
       </c>
       <c r="J122" s="1">
@@ -13235,10 +13232,10 @@
       <c r="S122" s="8">
         <v>90</v>
       </c>
-      <c r="T122" s="27" t="s">
+      <c r="T122" s="26" t="s">
         <v>780</v>
       </c>
-      <c r="U122" s="27" t="s">
+      <c r="U122" s="26" t="s">
         <v>780</v>
       </c>
       <c r="V122" s="8"/>
@@ -13262,13 +13259,13 @@
       <c r="F123" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="G123" s="31" t="s">
+      <c r="G123" s="30" t="s">
         <v>784</v>
       </c>
-      <c r="H123" s="27" t="s">
+      <c r="H123" s="26" t="s">
         <v>784</v>
       </c>
-      <c r="I123" s="32" t="s">
+      <c r="I123" s="31" t="s">
         <v>785</v>
       </c>
       <c r="J123" s="1">
@@ -13307,10 +13304,10 @@
       <c r="S123" s="8">
         <v>90</v>
       </c>
-      <c r="T123" s="27" t="s">
+      <c r="T123" s="26" t="s">
         <v>786</v>
       </c>
-      <c r="U123" s="27" t="s">
+      <c r="U123" s="26" t="s">
         <v>786</v>
       </c>
       <c r="V123" s="8"/>
@@ -13334,13 +13331,13 @@
       <c r="F124" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="G124" s="31" t="s">
+      <c r="G124" s="30" t="s">
         <v>790</v>
       </c>
-      <c r="H124" s="27" t="s">
+      <c r="H124" s="26" t="s">
         <v>790</v>
       </c>
-      <c r="I124" s="32" t="s">
+      <c r="I124" s="31" t="s">
         <v>791</v>
       </c>
       <c r="J124" s="1">
@@ -13379,10 +13376,10 @@
       <c r="S124" s="8">
         <v>90</v>
       </c>
-      <c r="T124" s="27" t="s">
+      <c r="T124" s="26" t="s">
         <v>792</v>
       </c>
-      <c r="U124" s="27" t="s">
+      <c r="U124" s="26" t="s">
         <v>792</v>
       </c>
       <c r="V124" s="8"/>
@@ -13406,13 +13403,13 @@
       <c r="F125" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="G125" s="31" t="s">
+      <c r="G125" s="30" t="s">
         <v>796</v>
       </c>
-      <c r="H125" s="27" t="s">
+      <c r="H125" s="26" t="s">
         <v>796</v>
       </c>
-      <c r="I125" s="32" t="s">
+      <c r="I125" s="31" t="s">
         <v>797</v>
       </c>
       <c r="J125" s="1">
@@ -13451,10 +13448,10 @@
       <c r="S125" s="8">
         <v>90</v>
       </c>
-      <c r="T125" s="27" t="s">
+      <c r="T125" s="26" t="s">
         <v>798</v>
       </c>
-      <c r="U125" s="27" t="s">
+      <c r="U125" s="26" t="s">
         <v>798</v>
       </c>
       <c r="V125" s="8"/>
@@ -13478,13 +13475,13 @@
       <c r="F126" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="G126" s="31" t="s">
+      <c r="G126" s="30" t="s">
         <v>802</v>
       </c>
-      <c r="H126" s="27" t="s">
+      <c r="H126" s="26" t="s">
         <v>802</v>
       </c>
-      <c r="I126" s="32" t="s">
+      <c r="I126" s="31" t="s">
         <v>803</v>
       </c>
       <c r="J126" s="1">
@@ -13523,10 +13520,10 @@
       <c r="S126" s="8">
         <v>90</v>
       </c>
-      <c r="T126" s="27" t="s">
+      <c r="T126" s="26" t="s">
         <v>804</v>
       </c>
-      <c r="U126" s="27" t="s">
+      <c r="U126" s="26" t="s">
         <v>804</v>
       </c>
       <c r="V126" s="8"/>
@@ -13550,13 +13547,13 @@
       <c r="F127" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="G127" s="31" t="s">
+      <c r="G127" s="30" t="s">
         <v>808</v>
       </c>
-      <c r="H127" s="27" t="s">
+      <c r="H127" s="26" t="s">
         <v>808</v>
       </c>
-      <c r="I127" s="32" t="s">
+      <c r="I127" s="31" t="s">
         <v>809</v>
       </c>
       <c r="J127" s="1">
@@ -13595,10 +13592,10 @@
       <c r="S127" s="8">
         <v>90</v>
       </c>
-      <c r="T127" s="27" t="s">
+      <c r="T127" s="26" t="s">
         <v>810</v>
       </c>
-      <c r="U127" s="27" t="s">
+      <c r="U127" s="26" t="s">
         <v>810</v>
       </c>
       <c r="V127" s="8"/>
@@ -13622,13 +13619,13 @@
       <c r="F128" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="G128" s="31" t="s">
+      <c r="G128" s="30" t="s">
         <v>814</v>
       </c>
-      <c r="H128" s="27" t="s">
+      <c r="H128" s="26" t="s">
         <v>814</v>
       </c>
-      <c r="I128" s="32" t="s">
+      <c r="I128" s="31" t="s">
         <v>815</v>
       </c>
       <c r="J128" s="1">
@@ -13667,10 +13664,10 @@
       <c r="S128" s="8">
         <v>90</v>
       </c>
-      <c r="T128" s="27" t="s">
+      <c r="T128" s="26" t="s">
         <v>816</v>
       </c>
-      <c r="U128" s="27" t="s">
+      <c r="U128" s="26" t="s">
         <v>816</v>
       </c>
       <c r="V128" s="8"/>
@@ -13694,13 +13691,13 @@
       <c r="F129" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="G129" s="31" t="s">
+      <c r="G129" s="30" t="s">
         <v>820</v>
       </c>
-      <c r="H129" s="27" t="s">
+      <c r="H129" s="26" t="s">
         <v>820</v>
       </c>
-      <c r="I129" s="32" t="s">
+      <c r="I129" s="31" t="s">
         <v>821</v>
       </c>
       <c r="J129" s="1">
@@ -13739,10 +13736,10 @@
       <c r="S129" s="8">
         <v>90</v>
       </c>
-      <c r="T129" s="27" t="s">
+      <c r="T129" s="26" t="s">
         <v>822</v>
       </c>
-      <c r="U129" s="27" t="s">
+      <c r="U129" s="26" t="s">
         <v>822</v>
       </c>
       <c r="V129" s="8"/>
@@ -13766,13 +13763,13 @@
       <c r="F130" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="G130" s="31" t="s">
+      <c r="G130" s="30" t="s">
         <v>826</v>
       </c>
-      <c r="H130" s="27" t="s">
+      <c r="H130" s="26" t="s">
         <v>826</v>
       </c>
-      <c r="I130" s="32" t="s">
+      <c r="I130" s="31" t="s">
         <v>827</v>
       </c>
       <c r="J130" s="1">
@@ -13811,10 +13808,10 @@
       <c r="S130" s="8">
         <v>90</v>
       </c>
-      <c r="T130" s="27" t="s">
+      <c r="T130" s="26" t="s">
         <v>828</v>
       </c>
-      <c r="U130" s="27" t="s">
+      <c r="U130" s="26" t="s">
         <v>828</v>
       </c>
       <c r="V130" s="8"/>
@@ -13836,13 +13833,13 @@
       <c r="F131" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="G131" s="31" t="s">
+      <c r="G131" s="30" t="s">
         <v>832</v>
       </c>
-      <c r="H131" s="27" t="s">
+      <c r="H131" s="26" t="s">
         <v>832</v>
       </c>
-      <c r="I131" s="32" t="s">
+      <c r="I131" s="31" t="s">
         <v>833</v>
       </c>
       <c r="J131" s="1">
@@ -13881,10 +13878,10 @@
       <c r="S131" s="8">
         <v>92</v>
       </c>
-      <c r="T131" s="27" t="s">
+      <c r="T131" s="26" t="s">
         <v>834</v>
       </c>
-      <c r="U131" s="27" t="s">
+      <c r="U131" s="26" t="s">
         <v>834</v>
       </c>
     </row>
@@ -13901,13 +13898,13 @@
       <c r="F132" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="G132" s="31" t="s">
+      <c r="G132" s="30" t="s">
         <v>838</v>
       </c>
-      <c r="H132" s="27" t="s">
+      <c r="H132" s="26" t="s">
         <v>838</v>
       </c>
-      <c r="I132" s="32" t="s">
+      <c r="I132" s="31" t="s">
         <v>839</v>
       </c>
       <c r="J132" s="1">
@@ -13946,10 +13943,10 @@
       <c r="S132" s="8">
         <v>94</v>
       </c>
-      <c r="T132" s="27" t="s">
+      <c r="T132" s="26" t="s">
         <v>840</v>
       </c>
-      <c r="U132" s="27" t="s">
+      <c r="U132" s="26" t="s">
         <v>840</v>
       </c>
     </row>
@@ -13966,13 +13963,13 @@
       <c r="F133" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="G133" s="31" t="s">
+      <c r="G133" s="30" t="s">
         <v>844</v>
       </c>
-      <c r="H133" s="27" t="s">
+      <c r="H133" s="26" t="s">
         <v>844</v>
       </c>
-      <c r="I133" s="32" t="s">
+      <c r="I133" s="31" t="s">
         <v>845</v>
       </c>
       <c r="J133" s="1">
@@ -14011,10 +14008,10 @@
       <c r="S133" s="8">
         <v>96</v>
       </c>
-      <c r="T133" s="27" t="s">
+      <c r="T133" s="26" t="s">
         <v>846</v>
       </c>
-      <c r="U133" s="27" t="s">
+      <c r="U133" s="26" t="s">
         <v>846</v>
       </c>
     </row>
@@ -14031,13 +14028,13 @@
       <c r="F134" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="G134" s="31" t="s">
+      <c r="G134" s="30" t="s">
         <v>850</v>
       </c>
-      <c r="H134" s="27" t="s">
+      <c r="H134" s="26" t="s">
         <v>850</v>
       </c>
-      <c r="I134" s="32" t="s">
+      <c r="I134" s="31" t="s">
         <v>851</v>
       </c>
       <c r="J134" s="1">
@@ -14076,10 +14073,10 @@
       <c r="S134" s="8">
         <v>98</v>
       </c>
-      <c r="T134" s="27" t="s">
+      <c r="T134" s="26" t="s">
         <v>852</v>
       </c>
-      <c r="U134" s="27" t="s">
+      <c r="U134" s="26" t="s">
         <v>852</v>
       </c>
     </row>
@@ -14096,13 +14093,13 @@
       <c r="F135" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="G135" s="31" t="s">
+      <c r="G135" s="30" t="s">
         <v>856</v>
       </c>
-      <c r="H135" s="27" t="s">
+      <c r="H135" s="26" t="s">
         <v>856</v>
       </c>
-      <c r="I135" s="32" t="s">
+      <c r="I135" s="31" t="s">
         <v>857</v>
       </c>
       <c r="J135" s="1">
@@ -14141,10 +14138,10 @@
       <c r="S135" s="8">
         <v>99</v>
       </c>
-      <c r="T135" s="27" t="s">
+      <c r="T135" s="26" t="s">
         <v>858</v>
       </c>
-      <c r="U135" s="27" t="s">
+      <c r="U135" s="26" t="s">
         <v>858</v>
       </c>
     </row>
@@ -14161,13 +14158,13 @@
       <c r="F136" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="G136" s="31" t="s">
+      <c r="G136" s="30" t="s">
         <v>862</v>
       </c>
-      <c r="H136" s="27" t="s">
+      <c r="H136" s="26" t="s">
         <v>862</v>
       </c>
-      <c r="I136" s="32" t="s">
+      <c r="I136" s="31" t="s">
         <v>863</v>
       </c>
       <c r="J136" s="1">
@@ -14206,10 +14203,10 @@
       <c r="S136" s="8">
         <v>99.2</v>
       </c>
-      <c r="T136" s="27" t="s">
+      <c r="T136" s="26" t="s">
         <v>864</v>
       </c>
-      <c r="U136" s="27" t="s">
+      <c r="U136" s="26" t="s">
         <v>864</v>
       </c>
     </row>
@@ -14226,13 +14223,13 @@
       <c r="F137" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="G137" s="31" t="s">
+      <c r="G137" s="30" t="s">
         <v>868</v>
       </c>
-      <c r="H137" s="27" t="s">
+      <c r="H137" s="26" t="s">
         <v>868</v>
       </c>
-      <c r="I137" s="32" t="s">
+      <c r="I137" s="31" t="s">
         <v>869</v>
       </c>
       <c r="J137" s="1">
@@ -14271,10 +14268,10 @@
       <c r="S137" s="8">
         <v>99.4</v>
       </c>
-      <c r="T137" s="27" t="s">
+      <c r="T137" s="26" t="s">
         <v>870</v>
       </c>
-      <c r="U137" s="27" t="s">
+      <c r="U137" s="26" t="s">
         <v>870</v>
       </c>
     </row>
@@ -14291,13 +14288,13 @@
       <c r="F138" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="G138" s="31" t="s">
+      <c r="G138" s="30" t="s">
         <v>874</v>
       </c>
-      <c r="H138" s="27" t="s">
+      <c r="H138" s="26" t="s">
         <v>874</v>
       </c>
-      <c r="I138" s="32" t="s">
+      <c r="I138" s="31" t="s">
         <v>875</v>
       </c>
       <c r="J138" s="1">
@@ -14336,10 +14333,10 @@
       <c r="S138" s="8">
         <v>99.6</v>
       </c>
-      <c r="T138" s="27" t="s">
+      <c r="T138" s="26" t="s">
         <v>876</v>
       </c>
-      <c r="U138" s="27" t="s">
+      <c r="U138" s="26" t="s">
         <v>876</v>
       </c>
     </row>
@@ -14356,13 +14353,13 @@
       <c r="F139" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="G139" s="31" t="s">
+      <c r="G139" s="30" t="s">
         <v>880</v>
       </c>
-      <c r="H139" s="27" t="s">
+      <c r="H139" s="26" t="s">
         <v>880</v>
       </c>
-      <c r="I139" s="32" t="s">
+      <c r="I139" s="31" t="s">
         <v>881</v>
       </c>
       <c r="J139" s="1">
@@ -14401,10 +14398,10 @@
       <c r="S139" s="8">
         <v>99.8</v>
       </c>
-      <c r="T139" s="27" t="s">
+      <c r="T139" s="26" t="s">
         <v>882</v>
       </c>
-      <c r="U139" s="27" t="s">
+      <c r="U139" s="26" t="s">
         <v>882</v>
       </c>
     </row>
@@ -14421,13 +14418,13 @@
       <c r="F140" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="G140" s="31" t="s">
+      <c r="G140" s="30" t="s">
         <v>886</v>
       </c>
-      <c r="H140" s="27" t="s">
+      <c r="H140" s="26" t="s">
         <v>886</v>
       </c>
-      <c r="I140" s="32" t="s">
+      <c r="I140" s="31" t="s">
         <v>887</v>
       </c>
       <c r="J140" s="1">
@@ -14466,10 +14463,10 @@
       <c r="S140" s="8">
         <v>99.9</v>
       </c>
-      <c r="T140" s="27" t="s">
+      <c r="T140" s="26" t="s">
         <v>888</v>
       </c>
-      <c r="U140" s="27" t="s">
+      <c r="U140" s="26" t="s">
         <v>888</v>
       </c>
     </row>
@@ -14488,13 +14485,13 @@
       <c r="F141" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="G141" s="31" t="s">
+      <c r="G141" s="30" t="s">
         <v>892</v>
       </c>
-      <c r="H141" s="27" t="s">
+      <c r="H141" s="26" t="s">
         <v>892</v>
       </c>
-      <c r="I141" s="32" t="s">
+      <c r="I141" s="31" t="s">
         <v>893</v>
       </c>
       <c r="J141" s="1">
@@ -14533,10 +14530,10 @@
       <c r="S141" s="8">
         <v>99.92</v>
       </c>
-      <c r="T141" s="27" t="s">
+      <c r="T141" s="26" t="s">
         <v>894</v>
       </c>
-      <c r="U141" s="27" t="s">
+      <c r="U141" s="26" t="s">
         <v>894</v>
       </c>
       <c r="V141" s="8"/>
@@ -14560,13 +14557,13 @@
       <c r="F142" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="G142" s="31" t="s">
+      <c r="G142" s="30" t="s">
         <v>898</v>
       </c>
-      <c r="H142" s="27" t="s">
+      <c r="H142" s="26" t="s">
         <v>898</v>
       </c>
-      <c r="I142" s="32" t="s">
+      <c r="I142" s="31" t="s">
         <v>899</v>
       </c>
       <c r="J142" s="1">
@@ -14605,10 +14602,10 @@
       <c r="S142" s="8">
         <v>99.94</v>
       </c>
-      <c r="T142" s="27" t="s">
+      <c r="T142" s="26" t="s">
         <v>900</v>
       </c>
-      <c r="U142" s="27" t="s">
+      <c r="U142" s="26" t="s">
         <v>900</v>
       </c>
       <c r="V142" s="8"/>
@@ -14632,13 +14629,13 @@
       <c r="F143" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="G143" s="31" t="s">
+      <c r="G143" s="30" t="s">
         <v>904</v>
       </c>
-      <c r="H143" s="27" t="s">
+      <c r="H143" s="26" t="s">
         <v>904</v>
       </c>
-      <c r="I143" s="32" t="s">
+      <c r="I143" s="31" t="s">
         <v>905</v>
       </c>
       <c r="J143" s="1">
@@ -14677,10 +14674,10 @@
       <c r="S143" s="8">
         <v>99.96</v>
       </c>
-      <c r="T143" s="27" t="s">
+      <c r="T143" s="26" t="s">
         <v>906</v>
       </c>
-      <c r="U143" s="27" t="s">
+      <c r="U143" s="26" t="s">
         <v>906</v>
       </c>
       <c r="V143" s="8"/>
@@ -14704,13 +14701,13 @@
       <c r="F144" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="G144" s="31" t="s">
+      <c r="G144" s="30" t="s">
         <v>910</v>
       </c>
-      <c r="H144" s="27" t="s">
+      <c r="H144" s="26" t="s">
         <v>910</v>
       </c>
-      <c r="I144" s="32" t="s">
+      <c r="I144" s="31" t="s">
         <v>911</v>
       </c>
       <c r="J144" s="1">
@@ -14749,10 +14746,10 @@
       <c r="S144" s="8">
         <v>99.98</v>
       </c>
-      <c r="T144" s="27" t="s">
+      <c r="T144" s="26" t="s">
         <v>912</v>
       </c>
-      <c r="U144" s="27" t="s">
+      <c r="U144" s="26" t="s">
         <v>912</v>
       </c>
       <c r="V144" s="8"/>
@@ -14821,10 +14818,10 @@
       <c r="S145" s="8">
         <v>99.99</v>
       </c>
-      <c r="T145" s="27" t="s">
+      <c r="T145" s="26" t="s">
         <v>918</v>
       </c>
-      <c r="U145" s="27" t="s">
+      <c r="U145" s="26" t="s">
         <v>918</v>
       </c>
       <c r="V145" s="8"/>
@@ -14854,7 +14851,7 @@
       <c r="H146" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="I146" s="26" t="s">
+      <c r="I146" s="24" t="s">
         <v>924</v>
       </c>
       <c r="J146" s="2">
@@ -14892,10 +14889,10 @@
       <c r="S146" s="16">
         <v>99.99</v>
       </c>
-      <c r="T146" s="33" t="s">
+      <c r="T146" s="32" t="s">
         <v>926</v>
       </c>
-      <c r="U146" s="33" t="s">
+      <c r="U146" s="32" t="s">
         <v>926</v>
       </c>
       <c r="X146" s="16"/>
@@ -14963,10 +14960,10 @@
       <c r="S147" s="8">
         <v>99.99</v>
       </c>
-      <c r="T147" s="27" t="s">
+      <c r="T147" s="26" t="s">
         <v>934</v>
       </c>
-      <c r="U147" s="27" t="s">
+      <c r="U147" s="26" t="s">
         <v>934</v>
       </c>
       <c r="X147" s="8"/>
@@ -15034,10 +15031,10 @@
       <c r="S148" s="8">
         <v>99.99</v>
       </c>
-      <c r="T148" s="27" t="s">
+      <c r="T148" s="26" t="s">
         <v>942</v>
       </c>
-      <c r="U148" s="27" t="s">
+      <c r="U148" s="26" t="s">
         <v>942</v>
       </c>
       <c r="X148" s="8"/>
@@ -15105,10 +15102,10 @@
       <c r="S149" s="8">
         <v>99.99</v>
       </c>
-      <c r="T149" s="27" t="s">
+      <c r="T149" s="26" t="s">
         <v>950</v>
       </c>
-      <c r="U149" s="27" t="s">
+      <c r="U149" s="26" t="s">
         <v>950</v>
       </c>
       <c r="X149" s="8"/>
@@ -15176,10 +15173,10 @@
       <c r="S150" s="8">
         <v>99.99</v>
       </c>
-      <c r="T150" s="27" t="s">
+      <c r="T150" s="26" t="s">
         <v>958</v>
       </c>
-      <c r="U150" s="27" t="s">
+      <c r="U150" s="26" t="s">
         <v>958</v>
       </c>
       <c r="X150" s="8"/>
@@ -15246,10 +15243,10 @@
       <c r="S151" s="8">
         <v>99.99</v>
       </c>
-      <c r="T151" s="27" t="s">
+      <c r="T151" s="26" t="s">
         <v>967</v>
       </c>
-      <c r="U151" s="27" t="s">
+      <c r="U151" s="26" t="s">
         <v>967</v>
       </c>
       <c r="V151" s="8"/>
@@ -15318,10 +15315,10 @@
       <c r="S152" s="8">
         <v>99.99</v>
       </c>
-      <c r="T152" s="27" t="s">
+      <c r="T152" s="26" t="s">
         <v>976</v>
       </c>
-      <c r="U152" s="27" t="s">
+      <c r="U152" s="26" t="s">
         <v>976</v>
       </c>
       <c r="V152" s="8"/>
@@ -15390,10 +15387,10 @@
       <c r="S153" s="8">
         <v>99.99</v>
       </c>
-      <c r="T153" s="27" t="s">
+      <c r="T153" s="26" t="s">
         <v>985</v>
       </c>
-      <c r="U153" s="27" t="s">
+      <c r="U153" s="26" t="s">
         <v>985</v>
       </c>
       <c r="V153" s="8"/>
@@ -15462,10 +15459,10 @@
       <c r="S154" s="8">
         <v>99.99</v>
       </c>
-      <c r="T154" s="27" t="s">
+      <c r="T154" s="26" t="s">
         <v>994</v>
       </c>
-      <c r="U154" s="27" t="s">
+      <c r="U154" s="26" t="s">
         <v>994</v>
       </c>
       <c r="V154" s="8"/>
@@ -15534,10 +15531,10 @@
       <c r="S155" s="8">
         <v>99.99</v>
       </c>
-      <c r="T155" s="27" t="s">
+      <c r="T155" s="26" t="s">
         <v>1003</v>
       </c>
-      <c r="U155" s="27" t="s">
+      <c r="U155" s="26" t="s">
         <v>1003</v>
       </c>
       <c r="V155" s="8"/>
@@ -15606,10 +15603,10 @@
       <c r="S156" s="8">
         <v>99.99</v>
       </c>
-      <c r="T156" s="27" t="s">
+      <c r="T156" s="26" t="s">
         <v>1012</v>
       </c>
-      <c r="U156" s="27" t="s">
+      <c r="U156" s="26" t="s">
         <v>1012</v>
       </c>
       <c r="V156" s="8"/>
@@ -15678,10 +15675,10 @@
       <c r="S157" s="8">
         <v>99.99</v>
       </c>
-      <c r="T157" s="27" t="s">
+      <c r="T157" s="26" t="s">
         <v>1021</v>
       </c>
-      <c r="U157" s="27" t="s">
+      <c r="U157" s="26" t="s">
         <v>1021</v>
       </c>
       <c r="V157" s="8"/>
@@ -15750,10 +15747,10 @@
       <c r="S158" s="8">
         <v>99.99</v>
       </c>
-      <c r="T158" s="27" t="s">
+      <c r="T158" s="26" t="s">
         <v>1030</v>
       </c>
-      <c r="U158" s="27" t="s">
+      <c r="U158" s="26" t="s">
         <v>1030</v>
       </c>
       <c r="V158" s="8"/>
@@ -15822,10 +15819,10 @@
       <c r="S159" s="8">
         <v>99.99</v>
       </c>
-      <c r="T159" s="27" t="s">
+      <c r="T159" s="26" t="s">
         <v>1039</v>
       </c>
-      <c r="U159" s="27" t="s">
+      <c r="U159" s="26" t="s">
         <v>1039</v>
       </c>
       <c r="V159" s="8"/>
@@ -15894,10 +15891,10 @@
       <c r="S160" s="8">
         <v>99.99</v>
       </c>
-      <c r="T160" s="27" t="s">
+      <c r="T160" s="26" t="s">
         <v>1048</v>
       </c>
-      <c r="U160" s="27" t="s">
+      <c r="U160" s="26" t="s">
         <v>1048</v>
       </c>
       <c r="V160" s="8"/>
@@ -15966,10 +15963,10 @@
       <c r="S161" s="8">
         <v>99.99</v>
       </c>
-      <c r="T161" s="27" t="s">
+      <c r="T161" s="26" t="s">
         <v>1057</v>
       </c>
-      <c r="U161" s="27" t="s">
+      <c r="U161" s="26" t="s">
         <v>1057</v>
       </c>
       <c r="V161" s="8"/>
@@ -16038,10 +16035,10 @@
       <c r="S162" s="8">
         <v>99.99</v>
       </c>
-      <c r="T162" s="27" t="s">
+      <c r="T162" s="26" t="s">
         <v>1066</v>
       </c>
-      <c r="U162" s="27" t="s">
+      <c r="U162" s="26" t="s">
         <v>1066</v>
       </c>
       <c r="V162" s="8"/>
@@ -16110,10 +16107,10 @@
       <c r="S163" s="8">
         <v>99.99</v>
       </c>
-      <c r="T163" s="27" t="s">
+      <c r="T163" s="26" t="s">
         <v>1075</v>
       </c>
-      <c r="U163" s="27" t="s">
+      <c r="U163" s="26" t="s">
         <v>1075</v>
       </c>
       <c r="V163" s="8"/>
@@ -16182,10 +16179,10 @@
       <c r="S164" s="18">
         <v>99.99</v>
       </c>
-      <c r="T164" s="34" t="s">
+      <c r="T164" s="33" t="s">
         <v>1084</v>
       </c>
-      <c r="U164" s="34" t="s">
+      <c r="U164" s="33" t="s">
         <v>1084</v>
       </c>
       <c r="V164" s="18"/>
@@ -16209,7 +16206,7 @@
       <c r="F165" s="4" t="s">
         <v>1087</v>
       </c>
-      <c r="G165" s="35" t="s">
+      <c r="G165" s="34" t="s">
         <v>1088</v>
       </c>
       <c r="H165" s="4" t="s">
@@ -16254,10 +16251,10 @@
       <c r="S165" s="19">
         <v>99.99</v>
       </c>
-      <c r="T165" s="36" t="s">
+      <c r="T165" s="35" t="s">
         <v>1093</v>
       </c>
-      <c r="U165" s="36" t="s">
+      <c r="U165" s="35" t="s">
         <v>1093</v>
       </c>
       <c r="V165" s="19"/>
@@ -16279,19 +16276,19 @@
       <c r="F166" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="G166" s="37" t="s">
+      <c r="G166" s="36" t="s">
         <v>1097</v>
       </c>
-      <c r="H166" s="37" t="s">
+      <c r="H166" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="I166" s="37" t="s">
+      <c r="I166" s="36" t="s">
         <v>1099</v>
       </c>
-      <c r="J166" s="37" t="s">
+      <c r="J166" s="36" t="s">
         <v>1100</v>
       </c>
-      <c r="K166" s="37" t="s">
+      <c r="K166" s="36" t="s">
         <v>1101</v>
       </c>
       <c r="L166" s="1">
@@ -16324,10 +16321,10 @@
       <c r="S166" s="8">
         <v>99.99</v>
       </c>
-      <c r="T166" s="27" t="s">
+      <c r="T166" s="26" t="s">
         <v>1102</v>
       </c>
-      <c r="U166" s="27" t="s">
+      <c r="U166" s="26" t="s">
         <v>1102</v>
       </c>
     </row>
@@ -16344,19 +16341,19 @@
       <c r="F167" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="G167" s="37" t="s">
+      <c r="G167" s="36" t="s">
         <v>1106</v>
       </c>
-      <c r="H167" s="37" t="s">
+      <c r="H167" s="36" t="s">
         <v>1107</v>
       </c>
-      <c r="I167" s="37" t="s">
+      <c r="I167" s="36" t="s">
         <v>1108</v>
       </c>
-      <c r="J167" s="37" t="s">
+      <c r="J167" s="36" t="s">
         <v>1109</v>
       </c>
-      <c r="K167" s="37" t="s">
+      <c r="K167" s="36" t="s">
         <v>1110</v>
       </c>
       <c r="L167" s="1">
@@ -16389,10 +16386,10 @@
       <c r="S167" s="8">
         <v>99.99</v>
       </c>
-      <c r="T167" s="27" t="s">
+      <c r="T167" s="26" t="s">
         <v>1111</v>
       </c>
-      <c r="U167" s="27" t="s">
+      <c r="U167" s="26" t="s">
         <v>1111</v>
       </c>
     </row>
@@ -16409,19 +16406,19 @@
       <c r="F168" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="G168" s="37" t="s">
+      <c r="G168" s="36" t="s">
         <v>1115</v>
       </c>
-      <c r="H168" s="37" t="s">
+      <c r="H168" s="36" t="s">
         <v>1116</v>
       </c>
-      <c r="I168" s="37" t="s">
+      <c r="I168" s="36" t="s">
         <v>1117</v>
       </c>
-      <c r="J168" s="37" t="s">
+      <c r="J168" s="36" t="s">
         <v>1118</v>
       </c>
-      <c r="K168" s="37" t="s">
+      <c r="K168" s="36" t="s">
         <v>1119</v>
       </c>
       <c r="L168" s="1">
@@ -16454,10 +16451,10 @@
       <c r="S168" s="8">
         <v>99.99</v>
       </c>
-      <c r="T168" s="27" t="s">
+      <c r="T168" s="26" t="s">
         <v>1120</v>
       </c>
-      <c r="U168" s="27" t="s">
+      <c r="U168" s="26" t="s">
         <v>1120</v>
       </c>
     </row>
@@ -16474,19 +16471,19 @@
       <c r="F169" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="G169" s="37" t="s">
+      <c r="G169" s="36" t="s">
         <v>1124</v>
       </c>
-      <c r="H169" s="37" t="s">
+      <c r="H169" s="36" t="s">
         <v>1125</v>
       </c>
-      <c r="I169" s="37" t="s">
+      <c r="I169" s="36" t="s">
         <v>1126</v>
       </c>
-      <c r="J169" s="37" t="s">
+      <c r="J169" s="36" t="s">
         <v>1127</v>
       </c>
-      <c r="K169" s="37" t="s">
+      <c r="K169" s="36" t="s">
         <v>1128</v>
       </c>
       <c r="L169" s="1">
@@ -16519,10 +16516,10 @@
       <c r="S169" s="8">
         <v>99.99</v>
       </c>
-      <c r="T169" s="27" t="s">
+      <c r="T169" s="26" t="s">
         <v>1129</v>
       </c>
-      <c r="U169" s="27" t="s">
+      <c r="U169" s="26" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -16539,19 +16536,19 @@
       <c r="F170" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="G170" s="37" t="s">
+      <c r="G170" s="36" t="s">
         <v>1133</v>
       </c>
-      <c r="H170" s="37" t="s">
+      <c r="H170" s="36" t="s">
         <v>1134</v>
       </c>
-      <c r="I170" s="37" t="s">
+      <c r="I170" s="36" t="s">
         <v>1135</v>
       </c>
-      <c r="J170" s="37" t="s">
+      <c r="J170" s="36" t="s">
         <v>1136</v>
       </c>
-      <c r="K170" s="37" t="s">
+      <c r="K170" s="36" t="s">
         <v>1137</v>
       </c>
       <c r="L170" s="1">
@@ -16584,10 +16581,10 @@
       <c r="S170" s="8">
         <v>99.99</v>
       </c>
-      <c r="T170" s="27" t="s">
+      <c r="T170" s="26" t="s">
         <v>1138</v>
       </c>
-      <c r="U170" s="27" t="s">
+      <c r="U170" s="26" t="s">
         <v>1138</v>
       </c>
     </row>
@@ -16604,19 +16601,19 @@
       <c r="F171" s="1" t="s">
         <v>1141</v>
       </c>
-      <c r="G171" s="37" t="s">
+      <c r="G171" s="36" t="s">
         <v>1142</v>
       </c>
-      <c r="H171" s="37" t="s">
+      <c r="H171" s="36" t="s">
         <v>1143</v>
       </c>
-      <c r="I171" s="37" t="s">
+      <c r="I171" s="36" t="s">
         <v>1144</v>
       </c>
-      <c r="J171" s="37" t="s">
+      <c r="J171" s="36" t="s">
         <v>1145</v>
       </c>
-      <c r="K171" s="37" t="s">
+      <c r="K171" s="36" t="s">
         <v>1146</v>
       </c>
       <c r="L171" s="1">
@@ -16649,10 +16646,10 @@
       <c r="S171" s="8">
         <v>99.99</v>
       </c>
-      <c r="T171" s="27" t="s">
+      <c r="T171" s="26" t="s">
         <v>1147</v>
       </c>
-      <c r="U171" s="27" t="s">
+      <c r="U171" s="26" t="s">
         <v>1147</v>
       </c>
     </row>
@@ -16669,19 +16666,19 @@
       <c r="F172" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="G172" s="37" t="s">
+      <c r="G172" s="36" t="s">
         <v>1151</v>
       </c>
-      <c r="H172" s="37" t="s">
+      <c r="H172" s="36" t="s">
         <v>1152</v>
       </c>
-      <c r="I172" s="37" t="s">
+      <c r="I172" s="36" t="s">
         <v>1153</v>
       </c>
-      <c r="J172" s="37" t="s">
+      <c r="J172" s="36" t="s">
         <v>1154</v>
       </c>
-      <c r="K172" s="37" t="s">
+      <c r="K172" s="36" t="s">
         <v>1155</v>
       </c>
       <c r="L172" s="1">
@@ -16714,10 +16711,10 @@
       <c r="S172" s="8">
         <v>99.99</v>
       </c>
-      <c r="T172" s="27" t="s">
+      <c r="T172" s="26" t="s">
         <v>1156</v>
       </c>
-      <c r="U172" s="27" t="s">
+      <c r="U172" s="26" t="s">
         <v>1156</v>
       </c>
     </row>
@@ -16734,19 +16731,19 @@
       <c r="F173" s="1" t="s">
         <v>1159</v>
       </c>
-      <c r="G173" s="37" t="s">
+      <c r="G173" s="36" t="s">
         <v>1160</v>
       </c>
-      <c r="H173" s="37" t="s">
+      <c r="H173" s="36" t="s">
         <v>1161</v>
       </c>
-      <c r="I173" s="37" t="s">
+      <c r="I173" s="36" t="s">
         <v>1162</v>
       </c>
-      <c r="J173" s="37" t="s">
+      <c r="J173" s="36" t="s">
         <v>1163</v>
       </c>
-      <c r="K173" s="37" t="s">
+      <c r="K173" s="36" t="s">
         <v>1164</v>
       </c>
       <c r="L173" s="1">
@@ -16779,10 +16776,10 @@
       <c r="S173" s="8">
         <v>99.99</v>
       </c>
-      <c r="T173" s="27" t="s">
+      <c r="T173" s="26" t="s">
         <v>1165</v>
       </c>
-      <c r="U173" s="27" t="s">
+      <c r="U173" s="26" t="s">
         <v>1165</v>
       </c>
     </row>
@@ -16799,19 +16796,19 @@
       <c r="F174" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="G174" s="37" t="s">
+      <c r="G174" s="36" t="s">
         <v>1169</v>
       </c>
-      <c r="H174" s="37" t="s">
+      <c r="H174" s="36" t="s">
         <v>1170</v>
       </c>
-      <c r="I174" s="37" t="s">
+      <c r="I174" s="36" t="s">
         <v>1171</v>
       </c>
-      <c r="J174" s="37" t="s">
+      <c r="J174" s="36" t="s">
         <v>1172</v>
       </c>
-      <c r="K174" s="37" t="s">
+      <c r="K174" s="36" t="s">
         <v>1173</v>
       </c>
       <c r="L174" s="1">
@@ -16844,10 +16841,10 @@
       <c r="S174" s="8">
         <v>99.99</v>
       </c>
-      <c r="T174" s="27" t="s">
+      <c r="T174" s="26" t="s">
         <v>1174</v>
       </c>
-      <c r="U174" s="27" t="s">
+      <c r="U174" s="26" t="s">
         <v>1174</v>
       </c>
     </row>
@@ -16864,19 +16861,19 @@
       <c r="F175" s="1" t="s">
         <v>1177</v>
       </c>
-      <c r="G175" s="37" t="s">
+      <c r="G175" s="36" t="s">
         <v>1178</v>
       </c>
-      <c r="H175" s="37" t="s">
+      <c r="H175" s="36" t="s">
         <v>1179</v>
       </c>
-      <c r="I175" s="37" t="s">
+      <c r="I175" s="36" t="s">
         <v>1180</v>
       </c>
-      <c r="J175" s="37" t="s">
+      <c r="J175" s="36" t="s">
         <v>1181</v>
       </c>
-      <c r="K175" s="37" t="s">
+      <c r="K175" s="36" t="s">
         <v>1182</v>
       </c>
       <c r="L175" s="1">
@@ -16909,10 +16906,10 @@
       <c r="S175" s="8">
         <v>99.99</v>
       </c>
-      <c r="T175" s="27" t="s">
+      <c r="T175" s="26" t="s">
         <v>1183</v>
       </c>
-      <c r="U175" s="27" t="s">
+      <c r="U175" s="26" t="s">
         <v>1183</v>
       </c>
     </row>
@@ -16931,19 +16928,19 @@
       <c r="F176" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="G176" s="37" t="s">
+      <c r="G176" s="36" t="s">
         <v>1187</v>
       </c>
-      <c r="H176" s="37" t="s">
+      <c r="H176" s="36" t="s">
         <v>1188</v>
       </c>
-      <c r="I176" s="37" t="s">
+      <c r="I176" s="36" t="s">
         <v>1189</v>
       </c>
-      <c r="J176" s="37" t="s">
+      <c r="J176" s="36" t="s">
         <v>1190</v>
       </c>
-      <c r="K176" s="37" t="s">
+      <c r="K176" s="36" t="s">
         <v>1191</v>
       </c>
       <c r="L176" s="1">
@@ -16976,10 +16973,10 @@
       <c r="S176" s="8">
         <v>99.99</v>
       </c>
-      <c r="T176" s="27" t="s">
+      <c r="T176" s="26" t="s">
         <v>1192</v>
       </c>
-      <c r="U176" s="27" t="s">
+      <c r="U176" s="26" t="s">
         <v>1192</v>
       </c>
       <c r="V176" s="8"/>
@@ -17003,19 +17000,19 @@
       <c r="F177" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="G177" s="37" t="s">
+      <c r="G177" s="36" t="s">
         <v>1196</v>
       </c>
-      <c r="H177" s="37" t="s">
+      <c r="H177" s="36" t="s">
         <v>1197</v>
       </c>
-      <c r="I177" s="37" t="s">
+      <c r="I177" s="36" t="s">
         <v>1198</v>
       </c>
-      <c r="J177" s="37" t="s">
+      <c r="J177" s="36" t="s">
         <v>1199</v>
       </c>
-      <c r="K177" s="37" t="s">
+      <c r="K177" s="36" t="s">
         <v>1200</v>
       </c>
       <c r="L177" s="1">
@@ -17048,10 +17045,10 @@
       <c r="S177" s="8">
         <v>99.99</v>
       </c>
-      <c r="T177" s="27" t="s">
+      <c r="T177" s="26" t="s">
         <v>1201</v>
       </c>
-      <c r="U177" s="27" t="s">
+      <c r="U177" s="26" t="s">
         <v>1201</v>
       </c>
       <c r="V177" s="8"/>
@@ -17075,19 +17072,19 @@
       <c r="F178" s="1" t="s">
         <v>1204</v>
       </c>
-      <c r="G178" s="37" t="s">
+      <c r="G178" s="36" t="s">
         <v>1205</v>
       </c>
-      <c r="H178" s="37" t="s">
+      <c r="H178" s="36" t="s">
         <v>1206</v>
       </c>
-      <c r="I178" s="37" t="s">
+      <c r="I178" s="36" t="s">
         <v>1207</v>
       </c>
-      <c r="J178" s="37" t="s">
+      <c r="J178" s="36" t="s">
         <v>1208</v>
       </c>
-      <c r="K178" s="37" t="s">
+      <c r="K178" s="36" t="s">
         <v>1209</v>
       </c>
       <c r="L178" s="1">
@@ -17120,10 +17117,10 @@
       <c r="S178" s="8">
         <v>99.99</v>
       </c>
-      <c r="T178" s="27" t="s">
+      <c r="T178" s="26" t="s">
         <v>1210</v>
       </c>
-      <c r="U178" s="27" t="s">
+      <c r="U178" s="26" t="s">
         <v>1210</v>
       </c>
       <c r="V178" s="8"/>
@@ -17147,19 +17144,19 @@
       <c r="F179" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="G179" s="37" t="s">
+      <c r="G179" s="36" t="s">
         <v>1214</v>
       </c>
-      <c r="H179" s="37" t="s">
+      <c r="H179" s="36" t="s">
         <v>1215</v>
       </c>
-      <c r="I179" s="37" t="s">
+      <c r="I179" s="36" t="s">
         <v>1216</v>
       </c>
-      <c r="J179" s="37" t="s">
+      <c r="J179" s="36" t="s">
         <v>1217</v>
       </c>
-      <c r="K179" s="37" t="s">
+      <c r="K179" s="36" t="s">
         <v>1218</v>
       </c>
       <c r="L179" s="1">
@@ -17192,10 +17189,10 @@
       <c r="S179" s="8">
         <v>99.99</v>
       </c>
-      <c r="T179" s="27" t="s">
+      <c r="T179" s="26" t="s">
         <v>1219</v>
       </c>
-      <c r="U179" s="27" t="s">
+      <c r="U179" s="26" t="s">
         <v>1219</v>
       </c>
       <c r="V179" s="8"/>
@@ -17219,19 +17216,19 @@
       <c r="F180" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="G180" s="37" t="s">
+      <c r="G180" s="36" t="s">
         <v>1223</v>
       </c>
-      <c r="H180" s="37" t="s">
+      <c r="H180" s="36" t="s">
         <v>1224</v>
       </c>
-      <c r="I180" s="37" t="s">
+      <c r="I180" s="36" t="s">
         <v>1225</v>
       </c>
-      <c r="J180" s="37" t="s">
+      <c r="J180" s="36" t="s">
         <v>1226</v>
       </c>
-      <c r="K180" s="37" t="s">
+      <c r="K180" s="36" t="s">
         <v>1227</v>
       </c>
       <c r="L180" s="1">
@@ -17264,10 +17261,10 @@
       <c r="S180" s="8">
         <v>99.99</v>
       </c>
-      <c r="T180" s="27" t="s">
+      <c r="T180" s="26" t="s">
         <v>1228</v>
       </c>
-      <c r="U180" s="27" t="s">
+      <c r="U180" s="26" t="s">
         <v>1228</v>
       </c>
       <c r="V180" s="8"/>
@@ -17291,50 +17288,51 @@
       <c r="F181" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="G181" s="38" t="s">
+      <c r="G181" s="37" t="s">
         <v>1230</v>
       </c>
-      <c r="H181" s="38" t="s">
+      <c r="H181" s="37" t="s">
         <v>1231</v>
       </c>
-      <c r="I181" s="38" t="s">
+      <c r="I181" s="37" t="s">
         <v>1232</v>
       </c>
-      <c r="J181" s="38" t="s">
+      <c r="J181" s="37" t="s">
         <v>1233</v>
       </c>
-      <c r="K181" s="38" t="s">
+      <c r="K181" s="37" t="s">
         <v>1234</v>
       </c>
       <c r="L181" s="2">
-        <v>40000</v>
+        <v>43000</v>
       </c>
       <c r="M181" s="2">
-        <v>40000</v>
+        <v>43000</v>
       </c>
       <c r="N181" s="2">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="O181" s="2">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="P181" s="2">
         <v>50</v>
       </c>
       <c r="Q181" s="16">
-        <f t="shared" ref="Q181:Q195" si="58">Q180+3</f>
-        <v>237</v>
+        <f t="shared" ref="Q181:Q185" si="58">Q180+9</f>
+        <v>243</v>
       </c>
       <c r="R181" s="16">
-        <v>150</v>
+        <f t="shared" ref="R181:R185" si="59">R180+10</f>
+        <v>346</v>
       </c>
       <c r="S181" s="16">
         <v>99.99</v>
       </c>
-      <c r="T181" s="33" t="s">
+      <c r="T181" s="32" t="s">
         <v>1235</v>
       </c>
-      <c r="U181" s="33" t="s">
+      <c r="U181" s="32" t="s">
         <v>1235</v>
       </c>
       <c r="X181" s="16"/>
@@ -17342,8 +17340,8 @@
       <c r="Z181" s="16"/>
     </row>
     <row r="182" s="5" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A182" s="23"/>
-      <c r="B182" s="23"/>
+      <c r="A182" s="10"/>
+      <c r="B182" s="10"/>
       <c r="C182" s="5">
         <v>10177</v>
       </c>
@@ -17356,65 +17354,65 @@
       <c r="F182" s="5" t="s">
         <v>1236</v>
       </c>
-      <c r="G182" s="39" t="s">
+      <c r="G182" s="36" t="s">
         <v>1237</v>
       </c>
-      <c r="H182" s="39" t="s">
+      <c r="H182" s="36" t="s">
         <v>1238</v>
       </c>
-      <c r="I182" s="39" t="s">
+      <c r="I182" s="36" t="s">
         <v>1239</v>
       </c>
-      <c r="J182" s="39" t="s">
+      <c r="J182" s="36" t="s">
         <v>1240</v>
       </c>
-      <c r="K182" s="39" t="s">
+      <c r="K182" s="36" t="s">
         <v>1241</v>
       </c>
       <c r="L182" s="5">
-        <f t="shared" si="42"/>
-        <v>40600</v>
+        <f t="shared" ref="L182:L185" si="60">L181+1000</f>
+        <v>44000</v>
       </c>
       <c r="M182" s="5">
-        <f t="shared" si="43"/>
-        <v>40600</v>
+        <f t="shared" ref="M182:M185" si="61">M181+1000</f>
+        <v>44000</v>
       </c>
       <c r="N182" s="5">
-        <f t="shared" ref="N181:N200" si="59">N181+250</f>
-        <v>20250</v>
+        <f t="shared" ref="N182:N185" si="62">N181+500</f>
+        <v>22500</v>
       </c>
       <c r="O182" s="5">
-        <f t="shared" ref="O181:O200" si="60">O181+250</f>
-        <v>20250</v>
+        <f t="shared" ref="O182:O185" si="63">O181+500</f>
+        <v>22500</v>
       </c>
       <c r="P182" s="5">
-        <f t="shared" ref="P182:P215" si="61">P181+3</f>
+        <f t="shared" ref="P182:P215" si="64">P181+3</f>
         <v>53</v>
       </c>
-      <c r="Q182" s="23">
+      <c r="Q182" s="25">
         <f t="shared" si="58"/>
-        <v>240</v>
-      </c>
-      <c r="R182" s="23">
-        <f t="shared" ref="R182:R195" si="62">R181+4</f>
-        <v>154</v>
-      </c>
-      <c r="S182" s="23">
+        <v>252</v>
+      </c>
+      <c r="R182" s="8">
+        <f t="shared" si="59"/>
+        <v>356</v>
+      </c>
+      <c r="S182" s="10">
         <v>99.99</v>
       </c>
-      <c r="T182" s="40" t="s">
+      <c r="T182" s="38" t="s">
         <v>1242</v>
       </c>
-      <c r="U182" s="40" t="s">
+      <c r="U182" s="38" t="s">
         <v>1242</v>
       </c>
-      <c r="X182" s="23"/>
-      <c r="Y182" s="23"/>
-      <c r="Z182" s="23"/>
+      <c r="X182" s="10"/>
+      <c r="Y182" s="10"/>
+      <c r="Z182" s="10"/>
     </row>
     <row r="183" s="5" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A183" s="23"/>
-      <c r="B183" s="23"/>
+      <c r="A183" s="10"/>
+      <c r="B183" s="10"/>
       <c r="C183" s="5">
         <v>10178</v>
       </c>
@@ -17427,65 +17425,65 @@
       <c r="F183" s="5" t="s">
         <v>1243</v>
       </c>
-      <c r="G183" s="39" t="s">
+      <c r="G183" s="36" t="s">
         <v>1244</v>
       </c>
-      <c r="H183" s="39" t="s">
+      <c r="H183" s="36" t="s">
         <v>1245</v>
       </c>
-      <c r="I183" s="39" t="s">
+      <c r="I183" s="36" t="s">
         <v>1246</v>
       </c>
-      <c r="J183" s="39" t="s">
+      <c r="J183" s="36" t="s">
         <v>1247</v>
       </c>
-      <c r="K183" s="39" t="s">
+      <c r="K183" s="36" t="s">
         <v>1248</v>
       </c>
       <c r="L183" s="5">
-        <f t="shared" si="42"/>
-        <v>41200</v>
+        <f t="shared" si="60"/>
+        <v>45000</v>
       </c>
       <c r="M183" s="5">
-        <f t="shared" si="43"/>
-        <v>41200</v>
+        <f t="shared" si="61"/>
+        <v>45000</v>
       </c>
       <c r="N183" s="5">
+        <f t="shared" si="62"/>
+        <v>23000</v>
+      </c>
+      <c r="O183" s="5">
+        <f t="shared" si="63"/>
+        <v>23000</v>
+      </c>
+      <c r="P183" s="5">
+        <f t="shared" si="64"/>
+        <v>56</v>
+      </c>
+      <c r="Q183" s="25">
+        <f t="shared" si="58"/>
+        <v>261</v>
+      </c>
+      <c r="R183" s="8">
         <f t="shared" si="59"/>
-        <v>20500</v>
-      </c>
-      <c r="O183" s="5">
-        <f t="shared" si="60"/>
-        <v>20500</v>
-      </c>
-      <c r="P183" s="5">
-        <f t="shared" si="61"/>
-        <v>56</v>
-      </c>
-      <c r="Q183" s="23">
-        <f t="shared" si="58"/>
-        <v>243</v>
-      </c>
-      <c r="R183" s="23">
-        <f t="shared" si="62"/>
-        <v>158</v>
-      </c>
-      <c r="S183" s="23">
+        <v>366</v>
+      </c>
+      <c r="S183" s="10">
         <v>99.99</v>
       </c>
-      <c r="T183" s="40" t="s">
+      <c r="T183" s="38" t="s">
         <v>1249</v>
       </c>
-      <c r="U183" s="40" t="s">
+      <c r="U183" s="38" t="s">
         <v>1249</v>
       </c>
-      <c r="X183" s="23"/>
-      <c r="Y183" s="23"/>
-      <c r="Z183" s="23"/>
+      <c r="X183" s="10"/>
+      <c r="Y183" s="10"/>
+      <c r="Z183" s="10"/>
     </row>
     <row r="184" s="5" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A184" s="23"/>
-      <c r="B184" s="23"/>
+      <c r="A184" s="10"/>
+      <c r="B184" s="10"/>
       <c r="C184" s="5">
         <v>10179</v>
       </c>
@@ -17498,65 +17496,65 @@
       <c r="F184" s="5" t="s">
         <v>1250</v>
       </c>
-      <c r="G184" s="39" t="s">
+      <c r="G184" s="36" t="s">
         <v>1251</v>
       </c>
-      <c r="H184" s="39" t="s">
+      <c r="H184" s="36" t="s">
         <v>1252</v>
       </c>
-      <c r="I184" s="39" t="s">
+      <c r="I184" s="36" t="s">
         <v>1253</v>
       </c>
-      <c r="J184" s="39" t="s">
+      <c r="J184" s="36" t="s">
         <v>1254</v>
       </c>
-      <c r="K184" s="39" t="s">
+      <c r="K184" s="36" t="s">
         <v>1255</v>
       </c>
       <c r="L184" s="5">
-        <f t="shared" si="42"/>
-        <v>41800</v>
+        <f t="shared" si="60"/>
+        <v>46000</v>
       </c>
       <c r="M184" s="5">
-        <f t="shared" si="43"/>
-        <v>41800</v>
+        <f t="shared" si="61"/>
+        <v>46000</v>
       </c>
       <c r="N184" s="5">
+        <f t="shared" si="62"/>
+        <v>23500</v>
+      </c>
+      <c r="O184" s="5">
+        <f t="shared" si="63"/>
+        <v>23500</v>
+      </c>
+      <c r="P184" s="5">
+        <f t="shared" si="64"/>
+        <v>59</v>
+      </c>
+      <c r="Q184" s="25">
+        <f t="shared" si="58"/>
+        <v>270</v>
+      </c>
+      <c r="R184" s="8">
         <f t="shared" si="59"/>
-        <v>20750</v>
-      </c>
-      <c r="O184" s="5">
-        <f t="shared" si="60"/>
-        <v>20750</v>
-      </c>
-      <c r="P184" s="5">
-        <f t="shared" si="61"/>
-        <v>59</v>
-      </c>
-      <c r="Q184" s="23">
-        <f t="shared" si="58"/>
-        <v>246</v>
-      </c>
-      <c r="R184" s="23">
-        <f t="shared" si="62"/>
-        <v>162</v>
-      </c>
-      <c r="S184" s="23">
+        <v>376</v>
+      </c>
+      <c r="S184" s="10">
         <v>99.99</v>
       </c>
-      <c r="T184" s="40" t="s">
+      <c r="T184" s="38" t="s">
         <v>1256</v>
       </c>
-      <c r="U184" s="40" t="s">
+      <c r="U184" s="38" t="s">
         <v>1256</v>
       </c>
-      <c r="X184" s="23"/>
-      <c r="Y184" s="23"/>
-      <c r="Z184" s="23"/>
+      <c r="X184" s="10"/>
+      <c r="Y184" s="10"/>
+      <c r="Z184" s="10"/>
     </row>
     <row r="185" s="5" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A185" s="23"/>
-      <c r="B185" s="23"/>
+      <c r="A185" s="10"/>
+      <c r="B185" s="10"/>
       <c r="C185" s="5">
         <v>10180</v>
       </c>
@@ -17569,61 +17567,61 @@
       <c r="F185" s="5" t="s">
         <v>1257</v>
       </c>
-      <c r="G185" s="39" t="s">
+      <c r="G185" s="36" t="s">
         <v>1258</v>
       </c>
-      <c r="H185" s="39" t="s">
+      <c r="H185" s="36" t="s">
         <v>1259</v>
       </c>
-      <c r="I185" s="39" t="s">
+      <c r="I185" s="36" t="s">
         <v>1260</v>
       </c>
-      <c r="J185" s="39" t="s">
+      <c r="J185" s="36" t="s">
         <v>1261</v>
       </c>
-      <c r="K185" s="39" t="s">
-        <v>1230</v>
+      <c r="K185" s="36" t="s">
+        <v>1262</v>
       </c>
       <c r="L185" s="5">
-        <f t="shared" si="42"/>
-        <v>42400</v>
+        <f t="shared" si="60"/>
+        <v>47000</v>
       </c>
       <c r="M185" s="5">
-        <f t="shared" si="43"/>
-        <v>42400</v>
+        <f t="shared" si="61"/>
+        <v>47000</v>
       </c>
       <c r="N185" s="5">
+        <f t="shared" si="62"/>
+        <v>24000</v>
+      </c>
+      <c r="O185" s="5">
+        <f t="shared" si="63"/>
+        <v>24000</v>
+      </c>
+      <c r="P185" s="5">
+        <f t="shared" si="64"/>
+        <v>62</v>
+      </c>
+      <c r="Q185" s="25">
+        <f t="shared" si="58"/>
+        <v>279</v>
+      </c>
+      <c r="R185" s="8">
         <f t="shared" si="59"/>
-        <v>21000</v>
-      </c>
-      <c r="O185" s="5">
-        <f t="shared" si="60"/>
-        <v>21000</v>
-      </c>
-      <c r="P185" s="5">
-        <f t="shared" si="61"/>
-        <v>62</v>
-      </c>
-      <c r="Q185" s="23">
-        <f t="shared" si="58"/>
-        <v>249</v>
-      </c>
-      <c r="R185" s="23">
-        <f t="shared" si="62"/>
-        <v>166</v>
-      </c>
-      <c r="S185" s="23">
+        <v>386</v>
+      </c>
+      <c r="S185" s="10">
         <v>99.99</v>
       </c>
-      <c r="T185" s="40" t="s">
-        <v>1262</v>
-      </c>
-      <c r="U185" s="40" t="s">
-        <v>1262</v>
-      </c>
-      <c r="X185" s="23"/>
-      <c r="Y185" s="23"/>
-      <c r="Z185" s="23"/>
+      <c r="T185" s="38" t="s">
+        <v>1263</v>
+      </c>
+      <c r="U185" s="38" t="s">
+        <v>1263</v>
+      </c>
+      <c r="X185" s="10"/>
+      <c r="Y185" s="10"/>
+      <c r="Z185" s="10"/>
     </row>
     <row r="186" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A186" s="7"/>
@@ -17638,58 +17636,58 @@
         <v>6</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>1263</v>
-      </c>
-      <c r="G186" s="41" t="s">
         <v>1264</v>
       </c>
-      <c r="H186" s="41" t="s">
+      <c r="G186" s="39" t="s">
         <v>1265</v>
       </c>
-      <c r="I186" s="41" t="s">
+      <c r="H186" s="39" t="s">
         <v>1266</v>
       </c>
-      <c r="J186" s="41" t="s">
+      <c r="I186" s="39" t="s">
         <v>1267</v>
       </c>
-      <c r="K186" s="41" t="s">
+      <c r="J186" s="39" t="s">
         <v>1268</v>
+      </c>
+      <c r="K186" s="39" t="s">
+        <v>1269</v>
       </c>
       <c r="L186" s="6">
         <f t="shared" si="42"/>
-        <v>43000</v>
+        <v>47600</v>
       </c>
       <c r="M186" s="6">
         <f t="shared" si="43"/>
-        <v>43000</v>
+        <v>47600</v>
       </c>
       <c r="N186" s="6">
-        <f t="shared" si="59"/>
-        <v>21250</v>
+        <f t="shared" ref="N181:N200" si="65">N185+250</f>
+        <v>24250</v>
       </c>
       <c r="O186" s="6">
-        <f t="shared" si="60"/>
-        <v>21250</v>
+        <f t="shared" ref="O181:O200" si="66">O185+250</f>
+        <v>24250</v>
       </c>
       <c r="P186" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>65</v>
       </c>
       <c r="Q186" s="7">
-        <f t="shared" si="58"/>
-        <v>252</v>
+        <f t="shared" ref="Q181:Q195" si="67">Q185+3</f>
+        <v>282</v>
       </c>
       <c r="R186" s="7">
-        <f t="shared" si="62"/>
-        <v>170</v>
+        <f t="shared" ref="R182:R195" si="68">R185+4</f>
+        <v>390</v>
       </c>
       <c r="S186" s="7">
         <v>99.99</v>
       </c>
-      <c r="T186" s="42" t="s">
+      <c r="T186" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U186" s="42" t="s">
+      <c r="U186" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V186" s="7"/>
@@ -17711,58 +17709,58 @@
         <v>6</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>1269</v>
-      </c>
-      <c r="G187" s="41" t="s">
         <v>1270</v>
       </c>
-      <c r="H187" s="41" t="s">
+      <c r="G187" s="39" t="s">
         <v>1271</v>
       </c>
-      <c r="I187" s="41" t="s">
+      <c r="H187" s="39" t="s">
         <v>1272</v>
       </c>
-      <c r="J187" s="41" t="s">
+      <c r="I187" s="39" t="s">
         <v>1273</v>
       </c>
-      <c r="K187" s="41" t="s">
+      <c r="J187" s="39" t="s">
         <v>1274</v>
+      </c>
+      <c r="K187" s="39" t="s">
+        <v>1275</v>
       </c>
       <c r="L187" s="6">
         <f t="shared" si="42"/>
-        <v>43600</v>
+        <v>48200</v>
       </c>
       <c r="M187" s="6">
         <f t="shared" si="43"/>
-        <v>43600</v>
+        <v>48200</v>
       </c>
       <c r="N187" s="6">
-        <f t="shared" si="59"/>
-        <v>21500</v>
+        <f t="shared" si="65"/>
+        <v>24500</v>
       </c>
       <c r="O187" s="6">
-        <f t="shared" si="60"/>
-        <v>21500</v>
+        <f t="shared" si="66"/>
+        <v>24500</v>
       </c>
       <c r="P187" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>68</v>
       </c>
       <c r="Q187" s="7">
-        <f t="shared" si="58"/>
-        <v>255</v>
+        <f t="shared" si="67"/>
+        <v>285</v>
       </c>
       <c r="R187" s="7">
-        <f t="shared" si="62"/>
-        <v>174</v>
+        <f t="shared" si="68"/>
+        <v>394</v>
       </c>
       <c r="S187" s="7">
         <v>99.99</v>
       </c>
-      <c r="T187" s="42" t="s">
+      <c r="T187" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U187" s="42" t="s">
+      <c r="U187" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V187" s="7"/>
@@ -17784,58 +17782,58 @@
         <v>6</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>1275</v>
-      </c>
-      <c r="G188" s="41" t="s">
         <v>1276</v>
       </c>
-      <c r="H188" s="41" t="s">
+      <c r="G188" s="39" t="s">
         <v>1277</v>
       </c>
-      <c r="I188" s="41" t="s">
+      <c r="H188" s="39" t="s">
         <v>1278</v>
       </c>
-      <c r="J188" s="41" t="s">
+      <c r="I188" s="39" t="s">
         <v>1279</v>
       </c>
-      <c r="K188" s="41" t="s">
+      <c r="J188" s="39" t="s">
         <v>1280</v>
+      </c>
+      <c r="K188" s="39" t="s">
+        <v>1281</v>
       </c>
       <c r="L188" s="6">
         <f t="shared" si="42"/>
-        <v>44200</v>
+        <v>48800</v>
       </c>
       <c r="M188" s="6">
         <f t="shared" si="43"/>
-        <v>44200</v>
+        <v>48800</v>
       </c>
       <c r="N188" s="6">
-        <f t="shared" si="59"/>
-        <v>21750</v>
+        <f t="shared" si="65"/>
+        <v>24750</v>
       </c>
       <c r="O188" s="6">
-        <f t="shared" si="60"/>
-        <v>21750</v>
+        <f t="shared" si="66"/>
+        <v>24750</v>
       </c>
       <c r="P188" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>71</v>
       </c>
       <c r="Q188" s="7">
-        <f t="shared" si="58"/>
-        <v>258</v>
+        <f t="shared" si="67"/>
+        <v>288</v>
       </c>
       <c r="R188" s="7">
-        <f t="shared" si="62"/>
-        <v>178</v>
+        <f t="shared" si="68"/>
+        <v>398</v>
       </c>
       <c r="S188" s="7">
         <v>99.99</v>
       </c>
-      <c r="T188" s="42" t="s">
+      <c r="T188" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U188" s="42" t="s">
+      <c r="U188" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V188" s="7"/>
@@ -17857,58 +17855,58 @@
         <v>6</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>1281</v>
-      </c>
-      <c r="G189" s="41" t="s">
+        <v>1282</v>
+      </c>
+      <c r="G189" s="39" t="s">
         <v>1098</v>
       </c>
-      <c r="H189" s="41" t="s">
-        <v>1282</v>
-      </c>
-      <c r="I189" s="41" t="s">
+      <c r="H189" s="39" t="s">
         <v>1283</v>
       </c>
-      <c r="J189" s="41" t="s">
+      <c r="I189" s="39" t="s">
         <v>1284</v>
       </c>
-      <c r="K189" s="41" t="s">
+      <c r="J189" s="39" t="s">
         <v>1285</v>
+      </c>
+      <c r="K189" s="39" t="s">
+        <v>1286</v>
       </c>
       <c r="L189" s="6">
         <f t="shared" si="42"/>
-        <v>44800</v>
+        <v>49400</v>
       </c>
       <c r="M189" s="6">
         <f t="shared" si="43"/>
-        <v>44800</v>
+        <v>49400</v>
       </c>
       <c r="N189" s="6">
-        <f t="shared" si="59"/>
-        <v>22000</v>
+        <f t="shared" si="65"/>
+        <v>25000</v>
       </c>
       <c r="O189" s="6">
-        <f t="shared" si="60"/>
-        <v>22000</v>
+        <f t="shared" si="66"/>
+        <v>25000</v>
       </c>
       <c r="P189" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>74</v>
       </c>
       <c r="Q189" s="7">
-        <f t="shared" si="58"/>
-        <v>261</v>
+        <f t="shared" si="67"/>
+        <v>291</v>
       </c>
       <c r="R189" s="7">
-        <f t="shared" si="62"/>
-        <v>182</v>
+        <f t="shared" si="68"/>
+        <v>402</v>
       </c>
       <c r="S189" s="7">
         <v>99.99</v>
       </c>
-      <c r="T189" s="42" t="s">
+      <c r="T189" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U189" s="42" t="s">
+      <c r="U189" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V189" s="7"/>
@@ -17930,58 +17928,58 @@
         <v>6</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>1286</v>
-      </c>
-      <c r="G190" s="41" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G190" s="39" t="s">
         <v>1107</v>
       </c>
-      <c r="H190" s="41" t="s">
-        <v>1287</v>
-      </c>
-      <c r="I190" s="41" t="s">
+      <c r="H190" s="39" t="s">
         <v>1288</v>
       </c>
-      <c r="J190" s="41" t="s">
+      <c r="I190" s="39" t="s">
         <v>1289</v>
       </c>
-      <c r="K190" s="41" t="s">
+      <c r="J190" s="39" t="s">
         <v>1290</v>
+      </c>
+      <c r="K190" s="39" t="s">
+        <v>1291</v>
       </c>
       <c r="L190" s="6">
         <f t="shared" si="42"/>
-        <v>45400</v>
+        <v>50000</v>
       </c>
       <c r="M190" s="6">
         <f t="shared" si="43"/>
-        <v>45400</v>
+        <v>50000</v>
       </c>
       <c r="N190" s="6">
-        <f t="shared" si="59"/>
-        <v>22250</v>
+        <f t="shared" si="65"/>
+        <v>25250</v>
       </c>
       <c r="O190" s="6">
-        <f t="shared" si="60"/>
-        <v>22250</v>
+        <f t="shared" si="66"/>
+        <v>25250</v>
       </c>
       <c r="P190" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>77</v>
       </c>
       <c r="Q190" s="7">
-        <f t="shared" si="58"/>
-        <v>264</v>
+        <f t="shared" si="67"/>
+        <v>294</v>
       </c>
       <c r="R190" s="7">
-        <f t="shared" si="62"/>
-        <v>186</v>
+        <f t="shared" si="68"/>
+        <v>406</v>
       </c>
       <c r="S190" s="7">
         <v>99.99</v>
       </c>
-      <c r="T190" s="42" t="s">
+      <c r="T190" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U190" s="42" t="s">
+      <c r="U190" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V190" s="7"/>
@@ -18003,58 +18001,58 @@
         <v>6</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>1291</v>
-      </c>
-      <c r="G191" s="41" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G191" s="39" t="s">
         <v>1116</v>
       </c>
-      <c r="H191" s="41" t="s">
-        <v>1292</v>
-      </c>
-      <c r="I191" s="41" t="s">
+      <c r="H191" s="39" t="s">
         <v>1293</v>
       </c>
-      <c r="J191" s="41" t="s">
+      <c r="I191" s="39" t="s">
         <v>1294</v>
       </c>
-      <c r="K191" s="41" t="s">
+      <c r="J191" s="39" t="s">
         <v>1295</v>
+      </c>
+      <c r="K191" s="39" t="s">
+        <v>1296</v>
       </c>
       <c r="L191" s="6">
         <f t="shared" si="42"/>
-        <v>46000</v>
+        <v>50600</v>
       </c>
       <c r="M191" s="6">
         <f t="shared" si="43"/>
-        <v>46000</v>
+        <v>50600</v>
       </c>
       <c r="N191" s="6">
-        <f t="shared" si="59"/>
-        <v>22500</v>
+        <f t="shared" si="65"/>
+        <v>25500</v>
       </c>
       <c r="O191" s="6">
-        <f t="shared" si="60"/>
-        <v>22500</v>
+        <f t="shared" si="66"/>
+        <v>25500</v>
       </c>
       <c r="P191" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>80</v>
       </c>
       <c r="Q191" s="7">
-        <f t="shared" si="58"/>
-        <v>267</v>
+        <f t="shared" si="67"/>
+        <v>297</v>
       </c>
       <c r="R191" s="7">
-        <f t="shared" si="62"/>
-        <v>190</v>
+        <f t="shared" si="68"/>
+        <v>410</v>
       </c>
       <c r="S191" s="7">
         <v>99.99</v>
       </c>
-      <c r="T191" s="42" t="s">
+      <c r="T191" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U191" s="42" t="s">
+      <c r="U191" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V191" s="7"/>
@@ -18076,58 +18074,58 @@
         <v>6</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>1296</v>
-      </c>
-      <c r="G192" s="41" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G192" s="39" t="s">
         <v>1125</v>
       </c>
-      <c r="H192" s="41" t="s">
-        <v>1297</v>
-      </c>
-      <c r="I192" s="41" t="s">
+      <c r="H192" s="39" t="s">
         <v>1298</v>
       </c>
-      <c r="J192" s="41" t="s">
+      <c r="I192" s="39" t="s">
         <v>1299</v>
       </c>
-      <c r="K192" s="41" t="s">
+      <c r="J192" s="39" t="s">
         <v>1300</v>
+      </c>
+      <c r="K192" s="39" t="s">
+        <v>1301</v>
       </c>
       <c r="L192" s="6">
         <f t="shared" si="42"/>
-        <v>46600</v>
+        <v>51200</v>
       </c>
       <c r="M192" s="6">
         <f t="shared" si="43"/>
-        <v>46600</v>
+        <v>51200</v>
       </c>
       <c r="N192" s="6">
-        <f t="shared" si="59"/>
-        <v>22750</v>
+        <f t="shared" si="65"/>
+        <v>25750</v>
       </c>
       <c r="O192" s="6">
-        <f t="shared" si="60"/>
-        <v>22750</v>
+        <f t="shared" si="66"/>
+        <v>25750</v>
       </c>
       <c r="P192" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>83</v>
       </c>
       <c r="Q192" s="7">
-        <f t="shared" si="58"/>
-        <v>270</v>
+        <f t="shared" si="67"/>
+        <v>300</v>
       </c>
       <c r="R192" s="7">
-        <f t="shared" si="62"/>
-        <v>194</v>
+        <f t="shared" si="68"/>
+        <v>414</v>
       </c>
       <c r="S192" s="7">
         <v>99.99</v>
       </c>
-      <c r="T192" s="42" t="s">
+      <c r="T192" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U192" s="42" t="s">
+      <c r="U192" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V192" s="7"/>
@@ -18149,58 +18147,58 @@
         <v>6</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>1301</v>
-      </c>
-      <c r="G193" s="41" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G193" s="39" t="s">
         <v>1134</v>
       </c>
-      <c r="H193" s="41" t="s">
-        <v>1302</v>
-      </c>
-      <c r="I193" s="41" t="s">
+      <c r="H193" s="39" t="s">
         <v>1303</v>
       </c>
-      <c r="J193" s="41" t="s">
+      <c r="I193" s="39" t="s">
         <v>1304</v>
       </c>
-      <c r="K193" s="41" t="s">
+      <c r="J193" s="39" t="s">
         <v>1305</v>
+      </c>
+      <c r="K193" s="39" t="s">
+        <v>1306</v>
       </c>
       <c r="L193" s="6">
         <f t="shared" si="42"/>
-        <v>47200</v>
+        <v>51800</v>
       </c>
       <c r="M193" s="6">
         <f t="shared" si="43"/>
-        <v>47200</v>
+        <v>51800</v>
       </c>
       <c r="N193" s="6">
-        <f t="shared" si="59"/>
-        <v>23000</v>
+        <f t="shared" si="65"/>
+        <v>26000</v>
       </c>
       <c r="O193" s="6">
-        <f t="shared" si="60"/>
-        <v>23000</v>
+        <f t="shared" si="66"/>
+        <v>26000</v>
       </c>
       <c r="P193" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>86</v>
       </c>
       <c r="Q193" s="7">
-        <f t="shared" si="58"/>
-        <v>273</v>
+        <f t="shared" si="67"/>
+        <v>303</v>
       </c>
       <c r="R193" s="7">
-        <f t="shared" si="62"/>
-        <v>198</v>
+        <f t="shared" si="68"/>
+        <v>418</v>
       </c>
       <c r="S193" s="7">
         <v>99.99</v>
       </c>
-      <c r="T193" s="42" t="s">
+      <c r="T193" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U193" s="42" t="s">
+      <c r="U193" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V193" s="7"/>
@@ -18222,58 +18220,58 @@
         <v>6</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>1306</v>
-      </c>
-      <c r="G194" s="41" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G194" s="39" t="s">
         <v>1143</v>
       </c>
-      <c r="H194" s="41" t="s">
-        <v>1307</v>
-      </c>
-      <c r="I194" s="41" t="s">
+      <c r="H194" s="39" t="s">
         <v>1308</v>
       </c>
-      <c r="J194" s="41" t="s">
+      <c r="I194" s="39" t="s">
         <v>1309</v>
       </c>
-      <c r="K194" s="41" t="s">
+      <c r="J194" s="39" t="s">
         <v>1310</v>
+      </c>
+      <c r="K194" s="39" t="s">
+        <v>1311</v>
       </c>
       <c r="L194" s="6">
         <f t="shared" si="42"/>
-        <v>47800</v>
+        <v>52400</v>
       </c>
       <c r="M194" s="6">
         <f t="shared" si="43"/>
-        <v>47800</v>
+        <v>52400</v>
       </c>
       <c r="N194" s="6">
-        <f t="shared" si="59"/>
-        <v>23250</v>
+        <f t="shared" si="65"/>
+        <v>26250</v>
       </c>
       <c r="O194" s="6">
-        <f t="shared" si="60"/>
-        <v>23250</v>
+        <f t="shared" si="66"/>
+        <v>26250</v>
       </c>
       <c r="P194" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>89</v>
       </c>
       <c r="Q194" s="7">
-        <f t="shared" si="58"/>
-        <v>276</v>
+        <f t="shared" si="67"/>
+        <v>306</v>
       </c>
       <c r="R194" s="7">
-        <f t="shared" si="62"/>
-        <v>202</v>
+        <f t="shared" si="68"/>
+        <v>422</v>
       </c>
       <c r="S194" s="7">
         <v>99.99</v>
       </c>
-      <c r="T194" s="42" t="s">
+      <c r="T194" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U194" s="42" t="s">
+      <c r="U194" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V194" s="7"/>
@@ -18295,58 +18293,58 @@
         <v>6</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G195" s="41" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G195" s="39" t="s">
         <v>1152</v>
       </c>
-      <c r="H195" s="41" t="s">
-        <v>1312</v>
-      </c>
-      <c r="I195" s="41" t="s">
+      <c r="H195" s="39" t="s">
         <v>1313</v>
       </c>
-      <c r="J195" s="41" t="s">
+      <c r="I195" s="39" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J195" s="39" t="s">
         <v>1137</v>
       </c>
-      <c r="K195" s="41" t="s">
-        <v>1314</v>
+      <c r="K195" s="39" t="s">
+        <v>1315</v>
       </c>
       <c r="L195" s="6">
         <f t="shared" si="42"/>
-        <v>48400</v>
+        <v>53000</v>
       </c>
       <c r="M195" s="6">
         <f t="shared" si="43"/>
-        <v>48400</v>
+        <v>53000</v>
       </c>
       <c r="N195" s="6">
-        <f t="shared" si="59"/>
-        <v>23500</v>
+        <f t="shared" si="65"/>
+        <v>26500</v>
       </c>
       <c r="O195" s="6">
-        <f t="shared" si="60"/>
-        <v>23500</v>
+        <f t="shared" si="66"/>
+        <v>26500</v>
       </c>
       <c r="P195" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>92</v>
       </c>
       <c r="Q195" s="7">
-        <f t="shared" si="58"/>
-        <v>279</v>
+        <f t="shared" si="67"/>
+        <v>309</v>
       </c>
       <c r="R195" s="7">
-        <f t="shared" si="62"/>
-        <v>206</v>
+        <f t="shared" si="68"/>
+        <v>426</v>
       </c>
       <c r="S195" s="7">
         <v>99.99</v>
       </c>
-      <c r="T195" s="42" t="s">
+      <c r="T195" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U195" s="42" t="s">
+      <c r="U195" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V195" s="7"/>
@@ -18368,58 +18366,58 @@
         <v>6</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>1315</v>
-      </c>
-      <c r="G196" s="41" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G196" s="39" t="s">
         <v>1161</v>
       </c>
-      <c r="H196" s="41" t="s">
-        <v>1316</v>
-      </c>
-      <c r="I196" s="41" t="s">
+      <c r="H196" s="39" t="s">
         <v>1317</v>
       </c>
-      <c r="J196" s="41" t="s">
+      <c r="I196" s="39" t="s">
         <v>1318</v>
       </c>
-      <c r="K196" s="41" t="s">
+      <c r="J196" s="39" t="s">
         <v>1319</v>
+      </c>
+      <c r="K196" s="39" t="s">
+        <v>1320</v>
       </c>
       <c r="L196" s="6">
         <f t="shared" si="42"/>
-        <v>49000</v>
+        <v>53600</v>
       </c>
       <c r="M196" s="6">
         <f t="shared" si="43"/>
-        <v>49000</v>
+        <v>53600</v>
       </c>
       <c r="N196" s="6">
-        <f t="shared" si="59"/>
-        <v>23750</v>
+        <f t="shared" si="65"/>
+        <v>26750</v>
       </c>
       <c r="O196" s="6">
-        <f t="shared" si="60"/>
-        <v>23750</v>
+        <f t="shared" si="66"/>
+        <v>26750</v>
       </c>
       <c r="P196" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>95</v>
       </c>
       <c r="Q196" s="7">
-        <f t="shared" ref="Q196:Q200" si="63">Q195+4</f>
-        <v>283</v>
+        <f t="shared" ref="Q196:Q200" si="69">Q195+4</f>
+        <v>313</v>
       </c>
       <c r="R196" s="7">
-        <f t="shared" ref="R196:R200" si="64">R195+5</f>
-        <v>211</v>
+        <f t="shared" ref="R196:R200" si="70">R195+5</f>
+        <v>431</v>
       </c>
       <c r="S196" s="7">
         <v>99.99</v>
       </c>
-      <c r="T196" s="42" t="s">
+      <c r="T196" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U196" s="42" t="s">
+      <c r="U196" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V196" s="7"/>
@@ -18441,58 +18439,58 @@
         <v>6</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>1320</v>
-      </c>
-      <c r="G197" s="41" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G197" s="39" t="s">
         <v>1170</v>
       </c>
-      <c r="H197" s="41" t="s">
-        <v>1321</v>
-      </c>
-      <c r="I197" s="41" t="s">
+      <c r="H197" s="39" t="s">
         <v>1322</v>
       </c>
-      <c r="J197" s="41" t="s">
+      <c r="I197" s="39" t="s">
         <v>1323</v>
       </c>
-      <c r="K197" s="41" t="s">
+      <c r="J197" s="39" t="s">
         <v>1324</v>
+      </c>
+      <c r="K197" s="39" t="s">
+        <v>1325</v>
       </c>
       <c r="L197" s="6">
         <f t="shared" si="42"/>
-        <v>49600</v>
+        <v>54200</v>
       </c>
       <c r="M197" s="6">
         <f t="shared" si="43"/>
-        <v>49600</v>
+        <v>54200</v>
       </c>
       <c r="N197" s="6">
-        <f t="shared" si="59"/>
-        <v>24000</v>
+        <f t="shared" si="65"/>
+        <v>27000</v>
       </c>
       <c r="O197" s="6">
-        <f t="shared" si="60"/>
-        <v>24000</v>
+        <f t="shared" si="66"/>
+        <v>27000</v>
       </c>
       <c r="P197" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>98</v>
       </c>
       <c r="Q197" s="7">
-        <f t="shared" si="63"/>
-        <v>287</v>
+        <f t="shared" si="69"/>
+        <v>317</v>
       </c>
       <c r="R197" s="7">
-        <f t="shared" si="64"/>
-        <v>216</v>
+        <f t="shared" si="70"/>
+        <v>436</v>
       </c>
       <c r="S197" s="7">
         <v>99.99</v>
       </c>
-      <c r="T197" s="42" t="s">
+      <c r="T197" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U197" s="42" t="s">
+      <c r="U197" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V197" s="7"/>
@@ -18514,58 +18512,58 @@
         <v>6</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>1325</v>
-      </c>
-      <c r="G198" s="41" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G198" s="39" t="s">
         <v>1179</v>
       </c>
-      <c r="H198" s="41" t="s">
-        <v>1326</v>
-      </c>
-      <c r="I198" s="41" t="s">
+      <c r="H198" s="39" t="s">
         <v>1327</v>
       </c>
-      <c r="J198" s="41" t="s">
+      <c r="I198" s="39" t="s">
         <v>1328</v>
       </c>
-      <c r="K198" s="41" t="s">
+      <c r="J198" s="39" t="s">
         <v>1329</v>
+      </c>
+      <c r="K198" s="39" t="s">
+        <v>1330</v>
       </c>
       <c r="L198" s="6">
         <f t="shared" si="42"/>
-        <v>50200</v>
+        <v>54800</v>
       </c>
       <c r="M198" s="6">
         <f t="shared" si="43"/>
-        <v>50200</v>
+        <v>54800</v>
       </c>
       <c r="N198" s="6">
-        <f t="shared" si="59"/>
-        <v>24250</v>
+        <f t="shared" si="65"/>
+        <v>27250</v>
       </c>
       <c r="O198" s="6">
-        <f t="shared" si="60"/>
-        <v>24250</v>
+        <f t="shared" si="66"/>
+        <v>27250</v>
       </c>
       <c r="P198" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>101</v>
       </c>
       <c r="Q198" s="7">
-        <f t="shared" si="63"/>
-        <v>291</v>
+        <f t="shared" si="69"/>
+        <v>321</v>
       </c>
       <c r="R198" s="7">
-        <f t="shared" si="64"/>
-        <v>221</v>
+        <f t="shared" si="70"/>
+        <v>441</v>
       </c>
       <c r="S198" s="7">
         <v>99.99</v>
       </c>
-      <c r="T198" s="42" t="s">
+      <c r="T198" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U198" s="42" t="s">
+      <c r="U198" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V198" s="7"/>
@@ -18587,58 +18585,58 @@
         <v>6</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>1330</v>
-      </c>
-      <c r="G199" s="41" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G199" s="39" t="s">
         <v>1188</v>
       </c>
-      <c r="H199" s="41" t="s">
-        <v>1331</v>
-      </c>
-      <c r="I199" s="41" t="s">
+      <c r="H199" s="39" t="s">
         <v>1332</v>
       </c>
-      <c r="J199" s="41" t="s">
+      <c r="I199" s="39" t="s">
         <v>1333</v>
       </c>
-      <c r="K199" s="41" t="s">
+      <c r="J199" s="39" t="s">
         <v>1334</v>
+      </c>
+      <c r="K199" s="39" t="s">
+        <v>1335</v>
       </c>
       <c r="L199" s="6">
         <f t="shared" si="42"/>
-        <v>50800</v>
+        <v>55400</v>
       </c>
       <c r="M199" s="6">
         <f t="shared" si="43"/>
-        <v>50800</v>
+        <v>55400</v>
       </c>
       <c r="N199" s="6">
-        <f t="shared" si="59"/>
-        <v>24500</v>
+        <f t="shared" si="65"/>
+        <v>27500</v>
       </c>
       <c r="O199" s="6">
-        <f t="shared" si="60"/>
-        <v>24500</v>
+        <f t="shared" si="66"/>
+        <v>27500</v>
       </c>
       <c r="P199" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>104</v>
       </c>
       <c r="Q199" s="7">
-        <f t="shared" si="63"/>
-        <v>295</v>
+        <f t="shared" si="69"/>
+        <v>325</v>
       </c>
       <c r="R199" s="7">
-        <f t="shared" si="64"/>
-        <v>226</v>
+        <f t="shared" si="70"/>
+        <v>446</v>
       </c>
       <c r="S199" s="7">
         <v>99.99</v>
       </c>
-      <c r="T199" s="42" t="s">
+      <c r="T199" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U199" s="42" t="s">
+      <c r="U199" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V199" s="7"/>
@@ -18660,58 +18658,58 @@
         <v>6</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>1335</v>
-      </c>
-      <c r="G200" s="41" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G200" s="39" t="s">
         <v>1197</v>
       </c>
-      <c r="H200" s="41" t="s">
-        <v>1336</v>
-      </c>
-      <c r="I200" s="41" t="s">
+      <c r="H200" s="39" t="s">
         <v>1337</v>
       </c>
-      <c r="J200" s="41" t="s">
+      <c r="I200" s="39" t="s">
         <v>1338</v>
       </c>
-      <c r="K200" s="41" t="s">
+      <c r="J200" s="39" t="s">
         <v>1339</v>
+      </c>
+      <c r="K200" s="39" t="s">
+        <v>1340</v>
       </c>
       <c r="L200" s="6">
         <f t="shared" si="42"/>
-        <v>51400</v>
+        <v>56000</v>
       </c>
       <c r="M200" s="6">
         <f t="shared" si="43"/>
-        <v>51400</v>
+        <v>56000</v>
       </c>
       <c r="N200" s="6">
-        <f t="shared" si="59"/>
-        <v>24750</v>
+        <f t="shared" si="65"/>
+        <v>27750</v>
       </c>
       <c r="O200" s="6">
-        <f t="shared" si="60"/>
-        <v>24750</v>
+        <f t="shared" si="66"/>
+        <v>27750</v>
       </c>
       <c r="P200" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>107</v>
       </c>
       <c r="Q200" s="7">
-        <f t="shared" si="63"/>
-        <v>299</v>
+        <f t="shared" si="69"/>
+        <v>329</v>
       </c>
       <c r="R200" s="7">
-        <f t="shared" si="64"/>
-        <v>231</v>
+        <f t="shared" si="70"/>
+        <v>451</v>
       </c>
       <c r="S200" s="7">
         <v>99.99</v>
       </c>
-      <c r="T200" s="42" t="s">
+      <c r="T200" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U200" s="42" t="s">
+      <c r="U200" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V200" s="7"/>
@@ -18731,58 +18729,58 @@
         <v>6</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>1340</v>
-      </c>
-      <c r="G201" s="41" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G201" s="39" t="s">
         <v>1206</v>
       </c>
-      <c r="H201" s="41" t="s">
-        <v>1341</v>
-      </c>
-      <c r="I201" s="41" t="s">
+      <c r="H201" s="39" t="s">
         <v>1342</v>
       </c>
-      <c r="J201" s="41" t="s">
+      <c r="I201" s="39" t="s">
         <v>1343</v>
       </c>
-      <c r="K201" s="41" t="s">
+      <c r="J201" s="39" t="s">
         <v>1344</v>
+      </c>
+      <c r="K201" s="39" t="s">
+        <v>1345</v>
       </c>
       <c r="L201" s="6">
         <f t="shared" si="42"/>
-        <v>52000</v>
+        <v>56600</v>
       </c>
       <c r="M201" s="6">
         <f t="shared" si="43"/>
-        <v>52000</v>
+        <v>56600</v>
       </c>
       <c r="N201" s="6">
-        <f t="shared" ref="N201:N205" si="65">N200+300</f>
-        <v>25050</v>
+        <f t="shared" ref="N201:N205" si="71">N200+300</f>
+        <v>28050</v>
       </c>
       <c r="O201" s="6">
-        <f t="shared" ref="O201:O205" si="66">O200+300</f>
-        <v>25050</v>
+        <f t="shared" ref="O201:O205" si="72">O200+300</f>
+        <v>28050</v>
       </c>
       <c r="P201" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>110</v>
       </c>
       <c r="Q201" s="7">
-        <f t="shared" ref="Q201:Q205" si="67">Q200+5</f>
-        <v>304</v>
+        <f t="shared" ref="Q201:Q205" si="73">Q200+5</f>
+        <v>334</v>
       </c>
       <c r="R201" s="7">
-        <f t="shared" ref="R201:R205" si="68">R200+6</f>
-        <v>237</v>
+        <f t="shared" ref="R201:R205" si="74">R200+6</f>
+        <v>457</v>
       </c>
       <c r="S201" s="7">
         <v>99.99</v>
       </c>
-      <c r="T201" s="42" t="s">
+      <c r="T201" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U201" s="42" t="s">
+      <c r="U201" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V201" s="6"/>
@@ -18799,58 +18797,58 @@
         <v>6</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>1345</v>
-      </c>
-      <c r="G202" s="41" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G202" s="39" t="s">
         <v>1215</v>
       </c>
-      <c r="H202" s="41" t="s">
-        <v>1346</v>
-      </c>
-      <c r="I202" s="41" t="s">
+      <c r="H202" s="39" t="s">
         <v>1347</v>
       </c>
-      <c r="J202" s="41" t="s">
+      <c r="I202" s="39" t="s">
         <v>1348</v>
       </c>
-      <c r="K202" s="41" t="s">
+      <c r="J202" s="39" t="s">
         <v>1349</v>
+      </c>
+      <c r="K202" s="39" t="s">
+        <v>1350</v>
       </c>
       <c r="L202" s="6">
         <f t="shared" si="42"/>
-        <v>52600</v>
+        <v>57200</v>
       </c>
       <c r="M202" s="6">
         <f t="shared" si="43"/>
-        <v>52600</v>
+        <v>57200</v>
       </c>
       <c r="N202" s="6">
-        <f t="shared" si="65"/>
-        <v>25350</v>
+        <f t="shared" si="71"/>
+        <v>28350</v>
       </c>
       <c r="O202" s="6">
-        <f t="shared" si="66"/>
-        <v>25350</v>
+        <f t="shared" si="72"/>
+        <v>28350</v>
       </c>
       <c r="P202" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>113</v>
       </c>
       <c r="Q202" s="7">
-        <f t="shared" si="67"/>
-        <v>309</v>
+        <f t="shared" si="73"/>
+        <v>339</v>
       </c>
       <c r="R202" s="7">
-        <f t="shared" si="68"/>
-        <v>243</v>
+        <f t="shared" si="74"/>
+        <v>463</v>
       </c>
       <c r="S202" s="7">
         <v>99.99</v>
       </c>
-      <c r="T202" s="42" t="s">
+      <c r="T202" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U202" s="42" t="s">
+      <c r="U202" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V202" s="6"/>
@@ -18867,58 +18865,58 @@
         <v>6</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>1350</v>
-      </c>
-      <c r="G203" s="41" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G203" s="39" t="s">
         <v>1224</v>
       </c>
-      <c r="H203" s="41" t="s">
-        <v>1351</v>
-      </c>
-      <c r="I203" s="41" t="s">
+      <c r="H203" s="39" t="s">
         <v>1352</v>
       </c>
-      <c r="J203" s="41" t="s">
+      <c r="I203" s="39" t="s">
         <v>1353</v>
       </c>
-      <c r="K203" s="41" t="s">
+      <c r="J203" s="39" t="s">
         <v>1354</v>
+      </c>
+      <c r="K203" s="39" t="s">
+        <v>1355</v>
       </c>
       <c r="L203" s="6">
         <f t="shared" si="42"/>
-        <v>53200</v>
+        <v>57800</v>
       </c>
       <c r="M203" s="6">
         <f t="shared" si="43"/>
-        <v>53200</v>
+        <v>57800</v>
       </c>
       <c r="N203" s="6">
-        <f t="shared" si="65"/>
-        <v>25650</v>
+        <f t="shared" si="71"/>
+        <v>28650</v>
       </c>
       <c r="O203" s="6">
-        <f t="shared" si="66"/>
-        <v>25650</v>
+        <f t="shared" si="72"/>
+        <v>28650</v>
       </c>
       <c r="P203" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>116</v>
       </c>
       <c r="Q203" s="7">
-        <f t="shared" si="67"/>
-        <v>314</v>
+        <f t="shared" si="73"/>
+        <v>344</v>
       </c>
       <c r="R203" s="7">
-        <f t="shared" si="68"/>
-        <v>249</v>
+        <f t="shared" si="74"/>
+        <v>469</v>
       </c>
       <c r="S203" s="7">
         <v>99.99</v>
       </c>
-      <c r="T203" s="42" t="s">
+      <c r="T203" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U203" s="42" t="s">
+      <c r="U203" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V203" s="6"/>
@@ -18935,58 +18933,58 @@
         <v>6</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>1355</v>
-      </c>
-      <c r="G204" s="41" t="s">
         <v>1356</v>
       </c>
-      <c r="H204" s="41" t="s">
+      <c r="G204" s="39" t="s">
         <v>1357</v>
       </c>
-      <c r="I204" s="41" t="s">
+      <c r="H204" s="39" t="s">
         <v>1358</v>
       </c>
-      <c r="J204" s="41" t="s">
+      <c r="I204" s="39" t="s">
         <v>1359</v>
       </c>
-      <c r="K204" s="41" t="s">
+      <c r="J204" s="39" t="s">
         <v>1360</v>
+      </c>
+      <c r="K204" s="39" t="s">
+        <v>1361</v>
       </c>
       <c r="L204" s="6">
         <f t="shared" si="42"/>
-        <v>53800</v>
+        <v>58400</v>
       </c>
       <c r="M204" s="6">
         <f t="shared" si="43"/>
-        <v>53800</v>
+        <v>58400</v>
       </c>
       <c r="N204" s="6">
-        <f t="shared" si="65"/>
-        <v>25950</v>
+        <f t="shared" si="71"/>
+        <v>28950</v>
       </c>
       <c r="O204" s="6">
-        <f t="shared" si="66"/>
-        <v>25950</v>
+        <f t="shared" si="72"/>
+        <v>28950</v>
       </c>
       <c r="P204" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>119</v>
       </c>
       <c r="Q204" s="7">
-        <f t="shared" si="67"/>
-        <v>319</v>
+        <f t="shared" si="73"/>
+        <v>349</v>
       </c>
       <c r="R204" s="7">
-        <f t="shared" si="68"/>
-        <v>255</v>
+        <f t="shared" si="74"/>
+        <v>475</v>
       </c>
       <c r="S204" s="7">
         <v>99.99</v>
       </c>
-      <c r="T204" s="42" t="s">
+      <c r="T204" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U204" s="42" t="s">
+      <c r="U204" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V204" s="6"/>
@@ -19003,58 +19001,58 @@
         <v>6</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>1361</v>
-      </c>
-      <c r="G205" s="41" t="s">
         <v>1362</v>
       </c>
-      <c r="H205" s="41" t="s">
+      <c r="G205" s="39" t="s">
         <v>1363</v>
       </c>
-      <c r="I205" s="41" t="s">
+      <c r="H205" s="39" t="s">
         <v>1364</v>
       </c>
-      <c r="J205" s="41" t="s">
+      <c r="I205" s="39" t="s">
         <v>1365</v>
       </c>
-      <c r="K205" s="41" t="s">
+      <c r="J205" s="39" t="s">
         <v>1366</v>
       </c>
+      <c r="K205" s="39" t="s">
+        <v>1367</v>
+      </c>
       <c r="L205" s="6">
-        <f t="shared" ref="L205:L215" si="69">L204+600</f>
-        <v>54400</v>
+        <f t="shared" ref="L205:L215" si="75">L204+600</f>
+        <v>59000</v>
       </c>
       <c r="M205" s="6">
-        <f t="shared" ref="M205:M215" si="70">M204+600</f>
-        <v>54400</v>
+        <f t="shared" ref="M205:M215" si="76">M204+600</f>
+        <v>59000</v>
       </c>
       <c r="N205" s="6">
-        <f t="shared" si="65"/>
-        <v>26250</v>
+        <f t="shared" si="71"/>
+        <v>29250</v>
       </c>
       <c r="O205" s="6">
-        <f t="shared" si="66"/>
-        <v>26250</v>
+        <f t="shared" si="72"/>
+        <v>29250</v>
       </c>
       <c r="P205" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>122</v>
       </c>
       <c r="Q205" s="7">
-        <f t="shared" si="67"/>
-        <v>324</v>
+        <f t="shared" si="73"/>
+        <v>354</v>
       </c>
       <c r="R205" s="7">
-        <f t="shared" si="68"/>
-        <v>261</v>
+        <f t="shared" si="74"/>
+        <v>481</v>
       </c>
       <c r="S205" s="7">
         <v>99.99</v>
       </c>
-      <c r="T205" s="42" t="s">
+      <c r="T205" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U205" s="42" t="s">
+      <c r="U205" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V205" s="6"/>
@@ -19071,58 +19069,58 @@
         <v>6</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>1367</v>
-      </c>
-      <c r="G206" s="41" t="s">
         <v>1368</v>
       </c>
-      <c r="H206" s="41" t="s">
+      <c r="G206" s="39" t="s">
         <v>1369</v>
       </c>
-      <c r="I206" s="41" t="s">
+      <c r="H206" s="39" t="s">
         <v>1370</v>
       </c>
-      <c r="J206" s="41" t="s">
+      <c r="I206" s="39" t="s">
         <v>1371</v>
       </c>
-      <c r="K206" s="41" t="s">
+      <c r="J206" s="39" t="s">
         <v>1372</v>
       </c>
+      <c r="K206" s="39" t="s">
+        <v>1373</v>
+      </c>
       <c r="L206" s="6">
-        <f t="shared" si="69"/>
-        <v>55000</v>
+        <f t="shared" si="75"/>
+        <v>59600</v>
       </c>
       <c r="M206" s="6">
-        <f t="shared" si="70"/>
-        <v>55000</v>
+        <f t="shared" si="76"/>
+        <v>59600</v>
       </c>
       <c r="N206" s="6">
-        <f t="shared" ref="N206:N210" si="71">N205+400</f>
-        <v>26650</v>
+        <f t="shared" ref="N206:N210" si="77">N205+400</f>
+        <v>29650</v>
       </c>
       <c r="O206" s="6">
-        <f t="shared" ref="O206:O210" si="72">O205+400</f>
-        <v>26650</v>
+        <f t="shared" ref="O206:O210" si="78">O205+400</f>
+        <v>29650</v>
       </c>
       <c r="P206" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>125</v>
       </c>
       <c r="Q206" s="7">
-        <f t="shared" ref="Q206:Q210" si="73">Q205+6</f>
-        <v>330</v>
+        <f t="shared" ref="Q206:Q210" si="79">Q205+6</f>
+        <v>360</v>
       </c>
       <c r="R206" s="7">
-        <f t="shared" ref="R206:R210" si="74">R205+7</f>
-        <v>268</v>
+        <f t="shared" ref="R206:R210" si="80">R205+7</f>
+        <v>488</v>
       </c>
       <c r="S206" s="7">
         <v>99.99</v>
       </c>
-      <c r="T206" s="42" t="s">
+      <c r="T206" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U206" s="42" t="s">
+      <c r="U206" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V206" s="6"/>
@@ -19139,58 +19137,58 @@
         <v>6</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>1373</v>
-      </c>
-      <c r="G207" s="41" t="s">
         <v>1374</v>
       </c>
-      <c r="H207" s="41" t="s">
+      <c r="G207" s="39" t="s">
         <v>1375</v>
       </c>
-      <c r="I207" s="41" t="s">
+      <c r="H207" s="39" t="s">
         <v>1376</v>
       </c>
-      <c r="J207" s="41" t="s">
+      <c r="I207" s="39" t="s">
         <v>1377</v>
       </c>
-      <c r="K207" s="41" t="s">
+      <c r="J207" s="39" t="s">
         <v>1378</v>
       </c>
+      <c r="K207" s="39" t="s">
+        <v>1379</v>
+      </c>
       <c r="L207" s="6">
-        <f t="shared" si="69"/>
-        <v>55600</v>
+        <f t="shared" si="75"/>
+        <v>60200</v>
       </c>
       <c r="M207" s="6">
-        <f t="shared" si="70"/>
-        <v>55600</v>
+        <f t="shared" si="76"/>
+        <v>60200</v>
       </c>
       <c r="N207" s="6">
-        <f t="shared" si="71"/>
-        <v>27050</v>
+        <f t="shared" si="77"/>
+        <v>30050</v>
       </c>
       <c r="O207" s="6">
-        <f t="shared" si="72"/>
-        <v>27050</v>
+        <f t="shared" si="78"/>
+        <v>30050</v>
       </c>
       <c r="P207" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>128</v>
       </c>
       <c r="Q207" s="7">
-        <f t="shared" si="73"/>
-        <v>336</v>
+        <f t="shared" si="79"/>
+        <v>366</v>
       </c>
       <c r="R207" s="7">
-        <f t="shared" si="74"/>
-        <v>275</v>
+        <f t="shared" si="80"/>
+        <v>495</v>
       </c>
       <c r="S207" s="7">
         <v>99.99</v>
       </c>
-      <c r="T207" s="42" t="s">
+      <c r="T207" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U207" s="42" t="s">
+      <c r="U207" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V207" s="6"/>
@@ -19207,58 +19205,58 @@
         <v>6</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G208" s="41" t="s">
         <v>1380</v>
       </c>
-      <c r="H208" s="41" t="s">
+      <c r="G208" s="39" t="s">
         <v>1381</v>
       </c>
-      <c r="I208" s="41" t="s">
+      <c r="H208" s="39" t="s">
         <v>1382</v>
       </c>
-      <c r="J208" s="41" t="s">
+      <c r="I208" s="39" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J208" s="39" t="s">
         <v>1227</v>
       </c>
-      <c r="K208" s="41" t="s">
-        <v>1383</v>
+      <c r="K208" s="39" t="s">
+        <v>1384</v>
       </c>
       <c r="L208" s="6">
-        <f t="shared" si="69"/>
-        <v>56200</v>
+        <f t="shared" si="75"/>
+        <v>60800</v>
       </c>
       <c r="M208" s="6">
-        <f t="shared" si="70"/>
-        <v>56200</v>
+        <f t="shared" si="76"/>
+        <v>60800</v>
       </c>
       <c r="N208" s="6">
-        <f t="shared" si="71"/>
-        <v>27450</v>
+        <f t="shared" si="77"/>
+        <v>30450</v>
       </c>
       <c r="O208" s="6">
-        <f t="shared" si="72"/>
-        <v>27450</v>
+        <f t="shared" si="78"/>
+        <v>30450</v>
       </c>
       <c r="P208" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>131</v>
       </c>
       <c r="Q208" s="7">
-        <f t="shared" si="73"/>
-        <v>342</v>
+        <f t="shared" si="79"/>
+        <v>372</v>
       </c>
       <c r="R208" s="7">
-        <f t="shared" si="74"/>
-        <v>282</v>
+        <f t="shared" si="80"/>
+        <v>502</v>
       </c>
       <c r="S208" s="7">
         <v>99.99</v>
       </c>
-      <c r="T208" s="42" t="s">
+      <c r="T208" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U208" s="42" t="s">
+      <c r="U208" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V208" s="6"/>
@@ -19275,58 +19273,58 @@
         <v>6</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G209" s="41" t="s">
-        <v>1265</v>
-      </c>
-      <c r="H209" s="41" t="s">
         <v>1385</v>
       </c>
-      <c r="I209" s="41" t="s">
+      <c r="G209" s="39" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H209" s="39" t="s">
         <v>1386</v>
       </c>
-      <c r="J209" s="41" t="s">
+      <c r="I209" s="39" t="s">
         <v>1387</v>
       </c>
-      <c r="K209" s="41" t="s">
+      <c r="J209" s="39" t="s">
         <v>1388</v>
       </c>
+      <c r="K209" s="39" t="s">
+        <v>1389</v>
+      </c>
       <c r="L209" s="6">
-        <f t="shared" si="69"/>
-        <v>56800</v>
+        <f t="shared" si="75"/>
+        <v>61400</v>
       </c>
       <c r="M209" s="6">
-        <f t="shared" si="70"/>
-        <v>56800</v>
+        <f t="shared" si="76"/>
+        <v>61400</v>
       </c>
       <c r="N209" s="6">
-        <f t="shared" si="71"/>
-        <v>27850</v>
+        <f t="shared" si="77"/>
+        <v>30850</v>
       </c>
       <c r="O209" s="6">
-        <f t="shared" si="72"/>
-        <v>27850</v>
+        <f t="shared" si="78"/>
+        <v>30850</v>
       </c>
       <c r="P209" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>134</v>
       </c>
       <c r="Q209" s="7">
-        <f t="shared" si="73"/>
-        <v>348</v>
+        <f t="shared" si="79"/>
+        <v>378</v>
       </c>
       <c r="R209" s="7">
-        <f t="shared" si="74"/>
-        <v>289</v>
+        <f t="shared" si="80"/>
+        <v>509</v>
       </c>
       <c r="S209" s="7">
         <v>99.99</v>
       </c>
-      <c r="T209" s="42" t="s">
+      <c r="T209" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U209" s="42" t="s">
+      <c r="U209" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V209" s="6"/>
@@ -19343,58 +19341,58 @@
         <v>6</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>1389</v>
-      </c>
-      <c r="G210" s="41" t="s">
-        <v>1271</v>
-      </c>
-      <c r="H210" s="41" t="s">
         <v>1390</v>
       </c>
-      <c r="I210" s="41" t="s">
+      <c r="G210" s="39" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H210" s="39" t="s">
         <v>1391</v>
       </c>
-      <c r="J210" s="41" t="s">
+      <c r="I210" s="39" t="s">
         <v>1392</v>
       </c>
-      <c r="K210" s="41" t="s">
+      <c r="J210" s="39" t="s">
         <v>1393</v>
       </c>
+      <c r="K210" s="39" t="s">
+        <v>1394</v>
+      </c>
       <c r="L210" s="6">
-        <f t="shared" si="69"/>
-        <v>57400</v>
+        <f t="shared" si="75"/>
+        <v>62000</v>
       </c>
       <c r="M210" s="6">
-        <f t="shared" si="70"/>
-        <v>57400</v>
+        <f t="shared" si="76"/>
+        <v>62000</v>
       </c>
       <c r="N210" s="6">
-        <f t="shared" si="71"/>
-        <v>28250</v>
+        <f t="shared" si="77"/>
+        <v>31250</v>
       </c>
       <c r="O210" s="6">
-        <f t="shared" si="72"/>
-        <v>28250</v>
+        <f t="shared" si="78"/>
+        <v>31250</v>
       </c>
       <c r="P210" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>137</v>
       </c>
       <c r="Q210" s="7">
-        <f t="shared" si="73"/>
-        <v>354</v>
+        <f t="shared" si="79"/>
+        <v>384</v>
       </c>
       <c r="R210" s="7">
-        <f t="shared" si="74"/>
-        <v>296</v>
+        <f t="shared" si="80"/>
+        <v>516</v>
       </c>
       <c r="S210" s="7">
         <v>99.99</v>
       </c>
-      <c r="T210" s="42" t="s">
+      <c r="T210" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U210" s="42" t="s">
+      <c r="U210" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V210" s="6"/>
@@ -19413,58 +19411,58 @@
         <v>6</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>1394</v>
-      </c>
-      <c r="G211" s="41" t="s">
-        <v>1277</v>
-      </c>
-      <c r="H211" s="41" t="s">
         <v>1395</v>
       </c>
-      <c r="I211" s="41" t="s">
+      <c r="G211" s="39" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H211" s="39" t="s">
         <v>1396</v>
       </c>
-      <c r="J211" s="41" t="s">
+      <c r="I211" s="39" t="s">
         <v>1397</v>
       </c>
-      <c r="K211" s="41" t="s">
+      <c r="J211" s="39" t="s">
         <v>1398</v>
       </c>
+      <c r="K211" s="39" t="s">
+        <v>1399</v>
+      </c>
       <c r="L211" s="6">
-        <f t="shared" si="69"/>
-        <v>58000</v>
+        <f t="shared" si="75"/>
+        <v>62600</v>
       </c>
       <c r="M211" s="6">
-        <f t="shared" si="70"/>
-        <v>58000</v>
+        <f t="shared" si="76"/>
+        <v>62600</v>
       </c>
       <c r="N211" s="6">
-        <f t="shared" ref="N211:N215" si="75">N210+500</f>
-        <v>28750</v>
+        <f t="shared" ref="N211:N215" si="81">N210+500</f>
+        <v>31750</v>
       </c>
       <c r="O211" s="6">
-        <f t="shared" ref="O211:O215" si="76">O210+500</f>
-        <v>28750</v>
+        <f t="shared" ref="O211:O215" si="82">O210+500</f>
+        <v>31750</v>
       </c>
       <c r="P211" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>140</v>
       </c>
       <c r="Q211" s="7">
-        <f t="shared" ref="Q211:Q215" si="77">Q210+7</f>
-        <v>361</v>
+        <f t="shared" ref="Q211:Q215" si="83">Q210+7</f>
+        <v>391</v>
       </c>
       <c r="R211" s="7">
-        <f t="shared" ref="R211:R215" si="78">R210+8</f>
-        <v>304</v>
+        <f t="shared" ref="R211:R215" si="84">R210+8</f>
+        <v>524</v>
       </c>
       <c r="S211" s="7">
         <v>99.99</v>
       </c>
-      <c r="T211" s="42" t="s">
+      <c r="T211" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U211" s="42" t="s">
+      <c r="U211" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V211" s="7"/>
@@ -19486,58 +19484,58 @@
         <v>6</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>1399</v>
-      </c>
-      <c r="G212" s="41" t="s">
-        <v>1282</v>
-      </c>
-      <c r="H212" s="41" t="s">
         <v>1400</v>
       </c>
-      <c r="I212" s="41" t="s">
+      <c r="G212" s="39" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H212" s="39" t="s">
         <v>1401</v>
       </c>
-      <c r="J212" s="41" t="s">
+      <c r="I212" s="39" t="s">
         <v>1402</v>
       </c>
-      <c r="K212" s="41" t="s">
+      <c r="J212" s="39" t="s">
         <v>1403</v>
       </c>
+      <c r="K212" s="39" t="s">
+        <v>1404</v>
+      </c>
       <c r="L212" s="6">
-        <f t="shared" si="69"/>
-        <v>58600</v>
+        <f t="shared" si="75"/>
+        <v>63200</v>
       </c>
       <c r="M212" s="6">
-        <f t="shared" si="70"/>
-        <v>58600</v>
+        <f t="shared" si="76"/>
+        <v>63200</v>
       </c>
       <c r="N212" s="6">
-        <f t="shared" si="75"/>
-        <v>29250</v>
+        <f t="shared" si="81"/>
+        <v>32250</v>
       </c>
       <c r="O212" s="6">
-        <f t="shared" si="76"/>
-        <v>29250</v>
+        <f t="shared" si="82"/>
+        <v>32250</v>
       </c>
       <c r="P212" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>143</v>
       </c>
       <c r="Q212" s="7">
-        <f t="shared" si="77"/>
-        <v>368</v>
+        <f t="shared" si="83"/>
+        <v>398</v>
       </c>
       <c r="R212" s="7">
-        <f t="shared" si="78"/>
-        <v>312</v>
+        <f t="shared" si="84"/>
+        <v>532</v>
       </c>
       <c r="S212" s="7">
         <v>99.99</v>
       </c>
-      <c r="T212" s="42" t="s">
+      <c r="T212" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U212" s="42" t="s">
+      <c r="U212" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V212" s="7"/>
@@ -19559,58 +19557,58 @@
         <v>6</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>1404</v>
-      </c>
-      <c r="G213" s="41" t="s">
-        <v>1287</v>
-      </c>
-      <c r="H213" s="41" t="s">
         <v>1405</v>
       </c>
-      <c r="I213" s="41" t="s">
+      <c r="G213" s="39" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H213" s="39" t="s">
         <v>1406</v>
       </c>
-      <c r="J213" s="41" t="s">
+      <c r="I213" s="39" t="s">
         <v>1407</v>
       </c>
-      <c r="K213" s="41" t="s">
+      <c r="J213" s="39" t="s">
         <v>1408</v>
       </c>
+      <c r="K213" s="39" t="s">
+        <v>1409</v>
+      </c>
       <c r="L213" s="6">
-        <f t="shared" si="69"/>
-        <v>59200</v>
+        <f t="shared" si="75"/>
+        <v>63800</v>
       </c>
       <c r="M213" s="6">
-        <f t="shared" si="70"/>
-        <v>59200</v>
+        <f t="shared" si="76"/>
+        <v>63800</v>
       </c>
       <c r="N213" s="6">
-        <f t="shared" si="75"/>
-        <v>29750</v>
+        <f t="shared" si="81"/>
+        <v>32750</v>
       </c>
       <c r="O213" s="6">
-        <f t="shared" si="76"/>
-        <v>29750</v>
+        <f t="shared" si="82"/>
+        <v>32750</v>
       </c>
       <c r="P213" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>146</v>
       </c>
       <c r="Q213" s="7">
-        <f t="shared" si="77"/>
-        <v>375</v>
+        <f t="shared" si="83"/>
+        <v>405</v>
       </c>
       <c r="R213" s="7">
-        <f t="shared" si="78"/>
-        <v>320</v>
+        <f t="shared" si="84"/>
+        <v>540</v>
       </c>
       <c r="S213" s="7">
         <v>99.99</v>
       </c>
-      <c r="T213" s="42" t="s">
+      <c r="T213" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U213" s="42" t="s">
+      <c r="U213" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V213" s="7"/>
@@ -19632,58 +19630,58 @@
         <v>6</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>1409</v>
-      </c>
-      <c r="G214" s="41" t="s">
-        <v>1292</v>
-      </c>
-      <c r="H214" s="41" t="s">
         <v>1410</v>
       </c>
-      <c r="I214" s="41" t="s">
+      <c r="G214" s="39" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H214" s="39" t="s">
         <v>1411</v>
       </c>
-      <c r="J214" s="41" t="s">
-        <v>1268</v>
-      </c>
-      <c r="K214" s="41" t="s">
+      <c r="I214" s="39" t="s">
         <v>1412</v>
       </c>
+      <c r="J214" s="39" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K214" s="39" t="s">
+        <v>1413</v>
+      </c>
       <c r="L214" s="6">
-        <f t="shared" si="69"/>
-        <v>59800</v>
+        <f t="shared" si="75"/>
+        <v>64400</v>
       </c>
       <c r="M214" s="6">
-        <f t="shared" si="70"/>
-        <v>59800</v>
+        <f t="shared" si="76"/>
+        <v>64400</v>
       </c>
       <c r="N214" s="6">
-        <f t="shared" si="75"/>
-        <v>30250</v>
+        <f t="shared" si="81"/>
+        <v>33250</v>
       </c>
       <c r="O214" s="6">
-        <f t="shared" si="76"/>
-        <v>30250</v>
+        <f t="shared" si="82"/>
+        <v>33250</v>
       </c>
       <c r="P214" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>149</v>
       </c>
       <c r="Q214" s="7">
-        <f t="shared" si="77"/>
-        <v>382</v>
+        <f t="shared" si="83"/>
+        <v>412</v>
       </c>
       <c r="R214" s="7">
-        <f t="shared" si="78"/>
-        <v>328</v>
+        <f t="shared" si="84"/>
+        <v>548</v>
       </c>
       <c r="S214" s="7">
         <v>99.99</v>
       </c>
-      <c r="T214" s="42" t="s">
+      <c r="T214" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U214" s="42" t="s">
+      <c r="U214" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V214" s="7"/>
@@ -19705,58 +19703,58 @@
         <v>6</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>1413</v>
-      </c>
-      <c r="G215" s="41" t="s">
-        <v>1297</v>
-      </c>
-      <c r="H215" s="41" t="s">
         <v>1414</v>
       </c>
-      <c r="I215" s="41" t="s">
+      <c r="G215" s="39" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H215" s="39" t="s">
         <v>1415</v>
       </c>
-      <c r="J215" s="41" t="s">
-        <v>1274</v>
-      </c>
-      <c r="K215" s="41" t="s">
+      <c r="I215" s="39" t="s">
         <v>1416</v>
       </c>
+      <c r="J215" s="39" t="s">
+        <v>1275</v>
+      </c>
+      <c r="K215" s="39" t="s">
+        <v>1417</v>
+      </c>
       <c r="L215" s="6">
-        <f t="shared" si="69"/>
-        <v>60400</v>
+        <f t="shared" si="75"/>
+        <v>65000</v>
       </c>
       <c r="M215" s="6">
-        <f t="shared" si="70"/>
-        <v>60400</v>
+        <f t="shared" si="76"/>
+        <v>65000</v>
       </c>
       <c r="N215" s="6">
-        <f t="shared" si="75"/>
-        <v>30750</v>
+        <f t="shared" si="81"/>
+        <v>33750</v>
       </c>
       <c r="O215" s="6">
-        <f t="shared" si="76"/>
-        <v>30750</v>
+        <f t="shared" si="82"/>
+        <v>33750</v>
       </c>
       <c r="P215" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>152</v>
       </c>
       <c r="Q215" s="7">
-        <f t="shared" si="77"/>
-        <v>389</v>
+        <f t="shared" si="83"/>
+        <v>419</v>
       </c>
       <c r="R215" s="7">
-        <f t="shared" si="78"/>
-        <v>336</v>
+        <f t="shared" si="84"/>
+        <v>556</v>
       </c>
       <c r="S215" s="7">
         <v>99.99</v>
       </c>
-      <c r="T215" s="42" t="s">
+      <c r="T215" s="40" t="s">
         <v>1228</v>
       </c>
-      <c r="U215" s="42" t="s">
+      <c r="U215" s="40" t="s">
         <v>1228</v>
       </c>
       <c r="V215" s="7"/>
@@ -19767,7 +19765,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P3 P4 P5 C3:O5 Q3:S5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:S5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="1438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="1439">
   <si>
     <t>ID</t>
   </si>
@@ -3845,7 +3845,7 @@
     <t>1E+106</t>
   </si>
   <si>
-    <t>9E+131</t>
+    <t>1E+131</t>
   </si>
   <si>
     <t>1E+160</t>
@@ -3869,7 +3869,7 @@
     <t>1E+109</t>
   </si>
   <si>
-    <t>9E+134</t>
+    <t>1E+134</t>
   </si>
   <si>
     <t>1E+163</t>
@@ -3890,7 +3890,7 @@
     <t>混沌骷髅</t>
   </si>
   <si>
-    <t>9E+137</t>
+    <t>1E+137</t>
   </si>
   <si>
     <t>1E+166</t>
@@ -3911,219 +3911,219 @@
     <t>1E+115</t>
   </si>
   <si>
+    <t>1E+140</t>
+  </si>
+  <si>
+    <t>1E+169</t>
+  </si>
+  <si>
+    <t>1E+57</t>
+  </si>
+  <si>
+    <t>1E+13</t>
+  </si>
+  <si>
+    <t>1E+102</t>
+  </si>
+  <si>
+    <t>180000000000</t>
+  </si>
+  <si>
+    <t>混沌毒蛇</t>
+  </si>
+  <si>
+    <t>1E+118</t>
+  </si>
+  <si>
+    <t>1E+143</t>
+  </si>
+  <si>
+    <t>1E+172</t>
+  </si>
+  <si>
+    <t>1E+59</t>
+  </si>
+  <si>
+    <t>1E+15</t>
+  </si>
+  <si>
+    <t>1E+105</t>
+  </si>
+  <si>
+    <t>185000000000</t>
+  </si>
+  <si>
+    <t>混沌野狼</t>
+  </si>
+  <si>
+    <t>1E+175</t>
+  </si>
+  <si>
+    <t>1E+17</t>
+  </si>
+  <si>
+    <t>1E+107</t>
+  </si>
+  <si>
+    <t>190000000000</t>
+  </si>
+  <si>
+    <t>混沌沙虫</t>
+  </si>
+  <si>
+    <t>1E+122</t>
+  </si>
+  <si>
+    <t>1E+178</t>
+  </si>
+  <si>
+    <t>1E+63</t>
+  </si>
+  <si>
+    <t>1E+19</t>
+  </si>
+  <si>
+    <t>195000000000</t>
+  </si>
+  <si>
+    <t>混沌小鹰</t>
+  </si>
+  <si>
+    <t>1E+181</t>
+  </si>
+  <si>
+    <t>1E+65</t>
+  </si>
+  <si>
+    <t>1E+21</t>
+  </si>
+  <si>
+    <t>1E+111</t>
+  </si>
+  <si>
+    <t>混沌角虫</t>
+  </si>
+  <si>
+    <t>1E+184</t>
+  </si>
+  <si>
+    <t>1E+67</t>
+  </si>
+  <si>
+    <t>1E+23</t>
+  </si>
+  <si>
+    <t>1E+113</t>
+  </si>
+  <si>
+    <t>210000000000</t>
+  </si>
+  <si>
+    <t>混沌蜈蚣</t>
+  </si>
+  <si>
+    <t>1E+187</t>
+  </si>
+  <si>
+    <t>1E+69</t>
+  </si>
+  <si>
+    <t>1E+25</t>
+  </si>
+  <si>
+    <t>220000000000</t>
+  </si>
+  <si>
+    <t>混沌钳虫</t>
+  </si>
+  <si>
+    <t>1E+130</t>
+  </si>
+  <si>
+    <t>1E+189</t>
+  </si>
+  <si>
+    <t>1E+70</t>
+  </si>
+  <si>
+    <t>1E+28</t>
+  </si>
+  <si>
+    <t>230000000000</t>
+  </si>
+  <si>
+    <t>混沌蠕虫</t>
+  </si>
+  <si>
+    <t>1E+132</t>
+  </si>
+  <si>
+    <t>1E+191</t>
+  </si>
+  <si>
+    <t>1E+71</t>
+  </si>
+  <si>
+    <t>1E+31</t>
+  </si>
+  <si>
+    <t>240000000000</t>
+  </si>
+  <si>
+    <t>混沌黑猪</t>
+  </si>
+  <si>
+    <t>1E+193</t>
+  </si>
+  <si>
+    <t>1E+72</t>
+  </si>
+  <si>
+    <t>1E+34</t>
+  </si>
+  <si>
+    <t>250000000000</t>
+  </si>
+  <si>
+    <t>混沌红猪</t>
+  </si>
+  <si>
+    <t>1E+136</t>
+  </si>
+  <si>
+    <t>1E+195</t>
+  </si>
+  <si>
+    <t>1E+73</t>
+  </si>
+  <si>
+    <t>1E+37</t>
+  </si>
+  <si>
+    <t>260000000000</t>
+  </si>
+  <si>
+    <t>混沌蝎蛇</t>
+  </si>
+  <si>
+    <t>1E+138</t>
+  </si>
+  <si>
+    <t>1E+197</t>
+  </si>
+  <si>
+    <t>1E+40</t>
+  </si>
+  <si>
+    <t>270000000000</t>
+  </si>
+  <si>
+    <t>混沌恶魔</t>
+  </si>
+  <si>
     <t>9E+140</t>
   </si>
   <si>
-    <t>1E+169</t>
-  </si>
-  <si>
-    <t>1E+57</t>
-  </si>
-  <si>
-    <t>1E+13</t>
-  </si>
-  <si>
-    <t>1E+102</t>
-  </si>
-  <si>
-    <t>180000000000</t>
-  </si>
-  <si>
-    <t>混沌毒蛇</t>
-  </si>
-  <si>
-    <t>1E+118</t>
-  </si>
-  <si>
-    <t>9E+143</t>
-  </si>
-  <si>
-    <t>1E+172</t>
-  </si>
-  <si>
-    <t>1E+59</t>
-  </si>
-  <si>
-    <t>1E+15</t>
-  </si>
-  <si>
-    <t>1E+105</t>
-  </si>
-  <si>
-    <t>185000000000</t>
-  </si>
-  <si>
-    <t>混沌野狼</t>
-  </si>
-  <si>
-    <t>1E+175</t>
-  </si>
-  <si>
-    <t>1E+17</t>
-  </si>
-  <si>
-    <t>1E+107</t>
-  </si>
-  <si>
-    <t>190000000000</t>
-  </si>
-  <si>
-    <t>混沌沙虫</t>
-  </si>
-  <si>
-    <t>1E+122</t>
-  </si>
-  <si>
-    <t>1E+178</t>
-  </si>
-  <si>
-    <t>1E+63</t>
-  </si>
-  <si>
-    <t>1E+19</t>
-  </si>
-  <si>
-    <t>195000000000</t>
-  </si>
-  <si>
-    <t>混沌小鹰</t>
-  </si>
-  <si>
-    <t>1E+181</t>
-  </si>
-  <si>
-    <t>1E+65</t>
-  </si>
-  <si>
-    <t>1E+21</t>
-  </si>
-  <si>
-    <t>1E+111</t>
-  </si>
-  <si>
-    <t>混沌角虫</t>
-  </si>
-  <si>
-    <t>1E+184</t>
-  </si>
-  <si>
-    <t>1E+67</t>
-  </si>
-  <si>
-    <t>1E+23</t>
-  </si>
-  <si>
-    <t>1E+113</t>
-  </si>
-  <si>
-    <t>210000000000</t>
-  </si>
-  <si>
-    <t>混沌蜈蚣</t>
-  </si>
-  <si>
-    <t>1E+187</t>
-  </si>
-  <si>
-    <t>1E+69</t>
-  </si>
-  <si>
-    <t>1E+25</t>
-  </si>
-  <si>
-    <t>220000000000</t>
-  </si>
-  <si>
-    <t>混沌钳虫</t>
-  </si>
-  <si>
-    <t>1E+130</t>
-  </si>
-  <si>
-    <t>1E+189</t>
-  </si>
-  <si>
-    <t>1E+70</t>
-  </si>
-  <si>
-    <t>1E+28</t>
-  </si>
-  <si>
-    <t>230000000000</t>
-  </si>
-  <si>
-    <t>混沌蠕虫</t>
-  </si>
-  <si>
-    <t>1E+132</t>
-  </si>
-  <si>
-    <t>1E+191</t>
-  </si>
-  <si>
-    <t>1E+71</t>
-  </si>
-  <si>
-    <t>1E+31</t>
-  </si>
-  <si>
-    <t>240000000000</t>
-  </si>
-  <si>
-    <t>混沌黑猪</t>
-  </si>
-  <si>
-    <t>1E+134</t>
-  </si>
-  <si>
-    <t>1E+193</t>
-  </si>
-  <si>
-    <t>1E+72</t>
-  </si>
-  <si>
-    <t>1E+34</t>
-  </si>
-  <si>
-    <t>250000000000</t>
-  </si>
-  <si>
-    <t>混沌红猪</t>
-  </si>
-  <si>
-    <t>1E+136</t>
-  </si>
-  <si>
-    <t>1E+195</t>
-  </si>
-  <si>
-    <t>1E+73</t>
-  </si>
-  <si>
-    <t>1E+37</t>
-  </si>
-  <si>
-    <t>260000000000</t>
-  </si>
-  <si>
-    <t>混沌蝎蛇</t>
-  </si>
-  <si>
-    <t>1E+138</t>
-  </si>
-  <si>
-    <t>1E+197</t>
-  </si>
-  <si>
-    <t>1E+40</t>
-  </si>
-  <si>
-    <t>270000000000</t>
-  </si>
-  <si>
-    <t>混沌恶魔</t>
-  </si>
-  <si>
     <t>1E+199</t>
   </si>
   <si>
@@ -4199,73 +4199,76 @@
     <t>混沌树妖</t>
   </si>
   <si>
-    <t>9E+107</t>
-  </si>
-  <si>
-    <t>256E+160</t>
-  </si>
-  <si>
-    <t>32E+64</t>
-  </si>
-  <si>
-    <t>32E+92</t>
+    <t>1E+209</t>
+  </si>
+  <si>
+    <t>1E+80</t>
+  </si>
+  <si>
+    <t>1E+58</t>
+  </si>
+  <si>
+    <t>330000000000</t>
   </si>
   <si>
     <t>混沌侍卫</t>
   </si>
   <si>
-    <t>9E+108</t>
-  </si>
-  <si>
-    <t>256E+161</t>
-  </si>
-  <si>
-    <t>32E+65</t>
-  </si>
-  <si>
-    <t>32E+93</t>
+    <t>1E+152</t>
+  </si>
+  <si>
+    <t>1E+211</t>
+  </si>
+  <si>
+    <t>1E+81</t>
+  </si>
+  <si>
+    <t>340000000000</t>
   </si>
   <si>
     <t>混沌剧毒</t>
   </si>
   <si>
-    <t>9E+109</t>
-  </si>
-  <si>
-    <t>256E+162</t>
-  </si>
-  <si>
-    <t>32E+94</t>
+    <t>1E+213</t>
+  </si>
+  <si>
+    <t>1E+64</t>
+  </si>
+  <si>
+    <t>350000000000</t>
   </si>
   <si>
     <t>混沌锤兵</t>
   </si>
   <si>
-    <t>9E+110</t>
-  </si>
-  <si>
-    <t>256E+163</t>
-  </si>
-  <si>
-    <t>32E+67</t>
-  </si>
-  <si>
-    <t>32E+95</t>
+    <t>1E+156</t>
+  </si>
+  <si>
+    <t>1E+215</t>
+  </si>
+  <si>
+    <t>1E+83</t>
+  </si>
+  <si>
+    <t>1E+144</t>
+  </si>
+  <si>
+    <t>360000000000</t>
   </si>
   <si>
     <t>混沌魔牛</t>
   </si>
   <si>
-    <t>9E+111</t>
-  </si>
-  <si>
-    <t>256E+164</t>
-  </si>
-  <si>
-    <t>32E+68</t>
-  </si>
-  <si>
-    <t>32E+96</t>
+    <t>1E+158</t>
+  </si>
+  <si>
+    <t>1E+217</t>
+  </si>
+  <si>
+    <t>1E+84</t>
+  </si>
+  <si>
+    <t>370000000000</t>
   </si>
   <si>
     <t>混沌水龙</t>
@@ -4997,7 +5000,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5005,9 +5008,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5033,10 +5036,22 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -5060,7 +5075,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
@@ -5678,13 +5701,13 @@
       <c r="F6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="38" t="s">
         <v>37</v>
       </c>
       <c r="J6" s="1">
@@ -9421,7 +9444,7 @@
       <c r="H65" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="I65" s="30" t="s">
+      <c r="I65" s="38" t="s">
         <v>440</v>
       </c>
       <c r="J65" s="1">
@@ -9490,7 +9513,7 @@
       <c r="H66" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="I66" s="30" t="s">
+      <c r="I66" s="38" t="s">
         <v>447</v>
       </c>
       <c r="J66" s="1">
@@ -9559,7 +9582,7 @@
       <c r="H67" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="I67" s="30" t="s">
+      <c r="I67" s="38" t="s">
         <v>454</v>
       </c>
       <c r="J67" s="1">
@@ -9628,7 +9651,7 @@
       <c r="H68" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="I68" s="30" t="s">
+      <c r="I68" s="38" t="s">
         <v>461</v>
       </c>
       <c r="J68" s="1">
@@ -9694,10 +9717,10 @@
       <c r="G69" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="H69" s="30" t="s">
+      <c r="H69" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="I69" s="30" t="s">
+      <c r="I69" s="38" t="s">
         <v>468</v>
       </c>
       <c r="J69" s="1">
@@ -9760,13 +9783,13 @@
       <c r="F70" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="G70" s="30" t="s">
+      <c r="G70" s="38" t="s">
         <v>473</v>
       </c>
-      <c r="H70" s="30" t="s">
+      <c r="H70" s="38" t="s">
         <v>474</v>
       </c>
-      <c r="I70" s="30" t="s">
+      <c r="I70" s="38" t="s">
         <v>475</v>
       </c>
       <c r="J70" s="1">
@@ -9829,13 +9852,13 @@
       <c r="F71" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="G71" s="30" t="s">
+      <c r="G71" s="38" t="s">
         <v>480</v>
       </c>
-      <c r="H71" s="30" t="s">
+      <c r="H71" s="38" t="s">
         <v>481</v>
       </c>
-      <c r="I71" s="30" t="s">
+      <c r="I71" s="38" t="s">
         <v>482</v>
       </c>
       <c r="J71" s="1">
@@ -9898,13 +9921,13 @@
       <c r="F72" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="G72" s="30" t="s">
+      <c r="G72" s="38" t="s">
         <v>487</v>
       </c>
-      <c r="H72" s="30" t="s">
+      <c r="H72" s="38" t="s">
         <v>488</v>
       </c>
-      <c r="I72" s="30" t="s">
+      <c r="I72" s="38" t="s">
         <v>489</v>
       </c>
       <c r="J72" s="1">
@@ -9967,13 +9990,13 @@
       <c r="F73" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G73" s="30" t="s">
+      <c r="G73" s="38" t="s">
         <v>494</v>
       </c>
-      <c r="H73" s="30" t="s">
+      <c r="H73" s="38" t="s">
         <v>495</v>
       </c>
-      <c r="I73" s="30" t="s">
+      <c r="I73" s="38" t="s">
         <v>496</v>
       </c>
       <c r="J73" s="1">
@@ -10036,13 +10059,13 @@
       <c r="F74" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="G74" s="30" t="s">
+      <c r="G74" s="38" t="s">
         <v>501</v>
       </c>
-      <c r="H74" s="30" t="s">
+      <c r="H74" s="38" t="s">
         <v>502</v>
       </c>
-      <c r="I74" s="30" t="s">
+      <c r="I74" s="38" t="s">
         <v>503</v>
       </c>
       <c r="J74" s="1">
@@ -10105,13 +10128,13 @@
       <c r="F75" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="G75" s="30" t="s">
+      <c r="G75" s="38" t="s">
         <v>508</v>
       </c>
-      <c r="H75" s="30" t="s">
+      <c r="H75" s="38" t="s">
         <v>509</v>
       </c>
-      <c r="I75" s="30" t="s">
+      <c r="I75" s="38" t="s">
         <v>510</v>
       </c>
       <c r="J75" s="1">
@@ -10151,7 +10174,7 @@
       <c r="U75" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="V75" s="30" t="s">
+      <c r="V75" s="38" t="s">
         <v>511</v>
       </c>
       <c r="W75" s="11"/>
@@ -10175,13 +10198,13 @@
       <c r="F76" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G76" s="30" t="s">
+      <c r="G76" s="38" t="s">
         <v>515</v>
       </c>
-      <c r="H76" s="30" t="s">
+      <c r="H76" s="38" t="s">
         <v>516</v>
       </c>
-      <c r="I76" s="30" t="s">
+      <c r="I76" s="38" t="s">
         <v>517</v>
       </c>
       <c r="J76" s="1">
@@ -10243,13 +10266,13 @@
       <c r="F77" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="G77" s="30" t="s">
+      <c r="G77" s="38" t="s">
         <v>521</v>
       </c>
-      <c r="H77" s="30" t="s">
+      <c r="H77" s="38" t="s">
         <v>522</v>
       </c>
-      <c r="I77" s="30" t="s">
+      <c r="I77" s="38" t="s">
         <v>523</v>
       </c>
       <c r="J77" s="1">
@@ -10311,13 +10334,13 @@
       <c r="F78" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="G78" s="30" t="s">
+      <c r="G78" s="38" t="s">
         <v>527</v>
       </c>
-      <c r="H78" s="30" t="s">
+      <c r="H78" s="38" t="s">
         <v>528</v>
       </c>
-      <c r="I78" s="30" t="s">
+      <c r="I78" s="38" t="s">
         <v>529</v>
       </c>
       <c r="J78" s="1">
@@ -10379,13 +10402,13 @@
       <c r="F79" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G79" s="30" t="s">
+      <c r="G79" s="38" t="s">
         <v>533</v>
       </c>
-      <c r="H79" s="30" t="s">
+      <c r="H79" s="38" t="s">
         <v>534</v>
       </c>
-      <c r="I79" s="30" t="s">
+      <c r="I79" s="38" t="s">
         <v>535</v>
       </c>
       <c r="J79" s="1">
@@ -10447,13 +10470,13 @@
       <c r="F80" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="G80" s="30" t="s">
+      <c r="G80" s="38" t="s">
         <v>539</v>
       </c>
-      <c r="H80" s="30" t="s">
+      <c r="H80" s="38" t="s">
         <v>540</v>
       </c>
-      <c r="I80" s="30" t="s">
+      <c r="I80" s="38" t="s">
         <v>541</v>
       </c>
       <c r="J80" s="1">
@@ -10515,13 +10538,13 @@
       <c r="F81" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="G81" s="30" t="s">
+      <c r="G81" s="38" t="s">
         <v>545</v>
       </c>
-      <c r="H81" s="30" t="s">
+      <c r="H81" s="38" t="s">
         <v>546</v>
       </c>
-      <c r="I81" s="30" t="s">
+      <c r="I81" s="38" t="s">
         <v>547</v>
       </c>
       <c r="J81" s="1">
@@ -10585,13 +10608,13 @@
       <c r="F82" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G82" s="30" t="s">
+      <c r="G82" s="38" t="s">
         <v>551</v>
       </c>
-      <c r="H82" s="30" t="s">
+      <c r="H82" s="38" t="s">
         <v>552</v>
       </c>
-      <c r="I82" s="30" t="s">
+      <c r="I82" s="38" t="s">
         <v>553</v>
       </c>
       <c r="J82" s="1">
@@ -10655,13 +10678,13 @@
       <c r="F83" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="G83" s="30" t="s">
+      <c r="G83" s="38" t="s">
         <v>557</v>
       </c>
-      <c r="H83" s="30" t="s">
+      <c r="H83" s="38" t="s">
         <v>558</v>
       </c>
-      <c r="I83" s="30" t="s">
+      <c r="I83" s="38" t="s">
         <v>559</v>
       </c>
       <c r="J83" s="1">
@@ -10725,13 +10748,13 @@
       <c r="F84" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G84" s="30" t="s">
+      <c r="G84" s="38" t="s">
         <v>563</v>
       </c>
-      <c r="H84" s="30" t="s">
+      <c r="H84" s="38" t="s">
         <v>564</v>
       </c>
-      <c r="I84" s="30" t="s">
+      <c r="I84" s="38" t="s">
         <v>565</v>
       </c>
       <c r="J84" s="1">
@@ -10795,13 +10818,13 @@
       <c r="F85" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="G85" s="30" t="s">
+      <c r="G85" s="38" t="s">
         <v>569</v>
       </c>
-      <c r="H85" s="30" t="s">
+      <c r="H85" s="38" t="s">
         <v>570</v>
       </c>
-      <c r="I85" s="30" t="s">
+      <c r="I85" s="38" t="s">
         <v>571</v>
       </c>
       <c r="J85" s="1">
@@ -10865,13 +10888,13 @@
       <c r="F86" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="G86" s="30" t="s">
+      <c r="G86" s="38" t="s">
         <v>575</v>
       </c>
-      <c r="H86" s="30" t="s">
+      <c r="H86" s="38" t="s">
         <v>539</v>
       </c>
-      <c r="I86" s="30" t="s">
+      <c r="I86" s="38" t="s">
         <v>576</v>
       </c>
       <c r="J86" s="1">
@@ -10935,13 +10958,13 @@
       <c r="F87" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="G87" s="30" t="s">
+      <c r="G87" s="38" t="s">
         <v>580</v>
       </c>
-      <c r="H87" s="30" t="s">
+      <c r="H87" s="38" t="s">
         <v>581</v>
       </c>
-      <c r="I87" s="30" t="s">
+      <c r="I87" s="38" t="s">
         <v>582</v>
       </c>
       <c r="J87" s="1">
@@ -11005,13 +11028,13 @@
       <c r="F88" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="G88" s="30" t="s">
+      <c r="G88" s="38" t="s">
         <v>489</v>
       </c>
-      <c r="H88" s="30" t="s">
+      <c r="H88" s="38" t="s">
         <v>454</v>
       </c>
-      <c r="I88" s="30" t="s">
+      <c r="I88" s="38" t="s">
         <v>586</v>
       </c>
       <c r="J88" s="1">
@@ -11075,13 +11098,13 @@
       <c r="F89" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="G89" s="30" t="s">
+      <c r="G89" s="38" t="s">
         <v>503</v>
       </c>
-      <c r="H89" s="30" t="s">
+      <c r="H89" s="38" t="s">
         <v>590</v>
       </c>
-      <c r="I89" s="30" t="s">
+      <c r="I89" s="38" t="s">
         <v>591</v>
       </c>
       <c r="J89" s="1">
@@ -11145,13 +11168,13 @@
       <c r="F90" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G90" s="30" t="s">
+      <c r="G90" s="38" t="s">
         <v>595</v>
       </c>
-      <c r="H90" s="30" t="s">
+      <c r="H90" s="38" t="s">
         <v>580</v>
       </c>
-      <c r="I90" s="30" t="s">
+      <c r="I90" s="38" t="s">
         <v>596</v>
       </c>
       <c r="J90" s="1">
@@ -11215,13 +11238,13 @@
       <c r="F91" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="G91" s="30" t="s">
+      <c r="G91" s="38" t="s">
         <v>600</v>
       </c>
-      <c r="H91" s="30" t="s">
+      <c r="H91" s="38" t="s">
         <v>601</v>
       </c>
-      <c r="I91" s="30" t="s">
+      <c r="I91" s="38" t="s">
         <v>602</v>
       </c>
       <c r="J91" s="1">
@@ -11285,13 +11308,13 @@
       <c r="F92" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="G92" s="30" t="s">
+      <c r="G92" s="38" t="s">
         <v>606</v>
       </c>
-      <c r="H92" s="30" t="s">
+      <c r="H92" s="38" t="s">
         <v>607</v>
       </c>
-      <c r="I92" s="30" t="s">
+      <c r="I92" s="38" t="s">
         <v>608</v>
       </c>
       <c r="J92" s="1">
@@ -11355,13 +11378,13 @@
       <c r="F93" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G93" s="30" t="s">
+      <c r="G93" s="38" t="s">
         <v>612</v>
       </c>
-      <c r="H93" s="30" t="s">
+      <c r="H93" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="I93" s="30" t="s">
+      <c r="I93" s="38" t="s">
         <v>614</v>
       </c>
       <c r="J93" s="1">
@@ -11425,13 +11448,13 @@
       <c r="F94" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="G94" s="30" t="s">
+      <c r="G94" s="38" t="s">
         <v>571</v>
       </c>
-      <c r="H94" s="30" t="s">
+      <c r="H94" s="38" t="s">
         <v>618</v>
       </c>
-      <c r="I94" s="30" t="s">
+      <c r="I94" s="38" t="s">
         <v>619</v>
       </c>
       <c r="J94" s="1">
@@ -11495,13 +11518,13 @@
       <c r="F95" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="G95" s="30" t="s">
+      <c r="G95" s="38" t="s">
         <v>576</v>
       </c>
-      <c r="H95" s="30" t="s">
+      <c r="H95" s="38" t="s">
         <v>623</v>
       </c>
-      <c r="I95" s="30" t="s">
+      <c r="I95" s="38" t="s">
         <v>624</v>
       </c>
       <c r="J95" s="1">
@@ -11563,13 +11586,13 @@
       <c r="F96" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="G96" s="30" t="s">
+      <c r="G96" s="38" t="s">
         <v>582</v>
       </c>
-      <c r="H96" s="30" t="s">
+      <c r="H96" s="38" t="s">
         <v>628</v>
       </c>
-      <c r="I96" s="30" t="s">
+      <c r="I96" s="38" t="s">
         <v>629</v>
       </c>
       <c r="J96" s="1">
@@ -11627,13 +11650,13 @@
       <c r="F97" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="G97" s="30" t="s">
+      <c r="G97" s="38" t="s">
         <v>586</v>
       </c>
-      <c r="H97" s="30" t="s">
+      <c r="H97" s="38" t="s">
         <v>633</v>
       </c>
-      <c r="I97" s="30" t="s">
+      <c r="I97" s="38" t="s">
         <v>634</v>
       </c>
       <c r="J97" s="1">
@@ -11691,13 +11714,13 @@
       <c r="F98" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="G98" s="30" t="s">
+      <c r="G98" s="38" t="s">
         <v>638</v>
       </c>
-      <c r="H98" s="30" t="s">
+      <c r="H98" s="38" t="s">
         <v>639</v>
       </c>
-      <c r="I98" s="30" t="s">
+      <c r="I98" s="38" t="s">
         <v>640</v>
       </c>
       <c r="J98" s="1">
@@ -11755,13 +11778,13 @@
       <c r="F99" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="G99" s="30" t="s">
+      <c r="G99" s="38" t="s">
         <v>644</v>
       </c>
-      <c r="H99" s="30" t="s">
+      <c r="H99" s="38" t="s">
         <v>645</v>
       </c>
-      <c r="I99" s="30" t="s">
+      <c r="I99" s="38" t="s">
         <v>646</v>
       </c>
       <c r="J99" s="1">
@@ -11819,13 +11842,13 @@
       <c r="F100" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="G100" s="30" t="s">
+      <c r="G100" s="38" t="s">
         <v>650</v>
       </c>
-      <c r="H100" s="30" t="s">
+      <c r="H100" s="38" t="s">
         <v>651</v>
       </c>
-      <c r="I100" s="30" t="s">
+      <c r="I100" s="38" t="s">
         <v>652</v>
       </c>
       <c r="J100" s="1">
@@ -11883,13 +11906,13 @@
       <c r="F101" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="G101" s="30" t="s">
+      <c r="G101" s="38" t="s">
         <v>656</v>
       </c>
-      <c r="H101" s="30" t="s">
+      <c r="H101" s="38" t="s">
         <v>657</v>
       </c>
-      <c r="I101" s="30" t="s">
+      <c r="I101" s="38" t="s">
         <v>658</v>
       </c>
       <c r="J101" s="1">
@@ -11947,13 +11970,13 @@
       <c r="F102" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="G102" s="30" t="s">
+      <c r="G102" s="38" t="s">
         <v>662</v>
       </c>
-      <c r="H102" s="30" t="s">
+      <c r="H102" s="38" t="s">
         <v>663</v>
       </c>
-      <c r="I102" s="30" t="s">
+      <c r="I102" s="38" t="s">
         <v>664</v>
       </c>
       <c r="J102" s="1">
@@ -12011,13 +12034,13 @@
       <c r="F103" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="G103" s="30" t="s">
+      <c r="G103" s="38" t="s">
         <v>668</v>
       </c>
-      <c r="H103" s="30" t="s">
+      <c r="H103" s="38" t="s">
         <v>669</v>
       </c>
-      <c r="I103" s="30" t="s">
+      <c r="I103" s="38" t="s">
         <v>670</v>
       </c>
       <c r="J103" s="1">
@@ -12075,13 +12098,13 @@
       <c r="F104" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="G104" s="30" t="s">
+      <c r="G104" s="38" t="s">
         <v>674</v>
       </c>
-      <c r="H104" s="30" t="s">
+      <c r="H104" s="38" t="s">
         <v>668</v>
       </c>
-      <c r="I104" s="30" t="s">
+      <c r="I104" s="38" t="s">
         <v>675</v>
       </c>
       <c r="J104" s="1">
@@ -12139,13 +12162,13 @@
       <c r="F105" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="G105" s="30" t="s">
+      <c r="G105" s="38" t="s">
         <v>679</v>
       </c>
-      <c r="H105" s="30" t="s">
+      <c r="H105" s="38" t="s">
         <v>674</v>
       </c>
-      <c r="I105" s="30" t="s">
+      <c r="I105" s="38" t="s">
         <v>680</v>
       </c>
       <c r="J105" s="1">
@@ -12205,13 +12228,13 @@
       <c r="F106" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="G106" s="30" t="s">
+      <c r="G106" s="38" t="s">
         <v>684</v>
       </c>
-      <c r="H106" s="30" t="s">
+      <c r="H106" s="38" t="s">
         <v>685</v>
       </c>
-      <c r="I106" s="30" t="s">
+      <c r="I106" s="38" t="s">
         <v>686</v>
       </c>
       <c r="J106" s="1">
@@ -12275,13 +12298,13 @@
       <c r="F107" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="G107" s="30" t="s">
+      <c r="G107" s="38" t="s">
         <v>690</v>
       </c>
-      <c r="H107" s="30" t="s">
+      <c r="H107" s="38" t="s">
         <v>691</v>
       </c>
-      <c r="I107" s="30" t="s">
+      <c r="I107" s="38" t="s">
         <v>692</v>
       </c>
       <c r="J107" s="1">
@@ -12345,13 +12368,13 @@
       <c r="F108" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="G108" s="30" t="s">
+      <c r="G108" s="38" t="s">
         <v>696</v>
       </c>
-      <c r="H108" s="30" t="s">
+      <c r="H108" s="38" t="s">
         <v>697</v>
       </c>
-      <c r="I108" s="30" t="s">
+      <c r="I108" s="38" t="s">
         <v>698</v>
       </c>
       <c r="J108" s="1">
@@ -12415,13 +12438,13 @@
       <c r="F109" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="G109" s="30" t="s">
+      <c r="G109" s="38" t="s">
         <v>702</v>
       </c>
-      <c r="H109" s="30" t="s">
+      <c r="H109" s="38" t="s">
         <v>703</v>
       </c>
-      <c r="I109" s="30" t="s">
+      <c r="I109" s="38" t="s">
         <v>704</v>
       </c>
       <c r="J109" s="1">
@@ -12485,13 +12508,13 @@
       <c r="F110" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="G110" s="30" t="s">
+      <c r="G110" s="38" t="s">
         <v>708</v>
       </c>
-      <c r="H110" s="30" t="s">
+      <c r="H110" s="38" t="s">
         <v>709</v>
       </c>
-      <c r="I110" s="30" t="s">
+      <c r="I110" s="38" t="s">
         <v>710</v>
       </c>
       <c r="J110" s="1">
@@ -12555,13 +12578,13 @@
       <c r="F111" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="G111" s="31" t="s">
+      <c r="G111" s="39" t="s">
         <v>714</v>
       </c>
-      <c r="H111" s="32" t="s">
+      <c r="H111" s="40" t="s">
         <v>714</v>
       </c>
-      <c r="I111" s="33" t="s">
+      <c r="I111" s="41" t="s">
         <v>715</v>
       </c>
       <c r="J111" s="1">
@@ -12594,10 +12617,10 @@
       <c r="T111" s="11">
         <v>90</v>
       </c>
-      <c r="U111" s="30" t="s">
+      <c r="U111" s="38" t="s">
         <v>716</v>
       </c>
-      <c r="V111" s="30" t="s">
+      <c r="V111" s="38" t="s">
         <v>716</v>
       </c>
       <c r="Y111" s="11"/>
@@ -12619,13 +12642,13 @@
       <c r="F112" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="G112" s="34" t="s">
+      <c r="G112" s="42" t="s">
         <v>720</v>
       </c>
-      <c r="H112" s="30" t="s">
+      <c r="H112" s="38" t="s">
         <v>720</v>
       </c>
-      <c r="I112" s="35" t="s">
+      <c r="I112" s="43" t="s">
         <v>721</v>
       </c>
       <c r="J112" s="1">
@@ -12663,10 +12686,10 @@
       <c r="T112" s="11">
         <v>90</v>
       </c>
-      <c r="U112" s="30" t="s">
+      <c r="U112" s="38" t="s">
         <v>722</v>
       </c>
-      <c r="V112" s="30" t="s">
+      <c r="V112" s="38" t="s">
         <v>722</v>
       </c>
       <c r="Y112" s="11"/>
@@ -12688,13 +12711,13 @@
       <c r="F113" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="G113" s="34" t="s">
+      <c r="G113" s="42" t="s">
         <v>726</v>
       </c>
-      <c r="H113" s="30" t="s">
+      <c r="H113" s="38" t="s">
         <v>726</v>
       </c>
-      <c r="I113" s="35" t="s">
+      <c r="I113" s="43" t="s">
         <v>727</v>
       </c>
       <c r="J113" s="1">
@@ -12732,10 +12755,10 @@
       <c r="T113" s="11">
         <v>90</v>
       </c>
-      <c r="U113" s="30" t="s">
+      <c r="U113" s="38" t="s">
         <v>728</v>
       </c>
-      <c r="V113" s="30" t="s">
+      <c r="V113" s="38" t="s">
         <v>728</v>
       </c>
       <c r="Y113" s="11"/>
@@ -12757,13 +12780,13 @@
       <c r="F114" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="G114" s="34" t="s">
+      <c r="G114" s="42" t="s">
         <v>732</v>
       </c>
-      <c r="H114" s="30" t="s">
+      <c r="H114" s="38" t="s">
         <v>732</v>
       </c>
-      <c r="I114" s="35" t="s">
+      <c r="I114" s="43" t="s">
         <v>733</v>
       </c>
       <c r="J114" s="1">
@@ -12801,10 +12824,10 @@
       <c r="T114" s="11">
         <v>90</v>
       </c>
-      <c r="U114" s="30" t="s">
+      <c r="U114" s="38" t="s">
         <v>734</v>
       </c>
-      <c r="V114" s="30" t="s">
+      <c r="V114" s="38" t="s">
         <v>734</v>
       </c>
       <c r="Y114" s="11"/>
@@ -12826,13 +12849,13 @@
       <c r="F115" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="G115" s="34" t="s">
+      <c r="G115" s="42" t="s">
         <v>738</v>
       </c>
-      <c r="H115" s="30" t="s">
+      <c r="H115" s="38" t="s">
         <v>738</v>
       </c>
-      <c r="I115" s="35" t="s">
+      <c r="I115" s="43" t="s">
         <v>739</v>
       </c>
       <c r="J115" s="1">
@@ -12870,10 +12893,10 @@
       <c r="T115" s="11">
         <v>90</v>
       </c>
-      <c r="U115" s="30" t="s">
+      <c r="U115" s="38" t="s">
         <v>740</v>
       </c>
-      <c r="V115" s="30" t="s">
+      <c r="V115" s="38" t="s">
         <v>740</v>
       </c>
       <c r="Y115" s="11"/>
@@ -12895,13 +12918,13 @@
       <c r="F116" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="G116" s="34" t="s">
+      <c r="G116" s="42" t="s">
         <v>744</v>
       </c>
-      <c r="H116" s="30" t="s">
+      <c r="H116" s="38" t="s">
         <v>744</v>
       </c>
-      <c r="I116" s="35" t="s">
+      <c r="I116" s="43" t="s">
         <v>745</v>
       </c>
       <c r="J116" s="1">
@@ -12939,10 +12962,10 @@
       <c r="T116" s="11">
         <v>90</v>
       </c>
-      <c r="U116" s="30" t="s">
+      <c r="U116" s="38" t="s">
         <v>746</v>
       </c>
-      <c r="V116" s="30" t="s">
+      <c r="V116" s="38" t="s">
         <v>746</v>
       </c>
       <c r="W116" s="11"/>
@@ -12966,13 +12989,13 @@
       <c r="F117" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="G117" s="34" t="s">
+      <c r="G117" s="42" t="s">
         <v>750</v>
       </c>
-      <c r="H117" s="30" t="s">
+      <c r="H117" s="38" t="s">
         <v>750</v>
       </c>
-      <c r="I117" s="35" t="s">
+      <c r="I117" s="43" t="s">
         <v>751</v>
       </c>
       <c r="J117" s="1">
@@ -13010,10 +13033,10 @@
       <c r="T117" s="11">
         <v>90</v>
       </c>
-      <c r="U117" s="30" t="s">
+      <c r="U117" s="38" t="s">
         <v>752</v>
       </c>
-      <c r="V117" s="30" t="s">
+      <c r="V117" s="38" t="s">
         <v>752</v>
       </c>
       <c r="W117" s="11"/>
@@ -13037,13 +13060,13 @@
       <c r="F118" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="G118" s="34" t="s">
+      <c r="G118" s="42" t="s">
         <v>756</v>
       </c>
-      <c r="H118" s="30" t="s">
+      <c r="H118" s="38" t="s">
         <v>756</v>
       </c>
-      <c r="I118" s="35" t="s">
+      <c r="I118" s="43" t="s">
         <v>757</v>
       </c>
       <c r="J118" s="1">
@@ -13081,10 +13104,10 @@
       <c r="T118" s="11">
         <v>90</v>
       </c>
-      <c r="U118" s="30" t="s">
+      <c r="U118" s="38" t="s">
         <v>758</v>
       </c>
-      <c r="V118" s="30" t="s">
+      <c r="V118" s="38" t="s">
         <v>758</v>
       </c>
       <c r="W118" s="11"/>
@@ -13108,13 +13131,13 @@
       <c r="F119" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="G119" s="34" t="s">
+      <c r="G119" s="42" t="s">
         <v>762</v>
       </c>
-      <c r="H119" s="30" t="s">
+      <c r="H119" s="38" t="s">
         <v>762</v>
       </c>
-      <c r="I119" s="35" t="s">
+      <c r="I119" s="43" t="s">
         <v>763</v>
       </c>
       <c r="J119" s="1">
@@ -13152,10 +13175,10 @@
       <c r="T119" s="11">
         <v>90</v>
       </c>
-      <c r="U119" s="30" t="s">
+      <c r="U119" s="38" t="s">
         <v>764</v>
       </c>
-      <c r="V119" s="30" t="s">
+      <c r="V119" s="38" t="s">
         <v>764</v>
       </c>
       <c r="W119" s="11"/>
@@ -13179,13 +13202,13 @@
       <c r="F120" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="G120" s="34" t="s">
+      <c r="G120" s="42" t="s">
         <v>768</v>
       </c>
-      <c r="H120" s="30" t="s">
+      <c r="H120" s="38" t="s">
         <v>768</v>
       </c>
-      <c r="I120" s="35" t="s">
+      <c r="I120" s="43" t="s">
         <v>769</v>
       </c>
       <c r="J120" s="1">
@@ -13223,10 +13246,10 @@
       <c r="T120" s="11">
         <v>90</v>
       </c>
-      <c r="U120" s="30" t="s">
+      <c r="U120" s="38" t="s">
         <v>770</v>
       </c>
-      <c r="V120" s="30" t="s">
+      <c r="V120" s="38" t="s">
         <v>770</v>
       </c>
       <c r="W120" s="11"/>
@@ -13250,13 +13273,13 @@
       <c r="F121" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="G121" s="34" t="s">
+      <c r="G121" s="42" t="s">
         <v>715</v>
       </c>
-      <c r="H121" s="30" t="s">
+      <c r="H121" s="38" t="s">
         <v>715</v>
       </c>
-      <c r="I121" s="35" t="s">
+      <c r="I121" s="43" t="s">
         <v>774</v>
       </c>
       <c r="J121" s="1">
@@ -13294,10 +13317,10 @@
       <c r="T121" s="11">
         <v>90</v>
       </c>
-      <c r="U121" s="30" t="s">
+      <c r="U121" s="38" t="s">
         <v>775</v>
       </c>
-      <c r="V121" s="30" t="s">
+      <c r="V121" s="38" t="s">
         <v>775</v>
       </c>
       <c r="W121" s="11"/>
@@ -13321,13 +13344,13 @@
       <c r="F122" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="G122" s="34" t="s">
+      <c r="G122" s="42" t="s">
         <v>779</v>
       </c>
-      <c r="H122" s="30" t="s">
+      <c r="H122" s="38" t="s">
         <v>779</v>
       </c>
-      <c r="I122" s="35" t="s">
+      <c r="I122" s="43" t="s">
         <v>780</v>
       </c>
       <c r="J122" s="1">
@@ -13366,10 +13389,10 @@
       <c r="T122" s="11">
         <v>90</v>
       </c>
-      <c r="U122" s="30" t="s">
+      <c r="U122" s="38" t="s">
         <v>781</v>
       </c>
-      <c r="V122" s="30" t="s">
+      <c r="V122" s="38" t="s">
         <v>781</v>
       </c>
       <c r="W122" s="11"/>
@@ -13393,13 +13416,13 @@
       <c r="F123" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="G123" s="34" t="s">
+      <c r="G123" s="42" t="s">
         <v>785</v>
       </c>
-      <c r="H123" s="30" t="s">
+      <c r="H123" s="38" t="s">
         <v>785</v>
       </c>
-      <c r="I123" s="35" t="s">
+      <c r="I123" s="43" t="s">
         <v>786</v>
       </c>
       <c r="J123" s="1">
@@ -13438,10 +13461,10 @@
       <c r="T123" s="11">
         <v>90</v>
       </c>
-      <c r="U123" s="30" t="s">
+      <c r="U123" s="38" t="s">
         <v>787</v>
       </c>
-      <c r="V123" s="30" t="s">
+      <c r="V123" s="38" t="s">
         <v>787</v>
       </c>
       <c r="W123" s="11"/>
@@ -13465,13 +13488,13 @@
       <c r="F124" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="G124" s="34" t="s">
+      <c r="G124" s="42" t="s">
         <v>791</v>
       </c>
-      <c r="H124" s="30" t="s">
+      <c r="H124" s="38" t="s">
         <v>791</v>
       </c>
-      <c r="I124" s="35" t="s">
+      <c r="I124" s="43" t="s">
         <v>792</v>
       </c>
       <c r="J124" s="1">
@@ -13510,10 +13533,10 @@
       <c r="T124" s="11">
         <v>90</v>
       </c>
-      <c r="U124" s="30" t="s">
+      <c r="U124" s="38" t="s">
         <v>793</v>
       </c>
-      <c r="V124" s="30" t="s">
+      <c r="V124" s="38" t="s">
         <v>793</v>
       </c>
       <c r="W124" s="11"/>
@@ -13537,13 +13560,13 @@
       <c r="F125" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="G125" s="34" t="s">
+      <c r="G125" s="42" t="s">
         <v>797</v>
       </c>
-      <c r="H125" s="30" t="s">
+      <c r="H125" s="38" t="s">
         <v>797</v>
       </c>
-      <c r="I125" s="35" t="s">
+      <c r="I125" s="43" t="s">
         <v>798</v>
       </c>
       <c r="J125" s="1">
@@ -13582,10 +13605,10 @@
       <c r="T125" s="11">
         <v>90</v>
       </c>
-      <c r="U125" s="30" t="s">
+      <c r="U125" s="38" t="s">
         <v>799</v>
       </c>
-      <c r="V125" s="30" t="s">
+      <c r="V125" s="38" t="s">
         <v>799</v>
       </c>
       <c r="W125" s="11"/>
@@ -13609,13 +13632,13 @@
       <c r="F126" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="G126" s="34" t="s">
+      <c r="G126" s="42" t="s">
         <v>803</v>
       </c>
-      <c r="H126" s="30" t="s">
+      <c r="H126" s="38" t="s">
         <v>803</v>
       </c>
-      <c r="I126" s="35" t="s">
+      <c r="I126" s="43" t="s">
         <v>804</v>
       </c>
       <c r="J126" s="1">
@@ -13654,10 +13677,10 @@
       <c r="T126" s="11">
         <v>90</v>
       </c>
-      <c r="U126" s="30" t="s">
+      <c r="U126" s="38" t="s">
         <v>805</v>
       </c>
-      <c r="V126" s="30" t="s">
+      <c r="V126" s="38" t="s">
         <v>805</v>
       </c>
       <c r="W126" s="11"/>
@@ -13681,13 +13704,13 @@
       <c r="F127" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="G127" s="34" t="s">
+      <c r="G127" s="42" t="s">
         <v>809</v>
       </c>
-      <c r="H127" s="30" t="s">
+      <c r="H127" s="38" t="s">
         <v>809</v>
       </c>
-      <c r="I127" s="35" t="s">
+      <c r="I127" s="43" t="s">
         <v>810</v>
       </c>
       <c r="J127" s="1">
@@ -13726,10 +13749,10 @@
       <c r="T127" s="11">
         <v>90</v>
       </c>
-      <c r="U127" s="30" t="s">
+      <c r="U127" s="38" t="s">
         <v>811</v>
       </c>
-      <c r="V127" s="30" t="s">
+      <c r="V127" s="38" t="s">
         <v>811</v>
       </c>
       <c r="W127" s="11"/>
@@ -13753,13 +13776,13 @@
       <c r="F128" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="G128" s="34" t="s">
+      <c r="G128" s="42" t="s">
         <v>815</v>
       </c>
-      <c r="H128" s="30" t="s">
+      <c r="H128" s="38" t="s">
         <v>815</v>
       </c>
-      <c r="I128" s="35" t="s">
+      <c r="I128" s="43" t="s">
         <v>816</v>
       </c>
       <c r="J128" s="1">
@@ -13798,10 +13821,10 @@
       <c r="T128" s="11">
         <v>90</v>
       </c>
-      <c r="U128" s="30" t="s">
+      <c r="U128" s="38" t="s">
         <v>817</v>
       </c>
-      <c r="V128" s="30" t="s">
+      <c r="V128" s="38" t="s">
         <v>817</v>
       </c>
       <c r="W128" s="11"/>
@@ -13825,13 +13848,13 @@
       <c r="F129" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="G129" s="34" t="s">
+      <c r="G129" s="42" t="s">
         <v>821</v>
       </c>
-      <c r="H129" s="30" t="s">
+      <c r="H129" s="38" t="s">
         <v>821</v>
       </c>
-      <c r="I129" s="35" t="s">
+      <c r="I129" s="43" t="s">
         <v>822</v>
       </c>
       <c r="J129" s="1">
@@ -13870,10 +13893,10 @@
       <c r="T129" s="11">
         <v>90</v>
       </c>
-      <c r="U129" s="30" t="s">
+      <c r="U129" s="38" t="s">
         <v>823</v>
       </c>
-      <c r="V129" s="30" t="s">
+      <c r="V129" s="38" t="s">
         <v>823</v>
       </c>
       <c r="W129" s="11"/>
@@ -13897,13 +13920,13 @@
       <c r="F130" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="G130" s="34" t="s">
+      <c r="G130" s="42" t="s">
         <v>827</v>
       </c>
-      <c r="H130" s="30" t="s">
+      <c r="H130" s="38" t="s">
         <v>827</v>
       </c>
-      <c r="I130" s="35" t="s">
+      <c r="I130" s="43" t="s">
         <v>828</v>
       </c>
       <c r="J130" s="1">
@@ -13942,10 +13965,10 @@
       <c r="T130" s="11">
         <v>90</v>
       </c>
-      <c r="U130" s="30" t="s">
+      <c r="U130" s="38" t="s">
         <v>829</v>
       </c>
-      <c r="V130" s="30" t="s">
+      <c r="V130" s="38" t="s">
         <v>829</v>
       </c>
       <c r="W130" s="11"/>
@@ -13967,13 +13990,13 @@
       <c r="F131" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="G131" s="34" t="s">
+      <c r="G131" s="42" t="s">
         <v>833</v>
       </c>
-      <c r="H131" s="30" t="s">
+      <c r="H131" s="38" t="s">
         <v>833</v>
       </c>
-      <c r="I131" s="35" t="s">
+      <c r="I131" s="43" t="s">
         <v>834</v>
       </c>
       <c r="J131" s="1">
@@ -14013,10 +14036,10 @@
       <c r="T131" s="11">
         <v>92</v>
       </c>
-      <c r="U131" s="30" t="s">
+      <c r="U131" s="38" t="s">
         <v>835</v>
       </c>
-      <c r="V131" s="30" t="s">
+      <c r="V131" s="38" t="s">
         <v>835</v>
       </c>
     </row>
@@ -14033,13 +14056,13 @@
       <c r="F132" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="G132" s="34" t="s">
+      <c r="G132" s="42" t="s">
         <v>839</v>
       </c>
-      <c r="H132" s="30" t="s">
+      <c r="H132" s="38" t="s">
         <v>839</v>
       </c>
-      <c r="I132" s="35" t="s">
+      <c r="I132" s="43" t="s">
         <v>840</v>
       </c>
       <c r="J132" s="1">
@@ -14079,10 +14102,10 @@
       <c r="T132" s="11">
         <v>94</v>
       </c>
-      <c r="U132" s="30" t="s">
+      <c r="U132" s="38" t="s">
         <v>841</v>
       </c>
-      <c r="V132" s="30" t="s">
+      <c r="V132" s="38" t="s">
         <v>841</v>
       </c>
     </row>
@@ -14099,13 +14122,13 @@
       <c r="F133" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="G133" s="34" t="s">
+      <c r="G133" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="H133" s="30" t="s">
+      <c r="H133" s="38" t="s">
         <v>845</v>
       </c>
-      <c r="I133" s="35" t="s">
+      <c r="I133" s="43" t="s">
         <v>846</v>
       </c>
       <c r="J133" s="1">
@@ -14145,10 +14168,10 @@
       <c r="T133" s="11">
         <v>96</v>
       </c>
-      <c r="U133" s="30" t="s">
+      <c r="U133" s="38" t="s">
         <v>847</v>
       </c>
-      <c r="V133" s="30" t="s">
+      <c r="V133" s="38" t="s">
         <v>847</v>
       </c>
     </row>
@@ -14165,13 +14188,13 @@
       <c r="F134" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="G134" s="34" t="s">
+      <c r="G134" s="42" t="s">
         <v>851</v>
       </c>
-      <c r="H134" s="30" t="s">
+      <c r="H134" s="38" t="s">
         <v>851</v>
       </c>
-      <c r="I134" s="35" t="s">
+      <c r="I134" s="43" t="s">
         <v>852</v>
       </c>
       <c r="J134" s="1">
@@ -14211,10 +14234,10 @@
       <c r="T134" s="11">
         <v>98</v>
       </c>
-      <c r="U134" s="30" t="s">
+      <c r="U134" s="38" t="s">
         <v>853</v>
       </c>
-      <c r="V134" s="30" t="s">
+      <c r="V134" s="38" t="s">
         <v>853</v>
       </c>
     </row>
@@ -14231,13 +14254,13 @@
       <c r="F135" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="G135" s="34" t="s">
+      <c r="G135" s="42" t="s">
         <v>857</v>
       </c>
-      <c r="H135" s="30" t="s">
+      <c r="H135" s="38" t="s">
         <v>857</v>
       </c>
-      <c r="I135" s="35" t="s">
+      <c r="I135" s="43" t="s">
         <v>858</v>
       </c>
       <c r="J135" s="1">
@@ -14277,10 +14300,10 @@
       <c r="T135" s="11">
         <v>99</v>
       </c>
-      <c r="U135" s="30" t="s">
+      <c r="U135" s="38" t="s">
         <v>859</v>
       </c>
-      <c r="V135" s="30" t="s">
+      <c r="V135" s="38" t="s">
         <v>859</v>
       </c>
     </row>
@@ -14297,13 +14320,13 @@
       <c r="F136" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="G136" s="34" t="s">
+      <c r="G136" s="42" t="s">
         <v>863</v>
       </c>
-      <c r="H136" s="30" t="s">
+      <c r="H136" s="38" t="s">
         <v>863</v>
       </c>
-      <c r="I136" s="35" t="s">
+      <c r="I136" s="43" t="s">
         <v>864</v>
       </c>
       <c r="J136" s="1">
@@ -14343,10 +14366,10 @@
       <c r="T136" s="11">
         <v>99.2</v>
       </c>
-      <c r="U136" s="30" t="s">
+      <c r="U136" s="38" t="s">
         <v>865</v>
       </c>
-      <c r="V136" s="30" t="s">
+      <c r="V136" s="38" t="s">
         <v>865</v>
       </c>
     </row>
@@ -14363,13 +14386,13 @@
       <c r="F137" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="G137" s="34" t="s">
+      <c r="G137" s="42" t="s">
         <v>869</v>
       </c>
-      <c r="H137" s="30" t="s">
+      <c r="H137" s="38" t="s">
         <v>869</v>
       </c>
-      <c r="I137" s="35" t="s">
+      <c r="I137" s="43" t="s">
         <v>870</v>
       </c>
       <c r="J137" s="1">
@@ -14409,10 +14432,10 @@
       <c r="T137" s="11">
         <v>99.4</v>
       </c>
-      <c r="U137" s="30" t="s">
+      <c r="U137" s="38" t="s">
         <v>871</v>
       </c>
-      <c r="V137" s="30" t="s">
+      <c r="V137" s="38" t="s">
         <v>871</v>
       </c>
     </row>
@@ -14429,13 +14452,13 @@
       <c r="F138" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="G138" s="34" t="s">
+      <c r="G138" s="42" t="s">
         <v>875</v>
       </c>
-      <c r="H138" s="30" t="s">
+      <c r="H138" s="38" t="s">
         <v>875</v>
       </c>
-      <c r="I138" s="35" t="s">
+      <c r="I138" s="43" t="s">
         <v>876</v>
       </c>
       <c r="J138" s="1">
@@ -14475,10 +14498,10 @@
       <c r="T138" s="11">
         <v>99.6</v>
       </c>
-      <c r="U138" s="30" t="s">
+      <c r="U138" s="38" t="s">
         <v>877</v>
       </c>
-      <c r="V138" s="30" t="s">
+      <c r="V138" s="38" t="s">
         <v>877</v>
       </c>
     </row>
@@ -14495,13 +14518,13 @@
       <c r="F139" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="G139" s="34" t="s">
+      <c r="G139" s="42" t="s">
         <v>881</v>
       </c>
-      <c r="H139" s="30" t="s">
+      <c r="H139" s="38" t="s">
         <v>881</v>
       </c>
-      <c r="I139" s="35" t="s">
+      <c r="I139" s="43" t="s">
         <v>882</v>
       </c>
       <c r="J139" s="1">
@@ -14541,10 +14564,10 @@
       <c r="T139" s="11">
         <v>99.8</v>
       </c>
-      <c r="U139" s="30" t="s">
+      <c r="U139" s="38" t="s">
         <v>883</v>
       </c>
-      <c r="V139" s="30" t="s">
+      <c r="V139" s="38" t="s">
         <v>883</v>
       </c>
     </row>
@@ -14561,13 +14584,13 @@
       <c r="F140" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="G140" s="34" t="s">
+      <c r="G140" s="42" t="s">
         <v>887</v>
       </c>
-      <c r="H140" s="30" t="s">
+      <c r="H140" s="38" t="s">
         <v>887</v>
       </c>
-      <c r="I140" s="35" t="s">
+      <c r="I140" s="43" t="s">
         <v>888</v>
       </c>
       <c r="J140" s="1">
@@ -14607,10 +14630,10 @@
       <c r="T140" s="11">
         <v>99.9</v>
       </c>
-      <c r="U140" s="30" t="s">
+      <c r="U140" s="38" t="s">
         <v>889</v>
       </c>
-      <c r="V140" s="30" t="s">
+      <c r="V140" s="38" t="s">
         <v>889</v>
       </c>
     </row>
@@ -14629,13 +14652,13 @@
       <c r="F141" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="G141" s="34" t="s">
+      <c r="G141" s="42" t="s">
         <v>893</v>
       </c>
-      <c r="H141" s="30" t="s">
+      <c r="H141" s="38" t="s">
         <v>893</v>
       </c>
-      <c r="I141" s="35" t="s">
+      <c r="I141" s="43" t="s">
         <v>894</v>
       </c>
       <c r="J141" s="1">
@@ -14674,10 +14697,10 @@
       <c r="T141" s="11">
         <v>99.92</v>
       </c>
-      <c r="U141" s="30" t="s">
+      <c r="U141" s="38" t="s">
         <v>895</v>
       </c>
-      <c r="V141" s="30" t="s">
+      <c r="V141" s="38" t="s">
         <v>895</v>
       </c>
       <c r="W141" s="11"/>
@@ -14701,13 +14724,13 @@
       <c r="F142" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="G142" s="34" t="s">
+      <c r="G142" s="42" t="s">
         <v>899</v>
       </c>
-      <c r="H142" s="30" t="s">
+      <c r="H142" s="38" t="s">
         <v>899</v>
       </c>
-      <c r="I142" s="35" t="s">
+      <c r="I142" s="43" t="s">
         <v>900</v>
       </c>
       <c r="J142" s="1">
@@ -14746,10 +14769,10 @@
       <c r="T142" s="11">
         <v>99.94</v>
       </c>
-      <c r="U142" s="30" t="s">
+      <c r="U142" s="38" t="s">
         <v>901</v>
       </c>
-      <c r="V142" s="30" t="s">
+      <c r="V142" s="38" t="s">
         <v>901</v>
       </c>
       <c r="W142" s="11"/>
@@ -14773,13 +14796,13 @@
       <c r="F143" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="G143" s="34" t="s">
+      <c r="G143" s="42" t="s">
         <v>905</v>
       </c>
-      <c r="H143" s="30" t="s">
+      <c r="H143" s="38" t="s">
         <v>905</v>
       </c>
-      <c r="I143" s="35" t="s">
+      <c r="I143" s="43" t="s">
         <v>906</v>
       </c>
       <c r="J143" s="1">
@@ -14818,10 +14841,10 @@
       <c r="T143" s="11">
         <v>99.96</v>
       </c>
-      <c r="U143" s="30" t="s">
+      <c r="U143" s="38" t="s">
         <v>907</v>
       </c>
-      <c r="V143" s="30" t="s">
+      <c r="V143" s="38" t="s">
         <v>907</v>
       </c>
       <c r="W143" s="11"/>
@@ -14845,13 +14868,13 @@
       <c r="F144" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="G144" s="34" t="s">
+      <c r="G144" s="42" t="s">
         <v>911</v>
       </c>
-      <c r="H144" s="30" t="s">
+      <c r="H144" s="38" t="s">
         <v>911</v>
       </c>
-      <c r="I144" s="35" t="s">
+      <c r="I144" s="43" t="s">
         <v>912</v>
       </c>
       <c r="J144" s="1">
@@ -14890,10 +14913,10 @@
       <c r="T144" s="11">
         <v>99.98</v>
       </c>
-      <c r="U144" s="30" t="s">
+      <c r="U144" s="38" t="s">
         <v>913</v>
       </c>
-      <c r="V144" s="30" t="s">
+      <c r="V144" s="38" t="s">
         <v>913</v>
       </c>
       <c r="W144" s="11"/>
@@ -14962,10 +14985,10 @@
       <c r="T145" s="11">
         <v>99.99</v>
       </c>
-      <c r="U145" s="30" t="s">
+      <c r="U145" s="38" t="s">
         <v>919</v>
       </c>
-      <c r="V145" s="30" t="s">
+      <c r="V145" s="38" t="s">
         <v>919</v>
       </c>
       <c r="W145" s="11"/>
@@ -15034,10 +15057,10 @@
       <c r="T146" s="19">
         <v>99.99</v>
       </c>
-      <c r="U146" s="36" t="s">
+      <c r="U146" s="44" t="s">
         <v>927</v>
       </c>
-      <c r="V146" s="36" t="s">
+      <c r="V146" s="44" t="s">
         <v>927</v>
       </c>
       <c r="Y146" s="19"/>
@@ -15105,10 +15128,10 @@
       <c r="T147" s="11">
         <v>99.99</v>
       </c>
-      <c r="U147" s="30" t="s">
+      <c r="U147" s="38" t="s">
         <v>935</v>
       </c>
-      <c r="V147" s="30" t="s">
+      <c r="V147" s="38" t="s">
         <v>935</v>
       </c>
       <c r="Y147" s="11"/>
@@ -15176,10 +15199,10 @@
       <c r="T148" s="11">
         <v>99.99</v>
       </c>
-      <c r="U148" s="30" t="s">
+      <c r="U148" s="38" t="s">
         <v>943</v>
       </c>
-      <c r="V148" s="30" t="s">
+      <c r="V148" s="38" t="s">
         <v>943</v>
       </c>
       <c r="Y148" s="11"/>
@@ -15247,10 +15270,10 @@
       <c r="T149" s="11">
         <v>99.99</v>
       </c>
-      <c r="U149" s="30" t="s">
+      <c r="U149" s="38" t="s">
         <v>951</v>
       </c>
-      <c r="V149" s="30" t="s">
+      <c r="V149" s="38" t="s">
         <v>951</v>
       </c>
       <c r="Y149" s="11"/>
@@ -15318,10 +15341,10 @@
       <c r="T150" s="11">
         <v>99.99</v>
       </c>
-      <c r="U150" s="30" t="s">
+      <c r="U150" s="38" t="s">
         <v>959</v>
       </c>
-      <c r="V150" s="30" t="s">
+      <c r="V150" s="38" t="s">
         <v>959</v>
       </c>
       <c r="Y150" s="11"/>
@@ -15388,10 +15411,10 @@
       <c r="T151" s="11">
         <v>99.99</v>
       </c>
-      <c r="U151" s="30" t="s">
+      <c r="U151" s="38" t="s">
         <v>968</v>
       </c>
-      <c r="V151" s="30" t="s">
+      <c r="V151" s="38" t="s">
         <v>968</v>
       </c>
       <c r="W151" s="11"/>
@@ -15460,10 +15483,10 @@
       <c r="T152" s="11">
         <v>99.99</v>
       </c>
-      <c r="U152" s="30" t="s">
+      <c r="U152" s="38" t="s">
         <v>977</v>
       </c>
-      <c r="V152" s="30" t="s">
+      <c r="V152" s="38" t="s">
         <v>977</v>
       </c>
       <c r="W152" s="11"/>
@@ -15532,10 +15555,10 @@
       <c r="T153" s="11">
         <v>99.99</v>
       </c>
-      <c r="U153" s="30" t="s">
+      <c r="U153" s="38" t="s">
         <v>986</v>
       </c>
-      <c r="V153" s="30" t="s">
+      <c r="V153" s="38" t="s">
         <v>986</v>
       </c>
       <c r="W153" s="11"/>
@@ -15604,10 +15627,10 @@
       <c r="T154" s="11">
         <v>99.99</v>
       </c>
-      <c r="U154" s="30" t="s">
+      <c r="U154" s="38" t="s">
         <v>995</v>
       </c>
-      <c r="V154" s="30" t="s">
+      <c r="V154" s="38" t="s">
         <v>995</v>
       </c>
       <c r="W154" s="11"/>
@@ -15676,10 +15699,10 @@
       <c r="T155" s="11">
         <v>99.99</v>
       </c>
-      <c r="U155" s="30" t="s">
+      <c r="U155" s="38" t="s">
         <v>1004</v>
       </c>
-      <c r="V155" s="30" t="s">
+      <c r="V155" s="38" t="s">
         <v>1004</v>
       </c>
       <c r="W155" s="11"/>
@@ -15748,10 +15771,10 @@
       <c r="T156" s="11">
         <v>99.99</v>
       </c>
-      <c r="U156" s="30" t="s">
+      <c r="U156" s="38" t="s">
         <v>1013</v>
       </c>
-      <c r="V156" s="30" t="s">
+      <c r="V156" s="38" t="s">
         <v>1013</v>
       </c>
       <c r="W156" s="11"/>
@@ -15820,10 +15843,10 @@
       <c r="T157" s="11">
         <v>99.99</v>
       </c>
-      <c r="U157" s="30" t="s">
+      <c r="U157" s="38" t="s">
         <v>1022</v>
       </c>
-      <c r="V157" s="30" t="s">
+      <c r="V157" s="38" t="s">
         <v>1022</v>
       </c>
       <c r="W157" s="11"/>
@@ -15892,10 +15915,10 @@
       <c r="T158" s="11">
         <v>99.99</v>
       </c>
-      <c r="U158" s="30" t="s">
+      <c r="U158" s="38" t="s">
         <v>1031</v>
       </c>
-      <c r="V158" s="30" t="s">
+      <c r="V158" s="38" t="s">
         <v>1031</v>
       </c>
       <c r="W158" s="11"/>
@@ -15964,10 +15987,10 @@
       <c r="T159" s="11">
         <v>99.99</v>
       </c>
-      <c r="U159" s="30" t="s">
+      <c r="U159" s="38" t="s">
         <v>1040</v>
       </c>
-      <c r="V159" s="30" t="s">
+      <c r="V159" s="38" t="s">
         <v>1040</v>
       </c>
       <c r="W159" s="11"/>
@@ -16036,10 +16059,10 @@
       <c r="T160" s="11">
         <v>99.99</v>
       </c>
-      <c r="U160" s="30" t="s">
+      <c r="U160" s="38" t="s">
         <v>1049</v>
       </c>
-      <c r="V160" s="30" t="s">
+      <c r="V160" s="38" t="s">
         <v>1049</v>
       </c>
       <c r="W160" s="11"/>
@@ -16108,10 +16131,10 @@
       <c r="T161" s="11">
         <v>99.99</v>
       </c>
-      <c r="U161" s="30" t="s">
+      <c r="U161" s="38" t="s">
         <v>1058</v>
       </c>
-      <c r="V161" s="30" t="s">
+      <c r="V161" s="38" t="s">
         <v>1058</v>
       </c>
       <c r="W161" s="11"/>
@@ -16180,10 +16203,10 @@
       <c r="T162" s="11">
         <v>99.99</v>
       </c>
-      <c r="U162" s="30" t="s">
+      <c r="U162" s="38" t="s">
         <v>1067</v>
       </c>
-      <c r="V162" s="30" t="s">
+      <c r="V162" s="38" t="s">
         <v>1067</v>
       </c>
       <c r="W162" s="11"/>
@@ -16252,10 +16275,10 @@
       <c r="T163" s="11">
         <v>99.99</v>
       </c>
-      <c r="U163" s="30" t="s">
+      <c r="U163" s="38" t="s">
         <v>1076</v>
       </c>
-      <c r="V163" s="30" t="s">
+      <c r="V163" s="38" t="s">
         <v>1076</v>
       </c>
       <c r="W163" s="11"/>
@@ -16325,10 +16348,10 @@
       <c r="T164" s="22">
         <v>99.99</v>
       </c>
-      <c r="U164" s="37" t="s">
+      <c r="U164" s="45" t="s">
         <v>1085</v>
       </c>
-      <c r="V164" s="37" t="s">
+      <c r="V164" s="45" t="s">
         <v>1085</v>
       </c>
       <c r="W164" s="22"/>
@@ -16352,7 +16375,7 @@
       <c r="F165" s="4" t="s">
         <v>1088</v>
       </c>
-      <c r="G165" s="38" t="s">
+      <c r="G165" s="46" t="s">
         <v>1089</v>
       </c>
       <c r="H165" s="4" t="s">
@@ -16398,10 +16421,10 @@
       <c r="T165" s="8">
         <v>99.99</v>
       </c>
-      <c r="U165" s="39" t="s">
+      <c r="U165" s="47" t="s">
         <v>1094</v>
       </c>
-      <c r="V165" s="39" t="s">
+      <c r="V165" s="47" t="s">
         <v>1094</v>
       </c>
       <c r="W165" s="8"/>
@@ -16423,20 +16446,20 @@
       <c r="F166" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="G166" s="40" t="s">
+      <c r="G166" s="48" t="s">
         <v>1098</v>
       </c>
-      <c r="H166" s="40" t="s">
+      <c r="H166" s="48" t="s">
         <v>1099</v>
       </c>
-      <c r="I166" s="40" t="s">
+      <c r="I166" s="48" t="s">
         <v>1100</v>
       </c>
-      <c r="J166" s="40" t="s">
+      <c r="J166" s="48" t="s">
         <v>1101</v>
       </c>
       <c r="K166" s="1"/>
-      <c r="L166" s="40" t="s">
+      <c r="L166" s="48" t="s">
         <v>1102</v>
       </c>
       <c r="M166" s="1">
@@ -16469,10 +16492,10 @@
       <c r="T166" s="11">
         <v>99.99</v>
       </c>
-      <c r="U166" s="30" t="s">
+      <c r="U166" s="38" t="s">
         <v>1103</v>
       </c>
-      <c r="V166" s="30" t="s">
+      <c r="V166" s="38" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -16489,20 +16512,20 @@
       <c r="F167" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="G167" s="40" t="s">
+      <c r="G167" s="48" t="s">
         <v>1107</v>
       </c>
-      <c r="H167" s="40" t="s">
+      <c r="H167" s="48" t="s">
         <v>1108</v>
       </c>
-      <c r="I167" s="40" t="s">
+      <c r="I167" s="48" t="s">
         <v>1109</v>
       </c>
-      <c r="J167" s="40" t="s">
+      <c r="J167" s="48" t="s">
         <v>1110</v>
       </c>
       <c r="K167" s="1"/>
-      <c r="L167" s="40" t="s">
+      <c r="L167" s="48" t="s">
         <v>1111</v>
       </c>
       <c r="M167" s="1">
@@ -16535,10 +16558,10 @@
       <c r="T167" s="11">
         <v>99.99</v>
       </c>
-      <c r="U167" s="30" t="s">
+      <c r="U167" s="38" t="s">
         <v>1112</v>
       </c>
-      <c r="V167" s="30" t="s">
+      <c r="V167" s="38" t="s">
         <v>1112</v>
       </c>
     </row>
@@ -16555,20 +16578,20 @@
       <c r="F168" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="G168" s="40" t="s">
+      <c r="G168" s="48" t="s">
         <v>1116</v>
       </c>
-      <c r="H168" s="40" t="s">
+      <c r="H168" s="48" t="s">
         <v>1117</v>
       </c>
-      <c r="I168" s="40" t="s">
+      <c r="I168" s="48" t="s">
         <v>1118</v>
       </c>
-      <c r="J168" s="40" t="s">
+      <c r="J168" s="48" t="s">
         <v>1119</v>
       </c>
       <c r="K168" s="1"/>
-      <c r="L168" s="40" t="s">
+      <c r="L168" s="48" t="s">
         <v>1120</v>
       </c>
       <c r="M168" s="1">
@@ -16601,10 +16624,10 @@
       <c r="T168" s="11">
         <v>99.99</v>
       </c>
-      <c r="U168" s="30" t="s">
+      <c r="U168" s="38" t="s">
         <v>1121</v>
       </c>
-      <c r="V168" s="30" t="s">
+      <c r="V168" s="38" t="s">
         <v>1121</v>
       </c>
     </row>
@@ -16621,20 +16644,20 @@
       <c r="F169" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="G169" s="40" t="s">
+      <c r="G169" s="48" t="s">
         <v>1125</v>
       </c>
-      <c r="H169" s="40" t="s">
+      <c r="H169" s="48" t="s">
         <v>1126</v>
       </c>
-      <c r="I169" s="40" t="s">
+      <c r="I169" s="48" t="s">
         <v>1127</v>
       </c>
-      <c r="J169" s="40" t="s">
+      <c r="J169" s="48" t="s">
         <v>1128</v>
       </c>
       <c r="K169" s="1"/>
-      <c r="L169" s="40" t="s">
+      <c r="L169" s="48" t="s">
         <v>1129</v>
       </c>
       <c r="M169" s="1">
@@ -16667,10 +16690,10 @@
       <c r="T169" s="11">
         <v>99.99</v>
       </c>
-      <c r="U169" s="30" t="s">
+      <c r="U169" s="38" t="s">
         <v>1130</v>
       </c>
-      <c r="V169" s="30" t="s">
+      <c r="V169" s="38" t="s">
         <v>1130</v>
       </c>
     </row>
@@ -16687,20 +16710,20 @@
       <c r="F170" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="G170" s="40" t="s">
+      <c r="G170" s="48" t="s">
         <v>1134</v>
       </c>
-      <c r="H170" s="40" t="s">
+      <c r="H170" s="48" t="s">
         <v>1135</v>
       </c>
-      <c r="I170" s="40" t="s">
+      <c r="I170" s="48" t="s">
         <v>1136</v>
       </c>
-      <c r="J170" s="40" t="s">
+      <c r="J170" s="48" t="s">
         <v>1137</v>
       </c>
       <c r="K170" s="1"/>
-      <c r="L170" s="40" t="s">
+      <c r="L170" s="48" t="s">
         <v>1138</v>
       </c>
       <c r="M170" s="1">
@@ -16733,10 +16756,10 @@
       <c r="T170" s="11">
         <v>99.99</v>
       </c>
-      <c r="U170" s="30" t="s">
+      <c r="U170" s="38" t="s">
         <v>1139</v>
       </c>
-      <c r="V170" s="30" t="s">
+      <c r="V170" s="38" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -16753,20 +16776,20 @@
       <c r="F171" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="G171" s="40" t="s">
+      <c r="G171" s="48" t="s">
         <v>1143</v>
       </c>
-      <c r="H171" s="40" t="s">
+      <c r="H171" s="48" t="s">
         <v>1144</v>
       </c>
-      <c r="I171" s="40" t="s">
+      <c r="I171" s="48" t="s">
         <v>1145</v>
       </c>
-      <c r="J171" s="40" t="s">
+      <c r="J171" s="48" t="s">
         <v>1146</v>
       </c>
       <c r="K171" s="1"/>
-      <c r="L171" s="40" t="s">
+      <c r="L171" s="48" t="s">
         <v>1147</v>
       </c>
       <c r="M171" s="1">
@@ -16799,10 +16822,10 @@
       <c r="T171" s="11">
         <v>99.99</v>
       </c>
-      <c r="U171" s="30" t="s">
+      <c r="U171" s="38" t="s">
         <v>1148</v>
       </c>
-      <c r="V171" s="30" t="s">
+      <c r="V171" s="38" t="s">
         <v>1148</v>
       </c>
     </row>
@@ -16819,20 +16842,20 @@
       <c r="F172" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="G172" s="40" t="s">
+      <c r="G172" s="48" t="s">
         <v>1152</v>
       </c>
-      <c r="H172" s="40" t="s">
+      <c r="H172" s="48" t="s">
         <v>1153</v>
       </c>
-      <c r="I172" s="40" t="s">
+      <c r="I172" s="48" t="s">
         <v>1154</v>
       </c>
-      <c r="J172" s="40" t="s">
+      <c r="J172" s="48" t="s">
         <v>1155</v>
       </c>
       <c r="K172" s="1"/>
-      <c r="L172" s="40" t="s">
+      <c r="L172" s="48" t="s">
         <v>1156</v>
       </c>
       <c r="M172" s="1">
@@ -16865,10 +16888,10 @@
       <c r="T172" s="11">
         <v>99.99</v>
       </c>
-      <c r="U172" s="30" t="s">
+      <c r="U172" s="38" t="s">
         <v>1157</v>
       </c>
-      <c r="V172" s="30" t="s">
+      <c r="V172" s="38" t="s">
         <v>1157</v>
       </c>
     </row>
@@ -16885,20 +16908,20 @@
       <c r="F173" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="G173" s="40" t="s">
+      <c r="G173" s="48" t="s">
         <v>1161</v>
       </c>
-      <c r="H173" s="40" t="s">
+      <c r="H173" s="48" t="s">
         <v>1162</v>
       </c>
-      <c r="I173" s="40" t="s">
+      <c r="I173" s="48" t="s">
         <v>1163</v>
       </c>
-      <c r="J173" s="40" t="s">
+      <c r="J173" s="48" t="s">
         <v>1164</v>
       </c>
       <c r="K173" s="1"/>
-      <c r="L173" s="40" t="s">
+      <c r="L173" s="48" t="s">
         <v>1165</v>
       </c>
       <c r="M173" s="1">
@@ -16931,10 +16954,10 @@
       <c r="T173" s="11">
         <v>99.99</v>
       </c>
-      <c r="U173" s="30" t="s">
+      <c r="U173" s="38" t="s">
         <v>1166</v>
       </c>
-      <c r="V173" s="30" t="s">
+      <c r="V173" s="38" t="s">
         <v>1166</v>
       </c>
     </row>
@@ -16951,20 +16974,20 @@
       <c r="F174" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="G174" s="40" t="s">
+      <c r="G174" s="48" t="s">
         <v>1170</v>
       </c>
-      <c r="H174" s="40" t="s">
+      <c r="H174" s="48" t="s">
         <v>1171</v>
       </c>
-      <c r="I174" s="40" t="s">
+      <c r="I174" s="48" t="s">
         <v>1172</v>
       </c>
-      <c r="J174" s="40" t="s">
+      <c r="J174" s="48" t="s">
         <v>1173</v>
       </c>
       <c r="K174" s="1"/>
-      <c r="L174" s="40" t="s">
+      <c r="L174" s="48" t="s">
         <v>1174</v>
       </c>
       <c r="M174" s="1">
@@ -16997,10 +17020,10 @@
       <c r="T174" s="11">
         <v>99.99</v>
       </c>
-      <c r="U174" s="30" t="s">
+      <c r="U174" s="38" t="s">
         <v>1175</v>
       </c>
-      <c r="V174" s="30" t="s">
+      <c r="V174" s="38" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -17017,20 +17040,20 @@
       <c r="F175" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="G175" s="40" t="s">
+      <c r="G175" s="48" t="s">
         <v>1179</v>
       </c>
-      <c r="H175" s="40" t="s">
+      <c r="H175" s="48" t="s">
         <v>1180</v>
       </c>
-      <c r="I175" s="40" t="s">
+      <c r="I175" s="48" t="s">
         <v>1181</v>
       </c>
-      <c r="J175" s="40" t="s">
+      <c r="J175" s="48" t="s">
         <v>1182</v>
       </c>
       <c r="K175" s="1"/>
-      <c r="L175" s="40" t="s">
+      <c r="L175" s="48" t="s">
         <v>1183</v>
       </c>
       <c r="M175" s="1">
@@ -17063,10 +17086,10 @@
       <c r="T175" s="11">
         <v>99.99</v>
       </c>
-      <c r="U175" s="30" t="s">
+      <c r="U175" s="38" t="s">
         <v>1184</v>
       </c>
-      <c r="V175" s="30" t="s">
+      <c r="V175" s="38" t="s">
         <v>1184</v>
       </c>
     </row>
@@ -17085,19 +17108,19 @@
       <c r="F176" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="G176" s="40" t="s">
+      <c r="G176" s="48" t="s">
         <v>1188</v>
       </c>
-      <c r="H176" s="40" t="s">
+      <c r="H176" s="48" t="s">
         <v>1189</v>
       </c>
-      <c r="I176" s="40" t="s">
+      <c r="I176" s="48" t="s">
         <v>1190</v>
       </c>
-      <c r="J176" s="40" t="s">
+      <c r="J176" s="48" t="s">
         <v>1191</v>
       </c>
-      <c r="L176" s="40" t="s">
+      <c r="L176" s="48" t="s">
         <v>1192</v>
       </c>
       <c r="M176" s="1">
@@ -17130,10 +17153,10 @@
       <c r="T176" s="11">
         <v>99.99</v>
       </c>
-      <c r="U176" s="30" t="s">
+      <c r="U176" s="38" t="s">
         <v>1193</v>
       </c>
-      <c r="V176" s="30" t="s">
+      <c r="V176" s="38" t="s">
         <v>1193</v>
       </c>
       <c r="W176" s="11"/>
@@ -17157,19 +17180,19 @@
       <c r="F177" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="G177" s="40" t="s">
+      <c r="G177" s="48" t="s">
         <v>1197</v>
       </c>
-      <c r="H177" s="40" t="s">
+      <c r="H177" s="48" t="s">
         <v>1198</v>
       </c>
-      <c r="I177" s="40" t="s">
+      <c r="I177" s="48" t="s">
         <v>1199</v>
       </c>
-      <c r="J177" s="40" t="s">
+      <c r="J177" s="48" t="s">
         <v>1200</v>
       </c>
-      <c r="L177" s="40" t="s">
+      <c r="L177" s="48" t="s">
         <v>1201</v>
       </c>
       <c r="M177" s="1">
@@ -17202,10 +17225,10 @@
       <c r="T177" s="11">
         <v>99.99</v>
       </c>
-      <c r="U177" s="30" t="s">
+      <c r="U177" s="38" t="s">
         <v>1202</v>
       </c>
-      <c r="V177" s="30" t="s">
+      <c r="V177" s="38" t="s">
         <v>1202</v>
       </c>
       <c r="W177" s="11"/>
@@ -17229,19 +17252,19 @@
       <c r="F178" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="G178" s="40" t="s">
+      <c r="G178" s="48" t="s">
         <v>1206</v>
       </c>
-      <c r="H178" s="40" t="s">
+      <c r="H178" s="48" t="s">
         <v>1207</v>
       </c>
-      <c r="I178" s="40" t="s">
+      <c r="I178" s="48" t="s">
         <v>1208</v>
       </c>
-      <c r="J178" s="40" t="s">
+      <c r="J178" s="48" t="s">
         <v>1209</v>
       </c>
-      <c r="L178" s="40" t="s">
+      <c r="L178" s="48" t="s">
         <v>1210</v>
       </c>
       <c r="M178" s="1">
@@ -17274,10 +17297,10 @@
       <c r="T178" s="11">
         <v>99.99</v>
       </c>
-      <c r="U178" s="30" t="s">
+      <c r="U178" s="38" t="s">
         <v>1211</v>
       </c>
-      <c r="V178" s="30" t="s">
+      <c r="V178" s="38" t="s">
         <v>1211</v>
       </c>
       <c r="W178" s="11"/>
@@ -17301,19 +17324,19 @@
       <c r="F179" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="G179" s="40" t="s">
+      <c r="G179" s="48" t="s">
         <v>1215</v>
       </c>
-      <c r="H179" s="40" t="s">
+      <c r="H179" s="48" t="s">
         <v>1216</v>
       </c>
-      <c r="I179" s="40" t="s">
+      <c r="I179" s="48" t="s">
         <v>1217</v>
       </c>
-      <c r="J179" s="40" t="s">
+      <c r="J179" s="48" t="s">
         <v>1218</v>
       </c>
-      <c r="L179" s="40" t="s">
+      <c r="L179" s="48" t="s">
         <v>1219</v>
       </c>
       <c r="M179" s="1">
@@ -17346,10 +17369,10 @@
       <c r="T179" s="11">
         <v>99.99</v>
       </c>
-      <c r="U179" s="30" t="s">
+      <c r="U179" s="38" t="s">
         <v>1220</v>
       </c>
-      <c r="V179" s="30" t="s">
+      <c r="V179" s="38" t="s">
         <v>1220</v>
       </c>
       <c r="W179" s="11"/>
@@ -17373,19 +17396,19 @@
       <c r="F180" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="G180" s="40" t="s">
+      <c r="G180" s="48" t="s">
         <v>1224</v>
       </c>
-      <c r="H180" s="40" t="s">
+      <c r="H180" s="48" t="s">
         <v>1225</v>
       </c>
-      <c r="I180" s="40" t="s">
+      <c r="I180" s="48" t="s">
         <v>1226</v>
       </c>
-      <c r="J180" s="40" t="s">
+      <c r="J180" s="48" t="s">
         <v>1227</v>
       </c>
-      <c r="L180" s="40" t="s">
+      <c r="L180" s="48" t="s">
         <v>1228</v>
       </c>
       <c r="M180" s="1">
@@ -17418,10 +17441,10 @@
       <c r="T180" s="11">
         <v>99.99</v>
       </c>
-      <c r="U180" s="30" t="s">
+      <c r="U180" s="38" t="s">
         <v>1229</v>
       </c>
-      <c r="V180" s="30" t="s">
+      <c r="V180" s="38" t="s">
         <v>1229</v>
       </c>
       <c r="W180" s="11"/>
@@ -17445,22 +17468,22 @@
       <c r="F181" s="2" t="s">
         <v>1230</v>
       </c>
-      <c r="G181" s="41" t="s">
+      <c r="G181" s="49" t="s">
         <v>1231</v>
       </c>
-      <c r="H181" s="41" t="s">
+      <c r="H181" s="49" t="s">
         <v>1232</v>
       </c>
-      <c r="I181" s="41" t="s">
+      <c r="I181" s="49" t="s">
         <v>1233</v>
       </c>
-      <c r="J181" s="41" t="s">
+      <c r="J181" s="49" t="s">
         <v>1234</v>
       </c>
-      <c r="K181" s="36" t="s">
+      <c r="K181" s="44" t="s">
         <v>1235</v>
       </c>
-      <c r="L181" s="41" t="s">
+      <c r="L181" s="49" t="s">
         <v>1236</v>
       </c>
       <c r="M181" s="2">
@@ -17489,10 +17512,10 @@
       <c r="T181" s="19">
         <v>99.99</v>
       </c>
-      <c r="U181" s="36" t="s">
+      <c r="U181" s="44" t="s">
         <v>1237</v>
       </c>
-      <c r="V181" s="36" t="s">
+      <c r="V181" s="44" t="s">
         <v>1237</v>
       </c>
       <c r="Y181" s="19"/>
@@ -17514,22 +17537,22 @@
       <c r="F182" s="5" t="s">
         <v>1238</v>
       </c>
-      <c r="G182" s="40" t="s">
+      <c r="G182" s="48" t="s">
         <v>1239</v>
       </c>
-      <c r="H182" s="40" t="s">
+      <c r="H182" s="48" t="s">
         <v>1240</v>
       </c>
-      <c r="I182" s="40" t="s">
+      <c r="I182" s="48" t="s">
         <v>1241</v>
       </c>
-      <c r="J182" s="40" t="s">
+      <c r="J182" s="48" t="s">
         <v>1242</v>
       </c>
-      <c r="K182" s="42" t="s">
+      <c r="K182" s="50" t="s">
         <v>1243</v>
       </c>
-      <c r="L182" s="40" t="s">
+      <c r="L182" s="48" t="s">
         <v>1244</v>
       </c>
       <c r="M182" s="5">
@@ -17563,10 +17586,10 @@
       <c r="T182" s="13">
         <v>99.99</v>
       </c>
-      <c r="U182" s="42" t="s">
+      <c r="U182" s="50" t="s">
         <v>1245</v>
       </c>
-      <c r="V182" s="42" t="s">
+      <c r="V182" s="50" t="s">
         <v>1245</v>
       </c>
       <c r="Y182" s="13"/>
@@ -17588,22 +17611,22 @@
       <c r="F183" s="5" t="s">
         <v>1246</v>
       </c>
-      <c r="G183" s="40" t="s">
+      <c r="G183" s="48" t="s">
         <v>1247</v>
       </c>
-      <c r="H183" s="40" t="s">
+      <c r="H183" s="48" t="s">
         <v>1248</v>
       </c>
-      <c r="I183" s="40" t="s">
+      <c r="I183" s="48" t="s">
         <v>1249</v>
       </c>
-      <c r="J183" s="40" t="s">
+      <c r="J183" s="48" t="s">
         <v>1250</v>
       </c>
-      <c r="K183" s="42" t="s">
+      <c r="K183" s="50" t="s">
         <v>1251</v>
       </c>
-      <c r="L183" s="40" t="s">
+      <c r="L183" s="48" t="s">
         <v>1252</v>
       </c>
       <c r="M183" s="5">
@@ -17637,10 +17660,10 @@
       <c r="T183" s="13">
         <v>99.99</v>
       </c>
-      <c r="U183" s="42" t="s">
+      <c r="U183" s="50" t="s">
         <v>1253</v>
       </c>
-      <c r="V183" s="42" t="s">
+      <c r="V183" s="50" t="s">
         <v>1253</v>
       </c>
       <c r="Y183" s="13"/>
@@ -17662,22 +17685,22 @@
       <c r="F184" s="5" t="s">
         <v>1254</v>
       </c>
-      <c r="G184" s="40" t="s">
+      <c r="G184" s="48" t="s">
         <v>1255</v>
       </c>
-      <c r="H184" s="40" t="s">
+      <c r="H184" s="48" t="s">
         <v>1256</v>
       </c>
-      <c r="I184" s="40" t="s">
+      <c r="I184" s="48" t="s">
         <v>1257</v>
       </c>
-      <c r="J184" s="40" t="s">
+      <c r="J184" s="48" t="s">
         <v>1258</v>
       </c>
-      <c r="K184" s="42" t="s">
+      <c r="K184" s="50" t="s">
         <v>1259</v>
       </c>
-      <c r="L184" s="40" t="s">
+      <c r="L184" s="48" t="s">
         <v>1260</v>
       </c>
       <c r="M184" s="5">
@@ -17711,10 +17734,10 @@
       <c r="T184" s="13">
         <v>99.99</v>
       </c>
-      <c r="U184" s="42" t="s">
+      <c r="U184" s="50" t="s">
         <v>1261</v>
       </c>
-      <c r="V184" s="42" t="s">
+      <c r="V184" s="50" t="s">
         <v>1261</v>
       </c>
       <c r="Y184" s="13"/>
@@ -17736,22 +17759,22 @@
       <c r="F185" s="5" t="s">
         <v>1262</v>
       </c>
-      <c r="G185" s="40" t="s">
+      <c r="G185" s="48" t="s">
         <v>1263</v>
       </c>
-      <c r="H185" s="40" t="s">
+      <c r="H185" s="48" t="s">
         <v>1264</v>
       </c>
-      <c r="I185" s="40" t="s">
+      <c r="I185" s="48" t="s">
         <v>1265</v>
       </c>
-      <c r="J185" s="40" t="s">
+      <c r="J185" s="48" t="s">
         <v>1266</v>
       </c>
-      <c r="K185" s="42" t="s">
+      <c r="K185" s="50" t="s">
         <v>1267</v>
       </c>
-      <c r="L185" s="40" t="s">
+      <c r="L185" s="48" t="s">
         <v>1268</v>
       </c>
       <c r="M185" s="5">
@@ -17785,10 +17808,10 @@
       <c r="T185" s="13">
         <v>99.99</v>
       </c>
-      <c r="U185" s="42" t="s">
+      <c r="U185" s="50" t="s">
         <v>1269</v>
       </c>
-      <c r="V185" s="42" t="s">
+      <c r="V185" s="50" t="s">
         <v>1269</v>
       </c>
       <c r="Y185" s="13"/>
@@ -17810,22 +17833,22 @@
       <c r="F186" s="6" t="s">
         <v>1270</v>
       </c>
-      <c r="G186" s="40" t="s">
+      <c r="G186" s="48" t="s">
         <v>1271</v>
       </c>
-      <c r="H186" s="38" t="s">
+      <c r="H186" s="46" t="s">
         <v>1272</v>
       </c>
-      <c r="I186" s="38" t="s">
+      <c r="I186" s="46" t="s">
         <v>1273</v>
       </c>
-      <c r="J186" s="38" t="s">
+      <c r="J186" s="46" t="s">
         <v>1274</v>
       </c>
-      <c r="K186" s="42" t="s">
+      <c r="K186" s="50" t="s">
         <v>1275</v>
       </c>
-      <c r="L186" s="38" t="s">
+      <c r="L186" s="46" t="s">
         <v>1276</v>
       </c>
       <c r="M186" s="6">
@@ -17859,10 +17882,10 @@
       <c r="T186" s="26">
         <v>99.99</v>
       </c>
-      <c r="U186" s="43" t="s">
+      <c r="U186" s="51" t="s">
         <v>1277</v>
       </c>
-      <c r="V186" s="43" t="s">
+      <c r="V186" s="51" t="s">
         <v>1277</v>
       </c>
       <c r="W186" s="26"/>
@@ -17886,22 +17909,22 @@
       <c r="F187" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="G187" s="40" t="s">
+      <c r="G187" s="48" t="s">
         <v>1279</v>
       </c>
-      <c r="H187" s="38" t="s">
+      <c r="H187" s="46" t="s">
         <v>1280</v>
       </c>
-      <c r="I187" s="38" t="s">
+      <c r="I187" s="46" t="s">
         <v>1281</v>
       </c>
-      <c r="J187" s="38" t="s">
+      <c r="J187" s="46" t="s">
         <v>1282</v>
       </c>
-      <c r="K187" s="42" t="s">
+      <c r="K187" s="50" t="s">
         <v>1283</v>
       </c>
-      <c r="L187" s="38" t="s">
+      <c r="L187" s="46" t="s">
         <v>1284</v>
       </c>
       <c r="M187" s="4">
@@ -17935,10 +17958,10 @@
       <c r="T187" s="8">
         <v>99.99</v>
       </c>
-      <c r="U187" s="39" t="s">
+      <c r="U187" s="47" t="s">
         <v>1285</v>
       </c>
-      <c r="V187" s="39" t="s">
+      <c r="V187" s="47" t="s">
         <v>1285</v>
       </c>
       <c r="W187" s="8"/>
@@ -17962,22 +17985,22 @@
       <c r="F188" s="4" t="s">
         <v>1286</v>
       </c>
-      <c r="G188" s="40" t="s">
+      <c r="G188" s="48" t="s">
         <v>1232</v>
       </c>
-      <c r="H188" s="38" t="s">
+      <c r="H188" s="46" t="s">
         <v>1287</v>
       </c>
-      <c r="I188" s="38" t="s">
+      <c r="I188" s="46" t="s">
         <v>1288</v>
       </c>
-      <c r="J188" s="38" t="s">
+      <c r="J188" s="46" t="s">
         <v>1289</v>
       </c>
-      <c r="K188" s="42" t="s">
+      <c r="K188" s="50" t="s">
         <v>1290</v>
       </c>
-      <c r="L188" s="38" t="s">
+      <c r="L188" s="46" t="s">
         <v>1255</v>
       </c>
       <c r="M188" s="4">
@@ -18011,10 +18034,10 @@
       <c r="T188" s="8">
         <v>99.99</v>
       </c>
-      <c r="U188" s="39" t="s">
+      <c r="U188" s="47" t="s">
         <v>1291</v>
       </c>
-      <c r="V188" s="39" t="s">
+      <c r="V188" s="47" t="s">
         <v>1291</v>
       </c>
       <c r="W188" s="8"/>
@@ -18038,22 +18061,22 @@
       <c r="F189" s="4" t="s">
         <v>1292</v>
       </c>
-      <c r="G189" s="40" t="s">
+      <c r="G189" s="48" t="s">
         <v>1293</v>
       </c>
-      <c r="H189" s="38" t="s">
+      <c r="H189" s="46" t="s">
         <v>1294</v>
       </c>
-      <c r="I189" s="38" t="s">
+      <c r="I189" s="46" t="s">
         <v>1295</v>
       </c>
-      <c r="J189" s="38" t="s">
+      <c r="J189" s="46" t="s">
         <v>1296</v>
       </c>
-      <c r="K189" s="42" t="s">
+      <c r="K189" s="50" t="s">
         <v>1297</v>
       </c>
-      <c r="L189" s="38" t="s">
+      <c r="L189" s="46" t="s">
         <v>1298</v>
       </c>
       <c r="M189" s="4">
@@ -18087,10 +18110,10 @@
       <c r="T189" s="8">
         <v>99.99</v>
       </c>
-      <c r="U189" s="39" t="s">
+      <c r="U189" s="47" t="s">
         <v>1299</v>
       </c>
-      <c r="V189" s="39" t="s">
+      <c r="V189" s="47" t="s">
         <v>1299</v>
       </c>
       <c r="W189" s="8"/>
@@ -18114,22 +18137,22 @@
       <c r="F190" s="4" t="s">
         <v>1300</v>
       </c>
-      <c r="G190" s="40" t="s">
+      <c r="G190" s="48" t="s">
         <v>1301</v>
       </c>
-      <c r="H190" s="38" t="s">
+      <c r="H190" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I190" s="38" t="s">
+      <c r="I190" s="46" t="s">
         <v>1303</v>
       </c>
-      <c r="J190" s="38" t="s">
+      <c r="J190" s="46" t="s">
         <v>1304</v>
       </c>
-      <c r="K190" s="42" t="s">
+      <c r="K190" s="50" t="s">
         <v>1305</v>
       </c>
-      <c r="L190" s="38" t="s">
+      <c r="L190" s="46" t="s">
         <v>1306</v>
       </c>
       <c r="M190" s="4">
@@ -18163,10 +18186,10 @@
       <c r="T190" s="8">
         <v>99.99</v>
       </c>
-      <c r="U190" s="39" t="s">
+      <c r="U190" s="47" t="s">
         <v>1307</v>
       </c>
-      <c r="V190" s="39" t="s">
+      <c r="V190" s="47" t="s">
         <v>1307</v>
       </c>
       <c r="W190" s="8"/>
@@ -18190,22 +18213,22 @@
       <c r="F191" s="6" t="s">
         <v>1308</v>
       </c>
-      <c r="G191" s="40" t="s">
+      <c r="G191" s="48" t="s">
         <v>1248</v>
       </c>
-      <c r="H191" s="38" t="s">
+      <c r="H191" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I191" s="38" t="s">
+      <c r="I191" s="46" t="s">
         <v>1309</v>
       </c>
-      <c r="J191" s="38" t="s">
+      <c r="J191" s="46" t="s">
         <v>1183</v>
       </c>
-      <c r="K191" s="42" t="s">
+      <c r="K191" s="50" t="s">
         <v>1310</v>
       </c>
-      <c r="L191" s="38" t="s">
+      <c r="L191" s="46" t="s">
         <v>1311</v>
       </c>
       <c r="M191" s="6">
@@ -18239,10 +18262,10 @@
       <c r="T191" s="26">
         <v>99.99</v>
       </c>
-      <c r="U191" s="43" t="s">
+      <c r="U191" s="51" t="s">
         <v>1312</v>
       </c>
-      <c r="V191" s="43" t="s">
+      <c r="V191" s="51" t="s">
         <v>1312</v>
       </c>
       <c r="W191" s="26"/>
@@ -18266,22 +18289,22 @@
       <c r="F192" s="4" t="s">
         <v>1313</v>
       </c>
-      <c r="G192" s="40" t="s">
+      <c r="G192" s="48" t="s">
         <v>1314</v>
       </c>
-      <c r="H192" s="38" t="s">
+      <c r="H192" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I192" s="38" t="s">
+      <c r="I192" s="46" t="s">
         <v>1315</v>
       </c>
-      <c r="J192" s="38" t="s">
+      <c r="J192" s="46" t="s">
         <v>1316</v>
       </c>
-      <c r="K192" s="42" t="s">
+      <c r="K192" s="50" t="s">
         <v>1317</v>
       </c>
-      <c r="L192" s="38" t="s">
+      <c r="L192" s="46" t="s">
         <v>1279</v>
       </c>
       <c r="M192" s="4">
@@ -18315,10 +18338,10 @@
       <c r="T192" s="8">
         <v>99.99</v>
       </c>
-      <c r="U192" s="39" t="s">
+      <c r="U192" s="47" t="s">
         <v>1318</v>
       </c>
-      <c r="V192" s="39" t="s">
+      <c r="V192" s="47" t="s">
         <v>1318</v>
       </c>
       <c r="W192" s="8"/>
@@ -18342,22 +18365,22 @@
       <c r="F193" s="4" t="s">
         <v>1319</v>
       </c>
-      <c r="G193" s="40" t="s">
+      <c r="G193" s="48" t="s">
         <v>1256</v>
       </c>
-      <c r="H193" s="38" t="s">
+      <c r="H193" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I193" s="38" t="s">
+      <c r="I193" s="46" t="s">
         <v>1320</v>
       </c>
-      <c r="J193" s="38" t="s">
+      <c r="J193" s="46" t="s">
         <v>1321</v>
       </c>
-      <c r="K193" s="42" t="s">
+      <c r="K193" s="50" t="s">
         <v>1322</v>
       </c>
-      <c r="L193" s="38" t="s">
+      <c r="L193" s="46" t="s">
         <v>1323</v>
       </c>
       <c r="M193" s="4">
@@ -18391,10 +18414,10 @@
       <c r="T193" s="8">
         <v>99.99</v>
       </c>
-      <c r="U193" s="39" t="s">
+      <c r="U193" s="47" t="s">
         <v>432</v>
       </c>
-      <c r="V193" s="39" t="s">
+      <c r="V193" s="47" t="s">
         <v>432</v>
       </c>
       <c r="W193" s="8"/>
@@ -18418,22 +18441,22 @@
       <c r="F194" s="4" t="s">
         <v>1324</v>
       </c>
-      <c r="G194" s="40" t="s">
+      <c r="G194" s="48" t="s">
         <v>1154</v>
       </c>
-      <c r="H194" s="38" t="s">
+      <c r="H194" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I194" s="38" t="s">
+      <c r="I194" s="46" t="s">
         <v>1325</v>
       </c>
-      <c r="J194" s="38" t="s">
+      <c r="J194" s="46" t="s">
         <v>1326</v>
       </c>
-      <c r="K194" s="42" t="s">
+      <c r="K194" s="50" t="s">
         <v>1327</v>
       </c>
-      <c r="L194" s="38" t="s">
+      <c r="L194" s="46" t="s">
         <v>1328</v>
       </c>
       <c r="M194" s="4">
@@ -18467,10 +18490,10 @@
       <c r="T194" s="8">
         <v>99.99</v>
       </c>
-      <c r="U194" s="39" t="s">
+      <c r="U194" s="47" t="s">
         <v>1329</v>
       </c>
-      <c r="V194" s="39" t="s">
+      <c r="V194" s="47" t="s">
         <v>1329</v>
       </c>
       <c r="W194" s="8"/>
@@ -18494,22 +18517,22 @@
       <c r="F195" s="4" t="s">
         <v>1330</v>
       </c>
-      <c r="G195" s="40" t="s">
+      <c r="G195" s="48" t="s">
         <v>1264</v>
       </c>
-      <c r="H195" s="38" t="s">
+      <c r="H195" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I195" s="38" t="s">
+      <c r="I195" s="46" t="s">
         <v>1331</v>
       </c>
-      <c r="J195" s="38" t="s">
+      <c r="J195" s="46" t="s">
         <v>1332</v>
       </c>
-      <c r="K195" s="42" t="s">
+      <c r="K195" s="50" t="s">
         <v>1333</v>
       </c>
-      <c r="L195" s="38" t="s">
+      <c r="L195" s="46" t="s">
         <v>1293</v>
       </c>
       <c r="M195" s="4">
@@ -18543,10 +18566,10 @@
       <c r="T195" s="8">
         <v>99.99</v>
       </c>
-      <c r="U195" s="39" t="s">
+      <c r="U195" s="47" t="s">
         <v>1334</v>
       </c>
-      <c r="V195" s="39" t="s">
+      <c r="V195" s="47" t="s">
         <v>1334</v>
       </c>
       <c r="W195" s="8"/>
@@ -18570,22 +18593,22 @@
       <c r="F196" s="6" t="s">
         <v>1335</v>
       </c>
-      <c r="G196" s="40" t="s">
+      <c r="G196" s="48" t="s">
         <v>1336</v>
       </c>
-      <c r="H196" s="38" t="s">
+      <c r="H196" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I196" s="38" t="s">
+      <c r="I196" s="46" t="s">
         <v>1337</v>
       </c>
-      <c r="J196" s="38" t="s">
+      <c r="J196" s="46" t="s">
         <v>1338</v>
       </c>
-      <c r="K196" s="42" t="s">
+      <c r="K196" s="50" t="s">
         <v>1339</v>
       </c>
-      <c r="L196" s="38" t="s">
+      <c r="L196" s="46" t="s">
         <v>1301</v>
       </c>
       <c r="M196" s="6">
@@ -18619,10 +18642,10 @@
       <c r="T196" s="26">
         <v>99.99</v>
       </c>
-      <c r="U196" s="43" t="s">
+      <c r="U196" s="51" t="s">
         <v>1340</v>
       </c>
-      <c r="V196" s="43" t="s">
+      <c r="V196" s="51" t="s">
         <v>1340</v>
       </c>
       <c r="W196" s="26"/>
@@ -18646,22 +18669,22 @@
       <c r="F197" s="4" t="s">
         <v>1341</v>
       </c>
-      <c r="G197" s="40" t="s">
+      <c r="G197" s="48" t="s">
         <v>1342</v>
       </c>
-      <c r="H197" s="38" t="s">
+      <c r="H197" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I197" s="38" t="s">
+      <c r="I197" s="46" t="s">
         <v>1343</v>
       </c>
-      <c r="J197" s="38" t="s">
+      <c r="J197" s="46" t="s">
         <v>1344</v>
       </c>
-      <c r="K197" s="42" t="s">
+      <c r="K197" s="50" t="s">
         <v>1345</v>
       </c>
-      <c r="L197" s="38" t="s">
+      <c r="L197" s="46" t="s">
         <v>1248</v>
       </c>
       <c r="M197" s="4">
@@ -18695,10 +18718,10 @@
       <c r="T197" s="8">
         <v>99.99</v>
       </c>
-      <c r="U197" s="39" t="s">
+      <c r="U197" s="47" t="s">
         <v>1346</v>
       </c>
-      <c r="V197" s="39" t="s">
+      <c r="V197" s="47" t="s">
         <v>1346</v>
       </c>
       <c r="W197" s="8"/>
@@ -18722,22 +18745,22 @@
       <c r="F198" s="4" t="s">
         <v>1347</v>
       </c>
-      <c r="G198" s="40" t="s">
+      <c r="G198" s="48" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H198" s="46" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I198" s="46" t="s">
         <v>1348</v>
       </c>
-      <c r="H198" s="38" t="s">
-        <v>1302</v>
-      </c>
-      <c r="I198" s="38" t="s">
+      <c r="J198" s="46" t="s">
         <v>1349</v>
       </c>
-      <c r="J198" s="38" t="s">
+      <c r="K198" s="50" t="s">
         <v>1350</v>
       </c>
-      <c r="K198" s="42" t="s">
-        <v>1351</v>
-      </c>
-      <c r="L198" s="38" t="s">
+      <c r="L198" s="46" t="s">
         <v>1314</v>
       </c>
       <c r="M198" s="4">
@@ -18771,11 +18794,11 @@
       <c r="T198" s="8">
         <v>99.99</v>
       </c>
-      <c r="U198" s="39" t="s">
-        <v>1352</v>
-      </c>
-      <c r="V198" s="39" t="s">
-        <v>1352</v>
+      <c r="U198" s="47" t="s">
+        <v>1351</v>
+      </c>
+      <c r="V198" s="47" t="s">
+        <v>1351</v>
       </c>
       <c r="W198" s="8"/>
       <c r="X198" s="8"/>
@@ -18796,24 +18819,24 @@
         <v>6</v>
       </c>
       <c r="F199" s="4" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G199" s="48" t="s">
         <v>1353</v>
       </c>
-      <c r="G199" s="40" t="s">
+      <c r="H199" s="46" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I199" s="46" t="s">
         <v>1354</v>
       </c>
-      <c r="H199" s="38" t="s">
-        <v>1302</v>
-      </c>
-      <c r="I199" s="38" t="s">
+      <c r="J199" s="46" t="s">
         <v>1355</v>
       </c>
-      <c r="J199" s="38" t="s">
+      <c r="K199" s="50" t="s">
         <v>1356</v>
       </c>
-      <c r="K199" s="42" t="s">
-        <v>1357</v>
-      </c>
-      <c r="L199" s="38" t="s">
+      <c r="L199" s="46" t="s">
         <v>1256</v>
       </c>
       <c r="M199" s="4">
@@ -18847,11 +18870,11 @@
       <c r="T199" s="8">
         <v>99.99</v>
       </c>
-      <c r="U199" s="39" t="s">
-        <v>1358</v>
-      </c>
-      <c r="V199" s="39" t="s">
-        <v>1358</v>
+      <c r="U199" s="47" t="s">
+        <v>1357</v>
+      </c>
+      <c r="V199" s="47" t="s">
+        <v>1357</v>
       </c>
       <c r="W199" s="8"/>
       <c r="X199" s="8"/>
@@ -18872,24 +18895,24 @@
         <v>6</v>
       </c>
       <c r="F200" s="4" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G200" s="48" t="s">
         <v>1359</v>
       </c>
-      <c r="G200" s="40" t="s">
+      <c r="H200" s="46" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I200" s="46" t="s">
         <v>1360</v>
       </c>
-      <c r="H200" s="38" t="s">
-        <v>1302</v>
-      </c>
-      <c r="I200" s="38" t="s">
+      <c r="J200" s="46" t="s">
+        <v>1236</v>
+      </c>
+      <c r="K200" s="50" t="s">
         <v>1361</v>
       </c>
-      <c r="J200" s="38" t="s">
-        <v>1236</v>
-      </c>
-      <c r="K200" s="42" t="s">
-        <v>1362</v>
-      </c>
-      <c r="L200" s="38" t="s">
+      <c r="L200" s="46" t="s">
         <v>1154</v>
       </c>
       <c r="M200" s="4">
@@ -18923,11 +18946,11 @@
       <c r="T200" s="8">
         <v>99.99</v>
       </c>
-      <c r="U200" s="39" t="s">
-        <v>1363</v>
-      </c>
-      <c r="V200" s="39" t="s">
-        <v>1363</v>
+      <c r="U200" s="47" t="s">
+        <v>1362</v>
+      </c>
+      <c r="V200" s="47" t="s">
+        <v>1362</v>
       </c>
       <c r="W200" s="8"/>
       <c r="X200" s="8"/>
@@ -18946,61 +18969,61 @@
         <v>6</v>
       </c>
       <c r="F201" s="27" t="s">
+        <v>1363</v>
+      </c>
+      <c r="G201" s="52" t="s">
         <v>1364</v>
       </c>
-      <c r="G201" s="44" t="s">
-        <v>1294</v>
-      </c>
-      <c r="H201" s="38" t="s">
+      <c r="H201" s="53" t="s">
         <v>1302</v>
       </c>
-      <c r="I201" s="38" t="s">
+      <c r="I201" s="53" t="s">
         <v>1365</v>
       </c>
-      <c r="J201" s="38" t="s">
+      <c r="J201" s="53" t="s">
         <v>1366</v>
       </c>
-      <c r="K201" s="42" t="s">
+      <c r="K201" s="54" t="s">
         <v>1242</v>
       </c>
-      <c r="L201" s="38" t="s">
+      <c r="L201" s="53" t="s">
         <v>1264</v>
       </c>
-      <c r="M201" s="4">
+      <c r="M201" s="31">
         <f t="shared" ref="M201:P201" si="70">M200+5000</f>
         <v>61000</v>
       </c>
-      <c r="N201" s="4">
+      <c r="N201" s="31">
         <f t="shared" si="70"/>
         <v>61000</v>
       </c>
-      <c r="O201" s="4">
+      <c r="O201" s="31">
         <f t="shared" si="70"/>
         <v>32750</v>
       </c>
-      <c r="P201" s="4">
+      <c r="P201" s="31">
         <f t="shared" si="70"/>
         <v>32750</v>
       </c>
-      <c r="Q201" s="4">
-        <f t="shared" ref="Q201:Q205" si="71">Q200+6</f>
+      <c r="Q201" s="31">
+        <f t="shared" ref="Q201:Q210" si="71">Q200+6</f>
         <v>113</v>
       </c>
-      <c r="R201" s="8">
-        <f t="shared" ref="R201:R205" si="72">R200+15</f>
+      <c r="R201" s="32">
+        <f t="shared" ref="R201:R210" si="72">R200+15</f>
         <v>444</v>
       </c>
-      <c r="S201" s="8">
-        <f t="shared" ref="S201:S205" si="73">S200+15</f>
+      <c r="S201" s="32">
+        <f t="shared" ref="S201:S210" si="73">S200+15</f>
         <v>561</v>
       </c>
       <c r="T201" s="7">
         <v>99.99</v>
       </c>
-      <c r="U201" s="39" t="s">
+      <c r="U201" s="55" t="s">
         <v>1367</v>
       </c>
-      <c r="V201" s="39" t="s">
+      <c r="V201" s="55" t="s">
         <v>1367</v>
       </c>
       <c r="W201" s="27"/>
@@ -19019,22 +19042,22 @@
       <c r="F202" s="4" t="s">
         <v>1368</v>
       </c>
-      <c r="G202" s="38" t="s">
+      <c r="G202" s="46" t="s">
         <v>1369</v>
       </c>
-      <c r="H202" s="38" t="s">
+      <c r="H202" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I202" s="38" t="s">
+      <c r="I202" s="46" t="s">
         <v>1370</v>
       </c>
-      <c r="J202" s="38" t="s">
+      <c r="J202" s="46" t="s">
         <v>1371</v>
       </c>
-      <c r="K202" s="42" t="s">
+      <c r="K202" s="50" t="s">
         <v>1372</v>
       </c>
-      <c r="L202" s="38" t="s">
+      <c r="L202" s="46" t="s">
         <v>1336</v>
       </c>
       <c r="M202" s="4">
@@ -19068,10 +19091,10 @@
       <c r="T202" s="8">
         <v>99.99</v>
       </c>
-      <c r="U202" s="39" t="s">
+      <c r="U202" s="47" t="s">
         <v>1373</v>
       </c>
-      <c r="V202" s="39" t="s">
+      <c r="V202" s="47" t="s">
         <v>1373</v>
       </c>
       <c r="W202" s="4"/>
@@ -19090,22 +19113,22 @@
       <c r="F203" s="4" t="s">
         <v>1374</v>
       </c>
-      <c r="G203" s="38" t="s">
+      <c r="G203" s="46" t="s">
         <v>1375</v>
       </c>
-      <c r="H203" s="38" t="s">
+      <c r="H203" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I203" s="38" t="s">
+      <c r="I203" s="46" t="s">
         <v>1376</v>
       </c>
-      <c r="J203" s="38" t="s">
+      <c r="J203" s="46" t="s">
         <v>1377</v>
       </c>
-      <c r="K203" s="42" t="s">
+      <c r="K203" s="50" t="s">
         <v>1266</v>
       </c>
-      <c r="L203" s="38" t="s">
+      <c r="L203" s="46" t="s">
         <v>1342</v>
       </c>
       <c r="M203" s="4">
@@ -19139,10 +19162,10 @@
       <c r="T203" s="8">
         <v>99.99</v>
       </c>
-      <c r="U203" s="39" t="s">
+      <c r="U203" s="47" t="s">
         <v>1378</v>
       </c>
-      <c r="V203" s="39" t="s">
+      <c r="V203" s="47" t="s">
         <v>1378</v>
       </c>
       <c r="W203" s="4"/>
@@ -19161,23 +19184,23 @@
       <c r="F204" s="4" t="s">
         <v>1379</v>
       </c>
-      <c r="G204" s="38" t="s">
+      <c r="G204" s="46" t="s">
         <v>1380</v>
       </c>
-      <c r="H204" s="38" t="s">
+      <c r="H204" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I204" s="38" t="s">
+      <c r="I204" s="46" t="s">
         <v>1381</v>
       </c>
-      <c r="J204" s="38" t="s">
+      <c r="J204" s="46" t="s">
         <v>1244</v>
       </c>
-      <c r="K204" s="42" t="s">
+      <c r="K204" s="50" t="s">
         <v>1382</v>
       </c>
-      <c r="L204" s="38" t="s">
-        <v>1348</v>
+      <c r="L204" s="46" t="s">
+        <v>1280</v>
       </c>
       <c r="M204" s="4">
         <f t="shared" ref="M204:P204" si="76">M203+5000</f>
@@ -19210,10 +19233,10 @@
       <c r="T204" s="8">
         <v>99.99</v>
       </c>
-      <c r="U204" s="39" t="s">
+      <c r="U204" s="47" t="s">
         <v>1383</v>
       </c>
-      <c r="V204" s="39" t="s">
+      <c r="V204" s="47" t="s">
         <v>1383</v>
       </c>
       <c r="W204" s="4"/>
@@ -19232,38 +19255,38 @@
       <c r="F205" s="4" t="s">
         <v>1384</v>
       </c>
-      <c r="G205" s="38" t="s">
+      <c r="G205" s="46" t="s">
         <v>1385</v>
       </c>
-      <c r="H205" s="38" t="s">
+      <c r="H205" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I205" s="38" t="s">
+      <c r="I205" s="46" t="s">
         <v>1386</v>
       </c>
-      <c r="J205" s="38" t="s">
+      <c r="J205" s="46" t="s">
         <v>1387</v>
       </c>
-      <c r="K205" s="42" t="s">
+      <c r="K205" s="50" t="s">
         <v>1289</v>
       </c>
-      <c r="L205" s="38" t="s">
-        <v>1354</v>
+      <c r="L205" s="46" t="s">
+        <v>1353</v>
       </c>
       <c r="M205" s="4">
-        <f t="shared" ref="M205:P205" si="77">M204+5000</f>
+        <f>M204+5000</f>
         <v>81000</v>
       </c>
       <c r="N205" s="4">
-        <f t="shared" si="77"/>
+        <f>N204+5000</f>
         <v>81000</v>
       </c>
       <c r="O205" s="4">
-        <f t="shared" si="77"/>
+        <f>O204+5000</f>
         <v>52750</v>
       </c>
       <c r="P205" s="4">
-        <f t="shared" si="77"/>
+        <f>P204+5000</f>
         <v>52750</v>
       </c>
       <c r="Q205" s="4">
@@ -19281,363 +19304,373 @@
       <c r="T205" s="8">
         <v>99.99</v>
       </c>
-      <c r="U205" s="39" t="s">
+      <c r="U205" s="47" t="s">
         <v>1388</v>
       </c>
-      <c r="V205" s="39" t="s">
+      <c r="V205" s="47" t="s">
         <v>1388</v>
       </c>
       <c r="W205" s="4"/>
       <c r="X205" s="4"/>
     </row>
     <row r="206" s="9" customFormat="1" customHeight="1" spans="1:27">
-      <c r="C206" s="10">
+      <c r="C206" s="33">
         <v>10201</v>
       </c>
-      <c r="D206" s="10">
+      <c r="D206" s="33">
         <v>1200</v>
       </c>
-      <c r="E206" s="10">
+      <c r="E206" s="33">
         <v>6</v>
       </c>
-      <c r="F206" s="10" t="s">
+      <c r="F206" s="33" t="s">
         <v>1389</v>
       </c>
-      <c r="G206" s="45" t="s">
+      <c r="G206" s="56" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H206" s="46" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I206" s="46" t="s">
         <v>1390</v>
       </c>
-      <c r="H206" s="38" t="s">
+      <c r="J206" s="46" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K206" s="50" t="s">
+        <v>1392</v>
+      </c>
+      <c r="L206" s="46" t="s">
+        <v>1359</v>
+      </c>
+      <c r="M206" s="4">
+        <f t="shared" ref="M206:M210" si="77">M205+10000</f>
+        <v>91000</v>
+      </c>
+      <c r="N206" s="4">
+        <f t="shared" ref="N206:N210" si="78">N205+10000</f>
+        <v>91000</v>
+      </c>
+      <c r="O206" s="4">
+        <f t="shared" ref="O206:O210" si="79">O205+10000</f>
+        <v>62750</v>
+      </c>
+      <c r="P206" s="4">
+        <f t="shared" ref="P206:P210" si="80">P205+10000</f>
+        <v>62750</v>
+      </c>
+      <c r="Q206" s="35">
+        <f t="shared" si="71"/>
+        <v>143</v>
+      </c>
+      <c r="R206" s="8">
+        <f t="shared" si="72"/>
+        <v>519</v>
+      </c>
+      <c r="S206" s="8">
+        <f t="shared" si="73"/>
+        <v>636</v>
+      </c>
+      <c r="T206" s="8">
+        <v>99.99</v>
+      </c>
+      <c r="U206" s="47" t="s">
+        <v>1393</v>
+      </c>
+      <c r="V206" s="47" t="s">
+        <v>1393</v>
+      </c>
+      <c r="W206" s="33"/>
+      <c r="X206" s="33"/>
+    </row>
+    <row r="207" s="8" customFormat="1" customHeight="1" spans="1:27">
+      <c r="C207" s="4">
+        <v>10202</v>
+      </c>
+      <c r="D207" s="4">
+        <v>1201</v>
+      </c>
+      <c r="E207" s="4">
+        <v>6</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G207" s="46" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H207" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I206" s="45" t="s">
-        <v>1391</v>
-      </c>
-      <c r="J206" s="45" t="s">
-        <v>1392</v>
-      </c>
-      <c r="K206" s="10"/>
-      <c r="L206" s="45" t="s">
-        <v>1393</v>
-      </c>
-      <c r="M206" s="10">
-        <f t="shared" ref="M205:M215" si="78">M205+600</f>
-        <v>81600</v>
-      </c>
-      <c r="N206" s="10">
-        <f t="shared" ref="N205:N215" si="79">N205+600</f>
-        <v>81600</v>
-      </c>
-      <c r="O206" s="10">
-        <f t="shared" ref="O206:O210" si="80">O205+400</f>
-        <v>53150</v>
-      </c>
-      <c r="P206" s="10">
-        <f t="shared" ref="P206:P210" si="81">P205+400</f>
-        <v>53150</v>
-      </c>
-      <c r="Q206" s="10">
-        <f t="shared" si="64"/>
-        <v>140</v>
-      </c>
-      <c r="R206" s="9">
-        <f t="shared" si="69"/>
-        <v>514</v>
-      </c>
-      <c r="S206" s="9">
-        <f t="shared" si="59"/>
-        <v>631</v>
-      </c>
-      <c r="T206" s="9">
+      <c r="I207" s="46" t="s">
+        <v>1396</v>
+      </c>
+      <c r="J207" s="46" t="s">
+        <v>1397</v>
+      </c>
+      <c r="K207" s="50" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L207" s="46" t="s">
+        <v>1294</v>
+      </c>
+      <c r="M207" s="4">
+        <f t="shared" si="77"/>
+        <v>101000</v>
+      </c>
+      <c r="N207" s="4">
+        <f t="shared" si="78"/>
+        <v>101000</v>
+      </c>
+      <c r="O207" s="4">
+        <f t="shared" si="79"/>
+        <v>72750</v>
+      </c>
+      <c r="P207" s="4">
+        <f t="shared" si="80"/>
+        <v>72750</v>
+      </c>
+      <c r="Q207" s="27">
+        <f t="shared" si="71"/>
+        <v>149</v>
+      </c>
+      <c r="R207" s="8">
+        <f t="shared" si="72"/>
+        <v>534</v>
+      </c>
+      <c r="S207" s="8">
+        <f t="shared" si="73"/>
+        <v>651</v>
+      </c>
+      <c r="T207" s="8">
         <v>99.99</v>
       </c>
-      <c r="U206" s="46" t="s">
-        <v>1229</v>
-      </c>
-      <c r="V206" s="46" t="s">
-        <v>1229</v>
-      </c>
-      <c r="W206" s="10"/>
-      <c r="X206" s="10"/>
-    </row>
-    <row r="207" s="9" customFormat="1" customHeight="1" spans="1:27">
-      <c r="C207" s="10">
-        <v>10202</v>
-      </c>
-      <c r="D207" s="10">
-        <v>1201</v>
-      </c>
-      <c r="E207" s="10">
+      <c r="U207" s="47" t="s">
+        <v>1398</v>
+      </c>
+      <c r="V207" s="47" t="s">
+        <v>1398</v>
+      </c>
+      <c r="W207" s="4"/>
+      <c r="X207" s="4"/>
+    </row>
+    <row r="208" s="8" customFormat="1" customHeight="1" spans="1:27">
+      <c r="C208" s="4">
+        <v>10203</v>
+      </c>
+      <c r="D208" s="4">
+        <v>1202</v>
+      </c>
+      <c r="E208" s="4">
         <v>6</v>
       </c>
-      <c r="F207" s="10" t="s">
-        <v>1394</v>
-      </c>
-      <c r="G207" s="45" t="s">
-        <v>1395</v>
-      </c>
-      <c r="H207" s="38" t="s">
+      <c r="F208" s="4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G208" s="46" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H208" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I207" s="45" t="s">
-        <v>1396</v>
-      </c>
-      <c r="J207" s="45" t="s">
-        <v>1397</v>
-      </c>
-      <c r="K207" s="10"/>
-      <c r="L207" s="45" t="s">
-        <v>1398</v>
-      </c>
-      <c r="M207" s="10">
+      <c r="I208" s="46" t="s">
+        <v>1400</v>
+      </c>
+      <c r="J208" s="46" t="s">
+        <v>1252</v>
+      </c>
+      <c r="K208" s="50" t="s">
+        <v>1401</v>
+      </c>
+      <c r="L208" s="46" t="s">
+        <v>1233</v>
+      </c>
+      <c r="M208" s="4">
+        <f t="shared" si="77"/>
+        <v>111000</v>
+      </c>
+      <c r="N208" s="4">
         <f t="shared" si="78"/>
-        <v>82200</v>
-      </c>
-      <c r="N207" s="10">
+        <v>111000</v>
+      </c>
+      <c r="O208" s="4">
         <f t="shared" si="79"/>
-        <v>82200</v>
-      </c>
-      <c r="O207" s="10">
+        <v>82750</v>
+      </c>
+      <c r="P208" s="4">
         <f t="shared" si="80"/>
-        <v>53550</v>
-      </c>
-      <c r="P207" s="10">
-        <f t="shared" si="81"/>
-        <v>53550</v>
-      </c>
-      <c r="Q207" s="10">
-        <f t="shared" si="64"/>
-        <v>143</v>
-      </c>
-      <c r="R207" s="9">
-        <f t="shared" si="69"/>
-        <v>524</v>
-      </c>
-      <c r="S207" s="9">
-        <f t="shared" si="59"/>
-        <v>641</v>
-      </c>
-      <c r="T207" s="9">
+        <v>82750</v>
+      </c>
+      <c r="Q208" s="27">
+        <f t="shared" si="71"/>
+        <v>155</v>
+      </c>
+      <c r="R208" s="8">
+        <f t="shared" si="72"/>
+        <v>549</v>
+      </c>
+      <c r="S208" s="8">
+        <f t="shared" si="73"/>
+        <v>666</v>
+      </c>
+      <c r="T208" s="8">
         <v>99.99</v>
       </c>
-      <c r="U207" s="46" t="s">
-        <v>1229</v>
-      </c>
-      <c r="V207" s="46" t="s">
-        <v>1229</v>
-      </c>
-      <c r="W207" s="10"/>
-      <c r="X207" s="10"/>
-    </row>
-    <row r="208" s="9" customFormat="1" customHeight="1" spans="1:27">
-      <c r="C208" s="10">
-        <v>10203</v>
-      </c>
-      <c r="D208" s="10">
-        <v>1202</v>
-      </c>
-      <c r="E208" s="10">
+      <c r="U208" s="47" t="s">
+        <v>1402</v>
+      </c>
+      <c r="V208" s="47" t="s">
+        <v>1402</v>
+      </c>
+      <c r="W208" s="4"/>
+      <c r="X208" s="4"/>
+    </row>
+    <row r="209" s="8" customFormat="1" customHeight="1" spans="1:27">
+      <c r="C209" s="4">
+        <v>10204</v>
+      </c>
+      <c r="D209" s="4">
+        <v>1203</v>
+      </c>
+      <c r="E209" s="4">
         <v>6</v>
       </c>
-      <c r="F208" s="10" t="s">
-        <v>1399</v>
-      </c>
-      <c r="G208" s="45" t="s">
-        <v>1400</v>
-      </c>
-      <c r="H208" s="38" t="s">
+      <c r="F209" s="4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="G209" s="46" t="s">
+        <v>1404</v>
+      </c>
+      <c r="H209" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I208" s="45" t="s">
-        <v>1401</v>
-      </c>
-      <c r="J208" s="45" t="s">
-        <v>1228</v>
-      </c>
-      <c r="K208" s="10"/>
-      <c r="L208" s="45" t="s">
-        <v>1402</v>
-      </c>
-      <c r="M208" s="10">
+      <c r="I209" s="46" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J209" s="46" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K209" s="50" t="s">
+        <v>1326</v>
+      </c>
+      <c r="L209" s="46" t="s">
+        <v>1407</v>
+      </c>
+      <c r="M209" s="4">
+        <f t="shared" si="77"/>
+        <v>121000</v>
+      </c>
+      <c r="N209" s="4">
         <f t="shared" si="78"/>
-        <v>82800</v>
-      </c>
-      <c r="N208" s="10">
+        <v>121000</v>
+      </c>
+      <c r="O209" s="4">
         <f t="shared" si="79"/>
-        <v>82800</v>
-      </c>
-      <c r="O208" s="10">
+        <v>92750</v>
+      </c>
+      <c r="P209" s="4">
         <f t="shared" si="80"/>
-        <v>53950</v>
-      </c>
-      <c r="P208" s="10">
-        <f t="shared" si="81"/>
-        <v>53950</v>
-      </c>
-      <c r="Q208" s="10">
-        <f t="shared" si="64"/>
-        <v>146</v>
-      </c>
-      <c r="R208" s="9">
-        <f t="shared" si="69"/>
-        <v>534</v>
-      </c>
-      <c r="S208" s="9">
-        <f t="shared" si="59"/>
-        <v>651</v>
-      </c>
-      <c r="T208" s="9">
+        <v>92750</v>
+      </c>
+      <c r="Q209" s="27">
+        <f t="shared" si="71"/>
+        <v>161</v>
+      </c>
+      <c r="R209" s="8">
+        <f t="shared" si="72"/>
+        <v>564</v>
+      </c>
+      <c r="S209" s="8">
+        <f t="shared" si="73"/>
+        <v>681</v>
+      </c>
+      <c r="T209" s="8">
         <v>99.99</v>
       </c>
-      <c r="U208" s="46" t="s">
-        <v>1229</v>
-      </c>
-      <c r="V208" s="46" t="s">
-        <v>1229</v>
-      </c>
-      <c r="W208" s="10"/>
-      <c r="X208" s="10"/>
-    </row>
-    <row r="209" s="9" customFormat="1" customHeight="1" spans="1:27">
-      <c r="C209" s="10">
-        <v>10204</v>
-      </c>
-      <c r="D209" s="10">
-        <v>1203</v>
-      </c>
-      <c r="E209" s="10">
+      <c r="U209" s="47" t="s">
+        <v>1408</v>
+      </c>
+      <c r="V209" s="47" t="s">
+        <v>1408</v>
+      </c>
+      <c r="W209" s="4"/>
+      <c r="X209" s="4"/>
+    </row>
+    <row r="210" s="8" customFormat="1" customHeight="1" spans="1:27">
+      <c r="C210" s="4">
+        <v>10205</v>
+      </c>
+      <c r="D210" s="4">
+        <v>1204</v>
+      </c>
+      <c r="E210" s="4">
         <v>6</v>
       </c>
-      <c r="F209" s="10" t="s">
-        <v>1403</v>
-      </c>
-      <c r="G209" s="45" t="s">
-        <v>1404</v>
-      </c>
-      <c r="H209" s="38" t="s">
+      <c r="F210" s="4" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G210" s="46" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H210" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I209" s="45" t="s">
-        <v>1405</v>
-      </c>
-      <c r="J209" s="45" t="s">
-        <v>1406</v>
-      </c>
-      <c r="K209" s="10"/>
-      <c r="L209" s="45" t="s">
-        <v>1407</v>
-      </c>
-      <c r="M209" s="10">
+      <c r="I210" s="46" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J210" s="46" t="s">
+        <v>1412</v>
+      </c>
+      <c r="K210" s="50" t="s">
+        <v>1338</v>
+      </c>
+      <c r="L210" s="46" t="s">
+        <v>1241</v>
+      </c>
+      <c r="M210" s="4">
+        <f t="shared" si="77"/>
+        <v>131000</v>
+      </c>
+      <c r="N210" s="4">
         <f t="shared" si="78"/>
-        <v>83400</v>
-      </c>
-      <c r="N209" s="10">
+        <v>131000</v>
+      </c>
+      <c r="O210" s="4">
         <f t="shared" si="79"/>
-        <v>83400</v>
-      </c>
-      <c r="O209" s="10">
+        <v>102750</v>
+      </c>
+      <c r="P210" s="4">
         <f t="shared" si="80"/>
-        <v>54350</v>
-      </c>
-      <c r="P209" s="10">
-        <f t="shared" si="81"/>
-        <v>54350</v>
-      </c>
-      <c r="Q209" s="10">
-        <f t="shared" si="64"/>
-        <v>149</v>
-      </c>
-      <c r="R209" s="9">
-        <f t="shared" si="69"/>
-        <v>544</v>
-      </c>
-      <c r="S209" s="9">
-        <f t="shared" si="59"/>
-        <v>661</v>
-      </c>
-      <c r="T209" s="9">
+        <v>102750</v>
+      </c>
+      <c r="Q210" s="27">
+        <f t="shared" si="71"/>
+        <v>167</v>
+      </c>
+      <c r="R210" s="8">
+        <f t="shared" si="72"/>
+        <v>579</v>
+      </c>
+      <c r="S210" s="8">
+        <f t="shared" si="73"/>
+        <v>696</v>
+      </c>
+      <c r="T210" s="8">
         <v>99.99</v>
       </c>
-      <c r="U209" s="46" t="s">
-        <v>1229</v>
-      </c>
-      <c r="V209" s="46" t="s">
-        <v>1229</v>
-      </c>
-      <c r="W209" s="10"/>
-      <c r="X209" s="10"/>
-    </row>
-    <row r="210" s="9" customFormat="1" customHeight="1" spans="1:27">
-      <c r="C210" s="10">
-        <v>10205</v>
-      </c>
-      <c r="D210" s="10">
-        <v>1204</v>
-      </c>
-      <c r="E210" s="10">
-        <v>6</v>
-      </c>
-      <c r="F210" s="10" t="s">
-        <v>1408</v>
-      </c>
-      <c r="G210" s="45" t="s">
-        <v>1409</v>
-      </c>
-      <c r="H210" s="38" t="s">
-        <v>1302</v>
-      </c>
-      <c r="I210" s="45" t="s">
-        <v>1410</v>
-      </c>
-      <c r="J210" s="45" t="s">
-        <v>1411</v>
-      </c>
-      <c r="K210" s="10"/>
-      <c r="L210" s="45" t="s">
-        <v>1412</v>
-      </c>
-      <c r="M210" s="10">
-        <f t="shared" si="78"/>
-        <v>84000</v>
-      </c>
-      <c r="N210" s="10">
-        <f t="shared" si="79"/>
-        <v>84000</v>
-      </c>
-      <c r="O210" s="10">
-        <f t="shared" si="80"/>
-        <v>54750</v>
-      </c>
-      <c r="P210" s="10">
-        <f t="shared" si="81"/>
-        <v>54750</v>
-      </c>
-      <c r="Q210" s="10">
-        <f t="shared" si="64"/>
-        <v>152</v>
-      </c>
-      <c r="R210" s="9">
-        <f t="shared" si="69"/>
-        <v>554</v>
-      </c>
-      <c r="S210" s="9">
-        <f t="shared" si="59"/>
-        <v>671</v>
-      </c>
-      <c r="T210" s="9">
-        <v>99.99</v>
-      </c>
-      <c r="U210" s="46" t="s">
-        <v>1229</v>
-      </c>
-      <c r="V210" s="46" t="s">
-        <v>1229</v>
-      </c>
-      <c r="W210" s="10"/>
-      <c r="X210" s="10"/>
+      <c r="U210" s="47" t="s">
+        <v>1413</v>
+      </c>
+      <c r="V210" s="47" t="s">
+        <v>1413</v>
+      </c>
+      <c r="W210" s="4"/>
+      <c r="X210" s="4"/>
     </row>
     <row r="211" s="10" customFormat="1" customHeight="1" spans="1:27">
-      <c r="A211" s="9"/>
-      <c r="B211" s="9"/>
+      <c r="A211" s="36"/>
+      <c r="B211" s="36"/>
       <c r="C211" s="10">
         <v>10206</v>
       </c>
@@ -19648,69 +19681,69 @@
         <v>6</v>
       </c>
       <c r="F211" s="10" t="s">
-        <v>1413</v>
-      </c>
-      <c r="G211" s="45" t="s">
         <v>1414</v>
       </c>
-      <c r="H211" s="38" t="s">
+      <c r="G211" s="57" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H211" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I211" s="45" t="s">
-        <v>1415</v>
-      </c>
-      <c r="J211" s="45" t="s">
+      <c r="I211" s="57" t="s">
         <v>1416</v>
       </c>
-      <c r="L211" s="45" t="s">
+      <c r="J211" s="57" t="s">
         <v>1417</v>
       </c>
+      <c r="L211" s="57" t="s">
+        <v>1418</v>
+      </c>
       <c r="M211" s="10">
-        <f t="shared" si="78"/>
-        <v>84600</v>
+        <f t="shared" ref="M205:M215" si="81">M210+600</f>
+        <v>131600</v>
       </c>
       <c r="N211" s="10">
-        <f t="shared" si="79"/>
-        <v>84600</v>
+        <f t="shared" ref="N205:N215" si="82">N210+600</f>
+        <v>131600</v>
       </c>
       <c r="O211" s="10">
-        <f t="shared" ref="O211:O215" si="82">O210+500</f>
-        <v>55250</v>
+        <f t="shared" ref="O211:O215" si="83">O210+500</f>
+        <v>103250</v>
       </c>
       <c r="P211" s="10">
-        <f t="shared" ref="P211:P215" si="83">P210+500</f>
-        <v>55250</v>
+        <f t="shared" ref="P211:P215" si="84">P210+500</f>
+        <v>103250</v>
       </c>
       <c r="Q211" s="10">
         <f t="shared" si="64"/>
-        <v>155</v>
-      </c>
-      <c r="R211" s="9">
+        <v>170</v>
+      </c>
+      <c r="R211" s="36">
         <f t="shared" si="69"/>
-        <v>564</v>
-      </c>
-      <c r="S211" s="9">
+        <v>589</v>
+      </c>
+      <c r="S211" s="36">
         <f t="shared" si="59"/>
-        <v>681</v>
-      </c>
-      <c r="T211" s="9">
+        <v>706</v>
+      </c>
+      <c r="T211" s="36">
         <v>99.99</v>
       </c>
-      <c r="U211" s="46" t="s">
+      <c r="U211" s="58" t="s">
         <v>1229</v>
       </c>
-      <c r="V211" s="46" t="s">
+      <c r="V211" s="58" t="s">
         <v>1229</v>
       </c>
-      <c r="W211" s="9"/>
-      <c r="X211" s="9"/>
-      <c r="Y211" s="9"/>
-      <c r="Z211" s="9"/>
-      <c r="AA211" s="9"/>
+      <c r="W211" s="36"/>
+      <c r="X211" s="36"/>
+      <c r="Y211" s="36"/>
+      <c r="Z211" s="36"/>
+      <c r="AA211" s="36"/>
     </row>
     <row r="212" s="10" customFormat="1" customHeight="1" spans="1:27">
-      <c r="A212" s="9"/>
-      <c r="B212" s="9"/>
+      <c r="A212" s="36"/>
+      <c r="B212" s="36"/>
       <c r="C212" s="10">
         <v>10207</v>
       </c>
@@ -19721,69 +19754,69 @@
         <v>6</v>
       </c>
       <c r="F212" s="10" t="s">
-        <v>1418</v>
-      </c>
-      <c r="G212" s="45" t="s">
         <v>1419</v>
       </c>
-      <c r="H212" s="38" t="s">
+      <c r="G212" s="57" t="s">
+        <v>1420</v>
+      </c>
+      <c r="H212" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I212" s="45" t="s">
-        <v>1420</v>
-      </c>
-      <c r="J212" s="45" t="s">
+      <c r="I212" s="57" t="s">
         <v>1421</v>
       </c>
-      <c r="L212" s="45" t="s">
+      <c r="J212" s="57" t="s">
         <v>1422</v>
       </c>
+      <c r="L212" s="57" t="s">
+        <v>1423</v>
+      </c>
       <c r="M212" s="10">
-        <f t="shared" si="78"/>
-        <v>85200</v>
+        <f t="shared" si="81"/>
+        <v>132200</v>
       </c>
       <c r="N212" s="10">
-        <f t="shared" si="79"/>
-        <v>85200</v>
+        <f t="shared" si="82"/>
+        <v>132200</v>
       </c>
       <c r="O212" s="10">
-        <f t="shared" si="82"/>
-        <v>55750</v>
+        <f t="shared" si="83"/>
+        <v>103750</v>
       </c>
       <c r="P212" s="10">
-        <f t="shared" si="83"/>
-        <v>55750</v>
+        <f t="shared" si="84"/>
+        <v>103750</v>
       </c>
       <c r="Q212" s="10">
         <f t="shared" si="64"/>
-        <v>158</v>
-      </c>
-      <c r="R212" s="9">
+        <v>173</v>
+      </c>
+      <c r="R212" s="36">
         <f t="shared" si="69"/>
-        <v>574</v>
-      </c>
-      <c r="S212" s="9">
+        <v>599</v>
+      </c>
+      <c r="S212" s="36">
         <f t="shared" si="59"/>
-        <v>691</v>
-      </c>
-      <c r="T212" s="9">
+        <v>716</v>
+      </c>
+      <c r="T212" s="36">
         <v>99.99</v>
       </c>
-      <c r="U212" s="46" t="s">
+      <c r="U212" s="58" t="s">
         <v>1229</v>
       </c>
-      <c r="V212" s="46" t="s">
+      <c r="V212" s="58" t="s">
         <v>1229</v>
       </c>
-      <c r="W212" s="9"/>
-      <c r="X212" s="9"/>
-      <c r="Y212" s="9"/>
-      <c r="Z212" s="9"/>
-      <c r="AA212" s="9"/>
+      <c r="W212" s="36"/>
+      <c r="X212" s="36"/>
+      <c r="Y212" s="36"/>
+      <c r="Z212" s="36"/>
+      <c r="AA212" s="36"/>
     </row>
     <row r="213" s="10" customFormat="1" customHeight="1" spans="1:27">
-      <c r="A213" s="9"/>
-      <c r="B213" s="9"/>
+      <c r="A213" s="36"/>
+      <c r="B213" s="36"/>
       <c r="C213" s="10">
         <v>10208</v>
       </c>
@@ -19794,69 +19827,69 @@
         <v>6</v>
       </c>
       <c r="F213" s="10" t="s">
-        <v>1423</v>
-      </c>
-      <c r="G213" s="45" t="s">
         <v>1424</v>
       </c>
-      <c r="H213" s="38" t="s">
+      <c r="G213" s="57" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H213" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I213" s="45" t="s">
-        <v>1425</v>
-      </c>
-      <c r="J213" s="45" t="s">
+      <c r="I213" s="57" t="s">
         <v>1426</v>
       </c>
-      <c r="L213" s="45" t="s">
+      <c r="J213" s="57" t="s">
         <v>1427</v>
       </c>
+      <c r="L213" s="57" t="s">
+        <v>1428</v>
+      </c>
       <c r="M213" s="10">
-        <f t="shared" si="78"/>
-        <v>85800</v>
+        <f t="shared" si="81"/>
+        <v>132800</v>
       </c>
       <c r="N213" s="10">
-        <f t="shared" si="79"/>
-        <v>85800</v>
+        <f t="shared" si="82"/>
+        <v>132800</v>
       </c>
       <c r="O213" s="10">
-        <f t="shared" si="82"/>
-        <v>56250</v>
+        <f t="shared" si="83"/>
+        <v>104250</v>
       </c>
       <c r="P213" s="10">
-        <f t="shared" si="83"/>
-        <v>56250</v>
+        <f t="shared" si="84"/>
+        <v>104250</v>
       </c>
       <c r="Q213" s="10">
         <f t="shared" si="64"/>
-        <v>161</v>
-      </c>
-      <c r="R213" s="9">
+        <v>176</v>
+      </c>
+      <c r="R213" s="36">
         <f t="shared" si="69"/>
-        <v>584</v>
-      </c>
-      <c r="S213" s="9">
+        <v>609</v>
+      </c>
+      <c r="S213" s="36">
         <f t="shared" si="59"/>
-        <v>701</v>
-      </c>
-      <c r="T213" s="9">
+        <v>726</v>
+      </c>
+      <c r="T213" s="36">
         <v>99.99</v>
       </c>
-      <c r="U213" s="46" t="s">
+      <c r="U213" s="58" t="s">
         <v>1229</v>
       </c>
-      <c r="V213" s="46" t="s">
+      <c r="V213" s="58" t="s">
         <v>1229</v>
       </c>
-      <c r="W213" s="9"/>
-      <c r="X213" s="9"/>
-      <c r="Y213" s="9"/>
-      <c r="Z213" s="9"/>
-      <c r="AA213" s="9"/>
+      <c r="W213" s="36"/>
+      <c r="X213" s="36"/>
+      <c r="Y213" s="36"/>
+      <c r="Z213" s="36"/>
+      <c r="AA213" s="36"/>
     </row>
     <row r="214" s="10" customFormat="1" customHeight="1" spans="1:27">
-      <c r="A214" s="9"/>
-      <c r="B214" s="9"/>
+      <c r="A214" s="36"/>
+      <c r="B214" s="36"/>
       <c r="C214" s="10">
         <v>10209</v>
       </c>
@@ -19867,69 +19900,69 @@
         <v>6</v>
       </c>
       <c r="F214" s="10" t="s">
-        <v>1428</v>
-      </c>
-      <c r="G214" s="45" t="s">
         <v>1429</v>
       </c>
-      <c r="H214" s="38" t="s">
+      <c r="G214" s="57" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H214" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I214" s="45" t="s">
-        <v>1430</v>
-      </c>
-      <c r="J214" s="45" t="s">
+      <c r="I214" s="57" t="s">
         <v>1431</v>
       </c>
-      <c r="L214" s="45" t="s">
+      <c r="J214" s="57" t="s">
         <v>1432</v>
       </c>
+      <c r="L214" s="57" t="s">
+        <v>1433</v>
+      </c>
       <c r="M214" s="10">
-        <f t="shared" si="78"/>
-        <v>86400</v>
+        <f t="shared" si="81"/>
+        <v>133400</v>
       </c>
       <c r="N214" s="10">
-        <f t="shared" si="79"/>
-        <v>86400</v>
+        <f t="shared" si="82"/>
+        <v>133400</v>
       </c>
       <c r="O214" s="10">
-        <f t="shared" si="82"/>
-        <v>56750</v>
+        <f t="shared" si="83"/>
+        <v>104750</v>
       </c>
       <c r="P214" s="10">
-        <f t="shared" si="83"/>
-        <v>56750</v>
+        <f t="shared" si="84"/>
+        <v>104750</v>
       </c>
       <c r="Q214" s="10">
         <f t="shared" si="64"/>
-        <v>164</v>
-      </c>
-      <c r="R214" s="9">
+        <v>179</v>
+      </c>
+      <c r="R214" s="36">
         <f t="shared" si="69"/>
-        <v>594</v>
-      </c>
-      <c r="S214" s="9">
+        <v>619</v>
+      </c>
+      <c r="S214" s="36">
         <f t="shared" si="59"/>
-        <v>711</v>
-      </c>
-      <c r="T214" s="9">
+        <v>736</v>
+      </c>
+      <c r="T214" s="36">
         <v>99.99</v>
       </c>
-      <c r="U214" s="46" t="s">
+      <c r="U214" s="58" t="s">
         <v>1229</v>
       </c>
-      <c r="V214" s="46" t="s">
+      <c r="V214" s="58" t="s">
         <v>1229</v>
       </c>
-      <c r="W214" s="9"/>
-      <c r="X214" s="9"/>
-      <c r="Y214" s="9"/>
-      <c r="Z214" s="9"/>
-      <c r="AA214" s="9"/>
+      <c r="W214" s="36"/>
+      <c r="X214" s="36"/>
+      <c r="Y214" s="36"/>
+      <c r="Z214" s="36"/>
+      <c r="AA214" s="36"/>
     </row>
     <row r="215" s="10" customFormat="1" customHeight="1" spans="1:27">
-      <c r="A215" s="9"/>
-      <c r="B215" s="9"/>
+      <c r="A215" s="36"/>
+      <c r="B215" s="36"/>
       <c r="C215" s="10">
         <v>10210</v>
       </c>
@@ -19940,65 +19973,65 @@
         <v>6</v>
       </c>
       <c r="F215" s="10" t="s">
-        <v>1433</v>
-      </c>
-      <c r="G215" s="45" t="s">
         <v>1434</v>
       </c>
-      <c r="H215" s="38" t="s">
+      <c r="G215" s="57" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H215" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="I215" s="45" t="s">
-        <v>1435</v>
-      </c>
-      <c r="J215" s="45" t="s">
+      <c r="I215" s="57" t="s">
         <v>1436</v>
       </c>
-      <c r="L215" s="45" t="s">
+      <c r="J215" s="57" t="s">
         <v>1437</v>
       </c>
+      <c r="L215" s="57" t="s">
+        <v>1438</v>
+      </c>
       <c r="M215" s="10">
-        <f t="shared" si="78"/>
-        <v>87000</v>
+        <f t="shared" si="81"/>
+        <v>134000</v>
       </c>
       <c r="N215" s="10">
-        <f t="shared" si="79"/>
-        <v>87000</v>
+        <f t="shared" si="82"/>
+        <v>134000</v>
       </c>
       <c r="O215" s="10">
-        <f t="shared" si="82"/>
-        <v>57250</v>
+        <f t="shared" si="83"/>
+        <v>105250</v>
       </c>
       <c r="P215" s="10">
-        <f t="shared" si="83"/>
-        <v>57250</v>
+        <f t="shared" si="84"/>
+        <v>105250</v>
       </c>
       <c r="Q215" s="10">
         <f t="shared" si="64"/>
-        <v>167</v>
-      </c>
-      <c r="R215" s="9">
+        <v>182</v>
+      </c>
+      <c r="R215" s="36">
         <f t="shared" si="69"/>
-        <v>604</v>
-      </c>
-      <c r="S215" s="9">
+        <v>629</v>
+      </c>
+      <c r="S215" s="36">
         <f t="shared" si="59"/>
-        <v>721</v>
-      </c>
-      <c r="T215" s="9">
+        <v>746</v>
+      </c>
+      <c r="T215" s="36">
         <v>99.99</v>
       </c>
-      <c r="U215" s="46" t="s">
+      <c r="U215" s="58" t="s">
         <v>1229</v>
       </c>
-      <c r="V215" s="46" t="s">
+      <c r="V215" s="58" t="s">
         <v>1229</v>
       </c>
-      <c r="W215" s="9"/>
-      <c r="X215" s="9"/>
-      <c r="Y215" s="9"/>
-      <c r="Z215" s="9"/>
-      <c r="AA215" s="9"/>
+      <c r="W215" s="36"/>
+      <c r="X215" s="36"/>
+      <c r="Y215" s="36"/>
+      <c r="Z215" s="36"/>
+      <c r="AA215" s="36"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="1489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="1507">
   <si>
     <t>ID</t>
   </si>
@@ -4409,16 +4409,70 @@
     <t>虚无雪人</t>
   </si>
   <si>
+    <t>1E+256</t>
+  </si>
+  <si>
+    <t>1E+108</t>
+  </si>
+  <si>
+    <t>480000000000</t>
+  </si>
+  <si>
     <t>虚无蝙蝠</t>
   </si>
   <si>
+    <t>1E+230</t>
+  </si>
+  <si>
+    <t>1E+260</t>
+  </si>
+  <si>
+    <t>490000000000</t>
+  </si>
+  <si>
     <t>虚无骷髅</t>
   </si>
   <si>
+    <t>1E+235</t>
+  </si>
+  <si>
+    <t>1E+264</t>
+  </si>
+  <si>
+    <t>1E+114</t>
+  </si>
+  <si>
+    <t>500000000000</t>
+  </si>
+  <si>
     <t>虚无僵尸</t>
   </si>
   <si>
+    <t>1E+240</t>
+  </si>
+  <si>
+    <t>1E+268</t>
+  </si>
+  <si>
+    <t>1E+121</t>
+  </si>
+  <si>
+    <t>1E+117</t>
+  </si>
+  <si>
+    <t>510000000000</t>
+  </si>
+  <si>
     <t>虚无毒蛇</t>
+  </si>
+  <si>
+    <t>1E+245</t>
+  </si>
+  <si>
+    <t>1E+272</t>
+  </si>
+  <si>
+    <t>520000000000</t>
   </si>
   <si>
     <t>虚无野狼</t>
@@ -5138,7 +5192,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5171,10 +5225,9 @@
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -5195,10 +5248,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5810,13 +5862,13 @@
       <c r="F6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="26" t="s">
+      <c r="I6" s="25" t="s">
         <v>37</v>
       </c>
       <c r="J6" s="1">
@@ -9553,7 +9605,7 @@
       <c r="H65" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="I65" s="26" t="s">
+      <c r="I65" s="25" t="s">
         <v>440</v>
       </c>
       <c r="J65" s="1">
@@ -9622,7 +9674,7 @@
       <c r="H66" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="I66" s="26" t="s">
+      <c r="I66" s="25" t="s">
         <v>447</v>
       </c>
       <c r="J66" s="1">
@@ -9691,7 +9743,7 @@
       <c r="H67" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="I67" s="26" t="s">
+      <c r="I67" s="25" t="s">
         <v>454</v>
       </c>
       <c r="J67" s="1">
@@ -9760,7 +9812,7 @@
       <c r="H68" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="I68" s="26" t="s">
+      <c r="I68" s="25" t="s">
         <v>461</v>
       </c>
       <c r="J68" s="1">
@@ -9826,10 +9878,10 @@
       <c r="G69" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="H69" s="26" t="s">
+      <c r="H69" s="25" t="s">
         <v>467</v>
       </c>
-      <c r="I69" s="26" t="s">
+      <c r="I69" s="25" t="s">
         <v>468</v>
       </c>
       <c r="J69" s="1">
@@ -9892,13 +9944,13 @@
       <c r="F70" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="G70" s="26" t="s">
+      <c r="G70" s="25" t="s">
         <v>473</v>
       </c>
-      <c r="H70" s="26" t="s">
+      <c r="H70" s="25" t="s">
         <v>474</v>
       </c>
-      <c r="I70" s="26" t="s">
+      <c r="I70" s="25" t="s">
         <v>475</v>
       </c>
       <c r="J70" s="1">
@@ -9961,13 +10013,13 @@
       <c r="F71" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="G71" s="26" t="s">
+      <c r="G71" s="25" t="s">
         <v>480</v>
       </c>
-      <c r="H71" s="26" t="s">
+      <c r="H71" s="25" t="s">
         <v>481</v>
       </c>
-      <c r="I71" s="26" t="s">
+      <c r="I71" s="25" t="s">
         <v>482</v>
       </c>
       <c r="J71" s="1">
@@ -10030,13 +10082,13 @@
       <c r="F72" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="G72" s="26" t="s">
+      <c r="G72" s="25" t="s">
         <v>487</v>
       </c>
-      <c r="H72" s="26" t="s">
+      <c r="H72" s="25" t="s">
         <v>488</v>
       </c>
-      <c r="I72" s="26" t="s">
+      <c r="I72" s="25" t="s">
         <v>489</v>
       </c>
       <c r="J72" s="1">
@@ -10099,13 +10151,13 @@
       <c r="F73" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G73" s="26" t="s">
+      <c r="G73" s="25" t="s">
         <v>494</v>
       </c>
-      <c r="H73" s="26" t="s">
+      <c r="H73" s="25" t="s">
         <v>495</v>
       </c>
-      <c r="I73" s="26" t="s">
+      <c r="I73" s="25" t="s">
         <v>496</v>
       </c>
       <c r="J73" s="1">
@@ -10168,13 +10220,13 @@
       <c r="F74" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="G74" s="26" t="s">
+      <c r="G74" s="25" t="s">
         <v>501</v>
       </c>
-      <c r="H74" s="26" t="s">
+      <c r="H74" s="25" t="s">
         <v>502</v>
       </c>
-      <c r="I74" s="26" t="s">
+      <c r="I74" s="25" t="s">
         <v>503</v>
       </c>
       <c r="J74" s="1">
@@ -10237,13 +10289,13 @@
       <c r="F75" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="G75" s="26" t="s">
+      <c r="G75" s="25" t="s">
         <v>508</v>
       </c>
-      <c r="H75" s="26" t="s">
+      <c r="H75" s="25" t="s">
         <v>509</v>
       </c>
-      <c r="I75" s="26" t="s">
+      <c r="I75" s="25" t="s">
         <v>510</v>
       </c>
       <c r="J75" s="1">
@@ -10283,7 +10335,7 @@
       <c r="U75" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="V75" s="26" t="s">
+      <c r="V75" s="25" t="s">
         <v>511</v>
       </c>
       <c r="W75" s="9"/>
@@ -10307,13 +10359,13 @@
       <c r="F76" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G76" s="26" t="s">
+      <c r="G76" s="25" t="s">
         <v>515</v>
       </c>
-      <c r="H76" s="26" t="s">
+      <c r="H76" s="25" t="s">
         <v>516</v>
       </c>
-      <c r="I76" s="26" t="s">
+      <c r="I76" s="25" t="s">
         <v>517</v>
       </c>
       <c r="J76" s="1">
@@ -10375,13 +10427,13 @@
       <c r="F77" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="G77" s="26" t="s">
+      <c r="G77" s="25" t="s">
         <v>521</v>
       </c>
-      <c r="H77" s="26" t="s">
+      <c r="H77" s="25" t="s">
         <v>522</v>
       </c>
-      <c r="I77" s="26" t="s">
+      <c r="I77" s="25" t="s">
         <v>523</v>
       </c>
       <c r="J77" s="1">
@@ -10443,13 +10495,13 @@
       <c r="F78" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="G78" s="26" t="s">
+      <c r="G78" s="25" t="s">
         <v>527</v>
       </c>
-      <c r="H78" s="26" t="s">
+      <c r="H78" s="25" t="s">
         <v>528</v>
       </c>
-      <c r="I78" s="26" t="s">
+      <c r="I78" s="25" t="s">
         <v>529</v>
       </c>
       <c r="J78" s="1">
@@ -10511,13 +10563,13 @@
       <c r="F79" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G79" s="26" t="s">
+      <c r="G79" s="25" t="s">
         <v>533</v>
       </c>
-      <c r="H79" s="26" t="s">
+      <c r="H79" s="25" t="s">
         <v>534</v>
       </c>
-      <c r="I79" s="26" t="s">
+      <c r="I79" s="25" t="s">
         <v>535</v>
       </c>
       <c r="J79" s="1">
@@ -10579,13 +10631,13 @@
       <c r="F80" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="G80" s="26" t="s">
+      <c r="G80" s="25" t="s">
         <v>539</v>
       </c>
-      <c r="H80" s="26" t="s">
+      <c r="H80" s="25" t="s">
         <v>540</v>
       </c>
-      <c r="I80" s="26" t="s">
+      <c r="I80" s="25" t="s">
         <v>541</v>
       </c>
       <c r="J80" s="1">
@@ -10647,13 +10699,13 @@
       <c r="F81" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="G81" s="26" t="s">
+      <c r="G81" s="25" t="s">
         <v>545</v>
       </c>
-      <c r="H81" s="26" t="s">
+      <c r="H81" s="25" t="s">
         <v>546</v>
       </c>
-      <c r="I81" s="26" t="s">
+      <c r="I81" s="25" t="s">
         <v>547</v>
       </c>
       <c r="J81" s="1">
@@ -10717,13 +10769,13 @@
       <c r="F82" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G82" s="26" t="s">
+      <c r="G82" s="25" t="s">
         <v>551</v>
       </c>
-      <c r="H82" s="26" t="s">
+      <c r="H82" s="25" t="s">
         <v>552</v>
       </c>
-      <c r="I82" s="26" t="s">
+      <c r="I82" s="25" t="s">
         <v>553</v>
       </c>
       <c r="J82" s="1">
@@ -10787,13 +10839,13 @@
       <c r="F83" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="G83" s="26" t="s">
+      <c r="G83" s="25" t="s">
         <v>557</v>
       </c>
-      <c r="H83" s="26" t="s">
+      <c r="H83" s="25" t="s">
         <v>558</v>
       </c>
-      <c r="I83" s="26" t="s">
+      <c r="I83" s="25" t="s">
         <v>559</v>
       </c>
       <c r="J83" s="1">
@@ -10857,13 +10909,13 @@
       <c r="F84" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G84" s="26" t="s">
+      <c r="G84" s="25" t="s">
         <v>563</v>
       </c>
-      <c r="H84" s="26" t="s">
+      <c r="H84" s="25" t="s">
         <v>564</v>
       </c>
-      <c r="I84" s="26" t="s">
+      <c r="I84" s="25" t="s">
         <v>565</v>
       </c>
       <c r="J84" s="1">
@@ -10927,13 +10979,13 @@
       <c r="F85" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="G85" s="26" t="s">
+      <c r="G85" s="25" t="s">
         <v>569</v>
       </c>
-      <c r="H85" s="26" t="s">
+      <c r="H85" s="25" t="s">
         <v>570</v>
       </c>
-      <c r="I85" s="26" t="s">
+      <c r="I85" s="25" t="s">
         <v>571</v>
       </c>
       <c r="J85" s="1">
@@ -10997,13 +11049,13 @@
       <c r="F86" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="G86" s="26" t="s">
+      <c r="G86" s="25" t="s">
         <v>575</v>
       </c>
-      <c r="H86" s="26" t="s">
+      <c r="H86" s="25" t="s">
         <v>539</v>
       </c>
-      <c r="I86" s="26" t="s">
+      <c r="I86" s="25" t="s">
         <v>576</v>
       </c>
       <c r="J86" s="1">
@@ -11067,13 +11119,13 @@
       <c r="F87" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="G87" s="26" t="s">
+      <c r="G87" s="25" t="s">
         <v>580</v>
       </c>
-      <c r="H87" s="26" t="s">
+      <c r="H87" s="25" t="s">
         <v>581</v>
       </c>
-      <c r="I87" s="26" t="s">
+      <c r="I87" s="25" t="s">
         <v>582</v>
       </c>
       <c r="J87" s="1">
@@ -11137,13 +11189,13 @@
       <c r="F88" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="G88" s="26" t="s">
+      <c r="G88" s="25" t="s">
         <v>489</v>
       </c>
-      <c r="H88" s="26" t="s">
+      <c r="H88" s="25" t="s">
         <v>454</v>
       </c>
-      <c r="I88" s="26" t="s">
+      <c r="I88" s="25" t="s">
         <v>586</v>
       </c>
       <c r="J88" s="1">
@@ -11207,13 +11259,13 @@
       <c r="F89" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="G89" s="26" t="s">
+      <c r="G89" s="25" t="s">
         <v>503</v>
       </c>
-      <c r="H89" s="26" t="s">
+      <c r="H89" s="25" t="s">
         <v>590</v>
       </c>
-      <c r="I89" s="26" t="s">
+      <c r="I89" s="25" t="s">
         <v>591</v>
       </c>
       <c r="J89" s="1">
@@ -11277,13 +11329,13 @@
       <c r="F90" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G90" s="26" t="s">
+      <c r="G90" s="25" t="s">
         <v>595</v>
       </c>
-      <c r="H90" s="26" t="s">
+      <c r="H90" s="25" t="s">
         <v>580</v>
       </c>
-      <c r="I90" s="26" t="s">
+      <c r="I90" s="25" t="s">
         <v>596</v>
       </c>
       <c r="J90" s="1">
@@ -11347,13 +11399,13 @@
       <c r="F91" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="G91" s="26" t="s">
+      <c r="G91" s="25" t="s">
         <v>600</v>
       </c>
-      <c r="H91" s="26" t="s">
+      <c r="H91" s="25" t="s">
         <v>601</v>
       </c>
-      <c r="I91" s="26" t="s">
+      <c r="I91" s="25" t="s">
         <v>602</v>
       </c>
       <c r="J91" s="1">
@@ -11417,13 +11469,13 @@
       <c r="F92" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="G92" s="26" t="s">
+      <c r="G92" s="25" t="s">
         <v>606</v>
       </c>
-      <c r="H92" s="26" t="s">
+      <c r="H92" s="25" t="s">
         <v>607</v>
       </c>
-      <c r="I92" s="26" t="s">
+      <c r="I92" s="25" t="s">
         <v>608</v>
       </c>
       <c r="J92" s="1">
@@ -11487,13 +11539,13 @@
       <c r="F93" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G93" s="26" t="s">
+      <c r="G93" s="25" t="s">
         <v>612</v>
       </c>
-      <c r="H93" s="26" t="s">
+      <c r="H93" s="25" t="s">
         <v>613</v>
       </c>
-      <c r="I93" s="26" t="s">
+      <c r="I93" s="25" t="s">
         <v>614</v>
       </c>
       <c r="J93" s="1">
@@ -11557,13 +11609,13 @@
       <c r="F94" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="G94" s="26" t="s">
+      <c r="G94" s="25" t="s">
         <v>571</v>
       </c>
-      <c r="H94" s="26" t="s">
+      <c r="H94" s="25" t="s">
         <v>618</v>
       </c>
-      <c r="I94" s="26" t="s">
+      <c r="I94" s="25" t="s">
         <v>619</v>
       </c>
       <c r="J94" s="1">
@@ -11627,13 +11679,13 @@
       <c r="F95" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="G95" s="26" t="s">
+      <c r="G95" s="25" t="s">
         <v>576</v>
       </c>
-      <c r="H95" s="26" t="s">
+      <c r="H95" s="25" t="s">
         <v>623</v>
       </c>
-      <c r="I95" s="26" t="s">
+      <c r="I95" s="25" t="s">
         <v>624</v>
       </c>
       <c r="J95" s="1">
@@ -11695,13 +11747,13 @@
       <c r="F96" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="G96" s="26" t="s">
+      <c r="G96" s="25" t="s">
         <v>582</v>
       </c>
-      <c r="H96" s="26" t="s">
+      <c r="H96" s="25" t="s">
         <v>628</v>
       </c>
-      <c r="I96" s="26" t="s">
+      <c r="I96" s="25" t="s">
         <v>629</v>
       </c>
       <c r="J96" s="1">
@@ -11759,13 +11811,13 @@
       <c r="F97" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="G97" s="26" t="s">
+      <c r="G97" s="25" t="s">
         <v>586</v>
       </c>
-      <c r="H97" s="26" t="s">
+      <c r="H97" s="25" t="s">
         <v>633</v>
       </c>
-      <c r="I97" s="26" t="s">
+      <c r="I97" s="25" t="s">
         <v>634</v>
       </c>
       <c r="J97" s="1">
@@ -11823,13 +11875,13 @@
       <c r="F98" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="G98" s="26" t="s">
+      <c r="G98" s="25" t="s">
         <v>638</v>
       </c>
-      <c r="H98" s="26" t="s">
+      <c r="H98" s="25" t="s">
         <v>639</v>
       </c>
-      <c r="I98" s="26" t="s">
+      <c r="I98" s="25" t="s">
         <v>640</v>
       </c>
       <c r="J98" s="1">
@@ -11887,13 +11939,13 @@
       <c r="F99" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="G99" s="26" t="s">
+      <c r="G99" s="25" t="s">
         <v>644</v>
       </c>
-      <c r="H99" s="26" t="s">
+      <c r="H99" s="25" t="s">
         <v>645</v>
       </c>
-      <c r="I99" s="26" t="s">
+      <c r="I99" s="25" t="s">
         <v>646</v>
       </c>
       <c r="J99" s="1">
@@ -11951,13 +12003,13 @@
       <c r="F100" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="G100" s="26" t="s">
+      <c r="G100" s="25" t="s">
         <v>650</v>
       </c>
-      <c r="H100" s="26" t="s">
+      <c r="H100" s="25" t="s">
         <v>651</v>
       </c>
-      <c r="I100" s="26" t="s">
+      <c r="I100" s="25" t="s">
         <v>652</v>
       </c>
       <c r="J100" s="1">
@@ -12015,13 +12067,13 @@
       <c r="F101" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="G101" s="26" t="s">
+      <c r="G101" s="25" t="s">
         <v>656</v>
       </c>
-      <c r="H101" s="26" t="s">
+      <c r="H101" s="25" t="s">
         <v>657</v>
       </c>
-      <c r="I101" s="26" t="s">
+      <c r="I101" s="25" t="s">
         <v>658</v>
       </c>
       <c r="J101" s="1">
@@ -12079,13 +12131,13 @@
       <c r="F102" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="G102" s="26" t="s">
+      <c r="G102" s="25" t="s">
         <v>662</v>
       </c>
-      <c r="H102" s="26" t="s">
+      <c r="H102" s="25" t="s">
         <v>663</v>
       </c>
-      <c r="I102" s="26" t="s">
+      <c r="I102" s="25" t="s">
         <v>664</v>
       </c>
       <c r="J102" s="1">
@@ -12143,13 +12195,13 @@
       <c r="F103" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="G103" s="26" t="s">
+      <c r="G103" s="25" t="s">
         <v>668</v>
       </c>
-      <c r="H103" s="26" t="s">
+      <c r="H103" s="25" t="s">
         <v>669</v>
       </c>
-      <c r="I103" s="26" t="s">
+      <c r="I103" s="25" t="s">
         <v>670</v>
       </c>
       <c r="J103" s="1">
@@ -12207,13 +12259,13 @@
       <c r="F104" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="G104" s="26" t="s">
+      <c r="G104" s="25" t="s">
         <v>674</v>
       </c>
-      <c r="H104" s="26" t="s">
+      <c r="H104" s="25" t="s">
         <v>668</v>
       </c>
-      <c r="I104" s="26" t="s">
+      <c r="I104" s="25" t="s">
         <v>675</v>
       </c>
       <c r="J104" s="1">
@@ -12271,13 +12323,13 @@
       <c r="F105" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="G105" s="26" t="s">
+      <c r="G105" s="25" t="s">
         <v>679</v>
       </c>
-      <c r="H105" s="26" t="s">
+      <c r="H105" s="25" t="s">
         <v>674</v>
       </c>
-      <c r="I105" s="26" t="s">
+      <c r="I105" s="25" t="s">
         <v>680</v>
       </c>
       <c r="J105" s="1">
@@ -12337,13 +12389,13 @@
       <c r="F106" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="G106" s="26" t="s">
+      <c r="G106" s="25" t="s">
         <v>684</v>
       </c>
-      <c r="H106" s="26" t="s">
+      <c r="H106" s="25" t="s">
         <v>685</v>
       </c>
-      <c r="I106" s="26" t="s">
+      <c r="I106" s="25" t="s">
         <v>686</v>
       </c>
       <c r="J106" s="1">
@@ -12407,13 +12459,13 @@
       <c r="F107" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="G107" s="26" t="s">
+      <c r="G107" s="25" t="s">
         <v>690</v>
       </c>
-      <c r="H107" s="26" t="s">
+      <c r="H107" s="25" t="s">
         <v>691</v>
       </c>
-      <c r="I107" s="26" t="s">
+      <c r="I107" s="25" t="s">
         <v>692</v>
       </c>
       <c r="J107" s="1">
@@ -12477,13 +12529,13 @@
       <c r="F108" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="G108" s="26" t="s">
+      <c r="G108" s="25" t="s">
         <v>696</v>
       </c>
-      <c r="H108" s="26" t="s">
+      <c r="H108" s="25" t="s">
         <v>697</v>
       </c>
-      <c r="I108" s="26" t="s">
+      <c r="I108" s="25" t="s">
         <v>698</v>
       </c>
       <c r="J108" s="1">
@@ -12547,13 +12599,13 @@
       <c r="F109" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="G109" s="26" t="s">
+      <c r="G109" s="25" t="s">
         <v>702</v>
       </c>
-      <c r="H109" s="26" t="s">
+      <c r="H109" s="25" t="s">
         <v>703</v>
       </c>
-      <c r="I109" s="26" t="s">
+      <c r="I109" s="25" t="s">
         <v>704</v>
       </c>
       <c r="J109" s="1">
@@ -12617,13 +12669,13 @@
       <c r="F110" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="G110" s="26" t="s">
+      <c r="G110" s="25" t="s">
         <v>708</v>
       </c>
-      <c r="H110" s="26" t="s">
+      <c r="H110" s="25" t="s">
         <v>709</v>
       </c>
-      <c r="I110" s="26" t="s">
+      <c r="I110" s="25" t="s">
         <v>710</v>
       </c>
       <c r="J110" s="1">
@@ -12687,13 +12739,13 @@
       <c r="F111" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="G111" s="27" t="s">
+      <c r="G111" s="26" t="s">
         <v>714</v>
       </c>
-      <c r="H111" s="28" t="s">
+      <c r="H111" s="27" t="s">
         <v>714</v>
       </c>
-      <c r="I111" s="29" t="s">
+      <c r="I111" s="28" t="s">
         <v>715</v>
       </c>
       <c r="J111" s="1">
@@ -12726,10 +12778,10 @@
       <c r="T111" s="9">
         <v>90</v>
       </c>
-      <c r="U111" s="26" t="s">
+      <c r="U111" s="25" t="s">
         <v>716</v>
       </c>
-      <c r="V111" s="26" t="s">
+      <c r="V111" s="25" t="s">
         <v>716</v>
       </c>
       <c r="Y111" s="9"/>
@@ -12751,13 +12803,13 @@
       <c r="F112" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="G112" s="30" t="s">
+      <c r="G112" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="H112" s="26" t="s">
+      <c r="H112" s="25" t="s">
         <v>720</v>
       </c>
-      <c r="I112" s="31" t="s">
+      <c r="I112" s="30" t="s">
         <v>721</v>
       </c>
       <c r="J112" s="1">
@@ -12795,10 +12847,10 @@
       <c r="T112" s="9">
         <v>90</v>
       </c>
-      <c r="U112" s="26" t="s">
+      <c r="U112" s="25" t="s">
         <v>722</v>
       </c>
-      <c r="V112" s="26" t="s">
+      <c r="V112" s="25" t="s">
         <v>722</v>
       </c>
       <c r="Y112" s="9"/>
@@ -12820,13 +12872,13 @@
       <c r="F113" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="G113" s="30" t="s">
+      <c r="G113" s="29" t="s">
         <v>726</v>
       </c>
-      <c r="H113" s="26" t="s">
+      <c r="H113" s="25" t="s">
         <v>726</v>
       </c>
-      <c r="I113" s="31" t="s">
+      <c r="I113" s="30" t="s">
         <v>727</v>
       </c>
       <c r="J113" s="1">
@@ -12864,10 +12916,10 @@
       <c r="T113" s="9">
         <v>90</v>
       </c>
-      <c r="U113" s="26" t="s">
+      <c r="U113" s="25" t="s">
         <v>728</v>
       </c>
-      <c r="V113" s="26" t="s">
+      <c r="V113" s="25" t="s">
         <v>728</v>
       </c>
       <c r="Y113" s="9"/>
@@ -12889,13 +12941,13 @@
       <c r="F114" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="G114" s="30" t="s">
+      <c r="G114" s="29" t="s">
         <v>732</v>
       </c>
-      <c r="H114" s="26" t="s">
+      <c r="H114" s="25" t="s">
         <v>732</v>
       </c>
-      <c r="I114" s="31" t="s">
+      <c r="I114" s="30" t="s">
         <v>733</v>
       </c>
       <c r="J114" s="1">
@@ -12933,10 +12985,10 @@
       <c r="T114" s="9">
         <v>90</v>
       </c>
-      <c r="U114" s="26" t="s">
+      <c r="U114" s="25" t="s">
         <v>734</v>
       </c>
-      <c r="V114" s="26" t="s">
+      <c r="V114" s="25" t="s">
         <v>734</v>
       </c>
       <c r="Y114" s="9"/>
@@ -12958,13 +13010,13 @@
       <c r="F115" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="G115" s="30" t="s">
+      <c r="G115" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="H115" s="26" t="s">
+      <c r="H115" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="I115" s="31" t="s">
+      <c r="I115" s="30" t="s">
         <v>739</v>
       </c>
       <c r="J115" s="1">
@@ -13002,10 +13054,10 @@
       <c r="T115" s="9">
         <v>90</v>
       </c>
-      <c r="U115" s="26" t="s">
+      <c r="U115" s="25" t="s">
         <v>740</v>
       </c>
-      <c r="V115" s="26" t="s">
+      <c r="V115" s="25" t="s">
         <v>740</v>
       </c>
       <c r="Y115" s="9"/>
@@ -13027,13 +13079,13 @@
       <c r="F116" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="G116" s="30" t="s">
+      <c r="G116" s="29" t="s">
         <v>744</v>
       </c>
-      <c r="H116" s="26" t="s">
+      <c r="H116" s="25" t="s">
         <v>744</v>
       </c>
-      <c r="I116" s="31" t="s">
+      <c r="I116" s="30" t="s">
         <v>745</v>
       </c>
       <c r="J116" s="1">
@@ -13071,10 +13123,10 @@
       <c r="T116" s="9">
         <v>90</v>
       </c>
-      <c r="U116" s="26" t="s">
+      <c r="U116" s="25" t="s">
         <v>746</v>
       </c>
-      <c r="V116" s="26" t="s">
+      <c r="V116" s="25" t="s">
         <v>746</v>
       </c>
       <c r="W116" s="9"/>
@@ -13098,13 +13150,13 @@
       <c r="F117" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="G117" s="30" t="s">
+      <c r="G117" s="29" t="s">
         <v>750</v>
       </c>
-      <c r="H117" s="26" t="s">
+      <c r="H117" s="25" t="s">
         <v>750</v>
       </c>
-      <c r="I117" s="31" t="s">
+      <c r="I117" s="30" t="s">
         <v>751</v>
       </c>
       <c r="J117" s="1">
@@ -13142,10 +13194,10 @@
       <c r="T117" s="9">
         <v>90</v>
       </c>
-      <c r="U117" s="26" t="s">
+      <c r="U117" s="25" t="s">
         <v>752</v>
       </c>
-      <c r="V117" s="26" t="s">
+      <c r="V117" s="25" t="s">
         <v>752</v>
       </c>
       <c r="W117" s="9"/>
@@ -13169,13 +13221,13 @@
       <c r="F118" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="G118" s="30" t="s">
+      <c r="G118" s="29" t="s">
         <v>756</v>
       </c>
-      <c r="H118" s="26" t="s">
+      <c r="H118" s="25" t="s">
         <v>756</v>
       </c>
-      <c r="I118" s="31" t="s">
+      <c r="I118" s="30" t="s">
         <v>757</v>
       </c>
       <c r="J118" s="1">
@@ -13213,10 +13265,10 @@
       <c r="T118" s="9">
         <v>90</v>
       </c>
-      <c r="U118" s="26" t="s">
+      <c r="U118" s="25" t="s">
         <v>758</v>
       </c>
-      <c r="V118" s="26" t="s">
+      <c r="V118" s="25" t="s">
         <v>758</v>
       </c>
       <c r="W118" s="9"/>
@@ -13240,13 +13292,13 @@
       <c r="F119" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="G119" s="30" t="s">
+      <c r="G119" s="29" t="s">
         <v>762</v>
       </c>
-      <c r="H119" s="26" t="s">
+      <c r="H119" s="25" t="s">
         <v>762</v>
       </c>
-      <c r="I119" s="31" t="s">
+      <c r="I119" s="30" t="s">
         <v>763</v>
       </c>
       <c r="J119" s="1">
@@ -13284,10 +13336,10 @@
       <c r="T119" s="9">
         <v>90</v>
       </c>
-      <c r="U119" s="26" t="s">
+      <c r="U119" s="25" t="s">
         <v>764</v>
       </c>
-      <c r="V119" s="26" t="s">
+      <c r="V119" s="25" t="s">
         <v>764</v>
       </c>
       <c r="W119" s="9"/>
@@ -13311,13 +13363,13 @@
       <c r="F120" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="G120" s="30" t="s">
+      <c r="G120" s="29" t="s">
         <v>768</v>
       </c>
-      <c r="H120" s="26" t="s">
+      <c r="H120" s="25" t="s">
         <v>768</v>
       </c>
-      <c r="I120" s="31" t="s">
+      <c r="I120" s="30" t="s">
         <v>769</v>
       </c>
       <c r="J120" s="1">
@@ -13355,10 +13407,10 @@
       <c r="T120" s="9">
         <v>90</v>
       </c>
-      <c r="U120" s="26" t="s">
+      <c r="U120" s="25" t="s">
         <v>770</v>
       </c>
-      <c r="V120" s="26" t="s">
+      <c r="V120" s="25" t="s">
         <v>770</v>
       </c>
       <c r="W120" s="9"/>
@@ -13382,13 +13434,13 @@
       <c r="F121" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="G121" s="30" t="s">
+      <c r="G121" s="29" t="s">
         <v>715</v>
       </c>
-      <c r="H121" s="26" t="s">
+      <c r="H121" s="25" t="s">
         <v>715</v>
       </c>
-      <c r="I121" s="31" t="s">
+      <c r="I121" s="30" t="s">
         <v>774</v>
       </c>
       <c r="J121" s="1">
@@ -13426,10 +13478,10 @@
       <c r="T121" s="9">
         <v>90</v>
       </c>
-      <c r="U121" s="26" t="s">
+      <c r="U121" s="25" t="s">
         <v>775</v>
       </c>
-      <c r="V121" s="26" t="s">
+      <c r="V121" s="25" t="s">
         <v>775</v>
       </c>
       <c r="W121" s="9"/>
@@ -13453,13 +13505,13 @@
       <c r="F122" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="G122" s="30" t="s">
+      <c r="G122" s="29" t="s">
         <v>779</v>
       </c>
-      <c r="H122" s="26" t="s">
+      <c r="H122" s="25" t="s">
         <v>779</v>
       </c>
-      <c r="I122" s="31" t="s">
+      <c r="I122" s="30" t="s">
         <v>780</v>
       </c>
       <c r="J122" s="1">
@@ -13498,10 +13550,10 @@
       <c r="T122" s="9">
         <v>90</v>
       </c>
-      <c r="U122" s="26" t="s">
+      <c r="U122" s="25" t="s">
         <v>781</v>
       </c>
-      <c r="V122" s="26" t="s">
+      <c r="V122" s="25" t="s">
         <v>781</v>
       </c>
       <c r="W122" s="9"/>
@@ -13525,13 +13577,13 @@
       <c r="F123" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="G123" s="30" t="s">
+      <c r="G123" s="29" t="s">
         <v>785</v>
       </c>
-      <c r="H123" s="26" t="s">
+      <c r="H123" s="25" t="s">
         <v>785</v>
       </c>
-      <c r="I123" s="31" t="s">
+      <c r="I123" s="30" t="s">
         <v>786</v>
       </c>
       <c r="J123" s="1">
@@ -13570,10 +13622,10 @@
       <c r="T123" s="9">
         <v>90</v>
       </c>
-      <c r="U123" s="26" t="s">
+      <c r="U123" s="25" t="s">
         <v>787</v>
       </c>
-      <c r="V123" s="26" t="s">
+      <c r="V123" s="25" t="s">
         <v>787</v>
       </c>
       <c r="W123" s="9"/>
@@ -13597,13 +13649,13 @@
       <c r="F124" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="G124" s="30" t="s">
+      <c r="G124" s="29" t="s">
         <v>791</v>
       </c>
-      <c r="H124" s="26" t="s">
+      <c r="H124" s="25" t="s">
         <v>791</v>
       </c>
-      <c r="I124" s="31" t="s">
+      <c r="I124" s="30" t="s">
         <v>792</v>
       </c>
       <c r="J124" s="1">
@@ -13642,10 +13694,10 @@
       <c r="T124" s="9">
         <v>90</v>
       </c>
-      <c r="U124" s="26" t="s">
+      <c r="U124" s="25" t="s">
         <v>793</v>
       </c>
-      <c r="V124" s="26" t="s">
+      <c r="V124" s="25" t="s">
         <v>793</v>
       </c>
       <c r="W124" s="9"/>
@@ -13669,13 +13721,13 @@
       <c r="F125" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="G125" s="30" t="s">
+      <c r="G125" s="29" t="s">
         <v>797</v>
       </c>
-      <c r="H125" s="26" t="s">
+      <c r="H125" s="25" t="s">
         <v>797</v>
       </c>
-      <c r="I125" s="31" t="s">
+      <c r="I125" s="30" t="s">
         <v>798</v>
       </c>
       <c r="J125" s="1">
@@ -13714,10 +13766,10 @@
       <c r="T125" s="9">
         <v>90</v>
       </c>
-      <c r="U125" s="26" t="s">
+      <c r="U125" s="25" t="s">
         <v>799</v>
       </c>
-      <c r="V125" s="26" t="s">
+      <c r="V125" s="25" t="s">
         <v>799</v>
       </c>
       <c r="W125" s="9"/>
@@ -13741,13 +13793,13 @@
       <c r="F126" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="G126" s="30" t="s">
+      <c r="G126" s="29" t="s">
         <v>803</v>
       </c>
-      <c r="H126" s="26" t="s">
+      <c r="H126" s="25" t="s">
         <v>803</v>
       </c>
-      <c r="I126" s="31" t="s">
+      <c r="I126" s="30" t="s">
         <v>804</v>
       </c>
       <c r="J126" s="1">
@@ -13786,10 +13838,10 @@
       <c r="T126" s="9">
         <v>90</v>
       </c>
-      <c r="U126" s="26" t="s">
+      <c r="U126" s="25" t="s">
         <v>805</v>
       </c>
-      <c r="V126" s="26" t="s">
+      <c r="V126" s="25" t="s">
         <v>805</v>
       </c>
       <c r="W126" s="9"/>
@@ -13813,13 +13865,13 @@
       <c r="F127" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="G127" s="30" t="s">
+      <c r="G127" s="29" t="s">
         <v>809</v>
       </c>
-      <c r="H127" s="26" t="s">
+      <c r="H127" s="25" t="s">
         <v>809</v>
       </c>
-      <c r="I127" s="31" t="s">
+      <c r="I127" s="30" t="s">
         <v>810</v>
       </c>
       <c r="J127" s="1">
@@ -13858,10 +13910,10 @@
       <c r="T127" s="9">
         <v>90</v>
       </c>
-      <c r="U127" s="26" t="s">
+      <c r="U127" s="25" t="s">
         <v>811</v>
       </c>
-      <c r="V127" s="26" t="s">
+      <c r="V127" s="25" t="s">
         <v>811</v>
       </c>
       <c r="W127" s="9"/>
@@ -13885,13 +13937,13 @@
       <c r="F128" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="G128" s="30" t="s">
+      <c r="G128" s="29" t="s">
         <v>815</v>
       </c>
-      <c r="H128" s="26" t="s">
+      <c r="H128" s="25" t="s">
         <v>815</v>
       </c>
-      <c r="I128" s="31" t="s">
+      <c r="I128" s="30" t="s">
         <v>816</v>
       </c>
       <c r="J128" s="1">
@@ -13930,10 +13982,10 @@
       <c r="T128" s="9">
         <v>90</v>
       </c>
-      <c r="U128" s="26" t="s">
+      <c r="U128" s="25" t="s">
         <v>817</v>
       </c>
-      <c r="V128" s="26" t="s">
+      <c r="V128" s="25" t="s">
         <v>817</v>
       </c>
       <c r="W128" s="9"/>
@@ -13957,13 +14009,13 @@
       <c r="F129" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="G129" s="30" t="s">
+      <c r="G129" s="29" t="s">
         <v>821</v>
       </c>
-      <c r="H129" s="26" t="s">
+      <c r="H129" s="25" t="s">
         <v>821</v>
       </c>
-      <c r="I129" s="31" t="s">
+      <c r="I129" s="30" t="s">
         <v>822</v>
       </c>
       <c r="J129" s="1">
@@ -14002,10 +14054,10 @@
       <c r="T129" s="9">
         <v>90</v>
       </c>
-      <c r="U129" s="26" t="s">
+      <c r="U129" s="25" t="s">
         <v>823</v>
       </c>
-      <c r="V129" s="26" t="s">
+      <c r="V129" s="25" t="s">
         <v>823</v>
       </c>
       <c r="W129" s="9"/>
@@ -14029,13 +14081,13 @@
       <c r="F130" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="G130" s="30" t="s">
+      <c r="G130" s="29" t="s">
         <v>827</v>
       </c>
-      <c r="H130" s="26" t="s">
+      <c r="H130" s="25" t="s">
         <v>827</v>
       </c>
-      <c r="I130" s="31" t="s">
+      <c r="I130" s="30" t="s">
         <v>828</v>
       </c>
       <c r="J130" s="1">
@@ -14074,10 +14126,10 @@
       <c r="T130" s="9">
         <v>90</v>
       </c>
-      <c r="U130" s="26" t="s">
+      <c r="U130" s="25" t="s">
         <v>829</v>
       </c>
-      <c r="V130" s="26" t="s">
+      <c r="V130" s="25" t="s">
         <v>829</v>
       </c>
       <c r="W130" s="9"/>
@@ -14099,13 +14151,13 @@
       <c r="F131" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="G131" s="30" t="s">
+      <c r="G131" s="29" t="s">
         <v>833</v>
       </c>
-      <c r="H131" s="26" t="s">
+      <c r="H131" s="25" t="s">
         <v>833</v>
       </c>
-      <c r="I131" s="31" t="s">
+      <c r="I131" s="30" t="s">
         <v>834</v>
       </c>
       <c r="J131" s="1">
@@ -14145,10 +14197,10 @@
       <c r="T131" s="9">
         <v>92</v>
       </c>
-      <c r="U131" s="26" t="s">
+      <c r="U131" s="25" t="s">
         <v>835</v>
       </c>
-      <c r="V131" s="26" t="s">
+      <c r="V131" s="25" t="s">
         <v>835</v>
       </c>
     </row>
@@ -14165,13 +14217,13 @@
       <c r="F132" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="G132" s="30" t="s">
+      <c r="G132" s="29" t="s">
         <v>839</v>
       </c>
-      <c r="H132" s="26" t="s">
+      <c r="H132" s="25" t="s">
         <v>839</v>
       </c>
-      <c r="I132" s="31" t="s">
+      <c r="I132" s="30" t="s">
         <v>840</v>
       </c>
       <c r="J132" s="1">
@@ -14211,10 +14263,10 @@
       <c r="T132" s="9">
         <v>94</v>
       </c>
-      <c r="U132" s="26" t="s">
+      <c r="U132" s="25" t="s">
         <v>841</v>
       </c>
-      <c r="V132" s="26" t="s">
+      <c r="V132" s="25" t="s">
         <v>841</v>
       </c>
     </row>
@@ -14231,13 +14283,13 @@
       <c r="F133" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="G133" s="30" t="s">
+      <c r="G133" s="29" t="s">
         <v>845</v>
       </c>
-      <c r="H133" s="26" t="s">
+      <c r="H133" s="25" t="s">
         <v>845</v>
       </c>
-      <c r="I133" s="31" t="s">
+      <c r="I133" s="30" t="s">
         <v>846</v>
       </c>
       <c r="J133" s="1">
@@ -14277,10 +14329,10 @@
       <c r="T133" s="9">
         <v>96</v>
       </c>
-      <c r="U133" s="26" t="s">
+      <c r="U133" s="25" t="s">
         <v>847</v>
       </c>
-      <c r="V133" s="26" t="s">
+      <c r="V133" s="25" t="s">
         <v>847</v>
       </c>
     </row>
@@ -14297,13 +14349,13 @@
       <c r="F134" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="G134" s="30" t="s">
+      <c r="G134" s="29" t="s">
         <v>851</v>
       </c>
-      <c r="H134" s="26" t="s">
+      <c r="H134" s="25" t="s">
         <v>851</v>
       </c>
-      <c r="I134" s="31" t="s">
+      <c r="I134" s="30" t="s">
         <v>852</v>
       </c>
       <c r="J134" s="1">
@@ -14343,10 +14395,10 @@
       <c r="T134" s="9">
         <v>98</v>
       </c>
-      <c r="U134" s="26" t="s">
+      <c r="U134" s="25" t="s">
         <v>853</v>
       </c>
-      <c r="V134" s="26" t="s">
+      <c r="V134" s="25" t="s">
         <v>853</v>
       </c>
     </row>
@@ -14363,13 +14415,13 @@
       <c r="F135" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="G135" s="30" t="s">
+      <c r="G135" s="29" t="s">
         <v>857</v>
       </c>
-      <c r="H135" s="26" t="s">
+      <c r="H135" s="25" t="s">
         <v>857</v>
       </c>
-      <c r="I135" s="31" t="s">
+      <c r="I135" s="30" t="s">
         <v>858</v>
       </c>
       <c r="J135" s="1">
@@ -14409,10 +14461,10 @@
       <c r="T135" s="9">
         <v>99</v>
       </c>
-      <c r="U135" s="26" t="s">
+      <c r="U135" s="25" t="s">
         <v>859</v>
       </c>
-      <c r="V135" s="26" t="s">
+      <c r="V135" s="25" t="s">
         <v>859</v>
       </c>
     </row>
@@ -14429,13 +14481,13 @@
       <c r="F136" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="G136" s="30" t="s">
+      <c r="G136" s="29" t="s">
         <v>863</v>
       </c>
-      <c r="H136" s="26" t="s">
+      <c r="H136" s="25" t="s">
         <v>863</v>
       </c>
-      <c r="I136" s="31" t="s">
+      <c r="I136" s="30" t="s">
         <v>864</v>
       </c>
       <c r="J136" s="1">
@@ -14475,10 +14527,10 @@
       <c r="T136" s="9">
         <v>99.2</v>
       </c>
-      <c r="U136" s="26" t="s">
+      <c r="U136" s="25" t="s">
         <v>865</v>
       </c>
-      <c r="V136" s="26" t="s">
+      <c r="V136" s="25" t="s">
         <v>865</v>
       </c>
     </row>
@@ -14495,13 +14547,13 @@
       <c r="F137" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="G137" s="30" t="s">
+      <c r="G137" s="29" t="s">
         <v>869</v>
       </c>
-      <c r="H137" s="26" t="s">
+      <c r="H137" s="25" t="s">
         <v>869</v>
       </c>
-      <c r="I137" s="31" t="s">
+      <c r="I137" s="30" t="s">
         <v>870</v>
       </c>
       <c r="J137" s="1">
@@ -14541,10 +14593,10 @@
       <c r="T137" s="9">
         <v>99.4</v>
       </c>
-      <c r="U137" s="26" t="s">
+      <c r="U137" s="25" t="s">
         <v>871</v>
       </c>
-      <c r="V137" s="26" t="s">
+      <c r="V137" s="25" t="s">
         <v>871</v>
       </c>
     </row>
@@ -14561,13 +14613,13 @@
       <c r="F138" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="G138" s="30" t="s">
+      <c r="G138" s="29" t="s">
         <v>875</v>
       </c>
-      <c r="H138" s="26" t="s">
+      <c r="H138" s="25" t="s">
         <v>875</v>
       </c>
-      <c r="I138" s="31" t="s">
+      <c r="I138" s="30" t="s">
         <v>876</v>
       </c>
       <c r="J138" s="1">
@@ -14607,10 +14659,10 @@
       <c r="T138" s="9">
         <v>99.6</v>
       </c>
-      <c r="U138" s="26" t="s">
+      <c r="U138" s="25" t="s">
         <v>877</v>
       </c>
-      <c r="V138" s="26" t="s">
+      <c r="V138" s="25" t="s">
         <v>877</v>
       </c>
     </row>
@@ -14627,13 +14679,13 @@
       <c r="F139" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="G139" s="30" t="s">
+      <c r="G139" s="29" t="s">
         <v>881</v>
       </c>
-      <c r="H139" s="26" t="s">
+      <c r="H139" s="25" t="s">
         <v>881</v>
       </c>
-      <c r="I139" s="31" t="s">
+      <c r="I139" s="30" t="s">
         <v>882</v>
       </c>
       <c r="J139" s="1">
@@ -14673,10 +14725,10 @@
       <c r="T139" s="9">
         <v>99.8</v>
       </c>
-      <c r="U139" s="26" t="s">
+      <c r="U139" s="25" t="s">
         <v>883</v>
       </c>
-      <c r="V139" s="26" t="s">
+      <c r="V139" s="25" t="s">
         <v>883</v>
       </c>
     </row>
@@ -14693,13 +14745,13 @@
       <c r="F140" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="G140" s="30" t="s">
+      <c r="G140" s="29" t="s">
         <v>887</v>
       </c>
-      <c r="H140" s="26" t="s">
+      <c r="H140" s="25" t="s">
         <v>887</v>
       </c>
-      <c r="I140" s="31" t="s">
+      <c r="I140" s="30" t="s">
         <v>888</v>
       </c>
       <c r="J140" s="1">
@@ -14739,10 +14791,10 @@
       <c r="T140" s="9">
         <v>99.9</v>
       </c>
-      <c r="U140" s="26" t="s">
+      <c r="U140" s="25" t="s">
         <v>889</v>
       </c>
-      <c r="V140" s="26" t="s">
+      <c r="V140" s="25" t="s">
         <v>889</v>
       </c>
     </row>
@@ -14761,13 +14813,13 @@
       <c r="F141" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="G141" s="30" t="s">
+      <c r="G141" s="29" t="s">
         <v>893</v>
       </c>
-      <c r="H141" s="26" t="s">
+      <c r="H141" s="25" t="s">
         <v>893</v>
       </c>
-      <c r="I141" s="31" t="s">
+      <c r="I141" s="30" t="s">
         <v>894</v>
       </c>
       <c r="J141" s="1">
@@ -14806,10 +14858,10 @@
       <c r="T141" s="9">
         <v>99.92</v>
       </c>
-      <c r="U141" s="26" t="s">
+      <c r="U141" s="25" t="s">
         <v>895</v>
       </c>
-      <c r="V141" s="26" t="s">
+      <c r="V141" s="25" t="s">
         <v>895</v>
       </c>
       <c r="W141" s="9"/>
@@ -14833,13 +14885,13 @@
       <c r="F142" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="G142" s="30" t="s">
+      <c r="G142" s="29" t="s">
         <v>899</v>
       </c>
-      <c r="H142" s="26" t="s">
+      <c r="H142" s="25" t="s">
         <v>899</v>
       </c>
-      <c r="I142" s="31" t="s">
+      <c r="I142" s="30" t="s">
         <v>900</v>
       </c>
       <c r="J142" s="1">
@@ -14878,10 +14930,10 @@
       <c r="T142" s="9">
         <v>99.94</v>
       </c>
-      <c r="U142" s="26" t="s">
+      <c r="U142" s="25" t="s">
         <v>901</v>
       </c>
-      <c r="V142" s="26" t="s">
+      <c r="V142" s="25" t="s">
         <v>901</v>
       </c>
       <c r="W142" s="9"/>
@@ -14905,13 +14957,13 @@
       <c r="F143" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="G143" s="30" t="s">
+      <c r="G143" s="29" t="s">
         <v>905</v>
       </c>
-      <c r="H143" s="26" t="s">
+      <c r="H143" s="25" t="s">
         <v>905</v>
       </c>
-      <c r="I143" s="31" t="s">
+      <c r="I143" s="30" t="s">
         <v>906</v>
       </c>
       <c r="J143" s="1">
@@ -14950,10 +15002,10 @@
       <c r="T143" s="9">
         <v>99.96</v>
       </c>
-      <c r="U143" s="26" t="s">
+      <c r="U143" s="25" t="s">
         <v>907</v>
       </c>
-      <c r="V143" s="26" t="s">
+      <c r="V143" s="25" t="s">
         <v>907</v>
       </c>
       <c r="W143" s="9"/>
@@ -14977,13 +15029,13 @@
       <c r="F144" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="G144" s="30" t="s">
+      <c r="G144" s="29" t="s">
         <v>911</v>
       </c>
-      <c r="H144" s="26" t="s">
+      <c r="H144" s="25" t="s">
         <v>911</v>
       </c>
-      <c r="I144" s="31" t="s">
+      <c r="I144" s="30" t="s">
         <v>912</v>
       </c>
       <c r="J144" s="1">
@@ -15022,10 +15074,10 @@
       <c r="T144" s="9">
         <v>99.98</v>
       </c>
-      <c r="U144" s="26" t="s">
+      <c r="U144" s="25" t="s">
         <v>913</v>
       </c>
-      <c r="V144" s="26" t="s">
+      <c r="V144" s="25" t="s">
         <v>913</v>
       </c>
       <c r="W144" s="9"/>
@@ -15094,10 +15146,10 @@
       <c r="T145" s="9">
         <v>99.99</v>
       </c>
-      <c r="U145" s="26" t="s">
+      <c r="U145" s="25" t="s">
         <v>919</v>
       </c>
-      <c r="V145" s="26" t="s">
+      <c r="V145" s="25" t="s">
         <v>919</v>
       </c>
       <c r="W145" s="9"/>
@@ -15166,10 +15218,10 @@
       <c r="T146" s="17">
         <v>99.99</v>
       </c>
-      <c r="U146" s="32" t="s">
+      <c r="U146" s="31" t="s">
         <v>927</v>
       </c>
-      <c r="V146" s="32" t="s">
+      <c r="V146" s="31" t="s">
         <v>927</v>
       </c>
       <c r="Y146" s="17"/>
@@ -15237,10 +15289,10 @@
       <c r="T147" s="9">
         <v>99.99</v>
       </c>
-      <c r="U147" s="26" t="s">
+      <c r="U147" s="25" t="s">
         <v>935</v>
       </c>
-      <c r="V147" s="26" t="s">
+      <c r="V147" s="25" t="s">
         <v>935</v>
       </c>
       <c r="Y147" s="9"/>
@@ -15308,10 +15360,10 @@
       <c r="T148" s="9">
         <v>99.99</v>
       </c>
-      <c r="U148" s="26" t="s">
+      <c r="U148" s="25" t="s">
         <v>943</v>
       </c>
-      <c r="V148" s="26" t="s">
+      <c r="V148" s="25" t="s">
         <v>943</v>
       </c>
       <c r="Y148" s="9"/>
@@ -15379,10 +15431,10 @@
       <c r="T149" s="9">
         <v>99.99</v>
       </c>
-      <c r="U149" s="26" t="s">
+      <c r="U149" s="25" t="s">
         <v>951</v>
       </c>
-      <c r="V149" s="26" t="s">
+      <c r="V149" s="25" t="s">
         <v>951</v>
       </c>
       <c r="Y149" s="9"/>
@@ -15450,10 +15502,10 @@
       <c r="T150" s="9">
         <v>99.99</v>
       </c>
-      <c r="U150" s="26" t="s">
+      <c r="U150" s="25" t="s">
         <v>959</v>
       </c>
-      <c r="V150" s="26" t="s">
+      <c r="V150" s="25" t="s">
         <v>959</v>
       </c>
       <c r="Y150" s="9"/>
@@ -15520,10 +15572,10 @@
       <c r="T151" s="9">
         <v>99.99</v>
       </c>
-      <c r="U151" s="26" t="s">
+      <c r="U151" s="25" t="s">
         <v>968</v>
       </c>
-      <c r="V151" s="26" t="s">
+      <c r="V151" s="25" t="s">
         <v>968</v>
       </c>
       <c r="W151" s="9"/>
@@ -15592,10 +15644,10 @@
       <c r="T152" s="9">
         <v>99.99</v>
       </c>
-      <c r="U152" s="26" t="s">
+      <c r="U152" s="25" t="s">
         <v>977</v>
       </c>
-      <c r="V152" s="26" t="s">
+      <c r="V152" s="25" t="s">
         <v>977</v>
       </c>
       <c r="W152" s="9"/>
@@ -15664,10 +15716,10 @@
       <c r="T153" s="9">
         <v>99.99</v>
       </c>
-      <c r="U153" s="26" t="s">
+      <c r="U153" s="25" t="s">
         <v>986</v>
       </c>
-      <c r="V153" s="26" t="s">
+      <c r="V153" s="25" t="s">
         <v>986</v>
       </c>
       <c r="W153" s="9"/>
@@ -15736,10 +15788,10 @@
       <c r="T154" s="9">
         <v>99.99</v>
       </c>
-      <c r="U154" s="26" t="s">
+      <c r="U154" s="25" t="s">
         <v>995</v>
       </c>
-      <c r="V154" s="26" t="s">
+      <c r="V154" s="25" t="s">
         <v>995</v>
       </c>
       <c r="W154" s="9"/>
@@ -15808,10 +15860,10 @@
       <c r="T155" s="9">
         <v>99.99</v>
       </c>
-      <c r="U155" s="26" t="s">
+      <c r="U155" s="25" t="s">
         <v>1004</v>
       </c>
-      <c r="V155" s="26" t="s">
+      <c r="V155" s="25" t="s">
         <v>1004</v>
       </c>
       <c r="W155" s="9"/>
@@ -15880,10 +15932,10 @@
       <c r="T156" s="9">
         <v>99.99</v>
       </c>
-      <c r="U156" s="26" t="s">
+      <c r="U156" s="25" t="s">
         <v>1013</v>
       </c>
-      <c r="V156" s="26" t="s">
+      <c r="V156" s="25" t="s">
         <v>1013</v>
       </c>
       <c r="W156" s="9"/>
@@ -15952,10 +16004,10 @@
       <c r="T157" s="9">
         <v>99.99</v>
       </c>
-      <c r="U157" s="26" t="s">
+      <c r="U157" s="25" t="s">
         <v>1022</v>
       </c>
-      <c r="V157" s="26" t="s">
+      <c r="V157" s="25" t="s">
         <v>1022</v>
       </c>
       <c r="W157" s="9"/>
@@ -16024,10 +16076,10 @@
       <c r="T158" s="9">
         <v>99.99</v>
       </c>
-      <c r="U158" s="26" t="s">
+      <c r="U158" s="25" t="s">
         <v>1031</v>
       </c>
-      <c r="V158" s="26" t="s">
+      <c r="V158" s="25" t="s">
         <v>1031</v>
       </c>
       <c r="W158" s="9"/>
@@ -16096,10 +16148,10 @@
       <c r="T159" s="9">
         <v>99.99</v>
       </c>
-      <c r="U159" s="26" t="s">
+      <c r="U159" s="25" t="s">
         <v>1040</v>
       </c>
-      <c r="V159" s="26" t="s">
+      <c r="V159" s="25" t="s">
         <v>1040</v>
       </c>
       <c r="W159" s="9"/>
@@ -16168,10 +16220,10 @@
       <c r="T160" s="9">
         <v>99.99</v>
       </c>
-      <c r="U160" s="26" t="s">
+      <c r="U160" s="25" t="s">
         <v>1049</v>
       </c>
-      <c r="V160" s="26" t="s">
+      <c r="V160" s="25" t="s">
         <v>1049</v>
       </c>
       <c r="W160" s="9"/>
@@ -16240,10 +16292,10 @@
       <c r="T161" s="9">
         <v>99.99</v>
       </c>
-      <c r="U161" s="26" t="s">
+      <c r="U161" s="25" t="s">
         <v>1058</v>
       </c>
-      <c r="V161" s="26" t="s">
+      <c r="V161" s="25" t="s">
         <v>1058</v>
       </c>
       <c r="W161" s="9"/>
@@ -16312,10 +16364,10 @@
       <c r="T162" s="9">
         <v>99.99</v>
       </c>
-      <c r="U162" s="26" t="s">
+      <c r="U162" s="25" t="s">
         <v>1067</v>
       </c>
-      <c r="V162" s="26" t="s">
+      <c r="V162" s="25" t="s">
         <v>1067</v>
       </c>
       <c r="W162" s="9"/>
@@ -16384,10 +16436,10 @@
       <c r="T163" s="9">
         <v>99.99</v>
       </c>
-      <c r="U163" s="26" t="s">
+      <c r="U163" s="25" t="s">
         <v>1076</v>
       </c>
-      <c r="V163" s="26" t="s">
+      <c r="V163" s="25" t="s">
         <v>1076</v>
       </c>
       <c r="W163" s="9"/>
@@ -16457,10 +16509,10 @@
       <c r="T164" s="20">
         <v>99.99</v>
       </c>
-      <c r="U164" s="33" t="s">
+      <c r="U164" s="32" t="s">
         <v>1085</v>
       </c>
-      <c r="V164" s="33" t="s">
+      <c r="V164" s="32" t="s">
         <v>1085</v>
       </c>
       <c r="W164" s="20"/>
@@ -16484,7 +16536,7 @@
       <c r="F165" s="4" t="s">
         <v>1088</v>
       </c>
-      <c r="G165" s="34" t="s">
+      <c r="G165" s="33" t="s">
         <v>1089</v>
       </c>
       <c r="H165" s="4" t="s">
@@ -16530,10 +16582,10 @@
       <c r="T165" s="8">
         <v>99.99</v>
       </c>
-      <c r="U165" s="35" t="s">
+      <c r="U165" s="34" t="s">
         <v>1094</v>
       </c>
-      <c r="V165" s="35" t="s">
+      <c r="V165" s="34" t="s">
         <v>1094</v>
       </c>
       <c r="W165" s="8"/>
@@ -16555,20 +16607,20 @@
       <c r="F166" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="G166" s="36" t="s">
+      <c r="G166" s="35" t="s">
         <v>1098</v>
       </c>
-      <c r="H166" s="36" t="s">
+      <c r="H166" s="35" t="s">
         <v>1099</v>
       </c>
-      <c r="I166" s="36" t="s">
+      <c r="I166" s="35" t="s">
         <v>1100</v>
       </c>
-      <c r="J166" s="36" t="s">
+      <c r="J166" s="35" t="s">
         <v>1101</v>
       </c>
       <c r="K166" s="1"/>
-      <c r="L166" s="36" t="s">
+      <c r="L166" s="35" t="s">
         <v>1102</v>
       </c>
       <c r="M166" s="1">
@@ -16601,10 +16653,10 @@
       <c r="T166" s="9">
         <v>99.99</v>
       </c>
-      <c r="U166" s="26" t="s">
+      <c r="U166" s="25" t="s">
         <v>1103</v>
       </c>
-      <c r="V166" s="26" t="s">
+      <c r="V166" s="25" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -16621,20 +16673,20 @@
       <c r="F167" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="G167" s="36" t="s">
+      <c r="G167" s="35" t="s">
         <v>1107</v>
       </c>
-      <c r="H167" s="36" t="s">
+      <c r="H167" s="35" t="s">
         <v>1108</v>
       </c>
-      <c r="I167" s="36" t="s">
+      <c r="I167" s="35" t="s">
         <v>1109</v>
       </c>
-      <c r="J167" s="36" t="s">
+      <c r="J167" s="35" t="s">
         <v>1110</v>
       </c>
       <c r="K167" s="1"/>
-      <c r="L167" s="36" t="s">
+      <c r="L167" s="35" t="s">
         <v>1111</v>
       </c>
       <c r="M167" s="1">
@@ -16667,10 +16719,10 @@
       <c r="T167" s="9">
         <v>99.99</v>
       </c>
-      <c r="U167" s="26" t="s">
+      <c r="U167" s="25" t="s">
         <v>1112</v>
       </c>
-      <c r="V167" s="26" t="s">
+      <c r="V167" s="25" t="s">
         <v>1112</v>
       </c>
     </row>
@@ -16687,20 +16739,20 @@
       <c r="F168" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="G168" s="36" t="s">
+      <c r="G168" s="35" t="s">
         <v>1116</v>
       </c>
-      <c r="H168" s="36" t="s">
+      <c r="H168" s="35" t="s">
         <v>1117</v>
       </c>
-      <c r="I168" s="36" t="s">
+      <c r="I168" s="35" t="s">
         <v>1118</v>
       </c>
-      <c r="J168" s="36" t="s">
+      <c r="J168" s="35" t="s">
         <v>1119</v>
       </c>
       <c r="K168" s="1"/>
-      <c r="L168" s="36" t="s">
+      <c r="L168" s="35" t="s">
         <v>1120</v>
       </c>
       <c r="M168" s="1">
@@ -16733,10 +16785,10 @@
       <c r="T168" s="9">
         <v>99.99</v>
       </c>
-      <c r="U168" s="26" t="s">
+      <c r="U168" s="25" t="s">
         <v>1121</v>
       </c>
-      <c r="V168" s="26" t="s">
+      <c r="V168" s="25" t="s">
         <v>1121</v>
       </c>
     </row>
@@ -16753,20 +16805,20 @@
       <c r="F169" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="G169" s="36" t="s">
+      <c r="G169" s="35" t="s">
         <v>1125</v>
       </c>
-      <c r="H169" s="36" t="s">
+      <c r="H169" s="35" t="s">
         <v>1126</v>
       </c>
-      <c r="I169" s="36" t="s">
+      <c r="I169" s="35" t="s">
         <v>1127</v>
       </c>
-      <c r="J169" s="36" t="s">
+      <c r="J169" s="35" t="s">
         <v>1128</v>
       </c>
       <c r="K169" s="1"/>
-      <c r="L169" s="36" t="s">
+      <c r="L169" s="35" t="s">
         <v>1129</v>
       </c>
       <c r="M169" s="1">
@@ -16799,10 +16851,10 @@
       <c r="T169" s="9">
         <v>99.99</v>
       </c>
-      <c r="U169" s="26" t="s">
+      <c r="U169" s="25" t="s">
         <v>1130</v>
       </c>
-      <c r="V169" s="26" t="s">
+      <c r="V169" s="25" t="s">
         <v>1130</v>
       </c>
     </row>
@@ -16819,20 +16871,20 @@
       <c r="F170" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="G170" s="36" t="s">
+      <c r="G170" s="35" t="s">
         <v>1134</v>
       </c>
-      <c r="H170" s="36" t="s">
+      <c r="H170" s="35" t="s">
         <v>1135</v>
       </c>
-      <c r="I170" s="36" t="s">
+      <c r="I170" s="35" t="s">
         <v>1136</v>
       </c>
-      <c r="J170" s="36" t="s">
+      <c r="J170" s="35" t="s">
         <v>1137</v>
       </c>
       <c r="K170" s="1"/>
-      <c r="L170" s="36" t="s">
+      <c r="L170" s="35" t="s">
         <v>1138</v>
       </c>
       <c r="M170" s="1">
@@ -16865,10 +16917,10 @@
       <c r="T170" s="9">
         <v>99.99</v>
       </c>
-      <c r="U170" s="26" t="s">
+      <c r="U170" s="25" t="s">
         <v>1139</v>
       </c>
-      <c r="V170" s="26" t="s">
+      <c r="V170" s="25" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -16885,20 +16937,20 @@
       <c r="F171" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="G171" s="36" t="s">
+      <c r="G171" s="35" t="s">
         <v>1143</v>
       </c>
-      <c r="H171" s="36" t="s">
+      <c r="H171" s="35" t="s">
         <v>1144</v>
       </c>
-      <c r="I171" s="36" t="s">
+      <c r="I171" s="35" t="s">
         <v>1145</v>
       </c>
-      <c r="J171" s="36" t="s">
+      <c r="J171" s="35" t="s">
         <v>1146</v>
       </c>
       <c r="K171" s="1"/>
-      <c r="L171" s="36" t="s">
+      <c r="L171" s="35" t="s">
         <v>1147</v>
       </c>
       <c r="M171" s="1">
@@ -16931,10 +16983,10 @@
       <c r="T171" s="9">
         <v>99.99</v>
       </c>
-      <c r="U171" s="26" t="s">
+      <c r="U171" s="25" t="s">
         <v>1148</v>
       </c>
-      <c r="V171" s="26" t="s">
+      <c r="V171" s="25" t="s">
         <v>1148</v>
       </c>
     </row>
@@ -16951,20 +17003,20 @@
       <c r="F172" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="G172" s="36" t="s">
+      <c r="G172" s="35" t="s">
         <v>1152</v>
       </c>
-      <c r="H172" s="36" t="s">
+      <c r="H172" s="35" t="s">
         <v>1153</v>
       </c>
-      <c r="I172" s="36" t="s">
+      <c r="I172" s="35" t="s">
         <v>1154</v>
       </c>
-      <c r="J172" s="36" t="s">
+      <c r="J172" s="35" t="s">
         <v>1155</v>
       </c>
       <c r="K172" s="1"/>
-      <c r="L172" s="36" t="s">
+      <c r="L172" s="35" t="s">
         <v>1156</v>
       </c>
       <c r="M172" s="1">
@@ -16997,10 +17049,10 @@
       <c r="T172" s="9">
         <v>99.99</v>
       </c>
-      <c r="U172" s="26" t="s">
+      <c r="U172" s="25" t="s">
         <v>1157</v>
       </c>
-      <c r="V172" s="26" t="s">
+      <c r="V172" s="25" t="s">
         <v>1157</v>
       </c>
     </row>
@@ -17017,20 +17069,20 @@
       <c r="F173" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="G173" s="36" t="s">
+      <c r="G173" s="35" t="s">
         <v>1161</v>
       </c>
-      <c r="H173" s="36" t="s">
+      <c r="H173" s="35" t="s">
         <v>1162</v>
       </c>
-      <c r="I173" s="36" t="s">
+      <c r="I173" s="35" t="s">
         <v>1163</v>
       </c>
-      <c r="J173" s="36" t="s">
+      <c r="J173" s="35" t="s">
         <v>1164</v>
       </c>
       <c r="K173" s="1"/>
-      <c r="L173" s="36" t="s">
+      <c r="L173" s="35" t="s">
         <v>1165</v>
       </c>
       <c r="M173" s="1">
@@ -17063,10 +17115,10 @@
       <c r="T173" s="9">
         <v>99.99</v>
       </c>
-      <c r="U173" s="26" t="s">
+      <c r="U173" s="25" t="s">
         <v>1166</v>
       </c>
-      <c r="V173" s="26" t="s">
+      <c r="V173" s="25" t="s">
         <v>1166</v>
       </c>
     </row>
@@ -17083,20 +17135,20 @@
       <c r="F174" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="G174" s="36" t="s">
+      <c r="G174" s="35" t="s">
         <v>1170</v>
       </c>
-      <c r="H174" s="36" t="s">
+      <c r="H174" s="35" t="s">
         <v>1171</v>
       </c>
-      <c r="I174" s="36" t="s">
+      <c r="I174" s="35" t="s">
         <v>1172</v>
       </c>
-      <c r="J174" s="36" t="s">
+      <c r="J174" s="35" t="s">
         <v>1173</v>
       </c>
       <c r="K174" s="1"/>
-      <c r="L174" s="36" t="s">
+      <c r="L174" s="35" t="s">
         <v>1174</v>
       </c>
       <c r="M174" s="1">
@@ -17129,10 +17181,10 @@
       <c r="T174" s="9">
         <v>99.99</v>
       </c>
-      <c r="U174" s="26" t="s">
+      <c r="U174" s="25" t="s">
         <v>1175</v>
       </c>
-      <c r="V174" s="26" t="s">
+      <c r="V174" s="25" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -17149,20 +17201,20 @@
       <c r="F175" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="G175" s="36" t="s">
+      <c r="G175" s="35" t="s">
         <v>1179</v>
       </c>
-      <c r="H175" s="36" t="s">
+      <c r="H175" s="35" t="s">
         <v>1180</v>
       </c>
-      <c r="I175" s="36" t="s">
+      <c r="I175" s="35" t="s">
         <v>1181</v>
       </c>
-      <c r="J175" s="36" t="s">
+      <c r="J175" s="35" t="s">
         <v>1182</v>
       </c>
       <c r="K175" s="1"/>
-      <c r="L175" s="36" t="s">
+      <c r="L175" s="35" t="s">
         <v>1183</v>
       </c>
       <c r="M175" s="1">
@@ -17195,10 +17247,10 @@
       <c r="T175" s="9">
         <v>99.99</v>
       </c>
-      <c r="U175" s="26" t="s">
+      <c r="U175" s="25" t="s">
         <v>1184</v>
       </c>
-      <c r="V175" s="26" t="s">
+      <c r="V175" s="25" t="s">
         <v>1184</v>
       </c>
     </row>
@@ -17217,19 +17269,19 @@
       <c r="F176" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="G176" s="36" t="s">
+      <c r="G176" s="35" t="s">
         <v>1188</v>
       </c>
-      <c r="H176" s="36" t="s">
+      <c r="H176" s="35" t="s">
         <v>1189</v>
       </c>
-      <c r="I176" s="36" t="s">
+      <c r="I176" s="35" t="s">
         <v>1190</v>
       </c>
-      <c r="J176" s="36" t="s">
+      <c r="J176" s="35" t="s">
         <v>1191</v>
       </c>
-      <c r="L176" s="36" t="s">
+      <c r="L176" s="35" t="s">
         <v>1192</v>
       </c>
       <c r="M176" s="1">
@@ -17262,10 +17314,10 @@
       <c r="T176" s="9">
         <v>99.99</v>
       </c>
-      <c r="U176" s="26" t="s">
+      <c r="U176" s="25" t="s">
         <v>1193</v>
       </c>
-      <c r="V176" s="26" t="s">
+      <c r="V176" s="25" t="s">
         <v>1193</v>
       </c>
       <c r="W176" s="9"/>
@@ -17289,19 +17341,19 @@
       <c r="F177" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="G177" s="36" t="s">
+      <c r="G177" s="35" t="s">
         <v>1197</v>
       </c>
-      <c r="H177" s="36" t="s">
+      <c r="H177" s="35" t="s">
         <v>1198</v>
       </c>
-      <c r="I177" s="36" t="s">
+      <c r="I177" s="35" t="s">
         <v>1199</v>
       </c>
-      <c r="J177" s="36" t="s">
+      <c r="J177" s="35" t="s">
         <v>1200</v>
       </c>
-      <c r="L177" s="36" t="s">
+      <c r="L177" s="35" t="s">
         <v>1201</v>
       </c>
       <c r="M177" s="1">
@@ -17334,10 +17386,10 @@
       <c r="T177" s="9">
         <v>99.99</v>
       </c>
-      <c r="U177" s="26" t="s">
+      <c r="U177" s="25" t="s">
         <v>1202</v>
       </c>
-      <c r="V177" s="26" t="s">
+      <c r="V177" s="25" t="s">
         <v>1202</v>
       </c>
       <c r="W177" s="9"/>
@@ -17361,19 +17413,19 @@
       <c r="F178" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="G178" s="36" t="s">
+      <c r="G178" s="35" t="s">
         <v>1206</v>
       </c>
-      <c r="H178" s="36" t="s">
+      <c r="H178" s="35" t="s">
         <v>1207</v>
       </c>
-      <c r="I178" s="36" t="s">
+      <c r="I178" s="35" t="s">
         <v>1208</v>
       </c>
-      <c r="J178" s="36" t="s">
+      <c r="J178" s="35" t="s">
         <v>1209</v>
       </c>
-      <c r="L178" s="36" t="s">
+      <c r="L178" s="35" t="s">
         <v>1210</v>
       </c>
       <c r="M178" s="1">
@@ -17406,10 +17458,10 @@
       <c r="T178" s="9">
         <v>99.99</v>
       </c>
-      <c r="U178" s="26" t="s">
+      <c r="U178" s="25" t="s">
         <v>1211</v>
       </c>
-      <c r="V178" s="26" t="s">
+      <c r="V178" s="25" t="s">
         <v>1211</v>
       </c>
       <c r="W178" s="9"/>
@@ -17433,19 +17485,19 @@
       <c r="F179" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="G179" s="36" t="s">
+      <c r="G179" s="35" t="s">
         <v>1215</v>
       </c>
-      <c r="H179" s="36" t="s">
+      <c r="H179" s="35" t="s">
         <v>1216</v>
       </c>
-      <c r="I179" s="36" t="s">
+      <c r="I179" s="35" t="s">
         <v>1217</v>
       </c>
-      <c r="J179" s="36" t="s">
+      <c r="J179" s="35" t="s">
         <v>1218</v>
       </c>
-      <c r="L179" s="36" t="s">
+      <c r="L179" s="35" t="s">
         <v>1219</v>
       </c>
       <c r="M179" s="1">
@@ -17478,10 +17530,10 @@
       <c r="T179" s="9">
         <v>99.99</v>
       </c>
-      <c r="U179" s="26" t="s">
+      <c r="U179" s="25" t="s">
         <v>1220</v>
       </c>
-      <c r="V179" s="26" t="s">
+      <c r="V179" s="25" t="s">
         <v>1220</v>
       </c>
       <c r="W179" s="9"/>
@@ -17505,19 +17557,19 @@
       <c r="F180" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="G180" s="36" t="s">
+      <c r="G180" s="35" t="s">
         <v>1224</v>
       </c>
-      <c r="H180" s="36" t="s">
+      <c r="H180" s="35" t="s">
         <v>1225</v>
       </c>
-      <c r="I180" s="36" t="s">
+      <c r="I180" s="35" t="s">
         <v>1226</v>
       </c>
-      <c r="J180" s="36" t="s">
+      <c r="J180" s="35" t="s">
         <v>1227</v>
       </c>
-      <c r="L180" s="36" t="s">
+      <c r="L180" s="35" t="s">
         <v>1228</v>
       </c>
       <c r="M180" s="1">
@@ -17550,10 +17602,10 @@
       <c r="T180" s="9">
         <v>99.99</v>
       </c>
-      <c r="U180" s="26" t="s">
+      <c r="U180" s="25" t="s">
         <v>1229</v>
       </c>
-      <c r="V180" s="26" t="s">
+      <c r="V180" s="25" t="s">
         <v>1229</v>
       </c>
       <c r="W180" s="9"/>
@@ -17577,22 +17629,22 @@
       <c r="F181" s="2" t="s">
         <v>1230</v>
       </c>
-      <c r="G181" s="37" t="s">
+      <c r="G181" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H181" s="37" t="s">
+      <c r="H181" s="36" t="s">
         <v>1232</v>
       </c>
-      <c r="I181" s="37" t="s">
+      <c r="I181" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J181" s="37" t="s">
+      <c r="J181" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K181" s="32" t="s">
+      <c r="K181" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L181" s="37" t="s">
+      <c r="L181" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M181" s="2">
@@ -17621,10 +17673,10 @@
       <c r="T181" s="17">
         <v>99.99</v>
       </c>
-      <c r="U181" s="32" t="s">
+      <c r="U181" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V181" s="32" t="s">
+      <c r="V181" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="Y181" s="17"/>
@@ -17646,22 +17698,22 @@
       <c r="F182" s="5" t="s">
         <v>1238</v>
       </c>
-      <c r="G182" s="36" t="s">
+      <c r="G182" s="35" t="s">
         <v>1239</v>
       </c>
-      <c r="H182" s="36" t="s">
+      <c r="H182" s="35" t="s">
         <v>1240</v>
       </c>
-      <c r="I182" s="36" t="s">
+      <c r="I182" s="35" t="s">
         <v>1241</v>
       </c>
-      <c r="J182" s="36" t="s">
+      <c r="J182" s="35" t="s">
         <v>1242</v>
       </c>
-      <c r="K182" s="38" t="s">
+      <c r="K182" s="37" t="s">
         <v>1243</v>
       </c>
-      <c r="L182" s="36" t="s">
+      <c r="L182" s="35" t="s">
         <v>1244</v>
       </c>
       <c r="M182" s="5">
@@ -17695,10 +17747,10 @@
       <c r="T182" s="11">
         <v>99.99</v>
       </c>
-      <c r="U182" s="38" t="s">
+      <c r="U182" s="37" t="s">
         <v>1245</v>
       </c>
-      <c r="V182" s="38" t="s">
+      <c r="V182" s="37" t="s">
         <v>1245</v>
       </c>
       <c r="Y182" s="11"/>
@@ -17720,22 +17772,22 @@
       <c r="F183" s="5" t="s">
         <v>1246</v>
       </c>
-      <c r="G183" s="36" t="s">
+      <c r="G183" s="35" t="s">
         <v>1247</v>
       </c>
-      <c r="H183" s="36" t="s">
+      <c r="H183" s="35" t="s">
         <v>1248</v>
       </c>
-      <c r="I183" s="36" t="s">
+      <c r="I183" s="35" t="s">
         <v>1249</v>
       </c>
-      <c r="J183" s="36" t="s">
+      <c r="J183" s="35" t="s">
         <v>1250</v>
       </c>
-      <c r="K183" s="38" t="s">
+      <c r="K183" s="37" t="s">
         <v>1251</v>
       </c>
-      <c r="L183" s="36" t="s">
+      <c r="L183" s="35" t="s">
         <v>1252</v>
       </c>
       <c r="M183" s="5">
@@ -17769,10 +17821,10 @@
       <c r="T183" s="11">
         <v>99.99</v>
       </c>
-      <c r="U183" s="38" t="s">
+      <c r="U183" s="37" t="s">
         <v>1253</v>
       </c>
-      <c r="V183" s="38" t="s">
+      <c r="V183" s="37" t="s">
         <v>1253</v>
       </c>
       <c r="Y183" s="11"/>
@@ -17794,22 +17846,22 @@
       <c r="F184" s="5" t="s">
         <v>1254</v>
       </c>
-      <c r="G184" s="36" t="s">
+      <c r="G184" s="35" t="s">
         <v>1255</v>
       </c>
-      <c r="H184" s="36" t="s">
+      <c r="H184" s="35" t="s">
         <v>1256</v>
       </c>
-      <c r="I184" s="36" t="s">
+      <c r="I184" s="35" t="s">
         <v>1257</v>
       </c>
-      <c r="J184" s="36" t="s">
+      <c r="J184" s="35" t="s">
         <v>1258</v>
       </c>
-      <c r="K184" s="38" t="s">
+      <c r="K184" s="37" t="s">
         <v>1259</v>
       </c>
-      <c r="L184" s="36" t="s">
+      <c r="L184" s="35" t="s">
         <v>1260</v>
       </c>
       <c r="M184" s="5">
@@ -17843,10 +17895,10 @@
       <c r="T184" s="11">
         <v>99.99</v>
       </c>
-      <c r="U184" s="38" t="s">
+      <c r="U184" s="37" t="s">
         <v>1261</v>
       </c>
-      <c r="V184" s="38" t="s">
+      <c r="V184" s="37" t="s">
         <v>1261</v>
       </c>
       <c r="Y184" s="11"/>
@@ -17868,22 +17920,22 @@
       <c r="F185" s="5" t="s">
         <v>1262</v>
       </c>
-      <c r="G185" s="36" t="s">
+      <c r="G185" s="35" t="s">
         <v>1263</v>
       </c>
-      <c r="H185" s="36" t="s">
+      <c r="H185" s="35" t="s">
         <v>1264</v>
       </c>
-      <c r="I185" s="36" t="s">
+      <c r="I185" s="35" t="s">
         <v>1265</v>
       </c>
-      <c r="J185" s="36" t="s">
+      <c r="J185" s="35" t="s">
         <v>1266</v>
       </c>
-      <c r="K185" s="38" t="s">
+      <c r="K185" s="37" t="s">
         <v>1267</v>
       </c>
-      <c r="L185" s="36" t="s">
+      <c r="L185" s="35" t="s">
         <v>1268</v>
       </c>
       <c r="M185" s="5">
@@ -17917,10 +17969,10 @@
       <c r="T185" s="11">
         <v>99.99</v>
       </c>
-      <c r="U185" s="38" t="s">
+      <c r="U185" s="37" t="s">
         <v>1269</v>
       </c>
-      <c r="V185" s="38" t="s">
+      <c r="V185" s="37" t="s">
         <v>1269</v>
       </c>
       <c r="Y185" s="11"/>
@@ -17942,22 +17994,22 @@
       <c r="F186" s="6" t="s">
         <v>1270</v>
       </c>
-      <c r="G186" s="36" t="s">
+      <c r="G186" s="35" t="s">
         <v>1271</v>
       </c>
-      <c r="H186" s="34" t="s">
+      <c r="H186" s="33" t="s">
         <v>1272</v>
       </c>
-      <c r="I186" s="34" t="s">
+      <c r="I186" s="33" t="s">
         <v>1273</v>
       </c>
-      <c r="J186" s="34" t="s">
+      <c r="J186" s="33" t="s">
         <v>1274</v>
       </c>
-      <c r="K186" s="38" t="s">
+      <c r="K186" s="37" t="s">
         <v>1275</v>
       </c>
-      <c r="L186" s="34" t="s">
+      <c r="L186" s="33" t="s">
         <v>1276</v>
       </c>
       <c r="M186" s="6">
@@ -17991,10 +18043,10 @@
       <c r="T186" s="7">
         <v>99.99</v>
       </c>
-      <c r="U186" s="39" t="s">
+      <c r="U186" s="38" t="s">
         <v>1277</v>
       </c>
-      <c r="V186" s="39" t="s">
+      <c r="V186" s="38" t="s">
         <v>1277</v>
       </c>
       <c r="W186" s="7"/>
@@ -18018,22 +18070,22 @@
       <c r="F187" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="G187" s="36" t="s">
+      <c r="G187" s="35" t="s">
         <v>1279</v>
       </c>
-      <c r="H187" s="34" t="s">
+      <c r="H187" s="33" t="s">
         <v>1280</v>
       </c>
-      <c r="I187" s="34" t="s">
+      <c r="I187" s="33" t="s">
         <v>1281</v>
       </c>
-      <c r="J187" s="34" t="s">
+      <c r="J187" s="33" t="s">
         <v>1282</v>
       </c>
-      <c r="K187" s="38" t="s">
+      <c r="K187" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L187" s="34" t="s">
+      <c r="L187" s="33" t="s">
         <v>1284</v>
       </c>
       <c r="M187" s="4">
@@ -18067,10 +18119,10 @@
       <c r="T187" s="8">
         <v>99.99</v>
       </c>
-      <c r="U187" s="35" t="s">
+      <c r="U187" s="34" t="s">
         <v>1285</v>
       </c>
-      <c r="V187" s="35" t="s">
+      <c r="V187" s="34" t="s">
         <v>1285</v>
       </c>
       <c r="W187" s="8"/>
@@ -18094,22 +18146,22 @@
       <c r="F188" s="4" t="s">
         <v>1286</v>
       </c>
-      <c r="G188" s="36" t="s">
+      <c r="G188" s="35" t="s">
         <v>1232</v>
       </c>
-      <c r="H188" s="34" t="s">
+      <c r="H188" s="33" t="s">
         <v>1287</v>
       </c>
-      <c r="I188" s="34" t="s">
+      <c r="I188" s="33" t="s">
         <v>1288</v>
       </c>
-      <c r="J188" s="34" t="s">
+      <c r="J188" s="33" t="s">
         <v>1289</v>
       </c>
-      <c r="K188" s="38" t="s">
+      <c r="K188" s="37" t="s">
         <v>1290</v>
       </c>
-      <c r="L188" s="34" t="s">
+      <c r="L188" s="33" t="s">
         <v>1255</v>
       </c>
       <c r="M188" s="4">
@@ -18143,10 +18195,10 @@
       <c r="T188" s="8">
         <v>99.99</v>
       </c>
-      <c r="U188" s="35" t="s">
+      <c r="U188" s="34" t="s">
         <v>1291</v>
       </c>
-      <c r="V188" s="35" t="s">
+      <c r="V188" s="34" t="s">
         <v>1291</v>
       </c>
       <c r="W188" s="8"/>
@@ -18170,22 +18222,22 @@
       <c r="F189" s="4" t="s">
         <v>1292</v>
       </c>
-      <c r="G189" s="36" t="s">
+      <c r="G189" s="35" t="s">
         <v>1293</v>
       </c>
-      <c r="H189" s="34" t="s">
+      <c r="H189" s="33" t="s">
         <v>1294</v>
       </c>
-      <c r="I189" s="34" t="s">
+      <c r="I189" s="33" t="s">
         <v>1295</v>
       </c>
-      <c r="J189" s="34" t="s">
+      <c r="J189" s="33" t="s">
         <v>1296</v>
       </c>
-      <c r="K189" s="38" t="s">
+      <c r="K189" s="37" t="s">
         <v>1297</v>
       </c>
-      <c r="L189" s="34" t="s">
+      <c r="L189" s="33" t="s">
         <v>1298</v>
       </c>
       <c r="M189" s="4">
@@ -18219,10 +18271,10 @@
       <c r="T189" s="8">
         <v>99.99</v>
       </c>
-      <c r="U189" s="35" t="s">
+      <c r="U189" s="34" t="s">
         <v>1299</v>
       </c>
-      <c r="V189" s="35" t="s">
+      <c r="V189" s="34" t="s">
         <v>1299</v>
       </c>
       <c r="W189" s="8"/>
@@ -18246,22 +18298,22 @@
       <c r="F190" s="4" t="s">
         <v>1300</v>
       </c>
-      <c r="G190" s="36" t="s">
+      <c r="G190" s="35" t="s">
         <v>1301</v>
       </c>
-      <c r="H190" s="34" t="s">
+      <c r="H190" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I190" s="34" t="s">
+      <c r="I190" s="33" t="s">
         <v>1303</v>
       </c>
-      <c r="J190" s="34" t="s">
+      <c r="J190" s="33" t="s">
         <v>1304</v>
       </c>
-      <c r="K190" s="38" t="s">
+      <c r="K190" s="37" t="s">
         <v>1305</v>
       </c>
-      <c r="L190" s="34" t="s">
+      <c r="L190" s="33" t="s">
         <v>1306</v>
       </c>
       <c r="M190" s="4">
@@ -18295,10 +18347,10 @@
       <c r="T190" s="8">
         <v>99.99</v>
       </c>
-      <c r="U190" s="35" t="s">
+      <c r="U190" s="34" t="s">
         <v>1307</v>
       </c>
-      <c r="V190" s="35" t="s">
+      <c r="V190" s="34" t="s">
         <v>1307</v>
       </c>
       <c r="W190" s="8"/>
@@ -18322,22 +18374,22 @@
       <c r="F191" s="6" t="s">
         <v>1308</v>
       </c>
-      <c r="G191" s="36" t="s">
+      <c r="G191" s="35" t="s">
         <v>1248</v>
       </c>
-      <c r="H191" s="34" t="s">
+      <c r="H191" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I191" s="34" t="s">
+      <c r="I191" s="33" t="s">
         <v>1309</v>
       </c>
-      <c r="J191" s="34" t="s">
+      <c r="J191" s="33" t="s">
         <v>1183</v>
       </c>
-      <c r="K191" s="38" t="s">
+      <c r="K191" s="37" t="s">
         <v>1310</v>
       </c>
-      <c r="L191" s="34" t="s">
+      <c r="L191" s="33" t="s">
         <v>1311</v>
       </c>
       <c r="M191" s="6">
@@ -18371,10 +18423,10 @@
       <c r="T191" s="7">
         <v>99.99</v>
       </c>
-      <c r="U191" s="39" t="s">
+      <c r="U191" s="38" t="s">
         <v>1312</v>
       </c>
-      <c r="V191" s="39" t="s">
+      <c r="V191" s="38" t="s">
         <v>1312</v>
       </c>
       <c r="W191" s="7"/>
@@ -18398,22 +18450,22 @@
       <c r="F192" s="4" t="s">
         <v>1313</v>
       </c>
-      <c r="G192" s="36" t="s">
+      <c r="G192" s="35" t="s">
         <v>1314</v>
       </c>
-      <c r="H192" s="34" t="s">
+      <c r="H192" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I192" s="34" t="s">
+      <c r="I192" s="33" t="s">
         <v>1315</v>
       </c>
-      <c r="J192" s="34" t="s">
+      <c r="J192" s="33" t="s">
         <v>1316</v>
       </c>
-      <c r="K192" s="38" t="s">
+      <c r="K192" s="37" t="s">
         <v>1317</v>
       </c>
-      <c r="L192" s="34" t="s">
+      <c r="L192" s="33" t="s">
         <v>1279</v>
       </c>
       <c r="M192" s="4">
@@ -18447,10 +18499,10 @@
       <c r="T192" s="8">
         <v>99.99</v>
       </c>
-      <c r="U192" s="35" t="s">
+      <c r="U192" s="34" t="s">
         <v>1318</v>
       </c>
-      <c r="V192" s="35" t="s">
+      <c r="V192" s="34" t="s">
         <v>1318</v>
       </c>
       <c r="W192" s="8"/>
@@ -18474,22 +18526,22 @@
       <c r="F193" s="4" t="s">
         <v>1319</v>
       </c>
-      <c r="G193" s="36" t="s">
+      <c r="G193" s="35" t="s">
         <v>1256</v>
       </c>
-      <c r="H193" s="34" t="s">
+      <c r="H193" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I193" s="34" t="s">
+      <c r="I193" s="33" t="s">
         <v>1320</v>
       </c>
-      <c r="J193" s="34" t="s">
+      <c r="J193" s="33" t="s">
         <v>1321</v>
       </c>
-      <c r="K193" s="38" t="s">
+      <c r="K193" s="37" t="s">
         <v>1322</v>
       </c>
-      <c r="L193" s="34" t="s">
+      <c r="L193" s="33" t="s">
         <v>1323</v>
       </c>
       <c r="M193" s="4">
@@ -18523,10 +18575,10 @@
       <c r="T193" s="8">
         <v>99.99</v>
       </c>
-      <c r="U193" s="35" t="s">
+      <c r="U193" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="V193" s="35" t="s">
+      <c r="V193" s="34" t="s">
         <v>432</v>
       </c>
       <c r="W193" s="8"/>
@@ -18550,22 +18602,22 @@
       <c r="F194" s="4" t="s">
         <v>1324</v>
       </c>
-      <c r="G194" s="36" t="s">
+      <c r="G194" s="35" t="s">
         <v>1154</v>
       </c>
-      <c r="H194" s="34" t="s">
+      <c r="H194" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I194" s="34" t="s">
+      <c r="I194" s="33" t="s">
         <v>1325</v>
       </c>
-      <c r="J194" s="34" t="s">
+      <c r="J194" s="33" t="s">
         <v>1326</v>
       </c>
-      <c r="K194" s="38" t="s">
+      <c r="K194" s="37" t="s">
         <v>1327</v>
       </c>
-      <c r="L194" s="34" t="s">
+      <c r="L194" s="33" t="s">
         <v>1328</v>
       </c>
       <c r="M194" s="4">
@@ -18599,10 +18651,10 @@
       <c r="T194" s="8">
         <v>99.99</v>
       </c>
-      <c r="U194" s="35" t="s">
+      <c r="U194" s="34" t="s">
         <v>1329</v>
       </c>
-      <c r="V194" s="35" t="s">
+      <c r="V194" s="34" t="s">
         <v>1329</v>
       </c>
       <c r="W194" s="8"/>
@@ -18626,22 +18678,22 @@
       <c r="F195" s="4" t="s">
         <v>1330</v>
       </c>
-      <c r="G195" s="36" t="s">
+      <c r="G195" s="35" t="s">
         <v>1264</v>
       </c>
-      <c r="H195" s="34" t="s">
+      <c r="H195" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I195" s="34" t="s">
+      <c r="I195" s="33" t="s">
         <v>1331</v>
       </c>
-      <c r="J195" s="34" t="s">
+      <c r="J195" s="33" t="s">
         <v>1332</v>
       </c>
-      <c r="K195" s="38" t="s">
+      <c r="K195" s="37" t="s">
         <v>1333</v>
       </c>
-      <c r="L195" s="34" t="s">
+      <c r="L195" s="33" t="s">
         <v>1293</v>
       </c>
       <c r="M195" s="4">
@@ -18675,10 +18727,10 @@
       <c r="T195" s="8">
         <v>99.99</v>
       </c>
-      <c r="U195" s="35" t="s">
+      <c r="U195" s="34" t="s">
         <v>1334</v>
       </c>
-      <c r="V195" s="35" t="s">
+      <c r="V195" s="34" t="s">
         <v>1334</v>
       </c>
       <c r="W195" s="8"/>
@@ -18702,22 +18754,22 @@
       <c r="F196" s="6" t="s">
         <v>1335</v>
       </c>
-      <c r="G196" s="36" t="s">
+      <c r="G196" s="35" t="s">
         <v>1336</v>
       </c>
-      <c r="H196" s="34" t="s">
+      <c r="H196" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I196" s="34" t="s">
+      <c r="I196" s="33" t="s">
         <v>1337</v>
       </c>
-      <c r="J196" s="34" t="s">
+      <c r="J196" s="33" t="s">
         <v>1338</v>
       </c>
-      <c r="K196" s="38" t="s">
+      <c r="K196" s="37" t="s">
         <v>1339</v>
       </c>
-      <c r="L196" s="34" t="s">
+      <c r="L196" s="33" t="s">
         <v>1301</v>
       </c>
       <c r="M196" s="6">
@@ -18751,10 +18803,10 @@
       <c r="T196" s="7">
         <v>99.99</v>
       </c>
-      <c r="U196" s="39" t="s">
+      <c r="U196" s="38" t="s">
         <v>1340</v>
       </c>
-      <c r="V196" s="39" t="s">
+      <c r="V196" s="38" t="s">
         <v>1340</v>
       </c>
       <c r="W196" s="7"/>
@@ -18778,22 +18830,22 @@
       <c r="F197" s="4" t="s">
         <v>1341</v>
       </c>
-      <c r="G197" s="36" t="s">
+      <c r="G197" s="35" t="s">
         <v>1342</v>
       </c>
-      <c r="H197" s="34" t="s">
+      <c r="H197" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I197" s="34" t="s">
+      <c r="I197" s="33" t="s">
         <v>1343</v>
       </c>
-      <c r="J197" s="34" t="s">
+      <c r="J197" s="33" t="s">
         <v>1344</v>
       </c>
-      <c r="K197" s="38" t="s">
+      <c r="K197" s="37" t="s">
         <v>1345</v>
       </c>
-      <c r="L197" s="34" t="s">
+      <c r="L197" s="33" t="s">
         <v>1248</v>
       </c>
       <c r="M197" s="4">
@@ -18827,10 +18879,10 @@
       <c r="T197" s="8">
         <v>99.99</v>
       </c>
-      <c r="U197" s="35" t="s">
+      <c r="U197" s="34" t="s">
         <v>1346</v>
       </c>
-      <c r="V197" s="35" t="s">
+      <c r="V197" s="34" t="s">
         <v>1346</v>
       </c>
       <c r="W197" s="8"/>
@@ -18854,22 +18906,22 @@
       <c r="F198" s="4" t="s">
         <v>1347</v>
       </c>
-      <c r="G198" s="36" t="s">
+      <c r="G198" s="35" t="s">
         <v>1280</v>
       </c>
-      <c r="H198" s="34" t="s">
+      <c r="H198" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I198" s="34" t="s">
+      <c r="I198" s="33" t="s">
         <v>1348</v>
       </c>
-      <c r="J198" s="34" t="s">
+      <c r="J198" s="33" t="s">
         <v>1349</v>
       </c>
-      <c r="K198" s="38" t="s">
+      <c r="K198" s="37" t="s">
         <v>1350</v>
       </c>
-      <c r="L198" s="34" t="s">
+      <c r="L198" s="33" t="s">
         <v>1314</v>
       </c>
       <c r="M198" s="4">
@@ -18903,10 +18955,10 @@
       <c r="T198" s="8">
         <v>99.99</v>
       </c>
-      <c r="U198" s="35" t="s">
+      <c r="U198" s="34" t="s">
         <v>1351</v>
       </c>
-      <c r="V198" s="35" t="s">
+      <c r="V198" s="34" t="s">
         <v>1351</v>
       </c>
       <c r="W198" s="8"/>
@@ -18930,22 +18982,22 @@
       <c r="F199" s="4" t="s">
         <v>1352</v>
       </c>
-      <c r="G199" s="36" t="s">
+      <c r="G199" s="35" t="s">
         <v>1353</v>
       </c>
-      <c r="H199" s="34" t="s">
+      <c r="H199" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I199" s="34" t="s">
+      <c r="I199" s="33" t="s">
         <v>1354</v>
       </c>
-      <c r="J199" s="34" t="s">
+      <c r="J199" s="33" t="s">
         <v>1355</v>
       </c>
-      <c r="K199" s="38" t="s">
+      <c r="K199" s="37" t="s">
         <v>1356</v>
       </c>
-      <c r="L199" s="34" t="s">
+      <c r="L199" s="33" t="s">
         <v>1256</v>
       </c>
       <c r="M199" s="4">
@@ -18979,10 +19031,10 @@
       <c r="T199" s="8">
         <v>99.99</v>
       </c>
-      <c r="U199" s="35" t="s">
+      <c r="U199" s="34" t="s">
         <v>1357</v>
       </c>
-      <c r="V199" s="35" t="s">
+      <c r="V199" s="34" t="s">
         <v>1357</v>
       </c>
       <c r="W199" s="8"/>
@@ -19006,22 +19058,22 @@
       <c r="F200" s="4" t="s">
         <v>1358</v>
       </c>
-      <c r="G200" s="36" t="s">
+      <c r="G200" s="35" t="s">
         <v>1359</v>
       </c>
-      <c r="H200" s="34" t="s">
+      <c r="H200" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I200" s="34" t="s">
+      <c r="I200" s="33" t="s">
         <v>1360</v>
       </c>
-      <c r="J200" s="34" t="s">
+      <c r="J200" s="33" t="s">
         <v>1236</v>
       </c>
-      <c r="K200" s="38" t="s">
+      <c r="K200" s="37" t="s">
         <v>1361</v>
       </c>
-      <c r="L200" s="34" t="s">
+      <c r="L200" s="33" t="s">
         <v>1154</v>
       </c>
       <c r="M200" s="4">
@@ -19055,10 +19107,10 @@
       <c r="T200" s="8">
         <v>99.99</v>
       </c>
-      <c r="U200" s="35" t="s">
+      <c r="U200" s="34" t="s">
         <v>1362</v>
       </c>
-      <c r="V200" s="35" t="s">
+      <c r="V200" s="34" t="s">
         <v>1362</v>
       </c>
       <c r="W200" s="8"/>
@@ -19080,22 +19132,22 @@
       <c r="F201" s="6" t="s">
         <v>1363</v>
       </c>
-      <c r="G201" s="34" t="s">
+      <c r="G201" s="33" t="s">
         <v>1364</v>
       </c>
-      <c r="H201" s="34" t="s">
+      <c r="H201" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I201" s="34" t="s">
+      <c r="I201" s="33" t="s">
         <v>1365</v>
       </c>
-      <c r="J201" s="34" t="s">
+      <c r="J201" s="33" t="s">
         <v>1366</v>
       </c>
-      <c r="K201" s="38" t="s">
+      <c r="K201" s="37" t="s">
         <v>1242</v>
       </c>
-      <c r="L201" s="34" t="s">
+      <c r="L201" s="33" t="s">
         <v>1264</v>
       </c>
       <c r="M201" s="6">
@@ -19129,10 +19181,10 @@
       <c r="T201" s="7">
         <v>99.99</v>
       </c>
-      <c r="U201" s="39" t="s">
+      <c r="U201" s="38" t="s">
         <v>1367</v>
       </c>
-      <c r="V201" s="39" t="s">
+      <c r="V201" s="38" t="s">
         <v>1367</v>
       </c>
       <c r="W201" s="6"/>
@@ -19151,22 +19203,22 @@
       <c r="F202" s="4" t="s">
         <v>1368</v>
       </c>
-      <c r="G202" s="34" t="s">
+      <c r="G202" s="33" t="s">
         <v>1369</v>
       </c>
-      <c r="H202" s="34" t="s">
+      <c r="H202" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I202" s="34" t="s">
+      <c r="I202" s="33" t="s">
         <v>1370</v>
       </c>
-      <c r="J202" s="34" t="s">
+      <c r="J202" s="33" t="s">
         <v>1371</v>
       </c>
-      <c r="K202" s="38" t="s">
+      <c r="K202" s="37" t="s">
         <v>1372</v>
       </c>
-      <c r="L202" s="34" t="s">
+      <c r="L202" s="33" t="s">
         <v>1336</v>
       </c>
       <c r="M202" s="4">
@@ -19200,10 +19252,10 @@
       <c r="T202" s="8">
         <v>99.99</v>
       </c>
-      <c r="U202" s="35" t="s">
+      <c r="U202" s="34" t="s">
         <v>1373</v>
       </c>
-      <c r="V202" s="35" t="s">
+      <c r="V202" s="34" t="s">
         <v>1373</v>
       </c>
       <c r="W202" s="4"/>
@@ -19222,22 +19274,22 @@
       <c r="F203" s="4" t="s">
         <v>1374</v>
       </c>
-      <c r="G203" s="34" t="s">
+      <c r="G203" s="33" t="s">
         <v>1375</v>
       </c>
-      <c r="H203" s="34" t="s">
+      <c r="H203" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I203" s="34" t="s">
+      <c r="I203" s="33" t="s">
         <v>1376</v>
       </c>
-      <c r="J203" s="34" t="s">
+      <c r="J203" s="33" t="s">
         <v>1377</v>
       </c>
-      <c r="K203" s="38" t="s">
+      <c r="K203" s="37" t="s">
         <v>1266</v>
       </c>
-      <c r="L203" s="34" t="s">
+      <c r="L203" s="33" t="s">
         <v>1342</v>
       </c>
       <c r="M203" s="4">
@@ -19271,10 +19323,10 @@
       <c r="T203" s="8">
         <v>99.99</v>
       </c>
-      <c r="U203" s="35" t="s">
+      <c r="U203" s="34" t="s">
         <v>1378</v>
       </c>
-      <c r="V203" s="35" t="s">
+      <c r="V203" s="34" t="s">
         <v>1378</v>
       </c>
       <c r="W203" s="4"/>
@@ -19293,22 +19345,22 @@
       <c r="F204" s="4" t="s">
         <v>1379</v>
       </c>
-      <c r="G204" s="34" t="s">
+      <c r="G204" s="33" t="s">
         <v>1380</v>
       </c>
-      <c r="H204" s="34" t="s">
+      <c r="H204" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I204" s="34" t="s">
+      <c r="I204" s="33" t="s">
         <v>1381</v>
       </c>
-      <c r="J204" s="34" t="s">
+      <c r="J204" s="33" t="s">
         <v>1244</v>
       </c>
-      <c r="K204" s="38" t="s">
+      <c r="K204" s="37" t="s">
         <v>1382</v>
       </c>
-      <c r="L204" s="34" t="s">
+      <c r="L204" s="33" t="s">
         <v>1280</v>
       </c>
       <c r="M204" s="4">
@@ -19342,10 +19394,10 @@
       <c r="T204" s="8">
         <v>99.99</v>
       </c>
-      <c r="U204" s="35" t="s">
+      <c r="U204" s="34" t="s">
         <v>1383</v>
       </c>
-      <c r="V204" s="35" t="s">
+      <c r="V204" s="34" t="s">
         <v>1383</v>
       </c>
       <c r="W204" s="4"/>
@@ -19364,22 +19416,22 @@
       <c r="F205" s="4" t="s">
         <v>1384</v>
       </c>
-      <c r="G205" s="34" t="s">
+      <c r="G205" s="33" t="s">
         <v>1385</v>
       </c>
-      <c r="H205" s="34" t="s">
+      <c r="H205" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I205" s="34" t="s">
+      <c r="I205" s="33" t="s">
         <v>1386</v>
       </c>
-      <c r="J205" s="34" t="s">
+      <c r="J205" s="33" t="s">
         <v>1387</v>
       </c>
-      <c r="K205" s="38" t="s">
+      <c r="K205" s="37" t="s">
         <v>1289</v>
       </c>
-      <c r="L205" s="34" t="s">
+      <c r="L205" s="33" t="s">
         <v>1353</v>
       </c>
       <c r="M205" s="4">
@@ -19413,10 +19465,10 @@
       <c r="T205" s="8">
         <v>99.99</v>
       </c>
-      <c r="U205" s="35" t="s">
+      <c r="U205" s="34" t="s">
         <v>1388</v>
       </c>
-      <c r="V205" s="35" t="s">
+      <c r="V205" s="34" t="s">
         <v>1388</v>
       </c>
       <c r="W205" s="4"/>
@@ -19435,22 +19487,22 @@
       <c r="F206" s="6" t="s">
         <v>1389</v>
       </c>
-      <c r="G206" s="34" t="s">
+      <c r="G206" s="33" t="s">
         <v>1249</v>
       </c>
-      <c r="H206" s="34" t="s">
+      <c r="H206" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I206" s="34" t="s">
+      <c r="I206" s="33" t="s">
         <v>1390</v>
       </c>
-      <c r="J206" s="34" t="s">
+      <c r="J206" s="33" t="s">
         <v>1391</v>
       </c>
-      <c r="K206" s="38" t="s">
+      <c r="K206" s="37" t="s">
         <v>1392</v>
       </c>
-      <c r="L206" s="34" t="s">
+      <c r="L206" s="33" t="s">
         <v>1359</v>
       </c>
       <c r="M206" s="6">
@@ -19484,10 +19536,10 @@
       <c r="T206" s="7">
         <v>99.99</v>
       </c>
-      <c r="U206" s="39" t="s">
+      <c r="U206" s="38" t="s">
         <v>1393</v>
       </c>
-      <c r="V206" s="39" t="s">
+      <c r="V206" s="38" t="s">
         <v>1393</v>
       </c>
       <c r="W206" s="6"/>
@@ -19506,22 +19558,22 @@
       <c r="F207" s="4" t="s">
         <v>1394</v>
       </c>
-      <c r="G207" s="34" t="s">
+      <c r="G207" s="33" t="s">
         <v>1395</v>
       </c>
-      <c r="H207" s="34" t="s">
+      <c r="H207" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I207" s="34" t="s">
+      <c r="I207" s="33" t="s">
         <v>1396</v>
       </c>
-      <c r="J207" s="34" t="s">
+      <c r="J207" s="33" t="s">
         <v>1397</v>
       </c>
-      <c r="K207" s="38" t="s">
+      <c r="K207" s="37" t="s">
         <v>1183</v>
       </c>
-      <c r="L207" s="34" t="s">
+      <c r="L207" s="33" t="s">
         <v>1294</v>
       </c>
       <c r="M207" s="4">
@@ -19555,10 +19607,10 @@
       <c r="T207" s="8">
         <v>99.99</v>
       </c>
-      <c r="U207" s="35" t="s">
+      <c r="U207" s="34" t="s">
         <v>1398</v>
       </c>
-      <c r="V207" s="35" t="s">
+      <c r="V207" s="34" t="s">
         <v>1398</v>
       </c>
       <c r="W207" s="4"/>
@@ -19577,22 +19629,22 @@
       <c r="F208" s="4" t="s">
         <v>1399</v>
       </c>
-      <c r="G208" s="34" t="s">
+      <c r="G208" s="33" t="s">
         <v>1257</v>
       </c>
-      <c r="H208" s="34" t="s">
+      <c r="H208" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I208" s="34" t="s">
+      <c r="I208" s="33" t="s">
         <v>1400</v>
       </c>
-      <c r="J208" s="34" t="s">
+      <c r="J208" s="33" t="s">
         <v>1252</v>
       </c>
-      <c r="K208" s="38" t="s">
+      <c r="K208" s="37" t="s">
         <v>1401</v>
       </c>
-      <c r="L208" s="34" t="s">
+      <c r="L208" s="33" t="s">
         <v>1233</v>
       </c>
       <c r="M208" s="4">
@@ -19626,10 +19678,10 @@
       <c r="T208" s="8">
         <v>99.99</v>
       </c>
-      <c r="U208" s="35" t="s">
+      <c r="U208" s="34" t="s">
         <v>1402</v>
       </c>
-      <c r="V208" s="35" t="s">
+      <c r="V208" s="34" t="s">
         <v>1402</v>
       </c>
       <c r="W208" s="4"/>
@@ -19648,22 +19700,22 @@
       <c r="F209" s="4" t="s">
         <v>1403</v>
       </c>
-      <c r="G209" s="34" t="s">
+      <c r="G209" s="33" t="s">
         <v>1404</v>
       </c>
-      <c r="H209" s="34" t="s">
+      <c r="H209" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I209" s="34" t="s">
+      <c r="I209" s="33" t="s">
         <v>1405</v>
       </c>
-      <c r="J209" s="34" t="s">
+      <c r="J209" s="33" t="s">
         <v>1406</v>
       </c>
-      <c r="K209" s="38" t="s">
+      <c r="K209" s="37" t="s">
         <v>1326</v>
       </c>
-      <c r="L209" s="34" t="s">
+      <c r="L209" s="33" t="s">
         <v>1407</v>
       </c>
       <c r="M209" s="4">
@@ -19697,10 +19749,10 @@
       <c r="T209" s="8">
         <v>99.99</v>
       </c>
-      <c r="U209" s="35" t="s">
+      <c r="U209" s="34" t="s">
         <v>1408</v>
       </c>
-      <c r="V209" s="35" t="s">
+      <c r="V209" s="34" t="s">
         <v>1408</v>
       </c>
       <c r="W209" s="4"/>
@@ -19719,22 +19771,22 @@
       <c r="F210" s="4" t="s">
         <v>1409</v>
       </c>
-      <c r="G210" s="34" t="s">
+      <c r="G210" s="33" t="s">
         <v>1410</v>
       </c>
-      <c r="H210" s="34" t="s">
+      <c r="H210" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I210" s="34" t="s">
+      <c r="I210" s="33" t="s">
         <v>1411</v>
       </c>
-      <c r="J210" s="34" t="s">
+      <c r="J210" s="33" t="s">
         <v>1412</v>
       </c>
-      <c r="K210" s="38" t="s">
+      <c r="K210" s="37" t="s">
         <v>1338</v>
       </c>
-      <c r="L210" s="34" t="s">
+      <c r="L210" s="33" t="s">
         <v>1241</v>
       </c>
       <c r="M210" s="4">
@@ -19768,10 +19820,10 @@
       <c r="T210" s="8">
         <v>99.99</v>
       </c>
-      <c r="U210" s="35" t="s">
+      <c r="U210" s="34" t="s">
         <v>1413</v>
       </c>
-      <c r="V210" s="35" t="s">
+      <c r="V210" s="34" t="s">
         <v>1413</v>
       </c>
       <c r="W210" s="4"/>
@@ -19792,22 +19844,22 @@
       <c r="F211" s="4" t="s">
         <v>1414</v>
       </c>
-      <c r="G211" s="34" t="s">
+      <c r="G211" s="33" t="s">
         <v>1273</v>
       </c>
-      <c r="H211" s="34" t="s">
+      <c r="H211" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I211" s="34" t="s">
+      <c r="I211" s="33" t="s">
         <v>1415</v>
       </c>
-      <c r="J211" s="34" t="s">
+      <c r="J211" s="33" t="s">
         <v>1416</v>
       </c>
-      <c r="K211" s="38" t="s">
+      <c r="K211" s="37" t="s">
         <v>1355</v>
       </c>
-      <c r="L211" s="34" t="s">
+      <c r="L211" s="33" t="s">
         <v>1417</v>
       </c>
       <c r="M211" s="4">
@@ -19831,7 +19883,7 @@
         <v>173</v>
       </c>
       <c r="R211" s="8">
-        <f t="shared" ref="R211:R220" si="84">R210+20</f>
+        <f t="shared" ref="R211:R225" si="84">R210+20</f>
         <v>599</v>
       </c>
       <c r="S211" s="8">
@@ -19841,10 +19893,10 @@
       <c r="T211" s="8">
         <v>99.99</v>
       </c>
-      <c r="U211" s="35" t="s">
+      <c r="U211" s="34" t="s">
         <v>1418</v>
       </c>
-      <c r="V211" s="35" t="s">
+      <c r="V211" s="34" t="s">
         <v>1418</v>
       </c>
       <c r="W211" s="8"/>
@@ -19868,22 +19920,22 @@
       <c r="F212" s="4" t="s">
         <v>1419</v>
       </c>
-      <c r="G212" s="34" t="s">
+      <c r="G212" s="33" t="s">
         <v>1420</v>
       </c>
-      <c r="H212" s="34" t="s">
+      <c r="H212" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I212" s="34" t="s">
+      <c r="I212" s="33" t="s">
         <v>1421</v>
       </c>
-      <c r="J212" s="34" t="s">
+      <c r="J212" s="33" t="s">
         <v>1260</v>
       </c>
-      <c r="K212" s="38" t="s">
+      <c r="K212" s="37" t="s">
         <v>1371</v>
       </c>
-      <c r="L212" s="34" t="s">
+      <c r="L212" s="33" t="s">
         <v>1249</v>
       </c>
       <c r="M212" s="4">
@@ -19917,10 +19969,10 @@
       <c r="T212" s="8">
         <v>99.99</v>
       </c>
-      <c r="U212" s="35" t="s">
+      <c r="U212" s="34" t="s">
         <v>1422</v>
       </c>
-      <c r="V212" s="35" t="s">
+      <c r="V212" s="34" t="s">
         <v>1422</v>
       </c>
       <c r="W212" s="8"/>
@@ -19944,22 +19996,22 @@
       <c r="F213" s="4" t="s">
         <v>1423</v>
       </c>
-      <c r="G213" s="34" t="s">
+      <c r="G213" s="33" t="s">
         <v>1424</v>
       </c>
-      <c r="H213" s="34" t="s">
+      <c r="H213" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I213" s="34" t="s">
+      <c r="I213" s="33" t="s">
         <v>1425</v>
       </c>
-      <c r="J213" s="34" t="s">
+      <c r="J213" s="33" t="s">
         <v>1231</v>
       </c>
-      <c r="K213" s="38" t="s">
+      <c r="K213" s="37" t="s">
         <v>1387</v>
       </c>
-      <c r="L213" s="34" t="s">
+      <c r="L213" s="33" t="s">
         <v>1395</v>
       </c>
       <c r="M213" s="4">
@@ -19993,10 +20045,10 @@
       <c r="T213" s="8">
         <v>99.99</v>
       </c>
-      <c r="U213" s="35" t="s">
+      <c r="U213" s="34" t="s">
         <v>1426</v>
       </c>
-      <c r="V213" s="35" t="s">
+      <c r="V213" s="34" t="s">
         <v>1426</v>
       </c>
       <c r="W213" s="8"/>
@@ -20020,22 +20072,22 @@
       <c r="F214" s="4" t="s">
         <v>1427</v>
       </c>
-      <c r="G214" s="34" t="s">
+      <c r="G214" s="33" t="s">
         <v>1288</v>
       </c>
-      <c r="H214" s="34" t="s">
+      <c r="H214" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I214" s="34" t="s">
+      <c r="I214" s="33" t="s">
         <v>1428</v>
       </c>
-      <c r="J214" s="34" t="s">
+      <c r="J214" s="33" t="s">
         <v>1429</v>
       </c>
-      <c r="K214" s="38" t="s">
+      <c r="K214" s="37" t="s">
         <v>1252</v>
       </c>
-      <c r="L214" s="34" t="s">
+      <c r="L214" s="33" t="s">
         <v>1257</v>
       </c>
       <c r="M214" s="4">
@@ -20069,10 +20121,10 @@
       <c r="T214" s="8">
         <v>99.99</v>
       </c>
-      <c r="U214" s="35" t="s">
+      <c r="U214" s="34" t="s">
         <v>1430</v>
       </c>
-      <c r="V214" s="35" t="s">
+      <c r="V214" s="34" t="s">
         <v>1430</v>
       </c>
       <c r="W214" s="8"/>
@@ -20096,22 +20148,22 @@
       <c r="F215" s="4" t="s">
         <v>1431</v>
       </c>
-      <c r="G215" s="34" t="s">
+      <c r="G215" s="33" t="s">
         <v>1432</v>
       </c>
-      <c r="H215" s="34" t="s">
+      <c r="H215" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I215" s="34" t="s">
+      <c r="I215" s="33" t="s">
         <v>1433</v>
       </c>
-      <c r="J215" s="34" t="s">
+      <c r="J215" s="33" t="s">
         <v>1434</v>
       </c>
-      <c r="K215" s="38" t="s">
+      <c r="K215" s="37" t="s">
         <v>1416</v>
       </c>
-      <c r="L215" s="34" t="s">
+      <c r="L215" s="33" t="s">
         <v>1404</v>
       </c>
       <c r="M215" s="4">
@@ -20145,10 +20197,10 @@
       <c r="T215" s="8">
         <v>99.99</v>
       </c>
-      <c r="U215" s="35" t="s">
+      <c r="U215" s="34" t="s">
         <v>1435</v>
       </c>
-      <c r="V215" s="35" t="s">
+      <c r="V215" s="34" t="s">
         <v>1435</v>
       </c>
       <c r="W215" s="8"/>
@@ -20172,22 +20224,22 @@
       <c r="F216" s="2" t="s">
         <v>1436</v>
       </c>
-      <c r="G216" s="37" t="s">
+      <c r="G216" s="36" t="s">
         <v>1437</v>
       </c>
-      <c r="H216" s="34" t="s">
+      <c r="H216" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I216" s="37" t="s">
+      <c r="I216" s="36" t="s">
         <v>1438</v>
       </c>
-      <c r="J216" s="37" t="s">
+      <c r="J216" s="36" t="s">
         <v>1276</v>
       </c>
-      <c r="K216" s="32" t="s">
+      <c r="K216" s="31" t="s">
         <v>1434</v>
       </c>
-      <c r="L216" s="37" t="s">
+      <c r="L216" s="36" t="s">
         <v>1439</v>
       </c>
       <c r="M216" s="4">
@@ -20207,7 +20259,7 @@
         <v>232750</v>
       </c>
       <c r="Q216" s="6">
-        <f t="shared" ref="Q216:Q220" si="87">Q215+7</f>
+        <f t="shared" ref="Q216:Q225" si="87">Q215+7</f>
         <v>204</v>
       </c>
       <c r="R216" s="8">
@@ -20215,16 +20267,16 @@
         <v>699</v>
       </c>
       <c r="S216" s="8">
-        <f t="shared" ref="S216:S220" si="88">S215+30</f>
+        <f t="shared" ref="S216:S225" si="88">S215+30</f>
         <v>826</v>
       </c>
       <c r="T216" s="8">
         <v>99.99</v>
       </c>
-      <c r="U216" s="35" t="s">
+      <c r="U216" s="34" t="s">
         <v>1440</v>
       </c>
-      <c r="V216" s="35" t="s">
+      <c r="V216" s="34" t="s">
         <v>1440</v>
       </c>
       <c r="W216" s="8"/>
@@ -20249,22 +20301,22 @@
       <c r="F217" s="5" t="s">
         <v>1441</v>
       </c>
-      <c r="G217" s="40" t="s">
+      <c r="G217" s="35" t="s">
         <v>1381</v>
       </c>
-      <c r="H217" s="34" t="s">
+      <c r="H217" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I217" s="40" t="s">
+      <c r="I217" s="35" t="s">
         <v>1442</v>
       </c>
-      <c r="J217" s="40" t="s">
+      <c r="J217" s="35" t="s">
         <v>1443</v>
       </c>
-      <c r="K217" s="41" t="s">
+      <c r="K217" s="37" t="s">
         <v>1276</v>
       </c>
-      <c r="L217" s="40" t="s">
+      <c r="L217" s="35" t="s">
         <v>1444</v>
       </c>
       <c r="M217" s="4">
@@ -20298,10 +20350,10 @@
       <c r="T217" s="8">
         <v>99.99</v>
       </c>
-      <c r="U217" s="35" t="s">
+      <c r="U217" s="34" t="s">
         <v>1445</v>
       </c>
-      <c r="V217" s="35" t="s">
+      <c r="V217" s="34" t="s">
         <v>1445</v>
       </c>
       <c r="W217" s="8"/>
@@ -20326,22 +20378,22 @@
       <c r="F218" s="5" t="s">
         <v>1446</v>
       </c>
-      <c r="G218" s="40" t="s">
+      <c r="G218" s="35" t="s">
         <v>1447</v>
       </c>
-      <c r="H218" s="34" t="s">
+      <c r="H218" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I218" s="40" t="s">
+      <c r="I218" s="35" t="s">
         <v>1448</v>
       </c>
-      <c r="J218" s="40" t="s">
+      <c r="J218" s="35" t="s">
         <v>1449</v>
       </c>
-      <c r="K218" s="40" t="s">
+      <c r="K218" s="35" t="s">
         <v>1443</v>
       </c>
-      <c r="L218" s="40" t="s">
+      <c r="L218" s="35" t="s">
         <v>1450</v>
       </c>
       <c r="M218" s="4">
@@ -20375,10 +20427,10 @@
       <c r="T218" s="8">
         <v>99.99</v>
       </c>
-      <c r="U218" s="35" t="s">
+      <c r="U218" s="34" t="s">
         <v>1451</v>
       </c>
-      <c r="V218" s="35" t="s">
+      <c r="V218" s="34" t="s">
         <v>1451</v>
       </c>
       <c r="W218" s="8"/>
@@ -20403,22 +20455,22 @@
       <c r="F219" s="5" t="s">
         <v>1452</v>
       </c>
-      <c r="G219" s="40" t="s">
+      <c r="G219" s="35" t="s">
         <v>1405</v>
       </c>
-      <c r="H219" s="34" t="s">
+      <c r="H219" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I219" s="40" t="s">
+      <c r="I219" s="35" t="s">
         <v>1453</v>
       </c>
-      <c r="J219" s="40" t="s">
+      <c r="J219" s="35" t="s">
         <v>1306</v>
       </c>
-      <c r="K219" s="40" t="s">
+      <c r="K219" s="35" t="s">
         <v>1449</v>
       </c>
-      <c r="L219" s="40" t="s">
+      <c r="L219" s="35" t="s">
         <v>1354</v>
       </c>
       <c r="M219" s="4">
@@ -20452,10 +20504,10 @@
       <c r="T219" s="8">
         <v>99.99</v>
       </c>
-      <c r="U219" s="35" t="s">
+      <c r="U219" s="34" t="s">
         <v>1454</v>
       </c>
-      <c r="V219" s="35" t="s">
+      <c r="V219" s="34" t="s">
         <v>1454</v>
       </c>
       <c r="W219" s="8"/>
@@ -20480,38 +20532,38 @@
       <c r="F220" s="5" t="s">
         <v>1455</v>
       </c>
-      <c r="G220" s="40" t="s">
+      <c r="G220" s="35" t="s">
         <v>1456</v>
       </c>
-      <c r="H220" s="34" t="s">
+      <c r="H220" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I220" s="40" t="s">
+      <c r="I220" s="35" t="s">
         <v>1457</v>
       </c>
-      <c r="J220" s="40" t="s">
+      <c r="J220" s="35" t="s">
         <v>1279</v>
       </c>
-      <c r="K220" s="40" t="s">
+      <c r="K220" s="35" t="s">
         <v>1306</v>
       </c>
-      <c r="L220" s="40" t="s">
+      <c r="L220" s="35" t="s">
         <v>1437</v>
       </c>
       <c r="M220" s="4">
-        <f t="shared" ref="M220:P220" si="92">M219+30000</f>
+        <f t="shared" ref="M220:M225" si="92">M219+30000</f>
         <v>381000</v>
       </c>
       <c r="N220" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="N220:N225" si="93">N219+30000</f>
         <v>381000</v>
       </c>
       <c r="O220" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="O220:O225" si="94">O219+30000</f>
         <v>352750</v>
       </c>
       <c r="P220" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="P220:P225" si="95">P219+30000</f>
         <v>352750</v>
       </c>
       <c r="Q220" s="6">
@@ -20529,10 +20581,10 @@
       <c r="T220" s="8">
         <v>99.99</v>
       </c>
-      <c r="U220" s="35" t="s">
+      <c r="U220" s="34" t="s">
         <v>1458</v>
       </c>
-      <c r="V220" s="35" t="s">
+      <c r="V220" s="34" t="s">
         <v>1458</v>
       </c>
       <c r="W220" s="8"/>
@@ -20557,55 +20609,60 @@
       <c r="F221" s="6" t="s">
         <v>1459</v>
       </c>
-      <c r="G221" s="37" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H221" s="34" t="s">
+      <c r="G221" s="35" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H221" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I221" s="37" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J221" s="37" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K221" s="32" t="s">
-        <v>1235</v>
-      </c>
-      <c r="L221" s="37" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M221" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N221" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O221" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P221" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q221" s="2">
-        <v>50</v>
-      </c>
-      <c r="R221" s="17">
-        <f t="shared" ref="R216:R250" si="93">R220+9</f>
-        <v>788</v>
-      </c>
-      <c r="S221" s="17">
-        <f t="shared" ref="S216:S250" si="94">S220+10</f>
-        <v>956</v>
-      </c>
-      <c r="T221" s="17">
+      <c r="I221" s="35" t="s">
+        <v>1460</v>
+      </c>
+      <c r="J221" s="35" t="s">
+        <v>1232</v>
+      </c>
+      <c r="K221" s="35" t="s">
+        <v>1461</v>
+      </c>
+      <c r="L221" s="35" t="s">
+        <v>1381</v>
+      </c>
+      <c r="M221" s="4">
+        <f t="shared" si="92"/>
+        <v>411000</v>
+      </c>
+      <c r="N221" s="4">
+        <f t="shared" si="93"/>
+        <v>411000</v>
+      </c>
+      <c r="O221" s="4">
+        <f t="shared" si="94"/>
+        <v>382750</v>
+      </c>
+      <c r="P221" s="4">
+        <f t="shared" si="95"/>
+        <v>382750</v>
+      </c>
+      <c r="Q221" s="6">
+        <f t="shared" si="87"/>
+        <v>239</v>
+      </c>
+      <c r="R221" s="8">
+        <f t="shared" si="84"/>
+        <v>799</v>
+      </c>
+      <c r="S221" s="8">
+        <f t="shared" si="88"/>
+        <v>976</v>
+      </c>
+      <c r="T221" s="8">
         <v>99.99</v>
       </c>
-      <c r="U221" s="32" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V221" s="32" t="s">
-        <v>1237</v>
+      <c r="U221" s="34" t="s">
+        <v>1462</v>
+      </c>
+      <c r="V221" s="34" t="s">
+        <v>1462</v>
       </c>
       <c r="W221" s="8"/>
       <c r="X221" s="8"/>
@@ -20627,57 +20684,62 @@
         <v>7</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>1460</v>
-      </c>
-      <c r="G222" s="37" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H222" s="34" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G222" s="35" t="s">
+        <v>1464</v>
+      </c>
+      <c r="H222" s="39" t="s">
         <v>1302</v>
       </c>
-      <c r="I222" s="37" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J222" s="37" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K222" s="32" t="s">
-        <v>1235</v>
-      </c>
-      <c r="L222" s="37" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M222" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N222" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O222" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P222" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q222" s="2">
-        <v>50</v>
-      </c>
-      <c r="R222" s="17">
+      <c r="I222" s="35" t="s">
+        <v>1465</v>
+      </c>
+      <c r="J222" s="35" t="s">
+        <v>1293</v>
+      </c>
+      <c r="K222" s="35" t="s">
+        <v>1323</v>
+      </c>
+      <c r="L222" s="35" t="s">
+        <v>1447</v>
+      </c>
+      <c r="M222" s="4">
+        <f t="shared" si="92"/>
+        <v>441000</v>
+      </c>
+      <c r="N222" s="4">
         <f t="shared" si="93"/>
-        <v>797</v>
-      </c>
-      <c r="S222" s="17">
+        <v>441000</v>
+      </c>
+      <c r="O222" s="4">
         <f t="shared" si="94"/>
-        <v>966</v>
-      </c>
-      <c r="T222" s="17">
+        <v>412750</v>
+      </c>
+      <c r="P222" s="4">
+        <f t="shared" si="95"/>
+        <v>412750</v>
+      </c>
+      <c r="Q222" s="6">
+        <f t="shared" si="87"/>
+        <v>246</v>
+      </c>
+      <c r="R222" s="8">
+        <f t="shared" si="84"/>
+        <v>819</v>
+      </c>
+      <c r="S222" s="8">
+        <f t="shared" si="88"/>
+        <v>1006</v>
+      </c>
+      <c r="T222" s="8">
         <v>99.99</v>
       </c>
-      <c r="U222" s="32" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V222" s="32" t="s">
-        <v>1237</v>
+      <c r="U222" s="34" t="s">
+        <v>1466</v>
+      </c>
+      <c r="V222" s="34" t="s">
+        <v>1466</v>
       </c>
       <c r="W222" s="8"/>
       <c r="X222" s="8"/>
@@ -20699,57 +20761,62 @@
         <v>7</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>1461</v>
-      </c>
-      <c r="G223" s="37" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H223" s="34" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G223" s="35" t="s">
+        <v>1468</v>
+      </c>
+      <c r="H223" s="39" t="s">
         <v>1302</v>
       </c>
-      <c r="I223" s="37" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J223" s="37" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K223" s="32" t="s">
-        <v>1235</v>
-      </c>
-      <c r="L223" s="37" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M223" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N223" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O223" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P223" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q223" s="2">
-        <v>50</v>
-      </c>
-      <c r="R223" s="17">
+      <c r="I223" s="35" t="s">
+        <v>1469</v>
+      </c>
+      <c r="J223" s="35" t="s">
+        <v>1301</v>
+      </c>
+      <c r="K223" s="35" t="s">
+        <v>1470</v>
+      </c>
+      <c r="L223" s="35" t="s">
+        <v>1405</v>
+      </c>
+      <c r="M223" s="4">
+        <f t="shared" si="92"/>
+        <v>471000</v>
+      </c>
+      <c r="N223" s="4">
         <f t="shared" si="93"/>
-        <v>806</v>
-      </c>
-      <c r="S223" s="17">
+        <v>471000</v>
+      </c>
+      <c r="O223" s="4">
         <f t="shared" si="94"/>
-        <v>976</v>
-      </c>
-      <c r="T223" s="17">
+        <v>442750</v>
+      </c>
+      <c r="P223" s="4">
+        <f t="shared" si="95"/>
+        <v>442750</v>
+      </c>
+      <c r="Q223" s="6">
+        <f t="shared" si="87"/>
+        <v>253</v>
+      </c>
+      <c r="R223" s="8">
+        <f t="shared" si="84"/>
+        <v>839</v>
+      </c>
+      <c r="S223" s="8">
+        <f t="shared" si="88"/>
+        <v>1036</v>
+      </c>
+      <c r="T223" s="8">
         <v>99.99</v>
       </c>
-      <c r="U223" s="32" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V223" s="32" t="s">
-        <v>1237</v>
+      <c r="U223" s="34" t="s">
+        <v>1471</v>
+      </c>
+      <c r="V223" s="34" t="s">
+        <v>1471</v>
       </c>
       <c r="W223" s="8"/>
       <c r="X223" s="8"/>
@@ -20771,57 +20838,62 @@
         <v>7</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>1462</v>
-      </c>
-      <c r="G224" s="37" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H224" s="34" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G224" s="35" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H224" s="39" t="s">
         <v>1302</v>
       </c>
-      <c r="I224" s="37" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J224" s="37" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K224" s="32" t="s">
-        <v>1235</v>
-      </c>
-      <c r="L224" s="37" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M224" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N224" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O224" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P224" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q224" s="2">
-        <v>50</v>
-      </c>
-      <c r="R224" s="17">
+      <c r="I224" s="35" t="s">
+        <v>1474</v>
+      </c>
+      <c r="J224" s="35" t="s">
+        <v>1475</v>
+      </c>
+      <c r="K224" s="35" t="s">
+        <v>1476</v>
+      </c>
+      <c r="L224" s="35" t="s">
+        <v>1456</v>
+      </c>
+      <c r="M224" s="4">
+        <f t="shared" si="92"/>
+        <v>501000</v>
+      </c>
+      <c r="N224" s="4">
         <f t="shared" si="93"/>
-        <v>815</v>
-      </c>
-      <c r="S224" s="17">
+        <v>501000</v>
+      </c>
+      <c r="O224" s="4">
         <f t="shared" si="94"/>
-        <v>986</v>
-      </c>
-      <c r="T224" s="17">
+        <v>472750</v>
+      </c>
+      <c r="P224" s="4">
+        <f t="shared" si="95"/>
+        <v>472750</v>
+      </c>
+      <c r="Q224" s="6">
+        <f t="shared" si="87"/>
+        <v>260</v>
+      </c>
+      <c r="R224" s="8">
+        <f t="shared" si="84"/>
+        <v>859</v>
+      </c>
+      <c r="S224" s="8">
+        <f t="shared" si="88"/>
+        <v>1066</v>
+      </c>
+      <c r="T224" s="8">
         <v>99.99</v>
       </c>
-      <c r="U224" s="32" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V224" s="32" t="s">
-        <v>1237</v>
+      <c r="U224" s="34" t="s">
+        <v>1477</v>
+      </c>
+      <c r="V224" s="34" t="s">
+        <v>1477</v>
       </c>
       <c r="W224" s="8"/>
       <c r="X224" s="8"/>
@@ -20843,57 +20915,62 @@
         <v>7</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>1463</v>
-      </c>
-      <c r="G225" s="37" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H225" s="34" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G225" s="35" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H225" s="39" t="s">
         <v>1302</v>
       </c>
-      <c r="I225" s="37" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J225" s="37" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K225" s="32" t="s">
-        <v>1235</v>
-      </c>
-      <c r="L225" s="37" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M225" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N225" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O225" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P225" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q225" s="2">
-        <v>50</v>
-      </c>
-      <c r="R225" s="17">
+      <c r="I225" s="35" t="s">
+        <v>1480</v>
+      </c>
+      <c r="J225" s="35" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K225" s="35" t="s">
+        <v>1248</v>
+      </c>
+      <c r="L225" s="35" t="s">
+        <v>1428</v>
+      </c>
+      <c r="M225" s="4">
+        <f t="shared" si="92"/>
+        <v>531000</v>
+      </c>
+      <c r="N225" s="4">
         <f t="shared" si="93"/>
-        <v>824</v>
-      </c>
-      <c r="S225" s="17">
+        <v>531000</v>
+      </c>
+      <c r="O225" s="4">
         <f t="shared" si="94"/>
-        <v>996</v>
-      </c>
-      <c r="T225" s="17">
+        <v>502750</v>
+      </c>
+      <c r="P225" s="4">
+        <f t="shared" si="95"/>
+        <v>502750</v>
+      </c>
+      <c r="Q225" s="6">
+        <f t="shared" si="87"/>
+        <v>267</v>
+      </c>
+      <c r="R225" s="8">
+        <f t="shared" si="84"/>
+        <v>879</v>
+      </c>
+      <c r="S225" s="8">
+        <f t="shared" si="88"/>
+        <v>1096</v>
+      </c>
+      <c r="T225" s="8">
         <v>99.99</v>
       </c>
-      <c r="U225" s="32" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V225" s="32" t="s">
-        <v>1237</v>
+      <c r="U225" s="34" t="s">
+        <v>1481</v>
+      </c>
+      <c r="V225" s="34" t="s">
+        <v>1481</v>
       </c>
       <c r="W225" s="8"/>
       <c r="X225" s="8"/>
@@ -20915,24 +20992,24 @@
         <v>7</v>
       </c>
       <c r="F226" s="6" t="s">
-        <v>1464</v>
-      </c>
-      <c r="G226" s="37" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G226" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H226" s="34" t="s">
+      <c r="H226" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I226" s="37" t="s">
+      <c r="I226" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J226" s="37" t="s">
+      <c r="J226" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K226" s="32" t="s">
+      <c r="K226" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L226" s="37" t="s">
+      <c r="L226" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M226" s="2">
@@ -20951,20 +21028,20 @@
         <v>50</v>
       </c>
       <c r="R226" s="17">
-        <f t="shared" si="93"/>
-        <v>833</v>
+        <f t="shared" ref="R216:R250" si="96">R225+9</f>
+        <v>888</v>
       </c>
       <c r="S226" s="17">
-        <f t="shared" si="94"/>
-        <v>1006</v>
+        <f t="shared" ref="S216:S250" si="97">S225+10</f>
+        <v>1106</v>
       </c>
       <c r="T226" s="17">
         <v>99.99</v>
       </c>
-      <c r="U226" s="32" t="s">
+      <c r="U226" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V226" s="32" t="s">
+      <c r="V226" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W226" s="8"/>
@@ -20987,24 +21064,24 @@
         <v>7</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G227" s="37" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G227" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H227" s="34" t="s">
+      <c r="H227" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I227" s="37" t="s">
+      <c r="I227" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J227" s="37" t="s">
+      <c r="J227" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K227" s="32" t="s">
+      <c r="K227" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L227" s="37" t="s">
+      <c r="L227" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M227" s="2">
@@ -21023,20 +21100,20 @@
         <v>50</v>
       </c>
       <c r="R227" s="17">
-        <f t="shared" si="93"/>
-        <v>842</v>
+        <f t="shared" si="96"/>
+        <v>897</v>
       </c>
       <c r="S227" s="17">
-        <f t="shared" si="94"/>
-        <v>1016</v>
+        <f t="shared" si="97"/>
+        <v>1116</v>
       </c>
       <c r="T227" s="17">
         <v>99.99</v>
       </c>
-      <c r="U227" s="32" t="s">
+      <c r="U227" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V227" s="32" t="s">
+      <c r="V227" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W227" s="8"/>
@@ -21059,24 +21136,24 @@
         <v>7</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>1466</v>
-      </c>
-      <c r="G228" s="37" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G228" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H228" s="34" t="s">
+      <c r="H228" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I228" s="37" t="s">
+      <c r="I228" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J228" s="37" t="s">
+      <c r="J228" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K228" s="32" t="s">
+      <c r="K228" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L228" s="37" t="s">
+      <c r="L228" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M228" s="2">
@@ -21095,20 +21172,20 @@
         <v>50</v>
       </c>
       <c r="R228" s="17">
-        <f t="shared" si="93"/>
-        <v>851</v>
+        <f t="shared" si="96"/>
+        <v>906</v>
       </c>
       <c r="S228" s="17">
-        <f t="shared" si="94"/>
-        <v>1026</v>
+        <f t="shared" si="97"/>
+        <v>1126</v>
       </c>
       <c r="T228" s="17">
         <v>99.99</v>
       </c>
-      <c r="U228" s="32" t="s">
+      <c r="U228" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V228" s="32" t="s">
+      <c r="V228" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W228" s="8"/>
@@ -21131,24 +21208,24 @@
         <v>7</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>1467</v>
-      </c>
-      <c r="G229" s="37" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G229" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H229" s="34" t="s">
+      <c r="H229" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I229" s="37" t="s">
+      <c r="I229" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J229" s="37" t="s">
+      <c r="J229" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K229" s="32" t="s">
+      <c r="K229" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L229" s="37" t="s">
+      <c r="L229" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M229" s="2">
@@ -21167,20 +21244,20 @@
         <v>50</v>
       </c>
       <c r="R229" s="17">
-        <f t="shared" si="93"/>
-        <v>860</v>
+        <f t="shared" si="96"/>
+        <v>915</v>
       </c>
       <c r="S229" s="17">
-        <f t="shared" si="94"/>
-        <v>1036</v>
+        <f t="shared" si="97"/>
+        <v>1136</v>
       </c>
       <c r="T229" s="17">
         <v>99.99</v>
       </c>
-      <c r="U229" s="32" t="s">
+      <c r="U229" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V229" s="32" t="s">
+      <c r="V229" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W229" s="8"/>
@@ -21203,24 +21280,24 @@
         <v>7</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>1468</v>
-      </c>
-      <c r="G230" s="37" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G230" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H230" s="34" t="s">
+      <c r="H230" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I230" s="37" t="s">
+      <c r="I230" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J230" s="37" t="s">
+      <c r="J230" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K230" s="32" t="s">
+      <c r="K230" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L230" s="37" t="s">
+      <c r="L230" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M230" s="2">
@@ -21239,20 +21316,20 @@
         <v>50</v>
       </c>
       <c r="R230" s="17">
-        <f t="shared" si="93"/>
-        <v>869</v>
+        <f t="shared" si="96"/>
+        <v>924</v>
       </c>
       <c r="S230" s="17">
-        <f t="shared" si="94"/>
-        <v>1046</v>
+        <f t="shared" si="97"/>
+        <v>1146</v>
       </c>
       <c r="T230" s="17">
         <v>99.99</v>
       </c>
-      <c r="U230" s="32" t="s">
+      <c r="U230" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V230" s="32" t="s">
+      <c r="V230" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W230" s="8"/>
@@ -21275,24 +21352,24 @@
         <v>7</v>
       </c>
       <c r="F231" s="6" t="s">
-        <v>1469</v>
-      </c>
-      <c r="G231" s="37" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G231" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H231" s="34" t="s">
+      <c r="H231" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I231" s="37" t="s">
+      <c r="I231" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J231" s="37" t="s">
+      <c r="J231" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K231" s="32" t="s">
+      <c r="K231" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L231" s="37" t="s">
+      <c r="L231" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M231" s="2">
@@ -21311,20 +21388,20 @@
         <v>50</v>
       </c>
       <c r="R231" s="17">
-        <f t="shared" si="93"/>
-        <v>878</v>
+        <f t="shared" si="96"/>
+        <v>933</v>
       </c>
       <c r="S231" s="17">
-        <f t="shared" si="94"/>
-        <v>1056</v>
+        <f t="shared" si="97"/>
+        <v>1156</v>
       </c>
       <c r="T231" s="17">
         <v>99.99</v>
       </c>
-      <c r="U231" s="32" t="s">
+      <c r="U231" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V231" s="32" t="s">
+      <c r="V231" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W231" s="8"/>
@@ -21347,24 +21424,24 @@
         <v>7</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>1470</v>
-      </c>
-      <c r="G232" s="37" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G232" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H232" s="34" t="s">
+      <c r="H232" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I232" s="37" t="s">
+      <c r="I232" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J232" s="37" t="s">
+      <c r="J232" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K232" s="32" t="s">
+      <c r="K232" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L232" s="37" t="s">
+      <c r="L232" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M232" s="2">
@@ -21383,20 +21460,20 @@
         <v>50</v>
       </c>
       <c r="R232" s="17">
-        <f t="shared" si="93"/>
-        <v>887</v>
+        <f t="shared" si="96"/>
+        <v>942</v>
       </c>
       <c r="S232" s="17">
-        <f t="shared" si="94"/>
-        <v>1066</v>
+        <f t="shared" si="97"/>
+        <v>1166</v>
       </c>
       <c r="T232" s="17">
         <v>99.99</v>
       </c>
-      <c r="U232" s="32" t="s">
+      <c r="U232" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V232" s="32" t="s">
+      <c r="V232" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W232" s="8"/>
@@ -21419,24 +21496,24 @@
         <v>7</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>1471</v>
-      </c>
-      <c r="G233" s="37" t="s">
+        <v>1489</v>
+      </c>
+      <c r="G233" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H233" s="34" t="s">
+      <c r="H233" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I233" s="37" t="s">
+      <c r="I233" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J233" s="37" t="s">
+      <c r="J233" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K233" s="32" t="s">
+      <c r="K233" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L233" s="37" t="s">
+      <c r="L233" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M233" s="2">
@@ -21455,20 +21532,20 @@
         <v>50</v>
       </c>
       <c r="R233" s="17">
-        <f t="shared" si="93"/>
-        <v>896</v>
+        <f t="shared" si="96"/>
+        <v>951</v>
       </c>
       <c r="S233" s="17">
-        <f t="shared" si="94"/>
-        <v>1076</v>
+        <f t="shared" si="97"/>
+        <v>1176</v>
       </c>
       <c r="T233" s="17">
         <v>99.99</v>
       </c>
-      <c r="U233" s="32" t="s">
+      <c r="U233" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V233" s="32" t="s">
+      <c r="V233" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W233" s="8"/>
@@ -21491,24 +21568,24 @@
         <v>7</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>1472</v>
-      </c>
-      <c r="G234" s="37" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G234" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H234" s="34" t="s">
+      <c r="H234" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I234" s="37" t="s">
+      <c r="I234" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J234" s="37" t="s">
+      <c r="J234" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K234" s="32" t="s">
+      <c r="K234" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L234" s="37" t="s">
+      <c r="L234" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M234" s="2">
@@ -21527,20 +21604,20 @@
         <v>50</v>
       </c>
       <c r="R234" s="17">
-        <f t="shared" si="93"/>
-        <v>905</v>
+        <f t="shared" si="96"/>
+        <v>960</v>
       </c>
       <c r="S234" s="17">
-        <f t="shared" si="94"/>
-        <v>1086</v>
+        <f t="shared" si="97"/>
+        <v>1186</v>
       </c>
       <c r="T234" s="17">
         <v>99.99</v>
       </c>
-      <c r="U234" s="32" t="s">
+      <c r="U234" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V234" s="32" t="s">
+      <c r="V234" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W234" s="8"/>
@@ -21563,24 +21640,24 @@
         <v>7</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>1473</v>
-      </c>
-      <c r="G235" s="37" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G235" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H235" s="34" t="s">
+      <c r="H235" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I235" s="37" t="s">
+      <c r="I235" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J235" s="37" t="s">
+      <c r="J235" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K235" s="32" t="s">
+      <c r="K235" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L235" s="37" t="s">
+      <c r="L235" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M235" s="2">
@@ -21599,20 +21676,20 @@
         <v>50</v>
       </c>
       <c r="R235" s="17">
-        <f t="shared" si="93"/>
-        <v>914</v>
+        <f t="shared" si="96"/>
+        <v>969</v>
       </c>
       <c r="S235" s="17">
-        <f t="shared" si="94"/>
-        <v>1096</v>
+        <f t="shared" si="97"/>
+        <v>1196</v>
       </c>
       <c r="T235" s="17">
         <v>99.99</v>
       </c>
-      <c r="U235" s="32" t="s">
+      <c r="U235" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V235" s="32" t="s">
+      <c r="V235" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W235" s="8"/>
@@ -21635,24 +21712,24 @@
         <v>7</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>1474</v>
-      </c>
-      <c r="G236" s="37" t="s">
+        <v>1492</v>
+      </c>
+      <c r="G236" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H236" s="34" t="s">
+      <c r="H236" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I236" s="37" t="s">
+      <c r="I236" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J236" s="37" t="s">
+      <c r="J236" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K236" s="32" t="s">
+      <c r="K236" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L236" s="37" t="s">
+      <c r="L236" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M236" s="2">
@@ -21671,20 +21748,20 @@
         <v>50</v>
       </c>
       <c r="R236" s="17">
-        <f t="shared" si="93"/>
-        <v>923</v>
+        <f t="shared" si="96"/>
+        <v>978</v>
       </c>
       <c r="S236" s="17">
-        <f t="shared" si="94"/>
-        <v>1106</v>
+        <f t="shared" si="97"/>
+        <v>1206</v>
       </c>
       <c r="T236" s="17">
         <v>99.99</v>
       </c>
-      <c r="U236" s="32" t="s">
+      <c r="U236" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V236" s="32" t="s">
+      <c r="V236" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W236" s="8"/>
@@ -21707,24 +21784,24 @@
         <v>7</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>1475</v>
-      </c>
-      <c r="G237" s="37" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G237" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H237" s="34" t="s">
+      <c r="H237" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I237" s="37" t="s">
+      <c r="I237" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J237" s="37" t="s">
+      <c r="J237" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K237" s="32" t="s">
+      <c r="K237" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L237" s="37" t="s">
+      <c r="L237" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M237" s="2">
@@ -21743,20 +21820,20 @@
         <v>50</v>
       </c>
       <c r="R237" s="17">
-        <f t="shared" si="93"/>
-        <v>932</v>
+        <f t="shared" si="96"/>
+        <v>987</v>
       </c>
       <c r="S237" s="17">
-        <f t="shared" si="94"/>
-        <v>1116</v>
+        <f t="shared" si="97"/>
+        <v>1216</v>
       </c>
       <c r="T237" s="17">
         <v>99.99</v>
       </c>
-      <c r="U237" s="32" t="s">
+      <c r="U237" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V237" s="32" t="s">
+      <c r="V237" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W237" s="8"/>
@@ -21779,24 +21856,24 @@
         <v>7</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>1476</v>
-      </c>
-      <c r="G238" s="37" t="s">
+        <v>1494</v>
+      </c>
+      <c r="G238" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H238" s="34" t="s">
+      <c r="H238" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I238" s="37" t="s">
+      <c r="I238" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J238" s="37" t="s">
+      <c r="J238" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K238" s="32" t="s">
+      <c r="K238" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L238" s="37" t="s">
+      <c r="L238" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M238" s="2">
@@ -21815,20 +21892,20 @@
         <v>50</v>
       </c>
       <c r="R238" s="17">
-        <f t="shared" si="93"/>
-        <v>941</v>
+        <f t="shared" si="96"/>
+        <v>996</v>
       </c>
       <c r="S238" s="17">
-        <f t="shared" si="94"/>
-        <v>1126</v>
+        <f t="shared" si="97"/>
+        <v>1226</v>
       </c>
       <c r="T238" s="17">
         <v>99.99</v>
       </c>
-      <c r="U238" s="32" t="s">
+      <c r="U238" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V238" s="32" t="s">
+      <c r="V238" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W238" s="8"/>
@@ -21851,24 +21928,24 @@
         <v>7</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>1477</v>
-      </c>
-      <c r="G239" s="37" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G239" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H239" s="34" t="s">
+      <c r="H239" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I239" s="37" t="s">
+      <c r="I239" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J239" s="37" t="s">
+      <c r="J239" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K239" s="32" t="s">
+      <c r="K239" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L239" s="37" t="s">
+      <c r="L239" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M239" s="2">
@@ -21887,20 +21964,20 @@
         <v>50</v>
       </c>
       <c r="R239" s="17">
-        <f t="shared" si="93"/>
-        <v>950</v>
+        <f t="shared" si="96"/>
+        <v>1005</v>
       </c>
       <c r="S239" s="17">
-        <f t="shared" si="94"/>
-        <v>1136</v>
+        <f t="shared" si="97"/>
+        <v>1236</v>
       </c>
       <c r="T239" s="17">
         <v>99.99</v>
       </c>
-      <c r="U239" s="32" t="s">
+      <c r="U239" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V239" s="32" t="s">
+      <c r="V239" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W239" s="8"/>
@@ -21923,24 +22000,24 @@
         <v>7</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1478</v>
-      </c>
-      <c r="G240" s="37" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G240" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H240" s="34" t="s">
+      <c r="H240" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I240" s="37" t="s">
+      <c r="I240" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J240" s="37" t="s">
+      <c r="J240" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K240" s="32" t="s">
+      <c r="K240" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L240" s="37" t="s">
+      <c r="L240" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M240" s="2">
@@ -21959,20 +22036,20 @@
         <v>50</v>
       </c>
       <c r="R240" s="17">
-        <f t="shared" si="93"/>
-        <v>959</v>
+        <f t="shared" si="96"/>
+        <v>1014</v>
       </c>
       <c r="S240" s="17">
-        <f t="shared" si="94"/>
-        <v>1146</v>
+        <f t="shared" si="97"/>
+        <v>1246</v>
       </c>
       <c r="T240" s="17">
         <v>99.99</v>
       </c>
-      <c r="U240" s="32" t="s">
+      <c r="U240" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V240" s="32" t="s">
+      <c r="V240" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W240" s="8"/>
@@ -21995,24 +22072,24 @@
         <v>7</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>1479</v>
-      </c>
-      <c r="G241" s="37" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G241" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H241" s="34" t="s">
+      <c r="H241" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I241" s="37" t="s">
+      <c r="I241" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J241" s="37" t="s">
+      <c r="J241" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K241" s="32" t="s">
+      <c r="K241" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L241" s="37" t="s">
+      <c r="L241" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M241" s="2">
@@ -22031,20 +22108,20 @@
         <v>50</v>
       </c>
       <c r="R241" s="17">
-        <f t="shared" si="93"/>
-        <v>968</v>
+        <f t="shared" si="96"/>
+        <v>1023</v>
       </c>
       <c r="S241" s="17">
-        <f t="shared" si="94"/>
-        <v>1156</v>
+        <f t="shared" si="97"/>
+        <v>1256</v>
       </c>
       <c r="T241" s="17">
         <v>99.99</v>
       </c>
-      <c r="U241" s="32" t="s">
+      <c r="U241" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V241" s="32" t="s">
+      <c r="V241" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W241" s="8"/>
@@ -22067,24 +22144,24 @@
         <v>7</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>1480</v>
-      </c>
-      <c r="G242" s="37" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G242" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H242" s="34" t="s">
+      <c r="H242" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I242" s="37" t="s">
+      <c r="I242" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J242" s="37" t="s">
+      <c r="J242" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K242" s="32" t="s">
+      <c r="K242" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L242" s="37" t="s">
+      <c r="L242" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M242" s="2">
@@ -22103,20 +22180,20 @@
         <v>50</v>
       </c>
       <c r="R242" s="17">
-        <f t="shared" si="93"/>
-        <v>977</v>
+        <f t="shared" si="96"/>
+        <v>1032</v>
       </c>
       <c r="S242" s="17">
-        <f t="shared" si="94"/>
-        <v>1166</v>
+        <f t="shared" si="97"/>
+        <v>1266</v>
       </c>
       <c r="T242" s="17">
         <v>99.99</v>
       </c>
-      <c r="U242" s="32" t="s">
+      <c r="U242" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V242" s="32" t="s">
+      <c r="V242" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W242" s="8"/>
@@ -22139,24 +22216,24 @@
         <v>7</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>1481</v>
-      </c>
-      <c r="G243" s="37" t="s">
+        <v>1499</v>
+      </c>
+      <c r="G243" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H243" s="34" t="s">
+      <c r="H243" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I243" s="37" t="s">
+      <c r="I243" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J243" s="37" t="s">
+      <c r="J243" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K243" s="32" t="s">
+      <c r="K243" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L243" s="37" t="s">
+      <c r="L243" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M243" s="2">
@@ -22175,20 +22252,20 @@
         <v>50</v>
       </c>
       <c r="R243" s="17">
-        <f t="shared" si="93"/>
-        <v>986</v>
+        <f t="shared" si="96"/>
+        <v>1041</v>
       </c>
       <c r="S243" s="17">
-        <f t="shared" si="94"/>
-        <v>1176</v>
+        <f t="shared" si="97"/>
+        <v>1276</v>
       </c>
       <c r="T243" s="17">
         <v>99.99</v>
       </c>
-      <c r="U243" s="32" t="s">
+      <c r="U243" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V243" s="32" t="s">
+      <c r="V243" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W243" s="8"/>
@@ -22211,24 +22288,24 @@
         <v>7</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>1482</v>
-      </c>
-      <c r="G244" s="37" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G244" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H244" s="34" t="s">
+      <c r="H244" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I244" s="37" t="s">
+      <c r="I244" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J244" s="37" t="s">
+      <c r="J244" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K244" s="32" t="s">
+      <c r="K244" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L244" s="37" t="s">
+      <c r="L244" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M244" s="2">
@@ -22247,20 +22324,20 @@
         <v>50</v>
       </c>
       <c r="R244" s="17">
-        <f t="shared" si="93"/>
-        <v>995</v>
+        <f t="shared" si="96"/>
+        <v>1050</v>
       </c>
       <c r="S244" s="17">
-        <f t="shared" si="94"/>
-        <v>1186</v>
+        <f t="shared" si="97"/>
+        <v>1286</v>
       </c>
       <c r="T244" s="17">
         <v>99.99</v>
       </c>
-      <c r="U244" s="32" t="s">
+      <c r="U244" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V244" s="32" t="s">
+      <c r="V244" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W244" s="8"/>
@@ -22283,24 +22360,24 @@
         <v>7</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>1483</v>
-      </c>
-      <c r="G245" s="37" t="s">
+        <v>1501</v>
+      </c>
+      <c r="G245" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H245" s="34" t="s">
+      <c r="H245" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I245" s="37" t="s">
+      <c r="I245" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J245" s="37" t="s">
+      <c r="J245" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K245" s="32" t="s">
+      <c r="K245" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L245" s="37" t="s">
+      <c r="L245" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M245" s="2">
@@ -22319,20 +22396,20 @@
         <v>50</v>
       </c>
       <c r="R245" s="17">
-        <f t="shared" si="93"/>
-        <v>1004</v>
+        <f t="shared" si="96"/>
+        <v>1059</v>
       </c>
       <c r="S245" s="17">
-        <f t="shared" si="94"/>
-        <v>1196</v>
+        <f t="shared" si="97"/>
+        <v>1296</v>
       </c>
       <c r="T245" s="17">
         <v>99.99</v>
       </c>
-      <c r="U245" s="32" t="s">
+      <c r="U245" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V245" s="32" t="s">
+      <c r="V245" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W245" s="8"/>
@@ -22355,24 +22432,24 @@
         <v>7</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>1484</v>
-      </c>
-      <c r="G246" s="37" t="s">
+        <v>1502</v>
+      </c>
+      <c r="G246" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H246" s="34" t="s">
+      <c r="H246" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I246" s="37" t="s">
+      <c r="I246" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J246" s="37" t="s">
+      <c r="J246" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K246" s="32" t="s">
+      <c r="K246" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L246" s="37" t="s">
+      <c r="L246" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M246" s="2">
@@ -22391,20 +22468,20 @@
         <v>50</v>
       </c>
       <c r="R246" s="17">
-        <f t="shared" si="93"/>
-        <v>1013</v>
+        <f t="shared" si="96"/>
+        <v>1068</v>
       </c>
       <c r="S246" s="17">
-        <f t="shared" si="94"/>
-        <v>1206</v>
+        <f t="shared" si="97"/>
+        <v>1306</v>
       </c>
       <c r="T246" s="17">
         <v>99.99</v>
       </c>
-      <c r="U246" s="32" t="s">
+      <c r="U246" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V246" s="32" t="s">
+      <c r="V246" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W246" s="8"/>
@@ -22427,24 +22504,24 @@
         <v>7</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>1485</v>
-      </c>
-      <c r="G247" s="37" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G247" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H247" s="34" t="s">
+      <c r="H247" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I247" s="37" t="s">
+      <c r="I247" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J247" s="37" t="s">
+      <c r="J247" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K247" s="32" t="s">
+      <c r="K247" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L247" s="37" t="s">
+      <c r="L247" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M247" s="2">
@@ -22463,20 +22540,20 @@
         <v>50</v>
       </c>
       <c r="R247" s="17">
-        <f t="shared" si="93"/>
-        <v>1022</v>
+        <f t="shared" si="96"/>
+        <v>1077</v>
       </c>
       <c r="S247" s="17">
-        <f t="shared" si="94"/>
-        <v>1216</v>
+        <f t="shared" si="97"/>
+        <v>1316</v>
       </c>
       <c r="T247" s="17">
         <v>99.99</v>
       </c>
-      <c r="U247" s="32" t="s">
+      <c r="U247" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V247" s="32" t="s">
+      <c r="V247" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W247" s="8"/>
@@ -22499,24 +22576,24 @@
         <v>7</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>1486</v>
-      </c>
-      <c r="G248" s="37" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G248" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H248" s="34" t="s">
+      <c r="H248" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I248" s="37" t="s">
+      <c r="I248" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J248" s="37" t="s">
+      <c r="J248" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K248" s="32" t="s">
+      <c r="K248" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L248" s="37" t="s">
+      <c r="L248" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M248" s="2">
@@ -22535,20 +22612,20 @@
         <v>50</v>
       </c>
       <c r="R248" s="17">
-        <f t="shared" si="93"/>
-        <v>1031</v>
+        <f t="shared" si="96"/>
+        <v>1086</v>
       </c>
       <c r="S248" s="17">
-        <f t="shared" si="94"/>
-        <v>1226</v>
+        <f t="shared" si="97"/>
+        <v>1326</v>
       </c>
       <c r="T248" s="17">
         <v>99.99</v>
       </c>
-      <c r="U248" s="32" t="s">
+      <c r="U248" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V248" s="32" t="s">
+      <c r="V248" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W248" s="8"/>
@@ -22571,24 +22648,24 @@
         <v>7</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>1487</v>
-      </c>
-      <c r="G249" s="37" t="s">
+        <v>1505</v>
+      </c>
+      <c r="G249" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H249" s="34" t="s">
+      <c r="H249" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I249" s="37" t="s">
+      <c r="I249" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J249" s="37" t="s">
+      <c r="J249" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K249" s="32" t="s">
+      <c r="K249" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L249" s="37" t="s">
+      <c r="L249" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M249" s="2">
@@ -22607,20 +22684,20 @@
         <v>50</v>
       </c>
       <c r="R249" s="17">
-        <f t="shared" si="93"/>
-        <v>1040</v>
+        <f t="shared" si="96"/>
+        <v>1095</v>
       </c>
       <c r="S249" s="17">
-        <f t="shared" si="94"/>
-        <v>1236</v>
+        <f t="shared" si="97"/>
+        <v>1336</v>
       </c>
       <c r="T249" s="17">
         <v>99.99</v>
       </c>
-      <c r="U249" s="32" t="s">
+      <c r="U249" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V249" s="32" t="s">
+      <c r="V249" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W249" s="8"/>
@@ -22643,24 +22720,24 @@
         <v>7</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>1488</v>
-      </c>
-      <c r="G250" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="G250" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="H250" s="34" t="s">
+      <c r="H250" s="33" t="s">
         <v>1302</v>
       </c>
-      <c r="I250" s="37" t="s">
+      <c r="I250" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="J250" s="37" t="s">
+      <c r="J250" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="K250" s="32" t="s">
+      <c r="K250" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="L250" s="37" t="s">
+      <c r="L250" s="36" t="s">
         <v>1236</v>
       </c>
       <c r="M250" s="2">
@@ -22679,20 +22756,20 @@
         <v>50</v>
       </c>
       <c r="R250" s="17">
-        <f t="shared" si="93"/>
-        <v>1049</v>
+        <f t="shared" si="96"/>
+        <v>1104</v>
       </c>
       <c r="S250" s="17">
-        <f t="shared" si="94"/>
-        <v>1246</v>
+        <f t="shared" si="97"/>
+        <v>1346</v>
       </c>
       <c r="T250" s="17">
         <v>99.99</v>
       </c>
-      <c r="U250" s="32" t="s">
+      <c r="U250" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="V250" s="32" t="s">
+      <c r="V250" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="W250" s="8"/>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="1518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="1533">
   <si>
     <t>ID</t>
   </si>
@@ -4526,16 +4526,61 @@
     <t>虚无钳虫</t>
   </si>
   <si>
+    <t>1E+275</t>
+  </si>
+  <si>
+    <t>1E+252</t>
+  </si>
+  <si>
+    <t>580000000000</t>
+  </si>
+  <si>
     <t>虚无蠕虫</t>
   </si>
   <si>
+    <t>1E+278</t>
+  </si>
+  <si>
+    <t>1E+141</t>
+  </si>
+  <si>
+    <t>590000000000</t>
+  </si>
+  <si>
     <t>虚无黑猪</t>
   </si>
   <si>
+    <t>1E+281</t>
+  </si>
+  <si>
+    <t>1E+256</t>
+  </si>
+  <si>
+    <t>600000000000</t>
+  </si>
+  <si>
     <t>虚无红猪</t>
   </si>
   <si>
+    <t>1E+284</t>
+  </si>
+  <si>
+    <t>1E+147</t>
+  </si>
+  <si>
+    <t>1E+258</t>
+  </si>
+  <si>
+    <t>610000000000</t>
+  </si>
+  <si>
     <t>虚无蝎蛇</t>
+  </si>
+  <si>
+    <t>1E+287</t>
+  </si>
+  <si>
+    <t>620000000000</t>
   </si>
   <si>
     <t>虚无恶魔</t>
@@ -4771,7 +4816,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4781,6 +4826,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5101,7 +5152,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5125,16 +5176,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -5143,89 +5194,89 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5235,15 +5286,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -5259,18 +5310,15 @@
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -5287,13 +5335,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5905,13 +5949,13 @@
       <c r="F6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="28" t="s">
         <v>37</v>
       </c>
       <c r="J6" s="1">
@@ -9648,7 +9692,7 @@
       <c r="H65" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="I65" s="29" t="s">
+      <c r="I65" s="28" t="s">
         <v>440</v>
       </c>
       <c r="J65" s="1">
@@ -9717,7 +9761,7 @@
       <c r="H66" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="I66" s="29" t="s">
+      <c r="I66" s="28" t="s">
         <v>447</v>
       </c>
       <c r="J66" s="1">
@@ -9786,7 +9830,7 @@
       <c r="H67" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="I67" s="29" t="s">
+      <c r="I67" s="28" t="s">
         <v>454</v>
       </c>
       <c r="J67" s="1">
@@ -9855,7 +9899,7 @@
       <c r="H68" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="I68" s="29" t="s">
+      <c r="I68" s="28" t="s">
         <v>461</v>
       </c>
       <c r="J68" s="1">
@@ -9921,10 +9965,10 @@
       <c r="G69" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="H69" s="29" t="s">
+      <c r="H69" s="28" t="s">
         <v>467</v>
       </c>
-      <c r="I69" s="29" t="s">
+      <c r="I69" s="28" t="s">
         <v>468</v>
       </c>
       <c r="J69" s="1">
@@ -9987,13 +10031,13 @@
       <c r="F70" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="G70" s="29" t="s">
+      <c r="G70" s="28" t="s">
         <v>473</v>
       </c>
-      <c r="H70" s="29" t="s">
+      <c r="H70" s="28" t="s">
         <v>474</v>
       </c>
-      <c r="I70" s="29" t="s">
+      <c r="I70" s="28" t="s">
         <v>475</v>
       </c>
       <c r="J70" s="1">
@@ -10056,13 +10100,13 @@
       <c r="F71" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="G71" s="29" t="s">
+      <c r="G71" s="28" t="s">
         <v>480</v>
       </c>
-      <c r="H71" s="29" t="s">
+      <c r="H71" s="28" t="s">
         <v>481</v>
       </c>
-      <c r="I71" s="29" t="s">
+      <c r="I71" s="28" t="s">
         <v>482</v>
       </c>
       <c r="J71" s="1">
@@ -10125,13 +10169,13 @@
       <c r="F72" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="G72" s="29" t="s">
+      <c r="G72" s="28" t="s">
         <v>487</v>
       </c>
-      <c r="H72" s="29" t="s">
+      <c r="H72" s="28" t="s">
         <v>488</v>
       </c>
-      <c r="I72" s="29" t="s">
+      <c r="I72" s="28" t="s">
         <v>489</v>
       </c>
       <c r="J72" s="1">
@@ -10194,13 +10238,13 @@
       <c r="F73" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G73" s="29" t="s">
+      <c r="G73" s="28" t="s">
         <v>494</v>
       </c>
-      <c r="H73" s="29" t="s">
+      <c r="H73" s="28" t="s">
         <v>495</v>
       </c>
-      <c r="I73" s="29" t="s">
+      <c r="I73" s="28" t="s">
         <v>496</v>
       </c>
       <c r="J73" s="1">
@@ -10263,13 +10307,13 @@
       <c r="F74" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="G74" s="29" t="s">
+      <c r="G74" s="28" t="s">
         <v>501</v>
       </c>
-      <c r="H74" s="29" t="s">
+      <c r="H74" s="28" t="s">
         <v>502</v>
       </c>
-      <c r="I74" s="29" t="s">
+      <c r="I74" s="28" t="s">
         <v>503</v>
       </c>
       <c r="J74" s="1">
@@ -10332,13 +10376,13 @@
       <c r="F75" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="G75" s="29" t="s">
+      <c r="G75" s="28" t="s">
         <v>508</v>
       </c>
-      <c r="H75" s="29" t="s">
+      <c r="H75" s="28" t="s">
         <v>509</v>
       </c>
-      <c r="I75" s="29" t="s">
+      <c r="I75" s="28" t="s">
         <v>510</v>
       </c>
       <c r="J75" s="1">
@@ -10378,7 +10422,7 @@
       <c r="U75" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="V75" s="29" t="s">
+      <c r="V75" s="28" t="s">
         <v>511</v>
       </c>
       <c r="W75" s="10"/>
@@ -10402,13 +10446,13 @@
       <c r="F76" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G76" s="29" t="s">
+      <c r="G76" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="H76" s="29" t="s">
+      <c r="H76" s="28" t="s">
         <v>516</v>
       </c>
-      <c r="I76" s="29" t="s">
+      <c r="I76" s="28" t="s">
         <v>517</v>
       </c>
       <c r="J76" s="1">
@@ -10470,13 +10514,13 @@
       <c r="F77" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="G77" s="29" t="s">
+      <c r="G77" s="28" t="s">
         <v>521</v>
       </c>
-      <c r="H77" s="29" t="s">
+      <c r="H77" s="28" t="s">
         <v>522</v>
       </c>
-      <c r="I77" s="29" t="s">
+      <c r="I77" s="28" t="s">
         <v>523</v>
       </c>
       <c r="J77" s="1">
@@ -10538,13 +10582,13 @@
       <c r="F78" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="G78" s="29" t="s">
+      <c r="G78" s="28" t="s">
         <v>527</v>
       </c>
-      <c r="H78" s="29" t="s">
+      <c r="H78" s="28" t="s">
         <v>528</v>
       </c>
-      <c r="I78" s="29" t="s">
+      <c r="I78" s="28" t="s">
         <v>529</v>
       </c>
       <c r="J78" s="1">
@@ -10606,13 +10650,13 @@
       <c r="F79" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G79" s="29" t="s">
+      <c r="G79" s="28" t="s">
         <v>533</v>
       </c>
-      <c r="H79" s="29" t="s">
+      <c r="H79" s="28" t="s">
         <v>534</v>
       </c>
-      <c r="I79" s="29" t="s">
+      <c r="I79" s="28" t="s">
         <v>535</v>
       </c>
       <c r="J79" s="1">
@@ -10674,13 +10718,13 @@
       <c r="F80" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="G80" s="29" t="s">
+      <c r="G80" s="28" t="s">
         <v>539</v>
       </c>
-      <c r="H80" s="29" t="s">
+      <c r="H80" s="28" t="s">
         <v>540</v>
       </c>
-      <c r="I80" s="29" t="s">
+      <c r="I80" s="28" t="s">
         <v>541</v>
       </c>
       <c r="J80" s="1">
@@ -10742,13 +10786,13 @@
       <c r="F81" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="G81" s="29" t="s">
+      <c r="G81" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="H81" s="29" t="s">
+      <c r="H81" s="28" t="s">
         <v>546</v>
       </c>
-      <c r="I81" s="29" t="s">
+      <c r="I81" s="28" t="s">
         <v>547</v>
       </c>
       <c r="J81" s="1">
@@ -10812,13 +10856,13 @@
       <c r="F82" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G82" s="29" t="s">
+      <c r="G82" s="28" t="s">
         <v>551</v>
       </c>
-      <c r="H82" s="29" t="s">
+      <c r="H82" s="28" t="s">
         <v>552</v>
       </c>
-      <c r="I82" s="29" t="s">
+      <c r="I82" s="28" t="s">
         <v>553</v>
       </c>
       <c r="J82" s="1">
@@ -10882,13 +10926,13 @@
       <c r="F83" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="G83" s="29" t="s">
+      <c r="G83" s="28" t="s">
         <v>557</v>
       </c>
-      <c r="H83" s="29" t="s">
+      <c r="H83" s="28" t="s">
         <v>558</v>
       </c>
-      <c r="I83" s="29" t="s">
+      <c r="I83" s="28" t="s">
         <v>559</v>
       </c>
       <c r="J83" s="1">
@@ -10952,13 +10996,13 @@
       <c r="F84" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G84" s="29" t="s">
+      <c r="G84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="H84" s="29" t="s">
+      <c r="H84" s="28" t="s">
         <v>564</v>
       </c>
-      <c r="I84" s="29" t="s">
+      <c r="I84" s="28" t="s">
         <v>565</v>
       </c>
       <c r="J84" s="1">
@@ -11022,13 +11066,13 @@
       <c r="F85" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="G85" s="29" t="s">
+      <c r="G85" s="28" t="s">
         <v>569</v>
       </c>
-      <c r="H85" s="29" t="s">
+      <c r="H85" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="I85" s="29" t="s">
+      <c r="I85" s="28" t="s">
         <v>571</v>
       </c>
       <c r="J85" s="1">
@@ -11092,13 +11136,13 @@
       <c r="F86" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="G86" s="29" t="s">
+      <c r="G86" s="28" t="s">
         <v>575</v>
       </c>
-      <c r="H86" s="29" t="s">
+      <c r="H86" s="28" t="s">
         <v>539</v>
       </c>
-      <c r="I86" s="29" t="s">
+      <c r="I86" s="28" t="s">
         <v>576</v>
       </c>
       <c r="J86" s="1">
@@ -11162,13 +11206,13 @@
       <c r="F87" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="G87" s="29" t="s">
+      <c r="G87" s="28" t="s">
         <v>580</v>
       </c>
-      <c r="H87" s="29" t="s">
+      <c r="H87" s="28" t="s">
         <v>581</v>
       </c>
-      <c r="I87" s="29" t="s">
+      <c r="I87" s="28" t="s">
         <v>582</v>
       </c>
       <c r="J87" s="1">
@@ -11232,13 +11276,13 @@
       <c r="F88" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="G88" s="29" t="s">
+      <c r="G88" s="28" t="s">
         <v>489</v>
       </c>
-      <c r="H88" s="29" t="s">
+      <c r="H88" s="28" t="s">
         <v>454</v>
       </c>
-      <c r="I88" s="29" t="s">
+      <c r="I88" s="28" t="s">
         <v>586</v>
       </c>
       <c r="J88" s="1">
@@ -11302,13 +11346,13 @@
       <c r="F89" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="G89" s="29" t="s">
+      <c r="G89" s="28" t="s">
         <v>503</v>
       </c>
-      <c r="H89" s="29" t="s">
+      <c r="H89" s="28" t="s">
         <v>590</v>
       </c>
-      <c r="I89" s="29" t="s">
+      <c r="I89" s="28" t="s">
         <v>591</v>
       </c>
       <c r="J89" s="1">
@@ -11372,13 +11416,13 @@
       <c r="F90" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G90" s="29" t="s">
+      <c r="G90" s="28" t="s">
         <v>595</v>
       </c>
-      <c r="H90" s="29" t="s">
+      <c r="H90" s="28" t="s">
         <v>580</v>
       </c>
-      <c r="I90" s="29" t="s">
+      <c r="I90" s="28" t="s">
         <v>596</v>
       </c>
       <c r="J90" s="1">
@@ -11442,13 +11486,13 @@
       <c r="F91" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="G91" s="29" t="s">
+      <c r="G91" s="28" t="s">
         <v>600</v>
       </c>
-      <c r="H91" s="29" t="s">
+      <c r="H91" s="28" t="s">
         <v>601</v>
       </c>
-      <c r="I91" s="29" t="s">
+      <c r="I91" s="28" t="s">
         <v>602</v>
       </c>
       <c r="J91" s="1">
@@ -11512,13 +11556,13 @@
       <c r="F92" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="G92" s="29" t="s">
+      <c r="G92" s="28" t="s">
         <v>606</v>
       </c>
-      <c r="H92" s="29" t="s">
+      <c r="H92" s="28" t="s">
         <v>607</v>
       </c>
-      <c r="I92" s="29" t="s">
+      <c r="I92" s="28" t="s">
         <v>608</v>
       </c>
       <c r="J92" s="1">
@@ -11582,13 +11626,13 @@
       <c r="F93" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G93" s="29" t="s">
+      <c r="G93" s="28" t="s">
         <v>612</v>
       </c>
-      <c r="H93" s="29" t="s">
+      <c r="H93" s="28" t="s">
         <v>613</v>
       </c>
-      <c r="I93" s="29" t="s">
+      <c r="I93" s="28" t="s">
         <v>614</v>
       </c>
       <c r="J93" s="1">
@@ -11652,13 +11696,13 @@
       <c r="F94" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="G94" s="29" t="s">
+      <c r="G94" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="H94" s="29" t="s">
+      <c r="H94" s="28" t="s">
         <v>618</v>
       </c>
-      <c r="I94" s="29" t="s">
+      <c r="I94" s="28" t="s">
         <v>619</v>
       </c>
       <c r="J94" s="1">
@@ -11722,13 +11766,13 @@
       <c r="F95" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="G95" s="29" t="s">
+      <c r="G95" s="28" t="s">
         <v>576</v>
       </c>
-      <c r="H95" s="29" t="s">
+      <c r="H95" s="28" t="s">
         <v>623</v>
       </c>
-      <c r="I95" s="29" t="s">
+      <c r="I95" s="28" t="s">
         <v>624</v>
       </c>
       <c r="J95" s="1">
@@ -11790,13 +11834,13 @@
       <c r="F96" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="G96" s="29" t="s">
+      <c r="G96" s="28" t="s">
         <v>582</v>
       </c>
-      <c r="H96" s="29" t="s">
+      <c r="H96" s="28" t="s">
         <v>628</v>
       </c>
-      <c r="I96" s="29" t="s">
+      <c r="I96" s="28" t="s">
         <v>629</v>
       </c>
       <c r="J96" s="1">
@@ -11854,13 +11898,13 @@
       <c r="F97" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="G97" s="29" t="s">
+      <c r="G97" s="28" t="s">
         <v>586</v>
       </c>
-      <c r="H97" s="29" t="s">
+      <c r="H97" s="28" t="s">
         <v>633</v>
       </c>
-      <c r="I97" s="29" t="s">
+      <c r="I97" s="28" t="s">
         <v>634</v>
       </c>
       <c r="J97" s="1">
@@ -11918,13 +11962,13 @@
       <c r="F98" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="G98" s="29" t="s">
+      <c r="G98" s="28" t="s">
         <v>638</v>
       </c>
-      <c r="H98" s="29" t="s">
+      <c r="H98" s="28" t="s">
         <v>639</v>
       </c>
-      <c r="I98" s="29" t="s">
+      <c r="I98" s="28" t="s">
         <v>640</v>
       </c>
       <c r="J98" s="1">
@@ -11982,13 +12026,13 @@
       <c r="F99" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="G99" s="29" t="s">
+      <c r="G99" s="28" t="s">
         <v>644</v>
       </c>
-      <c r="H99" s="29" t="s">
+      <c r="H99" s="28" t="s">
         <v>645</v>
       </c>
-      <c r="I99" s="29" t="s">
+      <c r="I99" s="28" t="s">
         <v>646</v>
       </c>
       <c r="J99" s="1">
@@ -12046,13 +12090,13 @@
       <c r="F100" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="G100" s="29" t="s">
+      <c r="G100" s="28" t="s">
         <v>650</v>
       </c>
-      <c r="H100" s="29" t="s">
+      <c r="H100" s="28" t="s">
         <v>651</v>
       </c>
-      <c r="I100" s="29" t="s">
+      <c r="I100" s="28" t="s">
         <v>652</v>
       </c>
       <c r="J100" s="1">
@@ -12110,13 +12154,13 @@
       <c r="F101" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="G101" s="29" t="s">
+      <c r="G101" s="28" t="s">
         <v>656</v>
       </c>
-      <c r="H101" s="29" t="s">
+      <c r="H101" s="28" t="s">
         <v>657</v>
       </c>
-      <c r="I101" s="29" t="s">
+      <c r="I101" s="28" t="s">
         <v>658</v>
       </c>
       <c r="J101" s="1">
@@ -12174,13 +12218,13 @@
       <c r="F102" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="G102" s="29" t="s">
+      <c r="G102" s="28" t="s">
         <v>662</v>
       </c>
-      <c r="H102" s="29" t="s">
+      <c r="H102" s="28" t="s">
         <v>663</v>
       </c>
-      <c r="I102" s="29" t="s">
+      <c r="I102" s="28" t="s">
         <v>664</v>
       </c>
       <c r="J102" s="1">
@@ -12238,13 +12282,13 @@
       <c r="F103" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="G103" s="29" t="s">
+      <c r="G103" s="28" t="s">
         <v>668</v>
       </c>
-      <c r="H103" s="29" t="s">
+      <c r="H103" s="28" t="s">
         <v>669</v>
       </c>
-      <c r="I103" s="29" t="s">
+      <c r="I103" s="28" t="s">
         <v>670</v>
       </c>
       <c r="J103" s="1">
@@ -12302,13 +12346,13 @@
       <c r="F104" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="G104" s="29" t="s">
+      <c r="G104" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="H104" s="29" t="s">
+      <c r="H104" s="28" t="s">
         <v>668</v>
       </c>
-      <c r="I104" s="29" t="s">
+      <c r="I104" s="28" t="s">
         <v>675</v>
       </c>
       <c r="J104" s="1">
@@ -12366,13 +12410,13 @@
       <c r="F105" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="G105" s="29" t="s">
+      <c r="G105" s="28" t="s">
         <v>679</v>
       </c>
-      <c r="H105" s="29" t="s">
+      <c r="H105" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="I105" s="29" t="s">
+      <c r="I105" s="28" t="s">
         <v>680</v>
       </c>
       <c r="J105" s="1">
@@ -12432,13 +12476,13 @@
       <c r="F106" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="G106" s="29" t="s">
+      <c r="G106" s="28" t="s">
         <v>684</v>
       </c>
-      <c r="H106" s="29" t="s">
+      <c r="H106" s="28" t="s">
         <v>685</v>
       </c>
-      <c r="I106" s="29" t="s">
+      <c r="I106" s="28" t="s">
         <v>686</v>
       </c>
       <c r="J106" s="1">
@@ -12502,13 +12546,13 @@
       <c r="F107" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="G107" s="29" t="s">
+      <c r="G107" s="28" t="s">
         <v>690</v>
       </c>
-      <c r="H107" s="29" t="s">
+      <c r="H107" s="28" t="s">
         <v>691</v>
       </c>
-      <c r="I107" s="29" t="s">
+      <c r="I107" s="28" t="s">
         <v>692</v>
       </c>
       <c r="J107" s="1">
@@ -12572,13 +12616,13 @@
       <c r="F108" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="G108" s="29" t="s">
+      <c r="G108" s="28" t="s">
         <v>696</v>
       </c>
-      <c r="H108" s="29" t="s">
+      <c r="H108" s="28" t="s">
         <v>697</v>
       </c>
-      <c r="I108" s="29" t="s">
+      <c r="I108" s="28" t="s">
         <v>698</v>
       </c>
       <c r="J108" s="1">
@@ -12642,13 +12686,13 @@
       <c r="F109" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="G109" s="29" t="s">
+      <c r="G109" s="28" t="s">
         <v>702</v>
       </c>
-      <c r="H109" s="29" t="s">
+      <c r="H109" s="28" t="s">
         <v>703</v>
       </c>
-      <c r="I109" s="29" t="s">
+      <c r="I109" s="28" t="s">
         <v>704</v>
       </c>
       <c r="J109" s="1">
@@ -12712,13 +12756,13 @@
       <c r="F110" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="G110" s="29" t="s">
+      <c r="G110" s="28" t="s">
         <v>708</v>
       </c>
-      <c r="H110" s="29" t="s">
+      <c r="H110" s="28" t="s">
         <v>709</v>
       </c>
-      <c r="I110" s="29" t="s">
+      <c r="I110" s="28" t="s">
         <v>710</v>
       </c>
       <c r="J110" s="1">
@@ -12782,13 +12826,13 @@
       <c r="F111" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="G111" s="30" t="s">
+      <c r="G111" s="29" t="s">
         <v>714</v>
       </c>
-      <c r="H111" s="31" t="s">
+      <c r="H111" s="30" t="s">
         <v>714</v>
       </c>
-      <c r="I111" s="32" t="s">
+      <c r="I111" s="31" t="s">
         <v>715</v>
       </c>
       <c r="J111" s="1">
@@ -12821,10 +12865,10 @@
       <c r="T111" s="10">
         <v>90</v>
       </c>
-      <c r="U111" s="29" t="s">
+      <c r="U111" s="28" t="s">
         <v>716</v>
       </c>
-      <c r="V111" s="29" t="s">
+      <c r="V111" s="28" t="s">
         <v>716</v>
       </c>
       <c r="Y111" s="10"/>
@@ -12846,13 +12890,13 @@
       <c r="F112" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="G112" s="33" t="s">
+      <c r="G112" s="32" t="s">
         <v>720</v>
       </c>
-      <c r="H112" s="29" t="s">
+      <c r="H112" s="28" t="s">
         <v>720</v>
       </c>
-      <c r="I112" s="34" t="s">
+      <c r="I112" s="33" t="s">
         <v>721</v>
       </c>
       <c r="J112" s="1">
@@ -12890,10 +12934,10 @@
       <c r="T112" s="10">
         <v>90</v>
       </c>
-      <c r="U112" s="29" t="s">
+      <c r="U112" s="28" t="s">
         <v>722</v>
       </c>
-      <c r="V112" s="29" t="s">
+      <c r="V112" s="28" t="s">
         <v>722</v>
       </c>
       <c r="Y112" s="10"/>
@@ -12915,13 +12959,13 @@
       <c r="F113" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="G113" s="33" t="s">
+      <c r="G113" s="32" t="s">
         <v>726</v>
       </c>
-      <c r="H113" s="29" t="s">
+      <c r="H113" s="28" t="s">
         <v>726</v>
       </c>
-      <c r="I113" s="34" t="s">
+      <c r="I113" s="33" t="s">
         <v>727</v>
       </c>
       <c r="J113" s="1">
@@ -12959,10 +13003,10 @@
       <c r="T113" s="10">
         <v>90</v>
       </c>
-      <c r="U113" s="29" t="s">
+      <c r="U113" s="28" t="s">
         <v>728</v>
       </c>
-      <c r="V113" s="29" t="s">
+      <c r="V113" s="28" t="s">
         <v>728</v>
       </c>
       <c r="Y113" s="10"/>
@@ -12984,13 +13028,13 @@
       <c r="F114" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="G114" s="33" t="s">
+      <c r="G114" s="32" t="s">
         <v>732</v>
       </c>
-      <c r="H114" s="29" t="s">
+      <c r="H114" s="28" t="s">
         <v>732</v>
       </c>
-      <c r="I114" s="34" t="s">
+      <c r="I114" s="33" t="s">
         <v>733</v>
       </c>
       <c r="J114" s="1">
@@ -13028,10 +13072,10 @@
       <c r="T114" s="10">
         <v>90</v>
       </c>
-      <c r="U114" s="29" t="s">
+      <c r="U114" s="28" t="s">
         <v>734</v>
       </c>
-      <c r="V114" s="29" t="s">
+      <c r="V114" s="28" t="s">
         <v>734</v>
       </c>
       <c r="Y114" s="10"/>
@@ -13053,13 +13097,13 @@
       <c r="F115" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="G115" s="33" t="s">
+      <c r="G115" s="32" t="s">
         <v>738</v>
       </c>
-      <c r="H115" s="29" t="s">
+      <c r="H115" s="28" t="s">
         <v>738</v>
       </c>
-      <c r="I115" s="34" t="s">
+      <c r="I115" s="33" t="s">
         <v>739</v>
       </c>
       <c r="J115" s="1">
@@ -13097,10 +13141,10 @@
       <c r="T115" s="10">
         <v>90</v>
       </c>
-      <c r="U115" s="29" t="s">
+      <c r="U115" s="28" t="s">
         <v>740</v>
       </c>
-      <c r="V115" s="29" t="s">
+      <c r="V115" s="28" t="s">
         <v>740</v>
       </c>
       <c r="Y115" s="10"/>
@@ -13122,13 +13166,13 @@
       <c r="F116" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="G116" s="33" t="s">
+      <c r="G116" s="32" t="s">
         <v>744</v>
       </c>
-      <c r="H116" s="29" t="s">
+      <c r="H116" s="28" t="s">
         <v>744</v>
       </c>
-      <c r="I116" s="34" t="s">
+      <c r="I116" s="33" t="s">
         <v>745</v>
       </c>
       <c r="J116" s="1">
@@ -13166,10 +13210,10 @@
       <c r="T116" s="10">
         <v>90</v>
       </c>
-      <c r="U116" s="29" t="s">
+      <c r="U116" s="28" t="s">
         <v>746</v>
       </c>
-      <c r="V116" s="29" t="s">
+      <c r="V116" s="28" t="s">
         <v>746</v>
       </c>
       <c r="W116" s="10"/>
@@ -13193,13 +13237,13 @@
       <c r="F117" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="G117" s="33" t="s">
+      <c r="G117" s="32" t="s">
         <v>750</v>
       </c>
-      <c r="H117" s="29" t="s">
+      <c r="H117" s="28" t="s">
         <v>750</v>
       </c>
-      <c r="I117" s="34" t="s">
+      <c r="I117" s="33" t="s">
         <v>751</v>
       </c>
       <c r="J117" s="1">
@@ -13237,10 +13281,10 @@
       <c r="T117" s="10">
         <v>90</v>
       </c>
-      <c r="U117" s="29" t="s">
+      <c r="U117" s="28" t="s">
         <v>752</v>
       </c>
-      <c r="V117" s="29" t="s">
+      <c r="V117" s="28" t="s">
         <v>752</v>
       </c>
       <c r="W117" s="10"/>
@@ -13264,13 +13308,13 @@
       <c r="F118" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="G118" s="33" t="s">
+      <c r="G118" s="32" t="s">
         <v>756</v>
       </c>
-      <c r="H118" s="29" t="s">
+      <c r="H118" s="28" t="s">
         <v>756</v>
       </c>
-      <c r="I118" s="34" t="s">
+      <c r="I118" s="33" t="s">
         <v>757</v>
       </c>
       <c r="J118" s="1">
@@ -13308,10 +13352,10 @@
       <c r="T118" s="10">
         <v>90</v>
       </c>
-      <c r="U118" s="29" t="s">
+      <c r="U118" s="28" t="s">
         <v>758</v>
       </c>
-      <c r="V118" s="29" t="s">
+      <c r="V118" s="28" t="s">
         <v>758</v>
       </c>
       <c r="W118" s="10"/>
@@ -13335,13 +13379,13 @@
       <c r="F119" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="G119" s="33" t="s">
+      <c r="G119" s="32" t="s">
         <v>762</v>
       </c>
-      <c r="H119" s="29" t="s">
+      <c r="H119" s="28" t="s">
         <v>762</v>
       </c>
-      <c r="I119" s="34" t="s">
+      <c r="I119" s="33" t="s">
         <v>763</v>
       </c>
       <c r="J119" s="1">
@@ -13379,10 +13423,10 @@
       <c r="T119" s="10">
         <v>90</v>
       </c>
-      <c r="U119" s="29" t="s">
+      <c r="U119" s="28" t="s">
         <v>764</v>
       </c>
-      <c r="V119" s="29" t="s">
+      <c r="V119" s="28" t="s">
         <v>764</v>
       </c>
       <c r="W119" s="10"/>
@@ -13406,13 +13450,13 @@
       <c r="F120" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="G120" s="33" t="s">
+      <c r="G120" s="32" t="s">
         <v>768</v>
       </c>
-      <c r="H120" s="29" t="s">
+      <c r="H120" s="28" t="s">
         <v>768</v>
       </c>
-      <c r="I120" s="34" t="s">
+      <c r="I120" s="33" t="s">
         <v>769</v>
       </c>
       <c r="J120" s="1">
@@ -13450,10 +13494,10 @@
       <c r="T120" s="10">
         <v>90</v>
       </c>
-      <c r="U120" s="29" t="s">
+      <c r="U120" s="28" t="s">
         <v>770</v>
       </c>
-      <c r="V120" s="29" t="s">
+      <c r="V120" s="28" t="s">
         <v>770</v>
       </c>
       <c r="W120" s="10"/>
@@ -13477,13 +13521,13 @@
       <c r="F121" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="G121" s="33" t="s">
+      <c r="G121" s="32" t="s">
         <v>715</v>
       </c>
-      <c r="H121" s="29" t="s">
+      <c r="H121" s="28" t="s">
         <v>715</v>
       </c>
-      <c r="I121" s="34" t="s">
+      <c r="I121" s="33" t="s">
         <v>774</v>
       </c>
       <c r="J121" s="1">
@@ -13521,10 +13565,10 @@
       <c r="T121" s="10">
         <v>90</v>
       </c>
-      <c r="U121" s="29" t="s">
+      <c r="U121" s="28" t="s">
         <v>775</v>
       </c>
-      <c r="V121" s="29" t="s">
+      <c r="V121" s="28" t="s">
         <v>775</v>
       </c>
       <c r="W121" s="10"/>
@@ -13548,13 +13592,13 @@
       <c r="F122" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="G122" s="33" t="s">
+      <c r="G122" s="32" t="s">
         <v>779</v>
       </c>
-      <c r="H122" s="29" t="s">
+      <c r="H122" s="28" t="s">
         <v>779</v>
       </c>
-      <c r="I122" s="34" t="s">
+      <c r="I122" s="33" t="s">
         <v>780</v>
       </c>
       <c r="J122" s="1">
@@ -13593,10 +13637,10 @@
       <c r="T122" s="10">
         <v>90</v>
       </c>
-      <c r="U122" s="29" t="s">
+      <c r="U122" s="28" t="s">
         <v>781</v>
       </c>
-      <c r="V122" s="29" t="s">
+      <c r="V122" s="28" t="s">
         <v>781</v>
       </c>
       <c r="W122" s="10"/>
@@ -13620,13 +13664,13 @@
       <c r="F123" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="G123" s="33" t="s">
+      <c r="G123" s="32" t="s">
         <v>785</v>
       </c>
-      <c r="H123" s="29" t="s">
+      <c r="H123" s="28" t="s">
         <v>785</v>
       </c>
-      <c r="I123" s="34" t="s">
+      <c r="I123" s="33" t="s">
         <v>786</v>
       </c>
       <c r="J123" s="1">
@@ -13665,10 +13709,10 @@
       <c r="T123" s="10">
         <v>90</v>
       </c>
-      <c r="U123" s="29" t="s">
+      <c r="U123" s="28" t="s">
         <v>787</v>
       </c>
-      <c r="V123" s="29" t="s">
+      <c r="V123" s="28" t="s">
         <v>787</v>
       </c>
       <c r="W123" s="10"/>
@@ -13692,13 +13736,13 @@
       <c r="F124" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="G124" s="33" t="s">
+      <c r="G124" s="32" t="s">
         <v>791</v>
       </c>
-      <c r="H124" s="29" t="s">
+      <c r="H124" s="28" t="s">
         <v>791</v>
       </c>
-      <c r="I124" s="34" t="s">
+      <c r="I124" s="33" t="s">
         <v>792</v>
       </c>
       <c r="J124" s="1">
@@ -13737,10 +13781,10 @@
       <c r="T124" s="10">
         <v>90</v>
       </c>
-      <c r="U124" s="29" t="s">
+      <c r="U124" s="28" t="s">
         <v>793</v>
       </c>
-      <c r="V124" s="29" t="s">
+      <c r="V124" s="28" t="s">
         <v>793</v>
       </c>
       <c r="W124" s="10"/>
@@ -13764,13 +13808,13 @@
       <c r="F125" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="G125" s="33" t="s">
+      <c r="G125" s="32" t="s">
         <v>797</v>
       </c>
-      <c r="H125" s="29" t="s">
+      <c r="H125" s="28" t="s">
         <v>797</v>
       </c>
-      <c r="I125" s="34" t="s">
+      <c r="I125" s="33" t="s">
         <v>798</v>
       </c>
       <c r="J125" s="1">
@@ -13809,10 +13853,10 @@
       <c r="T125" s="10">
         <v>90</v>
       </c>
-      <c r="U125" s="29" t="s">
+      <c r="U125" s="28" t="s">
         <v>799</v>
       </c>
-      <c r="V125" s="29" t="s">
+      <c r="V125" s="28" t="s">
         <v>799</v>
       </c>
       <c r="W125" s="10"/>
@@ -13836,13 +13880,13 @@
       <c r="F126" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="G126" s="33" t="s">
+      <c r="G126" s="32" t="s">
         <v>803</v>
       </c>
-      <c r="H126" s="29" t="s">
+      <c r="H126" s="28" t="s">
         <v>803</v>
       </c>
-      <c r="I126" s="34" t="s">
+      <c r="I126" s="33" t="s">
         <v>804</v>
       </c>
       <c r="J126" s="1">
@@ -13881,10 +13925,10 @@
       <c r="T126" s="10">
         <v>90</v>
       </c>
-      <c r="U126" s="29" t="s">
+      <c r="U126" s="28" t="s">
         <v>805</v>
       </c>
-      <c r="V126" s="29" t="s">
+      <c r="V126" s="28" t="s">
         <v>805</v>
       </c>
       <c r="W126" s="10"/>
@@ -13908,13 +13952,13 @@
       <c r="F127" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="G127" s="33" t="s">
+      <c r="G127" s="32" t="s">
         <v>809</v>
       </c>
-      <c r="H127" s="29" t="s">
+      <c r="H127" s="28" t="s">
         <v>809</v>
       </c>
-      <c r="I127" s="34" t="s">
+      <c r="I127" s="33" t="s">
         <v>810</v>
       </c>
       <c r="J127" s="1">
@@ -13953,10 +13997,10 @@
       <c r="T127" s="10">
         <v>90</v>
       </c>
-      <c r="U127" s="29" t="s">
+      <c r="U127" s="28" t="s">
         <v>811</v>
       </c>
-      <c r="V127" s="29" t="s">
+      <c r="V127" s="28" t="s">
         <v>811</v>
       </c>
       <c r="W127" s="10"/>
@@ -13980,13 +14024,13 @@
       <c r="F128" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="G128" s="33" t="s">
+      <c r="G128" s="32" t="s">
         <v>815</v>
       </c>
-      <c r="H128" s="29" t="s">
+      <c r="H128" s="28" t="s">
         <v>815</v>
       </c>
-      <c r="I128" s="34" t="s">
+      <c r="I128" s="33" t="s">
         <v>816</v>
       </c>
       <c r="J128" s="1">
@@ -14025,10 +14069,10 @@
       <c r="T128" s="10">
         <v>90</v>
       </c>
-      <c r="U128" s="29" t="s">
+      <c r="U128" s="28" t="s">
         <v>817</v>
       </c>
-      <c r="V128" s="29" t="s">
+      <c r="V128" s="28" t="s">
         <v>817</v>
       </c>
       <c r="W128" s="10"/>
@@ -14052,13 +14096,13 @@
       <c r="F129" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="G129" s="33" t="s">
+      <c r="G129" s="32" t="s">
         <v>821</v>
       </c>
-      <c r="H129" s="29" t="s">
+      <c r="H129" s="28" t="s">
         <v>821</v>
       </c>
-      <c r="I129" s="34" t="s">
+      <c r="I129" s="33" t="s">
         <v>822</v>
       </c>
       <c r="J129" s="1">
@@ -14097,10 +14141,10 @@
       <c r="T129" s="10">
         <v>90</v>
       </c>
-      <c r="U129" s="29" t="s">
+      <c r="U129" s="28" t="s">
         <v>823</v>
       </c>
-      <c r="V129" s="29" t="s">
+      <c r="V129" s="28" t="s">
         <v>823</v>
       </c>
       <c r="W129" s="10"/>
@@ -14124,13 +14168,13 @@
       <c r="F130" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="G130" s="33" t="s">
+      <c r="G130" s="32" t="s">
         <v>827</v>
       </c>
-      <c r="H130" s="29" t="s">
+      <c r="H130" s="28" t="s">
         <v>827</v>
       </c>
-      <c r="I130" s="34" t="s">
+      <c r="I130" s="33" t="s">
         <v>828</v>
       </c>
       <c r="J130" s="1">
@@ -14169,10 +14213,10 @@
       <c r="T130" s="10">
         <v>90</v>
       </c>
-      <c r="U130" s="29" t="s">
+      <c r="U130" s="28" t="s">
         <v>829</v>
       </c>
-      <c r="V130" s="29" t="s">
+      <c r="V130" s="28" t="s">
         <v>829</v>
       </c>
       <c r="W130" s="10"/>
@@ -14194,13 +14238,13 @@
       <c r="F131" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="G131" s="33" t="s">
+      <c r="G131" s="32" t="s">
         <v>833</v>
       </c>
-      <c r="H131" s="29" t="s">
+      <c r="H131" s="28" t="s">
         <v>833</v>
       </c>
-      <c r="I131" s="34" t="s">
+      <c r="I131" s="33" t="s">
         <v>834</v>
       </c>
       <c r="J131" s="1">
@@ -14240,10 +14284,10 @@
       <c r="T131" s="10">
         <v>92</v>
       </c>
-      <c r="U131" s="29" t="s">
+      <c r="U131" s="28" t="s">
         <v>835</v>
       </c>
-      <c r="V131" s="29" t="s">
+      <c r="V131" s="28" t="s">
         <v>835</v>
       </c>
     </row>
@@ -14260,13 +14304,13 @@
       <c r="F132" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="G132" s="33" t="s">
+      <c r="G132" s="32" t="s">
         <v>839</v>
       </c>
-      <c r="H132" s="29" t="s">
+      <c r="H132" s="28" t="s">
         <v>839</v>
       </c>
-      <c r="I132" s="34" t="s">
+      <c r="I132" s="33" t="s">
         <v>840</v>
       </c>
       <c r="J132" s="1">
@@ -14306,10 +14350,10 @@
       <c r="T132" s="10">
         <v>94</v>
       </c>
-      <c r="U132" s="29" t="s">
+      <c r="U132" s="28" t="s">
         <v>841</v>
       </c>
-      <c r="V132" s="29" t="s">
+      <c r="V132" s="28" t="s">
         <v>841</v>
       </c>
     </row>
@@ -14326,13 +14370,13 @@
       <c r="F133" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="G133" s="33" t="s">
+      <c r="G133" s="32" t="s">
         <v>845</v>
       </c>
-      <c r="H133" s="29" t="s">
+      <c r="H133" s="28" t="s">
         <v>845</v>
       </c>
-      <c r="I133" s="34" t="s">
+      <c r="I133" s="33" t="s">
         <v>846</v>
       </c>
       <c r="J133" s="1">
@@ -14372,10 +14416,10 @@
       <c r="T133" s="10">
         <v>96</v>
       </c>
-      <c r="U133" s="29" t="s">
+      <c r="U133" s="28" t="s">
         <v>847</v>
       </c>
-      <c r="V133" s="29" t="s">
+      <c r="V133" s="28" t="s">
         <v>847</v>
       </c>
     </row>
@@ -14392,13 +14436,13 @@
       <c r="F134" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="G134" s="33" t="s">
+      <c r="G134" s="32" t="s">
         <v>851</v>
       </c>
-      <c r="H134" s="29" t="s">
+      <c r="H134" s="28" t="s">
         <v>851</v>
       </c>
-      <c r="I134" s="34" t="s">
+      <c r="I134" s="33" t="s">
         <v>852</v>
       </c>
       <c r="J134" s="1">
@@ -14438,10 +14482,10 @@
       <c r="T134" s="10">
         <v>98</v>
       </c>
-      <c r="U134" s="29" t="s">
+      <c r="U134" s="28" t="s">
         <v>853</v>
       </c>
-      <c r="V134" s="29" t="s">
+      <c r="V134" s="28" t="s">
         <v>853</v>
       </c>
     </row>
@@ -14458,13 +14502,13 @@
       <c r="F135" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="G135" s="33" t="s">
+      <c r="G135" s="32" t="s">
         <v>857</v>
       </c>
-      <c r="H135" s="29" t="s">
+      <c r="H135" s="28" t="s">
         <v>857</v>
       </c>
-      <c r="I135" s="34" t="s">
+      <c r="I135" s="33" t="s">
         <v>858</v>
       </c>
       <c r="J135" s="1">
@@ -14504,10 +14548,10 @@
       <c r="T135" s="10">
         <v>99</v>
       </c>
-      <c r="U135" s="29" t="s">
+      <c r="U135" s="28" t="s">
         <v>859</v>
       </c>
-      <c r="V135" s="29" t="s">
+      <c r="V135" s="28" t="s">
         <v>859</v>
       </c>
     </row>
@@ -14524,13 +14568,13 @@
       <c r="F136" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="G136" s="33" t="s">
+      <c r="G136" s="32" t="s">
         <v>863</v>
       </c>
-      <c r="H136" s="29" t="s">
+      <c r="H136" s="28" t="s">
         <v>863</v>
       </c>
-      <c r="I136" s="34" t="s">
+      <c r="I136" s="33" t="s">
         <v>864</v>
       </c>
       <c r="J136" s="1">
@@ -14570,10 +14614,10 @@
       <c r="T136" s="10">
         <v>99.2</v>
       </c>
-      <c r="U136" s="29" t="s">
+      <c r="U136" s="28" t="s">
         <v>865</v>
       </c>
-      <c r="V136" s="29" t="s">
+      <c r="V136" s="28" t="s">
         <v>865</v>
       </c>
     </row>
@@ -14590,13 +14634,13 @@
       <c r="F137" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="G137" s="33" t="s">
+      <c r="G137" s="32" t="s">
         <v>869</v>
       </c>
-      <c r="H137" s="29" t="s">
+      <c r="H137" s="28" t="s">
         <v>869</v>
       </c>
-      <c r="I137" s="34" t="s">
+      <c r="I137" s="33" t="s">
         <v>870</v>
       </c>
       <c r="J137" s="1">
@@ -14636,10 +14680,10 @@
       <c r="T137" s="10">
         <v>99.4</v>
       </c>
-      <c r="U137" s="29" t="s">
+      <c r="U137" s="28" t="s">
         <v>871</v>
       </c>
-      <c r="V137" s="29" t="s">
+      <c r="V137" s="28" t="s">
         <v>871</v>
       </c>
     </row>
@@ -14656,13 +14700,13 @@
       <c r="F138" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="G138" s="33" t="s">
+      <c r="G138" s="32" t="s">
         <v>875</v>
       </c>
-      <c r="H138" s="29" t="s">
+      <c r="H138" s="28" t="s">
         <v>875</v>
       </c>
-      <c r="I138" s="34" t="s">
+      <c r="I138" s="33" t="s">
         <v>876</v>
       </c>
       <c r="J138" s="1">
@@ -14702,10 +14746,10 @@
       <c r="T138" s="10">
         <v>99.6</v>
       </c>
-      <c r="U138" s="29" t="s">
+      <c r="U138" s="28" t="s">
         <v>877</v>
       </c>
-      <c r="V138" s="29" t="s">
+      <c r="V138" s="28" t="s">
         <v>877</v>
       </c>
     </row>
@@ -14722,13 +14766,13 @@
       <c r="F139" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="G139" s="33" t="s">
+      <c r="G139" s="32" t="s">
         <v>881</v>
       </c>
-      <c r="H139" s="29" t="s">
+      <c r="H139" s="28" t="s">
         <v>881</v>
       </c>
-      <c r="I139" s="34" t="s">
+      <c r="I139" s="33" t="s">
         <v>882</v>
       </c>
       <c r="J139" s="1">
@@ -14768,10 +14812,10 @@
       <c r="T139" s="10">
         <v>99.8</v>
       </c>
-      <c r="U139" s="29" t="s">
+      <c r="U139" s="28" t="s">
         <v>883</v>
       </c>
-      <c r="V139" s="29" t="s">
+      <c r="V139" s="28" t="s">
         <v>883</v>
       </c>
     </row>
@@ -14788,13 +14832,13 @@
       <c r="F140" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="G140" s="33" t="s">
+      <c r="G140" s="32" t="s">
         <v>887</v>
       </c>
-      <c r="H140" s="29" t="s">
+      <c r="H140" s="28" t="s">
         <v>887</v>
       </c>
-      <c r="I140" s="34" t="s">
+      <c r="I140" s="33" t="s">
         <v>888</v>
       </c>
       <c r="J140" s="1">
@@ -14834,10 +14878,10 @@
       <c r="T140" s="10">
         <v>99.9</v>
       </c>
-      <c r="U140" s="29" t="s">
+      <c r="U140" s="28" t="s">
         <v>889</v>
       </c>
-      <c r="V140" s="29" t="s">
+      <c r="V140" s="28" t="s">
         <v>889</v>
       </c>
     </row>
@@ -14856,13 +14900,13 @@
       <c r="F141" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="G141" s="33" t="s">
+      <c r="G141" s="32" t="s">
         <v>893</v>
       </c>
-      <c r="H141" s="29" t="s">
+      <c r="H141" s="28" t="s">
         <v>893</v>
       </c>
-      <c r="I141" s="34" t="s">
+      <c r="I141" s="33" t="s">
         <v>894</v>
       </c>
       <c r="J141" s="1">
@@ -14901,10 +14945,10 @@
       <c r="T141" s="10">
         <v>99.92</v>
       </c>
-      <c r="U141" s="29" t="s">
+      <c r="U141" s="28" t="s">
         <v>895</v>
       </c>
-      <c r="V141" s="29" t="s">
+      <c r="V141" s="28" t="s">
         <v>895</v>
       </c>
       <c r="W141" s="10"/>
@@ -14928,13 +14972,13 @@
       <c r="F142" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="G142" s="33" t="s">
+      <c r="G142" s="32" t="s">
         <v>899</v>
       </c>
-      <c r="H142" s="29" t="s">
+      <c r="H142" s="28" t="s">
         <v>899</v>
       </c>
-      <c r="I142" s="34" t="s">
+      <c r="I142" s="33" t="s">
         <v>900</v>
       </c>
       <c r="J142" s="1">
@@ -14973,10 +15017,10 @@
       <c r="T142" s="10">
         <v>99.94</v>
       </c>
-      <c r="U142" s="29" t="s">
+      <c r="U142" s="28" t="s">
         <v>901</v>
       </c>
-      <c r="V142" s="29" t="s">
+      <c r="V142" s="28" t="s">
         <v>901</v>
       </c>
       <c r="W142" s="10"/>
@@ -15000,13 +15044,13 @@
       <c r="F143" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="G143" s="33" t="s">
+      <c r="G143" s="32" t="s">
         <v>905</v>
       </c>
-      <c r="H143" s="29" t="s">
+      <c r="H143" s="28" t="s">
         <v>905</v>
       </c>
-      <c r="I143" s="34" t="s">
+      <c r="I143" s="33" t="s">
         <v>906</v>
       </c>
       <c r="J143" s="1">
@@ -15045,10 +15089,10 @@
       <c r="T143" s="10">
         <v>99.96</v>
       </c>
-      <c r="U143" s="29" t="s">
+      <c r="U143" s="28" t="s">
         <v>907</v>
       </c>
-      <c r="V143" s="29" t="s">
+      <c r="V143" s="28" t="s">
         <v>907</v>
       </c>
       <c r="W143" s="10"/>
@@ -15072,13 +15116,13 @@
       <c r="F144" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="G144" s="33" t="s">
+      <c r="G144" s="32" t="s">
         <v>911</v>
       </c>
-      <c r="H144" s="29" t="s">
+      <c r="H144" s="28" t="s">
         <v>911</v>
       </c>
-      <c r="I144" s="34" t="s">
+      <c r="I144" s="33" t="s">
         <v>912</v>
       </c>
       <c r="J144" s="1">
@@ -15117,10 +15161,10 @@
       <c r="T144" s="10">
         <v>99.98</v>
       </c>
-      <c r="U144" s="29" t="s">
+      <c r="U144" s="28" t="s">
         <v>913</v>
       </c>
-      <c r="V144" s="29" t="s">
+      <c r="V144" s="28" t="s">
         <v>913</v>
       </c>
       <c r="W144" s="10"/>
@@ -15189,10 +15233,10 @@
       <c r="T145" s="10">
         <v>99.99</v>
       </c>
-      <c r="U145" s="29" t="s">
+      <c r="U145" s="28" t="s">
         <v>919</v>
       </c>
-      <c r="V145" s="29" t="s">
+      <c r="V145" s="28" t="s">
         <v>919</v>
       </c>
       <c r="W145" s="10"/>
@@ -15261,10 +15305,10 @@
       <c r="T146" s="18">
         <v>99.99</v>
       </c>
-      <c r="U146" s="35" t="s">
+      <c r="U146" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="V146" s="35" t="s">
+      <c r="V146" s="34" t="s">
         <v>927</v>
       </c>
       <c r="Y146" s="18"/>
@@ -15332,10 +15376,10 @@
       <c r="T147" s="10">
         <v>99.99</v>
       </c>
-      <c r="U147" s="29" t="s">
+      <c r="U147" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="V147" s="29" t="s">
+      <c r="V147" s="28" t="s">
         <v>935</v>
       </c>
       <c r="Y147" s="10"/>
@@ -15403,10 +15447,10 @@
       <c r="T148" s="10">
         <v>99.99</v>
       </c>
-      <c r="U148" s="29" t="s">
+      <c r="U148" s="28" t="s">
         <v>943</v>
       </c>
-      <c r="V148" s="29" t="s">
+      <c r="V148" s="28" t="s">
         <v>943</v>
       </c>
       <c r="Y148" s="10"/>
@@ -15474,10 +15518,10 @@
       <c r="T149" s="10">
         <v>99.99</v>
       </c>
-      <c r="U149" s="29" t="s">
+      <c r="U149" s="28" t="s">
         <v>951</v>
       </c>
-      <c r="V149" s="29" t="s">
+      <c r="V149" s="28" t="s">
         <v>951</v>
       </c>
       <c r="Y149" s="10"/>
@@ -15545,10 +15589,10 @@
       <c r="T150" s="10">
         <v>99.99</v>
       </c>
-      <c r="U150" s="29" t="s">
+      <c r="U150" s="28" t="s">
         <v>959</v>
       </c>
-      <c r="V150" s="29" t="s">
+      <c r="V150" s="28" t="s">
         <v>959</v>
       </c>
       <c r="Y150" s="10"/>
@@ -15615,10 +15659,10 @@
       <c r="T151" s="10">
         <v>99.99</v>
       </c>
-      <c r="U151" s="29" t="s">
+      <c r="U151" s="28" t="s">
         <v>968</v>
       </c>
-      <c r="V151" s="29" t="s">
+      <c r="V151" s="28" t="s">
         <v>968</v>
       </c>
       <c r="W151" s="10"/>
@@ -15687,10 +15731,10 @@
       <c r="T152" s="10">
         <v>99.99</v>
       </c>
-      <c r="U152" s="29" t="s">
+      <c r="U152" s="28" t="s">
         <v>977</v>
       </c>
-      <c r="V152" s="29" t="s">
+      <c r="V152" s="28" t="s">
         <v>977</v>
       </c>
       <c r="W152" s="10"/>
@@ -15759,10 +15803,10 @@
       <c r="T153" s="10">
         <v>99.99</v>
       </c>
-      <c r="U153" s="29" t="s">
+      <c r="U153" s="28" t="s">
         <v>986</v>
       </c>
-      <c r="V153" s="29" t="s">
+      <c r="V153" s="28" t="s">
         <v>986</v>
       </c>
       <c r="W153" s="10"/>
@@ -15831,10 +15875,10 @@
       <c r="T154" s="10">
         <v>99.99</v>
       </c>
-      <c r="U154" s="29" t="s">
+      <c r="U154" s="28" t="s">
         <v>995</v>
       </c>
-      <c r="V154" s="29" t="s">
+      <c r="V154" s="28" t="s">
         <v>995</v>
       </c>
       <c r="W154" s="10"/>
@@ -15903,10 +15947,10 @@
       <c r="T155" s="10">
         <v>99.99</v>
       </c>
-      <c r="U155" s="29" t="s">
+      <c r="U155" s="28" t="s">
         <v>1004</v>
       </c>
-      <c r="V155" s="29" t="s">
+      <c r="V155" s="28" t="s">
         <v>1004</v>
       </c>
       <c r="W155" s="10"/>
@@ -15975,10 +16019,10 @@
       <c r="T156" s="10">
         <v>99.99</v>
       </c>
-      <c r="U156" s="29" t="s">
+      <c r="U156" s="28" t="s">
         <v>1013</v>
       </c>
-      <c r="V156" s="29" t="s">
+      <c r="V156" s="28" t="s">
         <v>1013</v>
       </c>
       <c r="W156" s="10"/>
@@ -16047,10 +16091,10 @@
       <c r="T157" s="10">
         <v>99.99</v>
       </c>
-      <c r="U157" s="29" t="s">
+      <c r="U157" s="28" t="s">
         <v>1022</v>
       </c>
-      <c r="V157" s="29" t="s">
+      <c r="V157" s="28" t="s">
         <v>1022</v>
       </c>
       <c r="W157" s="10"/>
@@ -16119,10 +16163,10 @@
       <c r="T158" s="10">
         <v>99.99</v>
       </c>
-      <c r="U158" s="29" t="s">
+      <c r="U158" s="28" t="s">
         <v>1031</v>
       </c>
-      <c r="V158" s="29" t="s">
+      <c r="V158" s="28" t="s">
         <v>1031</v>
       </c>
       <c r="W158" s="10"/>
@@ -16191,10 +16235,10 @@
       <c r="T159" s="10">
         <v>99.99</v>
       </c>
-      <c r="U159" s="29" t="s">
+      <c r="U159" s="28" t="s">
         <v>1040</v>
       </c>
-      <c r="V159" s="29" t="s">
+      <c r="V159" s="28" t="s">
         <v>1040</v>
       </c>
       <c r="W159" s="10"/>
@@ -16263,10 +16307,10 @@
       <c r="T160" s="10">
         <v>99.99</v>
       </c>
-      <c r="U160" s="29" t="s">
+      <c r="U160" s="28" t="s">
         <v>1049</v>
       </c>
-      <c r="V160" s="29" t="s">
+      <c r="V160" s="28" t="s">
         <v>1049</v>
       </c>
       <c r="W160" s="10"/>
@@ -16335,10 +16379,10 @@
       <c r="T161" s="10">
         <v>99.99</v>
       </c>
-      <c r="U161" s="29" t="s">
+      <c r="U161" s="28" t="s">
         <v>1058</v>
       </c>
-      <c r="V161" s="29" t="s">
+      <c r="V161" s="28" t="s">
         <v>1058</v>
       </c>
       <c r="W161" s="10"/>
@@ -16407,10 +16451,10 @@
       <c r="T162" s="10">
         <v>99.99</v>
       </c>
-      <c r="U162" s="29" t="s">
+      <c r="U162" s="28" t="s">
         <v>1067</v>
       </c>
-      <c r="V162" s="29" t="s">
+      <c r="V162" s="28" t="s">
         <v>1067</v>
       </c>
       <c r="W162" s="10"/>
@@ -16479,10 +16523,10 @@
       <c r="T163" s="10">
         <v>99.99</v>
       </c>
-      <c r="U163" s="29" t="s">
+      <c r="U163" s="28" t="s">
         <v>1076</v>
       </c>
-      <c r="V163" s="29" t="s">
+      <c r="V163" s="28" t="s">
         <v>1076</v>
       </c>
       <c r="W163" s="10"/>
@@ -16552,10 +16596,10 @@
       <c r="T164" s="21">
         <v>99.99</v>
       </c>
-      <c r="U164" s="36" t="s">
+      <c r="U164" s="35" t="s">
         <v>1085</v>
       </c>
-      <c r="V164" s="36" t="s">
+      <c r="V164" s="35" t="s">
         <v>1085</v>
       </c>
       <c r="W164" s="21"/>
@@ -16579,7 +16623,7 @@
       <c r="F165" s="4" t="s">
         <v>1088</v>
       </c>
-      <c r="G165" s="37" t="s">
+      <c r="G165" s="36" t="s">
         <v>1089</v>
       </c>
       <c r="H165" s="4" t="s">
@@ -16625,10 +16669,10 @@
       <c r="T165" s="8">
         <v>99.99</v>
       </c>
-      <c r="U165" s="38" t="s">
+      <c r="U165" s="37" t="s">
         <v>1094</v>
       </c>
-      <c r="V165" s="38" t="s">
+      <c r="V165" s="37" t="s">
         <v>1094</v>
       </c>
       <c r="W165" s="8"/>
@@ -16650,20 +16694,20 @@
       <c r="F166" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="G166" s="39" t="s">
+      <c r="G166" s="38" t="s">
         <v>1098</v>
       </c>
-      <c r="H166" s="39" t="s">
+      <c r="H166" s="38" t="s">
         <v>1099</v>
       </c>
-      <c r="I166" s="39" t="s">
+      <c r="I166" s="38" t="s">
         <v>1100</v>
       </c>
-      <c r="J166" s="39" t="s">
+      <c r="J166" s="38" t="s">
         <v>1101</v>
       </c>
       <c r="K166" s="1"/>
-      <c r="L166" s="39" t="s">
+      <c r="L166" s="38" t="s">
         <v>1102</v>
       </c>
       <c r="M166" s="1">
@@ -16696,10 +16740,10 @@
       <c r="T166" s="10">
         <v>99.99</v>
       </c>
-      <c r="U166" s="29" t="s">
+      <c r="U166" s="28" t="s">
         <v>1103</v>
       </c>
-      <c r="V166" s="29" t="s">
+      <c r="V166" s="28" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -16716,20 +16760,20 @@
       <c r="F167" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="G167" s="39" t="s">
+      <c r="G167" s="38" t="s">
         <v>1107</v>
       </c>
-      <c r="H167" s="39" t="s">
+      <c r="H167" s="38" t="s">
         <v>1108</v>
       </c>
-      <c r="I167" s="39" t="s">
+      <c r="I167" s="38" t="s">
         <v>1109</v>
       </c>
-      <c r="J167" s="39" t="s">
+      <c r="J167" s="38" t="s">
         <v>1110</v>
       </c>
       <c r="K167" s="1"/>
-      <c r="L167" s="39" t="s">
+      <c r="L167" s="38" t="s">
         <v>1111</v>
       </c>
       <c r="M167" s="1">
@@ -16762,10 +16806,10 @@
       <c r="T167" s="10">
         <v>99.99</v>
       </c>
-      <c r="U167" s="29" t="s">
+      <c r="U167" s="28" t="s">
         <v>1112</v>
       </c>
-      <c r="V167" s="29" t="s">
+      <c r="V167" s="28" t="s">
         <v>1112</v>
       </c>
     </row>
@@ -16782,20 +16826,20 @@
       <c r="F168" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="G168" s="39" t="s">
+      <c r="G168" s="38" t="s">
         <v>1116</v>
       </c>
-      <c r="H168" s="39" t="s">
+      <c r="H168" s="38" t="s">
         <v>1117</v>
       </c>
-      <c r="I168" s="39" t="s">
+      <c r="I168" s="38" t="s">
         <v>1118</v>
       </c>
-      <c r="J168" s="39" t="s">
+      <c r="J168" s="38" t="s">
         <v>1119</v>
       </c>
       <c r="K168" s="1"/>
-      <c r="L168" s="39" t="s">
+      <c r="L168" s="38" t="s">
         <v>1120</v>
       </c>
       <c r="M168" s="1">
@@ -16828,10 +16872,10 @@
       <c r="T168" s="10">
         <v>99.99</v>
       </c>
-      <c r="U168" s="29" t="s">
+      <c r="U168" s="28" t="s">
         <v>1121</v>
       </c>
-      <c r="V168" s="29" t="s">
+      <c r="V168" s="28" t="s">
         <v>1121</v>
       </c>
     </row>
@@ -16848,20 +16892,20 @@
       <c r="F169" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="G169" s="39" t="s">
+      <c r="G169" s="38" t="s">
         <v>1125</v>
       </c>
-      <c r="H169" s="39" t="s">
+      <c r="H169" s="38" t="s">
         <v>1126</v>
       </c>
-      <c r="I169" s="39" t="s">
+      <c r="I169" s="38" t="s">
         <v>1127</v>
       </c>
-      <c r="J169" s="39" t="s">
+      <c r="J169" s="38" t="s">
         <v>1128</v>
       </c>
       <c r="K169" s="1"/>
-      <c r="L169" s="39" t="s">
+      <c r="L169" s="38" t="s">
         <v>1129</v>
       </c>
       <c r="M169" s="1">
@@ -16894,10 +16938,10 @@
       <c r="T169" s="10">
         <v>99.99</v>
       </c>
-      <c r="U169" s="29" t="s">
+      <c r="U169" s="28" t="s">
         <v>1130</v>
       </c>
-      <c r="V169" s="29" t="s">
+      <c r="V169" s="28" t="s">
         <v>1130</v>
       </c>
     </row>
@@ -16914,20 +16958,20 @@
       <c r="F170" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="G170" s="39" t="s">
+      <c r="G170" s="38" t="s">
         <v>1134</v>
       </c>
-      <c r="H170" s="39" t="s">
+      <c r="H170" s="38" t="s">
         <v>1135</v>
       </c>
-      <c r="I170" s="39" t="s">
+      <c r="I170" s="38" t="s">
         <v>1136</v>
       </c>
-      <c r="J170" s="39" t="s">
+      <c r="J170" s="38" t="s">
         <v>1137</v>
       </c>
       <c r="K170" s="1"/>
-      <c r="L170" s="39" t="s">
+      <c r="L170" s="38" t="s">
         <v>1138</v>
       </c>
       <c r="M170" s="1">
@@ -16960,10 +17004,10 @@
       <c r="T170" s="10">
         <v>99.99</v>
       </c>
-      <c r="U170" s="29" t="s">
+      <c r="U170" s="28" t="s">
         <v>1139</v>
       </c>
-      <c r="V170" s="29" t="s">
+      <c r="V170" s="28" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -16980,20 +17024,20 @@
       <c r="F171" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="G171" s="39" t="s">
+      <c r="G171" s="38" t="s">
         <v>1143</v>
       </c>
-      <c r="H171" s="39" t="s">
+      <c r="H171" s="38" t="s">
         <v>1144</v>
       </c>
-      <c r="I171" s="39" t="s">
+      <c r="I171" s="38" t="s">
         <v>1145</v>
       </c>
-      <c r="J171" s="39" t="s">
+      <c r="J171" s="38" t="s">
         <v>1146</v>
       </c>
       <c r="K171" s="1"/>
-      <c r="L171" s="39" t="s">
+      <c r="L171" s="38" t="s">
         <v>1147</v>
       </c>
       <c r="M171" s="1">
@@ -17026,10 +17070,10 @@
       <c r="T171" s="10">
         <v>99.99</v>
       </c>
-      <c r="U171" s="29" t="s">
+      <c r="U171" s="28" t="s">
         <v>1148</v>
       </c>
-      <c r="V171" s="29" t="s">
+      <c r="V171" s="28" t="s">
         <v>1148</v>
       </c>
     </row>
@@ -17046,20 +17090,20 @@
       <c r="F172" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="G172" s="39" t="s">
+      <c r="G172" s="38" t="s">
         <v>1152</v>
       </c>
-      <c r="H172" s="39" t="s">
+      <c r="H172" s="38" t="s">
         <v>1153</v>
       </c>
-      <c r="I172" s="39" t="s">
+      <c r="I172" s="38" t="s">
         <v>1154</v>
       </c>
-      <c r="J172" s="39" t="s">
+      <c r="J172" s="38" t="s">
         <v>1155</v>
       </c>
       <c r="K172" s="1"/>
-      <c r="L172" s="39" t="s">
+      <c r="L172" s="38" t="s">
         <v>1156</v>
       </c>
       <c r="M172" s="1">
@@ -17092,10 +17136,10 @@
       <c r="T172" s="10">
         <v>99.99</v>
       </c>
-      <c r="U172" s="29" t="s">
+      <c r="U172" s="28" t="s">
         <v>1157</v>
       </c>
-      <c r="V172" s="29" t="s">
+      <c r="V172" s="28" t="s">
         <v>1157</v>
       </c>
     </row>
@@ -17112,20 +17156,20 @@
       <c r="F173" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="G173" s="39" t="s">
+      <c r="G173" s="38" t="s">
         <v>1161</v>
       </c>
-      <c r="H173" s="39" t="s">
+      <c r="H173" s="38" t="s">
         <v>1162</v>
       </c>
-      <c r="I173" s="39" t="s">
+      <c r="I173" s="38" t="s">
         <v>1163</v>
       </c>
-      <c r="J173" s="39" t="s">
+      <c r="J173" s="38" t="s">
         <v>1164</v>
       </c>
       <c r="K173" s="1"/>
-      <c r="L173" s="39" t="s">
+      <c r="L173" s="38" t="s">
         <v>1165</v>
       </c>
       <c r="M173" s="1">
@@ -17158,10 +17202,10 @@
       <c r="T173" s="10">
         <v>99.99</v>
       </c>
-      <c r="U173" s="29" t="s">
+      <c r="U173" s="28" t="s">
         <v>1166</v>
       </c>
-      <c r="V173" s="29" t="s">
+      <c r="V173" s="28" t="s">
         <v>1166</v>
       </c>
     </row>
@@ -17178,20 +17222,20 @@
       <c r="F174" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="G174" s="39" t="s">
+      <c r="G174" s="38" t="s">
         <v>1170</v>
       </c>
-      <c r="H174" s="39" t="s">
+      <c r="H174" s="38" t="s">
         <v>1171</v>
       </c>
-      <c r="I174" s="39" t="s">
+      <c r="I174" s="38" t="s">
         <v>1172</v>
       </c>
-      <c r="J174" s="39" t="s">
+      <c r="J174" s="38" t="s">
         <v>1173</v>
       </c>
       <c r="K174" s="1"/>
-      <c r="L174" s="39" t="s">
+      <c r="L174" s="38" t="s">
         <v>1174</v>
       </c>
       <c r="M174" s="1">
@@ -17224,10 +17268,10 @@
       <c r="T174" s="10">
         <v>99.99</v>
       </c>
-      <c r="U174" s="29" t="s">
+      <c r="U174" s="28" t="s">
         <v>1175</v>
       </c>
-      <c r="V174" s="29" t="s">
+      <c r="V174" s="28" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -17244,20 +17288,20 @@
       <c r="F175" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="G175" s="39" t="s">
+      <c r="G175" s="38" t="s">
         <v>1179</v>
       </c>
-      <c r="H175" s="39" t="s">
+      <c r="H175" s="38" t="s">
         <v>1180</v>
       </c>
-      <c r="I175" s="39" t="s">
+      <c r="I175" s="38" t="s">
         <v>1181</v>
       </c>
-      <c r="J175" s="39" t="s">
+      <c r="J175" s="38" t="s">
         <v>1182</v>
       </c>
       <c r="K175" s="1"/>
-      <c r="L175" s="39" t="s">
+      <c r="L175" s="38" t="s">
         <v>1183</v>
       </c>
       <c r="M175" s="1">
@@ -17290,10 +17334,10 @@
       <c r="T175" s="10">
         <v>99.99</v>
       </c>
-      <c r="U175" s="29" t="s">
+      <c r="U175" s="28" t="s">
         <v>1184</v>
       </c>
-      <c r="V175" s="29" t="s">
+      <c r="V175" s="28" t="s">
         <v>1184</v>
       </c>
     </row>
@@ -17312,19 +17356,19 @@
       <c r="F176" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="G176" s="39" t="s">
+      <c r="G176" s="38" t="s">
         <v>1188</v>
       </c>
-      <c r="H176" s="39" t="s">
+      <c r="H176" s="38" t="s">
         <v>1189</v>
       </c>
-      <c r="I176" s="39" t="s">
+      <c r="I176" s="38" t="s">
         <v>1190</v>
       </c>
-      <c r="J176" s="39" t="s">
+      <c r="J176" s="38" t="s">
         <v>1191</v>
       </c>
-      <c r="L176" s="39" t="s">
+      <c r="L176" s="38" t="s">
         <v>1192</v>
       </c>
       <c r="M176" s="1">
@@ -17357,10 +17401,10 @@
       <c r="T176" s="10">
         <v>99.99</v>
       </c>
-      <c r="U176" s="29" t="s">
+      <c r="U176" s="28" t="s">
         <v>1193</v>
       </c>
-      <c r="V176" s="29" t="s">
+      <c r="V176" s="28" t="s">
         <v>1193</v>
       </c>
       <c r="W176" s="10"/>
@@ -17384,19 +17428,19 @@
       <c r="F177" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="G177" s="39" t="s">
+      <c r="G177" s="38" t="s">
         <v>1197</v>
       </c>
-      <c r="H177" s="39" t="s">
+      <c r="H177" s="38" t="s">
         <v>1198</v>
       </c>
-      <c r="I177" s="39" t="s">
+      <c r="I177" s="38" t="s">
         <v>1199</v>
       </c>
-      <c r="J177" s="39" t="s">
+      <c r="J177" s="38" t="s">
         <v>1200</v>
       </c>
-      <c r="L177" s="39" t="s">
+      <c r="L177" s="38" t="s">
         <v>1201</v>
       </c>
       <c r="M177" s="1">
@@ -17429,10 +17473,10 @@
       <c r="T177" s="10">
         <v>99.99</v>
       </c>
-      <c r="U177" s="29" t="s">
+      <c r="U177" s="28" t="s">
         <v>1202</v>
       </c>
-      <c r="V177" s="29" t="s">
+      <c r="V177" s="28" t="s">
         <v>1202</v>
       </c>
       <c r="W177" s="10"/>
@@ -17456,19 +17500,19 @@
       <c r="F178" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="G178" s="39" t="s">
+      <c r="G178" s="38" t="s">
         <v>1206</v>
       </c>
-      <c r="H178" s="39" t="s">
+      <c r="H178" s="38" t="s">
         <v>1207</v>
       </c>
-      <c r="I178" s="39" t="s">
+      <c r="I178" s="38" t="s">
         <v>1208</v>
       </c>
-      <c r="J178" s="39" t="s">
+      <c r="J178" s="38" t="s">
         <v>1209</v>
       </c>
-      <c r="L178" s="39" t="s">
+      <c r="L178" s="38" t="s">
         <v>1210</v>
       </c>
       <c r="M178" s="1">
@@ -17501,10 +17545,10 @@
       <c r="T178" s="10">
         <v>99.99</v>
       </c>
-      <c r="U178" s="29" t="s">
+      <c r="U178" s="28" t="s">
         <v>1211</v>
       </c>
-      <c r="V178" s="29" t="s">
+      <c r="V178" s="28" t="s">
         <v>1211</v>
       </c>
       <c r="W178" s="10"/>
@@ -17528,19 +17572,19 @@
       <c r="F179" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="G179" s="39" t="s">
+      <c r="G179" s="38" t="s">
         <v>1215</v>
       </c>
-      <c r="H179" s="39" t="s">
+      <c r="H179" s="38" t="s">
         <v>1216</v>
       </c>
-      <c r="I179" s="39" t="s">
+      <c r="I179" s="38" t="s">
         <v>1217</v>
       </c>
-      <c r="J179" s="39" t="s">
+      <c r="J179" s="38" t="s">
         <v>1218</v>
       </c>
-      <c r="L179" s="39" t="s">
+      <c r="L179" s="38" t="s">
         <v>1219</v>
       </c>
       <c r="M179" s="1">
@@ -17573,10 +17617,10 @@
       <c r="T179" s="10">
         <v>99.99</v>
       </c>
-      <c r="U179" s="29" t="s">
+      <c r="U179" s="28" t="s">
         <v>1220</v>
       </c>
-      <c r="V179" s="29" t="s">
+      <c r="V179" s="28" t="s">
         <v>1220</v>
       </c>
       <c r="W179" s="10"/>
@@ -17600,19 +17644,19 @@
       <c r="F180" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="G180" s="39" t="s">
+      <c r="G180" s="38" t="s">
         <v>1224</v>
       </c>
-      <c r="H180" s="39" t="s">
+      <c r="H180" s="38" t="s">
         <v>1225</v>
       </c>
-      <c r="I180" s="39" t="s">
+      <c r="I180" s="38" t="s">
         <v>1226</v>
       </c>
-      <c r="J180" s="39" t="s">
+      <c r="J180" s="38" t="s">
         <v>1227</v>
       </c>
-      <c r="L180" s="39" t="s">
+      <c r="L180" s="38" t="s">
         <v>1228</v>
       </c>
       <c r="M180" s="1">
@@ -17645,10 +17689,10 @@
       <c r="T180" s="10">
         <v>99.99</v>
       </c>
-      <c r="U180" s="29" t="s">
+      <c r="U180" s="28" t="s">
         <v>1229</v>
       </c>
-      <c r="V180" s="29" t="s">
+      <c r="V180" s="28" t="s">
         <v>1229</v>
       </c>
       <c r="W180" s="10"/>
@@ -17672,22 +17716,22 @@
       <c r="F181" s="2" t="s">
         <v>1230</v>
       </c>
-      <c r="G181" s="40" t="s">
+      <c r="G181" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H181" s="40" t="s">
+      <c r="H181" s="39" t="s">
         <v>1232</v>
       </c>
-      <c r="I181" s="40" t="s">
+      <c r="I181" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J181" s="40" t="s">
+      <c r="J181" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K181" s="35" t="s">
+      <c r="K181" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L181" s="40" t="s">
+      <c r="L181" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M181" s="2">
@@ -17716,10 +17760,10 @@
       <c r="T181" s="18">
         <v>99.99</v>
       </c>
-      <c r="U181" s="35" t="s">
+      <c r="U181" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V181" s="35" t="s">
+      <c r="V181" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="Y181" s="18"/>
@@ -17741,22 +17785,22 @@
       <c r="F182" s="5" t="s">
         <v>1238</v>
       </c>
-      <c r="G182" s="39" t="s">
+      <c r="G182" s="38" t="s">
         <v>1239</v>
       </c>
-      <c r="H182" s="39" t="s">
+      <c r="H182" s="38" t="s">
         <v>1240</v>
       </c>
-      <c r="I182" s="39" t="s">
+      <c r="I182" s="38" t="s">
         <v>1241</v>
       </c>
-      <c r="J182" s="39" t="s">
+      <c r="J182" s="38" t="s">
         <v>1242</v>
       </c>
-      <c r="K182" s="41" t="s">
+      <c r="K182" s="40" t="s">
         <v>1243</v>
       </c>
-      <c r="L182" s="39" t="s">
+      <c r="L182" s="38" t="s">
         <v>1244</v>
       </c>
       <c r="M182" s="5">
@@ -17790,10 +17834,10 @@
       <c r="T182" s="12">
         <v>99.99</v>
       </c>
-      <c r="U182" s="41" t="s">
+      <c r="U182" s="40" t="s">
         <v>1245</v>
       </c>
-      <c r="V182" s="41" t="s">
+      <c r="V182" s="40" t="s">
         <v>1245</v>
       </c>
       <c r="Y182" s="12"/>
@@ -17815,22 +17859,22 @@
       <c r="F183" s="5" t="s">
         <v>1246</v>
       </c>
-      <c r="G183" s="39" t="s">
+      <c r="G183" s="38" t="s">
         <v>1247</v>
       </c>
-      <c r="H183" s="39" t="s">
+      <c r="H183" s="38" t="s">
         <v>1248</v>
       </c>
-      <c r="I183" s="39" t="s">
+      <c r="I183" s="38" t="s">
         <v>1249</v>
       </c>
-      <c r="J183" s="39" t="s">
+      <c r="J183" s="38" t="s">
         <v>1250</v>
       </c>
-      <c r="K183" s="41" t="s">
+      <c r="K183" s="40" t="s">
         <v>1251</v>
       </c>
-      <c r="L183" s="39" t="s">
+      <c r="L183" s="38" t="s">
         <v>1252</v>
       </c>
       <c r="M183" s="5">
@@ -17864,10 +17908,10 @@
       <c r="T183" s="12">
         <v>99.99</v>
       </c>
-      <c r="U183" s="41" t="s">
+      <c r="U183" s="40" t="s">
         <v>1253</v>
       </c>
-      <c r="V183" s="41" t="s">
+      <c r="V183" s="40" t="s">
         <v>1253</v>
       </c>
       <c r="Y183" s="12"/>
@@ -17889,22 +17933,22 @@
       <c r="F184" s="5" t="s">
         <v>1254</v>
       </c>
-      <c r="G184" s="39" t="s">
+      <c r="G184" s="38" t="s">
         <v>1255</v>
       </c>
-      <c r="H184" s="39" t="s">
+      <c r="H184" s="38" t="s">
         <v>1256</v>
       </c>
-      <c r="I184" s="39" t="s">
+      <c r="I184" s="38" t="s">
         <v>1257</v>
       </c>
-      <c r="J184" s="39" t="s">
+      <c r="J184" s="38" t="s">
         <v>1258</v>
       </c>
-      <c r="K184" s="41" t="s">
+      <c r="K184" s="40" t="s">
         <v>1259</v>
       </c>
-      <c r="L184" s="39" t="s">
+      <c r="L184" s="38" t="s">
         <v>1260</v>
       </c>
       <c r="M184" s="5">
@@ -17938,10 +17982,10 @@
       <c r="T184" s="12">
         <v>99.99</v>
       </c>
-      <c r="U184" s="41" t="s">
+      <c r="U184" s="40" t="s">
         <v>1261</v>
       </c>
-      <c r="V184" s="41" t="s">
+      <c r="V184" s="40" t="s">
         <v>1261</v>
       </c>
       <c r="Y184" s="12"/>
@@ -17963,22 +18007,22 @@
       <c r="F185" s="5" t="s">
         <v>1262</v>
       </c>
-      <c r="G185" s="39" t="s">
+      <c r="G185" s="38" t="s">
         <v>1263</v>
       </c>
-      <c r="H185" s="39" t="s">
+      <c r="H185" s="38" t="s">
         <v>1264</v>
       </c>
-      <c r="I185" s="39" t="s">
+      <c r="I185" s="38" t="s">
         <v>1265</v>
       </c>
-      <c r="J185" s="39" t="s">
+      <c r="J185" s="38" t="s">
         <v>1266</v>
       </c>
-      <c r="K185" s="41" t="s">
+      <c r="K185" s="40" t="s">
         <v>1267</v>
       </c>
-      <c r="L185" s="39" t="s">
+      <c r="L185" s="38" t="s">
         <v>1268</v>
       </c>
       <c r="M185" s="5">
@@ -18012,10 +18056,10 @@
       <c r="T185" s="12">
         <v>99.99</v>
       </c>
-      <c r="U185" s="41" t="s">
+      <c r="U185" s="40" t="s">
         <v>1269</v>
       </c>
-      <c r="V185" s="41" t="s">
+      <c r="V185" s="40" t="s">
         <v>1269</v>
       </c>
       <c r="Y185" s="12"/>
@@ -18037,22 +18081,22 @@
       <c r="F186" s="6" t="s">
         <v>1270</v>
       </c>
-      <c r="G186" s="39" t="s">
+      <c r="G186" s="38" t="s">
         <v>1271</v>
       </c>
-      <c r="H186" s="37" t="s">
+      <c r="H186" s="36" t="s">
         <v>1272</v>
       </c>
-      <c r="I186" s="37" t="s">
+      <c r="I186" s="36" t="s">
         <v>1273</v>
       </c>
-      <c r="J186" s="37" t="s">
+      <c r="J186" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="K186" s="41" t="s">
+      <c r="K186" s="40" t="s">
         <v>1275</v>
       </c>
-      <c r="L186" s="37" t="s">
+      <c r="L186" s="36" t="s">
         <v>1276</v>
       </c>
       <c r="M186" s="6">
@@ -18086,10 +18130,10 @@
       <c r="T186" s="7">
         <v>99.99</v>
       </c>
-      <c r="U186" s="42" t="s">
+      <c r="U186" s="41" t="s">
         <v>1277</v>
       </c>
-      <c r="V186" s="42" t="s">
+      <c r="V186" s="41" t="s">
         <v>1277</v>
       </c>
       <c r="W186" s="7"/>
@@ -18113,22 +18157,22 @@
       <c r="F187" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="G187" s="39" t="s">
+      <c r="G187" s="38" t="s">
         <v>1279</v>
       </c>
-      <c r="H187" s="37" t="s">
+      <c r="H187" s="36" t="s">
         <v>1280</v>
       </c>
-      <c r="I187" s="37" t="s">
+      <c r="I187" s="36" t="s">
         <v>1281</v>
       </c>
-      <c r="J187" s="37" t="s">
+      <c r="J187" s="36" t="s">
         <v>1282</v>
       </c>
-      <c r="K187" s="41" t="s">
+      <c r="K187" s="40" t="s">
         <v>1283</v>
       </c>
-      <c r="L187" s="37" t="s">
+      <c r="L187" s="36" t="s">
         <v>1284</v>
       </c>
       <c r="M187" s="4">
@@ -18162,10 +18206,10 @@
       <c r="T187" s="8">
         <v>99.99</v>
       </c>
-      <c r="U187" s="38" t="s">
+      <c r="U187" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V187" s="38" t="s">
+      <c r="V187" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="W187" s="8"/>
@@ -18189,22 +18233,22 @@
       <c r="F188" s="4" t="s">
         <v>1286</v>
       </c>
-      <c r="G188" s="39" t="s">
+      <c r="G188" s="38" t="s">
         <v>1232</v>
       </c>
-      <c r="H188" s="37" t="s">
+      <c r="H188" s="36" t="s">
         <v>1287</v>
       </c>
-      <c r="I188" s="37" t="s">
+      <c r="I188" s="36" t="s">
         <v>1288</v>
       </c>
-      <c r="J188" s="37" t="s">
+      <c r="J188" s="36" t="s">
         <v>1289</v>
       </c>
-      <c r="K188" s="41" t="s">
+      <c r="K188" s="40" t="s">
         <v>1290</v>
       </c>
-      <c r="L188" s="37" t="s">
+      <c r="L188" s="36" t="s">
         <v>1255</v>
       </c>
       <c r="M188" s="4">
@@ -18238,10 +18282,10 @@
       <c r="T188" s="8">
         <v>99.99</v>
       </c>
-      <c r="U188" s="38" t="s">
+      <c r="U188" s="37" t="s">
         <v>1291</v>
       </c>
-      <c r="V188" s="38" t="s">
+      <c r="V188" s="37" t="s">
         <v>1291</v>
       </c>
       <c r="W188" s="8"/>
@@ -18265,22 +18309,22 @@
       <c r="F189" s="4" t="s">
         <v>1292</v>
       </c>
-      <c r="G189" s="39" t="s">
+      <c r="G189" s="38" t="s">
         <v>1293</v>
       </c>
-      <c r="H189" s="37" t="s">
+      <c r="H189" s="36" t="s">
         <v>1294</v>
       </c>
-      <c r="I189" s="37" t="s">
+      <c r="I189" s="36" t="s">
         <v>1295</v>
       </c>
-      <c r="J189" s="37" t="s">
+      <c r="J189" s="36" t="s">
         <v>1296</v>
       </c>
-      <c r="K189" s="41" t="s">
+      <c r="K189" s="40" t="s">
         <v>1297</v>
       </c>
-      <c r="L189" s="37" t="s">
+      <c r="L189" s="36" t="s">
         <v>1298</v>
       </c>
       <c r="M189" s="4">
@@ -18314,10 +18358,10 @@
       <c r="T189" s="8">
         <v>99.99</v>
       </c>
-      <c r="U189" s="38" t="s">
+      <c r="U189" s="37" t="s">
         <v>1299</v>
       </c>
-      <c r="V189" s="38" t="s">
+      <c r="V189" s="37" t="s">
         <v>1299</v>
       </c>
       <c r="W189" s="8"/>
@@ -18341,22 +18385,22 @@
       <c r="F190" s="4" t="s">
         <v>1300</v>
       </c>
-      <c r="G190" s="39" t="s">
+      <c r="G190" s="38" t="s">
         <v>1301</v>
       </c>
-      <c r="H190" s="37" t="s">
+      <c r="H190" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I190" s="37" t="s">
+      <c r="I190" s="36" t="s">
         <v>1303</v>
       </c>
-      <c r="J190" s="37" t="s">
+      <c r="J190" s="36" t="s">
         <v>1304</v>
       </c>
-      <c r="K190" s="41" t="s">
+      <c r="K190" s="40" t="s">
         <v>1305</v>
       </c>
-      <c r="L190" s="37" t="s">
+      <c r="L190" s="36" t="s">
         <v>1306</v>
       </c>
       <c r="M190" s="4">
@@ -18390,10 +18434,10 @@
       <c r="T190" s="8">
         <v>99.99</v>
       </c>
-      <c r="U190" s="38" t="s">
+      <c r="U190" s="37" t="s">
         <v>1307</v>
       </c>
-      <c r="V190" s="38" t="s">
+      <c r="V190" s="37" t="s">
         <v>1307</v>
       </c>
       <c r="W190" s="8"/>
@@ -18417,22 +18461,22 @@
       <c r="F191" s="6" t="s">
         <v>1308</v>
       </c>
-      <c r="G191" s="39" t="s">
+      <c r="G191" s="38" t="s">
         <v>1248</v>
       </c>
-      <c r="H191" s="37" t="s">
+      <c r="H191" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I191" s="37" t="s">
+      <c r="I191" s="36" t="s">
         <v>1309</v>
       </c>
-      <c r="J191" s="37" t="s">
+      <c r="J191" s="36" t="s">
         <v>1183</v>
       </c>
-      <c r="K191" s="41" t="s">
+      <c r="K191" s="40" t="s">
         <v>1310</v>
       </c>
-      <c r="L191" s="37" t="s">
+      <c r="L191" s="36" t="s">
         <v>1311</v>
       </c>
       <c r="M191" s="6">
@@ -18466,10 +18510,10 @@
       <c r="T191" s="7">
         <v>99.99</v>
       </c>
-      <c r="U191" s="42" t="s">
+      <c r="U191" s="41" t="s">
         <v>1312</v>
       </c>
-      <c r="V191" s="42" t="s">
+      <c r="V191" s="41" t="s">
         <v>1312</v>
       </c>
       <c r="W191" s="7"/>
@@ -18493,22 +18537,22 @@
       <c r="F192" s="4" t="s">
         <v>1313</v>
       </c>
-      <c r="G192" s="39" t="s">
+      <c r="G192" s="38" t="s">
         <v>1314</v>
       </c>
-      <c r="H192" s="37" t="s">
+      <c r="H192" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I192" s="37" t="s">
+      <c r="I192" s="36" t="s">
         <v>1315</v>
       </c>
-      <c r="J192" s="37" t="s">
+      <c r="J192" s="36" t="s">
         <v>1316</v>
       </c>
-      <c r="K192" s="41" t="s">
+      <c r="K192" s="40" t="s">
         <v>1317</v>
       </c>
-      <c r="L192" s="37" t="s">
+      <c r="L192" s="36" t="s">
         <v>1279</v>
       </c>
       <c r="M192" s="4">
@@ -18542,10 +18586,10 @@
       <c r="T192" s="8">
         <v>99.99</v>
       </c>
-      <c r="U192" s="38" t="s">
+      <c r="U192" s="37" t="s">
         <v>1318</v>
       </c>
-      <c r="V192" s="38" t="s">
+      <c r="V192" s="37" t="s">
         <v>1318</v>
       </c>
       <c r="W192" s="8"/>
@@ -18569,22 +18613,22 @@
       <c r="F193" s="4" t="s">
         <v>1319</v>
       </c>
-      <c r="G193" s="39" t="s">
+      <c r="G193" s="38" t="s">
         <v>1256</v>
       </c>
-      <c r="H193" s="37" t="s">
+      <c r="H193" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I193" s="37" t="s">
+      <c r="I193" s="36" t="s">
         <v>1320</v>
       </c>
-      <c r="J193" s="37" t="s">
+      <c r="J193" s="36" t="s">
         <v>1321</v>
       </c>
-      <c r="K193" s="41" t="s">
+      <c r="K193" s="40" t="s">
         <v>1322</v>
       </c>
-      <c r="L193" s="37" t="s">
+      <c r="L193" s="36" t="s">
         <v>1323</v>
       </c>
       <c r="M193" s="4">
@@ -18618,10 +18662,10 @@
       <c r="T193" s="8">
         <v>99.99</v>
       </c>
-      <c r="U193" s="38" t="s">
+      <c r="U193" s="37" t="s">
         <v>432</v>
       </c>
-      <c r="V193" s="38" t="s">
+      <c r="V193" s="37" t="s">
         <v>432</v>
       </c>
       <c r="W193" s="8"/>
@@ -18645,22 +18689,22 @@
       <c r="F194" s="4" t="s">
         <v>1324</v>
       </c>
-      <c r="G194" s="39" t="s">
+      <c r="G194" s="38" t="s">
         <v>1154</v>
       </c>
-      <c r="H194" s="37" t="s">
+      <c r="H194" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I194" s="37" t="s">
+      <c r="I194" s="36" t="s">
         <v>1325</v>
       </c>
-      <c r="J194" s="37" t="s">
+      <c r="J194" s="36" t="s">
         <v>1326</v>
       </c>
-      <c r="K194" s="41" t="s">
+      <c r="K194" s="40" t="s">
         <v>1327</v>
       </c>
-      <c r="L194" s="37" t="s">
+      <c r="L194" s="36" t="s">
         <v>1328</v>
       </c>
       <c r="M194" s="4">
@@ -18694,10 +18738,10 @@
       <c r="T194" s="8">
         <v>99.99</v>
       </c>
-      <c r="U194" s="38" t="s">
+      <c r="U194" s="37" t="s">
         <v>1329</v>
       </c>
-      <c r="V194" s="38" t="s">
+      <c r="V194" s="37" t="s">
         <v>1329</v>
       </c>
       <c r="W194" s="8"/>
@@ -18721,22 +18765,22 @@
       <c r="F195" s="4" t="s">
         <v>1330</v>
       </c>
-      <c r="G195" s="39" t="s">
+      <c r="G195" s="38" t="s">
         <v>1264</v>
       </c>
-      <c r="H195" s="37" t="s">
+      <c r="H195" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I195" s="37" t="s">
+      <c r="I195" s="36" t="s">
         <v>1331</v>
       </c>
-      <c r="J195" s="37" t="s">
+      <c r="J195" s="36" t="s">
         <v>1332</v>
       </c>
-      <c r="K195" s="41" t="s">
+      <c r="K195" s="40" t="s">
         <v>1333</v>
       </c>
-      <c r="L195" s="37" t="s">
+      <c r="L195" s="36" t="s">
         <v>1293</v>
       </c>
       <c r="M195" s="4">
@@ -18770,10 +18814,10 @@
       <c r="T195" s="8">
         <v>99.99</v>
       </c>
-      <c r="U195" s="38" t="s">
+      <c r="U195" s="37" t="s">
         <v>1334</v>
       </c>
-      <c r="V195" s="38" t="s">
+      <c r="V195" s="37" t="s">
         <v>1334</v>
       </c>
       <c r="W195" s="8"/>
@@ -18797,22 +18841,22 @@
       <c r="F196" s="6" t="s">
         <v>1335</v>
       </c>
-      <c r="G196" s="39" t="s">
+      <c r="G196" s="38" t="s">
         <v>1336</v>
       </c>
-      <c r="H196" s="37" t="s">
+      <c r="H196" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I196" s="37" t="s">
+      <c r="I196" s="36" t="s">
         <v>1337</v>
       </c>
-      <c r="J196" s="37" t="s">
+      <c r="J196" s="36" t="s">
         <v>1338</v>
       </c>
-      <c r="K196" s="41" t="s">
+      <c r="K196" s="40" t="s">
         <v>1339</v>
       </c>
-      <c r="L196" s="37" t="s">
+      <c r="L196" s="36" t="s">
         <v>1301</v>
       </c>
       <c r="M196" s="6">
@@ -18846,10 +18890,10 @@
       <c r="T196" s="7">
         <v>99.99</v>
       </c>
-      <c r="U196" s="42" t="s">
+      <c r="U196" s="41" t="s">
         <v>1340</v>
       </c>
-      <c r="V196" s="42" t="s">
+      <c r="V196" s="41" t="s">
         <v>1340</v>
       </c>
       <c r="W196" s="7"/>
@@ -18873,22 +18917,22 @@
       <c r="F197" s="4" t="s">
         <v>1341</v>
       </c>
-      <c r="G197" s="39" t="s">
+      <c r="G197" s="38" t="s">
         <v>1342</v>
       </c>
-      <c r="H197" s="37" t="s">
+      <c r="H197" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I197" s="37" t="s">
+      <c r="I197" s="36" t="s">
         <v>1343</v>
       </c>
-      <c r="J197" s="37" t="s">
+      <c r="J197" s="36" t="s">
         <v>1344</v>
       </c>
-      <c r="K197" s="41" t="s">
+      <c r="K197" s="40" t="s">
         <v>1345</v>
       </c>
-      <c r="L197" s="37" t="s">
+      <c r="L197" s="36" t="s">
         <v>1248</v>
       </c>
       <c r="M197" s="4">
@@ -18922,10 +18966,10 @@
       <c r="T197" s="8">
         <v>99.99</v>
       </c>
-      <c r="U197" s="38" t="s">
+      <c r="U197" s="37" t="s">
         <v>1346</v>
       </c>
-      <c r="V197" s="38" t="s">
+      <c r="V197" s="37" t="s">
         <v>1346</v>
       </c>
       <c r="W197" s="8"/>
@@ -18949,22 +18993,22 @@
       <c r="F198" s="4" t="s">
         <v>1347</v>
       </c>
-      <c r="G198" s="39" t="s">
+      <c r="G198" s="38" t="s">
         <v>1280</v>
       </c>
-      <c r="H198" s="37" t="s">
+      <c r="H198" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I198" s="37" t="s">
+      <c r="I198" s="36" t="s">
         <v>1348</v>
       </c>
-      <c r="J198" s="37" t="s">
+      <c r="J198" s="36" t="s">
         <v>1349</v>
       </c>
-      <c r="K198" s="41" t="s">
+      <c r="K198" s="40" t="s">
         <v>1350</v>
       </c>
-      <c r="L198" s="37" t="s">
+      <c r="L198" s="36" t="s">
         <v>1314</v>
       </c>
       <c r="M198" s="4">
@@ -18998,10 +19042,10 @@
       <c r="T198" s="8">
         <v>99.99</v>
       </c>
-      <c r="U198" s="38" t="s">
+      <c r="U198" s="37" t="s">
         <v>1351</v>
       </c>
-      <c r="V198" s="38" t="s">
+      <c r="V198" s="37" t="s">
         <v>1351</v>
       </c>
       <c r="W198" s="8"/>
@@ -19025,22 +19069,22 @@
       <c r="F199" s="4" t="s">
         <v>1352</v>
       </c>
-      <c r="G199" s="39" t="s">
+      <c r="G199" s="38" t="s">
         <v>1353</v>
       </c>
-      <c r="H199" s="37" t="s">
+      <c r="H199" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I199" s="37" t="s">
+      <c r="I199" s="36" t="s">
         <v>1354</v>
       </c>
-      <c r="J199" s="37" t="s">
+      <c r="J199" s="36" t="s">
         <v>1355</v>
       </c>
-      <c r="K199" s="41" t="s">
+      <c r="K199" s="40" t="s">
         <v>1356</v>
       </c>
-      <c r="L199" s="37" t="s">
+      <c r="L199" s="36" t="s">
         <v>1256</v>
       </c>
       <c r="M199" s="4">
@@ -19074,10 +19118,10 @@
       <c r="T199" s="8">
         <v>99.99</v>
       </c>
-      <c r="U199" s="38" t="s">
+      <c r="U199" s="37" t="s">
         <v>1357</v>
       </c>
-      <c r="V199" s="38" t="s">
+      <c r="V199" s="37" t="s">
         <v>1357</v>
       </c>
       <c r="W199" s="8"/>
@@ -19101,22 +19145,22 @@
       <c r="F200" s="4" t="s">
         <v>1358</v>
       </c>
-      <c r="G200" s="39" t="s">
+      <c r="G200" s="38" t="s">
         <v>1359</v>
       </c>
-      <c r="H200" s="37" t="s">
+      <c r="H200" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I200" s="37" t="s">
+      <c r="I200" s="36" t="s">
         <v>1360</v>
       </c>
-      <c r="J200" s="37" t="s">
+      <c r="J200" s="36" t="s">
         <v>1236</v>
       </c>
-      <c r="K200" s="41" t="s">
+      <c r="K200" s="40" t="s">
         <v>1361</v>
       </c>
-      <c r="L200" s="37" t="s">
+      <c r="L200" s="36" t="s">
         <v>1154</v>
       </c>
       <c r="M200" s="4">
@@ -19150,10 +19194,10 @@
       <c r="T200" s="8">
         <v>99.99</v>
       </c>
-      <c r="U200" s="38" t="s">
+      <c r="U200" s="37" t="s">
         <v>1362</v>
       </c>
-      <c r="V200" s="38" t="s">
+      <c r="V200" s="37" t="s">
         <v>1362</v>
       </c>
       <c r="W200" s="8"/>
@@ -19175,22 +19219,22 @@
       <c r="F201" s="6" t="s">
         <v>1363</v>
       </c>
-      <c r="G201" s="37" t="s">
+      <c r="G201" s="36" t="s">
         <v>1364</v>
       </c>
-      <c r="H201" s="37" t="s">
+      <c r="H201" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I201" s="37" t="s">
+      <c r="I201" s="36" t="s">
         <v>1365</v>
       </c>
-      <c r="J201" s="37" t="s">
+      <c r="J201" s="36" t="s">
         <v>1366</v>
       </c>
-      <c r="K201" s="41" t="s">
+      <c r="K201" s="40" t="s">
         <v>1242</v>
       </c>
-      <c r="L201" s="37" t="s">
+      <c r="L201" s="36" t="s">
         <v>1264</v>
       </c>
       <c r="M201" s="6">
@@ -19224,10 +19268,10 @@
       <c r="T201" s="7">
         <v>99.99</v>
       </c>
-      <c r="U201" s="42" t="s">
+      <c r="U201" s="41" t="s">
         <v>1367</v>
       </c>
-      <c r="V201" s="42" t="s">
+      <c r="V201" s="41" t="s">
         <v>1367</v>
       </c>
       <c r="W201" s="6"/>
@@ -19246,22 +19290,22 @@
       <c r="F202" s="4" t="s">
         <v>1368</v>
       </c>
-      <c r="G202" s="37" t="s">
+      <c r="G202" s="36" t="s">
         <v>1369</v>
       </c>
-      <c r="H202" s="37" t="s">
+      <c r="H202" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I202" s="37" t="s">
+      <c r="I202" s="36" t="s">
         <v>1370</v>
       </c>
-      <c r="J202" s="37" t="s">
+      <c r="J202" s="36" t="s">
         <v>1371</v>
       </c>
-      <c r="K202" s="41" t="s">
+      <c r="K202" s="40" t="s">
         <v>1372</v>
       </c>
-      <c r="L202" s="37" t="s">
+      <c r="L202" s="36" t="s">
         <v>1336</v>
       </c>
       <c r="M202" s="4">
@@ -19295,10 +19339,10 @@
       <c r="T202" s="8">
         <v>99.99</v>
       </c>
-      <c r="U202" s="38" t="s">
+      <c r="U202" s="37" t="s">
         <v>1373</v>
       </c>
-      <c r="V202" s="38" t="s">
+      <c r="V202" s="37" t="s">
         <v>1373</v>
       </c>
       <c r="W202" s="4"/>
@@ -19317,22 +19361,22 @@
       <c r="F203" s="4" t="s">
         <v>1374</v>
       </c>
-      <c r="G203" s="37" t="s">
+      <c r="G203" s="36" t="s">
         <v>1375</v>
       </c>
-      <c r="H203" s="37" t="s">
+      <c r="H203" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I203" s="37" t="s">
+      <c r="I203" s="36" t="s">
         <v>1376</v>
       </c>
-      <c r="J203" s="37" t="s">
+      <c r="J203" s="36" t="s">
         <v>1377</v>
       </c>
-      <c r="K203" s="41" t="s">
+      <c r="K203" s="40" t="s">
         <v>1266</v>
       </c>
-      <c r="L203" s="37" t="s">
+      <c r="L203" s="36" t="s">
         <v>1342</v>
       </c>
       <c r="M203" s="4">
@@ -19366,10 +19410,10 @@
       <c r="T203" s="8">
         <v>99.99</v>
       </c>
-      <c r="U203" s="38" t="s">
+      <c r="U203" s="37" t="s">
         <v>1378</v>
       </c>
-      <c r="V203" s="38" t="s">
+      <c r="V203" s="37" t="s">
         <v>1378</v>
       </c>
       <c r="W203" s="4"/>
@@ -19388,22 +19432,22 @@
       <c r="F204" s="4" t="s">
         <v>1379</v>
       </c>
-      <c r="G204" s="37" t="s">
+      <c r="G204" s="36" t="s">
         <v>1380</v>
       </c>
-      <c r="H204" s="37" t="s">
+      <c r="H204" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I204" s="37" t="s">
+      <c r="I204" s="36" t="s">
         <v>1381</v>
       </c>
-      <c r="J204" s="37" t="s">
+      <c r="J204" s="36" t="s">
         <v>1244</v>
       </c>
-      <c r="K204" s="41" t="s">
+      <c r="K204" s="40" t="s">
         <v>1382</v>
       </c>
-      <c r="L204" s="37" t="s">
+      <c r="L204" s="36" t="s">
         <v>1280</v>
       </c>
       <c r="M204" s="4">
@@ -19437,10 +19481,10 @@
       <c r="T204" s="8">
         <v>99.99</v>
       </c>
-      <c r="U204" s="38" t="s">
+      <c r="U204" s="37" t="s">
         <v>1383</v>
       </c>
-      <c r="V204" s="38" t="s">
+      <c r="V204" s="37" t="s">
         <v>1383</v>
       </c>
       <c r="W204" s="4"/>
@@ -19459,22 +19503,22 @@
       <c r="F205" s="4" t="s">
         <v>1384</v>
       </c>
-      <c r="G205" s="37" t="s">
+      <c r="G205" s="36" t="s">
         <v>1385</v>
       </c>
-      <c r="H205" s="37" t="s">
+      <c r="H205" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I205" s="37" t="s">
+      <c r="I205" s="36" t="s">
         <v>1386</v>
       </c>
-      <c r="J205" s="37" t="s">
+      <c r="J205" s="36" t="s">
         <v>1387</v>
       </c>
-      <c r="K205" s="41" t="s">
+      <c r="K205" s="40" t="s">
         <v>1289</v>
       </c>
-      <c r="L205" s="37" t="s">
+      <c r="L205" s="36" t="s">
         <v>1353</v>
       </c>
       <c r="M205" s="4">
@@ -19508,10 +19552,10 @@
       <c r="T205" s="8">
         <v>99.99</v>
       </c>
-      <c r="U205" s="38" t="s">
+      <c r="U205" s="37" t="s">
         <v>1388</v>
       </c>
-      <c r="V205" s="38" t="s">
+      <c r="V205" s="37" t="s">
         <v>1388</v>
       </c>
       <c r="W205" s="4"/>
@@ -19530,22 +19574,22 @@
       <c r="F206" s="6" t="s">
         <v>1389</v>
       </c>
-      <c r="G206" s="37" t="s">
+      <c r="G206" s="36" t="s">
         <v>1249</v>
       </c>
-      <c r="H206" s="37" t="s">
+      <c r="H206" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I206" s="37" t="s">
+      <c r="I206" s="36" t="s">
         <v>1390</v>
       </c>
-      <c r="J206" s="37" t="s">
+      <c r="J206" s="36" t="s">
         <v>1391</v>
       </c>
-      <c r="K206" s="41" t="s">
+      <c r="K206" s="40" t="s">
         <v>1392</v>
       </c>
-      <c r="L206" s="37" t="s">
+      <c r="L206" s="36" t="s">
         <v>1359</v>
       </c>
       <c r="M206" s="6">
@@ -19579,10 +19623,10 @@
       <c r="T206" s="7">
         <v>99.99</v>
       </c>
-      <c r="U206" s="42" t="s">
+      <c r="U206" s="41" t="s">
         <v>1393</v>
       </c>
-      <c r="V206" s="42" t="s">
+      <c r="V206" s="41" t="s">
         <v>1393</v>
       </c>
       <c r="W206" s="6"/>
@@ -19601,22 +19645,22 @@
       <c r="F207" s="4" t="s">
         <v>1394</v>
       </c>
-      <c r="G207" s="37" t="s">
+      <c r="G207" s="36" t="s">
         <v>1395</v>
       </c>
-      <c r="H207" s="37" t="s">
+      <c r="H207" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I207" s="37" t="s">
+      <c r="I207" s="36" t="s">
         <v>1396</v>
       </c>
-      <c r="J207" s="37" t="s">
+      <c r="J207" s="36" t="s">
         <v>1397</v>
       </c>
-      <c r="K207" s="41" t="s">
+      <c r="K207" s="40" t="s">
         <v>1183</v>
       </c>
-      <c r="L207" s="37" t="s">
+      <c r="L207" s="36" t="s">
         <v>1294</v>
       </c>
       <c r="M207" s="4">
@@ -19650,10 +19694,10 @@
       <c r="T207" s="8">
         <v>99.99</v>
       </c>
-      <c r="U207" s="38" t="s">
+      <c r="U207" s="37" t="s">
         <v>1398</v>
       </c>
-      <c r="V207" s="38" t="s">
+      <c r="V207" s="37" t="s">
         <v>1398</v>
       </c>
       <c r="W207" s="4"/>
@@ -19672,22 +19716,22 @@
       <c r="F208" s="4" t="s">
         <v>1399</v>
       </c>
-      <c r="G208" s="37" t="s">
+      <c r="G208" s="36" t="s">
         <v>1257</v>
       </c>
-      <c r="H208" s="37" t="s">
+      <c r="H208" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I208" s="37" t="s">
+      <c r="I208" s="36" t="s">
         <v>1400</v>
       </c>
-      <c r="J208" s="37" t="s">
+      <c r="J208" s="36" t="s">
         <v>1252</v>
       </c>
-      <c r="K208" s="41" t="s">
+      <c r="K208" s="40" t="s">
         <v>1401</v>
       </c>
-      <c r="L208" s="37" t="s">
+      <c r="L208" s="36" t="s">
         <v>1233</v>
       </c>
       <c r="M208" s="4">
@@ -19721,10 +19765,10 @@
       <c r="T208" s="8">
         <v>99.99</v>
       </c>
-      <c r="U208" s="38" t="s">
+      <c r="U208" s="37" t="s">
         <v>1402</v>
       </c>
-      <c r="V208" s="38" t="s">
+      <c r="V208" s="37" t="s">
         <v>1402</v>
       </c>
       <c r="W208" s="4"/>
@@ -19743,22 +19787,22 @@
       <c r="F209" s="4" t="s">
         <v>1403</v>
       </c>
-      <c r="G209" s="37" t="s">
+      <c r="G209" s="36" t="s">
         <v>1404</v>
       </c>
-      <c r="H209" s="37" t="s">
+      <c r="H209" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I209" s="37" t="s">
+      <c r="I209" s="36" t="s">
         <v>1405</v>
       </c>
-      <c r="J209" s="37" t="s">
+      <c r="J209" s="36" t="s">
         <v>1406</v>
       </c>
-      <c r="K209" s="41" t="s">
+      <c r="K209" s="40" t="s">
         <v>1326</v>
       </c>
-      <c r="L209" s="37" t="s">
+      <c r="L209" s="36" t="s">
         <v>1407</v>
       </c>
       <c r="M209" s="4">
@@ -19792,10 +19836,10 @@
       <c r="T209" s="8">
         <v>99.99</v>
       </c>
-      <c r="U209" s="38" t="s">
+      <c r="U209" s="37" t="s">
         <v>1408</v>
       </c>
-      <c r="V209" s="38" t="s">
+      <c r="V209" s="37" t="s">
         <v>1408</v>
       </c>
       <c r="W209" s="4"/>
@@ -19814,22 +19858,22 @@
       <c r="F210" s="4" t="s">
         <v>1409</v>
       </c>
-      <c r="G210" s="37" t="s">
+      <c r="G210" s="36" t="s">
         <v>1410</v>
       </c>
-      <c r="H210" s="37" t="s">
+      <c r="H210" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I210" s="37" t="s">
+      <c r="I210" s="36" t="s">
         <v>1411</v>
       </c>
-      <c r="J210" s="37" t="s">
+      <c r="J210" s="36" t="s">
         <v>1412</v>
       </c>
-      <c r="K210" s="41" t="s">
+      <c r="K210" s="40" t="s">
         <v>1338</v>
       </c>
-      <c r="L210" s="37" t="s">
+      <c r="L210" s="36" t="s">
         <v>1241</v>
       </c>
       <c r="M210" s="4">
@@ -19863,10 +19907,10 @@
       <c r="T210" s="8">
         <v>99.99</v>
       </c>
-      <c r="U210" s="38" t="s">
+      <c r="U210" s="37" t="s">
         <v>1413</v>
       </c>
-      <c r="V210" s="38" t="s">
+      <c r="V210" s="37" t="s">
         <v>1413</v>
       </c>
       <c r="W210" s="4"/>
@@ -19887,22 +19931,22 @@
       <c r="F211" s="4" t="s">
         <v>1414</v>
       </c>
-      <c r="G211" s="37" t="s">
+      <c r="G211" s="36" t="s">
         <v>1273</v>
       </c>
-      <c r="H211" s="37" t="s">
+      <c r="H211" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I211" s="37" t="s">
+      <c r="I211" s="36" t="s">
         <v>1415</v>
       </c>
-      <c r="J211" s="37" t="s">
+      <c r="J211" s="36" t="s">
         <v>1416</v>
       </c>
-      <c r="K211" s="41" t="s">
+      <c r="K211" s="40" t="s">
         <v>1355</v>
       </c>
-      <c r="L211" s="37" t="s">
+      <c r="L211" s="36" t="s">
         <v>1417</v>
       </c>
       <c r="M211" s="4">
@@ -19926,7 +19970,7 @@
         <v>173</v>
       </c>
       <c r="R211" s="8">
-        <f t="shared" ref="R211:R230" si="84">R210+20</f>
+        <f t="shared" ref="R211:R235" si="84">R210+20</f>
         <v>599</v>
       </c>
       <c r="S211" s="8">
@@ -19936,10 +19980,10 @@
       <c r="T211" s="8">
         <v>99.99</v>
       </c>
-      <c r="U211" s="38" t="s">
+      <c r="U211" s="37" t="s">
         <v>1418</v>
       </c>
-      <c r="V211" s="38" t="s">
+      <c r="V211" s="37" t="s">
         <v>1418</v>
       </c>
       <c r="W211" s="8"/>
@@ -19963,22 +20007,22 @@
       <c r="F212" s="4" t="s">
         <v>1419</v>
       </c>
-      <c r="G212" s="37" t="s">
+      <c r="G212" s="36" t="s">
         <v>1420</v>
       </c>
-      <c r="H212" s="37" t="s">
+      <c r="H212" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I212" s="37" t="s">
+      <c r="I212" s="36" t="s">
         <v>1421</v>
       </c>
-      <c r="J212" s="37" t="s">
+      <c r="J212" s="36" t="s">
         <v>1260</v>
       </c>
-      <c r="K212" s="41" t="s">
+      <c r="K212" s="40" t="s">
         <v>1371</v>
       </c>
-      <c r="L212" s="37" t="s">
+      <c r="L212" s="36" t="s">
         <v>1249</v>
       </c>
       <c r="M212" s="4">
@@ -20012,10 +20056,10 @@
       <c r="T212" s="8">
         <v>99.99</v>
       </c>
-      <c r="U212" s="38" t="s">
+      <c r="U212" s="37" t="s">
         <v>1422</v>
       </c>
-      <c r="V212" s="38" t="s">
+      <c r="V212" s="37" t="s">
         <v>1422</v>
       </c>
       <c r="W212" s="8"/>
@@ -20039,22 +20083,22 @@
       <c r="F213" s="4" t="s">
         <v>1423</v>
       </c>
-      <c r="G213" s="37" t="s">
+      <c r="G213" s="36" t="s">
         <v>1424</v>
       </c>
-      <c r="H213" s="37" t="s">
+      <c r="H213" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I213" s="37" t="s">
+      <c r="I213" s="36" t="s">
         <v>1425</v>
       </c>
-      <c r="J213" s="37" t="s">
+      <c r="J213" s="36" t="s">
         <v>1231</v>
       </c>
-      <c r="K213" s="41" t="s">
+      <c r="K213" s="40" t="s">
         <v>1387</v>
       </c>
-      <c r="L213" s="37" t="s">
+      <c r="L213" s="36" t="s">
         <v>1395</v>
       </c>
       <c r="M213" s="4">
@@ -20088,10 +20132,10 @@
       <c r="T213" s="8">
         <v>99.99</v>
       </c>
-      <c r="U213" s="38" t="s">
+      <c r="U213" s="37" t="s">
         <v>1426</v>
       </c>
-      <c r="V213" s="38" t="s">
+      <c r="V213" s="37" t="s">
         <v>1426</v>
       </c>
       <c r="W213" s="8"/>
@@ -20115,22 +20159,22 @@
       <c r="F214" s="4" t="s">
         <v>1427</v>
       </c>
-      <c r="G214" s="37" t="s">
+      <c r="G214" s="36" t="s">
         <v>1288</v>
       </c>
-      <c r="H214" s="37" t="s">
+      <c r="H214" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I214" s="37" t="s">
+      <c r="I214" s="36" t="s">
         <v>1428</v>
       </c>
-      <c r="J214" s="37" t="s">
+      <c r="J214" s="36" t="s">
         <v>1429</v>
       </c>
-      <c r="K214" s="41" t="s">
+      <c r="K214" s="40" t="s">
         <v>1252</v>
       </c>
-      <c r="L214" s="37" t="s">
+      <c r="L214" s="36" t="s">
         <v>1257</v>
       </c>
       <c r="M214" s="4">
@@ -20164,10 +20208,10 @@
       <c r="T214" s="8">
         <v>99.99</v>
       </c>
-      <c r="U214" s="38" t="s">
+      <c r="U214" s="37" t="s">
         <v>1430</v>
       </c>
-      <c r="V214" s="38" t="s">
+      <c r="V214" s="37" t="s">
         <v>1430</v>
       </c>
       <c r="W214" s="8"/>
@@ -20191,22 +20235,22 @@
       <c r="F215" s="4" t="s">
         <v>1431</v>
       </c>
-      <c r="G215" s="37" t="s">
+      <c r="G215" s="36" t="s">
         <v>1432</v>
       </c>
-      <c r="H215" s="37" t="s">
+      <c r="H215" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I215" s="37" t="s">
+      <c r="I215" s="36" t="s">
         <v>1433</v>
       </c>
-      <c r="J215" s="37" t="s">
+      <c r="J215" s="36" t="s">
         <v>1434</v>
       </c>
-      <c r="K215" s="41" t="s">
+      <c r="K215" s="40" t="s">
         <v>1416</v>
       </c>
-      <c r="L215" s="37" t="s">
+      <c r="L215" s="36" t="s">
         <v>1404</v>
       </c>
       <c r="M215" s="4">
@@ -20240,10 +20284,10 @@
       <c r="T215" s="8">
         <v>99.99</v>
       </c>
-      <c r="U215" s="38" t="s">
+      <c r="U215" s="37" t="s">
         <v>1435</v>
       </c>
-      <c r="V215" s="38" t="s">
+      <c r="V215" s="37" t="s">
         <v>1435</v>
       </c>
       <c r="W215" s="8"/>
@@ -20267,22 +20311,22 @@
       <c r="F216" s="2" t="s">
         <v>1436</v>
       </c>
-      <c r="G216" s="40" t="s">
+      <c r="G216" s="39" t="s">
         <v>1437</v>
       </c>
-      <c r="H216" s="37" t="s">
+      <c r="H216" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I216" s="40" t="s">
+      <c r="I216" s="39" t="s">
         <v>1438</v>
       </c>
-      <c r="J216" s="40" t="s">
+      <c r="J216" s="39" t="s">
         <v>1276</v>
       </c>
-      <c r="K216" s="35" t="s">
+      <c r="K216" s="34" t="s">
         <v>1434</v>
       </c>
-      <c r="L216" s="40" t="s">
+      <c r="L216" s="39" t="s">
         <v>1439</v>
       </c>
       <c r="M216" s="4">
@@ -20302,7 +20346,7 @@
         <v>232750</v>
       </c>
       <c r="Q216" s="6">
-        <f t="shared" ref="Q216:Q230" si="87">Q215+7</f>
+        <f t="shared" ref="Q216:Q235" si="87">Q215+7</f>
         <v>204</v>
       </c>
       <c r="R216" s="8">
@@ -20310,16 +20354,16 @@
         <v>699</v>
       </c>
       <c r="S216" s="8">
-        <f t="shared" ref="S216:S230" si="88">S215+30</f>
+        <f t="shared" ref="S216:S235" si="88">S215+30</f>
         <v>826</v>
       </c>
       <c r="T216" s="8">
         <v>99.99</v>
       </c>
-      <c r="U216" s="38" t="s">
+      <c r="U216" s="37" t="s">
         <v>1440</v>
       </c>
-      <c r="V216" s="38" t="s">
+      <c r="V216" s="37" t="s">
         <v>1440</v>
       </c>
       <c r="W216" s="8"/>
@@ -20344,22 +20388,22 @@
       <c r="F217" s="5" t="s">
         <v>1441</v>
       </c>
-      <c r="G217" s="39" t="s">
+      <c r="G217" s="38" t="s">
         <v>1381</v>
       </c>
-      <c r="H217" s="37" t="s">
+      <c r="H217" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I217" s="39" t="s">
+      <c r="I217" s="38" t="s">
         <v>1442</v>
       </c>
-      <c r="J217" s="41" t="s">
+      <c r="J217" s="40" t="s">
         <v>1284</v>
       </c>
-      <c r="K217" s="41" t="s">
+      <c r="K217" s="40" t="s">
         <v>1276</v>
       </c>
-      <c r="L217" s="39" t="s">
+      <c r="L217" s="38" t="s">
         <v>1443</v>
       </c>
       <c r="M217" s="4">
@@ -20393,10 +20437,10 @@
       <c r="T217" s="8">
         <v>99.99</v>
       </c>
-      <c r="U217" s="38" t="s">
+      <c r="U217" s="37" t="s">
         <v>1444</v>
       </c>
-      <c r="V217" s="38" t="s">
+      <c r="V217" s="37" t="s">
         <v>1444</v>
       </c>
       <c r="W217" s="8"/>
@@ -20421,22 +20465,22 @@
       <c r="F218" s="5" t="s">
         <v>1445</v>
       </c>
-      <c r="G218" s="39" t="s">
+      <c r="G218" s="38" t="s">
         <v>1446</v>
       </c>
-      <c r="H218" s="37" t="s">
+      <c r="H218" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I218" s="39" t="s">
+      <c r="I218" s="38" t="s">
         <v>1447</v>
       </c>
-      <c r="J218" s="39" t="s">
+      <c r="J218" s="38" t="s">
         <v>1255</v>
       </c>
-      <c r="K218" s="39" t="s">
+      <c r="K218" s="38" t="s">
         <v>1448</v>
       </c>
-      <c r="L218" s="39" t="s">
+      <c r="L218" s="38" t="s">
         <v>1449</v>
       </c>
       <c r="M218" s="4">
@@ -20470,10 +20514,10 @@
       <c r="T218" s="8">
         <v>99.99</v>
       </c>
-      <c r="U218" s="38" t="s">
+      <c r="U218" s="37" t="s">
         <v>1450</v>
       </c>
-      <c r="V218" s="38" t="s">
+      <c r="V218" s="37" t="s">
         <v>1450</v>
       </c>
       <c r="W218" s="8"/>
@@ -20498,22 +20542,22 @@
       <c r="F219" s="5" t="s">
         <v>1451</v>
       </c>
-      <c r="G219" s="39" t="s">
+      <c r="G219" s="38" t="s">
         <v>1405</v>
       </c>
-      <c r="H219" s="37" t="s">
+      <c r="H219" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I219" s="39" t="s">
+      <c r="I219" s="38" t="s">
         <v>1452</v>
       </c>
-      <c r="J219" s="39" t="s">
+      <c r="J219" s="38" t="s">
         <v>1298</v>
       </c>
-      <c r="K219" s="39" t="s">
+      <c r="K219" s="38" t="s">
         <v>1453</v>
       </c>
-      <c r="L219" s="39" t="s">
+      <c r="L219" s="38" t="s">
         <v>1354</v>
       </c>
       <c r="M219" s="4">
@@ -20547,10 +20591,10 @@
       <c r="T219" s="8">
         <v>99.99</v>
       </c>
-      <c r="U219" s="38" t="s">
+      <c r="U219" s="37" t="s">
         <v>1454</v>
       </c>
-      <c r="V219" s="38" t="s">
+      <c r="V219" s="37" t="s">
         <v>1454</v>
       </c>
       <c r="W219" s="8"/>
@@ -20575,38 +20619,38 @@
       <c r="F220" s="5" t="s">
         <v>1455</v>
       </c>
-      <c r="G220" s="39" t="s">
+      <c r="G220" s="38" t="s">
         <v>1456</v>
       </c>
-      <c r="H220" s="37" t="s">
+      <c r="H220" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I220" s="39" t="s">
+      <c r="I220" s="38" t="s">
         <v>1457</v>
       </c>
-      <c r="J220" s="39" t="s">
+      <c r="J220" s="38" t="s">
         <v>1306</v>
       </c>
-      <c r="K220" s="39" t="s">
+      <c r="K220" s="38" t="s">
         <v>1306</v>
       </c>
-      <c r="L220" s="39" t="s">
+      <c r="L220" s="38" t="s">
         <v>1437</v>
       </c>
       <c r="M220" s="4">
-        <f t="shared" ref="M220:M230" si="92">M219+30000</f>
+        <f t="shared" ref="M220:M235" si="92">M219+30000</f>
         <v>381000</v>
       </c>
       <c r="N220" s="4">
-        <f t="shared" ref="N220:N230" si="93">N219+30000</f>
+        <f t="shared" ref="N220:N235" si="93">N219+30000</f>
         <v>381000</v>
       </c>
       <c r="O220" s="4">
-        <f t="shared" ref="O220:O230" si="94">O219+30000</f>
+        <f t="shared" ref="O220:O235" si="94">O219+30000</f>
         <v>352750</v>
       </c>
       <c r="P220" s="4">
-        <f t="shared" ref="P220:P230" si="95">P219+30000</f>
+        <f t="shared" ref="P220:P235" si="95">P219+30000</f>
         <v>352750</v>
       </c>
       <c r="Q220" s="6">
@@ -20624,10 +20668,10 @@
       <c r="T220" s="8">
         <v>99.99</v>
       </c>
-      <c r="U220" s="38" t="s">
+      <c r="U220" s="37" t="s">
         <v>1458</v>
       </c>
-      <c r="V220" s="38" t="s">
+      <c r="V220" s="37" t="s">
         <v>1458</v>
       </c>
       <c r="W220" s="8"/>
@@ -20652,22 +20696,22 @@
       <c r="F221" s="6" t="s">
         <v>1459</v>
       </c>
-      <c r="G221" s="39" t="s">
+      <c r="G221" s="38" t="s">
         <v>1428</v>
       </c>
-      <c r="H221" s="37" t="s">
+      <c r="H221" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I221" s="39" t="s">
+      <c r="I221" s="38" t="s">
         <v>1460</v>
       </c>
-      <c r="J221" s="39" t="s">
+      <c r="J221" s="38" t="s">
         <v>1461</v>
       </c>
-      <c r="K221" s="39" t="s">
+      <c r="K221" s="38" t="s">
         <v>1461</v>
       </c>
-      <c r="L221" s="39" t="s">
+      <c r="L221" s="38" t="s">
         <v>1381</v>
       </c>
       <c r="M221" s="4">
@@ -20701,10 +20745,10 @@
       <c r="T221" s="8">
         <v>99.99</v>
       </c>
-      <c r="U221" s="38" t="s">
+      <c r="U221" s="37" t="s">
         <v>1462</v>
       </c>
-      <c r="V221" s="38" t="s">
+      <c r="V221" s="37" t="s">
         <v>1462</v>
       </c>
       <c r="W221" s="8"/>
@@ -20729,22 +20773,22 @@
       <c r="F222" s="4" t="s">
         <v>1463</v>
       </c>
-      <c r="G222" s="39" t="s">
+      <c r="G222" s="38" t="s">
         <v>1438</v>
       </c>
-      <c r="H222" s="37" t="s">
+      <c r="H222" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I222" s="39" t="s">
+      <c r="I222" s="38" t="s">
         <v>1464</v>
       </c>
-      <c r="J222" s="39" t="s">
+      <c r="J222" s="38" t="s">
         <v>1323</v>
       </c>
-      <c r="K222" s="39" t="s">
+      <c r="K222" s="38" t="s">
         <v>1323</v>
       </c>
-      <c r="L222" s="39" t="s">
+      <c r="L222" s="38" t="s">
         <v>1446</v>
       </c>
       <c r="M222" s="4">
@@ -20778,10 +20822,10 @@
       <c r="T222" s="8">
         <v>99.99</v>
       </c>
-      <c r="U222" s="38" t="s">
+      <c r="U222" s="37" t="s">
         <v>1465</v>
       </c>
-      <c r="V222" s="38" t="s">
+      <c r="V222" s="37" t="s">
         <v>1465</v>
       </c>
       <c r="W222" s="8"/>
@@ -20806,22 +20850,22 @@
       <c r="F223" s="4" t="s">
         <v>1466</v>
       </c>
-      <c r="G223" s="39" t="s">
+      <c r="G223" s="38" t="s">
         <v>1467</v>
       </c>
-      <c r="H223" s="37" t="s">
+      <c r="H223" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I223" s="39" t="s">
+      <c r="I223" s="38" t="s">
         <v>1468</v>
       </c>
-      <c r="J223" s="39" t="s">
+      <c r="J223" s="38" t="s">
         <v>1469</v>
       </c>
-      <c r="K223" s="39" t="s">
+      <c r="K223" s="38" t="s">
         <v>1469</v>
       </c>
-      <c r="L223" s="39" t="s">
+      <c r="L223" s="38" t="s">
         <v>1405</v>
       </c>
       <c r="M223" s="4">
@@ -20855,10 +20899,10 @@
       <c r="T223" s="8">
         <v>99.99</v>
       </c>
-      <c r="U223" s="38" t="s">
+      <c r="U223" s="37" t="s">
         <v>1470</v>
       </c>
-      <c r="V223" s="38" t="s">
+      <c r="V223" s="37" t="s">
         <v>1470</v>
       </c>
       <c r="W223" s="8"/>
@@ -20883,22 +20927,22 @@
       <c r="F224" s="4" t="s">
         <v>1471</v>
       </c>
-      <c r="G224" s="39" t="s">
+      <c r="G224" s="38" t="s">
         <v>1472</v>
       </c>
-      <c r="H224" s="37" t="s">
+      <c r="H224" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I224" s="39" t="s">
+      <c r="I224" s="38" t="s">
         <v>1473</v>
       </c>
-      <c r="J224" s="39" t="s">
+      <c r="J224" s="38" t="s">
         <v>1474</v>
       </c>
-      <c r="K224" s="39" t="s">
+      <c r="K224" s="38" t="s">
         <v>1474</v>
       </c>
-      <c r="L224" s="39" t="s">
+      <c r="L224" s="38" t="s">
         <v>1456</v>
       </c>
       <c r="M224" s="4">
@@ -20932,10 +20976,10 @@
       <c r="T224" s="8">
         <v>99.99</v>
       </c>
-      <c r="U224" s="38" t="s">
+      <c r="U224" s="37" t="s">
         <v>1475</v>
       </c>
-      <c r="V224" s="38" t="s">
+      <c r="V224" s="37" t="s">
         <v>1475</v>
       </c>
       <c r="W224" s="8"/>
@@ -20960,22 +21004,22 @@
       <c r="F225" s="4" t="s">
         <v>1476</v>
       </c>
-      <c r="G225" s="39" t="s">
+      <c r="G225" s="38" t="s">
         <v>1460</v>
       </c>
-      <c r="H225" s="37" t="s">
+      <c r="H225" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I225" s="39" t="s">
+      <c r="I225" s="38" t="s">
         <v>1477</v>
       </c>
-      <c r="J225" s="39" t="s">
+      <c r="J225" s="38" t="s">
         <v>1248</v>
       </c>
-      <c r="K225" s="39" t="s">
+      <c r="K225" s="38" t="s">
         <v>1248</v>
       </c>
-      <c r="L225" s="39" t="s">
+      <c r="L225" s="38" t="s">
         <v>1428</v>
       </c>
       <c r="M225" s="4">
@@ -21009,10 +21053,10 @@
       <c r="T225" s="8">
         <v>99.99</v>
       </c>
-      <c r="U225" s="38" t="s">
+      <c r="U225" s="37" t="s">
         <v>1478</v>
       </c>
-      <c r="V225" s="38" t="s">
+      <c r="V225" s="37" t="s">
         <v>1478</v>
       </c>
       <c r="W225" s="8"/>
@@ -21022,37 +21066,37 @@
       <c r="AA225" s="8"/>
       <c r="AB225" s="4"/>
     </row>
-    <row r="226" s="9" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A226" s="25"/>
-      <c r="B226" s="25"/>
-      <c r="C226" s="26">
+    <row r="226" s="5" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A226" s="7"/>
+      <c r="B226" s="7"/>
+      <c r="C226" s="6">
         <v>10221</v>
       </c>
-      <c r="D226" s="26">
+      <c r="D226" s="6">
         <v>1220</v>
       </c>
-      <c r="E226" s="26">
+      <c r="E226" s="6">
         <v>7</v>
       </c>
-      <c r="F226" s="26" t="s">
+      <c r="F226" s="6" t="s">
         <v>1479</v>
       </c>
-      <c r="G226" s="43" t="s">
+      <c r="G226" s="38" t="s">
         <v>1464</v>
       </c>
-      <c r="H226" s="44" t="s">
+      <c r="H226" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I226" s="43" t="s">
+      <c r="I226" s="38" t="s">
         <v>1480</v>
       </c>
-      <c r="J226" s="45" t="s">
+      <c r="J226" s="40" t="s">
         <v>1481</v>
       </c>
-      <c r="K226" s="45" t="s">
+      <c r="K226" s="40" t="s">
         <v>1481</v>
       </c>
-      <c r="L226" s="43" t="s">
+      <c r="L226" s="38" t="s">
         <v>1438</v>
       </c>
       <c r="M226" s="4">
@@ -21086,50 +21130,50 @@
       <c r="T226" s="8">
         <v>99.99</v>
       </c>
-      <c r="U226" s="38" t="s">
+      <c r="U226" s="37" t="s">
         <v>1482</v>
       </c>
-      <c r="V226" s="38" t="s">
+      <c r="V226" s="37" t="s">
         <v>1482</v>
       </c>
-      <c r="W226" s="25"/>
-      <c r="X226" s="25"/>
-      <c r="Y226" s="25"/>
-      <c r="Z226" s="25"/>
-      <c r="AA226" s="25"/>
-      <c r="AB226" s="26"/>
-    </row>
-    <row r="227" s="9" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A227" s="25"/>
-      <c r="B227" s="25"/>
-      <c r="C227" s="26">
+      <c r="W226" s="7"/>
+      <c r="X226" s="7"/>
+      <c r="Y226" s="7"/>
+      <c r="Z226" s="7"/>
+      <c r="AA226" s="7"/>
+      <c r="AB226" s="6"/>
+    </row>
+    <row r="227" s="5" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A227" s="7"/>
+      <c r="B227" s="7"/>
+      <c r="C227" s="6">
         <v>10222</v>
       </c>
-      <c r="D227" s="26">
+      <c r="D227" s="6">
         <v>1221</v>
       </c>
-      <c r="E227" s="26">
+      <c r="E227" s="6">
         <v>7</v>
       </c>
-      <c r="F227" s="26" t="s">
+      <c r="F227" s="6" t="s">
         <v>1483</v>
       </c>
-      <c r="G227" s="43" t="s">
+      <c r="G227" s="38" t="s">
         <v>1468</v>
       </c>
-      <c r="H227" s="44" t="s">
+      <c r="H227" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I227" s="43" t="s">
+      <c r="I227" s="38" t="s">
         <v>1484</v>
       </c>
-      <c r="J227" s="45" t="s">
+      <c r="J227" s="40" t="s">
         <v>1154</v>
       </c>
-      <c r="K227" s="45" t="s">
+      <c r="K227" s="40" t="s">
         <v>1154</v>
       </c>
-      <c r="L227" s="43" t="s">
+      <c r="L227" s="38" t="s">
         <v>1467</v>
       </c>
       <c r="M227" s="4">
@@ -21163,50 +21207,50 @@
       <c r="T227" s="8">
         <v>99.99</v>
       </c>
-      <c r="U227" s="38" t="s">
+      <c r="U227" s="37" t="s">
         <v>1485</v>
       </c>
-      <c r="V227" s="38" t="s">
+      <c r="V227" s="37" t="s">
         <v>1485</v>
       </c>
-      <c r="W227" s="25"/>
-      <c r="X227" s="25"/>
-      <c r="Y227" s="25"/>
-      <c r="Z227" s="25"/>
-      <c r="AA227" s="25"/>
-      <c r="AB227" s="26"/>
-    </row>
-    <row r="228" s="9" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A228" s="25"/>
-      <c r="B228" s="25"/>
-      <c r="C228" s="26">
+      <c r="W227" s="7"/>
+      <c r="X227" s="7"/>
+      <c r="Y227" s="7"/>
+      <c r="Z227" s="7"/>
+      <c r="AA227" s="7"/>
+      <c r="AB227" s="6"/>
+    </row>
+    <row r="228" s="5" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A228" s="7"/>
+      <c r="B228" s="7"/>
+      <c r="C228" s="6">
         <v>10223</v>
       </c>
-      <c r="D228" s="26">
+      <c r="D228" s="6">
         <v>1222</v>
       </c>
-      <c r="E228" s="26">
+      <c r="E228" s="6">
         <v>7</v>
       </c>
-      <c r="F228" s="26" t="s">
+      <c r="F228" s="6" t="s">
         <v>1486</v>
       </c>
-      <c r="G228" s="43" t="s">
+      <c r="G228" s="38" t="s">
         <v>1473</v>
       </c>
-      <c r="H228" s="44" t="s">
+      <c r="H228" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I228" s="43" t="s">
+      <c r="I228" s="38" t="s">
         <v>1487</v>
       </c>
-      <c r="J228" s="45" t="s">
+      <c r="J228" s="40" t="s">
         <v>1488</v>
       </c>
-      <c r="K228" s="45" t="s">
+      <c r="K228" s="40" t="s">
         <v>1488</v>
       </c>
-      <c r="L228" s="43" t="s">
+      <c r="L228" s="38" t="s">
         <v>1472</v>
       </c>
       <c r="M228" s="4">
@@ -21240,50 +21284,50 @@
       <c r="T228" s="8">
         <v>99.99</v>
       </c>
-      <c r="U228" s="38" t="s">
+      <c r="U228" s="37" t="s">
         <v>1489</v>
       </c>
-      <c r="V228" s="38" t="s">
+      <c r="V228" s="37" t="s">
         <v>1489</v>
       </c>
-      <c r="W228" s="25"/>
-      <c r="X228" s="25"/>
-      <c r="Y228" s="25"/>
-      <c r="Z228" s="25"/>
-      <c r="AA228" s="25"/>
-      <c r="AB228" s="26"/>
-    </row>
-    <row r="229" s="9" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A229" s="25"/>
-      <c r="B229" s="25"/>
-      <c r="C229" s="26">
+      <c r="W228" s="7"/>
+      <c r="X228" s="7"/>
+      <c r="Y228" s="7"/>
+      <c r="Z228" s="7"/>
+      <c r="AA228" s="7"/>
+      <c r="AB228" s="6"/>
+    </row>
+    <row r="229" s="5" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A229" s="7"/>
+      <c r="B229" s="7"/>
+      <c r="C229" s="6">
         <v>10224</v>
       </c>
-      <c r="D229" s="26">
+      <c r="D229" s="6">
         <v>1223</v>
       </c>
-      <c r="E229" s="26">
+      <c r="E229" s="6">
         <v>7</v>
       </c>
-      <c r="F229" s="26" t="s">
+      <c r="F229" s="6" t="s">
         <v>1490</v>
       </c>
-      <c r="G229" s="43" t="s">
+      <c r="G229" s="38" t="s">
         <v>1477</v>
       </c>
-      <c r="H229" s="44" t="s">
+      <c r="H229" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I229" s="43" t="s">
+      <c r="I229" s="38" t="s">
         <v>1491</v>
       </c>
-      <c r="J229" s="45" t="s">
+      <c r="J229" s="40" t="s">
         <v>1342</v>
       </c>
-      <c r="K229" s="45" t="s">
+      <c r="K229" s="40" t="s">
         <v>1342</v>
       </c>
-      <c r="L229" s="43" t="s">
+      <c r="L229" s="38" t="s">
         <v>1460</v>
       </c>
       <c r="M229" s="4">
@@ -21317,50 +21361,50 @@
       <c r="T229" s="8">
         <v>99.99</v>
       </c>
-      <c r="U229" s="38" t="s">
+      <c r="U229" s="37" t="s">
         <v>1492</v>
       </c>
-      <c r="V229" s="38" t="s">
+      <c r="V229" s="37" t="s">
         <v>1492</v>
       </c>
-      <c r="W229" s="25"/>
-      <c r="X229" s="25"/>
-      <c r="Y229" s="25"/>
-      <c r="Z229" s="25"/>
-      <c r="AA229" s="25"/>
-      <c r="AB229" s="26"/>
-    </row>
-    <row r="230" s="9" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A230" s="25"/>
-      <c r="B230" s="25"/>
-      <c r="C230" s="26">
+      <c r="W229" s="7"/>
+      <c r="X229" s="7"/>
+      <c r="Y229" s="7"/>
+      <c r="Z229" s="7"/>
+      <c r="AA229" s="7"/>
+      <c r="AB229" s="6"/>
+    </row>
+    <row r="230" s="5" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A230" s="7"/>
+      <c r="B230" s="7"/>
+      <c r="C230" s="6">
         <v>10225</v>
       </c>
-      <c r="D230" s="26">
+      <c r="D230" s="6">
         <v>1224</v>
       </c>
-      <c r="E230" s="26">
+      <c r="E230" s="6">
         <v>7</v>
       </c>
-      <c r="F230" s="26" t="s">
+      <c r="F230" s="6" t="s">
         <v>1493</v>
       </c>
-      <c r="G230" s="43" t="s">
+      <c r="G230" s="38" t="s">
         <v>1480</v>
       </c>
-      <c r="H230" s="44" t="s">
+      <c r="H230" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I230" s="43" t="s">
+      <c r="I230" s="38" t="s">
         <v>1494</v>
       </c>
-      <c r="J230" s="45" t="s">
+      <c r="J230" s="40" t="s">
         <v>1495</v>
       </c>
-      <c r="K230" s="45" t="s">
+      <c r="K230" s="40" t="s">
         <v>1495</v>
       </c>
-      <c r="L230" s="43" t="s">
+      <c r="L230" s="38" t="s">
         <v>1496</v>
       </c>
       <c r="M230" s="4">
@@ -21394,18 +21438,18 @@
       <c r="T230" s="8">
         <v>99.99</v>
       </c>
-      <c r="U230" s="38" t="s">
+      <c r="U230" s="37" t="s">
         <v>1497</v>
       </c>
-      <c r="V230" s="38" t="s">
+      <c r="V230" s="37" t="s">
         <v>1497</v>
       </c>
-      <c r="W230" s="25"/>
-      <c r="X230" s="25"/>
-      <c r="Y230" s="25"/>
-      <c r="Z230" s="25"/>
-      <c r="AA230" s="25"/>
-      <c r="AB230" s="26"/>
+      <c r="W230" s="7"/>
+      <c r="X230" s="7"/>
+      <c r="Y230" s="7"/>
+      <c r="Z230" s="7"/>
+      <c r="AA230" s="7"/>
+      <c r="AB230" s="6"/>
     </row>
     <row r="231" s="2" customFormat="1" customHeight="1" spans="1:28">
       <c r="A231" s="8"/>
@@ -21422,55 +21466,60 @@
       <c r="F231" s="6" t="s">
         <v>1498</v>
       </c>
-      <c r="G231" s="40" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H231" s="37" t="s">
+      <c r="G231" s="38" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H231" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I231" s="40" t="s">
-        <v>1233</v>
+      <c r="I231" s="38" t="s">
+        <v>1499</v>
       </c>
       <c r="J231" s="40" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K231" s="35" t="s">
-        <v>1235</v>
-      </c>
-      <c r="L231" s="40" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M231" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N231" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O231" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P231" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q231" s="2">
-        <v>50</v>
-      </c>
-      <c r="R231" s="18">
-        <f t="shared" ref="R216:R250" si="96">R230+9</f>
-        <v>988</v>
-      </c>
-      <c r="S231" s="18">
-        <f t="shared" ref="S216:S250" si="97">S230+10</f>
-        <v>1256</v>
-      </c>
-      <c r="T231" s="18">
+        <v>1359</v>
+      </c>
+      <c r="K231" s="40" t="s">
+        <v>1359</v>
+      </c>
+      <c r="L231" s="38" t="s">
+        <v>1500</v>
+      </c>
+      <c r="M231" s="4">
+        <f t="shared" si="92"/>
+        <v>711000</v>
+      </c>
+      <c r="N231" s="4">
+        <f t="shared" si="93"/>
+        <v>711000</v>
+      </c>
+      <c r="O231" s="4">
+        <f t="shared" si="94"/>
+        <v>682750</v>
+      </c>
+      <c r="P231" s="4">
+        <f t="shared" si="95"/>
+        <v>682750</v>
+      </c>
+      <c r="Q231" s="6">
+        <f t="shared" si="87"/>
+        <v>309</v>
+      </c>
+      <c r="R231" s="8">
+        <f t="shared" si="84"/>
+        <v>999</v>
+      </c>
+      <c r="S231" s="8">
+        <f t="shared" si="88"/>
+        <v>1276</v>
+      </c>
+      <c r="T231" s="8">
         <v>99.99</v>
       </c>
-      <c r="U231" s="35" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V231" s="35" t="s">
-        <v>1237</v>
+      <c r="U231" s="37" t="s">
+        <v>1501</v>
+      </c>
+      <c r="V231" s="37" t="s">
+        <v>1501</v>
       </c>
       <c r="W231" s="8"/>
       <c r="X231" s="8"/>
@@ -21492,57 +21541,62 @@
         <v>7</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>1499</v>
-      </c>
-      <c r="G232" s="40" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H232" s="37" t="s">
+        <v>1502</v>
+      </c>
+      <c r="G232" s="38" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H232" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I232" s="40" t="s">
-        <v>1233</v>
+      <c r="I232" s="38" t="s">
+        <v>1503</v>
       </c>
       <c r="J232" s="40" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K232" s="35" t="s">
-        <v>1235</v>
-      </c>
-      <c r="L232" s="40" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M232" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N232" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O232" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P232" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q232" s="2">
-        <v>50</v>
-      </c>
-      <c r="R232" s="18">
-        <f t="shared" si="96"/>
-        <v>997</v>
-      </c>
-      <c r="S232" s="18">
-        <f t="shared" si="97"/>
-        <v>1266</v>
-      </c>
-      <c r="T232" s="18">
+        <v>1504</v>
+      </c>
+      <c r="K232" s="40" t="s">
+        <v>1504</v>
+      </c>
+      <c r="L232" s="38" t="s">
+        <v>1473</v>
+      </c>
+      <c r="M232" s="4">
+        <f t="shared" si="92"/>
+        <v>741000</v>
+      </c>
+      <c r="N232" s="4">
+        <f t="shared" si="93"/>
+        <v>741000</v>
+      </c>
+      <c r="O232" s="4">
+        <f t="shared" si="94"/>
+        <v>712750</v>
+      </c>
+      <c r="P232" s="4">
+        <f t="shared" si="95"/>
+        <v>712750</v>
+      </c>
+      <c r="Q232" s="6">
+        <f t="shared" si="87"/>
+        <v>316</v>
+      </c>
+      <c r="R232" s="8">
+        <f t="shared" si="84"/>
+        <v>1019</v>
+      </c>
+      <c r="S232" s="8">
+        <f t="shared" si="88"/>
+        <v>1306</v>
+      </c>
+      <c r="T232" s="8">
         <v>99.99</v>
       </c>
-      <c r="U232" s="35" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V232" s="35" t="s">
-        <v>1237</v>
+      <c r="U232" s="37" t="s">
+        <v>1505</v>
+      </c>
+      <c r="V232" s="37" t="s">
+        <v>1505</v>
       </c>
       <c r="W232" s="8"/>
       <c r="X232" s="8"/>
@@ -21564,57 +21618,62 @@
         <v>7</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>1500</v>
-      </c>
-      <c r="G233" s="40" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H233" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="G233" s="38" t="s">
+        <v>1491</v>
+      </c>
+      <c r="H233" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I233" s="40" t="s">
-        <v>1233</v>
+      <c r="I233" s="38" t="s">
+        <v>1507</v>
       </c>
       <c r="J233" s="40" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K233" s="35" t="s">
-        <v>1235</v>
-      </c>
-      <c r="L233" s="40" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M233" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N233" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O233" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P233" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q233" s="2">
-        <v>50</v>
-      </c>
-      <c r="R233" s="18">
-        <f t="shared" si="96"/>
-        <v>1006</v>
-      </c>
-      <c r="S233" s="18">
-        <f t="shared" si="97"/>
-        <v>1276</v>
-      </c>
-      <c r="T233" s="18">
+        <v>1407</v>
+      </c>
+      <c r="K233" s="40" t="s">
+        <v>1407</v>
+      </c>
+      <c r="L233" s="38" t="s">
+        <v>1508</v>
+      </c>
+      <c r="M233" s="4">
+        <f t="shared" si="92"/>
+        <v>771000</v>
+      </c>
+      <c r="N233" s="4">
+        <f t="shared" si="93"/>
+        <v>771000</v>
+      </c>
+      <c r="O233" s="4">
+        <f t="shared" si="94"/>
+        <v>742750</v>
+      </c>
+      <c r="P233" s="4">
+        <f t="shared" si="95"/>
+        <v>742750</v>
+      </c>
+      <c r="Q233" s="6">
+        <f t="shared" si="87"/>
+        <v>323</v>
+      </c>
+      <c r="R233" s="8">
+        <f t="shared" si="84"/>
+        <v>1039</v>
+      </c>
+      <c r="S233" s="8">
+        <f t="shared" si="88"/>
+        <v>1336</v>
+      </c>
+      <c r="T233" s="8">
         <v>99.99</v>
       </c>
-      <c r="U233" s="35" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V233" s="35" t="s">
-        <v>1237</v>
+      <c r="U233" s="37" t="s">
+        <v>1509</v>
+      </c>
+      <c r="V233" s="37" t="s">
+        <v>1509</v>
       </c>
       <c r="W233" s="8"/>
       <c r="X233" s="8"/>
@@ -21636,57 +21695,62 @@
         <v>7</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>1501</v>
-      </c>
-      <c r="G234" s="40" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H234" s="37" t="s">
+        <v>1510</v>
+      </c>
+      <c r="G234" s="38" t="s">
+        <v>1494</v>
+      </c>
+      <c r="H234" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I234" s="40" t="s">
-        <v>1233</v>
+      <c r="I234" s="38" t="s">
+        <v>1511</v>
       </c>
       <c r="J234" s="40" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K234" s="35" t="s">
-        <v>1235</v>
-      </c>
-      <c r="L234" s="40" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M234" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N234" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O234" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P234" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q234" s="2">
-        <v>50</v>
-      </c>
-      <c r="R234" s="18">
-        <f t="shared" si="96"/>
-        <v>1015</v>
-      </c>
-      <c r="S234" s="18">
-        <f t="shared" si="97"/>
-        <v>1286</v>
-      </c>
-      <c r="T234" s="18">
+        <v>1512</v>
+      </c>
+      <c r="K234" s="40" t="s">
+        <v>1512</v>
+      </c>
+      <c r="L234" s="38" t="s">
+        <v>1513</v>
+      </c>
+      <c r="M234" s="4">
+        <f t="shared" si="92"/>
+        <v>801000</v>
+      </c>
+      <c r="N234" s="4">
+        <f t="shared" si="93"/>
+        <v>801000</v>
+      </c>
+      <c r="O234" s="4">
+        <f t="shared" si="94"/>
+        <v>772750</v>
+      </c>
+      <c r="P234" s="4">
+        <f t="shared" si="95"/>
+        <v>772750</v>
+      </c>
+      <c r="Q234" s="6">
+        <f t="shared" si="87"/>
+        <v>330</v>
+      </c>
+      <c r="R234" s="8">
+        <f t="shared" si="84"/>
+        <v>1059</v>
+      </c>
+      <c r="S234" s="8">
+        <f t="shared" si="88"/>
+        <v>1366</v>
+      </c>
+      <c r="T234" s="8">
         <v>99.99</v>
       </c>
-      <c r="U234" s="35" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V234" s="35" t="s">
-        <v>1237</v>
+      <c r="U234" s="37" t="s">
+        <v>1514</v>
+      </c>
+      <c r="V234" s="37" t="s">
+        <v>1514</v>
       </c>
       <c r="W234" s="8"/>
       <c r="X234" s="8"/>
@@ -21695,77 +21759,82 @@
       <c r="AA234" s="8"/>
       <c r="AB234" s="4"/>
     </row>
-    <row r="235" s="2" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A235" s="8"/>
-      <c r="B235" s="8"/>
-      <c r="C235" s="4">
+    <row r="235" s="9" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A235" s="25"/>
+      <c r="B235" s="25"/>
+      <c r="C235" s="26">
         <v>10230</v>
       </c>
-      <c r="D235" s="4">
+      <c r="D235" s="26">
         <v>1229</v>
       </c>
-      <c r="E235" s="4">
+      <c r="E235" s="26">
         <v>7</v>
       </c>
-      <c r="F235" s="4" t="s">
-        <v>1502</v>
-      </c>
-      <c r="G235" s="40" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H235" s="37" t="s">
+      <c r="F235" s="26" t="s">
+        <v>1515</v>
+      </c>
+      <c r="G235" s="38" t="s">
+        <v>1499</v>
+      </c>
+      <c r="H235" s="42" t="s">
         <v>1302</v>
       </c>
-      <c r="I235" s="40" t="s">
-        <v>1233</v>
+      <c r="I235" s="38" t="s">
+        <v>1516</v>
       </c>
       <c r="J235" s="40" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K235" s="35" t="s">
-        <v>1235</v>
-      </c>
-      <c r="L235" s="40" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M235" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N235" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O235" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P235" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q235" s="2">
-        <v>50</v>
-      </c>
-      <c r="R235" s="18">
-        <f t="shared" si="96"/>
-        <v>1024</v>
-      </c>
-      <c r="S235" s="18">
-        <f t="shared" si="97"/>
-        <v>1296</v>
-      </c>
-      <c r="T235" s="18">
+        <v>1249</v>
+      </c>
+      <c r="K235" s="40" t="s">
+        <v>1249</v>
+      </c>
+      <c r="L235" s="38" t="s">
+        <v>1480</v>
+      </c>
+      <c r="M235" s="4">
+        <f t="shared" si="92"/>
+        <v>831000</v>
+      </c>
+      <c r="N235" s="4">
+        <f t="shared" si="93"/>
+        <v>831000</v>
+      </c>
+      <c r="O235" s="4">
+        <f t="shared" si="94"/>
+        <v>802750</v>
+      </c>
+      <c r="P235" s="4">
+        <f t="shared" si="95"/>
+        <v>802750</v>
+      </c>
+      <c r="Q235" s="6">
+        <f t="shared" si="87"/>
+        <v>337</v>
+      </c>
+      <c r="R235" s="8">
+        <f t="shared" si="84"/>
+        <v>1079</v>
+      </c>
+      <c r="S235" s="8">
+        <f t="shared" si="88"/>
+        <v>1396</v>
+      </c>
+      <c r="T235" s="8">
         <v>99.99</v>
       </c>
-      <c r="U235" s="35" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V235" s="35" t="s">
-        <v>1237</v>
-      </c>
-      <c r="W235" s="8"/>
-      <c r="X235" s="8"/>
-      <c r="Y235" s="8"/>
-      <c r="Z235" s="8"/>
-      <c r="AA235" s="8"/>
-      <c r="AB235" s="4"/>
+      <c r="U235" s="37" t="s">
+        <v>1517</v>
+      </c>
+      <c r="V235" s="37" t="s">
+        <v>1517</v>
+      </c>
+      <c r="W235" s="25"/>
+      <c r="X235" s="25"/>
+      <c r="Y235" s="25"/>
+      <c r="Z235" s="25"/>
+      <c r="AA235" s="25"/>
+      <c r="AB235" s="26"/>
     </row>
     <row r="236" s="2" customFormat="1" customHeight="1" spans="1:28">
       <c r="A236" s="8"/>
@@ -21780,24 +21849,24 @@
         <v>7</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>1503</v>
-      </c>
-      <c r="G236" s="40" t="s">
+        <v>1518</v>
+      </c>
+      <c r="G236" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H236" s="37" t="s">
+      <c r="H236" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I236" s="40" t="s">
+      <c r="I236" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J236" s="40" t="s">
+      <c r="J236" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K236" s="35" t="s">
+      <c r="K236" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L236" s="40" t="s">
+      <c r="L236" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M236" s="2">
@@ -21816,20 +21885,20 @@
         <v>50</v>
       </c>
       <c r="R236" s="18">
-        <f t="shared" si="96"/>
-        <v>1033</v>
+        <f>R235+9</f>
+        <v>1088</v>
       </c>
       <c r="S236" s="18">
-        <f t="shared" si="97"/>
-        <v>1306</v>
+        <f>S235+10</f>
+        <v>1406</v>
       </c>
       <c r="T236" s="18">
         <v>99.99</v>
       </c>
-      <c r="U236" s="35" t="s">
+      <c r="U236" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V236" s="35" t="s">
+      <c r="V236" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W236" s="8"/>
@@ -21852,24 +21921,24 @@
         <v>7</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>1504</v>
-      </c>
-      <c r="G237" s="40" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G237" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H237" s="37" t="s">
+      <c r="H237" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I237" s="40" t="s">
+      <c r="I237" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J237" s="40" t="s">
+      <c r="J237" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K237" s="35" t="s">
+      <c r="K237" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L237" s="40" t="s">
+      <c r="L237" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M237" s="2">
@@ -21888,20 +21957,20 @@
         <v>50</v>
       </c>
       <c r="R237" s="18">
-        <f t="shared" si="96"/>
-        <v>1042</v>
+        <f>R236+9</f>
+        <v>1097</v>
       </c>
       <c r="S237" s="18">
-        <f t="shared" si="97"/>
-        <v>1316</v>
+        <f>S236+10</f>
+        <v>1416</v>
       </c>
       <c r="T237" s="18">
         <v>99.99</v>
       </c>
-      <c r="U237" s="35" t="s">
+      <c r="U237" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V237" s="35" t="s">
+      <c r="V237" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W237" s="8"/>
@@ -21924,24 +21993,24 @@
         <v>7</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>1505</v>
-      </c>
-      <c r="G238" s="40" t="s">
+        <v>1520</v>
+      </c>
+      <c r="G238" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H238" s="37" t="s">
+      <c r="H238" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I238" s="40" t="s">
+      <c r="I238" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J238" s="40" t="s">
+      <c r="J238" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K238" s="35" t="s">
+      <c r="K238" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L238" s="40" t="s">
+      <c r="L238" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M238" s="2">
@@ -21960,20 +22029,20 @@
         <v>50</v>
       </c>
       <c r="R238" s="18">
-        <f t="shared" si="96"/>
-        <v>1051</v>
+        <f>R237+9</f>
+        <v>1106</v>
       </c>
       <c r="S238" s="18">
-        <f t="shared" si="97"/>
-        <v>1326</v>
+        <f>S237+10</f>
+        <v>1426</v>
       </c>
       <c r="T238" s="18">
         <v>99.99</v>
       </c>
-      <c r="U238" s="35" t="s">
+      <c r="U238" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V238" s="35" t="s">
+      <c r="V238" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W238" s="8"/>
@@ -21996,24 +22065,24 @@
         <v>7</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>1506</v>
-      </c>
-      <c r="G239" s="40" t="s">
+        <v>1521</v>
+      </c>
+      <c r="G239" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H239" s="37" t="s">
+      <c r="H239" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I239" s="40" t="s">
+      <c r="I239" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J239" s="40" t="s">
+      <c r="J239" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K239" s="35" t="s">
+      <c r="K239" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L239" s="40" t="s">
+      <c r="L239" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M239" s="2">
@@ -22032,20 +22101,20 @@
         <v>50</v>
       </c>
       <c r="R239" s="18">
-        <f t="shared" si="96"/>
-        <v>1060</v>
+        <f>R238+9</f>
+        <v>1115</v>
       </c>
       <c r="S239" s="18">
-        <f t="shared" si="97"/>
-        <v>1336</v>
+        <f>S238+10</f>
+        <v>1436</v>
       </c>
       <c r="T239" s="18">
         <v>99.99</v>
       </c>
-      <c r="U239" s="35" t="s">
+      <c r="U239" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V239" s="35" t="s">
+      <c r="V239" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W239" s="8"/>
@@ -22068,24 +22137,24 @@
         <v>7</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1507</v>
-      </c>
-      <c r="G240" s="40" t="s">
+        <v>1522</v>
+      </c>
+      <c r="G240" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H240" s="37" t="s">
+      <c r="H240" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I240" s="40" t="s">
+      <c r="I240" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J240" s="40" t="s">
+      <c r="J240" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K240" s="35" t="s">
+      <c r="K240" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L240" s="40" t="s">
+      <c r="L240" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M240" s="2">
@@ -22104,20 +22173,20 @@
         <v>50</v>
       </c>
       <c r="R240" s="18">
-        <f t="shared" si="96"/>
-        <v>1069</v>
+        <f>R239+9</f>
+        <v>1124</v>
       </c>
       <c r="S240" s="18">
-        <f t="shared" si="97"/>
-        <v>1346</v>
+        <f>S239+10</f>
+        <v>1446</v>
       </c>
       <c r="T240" s="18">
         <v>99.99</v>
       </c>
-      <c r="U240" s="35" t="s">
+      <c r="U240" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V240" s="35" t="s">
+      <c r="V240" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W240" s="8"/>
@@ -22140,24 +22209,24 @@
         <v>7</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>1508</v>
-      </c>
-      <c r="G241" s="40" t="s">
+        <v>1523</v>
+      </c>
+      <c r="G241" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H241" s="37" t="s">
+      <c r="H241" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I241" s="40" t="s">
+      <c r="I241" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J241" s="40" t="s">
+      <c r="J241" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K241" s="35" t="s">
+      <c r="K241" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L241" s="40" t="s">
+      <c r="L241" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M241" s="2">
@@ -22176,20 +22245,20 @@
         <v>50</v>
       </c>
       <c r="R241" s="18">
-        <f t="shared" si="96"/>
-        <v>1078</v>
+        <f>R240+9</f>
+        <v>1133</v>
       </c>
       <c r="S241" s="18">
-        <f t="shared" si="97"/>
-        <v>1356</v>
+        <f>S240+10</f>
+        <v>1456</v>
       </c>
       <c r="T241" s="18">
         <v>99.99</v>
       </c>
-      <c r="U241" s="35" t="s">
+      <c r="U241" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V241" s="35" t="s">
+      <c r="V241" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W241" s="8"/>
@@ -22212,24 +22281,24 @@
         <v>7</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>1509</v>
-      </c>
-      <c r="G242" s="40" t="s">
+        <v>1524</v>
+      </c>
+      <c r="G242" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H242" s="37" t="s">
+      <c r="H242" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I242" s="40" t="s">
+      <c r="I242" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J242" s="40" t="s">
+      <c r="J242" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K242" s="35" t="s">
+      <c r="K242" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L242" s="40" t="s">
+      <c r="L242" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M242" s="2">
@@ -22248,20 +22317,20 @@
         <v>50</v>
       </c>
       <c r="R242" s="18">
-        <f t="shared" si="96"/>
-        <v>1087</v>
+        <f>R241+9</f>
+        <v>1142</v>
       </c>
       <c r="S242" s="18">
-        <f t="shared" si="97"/>
-        <v>1366</v>
+        <f>S241+10</f>
+        <v>1466</v>
       </c>
       <c r="T242" s="18">
         <v>99.99</v>
       </c>
-      <c r="U242" s="35" t="s">
+      <c r="U242" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V242" s="35" t="s">
+      <c r="V242" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W242" s="8"/>
@@ -22284,24 +22353,24 @@
         <v>7</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>1510</v>
-      </c>
-      <c r="G243" s="40" t="s">
+        <v>1525</v>
+      </c>
+      <c r="G243" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H243" s="37" t="s">
+      <c r="H243" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I243" s="40" t="s">
+      <c r="I243" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J243" s="40" t="s">
+      <c r="J243" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K243" s="35" t="s">
+      <c r="K243" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L243" s="40" t="s">
+      <c r="L243" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M243" s="2">
@@ -22320,20 +22389,20 @@
         <v>50</v>
       </c>
       <c r="R243" s="18">
-        <f t="shared" si="96"/>
-        <v>1096</v>
+        <f>R242+9</f>
+        <v>1151</v>
       </c>
       <c r="S243" s="18">
-        <f t="shared" si="97"/>
-        <v>1376</v>
+        <f>S242+10</f>
+        <v>1476</v>
       </c>
       <c r="T243" s="18">
         <v>99.99</v>
       </c>
-      <c r="U243" s="35" t="s">
+      <c r="U243" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V243" s="35" t="s">
+      <c r="V243" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W243" s="8"/>
@@ -22356,24 +22425,24 @@
         <v>7</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>1511</v>
-      </c>
-      <c r="G244" s="40" t="s">
+        <v>1526</v>
+      </c>
+      <c r="G244" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H244" s="37" t="s">
+      <c r="H244" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I244" s="40" t="s">
+      <c r="I244" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J244" s="40" t="s">
+      <c r="J244" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K244" s="35" t="s">
+      <c r="K244" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L244" s="40" t="s">
+      <c r="L244" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M244" s="2">
@@ -22392,20 +22461,20 @@
         <v>50</v>
       </c>
       <c r="R244" s="18">
-        <f t="shared" si="96"/>
-        <v>1105</v>
+        <f>R243+9</f>
+        <v>1160</v>
       </c>
       <c r="S244" s="18">
-        <f t="shared" si="97"/>
-        <v>1386</v>
+        <f>S243+10</f>
+        <v>1486</v>
       </c>
       <c r="T244" s="18">
         <v>99.99</v>
       </c>
-      <c r="U244" s="35" t="s">
+      <c r="U244" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V244" s="35" t="s">
+      <c r="V244" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W244" s="8"/>
@@ -22428,24 +22497,24 @@
         <v>7</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>1512</v>
-      </c>
-      <c r="G245" s="40" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G245" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H245" s="37" t="s">
+      <c r="H245" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I245" s="40" t="s">
+      <c r="I245" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J245" s="40" t="s">
+      <c r="J245" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K245" s="35" t="s">
+      <c r="K245" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L245" s="40" t="s">
+      <c r="L245" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M245" s="2">
@@ -22464,20 +22533,20 @@
         <v>50</v>
       </c>
       <c r="R245" s="18">
-        <f t="shared" si="96"/>
-        <v>1114</v>
+        <f>R244+9</f>
+        <v>1169</v>
       </c>
       <c r="S245" s="18">
-        <f t="shared" si="97"/>
-        <v>1396</v>
+        <f>S244+10</f>
+        <v>1496</v>
       </c>
       <c r="T245" s="18">
         <v>99.99</v>
       </c>
-      <c r="U245" s="35" t="s">
+      <c r="U245" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V245" s="35" t="s">
+      <c r="V245" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W245" s="8"/>
@@ -22500,24 +22569,24 @@
         <v>7</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>1513</v>
-      </c>
-      <c r="G246" s="40" t="s">
+        <v>1528</v>
+      </c>
+      <c r="G246" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H246" s="37" t="s">
+      <c r="H246" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I246" s="40" t="s">
+      <c r="I246" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J246" s="40" t="s">
+      <c r="J246" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K246" s="35" t="s">
+      <c r="K246" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L246" s="40" t="s">
+      <c r="L246" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M246" s="2">
@@ -22536,20 +22605,20 @@
         <v>50</v>
       </c>
       <c r="R246" s="18">
-        <f t="shared" si="96"/>
-        <v>1123</v>
+        <f>R245+9</f>
+        <v>1178</v>
       </c>
       <c r="S246" s="18">
-        <f t="shared" si="97"/>
-        <v>1406</v>
+        <f>S245+10</f>
+        <v>1506</v>
       </c>
       <c r="T246" s="18">
         <v>99.99</v>
       </c>
-      <c r="U246" s="35" t="s">
+      <c r="U246" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V246" s="35" t="s">
+      <c r="V246" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W246" s="8"/>
@@ -22572,24 +22641,24 @@
         <v>7</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>1514</v>
-      </c>
-      <c r="G247" s="40" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G247" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H247" s="37" t="s">
+      <c r="H247" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I247" s="40" t="s">
+      <c r="I247" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J247" s="40" t="s">
+      <c r="J247" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K247" s="35" t="s">
+      <c r="K247" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L247" s="40" t="s">
+      <c r="L247" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M247" s="2">
@@ -22608,20 +22677,20 @@
         <v>50</v>
       </c>
       <c r="R247" s="18">
-        <f t="shared" si="96"/>
-        <v>1132</v>
+        <f>R246+9</f>
+        <v>1187</v>
       </c>
       <c r="S247" s="18">
-        <f t="shared" si="97"/>
-        <v>1416</v>
+        <f>S246+10</f>
+        <v>1516</v>
       </c>
       <c r="T247" s="18">
         <v>99.99</v>
       </c>
-      <c r="U247" s="35" t="s">
+      <c r="U247" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V247" s="35" t="s">
+      <c r="V247" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W247" s="8"/>
@@ -22644,24 +22713,24 @@
         <v>7</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>1515</v>
-      </c>
-      <c r="G248" s="40" t="s">
+        <v>1530</v>
+      </c>
+      <c r="G248" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H248" s="37" t="s">
+      <c r="H248" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I248" s="40" t="s">
+      <c r="I248" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J248" s="40" t="s">
+      <c r="J248" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K248" s="35" t="s">
+      <c r="K248" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L248" s="40" t="s">
+      <c r="L248" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M248" s="2">
@@ -22680,20 +22749,20 @@
         <v>50</v>
       </c>
       <c r="R248" s="18">
-        <f t="shared" si="96"/>
-        <v>1141</v>
+        <f>R247+9</f>
+        <v>1196</v>
       </c>
       <c r="S248" s="18">
-        <f t="shared" si="97"/>
-        <v>1426</v>
+        <f>S247+10</f>
+        <v>1526</v>
       </c>
       <c r="T248" s="18">
         <v>99.99</v>
       </c>
-      <c r="U248" s="35" t="s">
+      <c r="U248" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V248" s="35" t="s">
+      <c r="V248" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W248" s="8"/>
@@ -22716,24 +22785,24 @@
         <v>7</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>1516</v>
-      </c>
-      <c r="G249" s="40" t="s">
+        <v>1531</v>
+      </c>
+      <c r="G249" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H249" s="37" t="s">
+      <c r="H249" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I249" s="40" t="s">
+      <c r="I249" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J249" s="40" t="s">
+      <c r="J249" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K249" s="35" t="s">
+      <c r="K249" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L249" s="40" t="s">
+      <c r="L249" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M249" s="2">
@@ -22752,20 +22821,20 @@
         <v>50</v>
       </c>
       <c r="R249" s="18">
-        <f t="shared" si="96"/>
-        <v>1150</v>
+        <f>R248+9</f>
+        <v>1205</v>
       </c>
       <c r="S249" s="18">
-        <f t="shared" si="97"/>
-        <v>1436</v>
+        <f>S248+10</f>
+        <v>1536</v>
       </c>
       <c r="T249" s="18">
         <v>99.99</v>
       </c>
-      <c r="U249" s="35" t="s">
+      <c r="U249" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V249" s="35" t="s">
+      <c r="V249" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W249" s="8"/>
@@ -22788,24 +22857,24 @@
         <v>7</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>1517</v>
-      </c>
-      <c r="G250" s="40" t="s">
+        <v>1532</v>
+      </c>
+      <c r="G250" s="39" t="s">
         <v>1231</v>
       </c>
-      <c r="H250" s="37" t="s">
+      <c r="H250" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="I250" s="40" t="s">
+      <c r="I250" s="39" t="s">
         <v>1233</v>
       </c>
-      <c r="J250" s="40" t="s">
+      <c r="J250" s="39" t="s">
         <v>1234</v>
       </c>
-      <c r="K250" s="35" t="s">
+      <c r="K250" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="L250" s="40" t="s">
+      <c r="L250" s="39" t="s">
         <v>1236</v>
       </c>
       <c r="M250" s="2">
@@ -22824,20 +22893,20 @@
         <v>50</v>
       </c>
       <c r="R250" s="18">
-        <f t="shared" si="96"/>
-        <v>1159</v>
+        <f>R249+9</f>
+        <v>1214</v>
       </c>
       <c r="S250" s="18">
-        <f t="shared" si="97"/>
-        <v>1446</v>
+        <f>S249+10</f>
+        <v>1546</v>
       </c>
       <c r="T250" s="18">
         <v>99.99</v>
       </c>
-      <c r="U250" s="35" t="s">
+      <c r="U250" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="V250" s="35" t="s">
+      <c r="V250" s="34" t="s">
         <v>1237</v>
       </c>
       <c r="W250" s="8"/>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="1533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="1587">
   <si>
     <t>ID</t>
   </si>
@@ -4586,46 +4591,208 @@
     <t>虚无恶魔</t>
   </si>
   <si>
+    <t>1E+276</t>
+  </si>
+  <si>
+    <t>1E+290</t>
+  </si>
+  <si>
+    <t>1E+153</t>
+  </si>
+  <si>
+    <t>1E+262</t>
+  </si>
+  <si>
+    <t>630000000000</t>
+  </si>
+  <si>
     <t>虚无勇士</t>
   </si>
   <si>
+    <t>1E+277</t>
+  </si>
+  <si>
+    <t>1E+293</t>
+  </si>
+  <si>
+    <t>1E+264</t>
+  </si>
+  <si>
+    <t>640000000000</t>
+  </si>
+  <si>
     <t>虚无雕像</t>
   </si>
   <si>
+    <t>1E+296</t>
+  </si>
+  <si>
+    <t>1E+159</t>
+  </si>
+  <si>
+    <t>650000000000</t>
+  </si>
+  <si>
     <t>虚无卫士</t>
   </si>
   <si>
+    <t>1E+279</t>
+  </si>
+  <si>
+    <t>1E+299</t>
+  </si>
+  <si>
+    <t>1E+268</t>
+  </si>
+  <si>
+    <t>660000000000</t>
+  </si>
+  <si>
     <t>虚无魔猪</t>
   </si>
   <si>
+    <t>1E+280</t>
+  </si>
+  <si>
+    <t>1E+302</t>
+  </si>
+  <si>
+    <t>1E+165</t>
+  </si>
+  <si>
+    <t>1E+270</t>
+  </si>
+  <si>
+    <t>670000000000</t>
+  </si>
+  <si>
     <t>虚无树妖</t>
   </si>
   <si>
+    <t>1E+305</t>
+  </si>
+  <si>
+    <t>680000000000</t>
+  </si>
+  <si>
     <t>虚无侍卫</t>
   </si>
   <si>
+    <t>1E+282</t>
+  </si>
+  <si>
+    <t>1E+308</t>
+  </si>
+  <si>
+    <t>1E+171</t>
+  </si>
+  <si>
+    <t>1E+274</t>
+  </si>
+  <si>
+    <t>690000000000</t>
+  </si>
+  <si>
     <t>虚无剧毒</t>
   </si>
   <si>
+    <t>1E+283</t>
+  </si>
+  <si>
+    <t>1E+311</t>
+  </si>
+  <si>
+    <t>1E+174</t>
+  </si>
+  <si>
+    <t>700000000000</t>
+  </si>
+  <si>
     <t>虚无锤兵</t>
   </si>
   <si>
+    <t>1E+314</t>
+  </si>
+  <si>
+    <t>1E+177</t>
+  </si>
+  <si>
+    <t>720000000000</t>
+  </si>
+  <si>
     <t>虚无魔牛</t>
   </si>
   <si>
+    <t>1E+285</t>
+  </si>
+  <si>
+    <t>1E+317</t>
+  </si>
+  <si>
+    <t>740000000000</t>
+  </si>
+  <si>
     <t>虚无水龙</t>
   </si>
   <si>
+    <t>1E+286</t>
+  </si>
+  <si>
+    <t>1E+320</t>
+  </si>
+  <si>
+    <t>1E+183</t>
+  </si>
+  <si>
+    <t>760000000000</t>
+  </si>
+  <si>
     <t>虚无土龙</t>
   </si>
   <si>
+    <t>1E+323</t>
+  </si>
+  <si>
+    <t>1E+186</t>
+  </si>
+  <si>
+    <t>780000000000</t>
+  </si>
+  <si>
     <t>虚无毒龙</t>
   </si>
   <si>
+    <t>1E+288</t>
+  </si>
+  <si>
+    <t>1E+326</t>
+  </si>
+  <si>
+    <t>800000000000</t>
+  </si>
+  <si>
     <t>虚无火龙</t>
   </si>
   <si>
+    <t>1E+289</t>
+  </si>
+  <si>
+    <t>1E+329</t>
+  </si>
+  <si>
+    <t>1E+192</t>
+  </si>
+  <si>
+    <t>820000000000</t>
+  </si>
+  <si>
     <t>虚无冰龙</t>
+  </si>
+  <si>
+    <t>1E+332</t>
+  </si>
+  <si>
+    <t>840000000000</t>
   </si>
 </sst>
 </file>
@@ -5276,7 +5443,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5315,6 +5482,9 @@
     <xf numFmtId="176" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -5336,6 +5506,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -5949,13 +6122,13 @@
       <c r="F6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="29" t="s">
         <v>37</v>
       </c>
       <c r="J6" s="1">
@@ -9692,7 +9865,7 @@
       <c r="H65" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="I65" s="28" t="s">
+      <c r="I65" s="29" t="s">
         <v>440</v>
       </c>
       <c r="J65" s="1">
@@ -9761,7 +9934,7 @@
       <c r="H66" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="I66" s="28" t="s">
+      <c r="I66" s="29" t="s">
         <v>447</v>
       </c>
       <c r="J66" s="1">
@@ -9830,7 +10003,7 @@
       <c r="H67" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="I67" s="28" t="s">
+      <c r="I67" s="29" t="s">
         <v>454</v>
       </c>
       <c r="J67" s="1">
@@ -9899,7 +10072,7 @@
       <c r="H68" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="I68" s="28" t="s">
+      <c r="I68" s="29" t="s">
         <v>461</v>
       </c>
       <c r="J68" s="1">
@@ -9965,10 +10138,10 @@
       <c r="G69" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="H69" s="28" t="s">
+      <c r="H69" s="29" t="s">
         <v>467</v>
       </c>
-      <c r="I69" s="28" t="s">
+      <c r="I69" s="29" t="s">
         <v>468</v>
       </c>
       <c r="J69" s="1">
@@ -10031,13 +10204,13 @@
       <c r="F70" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="G70" s="28" t="s">
+      <c r="G70" s="29" t="s">
         <v>473</v>
       </c>
-      <c r="H70" s="28" t="s">
+      <c r="H70" s="29" t="s">
         <v>474</v>
       </c>
-      <c r="I70" s="28" t="s">
+      <c r="I70" s="29" t="s">
         <v>475</v>
       </c>
       <c r="J70" s="1">
@@ -10100,13 +10273,13 @@
       <c r="F71" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="G71" s="28" t="s">
+      <c r="G71" s="29" t="s">
         <v>480</v>
       </c>
-      <c r="H71" s="28" t="s">
+      <c r="H71" s="29" t="s">
         <v>481</v>
       </c>
-      <c r="I71" s="28" t="s">
+      <c r="I71" s="29" t="s">
         <v>482</v>
       </c>
       <c r="J71" s="1">
@@ -10169,13 +10342,13 @@
       <c r="F72" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="G72" s="28" t="s">
+      <c r="G72" s="29" t="s">
         <v>487</v>
       </c>
-      <c r="H72" s="28" t="s">
+      <c r="H72" s="29" t="s">
         <v>488</v>
       </c>
-      <c r="I72" s="28" t="s">
+      <c r="I72" s="29" t="s">
         <v>489</v>
       </c>
       <c r="J72" s="1">
@@ -10238,13 +10411,13 @@
       <c r="F73" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G73" s="28" t="s">
+      <c r="G73" s="29" t="s">
         <v>494</v>
       </c>
-      <c r="H73" s="28" t="s">
+      <c r="H73" s="29" t="s">
         <v>495</v>
       </c>
-      <c r="I73" s="28" t="s">
+      <c r="I73" s="29" t="s">
         <v>496</v>
       </c>
       <c r="J73" s="1">
@@ -10307,13 +10480,13 @@
       <c r="F74" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="G74" s="28" t="s">
+      <c r="G74" s="29" t="s">
         <v>501</v>
       </c>
-      <c r="H74" s="28" t="s">
+      <c r="H74" s="29" t="s">
         <v>502</v>
       </c>
-      <c r="I74" s="28" t="s">
+      <c r="I74" s="29" t="s">
         <v>503</v>
       </c>
       <c r="J74" s="1">
@@ -10376,13 +10549,13 @@
       <c r="F75" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="G75" s="28" t="s">
+      <c r="G75" s="29" t="s">
         <v>508</v>
       </c>
-      <c r="H75" s="28" t="s">
+      <c r="H75" s="29" t="s">
         <v>509</v>
       </c>
-      <c r="I75" s="28" t="s">
+      <c r="I75" s="29" t="s">
         <v>510</v>
       </c>
       <c r="J75" s="1">
@@ -10422,7 +10595,7 @@
       <c r="U75" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="V75" s="28" t="s">
+      <c r="V75" s="29" t="s">
         <v>511</v>
       </c>
       <c r="W75" s="10"/>
@@ -10446,13 +10619,13 @@
       <c r="F76" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G76" s="28" t="s">
+      <c r="G76" s="29" t="s">
         <v>515</v>
       </c>
-      <c r="H76" s="28" t="s">
+      <c r="H76" s="29" t="s">
         <v>516</v>
       </c>
-      <c r="I76" s="28" t="s">
+      <c r="I76" s="29" t="s">
         <v>517</v>
       </c>
       <c r="J76" s="1">
@@ -10514,13 +10687,13 @@
       <c r="F77" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="G77" s="28" t="s">
+      <c r="G77" s="29" t="s">
         <v>521</v>
       </c>
-      <c r="H77" s="28" t="s">
+      <c r="H77" s="29" t="s">
         <v>522</v>
       </c>
-      <c r="I77" s="28" t="s">
+      <c r="I77" s="29" t="s">
         <v>523</v>
       </c>
       <c r="J77" s="1">
@@ -10582,13 +10755,13 @@
       <c r="F78" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="G78" s="28" t="s">
+      <c r="G78" s="29" t="s">
         <v>527</v>
       </c>
-      <c r="H78" s="28" t="s">
+      <c r="H78" s="29" t="s">
         <v>528</v>
       </c>
-      <c r="I78" s="28" t="s">
+      <c r="I78" s="29" t="s">
         <v>529</v>
       </c>
       <c r="J78" s="1">
@@ -10650,13 +10823,13 @@
       <c r="F79" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G79" s="28" t="s">
+      <c r="G79" s="29" t="s">
         <v>533</v>
       </c>
-      <c r="H79" s="28" t="s">
+      <c r="H79" s="29" t="s">
         <v>534</v>
       </c>
-      <c r="I79" s="28" t="s">
+      <c r="I79" s="29" t="s">
         <v>535</v>
       </c>
       <c r="J79" s="1">
@@ -10718,13 +10891,13 @@
       <c r="F80" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="G80" s="28" t="s">
+      <c r="G80" s="29" t="s">
         <v>539</v>
       </c>
-      <c r="H80" s="28" t="s">
+      <c r="H80" s="29" t="s">
         <v>540</v>
       </c>
-      <c r="I80" s="28" t="s">
+      <c r="I80" s="29" t="s">
         <v>541</v>
       </c>
       <c r="J80" s="1">
@@ -10786,13 +10959,13 @@
       <c r="F81" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="G81" s="28" t="s">
+      <c r="G81" s="29" t="s">
         <v>545</v>
       </c>
-      <c r="H81" s="28" t="s">
+      <c r="H81" s="29" t="s">
         <v>546</v>
       </c>
-      <c r="I81" s="28" t="s">
+      <c r="I81" s="29" t="s">
         <v>547</v>
       </c>
       <c r="J81" s="1">
@@ -10856,13 +11029,13 @@
       <c r="F82" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G82" s="28" t="s">
+      <c r="G82" s="29" t="s">
         <v>551</v>
       </c>
-      <c r="H82" s="28" t="s">
+      <c r="H82" s="29" t="s">
         <v>552</v>
       </c>
-      <c r="I82" s="28" t="s">
+      <c r="I82" s="29" t="s">
         <v>553</v>
       </c>
       <c r="J82" s="1">
@@ -10926,13 +11099,13 @@
       <c r="F83" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="G83" s="28" t="s">
+      <c r="G83" s="29" t="s">
         <v>557</v>
       </c>
-      <c r="H83" s="28" t="s">
+      <c r="H83" s="29" t="s">
         <v>558</v>
       </c>
-      <c r="I83" s="28" t="s">
+      <c r="I83" s="29" t="s">
         <v>559</v>
       </c>
       <c r="J83" s="1">
@@ -10996,13 +11169,13 @@
       <c r="F84" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G84" s="28" t="s">
+      <c r="G84" s="29" t="s">
         <v>563</v>
       </c>
-      <c r="H84" s="28" t="s">
+      <c r="H84" s="29" t="s">
         <v>564</v>
       </c>
-      <c r="I84" s="28" t="s">
+      <c r="I84" s="29" t="s">
         <v>565</v>
       </c>
       <c r="J84" s="1">
@@ -11066,13 +11239,13 @@
       <c r="F85" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="G85" s="28" t="s">
+      <c r="G85" s="29" t="s">
         <v>569</v>
       </c>
-      <c r="H85" s="28" t="s">
+      <c r="H85" s="29" t="s">
         <v>570</v>
       </c>
-      <c r="I85" s="28" t="s">
+      <c r="I85" s="29" t="s">
         <v>571</v>
       </c>
       <c r="J85" s="1">
@@ -11136,13 +11309,13 @@
       <c r="F86" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="G86" s="28" t="s">
+      <c r="G86" s="29" t="s">
         <v>575</v>
       </c>
-      <c r="H86" s="28" t="s">
+      <c r="H86" s="29" t="s">
         <v>539</v>
       </c>
-      <c r="I86" s="28" t="s">
+      <c r="I86" s="29" t="s">
         <v>576</v>
       </c>
       <c r="J86" s="1">
@@ -11206,13 +11379,13 @@
       <c r="F87" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="G87" s="28" t="s">
+      <c r="G87" s="29" t="s">
         <v>580</v>
       </c>
-      <c r="H87" s="28" t="s">
+      <c r="H87" s="29" t="s">
         <v>581</v>
       </c>
-      <c r="I87" s="28" t="s">
+      <c r="I87" s="29" t="s">
         <v>582</v>
       </c>
       <c r="J87" s="1">
@@ -11276,13 +11449,13 @@
       <c r="F88" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="G88" s="28" t="s">
+      <c r="G88" s="29" t="s">
         <v>489</v>
       </c>
-      <c r="H88" s="28" t="s">
+      <c r="H88" s="29" t="s">
         <v>454</v>
       </c>
-      <c r="I88" s="28" t="s">
+      <c r="I88" s="29" t="s">
         <v>586</v>
       </c>
       <c r="J88" s="1">
@@ -11346,13 +11519,13 @@
       <c r="F89" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="G89" s="28" t="s">
+      <c r="G89" s="29" t="s">
         <v>503</v>
       </c>
-      <c r="H89" s="28" t="s">
+      <c r="H89" s="29" t="s">
         <v>590</v>
       </c>
-      <c r="I89" s="28" t="s">
+      <c r="I89" s="29" t="s">
         <v>591</v>
       </c>
       <c r="J89" s="1">
@@ -11416,13 +11589,13 @@
       <c r="F90" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G90" s="28" t="s">
+      <c r="G90" s="29" t="s">
         <v>595</v>
       </c>
-      <c r="H90" s="28" t="s">
+      <c r="H90" s="29" t="s">
         <v>580</v>
       </c>
-      <c r="I90" s="28" t="s">
+      <c r="I90" s="29" t="s">
         <v>596</v>
       </c>
       <c r="J90" s="1">
@@ -11486,13 +11659,13 @@
       <c r="F91" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="G91" s="28" t="s">
+      <c r="G91" s="29" t="s">
         <v>600</v>
       </c>
-      <c r="H91" s="28" t="s">
+      <c r="H91" s="29" t="s">
         <v>601</v>
       </c>
-      <c r="I91" s="28" t="s">
+      <c r="I91" s="29" t="s">
         <v>602</v>
       </c>
       <c r="J91" s="1">
@@ -11556,13 +11729,13 @@
       <c r="F92" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="G92" s="28" t="s">
+      <c r="G92" s="29" t="s">
         <v>606</v>
       </c>
-      <c r="H92" s="28" t="s">
+      <c r="H92" s="29" t="s">
         <v>607</v>
       </c>
-      <c r="I92" s="28" t="s">
+      <c r="I92" s="29" t="s">
         <v>608</v>
       </c>
       <c r="J92" s="1">
@@ -11626,13 +11799,13 @@
       <c r="F93" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G93" s="28" t="s">
+      <c r="G93" s="29" t="s">
         <v>612</v>
       </c>
-      <c r="H93" s="28" t="s">
+      <c r="H93" s="29" t="s">
         <v>613</v>
       </c>
-      <c r="I93" s="28" t="s">
+      <c r="I93" s="29" t="s">
         <v>614</v>
       </c>
       <c r="J93" s="1">
@@ -11696,13 +11869,13 @@
       <c r="F94" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="G94" s="28" t="s">
+      <c r="G94" s="29" t="s">
         <v>571</v>
       </c>
-      <c r="H94" s="28" t="s">
+      <c r="H94" s="29" t="s">
         <v>618</v>
       </c>
-      <c r="I94" s="28" t="s">
+      <c r="I94" s="29" t="s">
         <v>619</v>
       </c>
       <c r="J94" s="1">
@@ -11766,13 +11939,13 @@
       <c r="F95" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="G95" s="28" t="s">
+      <c r="G95" s="29" t="s">
         <v>576</v>
       </c>
-      <c r="H95" s="28" t="s">
+      <c r="H95" s="29" t="s">
         <v>623</v>
       </c>
-      <c r="I95" s="28" t="s">
+      <c r="I95" s="29" t="s">
         <v>624</v>
       </c>
       <c r="J95" s="1">
@@ -11834,13 +12007,13 @@
       <c r="F96" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="G96" s="28" t="s">
+      <c r="G96" s="29" t="s">
         <v>582</v>
       </c>
-      <c r="H96" s="28" t="s">
+      <c r="H96" s="29" t="s">
         <v>628</v>
       </c>
-      <c r="I96" s="28" t="s">
+      <c r="I96" s="29" t="s">
         <v>629</v>
       </c>
       <c r="J96" s="1">
@@ -11898,13 +12071,13 @@
       <c r="F97" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="G97" s="28" t="s">
+      <c r="G97" s="29" t="s">
         <v>586</v>
       </c>
-      <c r="H97" s="28" t="s">
+      <c r="H97" s="29" t="s">
         <v>633</v>
       </c>
-      <c r="I97" s="28" t="s">
+      <c r="I97" s="29" t="s">
         <v>634</v>
       </c>
       <c r="J97" s="1">
@@ -11962,13 +12135,13 @@
       <c r="F98" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="G98" s="28" t="s">
+      <c r="G98" s="29" t="s">
         <v>638</v>
       </c>
-      <c r="H98" s="28" t="s">
+      <c r="H98" s="29" t="s">
         <v>639</v>
       </c>
-      <c r="I98" s="28" t="s">
+      <c r="I98" s="29" t="s">
         <v>640</v>
       </c>
       <c r="J98" s="1">
@@ -12026,13 +12199,13 @@
       <c r="F99" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="G99" s="28" t="s">
+      <c r="G99" s="29" t="s">
         <v>644</v>
       </c>
-      <c r="H99" s="28" t="s">
+      <c r="H99" s="29" t="s">
         <v>645</v>
       </c>
-      <c r="I99" s="28" t="s">
+      <c r="I99" s="29" t="s">
         <v>646</v>
       </c>
       <c r="J99" s="1">
@@ -12090,13 +12263,13 @@
       <c r="F100" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="G100" s="28" t="s">
+      <c r="G100" s="29" t="s">
         <v>650</v>
       </c>
-      <c r="H100" s="28" t="s">
+      <c r="H100" s="29" t="s">
         <v>651</v>
       </c>
-      <c r="I100" s="28" t="s">
+      <c r="I100" s="29" t="s">
         <v>652</v>
       </c>
       <c r="J100" s="1">
@@ -12154,13 +12327,13 @@
       <c r="F101" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="G101" s="28" t="s">
+      <c r="G101" s="29" t="s">
         <v>656</v>
       </c>
-      <c r="H101" s="28" t="s">
+      <c r="H101" s="29" t="s">
         <v>657</v>
       </c>
-      <c r="I101" s="28" t="s">
+      <c r="I101" s="29" t="s">
         <v>658</v>
       </c>
       <c r="J101" s="1">
@@ -12218,13 +12391,13 @@
       <c r="F102" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="G102" s="28" t="s">
+      <c r="G102" s="29" t="s">
         <v>662</v>
       </c>
-      <c r="H102" s="28" t="s">
+      <c r="H102" s="29" t="s">
         <v>663</v>
       </c>
-      <c r="I102" s="28" t="s">
+      <c r="I102" s="29" t="s">
         <v>664</v>
       </c>
       <c r="J102" s="1">
@@ -12282,13 +12455,13 @@
       <c r="F103" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="G103" s="28" t="s">
+      <c r="G103" s="29" t="s">
         <v>668</v>
       </c>
-      <c r="H103" s="28" t="s">
+      <c r="H103" s="29" t="s">
         <v>669</v>
       </c>
-      <c r="I103" s="28" t="s">
+      <c r="I103" s="29" t="s">
         <v>670</v>
       </c>
       <c r="J103" s="1">
@@ -12346,13 +12519,13 @@
       <c r="F104" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="G104" s="28" t="s">
+      <c r="G104" s="29" t="s">
         <v>674</v>
       </c>
-      <c r="H104" s="28" t="s">
+      <c r="H104" s="29" t="s">
         <v>668</v>
       </c>
-      <c r="I104" s="28" t="s">
+      <c r="I104" s="29" t="s">
         <v>675</v>
       </c>
       <c r="J104" s="1">
@@ -12410,13 +12583,13 @@
       <c r="F105" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="G105" s="28" t="s">
+      <c r="G105" s="29" t="s">
         <v>679</v>
       </c>
-      <c r="H105" s="28" t="s">
+      <c r="H105" s="29" t="s">
         <v>674</v>
       </c>
-      <c r="I105" s="28" t="s">
+      <c r="I105" s="29" t="s">
         <v>680</v>
       </c>
       <c r="J105" s="1">
@@ -12476,13 +12649,13 @@
       <c r="F106" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="G106" s="28" t="s">
+      <c r="G106" s="29" t="s">
         <v>684</v>
       </c>
-      <c r="H106" s="28" t="s">
+      <c r="H106" s="29" t="s">
         <v>685</v>
       </c>
-      <c r="I106" s="28" t="s">
+      <c r="I106" s="29" t="s">
         <v>686</v>
       </c>
       <c r="J106" s="1">
@@ -12546,13 +12719,13 @@
       <c r="F107" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="G107" s="28" t="s">
+      <c r="G107" s="29" t="s">
         <v>690</v>
       </c>
-      <c r="H107" s="28" t="s">
+      <c r="H107" s="29" t="s">
         <v>691</v>
       </c>
-      <c r="I107" s="28" t="s">
+      <c r="I107" s="29" t="s">
         <v>692</v>
       </c>
       <c r="J107" s="1">
@@ -12616,13 +12789,13 @@
       <c r="F108" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="G108" s="28" t="s">
+      <c r="G108" s="29" t="s">
         <v>696</v>
       </c>
-      <c r="H108" s="28" t="s">
+      <c r="H108" s="29" t="s">
         <v>697</v>
       </c>
-      <c r="I108" s="28" t="s">
+      <c r="I108" s="29" t="s">
         <v>698</v>
       </c>
       <c r="J108" s="1">
@@ -12686,13 +12859,13 @@
       <c r="F109" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="G109" s="28" t="s">
+      <c r="G109" s="29" t="s">
         <v>702</v>
       </c>
-      <c r="H109" s="28" t="s">
+      <c r="H109" s="29" t="s">
         <v>703</v>
       </c>
-      <c r="I109" s="28" t="s">
+      <c r="I109" s="29" t="s">
         <v>704</v>
       </c>
       <c r="J109" s="1">
@@ -12756,13 +12929,13 @@
       <c r="F110" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="G110" s="28" t="s">
+      <c r="G110" s="29" t="s">
         <v>708</v>
       </c>
-      <c r="H110" s="28" t="s">
+      <c r="H110" s="29" t="s">
         <v>709</v>
       </c>
-      <c r="I110" s="28" t="s">
+      <c r="I110" s="29" t="s">
         <v>710</v>
       </c>
       <c r="J110" s="1">
@@ -12826,13 +12999,13 @@
       <c r="F111" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="G111" s="29" t="s">
+      <c r="G111" s="30" t="s">
         <v>714</v>
       </c>
-      <c r="H111" s="30" t="s">
+      <c r="H111" s="31" t="s">
         <v>714</v>
       </c>
-      <c r="I111" s="31" t="s">
+      <c r="I111" s="32" t="s">
         <v>715</v>
       </c>
       <c r="J111" s="1">
@@ -12865,10 +13038,10 @@
       <c r="T111" s="10">
         <v>90</v>
       </c>
-      <c r="U111" s="28" t="s">
+      <c r="U111" s="29" t="s">
         <v>716</v>
       </c>
-      <c r="V111" s="28" t="s">
+      <c r="V111" s="29" t="s">
         <v>716</v>
       </c>
       <c r="Y111" s="10"/>
@@ -12890,13 +13063,13 @@
       <c r="F112" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="G112" s="32" t="s">
+      <c r="G112" s="33" t="s">
         <v>720</v>
       </c>
-      <c r="H112" s="28" t="s">
+      <c r="H112" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="I112" s="33" t="s">
+      <c r="I112" s="34" t="s">
         <v>721</v>
       </c>
       <c r="J112" s="1">
@@ -12934,10 +13107,10 @@
       <c r="T112" s="10">
         <v>90</v>
       </c>
-      <c r="U112" s="28" t="s">
+      <c r="U112" s="29" t="s">
         <v>722</v>
       </c>
-      <c r="V112" s="28" t="s">
+      <c r="V112" s="29" t="s">
         <v>722</v>
       </c>
       <c r="Y112" s="10"/>
@@ -12959,13 +13132,13 @@
       <c r="F113" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="G113" s="32" t="s">
+      <c r="G113" s="33" t="s">
         <v>726</v>
       </c>
-      <c r="H113" s="28" t="s">
+      <c r="H113" s="29" t="s">
         <v>726</v>
       </c>
-      <c r="I113" s="33" t="s">
+      <c r="I113" s="34" t="s">
         <v>727</v>
       </c>
       <c r="J113" s="1">
@@ -13003,10 +13176,10 @@
       <c r="T113" s="10">
         <v>90</v>
       </c>
-      <c r="U113" s="28" t="s">
+      <c r="U113" s="29" t="s">
         <v>728</v>
       </c>
-      <c r="V113" s="28" t="s">
+      <c r="V113" s="29" t="s">
         <v>728</v>
       </c>
       <c r="Y113" s="10"/>
@@ -13028,13 +13201,13 @@
       <c r="F114" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="G114" s="32" t="s">
+      <c r="G114" s="33" t="s">
         <v>732</v>
       </c>
-      <c r="H114" s="28" t="s">
+      <c r="H114" s="29" t="s">
         <v>732</v>
       </c>
-      <c r="I114" s="33" t="s">
+      <c r="I114" s="34" t="s">
         <v>733</v>
       </c>
       <c r="J114" s="1">
@@ -13072,10 +13245,10 @@
       <c r="T114" s="10">
         <v>90</v>
       </c>
-      <c r="U114" s="28" t="s">
+      <c r="U114" s="29" t="s">
         <v>734</v>
       </c>
-      <c r="V114" s="28" t="s">
+      <c r="V114" s="29" t="s">
         <v>734</v>
       </c>
       <c r="Y114" s="10"/>
@@ -13097,13 +13270,13 @@
       <c r="F115" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="G115" s="32" t="s">
+      <c r="G115" s="33" t="s">
         <v>738</v>
       </c>
-      <c r="H115" s="28" t="s">
+      <c r="H115" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="I115" s="33" t="s">
+      <c r="I115" s="34" t="s">
         <v>739</v>
       </c>
       <c r="J115" s="1">
@@ -13141,10 +13314,10 @@
       <c r="T115" s="10">
         <v>90</v>
       </c>
-      <c r="U115" s="28" t="s">
+      <c r="U115" s="29" t="s">
         <v>740</v>
       </c>
-      <c r="V115" s="28" t="s">
+      <c r="V115" s="29" t="s">
         <v>740</v>
       </c>
       <c r="Y115" s="10"/>
@@ -13166,13 +13339,13 @@
       <c r="F116" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="G116" s="32" t="s">
+      <c r="G116" s="33" t="s">
         <v>744</v>
       </c>
-      <c r="H116" s="28" t="s">
+      <c r="H116" s="29" t="s">
         <v>744</v>
       </c>
-      <c r="I116" s="33" t="s">
+      <c r="I116" s="34" t="s">
         <v>745</v>
       </c>
       <c r="J116" s="1">
@@ -13210,10 +13383,10 @@
       <c r="T116" s="10">
         <v>90</v>
       </c>
-      <c r="U116" s="28" t="s">
+      <c r="U116" s="29" t="s">
         <v>746</v>
       </c>
-      <c r="V116" s="28" t="s">
+      <c r="V116" s="29" t="s">
         <v>746</v>
       </c>
       <c r="W116" s="10"/>
@@ -13237,13 +13410,13 @@
       <c r="F117" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="G117" s="32" t="s">
+      <c r="G117" s="33" t="s">
         <v>750</v>
       </c>
-      <c r="H117" s="28" t="s">
+      <c r="H117" s="29" t="s">
         <v>750</v>
       </c>
-      <c r="I117" s="33" t="s">
+      <c r="I117" s="34" t="s">
         <v>751</v>
       </c>
       <c r="J117" s="1">
@@ -13281,10 +13454,10 @@
       <c r="T117" s="10">
         <v>90</v>
       </c>
-      <c r="U117" s="28" t="s">
+      <c r="U117" s="29" t="s">
         <v>752</v>
       </c>
-      <c r="V117" s="28" t="s">
+      <c r="V117" s="29" t="s">
         <v>752</v>
       </c>
       <c r="W117" s="10"/>
@@ -13308,13 +13481,13 @@
       <c r="F118" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="G118" s="32" t="s">
+      <c r="G118" s="33" t="s">
         <v>756</v>
       </c>
-      <c r="H118" s="28" t="s">
+      <c r="H118" s="29" t="s">
         <v>756</v>
       </c>
-      <c r="I118" s="33" t="s">
+      <c r="I118" s="34" t="s">
         <v>757</v>
       </c>
       <c r="J118" s="1">
@@ -13352,10 +13525,10 @@
       <c r="T118" s="10">
         <v>90</v>
       </c>
-      <c r="U118" s="28" t="s">
+      <c r="U118" s="29" t="s">
         <v>758</v>
       </c>
-      <c r="V118" s="28" t="s">
+      <c r="V118" s="29" t="s">
         <v>758</v>
       </c>
       <c r="W118" s="10"/>
@@ -13379,13 +13552,13 @@
       <c r="F119" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="G119" s="32" t="s">
+      <c r="G119" s="33" t="s">
         <v>762</v>
       </c>
-      <c r="H119" s="28" t="s">
+      <c r="H119" s="29" t="s">
         <v>762</v>
       </c>
-      <c r="I119" s="33" t="s">
+      <c r="I119" s="34" t="s">
         <v>763</v>
       </c>
       <c r="J119" s="1">
@@ -13423,10 +13596,10 @@
       <c r="T119" s="10">
         <v>90</v>
       </c>
-      <c r="U119" s="28" t="s">
+      <c r="U119" s="29" t="s">
         <v>764</v>
       </c>
-      <c r="V119" s="28" t="s">
+      <c r="V119" s="29" t="s">
         <v>764</v>
       </c>
       <c r="W119" s="10"/>
@@ -13450,13 +13623,13 @@
       <c r="F120" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="G120" s="32" t="s">
+      <c r="G120" s="33" t="s">
         <v>768</v>
       </c>
-      <c r="H120" s="28" t="s">
+      <c r="H120" s="29" t="s">
         <v>768</v>
       </c>
-      <c r="I120" s="33" t="s">
+      <c r="I120" s="34" t="s">
         <v>769</v>
       </c>
       <c r="J120" s="1">
@@ -13494,10 +13667,10 @@
       <c r="T120" s="10">
         <v>90</v>
       </c>
-      <c r="U120" s="28" t="s">
+      <c r="U120" s="29" t="s">
         <v>770</v>
       </c>
-      <c r="V120" s="28" t="s">
+      <c r="V120" s="29" t="s">
         <v>770</v>
       </c>
       <c r="W120" s="10"/>
@@ -13521,13 +13694,13 @@
       <c r="F121" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="G121" s="32" t="s">
+      <c r="G121" s="33" t="s">
         <v>715</v>
       </c>
-      <c r="H121" s="28" t="s">
+      <c r="H121" s="29" t="s">
         <v>715</v>
       </c>
-      <c r="I121" s="33" t="s">
+      <c r="I121" s="34" t="s">
         <v>774</v>
       </c>
       <c r="J121" s="1">
@@ -13565,10 +13738,10 @@
       <c r="T121" s="10">
         <v>90</v>
       </c>
-      <c r="U121" s="28" t="s">
+      <c r="U121" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="V121" s="28" t="s">
+      <c r="V121" s="29" t="s">
         <v>775</v>
       </c>
       <c r="W121" s="10"/>
@@ -13592,13 +13765,13 @@
       <c r="F122" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="G122" s="32" t="s">
+      <c r="G122" s="33" t="s">
         <v>779</v>
       </c>
-      <c r="H122" s="28" t="s">
+      <c r="H122" s="29" t="s">
         <v>779</v>
       </c>
-      <c r="I122" s="33" t="s">
+      <c r="I122" s="34" t="s">
         <v>780</v>
       </c>
       <c r="J122" s="1">
@@ -13637,10 +13810,10 @@
       <c r="T122" s="10">
         <v>90</v>
       </c>
-      <c r="U122" s="28" t="s">
+      <c r="U122" s="29" t="s">
         <v>781</v>
       </c>
-      <c r="V122" s="28" t="s">
+      <c r="V122" s="29" t="s">
         <v>781</v>
       </c>
       <c r="W122" s="10"/>
@@ -13664,13 +13837,13 @@
       <c r="F123" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="G123" s="32" t="s">
+      <c r="G123" s="33" t="s">
         <v>785</v>
       </c>
-      <c r="H123" s="28" t="s">
+      <c r="H123" s="29" t="s">
         <v>785</v>
       </c>
-      <c r="I123" s="33" t="s">
+      <c r="I123" s="34" t="s">
         <v>786</v>
       </c>
       <c r="J123" s="1">
@@ -13709,10 +13882,10 @@
       <c r="T123" s="10">
         <v>90</v>
       </c>
-      <c r="U123" s="28" t="s">
+      <c r="U123" s="29" t="s">
         <v>787</v>
       </c>
-      <c r="V123" s="28" t="s">
+      <c r="V123" s="29" t="s">
         <v>787</v>
       </c>
       <c r="W123" s="10"/>
@@ -13736,13 +13909,13 @@
       <c r="F124" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="G124" s="32" t="s">
+      <c r="G124" s="33" t="s">
         <v>791</v>
       </c>
-      <c r="H124" s="28" t="s">
+      <c r="H124" s="29" t="s">
         <v>791</v>
       </c>
-      <c r="I124" s="33" t="s">
+      <c r="I124" s="34" t="s">
         <v>792</v>
       </c>
       <c r="J124" s="1">
@@ -13781,10 +13954,10 @@
       <c r="T124" s="10">
         <v>90</v>
       </c>
-      <c r="U124" s="28" t="s">
+      <c r="U124" s="29" t="s">
         <v>793</v>
       </c>
-      <c r="V124" s="28" t="s">
+      <c r="V124" s="29" t="s">
         <v>793</v>
       </c>
       <c r="W124" s="10"/>
@@ -13808,13 +13981,13 @@
       <c r="F125" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="G125" s="32" t="s">
+      <c r="G125" s="33" t="s">
         <v>797</v>
       </c>
-      <c r="H125" s="28" t="s">
+      <c r="H125" s="29" t="s">
         <v>797</v>
       </c>
-      <c r="I125" s="33" t="s">
+      <c r="I125" s="34" t="s">
         <v>798</v>
       </c>
       <c r="J125" s="1">
@@ -13853,10 +14026,10 @@
       <c r="T125" s="10">
         <v>90</v>
       </c>
-      <c r="U125" s="28" t="s">
+      <c r="U125" s="29" t="s">
         <v>799</v>
       </c>
-      <c r="V125" s="28" t="s">
+      <c r="V125" s="29" t="s">
         <v>799</v>
       </c>
       <c r="W125" s="10"/>
@@ -13880,13 +14053,13 @@
       <c r="F126" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="G126" s="32" t="s">
+      <c r="G126" s="33" t="s">
         <v>803</v>
       </c>
-      <c r="H126" s="28" t="s">
+      <c r="H126" s="29" t="s">
         <v>803</v>
       </c>
-      <c r="I126" s="33" t="s">
+      <c r="I126" s="34" t="s">
         <v>804</v>
       </c>
       <c r="J126" s="1">
@@ -13925,10 +14098,10 @@
       <c r="T126" s="10">
         <v>90</v>
       </c>
-      <c r="U126" s="28" t="s">
+      <c r="U126" s="29" t="s">
         <v>805</v>
       </c>
-      <c r="V126" s="28" t="s">
+      <c r="V126" s="29" t="s">
         <v>805</v>
       </c>
       <c r="W126" s="10"/>
@@ -13952,13 +14125,13 @@
       <c r="F127" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="G127" s="32" t="s">
+      <c r="G127" s="33" t="s">
         <v>809</v>
       </c>
-      <c r="H127" s="28" t="s">
+      <c r="H127" s="29" t="s">
         <v>809</v>
       </c>
-      <c r="I127" s="33" t="s">
+      <c r="I127" s="34" t="s">
         <v>810</v>
       </c>
       <c r="J127" s="1">
@@ -13997,10 +14170,10 @@
       <c r="T127" s="10">
         <v>90</v>
       </c>
-      <c r="U127" s="28" t="s">
+      <c r="U127" s="29" t="s">
         <v>811</v>
       </c>
-      <c r="V127" s="28" t="s">
+      <c r="V127" s="29" t="s">
         <v>811</v>
       </c>
       <c r="W127" s="10"/>
@@ -14024,13 +14197,13 @@
       <c r="F128" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="G128" s="32" t="s">
+      <c r="G128" s="33" t="s">
         <v>815</v>
       </c>
-      <c r="H128" s="28" t="s">
+      <c r="H128" s="29" t="s">
         <v>815</v>
       </c>
-      <c r="I128" s="33" t="s">
+      <c r="I128" s="34" t="s">
         <v>816</v>
       </c>
       <c r="J128" s="1">
@@ -14069,10 +14242,10 @@
       <c r="T128" s="10">
         <v>90</v>
       </c>
-      <c r="U128" s="28" t="s">
+      <c r="U128" s="29" t="s">
         <v>817</v>
       </c>
-      <c r="V128" s="28" t="s">
+      <c r="V128" s="29" t="s">
         <v>817</v>
       </c>
       <c r="W128" s="10"/>
@@ -14096,13 +14269,13 @@
       <c r="F129" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="G129" s="32" t="s">
+      <c r="G129" s="33" t="s">
         <v>821</v>
       </c>
-      <c r="H129" s="28" t="s">
+      <c r="H129" s="29" t="s">
         <v>821</v>
       </c>
-      <c r="I129" s="33" t="s">
+      <c r="I129" s="34" t="s">
         <v>822</v>
       </c>
       <c r="J129" s="1">
@@ -14141,10 +14314,10 @@
       <c r="T129" s="10">
         <v>90</v>
       </c>
-      <c r="U129" s="28" t="s">
+      <c r="U129" s="29" t="s">
         <v>823</v>
       </c>
-      <c r="V129" s="28" t="s">
+      <c r="V129" s="29" t="s">
         <v>823</v>
       </c>
       <c r="W129" s="10"/>
@@ -14168,13 +14341,13 @@
       <c r="F130" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="G130" s="32" t="s">
+      <c r="G130" s="33" t="s">
         <v>827</v>
       </c>
-      <c r="H130" s="28" t="s">
+      <c r="H130" s="29" t="s">
         <v>827</v>
       </c>
-      <c r="I130" s="33" t="s">
+      <c r="I130" s="34" t="s">
         <v>828</v>
       </c>
       <c r="J130" s="1">
@@ -14213,10 +14386,10 @@
       <c r="T130" s="10">
         <v>90</v>
       </c>
-      <c r="U130" s="28" t="s">
+      <c r="U130" s="29" t="s">
         <v>829</v>
       </c>
-      <c r="V130" s="28" t="s">
+      <c r="V130" s="29" t="s">
         <v>829</v>
       </c>
       <c r="W130" s="10"/>
@@ -14238,13 +14411,13 @@
       <c r="F131" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="G131" s="32" t="s">
+      <c r="G131" s="33" t="s">
         <v>833</v>
       </c>
-      <c r="H131" s="28" t="s">
+      <c r="H131" s="29" t="s">
         <v>833</v>
       </c>
-      <c r="I131" s="33" t="s">
+      <c r="I131" s="34" t="s">
         <v>834</v>
       </c>
       <c r="J131" s="1">
@@ -14284,10 +14457,10 @@
       <c r="T131" s="10">
         <v>92</v>
       </c>
-      <c r="U131" s="28" t="s">
+      <c r="U131" s="29" t="s">
         <v>835</v>
       </c>
-      <c r="V131" s="28" t="s">
+      <c r="V131" s="29" t="s">
         <v>835</v>
       </c>
     </row>
@@ -14304,13 +14477,13 @@
       <c r="F132" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="G132" s="32" t="s">
+      <c r="G132" s="33" t="s">
         <v>839</v>
       </c>
-      <c r="H132" s="28" t="s">
+      <c r="H132" s="29" t="s">
         <v>839</v>
       </c>
-      <c r="I132" s="33" t="s">
+      <c r="I132" s="34" t="s">
         <v>840</v>
       </c>
       <c r="J132" s="1">
@@ -14350,10 +14523,10 @@
       <c r="T132" s="10">
         <v>94</v>
       </c>
-      <c r="U132" s="28" t="s">
+      <c r="U132" s="29" t="s">
         <v>841</v>
       </c>
-      <c r="V132" s="28" t="s">
+      <c r="V132" s="29" t="s">
         <v>841</v>
       </c>
     </row>
@@ -14370,13 +14543,13 @@
       <c r="F133" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="G133" s="32" t="s">
+      <c r="G133" s="33" t="s">
         <v>845</v>
       </c>
-      <c r="H133" s="28" t="s">
+      <c r="H133" s="29" t="s">
         <v>845</v>
       </c>
-      <c r="I133" s="33" t="s">
+      <c r="I133" s="34" t="s">
         <v>846</v>
       </c>
       <c r="J133" s="1">
@@ -14416,10 +14589,10 @@
       <c r="T133" s="10">
         <v>96</v>
       </c>
-      <c r="U133" s="28" t="s">
+      <c r="U133" s="29" t="s">
         <v>847</v>
       </c>
-      <c r="V133" s="28" t="s">
+      <c r="V133" s="29" t="s">
         <v>847</v>
       </c>
     </row>
@@ -14436,13 +14609,13 @@
       <c r="F134" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="G134" s="32" t="s">
+      <c r="G134" s="33" t="s">
         <v>851</v>
       </c>
-      <c r="H134" s="28" t="s">
+      <c r="H134" s="29" t="s">
         <v>851</v>
       </c>
-      <c r="I134" s="33" t="s">
+      <c r="I134" s="34" t="s">
         <v>852</v>
       </c>
       <c r="J134" s="1">
@@ -14482,10 +14655,10 @@
       <c r="T134" s="10">
         <v>98</v>
       </c>
-      <c r="U134" s="28" t="s">
+      <c r="U134" s="29" t="s">
         <v>853</v>
       </c>
-      <c r="V134" s="28" t="s">
+      <c r="V134" s="29" t="s">
         <v>853</v>
       </c>
     </row>
@@ -14502,13 +14675,13 @@
       <c r="F135" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="G135" s="32" t="s">
+      <c r="G135" s="33" t="s">
         <v>857</v>
       </c>
-      <c r="H135" s="28" t="s">
+      <c r="H135" s="29" t="s">
         <v>857</v>
       </c>
-      <c r="I135" s="33" t="s">
+      <c r="I135" s="34" t="s">
         <v>858</v>
       </c>
       <c r="J135" s="1">
@@ -14548,10 +14721,10 @@
       <c r="T135" s="10">
         <v>99</v>
       </c>
-      <c r="U135" s="28" t="s">
+      <c r="U135" s="29" t="s">
         <v>859</v>
       </c>
-      <c r="V135" s="28" t="s">
+      <c r="V135" s="29" t="s">
         <v>859</v>
       </c>
     </row>
@@ -14568,13 +14741,13 @@
       <c r="F136" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="G136" s="32" t="s">
+      <c r="G136" s="33" t="s">
         <v>863</v>
       </c>
-      <c r="H136" s="28" t="s">
+      <c r="H136" s="29" t="s">
         <v>863</v>
       </c>
-      <c r="I136" s="33" t="s">
+      <c r="I136" s="34" t="s">
         <v>864</v>
       </c>
       <c r="J136" s="1">
@@ -14614,10 +14787,10 @@
       <c r="T136" s="10">
         <v>99.2</v>
       </c>
-      <c r="U136" s="28" t="s">
+      <c r="U136" s="29" t="s">
         <v>865</v>
       </c>
-      <c r="V136" s="28" t="s">
+      <c r="V136" s="29" t="s">
         <v>865</v>
       </c>
     </row>
@@ -14634,13 +14807,13 @@
       <c r="F137" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="G137" s="32" t="s">
+      <c r="G137" s="33" t="s">
         <v>869</v>
       </c>
-      <c r="H137" s="28" t="s">
+      <c r="H137" s="29" t="s">
         <v>869</v>
       </c>
-      <c r="I137" s="33" t="s">
+      <c r="I137" s="34" t="s">
         <v>870</v>
       </c>
       <c r="J137" s="1">
@@ -14680,10 +14853,10 @@
       <c r="T137" s="10">
         <v>99.4</v>
       </c>
-      <c r="U137" s="28" t="s">
+      <c r="U137" s="29" t="s">
         <v>871</v>
       </c>
-      <c r="V137" s="28" t="s">
+      <c r="V137" s="29" t="s">
         <v>871</v>
       </c>
     </row>
@@ -14700,13 +14873,13 @@
       <c r="F138" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="G138" s="32" t="s">
+      <c r="G138" s="33" t="s">
         <v>875</v>
       </c>
-      <c r="H138" s="28" t="s">
+      <c r="H138" s="29" t="s">
         <v>875</v>
       </c>
-      <c r="I138" s="33" t="s">
+      <c r="I138" s="34" t="s">
         <v>876</v>
       </c>
       <c r="J138" s="1">
@@ -14746,10 +14919,10 @@
       <c r="T138" s="10">
         <v>99.6</v>
       </c>
-      <c r="U138" s="28" t="s">
+      <c r="U138" s="29" t="s">
         <v>877</v>
       </c>
-      <c r="V138" s="28" t="s">
+      <c r="V138" s="29" t="s">
         <v>877</v>
       </c>
     </row>
@@ -14766,13 +14939,13 @@
       <c r="F139" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="G139" s="32" t="s">
+      <c r="G139" s="33" t="s">
         <v>881</v>
       </c>
-      <c r="H139" s="28" t="s">
+      <c r="H139" s="29" t="s">
         <v>881</v>
       </c>
-      <c r="I139" s="33" t="s">
+      <c r="I139" s="34" t="s">
         <v>882</v>
       </c>
       <c r="J139" s="1">
@@ -14812,10 +14985,10 @@
       <c r="T139" s="10">
         <v>99.8</v>
       </c>
-      <c r="U139" s="28" t="s">
+      <c r="U139" s="29" t="s">
         <v>883</v>
       </c>
-      <c r="V139" s="28" t="s">
+      <c r="V139" s="29" t="s">
         <v>883</v>
       </c>
     </row>
@@ -14832,13 +15005,13 @@
       <c r="F140" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="G140" s="32" t="s">
+      <c r="G140" s="33" t="s">
         <v>887</v>
       </c>
-      <c r="H140" s="28" t="s">
+      <c r="H140" s="29" t="s">
         <v>887</v>
       </c>
-      <c r="I140" s="33" t="s">
+      <c r="I140" s="34" t="s">
         <v>888</v>
       </c>
       <c r="J140" s="1">
@@ -14878,10 +15051,10 @@
       <c r="T140" s="10">
         <v>99.9</v>
       </c>
-      <c r="U140" s="28" t="s">
+      <c r="U140" s="29" t="s">
         <v>889</v>
       </c>
-      <c r="V140" s="28" t="s">
+      <c r="V140" s="29" t="s">
         <v>889</v>
       </c>
     </row>
@@ -14900,13 +15073,13 @@
       <c r="F141" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="G141" s="32" t="s">
+      <c r="G141" s="33" t="s">
         <v>893</v>
       </c>
-      <c r="H141" s="28" t="s">
+      <c r="H141" s="29" t="s">
         <v>893</v>
       </c>
-      <c r="I141" s="33" t="s">
+      <c r="I141" s="34" t="s">
         <v>894</v>
       </c>
       <c r="J141" s="1">
@@ -14945,10 +15118,10 @@
       <c r="T141" s="10">
         <v>99.92</v>
       </c>
-      <c r="U141" s="28" t="s">
+      <c r="U141" s="29" t="s">
         <v>895</v>
       </c>
-      <c r="V141" s="28" t="s">
+      <c r="V141" s="29" t="s">
         <v>895</v>
       </c>
       <c r="W141" s="10"/>
@@ -14972,13 +15145,13 @@
       <c r="F142" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="G142" s="32" t="s">
+      <c r="G142" s="33" t="s">
         <v>899</v>
       </c>
-      <c r="H142" s="28" t="s">
+      <c r="H142" s="29" t="s">
         <v>899</v>
       </c>
-      <c r="I142" s="33" t="s">
+      <c r="I142" s="34" t="s">
         <v>900</v>
       </c>
       <c r="J142" s="1">
@@ -15017,10 +15190,10 @@
       <c r="T142" s="10">
         <v>99.94</v>
       </c>
-      <c r="U142" s="28" t="s">
+      <c r="U142" s="29" t="s">
         <v>901</v>
       </c>
-      <c r="V142" s="28" t="s">
+      <c r="V142" s="29" t="s">
         <v>901</v>
       </c>
       <c r="W142" s="10"/>
@@ -15044,13 +15217,13 @@
       <c r="F143" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="G143" s="32" t="s">
+      <c r="G143" s="33" t="s">
         <v>905</v>
       </c>
-      <c r="H143" s="28" t="s">
+      <c r="H143" s="29" t="s">
         <v>905</v>
       </c>
-      <c r="I143" s="33" t="s">
+      <c r="I143" s="34" t="s">
         <v>906</v>
       </c>
       <c r="J143" s="1">
@@ -15089,10 +15262,10 @@
       <c r="T143" s="10">
         <v>99.96</v>
       </c>
-      <c r="U143" s="28" t="s">
+      <c r="U143" s="29" t="s">
         <v>907</v>
       </c>
-      <c r="V143" s="28" t="s">
+      <c r="V143" s="29" t="s">
         <v>907</v>
       </c>
       <c r="W143" s="10"/>
@@ -15116,13 +15289,13 @@
       <c r="F144" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="G144" s="32" t="s">
+      <c r="G144" s="33" t="s">
         <v>911</v>
       </c>
-      <c r="H144" s="28" t="s">
+      <c r="H144" s="29" t="s">
         <v>911</v>
       </c>
-      <c r="I144" s="33" t="s">
+      <c r="I144" s="34" t="s">
         <v>912</v>
       </c>
       <c r="J144" s="1">
@@ -15161,10 +15334,10 @@
       <c r="T144" s="10">
         <v>99.98</v>
       </c>
-      <c r="U144" s="28" t="s">
+      <c r="U144" s="29" t="s">
         <v>913</v>
       </c>
-      <c r="V144" s="28" t="s">
+      <c r="V144" s="29" t="s">
         <v>913</v>
       </c>
       <c r="W144" s="10"/>
@@ -15233,10 +15406,10 @@
       <c r="T145" s="10">
         <v>99.99</v>
       </c>
-      <c r="U145" s="28" t="s">
+      <c r="U145" s="29" t="s">
         <v>919</v>
       </c>
-      <c r="V145" s="28" t="s">
+      <c r="V145" s="29" t="s">
         <v>919</v>
       </c>
       <c r="W145" s="10"/>
@@ -15305,10 +15478,10 @@
       <c r="T146" s="18">
         <v>99.99</v>
       </c>
-      <c r="U146" s="34" t="s">
+      <c r="U146" s="35" t="s">
         <v>927</v>
       </c>
-      <c r="V146" s="34" t="s">
+      <c r="V146" s="35" t="s">
         <v>927</v>
       </c>
       <c r="Y146" s="18"/>
@@ -15376,10 +15549,10 @@
       <c r="T147" s="10">
         <v>99.99</v>
       </c>
-      <c r="U147" s="28" t="s">
+      <c r="U147" s="29" t="s">
         <v>935</v>
       </c>
-      <c r="V147" s="28" t="s">
+      <c r="V147" s="29" t="s">
         <v>935</v>
       </c>
       <c r="Y147" s="10"/>
@@ -15447,10 +15620,10 @@
       <c r="T148" s="10">
         <v>99.99</v>
       </c>
-      <c r="U148" s="28" t="s">
+      <c r="U148" s="29" t="s">
         <v>943</v>
       </c>
-      <c r="V148" s="28" t="s">
+      <c r="V148" s="29" t="s">
         <v>943</v>
       </c>
       <c r="Y148" s="10"/>
@@ -15518,10 +15691,10 @@
       <c r="T149" s="10">
         <v>99.99</v>
       </c>
-      <c r="U149" s="28" t="s">
+      <c r="U149" s="29" t="s">
         <v>951</v>
       </c>
-      <c r="V149" s="28" t="s">
+      <c r="V149" s="29" t="s">
         <v>951</v>
       </c>
       <c r="Y149" s="10"/>
@@ -15589,10 +15762,10 @@
       <c r="T150" s="10">
         <v>99.99</v>
       </c>
-      <c r="U150" s="28" t="s">
+      <c r="U150" s="29" t="s">
         <v>959</v>
       </c>
-      <c r="V150" s="28" t="s">
+      <c r="V150" s="29" t="s">
         <v>959</v>
       </c>
       <c r="Y150" s="10"/>
@@ -15659,10 +15832,10 @@
       <c r="T151" s="10">
         <v>99.99</v>
       </c>
-      <c r="U151" s="28" t="s">
+      <c r="U151" s="29" t="s">
         <v>968</v>
       </c>
-      <c r="V151" s="28" t="s">
+      <c r="V151" s="29" t="s">
         <v>968</v>
       </c>
       <c r="W151" s="10"/>
@@ -15731,10 +15904,10 @@
       <c r="T152" s="10">
         <v>99.99</v>
       </c>
-      <c r="U152" s="28" t="s">
+      <c r="U152" s="29" t="s">
         <v>977</v>
       </c>
-      <c r="V152" s="28" t="s">
+      <c r="V152" s="29" t="s">
         <v>977</v>
       </c>
       <c r="W152" s="10"/>
@@ -15803,10 +15976,10 @@
       <c r="T153" s="10">
         <v>99.99</v>
       </c>
-      <c r="U153" s="28" t="s">
+      <c r="U153" s="29" t="s">
         <v>986</v>
       </c>
-      <c r="V153" s="28" t="s">
+      <c r="V153" s="29" t="s">
         <v>986</v>
       </c>
       <c r="W153" s="10"/>
@@ -15875,10 +16048,10 @@
       <c r="T154" s="10">
         <v>99.99</v>
       </c>
-      <c r="U154" s="28" t="s">
+      <c r="U154" s="29" t="s">
         <v>995</v>
       </c>
-      <c r="V154" s="28" t="s">
+      <c r="V154" s="29" t="s">
         <v>995</v>
       </c>
       <c r="W154" s="10"/>
@@ -15947,10 +16120,10 @@
       <c r="T155" s="10">
         <v>99.99</v>
       </c>
-      <c r="U155" s="28" t="s">
+      <c r="U155" s="29" t="s">
         <v>1004</v>
       </c>
-      <c r="V155" s="28" t="s">
+      <c r="V155" s="29" t="s">
         <v>1004</v>
       </c>
       <c r="W155" s="10"/>
@@ -16019,10 +16192,10 @@
       <c r="T156" s="10">
         <v>99.99</v>
       </c>
-      <c r="U156" s="28" t="s">
+      <c r="U156" s="29" t="s">
         <v>1013</v>
       </c>
-      <c r="V156" s="28" t="s">
+      <c r="V156" s="29" t="s">
         <v>1013</v>
       </c>
       <c r="W156" s="10"/>
@@ -16091,10 +16264,10 @@
       <c r="T157" s="10">
         <v>99.99</v>
       </c>
-      <c r="U157" s="28" t="s">
+      <c r="U157" s="29" t="s">
         <v>1022</v>
       </c>
-      <c r="V157" s="28" t="s">
+      <c r="V157" s="29" t="s">
         <v>1022</v>
       </c>
       <c r="W157" s="10"/>
@@ -16163,10 +16336,10 @@
       <c r="T158" s="10">
         <v>99.99</v>
       </c>
-      <c r="U158" s="28" t="s">
+      <c r="U158" s="29" t="s">
         <v>1031</v>
       </c>
-      <c r="V158" s="28" t="s">
+      <c r="V158" s="29" t="s">
         <v>1031</v>
       </c>
       <c r="W158" s="10"/>
@@ -16235,10 +16408,10 @@
       <c r="T159" s="10">
         <v>99.99</v>
       </c>
-      <c r="U159" s="28" t="s">
+      <c r="U159" s="29" t="s">
         <v>1040</v>
       </c>
-      <c r="V159" s="28" t="s">
+      <c r="V159" s="29" t="s">
         <v>1040</v>
       </c>
       <c r="W159" s="10"/>
@@ -16307,10 +16480,10 @@
       <c r="T160" s="10">
         <v>99.99</v>
       </c>
-      <c r="U160" s="28" t="s">
+      <c r="U160" s="29" t="s">
         <v>1049</v>
       </c>
-      <c r="V160" s="28" t="s">
+      <c r="V160" s="29" t="s">
         <v>1049</v>
       </c>
       <c r="W160" s="10"/>
@@ -16379,10 +16552,10 @@
       <c r="T161" s="10">
         <v>99.99</v>
       </c>
-      <c r="U161" s="28" t="s">
+      <c r="U161" s="29" t="s">
         <v>1058</v>
       </c>
-      <c r="V161" s="28" t="s">
+      <c r="V161" s="29" t="s">
         <v>1058</v>
       </c>
       <c r="W161" s="10"/>
@@ -16451,10 +16624,10 @@
       <c r="T162" s="10">
         <v>99.99</v>
       </c>
-      <c r="U162" s="28" t="s">
+      <c r="U162" s="29" t="s">
         <v>1067</v>
       </c>
-      <c r="V162" s="28" t="s">
+      <c r="V162" s="29" t="s">
         <v>1067</v>
       </c>
       <c r="W162" s="10"/>
@@ -16523,10 +16696,10 @@
       <c r="T163" s="10">
         <v>99.99</v>
       </c>
-      <c r="U163" s="28" t="s">
+      <c r="U163" s="29" t="s">
         <v>1076</v>
       </c>
-      <c r="V163" s="28" t="s">
+      <c r="V163" s="29" t="s">
         <v>1076</v>
       </c>
       <c r="W163" s="10"/>
@@ -16596,10 +16769,10 @@
       <c r="T164" s="21">
         <v>99.99</v>
       </c>
-      <c r="U164" s="35" t="s">
+      <c r="U164" s="36" t="s">
         <v>1085</v>
       </c>
-      <c r="V164" s="35" t="s">
+      <c r="V164" s="36" t="s">
         <v>1085</v>
       </c>
       <c r="W164" s="21"/>
@@ -16623,7 +16796,7 @@
       <c r="F165" s="4" t="s">
         <v>1088</v>
       </c>
-      <c r="G165" s="36" t="s">
+      <c r="G165" s="37" t="s">
         <v>1089</v>
       </c>
       <c r="H165" s="4" t="s">
@@ -16669,10 +16842,10 @@
       <c r="T165" s="8">
         <v>99.99</v>
       </c>
-      <c r="U165" s="37" t="s">
+      <c r="U165" s="38" t="s">
         <v>1094</v>
       </c>
-      <c r="V165" s="37" t="s">
+      <c r="V165" s="38" t="s">
         <v>1094</v>
       </c>
       <c r="W165" s="8"/>
@@ -16694,20 +16867,20 @@
       <c r="F166" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="G166" s="38" t="s">
+      <c r="G166" s="39" t="s">
         <v>1098</v>
       </c>
-      <c r="H166" s="38" t="s">
+      <c r="H166" s="39" t="s">
         <v>1099</v>
       </c>
-      <c r="I166" s="38" t="s">
+      <c r="I166" s="39" t="s">
         <v>1100</v>
       </c>
-      <c r="J166" s="38" t="s">
+      <c r="J166" s="39" t="s">
         <v>1101</v>
       </c>
       <c r="K166" s="1"/>
-      <c r="L166" s="38" t="s">
+      <c r="L166" s="39" t="s">
         <v>1102</v>
       </c>
       <c r="M166" s="1">
@@ -16740,10 +16913,10 @@
       <c r="T166" s="10">
         <v>99.99</v>
       </c>
-      <c r="U166" s="28" t="s">
+      <c r="U166" s="29" t="s">
         <v>1103</v>
       </c>
-      <c r="V166" s="28" t="s">
+      <c r="V166" s="29" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -16760,20 +16933,20 @@
       <c r="F167" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="G167" s="38" t="s">
+      <c r="G167" s="39" t="s">
         <v>1107</v>
       </c>
-      <c r="H167" s="38" t="s">
+      <c r="H167" s="39" t="s">
         <v>1108</v>
       </c>
-      <c r="I167" s="38" t="s">
+      <c r="I167" s="39" t="s">
         <v>1109</v>
       </c>
-      <c r="J167" s="38" t="s">
+      <c r="J167" s="39" t="s">
         <v>1110</v>
       </c>
       <c r="K167" s="1"/>
-      <c r="L167" s="38" t="s">
+      <c r="L167" s="39" t="s">
         <v>1111</v>
       </c>
       <c r="M167" s="1">
@@ -16806,10 +16979,10 @@
       <c r="T167" s="10">
         <v>99.99</v>
       </c>
-      <c r="U167" s="28" t="s">
+      <c r="U167" s="29" t="s">
         <v>1112</v>
       </c>
-      <c r="V167" s="28" t="s">
+      <c r="V167" s="29" t="s">
         <v>1112</v>
       </c>
     </row>
@@ -16826,20 +16999,20 @@
       <c r="F168" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="G168" s="38" t="s">
+      <c r="G168" s="39" t="s">
         <v>1116</v>
       </c>
-      <c r="H168" s="38" t="s">
+      <c r="H168" s="39" t="s">
         <v>1117</v>
       </c>
-      <c r="I168" s="38" t="s">
+      <c r="I168" s="39" t="s">
         <v>1118</v>
       </c>
-      <c r="J168" s="38" t="s">
+      <c r="J168" s="39" t="s">
         <v>1119</v>
       </c>
       <c r="K168" s="1"/>
-      <c r="L168" s="38" t="s">
+      <c r="L168" s="39" t="s">
         <v>1120</v>
       </c>
       <c r="M168" s="1">
@@ -16872,10 +17045,10 @@
       <c r="T168" s="10">
         <v>99.99</v>
       </c>
-      <c r="U168" s="28" t="s">
+      <c r="U168" s="29" t="s">
         <v>1121</v>
       </c>
-      <c r="V168" s="28" t="s">
+      <c r="V168" s="29" t="s">
         <v>1121</v>
       </c>
     </row>
@@ -16892,20 +17065,20 @@
       <c r="F169" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="G169" s="38" t="s">
+      <c r="G169" s="39" t="s">
         <v>1125</v>
       </c>
-      <c r="H169" s="38" t="s">
+      <c r="H169" s="39" t="s">
         <v>1126</v>
       </c>
-      <c r="I169" s="38" t="s">
+      <c r="I169" s="39" t="s">
         <v>1127</v>
       </c>
-      <c r="J169" s="38" t="s">
+      <c r="J169" s="39" t="s">
         <v>1128</v>
       </c>
       <c r="K169" s="1"/>
-      <c r="L169" s="38" t="s">
+      <c r="L169" s="39" t="s">
         <v>1129</v>
       </c>
       <c r="M169" s="1">
@@ -16938,10 +17111,10 @@
       <c r="T169" s="10">
         <v>99.99</v>
       </c>
-      <c r="U169" s="28" t="s">
+      <c r="U169" s="29" t="s">
         <v>1130</v>
       </c>
-      <c r="V169" s="28" t="s">
+      <c r="V169" s="29" t="s">
         <v>1130</v>
       </c>
     </row>
@@ -16958,20 +17131,20 @@
       <c r="F170" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="G170" s="38" t="s">
+      <c r="G170" s="39" t="s">
         <v>1134</v>
       </c>
-      <c r="H170" s="38" t="s">
+      <c r="H170" s="39" t="s">
         <v>1135</v>
       </c>
-      <c r="I170" s="38" t="s">
+      <c r="I170" s="39" t="s">
         <v>1136</v>
       </c>
-      <c r="J170" s="38" t="s">
+      <c r="J170" s="39" t="s">
         <v>1137</v>
       </c>
       <c r="K170" s="1"/>
-      <c r="L170" s="38" t="s">
+      <c r="L170" s="39" t="s">
         <v>1138</v>
       </c>
       <c r="M170" s="1">
@@ -17004,10 +17177,10 @@
       <c r="T170" s="10">
         <v>99.99</v>
       </c>
-      <c r="U170" s="28" t="s">
+      <c r="U170" s="29" t="s">
         <v>1139</v>
       </c>
-      <c r="V170" s="28" t="s">
+      <c r="V170" s="29" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -17024,20 +17197,20 @@
       <c r="F171" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="G171" s="38" t="s">
+      <c r="G171" s="39" t="s">
         <v>1143</v>
       </c>
-      <c r="H171" s="38" t="s">
+      <c r="H171" s="39" t="s">
         <v>1144</v>
       </c>
-      <c r="I171" s="38" t="s">
+      <c r="I171" s="39" t="s">
         <v>1145</v>
       </c>
-      <c r="J171" s="38" t="s">
+      <c r="J171" s="39" t="s">
         <v>1146</v>
       </c>
       <c r="K171" s="1"/>
-      <c r="L171" s="38" t="s">
+      <c r="L171" s="39" t="s">
         <v>1147</v>
       </c>
       <c r="M171" s="1">
@@ -17070,10 +17243,10 @@
       <c r="T171" s="10">
         <v>99.99</v>
       </c>
-      <c r="U171" s="28" t="s">
+      <c r="U171" s="29" t="s">
         <v>1148</v>
       </c>
-      <c r="V171" s="28" t="s">
+      <c r="V171" s="29" t="s">
         <v>1148</v>
       </c>
     </row>
@@ -17090,20 +17263,20 @@
       <c r="F172" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="G172" s="38" t="s">
+      <c r="G172" s="39" t="s">
         <v>1152</v>
       </c>
-      <c r="H172" s="38" t="s">
+      <c r="H172" s="39" t="s">
         <v>1153</v>
       </c>
-      <c r="I172" s="38" t="s">
+      <c r="I172" s="39" t="s">
         <v>1154</v>
       </c>
-      <c r="J172" s="38" t="s">
+      <c r="J172" s="39" t="s">
         <v>1155</v>
       </c>
       <c r="K172" s="1"/>
-      <c r="L172" s="38" t="s">
+      <c r="L172" s="39" t="s">
         <v>1156</v>
       </c>
       <c r="M172" s="1">
@@ -17136,10 +17309,10 @@
       <c r="T172" s="10">
         <v>99.99</v>
       </c>
-      <c r="U172" s="28" t="s">
+      <c r="U172" s="29" t="s">
         <v>1157</v>
       </c>
-      <c r="V172" s="28" t="s">
+      <c r="V172" s="29" t="s">
         <v>1157</v>
       </c>
     </row>
@@ -17156,20 +17329,20 @@
       <c r="F173" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="G173" s="38" t="s">
+      <c r="G173" s="39" t="s">
         <v>1161</v>
       </c>
-      <c r="H173" s="38" t="s">
+      <c r="H173" s="39" t="s">
         <v>1162</v>
       </c>
-      <c r="I173" s="38" t="s">
+      <c r="I173" s="39" t="s">
         <v>1163</v>
       </c>
-      <c r="J173" s="38" t="s">
+      <c r="J173" s="39" t="s">
         <v>1164</v>
       </c>
       <c r="K173" s="1"/>
-      <c r="L173" s="38" t="s">
+      <c r="L173" s="39" t="s">
         <v>1165</v>
       </c>
       <c r="M173" s="1">
@@ -17202,10 +17375,10 @@
       <c r="T173" s="10">
         <v>99.99</v>
       </c>
-      <c r="U173" s="28" t="s">
+      <c r="U173" s="29" t="s">
         <v>1166</v>
       </c>
-      <c r="V173" s="28" t="s">
+      <c r="V173" s="29" t="s">
         <v>1166</v>
       </c>
     </row>
@@ -17222,20 +17395,20 @@
       <c r="F174" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="G174" s="38" t="s">
+      <c r="G174" s="39" t="s">
         <v>1170</v>
       </c>
-      <c r="H174" s="38" t="s">
+      <c r="H174" s="39" t="s">
         <v>1171</v>
       </c>
-      <c r="I174" s="38" t="s">
+      <c r="I174" s="39" t="s">
         <v>1172</v>
       </c>
-      <c r="J174" s="38" t="s">
+      <c r="J174" s="39" t="s">
         <v>1173</v>
       </c>
       <c r="K174" s="1"/>
-      <c r="L174" s="38" t="s">
+      <c r="L174" s="39" t="s">
         <v>1174</v>
       </c>
       <c r="M174" s="1">
@@ -17268,10 +17441,10 @@
       <c r="T174" s="10">
         <v>99.99</v>
       </c>
-      <c r="U174" s="28" t="s">
+      <c r="U174" s="29" t="s">
         <v>1175</v>
       </c>
-      <c r="V174" s="28" t="s">
+      <c r="V174" s="29" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -17288,20 +17461,20 @@
       <c r="F175" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="G175" s="38" t="s">
+      <c r="G175" s="39" t="s">
         <v>1179</v>
       </c>
-      <c r="H175" s="38" t="s">
+      <c r="H175" s="39" t="s">
         <v>1180</v>
       </c>
-      <c r="I175" s="38" t="s">
+      <c r="I175" s="39" t="s">
         <v>1181</v>
       </c>
-      <c r="J175" s="38" t="s">
+      <c r="J175" s="39" t="s">
         <v>1182</v>
       </c>
       <c r="K175" s="1"/>
-      <c r="L175" s="38" t="s">
+      <c r="L175" s="39" t="s">
         <v>1183</v>
       </c>
       <c r="M175" s="1">
@@ -17334,10 +17507,10 @@
       <c r="T175" s="10">
         <v>99.99</v>
       </c>
-      <c r="U175" s="28" t="s">
+      <c r="U175" s="29" t="s">
         <v>1184</v>
       </c>
-      <c r="V175" s="28" t="s">
+      <c r="V175" s="29" t="s">
         <v>1184</v>
       </c>
     </row>
@@ -17356,19 +17529,19 @@
       <c r="F176" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="G176" s="38" t="s">
+      <c r="G176" s="39" t="s">
         <v>1188</v>
       </c>
-      <c r="H176" s="38" t="s">
+      <c r="H176" s="39" t="s">
         <v>1189</v>
       </c>
-      <c r="I176" s="38" t="s">
+      <c r="I176" s="39" t="s">
         <v>1190</v>
       </c>
-      <c r="J176" s="38" t="s">
+      <c r="J176" s="39" t="s">
         <v>1191</v>
       </c>
-      <c r="L176" s="38" t="s">
+      <c r="L176" s="39" t="s">
         <v>1192</v>
       </c>
       <c r="M176" s="1">
@@ -17401,10 +17574,10 @@
       <c r="T176" s="10">
         <v>99.99</v>
       </c>
-      <c r="U176" s="28" t="s">
+      <c r="U176" s="29" t="s">
         <v>1193</v>
       </c>
-      <c r="V176" s="28" t="s">
+      <c r="V176" s="29" t="s">
         <v>1193</v>
       </c>
       <c r="W176" s="10"/>
@@ -17428,19 +17601,19 @@
       <c r="F177" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="G177" s="38" t="s">
+      <c r="G177" s="39" t="s">
         <v>1197</v>
       </c>
-      <c r="H177" s="38" t="s">
+      <c r="H177" s="39" t="s">
         <v>1198</v>
       </c>
-      <c r="I177" s="38" t="s">
+      <c r="I177" s="39" t="s">
         <v>1199</v>
       </c>
-      <c r="J177" s="38" t="s">
+      <c r="J177" s="39" t="s">
         <v>1200</v>
       </c>
-      <c r="L177" s="38" t="s">
+      <c r="L177" s="39" t="s">
         <v>1201</v>
       </c>
       <c r="M177" s="1">
@@ -17473,10 +17646,10 @@
       <c r="T177" s="10">
         <v>99.99</v>
       </c>
-      <c r="U177" s="28" t="s">
+      <c r="U177" s="29" t="s">
         <v>1202</v>
       </c>
-      <c r="V177" s="28" t="s">
+      <c r="V177" s="29" t="s">
         <v>1202</v>
       </c>
       <c r="W177" s="10"/>
@@ -17500,19 +17673,19 @@
       <c r="F178" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="G178" s="38" t="s">
+      <c r="G178" s="39" t="s">
         <v>1206</v>
       </c>
-      <c r="H178" s="38" t="s">
+      <c r="H178" s="39" t="s">
         <v>1207</v>
       </c>
-      <c r="I178" s="38" t="s">
+      <c r="I178" s="39" t="s">
         <v>1208</v>
       </c>
-      <c r="J178" s="38" t="s">
+      <c r="J178" s="39" t="s">
         <v>1209</v>
       </c>
-      <c r="L178" s="38" t="s">
+      <c r="L178" s="39" t="s">
         <v>1210</v>
       </c>
       <c r="M178" s="1">
@@ -17545,10 +17718,10 @@
       <c r="T178" s="10">
         <v>99.99</v>
       </c>
-      <c r="U178" s="28" t="s">
+      <c r="U178" s="29" t="s">
         <v>1211</v>
       </c>
-      <c r="V178" s="28" t="s">
+      <c r="V178" s="29" t="s">
         <v>1211</v>
       </c>
       <c r="W178" s="10"/>
@@ -17572,19 +17745,19 @@
       <c r="F179" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="G179" s="38" t="s">
+      <c r="G179" s="39" t="s">
         <v>1215</v>
       </c>
-      <c r="H179" s="38" t="s">
+      <c r="H179" s="39" t="s">
         <v>1216</v>
       </c>
-      <c r="I179" s="38" t="s">
+      <c r="I179" s="39" t="s">
         <v>1217</v>
       </c>
-      <c r="J179" s="38" t="s">
+      <c r="J179" s="39" t="s">
         <v>1218</v>
       </c>
-      <c r="L179" s="38" t="s">
+      <c r="L179" s="39" t="s">
         <v>1219</v>
       </c>
       <c r="M179" s="1">
@@ -17617,10 +17790,10 @@
       <c r="T179" s="10">
         <v>99.99</v>
       </c>
-      <c r="U179" s="28" t="s">
+      <c r="U179" s="29" t="s">
         <v>1220</v>
       </c>
-      <c r="V179" s="28" t="s">
+      <c r="V179" s="29" t="s">
         <v>1220</v>
       </c>
       <c r="W179" s="10"/>
@@ -17644,19 +17817,19 @@
       <c r="F180" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="G180" s="38" t="s">
+      <c r="G180" s="39" t="s">
         <v>1224</v>
       </c>
-      <c r="H180" s="38" t="s">
+      <c r="H180" s="39" t="s">
         <v>1225</v>
       </c>
-      <c r="I180" s="38" t="s">
+      <c r="I180" s="39" t="s">
         <v>1226</v>
       </c>
-      <c r="J180" s="38" t="s">
+      <c r="J180" s="39" t="s">
         <v>1227</v>
       </c>
-      <c r="L180" s="38" t="s">
+      <c r="L180" s="39" t="s">
         <v>1228</v>
       </c>
       <c r="M180" s="1">
@@ -17689,10 +17862,10 @@
       <c r="T180" s="10">
         <v>99.99</v>
       </c>
-      <c r="U180" s="28" t="s">
+      <c r="U180" s="29" t="s">
         <v>1229</v>
       </c>
-      <c r="V180" s="28" t="s">
+      <c r="V180" s="29" t="s">
         <v>1229</v>
       </c>
       <c r="W180" s="10"/>
@@ -17716,22 +17889,22 @@
       <c r="F181" s="2" t="s">
         <v>1230</v>
       </c>
-      <c r="G181" s="39" t="s">
+      <c r="G181" s="40" t="s">
         <v>1231</v>
       </c>
-      <c r="H181" s="39" t="s">
+      <c r="H181" s="40" t="s">
         <v>1232</v>
       </c>
-      <c r="I181" s="39" t="s">
+      <c r="I181" s="40" t="s">
         <v>1233</v>
       </c>
-      <c r="J181" s="39" t="s">
+      <c r="J181" s="40" t="s">
         <v>1234</v>
       </c>
-      <c r="K181" s="34" t="s">
+      <c r="K181" s="35" t="s">
         <v>1235</v>
       </c>
-      <c r="L181" s="39" t="s">
+      <c r="L181" s="40" t="s">
         <v>1236</v>
       </c>
       <c r="M181" s="2">
@@ -17760,10 +17933,10 @@
       <c r="T181" s="18">
         <v>99.99</v>
       </c>
-      <c r="U181" s="34" t="s">
+      <c r="U181" s="35" t="s">
         <v>1237</v>
       </c>
-      <c r="V181" s="34" t="s">
+      <c r="V181" s="35" t="s">
         <v>1237</v>
       </c>
       <c r="Y181" s="18"/>
@@ -17785,22 +17958,22 @@
       <c r="F182" s="5" t="s">
         <v>1238</v>
       </c>
-      <c r="G182" s="38" t="s">
+      <c r="G182" s="39" t="s">
         <v>1239</v>
       </c>
-      <c r="H182" s="38" t="s">
+      <c r="H182" s="39" t="s">
         <v>1240</v>
       </c>
-      <c r="I182" s="38" t="s">
+      <c r="I182" s="39" t="s">
         <v>1241</v>
       </c>
-      <c r="J182" s="38" t="s">
+      <c r="J182" s="39" t="s">
         <v>1242</v>
       </c>
-      <c r="K182" s="40" t="s">
+      <c r="K182" s="41" t="s">
         <v>1243</v>
       </c>
-      <c r="L182" s="38" t="s">
+      <c r="L182" s="39" t="s">
         <v>1244</v>
       </c>
       <c r="M182" s="5">
@@ -17834,10 +18007,10 @@
       <c r="T182" s="12">
         <v>99.99</v>
       </c>
-      <c r="U182" s="40" t="s">
+      <c r="U182" s="41" t="s">
         <v>1245</v>
       </c>
-      <c r="V182" s="40" t="s">
+      <c r="V182" s="41" t="s">
         <v>1245</v>
       </c>
       <c r="Y182" s="12"/>
@@ -17859,22 +18032,22 @@
       <c r="F183" s="5" t="s">
         <v>1246</v>
       </c>
-      <c r="G183" s="38" t="s">
+      <c r="G183" s="39" t="s">
         <v>1247</v>
       </c>
-      <c r="H183" s="38" t="s">
+      <c r="H183" s="39" t="s">
         <v>1248</v>
       </c>
-      <c r="I183" s="38" t="s">
+      <c r="I183" s="39" t="s">
         <v>1249</v>
       </c>
-      <c r="J183" s="38" t="s">
+      <c r="J183" s="39" t="s">
         <v>1250</v>
       </c>
-      <c r="K183" s="40" t="s">
+      <c r="K183" s="41" t="s">
         <v>1251</v>
       </c>
-      <c r="L183" s="38" t="s">
+      <c r="L183" s="39" t="s">
         <v>1252</v>
       </c>
       <c r="M183" s="5">
@@ -17908,10 +18081,10 @@
       <c r="T183" s="12">
         <v>99.99</v>
       </c>
-      <c r="U183" s="40" t="s">
+      <c r="U183" s="41" t="s">
         <v>1253</v>
       </c>
-      <c r="V183" s="40" t="s">
+      <c r="V183" s="41" t="s">
         <v>1253</v>
       </c>
       <c r="Y183" s="12"/>
@@ -17933,22 +18106,22 @@
       <c r="F184" s="5" t="s">
         <v>1254</v>
       </c>
-      <c r="G184" s="38" t="s">
+      <c r="G184" s="39" t="s">
         <v>1255</v>
       </c>
-      <c r="H184" s="38" t="s">
+      <c r="H184" s="39" t="s">
         <v>1256</v>
       </c>
-      <c r="I184" s="38" t="s">
+      <c r="I184" s="39" t="s">
         <v>1257</v>
       </c>
-      <c r="J184" s="38" t="s">
+      <c r="J184" s="39" t="s">
         <v>1258</v>
       </c>
-      <c r="K184" s="40" t="s">
+      <c r="K184" s="41" t="s">
         <v>1259</v>
       </c>
-      <c r="L184" s="38" t="s">
+      <c r="L184" s="39" t="s">
         <v>1260</v>
       </c>
       <c r="M184" s="5">
@@ -17982,10 +18155,10 @@
       <c r="T184" s="12">
         <v>99.99</v>
       </c>
-      <c r="U184" s="40" t="s">
+      <c r="U184" s="41" t="s">
         <v>1261</v>
       </c>
-      <c r="V184" s="40" t="s">
+      <c r="V184" s="41" t="s">
         <v>1261</v>
       </c>
       <c r="Y184" s="12"/>
@@ -18007,22 +18180,22 @@
       <c r="F185" s="5" t="s">
         <v>1262</v>
       </c>
-      <c r="G185" s="38" t="s">
+      <c r="G185" s="39" t="s">
         <v>1263</v>
       </c>
-      <c r="H185" s="38" t="s">
+      <c r="H185" s="39" t="s">
         <v>1264</v>
       </c>
-      <c r="I185" s="38" t="s">
+      <c r="I185" s="39" t="s">
         <v>1265</v>
       </c>
-      <c r="J185" s="38" t="s">
+      <c r="J185" s="39" t="s">
         <v>1266</v>
       </c>
-      <c r="K185" s="40" t="s">
+      <c r="K185" s="41" t="s">
         <v>1267</v>
       </c>
-      <c r="L185" s="38" t="s">
+      <c r="L185" s="39" t="s">
         <v>1268</v>
       </c>
       <c r="M185" s="5">
@@ -18056,10 +18229,10 @@
       <c r="T185" s="12">
         <v>99.99</v>
       </c>
-      <c r="U185" s="40" t="s">
+      <c r="U185" s="41" t="s">
         <v>1269</v>
       </c>
-      <c r="V185" s="40" t="s">
+      <c r="V185" s="41" t="s">
         <v>1269</v>
       </c>
       <c r="Y185" s="12"/>
@@ -18081,22 +18254,22 @@
       <c r="F186" s="6" t="s">
         <v>1270</v>
       </c>
-      <c r="G186" s="38" t="s">
+      <c r="G186" s="39" t="s">
         <v>1271</v>
       </c>
-      <c r="H186" s="36" t="s">
+      <c r="H186" s="37" t="s">
         <v>1272</v>
       </c>
-      <c r="I186" s="36" t="s">
+      <c r="I186" s="37" t="s">
         <v>1273</v>
       </c>
-      <c r="J186" s="36" t="s">
+      <c r="J186" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="K186" s="40" t="s">
+      <c r="K186" s="41" t="s">
         <v>1275</v>
       </c>
-      <c r="L186" s="36" t="s">
+      <c r="L186" s="37" t="s">
         <v>1276</v>
       </c>
       <c r="M186" s="6">
@@ -18130,10 +18303,10 @@
       <c r="T186" s="7">
         <v>99.99</v>
       </c>
-      <c r="U186" s="41" t="s">
+      <c r="U186" s="42" t="s">
         <v>1277</v>
       </c>
-      <c r="V186" s="41" t="s">
+      <c r="V186" s="42" t="s">
         <v>1277</v>
       </c>
       <c r="W186" s="7"/>
@@ -18157,22 +18330,22 @@
       <c r="F187" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="G187" s="38" t="s">
+      <c r="G187" s="39" t="s">
         <v>1279</v>
       </c>
-      <c r="H187" s="36" t="s">
+      <c r="H187" s="37" t="s">
         <v>1280</v>
       </c>
-      <c r="I187" s="36" t="s">
+      <c r="I187" s="37" t="s">
         <v>1281</v>
       </c>
-      <c r="J187" s="36" t="s">
+      <c r="J187" s="37" t="s">
         <v>1282</v>
       </c>
-      <c r="K187" s="40" t="s">
+      <c r="K187" s="41" t="s">
         <v>1283</v>
       </c>
-      <c r="L187" s="36" t="s">
+      <c r="L187" s="37" t="s">
         <v>1284</v>
       </c>
       <c r="M187" s="4">
@@ -18206,10 +18379,10 @@
       <c r="T187" s="8">
         <v>99.99</v>
       </c>
-      <c r="U187" s="37" t="s">
+      <c r="U187" s="38" t="s">
         <v>1285</v>
       </c>
-      <c r="V187" s="37" t="s">
+      <c r="V187" s="38" t="s">
         <v>1285</v>
       </c>
       <c r="W187" s="8"/>
@@ -18233,22 +18406,22 @@
       <c r="F188" s="4" t="s">
         <v>1286</v>
       </c>
-      <c r="G188" s="38" t="s">
+      <c r="G188" s="39" t="s">
         <v>1232</v>
       </c>
-      <c r="H188" s="36" t="s">
+      <c r="H188" s="37" t="s">
         <v>1287</v>
       </c>
-      <c r="I188" s="36" t="s">
+      <c r="I188" s="37" t="s">
         <v>1288</v>
       </c>
-      <c r="J188" s="36" t="s">
+      <c r="J188" s="37" t="s">
         <v>1289</v>
       </c>
-      <c r="K188" s="40" t="s">
+      <c r="K188" s="41" t="s">
         <v>1290</v>
       </c>
-      <c r="L188" s="36" t="s">
+      <c r="L188" s="37" t="s">
         <v>1255</v>
       </c>
       <c r="M188" s="4">
@@ -18282,10 +18455,10 @@
       <c r="T188" s="8">
         <v>99.99</v>
       </c>
-      <c r="U188" s="37" t="s">
+      <c r="U188" s="38" t="s">
         <v>1291</v>
       </c>
-      <c r="V188" s="37" t="s">
+      <c r="V188" s="38" t="s">
         <v>1291</v>
       </c>
       <c r="W188" s="8"/>
@@ -18309,22 +18482,22 @@
       <c r="F189" s="4" t="s">
         <v>1292</v>
       </c>
-      <c r="G189" s="38" t="s">
+      <c r="G189" s="39" t="s">
         <v>1293</v>
       </c>
-      <c r="H189" s="36" t="s">
+      <c r="H189" s="37" t="s">
         <v>1294</v>
       </c>
-      <c r="I189" s="36" t="s">
+      <c r="I189" s="37" t="s">
         <v>1295</v>
       </c>
-      <c r="J189" s="36" t="s">
+      <c r="J189" s="37" t="s">
         <v>1296</v>
       </c>
-      <c r="K189" s="40" t="s">
+      <c r="K189" s="41" t="s">
         <v>1297</v>
       </c>
-      <c r="L189" s="36" t="s">
+      <c r="L189" s="37" t="s">
         <v>1298</v>
       </c>
       <c r="M189" s="4">
@@ -18358,10 +18531,10 @@
       <c r="T189" s="8">
         <v>99.99</v>
       </c>
-      <c r="U189" s="37" t="s">
+      <c r="U189" s="38" t="s">
         <v>1299</v>
       </c>
-      <c r="V189" s="37" t="s">
+      <c r="V189" s="38" t="s">
         <v>1299</v>
       </c>
       <c r="W189" s="8"/>
@@ -18385,22 +18558,22 @@
       <c r="F190" s="4" t="s">
         <v>1300</v>
       </c>
-      <c r="G190" s="38" t="s">
+      <c r="G190" s="39" t="s">
         <v>1301</v>
       </c>
-      <c r="H190" s="36" t="s">
+      <c r="H190" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I190" s="36" t="s">
+      <c r="I190" s="37" t="s">
         <v>1303</v>
       </c>
-      <c r="J190" s="36" t="s">
+      <c r="J190" s="37" t="s">
         <v>1304</v>
       </c>
-      <c r="K190" s="40" t="s">
+      <c r="K190" s="41" t="s">
         <v>1305</v>
       </c>
-      <c r="L190" s="36" t="s">
+      <c r="L190" s="37" t="s">
         <v>1306</v>
       </c>
       <c r="M190" s="4">
@@ -18434,10 +18607,10 @@
       <c r="T190" s="8">
         <v>99.99</v>
       </c>
-      <c r="U190" s="37" t="s">
+      <c r="U190" s="38" t="s">
         <v>1307</v>
       </c>
-      <c r="V190" s="37" t="s">
+      <c r="V190" s="38" t="s">
         <v>1307</v>
       </c>
       <c r="W190" s="8"/>
@@ -18461,22 +18634,22 @@
       <c r="F191" s="6" t="s">
         <v>1308</v>
       </c>
-      <c r="G191" s="38" t="s">
+      <c r="G191" s="39" t="s">
         <v>1248</v>
       </c>
-      <c r="H191" s="36" t="s">
+      <c r="H191" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I191" s="36" t="s">
+      <c r="I191" s="37" t="s">
         <v>1309</v>
       </c>
-      <c r="J191" s="36" t="s">
+      <c r="J191" s="37" t="s">
         <v>1183</v>
       </c>
-      <c r="K191" s="40" t="s">
+      <c r="K191" s="41" t="s">
         <v>1310</v>
       </c>
-      <c r="L191" s="36" t="s">
+      <c r="L191" s="37" t="s">
         <v>1311</v>
       </c>
       <c r="M191" s="6">
@@ -18510,10 +18683,10 @@
       <c r="T191" s="7">
         <v>99.99</v>
       </c>
-      <c r="U191" s="41" t="s">
+      <c r="U191" s="42" t="s">
         <v>1312</v>
       </c>
-      <c r="V191" s="41" t="s">
+      <c r="V191" s="42" t="s">
         <v>1312</v>
       </c>
       <c r="W191" s="7"/>
@@ -18537,22 +18710,22 @@
       <c r="F192" s="4" t="s">
         <v>1313</v>
       </c>
-      <c r="G192" s="38" t="s">
+      <c r="G192" s="39" t="s">
         <v>1314</v>
       </c>
-      <c r="H192" s="36" t="s">
+      <c r="H192" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I192" s="36" t="s">
+      <c r="I192" s="37" t="s">
         <v>1315</v>
       </c>
-      <c r="J192" s="36" t="s">
+      <c r="J192" s="37" t="s">
         <v>1316</v>
       </c>
-      <c r="K192" s="40" t="s">
+      <c r="K192" s="41" t="s">
         <v>1317</v>
       </c>
-      <c r="L192" s="36" t="s">
+      <c r="L192" s="37" t="s">
         <v>1279</v>
       </c>
       <c r="M192" s="4">
@@ -18586,10 +18759,10 @@
       <c r="T192" s="8">
         <v>99.99</v>
       </c>
-      <c r="U192" s="37" t="s">
+      <c r="U192" s="38" t="s">
         <v>1318</v>
       </c>
-      <c r="V192" s="37" t="s">
+      <c r="V192" s="38" t="s">
         <v>1318</v>
       </c>
       <c r="W192" s="8"/>
@@ -18613,22 +18786,22 @@
       <c r="F193" s="4" t="s">
         <v>1319</v>
       </c>
-      <c r="G193" s="38" t="s">
+      <c r="G193" s="39" t="s">
         <v>1256</v>
       </c>
-      <c r="H193" s="36" t="s">
+      <c r="H193" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I193" s="36" t="s">
+      <c r="I193" s="37" t="s">
         <v>1320</v>
       </c>
-      <c r="J193" s="36" t="s">
+      <c r="J193" s="37" t="s">
         <v>1321</v>
       </c>
-      <c r="K193" s="40" t="s">
+      <c r="K193" s="41" t="s">
         <v>1322</v>
       </c>
-      <c r="L193" s="36" t="s">
+      <c r="L193" s="37" t="s">
         <v>1323</v>
       </c>
       <c r="M193" s="4">
@@ -18662,10 +18835,10 @@
       <c r="T193" s="8">
         <v>99.99</v>
       </c>
-      <c r="U193" s="37" t="s">
+      <c r="U193" s="38" t="s">
         <v>432</v>
       </c>
-      <c r="V193" s="37" t="s">
+      <c r="V193" s="38" t="s">
         <v>432</v>
       </c>
       <c r="W193" s="8"/>
@@ -18689,22 +18862,22 @@
       <c r="F194" s="4" t="s">
         <v>1324</v>
       </c>
-      <c r="G194" s="38" t="s">
+      <c r="G194" s="39" t="s">
         <v>1154</v>
       </c>
-      <c r="H194" s="36" t="s">
+      <c r="H194" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I194" s="36" t="s">
+      <c r="I194" s="37" t="s">
         <v>1325</v>
       </c>
-      <c r="J194" s="36" t="s">
+      <c r="J194" s="37" t="s">
         <v>1326</v>
       </c>
-      <c r="K194" s="40" t="s">
+      <c r="K194" s="41" t="s">
         <v>1327</v>
       </c>
-      <c r="L194" s="36" t="s">
+      <c r="L194" s="37" t="s">
         <v>1328</v>
       </c>
       <c r="M194" s="4">
@@ -18738,10 +18911,10 @@
       <c r="T194" s="8">
         <v>99.99</v>
       </c>
-      <c r="U194" s="37" t="s">
+      <c r="U194" s="38" t="s">
         <v>1329</v>
       </c>
-      <c r="V194" s="37" t="s">
+      <c r="V194" s="38" t="s">
         <v>1329</v>
       </c>
       <c r="W194" s="8"/>
@@ -18765,22 +18938,22 @@
       <c r="F195" s="4" t="s">
         <v>1330</v>
       </c>
-      <c r="G195" s="38" t="s">
+      <c r="G195" s="39" t="s">
         <v>1264</v>
       </c>
-      <c r="H195" s="36" t="s">
+      <c r="H195" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I195" s="36" t="s">
+      <c r="I195" s="37" t="s">
         <v>1331</v>
       </c>
-      <c r="J195" s="36" t="s">
+      <c r="J195" s="37" t="s">
         <v>1332</v>
       </c>
-      <c r="K195" s="40" t="s">
+      <c r="K195" s="41" t="s">
         <v>1333</v>
       </c>
-      <c r="L195" s="36" t="s">
+      <c r="L195" s="37" t="s">
         <v>1293</v>
       </c>
       <c r="M195" s="4">
@@ -18814,10 +18987,10 @@
       <c r="T195" s="8">
         <v>99.99</v>
       </c>
-      <c r="U195" s="37" t="s">
+      <c r="U195" s="38" t="s">
         <v>1334</v>
       </c>
-      <c r="V195" s="37" t="s">
+      <c r="V195" s="38" t="s">
         <v>1334</v>
       </c>
       <c r="W195" s="8"/>
@@ -18841,22 +19014,22 @@
       <c r="F196" s="6" t="s">
         <v>1335</v>
       </c>
-      <c r="G196" s="38" t="s">
+      <c r="G196" s="39" t="s">
         <v>1336</v>
       </c>
-      <c r="H196" s="36" t="s">
+      <c r="H196" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I196" s="36" t="s">
+      <c r="I196" s="37" t="s">
         <v>1337</v>
       </c>
-      <c r="J196" s="36" t="s">
+      <c r="J196" s="37" t="s">
         <v>1338</v>
       </c>
-      <c r="K196" s="40" t="s">
+      <c r="K196" s="41" t="s">
         <v>1339</v>
       </c>
-      <c r="L196" s="36" t="s">
+      <c r="L196" s="37" t="s">
         <v>1301</v>
       </c>
       <c r="M196" s="6">
@@ -18890,10 +19063,10 @@
       <c r="T196" s="7">
         <v>99.99</v>
       </c>
-      <c r="U196" s="41" t="s">
+      <c r="U196" s="42" t="s">
         <v>1340</v>
       </c>
-      <c r="V196" s="41" t="s">
+      <c r="V196" s="42" t="s">
         <v>1340</v>
       </c>
       <c r="W196" s="7"/>
@@ -18917,22 +19090,22 @@
       <c r="F197" s="4" t="s">
         <v>1341</v>
       </c>
-      <c r="G197" s="38" t="s">
+      <c r="G197" s="39" t="s">
         <v>1342</v>
       </c>
-      <c r="H197" s="36" t="s">
+      <c r="H197" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I197" s="36" t="s">
+      <c r="I197" s="37" t="s">
         <v>1343</v>
       </c>
-      <c r="J197" s="36" t="s">
+      <c r="J197" s="37" t="s">
         <v>1344</v>
       </c>
-      <c r="K197" s="40" t="s">
+      <c r="K197" s="41" t="s">
         <v>1345</v>
       </c>
-      <c r="L197" s="36" t="s">
+      <c r="L197" s="37" t="s">
         <v>1248</v>
       </c>
       <c r="M197" s="4">
@@ -18966,10 +19139,10 @@
       <c r="T197" s="8">
         <v>99.99</v>
       </c>
-      <c r="U197" s="37" t="s">
+      <c r="U197" s="38" t="s">
         <v>1346</v>
       </c>
-      <c r="V197" s="37" t="s">
+      <c r="V197" s="38" t="s">
         <v>1346</v>
       </c>
       <c r="W197" s="8"/>
@@ -18993,22 +19166,22 @@
       <c r="F198" s="4" t="s">
         <v>1347</v>
       </c>
-      <c r="G198" s="38" t="s">
+      <c r="G198" s="39" t="s">
         <v>1280</v>
       </c>
-      <c r="H198" s="36" t="s">
+      <c r="H198" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I198" s="36" t="s">
+      <c r="I198" s="37" t="s">
         <v>1348</v>
       </c>
-      <c r="J198" s="36" t="s">
+      <c r="J198" s="37" t="s">
         <v>1349</v>
       </c>
-      <c r="K198" s="40" t="s">
+      <c r="K198" s="41" t="s">
         <v>1350</v>
       </c>
-      <c r="L198" s="36" t="s">
+      <c r="L198" s="37" t="s">
         <v>1314</v>
       </c>
       <c r="M198" s="4">
@@ -19042,10 +19215,10 @@
       <c r="T198" s="8">
         <v>99.99</v>
       </c>
-      <c r="U198" s="37" t="s">
+      <c r="U198" s="38" t="s">
         <v>1351</v>
       </c>
-      <c r="V198" s="37" t="s">
+      <c r="V198" s="38" t="s">
         <v>1351</v>
       </c>
       <c r="W198" s="8"/>
@@ -19069,22 +19242,22 @@
       <c r="F199" s="4" t="s">
         <v>1352</v>
       </c>
-      <c r="G199" s="38" t="s">
+      <c r="G199" s="39" t="s">
         <v>1353</v>
       </c>
-      <c r="H199" s="36" t="s">
+      <c r="H199" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I199" s="36" t="s">
+      <c r="I199" s="37" t="s">
         <v>1354</v>
       </c>
-      <c r="J199" s="36" t="s">
+      <c r="J199" s="37" t="s">
         <v>1355</v>
       </c>
-      <c r="K199" s="40" t="s">
+      <c r="K199" s="41" t="s">
         <v>1356</v>
       </c>
-      <c r="L199" s="36" t="s">
+      <c r="L199" s="37" t="s">
         <v>1256</v>
       </c>
       <c r="M199" s="4">
@@ -19118,10 +19291,10 @@
       <c r="T199" s="8">
         <v>99.99</v>
       </c>
-      <c r="U199" s="37" t="s">
+      <c r="U199" s="38" t="s">
         <v>1357</v>
       </c>
-      <c r="V199" s="37" t="s">
+      <c r="V199" s="38" t="s">
         <v>1357</v>
       </c>
       <c r="W199" s="8"/>
@@ -19145,22 +19318,22 @@
       <c r="F200" s="4" t="s">
         <v>1358</v>
       </c>
-      <c r="G200" s="38" t="s">
+      <c r="G200" s="39" t="s">
         <v>1359</v>
       </c>
-      <c r="H200" s="36" t="s">
+      <c r="H200" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I200" s="36" t="s">
+      <c r="I200" s="37" t="s">
         <v>1360</v>
       </c>
-      <c r="J200" s="36" t="s">
+      <c r="J200" s="37" t="s">
         <v>1236</v>
       </c>
-      <c r="K200" s="40" t="s">
+      <c r="K200" s="41" t="s">
         <v>1361</v>
       </c>
-      <c r="L200" s="36" t="s">
+      <c r="L200" s="37" t="s">
         <v>1154</v>
       </c>
       <c r="M200" s="4">
@@ -19194,10 +19367,10 @@
       <c r="T200" s="8">
         <v>99.99</v>
       </c>
-      <c r="U200" s="37" t="s">
+      <c r="U200" s="38" t="s">
         <v>1362</v>
       </c>
-      <c r="V200" s="37" t="s">
+      <c r="V200" s="38" t="s">
         <v>1362</v>
       </c>
       <c r="W200" s="8"/>
@@ -19219,22 +19392,22 @@
       <c r="F201" s="6" t="s">
         <v>1363</v>
       </c>
-      <c r="G201" s="36" t="s">
+      <c r="G201" s="37" t="s">
         <v>1364</v>
       </c>
-      <c r="H201" s="36" t="s">
+      <c r="H201" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I201" s="36" t="s">
+      <c r="I201" s="37" t="s">
         <v>1365</v>
       </c>
-      <c r="J201" s="36" t="s">
+      <c r="J201" s="37" t="s">
         <v>1366</v>
       </c>
-      <c r="K201" s="40" t="s">
+      <c r="K201" s="41" t="s">
         <v>1242</v>
       </c>
-      <c r="L201" s="36" t="s">
+      <c r="L201" s="37" t="s">
         <v>1264</v>
       </c>
       <c r="M201" s="6">
@@ -19258,20 +19431,20 @@
         <v>113</v>
       </c>
       <c r="R201" s="7">
-        <f t="shared" ref="R201:R215" si="71">R200+15</f>
+        <f>R200+15</f>
         <v>444</v>
       </c>
       <c r="S201" s="7">
-        <f t="shared" ref="S201:S215" si="72">S200+15</f>
+        <f t="shared" ref="S201:S215" si="71">S200+15</f>
         <v>561</v>
       </c>
       <c r="T201" s="7">
         <v>99.99</v>
       </c>
-      <c r="U201" s="41" t="s">
+      <c r="U201" s="42" t="s">
         <v>1367</v>
       </c>
-      <c r="V201" s="41" t="s">
+      <c r="V201" s="42" t="s">
         <v>1367</v>
       </c>
       <c r="W201" s="6"/>
@@ -19290,59 +19463,59 @@
       <c r="F202" s="4" t="s">
         <v>1368</v>
       </c>
-      <c r="G202" s="36" t="s">
+      <c r="G202" s="37" t="s">
         <v>1369</v>
       </c>
-      <c r="H202" s="36" t="s">
+      <c r="H202" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I202" s="36" t="s">
+      <c r="I202" s="37" t="s">
         <v>1370</v>
       </c>
-      <c r="J202" s="36" t="s">
+      <c r="J202" s="37" t="s">
         <v>1371</v>
       </c>
-      <c r="K202" s="40" t="s">
+      <c r="K202" s="41" t="s">
         <v>1372</v>
       </c>
-      <c r="L202" s="36" t="s">
+      <c r="L202" s="37" t="s">
         <v>1336</v>
       </c>
       <c r="M202" s="4">
-        <f t="shared" ref="M202:P202" si="73">M201+5000</f>
+        <f t="shared" ref="M202:P202" si="72">M201+5000</f>
         <v>66000</v>
       </c>
       <c r="N202" s="4">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>66000</v>
       </c>
       <c r="O202" s="4">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>37750</v>
       </c>
       <c r="P202" s="4">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>37750</v>
       </c>
       <c r="Q202" s="4">
         <f t="shared" si="70"/>
         <v>119</v>
       </c>
-      <c r="R202" s="8">
+      <c r="R202" s="7">
+        <f>R201+15</f>
+        <v>459</v>
+      </c>
+      <c r="S202" s="8">
         <f t="shared" si="71"/>
-        <v>459</v>
-      </c>
-      <c r="S202" s="8">
-        <f t="shared" si="72"/>
         <v>576</v>
       </c>
       <c r="T202" s="8">
         <v>99.99</v>
       </c>
-      <c r="U202" s="37" t="s">
+      <c r="U202" s="38" t="s">
         <v>1373</v>
       </c>
-      <c r="V202" s="37" t="s">
+      <c r="V202" s="38" t="s">
         <v>1373</v>
       </c>
       <c r="W202" s="4"/>
@@ -19361,59 +19534,59 @@
       <c r="F203" s="4" t="s">
         <v>1374</v>
       </c>
-      <c r="G203" s="36" t="s">
+      <c r="G203" s="37" t="s">
         <v>1375</v>
       </c>
-      <c r="H203" s="36" t="s">
+      <c r="H203" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I203" s="36" t="s">
+      <c r="I203" s="37" t="s">
         <v>1376</v>
       </c>
-      <c r="J203" s="36" t="s">
+      <c r="J203" s="37" t="s">
         <v>1377</v>
       </c>
-      <c r="K203" s="40" t="s">
+      <c r="K203" s="41" t="s">
         <v>1266</v>
       </c>
-      <c r="L203" s="36" t="s">
+      <c r="L203" s="37" t="s">
         <v>1342</v>
       </c>
       <c r="M203" s="4">
-        <f t="shared" ref="M203:P203" si="74">M202+5000</f>
+        <f t="shared" ref="M203:P203" si="73">M202+5000</f>
         <v>71000</v>
       </c>
       <c r="N203" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>71000</v>
       </c>
       <c r="O203" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>42750</v>
       </c>
       <c r="P203" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>42750</v>
       </c>
       <c r="Q203" s="4">
         <f t="shared" si="70"/>
         <v>125</v>
       </c>
-      <c r="R203" s="8">
+      <c r="R203" s="7">
+        <f>R202+15</f>
+        <v>474</v>
+      </c>
+      <c r="S203" s="8">
         <f t="shared" si="71"/>
-        <v>474</v>
-      </c>
-      <c r="S203" s="8">
-        <f t="shared" si="72"/>
         <v>591</v>
       </c>
       <c r="T203" s="8">
         <v>99.99</v>
       </c>
-      <c r="U203" s="37" t="s">
+      <c r="U203" s="38" t="s">
         <v>1378</v>
       </c>
-      <c r="V203" s="37" t="s">
+      <c r="V203" s="38" t="s">
         <v>1378</v>
       </c>
       <c r="W203" s="4"/>
@@ -19432,59 +19605,59 @@
       <c r="F204" s="4" t="s">
         <v>1379</v>
       </c>
-      <c r="G204" s="36" t="s">
+      <c r="G204" s="37" t="s">
         <v>1380</v>
       </c>
-      <c r="H204" s="36" t="s">
+      <c r="H204" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I204" s="36" t="s">
+      <c r="I204" s="37" t="s">
         <v>1381</v>
       </c>
-      <c r="J204" s="36" t="s">
+      <c r="J204" s="37" t="s">
         <v>1244</v>
       </c>
-      <c r="K204" s="40" t="s">
+      <c r="K204" s="41" t="s">
         <v>1382</v>
       </c>
-      <c r="L204" s="36" t="s">
+      <c r="L204" s="37" t="s">
         <v>1280</v>
       </c>
       <c r="M204" s="4">
-        <f t="shared" ref="M204:P204" si="75">M203+5000</f>
+        <f t="shared" ref="M204:P204" si="74">M203+5000</f>
         <v>76000</v>
       </c>
       <c r="N204" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>76000</v>
       </c>
       <c r="O204" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>47750</v>
       </c>
       <c r="P204" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>47750</v>
       </c>
       <c r="Q204" s="4">
         <f t="shared" si="70"/>
         <v>131</v>
       </c>
-      <c r="R204" s="8">
+      <c r="R204" s="7">
+        <f>R203+15</f>
+        <v>489</v>
+      </c>
+      <c r="S204" s="8">
         <f t="shared" si="71"/>
-        <v>489</v>
-      </c>
-      <c r="S204" s="8">
-        <f t="shared" si="72"/>
         <v>606</v>
       </c>
       <c r="T204" s="8">
         <v>99.99</v>
       </c>
-      <c r="U204" s="37" t="s">
+      <c r="U204" s="38" t="s">
         <v>1383</v>
       </c>
-      <c r="V204" s="37" t="s">
+      <c r="V204" s="38" t="s">
         <v>1383</v>
       </c>
       <c r="W204" s="4"/>
@@ -19503,22 +19676,22 @@
       <c r="F205" s="4" t="s">
         <v>1384</v>
       </c>
-      <c r="G205" s="36" t="s">
+      <c r="G205" s="37" t="s">
         <v>1385</v>
       </c>
-      <c r="H205" s="36" t="s">
+      <c r="H205" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I205" s="36" t="s">
+      <c r="I205" s="37" t="s">
         <v>1386</v>
       </c>
-      <c r="J205" s="36" t="s">
+      <c r="J205" s="37" t="s">
         <v>1387</v>
       </c>
-      <c r="K205" s="40" t="s">
+      <c r="K205" s="41" t="s">
         <v>1289</v>
       </c>
-      <c r="L205" s="36" t="s">
+      <c r="L205" s="37" t="s">
         <v>1353</v>
       </c>
       <c r="M205" s="4">
@@ -19541,21 +19714,21 @@
         <f t="shared" si="70"/>
         <v>137</v>
       </c>
-      <c r="R205" s="8">
+      <c r="R205" s="7">
+        <f>R204+15</f>
+        <v>504</v>
+      </c>
+      <c r="S205" s="8">
         <f t="shared" si="71"/>
-        <v>504</v>
-      </c>
-      <c r="S205" s="8">
-        <f t="shared" si="72"/>
         <v>621</v>
       </c>
       <c r="T205" s="8">
         <v>99.99</v>
       </c>
-      <c r="U205" s="37" t="s">
+      <c r="U205" s="38" t="s">
         <v>1388</v>
       </c>
-      <c r="V205" s="37" t="s">
+      <c r="V205" s="38" t="s">
         <v>1388</v>
       </c>
       <c r="W205" s="4"/>
@@ -19574,38 +19747,38 @@
       <c r="F206" s="6" t="s">
         <v>1389</v>
       </c>
-      <c r="G206" s="36" t="s">
+      <c r="G206" s="37" t="s">
         <v>1249</v>
       </c>
-      <c r="H206" s="36" t="s">
+      <c r="H206" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I206" s="36" t="s">
+      <c r="I206" s="37" t="s">
         <v>1390</v>
       </c>
-      <c r="J206" s="36" t="s">
+      <c r="J206" s="37" t="s">
         <v>1391</v>
       </c>
-      <c r="K206" s="40" t="s">
+      <c r="K206" s="41" t="s">
         <v>1392</v>
       </c>
-      <c r="L206" s="36" t="s">
+      <c r="L206" s="37" t="s">
         <v>1359</v>
       </c>
       <c r="M206" s="6">
-        <f t="shared" ref="M206:M210" si="76">M205+10000</f>
+        <f t="shared" ref="M206:M210" si="75">M205+10000</f>
         <v>91000</v>
       </c>
       <c r="N206" s="6">
-        <f t="shared" ref="N206:N210" si="77">N205+10000</f>
+        <f t="shared" ref="N206:N210" si="76">N205+10000</f>
         <v>91000</v>
       </c>
       <c r="O206" s="6">
-        <f t="shared" ref="O206:O210" si="78">O205+10000</f>
+        <f t="shared" ref="O206:O210" si="77">O205+10000</f>
         <v>62750</v>
       </c>
       <c r="P206" s="6">
-        <f t="shared" ref="P206:P210" si="79">P205+10000</f>
+        <f t="shared" ref="P206:P210" si="78">P205+10000</f>
         <v>62750</v>
       </c>
       <c r="Q206" s="6">
@@ -19613,20 +19786,20 @@
         <v>143</v>
       </c>
       <c r="R206" s="7">
+        <f>R205+15</f>
+        <v>519</v>
+      </c>
+      <c r="S206" s="7">
         <f t="shared" si="71"/>
-        <v>519</v>
-      </c>
-      <c r="S206" s="7">
-        <f t="shared" si="72"/>
         <v>636</v>
       </c>
       <c r="T206" s="7">
         <v>99.99</v>
       </c>
-      <c r="U206" s="41" t="s">
+      <c r="U206" s="42" t="s">
         <v>1393</v>
       </c>
-      <c r="V206" s="41" t="s">
+      <c r="V206" s="42" t="s">
         <v>1393</v>
       </c>
       <c r="W206" s="6"/>
@@ -19645,59 +19818,59 @@
       <c r="F207" s="4" t="s">
         <v>1394</v>
       </c>
-      <c r="G207" s="36" t="s">
+      <c r="G207" s="37" t="s">
         <v>1395</v>
       </c>
-      <c r="H207" s="36" t="s">
+      <c r="H207" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I207" s="36" t="s">
+      <c r="I207" s="37" t="s">
         <v>1396</v>
       </c>
-      <c r="J207" s="36" t="s">
+      <c r="J207" s="37" t="s">
         <v>1397</v>
       </c>
-      <c r="K207" s="40" t="s">
+      <c r="K207" s="41" t="s">
         <v>1183</v>
       </c>
-      <c r="L207" s="36" t="s">
+      <c r="L207" s="37" t="s">
         <v>1294</v>
       </c>
       <c r="M207" s="4">
+        <f t="shared" si="75"/>
+        <v>101000</v>
+      </c>
+      <c r="N207" s="4">
         <f t="shared" si="76"/>
         <v>101000</v>
       </c>
-      <c r="N207" s="4">
+      <c r="O207" s="4">
         <f t="shared" si="77"/>
-        <v>101000</v>
-      </c>
-      <c r="O207" s="4">
+        <v>72750</v>
+      </c>
+      <c r="P207" s="4">
         <f t="shared" si="78"/>
-        <v>72750</v>
-      </c>
-      <c r="P207" s="4">
-        <f t="shared" si="79"/>
         <v>72750</v>
       </c>
       <c r="Q207" s="6">
         <f t="shared" si="70"/>
         <v>149</v>
       </c>
-      <c r="R207" s="8">
+      <c r="R207" s="7">
+        <f>R206+15</f>
+        <v>534</v>
+      </c>
+      <c r="S207" s="8">
         <f t="shared" si="71"/>
-        <v>534</v>
-      </c>
-      <c r="S207" s="8">
-        <f t="shared" si="72"/>
         <v>651</v>
       </c>
       <c r="T207" s="8">
         <v>99.99</v>
       </c>
-      <c r="U207" s="37" t="s">
+      <c r="U207" s="38" t="s">
         <v>1398</v>
       </c>
-      <c r="V207" s="37" t="s">
+      <c r="V207" s="38" t="s">
         <v>1398</v>
       </c>
       <c r="W207" s="4"/>
@@ -19716,59 +19889,59 @@
       <c r="F208" s="4" t="s">
         <v>1399</v>
       </c>
-      <c r="G208" s="36" t="s">
+      <c r="G208" s="37" t="s">
         <v>1257</v>
       </c>
-      <c r="H208" s="36" t="s">
+      <c r="H208" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I208" s="36" t="s">
+      <c r="I208" s="37" t="s">
         <v>1400</v>
       </c>
-      <c r="J208" s="36" t="s">
+      <c r="J208" s="37" t="s">
         <v>1252</v>
       </c>
-      <c r="K208" s="40" t="s">
+      <c r="K208" s="41" t="s">
         <v>1401</v>
       </c>
-      <c r="L208" s="36" t="s">
+      <c r="L208" s="37" t="s">
         <v>1233</v>
       </c>
       <c r="M208" s="4">
+        <f t="shared" si="75"/>
+        <v>111000</v>
+      </c>
+      <c r="N208" s="4">
         <f t="shared" si="76"/>
         <v>111000</v>
       </c>
-      <c r="N208" s="4">
+      <c r="O208" s="4">
         <f t="shared" si="77"/>
-        <v>111000</v>
-      </c>
-      <c r="O208" s="4">
+        <v>82750</v>
+      </c>
+      <c r="P208" s="4">
         <f t="shared" si="78"/>
-        <v>82750</v>
-      </c>
-      <c r="P208" s="4">
-        <f t="shared" si="79"/>
         <v>82750</v>
       </c>
       <c r="Q208" s="6">
         <f t="shared" si="70"/>
         <v>155</v>
       </c>
-      <c r="R208" s="8">
+      <c r="R208" s="7">
+        <f>R207+15</f>
+        <v>549</v>
+      </c>
+      <c r="S208" s="8">
         <f t="shared" si="71"/>
-        <v>549</v>
-      </c>
-      <c r="S208" s="8">
-        <f t="shared" si="72"/>
         <v>666</v>
       </c>
       <c r="T208" s="8">
         <v>99.99</v>
       </c>
-      <c r="U208" s="37" t="s">
+      <c r="U208" s="38" t="s">
         <v>1402</v>
       </c>
-      <c r="V208" s="37" t="s">
+      <c r="V208" s="38" t="s">
         <v>1402</v>
       </c>
       <c r="W208" s="4"/>
@@ -19787,59 +19960,59 @@
       <c r="F209" s="4" t="s">
         <v>1403</v>
       </c>
-      <c r="G209" s="36" t="s">
+      <c r="G209" s="37" t="s">
         <v>1404</v>
       </c>
-      <c r="H209" s="36" t="s">
+      <c r="H209" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I209" s="36" t="s">
+      <c r="I209" s="37" t="s">
         <v>1405</v>
       </c>
-      <c r="J209" s="36" t="s">
+      <c r="J209" s="37" t="s">
         <v>1406</v>
       </c>
-      <c r="K209" s="40" t="s">
+      <c r="K209" s="41" t="s">
         <v>1326</v>
       </c>
-      <c r="L209" s="36" t="s">
+      <c r="L209" s="37" t="s">
         <v>1407</v>
       </c>
       <c r="M209" s="4">
+        <f t="shared" si="75"/>
+        <v>121000</v>
+      </c>
+      <c r="N209" s="4">
         <f t="shared" si="76"/>
         <v>121000</v>
       </c>
-      <c r="N209" s="4">
+      <c r="O209" s="4">
         <f t="shared" si="77"/>
-        <v>121000</v>
-      </c>
-      <c r="O209" s="4">
+        <v>92750</v>
+      </c>
+      <c r="P209" s="4">
         <f t="shared" si="78"/>
-        <v>92750</v>
-      </c>
-      <c r="P209" s="4">
-        <f t="shared" si="79"/>
         <v>92750</v>
       </c>
       <c r="Q209" s="6">
         <f t="shared" si="70"/>
         <v>161</v>
       </c>
-      <c r="R209" s="8">
+      <c r="R209" s="7">
+        <f>R208+15</f>
+        <v>564</v>
+      </c>
+      <c r="S209" s="8">
         <f t="shared" si="71"/>
-        <v>564</v>
-      </c>
-      <c r="S209" s="8">
-        <f t="shared" si="72"/>
         <v>681</v>
       </c>
       <c r="T209" s="8">
         <v>99.99</v>
       </c>
-      <c r="U209" s="37" t="s">
+      <c r="U209" s="38" t="s">
         <v>1408</v>
       </c>
-      <c r="V209" s="37" t="s">
+      <c r="V209" s="38" t="s">
         <v>1408</v>
       </c>
       <c r="W209" s="4"/>
@@ -19858,59 +20031,59 @@
       <c r="F210" s="4" t="s">
         <v>1409</v>
       </c>
-      <c r="G210" s="36" t="s">
+      <c r="G210" s="37" t="s">
         <v>1410</v>
       </c>
-      <c r="H210" s="36" t="s">
+      <c r="H210" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I210" s="36" t="s">
+      <c r="I210" s="37" t="s">
         <v>1411</v>
       </c>
-      <c r="J210" s="36" t="s">
+      <c r="J210" s="37" t="s">
         <v>1412</v>
       </c>
-      <c r="K210" s="40" t="s">
+      <c r="K210" s="41" t="s">
         <v>1338</v>
       </c>
-      <c r="L210" s="36" t="s">
+      <c r="L210" s="37" t="s">
         <v>1241</v>
       </c>
       <c r="M210" s="4">
+        <f t="shared" si="75"/>
+        <v>131000</v>
+      </c>
+      <c r="N210" s="4">
         <f t="shared" si="76"/>
         <v>131000</v>
       </c>
-      <c r="N210" s="4">
+      <c r="O210" s="4">
         <f t="shared" si="77"/>
-        <v>131000</v>
-      </c>
-      <c r="O210" s="4">
+        <v>102750</v>
+      </c>
+      <c r="P210" s="4">
         <f t="shared" si="78"/>
-        <v>102750</v>
-      </c>
-      <c r="P210" s="4">
-        <f t="shared" si="79"/>
         <v>102750</v>
       </c>
       <c r="Q210" s="6">
         <f t="shared" si="70"/>
         <v>167</v>
       </c>
-      <c r="R210" s="8">
+      <c r="R210" s="7">
+        <f>R209+15</f>
+        <v>579</v>
+      </c>
+      <c r="S210" s="8">
         <f t="shared" si="71"/>
-        <v>579</v>
-      </c>
-      <c r="S210" s="8">
-        <f t="shared" si="72"/>
         <v>696</v>
       </c>
       <c r="T210" s="8">
         <v>99.99</v>
       </c>
-      <c r="U210" s="37" t="s">
+      <c r="U210" s="38" t="s">
         <v>1413</v>
       </c>
-      <c r="V210" s="37" t="s">
+      <c r="V210" s="38" t="s">
         <v>1413</v>
       </c>
       <c r="W210" s="4"/>
@@ -19931,59 +20104,59 @@
       <c r="F211" s="4" t="s">
         <v>1414</v>
       </c>
-      <c r="G211" s="36" t="s">
+      <c r="G211" s="37" t="s">
         <v>1273</v>
       </c>
-      <c r="H211" s="36" t="s">
+      <c r="H211" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I211" s="36" t="s">
+      <c r="I211" s="37" t="s">
         <v>1415</v>
       </c>
-      <c r="J211" s="36" t="s">
+      <c r="J211" s="37" t="s">
         <v>1416</v>
       </c>
-      <c r="K211" s="40" t="s">
+      <c r="K211" s="41" t="s">
         <v>1355</v>
       </c>
-      <c r="L211" s="36" t="s">
+      <c r="L211" s="37" t="s">
         <v>1417</v>
       </c>
       <c r="M211" s="4">
-        <f t="shared" ref="M211:M215" si="80">M210+20000</f>
+        <f t="shared" ref="M211:M215" si="79">M210+20000</f>
         <v>151000</v>
       </c>
       <c r="N211" s="4">
-        <f t="shared" ref="N211:N215" si="81">N210+20000</f>
+        <f t="shared" ref="N211:N215" si="80">N210+20000</f>
         <v>151000</v>
       </c>
       <c r="O211" s="4">
-        <f t="shared" ref="O211:O215" si="82">O210+20000</f>
+        <f t="shared" ref="O211:O215" si="81">O210+20000</f>
         <v>122750</v>
       </c>
       <c r="P211" s="4">
-        <f t="shared" ref="P211:P215" si="83">P210+20000</f>
+        <f t="shared" ref="P211:P215" si="82">P210+20000</f>
         <v>122750</v>
       </c>
       <c r="Q211" s="6">
         <f t="shared" si="70"/>
         <v>173</v>
       </c>
-      <c r="R211" s="8">
-        <f t="shared" ref="R211:R235" si="84">R210+20</f>
-        <v>599</v>
+      <c r="R211" s="7">
+        <f>R210+15</f>
+        <v>594</v>
       </c>
       <c r="S211" s="8">
-        <f t="shared" ref="S211:S215" si="85">S210+20</f>
+        <f t="shared" ref="S211:S215" si="83">S210+20</f>
         <v>716</v>
       </c>
       <c r="T211" s="8">
         <v>99.99</v>
       </c>
-      <c r="U211" s="37" t="s">
+      <c r="U211" s="38" t="s">
         <v>1418</v>
       </c>
-      <c r="V211" s="37" t="s">
+      <c r="V211" s="38" t="s">
         <v>1418</v>
       </c>
       <c r="W211" s="8"/>
@@ -20007,59 +20180,59 @@
       <c r="F212" s="4" t="s">
         <v>1419</v>
       </c>
-      <c r="G212" s="36" t="s">
+      <c r="G212" s="37" t="s">
         <v>1420</v>
       </c>
-      <c r="H212" s="36" t="s">
+      <c r="H212" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I212" s="36" t="s">
+      <c r="I212" s="37" t="s">
         <v>1421</v>
       </c>
-      <c r="J212" s="36" t="s">
+      <c r="J212" s="37" t="s">
         <v>1260</v>
       </c>
-      <c r="K212" s="40" t="s">
+      <c r="K212" s="41" t="s">
         <v>1371</v>
       </c>
-      <c r="L212" s="36" t="s">
+      <c r="L212" s="37" t="s">
         <v>1249</v>
       </c>
       <c r="M212" s="4">
+        <f t="shared" si="79"/>
+        <v>171000</v>
+      </c>
+      <c r="N212" s="4">
         <f t="shared" si="80"/>
         <v>171000</v>
       </c>
-      <c r="N212" s="4">
+      <c r="O212" s="4">
         <f t="shared" si="81"/>
-        <v>171000</v>
-      </c>
-      <c r="O212" s="4">
+        <v>142750</v>
+      </c>
+      <c r="P212" s="4">
         <f t="shared" si="82"/>
-        <v>142750</v>
-      </c>
-      <c r="P212" s="4">
-        <f t="shared" si="83"/>
         <v>142750</v>
       </c>
       <c r="Q212" s="6">
         <f t="shared" si="70"/>
         <v>179</v>
       </c>
-      <c r="R212" s="8">
-        <f t="shared" si="84"/>
-        <v>619</v>
+      <c r="R212" s="7">
+        <f>R211+15</f>
+        <v>609</v>
       </c>
       <c r="S212" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>736</v>
       </c>
       <c r="T212" s="8">
         <v>99.99</v>
       </c>
-      <c r="U212" s="37" t="s">
+      <c r="U212" s="38" t="s">
         <v>1422</v>
       </c>
-      <c r="V212" s="37" t="s">
+      <c r="V212" s="38" t="s">
         <v>1422</v>
       </c>
       <c r="W212" s="8"/>
@@ -20083,59 +20256,59 @@
       <c r="F213" s="4" t="s">
         <v>1423</v>
       </c>
-      <c r="G213" s="36" t="s">
+      <c r="G213" s="37" t="s">
         <v>1424</v>
       </c>
-      <c r="H213" s="36" t="s">
+      <c r="H213" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I213" s="36" t="s">
+      <c r="I213" s="37" t="s">
         <v>1425</v>
       </c>
-      <c r="J213" s="36" t="s">
+      <c r="J213" s="37" t="s">
         <v>1231</v>
       </c>
-      <c r="K213" s="40" t="s">
+      <c r="K213" s="41" t="s">
         <v>1387</v>
       </c>
-      <c r="L213" s="36" t="s">
+      <c r="L213" s="37" t="s">
         <v>1395</v>
       </c>
       <c r="M213" s="4">
+        <f t="shared" si="79"/>
+        <v>191000</v>
+      </c>
+      <c r="N213" s="4">
         <f t="shared" si="80"/>
         <v>191000</v>
       </c>
-      <c r="N213" s="4">
+      <c r="O213" s="4">
         <f t="shared" si="81"/>
-        <v>191000</v>
-      </c>
-      <c r="O213" s="4">
+        <v>162750</v>
+      </c>
+      <c r="P213" s="4">
         <f t="shared" si="82"/>
-        <v>162750</v>
-      </c>
-      <c r="P213" s="4">
-        <f t="shared" si="83"/>
         <v>162750</v>
       </c>
       <c r="Q213" s="6">
         <f t="shared" si="70"/>
         <v>185</v>
       </c>
-      <c r="R213" s="8">
-        <f t="shared" si="84"/>
-        <v>639</v>
+      <c r="R213" s="7">
+        <f>R212+15</f>
+        <v>624</v>
       </c>
       <c r="S213" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>756</v>
       </c>
       <c r="T213" s="8">
         <v>99.99</v>
       </c>
-      <c r="U213" s="37" t="s">
+      <c r="U213" s="38" t="s">
         <v>1426</v>
       </c>
-      <c r="V213" s="37" t="s">
+      <c r="V213" s="38" t="s">
         <v>1426</v>
       </c>
       <c r="W213" s="8"/>
@@ -20159,59 +20332,59 @@
       <c r="F214" s="4" t="s">
         <v>1427</v>
       </c>
-      <c r="G214" s="36" t="s">
+      <c r="G214" s="37" t="s">
         <v>1288</v>
       </c>
-      <c r="H214" s="36" t="s">
+      <c r="H214" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I214" s="36" t="s">
+      <c r="I214" s="37" t="s">
         <v>1428</v>
       </c>
-      <c r="J214" s="36" t="s">
+      <c r="J214" s="37" t="s">
         <v>1429</v>
       </c>
-      <c r="K214" s="40" t="s">
+      <c r="K214" s="41" t="s">
         <v>1252</v>
       </c>
-      <c r="L214" s="36" t="s">
+      <c r="L214" s="37" t="s">
         <v>1257</v>
       </c>
       <c r="M214" s="4">
+        <f t="shared" si="79"/>
+        <v>211000</v>
+      </c>
+      <c r="N214" s="4">
         <f t="shared" si="80"/>
         <v>211000</v>
       </c>
-      <c r="N214" s="4">
+      <c r="O214" s="4">
         <f t="shared" si="81"/>
-        <v>211000</v>
-      </c>
-      <c r="O214" s="4">
+        <v>182750</v>
+      </c>
+      <c r="P214" s="4">
         <f t="shared" si="82"/>
-        <v>182750</v>
-      </c>
-      <c r="P214" s="4">
-        <f t="shared" si="83"/>
         <v>182750</v>
       </c>
       <c r="Q214" s="6">
         <f t="shared" si="70"/>
         <v>191</v>
       </c>
-      <c r="R214" s="8">
-        <f t="shared" si="84"/>
-        <v>659</v>
+      <c r="R214" s="7">
+        <f>R213+15</f>
+        <v>639</v>
       </c>
       <c r="S214" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>776</v>
       </c>
       <c r="T214" s="8">
         <v>99.99</v>
       </c>
-      <c r="U214" s="37" t="s">
+      <c r="U214" s="38" t="s">
         <v>1430</v>
       </c>
-      <c r="V214" s="37" t="s">
+      <c r="V214" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="W214" s="8"/>
@@ -20235,59 +20408,59 @@
       <c r="F215" s="4" t="s">
         <v>1431</v>
       </c>
-      <c r="G215" s="36" t="s">
+      <c r="G215" s="37" t="s">
         <v>1432</v>
       </c>
-      <c r="H215" s="36" t="s">
+      <c r="H215" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I215" s="36" t="s">
+      <c r="I215" s="37" t="s">
         <v>1433</v>
       </c>
-      <c r="J215" s="36" t="s">
+      <c r="J215" s="37" t="s">
         <v>1434</v>
       </c>
-      <c r="K215" s="40" t="s">
+      <c r="K215" s="41" t="s">
         <v>1416</v>
       </c>
-      <c r="L215" s="36" t="s">
+      <c r="L215" s="37" t="s">
         <v>1404</v>
       </c>
       <c r="M215" s="4">
+        <f t="shared" si="79"/>
+        <v>231000</v>
+      </c>
+      <c r="N215" s="4">
         <f t="shared" si="80"/>
         <v>231000</v>
       </c>
-      <c r="N215" s="4">
+      <c r="O215" s="4">
         <f t="shared" si="81"/>
-        <v>231000</v>
-      </c>
-      <c r="O215" s="4">
+        <v>202750</v>
+      </c>
+      <c r="P215" s="4">
         <f t="shared" si="82"/>
-        <v>202750</v>
-      </c>
-      <c r="P215" s="4">
-        <f t="shared" si="83"/>
         <v>202750</v>
       </c>
       <c r="Q215" s="6">
         <f t="shared" si="70"/>
         <v>197</v>
       </c>
-      <c r="R215" s="8">
-        <f t="shared" si="84"/>
-        <v>679</v>
+      <c r="R215" s="7">
+        <f>R214+15</f>
+        <v>654</v>
       </c>
       <c r="S215" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>796</v>
       </c>
       <c r="T215" s="8">
         <v>99.99</v>
       </c>
-      <c r="U215" s="37" t="s">
+      <c r="U215" s="38" t="s">
         <v>1435</v>
       </c>
-      <c r="V215" s="37" t="s">
+      <c r="V215" s="38" t="s">
         <v>1435</v>
       </c>
       <c r="W215" s="8"/>
@@ -20311,59 +20484,59 @@
       <c r="F216" s="2" t="s">
         <v>1436</v>
       </c>
-      <c r="G216" s="39" t="s">
+      <c r="G216" s="40" t="s">
         <v>1437</v>
       </c>
-      <c r="H216" s="36" t="s">
+      <c r="H216" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I216" s="39" t="s">
+      <c r="I216" s="40" t="s">
         <v>1438</v>
       </c>
-      <c r="J216" s="39" t="s">
+      <c r="J216" s="40" t="s">
         <v>1276</v>
       </c>
-      <c r="K216" s="34" t="s">
+      <c r="K216" s="35" t="s">
         <v>1434</v>
       </c>
-      <c r="L216" s="39" t="s">
+      <c r="L216" s="40" t="s">
         <v>1439</v>
       </c>
       <c r="M216" s="4">
-        <f t="shared" ref="M216:P216" si="86">M215+30000</f>
+        <f t="shared" ref="M216:P216" si="84">M215+30000</f>
         <v>261000</v>
       </c>
       <c r="N216" s="4">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>261000</v>
       </c>
       <c r="O216" s="4">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>232750</v>
       </c>
       <c r="P216" s="4">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>232750</v>
       </c>
       <c r="Q216" s="6">
-        <f t="shared" ref="Q216:Q235" si="87">Q215+7</f>
+        <f t="shared" ref="Q216:Q250" si="85">Q215+7</f>
         <v>204</v>
       </c>
-      <c r="R216" s="8">
-        <f t="shared" si="84"/>
-        <v>699</v>
+      <c r="R216" s="7">
+        <f t="shared" ref="R216:R250" si="86">R215+18</f>
+        <v>672</v>
       </c>
       <c r="S216" s="8">
-        <f t="shared" ref="S216:S235" si="88">S215+30</f>
+        <f t="shared" ref="S216:S250" si="87">S215+30</f>
         <v>826</v>
       </c>
       <c r="T216" s="8">
         <v>99.99</v>
       </c>
-      <c r="U216" s="37" t="s">
+      <c r="U216" s="38" t="s">
         <v>1440</v>
       </c>
-      <c r="V216" s="37" t="s">
+      <c r="V216" s="38" t="s">
         <v>1440</v>
       </c>
       <c r="W216" s="8"/>
@@ -20388,59 +20561,59 @@
       <c r="F217" s="5" t="s">
         <v>1441</v>
       </c>
-      <c r="G217" s="38" t="s">
+      <c r="G217" s="39" t="s">
         <v>1381</v>
       </c>
-      <c r="H217" s="36" t="s">
+      <c r="H217" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I217" s="38" t="s">
+      <c r="I217" s="39" t="s">
         <v>1442</v>
       </c>
-      <c r="J217" s="40" t="s">
+      <c r="J217" s="41" t="s">
         <v>1284</v>
       </c>
-      <c r="K217" s="40" t="s">
+      <c r="K217" s="41" t="s">
         <v>1276</v>
       </c>
-      <c r="L217" s="38" t="s">
+      <c r="L217" s="39" t="s">
         <v>1443</v>
       </c>
       <c r="M217" s="4">
-        <f t="shared" ref="M217:P217" si="89">M216+30000</f>
+        <f t="shared" ref="M217:P217" si="88">M216+30000</f>
         <v>291000</v>
       </c>
       <c r="N217" s="4">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>291000</v>
       </c>
       <c r="O217" s="4">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>262750</v>
       </c>
       <c r="P217" s="4">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>262750</v>
       </c>
       <c r="Q217" s="6">
+        <f t="shared" si="85"/>
+        <v>211</v>
+      </c>
+      <c r="R217" s="7">
+        <f t="shared" si="86"/>
+        <v>690</v>
+      </c>
+      <c r="S217" s="8">
         <f t="shared" si="87"/>
-        <v>211</v>
-      </c>
-      <c r="R217" s="8">
-        <f t="shared" si="84"/>
-        <v>719</v>
-      </c>
-      <c r="S217" s="8">
-        <f t="shared" si="88"/>
         <v>856</v>
       </c>
       <c r="T217" s="8">
         <v>99.99</v>
       </c>
-      <c r="U217" s="37" t="s">
+      <c r="U217" s="38" t="s">
         <v>1444</v>
       </c>
-      <c r="V217" s="37" t="s">
+      <c r="V217" s="38" t="s">
         <v>1444</v>
       </c>
       <c r="W217" s="8"/>
@@ -20465,59 +20638,59 @@
       <c r="F218" s="5" t="s">
         <v>1445</v>
       </c>
-      <c r="G218" s="38" t="s">
+      <c r="G218" s="39" t="s">
         <v>1446</v>
       </c>
-      <c r="H218" s="36" t="s">
+      <c r="H218" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I218" s="38" t="s">
+      <c r="I218" s="39" t="s">
         <v>1447</v>
       </c>
-      <c r="J218" s="38" t="s">
+      <c r="J218" s="39" t="s">
         <v>1255</v>
       </c>
-      <c r="K218" s="38" t="s">
+      <c r="K218" s="39" t="s">
         <v>1448</v>
       </c>
-      <c r="L218" s="38" t="s">
+      <c r="L218" s="39" t="s">
         <v>1449</v>
       </c>
       <c r="M218" s="4">
-        <f t="shared" ref="M218:P218" si="90">M217+30000</f>
+        <f t="shared" ref="M218:P218" si="89">M217+30000</f>
         <v>321000</v>
       </c>
       <c r="N218" s="4">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>321000</v>
       </c>
       <c r="O218" s="4">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>292750</v>
       </c>
       <c r="P218" s="4">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>292750</v>
       </c>
       <c r="Q218" s="6">
+        <f t="shared" si="85"/>
+        <v>218</v>
+      </c>
+      <c r="R218" s="7">
+        <f t="shared" si="86"/>
+        <v>708</v>
+      </c>
+      <c r="S218" s="8">
         <f t="shared" si="87"/>
-        <v>218</v>
-      </c>
-      <c r="R218" s="8">
-        <f t="shared" si="84"/>
-        <v>739</v>
-      </c>
-      <c r="S218" s="8">
-        <f t="shared" si="88"/>
         <v>886</v>
       </c>
       <c r="T218" s="8">
         <v>99.99</v>
       </c>
-      <c r="U218" s="37" t="s">
+      <c r="U218" s="38" t="s">
         <v>1450</v>
       </c>
-      <c r="V218" s="37" t="s">
+      <c r="V218" s="38" t="s">
         <v>1450</v>
       </c>
       <c r="W218" s="8"/>
@@ -20542,59 +20715,59 @@
       <c r="F219" s="5" t="s">
         <v>1451</v>
       </c>
-      <c r="G219" s="38" t="s">
+      <c r="G219" s="39" t="s">
         <v>1405</v>
       </c>
-      <c r="H219" s="36" t="s">
+      <c r="H219" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I219" s="38" t="s">
+      <c r="I219" s="39" t="s">
         <v>1452</v>
       </c>
-      <c r="J219" s="38" t="s">
+      <c r="J219" s="39" t="s">
         <v>1298</v>
       </c>
-      <c r="K219" s="38" t="s">
+      <c r="K219" s="39" t="s">
         <v>1453</v>
       </c>
-      <c r="L219" s="38" t="s">
+      <c r="L219" s="39" t="s">
         <v>1354</v>
       </c>
       <c r="M219" s="4">
-        <f t="shared" ref="M219:P219" si="91">M218+30000</f>
+        <f t="shared" ref="M219:P219" si="90">M218+30000</f>
         <v>351000</v>
       </c>
       <c r="N219" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>351000</v>
       </c>
       <c r="O219" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>322750</v>
       </c>
       <c r="P219" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>322750</v>
       </c>
       <c r="Q219" s="6">
+        <f t="shared" si="85"/>
+        <v>225</v>
+      </c>
+      <c r="R219" s="7">
+        <f t="shared" si="86"/>
+        <v>726</v>
+      </c>
+      <c r="S219" s="8">
         <f t="shared" si="87"/>
-        <v>225</v>
-      </c>
-      <c r="R219" s="8">
-        <f t="shared" si="84"/>
-        <v>759</v>
-      </c>
-      <c r="S219" s="8">
-        <f t="shared" si="88"/>
         <v>916</v>
       </c>
       <c r="T219" s="8">
         <v>99.99</v>
       </c>
-      <c r="U219" s="37" t="s">
+      <c r="U219" s="38" t="s">
         <v>1454</v>
       </c>
-      <c r="V219" s="37" t="s">
+      <c r="V219" s="38" t="s">
         <v>1454</v>
       </c>
       <c r="W219" s="8"/>
@@ -20619,59 +20792,59 @@
       <c r="F220" s="5" t="s">
         <v>1455</v>
       </c>
-      <c r="G220" s="38" t="s">
+      <c r="G220" s="39" t="s">
         <v>1456</v>
       </c>
-      <c r="H220" s="36" t="s">
+      <c r="H220" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I220" s="38" t="s">
+      <c r="I220" s="39" t="s">
         <v>1457</v>
       </c>
-      <c r="J220" s="38" t="s">
+      <c r="J220" s="39" t="s">
         <v>1306</v>
       </c>
-      <c r="K220" s="38" t="s">
+      <c r="K220" s="39" t="s">
         <v>1306</v>
       </c>
-      <c r="L220" s="38" t="s">
+      <c r="L220" s="39" t="s">
         <v>1437</v>
       </c>
       <c r="M220" s="4">
-        <f t="shared" ref="M220:M235" si="92">M219+30000</f>
+        <f t="shared" ref="M220:M250" si="91">M219+30000</f>
         <v>381000</v>
       </c>
       <c r="N220" s="4">
-        <f t="shared" ref="N220:N235" si="93">N219+30000</f>
+        <f t="shared" ref="N220:N250" si="92">N219+30000</f>
         <v>381000</v>
       </c>
       <c r="O220" s="4">
-        <f t="shared" ref="O220:O235" si="94">O219+30000</f>
+        <f t="shared" ref="O220:O250" si="93">O219+30000</f>
         <v>352750</v>
       </c>
       <c r="P220" s="4">
-        <f t="shared" ref="P220:P235" si="95">P219+30000</f>
+        <f t="shared" ref="P220:P250" si="94">P219+30000</f>
         <v>352750</v>
       </c>
       <c r="Q220" s="6">
+        <f t="shared" si="85"/>
+        <v>232</v>
+      </c>
+      <c r="R220" s="7">
+        <f t="shared" si="86"/>
+        <v>744</v>
+      </c>
+      <c r="S220" s="8">
         <f t="shared" si="87"/>
-        <v>232</v>
-      </c>
-      <c r="R220" s="8">
-        <f t="shared" si="84"/>
-        <v>779</v>
-      </c>
-      <c r="S220" s="8">
-        <f t="shared" si="88"/>
         <v>946</v>
       </c>
       <c r="T220" s="8">
         <v>99.99</v>
       </c>
-      <c r="U220" s="37" t="s">
+      <c r="U220" s="38" t="s">
         <v>1458</v>
       </c>
-      <c r="V220" s="37" t="s">
+      <c r="V220" s="38" t="s">
         <v>1458</v>
       </c>
       <c r="W220" s="8"/>
@@ -20696,59 +20869,59 @@
       <c r="F221" s="6" t="s">
         <v>1459</v>
       </c>
-      <c r="G221" s="38" t="s">
+      <c r="G221" s="39" t="s">
         <v>1428</v>
       </c>
-      <c r="H221" s="36" t="s">
+      <c r="H221" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I221" s="38" t="s">
+      <c r="I221" s="39" t="s">
         <v>1460</v>
       </c>
-      <c r="J221" s="38" t="s">
+      <c r="J221" s="39" t="s">
         <v>1461</v>
       </c>
-      <c r="K221" s="38" t="s">
+      <c r="K221" s="39" t="s">
         <v>1461</v>
       </c>
-      <c r="L221" s="38" t="s">
+      <c r="L221" s="39" t="s">
         <v>1381</v>
       </c>
       <c r="M221" s="4">
+        <f t="shared" si="91"/>
+        <v>411000</v>
+      </c>
+      <c r="N221" s="4">
         <f t="shared" si="92"/>
         <v>411000</v>
       </c>
-      <c r="N221" s="4">
+      <c r="O221" s="4">
         <f t="shared" si="93"/>
-        <v>411000</v>
-      </c>
-      <c r="O221" s="4">
+        <v>382750</v>
+      </c>
+      <c r="P221" s="4">
         <f t="shared" si="94"/>
         <v>382750</v>
       </c>
-      <c r="P221" s="4">
-        <f t="shared" si="95"/>
-        <v>382750</v>
-      </c>
       <c r="Q221" s="6">
+        <f t="shared" si="85"/>
+        <v>239</v>
+      </c>
+      <c r="R221" s="7">
+        <f t="shared" si="86"/>
+        <v>762</v>
+      </c>
+      <c r="S221" s="8">
         <f t="shared" si="87"/>
-        <v>239</v>
-      </c>
-      <c r="R221" s="8">
-        <f t="shared" si="84"/>
-        <v>799</v>
-      </c>
-      <c r="S221" s="8">
-        <f t="shared" si="88"/>
         <v>976</v>
       </c>
       <c r="T221" s="8">
         <v>99.99</v>
       </c>
-      <c r="U221" s="37" t="s">
+      <c r="U221" s="38" t="s">
         <v>1462</v>
       </c>
-      <c r="V221" s="37" t="s">
+      <c r="V221" s="38" t="s">
         <v>1462</v>
       </c>
       <c r="W221" s="8"/>
@@ -20773,59 +20946,59 @@
       <c r="F222" s="4" t="s">
         <v>1463</v>
       </c>
-      <c r="G222" s="38" t="s">
+      <c r="G222" s="39" t="s">
         <v>1438</v>
       </c>
-      <c r="H222" s="36" t="s">
+      <c r="H222" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I222" s="38" t="s">
+      <c r="I222" s="39" t="s">
         <v>1464</v>
       </c>
-      <c r="J222" s="38" t="s">
+      <c r="J222" s="39" t="s">
         <v>1323</v>
       </c>
-      <c r="K222" s="38" t="s">
+      <c r="K222" s="39" t="s">
         <v>1323</v>
       </c>
-      <c r="L222" s="38" t="s">
+      <c r="L222" s="39" t="s">
         <v>1446</v>
       </c>
       <c r="M222" s="4">
+        <f t="shared" si="91"/>
+        <v>441000</v>
+      </c>
+      <c r="N222" s="4">
         <f t="shared" si="92"/>
         <v>441000</v>
       </c>
-      <c r="N222" s="4">
+      <c r="O222" s="4">
         <f t="shared" si="93"/>
-        <v>441000</v>
-      </c>
-      <c r="O222" s="4">
+        <v>412750</v>
+      </c>
+      <c r="P222" s="4">
         <f t="shared" si="94"/>
         <v>412750</v>
       </c>
-      <c r="P222" s="4">
-        <f t="shared" si="95"/>
-        <v>412750</v>
-      </c>
       <c r="Q222" s="6">
+        <f t="shared" si="85"/>
+        <v>246</v>
+      </c>
+      <c r="R222" s="7">
+        <f t="shared" si="86"/>
+        <v>780</v>
+      </c>
+      <c r="S222" s="8">
         <f t="shared" si="87"/>
-        <v>246</v>
-      </c>
-      <c r="R222" s="8">
-        <f t="shared" si="84"/>
-        <v>819</v>
-      </c>
-      <c r="S222" s="8">
-        <f t="shared" si="88"/>
         <v>1006</v>
       </c>
       <c r="T222" s="8">
         <v>99.99</v>
       </c>
-      <c r="U222" s="37" t="s">
+      <c r="U222" s="38" t="s">
         <v>1465</v>
       </c>
-      <c r="V222" s="37" t="s">
+      <c r="V222" s="38" t="s">
         <v>1465</v>
       </c>
       <c r="W222" s="8"/>
@@ -20850,59 +21023,59 @@
       <c r="F223" s="4" t="s">
         <v>1466</v>
       </c>
-      <c r="G223" s="38" t="s">
+      <c r="G223" s="39" t="s">
         <v>1467</v>
       </c>
-      <c r="H223" s="36" t="s">
+      <c r="H223" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I223" s="38" t="s">
+      <c r="I223" s="39" t="s">
         <v>1468</v>
       </c>
-      <c r="J223" s="38" t="s">
+      <c r="J223" s="39" t="s">
         <v>1469</v>
       </c>
-      <c r="K223" s="38" t="s">
+      <c r="K223" s="39" t="s">
         <v>1469</v>
       </c>
-      <c r="L223" s="38" t="s">
+      <c r="L223" s="39" t="s">
         <v>1405</v>
       </c>
       <c r="M223" s="4">
+        <f t="shared" si="91"/>
+        <v>471000</v>
+      </c>
+      <c r="N223" s="4">
         <f t="shared" si="92"/>
         <v>471000</v>
       </c>
-      <c r="N223" s="4">
+      <c r="O223" s="4">
         <f t="shared" si="93"/>
-        <v>471000</v>
-      </c>
-      <c r="O223" s="4">
+        <v>442750</v>
+      </c>
+      <c r="P223" s="4">
         <f t="shared" si="94"/>
         <v>442750</v>
       </c>
-      <c r="P223" s="4">
-        <f t="shared" si="95"/>
-        <v>442750</v>
-      </c>
       <c r="Q223" s="6">
+        <f t="shared" si="85"/>
+        <v>253</v>
+      </c>
+      <c r="R223" s="7">
+        <f t="shared" si="86"/>
+        <v>798</v>
+      </c>
+      <c r="S223" s="8">
         <f t="shared" si="87"/>
-        <v>253</v>
-      </c>
-      <c r="R223" s="8">
-        <f t="shared" si="84"/>
-        <v>839</v>
-      </c>
-      <c r="S223" s="8">
-        <f t="shared" si="88"/>
         <v>1036</v>
       </c>
       <c r="T223" s="8">
         <v>99.99</v>
       </c>
-      <c r="U223" s="37" t="s">
+      <c r="U223" s="38" t="s">
         <v>1470</v>
       </c>
-      <c r="V223" s="37" t="s">
+      <c r="V223" s="38" t="s">
         <v>1470</v>
       </c>
       <c r="W223" s="8"/>
@@ -20927,59 +21100,59 @@
       <c r="F224" s="4" t="s">
         <v>1471</v>
       </c>
-      <c r="G224" s="38" t="s">
+      <c r="G224" s="39" t="s">
         <v>1472</v>
       </c>
-      <c r="H224" s="36" t="s">
+      <c r="H224" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I224" s="38" t="s">
+      <c r="I224" s="39" t="s">
         <v>1473</v>
       </c>
-      <c r="J224" s="38" t="s">
+      <c r="J224" s="39" t="s">
         <v>1474</v>
       </c>
-      <c r="K224" s="38" t="s">
+      <c r="K224" s="39" t="s">
         <v>1474</v>
       </c>
-      <c r="L224" s="38" t="s">
+      <c r="L224" s="39" t="s">
         <v>1456</v>
       </c>
       <c r="M224" s="4">
+        <f t="shared" si="91"/>
+        <v>501000</v>
+      </c>
+      <c r="N224" s="4">
         <f t="shared" si="92"/>
         <v>501000</v>
       </c>
-      <c r="N224" s="4">
+      <c r="O224" s="4">
         <f t="shared" si="93"/>
-        <v>501000</v>
-      </c>
-      <c r="O224" s="4">
+        <v>472750</v>
+      </c>
+      <c r="P224" s="4">
         <f t="shared" si="94"/>
         <v>472750</v>
       </c>
-      <c r="P224" s="4">
-        <f t="shared" si="95"/>
-        <v>472750</v>
-      </c>
       <c r="Q224" s="6">
+        <f t="shared" si="85"/>
+        <v>260</v>
+      </c>
+      <c r="R224" s="7">
+        <f t="shared" si="86"/>
+        <v>816</v>
+      </c>
+      <c r="S224" s="8">
         <f t="shared" si="87"/>
-        <v>260</v>
-      </c>
-      <c r="R224" s="8">
-        <f t="shared" si="84"/>
-        <v>859</v>
-      </c>
-      <c r="S224" s="8">
-        <f t="shared" si="88"/>
         <v>1066</v>
       </c>
       <c r="T224" s="8">
         <v>99.99</v>
       </c>
-      <c r="U224" s="37" t="s">
+      <c r="U224" s="38" t="s">
         <v>1475</v>
       </c>
-      <c r="V224" s="37" t="s">
+      <c r="V224" s="38" t="s">
         <v>1475</v>
       </c>
       <c r="W224" s="8"/>
@@ -21004,59 +21177,59 @@
       <c r="F225" s="4" t="s">
         <v>1476</v>
       </c>
-      <c r="G225" s="38" t="s">
+      <c r="G225" s="39" t="s">
         <v>1460</v>
       </c>
-      <c r="H225" s="36" t="s">
+      <c r="H225" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I225" s="38" t="s">
+      <c r="I225" s="39" t="s">
         <v>1477</v>
       </c>
-      <c r="J225" s="38" t="s">
+      <c r="J225" s="39" t="s">
         <v>1248</v>
       </c>
-      <c r="K225" s="38" t="s">
+      <c r="K225" s="39" t="s">
         <v>1248</v>
       </c>
-      <c r="L225" s="38" t="s">
+      <c r="L225" s="39" t="s">
         <v>1428</v>
       </c>
       <c r="M225" s="4">
+        <f t="shared" si="91"/>
+        <v>531000</v>
+      </c>
+      <c r="N225" s="4">
         <f t="shared" si="92"/>
         <v>531000</v>
       </c>
-      <c r="N225" s="4">
+      <c r="O225" s="4">
         <f t="shared" si="93"/>
-        <v>531000</v>
-      </c>
-      <c r="O225" s="4">
+        <v>502750</v>
+      </c>
+      <c r="P225" s="4">
         <f t="shared" si="94"/>
         <v>502750</v>
       </c>
-      <c r="P225" s="4">
-        <f t="shared" si="95"/>
-        <v>502750</v>
-      </c>
       <c r="Q225" s="6">
+        <f t="shared" si="85"/>
+        <v>267</v>
+      </c>
+      <c r="R225" s="7">
+        <f t="shared" si="86"/>
+        <v>834</v>
+      </c>
+      <c r="S225" s="8">
         <f t="shared" si="87"/>
-        <v>267</v>
-      </c>
-      <c r="R225" s="8">
-        <f t="shared" si="84"/>
-        <v>879</v>
-      </c>
-      <c r="S225" s="8">
-        <f t="shared" si="88"/>
         <v>1096</v>
       </c>
       <c r="T225" s="8">
         <v>99.99</v>
       </c>
-      <c r="U225" s="37" t="s">
+      <c r="U225" s="38" t="s">
         <v>1478</v>
       </c>
-      <c r="V225" s="37" t="s">
+      <c r="V225" s="38" t="s">
         <v>1478</v>
       </c>
       <c r="W225" s="8"/>
@@ -21081,59 +21254,59 @@
       <c r="F226" s="6" t="s">
         <v>1479</v>
       </c>
-      <c r="G226" s="38" t="s">
+      <c r="G226" s="39" t="s">
         <v>1464</v>
       </c>
-      <c r="H226" s="36" t="s">
+      <c r="H226" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I226" s="38" t="s">
+      <c r="I226" s="39" t="s">
         <v>1480</v>
       </c>
-      <c r="J226" s="40" t="s">
+      <c r="J226" s="41" t="s">
         <v>1481</v>
       </c>
-      <c r="K226" s="40" t="s">
+      <c r="K226" s="41" t="s">
         <v>1481</v>
       </c>
-      <c r="L226" s="38" t="s">
+      <c r="L226" s="39" t="s">
         <v>1438</v>
       </c>
       <c r="M226" s="4">
+        <f t="shared" si="91"/>
+        <v>561000</v>
+      </c>
+      <c r="N226" s="4">
         <f t="shared" si="92"/>
         <v>561000</v>
       </c>
-      <c r="N226" s="4">
+      <c r="O226" s="4">
         <f t="shared" si="93"/>
-        <v>561000</v>
-      </c>
-      <c r="O226" s="4">
+        <v>532750</v>
+      </c>
+      <c r="P226" s="4">
         <f t="shared" si="94"/>
         <v>532750</v>
       </c>
-      <c r="P226" s="4">
-        <f t="shared" si="95"/>
-        <v>532750</v>
-      </c>
       <c r="Q226" s="6">
+        <f t="shared" si="85"/>
+        <v>274</v>
+      </c>
+      <c r="R226" s="7">
+        <f t="shared" si="86"/>
+        <v>852</v>
+      </c>
+      <c r="S226" s="8">
         <f t="shared" si="87"/>
-        <v>274</v>
-      </c>
-      <c r="R226" s="8">
-        <f t="shared" si="84"/>
-        <v>899</v>
-      </c>
-      <c r="S226" s="8">
-        <f t="shared" si="88"/>
         <v>1126</v>
       </c>
       <c r="T226" s="8">
         <v>99.99</v>
       </c>
-      <c r="U226" s="37" t="s">
+      <c r="U226" s="38" t="s">
         <v>1482</v>
       </c>
-      <c r="V226" s="37" t="s">
+      <c r="V226" s="38" t="s">
         <v>1482</v>
       </c>
       <c r="W226" s="7"/>
@@ -21158,59 +21331,59 @@
       <c r="F227" s="6" t="s">
         <v>1483</v>
       </c>
-      <c r="G227" s="38" t="s">
+      <c r="G227" s="39" t="s">
         <v>1468</v>
       </c>
-      <c r="H227" s="36" t="s">
+      <c r="H227" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I227" s="38" t="s">
+      <c r="I227" s="39" t="s">
         <v>1484</v>
       </c>
-      <c r="J227" s="40" t="s">
+      <c r="J227" s="41" t="s">
         <v>1154</v>
       </c>
-      <c r="K227" s="40" t="s">
+      <c r="K227" s="41" t="s">
         <v>1154</v>
       </c>
-      <c r="L227" s="38" t="s">
+      <c r="L227" s="39" t="s">
         <v>1467</v>
       </c>
       <c r="M227" s="4">
+        <f t="shared" si="91"/>
+        <v>591000</v>
+      </c>
+      <c r="N227" s="4">
         <f t="shared" si="92"/>
         <v>591000</v>
       </c>
-      <c r="N227" s="4">
+      <c r="O227" s="4">
         <f t="shared" si="93"/>
-        <v>591000</v>
-      </c>
-      <c r="O227" s="4">
+        <v>562750</v>
+      </c>
+      <c r="P227" s="4">
         <f t="shared" si="94"/>
         <v>562750</v>
       </c>
-      <c r="P227" s="4">
-        <f t="shared" si="95"/>
-        <v>562750</v>
-      </c>
       <c r="Q227" s="6">
+        <f t="shared" si="85"/>
+        <v>281</v>
+      </c>
+      <c r="R227" s="7">
+        <f t="shared" si="86"/>
+        <v>870</v>
+      </c>
+      <c r="S227" s="8">
         <f t="shared" si="87"/>
-        <v>281</v>
-      </c>
-      <c r="R227" s="8">
-        <f t="shared" si="84"/>
-        <v>919</v>
-      </c>
-      <c r="S227" s="8">
-        <f t="shared" si="88"/>
         <v>1156</v>
       </c>
       <c r="T227" s="8">
         <v>99.99</v>
       </c>
-      <c r="U227" s="37" t="s">
+      <c r="U227" s="38" t="s">
         <v>1485</v>
       </c>
-      <c r="V227" s="37" t="s">
+      <c r="V227" s="38" t="s">
         <v>1485</v>
       </c>
       <c r="W227" s="7"/>
@@ -21235,59 +21408,59 @@
       <c r="F228" s="6" t="s">
         <v>1486</v>
       </c>
-      <c r="G228" s="38" t="s">
+      <c r="G228" s="39" t="s">
         <v>1473</v>
       </c>
-      <c r="H228" s="36" t="s">
+      <c r="H228" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I228" s="38" t="s">
+      <c r="I228" s="39" t="s">
         <v>1487</v>
       </c>
-      <c r="J228" s="40" t="s">
+      <c r="J228" s="41" t="s">
         <v>1488</v>
       </c>
-      <c r="K228" s="40" t="s">
+      <c r="K228" s="41" t="s">
         <v>1488</v>
       </c>
-      <c r="L228" s="38" t="s">
+      <c r="L228" s="39" t="s">
         <v>1472</v>
       </c>
       <c r="M228" s="4">
+        <f t="shared" si="91"/>
+        <v>621000</v>
+      </c>
+      <c r="N228" s="4">
         <f t="shared" si="92"/>
         <v>621000</v>
       </c>
-      <c r="N228" s="4">
+      <c r="O228" s="4">
         <f t="shared" si="93"/>
-        <v>621000</v>
-      </c>
-      <c r="O228" s="4">
+        <v>592750</v>
+      </c>
+      <c r="P228" s="4">
         <f t="shared" si="94"/>
         <v>592750</v>
       </c>
-      <c r="P228" s="4">
-        <f t="shared" si="95"/>
-        <v>592750</v>
-      </c>
       <c r="Q228" s="6">
+        <f t="shared" si="85"/>
+        <v>288</v>
+      </c>
+      <c r="R228" s="7">
+        <f t="shared" si="86"/>
+        <v>888</v>
+      </c>
+      <c r="S228" s="8">
         <f t="shared" si="87"/>
-        <v>288</v>
-      </c>
-      <c r="R228" s="8">
-        <f t="shared" si="84"/>
-        <v>939</v>
-      </c>
-      <c r="S228" s="8">
-        <f t="shared" si="88"/>
         <v>1186</v>
       </c>
       <c r="T228" s="8">
         <v>99.99</v>
       </c>
-      <c r="U228" s="37" t="s">
+      <c r="U228" s="38" t="s">
         <v>1489</v>
       </c>
-      <c r="V228" s="37" t="s">
+      <c r="V228" s="38" t="s">
         <v>1489</v>
       </c>
       <c r="W228" s="7"/>
@@ -21312,59 +21485,59 @@
       <c r="F229" s="6" t="s">
         <v>1490</v>
       </c>
-      <c r="G229" s="38" t="s">
+      <c r="G229" s="39" t="s">
         <v>1477</v>
       </c>
-      <c r="H229" s="36" t="s">
+      <c r="H229" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I229" s="38" t="s">
+      <c r="I229" s="39" t="s">
         <v>1491</v>
       </c>
-      <c r="J229" s="40" t="s">
+      <c r="J229" s="41" t="s">
         <v>1342</v>
       </c>
-      <c r="K229" s="40" t="s">
+      <c r="K229" s="41" t="s">
         <v>1342</v>
       </c>
-      <c r="L229" s="38" t="s">
+      <c r="L229" s="39" t="s">
         <v>1460</v>
       </c>
       <c r="M229" s="4">
+        <f t="shared" si="91"/>
+        <v>651000</v>
+      </c>
+      <c r="N229" s="4">
         <f t="shared" si="92"/>
         <v>651000</v>
       </c>
-      <c r="N229" s="4">
+      <c r="O229" s="4">
         <f t="shared" si="93"/>
-        <v>651000</v>
-      </c>
-      <c r="O229" s="4">
+        <v>622750</v>
+      </c>
+      <c r="P229" s="4">
         <f t="shared" si="94"/>
         <v>622750</v>
       </c>
-      <c r="P229" s="4">
-        <f t="shared" si="95"/>
-        <v>622750</v>
-      </c>
       <c r="Q229" s="6">
+        <f t="shared" si="85"/>
+        <v>295</v>
+      </c>
+      <c r="R229" s="7">
+        <f t="shared" si="86"/>
+        <v>906</v>
+      </c>
+      <c r="S229" s="8">
         <f t="shared" si="87"/>
-        <v>295</v>
-      </c>
-      <c r="R229" s="8">
-        <f t="shared" si="84"/>
-        <v>959</v>
-      </c>
-      <c r="S229" s="8">
-        <f t="shared" si="88"/>
         <v>1216</v>
       </c>
       <c r="T229" s="8">
         <v>99.99</v>
       </c>
-      <c r="U229" s="37" t="s">
+      <c r="U229" s="38" t="s">
         <v>1492</v>
       </c>
-      <c r="V229" s="37" t="s">
+      <c r="V229" s="38" t="s">
         <v>1492</v>
       </c>
       <c r="W229" s="7"/>
@@ -21389,59 +21562,59 @@
       <c r="F230" s="6" t="s">
         <v>1493</v>
       </c>
-      <c r="G230" s="38" t="s">
+      <c r="G230" s="39" t="s">
         <v>1480</v>
       </c>
-      <c r="H230" s="36" t="s">
+      <c r="H230" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I230" s="38" t="s">
+      <c r="I230" s="39" t="s">
         <v>1494</v>
       </c>
-      <c r="J230" s="40" t="s">
+      <c r="J230" s="41" t="s">
         <v>1495</v>
       </c>
-      <c r="K230" s="40" t="s">
+      <c r="K230" s="41" t="s">
         <v>1495</v>
       </c>
-      <c r="L230" s="38" t="s">
+      <c r="L230" s="39" t="s">
         <v>1496</v>
       </c>
       <c r="M230" s="4">
+        <f t="shared" si="91"/>
+        <v>681000</v>
+      </c>
+      <c r="N230" s="4">
         <f t="shared" si="92"/>
         <v>681000</v>
       </c>
-      <c r="N230" s="4">
+      <c r="O230" s="4">
         <f t="shared" si="93"/>
-        <v>681000</v>
-      </c>
-      <c r="O230" s="4">
+        <v>652750</v>
+      </c>
+      <c r="P230" s="4">
         <f t="shared" si="94"/>
         <v>652750</v>
       </c>
-      <c r="P230" s="4">
-        <f t="shared" si="95"/>
-        <v>652750</v>
-      </c>
       <c r="Q230" s="6">
+        <f t="shared" si="85"/>
+        <v>302</v>
+      </c>
+      <c r="R230" s="7">
+        <f t="shared" si="86"/>
+        <v>924</v>
+      </c>
+      <c r="S230" s="8">
         <f t="shared" si="87"/>
-        <v>302</v>
-      </c>
-      <c r="R230" s="8">
-        <f t="shared" si="84"/>
-        <v>979</v>
-      </c>
-      <c r="S230" s="8">
-        <f t="shared" si="88"/>
         <v>1246</v>
       </c>
       <c r="T230" s="8">
         <v>99.99</v>
       </c>
-      <c r="U230" s="37" t="s">
+      <c r="U230" s="38" t="s">
         <v>1497</v>
       </c>
-      <c r="V230" s="37" t="s">
+      <c r="V230" s="38" t="s">
         <v>1497</v>
       </c>
       <c r="W230" s="7"/>
@@ -21466,59 +21639,59 @@
       <c r="F231" s="6" t="s">
         <v>1498</v>
       </c>
-      <c r="G231" s="38" t="s">
+      <c r="G231" s="39" t="s">
         <v>1484</v>
       </c>
-      <c r="H231" s="36" t="s">
+      <c r="H231" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I231" s="38" t="s">
+      <c r="I231" s="39" t="s">
         <v>1499</v>
       </c>
-      <c r="J231" s="40" t="s">
+      <c r="J231" s="41" t="s">
         <v>1359</v>
       </c>
-      <c r="K231" s="40" t="s">
+      <c r="K231" s="41" t="s">
         <v>1359</v>
       </c>
-      <c r="L231" s="38" t="s">
+      <c r="L231" s="39" t="s">
         <v>1500</v>
       </c>
       <c r="M231" s="4">
+        <f t="shared" si="91"/>
+        <v>711000</v>
+      </c>
+      <c r="N231" s="4">
         <f t="shared" si="92"/>
         <v>711000</v>
       </c>
-      <c r="N231" s="4">
+      <c r="O231" s="4">
         <f t="shared" si="93"/>
-        <v>711000</v>
-      </c>
-      <c r="O231" s="4">
+        <v>682750</v>
+      </c>
+      <c r="P231" s="4">
         <f t="shared" si="94"/>
         <v>682750</v>
       </c>
-      <c r="P231" s="4">
-        <f t="shared" si="95"/>
-        <v>682750</v>
-      </c>
       <c r="Q231" s="6">
+        <f t="shared" si="85"/>
+        <v>309</v>
+      </c>
+      <c r="R231" s="7">
+        <f t="shared" si="86"/>
+        <v>942</v>
+      </c>
+      <c r="S231" s="8">
         <f t="shared" si="87"/>
-        <v>309</v>
-      </c>
-      <c r="R231" s="8">
-        <f t="shared" si="84"/>
-        <v>999</v>
-      </c>
-      <c r="S231" s="8">
-        <f t="shared" si="88"/>
         <v>1276</v>
       </c>
       <c r="T231" s="8">
         <v>99.99</v>
       </c>
-      <c r="U231" s="37" t="s">
+      <c r="U231" s="38" t="s">
         <v>1501</v>
       </c>
-      <c r="V231" s="37" t="s">
+      <c r="V231" s="38" t="s">
         <v>1501</v>
       </c>
       <c r="W231" s="8"/>
@@ -21543,59 +21716,59 @@
       <c r="F232" s="4" t="s">
         <v>1502</v>
       </c>
-      <c r="G232" s="38" t="s">
+      <c r="G232" s="39" t="s">
         <v>1487</v>
       </c>
-      <c r="H232" s="36" t="s">
+      <c r="H232" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I232" s="38" t="s">
+      <c r="I232" s="39" t="s">
         <v>1503</v>
       </c>
-      <c r="J232" s="40" t="s">
+      <c r="J232" s="41" t="s">
         <v>1504</v>
       </c>
-      <c r="K232" s="40" t="s">
+      <c r="K232" s="41" t="s">
         <v>1504</v>
       </c>
-      <c r="L232" s="38" t="s">
+      <c r="L232" s="39" t="s">
         <v>1473</v>
       </c>
       <c r="M232" s="4">
+        <f t="shared" si="91"/>
+        <v>741000</v>
+      </c>
+      <c r="N232" s="4">
         <f t="shared" si="92"/>
         <v>741000</v>
       </c>
-      <c r="N232" s="4">
+      <c r="O232" s="4">
         <f t="shared" si="93"/>
-        <v>741000</v>
-      </c>
-      <c r="O232" s="4">
+        <v>712750</v>
+      </c>
+      <c r="P232" s="4">
         <f t="shared" si="94"/>
         <v>712750</v>
       </c>
-      <c r="P232" s="4">
-        <f t="shared" si="95"/>
-        <v>712750</v>
-      </c>
       <c r="Q232" s="6">
+        <f t="shared" si="85"/>
+        <v>316</v>
+      </c>
+      <c r="R232" s="7">
+        <f t="shared" si="86"/>
+        <v>960</v>
+      </c>
+      <c r="S232" s="8">
         <f t="shared" si="87"/>
-        <v>316</v>
-      </c>
-      <c r="R232" s="8">
-        <f t="shared" si="84"/>
-        <v>1019</v>
-      </c>
-      <c r="S232" s="8">
-        <f t="shared" si="88"/>
         <v>1306</v>
       </c>
       <c r="T232" s="8">
         <v>99.99</v>
       </c>
-      <c r="U232" s="37" t="s">
+      <c r="U232" s="38" t="s">
         <v>1505</v>
       </c>
-      <c r="V232" s="37" t="s">
+      <c r="V232" s="38" t="s">
         <v>1505</v>
       </c>
       <c r="W232" s="8"/>
@@ -21620,59 +21793,59 @@
       <c r="F233" s="4" t="s">
         <v>1506</v>
       </c>
-      <c r="G233" s="38" t="s">
+      <c r="G233" s="39" t="s">
         <v>1491</v>
       </c>
-      <c r="H233" s="36" t="s">
+      <c r="H233" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I233" s="38" t="s">
+      <c r="I233" s="39" t="s">
         <v>1507</v>
       </c>
-      <c r="J233" s="40" t="s">
+      <c r="J233" s="41" t="s">
         <v>1407</v>
       </c>
-      <c r="K233" s="40" t="s">
+      <c r="K233" s="41" t="s">
         <v>1407</v>
       </c>
-      <c r="L233" s="38" t="s">
+      <c r="L233" s="39" t="s">
         <v>1508</v>
       </c>
       <c r="M233" s="4">
+        <f t="shared" si="91"/>
+        <v>771000</v>
+      </c>
+      <c r="N233" s="4">
         <f t="shared" si="92"/>
         <v>771000</v>
       </c>
-      <c r="N233" s="4">
+      <c r="O233" s="4">
         <f t="shared" si="93"/>
-        <v>771000</v>
-      </c>
-      <c r="O233" s="4">
+        <v>742750</v>
+      </c>
+      <c r="P233" s="4">
         <f t="shared" si="94"/>
         <v>742750</v>
       </c>
-      <c r="P233" s="4">
-        <f t="shared" si="95"/>
-        <v>742750</v>
-      </c>
       <c r="Q233" s="6">
+        <f t="shared" si="85"/>
+        <v>323</v>
+      </c>
+      <c r="R233" s="7">
+        <f t="shared" si="86"/>
+        <v>978</v>
+      </c>
+      <c r="S233" s="8">
         <f t="shared" si="87"/>
-        <v>323</v>
-      </c>
-      <c r="R233" s="8">
-        <f t="shared" si="84"/>
-        <v>1039</v>
-      </c>
-      <c r="S233" s="8">
-        <f t="shared" si="88"/>
         <v>1336</v>
       </c>
       <c r="T233" s="8">
         <v>99.99</v>
       </c>
-      <c r="U233" s="37" t="s">
+      <c r="U233" s="38" t="s">
         <v>1509</v>
       </c>
-      <c r="V233" s="37" t="s">
+      <c r="V233" s="38" t="s">
         <v>1509</v>
       </c>
       <c r="W233" s="8"/>
@@ -21697,59 +21870,59 @@
       <c r="F234" s="4" t="s">
         <v>1510</v>
       </c>
-      <c r="G234" s="38" t="s">
+      <c r="G234" s="39" t="s">
         <v>1494</v>
       </c>
-      <c r="H234" s="36" t="s">
+      <c r="H234" s="37" t="s">
         <v>1302</v>
       </c>
-      <c r="I234" s="38" t="s">
+      <c r="I234" s="39" t="s">
         <v>1511</v>
       </c>
-      <c r="J234" s="40" t="s">
+      <c r="J234" s="41" t="s">
         <v>1512</v>
       </c>
-      <c r="K234" s="40" t="s">
+      <c r="K234" s="41" t="s">
         <v>1512</v>
       </c>
-      <c r="L234" s="38" t="s">
+      <c r="L234" s="39" t="s">
         <v>1513</v>
       </c>
       <c r="M234" s="4">
+        <f t="shared" si="91"/>
+        <v>801000</v>
+      </c>
+      <c r="N234" s="4">
         <f t="shared" si="92"/>
         <v>801000</v>
       </c>
-      <c r="N234" s="4">
+      <c r="O234" s="4">
         <f t="shared" si="93"/>
-        <v>801000</v>
-      </c>
-      <c r="O234" s="4">
+        <v>772750</v>
+      </c>
+      <c r="P234" s="4">
         <f t="shared" si="94"/>
         <v>772750</v>
       </c>
-      <c r="P234" s="4">
-        <f t="shared" si="95"/>
-        <v>772750</v>
-      </c>
       <c r="Q234" s="6">
+        <f t="shared" si="85"/>
+        <v>330</v>
+      </c>
+      <c r="R234" s="7">
+        <f t="shared" si="86"/>
+        <v>996</v>
+      </c>
+      <c r="S234" s="8">
         <f t="shared" si="87"/>
-        <v>330</v>
-      </c>
-      <c r="R234" s="8">
-        <f t="shared" si="84"/>
-        <v>1059</v>
-      </c>
-      <c r="S234" s="8">
-        <f t="shared" si="88"/>
         <v>1366</v>
       </c>
       <c r="T234" s="8">
         <v>99.99</v>
       </c>
-      <c r="U234" s="37" t="s">
+      <c r="U234" s="38" t="s">
         <v>1514</v>
       </c>
-      <c r="V234" s="37" t="s">
+      <c r="V234" s="38" t="s">
         <v>1514</v>
       </c>
       <c r="W234" s="8"/>
@@ -21774,59 +21947,59 @@
       <c r="F235" s="26" t="s">
         <v>1515</v>
       </c>
-      <c r="G235" s="38" t="s">
+      <c r="G235" s="39" t="s">
         <v>1499</v>
       </c>
-      <c r="H235" s="42" t="s">
+      <c r="H235" s="43" t="s">
         <v>1302</v>
       </c>
-      <c r="I235" s="38" t="s">
+      <c r="I235" s="39" t="s">
         <v>1516</v>
       </c>
-      <c r="J235" s="40" t="s">
+      <c r="J235" s="41" t="s">
         <v>1249</v>
       </c>
-      <c r="K235" s="40" t="s">
+      <c r="K235" s="41" t="s">
         <v>1249</v>
       </c>
-      <c r="L235" s="38" t="s">
+      <c r="L235" s="39" t="s">
         <v>1480</v>
       </c>
       <c r="M235" s="4">
+        <f t="shared" si="91"/>
+        <v>831000</v>
+      </c>
+      <c r="N235" s="4">
         <f t="shared" si="92"/>
         <v>831000</v>
       </c>
-      <c r="N235" s="4">
+      <c r="O235" s="4">
         <f t="shared" si="93"/>
-        <v>831000</v>
-      </c>
-      <c r="O235" s="4">
+        <v>802750</v>
+      </c>
+      <c r="P235" s="4">
         <f t="shared" si="94"/>
         <v>802750</v>
       </c>
-      <c r="P235" s="4">
-        <f t="shared" si="95"/>
-        <v>802750</v>
-      </c>
       <c r="Q235" s="6">
+        <f t="shared" si="85"/>
+        <v>337</v>
+      </c>
+      <c r="R235" s="7">
+        <f t="shared" si="86"/>
+        <v>1014</v>
+      </c>
+      <c r="S235" s="8">
         <f t="shared" si="87"/>
-        <v>337</v>
-      </c>
-      <c r="R235" s="8">
-        <f t="shared" si="84"/>
-        <v>1079</v>
-      </c>
-      <c r="S235" s="8">
-        <f t="shared" si="88"/>
         <v>1396</v>
       </c>
       <c r="T235" s="8">
         <v>99.99</v>
       </c>
-      <c r="U235" s="37" t="s">
+      <c r="U235" s="38" t="s">
         <v>1517</v>
       </c>
-      <c r="V235" s="37" t="s">
+      <c r="V235" s="38" t="s">
         <v>1517</v>
       </c>
       <c r="W235" s="25"/>
@@ -21852,54 +22025,59 @@
         <v>1518</v>
       </c>
       <c r="G236" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H236" s="36" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H236" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I236" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J236" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K236" s="34" t="s">
-        <v>1235</v>
+        <v>1520</v>
+      </c>
+      <c r="J236" s="41" t="s">
+        <v>1521</v>
+      </c>
+      <c r="K236" s="41" t="s">
+        <v>1521</v>
       </c>
       <c r="L236" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M236" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N236" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O236" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P236" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q236" s="2">
-        <v>50</v>
-      </c>
-      <c r="R236" s="18">
-        <f>R235+9</f>
-        <v>1088</v>
-      </c>
-      <c r="S236" s="18">
-        <f>S235+10</f>
-        <v>1406</v>
-      </c>
-      <c r="T236" s="18">
+        <v>1522</v>
+      </c>
+      <c r="M236" s="4">
+        <f t="shared" si="91"/>
+        <v>861000</v>
+      </c>
+      <c r="N236" s="4">
+        <f t="shared" si="92"/>
+        <v>861000</v>
+      </c>
+      <c r="O236" s="4">
+        <f t="shared" si="93"/>
+        <v>832750</v>
+      </c>
+      <c r="P236" s="4">
+        <f t="shared" si="94"/>
+        <v>832750</v>
+      </c>
+      <c r="Q236" s="6">
+        <f t="shared" si="85"/>
+        <v>344</v>
+      </c>
+      <c r="R236" s="7">
+        <f t="shared" si="86"/>
+        <v>1032</v>
+      </c>
+      <c r="S236" s="8">
+        <f t="shared" si="87"/>
+        <v>1426</v>
+      </c>
+      <c r="T236" s="8">
         <v>99.99</v>
       </c>
-      <c r="U236" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V236" s="34" t="s">
-        <v>1237</v>
+      <c r="U236" s="38" t="s">
+        <v>1523</v>
+      </c>
+      <c r="V236" s="38" t="s">
+        <v>1523</v>
       </c>
       <c r="W236" s="8"/>
       <c r="X236" s="8"/>
@@ -21921,57 +22099,62 @@
         <v>7</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>1519</v>
+        <v>1524</v>
       </c>
       <c r="G237" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H237" s="36" t="s">
+        <v>1525</v>
+      </c>
+      <c r="H237" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I237" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J237" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K237" s="34" t="s">
-        <v>1235</v>
+        <v>1526</v>
+      </c>
+      <c r="J237" s="41" t="s">
+        <v>1404</v>
+      </c>
+      <c r="K237" s="41" t="s">
+        <v>1404</v>
       </c>
       <c r="L237" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M237" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N237" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O237" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P237" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q237" s="2">
-        <v>50</v>
-      </c>
-      <c r="R237" s="18">
-        <f>R236+9</f>
-        <v>1097</v>
-      </c>
-      <c r="S237" s="18">
-        <f>S236+10</f>
-        <v>1416</v>
-      </c>
-      <c r="T237" s="18">
+        <v>1527</v>
+      </c>
+      <c r="M237" s="4">
+        <f t="shared" si="91"/>
+        <v>891000</v>
+      </c>
+      <c r="N237" s="4">
+        <f t="shared" si="92"/>
+        <v>891000</v>
+      </c>
+      <c r="O237" s="4">
+        <f t="shared" si="93"/>
+        <v>862750</v>
+      </c>
+      <c r="P237" s="4">
+        <f t="shared" si="94"/>
+        <v>862750</v>
+      </c>
+      <c r="Q237" s="6">
+        <f t="shared" si="85"/>
+        <v>351</v>
+      </c>
+      <c r="R237" s="7">
+        <f t="shared" si="86"/>
+        <v>1050</v>
+      </c>
+      <c r="S237" s="8">
+        <f t="shared" si="87"/>
+        <v>1456</v>
+      </c>
+      <c r="T237" s="8">
         <v>99.99</v>
       </c>
-      <c r="U237" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V237" s="34" t="s">
-        <v>1237</v>
+      <c r="U237" s="38" t="s">
+        <v>1528</v>
+      </c>
+      <c r="V237" s="38" t="s">
+        <v>1528</v>
       </c>
       <c r="W237" s="8"/>
       <c r="X237" s="8"/>
@@ -21993,57 +22176,62 @@
         <v>7</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G238" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H238" s="36" t="s">
+        <v>1503</v>
+      </c>
+      <c r="H238" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I238" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J238" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K238" s="34" t="s">
-        <v>1235</v>
+        <v>1530</v>
+      </c>
+      <c r="J238" s="41" t="s">
+        <v>1531</v>
+      </c>
+      <c r="K238" s="41" t="s">
+        <v>1531</v>
       </c>
       <c r="L238" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M238" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N238" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O238" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P238" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q238" s="2">
-        <v>50</v>
-      </c>
-      <c r="R238" s="18">
-        <f>R237+9</f>
-        <v>1106</v>
-      </c>
-      <c r="S238" s="18">
-        <f>S237+10</f>
-        <v>1426</v>
-      </c>
-      <c r="T238" s="18">
+        <v>1487</v>
+      </c>
+      <c r="M238" s="4">
+        <f t="shared" si="91"/>
+        <v>921000</v>
+      </c>
+      <c r="N238" s="4">
+        <f t="shared" si="92"/>
+        <v>921000</v>
+      </c>
+      <c r="O238" s="4">
+        <f t="shared" si="93"/>
+        <v>892750</v>
+      </c>
+      <c r="P238" s="4">
+        <f t="shared" si="94"/>
+        <v>892750</v>
+      </c>
+      <c r="Q238" s="6">
+        <f t="shared" si="85"/>
+        <v>358</v>
+      </c>
+      <c r="R238" s="7">
+        <f t="shared" si="86"/>
+        <v>1068</v>
+      </c>
+      <c r="S238" s="8">
+        <f t="shared" si="87"/>
+        <v>1486</v>
+      </c>
+      <c r="T238" s="8">
         <v>99.99</v>
       </c>
-      <c r="U238" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V238" s="34" t="s">
-        <v>1237</v>
+      <c r="U238" s="38" t="s">
+        <v>1532</v>
+      </c>
+      <c r="V238" s="38" t="s">
+        <v>1532</v>
       </c>
       <c r="W238" s="8"/>
       <c r="X238" s="8"/>
@@ -22065,57 +22253,62 @@
         <v>7</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>1521</v>
+        <v>1533</v>
       </c>
       <c r="G239" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H239" s="36" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H239" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I239" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J239" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K239" s="34" t="s">
-        <v>1235</v>
+        <v>1535</v>
+      </c>
+      <c r="J239" s="41" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K239" s="41" t="s">
+        <v>1420</v>
       </c>
       <c r="L239" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M239" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N239" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O239" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P239" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q239" s="2">
-        <v>50</v>
-      </c>
-      <c r="R239" s="18">
-        <f>R238+9</f>
-        <v>1115</v>
-      </c>
-      <c r="S239" s="18">
-        <f>S238+10</f>
-        <v>1436</v>
-      </c>
-      <c r="T239" s="18">
+        <v>1536</v>
+      </c>
+      <c r="M239" s="4">
+        <f t="shared" si="91"/>
+        <v>951000</v>
+      </c>
+      <c r="N239" s="4">
+        <f t="shared" si="92"/>
+        <v>951000</v>
+      </c>
+      <c r="O239" s="4">
+        <f t="shared" si="93"/>
+        <v>922750</v>
+      </c>
+      <c r="P239" s="4">
+        <f t="shared" si="94"/>
+        <v>922750</v>
+      </c>
+      <c r="Q239" s="6">
+        <f t="shared" si="85"/>
+        <v>365</v>
+      </c>
+      <c r="R239" s="7">
+        <f t="shared" si="86"/>
+        <v>1086</v>
+      </c>
+      <c r="S239" s="8">
+        <f t="shared" si="87"/>
+        <v>1516</v>
+      </c>
+      <c r="T239" s="8">
         <v>99.99</v>
       </c>
-      <c r="U239" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V239" s="34" t="s">
-        <v>1237</v>
+      <c r="U239" s="38" t="s">
+        <v>1537</v>
+      </c>
+      <c r="V239" s="38" t="s">
+        <v>1537</v>
       </c>
       <c r="W239" s="8"/>
       <c r="X239" s="8"/>
@@ -22124,77 +22317,82 @@
       <c r="AA239" s="8"/>
       <c r="AB239" s="4"/>
     </row>
-    <row r="240" s="2" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A240" s="8"/>
-      <c r="B240" s="8"/>
-      <c r="C240" s="4">
+    <row r="240" s="9" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A240" s="25"/>
+      <c r="B240" s="25"/>
+      <c r="C240" s="26">
         <v>10235</v>
       </c>
-      <c r="D240" s="4">
+      <c r="D240" s="26">
         <v>1234</v>
       </c>
-      <c r="E240" s="4">
+      <c r="E240" s="26">
         <v>7</v>
       </c>
-      <c r="F240" s="4" t="s">
-        <v>1522</v>
-      </c>
-      <c r="G240" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H240" s="36" t="s">
+      <c r="F240" s="26" t="s">
+        <v>1538</v>
+      </c>
+      <c r="G240" s="44" t="s">
+        <v>1539</v>
+      </c>
+      <c r="H240" s="43" t="s">
         <v>1302</v>
       </c>
       <c r="I240" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J240" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K240" s="34" t="s">
-        <v>1235</v>
+        <v>1540</v>
+      </c>
+      <c r="J240" s="41" t="s">
+        <v>1541</v>
+      </c>
+      <c r="K240" s="41" t="s">
+        <v>1541</v>
       </c>
       <c r="L240" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M240" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N240" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O240" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P240" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q240" s="2">
-        <v>50</v>
-      </c>
-      <c r="R240" s="18">
-        <f>R239+9</f>
-        <v>1124</v>
-      </c>
-      <c r="S240" s="18">
-        <f>S239+10</f>
-        <v>1446</v>
-      </c>
-      <c r="T240" s="18">
+        <v>1542</v>
+      </c>
+      <c r="M240" s="4">
+        <f t="shared" si="91"/>
+        <v>981000</v>
+      </c>
+      <c r="N240" s="4">
+        <f t="shared" si="92"/>
+        <v>981000</v>
+      </c>
+      <c r="O240" s="4">
+        <f t="shared" si="93"/>
+        <v>952750</v>
+      </c>
+      <c r="P240" s="4">
+        <f t="shared" si="94"/>
+        <v>952750</v>
+      </c>
+      <c r="Q240" s="6">
+        <f t="shared" si="85"/>
+        <v>372</v>
+      </c>
+      <c r="R240" s="7">
+        <f t="shared" si="86"/>
+        <v>1104</v>
+      </c>
+      <c r="S240" s="8">
+        <f t="shared" si="87"/>
+        <v>1546</v>
+      </c>
+      <c r="T240" s="8">
         <v>99.99</v>
       </c>
-      <c r="U240" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V240" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="W240" s="8"/>
-      <c r="X240" s="8"/>
-      <c r="Y240" s="8"/>
-      <c r="Z240" s="8"/>
-      <c r="AA240" s="8"/>
-      <c r="AB240" s="4"/>
+      <c r="U240" s="38" t="s">
+        <v>1543</v>
+      </c>
+      <c r="V240" s="38" t="s">
+        <v>1543</v>
+      </c>
+      <c r="W240" s="25"/>
+      <c r="X240" s="25"/>
+      <c r="Y240" s="25"/>
+      <c r="Z240" s="25"/>
+      <c r="AA240" s="25"/>
+      <c r="AB240" s="26"/>
     </row>
     <row r="241" s="2" customFormat="1" customHeight="1" spans="1:28">
       <c r="A241" s="8"/>
@@ -22209,57 +22407,62 @@
         <v>7</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>1523</v>
+        <v>1544</v>
       </c>
       <c r="G241" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H241" s="36" t="s">
+        <v>1507</v>
+      </c>
+      <c r="H241" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I241" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J241" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K241" s="34" t="s">
-        <v>1235</v>
+        <v>1545</v>
+      </c>
+      <c r="J241" s="41" t="s">
+        <v>1432</v>
+      </c>
+      <c r="K241" s="41" t="s">
+        <v>1432</v>
       </c>
       <c r="L241" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M241" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N241" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O241" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P241" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q241" s="2">
-        <v>50</v>
-      </c>
-      <c r="R241" s="18">
-        <f>R240+9</f>
-        <v>1133</v>
-      </c>
-      <c r="S241" s="18">
-        <f>S240+10</f>
-        <v>1456</v>
-      </c>
-      <c r="T241" s="18">
+        <v>1494</v>
+      </c>
+      <c r="M241" s="4">
+        <f t="shared" si="91"/>
+        <v>1011000</v>
+      </c>
+      <c r="N241" s="4">
+        <f t="shared" si="92"/>
+        <v>1011000</v>
+      </c>
+      <c r="O241" s="4">
+        <f t="shared" si="93"/>
+        <v>982750</v>
+      </c>
+      <c r="P241" s="4">
+        <f t="shared" si="94"/>
+        <v>982750</v>
+      </c>
+      <c r="Q241" s="6">
+        <f t="shared" si="85"/>
+        <v>379</v>
+      </c>
+      <c r="R241" s="7">
+        <f t="shared" si="86"/>
+        <v>1122</v>
+      </c>
+      <c r="S241" s="8">
+        <f t="shared" si="87"/>
+        <v>1576</v>
+      </c>
+      <c r="T241" s="8">
         <v>99.99</v>
       </c>
-      <c r="U241" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V241" s="34" t="s">
-        <v>1237</v>
+      <c r="U241" s="38" t="s">
+        <v>1546</v>
+      </c>
+      <c r="V241" s="38" t="s">
+        <v>1546</v>
       </c>
       <c r="W241" s="8"/>
       <c r="X241" s="8"/>
@@ -22281,57 +22484,62 @@
         <v>7</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>1524</v>
+        <v>1547</v>
       </c>
       <c r="G242" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H242" s="36" t="s">
+        <v>1548</v>
+      </c>
+      <c r="H242" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I242" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J242" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K242" s="34" t="s">
-        <v>1235</v>
+        <v>1549</v>
+      </c>
+      <c r="J242" s="41" t="s">
+        <v>1550</v>
+      </c>
+      <c r="K242" s="41" t="s">
+        <v>1550</v>
       </c>
       <c r="L242" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M242" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N242" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O242" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P242" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q242" s="2">
-        <v>50</v>
-      </c>
-      <c r="R242" s="18">
-        <f>R241+9</f>
-        <v>1142</v>
-      </c>
-      <c r="S242" s="18">
-        <f>S241+10</f>
-        <v>1466</v>
-      </c>
-      <c r="T242" s="18">
+        <v>1551</v>
+      </c>
+      <c r="M242" s="4">
+        <f t="shared" si="91"/>
+        <v>1041000</v>
+      </c>
+      <c r="N242" s="4">
+        <f t="shared" si="92"/>
+        <v>1041000</v>
+      </c>
+      <c r="O242" s="4">
+        <f t="shared" si="93"/>
+        <v>1012750</v>
+      </c>
+      <c r="P242" s="4">
+        <f t="shared" si="94"/>
+        <v>1012750</v>
+      </c>
+      <c r="Q242" s="6">
+        <f t="shared" si="85"/>
+        <v>386</v>
+      </c>
+      <c r="R242" s="7">
+        <f t="shared" si="86"/>
+        <v>1140</v>
+      </c>
+      <c r="S242" s="8">
+        <f t="shared" si="87"/>
+        <v>1606</v>
+      </c>
+      <c r="T242" s="8">
         <v>99.99</v>
       </c>
-      <c r="U242" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V242" s="34" t="s">
-        <v>1237</v>
+      <c r="U242" s="38" t="s">
+        <v>1552</v>
+      </c>
+      <c r="V242" s="38" t="s">
+        <v>1552</v>
       </c>
       <c r="W242" s="8"/>
       <c r="X242" s="8"/>
@@ -22353,57 +22561,62 @@
         <v>7</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>1525</v>
+        <v>1553</v>
       </c>
       <c r="G243" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H243" s="36" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H243" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I243" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J243" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K243" s="34" t="s">
-        <v>1235</v>
+        <v>1555</v>
+      </c>
+      <c r="J243" s="41" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K243" s="41" t="s">
+        <v>1556</v>
       </c>
       <c r="L243" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M243" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N243" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O243" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P243" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q243" s="2">
-        <v>50</v>
-      </c>
-      <c r="R243" s="18">
-        <f>R242+9</f>
-        <v>1151</v>
-      </c>
-      <c r="S243" s="18">
-        <f>S242+10</f>
-        <v>1476</v>
-      </c>
-      <c r="T243" s="18">
+        <v>1519</v>
+      </c>
+      <c r="M243" s="4">
+        <f t="shared" si="91"/>
+        <v>1071000</v>
+      </c>
+      <c r="N243" s="4">
+        <f t="shared" si="92"/>
+        <v>1071000</v>
+      </c>
+      <c r="O243" s="4">
+        <f t="shared" si="93"/>
+        <v>1042750</v>
+      </c>
+      <c r="P243" s="4">
+        <f t="shared" si="94"/>
+        <v>1042750</v>
+      </c>
+      <c r="Q243" s="6">
+        <f t="shared" si="85"/>
+        <v>393</v>
+      </c>
+      <c r="R243" s="7">
+        <f t="shared" si="86"/>
+        <v>1158</v>
+      </c>
+      <c r="S243" s="8">
+        <f t="shared" si="87"/>
+        <v>1636</v>
+      </c>
+      <c r="T243" s="8">
         <v>99.99</v>
       </c>
-      <c r="U243" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V243" s="34" t="s">
-        <v>1237</v>
+      <c r="U243" s="38" t="s">
+        <v>1557</v>
+      </c>
+      <c r="V243" s="38" t="s">
+        <v>1557</v>
       </c>
       <c r="W243" s="8"/>
       <c r="X243" s="8"/>
@@ -22425,57 +22638,62 @@
         <v>7</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>1526</v>
+        <v>1558</v>
       </c>
       <c r="G244" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H244" s="36" t="s">
+        <v>1511</v>
+      </c>
+      <c r="H244" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I244" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J244" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K244" s="34" t="s">
-        <v>1235</v>
+        <v>1559</v>
+      </c>
+      <c r="J244" s="41" t="s">
+        <v>1560</v>
+      </c>
+      <c r="K244" s="41" t="s">
+        <v>1560</v>
       </c>
       <c r="L244" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M244" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N244" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O244" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P244" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q244" s="2">
-        <v>50</v>
-      </c>
-      <c r="R244" s="18">
-        <f>R243+9</f>
-        <v>1160</v>
-      </c>
-      <c r="S244" s="18">
-        <f>S243+10</f>
-        <v>1486</v>
-      </c>
-      <c r="T244" s="18">
+        <v>1503</v>
+      </c>
+      <c r="M244" s="4">
+        <f t="shared" si="91"/>
+        <v>1101000</v>
+      </c>
+      <c r="N244" s="4">
+        <f t="shared" si="92"/>
+        <v>1101000</v>
+      </c>
+      <c r="O244" s="4">
+        <f t="shared" si="93"/>
+        <v>1072750</v>
+      </c>
+      <c r="P244" s="4">
+        <f t="shared" si="94"/>
+        <v>1072750</v>
+      </c>
+      <c r="Q244" s="6">
+        <f t="shared" si="85"/>
+        <v>400</v>
+      </c>
+      <c r="R244" s="7">
+        <f t="shared" si="86"/>
+        <v>1176</v>
+      </c>
+      <c r="S244" s="8">
+        <f t="shared" si="87"/>
+        <v>1666</v>
+      </c>
+      <c r="T244" s="8">
         <v>99.99</v>
       </c>
-      <c r="U244" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V244" s="34" t="s">
-        <v>1237</v>
+      <c r="U244" s="38" t="s">
+        <v>1561</v>
+      </c>
+      <c r="V244" s="38" t="s">
+        <v>1561</v>
       </c>
       <c r="W244" s="8"/>
       <c r="X244" s="8"/>
@@ -22497,57 +22715,62 @@
         <v>7</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>1527</v>
+        <v>1562</v>
       </c>
       <c r="G245" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H245" s="36" t="s">
+        <v>1563</v>
+      </c>
+      <c r="H245" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I245" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J245" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K245" s="34" t="s">
-        <v>1235</v>
+        <v>1564</v>
+      </c>
+      <c r="J245" s="41" t="s">
+        <v>1439</v>
+      </c>
+      <c r="K245" s="41" t="s">
+        <v>1439</v>
       </c>
       <c r="L245" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M245" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N245" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O245" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P245" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q245" s="2">
-        <v>50</v>
-      </c>
-      <c r="R245" s="18">
-        <f>R244+9</f>
-        <v>1169</v>
-      </c>
-      <c r="S245" s="18">
-        <f>S244+10</f>
-        <v>1496</v>
-      </c>
-      <c r="T245" s="18">
+        <v>1539</v>
+      </c>
+      <c r="M245" s="4">
+        <f t="shared" si="91"/>
+        <v>1131000</v>
+      </c>
+      <c r="N245" s="4">
+        <f t="shared" si="92"/>
+        <v>1131000</v>
+      </c>
+      <c r="O245" s="4">
+        <f t="shared" si="93"/>
+        <v>1102750</v>
+      </c>
+      <c r="P245" s="4">
+        <f t="shared" si="94"/>
+        <v>1102750</v>
+      </c>
+      <c r="Q245" s="6">
+        <f t="shared" si="85"/>
+        <v>407</v>
+      </c>
+      <c r="R245" s="7">
+        <f t="shared" si="86"/>
+        <v>1194</v>
+      </c>
+      <c r="S245" s="8">
+        <f t="shared" si="87"/>
+        <v>1696</v>
+      </c>
+      <c r="T245" s="8">
         <v>99.99</v>
       </c>
-      <c r="U245" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V245" s="34" t="s">
-        <v>1237</v>
+      <c r="U245" s="38" t="s">
+        <v>1565</v>
+      </c>
+      <c r="V245" s="38" t="s">
+        <v>1565</v>
       </c>
       <c r="W245" s="8"/>
       <c r="X245" s="8"/>
@@ -22569,57 +22792,62 @@
         <v>7</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>1528</v>
+        <v>1566</v>
       </c>
       <c r="G246" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H246" s="36" t="s">
+        <v>1567</v>
+      </c>
+      <c r="H246" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I246" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J246" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K246" s="34" t="s">
-        <v>1235</v>
+        <v>1568</v>
+      </c>
+      <c r="J246" s="41" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K246" s="41" t="s">
+        <v>1569</v>
       </c>
       <c r="L246" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M246" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N246" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O246" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P246" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q246" s="2">
-        <v>50</v>
-      </c>
-      <c r="R246" s="18">
-        <f>R245+9</f>
-        <v>1178</v>
-      </c>
-      <c r="S246" s="18">
-        <f>S245+10</f>
-        <v>1506</v>
-      </c>
-      <c r="T246" s="18">
+        <v>1548</v>
+      </c>
+      <c r="M246" s="4">
+        <f t="shared" si="91"/>
+        <v>1161000</v>
+      </c>
+      <c r="N246" s="4">
+        <f t="shared" si="92"/>
+        <v>1161000</v>
+      </c>
+      <c r="O246" s="4">
+        <f t="shared" si="93"/>
+        <v>1132750</v>
+      </c>
+      <c r="P246" s="4">
+        <f t="shared" si="94"/>
+        <v>1132750</v>
+      </c>
+      <c r="Q246" s="6">
+        <f t="shared" si="85"/>
+        <v>414</v>
+      </c>
+      <c r="R246" s="7">
+        <f t="shared" si="86"/>
+        <v>1212</v>
+      </c>
+      <c r="S246" s="8">
+        <f t="shared" si="87"/>
+        <v>1726</v>
+      </c>
+      <c r="T246" s="8">
         <v>99.99</v>
       </c>
-      <c r="U246" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V246" s="34" t="s">
-        <v>1237</v>
+      <c r="U246" s="38" t="s">
+        <v>1570</v>
+      </c>
+      <c r="V246" s="38" t="s">
+        <v>1570</v>
       </c>
       <c r="W246" s="8"/>
       <c r="X246" s="8"/>
@@ -22641,57 +22869,62 @@
         <v>7</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>1529</v>
+        <v>1571</v>
       </c>
       <c r="G247" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H247" s="36" t="s">
+        <v>1516</v>
+      </c>
+      <c r="H247" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I247" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J247" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K247" s="34" t="s">
-        <v>1235</v>
+        <v>1572</v>
+      </c>
+      <c r="J247" s="41" t="s">
+        <v>1573</v>
+      </c>
+      <c r="K247" s="41" t="s">
+        <v>1573</v>
       </c>
       <c r="L247" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M247" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N247" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O247" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P247" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q247" s="2">
-        <v>50</v>
-      </c>
-      <c r="R247" s="18">
-        <f>R246+9</f>
-        <v>1187</v>
-      </c>
-      <c r="S247" s="18">
-        <f>S246+10</f>
-        <v>1516</v>
-      </c>
-      <c r="T247" s="18">
+        <v>1511</v>
+      </c>
+      <c r="M247" s="4">
+        <f t="shared" si="91"/>
+        <v>1191000</v>
+      </c>
+      <c r="N247" s="4">
+        <f t="shared" si="92"/>
+        <v>1191000</v>
+      </c>
+      <c r="O247" s="4">
+        <f t="shared" si="93"/>
+        <v>1162750</v>
+      </c>
+      <c r="P247" s="4">
+        <f t="shared" si="94"/>
+        <v>1162750</v>
+      </c>
+      <c r="Q247" s="6">
+        <f t="shared" si="85"/>
+        <v>421</v>
+      </c>
+      <c r="R247" s="7">
+        <f t="shared" si="86"/>
+        <v>1230</v>
+      </c>
+      <c r="S247" s="8">
+        <f t="shared" si="87"/>
+        <v>1756</v>
+      </c>
+      <c r="T247" s="8">
         <v>99.99</v>
       </c>
-      <c r="U247" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V247" s="34" t="s">
-        <v>1237</v>
+      <c r="U247" s="38" t="s">
+        <v>1574</v>
+      </c>
+      <c r="V247" s="38" t="s">
+        <v>1574</v>
       </c>
       <c r="W247" s="8"/>
       <c r="X247" s="8"/>
@@ -22713,57 +22946,62 @@
         <v>7</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>1530</v>
+        <v>1575</v>
       </c>
       <c r="G248" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H248" s="36" t="s">
+        <v>1576</v>
+      </c>
+      <c r="H248" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I248" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J248" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K248" s="34" t="s">
-        <v>1235</v>
+        <v>1577</v>
+      </c>
+      <c r="J248" s="41" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K248" s="41" t="s">
+        <v>1337</v>
       </c>
       <c r="L248" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M248" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N248" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O248" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P248" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q248" s="2">
-        <v>50</v>
-      </c>
-      <c r="R248" s="18">
-        <f>R247+9</f>
-        <v>1196</v>
-      </c>
-      <c r="S248" s="18">
-        <f>S247+10</f>
-        <v>1526</v>
-      </c>
-      <c r="T248" s="18">
+        <v>1567</v>
+      </c>
+      <c r="M248" s="4">
+        <f t="shared" si="91"/>
+        <v>1221000</v>
+      </c>
+      <c r="N248" s="4">
+        <f t="shared" si="92"/>
+        <v>1221000</v>
+      </c>
+      <c r="O248" s="4">
+        <f t="shared" si="93"/>
+        <v>1192750</v>
+      </c>
+      <c r="P248" s="4">
+        <f t="shared" si="94"/>
+        <v>1192750</v>
+      </c>
+      <c r="Q248" s="6">
+        <f t="shared" si="85"/>
+        <v>428</v>
+      </c>
+      <c r="R248" s="7">
+        <f t="shared" si="86"/>
+        <v>1248</v>
+      </c>
+      <c r="S248" s="8">
+        <f t="shared" si="87"/>
+        <v>1786</v>
+      </c>
+      <c r="T248" s="8">
         <v>99.99</v>
       </c>
-      <c r="U248" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V248" s="34" t="s">
-        <v>1237</v>
+      <c r="U248" s="38" t="s">
+        <v>1578</v>
+      </c>
+      <c r="V248" s="38" t="s">
+        <v>1578</v>
       </c>
       <c r="W248" s="8"/>
       <c r="X248" s="8"/>
@@ -22785,57 +23023,62 @@
         <v>7</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>1531</v>
+        <v>1579</v>
       </c>
       <c r="G249" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H249" s="36" t="s">
+        <v>1580</v>
+      </c>
+      <c r="H249" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I249" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J249" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K249" s="34" t="s">
-        <v>1235</v>
+        <v>1581</v>
+      </c>
+      <c r="J249" s="41" t="s">
+        <v>1582</v>
+      </c>
+      <c r="K249" s="41" t="s">
+        <v>1582</v>
       </c>
       <c r="L249" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M249" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N249" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O249" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P249" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q249" s="2">
-        <v>50</v>
-      </c>
-      <c r="R249" s="18">
-        <f>R248+9</f>
-        <v>1205</v>
-      </c>
-      <c r="S249" s="18">
-        <f>S248+10</f>
-        <v>1536</v>
-      </c>
-      <c r="T249" s="18">
+        <v>1576</v>
+      </c>
+      <c r="M249" s="4">
+        <f t="shared" si="91"/>
+        <v>1251000</v>
+      </c>
+      <c r="N249" s="4">
+        <f t="shared" si="92"/>
+        <v>1251000</v>
+      </c>
+      <c r="O249" s="4">
+        <f t="shared" si="93"/>
+        <v>1222750</v>
+      </c>
+      <c r="P249" s="4">
+        <f t="shared" si="94"/>
+        <v>1222750</v>
+      </c>
+      <c r="Q249" s="6">
+        <f t="shared" si="85"/>
+        <v>435</v>
+      </c>
+      <c r="R249" s="7">
+        <f t="shared" si="86"/>
+        <v>1266</v>
+      </c>
+      <c r="S249" s="8">
+        <f t="shared" si="87"/>
+        <v>1816</v>
+      </c>
+      <c r="T249" s="8">
         <v>99.99</v>
       </c>
-      <c r="U249" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V249" s="34" t="s">
-        <v>1237</v>
+      <c r="U249" s="38" t="s">
+        <v>1583</v>
+      </c>
+      <c r="V249" s="38" t="s">
+        <v>1583</v>
       </c>
       <c r="W249" s="8"/>
       <c r="X249" s="8"/>
@@ -22857,57 +23100,62 @@
         <v>7</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>1532</v>
+        <v>1584</v>
       </c>
       <c r="G250" s="39" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H250" s="36" t="s">
+        <v>1520</v>
+      </c>
+      <c r="H250" s="37" t="s">
         <v>1302</v>
       </c>
       <c r="I250" s="39" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J250" s="39" t="s">
-        <v>1234</v>
-      </c>
-      <c r="K250" s="34" t="s">
-        <v>1235</v>
+        <v>1585</v>
+      </c>
+      <c r="J250" s="41" t="s">
+        <v>1354</v>
+      </c>
+      <c r="K250" s="41" t="s">
+        <v>1354</v>
       </c>
       <c r="L250" s="39" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M250" s="2">
-        <v>43000</v>
-      </c>
-      <c r="N250" s="2">
-        <v>43000</v>
-      </c>
-      <c r="O250" s="2">
-        <v>22000</v>
-      </c>
-      <c r="P250" s="2">
-        <v>22000</v>
-      </c>
-      <c r="Q250" s="2">
-        <v>50</v>
-      </c>
-      <c r="R250" s="18">
-        <f>R249+9</f>
-        <v>1214</v>
-      </c>
-      <c r="S250" s="18">
-        <f>S249+10</f>
-        <v>1546</v>
-      </c>
-      <c r="T250" s="18">
+        <v>1520</v>
+      </c>
+      <c r="M250" s="4">
+        <f t="shared" si="91"/>
+        <v>1281000</v>
+      </c>
+      <c r="N250" s="4">
+        <f t="shared" si="92"/>
+        <v>1281000</v>
+      </c>
+      <c r="O250" s="4">
+        <f t="shared" si="93"/>
+        <v>1252750</v>
+      </c>
+      <c r="P250" s="4">
+        <f t="shared" si="94"/>
+        <v>1252750</v>
+      </c>
+      <c r="Q250" s="6">
+        <f t="shared" si="85"/>
+        <v>442</v>
+      </c>
+      <c r="R250" s="7">
+        <f t="shared" si="86"/>
+        <v>1284</v>
+      </c>
+      <c r="S250" s="8">
+        <f t="shared" si="87"/>
+        <v>1846</v>
+      </c>
+      <c r="T250" s="8">
         <v>99.99</v>
       </c>
-      <c r="U250" s="34" t="s">
-        <v>1237</v>
-      </c>
-      <c r="V250" s="34" t="s">
-        <v>1237</v>
+      <c r="U250" s="38" t="s">
+        <v>1586</v>
+      </c>
+      <c r="V250" s="38" t="s">
+        <v>1586</v>
       </c>
       <c r="W250" s="8"/>
       <c r="X250" s="8"/>
